--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -31280,14 +31280,14 @@
         <v>3561</v>
       </c>
       <c r="F191" s="8" t="str">
-        <f t="shared" ref="F191:F254" si="7">IF(A191="", "", "gift-codes.html?game=" &amp; A191)</f>
-        <v>gift-codes.html?game=手刀搶英雄</v>
+        <f>IF(A191="","", "https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/" &amp; A191 &amp; ".html")</f>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/手刀搶英雄.html</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>3560</v>
       </c>
       <c r="H191" s="10" t="str">
-        <f t="shared" ref="H191:H254" si="8">IF(A191="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A191)</f>
+        <f t="shared" ref="H191:H254" si="7">IF(A191="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A191)</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=手刀搶英雄</v>
       </c>
       <c r="I191" s="39" t="s">
@@ -31344,631 +31344,631 @@
     </row>
     <row r="192" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F192" s="8" t="str">
+        <f t="shared" ref="F191:F254" si="8">IF(A192="", "", "gift-codes.html?game=" &amp; A192)</f>
+        <v/>
+      </c>
+      <c r="H192" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H192" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="193" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F193" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H193" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H193" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="194" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F194" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H194" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H194" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="195" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F195" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H195" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H195" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="196" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F196" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H196" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H196" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="197" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F197" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H197" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H197" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="198" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F198" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H198" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H198" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="199" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F199" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H199" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H199" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="200" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F200" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H200" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H200" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="201" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F201" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H201" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H201" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="202" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F202" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H202" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H202" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="203" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F203" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H203" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H203" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="204" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F204" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H204" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H204" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="205" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F205" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H205" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H205" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="206" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F206" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H206" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H206" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="207" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F207" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H207" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H207" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="208" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F208" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H208" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H208" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="209" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F209" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H209" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H209" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="210" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F210" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H210" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H210" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="211" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F211" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H211" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H211" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="212" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F212" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H212" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H212" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="213" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F213" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H213" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H213" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="214" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F214" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H214" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H214" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="215" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F215" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H215" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H215" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="216" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F216" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H216" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H216" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="217" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F217" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H217" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H217" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="218" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F218" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H218" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H218" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="219" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F219" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H219" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H219" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="220" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F220" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H220" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H220" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="221" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F221" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H221" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H221" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="222" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F222" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H222" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H222" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="223" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F223" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H223" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H223" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="224" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F224" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H224" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H224" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="225" spans="6:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F225" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H225" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H225" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="226" spans="6:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F226" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H226" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H226" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="227" spans="6:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F227" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H227" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H227" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="228" spans="6:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F228" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H228" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H228" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="229" spans="6:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F229" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H229" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H229" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="230" spans="6:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F230" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H230" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H230" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="231" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F231" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H231" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H231" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="232" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F232" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H232" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H232" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="233" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F233" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H233" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H233" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="234" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F234" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H234" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H234" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="235" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F235" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H235" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H235" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="236" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F236" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H236" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H236" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="237" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F237" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H237" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H237" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="238" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F238" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H238" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H238" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="239" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F239" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H239" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H239" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="240" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F240" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H240" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H240" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="241" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F241" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H241" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H241" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="242" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F242" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H242" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H242" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="243" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F243" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H243" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H243" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="244" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F244" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H244" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H244" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="245" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F245" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H245" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H245" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="246" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F246" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H246" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H246" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="247" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F247" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H247" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H247" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="248" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F248" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H248" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H248" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="249" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F249" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H249" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H249" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="250" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F250" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H250" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H250" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="251" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F251" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H251" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H251" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="252" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F252" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H252" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H252" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="253" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F253" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H253" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H253" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="254" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F254" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H254" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H254" s="10" t="str">
-        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5333" uniqueCount="3579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5426" uniqueCount="3637">
   <si>
     <t>Facebook</t>
   </si>
@@ -14421,12 +14421,392 @@
     <t>高級英雄召喚券*10</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>破壞突擊隊</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《荒野亂鬥》是一款由</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Supercell </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>開發的快節奏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3v3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>多人對戰與大逃殺手機遊戲。其多樣化的英雄角色、豐富的遊戲模式和三分鐘一局的緊湊戰鬥，使其風靡全球。玩家可以與朋友組隊，或單槍匹馬在荒野中對決，解鎖和升級數十位擁有獨特技能的英雄。為了讓您的英雄更快成長，隨時關注官方發布的最新禮包碼，是獲取免費寶石和金幣的好方法。許多玩家也會尋找安全的代儲值管道，以優惠的價格購買遊戲內商品，迅速提升戰力，在各種模式中稱霸全場。無論是寶石爭奪戰、亂鬥足球還是賞金獵人模式，掌握英雄技巧並善用資源，就是通往勝利的關鍵。立即加入亂鬥，體驗這款刺激又有深度的競技手遊！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《遺忘之劍》是一款帶有經典像素風格的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> MMORPG </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>手遊，引領玩家重溫最初的冒險感動。遊戲打造了一個宏大的奇幻世界，玩家將扮演勇敢的冒險者，探索未知的地圖、挑戰強大的怪物，並與其他玩家組隊共鬥。遊戲核心特色在於其自由的職業養成與裝備打造系統，讓每位玩家都能走出自己的道路。想要在冒險旅程中快人一步，千萬別錯過官方社群發佈的限量禮包碼，這些序號能兌換稀有材料與實用道具。對於追求頂級裝備的玩家，選擇可靠的代儲值服務，能更有效率地獲取強化資源，打造屬於你的傳說神兵。無論你是喜愛獨自探索的孤狼，還是熱衷於公會團戰的領袖，都能在《遺忘之劍》的世界中找到屬於自己的樂趣。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《破壞突擊隊》是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Supercell </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>旗下最新力作，集結了《部落衝突》、《荒野亂鬥》等經典遊戲的超人氣角色，打造出獨一無二的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>人組隊對戰冒險。在每場比賽中，玩家將從單一角色開始，透過擊敗怪物和對手來收集金幣，擴大自己的突擊隊伍。遊戲的策略核心在於如何搭配不同角色的技能，組成最強大的戰隊。為了讓你的隊伍迅速成形，記得隨時搜尋最新的禮包碼，兌換豐富的開局獎勵。同時，透過安全的代儲值服務獲取寶石，能讓你更快解鎖強力角色和購買實用道具，在戰場上取得巨大優勢。遊戲融合了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Roguelike </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>隨機元素與大亂鬥的刺激感，每一局都是全新的體驗。快來召集你的夢幻隊伍，在《破壞突擊隊》中展開一場歡樂又混亂的冒險吧！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://supercell.com/en/games/brawlstars/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/brawlstars</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E8%8D%92%E9%87%8E%E4%BA%82%E9%AC%A5/id1229016807</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.supercell.brawlstars&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.supercell.squad&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E9%81%BA%E5%BF%98%E4%B9%8B%E5%8A%8D/id6744879430</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tw.ncsoft.com/lostsword</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/LostSwordOfficial.TW/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.nctaiwan.lsnct&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/SquadBustersGame/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://squadbusters.supercell.com/cn/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E7%A0%B4%E5%A3%9E%E7%AA%81%E6%93%8A%E9%9A%8A/id1668983788</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遺忘之劍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>荒野亂鬥</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>右下角齒輪設定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>左邊書籤的帳號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>右下方點酷碰登陸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GOBLIN0820STRONG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MERLIN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AUGLOSTSWORD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LSTHX200</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SUMMERGIFT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*1000+高級角色10 次召喚券*1(國際服)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*2000+
+高級角色 10次召喚券*2+高級寵物10 次召喚券*2+金幣*200萬(國際服)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*1000+高級寵物10 次召喚券*1(國際服)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*1000+五星角色召喚券*1(台服)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄禮物箱*1+盔甲強化咒文書*10(台服)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000寶石</t>
+  </si>
+  <si>
+    <t>950寶石</t>
+  </si>
+  <si>
+    <t>360寶石</t>
+  </si>
+  <si>
+    <t>170寶石</t>
+  </si>
+  <si>
+    <t>80寶石</t>
+  </si>
+  <si>
+    <t>8000里昂</t>
+  </si>
+  <si>
+    <t>4000里昂</t>
+  </si>
+  <si>
+    <t>2400里昂</t>
+  </si>
+  <si>
+    <t>800里昂</t>
+  </si>
+  <si>
+    <t>400里昂</t>
+  </si>
+  <si>
+    <t>240里昂</t>
+  </si>
+  <si>
+    <t>雙月票</t>
+  </si>
+  <si>
+    <t>月兔茶屋：悠閒之旅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E6%9C%88%E5%85%94%E8%8C%B6%E5%B1%8B-%E6%82%A0%E9%96%92%E4%B9%8B%E6%97%85-tsuki-tea-house/id6505020147</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.hyperbeard.tsukiteahouse&amp;hl=zh_HK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://hyperbeard.com/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/HyperBeardGames/</t>
+  </si>
+  <si>
+    <t>50000金蘿蔔</t>
+  </si>
+  <si>
+    <t>25000金蘿蔔</t>
+  </si>
+  <si>
+    <t>5000金蘿蔔</t>
+  </si>
+  <si>
+    <t>2500金蘿蔔</t>
+  </si>
+  <si>
+    <t>1250金蘿蔔</t>
+  </si>
+  <si>
+    <t>500金蘿蔔</t>
+  </si>
+  <si>
+    <t>新手包</t>
+  </si>
+  <si>
+    <t>月亮俱樂部</t>
+  </si>
+  <si>
+    <t>終極廣告卡</t>
+  </si>
+  <si>
+    <r>
+      <t>歡迎來到《月兔茶屋：悠閒之旅》，這是一款迷人又溫馨的模擬經營遊戲，讓您與可愛的月兔Tsuki在靜謐的鄉村中，共同打造夢想中的茶館。在這款療癒的放置型遊戲中，您的任務是協助Tsuki招待各式各樣的動物顧客，從沖泡完美的茶品到準備可口的小吃，每個細節都充滿了溫暖與人情味。您可以透過解鎖新食譜、擴展菜單、升級裝潢和聘請員工來逐步提升茶館的規模與吸引力。遊戲擁有輕鬆的步調與可愛的視覺風格，讓玩家能徹底放鬆，享受簡單生活的美好。為了讓您的茶館成長更迅速，隨時關注官方發布的最新</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，是獲得免費資源的好方法；若想加快遊戲進程，也可以考慮適度</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>來購買獨特裝飾，打造最獨一無二的溫馨茶屋！快來與Tsuki一起，展開這段美好的悠閒旅程吧！</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -14545,6 +14925,12 @@
       <name val="細明體"/>
       <family val="3"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -14763,7 +15149,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -14984,6 +15370,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -30853,61 +31242,61 @@
         <v>12</v>
       </c>
       <c r="K185" s="4">
-        <v>2539</v>
+        <v>2415</v>
       </c>
       <c r="L185" s="3" t="s">
         <v>13</v>
       </c>
       <c r="M185" s="4">
-        <v>1323</v>
+        <v>1225</v>
       </c>
       <c r="N185" s="3" t="s">
         <v>24</v>
       </c>
       <c r="O185" s="4">
-        <v>775</v>
+        <v>735</v>
       </c>
       <c r="P185" s="3" t="s">
         <v>15</v>
       </c>
       <c r="Q185" s="4">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="R185" s="3" t="s">
         <v>16</v>
       </c>
       <c r="S185" s="4">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="T185" s="3" t="s">
         <v>7</v>
       </c>
       <c r="U185" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V185" s="3" t="s">
         <v>107</v>
       </c>
       <c r="W185" s="4">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="X185" s="3" t="s">
         <v>1437</v>
       </c>
       <c r="Y185" s="4">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="Z185" s="3" t="s">
         <v>1657</v>
       </c>
       <c r="AA185" s="4">
-        <v>1166</v>
+        <v>1127</v>
       </c>
       <c r="AB185" s="3" t="s">
         <v>1658</v>
       </c>
       <c r="AC185" s="4">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="186" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -31342,47 +31731,305 @@
         <v>232</v>
       </c>
     </row>
-    <row r="192" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="21" t="s">
+        <v>3596</v>
+      </c>
+      <c r="C192" s="24" t="s">
+        <v>3584</v>
+      </c>
+      <c r="D192" s="23" t="s">
+        <v>3583</v>
+      </c>
+      <c r="E192" s="23" t="s">
+        <v>3585</v>
+      </c>
       <c r="F192" s="8" t="str">
         <f t="shared" ref="F191:F254" si="8">IF(A192="", "", "gift-codes.html?game=" &amp; A192)</f>
-        <v/>
+        <v>gift-codes.html?game=荒野亂鬥</v>
+      </c>
+      <c r="G192" s="23" t="s">
+        <v>3586</v>
       </c>
       <c r="H192" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=荒野亂鬥</v>
+      </c>
+      <c r="I192" s="39" t="s">
+        <v>3580</v>
+      </c>
+      <c r="J192" s="3" t="s">
+        <v>3610</v>
+      </c>
+      <c r="K192" s="4">
+        <v>2415</v>
+      </c>
+      <c r="L192" s="3" t="s">
+        <v>3611</v>
+      </c>
+      <c r="M192" s="4">
+        <v>1225</v>
+      </c>
+      <c r="N192" s="3" t="s">
+        <v>3612</v>
+      </c>
+      <c r="O192" s="4">
+        <v>497</v>
+      </c>
+      <c r="P192" s="3" t="s">
+        <v>3613</v>
+      </c>
+      <c r="Q192" s="4">
+        <v>248</v>
+      </c>
+      <c r="R192" s="3" t="s">
+        <v>3614</v>
+      </c>
+      <c r="S192" s="4">
+        <v>132</v>
+      </c>
+      <c r="T192" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U192" s="4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="193" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="21" t="s">
+        <v>3595</v>
+      </c>
+      <c r="C193" s="24" t="s">
+        <v>3590</v>
+      </c>
+      <c r="D193" s="23" t="s">
+        <v>3589</v>
+      </c>
+      <c r="E193" s="23" t="s">
+        <v>3588</v>
+      </c>
       <c r="F193" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=遺忘之劍</v>
+      </c>
+      <c r="G193" s="23" t="s">
+        <v>3591</v>
       </c>
       <c r="H193" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=遺忘之劍</v>
+      </c>
+      <c r="I193" s="39" t="s">
+        <v>3581</v>
+      </c>
+      <c r="J193" s="3" t="s">
+        <v>3615</v>
+      </c>
+      <c r="K193" s="4">
+        <v>1890</v>
+      </c>
+      <c r="L193" s="3" t="s">
+        <v>3616</v>
+      </c>
+      <c r="M193" s="4">
+        <v>945</v>
+      </c>
+      <c r="N193" s="3" t="s">
+        <v>3617</v>
+      </c>
+      <c r="O193" s="4">
+        <v>575</v>
+      </c>
+      <c r="P193" s="3" t="s">
+        <v>3618</v>
+      </c>
+      <c r="Q193" s="4">
+        <v>192</v>
+      </c>
+      <c r="R193" s="3" t="s">
+        <v>3619</v>
+      </c>
+      <c r="S193" s="4">
+        <v>102</v>
+      </c>
+      <c r="T193" s="3" t="s">
+        <v>3620</v>
+      </c>
+      <c r="U193" s="4">
+        <v>64</v>
+      </c>
+      <c r="V193" s="3" t="s">
+        <v>3621</v>
+      </c>
+      <c r="W193" s="4">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="83" t="s">
+        <v>3579</v>
+      </c>
+      <c r="C194" s="24" t="s">
+        <v>3592</v>
+      </c>
+      <c r="D194" s="23" t="s">
+        <v>3593</v>
+      </c>
+      <c r="E194" s="23" t="s">
+        <v>3594</v>
+      </c>
       <c r="F194" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=破壞突擊隊</v>
+      </c>
+      <c r="G194" s="23" t="s">
+        <v>3587</v>
       </c>
       <c r="H194" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=破壞突擊隊</v>
+      </c>
+      <c r="I194" s="39" t="s">
+        <v>3582</v>
+      </c>
+      <c r="J194" s="3" t="s">
+        <v>3627</v>
+      </c>
+      <c r="K194" s="4">
+        <v>622</v>
+      </c>
+      <c r="L194" s="3" t="s">
+        <v>3628</v>
+      </c>
+      <c r="M194" s="4">
+        <v>312</v>
+      </c>
+      <c r="N194" s="3" t="s">
+        <v>3629</v>
+      </c>
+      <c r="O194" s="4">
+        <v>176</v>
+      </c>
+      <c r="P194" s="3" t="s">
+        <v>3630</v>
+      </c>
+      <c r="Q194" s="4">
+        <v>102</v>
+      </c>
+      <c r="R194" s="3" t="s">
+        <v>3631</v>
+      </c>
+      <c r="S194" s="4">
+        <v>51</v>
+      </c>
+      <c r="T194" s="3" t="s">
+        <v>3632</v>
+      </c>
+      <c r="U194" s="4">
+        <v>26</v>
+      </c>
+      <c r="V194" s="3" t="s">
+        <v>3633</v>
+      </c>
+      <c r="W194" s="4">
+        <v>391</v>
+      </c>
+      <c r="X194" s="3" t="s">
+        <v>3634</v>
+      </c>
+      <c r="Y194" s="4">
+        <v>391</v>
+      </c>
+      <c r="Z194" s="3" t="s">
+        <v>3635</v>
+      </c>
+      <c r="AA194" s="4">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="195" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="22" t="s">
+        <v>3622</v>
+      </c>
+      <c r="C195" s="24" t="s">
+        <v>3626</v>
+      </c>
+      <c r="D195" s="23" t="s">
+        <v>3625</v>
+      </c>
+      <c r="E195" s="23" t="s">
+        <v>3623</v>
+      </c>
       <c r="F195" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=月兔茶屋：悠閒之旅</v>
+      </c>
+      <c r="G195" s="23" t="s">
+        <v>3624</v>
       </c>
       <c r="H195" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=月兔茶屋：悠閒之旅</v>
+      </c>
+      <c r="I195" t="s">
+        <v>3636</v>
+      </c>
+      <c r="J195" s="3" t="s">
+        <v>3627</v>
+      </c>
+      <c r="K195" s="4">
+        <v>622</v>
+      </c>
+      <c r="L195" s="3" t="s">
+        <v>3628</v>
+      </c>
+      <c r="M195" s="4">
+        <v>312</v>
+      </c>
+      <c r="N195" s="3" t="s">
+        <v>3629</v>
+      </c>
+      <c r="O195" s="4">
+        <v>176</v>
+      </c>
+      <c r="P195" s="3" t="s">
+        <v>3630</v>
+      </c>
+      <c r="Q195" s="4">
+        <v>102</v>
+      </c>
+      <c r="R195" s="3" t="s">
+        <v>3631</v>
+      </c>
+      <c r="S195" s="4">
+        <v>51</v>
+      </c>
+      <c r="T195" s="3" t="s">
+        <v>3632</v>
+      </c>
+      <c r="U195" s="4">
+        <v>26</v>
+      </c>
+      <c r="V195" s="3" t="s">
+        <v>3633</v>
+      </c>
+      <c r="W195" s="4">
+        <v>391</v>
+      </c>
+      <c r="X195" s="3" t="s">
+        <v>3634</v>
+      </c>
+      <c r="Y195" s="4">
+        <v>391</v>
+      </c>
+      <c r="Z195" s="3" t="s">
+        <v>3635</v>
+      </c>
+      <c r="AA195" s="4">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="196" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F196" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31392,7 +32039,7 @@
         <v/>
       </c>
     </row>
-    <row r="197" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F197" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31402,7 +32049,7 @@
         <v/>
       </c>
     </row>
-    <row r="198" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F198" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31412,7 +32059,7 @@
         <v/>
       </c>
     </row>
-    <row r="199" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F199" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31422,7 +32069,7 @@
         <v/>
       </c>
     </row>
-    <row r="200" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F200" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31432,7 +32079,7 @@
         <v/>
       </c>
     </row>
-    <row r="201" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F201" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31442,7 +32089,7 @@
         <v/>
       </c>
     </row>
-    <row r="202" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F202" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31452,7 +32099,7 @@
         <v/>
       </c>
     </row>
-    <row r="203" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F203" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31462,7 +32109,7 @@
         <v/>
       </c>
     </row>
-    <row r="204" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F204" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31472,7 +32119,7 @@
         <v/>
       </c>
     </row>
-    <row r="205" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F205" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31482,7 +32129,7 @@
         <v/>
       </c>
     </row>
-    <row r="206" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F206" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31492,7 +32139,7 @@
         <v/>
       </c>
     </row>
-    <row r="207" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F207" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31502,7 +32149,7 @@
         <v/>
       </c>
     </row>
-    <row r="208" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F208" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -35581,9 +36228,23 @@
     <hyperlink ref="E190" r:id="rId38"/>
     <hyperlink ref="D191" r:id="rId39"/>
     <hyperlink ref="C191" r:id="rId40"/>
+    <hyperlink ref="D192" r:id="rId41"/>
+    <hyperlink ref="C192" r:id="rId42"/>
+    <hyperlink ref="E192" r:id="rId43"/>
+    <hyperlink ref="G192" r:id="rId44"/>
+    <hyperlink ref="G194" r:id="rId45"/>
+    <hyperlink ref="E193" r:id="rId46"/>
+    <hyperlink ref="D193" r:id="rId47"/>
+    <hyperlink ref="C193" r:id="rId48"/>
+    <hyperlink ref="G193" r:id="rId49"/>
+    <hyperlink ref="C194" r:id="rId50"/>
+    <hyperlink ref="D194" r:id="rId51"/>
+    <hyperlink ref="E194" r:id="rId52"/>
+    <hyperlink ref="E195" r:id="rId53"/>
+    <hyperlink ref="G195" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId41"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId55"/>
 </worksheet>
 </file>
 
@@ -47689,60 +48350,190 @@
     <row r="192" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="49" t="str">
         <f>IF(games!A192="", "", games!A192)</f>
-        <v/>
+        <v>荒野亂鬥</v>
       </c>
       <c r="C192" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/荒野亂鬥-禮包碼.jpg</v>
       </c>
       <c r="D192" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>https://www.ssbuy.tw/gift-codes.html?game=荒野亂鬥</v>
+      </c>
+      <c r="E192" s="50" t="str">
+        <f>games!I192</f>
+        <v>《荒野亂鬥》是一款由 Supercell 開發的快節奏 3v3 多人對戰與大逃殺手機遊戲。其多樣化的英雄角色、豐富的遊戲模式和三分鐘一局的緊湊戰鬥，使其風靡全球。玩家可以與朋友組隊，或單槍匹馬在荒野中對決，解鎖和升級數十位擁有獨特技能的英雄。為了讓您的英雄更快成長，隨時關注官方發布的最新禮包碼，是獲取免費寶石和金幣的好方法。許多玩家也會尋找安全的代儲值管道，以優惠的價格購買遊戲內商品，迅速提升戰力，在各種模式中稱霸全場。無論是寶石爭奪戰、亂鬥足球還是賞金獵人模式，掌握英雄技巧並善用資源，就是通往勝利的關鍵。立即加入亂鬥，體驗這款刺激又有深度的競技手遊！</v>
+      </c>
+      <c r="F192" s="53" t="s">
+        <v>3519</v>
+      </c>
+      <c r="G192" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="H192" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="I192" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K192" s="53" t="s">
+        <v>3519</v>
+      </c>
+      <c r="L192" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M192" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="N192" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="193" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="49" t="str">
         <f>IF(games!A193="", "", games!A193)</f>
-        <v/>
+        <v>遺忘之劍</v>
       </c>
       <c r="C193" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/遺忘之劍-禮包碼.jpg</v>
       </c>
       <c r="D193" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>https://www.ssbuy.tw/gift-codes.html?game=遺忘之劍</v>
+      </c>
+      <c r="E193" s="50" t="str">
+        <f>games!I193</f>
+        <v>《遺忘之劍》是一款帶有經典像素風格的 MMORPG 手遊，引領玩家重溫最初的冒險感動。遊戲打造了一個宏大的奇幻世界，玩家將扮演勇敢的冒險者，探索未知的地圖、挑戰強大的怪物，並與其他玩家組隊共鬥。遊戲核心特色在於其自由的職業養成與裝備打造系統，讓每位玩家都能走出自己的道路。想要在冒險旅程中快人一步，千萬別錯過官方社群發佈的限量禮包碼，這些序號能兌換稀有材料與實用道具。對於追求頂級裝備的玩家，選擇可靠的代儲值服務，能更有效率地獲取強化資源，打造屬於你的傳說神兵。無論你是喜愛獨自探索的孤狼，還是熱衷於公會團戰的領袖，都能在《遺忘之劍》的世界中找到屬於自己的樂趣。</v>
+      </c>
+      <c r="F193" s="70" t="s">
+        <v>3597</v>
+      </c>
+      <c r="G193" s="49" t="s">
+        <v>3598</v>
+      </c>
+      <c r="H193" s="49" t="s">
+        <v>3599</v>
+      </c>
+      <c r="I193" s="49" t="s">
+        <v>2651</v>
+      </c>
+      <c r="K193" s="53" t="s">
+        <v>3600</v>
+      </c>
+      <c r="L193" s="49" t="s">
+        <v>3608</v>
+      </c>
+      <c r="M193" s="54" t="s">
+        <v>3601</v>
+      </c>
+      <c r="N193" s="49" t="s">
+        <v>3609</v>
+      </c>
+      <c r="O193" s="54" t="s">
+        <v>3602</v>
+      </c>
+      <c r="P193" s="61" t="s">
+        <v>3605</v>
+      </c>
+      <c r="Q193" s="54" t="s">
+        <v>3603</v>
+      </c>
+      <c r="R193" s="61" t="s">
+        <v>3606</v>
+      </c>
+      <c r="S193" s="54" t="s">
+        <v>3604</v>
+      </c>
+      <c r="T193" s="61" t="s">
+        <v>3607</v>
+      </c>
+    </row>
+    <row r="194" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="49" t="str">
         <f>IF(games!A194="", "", games!A194)</f>
-        <v/>
+        <v>破壞突擊隊</v>
       </c>
       <c r="C194" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/破壞突擊隊-禮包碼.jpg</v>
       </c>
       <c r="D194" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>https://www.ssbuy.tw/gift-codes.html?game=破壞突擊隊</v>
+      </c>
+      <c r="E194" s="50" t="str">
+        <f>IF(games!I194&lt;&gt;"", games!I194, "")</f>
+        <v>《破壞突擊隊》是 Supercell 旗下最新力作，集結了《部落衝突》、《荒野亂鬥》等經典遊戲的超人氣角色，打造出獨一無二的 10 人組隊對戰冒險。在每場比賽中，玩家將從單一角色開始，透過擊敗怪物和對手來收集金幣，擴大自己的突擊隊伍。遊戲的策略核心在於如何搭配不同角色的技能，組成最強大的戰隊。為了讓你的隊伍迅速成形，記得隨時搜尋最新的禮包碼，兌換豐富的開局獎勵。同時，透過安全的代儲值服務獲取寶石，能讓你更快解鎖強力角色和購買實用道具，在戰場上取得巨大優勢。遊戲融合了 Roguelike 隨機元素與大亂鬥的刺激感，每一局都是全新的體驗。快來召集你的夢幻隊伍，在《破壞突擊隊》中展開一場歡樂又混亂的冒險吧！</v>
+      </c>
+      <c r="F194" s="53" t="s">
+        <v>3519</v>
+      </c>
+      <c r="G194" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="H194" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="I194" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K194" s="53" t="s">
+        <v>3519</v>
+      </c>
+      <c r="L194" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M194" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="N194" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="195" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="49" t="str">
         <f>IF(games!A195="", "", games!A195)</f>
-        <v/>
+        <v>月兔茶屋：悠閒之旅</v>
       </c>
       <c r="C195" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/月兔茶屋：悠閒之旅-禮包碼.jpg</v>
       </c>
       <c r="D195" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>https://www.ssbuy.tw/gift-codes.html?game=月兔茶屋：悠閒之旅</v>
+      </c>
+      <c r="E195" s="50" t="str">
+        <f>IF(games!I195&lt;&gt;"", games!I195, "")</f>
+        <v>歡迎來到《月兔茶屋：悠閒之旅》，這是一款迷人又溫馨的模擬經營遊戲，讓您與可愛的月兔Tsuki在靜謐的鄉村中，共同打造夢想中的茶館。在這款療癒的放置型遊戲中，您的任務是協助Tsuki招待各式各樣的動物顧客，從沖泡完美的茶品到準備可口的小吃，每個細節都充滿了溫暖與人情味。您可以透過解鎖新食譜、擴展菜單、升級裝潢和聘請員工來逐步提升茶館的規模與吸引力。遊戲擁有輕鬆的步調與可愛的視覺風格，讓玩家能徹底放鬆，享受簡單生活的美好。為了讓您的茶館成長更迅速，隨時關注官方發布的最新禮包碼，是獲得免費資源的好方法；若想加快遊戲進程，也可以考慮適度儲值來購買獨特裝飾，打造最獨一無二的溫馨茶屋！快來與Tsuki一起，展開這段美好的悠閒旅程吧！</v>
+      </c>
+      <c r="F195" s="53" t="s">
+        <v>3519</v>
+      </c>
+      <c r="G195" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="H195" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="I195" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K195" s="53" t="s">
+        <v>3519</v>
+      </c>
+      <c r="L195" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M195" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="N195" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="196" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="49" t="str">
         <f>IF(games!A196="", "", games!A196)</f>
         <v/>
@@ -47755,8 +48546,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="197" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E196" s="50" t="str">
+        <f>IF(games!I196&lt;&gt;"", games!I196, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="49" t="str">
         <f>IF(games!A197="", "", games!A197)</f>
         <v/>
@@ -47769,8 +48564,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="198" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E197" s="50" t="str">
+        <f>IF(games!I197&lt;&gt;"", games!I197, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="49" t="str">
         <f>IF(games!A198="", "", games!A198)</f>
         <v/>
@@ -47783,8 +48582,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="199" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E198" s="50" t="str">
+        <f>IF(games!I198&lt;&gt;"", games!I198, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="49" t="str">
         <f>IF(games!A199="", "", games!A199)</f>
         <v/>
@@ -47797,8 +48600,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="200" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E199" s="50" t="str">
+        <f>IF(games!I199&lt;&gt;"", games!I199, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="49" t="str">
         <f>IF(games!A200="", "", games!A200)</f>
         <v/>
@@ -47811,8 +48618,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="201" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E200" s="50" t="str">
+        <f>IF(games!I200&lt;&gt;"", games!I200, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="49" t="str">
         <f>IF(games!A201="", "", games!A201)</f>
         <v/>
@@ -47826,7 +48637,7 @@
         <v/>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="49" t="str">
         <f>IF(games!A202="", "", games!A202)</f>
         <v/>
@@ -47840,7 +48651,7 @@
         <v/>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="49" t="str">
         <f>IF(games!A203="", "", games!A203)</f>
         <v/>
@@ -47854,7 +48665,7 @@
         <v/>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="49" t="str">
         <f>IF(games!A204="", "", games!A204)</f>
         <v/>
@@ -47868,7 +48679,7 @@
         <v/>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="49" t="str">
         <f>IF(games!A205="", "", games!A205)</f>
         <v/>
@@ -47882,7 +48693,7 @@
         <v/>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="49" t="str">
         <f>IF(games!A206="", "", games!A206)</f>
         <v/>
@@ -47896,7 +48707,7 @@
         <v/>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="49" t="str">
         <f>IF(games!A207="", "", games!A207)</f>
         <v/>
@@ -47910,7 +48721,7 @@
         <v/>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="49" t="str">
         <f>IF(games!A208="", "", games!A208)</f>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -14425,6 +14425,196 @@
     <t>破壞突擊隊</t>
   </si>
   <si>
+    <t>https://supercell.com/en/games/brawlstars/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/brawlstars</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E8%8D%92%E9%87%8E%E4%BA%82%E9%AC%A5/id1229016807</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.supercell.brawlstars&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.supercell.squad&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E9%81%BA%E5%BF%98%E4%B9%8B%E5%8A%8D/id6744879430</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tw.ncsoft.com/lostsword</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/LostSwordOfficial.TW/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.nctaiwan.lsnct&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/SquadBustersGame/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://squadbusters.supercell.com/cn/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E7%A0%B4%E5%A3%9E%E7%AA%81%E6%93%8A%E9%9A%8A/id1668983788</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遺忘之劍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>荒野亂鬥</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>右下角齒輪設定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>左邊書籤的帳號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>右下方點酷碰登陸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GOBLIN0820STRONG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MERLIN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AUGLOSTSWORD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LSTHX200</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SUMMERGIFT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*1000+高級角色10 次召喚券*1(國際服)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*2000+
+高級角色 10次召喚券*2+高級寵物10 次召喚券*2+金幣*200萬(國際服)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*1000+高級寵物10 次召喚券*1(國際服)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*1000+五星角色召喚券*1(台服)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄禮物箱*1+盔甲強化咒文書*10(台服)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000寶石</t>
+  </si>
+  <si>
+    <t>950寶石</t>
+  </si>
+  <si>
+    <t>360寶石</t>
+  </si>
+  <si>
+    <t>170寶石</t>
+  </si>
+  <si>
+    <t>80寶石</t>
+  </si>
+  <si>
+    <t>8000里昂</t>
+  </si>
+  <si>
+    <t>4000里昂</t>
+  </si>
+  <si>
+    <t>2400里昂</t>
+  </si>
+  <si>
+    <t>800里昂</t>
+  </si>
+  <si>
+    <t>400里昂</t>
+  </si>
+  <si>
+    <t>240里昂</t>
+  </si>
+  <si>
+    <t>雙月票</t>
+  </si>
+  <si>
+    <t>月兔茶屋：悠閒之旅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E6%9C%88%E5%85%94%E8%8C%B6%E5%B1%8B-%E6%82%A0%E9%96%92%E4%B9%8B%E6%97%85-tsuki-tea-house/id6505020147</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.hyperbeard.tsukiteahouse&amp;hl=zh_HK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://hyperbeard.com/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/HyperBeardGames/</t>
+  </si>
+  <si>
+    <t>50000金蘿蔔</t>
+  </si>
+  <si>
+    <t>25000金蘿蔔</t>
+  </si>
+  <si>
+    <t>5000金蘿蔔</t>
+  </si>
+  <si>
+    <t>2500金蘿蔔</t>
+  </si>
+  <si>
+    <t>1250金蘿蔔</t>
+  </si>
+  <si>
+    <t>500金蘿蔔</t>
+  </si>
+  <si>
+    <t>新手包</t>
+  </si>
+  <si>
+    <t>月亮俱樂部</t>
+  </si>
+  <si>
+    <t>終極廣告卡</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -14432,7 +14622,7 @@
         <family val="3"/>
         <charset val="136"/>
       </rPr>
-      <t>《荒野亂鬥》是一款由</t>
+      <t>《荒野亂鬥》是一款快節奏</t>
     </r>
     <r>
       <rPr>
@@ -14440,7 +14630,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Supercell </t>
+      <t>3v3</t>
     </r>
     <r>
       <rPr>
@@ -14449,312 +14639,13 @@
         <family val="3"/>
         <charset val="136"/>
       </rPr>
-      <t>開發的快節奏</t>
+      <t>多人對戰與大逃殺手遊。其多樣化的英雄、豐富模式與三分鐘緊湊戰鬥風靡全球。玩家可組隊或單獨對決，解鎖升級各具特色的英雄。想讓英雄更快成長，就別錯過官方發布的最新禮包碼，是獲取免費資源的好方法。許多玩家也會尋找安全的代儲值管道，以優惠價格購買商品提升戰力，在各種模式中稱霸全場。掌握英雄技巧並善用資源，就是通往勝利的關鍵。立即加入，體驗刺激的競技對決！</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3v3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>多人對戰與大逃殺手機遊戲。其多樣化的英雄角色、豐富的遊戲模式和三分鐘一局的緊湊戰鬥，使其風靡全球。玩家可以與朋友組隊，或單槍匹馬在荒野中對決，解鎖和升級數十位擁有獨特技能的英雄。為了讓您的英雄更快成長，隨時關注官方發布的最新禮包碼，是獲取免費寶石和金幣的好方法。許多玩家也會尋找安全的代儲值管道，以優惠的價格購買遊戲內商品，迅速提升戰力，在各種模式中稱霸全場。無論是寶石爭奪戰、亂鬥足球還是賞金獵人模式，掌握英雄技巧並善用資源，就是通往勝利的關鍵。立即加入亂鬥，體驗這款刺激又有深度的競技手遊！</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>《遺忘之劍》是一款帶有經典像素風格的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> MMORPG </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>手遊，引領玩家重溫最初的冒險感動。遊戲打造了一個宏大的奇幻世界，玩家將扮演勇敢的冒險者，探索未知的地圖、挑戰強大的怪物，並與其他玩家組隊共鬥。遊戲核心特色在於其自由的職業養成與裝備打造系統，讓每位玩家都能走出自己的道路。想要在冒險旅程中快人一步，千萬別錯過官方社群發佈的限量禮包碼，這些序號能兌換稀有材料與實用道具。對於追求頂級裝備的玩家，選擇可靠的代儲值服務，能更有效率地獲取強化資源，打造屬於你的傳說神兵。無論你是喜愛獨自探索的孤狼，還是熱衷於公會團戰的領袖，都能在《遺忘之劍》的世界中找到屬於自己的樂趣。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>《破壞突擊隊》是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Supercell </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>旗下最新力作，集結了《部落衝突》、《荒野亂鬥》等經典遊戲的超人氣角色，打造出獨一無二的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>人組隊對戰冒險。在每場比賽中，玩家將從單一角色開始，透過擊敗怪物和對手來收集金幣，擴大自己的突擊隊伍。遊戲的策略核心在於如何搭配不同角色的技能，組成最強大的戰隊。為了讓你的隊伍迅速成形，記得隨時搜尋最新的禮包碼，兌換豐富的開局獎勵。同時，透過安全的代儲值服務獲取寶石，能讓你更快解鎖強力角色和購買實用道具，在戰場上取得巨大優勢。遊戲融合了</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Roguelike </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>隨機元素與大亂鬥的刺激感，每一局都是全新的體驗。快來召集你的夢幻隊伍，在《破壞突擊隊》中展開一場歡樂又混亂的冒險吧！</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://supercell.com/en/games/brawlstars/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.facebook.com/brawlstars</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://apps.apple.com/tw/app/%E8%8D%92%E9%87%8E%E4%BA%82%E9%AC%A5/id1229016807</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://play.google.com/store/apps/details?id=com.supercell.brawlstars&amp;hl=zh_TW</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://play.google.com/store/apps/details?id=com.supercell.squad&amp;hl=zh_TW</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://apps.apple.com/tw/app/%E9%81%BA%E5%BF%98%E4%B9%8B%E5%8A%8D/id6744879430</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tw.ncsoft.com/lostsword</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.facebook.com/LostSwordOfficial.TW/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://play.google.com/store/apps/details?id=com.nctaiwan.lsnct&amp;hl=zh_TW</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.facebook.com/SquadBustersGame/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://squadbusters.supercell.com/cn/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://apps.apple.com/tw/app/%E7%A0%B4%E5%A3%9E%E7%AA%81%E6%93%8A%E9%9A%8A/id1668983788</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>遺忘之劍</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>荒野亂鬥</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>右下角齒輪設定</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>左邊書籤的帳號</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>右下方點酷碰登陸</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GOBLIN0820STRONG</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MERLIN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AUGLOSTSWORD</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LSTHX200</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SUMMERGIFT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*1000+高級角色10 次召喚券*1(國際服)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*2000+
-高級角色 10次召喚券*2+高級寵物10 次召喚券*2+金幣*200萬(國際服)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*1000+高級寵物10 次召喚券*1(國際服)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*1000+五星角色召喚券*1(台服)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>英雄禮物箱*1+盔甲強化咒文書*10(台服)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2000寶石</t>
-  </si>
-  <si>
-    <t>950寶石</t>
-  </si>
-  <si>
-    <t>360寶石</t>
-  </si>
-  <si>
-    <t>170寶石</t>
-  </si>
-  <si>
-    <t>80寶石</t>
-  </si>
-  <si>
-    <t>8000里昂</t>
-  </si>
-  <si>
-    <t>4000里昂</t>
-  </si>
-  <si>
-    <t>2400里昂</t>
-  </si>
-  <si>
-    <t>800里昂</t>
-  </si>
-  <si>
-    <t>400里昂</t>
-  </si>
-  <si>
-    <t>240里昂</t>
-  </si>
-  <si>
-    <t>雙月票</t>
-  </si>
-  <si>
-    <t>月兔茶屋：悠閒之旅</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://apps.apple.com/tw/app/%E6%9C%88%E5%85%94%E8%8C%B6%E5%B1%8B-%E6%82%A0%E9%96%92%E4%B9%8B%E6%97%85-tsuki-tea-house/id6505020147</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://play.google.com/store/apps/details?id=com.hyperbeard.tsukiteahouse&amp;hl=zh_HK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://hyperbeard.com/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/HyperBeardGames/</t>
-  </si>
-  <si>
-    <t>50000金蘿蔔</t>
-  </si>
-  <si>
-    <t>25000金蘿蔔</t>
-  </si>
-  <si>
-    <t>5000金蘿蔔</t>
-  </si>
-  <si>
-    <t>2500金蘿蔔</t>
-  </si>
-  <si>
-    <t>1250金蘿蔔</t>
-  </si>
-  <si>
-    <t>500金蘿蔔</t>
-  </si>
-  <si>
-    <t>新手包</t>
-  </si>
-  <si>
-    <t>月亮俱樂部</t>
-  </si>
-  <si>
-    <t>終極廣告卡</t>
-  </si>
-  <si>
-    <r>
-      <t>歡迎來到《月兔茶屋：悠閒之旅》，這是一款迷人又溫馨的模擬經營遊戲，讓您與可愛的月兔Tsuki在靜謐的鄉村中，共同打造夢想中的茶館。在這款療癒的放置型遊戲中，您的任務是協助Tsuki招待各式各樣的動物顧客，從沖泡完美的茶品到準備可口的小吃，每個細節都充滿了溫暖與人情味。您可以透過解鎖新食譜、擴展菜單、升級裝潢和聘請員工來逐步提升茶館的規模與吸引力。遊戲擁有輕鬆的步調與可愛的視覺風格，讓玩家能徹底放鬆，享受簡單生活的美好。為了讓您的茶館成長更迅速，隨時關注官方發布的最新</t>
+      <t>《破壞突擊隊》是Supercell最新力作，集結旗下經典遊戲人氣角色，展開10人組隊對戰。玩家將從單一角色開始，擊敗怪物收集金幣，不斷擴大隊伍。遊戲策略核心在於搭配角色技能，組成最強戰隊。為了讓隊伍迅速成形，別忘了搜尋最新</t>
     </r>
     <r>
       <rPr>
@@ -14776,7 +14667,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>，是獲得免費資源的好方法；若想加快遊戲進程，也可以考慮適度</t>
+      <t>兌換開局獎勵。透過安全的</t>
     </r>
     <r>
       <rPr>
@@ -14788,7 +14679,7 @@
         <charset val="136"/>
         <scheme val="minor"/>
       </rPr>
-      <t>儲值</t>
+      <t>代儲值</t>
     </r>
     <r>
       <rPr>
@@ -14798,15 +14689,72 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>來購買獨特裝飾，打造最獨一無二的溫馨茶屋！快來與Tsuki一起，展開這段美好的悠閒旅程吧！</t>
+      <t>服務獲取寶石，更能讓你解鎖強力角色，取得戰場優勢。遊戲融合Roguelike與大乱鬥的刺激感，每局都是全新體驗。快來召集你的夢幻隊伍吧！</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+      </rPr>
+      <t>《月兔茶屋：悠閒之旅》是一款療癒人心的模擬經營手遊，你將與月兔一同經營古色古香的茶屋。為森林裡的朋友們端上茶點，聆聽他們的故事，享受寧靜時光。遊戲核心是裝飾與互動，打造你獨一無二的夢幻茶屋。想讓茶屋更快變得漂亮？記得領取官方發佈的禮包碼，獲得限定家具。玩家也可利用方便的代儲值服務，購買精美裝飾品，讓小店更具魅力。快來月兔茶屋體驗最純粹的悠閒與溫暖，遠離所有煩囂。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《遺忘之劍》是一款精緻的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>橫向捲軸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>RPG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，你將與魅力角色們踏上穿越異世界的冒險，體驗趣味的羈絆與中文配音劇情。遊戲採自動攻擊搭配手動施放絕招，可透過裝備、卡片等多樣方式強化隊伍。想讓戰力快速提升？務必關注官方釋出的最新禮包碼來兌換豐富資源。玩家也能透過便利的代儲值服務，加速角色成長，輕鬆挑戰高難度副本與首領。立即加入，沉浸在這場華麗的冒險篇章！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -14930,6 +14878,11 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="新細明體"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -31733,57 +31686,57 @@
     </row>
     <row r="192" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="21" t="s">
-        <v>3596</v>
+        <v>3593</v>
       </c>
       <c r="C192" s="24" t="s">
-        <v>3584</v>
+        <v>3581</v>
       </c>
       <c r="D192" s="23" t="s">
+        <v>3580</v>
+      </c>
+      <c r="E192" s="23" t="s">
+        <v>3582</v>
+      </c>
+      <c r="F192" s="8" t="str">
+        <f t="shared" ref="F192:F254" si="8">IF(A192="", "", "gift-codes.html?game=" &amp; A192)</f>
+        <v>gift-codes.html?game=荒野亂鬥</v>
+      </c>
+      <c r="G192" s="23" t="s">
         <v>3583</v>
-      </c>
-      <c r="E192" s="23" t="s">
-        <v>3585</v>
-      </c>
-      <c r="F192" s="8" t="str">
-        <f t="shared" ref="F191:F254" si="8">IF(A192="", "", "gift-codes.html?game=" &amp; A192)</f>
-        <v>gift-codes.html?game=荒野亂鬥</v>
-      </c>
-      <c r="G192" s="23" t="s">
-        <v>3586</v>
       </c>
       <c r="H192" s="10" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=荒野亂鬥</v>
       </c>
       <c r="I192" s="39" t="s">
-        <v>3580</v>
+        <v>3633</v>
       </c>
       <c r="J192" s="3" t="s">
-        <v>3610</v>
+        <v>3607</v>
       </c>
       <c r="K192" s="4">
         <v>2415</v>
       </c>
       <c r="L192" s="3" t="s">
-        <v>3611</v>
+        <v>3608</v>
       </c>
       <c r="M192" s="4">
         <v>1225</v>
       </c>
       <c r="N192" s="3" t="s">
-        <v>3612</v>
+        <v>3609</v>
       </c>
       <c r="O192" s="4">
         <v>497</v>
       </c>
       <c r="P192" s="3" t="s">
-        <v>3613</v>
+        <v>3610</v>
       </c>
       <c r="Q192" s="4">
         <v>248</v>
       </c>
       <c r="R192" s="3" t="s">
-        <v>3614</v>
+        <v>3611</v>
       </c>
       <c r="S192" s="4">
         <v>132</v>
@@ -31797,233 +31750,233 @@
     </row>
     <row r="193" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="21" t="s">
-        <v>3595</v>
+        <v>3592</v>
       </c>
       <c r="C193" s="24" t="s">
-        <v>3590</v>
+        <v>3587</v>
       </c>
       <c r="D193" s="23" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="E193" s="23" t="s">
-        <v>3588</v>
+        <v>3585</v>
       </c>
       <c r="F193" s="8" t="str">
         <f t="shared" si="8"/>
         <v>gift-codes.html?game=遺忘之劍</v>
       </c>
       <c r="G193" s="23" t="s">
-        <v>3591</v>
+        <v>3588</v>
       </c>
       <c r="H193" s="10" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=遺忘之劍</v>
       </c>
       <c r="I193" s="39" t="s">
-        <v>3581</v>
+        <v>3636</v>
       </c>
       <c r="J193" s="3" t="s">
-        <v>3615</v>
+        <v>3612</v>
       </c>
       <c r="K193" s="4">
         <v>1890</v>
       </c>
       <c r="L193" s="3" t="s">
-        <v>3616</v>
+        <v>3613</v>
       </c>
       <c r="M193" s="4">
         <v>945</v>
       </c>
       <c r="N193" s="3" t="s">
-        <v>3617</v>
+        <v>3614</v>
       </c>
       <c r="O193" s="4">
         <v>575</v>
       </c>
       <c r="P193" s="3" t="s">
-        <v>3618</v>
+        <v>3615</v>
       </c>
       <c r="Q193" s="4">
         <v>192</v>
       </c>
       <c r="R193" s="3" t="s">
-        <v>3619</v>
+        <v>3616</v>
       </c>
       <c r="S193" s="4">
         <v>102</v>
       </c>
       <c r="T193" s="3" t="s">
-        <v>3620</v>
+        <v>3617</v>
       </c>
       <c r="U193" s="4">
         <v>64</v>
       </c>
       <c r="V193" s="3" t="s">
-        <v>3621</v>
+        <v>3618</v>
       </c>
       <c r="W193" s="4">
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="83" t="s">
         <v>3579</v>
       </c>
       <c r="C194" s="24" t="s">
-        <v>3592</v>
+        <v>3589</v>
       </c>
       <c r="D194" s="23" t="s">
-        <v>3593</v>
+        <v>3590</v>
       </c>
       <c r="E194" s="23" t="s">
-        <v>3594</v>
+        <v>3591</v>
       </c>
       <c r="F194" s="8" t="str">
         <f t="shared" si="8"/>
         <v>gift-codes.html?game=破壞突擊隊</v>
       </c>
       <c r="G194" s="23" t="s">
-        <v>3587</v>
+        <v>3584</v>
       </c>
       <c r="H194" s="10" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=破壞突擊隊</v>
       </c>
-      <c r="I194" s="39" t="s">
-        <v>3582</v>
+      <c r="I194" t="s">
+        <v>3634</v>
       </c>
       <c r="J194" s="3" t="s">
-        <v>3627</v>
+        <v>3624</v>
       </c>
       <c r="K194" s="4">
         <v>622</v>
       </c>
       <c r="L194" s="3" t="s">
-        <v>3628</v>
+        <v>3625</v>
       </c>
       <c r="M194" s="4">
         <v>312</v>
       </c>
       <c r="N194" s="3" t="s">
-        <v>3629</v>
+        <v>3626</v>
       </c>
       <c r="O194" s="4">
         <v>176</v>
       </c>
       <c r="P194" s="3" t="s">
-        <v>3630</v>
+        <v>3627</v>
       </c>
       <c r="Q194" s="4">
         <v>102</v>
       </c>
       <c r="R194" s="3" t="s">
-        <v>3631</v>
+        <v>3628</v>
       </c>
       <c r="S194" s="4">
         <v>51</v>
       </c>
       <c r="T194" s="3" t="s">
-        <v>3632</v>
+        <v>3629</v>
       </c>
       <c r="U194" s="4">
         <v>26</v>
       </c>
       <c r="V194" s="3" t="s">
-        <v>3633</v>
+        <v>3630</v>
       </c>
       <c r="W194" s="4">
         <v>391</v>
       </c>
       <c r="X194" s="3" t="s">
-        <v>3634</v>
+        <v>3631</v>
       </c>
       <c r="Y194" s="4">
         <v>391</v>
       </c>
       <c r="Z194" s="3" t="s">
-        <v>3635</v>
+        <v>3632</v>
       </c>
       <c r="AA194" s="4">
         <v>622</v>
       </c>
     </row>
-    <row r="195" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A195" s="22" t="s">
+        <v>3619</v>
+      </c>
+      <c r="C195" s="24" t="s">
+        <v>3623</v>
+      </c>
+      <c r="D195" s="23" t="s">
         <v>3622</v>
       </c>
-      <c r="C195" s="24" t="s">
-        <v>3626</v>
-      </c>
-      <c r="D195" s="23" t="s">
-        <v>3625</v>
-      </c>
       <c r="E195" s="23" t="s">
-        <v>3623</v>
+        <v>3620</v>
       </c>
       <c r="F195" s="8" t="str">
         <f t="shared" si="8"/>
         <v>gift-codes.html?game=月兔茶屋：悠閒之旅</v>
       </c>
       <c r="G195" s="23" t="s">
-        <v>3624</v>
+        <v>3621</v>
       </c>
       <c r="H195" s="10" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=月兔茶屋：悠閒之旅</v>
       </c>
-      <c r="I195" t="s">
-        <v>3636</v>
+      <c r="I195" s="2" t="s">
+        <v>3635</v>
       </c>
       <c r="J195" s="3" t="s">
-        <v>3627</v>
+        <v>3624</v>
       </c>
       <c r="K195" s="4">
         <v>622</v>
       </c>
       <c r="L195" s="3" t="s">
-        <v>3628</v>
+        <v>3625</v>
       </c>
       <c r="M195" s="4">
         <v>312</v>
       </c>
       <c r="N195" s="3" t="s">
-        <v>3629</v>
+        <v>3626</v>
       </c>
       <c r="O195" s="4">
         <v>176</v>
       </c>
       <c r="P195" s="3" t="s">
-        <v>3630</v>
+        <v>3627</v>
       </c>
       <c r="Q195" s="4">
         <v>102</v>
       </c>
       <c r="R195" s="3" t="s">
-        <v>3631</v>
+        <v>3628</v>
       </c>
       <c r="S195" s="4">
         <v>51</v>
       </c>
       <c r="T195" s="3" t="s">
-        <v>3632</v>
+        <v>3629</v>
       </c>
       <c r="U195" s="4">
         <v>26</v>
       </c>
       <c r="V195" s="3" t="s">
-        <v>3633</v>
+        <v>3630</v>
       </c>
       <c r="W195" s="4">
         <v>391</v>
       </c>
       <c r="X195" s="3" t="s">
-        <v>3634</v>
+        <v>3631</v>
       </c>
       <c r="Y195" s="4">
         <v>391</v>
       </c>
       <c r="Z195" s="3" t="s">
-        <v>3635</v>
+        <v>3632</v>
       </c>
       <c r="AA195" s="4">
         <v>622</v>
@@ -48362,7 +48315,7 @@
       </c>
       <c r="E192" s="50" t="str">
         <f>games!I192</f>
-        <v>《荒野亂鬥》是一款由 Supercell 開發的快節奏 3v3 多人對戰與大逃殺手機遊戲。其多樣化的英雄角色、豐富的遊戲模式和三分鐘一局的緊湊戰鬥，使其風靡全球。玩家可以與朋友組隊，或單槍匹馬在荒野中對決，解鎖和升級數十位擁有獨特技能的英雄。為了讓您的英雄更快成長，隨時關注官方發布的最新禮包碼，是獲取免費寶石和金幣的好方法。許多玩家也會尋找安全的代儲值管道，以優惠的價格購買遊戲內商品，迅速提升戰力，在各種模式中稱霸全場。無論是寶石爭奪戰、亂鬥足球還是賞金獵人模式，掌握英雄技巧並善用資源，就是通往勝利的關鍵。立即加入亂鬥，體驗這款刺激又有深度的競技手遊！</v>
+        <v>《荒野亂鬥》是一款快節奏3v3多人對戰與大逃殺手遊。其多樣化的英雄、豐富模式與三分鐘緊湊戰鬥風靡全球。玩家可組隊或單獨對決，解鎖升級各具特色的英雄。想讓英雄更快成長，就別錯過官方發布的最新禮包碼，是獲取免費資源的好方法。許多玩家也會尋找安全的代儲值管道，以優惠價格購買商品提升戰力，在各種模式中稱霸全場。掌握英雄技巧並善用資源，就是通往勝利的關鍵。立即加入，體驗刺激的競技對決！</v>
       </c>
       <c r="F192" s="53" t="s">
         <v>3519</v>
@@ -48404,49 +48357,49 @@
       </c>
       <c r="E193" s="50" t="str">
         <f>games!I193</f>
-        <v>《遺忘之劍》是一款帶有經典像素風格的 MMORPG 手遊，引領玩家重溫最初的冒險感動。遊戲打造了一個宏大的奇幻世界，玩家將扮演勇敢的冒險者，探索未知的地圖、挑戰強大的怪物，並與其他玩家組隊共鬥。遊戲核心特色在於其自由的職業養成與裝備打造系統，讓每位玩家都能走出自己的道路。想要在冒險旅程中快人一步，千萬別錯過官方社群發佈的限量禮包碼，這些序號能兌換稀有材料與實用道具。對於追求頂級裝備的玩家，選擇可靠的代儲值服務，能更有效率地獲取強化資源，打造屬於你的傳說神兵。無論你是喜愛獨自探索的孤狼，還是熱衷於公會團戰的領袖，都能在《遺忘之劍》的世界中找到屬於自己的樂趣。</v>
+        <v>《遺忘之劍》是一款精緻的2D橫向捲軸RPG，你將與魅力角色們踏上穿越異世界的冒險，體驗趣味的羈絆與中文配音劇情。遊戲採自動攻擊搭配手動施放絕招，可透過裝備、卡片等多樣方式強化隊伍。想讓戰力快速提升？務必關注官方釋出的最新禮包碼來兌換豐富資源。玩家也能透過便利的代儲值服務，加速角色成長，輕鬆挑戰高難度副本與首領。立即加入，沉浸在這場華麗的冒險篇章！</v>
       </c>
       <c r="F193" s="70" t="s">
-        <v>3597</v>
+        <v>3594</v>
       </c>
       <c r="G193" s="49" t="s">
-        <v>3598</v>
+        <v>3595</v>
       </c>
       <c r="H193" s="49" t="s">
-        <v>3599</v>
+        <v>3596</v>
       </c>
       <c r="I193" s="49" t="s">
         <v>2651</v>
       </c>
       <c r="K193" s="53" t="s">
+        <v>3597</v>
+      </c>
+      <c r="L193" s="49" t="s">
+        <v>3605</v>
+      </c>
+      <c r="M193" s="54" t="s">
+        <v>3598</v>
+      </c>
+      <c r="N193" s="49" t="s">
+        <v>3606</v>
+      </c>
+      <c r="O193" s="54" t="s">
+        <v>3599</v>
+      </c>
+      <c r="P193" s="61" t="s">
+        <v>3602</v>
+      </c>
+      <c r="Q193" s="54" t="s">
         <v>3600</v>
       </c>
-      <c r="L193" s="49" t="s">
-        <v>3608</v>
-      </c>
-      <c r="M193" s="54" t="s">
+      <c r="R193" s="61" t="s">
+        <v>3603</v>
+      </c>
+      <c r="S193" s="54" t="s">
         <v>3601</v>
       </c>
-      <c r="N193" s="49" t="s">
-        <v>3609</v>
-      </c>
-      <c r="O193" s="54" t="s">
-        <v>3602</v>
-      </c>
-      <c r="P193" s="61" t="s">
-        <v>3605</v>
-      </c>
-      <c r="Q193" s="54" t="s">
-        <v>3603</v>
-      </c>
-      <c r="R193" s="61" t="s">
-        <v>3606</v>
-      </c>
-      <c r="S193" s="54" t="s">
+      <c r="T193" s="61" t="s">
         <v>3604</v>
-      </c>
-      <c r="T193" s="61" t="s">
-        <v>3607</v>
       </c>
     </row>
     <row r="194" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -48464,7 +48417,7 @@
       </c>
       <c r="E194" s="50" t="str">
         <f>IF(games!I194&lt;&gt;"", games!I194, "")</f>
-        <v>《破壞突擊隊》是 Supercell 旗下最新力作，集結了《部落衝突》、《荒野亂鬥》等經典遊戲的超人氣角色，打造出獨一無二的 10 人組隊對戰冒險。在每場比賽中，玩家將從單一角色開始，透過擊敗怪物和對手來收集金幣，擴大自己的突擊隊伍。遊戲的策略核心在於如何搭配不同角色的技能，組成最強大的戰隊。為了讓你的隊伍迅速成形，記得隨時搜尋最新的禮包碼，兌換豐富的開局獎勵。同時，透過安全的代儲值服務獲取寶石，能讓你更快解鎖強力角色和購買實用道具，在戰場上取得巨大優勢。遊戲融合了 Roguelike 隨機元素與大亂鬥的刺激感，每一局都是全新的體驗。快來召集你的夢幻隊伍，在《破壞突擊隊》中展開一場歡樂又混亂的冒險吧！</v>
+        <v>《破壞突擊隊》是Supercell最新力作，集結旗下經典遊戲人氣角色，展開10人組隊對戰。玩家將從單一角色開始，擊敗怪物收集金幣，不斷擴大隊伍。遊戲策略核心在於搭配角色技能，組成最強戰隊。為了讓隊伍迅速成形，別忘了搜尋最新禮包碼兌換開局獎勵。透過安全的代儲值服務獲取寶石，更能讓你解鎖強力角色，取得戰場優勢。遊戲融合Roguelike與大乱鬥的刺激感，每局都是全新體驗。快來召集你的夢幻隊伍吧！</v>
       </c>
       <c r="F194" s="53" t="s">
         <v>3519</v>
@@ -48506,7 +48459,7 @@
       </c>
       <c r="E195" s="50" t="str">
         <f>IF(games!I195&lt;&gt;"", games!I195, "")</f>
-        <v>歡迎來到《月兔茶屋：悠閒之旅》，這是一款迷人又溫馨的模擬經營遊戲，讓您與可愛的月兔Tsuki在靜謐的鄉村中，共同打造夢想中的茶館。在這款療癒的放置型遊戲中，您的任務是協助Tsuki招待各式各樣的動物顧客，從沖泡完美的茶品到準備可口的小吃，每個細節都充滿了溫暖與人情味。您可以透過解鎖新食譜、擴展菜單、升級裝潢和聘請員工來逐步提升茶館的規模與吸引力。遊戲擁有輕鬆的步調與可愛的視覺風格，讓玩家能徹底放鬆，享受簡單生活的美好。為了讓您的茶館成長更迅速，隨時關注官方發布的最新禮包碼，是獲得免費資源的好方法；若想加快遊戲進程，也可以考慮適度儲值來購買獨特裝飾，打造最獨一無二的溫馨茶屋！快來與Tsuki一起，展開這段美好的悠閒旅程吧！</v>
+        <v>《月兔茶屋：悠閒之旅》是一款療癒人心的模擬經營手遊，你將與月兔一同經營古色古香的茶屋。為森林裡的朋友們端上茶點，聆聽他們的故事，享受寧靜時光。遊戲核心是裝飾與互動，打造你獨一無二的夢幻茶屋。想讓茶屋更快變得漂亮？記得領取官方發佈的禮包碼，獲得限定家具。玩家也可利用方便的代儲值服務，購買精美裝飾品，讓小店更具魅力。快來月兔茶屋體驗最純粹的悠閒與溫暖，遠離所有煩囂。</v>
       </c>
       <c r="F195" s="53" t="s">
         <v>3519</v>
@@ -51131,5 +51084,6 @@
     <hyperlink ref="G157" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5426" uniqueCount="3637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5450" uniqueCount="3659">
   <si>
     <t>Facebook</t>
   </si>
@@ -14748,6 +14748,155 @@
       <t>，你將與魅力角色們踏上穿越異世界的冒險，體驗趣味的羈絆與中文配音劇情。遊戲採自動攻擊搭配手動施放絕招，可透過裝備、卡片等多樣方式強化隊伍。想讓戰力快速提升？務必關注官方釋出的最新禮包碼來兌換豐富資源。玩家也能透過便利的代儲值服務，加速角色成長，輕鬆挑戰高難度副本與首領。立即加入，沉浸在這場華麗的冒險篇章！</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吞食天地 虛擬世界</t>
+  </si>
+  <si>
+    <t>https://ts5n.chinesegamer.hk/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ts5nmobile/?locale=zh_TW</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.chinesegamer.hk.ts5n</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E5%90%9E%E9%A3%9F%E5%A4%A9%E5%9C%B0-%E8%99%9B%E6%93%AC%E4%B8%96%E7%95%8C/id6738983582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2B05416LQ </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>隨機金將組合包*1+英雄帖*10+銅幣*100K</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主畫面右方箭頭裡面點齒輪設定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>右下角點虛寶兌換</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點確定之後在背包中領取免費禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《吞食天地</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>虛擬世界》經典三國</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>IP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>感動歸來！本作是款開放世界</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MMORPG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，完美還原回合制戰鬥與可愛畫風，重溫抓捕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、捕捉巴豆妖的樂趣。遊戲獨創地獄與轉生系統，提供豐富養成深度。想在亂世中快速崛起？務必尋找官方最新禮包碼，兌換稀有武將與道具。許多玩家也會選擇安全的代儲值服務來獲取元寶，加速隊伍成形，輕鬆制霸三國。立即加入，與熟悉的名將們一同再戰吞食新世界！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2990元寶</t>
+  </si>
+  <si>
+    <t>1490元寶</t>
+  </si>
+  <si>
+    <t>450元寶</t>
+  </si>
+  <si>
+    <t>180元寶</t>
+  </si>
+  <si>
+    <t>90元寶</t>
+  </si>
+  <si>
+    <t>30元寶</t>
+  </si>
+  <si>
+    <t>尊貴月卡</t>
+  </si>
+  <si>
+    <t>元寶月卡</t>
+  </si>
+  <si>
+    <t>資源月卡</t>
+  </si>
+  <si>
+    <t>資源周卡</t>
+  </si>
+  <si>
+    <t>元寶周卡</t>
   </si>
 </sst>
 </file>
@@ -31748,7 +31897,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="193" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="21" t="s">
         <v>3592</v>
       </c>
@@ -31818,7 +31967,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="83" t="s">
         <v>3579</v>
       </c>
@@ -31900,7 +32049,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="195" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A195" s="22" t="s">
         <v>3619</v>
       </c>
@@ -31982,17 +32131,107 @@
         <v>622</v>
       </c>
     </row>
-    <row r="196" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="20" t="s">
+        <v>3637</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>3639</v>
+      </c>
+      <c r="D196" s="23" t="s">
+        <v>3638</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>3641</v>
+      </c>
       <c r="F196" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=吞食天地 虛擬世界</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>3640</v>
       </c>
       <c r="H196" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=吞食天地 虛擬世界</v>
+      </c>
+      <c r="I196" s="39" t="s">
+        <v>3647</v>
+      </c>
+      <c r="J196" s="3" t="s">
+        <v>3648</v>
+      </c>
+      <c r="K196" s="4">
+        <v>2355</v>
+      </c>
+      <c r="L196" s="3" t="s">
+        <v>3649</v>
+      </c>
+      <c r="M196" s="4">
+        <v>1174</v>
+      </c>
+      <c r="N196" s="3" t="s">
+        <v>3650</v>
+      </c>
+      <c r="O196" s="4">
+        <v>359</v>
+      </c>
+      <c r="P196" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q196" s="4">
+        <v>240</v>
+      </c>
+      <c r="R196" s="3" t="s">
+        <v>3651</v>
+      </c>
+      <c r="S196" s="4">
+        <v>153</v>
+      </c>
+      <c r="T196" s="3" t="s">
+        <v>3652</v>
+      </c>
+      <c r="U196" s="4">
+        <v>77</v>
+      </c>
+      <c r="V196" s="3" t="s">
+        <v>3653</v>
+      </c>
+      <c r="W196" s="4">
+        <v>26</v>
+      </c>
+      <c r="X196" s="3" t="s">
+        <v>3654</v>
+      </c>
+      <c r="Y196" s="4">
+        <v>359</v>
+      </c>
+      <c r="Z196" s="3" t="s">
+        <v>3655</v>
+      </c>
+      <c r="AA196" s="4">
+        <v>240</v>
+      </c>
+      <c r="AB196" s="3" t="s">
+        <v>3656</v>
+      </c>
+      <c r="AC196" s="4">
+        <v>240</v>
+      </c>
+      <c r="AD196" s="3" t="s">
+        <v>3657</v>
+      </c>
+      <c r="AE196" s="4">
+        <v>128</v>
+      </c>
+      <c r="AF196" s="3" t="s">
+        <v>3658</v>
+      </c>
+      <c r="AG196" s="4">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="197" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F197" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -32002,7 +32241,7 @@
         <v/>
       </c>
     </row>
-    <row r="198" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F198" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -32012,7 +32251,7 @@
         <v/>
       </c>
     </row>
-    <row r="199" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F199" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -32022,7 +32261,7 @@
         <v/>
       </c>
     </row>
-    <row r="200" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F200" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -32032,7 +32271,7 @@
         <v/>
       </c>
     </row>
-    <row r="201" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F201" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -32042,7 +32281,7 @@
         <v/>
       </c>
     </row>
-    <row r="202" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F202" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -32052,7 +32291,7 @@
         <v/>
       </c>
     </row>
-    <row r="203" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F203" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -32062,7 +32301,7 @@
         <v/>
       </c>
     </row>
-    <row r="204" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F204" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -32072,7 +32311,7 @@
         <v/>
       </c>
     </row>
-    <row r="205" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F205" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -32082,7 +32321,7 @@
         <v/>
       </c>
     </row>
-    <row r="206" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F206" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -32092,7 +32331,7 @@
         <v/>
       </c>
     </row>
-    <row r="207" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F207" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -32102,7 +32341,7 @@
         <v/>
       </c>
     </row>
-    <row r="208" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F208" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -36195,9 +36434,10 @@
     <hyperlink ref="E194" r:id="rId52"/>
     <hyperlink ref="E195" r:id="rId53"/>
     <hyperlink ref="G195" r:id="rId54"/>
+    <hyperlink ref="D196" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId55"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId56"/>
 </worksheet>
 </file>
 
@@ -48489,19 +48729,37 @@
     <row r="196" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="49" t="str">
         <f>IF(games!A196="", "", games!A196)</f>
-        <v/>
+        <v>吞食天地 虛擬世界</v>
       </c>
       <c r="C196" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/吞食天地 虛擬世界-禮包碼.jpg</v>
       </c>
       <c r="D196" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=吞食天地 虛擬世界</v>
       </c>
       <c r="E196" s="50" t="str">
         <f>IF(games!I196&lt;&gt;"", games!I196, "")</f>
-        <v/>
+        <v>《吞食天地 虛擬世界》經典三國IP感動歸來！本作是款開放世界MMORPG，完美還原回合制戰鬥與可愛畫風，重溫抓捕NPC、捕捉巴豆妖的樂趣。遊戲獨創地獄與轉生系統，提供豐富養成深度。想在亂世中快速崛起？務必尋找官方最新禮包碼，兌換稀有武將與道具。許多玩家也會選擇安全的代儲值服務來獲取元寶，加速隊伍成形，輕鬆制霸三國。立即加入，與熟悉的名將們一同再戰吞食新世界！</v>
+      </c>
+      <c r="F196" s="70" t="s">
+        <v>3644</v>
+      </c>
+      <c r="G196" s="49" t="s">
+        <v>3645</v>
+      </c>
+      <c r="H196" s="49" t="s">
+        <v>2651</v>
+      </c>
+      <c r="I196" s="49" t="s">
+        <v>3646</v>
+      </c>
+      <c r="K196" s="53" t="s">
+        <v>3642</v>
+      </c>
+      <c r="L196" s="49" t="s">
+        <v>3643</v>
       </c>
     </row>
     <row r="197" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5450" uniqueCount="3659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5487" uniqueCount="3681">
   <si>
     <t>Facebook</t>
   </si>
@@ -14897,6 +14897,164 @@
   </si>
   <si>
     <t>元寶周卡</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>封神：蒼嵐契約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61578957816469</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E5%B0%81%E7%A5%9E-%E8%92%BC%E5%B5%90%E5%A5%91%E7%B4%84/id6748110726</t>
+  </si>
+  <si>
+    <t>https://l.facebook.com/l.php?u=https%3A%2F%2Fdrive.google.com%2Ffile%2Fd%2F1WEmdcrN1r89fbt9cynQyNvxLuHn9J60H%2Fview%3Fusp%3Dsharing%26fbclid%3DIwZXh0bgNhZW0CMTAAYnJpZBExbmtpd3BqTWJrZUlDZWNoTwEeQ5cl0F43dhNpC8AnzVWZ_veTkzTmNgUPWkXoN6AEXFsIC09XICD6mtx57zM_aem_IgtsGGeCFonJFWLK0_MP8g&amp;h=AT3O0X74-1aLpyWKfKAbKA2P-FnPBun8wlk55fCZ5kJlu-HiV6QGMJGcVKEYaI_2vXP4YqUfeg4aFZXZKMzCnxN_5Rhcx4O8-IGx58rmwag0rQuosSFM0muDWhQpjtj3cDvV_hJt3T5Xtys&amp;__tn__=-UK-R&amp;c[0]=AT0e-iUHSgjYHkfucwguW39OZ-bKaLMgQ6QXVja1fzGsEOaIACMKZfPRhU2ROJmD9TO-N86uuVOn339B_PZgkrlT8e7ih2UuTqfy65uPFdR3QiTTgY9oTSUr-qIxox3IZgwZ9z35ENVERE-kemQRiGakLM5p5qciTlv_QIjv_pCT6sNSqSNDG-E0Ixr0w-CzkQ8OdZ6vDIMZoAUs947ugU9PyZQq9g</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《封神：蒼嵐契約》是一款東方神話主題的放置卡牌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> RPG </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>手遊，帶您進入一個瑰麗奇幻的封神世界。遊戲以精美的國風美術風格，重新演繹哪吒、妲己、姜子牙等經典角色，打造出策略性十足的卡牌對戰體驗。玩家將扮演天命之人，召喚來自不同陣營的神將，巧妙佈陣，挑戰各式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>PVE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>關卡與</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>PVP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>競技場。遊戲核心玩法輕鬆放置，離線也能持續累積收益，讓您輕鬆養成心儀隊伍。為了幫助玩家快速成長，官方經常釋出豐富的禮包碼，提供大量虛寶獎勵。若想快人一步，透過安全的代儲值服務更能讓您輕鬆取得強力角色與稀有資源，在蒼嵐大陸的冒險旅途上，寫下屬於您的不朽傳奇。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>極品經驗丹*1+銅幣*20,000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>元寶*300+上品經驗丹*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>引魂燈*3+元寶*100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能量石*50+銅幣*10,000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上品經驗丹*3+銅幣*30,000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>極品經驗丹*1+元寶*300</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>引魂燈*3+上品經驗丹*3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>按主畫面左上角頭像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>畫面中央點虛寶碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>按確定領取免費禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>體力卡/月慧卡</t>
+  </si>
+  <si>
+    <t>尊享卡</t>
   </si>
 </sst>
 </file>
@@ -32231,14 +32389,98 @@
         <v>128</v>
       </c>
     </row>
-    <row r="197" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>3659</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>3660</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>3661</v>
+      </c>
       <c r="F197" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v xml:space="preserve">gift-codes.html?game=封神：蒼嵐契約 </v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>3662</v>
       </c>
       <c r="H197" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v xml:space="preserve">https://www.ssbuy.tw/game-detail.html?game=封神：蒼嵐契約 </v>
+      </c>
+      <c r="I197" s="39" t="s">
+        <v>3663</v>
+      </c>
+      <c r="J197" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="K197" s="4">
+        <v>2355</v>
+      </c>
+      <c r="L197" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="M197" s="4">
+        <v>1174</v>
+      </c>
+      <c r="N197" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="O197" s="4">
+        <v>780</v>
+      </c>
+      <c r="P197" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q197" s="4">
+        <v>535</v>
+      </c>
+      <c r="R197" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="S197" s="4">
+        <v>391</v>
+      </c>
+      <c r="T197" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="U197" s="4">
+        <v>264</v>
+      </c>
+      <c r="V197" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="W197" s="4">
+        <v>145</v>
+      </c>
+      <c r="X197" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y197" s="4">
+        <v>28</v>
+      </c>
+      <c r="Z197" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="AA197" s="4">
+        <v>780</v>
+      </c>
+      <c r="AB197" s="3" t="s">
+        <v>3679</v>
+      </c>
+      <c r="AC197" s="4">
+        <v>264</v>
+      </c>
+      <c r="AD197" s="3" t="s">
+        <v>3680</v>
+      </c>
+      <c r="AE197" s="4">
+        <v>391</v>
       </c>
     </row>
     <row r="198" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -48582,7 +48824,7 @@
         <v>2666</v>
       </c>
     </row>
-    <row r="193" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="49" t="str">
         <f>IF(games!A193="", "", games!A193)</f>
         <v>遺忘之劍</v>
@@ -48642,7 +48884,7 @@
         <v>3604</v>
       </c>
     </row>
-    <row r="194" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="49" t="str">
         <f>IF(games!A194="", "", games!A194)</f>
         <v>破壞突擊隊</v>
@@ -48684,7 +48926,7 @@
         <v>2666</v>
       </c>
     </row>
-    <row r="195" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="49" t="str">
         <f>IF(games!A195="", "", games!A195)</f>
         <v>月兔茶屋：悠閒之旅</v>
@@ -48726,7 +48968,7 @@
         <v>2666</v>
       </c>
     </row>
-    <row r="196" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="49" t="str">
         <f>IF(games!A196="", "", games!A196)</f>
         <v>吞食天地 虛擬世界</v>
@@ -48762,25 +49004,85 @@
         <v>3643</v>
       </c>
     </row>
-    <row r="197" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="49" t="str">
         <f>IF(games!A197="", "", games!A197)</f>
-        <v/>
+        <v xml:space="preserve">封神：蒼嵐契約 </v>
       </c>
       <c r="C197" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/封神：蒼嵐契約 -禮包碼.jpg</v>
       </c>
       <c r="D197" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v xml:space="preserve">https://www.ssbuy.tw/gift-codes.html?game=封神：蒼嵐契約 </v>
       </c>
       <c r="E197" s="50" t="str">
         <f>IF(games!I197&lt;&gt;"", games!I197, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>《封神：蒼嵐契約》是一款東方神話主題的放置卡牌 RPG 手遊，帶您進入一個瑰麗奇幻的封神世界。遊戲以精美的國風美術風格，重新演繹哪吒、妲己、姜子牙等經典角色，打造出策略性十足的卡牌對戰體驗。玩家將扮演天命之人，召喚來自不同陣營的神將，巧妙佈陣，挑戰各式PVE關卡與PVP競技場。遊戲核心玩法輕鬆放置，離線也能持續累積收益，讓您輕鬆養成心儀隊伍。為了幫助玩家快速成長，官方經常釋出豐富的禮包碼，提供大量虛寶獎勵。若想快人一步，透過安全的代儲值服務更能讓您輕鬆取得強力角色與稀有資源，在蒼嵐大陸的冒險旅途上，寫下屬於您的不朽傳奇。</v>
+      </c>
+      <c r="F197" s="70" t="s">
+        <v>3676</v>
+      </c>
+      <c r="G197" s="49" t="s">
+        <v>3677</v>
+      </c>
+      <c r="H197" s="49" t="s">
+        <v>2651</v>
+      </c>
+      <c r="I197" s="49" t="s">
+        <v>3678</v>
+      </c>
+      <c r="K197" s="53" t="s">
+        <v>1953</v>
+      </c>
+      <c r="L197" s="49" t="s">
+        <v>3675</v>
+      </c>
+      <c r="M197" s="53" t="s">
+        <v>3664</v>
+      </c>
+      <c r="N197" s="49" t="s">
+        <v>3665</v>
+      </c>
+      <c r="O197" s="54" t="s">
+        <v>3666</v>
+      </c>
+      <c r="P197" s="49" t="s">
+        <v>3667</v>
+      </c>
+      <c r="Q197" s="54" t="s">
+        <v>1952</v>
+      </c>
+      <c r="R197" s="49" t="s">
+        <v>3668</v>
+      </c>
+      <c r="S197" s="54" t="s">
+        <v>2424</v>
+      </c>
+      <c r="T197" s="49" t="s">
+        <v>3674</v>
+      </c>
+      <c r="U197" s="54" t="s">
+        <v>3671</v>
+      </c>
+      <c r="V197" s="49" t="s">
+        <v>3668</v>
+      </c>
+      <c r="W197" s="54" t="s">
+        <v>3672</v>
+      </c>
+      <c r="X197" s="49" t="s">
+        <v>3673</v>
+      </c>
+      <c r="Y197" s="54" t="s">
+        <v>3669</v>
+      </c>
+      <c r="Z197" s="49" t="s">
+        <v>3670</v>
+      </c>
+    </row>
+    <row r="198" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="49" t="str">
         <f>IF(games!A198="", "", games!A198)</f>
         <v/>
@@ -48798,7 +49100,7 @@
         <v/>
       </c>
     </row>
-    <row r="199" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="49" t="str">
         <f>IF(games!A199="", "", games!A199)</f>
         <v/>
@@ -48816,7 +49118,7 @@
         <v/>
       </c>
     </row>
-    <row r="200" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="49" t="str">
         <f>IF(games!A200="", "", games!A200)</f>
         <v/>
@@ -48834,7 +49136,7 @@
         <v/>
       </c>
     </row>
-    <row r="201" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="49" t="str">
         <f>IF(games!A201="", "", games!A201)</f>
         <v/>
@@ -48848,7 +49150,7 @@
         <v/>
       </c>
     </row>
-    <row r="202" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="49" t="str">
         <f>IF(games!A202="", "", games!A202)</f>
         <v/>
@@ -48862,7 +49164,7 @@
         <v/>
       </c>
     </row>
-    <row r="203" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="49" t="str">
         <f>IF(games!A203="", "", games!A203)</f>
         <v/>
@@ -48876,7 +49178,7 @@
         <v/>
       </c>
     </row>
-    <row r="204" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="49" t="str">
         <f>IF(games!A204="", "", games!A204)</f>
         <v/>
@@ -48890,7 +49192,7 @@
         <v/>
       </c>
     </row>
-    <row r="205" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="49" t="str">
         <f>IF(games!A205="", "", games!A205)</f>
         <v/>
@@ -48904,7 +49206,7 @@
         <v/>
       </c>
     </row>
-    <row r="206" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="49" t="str">
         <f>IF(games!A206="", "", games!A206)</f>
         <v/>
@@ -48918,7 +49220,7 @@
         <v/>
       </c>
     </row>
-    <row r="207" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="49" t="str">
         <f>IF(games!A207="", "", games!A207)</f>
         <v/>
@@ -48932,7 +49234,7 @@
         <v/>
       </c>
     </row>
-    <row r="208" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="49" t="str">
         <f>IF(games!A208="", "", games!A208)</f>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -14925,9 +14925,6 @@
     <t>https://apps.apple.com/tw/app/%E5%B0%81%E7%A5%9E-%E8%92%BC%E5%B5%90%E5%A5%91%E7%B4%84/id6748110726</t>
   </si>
   <si>
-    <t>https://l.facebook.com/l.php?u=https%3A%2F%2Fdrive.google.com%2Ffile%2Fd%2F1WEmdcrN1r89fbt9cynQyNvxLuHn9J60H%2Fview%3Fusp%3Dsharing%26fbclid%3DIwZXh0bgNhZW0CMTAAYnJpZBExbmtpd3BqTWJrZUlDZWNoTwEeQ5cl0F43dhNpC8AnzVWZ_veTkzTmNgUPWkXoN6AEXFsIC09XICD6mtx57zM_aem_IgtsGGeCFonJFWLK0_MP8g&amp;h=AT3O0X74-1aLpyWKfKAbKA2P-FnPBun8wlk55fCZ5kJlu-HiV6QGMJGcVKEYaI_2vXP4YqUfeg4aFZXZKMzCnxN_5Rhcx4O8-IGx58rmwag0rQuosSFM0muDWhQpjtj3cDvV_hJt3T5Xtys&amp;__tn__=-UK-R&amp;c[0]=AT0e-iUHSgjYHkfucwguW39OZ-bKaLMgQ6QXVja1fzGsEOaIACMKZfPRhU2ROJmD9TO-N86uuVOn339B_PZgkrlT8e7ih2UuTqfy65uPFdR3QiTTgY9oTSUr-qIxox3IZgwZ9z35ENVERE-kemQRiGakLM5p5qciTlv_QIjv_pCT6sNSqSNDG-E0Ixr0w-CzkQ8OdZ6vDIMZoAUs947ugU9PyZQq9g</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -15055,6 +15052,10 @@
   </si>
   <si>
     <t>尊享卡</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1WEmdcrN1r89fbt9cynQyNvxLuHn9J60H/view?fbclid=IwY2xjawMZI35leHRuA2FlbQIxMABicmlkETFiM29nWVdGSDIxQlFEc2UwAR7YUxJ-rQWS-i8tf0iw_ZdXfMrHt0NPIdf3_Uy6PP2BYOpVR9qSxrTptsOMjQ_aem_bWB-Pjdyt5IM3iosacdupA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -32406,15 +32407,15 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">gift-codes.html?game=封神：蒼嵐契約 </v>
       </c>
-      <c r="G197" s="2" t="s">
-        <v>3662</v>
+      <c r="G197" s="23" t="s">
+        <v>3680</v>
       </c>
       <c r="H197" s="10" t="str">
         <f t="shared" si="7"/>
         <v xml:space="preserve">https://www.ssbuy.tw/game-detail.html?game=封神：蒼嵐契約 </v>
       </c>
       <c r="I197" s="39" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="J197" s="3" t="s">
         <v>235</v>
@@ -32471,13 +32472,13 @@
         <v>780</v>
       </c>
       <c r="AB197" s="3" t="s">
-        <v>3679</v>
+        <v>3678</v>
       </c>
       <c r="AC197" s="4">
         <v>264</v>
       </c>
       <c r="AD197" s="3" t="s">
-        <v>3680</v>
+        <v>3679</v>
       </c>
       <c r="AE197" s="4">
         <v>391</v>
@@ -36677,9 +36678,10 @@
     <hyperlink ref="E195" r:id="rId53"/>
     <hyperlink ref="G195" r:id="rId54"/>
     <hyperlink ref="D196" r:id="rId55"/>
+    <hyperlink ref="G197" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId56"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId57"/>
 </worksheet>
 </file>
 
@@ -49022,64 +49024,64 @@
         <v>《封神：蒼嵐契約》是一款東方神話主題的放置卡牌 RPG 手遊，帶您進入一個瑰麗奇幻的封神世界。遊戲以精美的國風美術風格，重新演繹哪吒、妲己、姜子牙等經典角色，打造出策略性十足的卡牌對戰體驗。玩家將扮演天命之人，召喚來自不同陣營的神將，巧妙佈陣，挑戰各式PVE關卡與PVP競技場。遊戲核心玩法輕鬆放置，離線也能持續累積收益，讓您輕鬆養成心儀隊伍。為了幫助玩家快速成長，官方經常釋出豐富的禮包碼，提供大量虛寶獎勵。若想快人一步，透過安全的代儲值服務更能讓您輕鬆取得強力角色與稀有資源，在蒼嵐大陸的冒險旅途上，寫下屬於您的不朽傳奇。</v>
       </c>
       <c r="F197" s="70" t="s">
+        <v>3675</v>
+      </c>
+      <c r="G197" s="49" t="s">
         <v>3676</v>
-      </c>
-      <c r="G197" s="49" t="s">
-        <v>3677</v>
       </c>
       <c r="H197" s="49" t="s">
         <v>2651</v>
       </c>
       <c r="I197" s="49" t="s">
-        <v>3678</v>
+        <v>3677</v>
       </c>
       <c r="K197" s="53" t="s">
         <v>1953</v>
       </c>
       <c r="L197" s="49" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c r="M197" s="53" t="s">
+        <v>3663</v>
+      </c>
+      <c r="N197" s="49" t="s">
         <v>3664</v>
       </c>
-      <c r="N197" s="49" t="s">
+      <c r="O197" s="54" t="s">
         <v>3665</v>
       </c>
-      <c r="O197" s="54" t="s">
+      <c r="P197" s="49" t="s">
         <v>3666</v>
-      </c>
-      <c r="P197" s="49" t="s">
-        <v>3667</v>
       </c>
       <c r="Q197" s="54" t="s">
         <v>1952</v>
       </c>
       <c r="R197" s="49" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
       <c r="S197" s="54" t="s">
         <v>2424</v>
       </c>
       <c r="T197" s="49" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
       <c r="U197" s="54" t="s">
+        <v>3670</v>
+      </c>
+      <c r="V197" s="49" t="s">
+        <v>3667</v>
+      </c>
+      <c r="W197" s="54" t="s">
         <v>3671</v>
       </c>
-      <c r="V197" s="49" t="s">
+      <c r="X197" s="49" t="s">
+        <v>3672</v>
+      </c>
+      <c r="Y197" s="54" t="s">
         <v>3668</v>
       </c>
-      <c r="W197" s="54" t="s">
-        <v>3672</v>
-      </c>
-      <c r="X197" s="49" t="s">
-        <v>3673</v>
-      </c>
-      <c r="Y197" s="54" t="s">
+      <c r="Z197" s="49" t="s">
         <v>3669</v>
-      </c>
-      <c r="Z197" s="49" t="s">
-        <v>3670</v>
       </c>
     </row>
     <row r="198" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -14899,26 +14899,6 @@
     <t>元寶周卡</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>封神：蒼嵐契約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.facebook.com/profile.php?id=61578957816469</t>
   </si>
   <si>
@@ -15055,6 +15035,10 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1WEmdcrN1r89fbt9cynQyNvxLuHn9J60H/view?fbclid=IwY2xjawMZI35leHRuA2FlbQIxMABicmlkETFiM29nWVdGSDIxQlFEc2UwAR7YUxJ-rQWS-i8tf0iw_ZdXfMrHt0NPIdf3_Uy6PP2BYOpVR9qSxrTptsOMjQ_aem_bWB-Pjdyt5IM3iosacdupA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>封神：蒼嵐契約</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -32391,31 +32375,31 @@
       </c>
     </row>
     <row r="197" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="1" t="s">
+      <c r="A197" s="22" t="s">
+        <v>3680</v>
+      </c>
+      <c r="C197" s="1" t="s">
         <v>3659</v>
       </c>
-      <c r="C197" s="1" t="s">
+      <c r="D197" s="1" t="s">
+        <v>3659</v>
+      </c>
+      <c r="E197" s="2" t="s">
         <v>3660</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>3660</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>3661</v>
       </c>
       <c r="F197" s="8" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">gift-codes.html?game=封神：蒼嵐契約 </v>
+        <v>gift-codes.html?game=封神：蒼嵐契約</v>
       </c>
       <c r="G197" s="23" t="s">
-        <v>3680</v>
+        <v>3679</v>
       </c>
       <c r="H197" s="10" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">https://www.ssbuy.tw/game-detail.html?game=封神：蒼嵐契約 </v>
+        <v>https://www.ssbuy.tw/game-detail.html?game=封神：蒼嵐契約</v>
       </c>
       <c r="I197" s="39" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="J197" s="3" t="s">
         <v>235</v>
@@ -32472,13 +32456,13 @@
         <v>780</v>
       </c>
       <c r="AB197" s="3" t="s">
-        <v>3678</v>
+        <v>3677</v>
       </c>
       <c r="AC197" s="4">
         <v>264</v>
       </c>
       <c r="AD197" s="3" t="s">
-        <v>3679</v>
+        <v>3678</v>
       </c>
       <c r="AE197" s="4">
         <v>391</v>
@@ -49009,79 +48993,79 @@
     <row r="197" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="49" t="str">
         <f>IF(games!A197="", "", games!A197)</f>
-        <v xml:space="preserve">封神：蒼嵐契約 </v>
+        <v>封神：蒼嵐契約</v>
       </c>
       <c r="C197" s="49" t="str">
         <f t="shared" si="7"/>
-        <v>giftcodesbanner/封神：蒼嵐契約 -禮包碼.jpg</v>
+        <v>giftcodesbanner/封神：蒼嵐契約-禮包碼.jpg</v>
       </c>
       <c r="D197" s="49" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">https://www.ssbuy.tw/gift-codes.html?game=封神：蒼嵐契約 </v>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=封神：蒼嵐契約</v>
       </c>
       <c r="E197" s="50" t="str">
         <f>IF(games!I197&lt;&gt;"", games!I197, "")</f>
         <v>《封神：蒼嵐契約》是一款東方神話主題的放置卡牌 RPG 手遊，帶您進入一個瑰麗奇幻的封神世界。遊戲以精美的國風美術風格，重新演繹哪吒、妲己、姜子牙等經典角色，打造出策略性十足的卡牌對戰體驗。玩家將扮演天命之人，召喚來自不同陣營的神將，巧妙佈陣，挑戰各式PVE關卡與PVP競技場。遊戲核心玩法輕鬆放置，離線也能持續累積收益，讓您輕鬆養成心儀隊伍。為了幫助玩家快速成長，官方經常釋出豐富的禮包碼，提供大量虛寶獎勵。若想快人一步，透過安全的代儲值服務更能讓您輕鬆取得強力角色與稀有資源，在蒼嵐大陸的冒險旅途上，寫下屬於您的不朽傳奇。</v>
       </c>
       <c r="F197" s="70" t="s">
+        <v>3674</v>
+      </c>
+      <c r="G197" s="49" t="s">
         <v>3675</v>
-      </c>
-      <c r="G197" s="49" t="s">
-        <v>3676</v>
       </c>
       <c r="H197" s="49" t="s">
         <v>2651</v>
       </c>
       <c r="I197" s="49" t="s">
-        <v>3677</v>
+        <v>3676</v>
       </c>
       <c r="K197" s="53" t="s">
         <v>1953</v>
       </c>
       <c r="L197" s="49" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
       <c r="M197" s="53" t="s">
+        <v>3662</v>
+      </c>
+      <c r="N197" s="49" t="s">
         <v>3663</v>
       </c>
-      <c r="N197" s="49" t="s">
+      <c r="O197" s="54" t="s">
         <v>3664</v>
       </c>
-      <c r="O197" s="54" t="s">
+      <c r="P197" s="49" t="s">
         <v>3665</v>
-      </c>
-      <c r="P197" s="49" t="s">
-        <v>3666</v>
       </c>
       <c r="Q197" s="54" t="s">
         <v>1952</v>
       </c>
       <c r="R197" s="49" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="S197" s="54" t="s">
         <v>2424</v>
       </c>
       <c r="T197" s="49" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
       <c r="U197" s="54" t="s">
+        <v>3669</v>
+      </c>
+      <c r="V197" s="49" t="s">
+        <v>3666</v>
+      </c>
+      <c r="W197" s="54" t="s">
         <v>3670</v>
       </c>
-      <c r="V197" s="49" t="s">
+      <c r="X197" s="49" t="s">
+        <v>3671</v>
+      </c>
+      <c r="Y197" s="54" t="s">
         <v>3667</v>
       </c>
-      <c r="W197" s="54" t="s">
-        <v>3671</v>
-      </c>
-      <c r="X197" s="49" t="s">
-        <v>3672</v>
-      </c>
-      <c r="Y197" s="54" t="s">
+      <c r="Z197" s="49" t="s">
         <v>3668</v>
-      </c>
-      <c r="Z197" s="49" t="s">
-        <v>3669</v>
       </c>
     </row>
     <row r="198" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5487" uniqueCount="3681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5528" uniqueCount="3713">
   <si>
     <t>Facebook</t>
   </si>
@@ -15040,6 +15040,253 @@
   <si>
     <t>封神：蒼嵐契約</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gear Fight!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/gear-fight/id6738430824</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.EternalStudio.GearFight&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://voodoo.io/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Gear Fight</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>》是一款考驗策略與創造力的益智冒險手遊。玩家將化身為機械大師，親手設計戰爭機器，透過巧妙組合、放置齒輪，打造出獨一無二的自動化生產線來抵禦強敵。你需要在有限預算內，策略性地生產近戰兵、弓箭手等多樣單位。為了讓你的開局更順利，記得隨時搜尋最新的禮包碼來兌換豐厚獎勵；若想加速升級，安全的代儲值服務是你的最佳幫手，讓你輕鬆構築最強工廠，迎向勝利。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>700寶石</t>
+  </si>
+  <si>
+    <t>200寶石</t>
+  </si>
+  <si>
+    <t>25寶石</t>
+  </si>
+  <si>
+    <t>2X加速</t>
+  </si>
+  <si>
+    <t>植物部隊包</t>
+  </si>
+  <si>
+    <t>祝福禮包</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.gamania.tosm&amp;is_retargeting=true&amp;source_caller=ui&amp;shortlink=tr8m0yil&amp;c=0715preregister&amp;pid=pre-eventpage_registernowbtn&amp;af_xp=custom&amp;fbclid=IwY2xjawMat9dleHRuA2FlbQIxMABicmlkETFQdUxnS1dmdVZuODkyZWp0AR6xAzlsZNQNCXjTWaD3u5fhy0zWK0zT2-hw23w4-G2KqEx0eosDi8BsaQWa8w_aem_pSu3Tr4ufEnibbPRTHgBGw&amp;af_reengagement_window=61d</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>救世者之樹 M</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E6%95%91%E4%B8%96%E8%80%85%E4%B9%8B%E6%A8%B9%EF%BD%8D/id6458050011</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tosm-treeofsavior.beanfun.com/main</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/TreeofSaviorM/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《救世者之樹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>》是經典</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>線上遊戲《救世者之樹》的全新</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MMORPG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>手機版，完美繼承了其獨樹一幟的童話繪本美術風格。遊戲以精緻的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>場景搭配經典的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>角色，帶領玩家重溫最初的感動。遊戲提供劍士、巫師、弓箭手、牧師四大經典職業體系，玩家可以自由搭配技能與特性，打造專屬於你的獨特玩法。除了豐富的主線劇情，還有特色的「夥伴」系統與「隨機副本」等著你來探索。為了讓你的冒險旅程更加順利，記得隨時關注官方釋出的最新禮包碼，兌換豐富的開服好禮。此外，透過方便安全的代儲值服務，也能幫助你快速成長，讓角色戰力快人一步，輕鬆挑戰更高難度的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>BOSS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1F437D9FA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主畫面中按設定/個人頭像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到兌換碼禮包碼字樣點進去</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>按確定後到信箱領取免費禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1500TP</t>
+  </si>
+  <si>
+    <t>1150TP</t>
+  </si>
+  <si>
+    <t>580TP</t>
+  </si>
+  <si>
+    <t>350TP</t>
+  </si>
+  <si>
+    <t>165TP</t>
+  </si>
+  <si>
+    <t>80TP</t>
+  </si>
+  <si>
+    <t>40TP</t>
+  </si>
+  <si>
+    <t>13TP</t>
+  </si>
+  <si>
+    <t>TOSM上市新手禮包</t>
   </si>
 </sst>
 </file>
@@ -32468,24 +32715,150 @@
         <v>391</v>
       </c>
     </row>
-    <row r="198" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>3681</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>3685</v>
+      </c>
+      <c r="D198" s="23" t="s">
+        <v>3684</v>
+      </c>
+      <c r="E198" s="23" t="s">
+        <v>3682</v>
+      </c>
       <c r="F198" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=Gear Fight!</v>
+      </c>
+      <c r="G198" s="23" t="s">
+        <v>3683</v>
       </c>
       <c r="H198" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=Gear Fight!</v>
+      </c>
+      <c r="I198" s="39" t="s">
+        <v>3686</v>
+      </c>
+      <c r="J198" s="3" t="s">
+        <v>3687</v>
+      </c>
+      <c r="K198" s="4">
+        <v>780</v>
+      </c>
+      <c r="L198" s="3" t="s">
+        <v>3688</v>
+      </c>
+      <c r="M198" s="4">
+        <v>232</v>
+      </c>
+      <c r="N198" s="3" t="s">
+        <v>3689</v>
+      </c>
+      <c r="O198" s="4">
+        <v>51</v>
+      </c>
+      <c r="P198" s="3" t="s">
+        <v>3690</v>
+      </c>
+      <c r="Q198" s="4">
+        <v>232</v>
+      </c>
+      <c r="R198" s="3" t="s">
+        <v>3691</v>
+      </c>
+      <c r="S198" s="4">
+        <v>391</v>
+      </c>
+      <c r="T198" s="3" t="s">
+        <v>3692</v>
+      </c>
+      <c r="U198" s="4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="199" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="22" t="s">
+        <v>3694</v>
+      </c>
+      <c r="C199" s="24" t="s">
+        <v>3697</v>
+      </c>
+      <c r="D199" s="23" t="s">
+        <v>3696</v>
+      </c>
+      <c r="E199" s="23" t="s">
+        <v>3695</v>
+      </c>
       <c r="F199" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=救世者之樹 M</v>
+      </c>
+      <c r="G199" s="23" t="s">
+        <v>3693</v>
       </c>
       <c r="H199" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=救世者之樹 M</v>
+      </c>
+      <c r="I199" s="39" t="s">
+        <v>3698</v>
+      </c>
+      <c r="J199" s="3" t="s">
+        <v>3704</v>
+      </c>
+      <c r="K199" s="4">
+        <v>2555</v>
+      </c>
+      <c r="L199" s="3" t="s">
+        <v>3705</v>
+      </c>
+      <c r="M199" s="4">
+        <v>2119</v>
+      </c>
+      <c r="N199" s="3" t="s">
+        <v>3706</v>
+      </c>
+      <c r="O199" s="4">
+        <v>1063</v>
+      </c>
+      <c r="P199" s="3" t="s">
+        <v>3707</v>
+      </c>
+      <c r="Q199" s="4">
+        <v>701</v>
+      </c>
+      <c r="R199" s="3" t="s">
+        <v>3708</v>
+      </c>
+      <c r="S199" s="4">
+        <v>312</v>
+      </c>
+      <c r="T199" s="3" t="s">
+        <v>3709</v>
+      </c>
+      <c r="U199" s="4">
+        <v>162</v>
+      </c>
+      <c r="V199" s="3" t="s">
+        <v>3710</v>
+      </c>
+      <c r="W199" s="4">
+        <v>85</v>
+      </c>
+      <c r="X199" s="3" t="s">
+        <v>3711</v>
+      </c>
+      <c r="Y199" s="4">
+        <v>51</v>
+      </c>
+      <c r="Z199" s="3" t="s">
+        <v>3712</v>
+      </c>
+      <c r="AA199" s="4">
+        <v>654</v>
       </c>
     </row>
     <row r="200" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -36663,9 +37036,16 @@
     <hyperlink ref="G195" r:id="rId54"/>
     <hyperlink ref="D196" r:id="rId55"/>
     <hyperlink ref="G197" r:id="rId56"/>
+    <hyperlink ref="E198" r:id="rId57"/>
+    <hyperlink ref="G198" r:id="rId58"/>
+    <hyperlink ref="D198" r:id="rId59"/>
+    <hyperlink ref="G199"/>
+    <hyperlink ref="E199" r:id="rId60"/>
+    <hyperlink ref="D199" r:id="rId61"/>
+    <hyperlink ref="C199" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId57"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId63"/>
 </worksheet>
 </file>
 
@@ -49071,37 +49451,73 @@
     <row r="198" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="49" t="str">
         <f>IF(games!A198="", "", games!A198)</f>
-        <v/>
+        <v>Gear Fight!</v>
       </c>
       <c r="C198" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/Gear Fight!-禮包碼.jpg</v>
       </c>
       <c r="D198" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=Gear Fight!</v>
       </c>
       <c r="E198" s="50" t="str">
         <f>IF(games!I198&lt;&gt;"", games!I198, "")</f>
-        <v/>
+        <v>《Gear Fight》是一款考驗策略與創造力的益智冒險手遊。玩家將化身為機械大師，親手設計戰爭機器，透過巧妙組合、放置齒輪，打造出獨一無二的自動化生產線來抵禦強敵。你需要在有限預算內，策略性地生產近戰兵、弓箭手等多樣單位。為了讓你的開局更順利，記得隨時搜尋最新的禮包碼來兌換豐厚獎勵；若想加速升級，安全的代儲值服務是你的最佳幫手，讓你輕鬆構築最強工廠，迎向勝利。</v>
+      </c>
+      <c r="F198" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="G198" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="H198" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="I198" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K198" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L198" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M198" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="N198" s="49" t="s">
+        <v>2666</v>
       </c>
     </row>
     <row r="199" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="49" t="str">
         <f>IF(games!A199="", "", games!A199)</f>
-        <v/>
+        <v>救世者之樹 M</v>
       </c>
       <c r="C199" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/救世者之樹 M-禮包碼.jpg</v>
       </c>
       <c r="D199" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=救世者之樹 M</v>
       </c>
       <c r="E199" s="50" t="str">
         <f>IF(games!I199&lt;&gt;"", games!I199, "")</f>
-        <v/>
+        <v>《救世者之樹 M》是經典PC線上遊戲《救世者之樹》的全新MMORPG手機版，完美繼承了其獨樹一幟的童話繪本美術風格。遊戲以精緻的3D場景搭配經典的2D角色，帶領玩家重溫最初的感動。遊戲提供劍士、巫師、弓箭手、牧師四大經典職業體系，玩家可以自由搭配技能與特性，打造專屬於你的獨特玩法。除了豐富的主線劇情，還有特色的「夥伴」系統與「隨機副本」等著你來探索。為了讓你的冒險旅程更加順利，記得隨時關注官方釋出的最新禮包碼，兌換豐富的開服好禮。此外，透過方便安全的代儲值服務，也能幫助你快速成長，讓角色戰力快人一步，輕鬆挑戰更高難度的BOSS。</v>
+      </c>
+      <c r="F199" s="70" t="s">
+        <v>3701</v>
+      </c>
+      <c r="G199" s="49" t="s">
+        <v>3702</v>
+      </c>
+      <c r="H199" s="49" t="s">
+        <v>2651</v>
+      </c>
+      <c r="I199" s="49" t="s">
+        <v>3703</v>
       </c>
     </row>
     <row r="200" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -49120,6 +49536,12 @@
       <c r="E200" s="50" t="str">
         <f>IF(games!I200&lt;&gt;"", games!I200, "")</f>
         <v/>
+      </c>
+      <c r="K200" s="53" t="s">
+        <v>3699</v>
+      </c>
+      <c r="L200" s="49" t="s">
+        <v>3700</v>
       </c>
     </row>
     <row r="201" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5528" uniqueCount="3713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5544" uniqueCount="3722">
   <si>
     <t>Facebook</t>
   </si>
@@ -15287,6 +15287,42 @@
   </si>
   <si>
     <t>TOSM上市新手禮包</t>
+  </si>
+  <si>
+    <t>GOBLIN0820STRONG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fanghuo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣與強化禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>94AKAONI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>94DADA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RCB768501E</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>94MMD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B156BCDGBF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OB1CE9EJ5F</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -48789,6 +48825,12 @@
       <c r="N185" s="49" t="s">
         <v>2658</v>
       </c>
+      <c r="O185" s="54" t="s">
+        <v>3714</v>
+      </c>
+      <c r="P185" s="49" t="s">
+        <v>3715</v>
+      </c>
     </row>
     <row r="186" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="79" t="s">
@@ -49519,6 +49561,54 @@
       <c r="I199" s="49" t="s">
         <v>3703</v>
       </c>
+      <c r="K199" s="53" t="s">
+        <v>3699</v>
+      </c>
+      <c r="L199" s="49" t="s">
+        <v>3700</v>
+      </c>
+      <c r="M199" s="54" t="s">
+        <v>3713</v>
+      </c>
+      <c r="N199" s="49" t="s">
+        <v>3700</v>
+      </c>
+      <c r="O199" s="66" t="s">
+        <v>3718</v>
+      </c>
+      <c r="P199" s="49" t="s">
+        <v>3700</v>
+      </c>
+      <c r="Q199" s="66" t="s">
+        <v>3716</v>
+      </c>
+      <c r="R199" s="49" t="s">
+        <v>3700</v>
+      </c>
+      <c r="S199" s="54" t="s">
+        <v>3717</v>
+      </c>
+      <c r="T199" s="49" t="s">
+        <v>3700</v>
+      </c>
+      <c r="U199" s="54" t="s">
+        <v>3719</v>
+      </c>
+      <c r="V199" s="49" t="s">
+        <v>3700</v>
+      </c>
+      <c r="W199" s="54" t="s">
+        <v>3720</v>
+      </c>
+      <c r="X199" s="49" t="s">
+        <v>3700</v>
+      </c>
+      <c r="Y199" s="54" t="s">
+        <v>3721</v>
+      </c>
+      <c r="Z199" s="49" t="s">
+        <v>3700</v>
+      </c>
     </row>
     <row r="200" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="49" t="str">
@@ -49536,12 +49626,6 @@
       <c r="E200" s="50" t="str">
         <f>IF(games!I200&lt;&gt;"", games!I200, "")</f>
         <v/>
-      </c>
-      <c r="K200" s="53" t="s">
-        <v>3699</v>
-      </c>
-      <c r="L200" s="49" t="s">
-        <v>3700</v>
       </c>
     </row>
     <row r="201" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5544" uniqueCount="3722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5766" uniqueCount="3870">
   <si>
     <t>Facebook</t>
   </si>
@@ -15322,6 +15322,1044 @@
   </si>
   <si>
     <t>OB1CE9EJ5F</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>勝利女神：妮姬</t>
+  </si>
+  <si>
+    <t>野龍小隊</t>
+  </si>
+  <si>
+    <t>BangBang殭屍：避難所戰爭</t>
+  </si>
+  <si>
+    <t>主公超會閃</t>
+  </si>
+  <si>
+    <t>小兵來支援</t>
+  </si>
+  <si>
+    <t>姆姆鬥惡龍</t>
+  </si>
+  <si>
+    <t>發條特攻隊</t>
+  </si>
+  <si>
+    <t>天命：群星</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E5%8B%9D%E5%88%A9%E5%A5%B3%E7%A5%9E-%E5%A6%AE%E5%A7%AC/id1630883882</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E7%99%BC%E6%A2%9D%E7%89%B9%E6%94%BB%E9%9A%8A/id6499112583</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E5%B0%8F%E5%85%B5%E4%BE%86%E6%94%AF%E6%8F%B4/id6739828673?mt=8</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/hk/app/%E9%87%8E%E9%BE%8D%E5%B0%8F%E9%9A%8A/id6746182414</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E5%A7%86%E5%A7%86%E9%AC%A5%E6%83%A1%E9%BE%8D-i-slime/id6738974922</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.netease.g108hmt&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/us/app/bangbang%E5%83%B5%E5%B0%B8-%E9%81%BF%E9%9A%BE%E6%89%80%E6%88%98%E4%BA%89/id6747997392?l=zh-Hans-CN</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.proximabeta.nikke&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.lastshelter.gp&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.islime.android</t>
+  </si>
+  <si>
+    <t>https://www.playdestinyrising.com/tw/?is_retargeting=true&amp;source_caller=ui&amp;af_inactivity_window=14d&amp;shortlink=q2pit60k&amp;c=iOS%20Pre-Order%20from%20social%20media&amp;pid=marketing&amp;af_xp=custom&amp;af_reengagement_window=30d</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E5%A4%A9%E5%91%BD-%E7%BE%A4%E6%98%9F/id6744052056</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.vizta.wefly&amp;referrer=adjust_reftag%3DcvU68a2dF84ur%26utm_source%3DWefly_Marketing%26utm_campaign%3DWefly_SNS%26utm_content%3DSNS%26utm_term%3DEU</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ACECRAFTOFFICIAL/?brand_redir=512601458601885#</t>
+  </si>
+  <si>
+    <t>https://cn.moonton.com/</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>還在為推不過戰役、只能在指揮中心望著老婆嘆氣而煩惱嗎？《勝利女神：妮姬》是一款以末世為背景的第三人稱射擊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>RPG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，主打精美的角色立繪與爽快的射擊手感。想讓您的妮姬戰力突飛猛進，不再被萊徹按在地上摩擦？除了到處跪求那些虛無飄渺的禮包碼與兌換碼，不如來點實際的。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">SSbuy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>提供最專業的代儲值服務，讓您用最划算的價格武裝您的老婆們，輕鬆突破</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>160</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>等級的高牆，別再猶豫了，指揮官，是時候讓她們見識真正的火力了！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>別再看著別人的玩具大軍流口水了！《發條特攻隊》是一款充滿策略性的 Roguelike 塔防手遊，玩家將指揮可愛的玩具英雄抵禦一波波的敵人攻勢。是不是覺得自己的玩具箱總比別人空？抽來抽去都是些派不上用場的雜兵？與其大海撈針般地搜尋那些不知道過期了沒的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>和</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兌換碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，不如直接釜底抽薪。選擇 SSbuy 最可靠的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，讓您有足夠的資源抽到心儀的傳奇玩具，輕鬆碾壓對手。別再當陪跑的龍套了，是時候讓您的玩具成為全場最靚的仔！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>指揮官，您還在為守不住那幾波小怪而焦頭爛額嗎？《小兵來支援》是一款主打合成升級與 Roguelike 策略的創新塔防遊戲。看著別人的小兵都進化成鋼鐵巨獸，自己的還在原地踏步，心裡肯定不是滋味。網路上那些所謂的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兌換碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，領到的獎勵可能還不夠塞牙縫。與其浪費時間，不如考慮 SSbuy 提供的極速</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，讓您的資源瞬間爆倉，想怎麼合就怎麼合，輕鬆打造出讓敵人聞風喪膽的無敵大軍。別再讓您的小兵哭泣了，給他們最好的支援吧！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>還在被滿螢幕的彈幕追著跑，像個無助的原始人嗎？《野龍小隊》是一款結合 Roguelike 與彈幕射擊的恐龍主題手遊。看著別人的恐龍坐騎帥氣噴火，您的龍寶寶還在旁邊玩泥巴，這能忍？網路上流傳的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>和</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兌換碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>早就被領光了，剩下的都是些安慰獎。想讓您的恐龍一步到位，直接進化成食物鏈頂端的掠食者？來試試 SSbuy 最效率的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，用最少的花費換取最大的戰力提升，讓您在彈幕中橫著走。別再躲了，是時候讓對手嚐嚐被龍息支配的恐懼了！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>還在當一隻人見人欺的軟萌史萊姆嗎？《姆姆鬥惡龍: I-SLIME》是一款讓您從最底層開始進化的放置 RPG 手遊。看著排行榜上的大佬們都變成了毀天滅地的魔王，而您還在新手村吞小草，這合理嗎？網路上那些所謂的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>和</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兌換碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，給的資源可能還不夠您升一級。想跳過漫長的農怪過程，直接體驗當 BOSS 的快感？選擇 SSbuy 最優惠的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，讓您的姆姆直接嗑滿經驗藥水，裝備神裝，一步到位。別再慢慢吞了，是時候讓世界見識史萊姆的真正實力了！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>指揮官，您的避難所是不是又被幾隻殭屍小嘍囉給突破了？《BangBang殭屍-避難所戰爭》是一款末日生存塔防手遊。看著別人的防線固若金湯，英雄火力全開，而您的砲塔還在刮痧，這像話嗎？網路上那些早就被領爛的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>和</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兌換碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，給的資源還不夠修補圍牆的缺口。想讓您的避-難所成為殭屍絕不敢靠近的禁區？選擇 SSbuy 最划算的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，讓您的資源直接滿倉，英雄升到頂級，輕鬆體驗割草的快感。別再掙扎求生了，是時候讓殭屍們感受什麼叫做絕望了！</t>
+    </r>
+  </si>
+  <si>
+    <t>https://apps.apple.com/sg/app/%E4%B8%BB%E5%85%AC%E8%B6%85%E6%9C%83%E9%96%83/id6743072374</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>還在煩惱武將不夠力，推圖總是被小兵擋路嗎？《主公超會閃》是一款</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Q </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>版三國題材的放置卡牌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> RPG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，以其輕鬆詼諧的風格和豐富的武將收集系統，帶給玩家無負擔的遊戲樂趣。想要快人一步集齊所有心儀的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Q </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>萌神將，在競技場上大殺四方？除了上網苦苦搜尋那些稀有的禮包碼與兌換碼，不如選擇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> SSbuy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>提供的快速代儲值服務，讓您輕鬆入手核心武將，資源多到用不完。別再靠運氣抽卡了，主公，是時候用實力碾壓全場！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>想在浩瀚的宇宙中建立屬於自己的不朽帝國嗎？《天命</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>群星》是一款史詩級的星際策略手遊，玩家將化身指揮官，發展星球、建立強大艦隊，並與全球玩家展開聯盟對抗或星際戰爭。看著別人的艦隊縱橫星海，而您的艦隊還在母星系掙扎，心裡肯定不是滋味。與其浪費時間尋找那些早已過期的禮包碼和兌換碼，不如直接為您的帝國注入強力資源。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">SSbuy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>提供最安全的代儲值服務，助您快速升級基地、解鎖傳奇艦船，在星際戰爭中取得絕對優勢，實現稱霸宇宙的野望！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/TW.NIKKE</t>
+  </si>
+  <si>
+    <t>https://nikke.hotcool.tw/index.html</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.daerigame.dragon&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://daerisoft.imweb.me/</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/hk/developer/muye-games-co-ltd/id1601609293</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/flashmaster.tw</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E4%B8%BB%E5%85%AC%E8%B6%85%E6%9C%83%E9%96%83/id6743072374?mt=8</t>
+  </si>
+  <si>
+    <t>https://xbdzz-happytime.onelink.me/Qmv0/u7g0i82n</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/MergeKingdomsTW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://portaly.cc/MergeKingdomsTW?fbclid=IwY2xjawMb74dleHRuA2FlbQIxMABicmlkETFLeEF1eXdtQklRS1VnbGxLAR5i6W9gNz787knAKzTMiwdoi1sCnF6v4BvEazgA4Xj9mDASNF1SEDBh_F22cQ_aem_nGkpSYm8-3MmwK4qa3N2dA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/DestinyRisingHMT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.gameshub-online.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1790台幣禮包</t>
+  </si>
+  <si>
+    <t>830台幣禮包</t>
+  </si>
+  <si>
+    <t>270台幣禮包</t>
+  </si>
+  <si>
+    <t>130台幣禮包</t>
+  </si>
+  <si>
+    <t>70台幣禮包</t>
+  </si>
+  <si>
+    <t>2490台幣禮包</t>
+  </si>
+  <si>
+    <t>6480元寶禮包</t>
+  </si>
+  <si>
+    <t>3280元寶禮包</t>
+  </si>
+  <si>
+    <t>1980元寶禮包</t>
+  </si>
+  <si>
+    <t>1280元寶禮包</t>
+  </si>
+  <si>
+    <t>980元寶禮包</t>
+  </si>
+  <si>
+    <t>680元寶禮包</t>
+  </si>
+  <si>
+    <t>600元寶禮包</t>
+  </si>
+  <si>
+    <t>500元寶禮包</t>
+  </si>
+  <si>
+    <t>250元寶禮包</t>
+  </si>
+  <si>
+    <t>180元寶禮包</t>
+  </si>
+  <si>
+    <t>14000元寶</t>
+  </si>
+  <si>
+    <t>6500元寶</t>
+  </si>
+  <si>
+    <t>2500元寶</t>
+  </si>
+  <si>
+    <t>500元寶</t>
+  </si>
+  <si>
+    <t>特惠商店月禮包</t>
+  </si>
+  <si>
+    <t>特惠商店周禮包</t>
+  </si>
+  <si>
+    <t>段位基金</t>
+  </si>
+  <si>
+    <t>3000台幣禮包</t>
+  </si>
+  <si>
+    <t>1500台幣禮包</t>
+  </si>
+  <si>
+    <t>750台幣禮包</t>
+  </si>
+  <si>
+    <t>600台幣禮包</t>
+  </si>
+  <si>
+    <t>450台幣禮包</t>
+  </si>
+  <si>
+    <t>6000銀幣</t>
+  </si>
+  <si>
+    <t>1500銀幣</t>
+  </si>
+  <si>
+    <t>600銀幣</t>
+  </si>
+  <si>
+    <t>300銀幣</t>
+  </si>
+  <si>
+    <t>60銀幣</t>
+  </si>
+  <si>
+    <t>高級通行證</t>
+  </si>
+  <si>
+    <t>高級通行證豪華版</t>
+  </si>
+  <si>
+    <t>NIKKEGIFT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NIKKE1104</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>戰鬥數據輯盒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>信用點盒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點擊主畫面右上角的四個正方形按鈕</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點選「公告」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入「活動一覽」，找到「CDKey兌換入口」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>到信箱領取免費禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>qjzbbbyb</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q醬行前裝備包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>qjbjbyb</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q醬補給包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>qjzbb0728</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q醬行前裝備包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>qjbj0725</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q醬補給包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>qjzbb0721</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q醬行前裝備包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>qjbj0718</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>qjzbb0714</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q醬行前裝備包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>qjbj0711</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲主畫面中點頭像或設定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點禮包碼或兌換碼選項</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>按確定後領取免費禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NN666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NN888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛牛妹專屬禮包1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DD666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DD888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>豆寶專屬禮包1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>豆寶專屬禮包2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛牛妹專屬禮包2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>YUANBB666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>YUANBB888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yunabb專屬禮包1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yunabb專屬禮包2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMCC666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMCC888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>萌萌吃吃專屬禮包1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HZY666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HZY888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>萌萌吃吃專屬禮包2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>河智媛專屬禮包2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>河智媛專屬禮包1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PP666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PP888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘋蘋澎澎專屬禮包1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NL888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘋蘋澎澎專屬禮包2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NL666專屬禮包1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LJ888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>熊寶專屬禮包2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>熊寶專屬禮包1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LJ666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>羅杰專屬禮包1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>羅杰專屬禮包2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZT666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZT888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>曾甜專屬禮包2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XX666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XX888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>曾甜專屬禮包1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>湘湘專屬禮包1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>湘湘專屬禮包2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>qifei666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>飛行員招募卡x5、極地防護夾克x1、萊特卡包x3，以及金幣x5000、體力x20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲中選單點設定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>設定中找到兌換碼</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -15677,7 +16715,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -15902,6 +16940,7 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -16207,7 +17246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ633"/>
+  <dimension ref="A1:AQ632"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" style="1" customWidth="1"/>
@@ -32204,7 +33243,7 @@
         <v>3560</v>
       </c>
       <c r="H191" s="10" t="str">
-        <f t="shared" ref="H191:H254" si="7">IF(A191="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A191)</f>
+        <f t="shared" ref="H191:H253" si="7">IF(A191="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A191)</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=手刀搶英雄</v>
       </c>
       <c r="I191" s="39" t="s">
@@ -32273,7 +33312,7 @@
         <v>3582</v>
       </c>
       <c r="F192" s="8" t="str">
-        <f t="shared" ref="F192:F254" si="8">IF(A192="", "", "gift-codes.html?game=" &amp; A192)</f>
+        <f t="shared" ref="F192:F253" si="8">IF(A192="", "", "gift-codes.html?game=" &amp; A192)</f>
         <v>gift-codes.html?game=荒野亂鬥</v>
       </c>
       <c r="G192" s="23" t="s">
@@ -32286,7 +33325,7 @@
       <c r="I192" s="39" t="s">
         <v>3633</v>
       </c>
-      <c r="J192" s="3" t="s">
+      <c r="J192" s="38" t="s">
         <v>3607</v>
       </c>
       <c r="K192" s="4">
@@ -32350,7 +33389,7 @@
       <c r="I193" s="39" t="s">
         <v>3636</v>
       </c>
-      <c r="J193" s="3" t="s">
+      <c r="J193" s="38" t="s">
         <v>3612</v>
       </c>
       <c r="K193" s="4">
@@ -32417,10 +33456,10 @@
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=破壞突擊隊</v>
       </c>
-      <c r="I194" t="s">
+      <c r="I194" s="30" t="s">
         <v>3634</v>
       </c>
-      <c r="J194" s="3" t="s">
+      <c r="J194" s="38" t="s">
         <v>3624</v>
       </c>
       <c r="K194" s="4">
@@ -32499,10 +33538,10 @@
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=月兔茶屋：悠閒之旅</v>
       </c>
-      <c r="I195" s="2" t="s">
+      <c r="I195" s="39" t="s">
         <v>3635</v>
       </c>
-      <c r="J195" s="3" t="s">
+      <c r="J195" s="38" t="s">
         <v>3624</v>
       </c>
       <c r="K195" s="4">
@@ -32584,7 +33623,7 @@
       <c r="I196" s="39" t="s">
         <v>3647</v>
       </c>
-      <c r="J196" s="3" t="s">
+      <c r="J196" s="38" t="s">
         <v>3648</v>
       </c>
       <c r="K196" s="4">
@@ -32684,7 +33723,7 @@
       <c r="I197" s="39" t="s">
         <v>3661</v>
       </c>
-      <c r="J197" s="3" t="s">
+      <c r="J197" s="38" t="s">
         <v>235</v>
       </c>
       <c r="K197" s="4">
@@ -32778,7 +33817,7 @@
       <c r="I198" s="39" t="s">
         <v>3686</v>
       </c>
-      <c r="J198" s="3" t="s">
+      <c r="J198" s="38" t="s">
         <v>3687</v>
       </c>
       <c r="K198" s="4">
@@ -32842,7 +33881,7 @@
       <c r="I199" s="39" t="s">
         <v>3698</v>
       </c>
-      <c r="J199" s="3" t="s">
+      <c r="J199" s="38" t="s">
         <v>3704</v>
       </c>
       <c r="K199" s="4">
@@ -32897,93 +33936,652 @@
         <v>654</v>
       </c>
     </row>
-    <row r="200" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="19" t="s">
+        <v>3722</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>3754</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>3755</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>3730</v>
+      </c>
       <c r="F200" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=勝利女神：妮姬</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>3737</v>
       </c>
       <c r="H200" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=勝利女神：妮姬</v>
+      </c>
+      <c r="I200" s="39" t="s">
+        <v>3745</v>
+      </c>
+      <c r="J200" s="3" t="s">
+        <v>1428</v>
+      </c>
+      <c r="K200" s="4">
+        <v>2415</v>
+      </c>
+      <c r="L200" s="3" t="s">
+        <v>3766</v>
+      </c>
+      <c r="M200" s="4">
+        <v>1348</v>
+      </c>
+      <c r="N200" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="O200" s="4">
+        <v>735</v>
+      </c>
+      <c r="P200" s="3" t="s">
+        <v>3767</v>
+      </c>
+      <c r="Q200" s="4">
+        <v>621</v>
+      </c>
+      <c r="R200" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="S200" s="4">
+        <v>497</v>
+      </c>
+      <c r="T200" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="U200" s="4">
+        <v>373</v>
+      </c>
+      <c r="V200" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="W200" s="4">
+        <v>248</v>
+      </c>
+      <c r="X200" s="3" t="s">
+        <v>3768</v>
+      </c>
+      <c r="Y200" s="4">
+        <v>199</v>
+      </c>
+      <c r="Z200" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="AA200" s="4">
+        <v>132</v>
+      </c>
+      <c r="AB200" s="3" t="s">
+        <v>3769</v>
+      </c>
+      <c r="AC200" s="4">
+        <v>106</v>
+      </c>
+      <c r="AD200" s="3" t="s">
+        <v>3770</v>
+      </c>
+      <c r="AE200" s="4">
+        <v>53</v>
+      </c>
+      <c r="AF200" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="AG200" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="201" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="19" t="s">
+        <v>3723</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>3685</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>3757</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>3733</v>
+      </c>
       <c r="F201" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=野龍小隊</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>3756</v>
       </c>
       <c r="H201" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=野龍小隊</v>
+      </c>
+      <c r="I201" s="30" t="s">
+        <v>3748</v>
+      </c>
+      <c r="J201" s="3" t="s">
+        <v>3771</v>
+      </c>
+      <c r="K201" s="4">
+        <v>1961</v>
+      </c>
+      <c r="L201" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="M201" s="4">
+        <v>1016</v>
+      </c>
+      <c r="N201" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="O201" s="4">
+        <v>622</v>
+      </c>
+      <c r="P201" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q201" s="4">
+        <v>232</v>
+      </c>
+      <c r="R201" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="S201" s="4">
+        <v>102</v>
+      </c>
+      <c r="T201" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="U201" s="4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="202" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="19" t="s">
+        <v>3724</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>3685</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>3758</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>3736</v>
+      </c>
       <c r="F202" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=BangBang殭屍：避難所戰爭</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>3738</v>
       </c>
       <c r="H202" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=BangBang殭屍：避難所戰爭</v>
+      </c>
+      <c r="I202" s="30" t="s">
+        <v>3750</v>
+      </c>
+      <c r="J202" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="K202" s="4">
+        <v>2355</v>
+      </c>
+      <c r="L202" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="M202" s="4">
+        <v>1174</v>
+      </c>
+      <c r="N202" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="O202" s="4">
+        <v>780</v>
+      </c>
+      <c r="P202" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q202" s="4">
+        <v>551</v>
+      </c>
+      <c r="R202" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="S202" s="4">
+        <v>391</v>
+      </c>
+      <c r="T202" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="U202" s="4">
+        <v>312</v>
+      </c>
+      <c r="V202" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="W202" s="4">
+        <v>256</v>
+      </c>
+      <c r="X202" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y202" s="4">
+        <v>128</v>
+      </c>
+      <c r="Z202" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="AA202" s="4">
+        <v>102</v>
+      </c>
+      <c r="AB202" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="AC202" s="4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="203" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="19" t="s">
+        <v>3725</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>3759</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>3759</v>
+      </c>
+      <c r="E203" s="23" t="s">
+        <v>3751</v>
+      </c>
       <c r="F203" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=主公超會閃</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>3760</v>
       </c>
       <c r="H203" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="204" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=主公超會閃</v>
+      </c>
+      <c r="I203" s="39" t="s">
+        <v>3752</v>
+      </c>
+      <c r="J203" s="3" t="s">
+        <v>3772</v>
+      </c>
+      <c r="K203" s="4">
+        <v>2555</v>
+      </c>
+      <c r="L203" s="3" t="s">
+        <v>3773</v>
+      </c>
+      <c r="M203" s="4">
+        <v>1331</v>
+      </c>
+      <c r="N203" s="3" t="s">
+        <v>3774</v>
+      </c>
+      <c r="O203" s="4">
+        <v>780</v>
+      </c>
+      <c r="P203" s="3" t="s">
+        <v>3775</v>
+      </c>
+      <c r="Q203" s="4">
+        <v>535</v>
+      </c>
+      <c r="R203" s="3" t="s">
+        <v>3776</v>
+      </c>
+      <c r="S203" s="4">
+        <v>391</v>
+      </c>
+      <c r="T203" s="3" t="s">
+        <v>3777</v>
+      </c>
+      <c r="U203" s="4">
+        <v>264</v>
+      </c>
+      <c r="V203" s="3" t="s">
+        <v>3778</v>
+      </c>
+      <c r="W203" s="4">
+        <v>232</v>
+      </c>
+      <c r="X203" s="3" t="s">
+        <v>3779</v>
+      </c>
+      <c r="Y203" s="4">
+        <v>208</v>
+      </c>
+      <c r="Z203" s="3" t="s">
+        <v>3780</v>
+      </c>
+      <c r="AA203" s="4">
+        <v>111</v>
+      </c>
+      <c r="AB203" s="3" t="s">
+        <v>3781</v>
+      </c>
+      <c r="AC203" s="4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="204" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="19" t="s">
+        <v>3726</v>
+      </c>
+      <c r="C204" s="24" t="s">
+        <v>3762</v>
+      </c>
+      <c r="D204" s="23" t="s">
+        <v>3763</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>3732</v>
+      </c>
       <c r="F204" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <f>IF(A204="", "", "gift-codes.html?game=" &amp; A204)</f>
+        <v>gift-codes.html?game=小兵來支援</v>
+      </c>
+      <c r="G204" s="84" t="s">
+        <v>3761</v>
       </c>
       <c r="H204" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <f>IF(A204="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A204)</f>
+        <v>https://www.ssbuy.tw/game-detail.html?game=小兵來支援</v>
+      </c>
+      <c r="I204" s="30" t="s">
+        <v>3747</v>
+      </c>
+      <c r="J204" s="3" t="s">
+        <v>3782</v>
+      </c>
+      <c r="K204" s="4">
+        <v>2555</v>
+      </c>
+      <c r="L204" s="3" t="s">
+        <v>3783</v>
+      </c>
+      <c r="M204" s="4">
+        <v>1331</v>
+      </c>
+      <c r="N204" s="3" t="s">
+        <v>3784</v>
+      </c>
+      <c r="O204" s="4">
+        <v>535</v>
+      </c>
+      <c r="P204" s="3" t="s">
+        <v>3785</v>
+      </c>
+      <c r="Q204" s="4">
+        <v>145</v>
+      </c>
+      <c r="R204" s="3" t="s">
+        <v>3786</v>
+      </c>
+      <c r="S204" s="4">
+        <v>391</v>
+      </c>
+      <c r="T204" s="3" t="s">
+        <v>3787</v>
+      </c>
+      <c r="U204" s="4">
+        <v>780</v>
+      </c>
+      <c r="V204" s="3" t="s">
+        <v>3788</v>
+      </c>
+      <c r="W204" s="4">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="205" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="19" t="s">
+        <v>3727</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>3685</v>
+      </c>
+      <c r="D205" s="23" t="s">
+        <v>3765</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>3734</v>
+      </c>
       <c r="F205" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <f>IF(A205="", "", "gift-codes.html?game=" &amp; A205)</f>
+        <v>gift-codes.html?game=姆姆鬥惡龍</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>3739</v>
       </c>
       <c r="H205" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <f>IF(A205="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A205)</f>
+        <v>https://www.ssbuy.tw/game-detail.html?game=姆姆鬥惡龍</v>
+      </c>
+      <c r="I205" s="30" t="s">
+        <v>3749</v>
+      </c>
+      <c r="J205" s="3" t="s">
+        <v>1428</v>
+      </c>
+      <c r="K205" s="4">
+        <v>2555</v>
+      </c>
+      <c r="L205" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="M205" s="4">
+        <v>1331</v>
+      </c>
+      <c r="N205" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="O205" s="4">
+        <v>780</v>
+      </c>
+      <c r="P205" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q205" s="4">
+        <v>535</v>
+      </c>
+      <c r="R205" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="S205" s="4">
+        <v>391</v>
+      </c>
+      <c r="T205" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="U205" s="4">
+        <v>264</v>
+      </c>
+      <c r="V205" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="W205" s="4">
+        <v>145</v>
+      </c>
+      <c r="X205" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="Y205" s="4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="206" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="19" t="s">
+        <v>3728</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>3743</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>3744</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>3731</v>
+      </c>
       <c r="F206" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <f>IF(A206="", "", "gift-codes.html?game=" &amp; A206)</f>
+        <v>gift-codes.html?game=發條特攻隊</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>3742</v>
       </c>
       <c r="H206" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="207" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <f>IF(A206="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A206)</f>
+        <v>https://www.ssbuy.tw/game-detail.html?game=發條特攻隊</v>
+      </c>
+      <c r="I206" s="30" t="s">
+        <v>3746</v>
+      </c>
+      <c r="J206" s="3" t="s">
+        <v>3789</v>
+      </c>
+      <c r="K206" s="4">
+        <v>2363</v>
+      </c>
+      <c r="L206" s="3" t="s">
+        <v>3790</v>
+      </c>
+      <c r="M206" s="4">
+        <v>1182</v>
+      </c>
+      <c r="N206" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="O206" s="4">
+        <v>780</v>
+      </c>
+      <c r="P206" s="3" t="s">
+        <v>3791</v>
+      </c>
+      <c r="Q206" s="4">
+        <v>599</v>
+      </c>
+      <c r="R206" s="3" t="s">
+        <v>3792</v>
+      </c>
+      <c r="S206" s="4">
+        <v>479</v>
+      </c>
+      <c r="T206" s="3" t="s">
+        <v>3793</v>
+      </c>
+      <c r="U206" s="4">
+        <v>359</v>
+      </c>
+      <c r="V206" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="W206" s="4">
+        <v>240</v>
+      </c>
+      <c r="X206" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y206" s="4">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="207" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="19" t="s">
+        <v>3729</v>
+      </c>
+      <c r="C207" s="24" t="s">
+        <v>3764</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>3740</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>3741</v>
+      </c>
       <c r="F207" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <f>IF(A207="", "", "gift-codes.html?game=" &amp; A207)</f>
+        <v>gift-codes.html?game=天命：群星</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>3735</v>
       </c>
       <c r="H207" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <f>IF(A207="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A207)</f>
+        <v>https://www.ssbuy.tw/game-detail.html?game=天命：群星</v>
+      </c>
+      <c r="I207" s="39" t="s">
+        <v>3753</v>
+      </c>
+      <c r="J207" s="3" t="s">
+        <v>3794</v>
+      </c>
+      <c r="K207" s="4">
+        <v>2363</v>
+      </c>
+      <c r="L207" s="3" t="s">
+        <v>3794</v>
+      </c>
+      <c r="M207" s="4">
+        <v>1182</v>
+      </c>
+      <c r="N207" s="3" t="s">
+        <v>3795</v>
+      </c>
+      <c r="O207" s="4">
+        <v>599</v>
+      </c>
+      <c r="P207" s="3" t="s">
+        <v>3796</v>
+      </c>
+      <c r="Q207" s="4">
+        <v>240</v>
+      </c>
+      <c r="R207" s="3" t="s">
+        <v>3797</v>
+      </c>
+      <c r="S207" s="4">
+        <v>128</v>
+      </c>
+      <c r="T207" s="3" t="s">
+        <v>3798</v>
+      </c>
+      <c r="U207" s="4">
+        <v>26</v>
+      </c>
+      <c r="V207" s="3" t="s">
+        <v>3799</v>
+      </c>
+      <c r="W207" s="4">
+        <v>128</v>
+      </c>
+      <c r="X207" s="3" t="s">
+        <v>3800</v>
+      </c>
+      <c r="Y207" s="4">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="208" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="19"/>
       <c r="F208" s="8" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(A208="", "", "gift-codes.html?game=" &amp; A208)</f>
         <v/>
       </c>
       <c r="H208" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(A208="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A208)</f>
         <v/>
       </c>
     </row>
@@ -33137,7 +34735,7 @@
         <v/>
       </c>
     </row>
-    <row r="224" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="6:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F224" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -33197,7 +34795,7 @@
         <v/>
       </c>
     </row>
-    <row r="230" spans="6:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F230" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -33439,21 +35037,21 @@
     </row>
     <row r="254" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F254" s="8" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="F254:F317" si="9">IF(A254="", "", "gift-codes.html?game=" &amp; A254)</f>
         <v/>
       </c>
       <c r="H254" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="H254:H317" si="10">IF(A254="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A254)</f>
         <v/>
       </c>
     </row>
     <row r="255" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F255" s="8" t="str">
-        <f t="shared" ref="F255:F318" si="9">IF(A255="", "", "gift-codes.html?game=" &amp; A255)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="H255" s="10" t="str">
-        <f t="shared" ref="H255:H318" si="10">IF(A255="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A255)</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34079,21 +35677,21 @@
     </row>
     <row r="318" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F318" s="8" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="F318:F381" si="11">IF(A318="", "", "gift-codes.html?game=" &amp; A318)</f>
         <v/>
       </c>
       <c r="H318" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="H318:H381" si="12">IF(A318="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A318)</f>
         <v/>
       </c>
     </row>
     <row r="319" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F319" s="8" t="str">
-        <f t="shared" ref="F319:F382" si="11">IF(A319="", "", "gift-codes.html?game=" &amp; A319)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H319" s="10" t="str">
-        <f t="shared" ref="H319:H382" si="12">IF(A319="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A319)</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -34719,21 +36317,21 @@
     </row>
     <row r="382" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F382" s="8" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="F382:F445" si="13">IF(A382="", "", "gift-codes.html?game=" &amp; A382)</f>
         <v/>
       </c>
       <c r="H382" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="H382:H445" si="14">IF(A382="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A382)</f>
         <v/>
       </c>
     </row>
     <row r="383" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F383" s="8" t="str">
-        <f t="shared" ref="F383:F446" si="13">IF(A383="", "", "gift-codes.html?game=" &amp; A383)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="H383" s="10" t="str">
-        <f t="shared" ref="H383:H446" si="14">IF(A383="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A383)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -35359,21 +36957,21 @@
     </row>
     <row r="446" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F446" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="F446:F509" si="15">IF(A446="", "", "gift-codes.html?game=" &amp; A446)</f>
         <v/>
       </c>
       <c r="H446" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="H446:H509" si="16">IF(A446="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A446)</f>
         <v/>
       </c>
     </row>
     <row r="447" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F447" s="8" t="str">
-        <f t="shared" ref="F447:F510" si="15">IF(A447="", "", "gift-codes.html?game=" &amp; A447)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H447" s="10" t="str">
-        <f t="shared" ref="H447:H510" si="16">IF(A447="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A447)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -35999,21 +37597,21 @@
     </row>
     <row r="510" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F510" s="8" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="F510:F573" si="17">IF(A510="", "", "gift-codes.html?game=" &amp; A510)</f>
         <v/>
       </c>
       <c r="H510" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="H510:H573" si="18">IF(A510="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A510)</f>
         <v/>
       </c>
     </row>
     <row r="511" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F511" s="8" t="str">
-        <f t="shared" ref="F511:F574" si="17">IF(A511="", "", "gift-codes.html?game=" &amp; A511)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H511" s="10" t="str">
-        <f t="shared" ref="H511:H574" si="18">IF(A511="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A511)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -36639,21 +38237,21 @@
     </row>
     <row r="574" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F574" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="F574:F576" si="19">IF(A574="", "", "gift-codes.html?game=" &amp; A574)</f>
         <v/>
       </c>
       <c r="H574" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="H574:H632" si="20">IF(A574="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A574)</f>
         <v/>
       </c>
     </row>
     <row r="575" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F575" s="8" t="str">
-        <f t="shared" ref="F575:F577" si="19">IF(A575="", "", "gift-codes.html?game=" &amp; A575)</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H575" s="10" t="str">
-        <f t="shared" ref="H575:H633" si="20">IF(A575="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A575)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -36667,101 +38265,97 @@
         <v/>
       </c>
     </row>
-    <row r="577" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="F577" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
+    <row r="577" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H577" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="578" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="578" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H578" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="579" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="579" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H579" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="580" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="580" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H580" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="581" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="581" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H581" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="582" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="582" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H582" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="583" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="583" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H583" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="584" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="584" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H584" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="585" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="585" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H585" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="586" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="586" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H586" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="587" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="587" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H587" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="588" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="588" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H588" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="589" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="589" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H589" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="590" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="590" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H590" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="591" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="591" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H591" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="592" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="592" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H592" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -37003,12 +38597,6 @@
     </row>
     <row r="632" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H632" s="10" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="633" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="H633" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -37079,15 +38667,21 @@
     <hyperlink ref="E199" r:id="rId60"/>
     <hyperlink ref="D199" r:id="rId61"/>
     <hyperlink ref="C199" r:id="rId62"/>
+    <hyperlink ref="E203" r:id="rId63"/>
+    <hyperlink ref="G204" r:id="rId64" display="https://xbdzz-happytime.onelink.me/Qmv0/u7g0i82n?fbclid=IwZXh0bgNhZW0CMTAAYnJpZBExS3hBdXl3bUJJUUtVZ2xsSwEeUs-bWAhlY_UCiRiKxe1XXAQMZW7G7ZLu6k4Nz3va8Qwuburf2qH8D17Nxw4_aem_m3uaLESoBQce2a_nJHdw8Q"/>
+    <hyperlink ref="C204" r:id="rId65"/>
+    <hyperlink ref="D204" r:id="rId66"/>
+    <hyperlink ref="C207" r:id="rId67"/>
+    <hyperlink ref="D205" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId63"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId69"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AX441"/>
+  <dimension ref="A1:AX440"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="19.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.375" style="49" customWidth="1"/>
@@ -49151,11 +50745,11 @@
         <v>手刀搶英雄</v>
       </c>
       <c r="C191" s="49" t="str">
-        <f t="shared" ref="C191:C254" si="7">IF(A191="","", "giftcodesbanner/" &amp; A191 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" ref="C191:C253" si="7">IF(A191="","", "giftcodesbanner/" &amp; A191 &amp; "-禮包碼.jpg")</f>
         <v>giftcodesbanner/手刀搶英雄-禮包碼.jpg</v>
       </c>
       <c r="D191" s="49" t="str">
-        <f t="shared" ref="D191:D254" si="8">IF(A191="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A191)</f>
+        <f t="shared" ref="D191:D253" si="8">IF(A191="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A191)</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=手刀搶英雄</v>
       </c>
       <c r="E191" s="50" t="str">
@@ -49232,7 +50826,7 @@
         <v>2666</v>
       </c>
     </row>
-    <row r="193" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="49" t="str">
         <f>IF(games!A193="", "", games!A193)</f>
         <v>遺忘之劍</v>
@@ -49292,7 +50886,7 @@
         <v>3604</v>
       </c>
     </row>
-    <row r="194" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="49" t="str">
         <f>IF(games!A194="", "", games!A194)</f>
         <v>破壞突擊隊</v>
@@ -49334,7 +50928,7 @@
         <v>2666</v>
       </c>
     </row>
-    <row r="195" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="49" t="str">
         <f>IF(games!A195="", "", games!A195)</f>
         <v>月兔茶屋：悠閒之旅</v>
@@ -49376,7 +50970,7 @@
         <v>2666</v>
       </c>
     </row>
-    <row r="196" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="49" t="str">
         <f>IF(games!A196="", "", games!A196)</f>
         <v>吞食天地 虛擬世界</v>
@@ -49412,7 +51006,7 @@
         <v>3643</v>
       </c>
     </row>
-    <row r="197" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="49" t="str">
         <f>IF(games!A197="", "", games!A197)</f>
         <v>封神：蒼嵐契約</v>
@@ -49490,7 +51084,7 @@
         <v>3668</v>
       </c>
     </row>
-    <row r="198" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="49" t="str">
         <f>IF(games!A198="", "", games!A198)</f>
         <v>Gear Fight!</v>
@@ -49532,7 +51126,7 @@
         <v>2666</v>
       </c>
     </row>
-    <row r="199" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="49" t="str">
         <f>IF(games!A199="", "", games!A199)</f>
         <v>救世者之樹 M</v>
@@ -49610,123 +51204,466 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="200" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="49" t="str">
         <f>IF(games!A200="", "", games!A200)</f>
-        <v/>
+        <v>勝利女神：妮姬</v>
       </c>
       <c r="C200" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/勝利女神：妮姬-禮包碼.jpg</v>
       </c>
       <c r="D200" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=勝利女神：妮姬</v>
       </c>
       <c r="E200" s="50" t="str">
         <f>IF(games!I200&lt;&gt;"", games!I200, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>還在為推不過戰役、只能在指揮中心望著老婆嘆氣而煩惱嗎？《勝利女神：妮姬》是一款以末世為背景的第三人稱射擊RPG，主打精美的角色立繪與爽快的射擊手感。想讓您的妮姬戰力突飛猛進，不再被萊徹按在地上摩擦？除了到處跪求那些虛無飄渺的禮包碼與兌換碼，不如來點實際的。SSbuy 提供最專業的代儲值服務，讓您用最划算的價格武裝您的老婆們，輕鬆突破160等級的高牆，別再猶豫了，指揮官，是時候讓她們見識真正的火力了！</v>
+      </c>
+      <c r="F200" s="70" t="s">
+        <v>3805</v>
+      </c>
+      <c r="G200" s="49" t="s">
+        <v>3806</v>
+      </c>
+      <c r="H200" s="49" t="s">
+        <v>3807</v>
+      </c>
+      <c r="I200" s="49" t="s">
+        <v>2651</v>
+      </c>
+      <c r="J200" s="50" t="s">
+        <v>3808</v>
+      </c>
+      <c r="K200" s="53" t="s">
+        <v>3801</v>
+      </c>
+      <c r="L200" s="49" t="s">
+        <v>3803</v>
+      </c>
+      <c r="M200" s="54" t="s">
+        <v>3802</v>
+      </c>
+      <c r="N200" s="49" t="s">
+        <v>3804</v>
+      </c>
+    </row>
+    <row r="201" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="49" t="str">
         <f>IF(games!A201="", "", games!A201)</f>
-        <v/>
+        <v>野龍小隊</v>
       </c>
       <c r="C201" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/野龍小隊-禮包碼.jpg</v>
       </c>
       <c r="D201" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>https://www.ssbuy.tw/gift-codes.html?game=野龍小隊</v>
+      </c>
+      <c r="E201" s="50" t="str">
+        <f>IF(games!I201&lt;&gt;"", games!I201, "")</f>
+        <v>還在被滿螢幕的彈幕追著跑，像個無助的原始人嗎？《野龍小隊》是一款結合 Roguelike 與彈幕射擊的恐龍主題手遊。看著別人的恐龍坐騎帥氣噴火，您的龍寶寶還在旁邊玩泥巴，這能忍？網路上流傳的禮包碼和兌換碼早就被領光了，剩下的都是些安慰獎。想讓您的恐龍一步到位，直接進化成食物鏈頂端的掠食者？來試試 SSbuy 最效率的代儲值，用最少的花費換取最大的戰力提升，讓您在彈幕中橫著走。別再躲了，是時候讓對手嚐嚐被龍息支配的恐懼了！</v>
+      </c>
+      <c r="F201" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="G201" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="H201" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="I201" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K201" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L201" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M201" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="N201" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="202" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="49" t="str">
         <f>IF(games!A202="", "", games!A202)</f>
-        <v/>
+        <v>BangBang殭屍：避難所戰爭</v>
       </c>
       <c r="C202" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/BangBang殭屍：避難所戰爭-禮包碼.jpg</v>
       </c>
       <c r="D202" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>https://www.ssbuy.tw/gift-codes.html?game=BangBang殭屍：避難所戰爭</v>
+      </c>
+      <c r="E202" s="50" t="str">
+        <f>IF(games!I202&lt;&gt;"", games!I202, "")</f>
+        <v>指揮官，您的避難所是不是又被幾隻殭屍小嘍囉給突破了？《BangBang殭屍-避難所戰爭》是一款末日生存塔防手遊。看著別人的防線固若金湯，英雄火力全開，而您的砲塔還在刮痧，這像話嗎？網路上那些早就被領爛的禮包碼和兌換碼，給的資源還不夠修補圍牆的缺口。想讓您的避-難所成為殭屍絕不敢靠近的禁區？選擇 SSbuy 最划算的代儲值服務，讓您的資源直接滿倉，英雄升到頂級，輕鬆體驗割草的快感。別再掙扎求生了，是時候讓殭屍們感受什麼叫做絕望了！</v>
+      </c>
+      <c r="F202" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="G202" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="H202" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="I202" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K202" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L202" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M202" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="N202" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="203" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="49" t="str">
         <f>IF(games!A203="", "", games!A203)</f>
-        <v/>
+        <v>主公超會閃</v>
       </c>
       <c r="C203" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/主公超會閃-禮包碼.jpg</v>
       </c>
       <c r="D203" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="204" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>https://www.ssbuy.tw/gift-codes.html?game=主公超會閃</v>
+      </c>
+      <c r="E203" s="50" t="str">
+        <f>IF(games!I203&lt;&gt;"", games!I203, "")</f>
+        <v>還在煩惱武將不夠力，推圖總是被小兵擋路嗎？《主公超會閃》是一款 Q 版三國題材的放置卡牌 RPG，以其輕鬆詼諧的風格和豐富的武將收集系統，帶給玩家無負擔的遊戲樂趣。想要快人一步集齊所有心儀的 Q 萌神將，在競技場上大殺四方？除了上網苦苦搜尋那些稀有的禮包碼與兌換碼，不如選擇 SSbuy 提供的快速代儲值服務，讓您輕鬆入手核心武將，資源多到用不完。別再靠運氣抽卡了，主公，是時候用實力碾壓全場！</v>
+      </c>
+      <c r="F203" s="70" t="s">
+        <v>3823</v>
+      </c>
+      <c r="G203" s="49" t="s">
+        <v>3824</v>
+      </c>
+      <c r="H203" s="49" t="s">
+        <v>2651</v>
+      </c>
+      <c r="I203" s="49" t="s">
+        <v>3825</v>
+      </c>
+      <c r="K203" s="53" t="s">
+        <v>3809</v>
+      </c>
+      <c r="L203" s="49" t="s">
+        <v>3810</v>
+      </c>
+      <c r="M203" s="54" t="s">
+        <v>3811</v>
+      </c>
+      <c r="N203" s="49" t="s">
+        <v>3812</v>
+      </c>
+      <c r="O203" s="54" t="s">
+        <v>3813</v>
+      </c>
+      <c r="P203" s="49" t="s">
+        <v>3814</v>
+      </c>
+      <c r="Q203" s="54" t="s">
+        <v>3815</v>
+      </c>
+      <c r="R203" s="49" t="s">
+        <v>3816</v>
+      </c>
+      <c r="S203" s="54" t="s">
+        <v>3817</v>
+      </c>
+      <c r="T203" s="49" t="s">
+        <v>3818</v>
+      </c>
+      <c r="U203" s="54" t="s">
+        <v>3819</v>
+      </c>
+      <c r="V203" s="49" t="s">
+        <v>3816</v>
+      </c>
+      <c r="W203" s="54" t="s">
+        <v>3820</v>
+      </c>
+      <c r="X203" s="49" t="s">
+        <v>3821</v>
+      </c>
+      <c r="Y203" s="54" t="s">
+        <v>3822</v>
+      </c>
+      <c r="Z203" s="49" t="s">
+        <v>3816</v>
+      </c>
+    </row>
+    <row r="204" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="49" t="str">
         <f>IF(games!A204="", "", games!A204)</f>
-        <v/>
+        <v>小兵來支援</v>
       </c>
       <c r="C204" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/小兵來支援-禮包碼.jpg</v>
       </c>
       <c r="D204" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>https://www.ssbuy.tw/gift-codes.html?game=小兵來支援</v>
+      </c>
+      <c r="E204" s="50" t="str">
+        <f>IF(games!I204&lt;&gt;"", games!I204, "")</f>
+        <v>指揮官，您還在為守不住那幾波小怪而焦頭爛額嗎？《小兵來支援》是一款主打合成升級與 Roguelike 策略的創新塔防遊戲。看著別人的小兵都進化成鋼鐵巨獸，自己的還在原地踏步，心裡肯定不是滋味。網路上那些所謂的禮包碼、兌換碼，領到的獎勵可能還不夠塞牙縫。與其浪費時間，不如考慮 SSbuy 提供的極速代儲值服務，讓您的資源瞬間爆倉，想怎麼合就怎麼合，輕鬆打造出讓敵人聞風喪膽的無敵大軍。別再讓您的小兵哭泣了，給他們最好的支援吧！</v>
+      </c>
+      <c r="K204" s="53" t="s">
+        <v>3826</v>
+      </c>
+      <c r="L204" s="49" t="s">
+        <v>3828</v>
+      </c>
+      <c r="M204" s="54" t="s">
+        <v>3827</v>
+      </c>
+      <c r="N204" s="49" t="s">
+        <v>3833</v>
+      </c>
+      <c r="O204" s="54" t="s">
+        <v>3829</v>
+      </c>
+      <c r="P204" s="49" t="s">
+        <v>3831</v>
+      </c>
+      <c r="Q204" s="54" t="s">
+        <v>3830</v>
+      </c>
+      <c r="R204" s="49" t="s">
+        <v>3832</v>
+      </c>
+      <c r="S204" s="54" t="s">
+        <v>3834</v>
+      </c>
+      <c r="T204" s="49" t="s">
+        <v>3836</v>
+      </c>
+      <c r="U204" s="54" t="s">
+        <v>3835</v>
+      </c>
+      <c r="V204" s="49" t="s">
+        <v>3837</v>
+      </c>
+      <c r="W204" s="54" t="s">
+        <v>3838</v>
+      </c>
+      <c r="X204" s="49" t="s">
+        <v>3840</v>
+      </c>
+      <c r="Y204" s="54" t="s">
+        <v>3839</v>
+      </c>
+      <c r="Z204" s="49" t="s">
+        <v>3843</v>
+      </c>
+      <c r="AA204" s="54" t="s">
+        <v>3841</v>
+      </c>
+      <c r="AB204" s="49" t="s">
+        <v>3845</v>
+      </c>
+      <c r="AC204" s="54" t="s">
+        <v>3842</v>
+      </c>
+      <c r="AD204" s="49" t="s">
+        <v>3844</v>
+      </c>
+      <c r="AE204" s="54" t="s">
+        <v>3846</v>
+      </c>
+      <c r="AF204" s="49" t="s">
+        <v>3848</v>
+      </c>
+      <c r="AG204" s="54" t="s">
+        <v>3847</v>
+      </c>
+      <c r="AH204" s="49" t="s">
+        <v>3850</v>
+      </c>
+      <c r="AI204" s="54" t="s">
+        <v>3851</v>
+      </c>
+      <c r="AJ204" s="49" t="s">
+        <v>3854</v>
+      </c>
+      <c r="AK204" s="54" t="s">
+        <v>3849</v>
+      </c>
+      <c r="AL204" s="49" t="s">
+        <v>3853</v>
+      </c>
+      <c r="AM204" s="54" t="s">
+        <v>3855</v>
+      </c>
+      <c r="AN204" s="49" t="s">
+        <v>3856</v>
+      </c>
+      <c r="AO204" s="54" t="s">
+        <v>3852</v>
+      </c>
+      <c r="AP204" s="49" t="s">
+        <v>3857</v>
+      </c>
+      <c r="AQ204" s="54" t="s">
+        <v>3858</v>
+      </c>
+      <c r="AR204" s="49" t="s">
+        <v>3863</v>
+      </c>
+      <c r="AS204" s="54" t="s">
+        <v>3859</v>
+      </c>
+      <c r="AT204" s="49" t="s">
+        <v>3860</v>
+      </c>
+      <c r="AU204" s="54" t="s">
+        <v>3861</v>
+      </c>
+      <c r="AV204" s="49" t="s">
+        <v>3864</v>
+      </c>
+      <c r="AW204" s="54" t="s">
+        <v>3862</v>
+      </c>
+      <c r="AX204" s="49" t="s">
+        <v>3865</v>
+      </c>
+    </row>
+    <row r="205" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="49" t="str">
         <f>IF(games!A205="", "", games!A205)</f>
-        <v/>
+        <v>姆姆鬥惡龍</v>
       </c>
       <c r="C205" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/姆姆鬥惡龍-禮包碼.jpg</v>
       </c>
       <c r="D205" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>https://www.ssbuy.tw/gift-codes.html?game=姆姆鬥惡龍</v>
+      </c>
+      <c r="E205" s="50" t="str">
+        <f>IF(games!I205&lt;&gt;"", games!I205, "")</f>
+        <v>還在當一隻人見人欺的軟萌史萊姆嗎？《姆姆鬥惡龍: I-SLIME》是一款讓您從最底層開始進化的放置 RPG 手遊。看著排行榜上的大佬們都變成了毀天滅地的魔王，而您還在新手村吞小草，這合理嗎？網路上那些所謂的禮包碼和兌換碼，給的資源可能還不夠您升一級。想跳過漫長的農怪過程，直接體驗當 BOSS 的快感？選擇 SSbuy 最優惠的代儲值服務，讓您的姆姆直接嗑滿經驗藥水，裝備神裝，一步到位。別再慢慢吞了，是時候讓世界見識史萊姆的真正實力了！</v>
+      </c>
+      <c r="F205" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="G205" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="H205" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="I205" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K205" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L205" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M205" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="N205" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="206" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="49" t="str">
         <f>IF(games!A206="", "", games!A206)</f>
-        <v/>
+        <v>發條特攻隊</v>
       </c>
       <c r="C206" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/發條特攻隊-禮包碼.jpg</v>
       </c>
       <c r="D206" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="207" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>https://www.ssbuy.tw/gift-codes.html?game=發條特攻隊</v>
+      </c>
+      <c r="E206" s="50" t="str">
+        <f>IF(games!I206&lt;&gt;"", games!I206, "")</f>
+        <v>別再看著別人的玩具大軍流口水了！《發條特攻隊》是一款充滿策略性的 Roguelike 塔防手遊，玩家將指揮可愛的玩具英雄抵禦一波波的敵人攻勢。是不是覺得自己的玩具箱總比別人空？抽來抽去都是些派不上用場的雜兵？與其大海撈針般地搜尋那些不知道過期了沒的禮包碼和兌換碼，不如直接釜底抽薪。選擇 SSbuy 最可靠的代儲值服務，讓您有足夠的資源抽到心儀的傳奇玩具，輕鬆碾壓對手。別再當陪跑的龍套了，是時候讓您的玩具成為全場最靚的仔！</v>
+      </c>
+      <c r="F206" s="70" t="s">
+        <v>3868</v>
+      </c>
+      <c r="G206" s="49" t="s">
+        <v>3869</v>
+      </c>
+      <c r="H206" s="49" t="s">
+        <v>2651</v>
+      </c>
+      <c r="I206" s="49" t="s">
+        <v>3825</v>
+      </c>
+      <c r="K206" s="53" t="s">
+        <v>3866</v>
+      </c>
+      <c r="L206" s="49" t="s">
+        <v>3867</v>
+      </c>
+    </row>
+    <row r="207" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="49" t="str">
         <f>IF(games!A207="", "", games!A207)</f>
-        <v/>
+        <v>天命：群星</v>
       </c>
       <c r="C207" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/天命：群星-禮包碼.jpg</v>
       </c>
       <c r="D207" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>https://www.ssbuy.tw/gift-codes.html?game=天命：群星</v>
+      </c>
+      <c r="E207" s="50" t="str">
+        <f>IF(games!I207&lt;&gt;"", games!I207, "")</f>
+        <v>想在浩瀚的宇宙中建立屬於自己的不朽帝國嗎？《天命:群星》是一款史詩級的星際策略手遊，玩家將化身指揮官，發展星球、建立強大艦隊，並與全球玩家展開聯盟對抗或星際戰爭。看著別人的艦隊縱橫星海，而您的艦隊還在母星系掙扎，心裡肯定不是滋味。與其浪費時間尋找那些早已過期的禮包碼和兌換碼，不如直接為您的帝國注入強力資源。SSbuy 提供最安全的代儲值服務，助您快速升級基地、解鎖傳奇艦船，在星際戰爭中取得絕對優勢，實現稱霸宇宙的野望！</v>
+      </c>
+      <c r="F207" s="70" t="s">
+        <v>3823</v>
+      </c>
+      <c r="G207" s="49" t="s">
+        <v>3824</v>
+      </c>
+      <c r="H207" s="49" t="s">
+        <v>2651</v>
+      </c>
+      <c r="I207" s="49" t="s">
+        <v>3825</v>
+      </c>
+      <c r="K207" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L207" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="208" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="49" t="str">
         <f>IF(games!A208="", "", games!A208)</f>
         <v/>
@@ -49739,8 +51676,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="209" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E208" s="50" t="str">
+        <f>IF(games!I208&lt;&gt;"", games!I208, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="49" t="str">
         <f>IF(games!A209="", "", games!A209)</f>
         <v/>
@@ -49753,8 +51694,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="210" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E209" s="50" t="str">
+        <f>IF(games!I209&lt;&gt;"", games!I209, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="49" t="str">
         <f>IF(games!A210="", "", games!A210)</f>
         <v/>
@@ -49767,8 +51712,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="211" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E210" s="50" t="str">
+        <f>IF(games!I210&lt;&gt;"", games!I210, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="49" t="str">
         <f>IF(games!A211="", "", games!A211)</f>
         <v/>
@@ -49781,8 +51730,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="212" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E211" s="50" t="str">
+        <f>IF(games!I211&lt;&gt;"", games!I211, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="49" t="str">
         <f>IF(games!A212="", "", games!A212)</f>
         <v/>
@@ -49795,8 +51748,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="213" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E212" s="50" t="str">
+        <f>IF(games!I212&lt;&gt;"", games!I212, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="49" t="str">
         <f>IF(games!A213="", "", games!A213)</f>
         <v/>
@@ -49809,8 +51766,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="214" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E213" s="50" t="str">
+        <f>IF(games!I213&lt;&gt;"", games!I213, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="49" t="str">
         <f>IF(games!A214="", "", games!A214)</f>
         <v/>
@@ -49823,8 +51784,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="215" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E214" s="50" t="str">
+        <f>IF(games!I214&lt;&gt;"", games!I214, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="49" t="str">
         <f>IF(games!A215="", "", games!A215)</f>
         <v/>
@@ -49838,7 +51803,7 @@
         <v/>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="49" t="str">
         <f>IF(games!A216="", "", games!A216)</f>
         <v/>
@@ -49852,7 +51817,7 @@
         <v/>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="49" t="str">
         <f>IF(games!A217="", "", games!A217)</f>
         <v/>
@@ -49866,7 +51831,7 @@
         <v/>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="49" t="str">
         <f>IF(games!A218="", "", games!A218)</f>
         <v/>
@@ -49880,7 +51845,7 @@
         <v/>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="49" t="str">
         <f>IF(games!A219="", "", games!A219)</f>
         <v/>
@@ -49894,7 +51859,7 @@
         <v/>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="49" t="str">
         <f>IF(games!A220="", "", games!A220)</f>
         <v/>
@@ -49908,7 +51873,7 @@
         <v/>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="49" t="str">
         <f>IF(games!A221="", "", games!A221)</f>
         <v/>
@@ -49922,7 +51887,7 @@
         <v/>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="49" t="str">
         <f>IF(games!A222="", "", games!A222)</f>
         <v/>
@@ -49936,11 +51901,7 @@
         <v/>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="49" t="str">
-        <f>IF(games!A223="", "", games!A223)</f>
-        <v/>
-      </c>
+    <row r="223" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C223" s="49" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -49950,7 +51911,7 @@
         <v/>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C224" s="49" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -50252,21 +52213,21 @@
     </row>
     <row r="254" spans="3:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C254" s="49" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C254:C317" si="9">IF(A254="","", "giftcodesbanner/" &amp; A254 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D254" s="49" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="D254:D317" si="10">IF(A254="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A254)</f>
         <v/>
       </c>
     </row>
     <row r="255" spans="3:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C255" s="49" t="str">
-        <f t="shared" ref="C255:C318" si="9">IF(A255="","", "giftcodesbanner/" &amp; A255 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="D255" s="49" t="str">
-        <f t="shared" ref="D255:D318" si="10">IF(A255="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A255)</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -50310,7 +52271,7 @@
         <v/>
       </c>
     </row>
-    <row r="260" spans="3:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C260" s="49" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -50892,21 +52853,21 @@
     </row>
     <row r="318" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C318" s="49" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="C318:C381" si="11">IF(A318="","", "giftcodesbanner/" &amp; A318 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D318" s="49" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="D318:D381" si="12">IF(A318="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A318)</f>
         <v/>
       </c>
     </row>
     <row r="319" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C319" s="49" t="str">
-        <f t="shared" ref="C319:C382" si="11">IF(A319="","", "giftcodesbanner/" &amp; A319 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="D319" s="49" t="str">
-        <f t="shared" ref="D319:D382" si="12">IF(A319="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A319)</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -51532,21 +53493,21 @@
     </row>
     <row r="382" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C382" s="49" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="C382:C440" si="13">IF(A382="","", "giftcodesbanner/" &amp; A382 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D382" s="49" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="D382:D440" si="14">IF(A382="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A382)</f>
         <v/>
       </c>
     </row>
     <row r="383" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C383" s="49" t="str">
-        <f t="shared" ref="C383:C441" si="13">IF(A383="","", "giftcodesbanner/" &amp; A383 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D383" s="49" t="str">
-        <f t="shared" ref="D383:D441" si="14">IF(A383="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A383)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -52116,16 +54077,6 @@
         <v/>
       </c>
       <c r="D440" s="49" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="441" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C441" s="49" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="D441" s="49" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5766" uniqueCount="3870">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5837" uniqueCount="3923">
   <si>
     <t>Facebook</t>
   </si>
@@ -16361,6 +16361,290 @@
   <si>
     <t>設定中找到兌換碼</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>血影雙生</t>
+  </si>
+  <si>
+    <t>我的勇者外傳</t>
+  </si>
+  <si>
+    <t>女神契約：異世界遠征隊</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E6%88%91%E7%9A%84%E5%8B%87%E8%80%85%E5%A4%96%E5%82%B3/id6743834900</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.rsg.mystw&amp;fbclid=IwY2xjawMdUrlleHRuA2FlbQIxMABicmlkETFsdjc5bjFlVXI0Q2JGc201AR4MjK_64cfYC1z3AKt2sHu5YlVCHD4kYvZlgD4SWNMm5-6ZiS6uVTiriGoiFA_aem_ci-3pwxxWolXcoC97O3JAg</t>
+  </si>
+  <si>
+    <t>https://myheroes.v-brick.com.tw/act/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/myheroessidestory</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.mover.twds&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/PandaG0</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/us/app/%E5%A5%B3%E7%A5%9E%E5%A5%91%E7%B4%84-%E7%95%B0%E4%B8%96%E7%95%8C%E9%81%A0%E5%BE%81%E9%98%9F/id6747697091</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.spt.goddness</t>
+  </si>
+  <si>
+    <t>https://www.phecdagames.com/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/BloodTwins.mover</t>
+  </si>
+  <si>
+    <t>https://bloodtwins.movergames.com/?utm_source=fbfans&amp;utm_medium=fbfans&amp;utm_campaign=fbtosite0827&amp;fbclid=IwY2xjawMdVApleHRuA2FlbQIxMABicmlkETFtTWVLZFVVYmk1MVN0T2JsAR6wCHM8tphZpKMilOVChsFZGeNWi0KWHvr7AiBad-q-1K8cOdzKAzBCPEFGew_aem_LPrQ_KqTLOUfU5m_do5VDg</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E8%A1%80%E5%BD%B1%E9%9B%99%E7%94%9F/id6746142055</t>
+  </si>
+  <si>
+    <t>勇者集結</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>勇者無敵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*500+血源礦*200</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘技能幣*10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>歡迎來到《血影雙生》，一款讓你再度體驗上班打卡的東方幻想</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MMORPG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。遊戲主打獨特的「雙生」系統，讓你在兩種職業間切換自如，彷彿在提醒你現實中也得是個多功能的社畜。每天上線就是無盡的任務、副本和戰場，享受被數值統治的快感。覺得戰力升太慢？官方貼心準備了各種禮包碼與兌換碼，給你一點甜頭，讓你產生自己很強的錯覺。當然，想在伺服器裡抬頭挺胸，成為別人口中的大佬，誰都知道光靠農是不夠的。這時候，一個安全可靠的代儲值管道，才是你真正需要的神兵利器，能幫你省下寶貴的頭髮，直接用鈔能力碾壓那些還在傻傻手動的玩家。別猶豫了，快來加入這個大型線上社交薪資單比拚現場吧！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《我的勇者外傳》完美詮釋了什麼叫做「我玩遊戲，但又沒完全在玩」。這款像素風放置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>RPG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，讓你體驗當個薪水小偷的終極樂趣，手機放著，角色自動變強，數字不斷往上跳，帶來一種虛無的成就感。遊戲的目標，就是看著你的勇者從一個像素點，變成一個更強的像素點。官方大概也知道這樣有點無聊，所以會不定時發送禮包碼和兌換碼，用免費資源把你從睡夢中喚醒，提醒你該上線收菜了。但千萬別以為放置遊戲就很佛心，當你看到別人的數字跳得比你快，那股不服輸的焦慮感就會油然而生。此刻，優質的代儲值服務就是你的心靈雞湯，用最簡單粗暴的方式，讓你重新在排行榜上找到人生的意義。快來下載，體驗這場刺激的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>EXCEL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>表格養成之旅吧。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>隆重介紹，最新款的電子老婆收藏模擬器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>——</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《女神契約：異世界遠征隊》。這款遊戲讓你深刻體會到，養老婆跟養車一樣所費不貲。遊戲的核心玩法就是不斷抽卡，收集上百位畫風精美的女神，然後看著她們為你自動戰鬥，主打一個「陪伴感」。官方為了讓你保持抽卡的慾望，會施捨一些禮包碼和兌換碼，給你幾抽的機會去驗證自己的血統是非洲還是歐洲。然而，當你真心想要某位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SSR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>女神時，就會發現信仰跟運氣在資本面前一文不值。這時候，聰明的玩家早已找好最划算的代儲值方案，準備用魔法小卡片把整個卡池搬回家。別再相信單抽出奇蹟了，朋友，這是一個比拚財力的異世界，快來與你的女神（和你的帳單）簽訂契約吧！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主畫面的左下角按頭像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>畫面左邊按信息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>畫面中間按齒輪進入設定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點選兌換碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上在SSbuy複製好的禮包兌換碼按兌換</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>畫面右方四個方塊點開</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>畫面右上方按設置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最底下點啟動碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>按確定即可領取免費禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>648粉鑽禮包</t>
+  </si>
+  <si>
+    <t>328粉鑽禮包</t>
+  </si>
+  <si>
+    <t>128粉鑽禮包</t>
+  </si>
+  <si>
+    <t>68粉鑽禮包</t>
+  </si>
+  <si>
+    <t>30粉鑽禮包</t>
+  </si>
+  <si>
+    <t>12粉鑽禮包</t>
+  </si>
+  <si>
+    <t>6粉鑽禮包</t>
+  </si>
+  <si>
+    <t>開拓之路第一章</t>
+  </si>
+  <si>
+    <t>月卡禮袋</t>
+  </si>
+  <si>
+    <t>64800鑽石</t>
+  </si>
+  <si>
+    <t>32800鑽石</t>
+  </si>
+  <si>
+    <t>12800鑽石</t>
+  </si>
+  <si>
+    <t>6800鑽石</t>
+  </si>
+  <si>
+    <t>釣魚/農場/挖礦月卡</t>
+  </si>
+  <si>
+    <t>英雄/關卡/要塞基金</t>
+  </si>
+  <si>
+    <t>100彩鑽</t>
+  </si>
+  <si>
+    <t>50彩鑽</t>
+  </si>
+  <si>
+    <t>30彩鑽</t>
+  </si>
+  <si>
+    <t>20彩鑽</t>
+  </si>
+  <si>
+    <t>10彩鑽</t>
+  </si>
+  <si>
+    <t>5彩鑽</t>
+  </si>
+  <si>
+    <t>月卡特權</t>
   </si>
 </sst>
 </file>
@@ -34575,37 +34859,240 @@
       </c>
     </row>
     <row r="208" spans="1:33" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="19"/>
+      <c r="A208" s="19" t="s">
+        <v>3870</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>3882</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>3883</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>3884</v>
+      </c>
       <c r="F208" s="8" t="str">
         <f>IF(A208="", "", "gift-codes.html?game=" &amp; A208)</f>
-        <v/>
+        <v>gift-codes.html?game=血影雙生</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>3877</v>
       </c>
       <c r="H208" s="10" t="str">
         <f>IF(A208="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A208)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=血影雙生</v>
+      </c>
+      <c r="I208" s="39" t="s">
+        <v>3889</v>
+      </c>
+      <c r="J208" s="3" t="s">
+        <v>3916</v>
+      </c>
+      <c r="K208" s="4">
+        <v>2555</v>
+      </c>
+      <c r="L208" s="3" t="s">
+        <v>3917</v>
+      </c>
+      <c r="M208" s="4">
+        <v>1331</v>
+      </c>
+      <c r="N208" s="3" t="s">
+        <v>3918</v>
+      </c>
+      <c r="O208" s="4">
+        <v>780</v>
+      </c>
+      <c r="P208" s="3" t="s">
+        <v>3919</v>
+      </c>
+      <c r="Q208" s="4">
+        <v>535</v>
+      </c>
+      <c r="R208" s="3" t="s">
+        <v>3920</v>
+      </c>
+      <c r="S208" s="4">
+        <v>264</v>
+      </c>
+      <c r="T208" s="3" t="s">
+        <v>3921</v>
+      </c>
+      <c r="U208" s="4">
+        <v>145</v>
+      </c>
+      <c r="V208" s="3" t="s">
+        <v>3922</v>
+      </c>
+      <c r="W208" s="4">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="209" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="19" t="s">
+        <v>3871</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>3876</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>3875</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>3873</v>
+      </c>
       <c r="F209" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=我的勇者外傳</v>
+      </c>
+      <c r="G209" s="2" t="s">
+        <v>3874</v>
       </c>
       <c r="H209" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="210" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=我的勇者外傳</v>
+      </c>
+      <c r="I209" s="39" t="s">
+        <v>3890</v>
+      </c>
+      <c r="J209" s="3" t="s">
+        <v>3901</v>
+      </c>
+      <c r="K209" s="4">
+        <v>2555</v>
+      </c>
+      <c r="L209" s="3" t="s">
+        <v>3902</v>
+      </c>
+      <c r="M209" s="4">
+        <v>1331</v>
+      </c>
+      <c r="N209" s="3" t="s">
+        <v>3903</v>
+      </c>
+      <c r="O209" s="4">
+        <v>535</v>
+      </c>
+      <c r="P209" s="3" t="s">
+        <v>3904</v>
+      </c>
+      <c r="Q209" s="4">
+        <v>288</v>
+      </c>
+      <c r="R209" s="3" t="s">
+        <v>3905</v>
+      </c>
+      <c r="S209" s="4">
+        <v>145</v>
+      </c>
+      <c r="T209" s="3" t="s">
+        <v>3906</v>
+      </c>
+      <c r="U209" s="4">
+        <v>60</v>
+      </c>
+      <c r="V209" s="3" t="s">
+        <v>3907</v>
+      </c>
+      <c r="W209" s="4">
+        <v>28</v>
+      </c>
+      <c r="X209" s="3" t="s">
+        <v>3908</v>
+      </c>
+      <c r="Y209" s="4">
+        <v>145</v>
+      </c>
+      <c r="Z209" s="3" t="s">
+        <v>3909</v>
+      </c>
+      <c r="AA209" s="4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="210" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="19" t="s">
+        <v>3872</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>3878</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>3881</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>3879</v>
+      </c>
       <c r="F210" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=女神契約：異世界遠征隊</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>3880</v>
       </c>
       <c r="H210" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=女神契約：異世界遠征隊</v>
+      </c>
+      <c r="I210" s="39" t="s">
+        <v>3891</v>
+      </c>
+      <c r="J210" s="3" t="s">
+        <v>3910</v>
+      </c>
+      <c r="K210" s="4">
+        <v>2355</v>
+      </c>
+      <c r="L210" s="3" t="s">
+        <v>3911</v>
+      </c>
+      <c r="M210" s="4">
+        <v>1174</v>
+      </c>
+      <c r="N210" s="3" t="s">
+        <v>3912</v>
+      </c>
+      <c r="O210" s="4">
+        <v>551</v>
+      </c>
+      <c r="P210" s="3" t="s">
+        <v>3913</v>
+      </c>
+      <c r="Q210" s="4">
+        <v>256</v>
+      </c>
+      <c r="R210" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="S210" s="4">
+        <v>102</v>
+      </c>
+      <c r="T210" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="U210" s="4">
+        <v>26</v>
+      </c>
+      <c r="V210" s="3" t="s">
+        <v>3914</v>
+      </c>
+      <c r="W210" s="4">
+        <v>102</v>
+      </c>
+      <c r="X210" s="3" t="s">
+        <v>3915</v>
+      </c>
+      <c r="Y210" s="4">
+        <v>102</v>
+      </c>
+      <c r="Z210" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="AA210" s="4">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="211" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F211" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -34615,7 +35102,7 @@
         <v/>
       </c>
     </row>
-    <row r="212" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F212" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -34625,7 +35112,7 @@
         <v/>
       </c>
     </row>
-    <row r="213" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F213" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -34635,7 +35122,7 @@
         <v/>
       </c>
     </row>
-    <row r="214" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F214" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -34645,7 +35132,7 @@
         <v/>
       </c>
     </row>
-    <row r="215" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F215" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -34655,7 +35142,7 @@
         <v/>
       </c>
     </row>
-    <row r="216" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F216" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -34665,7 +35152,7 @@
         <v/>
       </c>
     </row>
-    <row r="217" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F217" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -34675,7 +35162,7 @@
         <v/>
       </c>
     </row>
-    <row r="218" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F218" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -34685,7 +35172,7 @@
         <v/>
       </c>
     </row>
-    <row r="219" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F219" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -34695,7 +35182,7 @@
         <v/>
       </c>
     </row>
-    <row r="220" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F220" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -34705,7 +35192,7 @@
         <v/>
       </c>
     </row>
-    <row r="221" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F221" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -34715,7 +35202,7 @@
         <v/>
       </c>
     </row>
-    <row r="222" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F222" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -34725,7 +35212,7 @@
         <v/>
       </c>
     </row>
-    <row r="223" spans="6:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F223" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -34735,7 +35222,7 @@
         <v/>
       </c>
     </row>
-    <row r="224" spans="6:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:27" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F224" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -51662,62 +52149,146 @@
       <c r="L207" s="49" t="s">
         <v>2666</v>
       </c>
+      <c r="M207" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="N207" s="49" t="s">
+        <v>2666</v>
+      </c>
     </row>
     <row r="208" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="49" t="str">
         <f>IF(games!A208="", "", games!A208)</f>
-        <v/>
+        <v>血影雙生</v>
       </c>
       <c r="C208" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/血影雙生-禮包碼.jpg</v>
       </c>
       <c r="D208" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=血影雙生</v>
       </c>
       <c r="E208" s="50" t="str">
         <f>IF(games!I208&lt;&gt;"", games!I208, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>歡迎來到《血影雙生》，一款讓你再度體驗上班打卡的東方幻想MMORPG。遊戲主打獨特的「雙生」系統，讓你在兩種職業間切換自如，彷彿在提醒你現實中也得是個多功能的社畜。每天上線就是無盡的任務、副本和戰場，享受被數值統治的快感。覺得戰力升太慢？官方貼心準備了各種禮包碼與兌換碼，給你一點甜頭，讓你產生自己很強的錯覺。當然，想在伺服器裡抬頭挺胸，成為別人口中的大佬，誰都知道光靠農是不夠的。這時候，一個安全可靠的代儲值管道，才是你真正需要的神兵利器，能幫你省下寶貴的頭髮，直接用鈔能力碾壓那些還在傻傻手動的玩家。別猶豫了，快來加入這個大型線上社交薪資單比拚現場吧！</v>
+      </c>
+      <c r="F208" s="53" t="s">
+        <v>3897</v>
+      </c>
+      <c r="G208" s="49" t="s">
+        <v>3898</v>
+      </c>
+      <c r="H208" s="54" t="s">
+        <v>3899</v>
+      </c>
+      <c r="I208" s="49" t="s">
+        <v>2651</v>
+      </c>
+      <c r="J208" s="50" t="s">
+        <v>3900</v>
+      </c>
+      <c r="K208" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L208" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M208" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="N208" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="49" t="str">
         <f>IF(games!A209="", "", games!A209)</f>
-        <v/>
+        <v>我的勇者外傳</v>
       </c>
       <c r="C209" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/我的勇者外傳-禮包碼.jpg</v>
       </c>
       <c r="D209" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=我的勇者外傳</v>
       </c>
       <c r="E209" s="50" t="str">
         <f>IF(games!I209&lt;&gt;"", games!I209, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="210" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>《我的勇者外傳》完美詮釋了什麼叫做「我玩遊戲，但又沒完全在玩」。這款像素風放置RPG，讓你體驗當個薪水小偷的終極樂趣，手機放著，角色自動變強，數字不斷往上跳，帶來一種虛無的成就感。遊戲的目標，就是看著你的勇者從一個像素點，變成一個更強的像素點。官方大概也知道這樣有點無聊，所以會不定時發送禮包碼和兌換碼，用免費資源把你從睡夢中喚醒，提醒你該上線收菜了。但千萬別以為放置遊戲就很佛心，當你看到別人的數字跳得比你快，那股不服輸的焦慮感就會油然而生。此刻，優質的代儲值服務就是你的心靈雞湯，用最簡單粗暴的方式，讓你重新在排行榜上找到人生的意義。快來下載，體驗這場刺激的EXCEL表格養成之旅吧。</v>
+      </c>
+      <c r="F209" s="70" t="s">
+        <v>3823</v>
+      </c>
+      <c r="G209" s="49" t="s">
+        <v>3824</v>
+      </c>
+      <c r="H209" s="49" t="s">
+        <v>2651</v>
+      </c>
+      <c r="I209" s="49" t="s">
+        <v>3825</v>
+      </c>
+      <c r="K209" s="53" t="s">
+        <v>3885</v>
+      </c>
+      <c r="L209" s="61" t="s">
+        <v>3887</v>
+      </c>
+      <c r="M209" s="54" t="s">
+        <v>3886</v>
+      </c>
+      <c r="N209" s="49" t="s">
+        <v>3888</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="49" t="str">
         <f>IF(games!A210="", "", games!A210)</f>
-        <v/>
+        <v>女神契約：異世界遠征隊</v>
       </c>
       <c r="C210" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/女神契約：異世界遠征隊-禮包碼.jpg</v>
       </c>
       <c r="D210" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=女神契約：異世界遠征隊</v>
       </c>
       <c r="E210" s="50" t="str">
         <f>IF(games!I210&lt;&gt;"", games!I210, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>隆重介紹，最新款的電子老婆收藏模擬器——《女神契約：異世界遠征隊》。這款遊戲讓你深刻體會到，養老婆跟養車一樣所費不貲。遊戲的核心玩法就是不斷抽卡，收集上百位畫風精美的女神，然後看著她們為你自動戰鬥，主打一個「陪伴感」。官方為了讓你保持抽卡的慾望，會施捨一些禮包碼和兌換碼，給你幾抽的機會去驗證自己的血統是非洲還是歐洲。然而，當你真心想要某位SSR女神時，就會發現信仰跟運氣在資本面前一文不值。這時候，聰明的玩家早已找好最划算的代儲值方案，準備用魔法小卡片把整個卡池搬回家。別再相信單抽出奇蹟了，朋友，這是一個比拚財力的異世界，快來與你的女神（和你的帳單）簽訂契約吧！</v>
+      </c>
+      <c r="F210" s="53" t="s">
+        <v>3892</v>
+      </c>
+      <c r="G210" s="49" t="s">
+        <v>3893</v>
+      </c>
+      <c r="H210" s="54" t="s">
+        <v>3894</v>
+      </c>
+      <c r="I210" s="49" t="s">
+        <v>3895</v>
+      </c>
+      <c r="J210" s="49" t="s">
+        <v>3896</v>
+      </c>
+      <c r="K210" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L210" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M210" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="N210" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="49" t="str">
         <f>IF(games!A211="", "", games!A211)</f>
         <v/>
@@ -51735,7 +52306,7 @@
         <v/>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="49" t="str">
         <f>IF(games!A212="", "", games!A212)</f>
         <v/>
@@ -51753,7 +52324,7 @@
         <v/>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="49" t="str">
         <f>IF(games!A213="", "", games!A213)</f>
         <v/>
@@ -51771,7 +52342,7 @@
         <v/>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="49" t="str">
         <f>IF(games!A214="", "", games!A214)</f>
         <v/>
@@ -51789,7 +52360,7 @@
         <v/>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="49" t="str">
         <f>IF(games!A215="", "", games!A215)</f>
         <v/>
@@ -51803,7 +52374,7 @@
         <v/>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="49" t="str">
         <f>IF(games!A216="", "", games!A216)</f>
         <v/>
@@ -51817,7 +52388,7 @@
         <v/>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="49" t="str">
         <f>IF(games!A217="", "", games!A217)</f>
         <v/>
@@ -51831,7 +52402,7 @@
         <v/>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="49" t="str">
         <f>IF(games!A218="", "", games!A218)</f>
         <v/>
@@ -51845,7 +52416,7 @@
         <v/>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="49" t="str">
         <f>IF(games!A219="", "", games!A219)</f>
         <v/>
@@ -51859,7 +52430,7 @@
         <v/>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="49" t="str">
         <f>IF(games!A220="", "", games!A220)</f>
         <v/>
@@ -51873,7 +52444,7 @@
         <v/>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="49" t="str">
         <f>IF(games!A221="", "", games!A221)</f>
         <v/>
@@ -51887,7 +52458,7 @@
         <v/>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="49" t="str">
         <f>IF(games!A222="", "", games!A222)</f>
         <v/>
@@ -51901,7 +52472,7 @@
         <v/>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C223" s="49" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -51911,7 +52482,7 @@
         <v/>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C224" s="49" t="str">
         <f t="shared" si="7"/>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5837" uniqueCount="3923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5853" uniqueCount="3946">
   <si>
     <t>Facebook</t>
   </si>
@@ -16645,6 +16645,98 @@
   </si>
   <si>
     <t>月卡特權</t>
+  </si>
+  <si>
+    <t>Blood111</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blood444</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blood777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>twins777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>twins666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>twins888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP111</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP444</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*30000+掃蕩卷軸*3+初級魂精*10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*30000+玫瑰花+月光精華*5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*30000+裝備強化石*5+初級經驗書*5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>榮耀證書*2+初級魂精*5+初級經驗書*8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘卷軸*3+初級靈植*8+月光精華*5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 經驗藥水+掃蕩卷軸*2+初級寶羽*5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*30000+靈獸異果*1+榮耀證書*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*30000+經驗藥水*1+初級靈植*10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>經驗藥水*1+勇者試煉通行卷*1+初級靈羽*8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>七夕快樂</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃金武器幣*10+卡羅拉*7+藍色妖姬*7+雨中佳人*7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>myhero</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DrumStick</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>女神禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -52189,19 +52281,61 @@
         <v>3900</v>
       </c>
       <c r="K208" s="53" t="s">
-        <v>2666</v>
+        <v>3923</v>
       </c>
       <c r="L208" s="49" t="s">
-        <v>2666</v>
+        <v>3931</v>
       </c>
       <c r="M208" s="53" t="s">
-        <v>2666</v>
+        <v>3924</v>
       </c>
       <c r="N208" s="49" t="s">
-        <v>2666</v>
-      </c>
-    </row>
-    <row r="209" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3932</v>
+      </c>
+      <c r="O208" s="54" t="s">
+        <v>3925</v>
+      </c>
+      <c r="P208" s="49" t="s">
+        <v>3933</v>
+      </c>
+      <c r="Q208" s="54" t="s">
+        <v>3926</v>
+      </c>
+      <c r="R208" s="49" t="s">
+        <v>3934</v>
+      </c>
+      <c r="S208" s="54" t="s">
+        <v>3927</v>
+      </c>
+      <c r="T208" s="49" t="s">
+        <v>3935</v>
+      </c>
+      <c r="U208" s="54" t="s">
+        <v>3928</v>
+      </c>
+      <c r="V208" s="49" t="s">
+        <v>3936</v>
+      </c>
+      <c r="W208" s="54" t="s">
+        <v>3929</v>
+      </c>
+      <c r="X208" s="49" t="s">
+        <v>3937</v>
+      </c>
+      <c r="Y208" s="54" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z208" s="49" t="s">
+        <v>3938</v>
+      </c>
+      <c r="AA208" s="54" t="s">
+        <v>3670</v>
+      </c>
+      <c r="AB208" s="49" t="s">
+        <v>3939</v>
+      </c>
+    </row>
+    <row r="209" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="49" t="str">
         <f>IF(games!A209="", "", games!A209)</f>
         <v>我的勇者外傳</v>
@@ -52242,8 +52376,20 @@
       <c r="N209" s="49" t="s">
         <v>3888</v>
       </c>
-    </row>
-    <row r="210" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O209" s="54" t="s">
+        <v>3940</v>
+      </c>
+      <c r="P209" s="49" t="s">
+        <v>3941</v>
+      </c>
+      <c r="Q209" s="54" t="s">
+        <v>3942</v>
+      </c>
+      <c r="R209" s="49" t="s">
+        <v>3943</v>
+      </c>
+    </row>
+    <row r="210" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="49" t="str">
         <f>IF(games!A210="", "", games!A210)</f>
         <v>女神契約：異世界遠征隊</v>
@@ -52276,19 +52422,14 @@
         <v>3896</v>
       </c>
       <c r="K210" s="53" t="s">
-        <v>2666</v>
+        <v>3944</v>
       </c>
       <c r="L210" s="49" t="s">
-        <v>2666</v>
-      </c>
-      <c r="M210" s="53" t="s">
-        <v>2666</v>
-      </c>
-      <c r="N210" s="49" t="s">
-        <v>2666</v>
-      </c>
-    </row>
-    <row r="211" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3945</v>
+      </c>
+      <c r="M210" s="53"/>
+    </row>
+    <row r="211" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="49" t="str">
         <f>IF(games!A211="", "", games!A211)</f>
         <v/>
@@ -52306,7 +52447,7 @@
         <v/>
       </c>
     </row>
-    <row r="212" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="49" t="str">
         <f>IF(games!A212="", "", games!A212)</f>
         <v/>
@@ -52324,7 +52465,7 @@
         <v/>
       </c>
     </row>
-    <row r="213" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="49" t="str">
         <f>IF(games!A213="", "", games!A213)</f>
         <v/>
@@ -52342,7 +52483,7 @@
         <v/>
       </c>
     </row>
-    <row r="214" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="49" t="str">
         <f>IF(games!A214="", "", games!A214)</f>
         <v/>
@@ -52360,7 +52501,7 @@
         <v/>
       </c>
     </row>
-    <row r="215" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="49" t="str">
         <f>IF(games!A215="", "", games!A215)</f>
         <v/>
@@ -52374,7 +52515,7 @@
         <v/>
       </c>
     </row>
-    <row r="216" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="49" t="str">
         <f>IF(games!A216="", "", games!A216)</f>
         <v/>
@@ -52388,7 +52529,7 @@
         <v/>
       </c>
     </row>
-    <row r="217" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="49" t="str">
         <f>IF(games!A217="", "", games!A217)</f>
         <v/>
@@ -52402,7 +52543,7 @@
         <v/>
       </c>
     </row>
-    <row r="218" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="49" t="str">
         <f>IF(games!A218="", "", games!A218)</f>
         <v/>
@@ -52416,7 +52557,7 @@
         <v/>
       </c>
     </row>
-    <row r="219" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="49" t="str">
         <f>IF(games!A219="", "", games!A219)</f>
         <v/>
@@ -52430,7 +52571,7 @@
         <v/>
       </c>
     </row>
-    <row r="220" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="49" t="str">
         <f>IF(games!A220="", "", games!A220)</f>
         <v/>
@@ -52444,7 +52585,7 @@
         <v/>
       </c>
     </row>
-    <row r="221" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="49" t="str">
         <f>IF(games!A221="", "", games!A221)</f>
         <v/>
@@ -52458,7 +52599,7 @@
         <v/>
       </c>
     </row>
-    <row r="222" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="49" t="str">
         <f>IF(games!A222="", "", games!A222)</f>
         <v/>
@@ -52472,7 +52613,7 @@
         <v/>
       </c>
     </row>
-    <row r="223" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C223" s="49" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -52482,7 +52623,7 @@
         <v/>
       </c>
     </row>
-    <row r="224" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C224" s="49" t="str">
         <f t="shared" si="7"/>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5853" uniqueCount="3946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5993" uniqueCount="4001">
   <si>
     <t>Facebook</t>
   </si>
@@ -16736,6 +16736,244 @@
   </si>
   <si>
     <t>女神禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixel Starships 2</t>
+  </si>
+  <si>
+    <t>升級村莊大作戰</t>
+  </si>
+  <si>
+    <t>新月同行</t>
+  </si>
+  <si>
+    <t>貓旅館物語</t>
+  </si>
+  <si>
+    <t>龍石戰爭</t>
+  </si>
+  <si>
+    <t>The King Of Fighters AFK</t>
+  </si>
+  <si>
+    <t>邪門鬼道</t>
+  </si>
+  <si>
+    <t>Wind Breaker不良英雄譚</t>
+  </si>
+  <si>
+    <t>https://www.pixelstarships.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/pixelstarships/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.savysoda.pss2.android</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/au/app/pixel-starships-2/id1621274842</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E5%8D%87%E7%B4%9A%E6%9D%91%E8%8E%8A%E5%A4%A7%E4%BD%9C%E6%88%B0/id6749028974</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=net.ekgames.projectr&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.garena.game.p42&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://fellowmoon.garena.com/zh_tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E6%96%B0%E6%9C%88%E5%90%8C%E8%A1%8C/id6737657871</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/fellowmoonTW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=jp.aktsk.games.kaiju_no8_the_game&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.mlgwy.ymxbgat</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.userjoy.dsw&amp;hl=da</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/the-king-of-fighters-afk/id6499177365</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E9%82%AA%E9%96%80%E9%AC%BC%E9%81%93/id6743704037</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/wind-breaker-%E4%B8%8D%E8%89%AF%E8%8B%B1%E9%9B%84%E8%AD%9A/id6747578364</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/us/app/kaiju-no-8-the-game/id6742088839</t>
+  </si>
+  <si>
+    <t>https://kj8-thegame.com/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/cathotelstory/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://linktr.ee/cathotel?fbclid=IwY2xjawMiqkJleHRuA2FlbQIxMABicmlkETFGbzB2OThYMEVrT1pjSFN6AR4gWQ29lgBx3LoNSLeTOdKbTzVxL3j9WGhbKk7fKwj1QcuIE4vEMknzDIXMtA_aem_M7p2pA8Q7xOdCg1Ut_MgZw</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E8%B2%93%E6%97%85%E9%A4%A8%E7%89%A9%E8%AA%9E/id6745919462</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/dsw.ujgame</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://dsw.userjoy.com/event/preregister/index.php#cover</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E9%BE%8D%E7%9F%B3%E6%88%B0%E7%88%AD-%E9%A6%B4%E9%BE%8D%E5%87%BA%E5%BE%81/id6743779102</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.netmarble.kofafk&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.v20.gptw&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.softstargames.wbrebelheroes&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/KOFAFKTC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://kofafk.netmarble.com/tc/?fbclid=IwY2xjawMiq7dleHRuA2FlbQIxMABicmlkETE4MG1ESk81V1hCTVVtWll4AR48rLbqUrQE2o9gl0cUTqaMn5txinPJqPyCvaQK9e_m7vqFbcqoRwo5Bg5Fxw_aem_YdIWK-jhdy2R12XwNyHVDA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/taleoftaoist</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://spg.taleoftaoist.com/site</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/windbreakerSSG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://wbrebelheroes.softstargames.com.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所以，你覺得自己能指揮一艘星際戰艦？別開玩笑了。在這款像素構成的殘酷宇宙裡，你的偉大艦隊大概率只是一坨會移動的太空垃圾。你將會絕望地在網路上搜尋最新的禮包碼，只為了一點點可憐的資源來修補你那破爛的船身。當你發現一個過期的兌換碼時，那種心碎的感覺會成為你的日常。很快，你就會意識到，所謂的「策略」不過是個笑話，真正能讓你跟上進度的，只有點開代儲值頁面的速度。畢竟，沒有鈔能力，你連在宇宙中當個靶子的資格都沒有。祝你好運，艦長，你的船員已經在考慮叛變了。準備好迎接你那必然的失敗了嗎？快來證明你不是只會花錢的冤大頭吧。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>想用拳頭守護街道，成為不良少年中的英雄？醒醒吧，你可能連街邊的小混混都打不過，只會成為被勒索午餐錢的那個。遊戲裡的戰鬥可不是靠著一腔熱血就能贏的，你那軟綿綿的拳頭只會讓對手覺得你在幫他按摩。為了讓自己看起來不那麼廢柴，你只能到處去求爺爺告奶奶，尋找官方施捨的禮包碼，換點強化道具。每一次成功輸入兌換碼，都像是給了你多一秒鐘在場上挨揍的時間。很快你就會明白，街頭的頂點不是靠拳頭決定的，而是由代儲值的金額決定的。別掙扎了，你的不良英雄譚，恐怕得從學會怎麼儲值開始寫起。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>踏入這個鬼神世界，你以為自己是天選的道士，能降妖除魔？別傻了，你頂多是個會被小鬼嚇到尿褲子的凡人。你手下的那些鬼神夥伴，與其說是幫手，不如說是一群等著你供養的飯桶。為了養活他們，你只能低聲下氣地尋找各種禮包碼，換取微薄的元寶和召喚符。你對兌換碼的渴望，簡直比惡鬼對鮮血的渴望還要強烈。當你卡在某個關卡被小妖反覆折磨時，你就會領悟到，玄學也救不了非洲人，但代儲值可以。快點吧，在你被那些「邪門鬼道」吞噬之前，先讓你的錢包體驗一下什麼叫真正的恐怖。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>想組建一支《拳皇》夢幻隊伍，重溫街機的熱血？恐怕你連新手教學的電腦都打不贏。這款遊戲告訴我們，就算放置掛機，沒有實力的你照樣是個輸家。你將會沉迷於在網路上搜尋任何可用的禮包碼，只為了多幾張招募券，然後抽出一堆你沒聽過的雜魚角色。每一次輸入兌換碼前的期待，都會在看到抽卡結果後化為泡影。別再妄想靠策略戰勝一切了，當對手的八神庵一招秒殺你全隊時，你就會明白，格鬥的真諦在於誰的代儲值按得更快。放棄吧，你的格鬥之魂，可能還不如你錢包的厚度來得可靠。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>開一家貓咪旅館，享受被毛茸茸包圍的療癒生活？聽起來很美好，但你很快就會發現，這些貓主子遠比你想像的要難伺候。你的旅館可能因為設施太差，連流浪貓都不屑一顧。為了討好這些小祖宗，你只能到處尋找禮包碼，換點可憐的裝飾品，假裝自己的旅館很高級。你對每一個兌換碼的執著，只是為了能解鎖一個貓咪看得上眼的貓抓板。當你看著空蕩蕩的旅館，你就會明白，沒有足夠的預算，你連當個合格鏟屎官的資格都沒有。放棄幻想吧，只有透過溫暖的代儲值，才能讓你打造出一個貓咪們願意賞臉入住的「五星級」監獄。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>想成為防衛隊英雄，和怪獸來一場熱血對決？省省吧，以你的實力，大概率是第一個被怪獸踩扁的路人角色。遊戲裡的怪獸可不像漫畫裡那樣會等你變身，它們只會把你當成開胃小菜。你將花費大量時間去尋找那些能讓你勉強跟上大部隊的禮包碼，多拿一點強化材料，好讓自己看起來不那麼像個砲灰。每一個兌換碼都像是救命稻草，讓你苟延殘喘。很快你就會發現，所謂的戰鬥技巧在絕對的力量面前毫無意義，而力量的來源，正是那閃閃發光的代儲值按鈕。別掙扎了，快承認吧，你想守護城市，首先得讓你的錢包為之奮鬥。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>超商勇者</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>白天經營超商，晚上進地城打怪，聽起來真是時間管理大師，但實際上你可能兩邊都搞得一團糟。你的超商貨架大概永遠是空的，因為你在地城裡連隻史萊姆都打不過，哪來的材料？於是，你只能寄望於官方偶爾施捨的禮包碼，換點啟動資金，讓你那家快倒閉的店多撐一天。你對兌換碼的渴望，甚至超過了對傳說武器的追求，畢竟前者至少能讓你買得起幾瓶藥水。不用多久你就會領悟，想靠自己的努力在地城裡殺出一條血路，根本是癡人說夢。快醒醒吧，只有無情的代儲值，才能讓你同時成為成功的商人和勉強及格的勇者。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>想成為傳說中的馴龍大師，在奇幻大陸上與巨龍並肩作戰嗎？這條路可不簡單。你將踏上一場史詩般的冒險，但初期夥伴的戰力或許會讓你有些哭笑不得。為了讓你的龍夥伴快快長大，展現真正的力量，你肯定會想方設法尋找官方發布的最新禮包碼，畢竟誰會拒絕免費的成長資源呢？當然，任何隱藏的兌換碼也絕對不能錯過，它們往往是前期突破瓶頸的關鍵。隨著挑戰越發艱鉅，你會發現，想讓你的龍小隊在眾多玩家中脫穎而出，偶爾依靠便捷的代儲值服務來獲取稀有龍蛋或強力裝備，似乎是一條聰明的捷徑。準備好迎接挑戰，用智慧和策略（當然還有一點點額外幫助），在龍石戰爭中寫下你的傳奇吧！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>歡迎來到你的村莊，這裡風景秀麗，但怪物多得有點不像話。作為守護者，你將肩負起抵禦無盡敵軍的重任。遊戲的樂趣在於看著防線從簡陋到堅固，但怪物升級的速度有時真的會讓人措手不及。為了不讓你的英雄們孤軍奮戰，積極尋找最新的禮包碼絕對是明智之舉，它能為你帶來急需的資源，緩解燃眉之急。網路上流傳的各種兌換碼也別放過，積少成多，才能讓你的村莊屹立不倒。當你面對某些實在難纏的關卡時，不妨考慮一下，透過安全的代儲值來快速提升英雄星級或解鎖強力技能，或許能讓你更快體驗到碾壓敵人的快感。來吧，展現你的策略，守護這片家園！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>成為「超管局」的部長，處理發生在都市裡的各種神秘事件，聽起來就充滿挑戰。你將與一群各具異能的夥伴並肩作戰，揭開謎團真相。然而，想招募到心儀的強力隊員，有時確實需要一點點運氣。因此，時刻關注官方釋出的禮包碼就顯得格外重要，它們是獲取珍貴招募道具最直接的方式。遊戲中隱藏的各種兌換碼也是不容錯過的小確幸，能為你的隊伍提供額外補給。在組建完美隊伍的過程中，如果實在不想錯過限定卡池中的關鍵角色，適時利用可靠的代儲值服務，確保將他們納入麾下，也是人之常情。準備好運用你的智慧，帶領團隊化解危機，守護這座城市的平衡吧。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.KCG.ConveniHero</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/kaijuno8.TheGame.EN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>怪獸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> THE GAME</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -17091,7 +17329,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -17317,6 +17555,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -17622,7 +17863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ632"/>
+  <dimension ref="A1:AQ631"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" style="1" customWidth="1"/>
@@ -33619,7 +33860,7 @@
         <v>3560</v>
       </c>
       <c r="H191" s="10" t="str">
-        <f t="shared" ref="H191:H253" si="7">IF(A191="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A191)</f>
+        <f t="shared" ref="H191:H252" si="7">IF(A191="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A191)</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=手刀搶英雄</v>
       </c>
       <c r="I191" s="39" t="s">
@@ -33688,7 +33929,7 @@
         <v>3582</v>
       </c>
       <c r="F192" s="8" t="str">
-        <f t="shared" ref="F192:F253" si="8">IF(A192="", "", "gift-codes.html?game=" &amp; A192)</f>
+        <f t="shared" ref="F192:F252" si="8">IF(A192="", "", "gift-codes.html?game=" &amp; A192)</f>
         <v>gift-codes.html?game=荒野亂鬥</v>
       </c>
       <c r="G192" s="23" t="s">
@@ -35184,104 +35425,404 @@
         <v>780</v>
       </c>
     </row>
-    <row r="211" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A211" s="19" t="s">
+        <v>3946</v>
+      </c>
+      <c r="C211" s="24" t="s">
+        <v>3955</v>
+      </c>
+      <c r="D211" s="23" t="s">
+        <v>3954</v>
+      </c>
+      <c r="E211" s="23" t="s">
+        <v>3957</v>
+      </c>
       <c r="F211" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=Pixel Starships 2</v>
+      </c>
+      <c r="G211" s="23" t="s">
+        <v>3956</v>
       </c>
       <c r="H211" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=Pixel Starships 2</v>
+      </c>
+      <c r="I211" s="31" t="s">
+        <v>3987</v>
+      </c>
+      <c r="J211" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K211" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L211" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M211" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="212" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A212" s="19" t="s">
+        <v>3947</v>
+      </c>
+      <c r="C212" s="24" t="s">
+        <v>3563</v>
+      </c>
+      <c r="D212" s="23" t="s">
+        <v>3958</v>
+      </c>
+      <c r="E212" s="23" t="s">
+        <v>3958</v>
+      </c>
       <c r="F212" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=升級村莊大作戰</v>
+      </c>
+      <c r="G212" s="23" t="s">
+        <v>3959</v>
       </c>
       <c r="H212" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="213" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=升級村莊大作戰</v>
+      </c>
+      <c r="I212" s="31" t="s">
+        <v>3996</v>
+      </c>
+      <c r="J212" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K212" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L212" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M212" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="213" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A213" s="19" t="s">
+        <v>3948</v>
+      </c>
+      <c r="C213" s="24" t="s">
+        <v>3963</v>
+      </c>
+      <c r="D213" s="23" t="s">
+        <v>3961</v>
+      </c>
+      <c r="E213" s="23" t="s">
+        <v>3962</v>
+      </c>
       <c r="F213" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=新月同行</v>
+      </c>
+      <c r="G213" s="2" t="s">
+        <v>3960</v>
       </c>
       <c r="H213" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=新月同行</v>
+      </c>
+      <c r="I213" s="31" t="s">
+        <v>3997</v>
+      </c>
+      <c r="J213" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K213" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L213" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M213" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="214" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A214" s="21" t="s">
+        <v>3993</v>
+      </c>
+      <c r="C214" s="24" t="s">
+        <v>3563</v>
+      </c>
+      <c r="D214" s="85" t="s">
+        <v>3998</v>
+      </c>
+      <c r="E214" s="85" t="s">
+        <v>3998</v>
+      </c>
       <c r="F214" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=超商勇者</v>
+      </c>
+      <c r="G214" s="85" t="s">
+        <v>3998</v>
       </c>
       <c r="H214" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=超商勇者</v>
+      </c>
+      <c r="I214" s="31" t="s">
+        <v>3994</v>
+      </c>
+      <c r="J214" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K214" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L214" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M214" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="215" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A215" s="19" t="s">
+        <v>4000</v>
+      </c>
+      <c r="C215" s="24" t="s">
+        <v>3999</v>
+      </c>
+      <c r="D215" s="23" t="s">
+        <v>3971</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>3970</v>
+      </c>
       <c r="F215" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=怪獸8號 THE GAME</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>3964</v>
       </c>
       <c r="H215" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="216" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=怪獸8號 THE GAME</v>
+      </c>
+      <c r="I215" s="31" t="s">
+        <v>3992</v>
+      </c>
+      <c r="J215" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K215" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L215" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M215" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="216" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A216" s="19" t="s">
+        <v>3949</v>
+      </c>
+      <c r="C216" s="24" t="s">
+        <v>3972</v>
+      </c>
+      <c r="D216" s="23" t="s">
+        <v>3973</v>
+      </c>
+      <c r="E216" s="23" t="s">
+        <v>3974</v>
+      </c>
       <c r="F216" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=貓旅館物語</v>
+      </c>
+      <c r="G216" s="2" t="s">
+        <v>3965</v>
       </c>
       <c r="H216" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=貓旅館物語</v>
+      </c>
+      <c r="I216" s="31" t="s">
+        <v>3991</v>
+      </c>
+      <c r="J216" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K216" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L216" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M216" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="217" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A217" s="19" t="s">
+        <v>3950</v>
+      </c>
+      <c r="C217" s="24" t="s">
+        <v>3975</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>3976</v>
+      </c>
+      <c r="E217" s="23" t="s">
+        <v>3977</v>
+      </c>
       <c r="F217" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=龍石戰爭</v>
+      </c>
+      <c r="G217" s="2" t="s">
+        <v>3966</v>
       </c>
       <c r="H217" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=龍石戰爭</v>
+      </c>
+      <c r="I217" s="31" t="s">
+        <v>3995</v>
+      </c>
+      <c r="J217" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K217" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L217" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M217" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="218" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A218" s="19" t="s">
+        <v>3951</v>
+      </c>
+      <c r="C218" s="24" t="s">
+        <v>3981</v>
+      </c>
+      <c r="D218" s="23" t="s">
+        <v>3982</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>3967</v>
+      </c>
       <c r="F218" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=The King Of Fighters AFK</v>
+      </c>
+      <c r="G218" s="23" t="s">
+        <v>3978</v>
       </c>
       <c r="H218" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="219" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=The King Of Fighters AFK</v>
+      </c>
+      <c r="I218" s="31" t="s">
+        <v>3990</v>
+      </c>
+      <c r="J218" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K218" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L218" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M218" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="219" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A219" s="19" t="s">
+        <v>3952</v>
+      </c>
+      <c r="C219" s="24" t="s">
+        <v>3983</v>
+      </c>
+      <c r="D219" s="23" t="s">
+        <v>3984</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>3968</v>
+      </c>
       <c r="F219" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=邪門鬼道</v>
+      </c>
+      <c r="G219" s="23" t="s">
+        <v>3979</v>
       </c>
       <c r="H219" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://www.ssbuy.tw/game-detail.html?game=邪門鬼道</v>
+      </c>
+      <c r="I219" s="31" t="s">
+        <v>3989</v>
+      </c>
+      <c r="J219" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K219" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L219" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M219" s="49" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="220" spans="1:27" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A220" s="19" t="s">
+        <v>3953</v>
+      </c>
+      <c r="C220" s="24" t="s">
+        <v>3985</v>
+      </c>
+      <c r="D220" s="23" t="s">
+        <v>3986</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>3969</v>
+      </c>
       <c r="F220" s="8" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>gift-codes.html?game=Wind Breaker不良英雄譚</v>
+      </c>
+      <c r="G220" s="23" t="s">
+        <v>3980</v>
       </c>
       <c r="H220" s="10" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=Wind Breaker不良英雄譚</v>
+      </c>
+      <c r="I220" s="31" t="s">
+        <v>3988</v>
+      </c>
+      <c r="J220" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K220" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L220" s="54" t="s">
+        <v>2666</v>
+      </c>
+      <c r="M220" s="49" t="s">
+        <v>2666</v>
       </c>
     </row>
     <row r="221" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -35304,7 +35845,7 @@
         <v/>
       </c>
     </row>
-    <row r="223" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:27" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F223" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -35364,7 +35905,7 @@
         <v/>
       </c>
     </row>
-    <row r="229" spans="6:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F229" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -35606,21 +36147,21 @@
     </row>
     <row r="253" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F253" s="8" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="F253:F316" si="9">IF(A253="", "", "gift-codes.html?game=" &amp; A253)</f>
         <v/>
       </c>
       <c r="H253" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="H253:H316" si="10">IF(A253="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A253)</f>
         <v/>
       </c>
     </row>
     <row r="254" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F254" s="8" t="str">
-        <f t="shared" ref="F254:F317" si="9">IF(A254="", "", "gift-codes.html?game=" &amp; A254)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="H254" s="10" t="str">
-        <f t="shared" ref="H254:H317" si="10">IF(A254="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A254)</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36246,21 +36787,21 @@
     </row>
     <row r="317" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F317" s="8" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="F317:F380" si="11">IF(A317="", "", "gift-codes.html?game=" &amp; A317)</f>
         <v/>
       </c>
       <c r="H317" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="H317:H380" si="12">IF(A317="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A317)</f>
         <v/>
       </c>
     </row>
     <row r="318" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F318" s="8" t="str">
-        <f t="shared" ref="F318:F381" si="11">IF(A318="", "", "gift-codes.html?game=" &amp; A318)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H318" s="10" t="str">
-        <f t="shared" ref="H318:H381" si="12">IF(A318="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A318)</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -36886,21 +37427,21 @@
     </row>
     <row r="381" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F381" s="8" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="F381:F444" si="13">IF(A381="", "", "gift-codes.html?game=" &amp; A381)</f>
         <v/>
       </c>
       <c r="H381" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="H381:H444" si="14">IF(A381="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A381)</f>
         <v/>
       </c>
     </row>
     <row r="382" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F382" s="8" t="str">
-        <f t="shared" ref="F382:F445" si="13">IF(A382="", "", "gift-codes.html?game=" &amp; A382)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="H382" s="10" t="str">
-        <f t="shared" ref="H382:H445" si="14">IF(A382="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A382)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -37526,21 +38067,21 @@
     </row>
     <row r="445" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F445" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="F445:F508" si="15">IF(A445="", "", "gift-codes.html?game=" &amp; A445)</f>
         <v/>
       </c>
       <c r="H445" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="H445:H508" si="16">IF(A445="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A445)</f>
         <v/>
       </c>
     </row>
     <row r="446" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F446" s="8" t="str">
-        <f t="shared" ref="F446:F509" si="15">IF(A446="", "", "gift-codes.html?game=" &amp; A446)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H446" s="10" t="str">
-        <f t="shared" ref="H446:H509" si="16">IF(A446="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A446)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -38166,21 +38707,21 @@
     </row>
     <row r="509" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F509" s="8" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="F509:F572" si="17">IF(A509="", "", "gift-codes.html?game=" &amp; A509)</f>
         <v/>
       </c>
       <c r="H509" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="H509:H572" si="18">IF(A509="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A509)</f>
         <v/>
       </c>
     </row>
     <row r="510" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F510" s="8" t="str">
-        <f t="shared" ref="F510:F573" si="17">IF(A510="", "", "gift-codes.html?game=" &amp; A510)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H510" s="10" t="str">
-        <f t="shared" ref="H510:H573" si="18">IF(A510="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A510)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -38806,21 +39347,21 @@
     </row>
     <row r="573" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F573" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="F573:F575" si="19">IF(A573="", "", "gift-codes.html?game=" &amp; A573)</f>
         <v/>
       </c>
       <c r="H573" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="H573:H631" si="20">IF(A573="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A573)</f>
         <v/>
       </c>
     </row>
     <row r="574" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="F574" s="8" t="str">
-        <f t="shared" ref="F574:F576" si="19">IF(A574="", "", "gift-codes.html?game=" &amp; A574)</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H574" s="10" t="str">
-        <f t="shared" ref="H574:H632" si="20">IF(A574="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A574)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -38835,10 +39376,6 @@
       </c>
     </row>
     <row r="576" spans="6:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="F576" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
       <c r="H576" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -39170,12 +39707,6 @@
     </row>
     <row r="631" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H631" s="10" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="632" spans="8:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="H632" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -39252,15 +39783,42 @@
     <hyperlink ref="D204" r:id="rId66"/>
     <hyperlink ref="C207" r:id="rId67"/>
     <hyperlink ref="D205" r:id="rId68"/>
+    <hyperlink ref="D211" r:id="rId69"/>
+    <hyperlink ref="C211" r:id="rId70"/>
+    <hyperlink ref="G211" r:id="rId71"/>
+    <hyperlink ref="E211" r:id="rId72"/>
+    <hyperlink ref="E212" r:id="rId73"/>
+    <hyperlink ref="G212" r:id="rId74"/>
+    <hyperlink ref="D213" r:id="rId75"/>
+    <hyperlink ref="E213" r:id="rId76"/>
+    <hyperlink ref="C213" r:id="rId77"/>
+    <hyperlink ref="C216" r:id="rId78"/>
+    <hyperlink ref="D216" r:id="rId79"/>
+    <hyperlink ref="E216" r:id="rId80"/>
+    <hyperlink ref="C217" r:id="rId81"/>
+    <hyperlink ref="E217" r:id="rId82"/>
+    <hyperlink ref="G218" r:id="rId83"/>
+    <hyperlink ref="G219" r:id="rId84"/>
+    <hyperlink ref="G220" r:id="rId85"/>
+    <hyperlink ref="C218" r:id="rId86"/>
+    <hyperlink ref="D218" r:id="rId87"/>
+    <hyperlink ref="C219" r:id="rId88"/>
+    <hyperlink ref="D219" r:id="rId89"/>
+    <hyperlink ref="C220" r:id="rId90"/>
+    <hyperlink ref="D220" r:id="rId91"/>
+    <hyperlink ref="D212" r:id="rId92"/>
+    <hyperlink ref="C214" r:id="rId93"/>
+    <hyperlink ref="C212" r:id="rId94"/>
+    <hyperlink ref="C215" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId69"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId96"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AX440"/>
+  <dimension ref="A1:AX439"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="19.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.375" style="49" customWidth="1"/>
@@ -51324,11 +51882,11 @@
         <v>手刀搶英雄</v>
       </c>
       <c r="C191" s="49" t="str">
-        <f t="shared" ref="C191:C253" si="7">IF(A191="","", "giftcodesbanner/" &amp; A191 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" ref="C191:C252" si="7">IF(A191="","", "giftcodesbanner/" &amp; A191 &amp; "-禮包碼.jpg")</f>
         <v>giftcodesbanner/手刀搶英雄-禮包碼.jpg</v>
       </c>
       <c r="D191" s="49" t="str">
-        <f t="shared" ref="D191:D253" si="8">IF(A191="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A191)</f>
+        <f t="shared" ref="D191:D252" si="8">IF(A191="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A191)</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=手刀搶英雄</v>
       </c>
       <c r="E191" s="50" t="str">
@@ -52432,157 +52990,301 @@
     <row r="211" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="49" t="str">
         <f>IF(games!A211="", "", games!A211)</f>
-        <v/>
+        <v>Pixel Starships 2</v>
       </c>
       <c r="C211" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/Pixel Starships 2-禮包碼.jpg</v>
       </c>
       <c r="D211" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=Pixel Starships 2</v>
       </c>
       <c r="E211" s="50" t="str">
         <f>IF(games!I211&lt;&gt;"", games!I211, "")</f>
-        <v/>
+        <v>所以，你覺得自己能指揮一艘星際戰艦？別開玩笑了。在這款像素構成的殘酷宇宙裡，你的偉大艦隊大概率只是一坨會移動的太空垃圾。你將會絕望地在網路上搜尋最新的禮包碼，只為了一點點可憐的資源來修補你那破爛的船身。當你發現一個過期的兌換碼時，那種心碎的感覺會成為你的日常。很快，你就會意識到，所謂的「策略」不過是個笑話，真正能讓你跟上進度的，只有點開代儲值頁面的速度。畢竟，沒有鈔能力，你連在宇宙中當個靶子的資格都沒有。祝你好運，艦長，你的船員已經在考慮叛變了。準備好迎接你那必然的失敗了嗎？快來證明你不是只會花錢的冤大頭吧。</v>
+      </c>
+      <c r="F211" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="G211" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K211" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L211" s="49" t="s">
+        <v>2666</v>
       </c>
     </row>
     <row r="212" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="49" t="str">
         <f>IF(games!A212="", "", games!A212)</f>
-        <v/>
+        <v>升級村莊大作戰</v>
       </c>
       <c r="C212" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/升級村莊大作戰-禮包碼.jpg</v>
       </c>
       <c r="D212" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=升級村莊大作戰</v>
       </c>
       <c r="E212" s="50" t="str">
         <f>IF(games!I212&lt;&gt;"", games!I212, "")</f>
-        <v/>
+        <v>歡迎來到你的村莊，這裡風景秀麗，但怪物多得有點不像話。作為守護者，你將肩負起抵禦無盡敵軍的重任。遊戲的樂趣在於看著防線從簡陋到堅固，但怪物升級的速度有時真的會讓人措手不及。為了不讓你的英雄們孤軍奮戰，積極尋找最新的禮包碼絕對是明智之舉，它能為你帶來急需的資源，緩解燃眉之急。網路上流傳的各種兌換碼也別放過，積少成多，才能讓你的村莊屹立不倒。當你面對某些實在難纏的關卡時，不妨考慮一下，透過安全的代儲值來快速提升英雄星級或解鎖強力技能，或許能讓你更快體驗到碾壓敵人的快感。來吧，展現你的策略，守護這片家園！</v>
+      </c>
+      <c r="F212" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="G212" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K212" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L212" s="49" t="s">
+        <v>2666</v>
       </c>
     </row>
     <row r="213" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="49" t="str">
         <f>IF(games!A213="", "", games!A213)</f>
-        <v/>
+        <v>新月同行</v>
       </c>
       <c r="C213" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/新月同行-禮包碼.jpg</v>
       </c>
       <c r="D213" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=新月同行</v>
       </c>
       <c r="E213" s="50" t="str">
         <f>IF(games!I213&lt;&gt;"", games!I213, "")</f>
-        <v/>
+        <v>成為「超管局」的部長，處理發生在都市裡的各種神秘事件，聽起來就充滿挑戰。你將與一群各具異能的夥伴並肩作戰，揭開謎團真相。然而，想招募到心儀的強力隊員，有時確實需要一點點運氣。因此，時刻關注官方釋出的禮包碼就顯得格外重要，它們是獲取珍貴招募道具最直接的方式。遊戲中隱藏的各種兌換碼也是不容錯過的小確幸，能為你的隊伍提供額外補給。在組建完美隊伍的過程中，如果實在不想錯過限定卡池中的關鍵角色，適時利用可靠的代儲值服務，確保將他們納入麾下，也是人之常情。準備好運用你的智慧，帶領團隊化解危機，守護這座城市的平衡吧。</v>
+      </c>
+      <c r="F213" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="G213" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K213" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L213" s="49" t="s">
+        <v>2666</v>
       </c>
     </row>
     <row r="214" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="49" t="str">
         <f>IF(games!A214="", "", games!A214)</f>
-        <v/>
+        <v>超商勇者</v>
       </c>
       <c r="C214" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/超商勇者-禮包碼.jpg</v>
       </c>
       <c r="D214" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=超商勇者</v>
       </c>
       <c r="E214" s="50" t="str">
         <f>IF(games!I214&lt;&gt;"", games!I214, "")</f>
-        <v/>
+        <v>白天經營超商，晚上進地城打怪，聽起來真是時間管理大師，但實際上你可能兩邊都搞得一團糟。你的超商貨架大概永遠是空的，因為你在地城裡連隻史萊姆都打不過，哪來的材料？於是，你只能寄望於官方偶爾施捨的禮包碼，換點啟動資金，讓你那家快倒閉的店多撐一天。你對兌換碼的渴望，甚至超過了對傳說武器的追求，畢竟前者至少能讓你買得起幾瓶藥水。不用多久你就會領悟，想靠自己的努力在地城裡殺出一條血路，根本是癡人說夢。快醒醒吧，只有無情的代儲值，才能讓你同時成為成功的商人和勉強及格的勇者。</v>
+      </c>
+      <c r="F214" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="G214" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K214" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L214" s="49" t="s">
+        <v>2666</v>
       </c>
     </row>
     <row r="215" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="49" t="str">
         <f>IF(games!A215="", "", games!A215)</f>
-        <v/>
+        <v>怪獸8號 THE GAME</v>
       </c>
       <c r="C215" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/怪獸8號 THE GAME-禮包碼.jpg</v>
       </c>
       <c r="D215" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=怪獸8號 THE GAME</v>
+      </c>
+      <c r="E215" s="50" t="str">
+        <f>IF(games!I215&lt;&gt;"", games!I215, "")</f>
+        <v>想成為防衛隊英雄，和怪獸來一場熱血對決？省省吧，以你的實力，大概率是第一個被怪獸踩扁的路人角色。遊戲裡的怪獸可不像漫畫裡那樣會等你變身，它們只會把你當成開胃小菜。你將花費大量時間去尋找那些能讓你勉強跟上大部隊的禮包碼，多拿一點強化材料，好讓自己看起來不那麼像個砲灰。每一個兌換碼都像是救命稻草，讓你苟延殘喘。很快你就會發現，所謂的戰鬥技巧在絕對的力量面前毫無意義，而力量的來源，正是那閃閃發光的代儲值按鈕。別掙扎了，快承認吧，你想守護城市，首先得讓你的錢包為之奮鬥。</v>
+      </c>
+      <c r="F215" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="G215" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K215" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L215" s="49" t="s">
+        <v>2666</v>
       </c>
     </row>
     <row r="216" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="49" t="str">
         <f>IF(games!A216="", "", games!A216)</f>
-        <v/>
+        <v>貓旅館物語</v>
       </c>
       <c r="C216" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/貓旅館物語-禮包碼.jpg</v>
       </c>
       <c r="D216" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=貓旅館物語</v>
+      </c>
+      <c r="E216" s="50" t="str">
+        <f>IF(games!I216&lt;&gt;"", games!I216, "")</f>
+        <v>開一家貓咪旅館，享受被毛茸茸包圍的療癒生活？聽起來很美好，但你很快就會發現，這些貓主子遠比你想像的要難伺候。你的旅館可能因為設施太差，連流浪貓都不屑一顧。為了討好這些小祖宗，你只能到處尋找禮包碼，換點可憐的裝飾品，假裝自己的旅館很高級。你對每一個兌換碼的執著，只是為了能解鎖一個貓咪看得上眼的貓抓板。當你看著空蕩蕩的旅館，你就會明白，沒有足夠的預算，你連當個合格鏟屎官的資格都沒有。放棄幻想吧，只有透過溫暖的代儲值，才能讓你打造出一個貓咪們願意賞臉入住的「五星級」監獄。</v>
+      </c>
+      <c r="F216" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="G216" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K216" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L216" s="49" t="s">
+        <v>2666</v>
       </c>
     </row>
     <row r="217" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="49" t="str">
         <f>IF(games!A217="", "", games!A217)</f>
-        <v/>
+        <v>龍石戰爭</v>
       </c>
       <c r="C217" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/龍石戰爭-禮包碼.jpg</v>
       </c>
       <c r="D217" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=龍石戰爭</v>
+      </c>
+      <c r="E217" s="50" t="str">
+        <f>IF(games!I217&lt;&gt;"", games!I217, "")</f>
+        <v>想成為傳說中的馴龍大師，在奇幻大陸上與巨龍並肩作戰嗎？這條路可不簡單。你將踏上一場史詩般的冒險，但初期夥伴的戰力或許會讓你有些哭笑不得。為了讓你的龍夥伴快快長大，展現真正的力量，你肯定會想方設法尋找官方發布的最新禮包碼，畢竟誰會拒絕免費的成長資源呢？當然，任何隱藏的兌換碼也絕對不能錯過，它們往往是前期突破瓶頸的關鍵。隨著挑戰越發艱鉅，你會發現，想讓你的龍小隊在眾多玩家中脫穎而出，偶爾依靠便捷的代儲值服務來獲取稀有龍蛋或強力裝備，似乎是一條聰明的捷徑。準備好迎接挑戰，用智慧和策略（當然還有一點點額外幫助），在龍石戰爭中寫下你的傳奇吧！</v>
+      </c>
+      <c r="F217" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="G217" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K217" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L217" s="49" t="s">
+        <v>2666</v>
       </c>
     </row>
     <row r="218" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="49" t="str">
         <f>IF(games!A218="", "", games!A218)</f>
-        <v/>
+        <v>The King Of Fighters AFK</v>
       </c>
       <c r="C218" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/The King Of Fighters AFK-禮包碼.jpg</v>
       </c>
       <c r="D218" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=The King Of Fighters AFK</v>
+      </c>
+      <c r="E218" s="50" t="str">
+        <f>IF(games!I218&lt;&gt;"", games!I218, "")</f>
+        <v>想組建一支《拳皇》夢幻隊伍，重溫街機的熱血？恐怕你連新手教學的電腦都打不贏。這款遊戲告訴我們，就算放置掛機，沒有實力的你照樣是個輸家。你將會沉迷於在網路上搜尋任何可用的禮包碼，只為了多幾張招募券，然後抽出一堆你沒聽過的雜魚角色。每一次輸入兌換碼前的期待，都會在看到抽卡結果後化為泡影。別再妄想靠策略戰勝一切了，當對手的八神庵一招秒殺你全隊時，你就會明白，格鬥的真諦在於誰的代儲值按得更快。放棄吧，你的格鬥之魂，可能還不如你錢包的厚度來得可靠。</v>
+      </c>
+      <c r="F218" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="G218" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K218" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L218" s="49" t="s">
+        <v>2666</v>
       </c>
     </row>
     <row r="219" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="49" t="str">
         <f>IF(games!A219="", "", games!A219)</f>
-        <v/>
+        <v>邪門鬼道</v>
       </c>
       <c r="C219" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/邪門鬼道-禮包碼.jpg</v>
       </c>
       <c r="D219" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=邪門鬼道</v>
+      </c>
+      <c r="E219" s="50" t="str">
+        <f>IF(games!I219&lt;&gt;"", games!I219, "")</f>
+        <v>踏入這個鬼神世界，你以為自己是天選的道士，能降妖除魔？別傻了，你頂多是個會被小鬼嚇到尿褲子的凡人。你手下的那些鬼神夥伴，與其說是幫手，不如說是一群等著你供養的飯桶。為了養活他們，你只能低聲下氣地尋找各種禮包碼，換取微薄的元寶和召喚符。你對兌換碼的渴望，簡直比惡鬼對鮮血的渴望還要強烈。當你卡在某個關卡被小妖反覆折磨時，你就會領悟到，玄學也救不了非洲人，但代儲值可以。快點吧，在你被那些「邪門鬼道」吞噬之前，先讓你的錢包體驗一下什麼叫真正的恐怖。</v>
+      </c>
+      <c r="F219" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="G219" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K219" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L219" s="49" t="s">
+        <v>2666</v>
       </c>
     </row>
     <row r="220" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="49" t="str">
         <f>IF(games!A220="", "", games!A220)</f>
-        <v/>
+        <v>Wind Breaker不良英雄譚</v>
       </c>
       <c r="C220" s="49" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/Wind Breaker不良英雄譚-禮包碼.jpg</v>
       </c>
       <c r="D220" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=Wind Breaker不良英雄譚</v>
+      </c>
+      <c r="E220" s="50" t="str">
+        <f>IF(games!I220&lt;&gt;"", games!I220, "")</f>
+        <v>想用拳頭守護街道，成為不良少年中的英雄？醒醒吧，你可能連街邊的小混混都打不過，只會成為被勒索午餐錢的那個。遊戲裡的戰鬥可不是靠著一腔熱血就能贏的，你那軟綿綿的拳頭只會讓對手覺得你在幫他按摩。為了讓自己看起來不那麼廢柴，你只能到處去求爺爺告奶奶，尋找官方施捨的禮包碼，換點強化道具。每一次成功輸入兌換碼，都像是給了你多一秒鐘在場上挨揍的時間。很快你就會明白，街頭的頂點不是靠拳頭決定的，而是由代儲值的金額決定的。別掙扎了，你的不良英雄譚，恐怕得從學會怎麼儲值開始寫起。</v>
+      </c>
+      <c r="F220" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="G220" s="49" t="s">
+        <v>2666</v>
+      </c>
+      <c r="K220" s="53" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L220" s="49" t="s">
+        <v>2666</v>
       </c>
     </row>
     <row r="221" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -52600,10 +53302,6 @@
       </c>
     </row>
     <row r="222" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="49" t="str">
-        <f>IF(games!A222="", "", games!A222)</f>
-        <v/>
-      </c>
       <c r="C222" s="49" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -52915,21 +53613,21 @@
     </row>
     <row r="253" spans="3:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C253" s="49" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C253:C316" si="9">IF(A253="","", "giftcodesbanner/" &amp; A253 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D253" s="49" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="D253:D316" si="10">IF(A253="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A253)</f>
         <v/>
       </c>
     </row>
     <row r="254" spans="3:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C254" s="49" t="str">
-        <f t="shared" ref="C254:C317" si="9">IF(A254="","", "giftcodesbanner/" &amp; A254 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="D254" s="49" t="str">
-        <f t="shared" ref="D254:D317" si="10">IF(A254="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A254)</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -52973,7 +53671,7 @@
         <v/>
       </c>
     </row>
-    <row r="259" spans="3:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C259" s="49" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -53555,21 +54253,21 @@
     </row>
     <row r="317" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C317" s="49" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="C317:C380" si="11">IF(A317="","", "giftcodesbanner/" &amp; A317 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D317" s="49" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="D317:D380" si="12">IF(A317="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A317)</f>
         <v/>
       </c>
     </row>
     <row r="318" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C318" s="49" t="str">
-        <f t="shared" ref="C318:C381" si="11">IF(A318="","", "giftcodesbanner/" &amp; A318 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="D318" s="49" t="str">
-        <f t="shared" ref="D318:D381" si="12">IF(A318="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A318)</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -54195,21 +54893,21 @@
     </row>
     <row r="381" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C381" s="49" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="C381:C439" si="13">IF(A381="","", "giftcodesbanner/" &amp; A381 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D381" s="49" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="D381:D439" si="14">IF(A381="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A381)</f>
         <v/>
       </c>
     </row>
     <row r="382" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C382" s="49" t="str">
-        <f t="shared" ref="C382:C440" si="13">IF(A382="","", "giftcodesbanner/" &amp; A382 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D382" s="49" t="str">
-        <f t="shared" ref="D382:D440" si="14">IF(A382="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A382)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -54779,16 +55477,6 @@
         <v/>
       </c>
       <c r="D439" s="49" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="440" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C440" s="49" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="D440" s="49" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6058" uniqueCount="4073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6062" uniqueCount="4076">
   <si>
     <t>Facebook</t>
   </si>
@@ -14985,10 +14985,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>點進去設定裡面</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>VIP666</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -15014,10 +15010,6 @@
   </si>
   <si>
     <t>戰爭補給禮包</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>按進去聯繫客服旁邊的禮包碼選項</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -15364,6 +15356,23 @@
   </si>
   <si>
     <t>特權卡</t>
+  </si>
+  <si>
+    <t>6580鑽石</t>
+  </si>
+  <si>
+    <t>白銀月卡</t>
+  </si>
+  <si>
+    <t>黃金月卡</t>
+  </si>
+  <si>
+    <t>點進去右下角設定裡面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>按右上角禮包兌換</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -22512,7 +22521,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=電鋸果汁大亂鬥</v>
       </c>
       <c r="I109" s="60" t="s">
-        <v>4052</v>
+        <v>4050</v>
       </c>
       <c r="J109" s="63" t="s">
         <v>1275</v>
@@ -26913,7 +26922,7 @@
         <v>548</v>
       </c>
       <c r="P169" s="75" t="s">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="Q169" s="74">
         <v>278</v>
@@ -26959,7 +26968,7 @@
         <v>1323</v>
       </c>
       <c r="N170" s="75" t="s">
-        <v>4019</v>
+        <v>4017</v>
       </c>
       <c r="O170" s="74">
         <v>579</v>
@@ -27125,7 +27134,7 @@
     </row>
     <row r="173" spans="1:43" ht="23.25" customHeight="1" thickBot="1">
       <c r="A173" s="50" t="s">
-        <v>4020</v>
+        <v>4018</v>
       </c>
       <c r="F173" s="44" t="str">
         <f t="shared" si="6"/>
@@ -27136,7 +27145,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=奇蹟MU：暴走之翼</v>
       </c>
       <c r="I173" s="46" t="s">
-        <v>4021</v>
+        <v>4019</v>
       </c>
       <c r="J173" s="73" t="s">
         <v>155</v>
@@ -27444,7 +27453,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=魔法黯道</v>
       </c>
       <c r="I178" s="49" t="s">
-        <v>4040</v>
+        <v>4038</v>
       </c>
       <c r="J178" s="73" t="s">
         <v>1554</v>
@@ -27784,7 +27793,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=超蝦大作戰</v>
       </c>
       <c r="I182" s="49" t="s">
-        <v>4041</v>
+        <v>4039</v>
       </c>
       <c r="J182" s="73" t="s">
         <v>1612</v>
@@ -27948,7 +27957,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=三國志Thrones</v>
       </c>
       <c r="I184" s="49" t="s">
-        <v>4042</v>
+        <v>4040</v>
       </c>
       <c r="J184" s="73" t="s">
         <v>235</v>
@@ -28012,7 +28021,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=英勇之地</v>
       </c>
       <c r="I185" s="46" t="s">
-        <v>4022</v>
+        <v>4020</v>
       </c>
       <c r="J185" s="73" t="s">
         <v>12</v>
@@ -28100,7 +28109,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=未鑑定勇者團</v>
       </c>
       <c r="I186" s="49" t="s">
-        <v>4043</v>
+        <v>4041</v>
       </c>
       <c r="J186" s="73" t="s">
         <v>1656</v>
@@ -28158,7 +28167,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=戰靈異聞社</v>
       </c>
       <c r="I187" s="49" t="s">
-        <v>4044</v>
+        <v>4042</v>
       </c>
       <c r="J187" s="73" t="s">
         <v>1661</v>
@@ -28240,7 +28249,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=見習骷髏王</v>
       </c>
       <c r="I188" s="49" t="s">
-        <v>4045</v>
+        <v>4043</v>
       </c>
       <c r="J188" s="73" t="s">
         <v>1675</v>
@@ -28320,7 +28329,7 @@
         <v>1687</v>
       </c>
       <c r="E189" s="48" t="s">
-        <v>4023</v>
+        <v>4021</v>
       </c>
       <c r="F189" s="44" t="str">
         <f t="shared" si="6"/>
@@ -28410,7 +28419,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=伊瑟</v>
       </c>
       <c r="I190" s="46" t="s">
-        <v>4024</v>
+        <v>4022</v>
       </c>
       <c r="J190" s="51" t="s">
         <v>3513</v>
@@ -28456,7 +28465,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=手刀搶英雄</v>
       </c>
       <c r="I191" s="46" t="s">
-        <v>4025</v>
+        <v>4023</v>
       </c>
       <c r="J191" s="73" t="s">
         <v>3546</v>
@@ -28532,7 +28541,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=荒野亂鬥</v>
       </c>
       <c r="I192" s="46" t="s">
-        <v>4026</v>
+        <v>4024</v>
       </c>
       <c r="J192" s="73" t="s">
         <v>3588</v>
@@ -28596,7 +28605,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=遺忘之劍</v>
       </c>
       <c r="I193" s="46" t="s">
-        <v>4027</v>
+        <v>4025</v>
       </c>
       <c r="J193" s="73" t="s">
         <v>3593</v>
@@ -28666,7 +28675,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=破壞突擊隊</v>
       </c>
       <c r="I194" s="49" t="s">
-        <v>4046</v>
+        <v>4044</v>
       </c>
       <c r="J194" s="73" t="s">
         <v>3605</v>
@@ -28748,7 +28757,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=月兔茶屋：悠閒之旅</v>
       </c>
       <c r="I195" s="46" t="s">
-        <v>4028</v>
+        <v>4026</v>
       </c>
       <c r="J195" s="73" t="s">
         <v>3605</v>
@@ -28830,7 +28839,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=吞食天地 虛擬世界</v>
       </c>
       <c r="I196" s="46" t="s">
-        <v>4029</v>
+        <v>4027</v>
       </c>
       <c r="J196" s="73" t="s">
         <v>3624</v>
@@ -28930,7 +28939,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=封神：蒼嵐契約</v>
       </c>
       <c r="I197" s="46" t="s">
-        <v>4030</v>
+        <v>4028</v>
       </c>
       <c r="J197" s="73" t="s">
         <v>235</v>
@@ -29024,7 +29033,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=Gear Fight!</v>
       </c>
       <c r="I198" s="46" t="s">
-        <v>4031</v>
+        <v>4029</v>
       </c>
       <c r="J198" s="73" t="s">
         <v>3661</v>
@@ -29088,7 +29097,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=救世者之樹 M</v>
       </c>
       <c r="I199" s="46" t="s">
-        <v>4032</v>
+        <v>4030</v>
       </c>
       <c r="J199" s="73" t="s">
         <v>3677</v>
@@ -29170,7 +29179,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=勝利女神：妮姬</v>
       </c>
       <c r="I200" s="46" t="s">
-        <v>4033</v>
+        <v>4031</v>
       </c>
       <c r="J200" s="75" t="s">
         <v>1427</v>
@@ -29270,7 +29279,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=野龍小隊</v>
       </c>
       <c r="I201" s="49" t="s">
-        <v>4047</v>
+        <v>4045</v>
       </c>
       <c r="J201" s="75" t="s">
         <v>3736</v>
@@ -29334,7 +29343,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=BangBang殭屍：避難所戰爭</v>
       </c>
       <c r="I202" s="49" t="s">
-        <v>4048</v>
+        <v>4046</v>
       </c>
       <c r="J202" s="75" t="s">
         <v>301</v>
@@ -29422,7 +29431,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=主公超會閃</v>
       </c>
       <c r="I203" s="46" t="s">
-        <v>4034</v>
+        <v>4032</v>
       </c>
       <c r="J203" s="75" t="s">
         <v>3737</v>
@@ -29510,7 +29519,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=小兵來支援</v>
       </c>
       <c r="I204" s="49" t="s">
-        <v>4049</v>
+        <v>4047</v>
       </c>
       <c r="J204" s="75" t="s">
         <v>3747</v>
@@ -29580,7 +29589,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=姆姆鬥惡龍</v>
       </c>
       <c r="I205" s="49" t="s">
-        <v>4050</v>
+        <v>4048</v>
       </c>
       <c r="J205" s="75" t="s">
         <v>1427</v>
@@ -29656,7 +29665,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=發條特攻隊</v>
       </c>
       <c r="I206" s="49" t="s">
-        <v>4051</v>
+        <v>4049</v>
       </c>
       <c r="J206" s="75" t="s">
         <v>3754</v>
@@ -29732,7 +29741,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=天命：群星</v>
       </c>
       <c r="I207" s="46" t="s">
-        <v>4035</v>
+        <v>4033</v>
       </c>
       <c r="J207" s="75" t="s">
         <v>3759</v>
@@ -29808,7 +29817,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=血影雙生</v>
       </c>
       <c r="I208" s="46" t="s">
-        <v>4036</v>
+        <v>4034</v>
       </c>
       <c r="J208" s="75" t="s">
         <v>3877</v>
@@ -29878,7 +29887,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=我的勇者外傳</v>
       </c>
       <c r="I209" s="46" t="s">
-        <v>4037</v>
+        <v>4035</v>
       </c>
       <c r="J209" s="75" t="s">
         <v>3862</v>
@@ -29937,7 +29946,7 @@
     </row>
     <row r="210" spans="1:33" ht="23.25" customHeight="1" thickBot="1">
       <c r="A210" s="53" t="s">
-        <v>4065</v>
+        <v>4063</v>
       </c>
       <c r="C210" s="44" t="s">
         <v>3842</v>
@@ -29960,7 +29969,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=女神契約：異世界遠征隊</v>
       </c>
       <c r="I210" s="46" t="s">
-        <v>4038</v>
+        <v>4036</v>
       </c>
       <c r="J210" s="75" t="s">
         <v>3871</v>
@@ -30019,7 +30028,7 @@
     </row>
     <row r="211" spans="1:33" ht="23.25" customHeight="1" thickBot="1">
       <c r="A211" s="53" t="s">
-        <v>4064</v>
+        <v>4062</v>
       </c>
       <c r="C211" s="47" t="s">
         <v>3915</v>
@@ -30045,43 +30054,43 @@
         <v>3947</v>
       </c>
       <c r="J211" s="75" t="s">
-        <v>3982</v>
+        <v>3980</v>
       </c>
       <c r="K211" s="74">
         <v>2355</v>
       </c>
       <c r="L211" s="75" t="s">
-        <v>3983</v>
+        <v>3981</v>
       </c>
       <c r="M211" s="74">
         <v>1174</v>
       </c>
       <c r="N211" s="75" t="s">
-        <v>3984</v>
+        <v>3982</v>
       </c>
       <c r="O211" s="74">
         <v>551</v>
       </c>
       <c r="P211" s="75" t="s">
-        <v>3985</v>
+        <v>3983</v>
       </c>
       <c r="Q211" s="74">
         <v>256</v>
       </c>
       <c r="R211" s="75" t="s">
-        <v>3986</v>
+        <v>3984</v>
       </c>
       <c r="S211" s="74">
         <v>128</v>
       </c>
       <c r="T211" s="75" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="U211" s="74">
         <v>51</v>
       </c>
       <c r="V211" s="75" t="s">
-        <v>3988</v>
+        <v>3986</v>
       </c>
       <c r="W211" s="74">
         <v>232</v>
@@ -30115,25 +30124,25 @@
         <v>3956</v>
       </c>
       <c r="J212" s="75" t="s">
-        <v>4008</v>
+        <v>4006</v>
       </c>
       <c r="K212" s="74">
         <v>1725</v>
       </c>
       <c r="L212" s="75" t="s">
-        <v>4009</v>
+        <v>4007</v>
       </c>
       <c r="M212" s="74">
         <v>827</v>
       </c>
       <c r="N212" s="75" t="s">
-        <v>4010</v>
+        <v>4008</v>
       </c>
       <c r="O212" s="74">
         <v>471</v>
       </c>
       <c r="P212" s="75" t="s">
-        <v>4011</v>
+        <v>4009</v>
       </c>
       <c r="Q212" s="74">
         <v>216</v>
@@ -30151,13 +30160,13 @@
         <v>60</v>
       </c>
       <c r="V212" s="75" t="s">
-        <v>3988</v>
+        <v>3986</v>
       </c>
       <c r="W212" s="74">
         <v>232</v>
       </c>
       <c r="X212" s="75" t="s">
-        <v>4012</v>
+        <v>4010</v>
       </c>
       <c r="Y212" s="74">
         <v>391</v>
@@ -30235,31 +30244,31 @@
         <v>2649</v>
       </c>
       <c r="K214" s="75" t="s">
-        <v>4013</v>
+        <v>4011</v>
       </c>
       <c r="L214" s="74">
         <v>162</v>
       </c>
       <c r="M214" s="75" t="s">
-        <v>4014</v>
+        <v>4012</v>
       </c>
       <c r="N214" s="74">
         <v>77</v>
       </c>
       <c r="O214" s="75" t="s">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="P214" s="74">
         <v>77</v>
       </c>
       <c r="Q214" s="75" t="s">
-        <v>4016</v>
+        <v>4014</v>
       </c>
       <c r="R214" s="74">
         <v>77</v>
       </c>
       <c r="S214" s="75" t="s">
-        <v>4017</v>
+        <v>4015</v>
       </c>
       <c r="T214" s="74">
         <v>162</v>
@@ -30267,7 +30276,7 @@
     </row>
     <row r="215" spans="1:33" ht="23.25" customHeight="1" thickBot="1">
       <c r="A215" s="53" t="s">
-        <v>4039</v>
+        <v>4037</v>
       </c>
       <c r="C215" s="47" t="s">
         <v>3959</v>
@@ -30293,67 +30302,67 @@
         <v>3952</v>
       </c>
       <c r="J215" s="1" t="s">
-        <v>4053</v>
+        <v>4051</v>
       </c>
       <c r="K215" s="2">
         <v>1567</v>
       </c>
       <c r="L215" s="1" t="s">
-        <v>4054</v>
+        <v>4052</v>
       </c>
       <c r="M215" s="2">
         <v>780</v>
       </c>
       <c r="N215" s="1" t="s">
-        <v>4055</v>
+        <v>4053</v>
       </c>
       <c r="O215" s="2">
         <v>551</v>
       </c>
       <c r="P215" s="1" t="s">
-        <v>4056</v>
+        <v>4054</v>
       </c>
       <c r="Q215" s="2">
         <v>256</v>
       </c>
       <c r="R215" s="1" t="s">
-        <v>4057</v>
+        <v>4055</v>
       </c>
       <c r="S215" s="2">
         <v>162</v>
       </c>
       <c r="T215" s="1" t="s">
-        <v>4058</v>
+        <v>4056</v>
       </c>
       <c r="U215" s="2">
         <v>77</v>
       </c>
       <c r="V215" s="1" t="s">
-        <v>4059</v>
+        <v>4057</v>
       </c>
       <c r="W215" s="2">
         <v>26</v>
       </c>
       <c r="X215" s="1" t="s">
-        <v>4060</v>
+        <v>4058</v>
       </c>
       <c r="Y215" s="2">
         <v>102</v>
       </c>
       <c r="Z215" s="1" t="s">
-        <v>4061</v>
+        <v>4059</v>
       </c>
       <c r="AA215" s="2">
         <v>391</v>
       </c>
       <c r="AB215" s="1" t="s">
-        <v>4062</v>
+        <v>4060</v>
       </c>
       <c r="AC215" s="2">
         <v>256</v>
       </c>
       <c r="AD215" s="1" t="s">
-        <v>4063</v>
+        <v>4061</v>
       </c>
       <c r="AE215" s="2">
         <v>256</v>
@@ -30387,43 +30396,43 @@
         <v>3951</v>
       </c>
       <c r="J216" s="1" t="s">
-        <v>4066</v>
+        <v>4064</v>
       </c>
       <c r="K216" s="2">
         <v>2355</v>
       </c>
       <c r="L216" s="1" t="s">
-        <v>4067</v>
+        <v>4065</v>
       </c>
       <c r="M216" s="2">
         <v>1174</v>
       </c>
       <c r="N216" s="1" t="s">
-        <v>4068</v>
+        <v>4066</v>
       </c>
       <c r="O216" s="2">
         <v>780</v>
       </c>
       <c r="P216" s="1" t="s">
-        <v>4069</v>
+        <v>4067</v>
       </c>
       <c r="Q216" s="2">
         <v>391</v>
       </c>
       <c r="R216" s="1" t="s">
-        <v>4070</v>
+        <v>4068</v>
       </c>
       <c r="S216" s="2">
         <v>128</v>
       </c>
       <c r="T216" s="1" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="U216" s="2">
         <v>26</v>
       </c>
       <c r="V216" s="1" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="W216" s="2">
         <v>128</v>
@@ -30456,17 +30465,53 @@
       <c r="I217" s="46" t="s">
         <v>3955</v>
       </c>
-      <c r="J217" s="77" t="s">
-        <v>2649</v>
-      </c>
-      <c r="K217" s="78" t="s">
-        <v>2649</v>
-      </c>
-      <c r="L217" s="79" t="s">
-        <v>2649</v>
-      </c>
-      <c r="M217" s="78" t="s">
-        <v>2649</v>
+      <c r="J217" s="1" t="s">
+        <v>4071</v>
+      </c>
+      <c r="K217" s="2">
+        <v>2555</v>
+      </c>
+      <c r="L217" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M217" s="2">
+        <v>1292</v>
+      </c>
+      <c r="N217" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O217" s="2">
+        <v>511</v>
+      </c>
+      <c r="P217" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q217" s="2">
+        <v>272</v>
+      </c>
+      <c r="R217" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S217" s="2">
+        <v>128</v>
+      </c>
+      <c r="T217" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="U217" s="2">
+        <v>51</v>
+      </c>
+      <c r="V217" s="1" t="s">
+        <v>4072</v>
+      </c>
+      <c r="W217" s="2">
+        <v>77</v>
+      </c>
+      <c r="X217" s="1" t="s">
+        <v>4073</v>
+      </c>
+      <c r="Y217" s="2">
+        <v>128</v>
       </c>
     </row>
     <row r="218" spans="1:33" ht="23.25" customHeight="1" thickBot="1">
@@ -30503,25 +30548,25 @@
         <v>2355</v>
       </c>
       <c r="L218" s="75" t="s">
-        <v>3989</v>
+        <v>3987</v>
       </c>
       <c r="M218" s="74">
         <v>937</v>
       </c>
       <c r="N218" s="75" t="s">
-        <v>3990</v>
+        <v>3988</v>
       </c>
       <c r="O218" s="74">
         <v>827</v>
       </c>
       <c r="P218" s="75" t="s">
-        <v>3991</v>
+        <v>3989</v>
       </c>
       <c r="Q218" s="74">
         <v>764</v>
       </c>
       <c r="R218" s="75" t="s">
-        <v>3992</v>
+        <v>3990</v>
       </c>
       <c r="S218" s="74">
         <v>583</v>
@@ -30539,7 +30584,7 @@
         <v>391</v>
       </c>
       <c r="X218" s="75" t="s">
-        <v>3993</v>
+        <v>3991</v>
       </c>
       <c r="Y218" s="74">
         <v>375</v>
@@ -30551,7 +30596,7 @@
         <v>232</v>
       </c>
       <c r="AB218" s="75" t="s">
-        <v>3994</v>
+        <v>3992</v>
       </c>
       <c r="AC218" s="74">
         <v>162</v>
@@ -30585,67 +30630,67 @@
         <v>3949</v>
       </c>
       <c r="J219" s="75" t="s">
-        <v>3997</v>
+        <v>3995</v>
       </c>
       <c r="K219" s="74">
         <v>2555</v>
       </c>
       <c r="L219" s="75" t="s">
-        <v>3998</v>
+        <v>3996</v>
       </c>
       <c r="M219" s="74">
         <v>1331</v>
       </c>
       <c r="N219" s="75" t="s">
-        <v>3999</v>
+        <v>3997</v>
       </c>
       <c r="O219" s="74">
         <v>780</v>
       </c>
       <c r="P219" s="75" t="s">
-        <v>4000</v>
+        <v>3998</v>
       </c>
       <c r="Q219" s="74">
         <v>733</v>
       </c>
       <c r="R219" s="75" t="s">
-        <v>4001</v>
+        <v>3999</v>
       </c>
       <c r="S219" s="74">
         <v>685</v>
       </c>
       <c r="T219" s="75" t="s">
-        <v>4002</v>
+        <v>4000</v>
       </c>
       <c r="U219" s="74">
         <v>583</v>
       </c>
       <c r="V219" s="75" t="s">
-        <v>4003</v>
+        <v>4001</v>
       </c>
       <c r="W219" s="74">
         <v>535</v>
       </c>
       <c r="X219" s="75" t="s">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="Y219" s="74">
         <v>471</v>
       </c>
       <c r="Z219" s="75" t="s">
-        <v>4005</v>
+        <v>4003</v>
       </c>
       <c r="AA219" s="74">
         <v>423</v>
       </c>
       <c r="AB219" s="75" t="s">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="AC219" s="74">
         <v>391</v>
       </c>
       <c r="AD219" s="75" t="s">
-        <v>4007</v>
+        <v>4005</v>
       </c>
       <c r="AE219" s="74">
         <v>264</v>
@@ -30697,7 +30742,7 @@
         <v>811</v>
       </c>
       <c r="N220" s="75" t="s">
-        <v>3995</v>
+        <v>3993</v>
       </c>
       <c r="O220" s="74">
         <v>479</v>
@@ -30721,7 +30766,7 @@
         <v>28</v>
       </c>
       <c r="V220" s="75" t="s">
-        <v>3996</v>
+        <v>3994</v>
       </c>
       <c r="W220" s="74">
         <v>170</v>
@@ -48093,85 +48138,85 @@
         <v>3967</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>3968</v>
+        <v>4074</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>3976</v>
+        <v>4075</v>
       </c>
       <c r="I217" s="10" t="s">
         <v>2634</v>
       </c>
       <c r="K217" s="14" t="s">
+        <v>3968</v>
+      </c>
+      <c r="L217" s="10" t="s">
+        <v>3974</v>
+      </c>
+      <c r="M217" s="15" t="s">
         <v>3969</v>
       </c>
-      <c r="L217" s="10" t="s">
-        <v>3975</v>
-      </c>
-      <c r="M217" s="15" t="s">
+      <c r="N217" s="10" t="s">
+        <v>3974</v>
+      </c>
+      <c r="O217" s="15" t="s">
         <v>3970</v>
       </c>
-      <c r="N217" s="10" t="s">
-        <v>3975</v>
-      </c>
-      <c r="O217" s="15" t="s">
-        <v>3971</v>
-      </c>
       <c r="P217" s="10" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="Q217" s="15" t="s">
         <v>1936</v>
       </c>
       <c r="R217" s="10" t="s">
+        <v>3974</v>
+      </c>
+      <c r="S217" s="15" t="s">
+        <v>3971</v>
+      </c>
+      <c r="T217" s="10" t="s">
+        <v>3974</v>
+      </c>
+      <c r="U217" s="15" t="s">
+        <v>3972</v>
+      </c>
+      <c r="V217" s="10" t="s">
+        <v>3974</v>
+      </c>
+      <c r="W217" s="15" t="s">
+        <v>3973</v>
+      </c>
+      <c r="X217" s="10" t="s">
+        <v>3974</v>
+      </c>
+      <c r="Y217" s="15" t="s">
         <v>3975</v>
       </c>
-      <c r="S217" s="15" t="s">
-        <v>3972</v>
-      </c>
-      <c r="T217" s="10" t="s">
-        <v>3975</v>
-      </c>
-      <c r="U217" s="15" t="s">
-        <v>3973</v>
-      </c>
-      <c r="V217" s="10" t="s">
-        <v>3975</v>
-      </c>
-      <c r="W217" s="15" t="s">
+      <c r="Z217" s="10" t="s">
         <v>3974</v>
       </c>
-      <c r="X217" s="10" t="s">
-        <v>3975</v>
-      </c>
-      <c r="Y217" s="15" t="s">
+      <c r="AA217" s="15" t="s">
+        <v>3976</v>
+      </c>
+      <c r="AB217" s="10" t="s">
+        <v>3974</v>
+      </c>
+      <c r="AC217" s="15" t="s">
         <v>3977</v>
       </c>
-      <c r="Z217" s="10" t="s">
-        <v>3975</v>
-      </c>
-      <c r="AA217" s="15" t="s">
+      <c r="AD217" s="10" t="s">
+        <v>3974</v>
+      </c>
+      <c r="AE217" s="15" t="s">
         <v>3978</v>
       </c>
-      <c r="AB217" s="10" t="s">
-        <v>3975</v>
-      </c>
-      <c r="AC217" s="15" t="s">
+      <c r="AF217" s="10" t="s">
+        <v>3974</v>
+      </c>
+      <c r="AG217" s="15" t="s">
         <v>3979</v>
       </c>
-      <c r="AD217" s="10" t="s">
-        <v>3975</v>
-      </c>
-      <c r="AE217" s="15" t="s">
-        <v>3980</v>
-      </c>
-      <c r="AF217" s="10" t="s">
-        <v>3975</v>
-      </c>
-      <c r="AG217" s="15" t="s">
-        <v>3981</v>
-      </c>
       <c r="AH217" s="10" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
     </row>
     <row r="218" spans="1:34" ht="22.5" customHeight="1">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6153" uniqueCount="4133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6167" uniqueCount="4141">
   <si>
     <t>Facebook</t>
   </si>
@@ -15591,6 +15591,38 @@
   </si>
   <si>
     <t>還在為你的王國不夠強大而煩惱嗎？別再幻想著靠時間累積資源，那只會讓你永遠落後。這款放置型策略手遊雖然看起來很佛系，但想在PVP中稱王稱霸，可不是光靠躺平就能辦到的。想讓你的王國快速安全地變得更強大，最明智的選擇就是直接代儲值。這樣你就能立刻擁有最強大的英雄和資源，輕鬆碾壓所有對手。當然，官方不定期發布的禮包碼和兌換碼也別忘了領取，這些免費資源能讓你在變強的路上更加輕鬆寫意。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOFAFKPHOTO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOFDOTGL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOFAFKYT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>99KYOLOVE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOFAFKLIGMA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOFAFKLAUNCH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOFISBACK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025最新禮包</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -31326,7 +31358,7 @@
         <v/>
       </c>
     </row>
-    <row r="229" spans="6:8" ht="99">
+    <row r="229" spans="6:8">
       <c r="F229" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31336,7 +31368,7 @@
         <v/>
       </c>
     </row>
-    <row r="230" spans="6:8" ht="99">
+    <row r="230" spans="6:8">
       <c r="F230" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31346,7 +31378,7 @@
         <v/>
       </c>
     </row>
-    <row r="231" spans="6:8" ht="99">
+    <row r="231" spans="6:8">
       <c r="F231" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31356,7 +31388,7 @@
         <v/>
       </c>
     </row>
-    <row r="232" spans="6:8" ht="99">
+    <row r="232" spans="6:8">
       <c r="F232" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31366,7 +31398,7 @@
         <v/>
       </c>
     </row>
-    <row r="233" spans="6:8" ht="99">
+    <row r="233" spans="6:8">
       <c r="F233" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31376,7 +31408,7 @@
         <v/>
       </c>
     </row>
-    <row r="234" spans="6:8" ht="99">
+    <row r="234" spans="6:8">
       <c r="F234" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31386,7 +31418,7 @@
         <v/>
       </c>
     </row>
-    <row r="235" spans="6:8" ht="99">
+    <row r="235" spans="6:8">
       <c r="F235" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31396,7 +31428,7 @@
         <v/>
       </c>
     </row>
-    <row r="236" spans="6:8" ht="99">
+    <row r="236" spans="6:8">
       <c r="F236" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31406,7 +31438,7 @@
         <v/>
       </c>
     </row>
-    <row r="237" spans="6:8" ht="99">
+    <row r="237" spans="6:8">
       <c r="F237" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31416,7 +31448,7 @@
         <v/>
       </c>
     </row>
-    <row r="238" spans="6:8" ht="99">
+    <row r="238" spans="6:8">
       <c r="F238" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31426,7 +31458,7 @@
         <v/>
       </c>
     </row>
-    <row r="239" spans="6:8" ht="99">
+    <row r="239" spans="6:8">
       <c r="F239" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31436,7 +31468,7 @@
         <v/>
       </c>
     </row>
-    <row r="240" spans="6:8" ht="99">
+    <row r="240" spans="6:8">
       <c r="F240" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31446,7 +31478,7 @@
         <v/>
       </c>
     </row>
-    <row r="241" spans="6:8" ht="99">
+    <row r="241" spans="6:8">
       <c r="F241" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31456,7 +31488,7 @@
         <v/>
       </c>
     </row>
-    <row r="242" spans="6:8" ht="99">
+    <row r="242" spans="6:8">
       <c r="F242" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31466,7 +31498,7 @@
         <v/>
       </c>
     </row>
-    <row r="243" spans="6:8" ht="99">
+    <row r="243" spans="6:8">
       <c r="F243" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31476,7 +31508,7 @@
         <v/>
       </c>
     </row>
-    <row r="244" spans="6:8" ht="99">
+    <row r="244" spans="6:8">
       <c r="F244" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31486,7 +31518,7 @@
         <v/>
       </c>
     </row>
-    <row r="245" spans="6:8" ht="99">
+    <row r="245" spans="6:8">
       <c r="F245" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31496,7 +31528,7 @@
         <v/>
       </c>
     </row>
-    <row r="246" spans="6:8" ht="99">
+    <row r="246" spans="6:8">
       <c r="F246" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31506,7 +31538,7 @@
         <v/>
       </c>
     </row>
-    <row r="247" spans="6:8" ht="99">
+    <row r="247" spans="6:8">
       <c r="F247" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31516,7 +31548,7 @@
         <v/>
       </c>
     </row>
-    <row r="248" spans="6:8" ht="99">
+    <row r="248" spans="6:8">
       <c r="F248" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31526,7 +31558,7 @@
         <v/>
       </c>
     </row>
-    <row r="249" spans="6:8" ht="99">
+    <row r="249" spans="6:8">
       <c r="F249" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31536,7 +31568,7 @@
         <v/>
       </c>
     </row>
-    <row r="250" spans="6:8" ht="99">
+    <row r="250" spans="6:8">
       <c r="F250" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31546,7 +31578,7 @@
         <v/>
       </c>
     </row>
-    <row r="251" spans="6:8" ht="99">
+    <row r="251" spans="6:8">
       <c r="F251" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31556,7 +31588,7 @@
         <v/>
       </c>
     </row>
-    <row r="252" spans="6:8" ht="99">
+    <row r="252" spans="6:8">
       <c r="F252" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31566,7 +31598,7 @@
         <v/>
       </c>
     </row>
-    <row r="253" spans="6:8" ht="99">
+    <row r="253" spans="6:8">
       <c r="F253" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31576,7 +31608,7 @@
         <v/>
       </c>
     </row>
-    <row r="254" spans="6:8" ht="99">
+    <row r="254" spans="6:8">
       <c r="F254" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31586,7 +31618,7 @@
         <v/>
       </c>
     </row>
-    <row r="255" spans="6:8" ht="99">
+    <row r="255" spans="6:8">
       <c r="F255" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31596,7 +31628,7 @@
         <v/>
       </c>
     </row>
-    <row r="256" spans="6:8" ht="99">
+    <row r="256" spans="6:8">
       <c r="F256" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31606,7 +31638,7 @@
         <v/>
       </c>
     </row>
-    <row r="257" spans="6:8" ht="99">
+    <row r="257" spans="6:8">
       <c r="F257" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31616,7 +31648,7 @@
         <v/>
       </c>
     </row>
-    <row r="258" spans="6:8" ht="99">
+    <row r="258" spans="6:8">
       <c r="F258" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31626,7 +31658,7 @@
         <v/>
       </c>
     </row>
-    <row r="259" spans="6:8" ht="99">
+    <row r="259" spans="6:8">
       <c r="F259" s="48" t="str">
         <f t="shared" ref="F259:F269" si="8">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
         <v/>
@@ -31636,7 +31668,7 @@
         <v/>
       </c>
     </row>
-    <row r="260" spans="6:8" ht="99">
+    <row r="260" spans="6:8">
       <c r="F260" s="48" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31646,7 +31678,7 @@
         <v/>
       </c>
     </row>
-    <row r="261" spans="6:8" ht="99">
+    <row r="261" spans="6:8">
       <c r="F261" s="48" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31656,7 +31688,7 @@
         <v/>
       </c>
     </row>
-    <row r="262" spans="6:8" ht="99">
+    <row r="262" spans="6:8">
       <c r="F262" s="48" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31666,7 +31698,7 @@
         <v/>
       </c>
     </row>
-    <row r="263" spans="6:8" ht="99">
+    <row r="263" spans="6:8">
       <c r="F263" s="48" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31676,7 +31708,7 @@
         <v/>
       </c>
     </row>
-    <row r="264" spans="6:8" ht="99">
+    <row r="264" spans="6:8">
       <c r="F264" s="48" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31686,7 +31718,7 @@
         <v/>
       </c>
     </row>
-    <row r="265" spans="6:8" ht="99">
+    <row r="265" spans="6:8">
       <c r="F265" s="48" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31696,7 +31728,7 @@
         <v/>
       </c>
     </row>
-    <row r="266" spans="6:8" ht="99">
+    <row r="266" spans="6:8">
       <c r="F266" s="48" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31706,7 +31738,7 @@
         <v/>
       </c>
     </row>
-    <row r="267" spans="6:8" ht="99">
+    <row r="267" spans="6:8">
       <c r="F267" s="48" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31716,7 +31748,7 @@
         <v/>
       </c>
     </row>
-    <row r="268" spans="6:8" ht="99">
+    <row r="268" spans="6:8">
       <c r="F268" s="48" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31726,7 +31758,7 @@
         <v/>
       </c>
     </row>
-    <row r="269" spans="6:8" ht="99">
+    <row r="269" spans="6:8">
       <c r="F269" s="48" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -31736,9 +31768,9 @@
         <v/>
       </c>
     </row>
-    <row r="270" spans="6:8" ht="49.5">
+    <row r="270" spans="6:8">
       <c r="F270" s="47" t="str">
-        <f t="shared" ref="F253:F316" si="10">IF(A270="", "", "gift-codes.html?game=" &amp; A270)</f>
+        <f t="shared" ref="F270:F316" si="10">IF(A270="", "", "gift-codes.html?game=" &amp; A270)</f>
         <v/>
       </c>
       <c r="H270" s="48" t="str">
@@ -31746,7 +31778,7 @@
         <v/>
       </c>
     </row>
-    <row r="271" spans="6:8" ht="49.5">
+    <row r="271" spans="6:8">
       <c r="F271" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31756,7 +31788,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" spans="6:8" ht="49.5">
+    <row r="272" spans="6:8">
       <c r="F272" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31766,7 +31798,7 @@
         <v/>
       </c>
     </row>
-    <row r="273" spans="6:8" ht="49.5">
+    <row r="273" spans="6:8">
       <c r="F273" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31776,7 +31808,7 @@
         <v/>
       </c>
     </row>
-    <row r="274" spans="6:8" ht="49.5">
+    <row r="274" spans="6:8">
       <c r="F274" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31786,7 +31818,7 @@
         <v/>
       </c>
     </row>
-    <row r="275" spans="6:8" ht="49.5">
+    <row r="275" spans="6:8">
       <c r="F275" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31796,7 +31828,7 @@
         <v/>
       </c>
     </row>
-    <row r="276" spans="6:8" ht="49.5">
+    <row r="276" spans="6:8">
       <c r="F276" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31806,7 +31838,7 @@
         <v/>
       </c>
     </row>
-    <row r="277" spans="6:8" ht="49.5">
+    <row r="277" spans="6:8">
       <c r="F277" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31816,7 +31848,7 @@
         <v/>
       </c>
     </row>
-    <row r="278" spans="6:8" ht="49.5">
+    <row r="278" spans="6:8">
       <c r="F278" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31826,7 +31858,7 @@
         <v/>
       </c>
     </row>
-    <row r="279" spans="6:8" ht="49.5">
+    <row r="279" spans="6:8">
       <c r="F279" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31836,7 +31868,7 @@
         <v/>
       </c>
     </row>
-    <row r="280" spans="6:8" ht="49.5">
+    <row r="280" spans="6:8">
       <c r="F280" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31846,7 +31878,7 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="6:8" ht="49.5">
+    <row r="281" spans="6:8">
       <c r="F281" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31856,7 +31888,7 @@
         <v/>
       </c>
     </row>
-    <row r="282" spans="6:8" ht="49.5">
+    <row r="282" spans="6:8">
       <c r="F282" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31866,7 +31898,7 @@
         <v/>
       </c>
     </row>
-    <row r="283" spans="6:8" ht="49.5">
+    <row r="283" spans="6:8">
       <c r="F283" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31876,7 +31908,7 @@
         <v/>
       </c>
     </row>
-    <row r="284" spans="6:8" ht="49.5">
+    <row r="284" spans="6:8">
       <c r="F284" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31886,7 +31918,7 @@
         <v/>
       </c>
     </row>
-    <row r="285" spans="6:8" ht="49.5">
+    <row r="285" spans="6:8">
       <c r="F285" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31896,7 +31928,7 @@
         <v/>
       </c>
     </row>
-    <row r="286" spans="6:8" ht="49.5">
+    <row r="286" spans="6:8">
       <c r="F286" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31906,7 +31938,7 @@
         <v/>
       </c>
     </row>
-    <row r="287" spans="6:8" ht="49.5">
+    <row r="287" spans="6:8">
       <c r="F287" s="47" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -31922,7 +31954,7 @@
         <v/>
       </c>
       <c r="H288" s="48" t="str">
-        <f t="shared" ref="H253:H316" si="11">IF(A288="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A288)</f>
+        <f t="shared" ref="H288:H316" si="11">IF(A288="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A288)</f>
         <v/>
       </c>
     </row>
@@ -48725,17 +48757,59 @@
         <f>IF(games!I218&lt;&gt;"", games!I218, "")</f>
         <v>想組建一支《拳皇》夢幻隊伍，重溫街機的熱血？恐怕你連新手教學的電腦都打不贏。這款遊戲告訴我們，就算放置掛機，沒有實力的你照樣是個輸家。你將會沉迷於在網路上搜尋任何可用的禮包碼，只為了多幾張招募券，然後抽出一堆你沒聽過的雜魚角色。每一次輸入兌換碼前的期待，都會在看到抽卡結果後化為泡影。別再妄想靠策略戰勝一切了，當對手的八神庵一招秒殺你全隊時，你就會明白，格鬥的真諦在於誰的代儲值按得更快。放棄吧，你的格鬥之魂，可能還不如你錢包的厚度來得可靠。</v>
       </c>
-      <c r="F218" s="17" t="s">
-        <v>2648</v>
+      <c r="F218" s="34" t="s">
+        <v>3787</v>
       </c>
       <c r="G218" s="13" t="s">
-        <v>2648</v>
+        <v>3788</v>
+      </c>
+      <c r="H218" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I218" s="13" t="s">
+        <v>3789</v>
       </c>
       <c r="K218" s="17" t="s">
-        <v>2648</v>
+        <v>4133</v>
       </c>
       <c r="L218" s="13" t="s">
-        <v>2648</v>
+        <v>4140</v>
+      </c>
+      <c r="M218" s="18" t="s">
+        <v>4134</v>
+      </c>
+      <c r="N218" s="13" t="s">
+        <v>4140</v>
+      </c>
+      <c r="O218" s="18" t="s">
+        <v>4135</v>
+      </c>
+      <c r="P218" s="13" t="s">
+        <v>4140</v>
+      </c>
+      <c r="Q218" s="18" t="s">
+        <v>4136</v>
+      </c>
+      <c r="R218" s="13" t="s">
+        <v>4140</v>
+      </c>
+      <c r="S218" s="18" t="s">
+        <v>4137</v>
+      </c>
+      <c r="T218" s="13" t="s">
+        <v>4140</v>
+      </c>
+      <c r="U218" s="18" t="s">
+        <v>4138</v>
+      </c>
+      <c r="V218" s="13" t="s">
+        <v>4140</v>
+      </c>
+      <c r="W218" s="18" t="s">
+        <v>4139</v>
+      </c>
+      <c r="X218" s="13" t="s">
+        <v>4140</v>
       </c>
     </row>
     <row r="219" spans="1:34" ht="22.5" customHeight="1">
@@ -49580,7 +49654,7 @@
         <v/>
       </c>
       <c r="D270" s="13" t="str">
-        <f t="shared" ref="D253:D316" si="11">IF(A270="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A270)</f>
+        <f t="shared" ref="D270:D316" si="11">IF(A270="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A270)</f>
         <v/>
       </c>
     </row>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6167" uniqueCount="4141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6239" uniqueCount="4177">
   <si>
     <t>Facebook</t>
   </si>
@@ -15624,6 +15624,138 @@
   <si>
     <t>2025最新禮包</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/AresTWofficial</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.theares.com.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.com2usholdings.arestw.android.google.tw.normal&amp;referrer=adjust_reftag%3DcQPtsgLXttBFs%26utm_source%3DMarket_badge%26utm_campaign%3DGoogle_play</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.QuestLab.DraftWar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Draft showdown</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E9%98%BF%E7%91%9E%E6%96%AF-%E5%91%BD%E9%81%8B%E7%9A%84%E9%81%B8%E6%93%87%E8%80%85/id6745206397</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/us/app/draft-showdown/id6743368869</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>什麼？還在為了升級煩惱，或被副本Boss虐到懷疑人生？快醒醒吧！在《阿瑞斯：命運的選擇者》中，你將扮演天選之人，解鎖傳說英雄，打造最強陣容，讓那些自以為是的敵人知道什麼叫「殘酷」的勝利。這裡的福利多到你不敢想像，各種獨家禮包碼、兌換碼隨便拿，讓你戰力起飛。覺得遊戲太肝又太慢？沒關係，我們的代儲值服務讓你體驗什麼叫「快速安全」，一秒讓你成為人上人，輕鬆碾壓所有對手，不用再當可憐的免費仔，讓別人看看什麼叫真正的歐洲血統！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Draft War: PvP Tower Defense
+簡介
+還在玩那些一成不變的塔防遊戲？拜託，醒醒吧！《Draft War》這款即時 PvP 策略遊戲將會顛覆你的世界觀。在這裡，你將能結合TCG、RPG、MOBA、RTS等多種元素，打造出專屬於你的戰術。想贏？除了運氣，更重要的是你的腦子！我們為你準備了超豐富的禮包碼與兌換碼，讓你開局就贏在起跑線，資源拿到手軟。如果等不及，想用最快的速度打造最強牌組，我們的代儲值服務將會是你最聰明的選擇，保證快速安全，讓你用最快的速度成為牌場王者，讓對手跪地求饒！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.snake.twgp&amp;referrer=adjust_reftag%3Dc5wqR98e7f8LF%26utm_source%3DFBZYJJ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔鏡2：瘋狂的蛇姬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://snake.joystarfun.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/DarkFairyTales</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E9%AD%94%E9%8F%A12-%E7%98%8B%E7%8B%82%E7%9A%84%E8%9B%87%E5%A7%AC/id6747476537</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.paradoxduel.myjd</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E9%87%8F%E5%AD%90%E6%A9%9F%E5%8B%95%E9%9A%8A/id6746777110</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://pre.paradoxduel.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61578881450274</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>還在玩那些只能當花瓶的卡牌遊戲？別傻了！《魔鏡2：瘋狂的蛇姬》將顛覆你對回合制RPG的想像。在這裡，你將能解鎖傳說英雄、打造最強陣容，讓那些自以為是的對手嚐嚐什麼叫殘酷的勝利。遊戲福利多到你不敢相信，各種獨家兌換碼、禮包碼隨便拿，讓你戰力起飛。覺得升級太慢太累？沒關係，我們的代儲值服務讓你體驗什麼叫快速安全，一秒成為人上人，輕鬆碾壓所有對手，不用再當可憐的免費仔，讓別人看看什麼叫真正的歐洲血統！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>量子機動隊</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>還在為那些看臉抽卡的遊戲心力交瘁？醒醒吧！在《量子機動隊》裡，你將化身為超能指揮官，集結各路英雄，打造一支所向披靡的隊伍，讓那些自以為是的對手嚐嚐什麼叫殘酷的勝利。我們準備了滿滿的兌換碼、禮包碼讓你開局就贏在起跑線，資源拿到手軟。覺得升級太慢太累？別擔心！我們的代儲值服務保證快速安全，讓你用最快的速度打造最強牌組，再也不用擔心牌運不佳，一秒成為牌場上的傳奇，用鈔能力向世界證明你的實力！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿瑞斯：命運的選擇者</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>去廣告七天</t>
+  </si>
+  <si>
+    <t>去廣告月費</t>
+  </si>
+  <si>
+    <t>60000金幣</t>
+  </si>
+  <si>
+    <t>27500金幣</t>
+  </si>
+  <si>
+    <t>10500金幣</t>
+  </si>
+  <si>
+    <t>2500金幣</t>
+  </si>
+  <si>
+    <t>幸運特權</t>
+  </si>
+  <si>
+    <t>晉升之梯</t>
+  </si>
+  <si>
+    <t>蛇王戰令</t>
+  </si>
+  <si>
+    <t>蛇年基金</t>
+  </si>
+  <si>
+    <t>39.99禮包</t>
+  </si>
+  <si>
+    <t>34.99禮包</t>
+  </si>
+  <si>
+    <t>24.99禮包</t>
+  </si>
+  <si>
+    <t>1.99禮包</t>
   </si>
 </sst>
 </file>
@@ -15992,7 +16124,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -16206,6 +16338,8 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -30500,37 +30634,34 @@
       <c r="I214" s="49" t="s">
         <v>3953</v>
       </c>
-      <c r="J214" s="80" t="s">
-        <v>2648</v>
-      </c>
-      <c r="K214" s="78" t="s">
+      <c r="J214" s="78" t="s">
         <v>4010</v>
       </c>
-      <c r="L214" s="77">
+      <c r="K214" s="77">
         <v>162</v>
       </c>
-      <c r="M214" s="78" t="s">
+      <c r="L214" s="78" t="s">
         <v>4011</v>
       </c>
-      <c r="N214" s="77">
+      <c r="M214" s="77">
         <v>77</v>
       </c>
-      <c r="O214" s="78" t="s">
+      <c r="N214" s="78" t="s">
         <v>4012</v>
       </c>
-      <c r="P214" s="77">
+      <c r="O214" s="77">
         <v>77</v>
       </c>
-      <c r="Q214" s="78" t="s">
+      <c r="P214" s="78" t="s">
         <v>4013</v>
       </c>
-      <c r="R214" s="77">
+      <c r="Q214" s="77">
         <v>77</v>
       </c>
-      <c r="S214" s="78" t="s">
+      <c r="R214" s="78" t="s">
         <v>4014</v>
       </c>
-      <c r="T214" s="77">
+      <c r="S214" s="77">
         <v>162</v>
       </c>
     </row>
@@ -31318,47 +31449,299 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225" spans="6:8" ht="22.15" customHeight="1">
+    <row r="225" spans="1:31" ht="22.15" customHeight="1" thickBot="1">
+      <c r="A225" s="84" t="s">
+        <v>4162</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>4141</v>
+      </c>
+      <c r="D225" s="4" t="s">
+        <v>4142</v>
+      </c>
+      <c r="E225" s="4" t="s">
+        <v>4146</v>
+      </c>
       <c r="F225" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/阿瑞斯：命運的選擇者.html</v>
+      </c>
+      <c r="G225" s="4" t="s">
+        <v>4143</v>
       </c>
       <c r="H225" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="6:8" ht="22.15" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/阿瑞斯：命運的選擇者.html</v>
+      </c>
+      <c r="I225" s="49" t="s">
+        <v>4148</v>
+      </c>
+      <c r="J225" s="80" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K225" s="81" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L225" s="80" t="s">
+        <v>2648</v>
+      </c>
+      <c r="M225" s="81" t="s">
+        <v>2648</v>
+      </c>
+      <c r="N225" s="80" t="s">
+        <v>2648</v>
+      </c>
+      <c r="O225" s="81" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="226" spans="1:31" ht="22.15" customHeight="1" thickBot="1">
+      <c r="A226" s="83" t="s">
+        <v>4145</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>4144</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>4144</v>
+      </c>
+      <c r="E226" s="4" t="s">
+        <v>4147</v>
+      </c>
       <c r="F226" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Draft showdown.html</v>
+      </c>
+      <c r="G226" s="4" t="s">
+        <v>4144</v>
       </c>
       <c r="H226" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="6:8" ht="22.15" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Draft showdown.html</v>
+      </c>
+      <c r="I226" s="49" t="s">
+        <v>4149</v>
+      </c>
+      <c r="J226" s="1" t="s">
+        <v>4163</v>
+      </c>
+      <c r="K226" s="2">
+        <v>171</v>
+      </c>
+      <c r="L226" s="1" t="s">
+        <v>4164</v>
+      </c>
+      <c r="M226" s="2">
+        <v>612</v>
+      </c>
+      <c r="N226" s="1" t="s">
+        <v>4165</v>
+      </c>
+      <c r="O226" s="2">
+        <v>2286</v>
+      </c>
+      <c r="P226" s="1" t="s">
+        <v>4166</v>
+      </c>
+      <c r="Q226" s="2">
+        <v>1139</v>
+      </c>
+      <c r="R226" s="1" t="s">
+        <v>4167</v>
+      </c>
+      <c r="S226" s="2">
+        <v>535</v>
+      </c>
+      <c r="T226" s="1" t="s">
+        <v>4168</v>
+      </c>
+      <c r="U226" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="227" spans="1:31" ht="22.15" customHeight="1" thickBot="1">
+      <c r="A227" s="47" t="s">
+        <v>4151</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>4153</v>
+      </c>
+      <c r="D227" s="4" t="s">
+        <v>4152</v>
+      </c>
+      <c r="E227" s="4" t="s">
+        <v>4154</v>
+      </c>
       <c r="F227" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/魔鏡2：瘋狂的蛇姬.html</v>
+      </c>
+      <c r="G227" s="4" t="s">
+        <v>4150</v>
       </c>
       <c r="H227" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="228" spans="6:8" ht="22.15" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/魔鏡2：瘋狂的蛇姬.html</v>
+      </c>
+      <c r="I227" s="49" t="s">
+        <v>4159</v>
+      </c>
+      <c r="J227" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K227" s="2">
+        <v>2479</v>
+      </c>
+      <c r="L227" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M227" s="2">
+        <v>1292</v>
+      </c>
+      <c r="N227" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O227" s="2">
+        <v>757</v>
+      </c>
+      <c r="P227" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q227" s="2">
+        <v>519</v>
+      </c>
+      <c r="R227" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="S227" s="2">
+        <v>256</v>
+      </c>
+      <c r="T227" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="U227" s="2">
+        <v>140</v>
+      </c>
+      <c r="V227" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W227" s="2">
+        <v>27</v>
+      </c>
+      <c r="X227" s="1" t="s">
+        <v>4169</v>
+      </c>
+      <c r="Y227" s="2">
+        <v>256</v>
+      </c>
+      <c r="Z227" s="1" t="s">
+        <v>4170</v>
+      </c>
+      <c r="AA227" s="2">
+        <v>757</v>
+      </c>
+      <c r="AB227" s="1" t="s">
+        <v>4171</v>
+      </c>
+      <c r="AC227" s="2">
+        <v>380</v>
+      </c>
+      <c r="AD227" s="1" t="s">
+        <v>4172</v>
+      </c>
+      <c r="AE227" s="2">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="228" spans="1:31" ht="22.15" customHeight="1" thickBot="1">
+      <c r="A228" s="47" t="s">
+        <v>4160</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>4158</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>4157</v>
+      </c>
+      <c r="E228" s="4" t="s">
+        <v>4156</v>
+      </c>
       <c r="F228" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/量子機動隊.html</v>
+      </c>
+      <c r="G228" s="4" t="s">
+        <v>4155</v>
       </c>
       <c r="H228" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="6:8">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/量子機動隊.html</v>
+      </c>
+      <c r="I228" s="49" t="s">
+        <v>4161</v>
+      </c>
+      <c r="J228" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="K228" s="2">
+        <v>2487</v>
+      </c>
+      <c r="L228" s="1" t="s">
+        <v>1661</v>
+      </c>
+      <c r="M228" s="2">
+        <v>1261</v>
+      </c>
+      <c r="N228" s="1" t="s">
+        <v>4173</v>
+      </c>
+      <c r="O228" s="2">
+        <v>1009</v>
+      </c>
+      <c r="P228" s="1" t="s">
+        <v>4174</v>
+      </c>
+      <c r="Q228" s="2">
+        <v>887</v>
+      </c>
+      <c r="R228" s="1" t="s">
+        <v>4175</v>
+      </c>
+      <c r="S228" s="2">
+        <v>631</v>
+      </c>
+      <c r="T228" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="U228" s="2">
+        <v>512</v>
+      </c>
+      <c r="V228" s="1" t="s">
+        <v>1666</v>
+      </c>
+      <c r="W228" s="2">
+        <v>256</v>
+      </c>
+      <c r="X228" s="1" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Y228" s="2">
+        <v>136</v>
+      </c>
+      <c r="Z228" s="1" t="s">
+        <v>4176</v>
+      </c>
+      <c r="AA228" s="2">
+        <v>57</v>
+      </c>
+      <c r="AB228" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="AC228" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="229" spans="1:31">
       <c r="F229" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31368,7 +31751,7 @@
         <v/>
       </c>
     </row>
-    <row r="230" spans="6:8">
+    <row r="230" spans="1:31">
       <c r="F230" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31378,7 +31761,7 @@
         <v/>
       </c>
     </row>
-    <row r="231" spans="6:8">
+    <row r="231" spans="1:31">
       <c r="F231" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31388,7 +31771,7 @@
         <v/>
       </c>
     </row>
-    <row r="232" spans="6:8">
+    <row r="232" spans="1:31">
       <c r="F232" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31398,7 +31781,7 @@
         <v/>
       </c>
     </row>
-    <row r="233" spans="6:8">
+    <row r="233" spans="1:31">
       <c r="F233" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31408,7 +31791,7 @@
         <v/>
       </c>
     </row>
-    <row r="234" spans="6:8">
+    <row r="234" spans="1:31">
       <c r="F234" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31418,7 +31801,7 @@
         <v/>
       </c>
     </row>
-    <row r="235" spans="6:8">
+    <row r="235" spans="1:31">
       <c r="F235" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31428,7 +31811,7 @@
         <v/>
       </c>
     </row>
-    <row r="236" spans="6:8">
+    <row r="236" spans="1:31">
       <c r="F236" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31438,7 +31821,7 @@
         <v/>
       </c>
     </row>
-    <row r="237" spans="6:8">
+    <row r="237" spans="1:31">
       <c r="F237" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31448,7 +31831,7 @@
         <v/>
       </c>
     </row>
-    <row r="238" spans="6:8">
+    <row r="238" spans="1:31">
       <c r="F238" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31458,7 +31841,7 @@
         <v/>
       </c>
     </row>
-    <row r="239" spans="6:8">
+    <row r="239" spans="1:31">
       <c r="F239" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -31468,7 +31851,7 @@
         <v/>
       </c>
     </row>
-    <row r="240" spans="6:8">
+    <row r="240" spans="1:31">
       <c r="F240" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -35278,9 +35661,25 @@
     <hyperlink ref="C224" r:id="rId108"/>
     <hyperlink ref="D224" r:id="rId109"/>
     <hyperlink ref="E224" r:id="rId110"/>
+    <hyperlink ref="C225" r:id="rId111"/>
+    <hyperlink ref="D225" r:id="rId112"/>
+    <hyperlink ref="E225" r:id="rId113"/>
+    <hyperlink ref="G225" r:id="rId114"/>
+    <hyperlink ref="E226" r:id="rId115"/>
+    <hyperlink ref="G226" r:id="rId116"/>
+    <hyperlink ref="D226" r:id="rId117"/>
+    <hyperlink ref="C226" r:id="rId118"/>
+    <hyperlink ref="G227" r:id="rId119"/>
+    <hyperlink ref="D227" r:id="rId120"/>
+    <hyperlink ref="C227" r:id="rId121"/>
+    <hyperlink ref="E227" r:id="rId122"/>
+    <hyperlink ref="G228" r:id="rId123"/>
+    <hyperlink ref="E228" r:id="rId124"/>
+    <hyperlink ref="D228" r:id="rId125"/>
+    <hyperlink ref="C228" r:id="rId126"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId111"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId127"/>
 </worksheet>
 </file>
 
@@ -49070,79 +49469,129 @@
         <v>4131</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="22.5" customHeight="1">
+    <row r="225" spans="1:12" ht="22.5" customHeight="1">
       <c r="A225" s="13" t="str">
         <f>IF(games!A225="", "", games!A225)</f>
-        <v/>
+        <v>阿瑞斯：命運的選擇者</v>
       </c>
       <c r="C225" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/阿瑞斯：命運的選擇者-禮包碼.jpg</v>
       </c>
       <c r="D225" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/阿瑞斯：命運的選擇者.html</v>
       </c>
       <c r="E225" s="14" t="str">
         <f>IF(games!I225&lt;&gt;"", games!I225, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="1:5" ht="22.5" customHeight="1">
+        <v>什麼？還在為了升級煩惱，或被副本Boss虐到懷疑人生？快醒醒吧！在《阿瑞斯：命運的選擇者》中，你將扮演天選之人，解鎖傳說英雄，打造最強陣容，讓那些自以為是的敵人知道什麼叫「殘酷」的勝利。這裡的福利多到你不敢想像，各種獨家禮包碼、兌換碼隨便拿，讓你戰力起飛。覺得遊戲太肝又太慢？沒關係，我們的代儲值服務讓你體驗什麼叫「快速安全」，一秒讓你成為人上人，輕鬆碾壓所有對手，不用再當可憐的免費仔，讓別人看看什麼叫真正的歐洲血統！</v>
+      </c>
+      <c r="F225" s="80" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G225" s="81" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K225" s="80" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L225" s="81" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" ht="22.5" customHeight="1">
       <c r="A226" s="13" t="str">
         <f>IF(games!A226="", "", games!A226)</f>
-        <v/>
+        <v>Draft showdown</v>
       </c>
       <c r="C226" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/Draft showdown-禮包碼.jpg</v>
       </c>
       <c r="D226" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Draft showdown.html</v>
       </c>
       <c r="E226" s="14" t="str">
         <f>IF(games!I226&lt;&gt;"", games!I226, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="1:5" ht="22.5" customHeight="1">
+        <v>Draft War: PvP Tower Defense
+簡介
+還在玩那些一成不變的塔防遊戲？拜託，醒醒吧！《Draft War》這款即時 PvP 策略遊戲將會顛覆你的世界觀。在這裡，你將能結合TCG、RPG、MOBA、RTS等多種元素，打造出專屬於你的戰術。想贏？除了運氣，更重要的是你的腦子！我們為你準備了超豐富的禮包碼與兌換碼，讓你開局就贏在起跑線，資源拿到手軟。如果等不及，想用最快的速度打造最強牌組，我們的代儲值服務將會是你最聰明的選擇，保證快速安全，讓你用最快的速度成為牌場王者，讓對手跪地求饒！</v>
+      </c>
+      <c r="F226" s="80" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G226" s="81" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K226" s="80" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L226" s="81" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" ht="22.5" customHeight="1">
       <c r="A227" s="13" t="str">
         <f>IF(games!A227="", "", games!A227)</f>
-        <v/>
+        <v>魔鏡2：瘋狂的蛇姬</v>
       </c>
       <c r="C227" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/魔鏡2：瘋狂的蛇姬-禮包碼.jpg</v>
       </c>
       <c r="D227" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/魔鏡2：瘋狂的蛇姬.html</v>
       </c>
       <c r="E227" s="14" t="str">
         <f>IF(games!I227&lt;&gt;"", games!I227, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="228" spans="1:5" ht="22.5" customHeight="1">
+        <v>還在玩那些只能當花瓶的卡牌遊戲？別傻了！《魔鏡2：瘋狂的蛇姬》將顛覆你對回合制RPG的想像。在這裡，你將能解鎖傳說英雄、打造最強陣容，讓那些自以為是的對手嚐嚐什麼叫殘酷的勝利。遊戲福利多到你不敢相信，各種獨家兌換碼、禮包碼隨便拿，讓你戰力起飛。覺得升級太慢太累？沒關係，我們的代儲值服務讓你體驗什麼叫快速安全，一秒成為人上人，輕鬆碾壓所有對手，不用再當可憐的免費仔，讓別人看看什麼叫真正的歐洲血統！</v>
+      </c>
+      <c r="F227" s="80" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G227" s="81" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K227" s="80" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L227" s="81" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" ht="22.5" customHeight="1">
       <c r="A228" s="13" t="str">
         <f>IF(games!A228="", "", games!A228)</f>
-        <v/>
+        <v>量子機動隊</v>
       </c>
       <c r="C228" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/量子機動隊-禮包碼.jpg</v>
       </c>
       <c r="D228" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/量子機動隊.html</v>
       </c>
       <c r="E228" s="14" t="str">
         <f>IF(games!I228&lt;&gt;"", games!I228, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="1:5" ht="22.5" customHeight="1">
+        <v>還在為那些看臉抽卡的遊戲心力交瘁？醒醒吧！在《量子機動隊》裡，你將化身為超能指揮官，集結各路英雄，打造一支所向披靡的隊伍，讓那些自以為是的對手嚐嚐什麼叫殘酷的勝利。我們準備了滿滿的兌換碼、禮包碼讓你開局就贏在起跑線，資源拿到手軟。覺得升級太慢太累？別擔心！我們的代儲值服務保證快速安全，讓你用最快的速度打造最強牌組，再也不用擔心牌運不佳，一秒成為牌場上的傳奇，用鈔能力向世界證明你的實力！</v>
+      </c>
+      <c r="F228" s="80" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G228" s="81" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K228" s="80" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L228" s="81" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" ht="22.5" customHeight="1">
       <c r="A229" s="13" t="str">
         <f>IF(games!A229="", "", games!A229)</f>
         <v/>
@@ -49160,7 +49609,7 @@
         <v/>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="22.5" customHeight="1">
+    <row r="230" spans="1:12" ht="22.5" customHeight="1">
       <c r="A230" s="13" t="str">
         <f>IF(games!A230="", "", games!A230)</f>
         <v/>
@@ -49178,7 +49627,7 @@
         <v/>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="22.5" customHeight="1">
+    <row r="231" spans="1:12" ht="22.5" customHeight="1">
       <c r="A231" s="13" t="str">
         <f>IF(games!A231="", "", games!A231)</f>
         <v/>
@@ -49192,7 +49641,7 @@
         <v/>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="22.5" customHeight="1">
+    <row r="232" spans="1:12" ht="22.5" customHeight="1">
       <c r="A232" s="13" t="str">
         <f>IF(games!A232="", "", games!A232)</f>
         <v/>
@@ -49206,7 +49655,7 @@
         <v/>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="22.5" customHeight="1">
+    <row r="233" spans="1:12" ht="22.5" customHeight="1">
       <c r="A233" s="13" t="str">
         <f>IF(games!A233="", "", games!A233)</f>
         <v/>
@@ -49220,7 +49669,7 @@
         <v/>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="22.5" customHeight="1">
+    <row r="234" spans="1:12" ht="22.5" customHeight="1">
       <c r="A234" s="13" t="str">
         <f>IF(games!A234="", "", games!A234)</f>
         <v/>
@@ -49234,7 +49683,7 @@
         <v/>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="22.5" customHeight="1">
+    <row r="235" spans="1:12" ht="22.5" customHeight="1">
       <c r="A235" s="13" t="str">
         <f>IF(games!A235="", "", games!A235)</f>
         <v/>
@@ -49248,7 +49697,7 @@
         <v/>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="22.5" customHeight="1">
+    <row r="236" spans="1:12" ht="22.5" customHeight="1">
       <c r="A236" s="13" t="str">
         <f>IF(games!A236="", "", games!A236)</f>
         <v/>
@@ -49262,7 +49711,7 @@
         <v/>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="22.5" customHeight="1">
+    <row r="237" spans="1:12" ht="22.5" customHeight="1">
       <c r="A237" s="13" t="str">
         <f>IF(games!A237="", "", games!A237)</f>
         <v/>
@@ -49276,7 +49725,7 @@
         <v/>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="22.5" customHeight="1">
+    <row r="238" spans="1:12" ht="22.5" customHeight="1">
       <c r="A238" s="13" t="str">
         <f>IF(games!A238="", "", games!A238)</f>
         <v/>
@@ -49290,7 +49739,7 @@
         <v/>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="22.5" customHeight="1">
+    <row r="239" spans="1:12" ht="22.5" customHeight="1">
       <c r="A239" s="13" t="str">
         <f>IF(games!A239="", "", games!A239)</f>
         <v/>
@@ -49304,7 +49753,7 @@
         <v/>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="22.5" customHeight="1">
+    <row r="240" spans="1:12" ht="22.5" customHeight="1">
       <c r="A240" s="13" t="str">
         <f>IF(games!A240="", "", games!A240)</f>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15642,10 +15642,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Draft showdown</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://apps.apple.com/tw/app/%E9%98%BF%E7%91%9E%E6%96%AF-%E5%91%BD%E9%81%8B%E7%9A%84%E9%81%B8%E6%93%87%E8%80%85/id6745206397</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -15756,6 +15752,10 @@
   </si>
   <si>
     <t>1.99禮包</t>
+  </si>
+  <si>
+    <t>Draft showdown</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -31451,7 +31451,7 @@
     </row>
     <row r="225" spans="1:31" ht="22.15" customHeight="1" thickBot="1">
       <c r="A225" s="84" t="s">
-        <v>4162</v>
+        <v>4161</v>
       </c>
       <c r="C225" s="5" t="s">
         <v>4141</v>
@@ -31460,7 +31460,7 @@
         <v>4142</v>
       </c>
       <c r="E225" s="4" t="s">
-        <v>4146</v>
+        <v>4145</v>
       </c>
       <c r="F225" s="48" t="str">
         <f t="shared" si="6"/>
@@ -31474,7 +31474,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/阿瑞斯：命運的選擇者.html</v>
       </c>
       <c r="I225" s="49" t="s">
-        <v>4148</v>
+        <v>4147</v>
       </c>
       <c r="J225" s="80" t="s">
         <v>2648</v>
@@ -31497,7 +31497,7 @@
     </row>
     <row r="226" spans="1:31" ht="22.15" customHeight="1" thickBot="1">
       <c r="A226" s="83" t="s">
-        <v>4145</v>
+        <v>4176</v>
       </c>
       <c r="C226" s="4" t="s">
         <v>4144</v>
@@ -31506,7 +31506,7 @@
         <v>4144</v>
       </c>
       <c r="E226" s="4" t="s">
-        <v>4147</v>
+        <v>4146</v>
       </c>
       <c r="F226" s="48" t="str">
         <f t="shared" si="6"/>
@@ -31520,40 +31520,40 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Draft showdown.html</v>
       </c>
       <c r="I226" s="49" t="s">
-        <v>4149</v>
+        <v>4148</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>4163</v>
+        <v>4162</v>
       </c>
       <c r="K226" s="2">
         <v>171</v>
       </c>
       <c r="L226" s="1" t="s">
-        <v>4164</v>
+        <v>4163</v>
       </c>
       <c r="M226" s="2">
         <v>612</v>
       </c>
       <c r="N226" s="1" t="s">
-        <v>4165</v>
+        <v>4164</v>
       </c>
       <c r="O226" s="2">
         <v>2286</v>
       </c>
       <c r="P226" s="1" t="s">
-        <v>4166</v>
+        <v>4165</v>
       </c>
       <c r="Q226" s="2">
         <v>1139</v>
       </c>
       <c r="R226" s="1" t="s">
-        <v>4167</v>
+        <v>4166</v>
       </c>
       <c r="S226" s="2">
         <v>535</v>
       </c>
       <c r="T226" s="1" t="s">
-        <v>4168</v>
+        <v>4167</v>
       </c>
       <c r="U226" s="2">
         <v>124</v>
@@ -31561,30 +31561,30 @@
     </row>
     <row r="227" spans="1:31" ht="22.15" customHeight="1" thickBot="1">
       <c r="A227" s="47" t="s">
+        <v>4150</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>4152</v>
+      </c>
+      <c r="D227" s="4" t="s">
         <v>4151</v>
       </c>
-      <c r="C227" s="5" t="s">
+      <c r="E227" s="4" t="s">
         <v>4153</v>
-      </c>
-      <c r="D227" s="4" t="s">
-        <v>4152</v>
-      </c>
-      <c r="E227" s="4" t="s">
-        <v>4154</v>
       </c>
       <c r="F227" s="48" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/魔鏡2：瘋狂的蛇姬.html</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>4150</v>
+        <v>4149</v>
       </c>
       <c r="H227" s="48" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/魔鏡2：瘋狂的蛇姬.html</v>
       </c>
       <c r="I227" s="49" t="s">
-        <v>4159</v>
+        <v>4158</v>
       </c>
       <c r="J227" s="1" t="s">
         <v>12</v>
@@ -31629,25 +31629,25 @@
         <v>27</v>
       </c>
       <c r="X227" s="1" t="s">
-        <v>4169</v>
+        <v>4168</v>
       </c>
       <c r="Y227" s="2">
         <v>256</v>
       </c>
       <c r="Z227" s="1" t="s">
-        <v>4170</v>
+        <v>4169</v>
       </c>
       <c r="AA227" s="2">
         <v>757</v>
       </c>
       <c r="AB227" s="1" t="s">
-        <v>4171</v>
+        <v>4170</v>
       </c>
       <c r="AC227" s="2">
         <v>380</v>
       </c>
       <c r="AD227" s="1" t="s">
-        <v>4172</v>
+        <v>4171</v>
       </c>
       <c r="AE227" s="2">
         <v>519</v>
@@ -31655,30 +31655,30 @@
     </row>
     <row r="228" spans="1:31" ht="22.15" customHeight="1" thickBot="1">
       <c r="A228" s="47" t="s">
-        <v>4160</v>
+        <v>4159</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>4158</v>
+        <v>4157</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>4157</v>
+        <v>4156</v>
       </c>
       <c r="E228" s="4" t="s">
-        <v>4156</v>
+        <v>4155</v>
       </c>
       <c r="F228" s="48" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/量子機動隊.html</v>
       </c>
       <c r="G228" s="4" t="s">
-        <v>4155</v>
+        <v>4154</v>
       </c>
       <c r="H228" s="48" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/量子機動隊.html</v>
       </c>
       <c r="I228" s="49" t="s">
-        <v>4161</v>
+        <v>4160</v>
       </c>
       <c r="J228" s="1" t="s">
         <v>1660</v>
@@ -31693,19 +31693,19 @@
         <v>1261</v>
       </c>
       <c r="N228" s="1" t="s">
-        <v>4173</v>
+        <v>4172</v>
       </c>
       <c r="O228" s="2">
         <v>1009</v>
       </c>
       <c r="P228" s="1" t="s">
-        <v>4174</v>
+        <v>4173</v>
       </c>
       <c r="Q228" s="2">
         <v>887</v>
       </c>
       <c r="R228" s="1" t="s">
-        <v>4175</v>
+        <v>4174</v>
       </c>
       <c r="S228" s="2">
         <v>631</v>
@@ -31729,7 +31729,7 @@
         <v>136</v>
       </c>
       <c r="Z228" s="1" t="s">
-        <v>4176</v>
+        <v>4175</v>
       </c>
       <c r="AA228" s="2">
         <v>57</v>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15877,6 +15877,10 @@
     <t>去廣告</t>
   </si>
   <si>
+    <t>https://play.google.com/store/apps/details?id=com.hungryzombies.gptw&amp;listing=tw_midea_ga_v1&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>https://www.facebook.com/jiakbazombies</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -15898,75 +15902,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>https://play.google.com/store/apps/details?id=games.synthez.zombie.survival.multiplayer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>https://deadimpact.com/</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>https://apps.apple.com/tw/app/dead-impact-survival-online/id6444281832</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://infinitybullets.com/en/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://apps.apple.com/tw/app/infinity-bullets/id6497716526</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://x.com/mugendan_en</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.facebook.com/deadimpactofficial/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://apps.apple.com/hk/app/dunkadillo/id6748931212</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.thomaskyoung.com/</t>
-  </si>
-  <si>
-    <t>https://x.com/tommy_ill</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>500台幣禮包</t>
-  </si>
-  <si>
-    <t>480台幣禮包</t>
-  </si>
-  <si>
-    <t>350台幣禮包</t>
-  </si>
-  <si>
-    <t>260台幣禮包</t>
-  </si>
-  <si>
-    <t>160台幣禮包</t>
-  </si>
-  <si>
-    <t>2000台幣禮包</t>
-  </si>
-  <si>
-    <t>1000台幣禮包</t>
-  </si>
-  <si>
-    <r>
-      <t>XXL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>猛漢町</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -15995,208 +15939,260 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>https://play.google.com/store/apps/details?id=jp.hexadrive.infinitybullets</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://infinitybullets.com/en/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/infinity-bullets/id6497716526</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://x.com/mugendan_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/deadimpactofficial/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/hk/app/dunkadillo/id6748931212</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.thomaskyoung.com/</t>
+  </si>
+  <si>
+    <t>https://x.com/tommy_ill</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>500台幣禮包</t>
+  </si>
+  <si>
+    <t>480台幣禮包</t>
+  </si>
+  <si>
+    <t>350台幣禮包</t>
+  </si>
+  <si>
+    <t>260台幣禮包</t>
+  </si>
+  <si>
+    <t>160台幣禮包</t>
+  </si>
+  <si>
+    <t>2000台幣禮包</t>
+  </si>
+  <si>
+    <t>1000台幣禮包</t>
+  </si>
+  <si>
+    <t>Dunkadillo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2金酒鈴  3能量飲料（30體力）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1徵才廣告 10速通券</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WOOFIA_PLAY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GAF7HHAVUXWQWE5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GULUBEARXXL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EAUEHNRZ3R73UWE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10銀酒鈴 3培育卡 3特賣型錄 20速通</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店版限定 5銀酒鈴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>左邊展開選設定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>下方書籤選其他之後按兌換碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>到信箱領取獎勵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AAMMHEERBTPCTSN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>開服序號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayHornyONLY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>銀鈴X10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SGARTSCEO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金鈴X10 &amp; 房間卡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AAXAH97R9T7GS93</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4AR6HSCPBRUDUNU</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAJKHNBPNR6GRAT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BAH5HPJPSR2SQWJ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NANKHE2P8R92SE9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CA5LH4FT7UE2Y9Y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能力+房卡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>培慾房卡x3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>千則留言獎勵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能量大滿罐</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能量大滿罐X3 &amp; 速通票</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金鈴X5 &amp; 能量飲X5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1800虹石</t>
+  </si>
+  <si>
+    <t>1200虹石</t>
+  </si>
+  <si>
+    <t>750虹石</t>
+  </si>
+  <si>
+    <t>480虹石</t>
+  </si>
+  <si>
+    <t>300虹石</t>
+  </si>
+  <si>
+    <t>180虹石</t>
+  </si>
+  <si>
+    <t>100虹石</t>
+  </si>
+  <si>
+    <t>50虹石</t>
+  </si>
+  <si>
+    <t>20虹石</t>
+  </si>
+  <si>
+    <t>嗚拓邦商務護照</t>
+  </si>
+  <si>
+    <t>嗚拓邦經濟護照</t>
+  </si>
+  <si>
+    <t>猛漢馬拉松</t>
+  </si>
+  <si>
+    <r>
+      <t>XXL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>猛漢町</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>無限子彈</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dunkadillo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://play.google.com/store/apps/details?id=com.hungryzombies.gptw&amp;listing=tw_midea_ga_v1&amp;hl=zh_TW</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://play.google.com/store/apps/details?id=com.megagames.xxlwoofia&amp;referrer=adjust_reftag%3DckszLl8ZK4OBq%26utm_source%3DKM_R15%25E9%25A0%2590%25E7%25B4%2584_AN</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>https://play.google.com/store/apps/details?id=games.synthez.zombie.survival.multiplayer</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://play.google.com/store/apps/details?id=jp.hexadrive.infinitybullets</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://play.google.com/store/apps/details?id=com.ThomasK.Young.Dunkadillo&amp;hl=zh_TW</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>這世界怎麼了？滿大街都是殭屍，只有你這個傻氣又帶點小聰明的倖存者，才有辦法用各種古怪武器殺出重圍，順便把殭屍變成美味的「殭屍醬」。別再猶豫了，如果你懶得肝又想變強，那就別錯過這款遊戲！我們提供超方便的代儲值，讓你一秒變課長，享受快速安全的服務。再加上滿滿的禮包碼與兌換碼，讓你不用花一毛錢也能成為最強的殭屍終結者！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>你是否厭倦了那些纖細柔弱的遊戲角色？現在，是時候讓你的猛男魂覺醒了！《XXL猛漢町》讓你體驗什麼叫做真正的拳拳到肉！別再說自己課不起，我們提供最優惠的代儲值服務，讓你用最實惠的價格，享受最快速安全的交易。再加上一堆免費的禮包碼與兌換碼，讓你在遊戲中橫著走，誰也擋不住！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>厭倦了單打獨鬥嗎？歡迎來到這個殭屍橫行的世界，你不只得想辦法活下去，還得隨時提防其他玩家。我們知道你很忙，沒時間慢慢農資源，所以我們提供了代儲值服務，讓你體驗什麼叫「用錢砸死殭屍」。保證快速安全，還有一大堆禮包碼跟兌換碼等著你，讓你輕鬆超車，成為末日世界的王者！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>這是一款讓你體驗什麼叫做「射到手軟」的遊戲！《無限子彈》讓你享受無腦射擊的快感，不用再煩惱子彈不夠用。如果你懶得農裝備，只想直接享受爽快感，沒問題，我們提供最優質的代儲值服務，快速安全又划算。別忘了，還有各種禮包碼和兌換碼等你來領，讓你輕鬆成為最強戰士，享受爆頭的樂趣！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>還在玩那些一成不變的籃球遊戲嗎？現在是土撥鼠灌籃的時代了！《Dunkadillo》這款遊戲充滿了古怪的角色和讓人摸不著頭緒的玩法。如果你想在比賽中輕鬆灌爆對手，又不願意花時間慢慢練習，那就來試試我們的代儲值服務，保證快速安全。此外，還有滿滿的禮包碼和兌換碼讓你領到手軟，讓你的土撥鼠成為灌籃界的傳奇！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>呷飽未？殭殭醬</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2金酒鈴  3能量飲料（30體力）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1徵才廣告 10速通券</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>WOOFIA_PLAY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GAF7HHAVUXWQWE5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GULUBEARXXL</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EAUEHNRZ3R73UWE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10銀酒鈴 3培育卡 3特賣型錄 20速通</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>商店版限定 5銀酒鈴</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>左邊展開選設定</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>下方書籤選其他之後按兌換碼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>到信箱領取獎勵</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AAMMHEERBTPCTSN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>開服序號</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PlayHornyONLY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>銀鈴X10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SGARTSCEO</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>金鈴X10 &amp; 房間卡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AAXAH97R9T7GS93</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4AR6HSCPBRUDUNU</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAJKHNBPNR6GRAT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BAH5HPJPSR2SQWJ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NANKHE2P8R92SE9</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CA5LH4FT7UE2Y9Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>能力+房卡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>培慾房卡x3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>千則留言獎勵</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>能量大滿罐</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>能量大滿罐X3 &amp; 速通票</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>金鈴X5 &amp; 能量飲X5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1800虹石</t>
-  </si>
-  <si>
-    <t>1200虹石</t>
-  </si>
-  <si>
-    <t>750虹石</t>
-  </si>
-  <si>
-    <t>480虹石</t>
-  </si>
-  <si>
-    <t>300虹石</t>
-  </si>
-  <si>
-    <t>180虹石</t>
-  </si>
-  <si>
-    <t>100虹石</t>
-  </si>
-  <si>
-    <t>50虹石</t>
-  </si>
-  <si>
-    <t>20虹石</t>
-  </si>
-  <si>
-    <t>嗚拓邦商務護照</t>
-  </si>
-  <si>
-    <t>嗚拓邦經濟護照</t>
-  </si>
-  <si>
-    <t>猛漢馬拉松</t>
+    <t>還在為找不到兌換碼、禮包碼煩惱嗎？這款《呷飽未？殭殭醬》讓你再也不用乞求官方施捨，直接用鈔能力碾壓那些非洲人。想快速變強，靠代儲值就行了！不用擔心被詐騙，我們提供最快速、最安全的代儲服務，讓你直接用鈔能力碾壓那些非洲人，讓他們在遊戲裡永遠抬不起頭。那些用外掛被鎖的，還不如來找我們！別再苦等活動了，課金才是唯一的王道！這是一個殘酷的遊戲世界，沒有人會同情弱者，只有強者才能稱霸！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>還在玩那些娘砲遊戲？《XXL猛漢町》讓你體驗什麼叫做真正的男子漢！禮包碼、兌換碼這種小玩意兒，我們才不稀罕。想在猛漢的世界裡出人頭地？靠代儲值快速安全地提升戰力，才是明智的選擇。別再傻傻地刷首抽了，我們幫你一步到位，直接享受最強猛漢的待遇！讓那些只會用腳色練功的玩家見識見識，什麼叫做真正的無敵！我們提供最快速、最安全的代儲服務，讓你直接稱霸猛漢的世界！</t>
+  </si>
+  <si>
+    <t>別再相信那些號稱佛心、免課金的遊戲了！《Dead Impact：Survival Online》告訴你，沒有錢寸步難行。找不到兌換碼？別浪費時間了。想要在末日生存下來，除了子彈，最重要的是你的錢包深度。透過我們快速安全的代儲值服務，讓你成為末日裡最閃亮的倖存者！那些在論壇上求禮包碼的，不過是一群可憐蟲罷了。這個世界不需要弱者，只有強者才能生存！別再猶豫了，現在就行動吧！</t>
+  </si>
+  <si>
+    <t>「無限子彈」？別傻了，現實裡沒有什麼是無限的，除了你的消費能力。還在苦苦搜尋兌換碼跟禮包碼？與其浪費時間，不如直接享受我們快速安全的代儲值服務，一秒擁有無限資源。讓那些只會用腳色練功的玩家見識見識，什麼叫做真正的無限！在這個遊戲裡，沒有人會同情弱者，只有強者才能生存！我們提供最快速、最安全的代儲服務，讓你直接稱霸這個世界！</t>
+  </si>
+  <si>
+    <t>還在玩那些要你肝要你課的爛遊戲嗎？《Dunkadillo》讓你體驗最純粹的籃球樂趣，不用再擔心兌換碼、禮包碼找不到，也不用煩惱代儲值不安全。我們提供的服務讓你快速又安全的享受遊戲，而不是無止盡的農。讓那些自稱高手卻只會到處找攻略的玩家知道，什麼才是真正的高速通關！在這個遊戲裡，沒有人會同情弱者，只有強者才能稱霸！</t>
   </si>
 </sst>
 </file>
@@ -32238,30 +32234,30 @@
     </row>
     <row r="229" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A229" s="3" t="s">
-        <v>4249</v>
+        <v>4285</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>4213</v>
+        <v>4214</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>4214</v>
+        <v>4215</v>
       </c>
       <c r="E229" s="48" t="s">
-        <v>4215</v>
+        <v>4216</v>
       </c>
       <c r="F229" s="48" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/呷飽未？殭殭醬.html</v>
       </c>
       <c r="G229" s="4" t="s">
-        <v>4239</v>
+        <v>4213</v>
       </c>
       <c r="H229" s="48" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/呷飽未？殭殭醬.html</v>
       </c>
-      <c r="I229" s="49" t="s">
-        <v>4244</v>
+      <c r="I229" t="s">
+        <v>4286</v>
       </c>
       <c r="J229" s="94" t="s">
         <v>3753</v>
@@ -32270,13 +32266,13 @@
         <v>2293</v>
       </c>
       <c r="L229" s="96" t="s">
-        <v>4233</v>
+        <v>4237</v>
       </c>
       <c r="M229" s="90">
         <v>1529</v>
       </c>
       <c r="N229" s="96" t="s">
-        <v>4234</v>
+        <v>4238</v>
       </c>
       <c r="O229" s="90">
         <v>764</v>
@@ -32288,19 +32284,19 @@
         <v>757</v>
       </c>
       <c r="R229" s="91" t="s">
-        <v>4228</v>
+        <v>4232</v>
       </c>
       <c r="S229" s="90">
         <v>388</v>
       </c>
       <c r="T229" s="91" t="s">
-        <v>4229</v>
+        <v>4233</v>
       </c>
       <c r="U229" s="90">
         <v>372</v>
       </c>
       <c r="V229" s="91" t="s">
-        <v>4230</v>
+        <v>4234</v>
       </c>
       <c r="W229" s="90">
         <v>271</v>
@@ -32312,13 +32308,13 @@
         <v>248</v>
       </c>
       <c r="Z229" s="91" t="s">
-        <v>4231</v>
+        <v>4235</v>
       </c>
       <c r="AA229" s="90">
         <v>202</v>
       </c>
       <c r="AB229" s="91" t="s">
-        <v>4232</v>
+        <v>4236</v>
       </c>
       <c r="AC229" s="90">
         <v>132</v>
@@ -32326,99 +32322,99 @@
     </row>
     <row r="230" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A230" s="80" t="s">
-        <v>4235</v>
+        <v>4281</v>
       </c>
       <c r="C230" s="47" t="s">
-        <v>4216</v>
+        <v>4217</v>
       </c>
       <c r="D230" s="4" t="s">
+        <v>4219</v>
+      </c>
+      <c r="E230" s="48" t="s">
         <v>4218</v>
-      </c>
-      <c r="E230" s="48" t="s">
-        <v>4217</v>
       </c>
       <c r="F230" s="48" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/XXL猛漢町.html</v>
       </c>
       <c r="G230" s="4" t="s">
-        <v>4240</v>
+        <v>4283</v>
       </c>
       <c r="H230" s="48" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/XXL猛漢町.html</v>
       </c>
-      <c r="I230" s="49" t="s">
-        <v>4245</v>
+      <c r="I230" t="s">
+        <v>4287</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>4279</v>
+        <v>4269</v>
       </c>
       <c r="K230" s="2">
         <v>4145</v>
       </c>
       <c r="L230" s="1" t="s">
-        <v>4280</v>
+        <v>4270</v>
       </c>
       <c r="M230" s="2">
         <v>2849</v>
       </c>
       <c r="N230" s="1" t="s">
-        <v>4281</v>
+        <v>4271</v>
       </c>
       <c r="O230" s="2">
         <v>1835</v>
       </c>
       <c r="P230" s="1" t="s">
-        <v>4282</v>
+        <v>4272</v>
       </c>
       <c r="Q230" s="2">
         <v>1208</v>
       </c>
       <c r="R230" s="1" t="s">
-        <v>4283</v>
+        <v>4273</v>
       </c>
       <c r="S230" s="2">
         <v>757</v>
       </c>
       <c r="T230" s="1" t="s">
-        <v>4284</v>
+        <v>4274</v>
       </c>
       <c r="U230" s="2">
         <v>465</v>
       </c>
       <c r="V230" s="1" t="s">
-        <v>4285</v>
+        <v>4275</v>
       </c>
       <c r="W230" s="2">
         <v>256</v>
       </c>
       <c r="X230" s="1" t="s">
-        <v>4286</v>
+        <v>4276</v>
       </c>
       <c r="Y230" s="2">
         <v>136</v>
       </c>
       <c r="Z230" s="1" t="s">
-        <v>4287</v>
+        <v>4277</v>
       </c>
       <c r="AA230" s="2">
         <v>54</v>
       </c>
       <c r="AB230" s="1" t="s">
-        <v>4288</v>
+        <v>4278</v>
       </c>
       <c r="AC230" s="2">
         <v>465</v>
       </c>
       <c r="AD230" s="1" t="s">
-        <v>4289</v>
+        <v>4279</v>
       </c>
       <c r="AE230" s="2">
         <v>165</v>
       </c>
       <c r="AF230" s="1" t="s">
-        <v>4290</v>
+        <v>4280</v>
       </c>
       <c r="AG230" s="2">
         <v>329</v>
@@ -32426,30 +32422,30 @@
     </row>
     <row r="231" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A231" s="80" t="s">
-        <v>4236</v>
+        <v>4223</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>4224</v>
+        <v>4228</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>4219</v>
+        <v>4221</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>4220</v>
+        <v>4222</v>
       </c>
       <c r="F231" s="48" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Dead Impact：Survival Online.html</v>
       </c>
       <c r="G231" s="4" t="s">
-        <v>4241</v>
+        <v>4220</v>
       </c>
       <c r="H231" s="48" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Dead Impact：Survival Online.html</v>
       </c>
-      <c r="I231" s="49" t="s">
-        <v>4246</v>
+      <c r="I231" t="s">
+        <v>4288</v>
       </c>
       <c r="J231" s="94" t="s">
         <v>4196</v>
@@ -32508,30 +32504,30 @@
     </row>
     <row r="232" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A232" s="3" t="s">
-        <v>4237</v>
+        <v>4282</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>4223</v>
+        <v>4227</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>4221</v>
+        <v>4225</v>
       </c>
       <c r="E232" s="4" t="s">
-        <v>4222</v>
+        <v>4226</v>
       </c>
       <c r="F232" s="48" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/無限子彈.html</v>
       </c>
       <c r="G232" s="4" t="s">
-        <v>4242</v>
+        <v>4224</v>
       </c>
       <c r="H232" s="48" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/無限子彈.html</v>
       </c>
-      <c r="I232" s="49" t="s">
-        <v>4247</v>
+      <c r="I232" t="s">
+        <v>4289</v>
       </c>
       <c r="J232" s="94" t="s">
         <v>4204</v>
@@ -32596,30 +32592,30 @@
     </row>
     <row r="233" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A233" s="80" t="s">
-        <v>4238</v>
+        <v>4239</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>4227</v>
+        <v>4231</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>4226</v>
+        <v>4230</v>
       </c>
       <c r="E233" s="4" t="s">
-        <v>4225</v>
+        <v>4229</v>
       </c>
       <c r="F233" s="48" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Dunkadillo.html</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>4243</v>
+        <v>4284</v>
       </c>
       <c r="H233" s="48" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Dunkadillo.html</v>
       </c>
-      <c r="I233" s="49" t="s">
-        <v>4248</v>
+      <c r="I233" t="s">
+        <v>4290</v>
       </c>
       <c r="J233" s="94" t="s">
         <v>4212</v>
@@ -50531,7 +50527,7 @@
       </c>
       <c r="E229" s="14" t="str">
         <f>IF(games!I229&lt;&gt;"", games!I229, "")</f>
-        <v>這世界怎麼了？滿大街都是殭屍，只有你這個傻氣又帶點小聰明的倖存者，才有辦法用各種古怪武器殺出重圍，順便把殭屍變成美味的「殭屍醬」。別再猶豫了，如果你懶得肝又想變強，那就別錯過這款遊戲！我們提供超方便的代儲值，讓你一秒變課長，享受快速安全的服務。再加上滿滿的禮包碼與兌換碼，讓你不用花一毛錢也能成為最強的殭屍終結者！</v>
+        <v>還在為找不到兌換碼、禮包碼煩惱嗎？這款《呷飽未？殭殭醬》讓你再也不用乞求官方施捨，直接用鈔能力碾壓那些非洲人。想快速變強，靠代儲值就行了！不用擔心被詐騙，我們提供最快速、最安全的代儲服務，讓你直接用鈔能力碾壓那些非洲人，讓他們在遊戲裡永遠抬不起頭。那些用外掛被鎖的，還不如來找我們！別再苦等活動了，課金才是唯一的王道！這是一個殘酷的遊戲世界，沒有人會同情弱者，只有強者才能稱霸！</v>
       </c>
       <c r="F229" s="75" t="s">
         <v>2648</v>
@@ -50561,97 +50557,97 @@
       </c>
       <c r="E230" s="14" t="str">
         <f>IF(games!I230&lt;&gt;"", games!I230, "")</f>
-        <v>你是否厭倦了那些纖細柔弱的遊戲角色？現在，是時候讓你的猛男魂覺醒了！《XXL猛漢町》讓你體驗什麼叫做真正的拳拳到肉！別再說自己課不起，我們提供最優惠的代儲值服務，讓你用最實惠的價格，享受最快速安全的交易。再加上一堆免費的禮包碼與兌換碼，讓你在遊戲中橫著走，誰也擋不住！</v>
+        <v>還在玩那些娘砲遊戲？《XXL猛漢町》讓你體驗什麼叫做真正的男子漢！禮包碼、兌換碼這種小玩意兒，我們才不稀罕。想在猛漢的世界裡出人頭地？靠代儲值快速安全地提升戰力，才是明智的選擇。別再傻傻地刷首抽了，我們幫你一步到位，直接享受最強猛漢的待遇！讓那些只會用腳色練功的玩家見識見識，什麼叫做真正的無敵！我們提供最快速、最安全的代儲服務，讓你直接稱霸猛漢的世界！</v>
       </c>
       <c r="F230" s="34" t="s">
-        <v>4258</v>
+        <v>4248</v>
       </c>
       <c r="G230" s="13" t="s">
-        <v>4259</v>
+        <v>4249</v>
       </c>
       <c r="H230" s="13" t="s">
         <v>2633</v>
       </c>
       <c r="I230" s="13" t="s">
+        <v>4250</v>
+      </c>
+      <c r="K230" s="17" t="s">
+        <v>4242</v>
+      </c>
+      <c r="L230" s="13" t="s">
+        <v>4240</v>
+      </c>
+      <c r="M230" s="18" t="s">
+        <v>4243</v>
+      </c>
+      <c r="N230" s="13" t="s">
+        <v>4241</v>
+      </c>
+      <c r="O230" s="18" t="s">
+        <v>4244</v>
+      </c>
+      <c r="P230" s="13" t="s">
+        <v>4246</v>
+      </c>
+      <c r="Q230" s="18" t="s">
+        <v>4245</v>
+      </c>
+      <c r="R230" s="13" t="s">
+        <v>4247</v>
+      </c>
+      <c r="S230" s="18" t="s">
+        <v>4251</v>
+      </c>
+      <c r="T230" s="13" t="s">
+        <v>4252</v>
+      </c>
+      <c r="U230" s="18" t="s">
+        <v>4253</v>
+      </c>
+      <c r="V230" s="13" t="s">
+        <v>4254</v>
+      </c>
+      <c r="W230" s="18" t="s">
+        <v>4255</v>
+      </c>
+      <c r="X230" s="13" t="s">
+        <v>4256</v>
+      </c>
+      <c r="Y230" s="18" t="s">
+        <v>4257</v>
+      </c>
+      <c r="Z230" s="13" t="s">
+        <v>4268</v>
+      </c>
+      <c r="AA230" s="18" t="s">
+        <v>4258</v>
+      </c>
+      <c r="AB230" s="13" t="s">
+        <v>4267</v>
+      </c>
+      <c r="AC230" s="18" t="s">
+        <v>4259</v>
+      </c>
+      <c r="AD230" s="13" t="s">
+        <v>4266</v>
+      </c>
+      <c r="AE230" s="18" t="s">
         <v>4260</v>
       </c>
-      <c r="K230" s="17" t="s">
-        <v>4252</v>
-      </c>
-      <c r="L230" s="13" t="s">
-        <v>4250</v>
-      </c>
-      <c r="M230" s="18" t="s">
-        <v>4253</v>
-      </c>
-      <c r="N230" s="13" t="s">
-        <v>4251</v>
-      </c>
-      <c r="O230" s="18" t="s">
-        <v>4254</v>
-      </c>
-      <c r="P230" s="13" t="s">
-        <v>4256</v>
-      </c>
-      <c r="Q230" s="18" t="s">
-        <v>4255</v>
-      </c>
-      <c r="R230" s="13" t="s">
-        <v>4257</v>
-      </c>
-      <c r="S230" s="18" t="s">
+      <c r="AF230" s="13" t="s">
+        <v>4265</v>
+      </c>
+      <c r="AG230" s="18" t="s">
         <v>4261</v>
       </c>
-      <c r="T230" s="13" t="s">
+      <c r="AH230" s="13" t="s">
+        <v>4264</v>
+      </c>
+      <c r="AI230" s="18" t="s">
         <v>4262</v>
       </c>
-      <c r="U230" s="18" t="s">
+      <c r="AJ230" s="13" t="s">
         <v>4263</v>
-      </c>
-      <c r="V230" s="13" t="s">
-        <v>4264</v>
-      </c>
-      <c r="W230" s="18" t="s">
-        <v>4265</v>
-      </c>
-      <c r="X230" s="13" t="s">
-        <v>4266</v>
-      </c>
-      <c r="Y230" s="18" t="s">
-        <v>4267</v>
-      </c>
-      <c r="Z230" s="13" t="s">
-        <v>4278</v>
-      </c>
-      <c r="AA230" s="18" t="s">
-        <v>4268</v>
-      </c>
-      <c r="AB230" s="13" t="s">
-        <v>4277</v>
-      </c>
-      <c r="AC230" s="18" t="s">
-        <v>4269</v>
-      </c>
-      <c r="AD230" s="13" t="s">
-        <v>4276</v>
-      </c>
-      <c r="AE230" s="18" t="s">
-        <v>4270</v>
-      </c>
-      <c r="AF230" s="13" t="s">
-        <v>4275</v>
-      </c>
-      <c r="AG230" s="18" t="s">
-        <v>4271</v>
-      </c>
-      <c r="AH230" s="13" t="s">
-        <v>4274</v>
-      </c>
-      <c r="AI230" s="18" t="s">
-        <v>4272</v>
-      </c>
-      <c r="AJ230" s="13" t="s">
-        <v>4273</v>
       </c>
     </row>
     <row r="231" spans="1:36" ht="22.5" customHeight="1">
@@ -50669,7 +50665,7 @@
       </c>
       <c r="E231" s="14" t="str">
         <f>IF(games!I231&lt;&gt;"", games!I231, "")</f>
-        <v>厭倦了單打獨鬥嗎？歡迎來到這個殭屍橫行的世界，你不只得想辦法活下去，還得隨時提防其他玩家。我們知道你很忙，沒時間慢慢農資源，所以我們提供了代儲值服務，讓你體驗什麼叫「用錢砸死殭屍」。保證快速安全，還有一大堆禮包碼跟兌換碼等著你，讓你輕鬆超車，成為末日世界的王者！</v>
+        <v>別再相信那些號稱佛心、免課金的遊戲了！《Dead Impact：Survival Online》告訴你，沒有錢寸步難行。找不到兌換碼？別浪費時間了。想要在末日生存下來，除了子彈，最重要的是你的錢包深度。透過我們快速安全的代儲值服務，讓你成為末日裡最閃亮的倖存者！那些在論壇上求禮包碼的，不過是一群可憐蟲罷了。這個世界不需要弱者，只有強者才能生存！別再猶豫了，現在就行動吧！</v>
       </c>
       <c r="F231" s="75" t="s">
         <v>2648</v>
@@ -50699,7 +50695,7 @@
       </c>
       <c r="E232" s="14" t="str">
         <f>IF(games!I232&lt;&gt;"", games!I232, "")</f>
-        <v>這是一款讓你體驗什麼叫做「射到手軟」的遊戲！《無限子彈》讓你享受無腦射擊的快感，不用再煩惱子彈不夠用。如果你懶得農裝備，只想直接享受爽快感，沒問題，我們提供最優質的代儲值服務，快速安全又划算。別忘了，還有各種禮包碼和兌換碼等你來領，讓你輕鬆成為最強戰士，享受爆頭的樂趣！</v>
+        <v>「無限子彈」？別傻了，現實裡沒有什麼是無限的，除了你的消費能力。還在苦苦搜尋兌換碼跟禮包碼？與其浪費時間，不如直接享受我們快速安全的代儲值服務，一秒擁有無限資源。讓那些只會用腳色練功的玩家見識見識，什麼叫做真正的無限！在這個遊戲裡，沒有人會同情弱者，只有強者才能生存！我們提供最快速、最安全的代儲服務，讓你直接稱霸這個世界！</v>
       </c>
       <c r="F232" s="75" t="s">
         <v>2648</v>
@@ -50729,7 +50725,7 @@
       </c>
       <c r="E233" s="14" t="str">
         <f>IF(games!I233&lt;&gt;"", games!I233, "")</f>
-        <v>還在玩那些一成不變的籃球遊戲嗎？現在是土撥鼠灌籃的時代了！《Dunkadillo》這款遊戲充滿了古怪的角色和讓人摸不著頭緒的玩法。如果你想在比賽中輕鬆灌爆對手，又不願意花時間慢慢練習，那就來試試我們的代儲值服務，保證快速安全。此外，還有滿滿的禮包碼和兌換碼讓你領到手軟，讓你的土撥鼠成為灌籃界的傳奇！</v>
+        <v>還在玩那些要你肝要你課的爛遊戲嗎？《Dunkadillo》讓你體驗最純粹的籃球樂趣，不用再擔心兌換碼、禮包碼找不到，也不用煩惱代儲值不安全。我們提供的服務讓你快速又安全的享受遊戲，而不是無止盡的農。讓那些自稱高手卻只會到處找攻略的玩家知道，什麼才是真正的高速通關！在這個遊戲裡，沒有人會同情弱者，只有強者才能稱霸！</v>
       </c>
       <c r="F233" s="75" t="s">
         <v>2648</v>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -16179,20 +16179,448 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>還在為找不到兌換碼、禮包碼煩惱嗎？這款《呷飽未？殭殭醬》讓你再也不用乞求官方施捨，直接用鈔能力碾壓那些非洲人。想快速變強，靠代儲值就行了！不用擔心被詐騙，我們提供最快速、最安全的代儲服務，讓你直接用鈔能力碾壓那些非洲人，讓他們在遊戲裡永遠抬不起頭。那些用外掛被鎖的，還不如來找我們！別再苦等活動了，課金才是唯一的王道！這是一個殘酷的遊戲世界，沒有人會同情弱者，只有強者才能稱霸！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>還在玩那些娘砲遊戲？《XXL猛漢町》讓你體驗什麼叫做真正的男子漢！禮包碼、兌換碼這種小玩意兒，我們才不稀罕。想在猛漢的世界裡出人頭地？靠代儲值快速安全地提升戰力，才是明智的選擇。別再傻傻地刷首抽了，我們幫你一步到位，直接享受最強猛漢的待遇！讓那些只會用腳色練功的玩家見識見識，什麼叫做真正的無敵！我們提供最快速、最安全的代儲服務，讓你直接稱霸猛漢的世界！</t>
-  </si>
-  <si>
-    <t>別再相信那些號稱佛心、免課金的遊戲了！《Dead Impact：Survival Online》告訴你，沒有錢寸步難行。找不到兌換碼？別浪費時間了。想要在末日生存下來，除了子彈，最重要的是你的錢包深度。透過我們快速安全的代儲值服務，讓你成為末日裡最閃亮的倖存者！那些在論壇上求禮包碼的，不過是一群可憐蟲罷了。這個世界不需要弱者，只有強者才能生存！別再猶豫了，現在就行動吧！</t>
-  </si>
-  <si>
-    <t>「無限子彈」？別傻了，現實裡沒有什麼是無限的，除了你的消費能力。還在苦苦搜尋兌換碼跟禮包碼？與其浪費時間，不如直接享受我們快速安全的代儲值服務，一秒擁有無限資源。讓那些只會用腳色練功的玩家見識見識，什麼叫做真正的無限！在這個遊戲裡，沒有人會同情弱者，只有強者才能生存！我們提供最快速、最安全的代儲服務，讓你直接稱霸這個世界！</t>
-  </si>
-  <si>
-    <t>還在玩那些要你肝要你課的爛遊戲嗎？《Dunkadillo》讓你體驗最純粹的籃球樂趣，不用再擔心兌換碼、禮包碼找不到，也不用煩惱代儲值不安全。我們提供的服務讓你快速又安全的享受遊戲，而不是無止盡的農。讓那些自稱高手卻只會到處找攻略的玩家知道，什麼才是真正的高速通關！在這個遊戲裡，沒有人會同情弱者，只有強者才能稱霸！</t>
+    <r>
+      <t>這款遊戲聽起來就很鬧！《呷飽未？殭殭醬》看著一群可愛又有趣的殭屍醬在末日世界裡奮力求生，你還在等什麼？趕快來體驗這款充滿挑戰與黑色幽默的生存冒險！什麼？你說玩到一半卡關、想變強又懶得農？別傻了，你以為我們是佛心公司嗎？當然不是！但為了你那高貴的自尊心，我們還是提供了多種加速變強的方式，包括不時釋出的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兌換碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，還有保證</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>快速安全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，讓你一秒成為末日最強！還不趕快跟上，讓你的殭屍醬成為最風騷的那一隻！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>這遊戲名字聽起來就很有「份量」！如果你厭倦了那些纖細弱小的角色，想體驗肌肉爆棚、拳拳到肉的快感，那《XXL猛漢町》絕對是你的菜。我們深知你對力量的渴望，但又懶得花時間從頭開始練起。沒關係，我們早已為你準備好</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兌換碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>與</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，讓你輕輕鬆鬆就擁有一身傲人肌肉。此外，我們還有</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>快速安全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，讓你瞬間成為鎮上最強的猛漢，免去農怪的痛苦。別再猶豫了，一起加入這場猛男的盛宴，用你的拳頭證明誰才是最頂的！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>你覺得自己是末日求生高手？那來試試《Dead Impact》吧！在這個殭屍橫行的世界裡，你將與其他玩家組隊，或獨自一人面對無盡的屍潮。你以為你夠強大？別天真了！想在末日活下去，光靠技術是不夠的。我們知道你不想輸在起跑點，所以特別提供了各種</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兌換碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>和</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，讓你在物資匱乏的末日世界中領先一步。至於那些想直接封頂的玩家，我們也準備了</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>快速安全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，讓你輕鬆成為殭屍堆中的王者。別再掙扎了，快來加入我們，用你的實力（或鈔能力）碾壓所有敵人！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>是不是覺得彈藥老是不夠用？是不是厭倦了每次戰鬥都得精打細算？那《無限子彈》絕對能滿足你的火力慾望！這款遊戲讓你體驗子彈像不用錢一樣狂噴的爽快感。不過，別以為子彈無限就能輕鬆破關。想更順利地通關，除了靠你的技術，更需要額外的資源！我們知道你懶得花時間收集，所以提供了定時釋出的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兌換碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>和</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，讓你輕鬆獲得強力武器和道具。而對於那些想更快變強的人，我們也有</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>快速安全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，讓你一秒成為戰場上的「移動軍火庫」。別再猶豫了，讓你的槍口冒煙吧！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>你準備好挑戰地心引力了嗎？《Dunkadillo》將帶你進入一場充滿挑戰與創意的灌籃冒險！在這個奇妙的世界裡，你將操控可愛的卡咪龜，用精準的技巧將球灌進籃框。你以為這遊戲只有可愛而已嗎？別鬧了，想打出完美灌籃可沒那麼容易！我們知道你可能會感到沮喪，但我們準備了</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兌換碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>與</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，幫助你解鎖更多酷炫造型和能力。如果你想一步登天、成為灌籃大師，我們的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>快速安全代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務也能幫你輕鬆達成。別再看著螢幕發呆了，快來成為灌籃高手，讓你的卡咪龜灌出屬於自己的傳奇！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -50527,7 +50955,7 @@
       </c>
       <c r="E229" s="14" t="str">
         <f>IF(games!I229&lt;&gt;"", games!I229, "")</f>
-        <v>還在為找不到兌換碼、禮包碼煩惱嗎？這款《呷飽未？殭殭醬》讓你再也不用乞求官方施捨，直接用鈔能力碾壓那些非洲人。想快速變強，靠代儲值就行了！不用擔心被詐騙，我們提供最快速、最安全的代儲服務，讓你直接用鈔能力碾壓那些非洲人，讓他們在遊戲裡永遠抬不起頭。那些用外掛被鎖的，還不如來找我們！別再苦等活動了，課金才是唯一的王道！這是一個殘酷的遊戲世界，沒有人會同情弱者，只有強者才能稱霸！</v>
+        <v>這款遊戲聽起來就很鬧！《呷飽未？殭殭醬》看著一群可愛又有趣的殭屍醬在末日世界裡奮力求生，你還在等什麼？趕快來體驗這款充滿挑戰與黑色幽默的生存冒險！什麼？你說玩到一半卡關、想變強又懶得農？別傻了，你以為我們是佛心公司嗎？當然不是！但為了你那高貴的自尊心，我們還是提供了多種加速變強的方式，包括不時釋出的兌換碼、禮包碼，還有保證快速安全的代儲值服務，讓你一秒成為末日最強！還不趕快跟上，讓你的殭屍醬成為最風騷的那一隻！</v>
       </c>
       <c r="F229" s="75" t="s">
         <v>2648</v>
@@ -50557,7 +50985,7 @@
       </c>
       <c r="E230" s="14" t="str">
         <f>IF(games!I230&lt;&gt;"", games!I230, "")</f>
-        <v>還在玩那些娘砲遊戲？《XXL猛漢町》讓你體驗什麼叫做真正的男子漢！禮包碼、兌換碼這種小玩意兒，我們才不稀罕。想在猛漢的世界裡出人頭地？靠代儲值快速安全地提升戰力，才是明智的選擇。別再傻傻地刷首抽了，我們幫你一步到位，直接享受最強猛漢的待遇！讓那些只會用腳色練功的玩家見識見識，什麼叫做真正的無敵！我們提供最快速、最安全的代儲服務，讓你直接稱霸猛漢的世界！</v>
+        <v>這遊戲名字聽起來就很有「份量」！如果你厭倦了那些纖細弱小的角色，想體驗肌肉爆棚、拳拳到肉的快感，那《XXL猛漢町》絕對是你的菜。我們深知你對力量的渴望，但又懶得花時間從頭開始練起。沒關係，我們早已為你準備好兌換碼與禮包碼，讓你輕輕鬆鬆就擁有一身傲人肌肉。此外，我們還有快速安全的代儲值服務，讓你瞬間成為鎮上最強的猛漢，免去農怪的痛苦。別再猶豫了，一起加入這場猛男的盛宴，用你的拳頭證明誰才是最頂的！</v>
       </c>
       <c r="F230" s="34" t="s">
         <v>4248</v>
@@ -50665,7 +51093,7 @@
       </c>
       <c r="E231" s="14" t="str">
         <f>IF(games!I231&lt;&gt;"", games!I231, "")</f>
-        <v>別再相信那些號稱佛心、免課金的遊戲了！《Dead Impact：Survival Online》告訴你，沒有錢寸步難行。找不到兌換碼？別浪費時間了。想要在末日生存下來，除了子彈，最重要的是你的錢包深度。透過我們快速安全的代儲值服務，讓你成為末日裡最閃亮的倖存者！那些在論壇上求禮包碼的，不過是一群可憐蟲罷了。這個世界不需要弱者，只有強者才能生存！別再猶豫了，現在就行動吧！</v>
+        <v>你覺得自己是末日求生高手？那來試試《Dead Impact》吧！在這個殭屍橫行的世界裡，你將與其他玩家組隊，或獨自一人面對無盡的屍潮。你以為你夠強大？別天真了！想在末日活下去，光靠技術是不夠的。我們知道你不想輸在起跑點，所以特別提供了各種兌換碼和禮包碼，讓你在物資匱乏的末日世界中領先一步。至於那些想直接封頂的玩家，我們也準備了快速安全的代儲值服務，讓你輕鬆成為殭屍堆中的王者。別再掙扎了，快來加入我們，用你的實力（或鈔能力）碾壓所有敵人！</v>
       </c>
       <c r="F231" s="75" t="s">
         <v>2648</v>
@@ -50695,7 +51123,7 @@
       </c>
       <c r="E232" s="14" t="str">
         <f>IF(games!I232&lt;&gt;"", games!I232, "")</f>
-        <v>「無限子彈」？別傻了，現實裡沒有什麼是無限的，除了你的消費能力。還在苦苦搜尋兌換碼跟禮包碼？與其浪費時間，不如直接享受我們快速安全的代儲值服務，一秒擁有無限資源。讓那些只會用腳色練功的玩家見識見識，什麼叫做真正的無限！在這個遊戲裡，沒有人會同情弱者，只有強者才能生存！我們提供最快速、最安全的代儲服務，讓你直接稱霸這個世界！</v>
+        <v>是不是覺得彈藥老是不夠用？是不是厭倦了每次戰鬥都得精打細算？那《無限子彈》絕對能滿足你的火力慾望！這款遊戲讓你體驗子彈像不用錢一樣狂噴的爽快感。不過，別以為子彈無限就能輕鬆破關。想更順利地通關，除了靠你的技術，更需要額外的資源！我們知道你懶得花時間收集，所以提供了定時釋出的兌換碼和禮包碼，讓你輕鬆獲得強力武器和道具。而對於那些想更快變強的人，我們也有快速安全的代儲值服務，讓你一秒成為戰場上的「移動軍火庫」。別再猶豫了，讓你的槍口冒煙吧！</v>
       </c>
       <c r="F232" s="75" t="s">
         <v>2648</v>
@@ -50725,7 +51153,7 @@
       </c>
       <c r="E233" s="14" t="str">
         <f>IF(games!I233&lt;&gt;"", games!I233, "")</f>
-        <v>還在玩那些要你肝要你課的爛遊戲嗎？《Dunkadillo》讓你體驗最純粹的籃球樂趣，不用再擔心兌換碼、禮包碼找不到，也不用煩惱代儲值不安全。我們提供的服務讓你快速又安全的享受遊戲，而不是無止盡的農。讓那些自稱高手卻只會到處找攻略的玩家知道，什麼才是真正的高速通關！在這個遊戲裡，沒有人會同情弱者，只有強者才能稱霸！</v>
+        <v>你準備好挑戰地心引力了嗎？《Dunkadillo》將帶你進入一場充滿挑戰與創意的灌籃冒險！在這個奇妙的世界裡，你將操控可愛的卡咪龜，用精準的技巧將球灌進籃框。你以為這遊戲只有可愛而已嗎？別鬧了，想打出完美灌籃可沒那麼容易！我們知道你可能會感到沮喪，但我們準備了兌換碼與禮包碼，幫助你解鎖更多酷炫造型和能力。如果你想一步登天、成為灌籃大師，我們的快速安全代儲值服務也能幫你輕鬆達成。別再看著螢幕發呆了，快來成為灌籃高手，讓你的卡咪龜灌出屬於自己的傳奇！</v>
       </c>
       <c r="F233" s="75" t="s">
         <v>2648</v>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6381" uniqueCount="4291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6537" uniqueCount="4394">
   <si>
     <t>Facebook</t>
   </si>
@@ -16622,12 +16622,355 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>遺跡的地平線</t>
+  </si>
+  <si>
+    <t>三國將將好</t>
+  </si>
+  <si>
+    <t>七騎士 Re：BIRTH</t>
+  </si>
+  <si>
+    <t>異界三國：死神契約</t>
+  </si>
+  <si>
+    <t>魔法師之徒</t>
+  </si>
+  <si>
+    <t>三國魂將傳</t>
+  </si>
+  <si>
+    <t>SL666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SL777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SL888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/horizonofruinstw</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E9%81%BA%E8%B7%A1%E7%9A%84%E5%9C%B0%E5%B9%B3%E7%B7%9A/id6747746222?fbclid=IwY2xjawMwta1leHRuA2FlbQIxMABicmlkETFIRVo4dUU2SWN0ckQ5NTFRAR7QCiAzwbqJ8VT7zPytXTU7Kb4zGM9vznMlZyDFZhvbMk811z-xyvU_-3DVvQ_aem_xyiUr4u70bCrUY0BXNIDcg</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.slsmsecond.tw.and&amp;hl=zh_TW&amp;fbclid=IwY2xjawMwta5leHRuA2FlbQIxMABicmlkETFIRVo4dUU2SWN0ckQ5NTFRAR4LCrnr8r0HDi9XXxbyRmP8Kgg_yOYjZ6j9za7Hj7a4jhbTM4-nVjiEf89wRQ_aem_kucaGaTsJ9U4Q7oJPq3xIg</t>
+  </si>
+  <si>
+    <t>https://www.rhinosgamestwhk.com/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61557443657424</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/officialsevenknightsrebirth/?brand_redir=466107870223667</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/death3kingdoms.mover</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/mageduelling</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/sghjz</t>
+  </si>
+  <si>
+    <t>https://www.sunjethk.com/sg/</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.gallop.tw&amp;fbclid=IwY2xjawMwtgFleHRuA2FlbQIxMABicmlkETFsZW1Yb0FGMmY1WWlsZTJzAR7p73Av7dnuHo8Xnq0Q-ID48JHJV43Y0-GFZQmOvUn_KR2JlWptUk3KHJUFzQ_aem_ZUR-hBgHuaVs9NAkcRzBcQ</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E4%B8%89%E5%9C%8B%E5%B0%87%E5%B0%87%E5%A5%BD/id6748985711?ppid=62af15db-5745-4fe6-af32-91578f791f01&amp;fbclid=IwY2xjawMwtgJleHRuA2FlbQIxMABicmlkETFsZW1Yb0FGMmY1WWlsZTJzAR5v_zNO4vHWmRZqL2za7JU_47zG8F88IBwbH9Ky-guCbPVbbmVMRlRodwlOpg_aem_bVpvCBKYt2ugKrk90Q2-7g</t>
+  </si>
+  <si>
+    <t>https://sena.netmarble.com/en/preorder?fbclid=IwY2xjawMwtg1leHRuA2FlbQIxMABicmlkETFsZW1Yb0FGMmY1WWlsZTJzAR7Ws9yOK0tFPfvCP1vEMlIca3YSiCmthnnKfb25REyfXxyiepdxupMVAfWhhg_aem_8hVLmq1IwgKUGr5Llmlh1A</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/us/app/seven-knights-re-birth/id6479595079</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.netmarble.tskgb</t>
+  </si>
+  <si>
+    <t>https://death3kings.movergames.com/event/pre/</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E7%95%B0%E7%95%8C%E4%B8%89%E5%9C%8B-%E6%AD%BB%E7%A5%9E%E5%A5%91%E7%B4%84/id6745937584</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.mover.twqyfhl</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.whsgz.gp&amp;fbclid=IwY2xjawMwtiNleHRuA2FlbQIxMABicmlkETFsZW1Yb0FGMmY1WWlsZTJzAR7C9y9DceXoL6YQK0naJqagvxLC8pW0kjGDCIC7D_9ME0W1HNZnMwfP8Rjsgw_aem_11PDGdQYUH8ZpLgZ1--2-w</t>
+  </si>
+  <si>
+    <t>https://www.liongame.net/whsgz/?fbclid=IwY2xjawMwtiNleHRuA2FlbQIxMABicmlkETFsZW1Yb0FGMmY1WWlsZTJzAR5JhEYj1xyAbg9GIL3E85BOWaG31F-FEBE891QMVyV31lWFIquiiNyrojvs7A_aem_x78YuW2oWbYkaDZSU44uYw</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/hk/app/%E4%B8%89%E5%9C%8B%E9%AD%82%E5%B0%87%E5%82%B3/id6751398562</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/hk/app/%E9%AD%94%E6%B3%95%E5%B8%AB%E4%B9%8B%E5%BE%92/id6747369877</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.teco.magicduel</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/mageduelling/</t>
+  </si>
+  <si>
+    <t>別再傻傻等官方佛心給禮包碼了，想在《遺跡的地平線》稱霸，就得自己動手豐衣足食。我們提供的兌換碼和禮包碼，保證讓你拿到手軟。至於代儲值？當然是快速又安全，別再用那些來路不明的平台了，你的肝寶貝、帳號寶貝，由我們來守護。想知道什麼是贏在起跑點嗎？就是別人還在慢慢農，你已經用我們的服務直接飛天了。別說我沒提醒你，機會是不等人的，錯過就要再等一年啦。如果你還在擔心戰力太低，被路人嘲笑，那真的別再猶豫了，快來加入我們的行列，讓那些對手看看什麼叫做「資源碾壓」，從此告別苦哈哈的冒險生涯。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩《三國將將好》還在慢慢推圖？別鬧了，你的對手早就用我們的兌換碼和禮包碼把戰力堆到你看不懂的境界了。我們的代儲值服務，給你最快速、最安全的加值體驗，讓你一秒變神豪，把那些還在課金猶豫不決的玩家遠遠甩在身後。別再說什麼「佛系」了，真正的佛系是資源多到用不完，而不是窮到只剩雙手合十。想逆天改命？從現在開始，讓你的將領比別人的更強大、更無敵，輕鬆征服整個三國世界。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>還在等《七騎士 Re：BIRTH》的官方公告？醒醒吧，真正的福利都在我們這裡。我們的兌換碼和禮包碼，讓你不用看臉，直接把稀有道具帶回家。想要快速安全地變強？我們的代儲值服務讓你省去繁瑣步驟，輕鬆稱霸全場。別再當那個被虐的弱雞了，加入我們的行列，讓那些對手看看什麼叫做「資源碾壓」。這遊戲的戰略再怎麼厲害，也比不過別人用錢堆出來的戰力。別再說什麼「佛系」了，真正的佛系是資源多到用不完，而不是窮到只剩雙手合十。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>別再當《魔法師之徒》裡的菜鳥了，想變強？先學會用我們的兌換碼和禮包碼。不用花時間刷刷刷，稀有道具直接入袋，讓你的魔法比別人的更強大。我們的代儲值服務，讓你快速又安全地擁有海量資源，將那些還在為金幣煩惱的玩家遠遠拋在腦後。別再說自己是非洲人了，是你不懂方法，懂嗎？當你擁有無限的資源時，任何魔法都將變得簡單。這款遊戲強調策略，但當你擁有無與倫比的資源時，任何策略都將變得簡單。想成為排行榜上的傳奇？這就是你的捷徑。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在《三國魂將傳》中，你還在努力招募將領？別傻了，真正的強者都用兌換碼和禮包碼直接領取資源了。我們的代儲值服務，快速又安全，讓你輕鬆超越那些還在慢慢肝的玩家。別再說什麼「肝帝」了，時間寶貴，用我們的方式，把時間省下來享受遊戲，而不是被遊戲玩。想稱霸三國，就從這裡開始。這款遊戲強調策略，但當你擁有無與倫比的資源時，任何策略都將變得簡單。想成為排行榜上的傳奇？這就是你的捷徑。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在《異界三國：死神契約》的世界裡，你還在辛辛苦苦推圖？別鬧了，你的對手早已透過我們的兌換碼和禮包碼，把戰力堆到你望塵莫及。我們的代儲值服務，保證快速又安全，讓你一秒變身課長，輕鬆超車，將那些還在農資源的玩家遠遠甩在身後。別再相信什麼「用愛發電」了，有課金才是王道。這款遊戲強調策略，但當你擁有無與倫比的資源時，任何策略都將變得簡單。想成為排行榜上的傳奇？這就是你的捷徑，省下你寶貴的睡眠時間，告別被虐的苦日子。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>adkt999</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>強健核心×500、礦石×100、金幣×1000、萬象萌種×5</t>
+  </si>
+  <si>
+    <t>主畫面左上角頭像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點兌換碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>手機玩家：前往官網序號兌換頁 → 輸入玩家ID與序號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC玩家：遊戲內直接於序號輸入區兌換</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>901MMNAG9NKIQE7O</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>901RC4SQK83CB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>901WXX5X8FTHM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>901KMMLVPVT5J</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>901Z7Q9LDMBBG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9013H4VDHXPZU</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9012PJ5CW24DD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>901YGEGQGAB8H</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>901VFTHQ6SSNP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9012ZLF3HQ24Z</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>90144V7QSWABV</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>901V3YY6FTUQ4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>901TCGE6DRSJK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>901SO2VA5XO5XG8R</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>90178H1QSMNJ0MQ5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>901D2VM4HRVU8MD6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>901VVP49Y2SFYSJ7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9017GS5A9VXJYG7P</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寶石×300</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>銀色相簿×3</t>
+  </si>
+  <si>
+    <t>菠蘿麵包×50</t>
+  </si>
+  <si>
+    <t>金色底片相機×10</t>
+  </si>
+  <si>
+    <t>金色的照片×10</t>
+  </si>
+  <si>
+    <t>高蛋白飲料×5</t>
+  </si>
+  <si>
+    <t>普通相簿×10</t>
+  </si>
+  <si>
+    <t>金色相簿×3</t>
+  </si>
+  <si>
+    <t>虹色相簿×1</t>
+  </si>
+  <si>
+    <t>虹色的照片×2</t>
+  </si>
+  <si>
+    <t>3290台幣道具商品</t>
+  </si>
+  <si>
+    <t>1690台幣道具商品</t>
+  </si>
+  <si>
+    <t>990台幣道具商品</t>
+  </si>
+  <si>
+    <t>870台幣道具商品</t>
+  </si>
+  <si>
+    <t>670台幣道具商品</t>
+  </si>
+  <si>
+    <t>490台幣道具商品</t>
+  </si>
+  <si>
+    <t>330台幣道具商品</t>
+  </si>
+  <si>
+    <t>270台幣道具商品</t>
+  </si>
+  <si>
+    <t>170台幣道具商品</t>
+  </si>
+  <si>
+    <t>100台幣道具商品</t>
+  </si>
+  <si>
+    <t>230台幣禮包</t>
+  </si>
+  <si>
+    <t>99.99美金商品</t>
+  </si>
+  <si>
+    <t>69.99美金商品</t>
+  </si>
+  <si>
+    <t>49.99美金商品</t>
+  </si>
+  <si>
+    <t>29.99美金商品</t>
+  </si>
+  <si>
+    <t>14.99美金商品</t>
+  </si>
+  <si>
+    <t>9.99美金商品</t>
+  </si>
+  <si>
+    <t>4.99美金商品</t>
+  </si>
+  <si>
+    <t>2.99美金商品</t>
+  </si>
+  <si>
+    <t>1.99美金商品</t>
+  </si>
+  <si>
+    <t>0.99美金商品</t>
+  </si>
+  <si>
+    <t>788HKD遊戲禮包</t>
+  </si>
+  <si>
+    <t>398HKD遊戲禮包</t>
+  </si>
+  <si>
+    <t>238HKD遊戲禮包</t>
+  </si>
+  <si>
+    <t>158HKD遊戲禮包</t>
+  </si>
+  <si>
+    <t>78HKD遊戲禮包</t>
+  </si>
+  <si>
+    <t>38HKD遊戲禮包</t>
+  </si>
+  <si>
+    <t>8HKD遊戲禮包</t>
+  </si>
+  <si>
+    <t>74.99禮包</t>
+  </si>
+  <si>
+    <t>16.99禮包</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -16778,8 +17121,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F0F0F"/>
+      <name val="Noto Sans TC"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F0F0F"/>
+      <name val="Inherit"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -16798,8 +17154,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -17003,12 +17365,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -17257,6 +17628,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -33052,64 +33427,508 @@
         <v>171</v>
       </c>
     </row>
-    <row r="234" spans="1:33" ht="22.5" customHeight="1">
+    <row r="234" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A234" s="80" t="s">
+        <v>4291</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>4300</v>
+      </c>
+      <c r="D234" s="48" t="s">
+        <v>4303</v>
+      </c>
+      <c r="E234" s="48" t="s">
+        <v>4301</v>
+      </c>
       <c r="F234" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/遺跡的地平線.html</v>
+      </c>
+      <c r="G234" s="48" t="s">
+        <v>4302</v>
       </c>
       <c r="H234" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="1:33" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/遺跡的地平線.html</v>
+      </c>
+      <c r="I234" s="49" t="s">
+        <v>4324</v>
+      </c>
+      <c r="J234" s="1" t="s">
+        <v>4364</v>
+      </c>
+      <c r="K234" s="2">
+        <v>2479</v>
+      </c>
+      <c r="L234" s="1" t="s">
+        <v>4365</v>
+      </c>
+      <c r="M234" s="2">
+        <v>1292</v>
+      </c>
+      <c r="N234" s="1" t="s">
+        <v>4366</v>
+      </c>
+      <c r="O234" s="2">
+        <v>757</v>
+      </c>
+      <c r="P234" s="1" t="s">
+        <v>4367</v>
+      </c>
+      <c r="Q234" s="2">
+        <v>665</v>
+      </c>
+      <c r="R234" s="1" t="s">
+        <v>4368</v>
+      </c>
+      <c r="S234" s="2">
+        <v>519</v>
+      </c>
+      <c r="T234" s="1" t="s">
+        <v>4369</v>
+      </c>
+      <c r="U234" s="2">
+        <v>380</v>
+      </c>
+      <c r="V234" s="1" t="s">
+        <v>4370</v>
+      </c>
+      <c r="W234" s="2">
+        <v>256</v>
+      </c>
+      <c r="X234" s="1" t="s">
+        <v>4371</v>
+      </c>
+      <c r="Y234" s="2">
+        <v>209</v>
+      </c>
+      <c r="Z234" s="1" t="s">
+        <v>4372</v>
+      </c>
+      <c r="AA234" s="2">
+        <v>140</v>
+      </c>
+      <c r="AB234" s="1" t="s">
+        <v>4373</v>
+      </c>
+      <c r="AC234" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="235" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A235" s="80" t="s">
+        <v>4292</v>
+      </c>
+      <c r="C235" s="47" t="s">
+        <v>4304</v>
+      </c>
+      <c r="D235" s="48" t="s">
+        <v>4309</v>
+      </c>
+      <c r="E235" s="48" t="s">
+        <v>4311</v>
+      </c>
       <c r="F235" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/三國將將好.html</v>
+      </c>
+      <c r="G235" s="48" t="s">
+        <v>4310</v>
       </c>
       <c r="H235" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="1:33" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/三國將將好.html</v>
+      </c>
+      <c r="I235" s="49" t="s">
+        <v>4325</v>
+      </c>
+      <c r="J235" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="K235" s="2">
+        <v>2286</v>
+      </c>
+      <c r="L235" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="M235" s="2">
+        <v>1139</v>
+      </c>
+      <c r="N235" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="O235" s="2">
+        <v>757</v>
+      </c>
+      <c r="P235" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q235" s="2">
+        <v>535</v>
+      </c>
+      <c r="R235" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="S235" s="2">
+        <v>380</v>
+      </c>
+      <c r="T235" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="U235" s="2">
+        <v>248</v>
+      </c>
+      <c r="V235" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="W235" s="2">
+        <v>171</v>
+      </c>
+      <c r="X235" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y235" s="2">
+        <v>124</v>
+      </c>
+      <c r="Z235" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="AA235" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="236" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A236" s="80" t="s">
+        <v>4293</v>
+      </c>
+      <c r="C236" s="47" t="s">
+        <v>4305</v>
+      </c>
+      <c r="D236" s="48" t="s">
+        <v>4312</v>
+      </c>
+      <c r="E236" s="48" t="s">
+        <v>4313</v>
+      </c>
       <c r="F236" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/七騎士 Re：BIRTH.html</v>
+      </c>
+      <c r="G236" s="48" t="s">
+        <v>4314</v>
       </c>
       <c r="H236" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="237" spans="1:33" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/七騎士 Re：BIRTH.html</v>
+      </c>
+      <c r="I236" s="49" t="s">
+        <v>4326</v>
+      </c>
+      <c r="J236" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="K236" s="2">
+        <v>2479</v>
+      </c>
+      <c r="L236" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="M236" s="2">
+        <v>1750</v>
+      </c>
+      <c r="N236" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="O236" s="2">
+        <v>1292</v>
+      </c>
+      <c r="P236" s="1" t="s">
+        <v>3987</v>
+      </c>
+      <c r="Q236" s="2">
+        <v>803</v>
+      </c>
+      <c r="R236" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="S236" s="2">
+        <v>757</v>
+      </c>
+      <c r="T236" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U236" s="2">
+        <v>519</v>
+      </c>
+      <c r="V236" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="W236" s="2">
+        <v>256</v>
+      </c>
+      <c r="X236" s="1" t="s">
+        <v>4374</v>
+      </c>
+      <c r="Y236" s="2">
+        <v>178</v>
+      </c>
+      <c r="Z236" s="1" t="s">
+        <v>3733</v>
+      </c>
+      <c r="AA236" s="2">
+        <v>107</v>
+      </c>
+      <c r="AB236" s="1" t="s">
+        <v>3734</v>
+      </c>
+      <c r="AC236" s="2">
+        <v>58</v>
+      </c>
+      <c r="AD236" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="AE236" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="237" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A237" s="80" t="s">
+        <v>4294</v>
+      </c>
+      <c r="C237" s="47" t="s">
+        <v>4306</v>
+      </c>
+      <c r="D237" s="48" t="s">
+        <v>4315</v>
+      </c>
+      <c r="E237" s="48" t="s">
+        <v>4316</v>
+      </c>
       <c r="F237" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/異界三國：死神契約.html</v>
+      </c>
+      <c r="G237" s="48" t="s">
+        <v>4317</v>
       </c>
       <c r="H237" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="1:33" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/異界三國：死神契約.html</v>
+      </c>
+      <c r="I237" s="49" t="s">
+        <v>4329</v>
+      </c>
+      <c r="J237" s="1" t="s">
+        <v>4375</v>
+      </c>
+      <c r="K237" s="2">
+        <v>2479</v>
+      </c>
+      <c r="L237" s="1" t="s">
+        <v>4376</v>
+      </c>
+      <c r="M237" s="2">
+        <v>1796</v>
+      </c>
+      <c r="N237" s="1" t="s">
+        <v>4377</v>
+      </c>
+      <c r="O237" s="2">
+        <v>1292</v>
+      </c>
+      <c r="P237" s="1" t="s">
+        <v>4378</v>
+      </c>
+      <c r="Q237" s="2">
+        <v>757</v>
+      </c>
+      <c r="R237" s="1" t="s">
+        <v>4379</v>
+      </c>
+      <c r="S237" s="2">
+        <v>380</v>
+      </c>
+      <c r="T237" s="1" t="s">
+        <v>4380</v>
+      </c>
+      <c r="U237" s="2">
+        <v>256</v>
+      </c>
+      <c r="V237" s="1" t="s">
+        <v>4381</v>
+      </c>
+      <c r="W237" s="2">
+        <v>140</v>
+      </c>
+      <c r="X237" s="1" t="s">
+        <v>4382</v>
+      </c>
+      <c r="Y237" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z237" s="1" t="s">
+        <v>4383</v>
+      </c>
+      <c r="AA237" s="2">
+        <v>58</v>
+      </c>
+      <c r="AB237" s="1" t="s">
+        <v>4384</v>
+      </c>
+      <c r="AC237" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="238" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A238" s="80" t="s">
+        <v>4295</v>
+      </c>
+      <c r="C238" s="47" t="s">
+        <v>4307</v>
+      </c>
+      <c r="D238" s="48" t="s">
+        <v>4323</v>
+      </c>
+      <c r="E238" s="48" t="s">
+        <v>4321</v>
+      </c>
       <c r="F238" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/魔法師之徒.html</v>
+      </c>
+      <c r="G238" s="48" t="s">
+        <v>4322</v>
       </c>
       <c r="H238" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="1:33" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/魔法師之徒.html</v>
+      </c>
+      <c r="I238" s="49" t="s">
+        <v>4327</v>
+      </c>
+      <c r="J238" s="1" t="s">
+        <v>4385</v>
+      </c>
+      <c r="K238" s="2">
+        <v>2479</v>
+      </c>
+      <c r="L238" s="1" t="s">
+        <v>4386</v>
+      </c>
+      <c r="M238" s="2">
+        <v>1292</v>
+      </c>
+      <c r="N238" s="1" t="s">
+        <v>4387</v>
+      </c>
+      <c r="O238" s="2">
+        <v>757</v>
+      </c>
+      <c r="P238" s="1" t="s">
+        <v>4388</v>
+      </c>
+      <c r="Q238" s="2">
+        <v>519</v>
+      </c>
+      <c r="R238" s="1" t="s">
+        <v>4389</v>
+      </c>
+      <c r="S238" s="2">
+        <v>256</v>
+      </c>
+      <c r="T238" s="1" t="s">
+        <v>4390</v>
+      </c>
+      <c r="U238" s="2">
+        <v>140</v>
+      </c>
+      <c r="V238" s="1" t="s">
+        <v>4391</v>
+      </c>
+      <c r="W238" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="239" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A239" s="80" t="s">
+        <v>4296</v>
+      </c>
+      <c r="C239" s="47" t="s">
+        <v>4308</v>
+      </c>
+      <c r="D239" s="48" t="s">
+        <v>4319</v>
+      </c>
+      <c r="E239" s="48" t="s">
+        <v>4320</v>
+      </c>
       <c r="F239" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/三國魂將傳.html</v>
+      </c>
+      <c r="G239" s="48" t="s">
+        <v>4318</v>
       </c>
       <c r="H239" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/三國魂將傳.html</v>
+      </c>
+      <c r="I239" s="49" t="s">
+        <v>4328</v>
+      </c>
+      <c r="J239" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="K239" s="2">
+        <v>2286</v>
+      </c>
+      <c r="L239" s="1" t="s">
+        <v>4392</v>
+      </c>
+      <c r="M239" s="2">
+        <v>1903</v>
+      </c>
+      <c r="N239" s="1" t="s">
+        <v>1661</v>
+      </c>
+      <c r="O239" s="2">
+        <v>1139</v>
+      </c>
+      <c r="P239" s="1" t="s">
+        <v>1662</v>
+      </c>
+      <c r="Q239" s="2">
+        <v>757</v>
+      </c>
+      <c r="R239" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="S239" s="2">
+        <v>519</v>
+      </c>
+      <c r="T239" s="1" t="s">
+        <v>4393</v>
+      </c>
+      <c r="U239" s="2">
+        <v>457</v>
+      </c>
+      <c r="V239" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="W239" s="2">
+        <v>380</v>
+      </c>
+      <c r="X239" s="1" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Y239" s="2">
+        <v>140</v>
+      </c>
+      <c r="Z239" s="1" t="s">
+        <v>4175</v>
+      </c>
+      <c r="AA239" s="2">
+        <v>58</v>
       </c>
     </row>
     <row r="240" spans="1:33" ht="22.5" customHeight="1">
@@ -36444,367 +37263,367 @@
     </row>
     <row r="573" spans="6:8">
       <c r="F573" s="47" t="str">
-        <f t="shared" ref="F573:F575" si="20">IF(A573="", "", "gift-codes.html?game=" &amp; A573)</f>
+        <f>IF(A573="", "", "gift-codes.html?game=" &amp; A573)</f>
         <v/>
       </c>
       <c r="H573" s="48" t="str">
-        <f t="shared" ref="H573:H631" si="21">IF(A573="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A573)</f>
+        <f t="shared" ref="H573:H631" si="20">IF(A573="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A573)</f>
         <v/>
       </c>
     </row>
     <row r="574" spans="6:8">
       <c r="F574" s="47" t="str">
+        <f>IF(A574="", "", "gift-codes.html?game=" &amp; A574)</f>
+        <v/>
+      </c>
+      <c r="H574" s="48" t="str">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="H574" s="48" t="str">
-        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="575" spans="6:8">
       <c r="F575" s="47" t="str">
+        <f>IF(A575="", "", "gift-codes.html?game=" &amp; A575)</f>
+        <v/>
+      </c>
+      <c r="H575" s="48" t="str">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="H575" s="48" t="str">
-        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="576" spans="6:8">
       <c r="H576" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="577" spans="8:8">
       <c r="H577" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="578" spans="8:8">
       <c r="H578" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="579" spans="8:8">
       <c r="H579" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="580" spans="8:8">
       <c r="H580" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="8:8">
       <c r="H581" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="8:8">
       <c r="H582" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="8:8">
       <c r="H583" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="8:8">
       <c r="H584" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="8:8">
       <c r="H585" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="8:8">
       <c r="H586" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="8:8">
       <c r="H587" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="8:8">
       <c r="H588" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="8:8">
       <c r="H589" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="8:8">
       <c r="H590" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="8:8">
       <c r="H591" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="8:8">
       <c r="H592" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="8:8">
       <c r="H593" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="8:8">
       <c r="H594" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="595" spans="8:8">
       <c r="H595" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="596" spans="8:8">
       <c r="H596" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="597" spans="8:8">
       <c r="H597" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="598" spans="8:8">
       <c r="H598" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="599" spans="8:8">
       <c r="H599" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="600" spans="8:8">
       <c r="H600" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="601" spans="8:8">
       <c r="H601" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="602" spans="8:8">
       <c r="H602" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="603" spans="8:8">
       <c r="H603" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="604" spans="8:8">
       <c r="H604" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="605" spans="8:8">
       <c r="H605" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="606" spans="8:8">
       <c r="H606" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="607" spans="8:8">
       <c r="H607" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="608" spans="8:8">
       <c r="H608" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="609" spans="8:8">
       <c r="H609" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="610" spans="8:8">
       <c r="H610" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="611" spans="8:8">
       <c r="H611" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="612" spans="8:8">
       <c r="H612" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="613" spans="8:8">
       <c r="H613" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="614" spans="8:8">
       <c r="H614" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="615" spans="8:8">
       <c r="H615" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="616" spans="8:8">
       <c r="H616" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="617" spans="8:8">
       <c r="H617" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="618" spans="8:8">
       <c r="H618" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="619" spans="8:8">
       <c r="H619" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="620" spans="8:8">
       <c r="H620" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="621" spans="8:8">
       <c r="H621" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="622" spans="8:8">
       <c r="H622" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="623" spans="8:8">
       <c r="H623" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="624" spans="8:8">
       <c r="H624" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="625" spans="8:8">
       <c r="H625" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="626" spans="8:8">
       <c r="H626" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="627" spans="8:8">
       <c r="H627" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="628" spans="8:8">
       <c r="H628" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="629" spans="8:8">
       <c r="H629" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="630" spans="8:8">
       <c r="H630" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="631" spans="8:8">
       <c r="H631" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -36954,9 +37773,10 @@
     <hyperlink ref="G233" r:id="rId140"/>
     <hyperlink ref="C233" r:id="rId141"/>
     <hyperlink ref="G230" r:id="rId142"/>
+    <hyperlink ref="C234" r:id="rId143"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId143"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId144"/>
 </worksheet>
 </file>
 
@@ -50037,7 +50857,7 @@
         <v>3899</v>
       </c>
     </row>
-    <row r="209" spans="1:39" ht="22.5" customHeight="1">
+    <row r="209" spans="1:46" ht="22.5" customHeight="1">
       <c r="A209" s="13" t="str">
         <f>IF(games!A209="", "", games!A209)</f>
         <v>我的勇者外傳</v>
@@ -50091,7 +50911,7 @@
         <v>3903</v>
       </c>
     </row>
-    <row r="210" spans="1:39" ht="22.5" customHeight="1">
+    <row r="210" spans="1:46" ht="22.5" customHeight="1">
       <c r="A210" s="13" t="str">
         <f>IF(games!A210="", "", games!A210)</f>
         <v>女神契約：異世界遠征隊</v>
@@ -50131,7 +50951,7 @@
       </c>
       <c r="M210" s="17"/>
     </row>
-    <row r="211" spans="1:39" ht="22.5" customHeight="1">
+    <row r="211" spans="1:46" ht="22.5" customHeight="1">
       <c r="A211" s="13" t="str">
         <f>IF(games!A211="", "", games!A211)</f>
         <v>Pixel Starships 2</v>
@@ -50161,7 +50981,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="212" spans="1:39" ht="22.5" customHeight="1">
+    <row r="212" spans="1:46" ht="22.5" customHeight="1">
       <c r="A212" s="13" t="str">
         <f>IF(games!A212="", "", games!A212)</f>
         <v>升級村莊大作戰</v>
@@ -50191,7 +51011,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="213" spans="1:39" ht="22.5" customHeight="1">
+    <row r="213" spans="1:46" ht="22.5" customHeight="1">
       <c r="A213" s="13" t="str">
         <f>IF(games!A213="", "", games!A213)</f>
         <v>新月同行</v>
@@ -50221,7 +51041,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="214" spans="1:39" ht="22.5" customHeight="1">
+    <row r="214" spans="1:46" ht="22.5" customHeight="1">
       <c r="A214" s="13" t="str">
         <f>IF(games!A214="", "", games!A214)</f>
         <v>超商勇者</v>
@@ -50251,7 +51071,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="215" spans="1:39" ht="22.5" customHeight="1">
+    <row r="215" spans="1:46" ht="22.5" customHeight="1">
       <c r="A215" s="13" t="str">
         <f>IF(games!A215="", "", games!A215)</f>
         <v>怪獸8號 THE GAME</v>
@@ -50281,7 +51101,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="216" spans="1:39" ht="22.5" customHeight="1">
+    <row r="216" spans="1:46" ht="22.5" customHeight="1">
       <c r="A216" s="13" t="str">
         <f>IF(games!A216="", "", games!A216)</f>
         <v>貓旅館物語</v>
@@ -50356,7 +51176,7 @@
         <v>4195</v>
       </c>
     </row>
-    <row r="217" spans="1:39" ht="22.5" customHeight="1">
+    <row r="217" spans="1:46" ht="22.5" customHeight="1">
       <c r="A217" s="13" t="str">
         <f>IF(games!A217="", "", games!A217)</f>
         <v>龍石戰爭</v>
@@ -50458,7 +51278,7 @@
         <v>3973</v>
       </c>
     </row>
-    <row r="218" spans="1:39" ht="22.5" customHeight="1">
+    <row r="218" spans="1:46" ht="22.5" customHeight="1">
       <c r="A218" s="13" t="str">
         <f>IF(games!A218="", "", games!A218)</f>
         <v>The King Of Fighters AFK</v>
@@ -50530,7 +51350,7 @@
         <v>4140</v>
       </c>
     </row>
-    <row r="219" spans="1:39" ht="22.5" customHeight="1">
+    <row r="219" spans="1:46" ht="22.5" customHeight="1">
       <c r="A219" s="13" t="str">
         <f>IF(games!A219="", "", games!A219)</f>
         <v>邪門鬼道</v>
@@ -50572,7 +51392,7 @@
         <v>3964</v>
       </c>
     </row>
-    <row r="220" spans="1:39" ht="22.5" customHeight="1">
+    <row r="220" spans="1:46" ht="22.5" customHeight="1" thickBot="1">
       <c r="A220" s="13" t="str">
         <f>IF(games!A220="", "", games!A220)</f>
         <v>Wind Breaker不良英雄譚</v>
@@ -50590,19 +51410,121 @@
         <v>想用拳頭守護街道，成為不良少年中的英雄？醒醒吧，你可能連街邊的小混混都打不過，只會成為被勒索午餐錢的那個。遊戲裡的戰鬥可不是靠著一腔熱血就能贏的，你那軟綿綿的拳頭只會讓對手覺得你在幫他按摩。為了讓自己看起來不那麼廢柴，你只能到處去求爺爺告奶奶，尋找官方施捨的禮包碼，換點強化道具。每一次成功輸入兌換碼，都像是給了你多一秒鐘在場上挨揍的時間。很快你就會明白，街頭的頂點不是靠拳頭決定的，而是由代儲值的金額決定的。別掙扎了，你的不良英雄譚，恐怕得從學會怎麼儲值開始寫起。</v>
       </c>
       <c r="F220" s="17" t="s">
-        <v>2648</v>
+        <v>4334</v>
       </c>
       <c r="G220" s="13" t="s">
-        <v>2648</v>
+        <v>4335</v>
       </c>
       <c r="K220" s="17" t="s">
-        <v>2648</v>
+        <v>4336</v>
       </c>
       <c r="L220" s="13" t="s">
-        <v>2648</v>
-      </c>
-    </row>
-    <row r="221" spans="1:39" ht="22.5" customHeight="1">
+        <v>4354</v>
+      </c>
+      <c r="M220" s="18" t="s">
+        <v>4337</v>
+      </c>
+      <c r="N220" s="97" t="s">
+        <v>4355</v>
+      </c>
+      <c r="O220" s="18" t="s">
+        <v>4338</v>
+      </c>
+      <c r="P220" s="97" t="s">
+        <v>4356</v>
+      </c>
+      <c r="Q220" s="18" t="s">
+        <v>4339</v>
+      </c>
+      <c r="R220" s="97" t="s">
+        <v>4356</v>
+      </c>
+      <c r="S220" s="18" t="s">
+        <v>4340</v>
+      </c>
+      <c r="T220" s="97" t="s">
+        <v>4356</v>
+      </c>
+      <c r="U220" s="18" t="s">
+        <v>4341</v>
+      </c>
+      <c r="V220" s="97" t="s">
+        <v>4357</v>
+      </c>
+      <c r="W220" s="18" t="s">
+        <v>4342</v>
+      </c>
+      <c r="X220" s="97" t="s">
+        <v>4357</v>
+      </c>
+      <c r="Y220" s="18" t="s">
+        <v>4343</v>
+      </c>
+      <c r="Z220" s="97" t="s">
+        <v>4357</v>
+      </c>
+      <c r="AA220" s="18" t="s">
+        <v>4344</v>
+      </c>
+      <c r="AB220" s="97" t="s">
+        <v>4357</v>
+      </c>
+      <c r="AC220" s="18" t="s">
+        <v>4345</v>
+      </c>
+      <c r="AD220" s="97" t="s">
+        <v>4358</v>
+      </c>
+      <c r="AE220" s="18" t="s">
+        <v>4346</v>
+      </c>
+      <c r="AF220" s="97" t="s">
+        <v>4359</v>
+      </c>
+      <c r="AG220" s="18" t="s">
+        <v>4347</v>
+      </c>
+      <c r="AH220" s="97" t="s">
+        <v>4359</v>
+      </c>
+      <c r="AI220" s="18" t="s">
+        <v>4348</v>
+      </c>
+      <c r="AJ220" s="97" t="s">
+        <v>4359</v>
+      </c>
+      <c r="AK220" s="18" t="s">
+        <v>4349</v>
+      </c>
+      <c r="AL220" s="98" t="s">
+        <v>4360</v>
+      </c>
+      <c r="AM220" s="18" t="s">
+        <v>4350</v>
+      </c>
+      <c r="AN220" s="97" t="s">
+        <v>4361</v>
+      </c>
+      <c r="AO220" s="18" t="s">
+        <v>4351</v>
+      </c>
+      <c r="AP220" s="97" t="s">
+        <v>4362</v>
+      </c>
+      <c r="AQ220" s="18" t="s">
+        <v>4352</v>
+      </c>
+      <c r="AR220" s="97" t="s">
+        <v>4362</v>
+      </c>
+      <c r="AS220" s="18" t="s">
+        <v>4353</v>
+      </c>
+      <c r="AT220" s="97" t="s">
+        <v>4363</v>
+      </c>
+    </row>
+    <row r="221" spans="1:46" ht="22.5" customHeight="1">
       <c r="A221" s="13" t="str">
         <f>IF(games!A221="", "", games!A221)</f>
         <v>野蠻生存錄</v>
@@ -50632,7 +51554,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="222" spans="1:39" ht="22.5" customHeight="1">
+    <row r="222" spans="1:46" ht="22.5" customHeight="1">
       <c r="A222" s="13" t="str">
         <f>IF(games!A222="", "", games!A222)</f>
         <v>萬獸崛起</v>
@@ -50692,7 +51614,7 @@
         <v>4084</v>
       </c>
     </row>
-    <row r="223" spans="1:39" ht="22.5" customHeight="1">
+    <row r="223" spans="1:46" ht="22.5" customHeight="1">
       <c r="A223" s="13" t="str">
         <f>IF(games!A223="", "", games!A223)</f>
         <v>劍靈神域</v>
@@ -50743,7 +51665,7 @@
         <v>4115</v>
       </c>
     </row>
-    <row r="224" spans="1:39" ht="22.5" customHeight="1">
+    <row r="224" spans="1:46" ht="22.5" customHeight="1">
       <c r="A224" s="13" t="str">
         <f>IF(games!A224="", "", games!A224)</f>
         <v>國王駕到！堡堡大作戰</v>
@@ -50897,17 +51819,29 @@
         <f>IF(games!I227&lt;&gt;"", games!I227, "")</f>
         <v>還在玩那些只能當花瓶的卡牌遊戲？別傻了！《魔鏡2：瘋狂的蛇姬》將顛覆你對回合制RPG的想像。在這裡，你將能解鎖傳說英雄、打造最強陣容，讓那些自以為是的對手嚐嚐什麼叫殘酷的勝利。遊戲福利多到你不敢相信，各種獨家兌換碼、禮包碼隨便拿，讓你戰力起飛。覺得升級太慢太累？沒關係，我們的代儲值服務讓你體驗什麼叫快速安全，一秒成為人上人，輕鬆碾壓所有對手，不用再當可憐的免費仔，讓別人看看什麼叫真正的歐洲血統！</v>
       </c>
-      <c r="F227" s="75" t="s">
-        <v>2648</v>
-      </c>
-      <c r="G227" s="76" t="s">
-        <v>2648</v>
+      <c r="F227" s="34" t="s">
+        <v>3787</v>
+      </c>
+      <c r="G227" s="13" t="s">
+        <v>3788</v>
+      </c>
+      <c r="H227" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I227" s="13" t="s">
+        <v>3789</v>
       </c>
       <c r="K227" s="75" t="s">
-        <v>2648</v>
+        <v>4297</v>
       </c>
       <c r="L227" s="76" t="s">
         <v>2648</v>
+      </c>
+      <c r="M227" s="18" t="s">
+        <v>4298</v>
+      </c>
+      <c r="O227" s="18" t="s">
+        <v>4299</v>
       </c>
     </row>
     <row r="228" spans="1:36" ht="22.5" customHeight="1">
@@ -50958,16 +51892,22 @@
         <v>這款遊戲聽起來就很鬧！《呷飽未？殭殭醬》看著一群可愛又有趣的殭屍醬在末日世界裡奮力求生，你還在等什麼？趕快來體驗這款充滿挑戰與黑色幽默的生存冒險！什麼？你說玩到一半卡關、想變強又懶得農？別傻了，你以為我們是佛心公司嗎？當然不是！但為了你那高貴的自尊心，我們還是提供了多種加速變強的方式，包括不時釋出的兌換碼、禮包碼，還有保證快速安全的代儲值服務，讓你一秒成為末日最強！還不趕快跟上，讓你的殭屍醬成為最風騷的那一隻！</v>
       </c>
       <c r="F229" s="75" t="s">
-        <v>2648</v>
+        <v>4332</v>
       </c>
       <c r="G229" s="76" t="s">
-        <v>2648</v>
+        <v>4333</v>
+      </c>
+      <c r="H229" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I229" s="13" t="s">
+        <v>3789</v>
       </c>
       <c r="K229" s="75" t="s">
-        <v>2648</v>
-      </c>
-      <c r="L229" s="76" t="s">
-        <v>2648</v>
+        <v>4330</v>
+      </c>
+      <c r="L229" s="97" t="s">
+        <v>4331</v>
       </c>
     </row>
     <row r="230" spans="1:36" ht="22.5" customHeight="1">
@@ -51171,109 +52111,181 @@
     <row r="234" spans="1:36" ht="22.5" customHeight="1">
       <c r="A234" s="13" t="str">
         <f>IF(games!A234="", "", games!A234)</f>
-        <v/>
+        <v>遺跡的地平線</v>
       </c>
       <c r="C234" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/遺跡的地平線-禮包碼.jpg</v>
       </c>
       <c r="D234" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/遺跡的地平線.html</v>
       </c>
       <c r="E234" s="14" t="str">
         <f>IF(games!I234&lt;&gt;"", games!I234, "")</f>
-        <v/>
+        <v>別再傻傻等官方佛心給禮包碼了，想在《遺跡的地平線》稱霸，就得自己動手豐衣足食。我們提供的兌換碼和禮包碼，保證讓你拿到手軟。至於代儲值？當然是快速又安全，別再用那些來路不明的平台了，你的肝寶貝、帳號寶貝，由我們來守護。想知道什麼是贏在起跑點嗎？就是別人還在慢慢農，你已經用我們的服務直接飛天了。別說我沒提醒你，機會是不等人的，錯過就要再等一年啦。如果你還在擔心戰力太低，被路人嘲笑，那真的別再猶豫了，快來加入我們的行列，讓那些對手看看什麼叫做「資源碾壓」，從此告別苦哈哈的冒險生涯。</v>
+      </c>
+      <c r="F234" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G234" s="76" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K234" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L234" s="76" t="s">
+        <v>2648</v>
       </c>
     </row>
     <row r="235" spans="1:36" ht="22.5" customHeight="1">
       <c r="A235" s="13" t="str">
         <f>IF(games!A235="", "", games!A235)</f>
-        <v/>
+        <v>三國將將好</v>
       </c>
       <c r="C235" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/三國將將好-禮包碼.jpg</v>
       </c>
       <c r="D235" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/三國將將好.html</v>
       </c>
       <c r="E235" s="14" t="str">
         <f>IF(games!I235&lt;&gt;"", games!I235, "")</f>
-        <v/>
+        <v>玩《三國將將好》還在慢慢推圖？別鬧了，你的對手早就用我們的兌換碼和禮包碼把戰力堆到你看不懂的境界了。我們的代儲值服務，給你最快速、最安全的加值體驗，讓你一秒變神豪，把那些還在課金猶豫不決的玩家遠遠甩在身後。別再說什麼「佛系」了，真正的佛系是資源多到用不完，而不是窮到只剩雙手合十。想逆天改命？從現在開始，讓你的將領比別人的更強大、更無敵，輕鬆征服整個三國世界。</v>
+      </c>
+      <c r="F235" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G235" s="76" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K235" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L235" s="76" t="s">
+        <v>2648</v>
       </c>
     </row>
     <row r="236" spans="1:36" ht="22.5" customHeight="1">
       <c r="A236" s="13" t="str">
         <f>IF(games!A236="", "", games!A236)</f>
-        <v/>
+        <v>七騎士 Re：BIRTH</v>
       </c>
       <c r="C236" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/七騎士 Re：BIRTH-禮包碼.jpg</v>
       </c>
       <c r="D236" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/七騎士 Re：BIRTH.html</v>
       </c>
       <c r="E236" s="14" t="str">
         <f>IF(games!I236&lt;&gt;"", games!I236, "")</f>
-        <v/>
+        <v>還在等《七騎士 Re：BIRTH》的官方公告？醒醒吧，真正的福利都在我們這裡。我們的兌換碼和禮包碼，讓你不用看臉，直接把稀有道具帶回家。想要快速安全地變強？我們的代儲值服務讓你省去繁瑣步驟，輕鬆稱霸全場。別再當那個被虐的弱雞了，加入我們的行列，讓那些對手看看什麼叫做「資源碾壓」。這遊戲的戰略再怎麼厲害，也比不過別人用錢堆出來的戰力。別再說什麼「佛系」了，真正的佛系是資源多到用不完，而不是窮到只剩雙手合十。</v>
+      </c>
+      <c r="F236" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G236" s="76" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K236" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L236" s="76" t="s">
+        <v>2648</v>
       </c>
     </row>
     <row r="237" spans="1:36" ht="22.5" customHeight="1">
       <c r="A237" s="13" t="str">
         <f>IF(games!A237="", "", games!A237)</f>
-        <v/>
+        <v>異界三國：死神契約</v>
       </c>
       <c r="C237" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/異界三國：死神契約-禮包碼.jpg</v>
       </c>
       <c r="D237" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/異界三國：死神契約.html</v>
       </c>
       <c r="E237" s="14" t="str">
         <f>IF(games!I237&lt;&gt;"", games!I237, "")</f>
-        <v/>
+        <v>在《異界三國：死神契約》的世界裡，你還在辛辛苦苦推圖？別鬧了，你的對手早已透過我們的兌換碼和禮包碼，把戰力堆到你望塵莫及。我們的代儲值服務，保證快速又安全，讓你一秒變身課長，輕鬆超車，將那些還在農資源的玩家遠遠甩在身後。別再相信什麼「用愛發電」了，有課金才是王道。這款遊戲強調策略，但當你擁有無與倫比的資源時，任何策略都將變得簡單。想成為排行榜上的傳奇？這就是你的捷徑，省下你寶貴的睡眠時間，告別被虐的苦日子。</v>
+      </c>
+      <c r="F237" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G237" s="76" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K237" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L237" s="76" t="s">
+        <v>2648</v>
       </c>
     </row>
     <row r="238" spans="1:36" ht="22.5" customHeight="1">
       <c r="A238" s="13" t="str">
         <f>IF(games!A238="", "", games!A238)</f>
-        <v/>
+        <v>魔法師之徒</v>
       </c>
       <c r="C238" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/魔法師之徒-禮包碼.jpg</v>
       </c>
       <c r="D238" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/魔法師之徒.html</v>
       </c>
       <c r="E238" s="14" t="str">
         <f>IF(games!I238&lt;&gt;"", games!I238, "")</f>
-        <v/>
+        <v>別再當《魔法師之徒》裡的菜鳥了，想變強？先學會用我們的兌換碼和禮包碼。不用花時間刷刷刷，稀有道具直接入袋，讓你的魔法比別人的更強大。我們的代儲值服務，讓你快速又安全地擁有海量資源，將那些還在為金幣煩惱的玩家遠遠拋在腦後。別再說自己是非洲人了，是你不懂方法，懂嗎？當你擁有無限的資源時，任何魔法都將變得簡單。這款遊戲強調策略，但當你擁有無與倫比的資源時，任何策略都將變得簡單。想成為排行榜上的傳奇？這就是你的捷徑。</v>
+      </c>
+      <c r="F238" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G238" s="76" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K238" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L238" s="76" t="s">
+        <v>2648</v>
       </c>
     </row>
     <row r="239" spans="1:36" ht="22.5" customHeight="1">
       <c r="A239" s="13" t="str">
         <f>IF(games!A239="", "", games!A239)</f>
-        <v/>
+        <v>三國魂將傳</v>
       </c>
       <c r="C239" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/三國魂將傳-禮包碼.jpg</v>
       </c>
       <c r="D239" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/三國魂將傳.html</v>
       </c>
       <c r="E239" s="14" t="str">
         <f>IF(games!I239&lt;&gt;"", games!I239, "")</f>
-        <v/>
+        <v>在《三國魂將傳》中，你還在努力招募將領？別傻了，真正的強者都用兌換碼和禮包碼直接領取資源了。我們的代儲值服務，快速又安全，讓你輕鬆超越那些還在慢慢肝的玩家。別再說什麼「肝帝」了，時間寶貴，用我們的方式，把時間省下來享受遊戲，而不是被遊戲玩。想稱霸三國，就從這裡開始。這款遊戲強調策略，但當你擁有無與倫比的資源時，任何策略都將變得簡單。想成為排行榜上的傳奇？這就是你的捷徑。</v>
+      </c>
+      <c r="F239" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G239" s="76" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K239" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L239" s="76" t="s">
+        <v>2648</v>
       </c>
     </row>
     <row r="240" spans="1:36" ht="22.5" customHeight="1">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6537" uniqueCount="4394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6561" uniqueCount="4413">
   <si>
     <t>Facebook</t>
   </si>
@@ -16964,6 +16964,68 @@
   </si>
   <si>
     <t>16.99禮包</t>
+  </si>
+  <si>
+    <t>ALBIS777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PMBX777</t>
+  </si>
+  <si>
+    <t>XX777</t>
+  </si>
+  <si>
+    <t>CDK773</t>
+  </si>
+  <si>
+    <t>RABBIT</t>
+  </si>
+  <si>
+    <t>VIP111</t>
+  </si>
+  <si>
+    <t>VIP333</t>
+  </si>
+  <si>
+    <t>SG6666</t>
+  </si>
+  <si>
+    <t>SG7777</t>
+  </si>
+  <si>
+    <t>SG8888</t>
+  </si>
+  <si>
+    <t>SG9999</t>
+  </si>
+  <si>
+    <t>畫面中間找兌換碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>按兌換後領取免費禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>YJSTART2025</t>
+  </si>
+  <si>
+    <t>YJOOPS2025</t>
+  </si>
+  <si>
+    <t>藍鑽x288、萌寵召喚券x3、酸酸果x5、銀幣x3萬</t>
+  </si>
+  <si>
+    <t>藍鑽x88、銀幣x5萬、初級羽翼精粹x3、藏寶圖x3</t>
+  </si>
+  <si>
+    <t>畫面中間找虛寶碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>按領取禮包即可獲得獎勵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -17379,7 +17441,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -17632,6 +17694,9 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -51740,7 +51805,7 @@
         <v>4182</v>
       </c>
     </row>
-    <row r="225" spans="1:36" ht="22.5" customHeight="1">
+    <row r="225" spans="1:47" ht="22.5" customHeight="1">
       <c r="A225" s="13" t="str">
         <f>IF(games!A225="", "", games!A225)</f>
         <v>阿瑞斯：命運的選擇者</v>
@@ -51770,7 +51835,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="226" spans="1:36" ht="22.5" customHeight="1">
+    <row r="226" spans="1:47" ht="22.5" customHeight="1">
       <c r="A226" s="13" t="str">
         <f>IF(games!A226="", "", games!A226)</f>
         <v>Draft showdown</v>
@@ -51802,7 +51867,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="227" spans="1:36" ht="22.5" customHeight="1">
+    <row r="227" spans="1:47" ht="22.5" customHeight="1">
       <c r="A227" s="13" t="str">
         <f>IF(games!A227="", "", games!A227)</f>
         <v>魔鏡2：瘋狂的蛇姬</v>
@@ -51844,7 +51909,7 @@
         <v>4299</v>
       </c>
     </row>
-    <row r="228" spans="1:36" ht="22.5" customHeight="1">
+    <row r="228" spans="1:47" ht="22.5" customHeight="1">
       <c r="A228" s="13" t="str">
         <f>IF(games!A228="", "", games!A228)</f>
         <v>量子機動隊</v>
@@ -51874,7 +51939,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="229" spans="1:36" ht="22.5" customHeight="1">
+    <row r="229" spans="1:47" ht="22.5" customHeight="1">
       <c r="A229" s="13" t="str">
         <f>IF(games!A229="", "", games!A229)</f>
         <v>呷飽未？殭殭醬</v>
@@ -51910,7 +51975,7 @@
         <v>4331</v>
       </c>
     </row>
-    <row r="230" spans="1:36" ht="22.5" customHeight="1">
+    <row r="230" spans="1:47" ht="22.5" customHeight="1">
       <c r="A230" s="13" t="str">
         <f>IF(games!A230="", "", games!A230)</f>
         <v>XXL猛漢町</v>
@@ -52018,7 +52083,7 @@
         <v>4263</v>
       </c>
     </row>
-    <row r="231" spans="1:36" ht="22.5" customHeight="1">
+    <row r="231" spans="1:47" ht="22.5" customHeight="1">
       <c r="A231" s="13" t="str">
         <f>IF(games!A231="", "", games!A231)</f>
         <v>Dead Impact：Survival Online</v>
@@ -52048,7 +52113,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="232" spans="1:36" ht="22.5" customHeight="1">
+    <row r="232" spans="1:47" ht="22.5" customHeight="1">
       <c r="A232" s="13" t="str">
         <f>IF(games!A232="", "", games!A232)</f>
         <v>無限子彈</v>
@@ -52078,7 +52143,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="233" spans="1:36" ht="22.5" customHeight="1">
+    <row r="233" spans="1:47" ht="22.5" customHeight="1">
       <c r="A233" s="13" t="str">
         <f>IF(games!A233="", "", games!A233)</f>
         <v>Dunkadillo</v>
@@ -52108,7 +52173,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="234" spans="1:36" ht="22.5" customHeight="1">
+    <row r="234" spans="1:47" ht="22.5" customHeight="1">
       <c r="A234" s="13" t="str">
         <f>IF(games!A234="", "", games!A234)</f>
         <v>遺跡的地平線</v>
@@ -52125,20 +52190,32 @@
         <f>IF(games!I234&lt;&gt;"", games!I234, "")</f>
         <v>別再傻傻等官方佛心給禮包碼了，想在《遺跡的地平線》稱霸，就得自己動手豐衣足食。我們提供的兌換碼和禮包碼，保證讓你拿到手軟。至於代儲值？當然是快速又安全，別再用那些來路不明的平台了，你的肝寶貝、帳號寶貝，由我們來守護。想知道什麼是贏在起跑點嗎？就是別人還在慢慢農，你已經用我們的服務直接飛天了。別說我沒提醒你，機會是不等人的，錯過就要再等一年啦。如果你還在擔心戰力太低，被路人嘲笑，那真的別再猶豫了，快來加入我們的行列，讓那些對手看看什麼叫做「資源碾壓」，從此告別苦哈哈的冒險生涯。</v>
       </c>
-      <c r="F234" s="75" t="s">
-        <v>2648</v>
+      <c r="F234" s="34" t="s">
+        <v>4127</v>
       </c>
       <c r="G234" s="76" t="s">
-        <v>2648</v>
-      </c>
-      <c r="K234" s="75" t="s">
-        <v>2648</v>
-      </c>
-      <c r="L234" s="76" t="s">
-        <v>2648</v>
-      </c>
-    </row>
-    <row r="235" spans="1:36" ht="22.5" customHeight="1">
+        <v>4411</v>
+      </c>
+      <c r="H234" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I234" s="13" t="s">
+        <v>4412</v>
+      </c>
+      <c r="K234" s="79" t="s">
+        <v>4407</v>
+      </c>
+      <c r="L234" s="79" t="s">
+        <v>4409</v>
+      </c>
+      <c r="M234" s="79" t="s">
+        <v>4408</v>
+      </c>
+      <c r="N234" s="79" t="s">
+        <v>4410</v>
+      </c>
+    </row>
+    <row r="235" spans="1:47" ht="22.5" customHeight="1">
       <c r="A235" s="13" t="str">
         <f>IF(games!A235="", "", games!A235)</f>
         <v>三國將將好</v>
@@ -52155,20 +52232,81 @@
         <f>IF(games!I235&lt;&gt;"", games!I235, "")</f>
         <v>玩《三國將將好》還在慢慢推圖？別鬧了，你的對手早就用我們的兌換碼和禮包碼把戰力堆到你看不懂的境界了。我們的代儲值服務，給你最快速、最安全的加值體驗，讓你一秒變神豪，把那些還在課金猶豫不決的玩家遠遠甩在身後。別再說什麼「佛系」了，真正的佛系是資源多到用不完，而不是窮到只剩雙手合十。想逆天改命？從現在開始，讓你的將領比別人的更強大、更無敵，輕鬆征服整個三國世界。</v>
       </c>
-      <c r="F235" s="75" t="s">
-        <v>2648</v>
+      <c r="F235" s="34" t="s">
+        <v>4127</v>
       </c>
       <c r="G235" s="76" t="s">
-        <v>2648</v>
+        <v>4405</v>
+      </c>
+      <c r="H235" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I235" s="13" t="s">
+        <v>4406</v>
       </c>
       <c r="K235" s="75" t="s">
-        <v>2648</v>
+        <v>4394</v>
       </c>
       <c r="L235" s="76" t="s">
         <v>2648</v>
       </c>
-    </row>
-    <row r="236" spans="1:36" ht="22.5" customHeight="1">
+      <c r="M235" s="79" t="s">
+        <v>4395</v>
+      </c>
+      <c r="O235" s="79" t="s">
+        <v>4396</v>
+      </c>
+      <c r="Q235" s="79" t="s">
+        <v>4397</v>
+      </c>
+      <c r="S235" s="79" t="s">
+        <v>4398</v>
+      </c>
+      <c r="U235" s="79" t="s">
+        <v>4396</v>
+      </c>
+      <c r="W235" s="79" t="s">
+        <v>4399</v>
+      </c>
+      <c r="Y235" s="99" t="s">
+        <v>2301</v>
+      </c>
+      <c r="Z235" s="99"/>
+      <c r="AA235" s="99" t="s">
+        <v>4400</v>
+      </c>
+      <c r="AC235" s="79" t="s">
+        <v>2300</v>
+      </c>
+      <c r="AE235" s="79" t="s">
+        <v>1821</v>
+      </c>
+      <c r="AG235" s="79" t="s">
+        <v>1784</v>
+      </c>
+      <c r="AI235" s="79" t="s">
+        <v>1716</v>
+      </c>
+      <c r="AK235" s="79" t="s">
+        <v>1717</v>
+      </c>
+      <c r="AM235" s="79" t="s">
+        <v>1822</v>
+      </c>
+      <c r="AO235" s="79" t="s">
+        <v>4401</v>
+      </c>
+      <c r="AQ235" s="79" t="s">
+        <v>4402</v>
+      </c>
+      <c r="AS235" s="79" t="s">
+        <v>4403</v>
+      </c>
+      <c r="AU235" s="79" t="s">
+        <v>4404</v>
+      </c>
+    </row>
+    <row r="236" spans="1:47" ht="22.5" customHeight="1">
       <c r="A236" s="13" t="str">
         <f>IF(games!A236="", "", games!A236)</f>
         <v>七騎士 Re：BIRTH</v>
@@ -52198,7 +52336,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="237" spans="1:36" ht="22.5" customHeight="1">
+    <row r="237" spans="1:47" ht="22.5" customHeight="1">
       <c r="A237" s="13" t="str">
         <f>IF(games!A237="", "", games!A237)</f>
         <v>異界三國：死神契約</v>
@@ -52228,7 +52366,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="238" spans="1:36" ht="22.5" customHeight="1">
+    <row r="238" spans="1:47" ht="22.5" customHeight="1">
       <c r="A238" s="13" t="str">
         <f>IF(games!A238="", "", games!A238)</f>
         <v>魔法師之徒</v>
@@ -52258,7 +52396,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="239" spans="1:36" ht="22.5" customHeight="1">
+    <row r="239" spans="1:47" ht="22.5" customHeight="1">
       <c r="A239" s="13" t="str">
         <f>IF(games!A239="", "", games!A239)</f>
         <v>三國魂將傳</v>
@@ -52288,7 +52426,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="240" spans="1:36" ht="22.5" customHeight="1">
+    <row r="240" spans="1:47" ht="22.5" customHeight="1">
       <c r="A240" s="13" t="str">
         <f>IF(games!A240="", "", games!A240)</f>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6561" uniqueCount="4413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6582" uniqueCount="4436">
   <si>
     <t>Facebook</t>
   </si>
@@ -17027,12 +17027,82 @@
     <t>按領取禮包即可獲得獎勵</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>TOP01ARES </t>
+  </si>
+  <si>
+    <t>ARESTWOPEN </t>
+  </si>
+  <si>
+    <t>SHOWCELE</t>
+  </si>
+  <si>
+    <t>JOINARES</t>
+  </si>
+  <si>
+    <t>GRANDGOGO</t>
+  </si>
+  <si>
+    <t>DINGARES</t>
+  </si>
+  <si>
+    <t>LINGGOLD</t>
+  </si>
+  <si>
+    <t>VIPDT888</t>
+  </si>
+  <si>
+    <t>GUANARES</t>
+  </si>
+  <si>
+    <t>BLACKVIP</t>
+  </si>
+  <si>
+    <t>DAD8ARES</t>
+  </si>
+  <si>
+    <t>SCARESGO</t>
+  </si>
+  <si>
+    <t>HSU7ARES</t>
+  </si>
+  <si>
+    <t>EPICARES</t>
+  </si>
+  <si>
+    <t>https://coupon.withhive.com/3003</t>
+  </si>
+  <si>
+    <t>選擇自己所屬的「伺服器」</t>
+  </si>
+  <si>
+    <t>輸入自己的「CS Code」</t>
+  </si>
+  <si>
+    <t>輸入「優惠券序號」</t>
+  </si>
+  <si>
+    <t>最後點擊「使用優惠券」</t>
+  </si>
+  <si>
+    <t>Maze666</t>
+  </si>
+  <si>
+    <t>Maze777</t>
+  </si>
+  <si>
+    <t>Maze888</t>
+  </si>
+  <si>
+    <t>一億鑽石+SSR角色自選寶箱+養成資源寶箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -17194,6 +17264,12 @@
       <sz val="12"/>
       <color rgb="FF0F0F0F"/>
       <name val="Inherit"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFE2E5E9"/>
+      <name val="Segoe UI Historic"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -17441,7 +17517,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -17698,6 +17774,8 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -51822,17 +51900,65 @@
         <f>IF(games!I225&lt;&gt;"", games!I225, "")</f>
         <v>什麼？還在為了升級煩惱，或被副本Boss虐到懷疑人生？快醒醒吧！在《阿瑞斯：命運的選擇者》中，你將扮演天選之人，解鎖傳說英雄，打造最強陣容，讓那些自以為是的敵人知道什麼叫「殘酷」的勝利。這裡的福利多到你不敢想像，各種獨家禮包碼、兌換碼隨便拿，讓你戰力起飛。覺得遊戲太肝又太慢？沒關係，我們的代儲值服務讓你體驗什麼叫「快速安全」，一秒讓你成為人上人，輕鬆碾壓所有對手，不用再當可憐的免費仔，讓別人看看什麼叫真正的歐洲血統！</v>
       </c>
-      <c r="F225" s="75" t="s">
-        <v>2648</v>
-      </c>
-      <c r="G225" s="76" t="s">
-        <v>2648</v>
-      </c>
-      <c r="K225" s="75" t="s">
-        <v>2648</v>
+      <c r="F225" s="100" t="s">
+        <v>4427</v>
+      </c>
+      <c r="G225" s="79" t="s">
+        <v>4428</v>
+      </c>
+      <c r="H225" s="79" t="s">
+        <v>4429</v>
+      </c>
+      <c r="I225" s="79" t="s">
+        <v>4430</v>
+      </c>
+      <c r="J225" s="79" t="s">
+        <v>4431</v>
+      </c>
+      <c r="K225" s="79" t="s">
+        <v>4413</v>
       </c>
       <c r="L225" s="76" t="s">
         <v>2648</v>
+      </c>
+      <c r="M225" s="79" t="s">
+        <v>4414</v>
+      </c>
+      <c r="O225" s="79" t="s">
+        <v>4415</v>
+      </c>
+      <c r="Q225" s="79" t="s">
+        <v>4416</v>
+      </c>
+      <c r="S225" s="79" t="s">
+        <v>4417</v>
+      </c>
+      <c r="U225" s="79" t="s">
+        <v>4418</v>
+      </c>
+      <c r="W225" s="79" t="s">
+        <v>4419</v>
+      </c>
+      <c r="Y225" s="79" t="s">
+        <v>4420</v>
+      </c>
+      <c r="AA225" s="79" t="s">
+        <v>4421</v>
+      </c>
+      <c r="AC225" s="79" t="s">
+        <v>4422</v>
+      </c>
+      <c r="AE225" s="79" t="s">
+        <v>4423</v>
+      </c>
+      <c r="AG225" s="79" t="s">
+        <v>4424</v>
+      </c>
+      <c r="AI225" s="79" t="s">
+        <v>4425</v>
+      </c>
+      <c r="AK225" s="79" t="s">
+        <v>4426</v>
       </c>
     </row>
     <row r="226" spans="1:47" ht="22.5" customHeight="1">
@@ -51899,14 +52025,30 @@
       <c r="K227" s="75" t="s">
         <v>4297</v>
       </c>
-      <c r="L227" s="76" t="s">
-        <v>2648</v>
-      </c>
+      <c r="L227" s="76"/>
       <c r="M227" s="18" t="s">
         <v>4298</v>
       </c>
       <c r="O227" s="18" t="s">
         <v>4299</v>
+      </c>
+      <c r="Q227" s="101" t="s">
+        <v>4432</v>
+      </c>
+      <c r="R227" s="13" t="s">
+        <v>4435</v>
+      </c>
+      <c r="S227" s="101" t="s">
+        <v>4433</v>
+      </c>
+      <c r="T227" s="13" t="s">
+        <v>4435</v>
+      </c>
+      <c r="U227" s="101" t="s">
+        <v>4434</v>
+      </c>
+      <c r="V227" s="13" t="s">
+        <v>4435</v>
       </c>
     </row>
     <row r="228" spans="1:47" ht="22.5" customHeight="1">
@@ -54474,8 +54616,9 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G157" r:id="rId1"/>
+    <hyperlink ref="F225" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6582" uniqueCount="4436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6604" uniqueCount="4455">
   <si>
     <t>Facebook</t>
   </si>
@@ -17096,6 +17096,72 @@
   <si>
     <t>一億鑽石+SSR角色自選寶箱+養成資源寶箱</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>龍息：神寂</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E9%BE%8D%E6%81%AF-%E7%A5%9E%E5%AF%82/id6746432809</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/DragonheirAsia/?locale=zh_TW</t>
+  </si>
+  <si>
+    <t>l.facebook.com/l.php?u=https%3A%2F%2Fdragonheir.sgrastudio.com%2Ftw%2F%3Ffbclid%3DIwZXh0bgNhZW0CMTAAYnJpZBExMGlscTREcGtiazA0VTViTAEePRkTxRmrKwBnI5tWxvqJwaufuCd4jXTd5eudK-IZhqQKIYmURFWD44XHtB0_aem_vibZcdBkkhAu4en-CFCiKQ&amp;h=AT2OPKiGKl1LDxZay1fK746aJJSiR4fe-mgpvt9YTNn_daF-IfoBrOuNDUNeYlbcpmju2WUKuafwkz87faLGyONg4ZM632eIRVWBW6tSsnlXVcVPxaT1dPBVJM9pYHhhk2cshVUaa4Pdng&amp;__tn__=-UK-R&amp;c[0]=AT14EFIXFxuOlashKNUc5J03r-P2tdLZ_iebj3woPaMQRs_6XDYgFV17Heqly2Z_JMbADSf5ZmrV6wHkQLZ9LNF3INpW1x9X7y9J0FGwL_6ogytHCXgnsEa1QhwN1Nr0Lxv5w0IYJvKrjFUNZ-PQf72nOm6yiNuuN67ZVNWbh9CYI-FV152pOLMLEknDlsOxEzQgZxUk1YEJ3g57SpHbvIi83FP7nzKo9CH5</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.sgra.dragon&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>還在為找不到兌換碼煩惱嗎？《龍息：神寂》這款MMORPG手遊，為你提供一個廣闊的魔幻世界，讓你沉浸在史詩級的冒險中。你將扮演天選之人，與夥伴們一起對抗邪惡的龍族，拯救瀕臨毀滅的王國。遊戲提供了多樣的職業選擇、華麗的技能特效和豐富的副本挑戰，無論是喜歡PVE的劇情黨，還是熱衷PVP的競技玩家，都能在這裡找到屬於自己的樂趣。你還在等什麼？趕快找尋你的兌換碼、禮包碼，用最快速安全的方式完成代儲值，輕鬆變強，加入這場冒險，成為傳說中的屠龍英雄吧！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>REBORN1MTH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>APKPURE999</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>骰子與金幣</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MONKEYKING</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>200龍晶石</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在遊戲介面中尋找「設定」選項</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點選「兌換碼」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7000龍晶石</t>
+  </si>
+  <si>
+    <t>3500龍晶石</t>
+  </si>
+  <si>
+    <t>2100龍晶石</t>
+  </si>
+  <si>
+    <t>1050龍晶石</t>
+  </si>
+  <si>
+    <t>350龍晶石</t>
+  </si>
+  <si>
+    <t>70龍晶石</t>
   </si>
 </sst>
 </file>
@@ -34074,14 +34140,68 @@
         <v>58</v>
       </c>
     </row>
-    <row r="240" spans="1:33" ht="22.5" customHeight="1">
+    <row r="240" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A240" t="s">
+        <v>4436</v>
+      </c>
+      <c r="C240" s="47" t="s">
+        <v>4438</v>
+      </c>
+      <c r="D240" s="48" t="s">
+        <v>4439</v>
+      </c>
+      <c r="E240" s="48" t="s">
+        <v>4437</v>
+      </c>
       <c r="F240" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/龍息：神寂.html</v>
+      </c>
+      <c r="G240" s="48" t="s">
+        <v>4440</v>
       </c>
       <c r="H240" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/龍息：神寂.html</v>
+      </c>
+      <c r="I240" s="49" t="s">
+        <v>4441</v>
+      </c>
+      <c r="J240" s="1" t="s">
+        <v>4449</v>
+      </c>
+      <c r="K240" s="2">
+        <v>2479</v>
+      </c>
+      <c r="L240" s="1" t="s">
+        <v>4450</v>
+      </c>
+      <c r="M240" s="2">
+        <v>1292</v>
+      </c>
+      <c r="N240" s="1" t="s">
+        <v>4451</v>
+      </c>
+      <c r="O240" s="2">
+        <v>757</v>
+      </c>
+      <c r="P240" s="1" t="s">
+        <v>4452</v>
+      </c>
+      <c r="Q240" s="2">
+        <v>380</v>
+      </c>
+      <c r="R240" s="1" t="s">
+        <v>4453</v>
+      </c>
+      <c r="S240" s="2">
+        <v>140</v>
+      </c>
+      <c r="T240" s="1" t="s">
+        <v>4454</v>
+      </c>
+      <c r="U240" s="2">
+        <v>50</v>
       </c>
     </row>
     <row r="241" spans="6:8" ht="22.5" customHeight="1">
@@ -52571,15 +52691,45 @@
     <row r="240" spans="1:47" ht="22.5" customHeight="1">
       <c r="A240" s="13" t="str">
         <f>IF(games!A240="", "", games!A240)</f>
-        <v/>
+        <v>龍息：神寂</v>
       </c>
       <c r="C240" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/龍息：神寂-禮包碼.jpg</v>
       </c>
       <c r="D240" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/龍息：神寂.html</v>
+      </c>
+      <c r="F240" s="34" t="s">
+        <v>4447</v>
+      </c>
+      <c r="G240" s="13" t="s">
+        <v>4448</v>
+      </c>
+      <c r="H240" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I240" s="13" t="s">
+        <v>4406</v>
+      </c>
+      <c r="K240" s="17" t="s">
+        <v>4442</v>
+      </c>
+      <c r="L240" s="13" t="s">
+        <v>4444</v>
+      </c>
+      <c r="M240" s="18" t="s">
+        <v>4443</v>
+      </c>
+      <c r="N240" s="13" t="s">
+        <v>4444</v>
+      </c>
+      <c r="O240" s="18" t="s">
+        <v>4445</v>
+      </c>
+      <c r="P240" s="13" t="s">
+        <v>4446</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="22.5" customHeight="1">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6604" uniqueCount="4455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6612" uniqueCount="4462">
   <si>
     <t>Facebook</t>
   </si>
@@ -17162,6 +17162,34 @@
   </si>
   <si>
     <t>70龍晶石</t>
+  </si>
+  <si>
+    <t>LYH2025</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C9R9U9S9H</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">RSOACT9 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SUN8ROC8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">R8O8C8 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROCSUN7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ROC777 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -47750,7 +47778,7 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="145" spans="1:32" ht="22.5" customHeight="1">
+    <row r="145" spans="1:34" ht="22.5" customHeight="1">
       <c r="A145" s="33" t="s">
         <v>198</v>
       </c>
@@ -47781,7 +47809,7 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="146" spans="1:32" ht="22.5" customHeight="1">
+    <row r="146" spans="1:34" ht="22.5" customHeight="1">
       <c r="A146" s="33" t="s">
         <v>199</v>
       </c>
@@ -47818,7 +47846,7 @@
         <v>2465</v>
       </c>
     </row>
-    <row r="147" spans="1:32" ht="22.5" customHeight="1">
+    <row r="147" spans="1:34" ht="22.5" customHeight="1">
       <c r="A147" s="13" t="s">
         <v>3247</v>
       </c>
@@ -47855,7 +47883,7 @@
         <v>2477</v>
       </c>
     </row>
-    <row r="148" spans="1:32" ht="22.5" customHeight="1">
+    <row r="148" spans="1:34" ht="22.5" customHeight="1">
       <c r="A148" s="33" t="s">
         <v>228</v>
       </c>
@@ -47945,8 +47973,14 @@
       <c r="AF148" s="13" t="s">
         <v>1922</v>
       </c>
-    </row>
-    <row r="149" spans="1:32" ht="22.5" customHeight="1">
+      <c r="AG148" s="18" t="s">
+        <v>4455</v>
+      </c>
+      <c r="AH148" s="13" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="149" spans="1:34" ht="22.5" customHeight="1">
       <c r="A149" s="33" t="s">
         <v>229</v>
       </c>
@@ -48001,7 +48035,7 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="150" spans="1:32" ht="22.5" customHeight="1">
+    <row r="150" spans="1:34" ht="22.5" customHeight="1">
       <c r="A150" s="33" t="s">
         <v>241</v>
       </c>
@@ -48038,7 +48072,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="151" spans="1:32" ht="22.5" customHeight="1">
+    <row r="151" spans="1:34" ht="22.5" customHeight="1">
       <c r="A151" s="33" t="s">
         <v>242</v>
       </c>
@@ -48091,7 +48125,7 @@
       <c r="AA151" s="24"/>
       <c r="AB151" s="16"/>
     </row>
-    <row r="152" spans="1:32" ht="22.5" customHeight="1">
+    <row r="152" spans="1:34" ht="22.5" customHeight="1">
       <c r="A152" s="13" t="s">
         <v>2533</v>
       </c>
@@ -48179,7 +48213,7 @@
         <v>3284</v>
       </c>
     </row>
-    <row r="153" spans="1:32" ht="22.5" customHeight="1">
+    <row r="153" spans="1:34" ht="22.5" customHeight="1">
       <c r="A153" s="13" t="s">
         <v>3286</v>
       </c>
@@ -48228,7 +48262,7 @@
         <v>3294</v>
       </c>
     </row>
-    <row r="154" spans="1:32" ht="22.5" customHeight="1">
+    <row r="154" spans="1:34" ht="22.5" customHeight="1">
       <c r="A154" s="13" t="s">
         <v>2543</v>
       </c>
@@ -48286,7 +48320,7 @@
         <v>3306</v>
       </c>
     </row>
-    <row r="155" spans="1:32" ht="22.5" customHeight="1">
+    <row r="155" spans="1:34" ht="22.5" customHeight="1">
       <c r="A155" s="33" t="s">
         <v>3307</v>
       </c>
@@ -48335,7 +48369,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="156" spans="1:32" ht="22.5" customHeight="1">
+    <row r="156" spans="1:34" ht="22.5" customHeight="1">
       <c r="A156" s="33" t="s">
         <v>305</v>
       </c>
@@ -48365,8 +48399,26 @@
       <c r="L156" s="13" t="s">
         <v>3316</v>
       </c>
-    </row>
-    <row r="157" spans="1:32" ht="22.5" customHeight="1">
+      <c r="M156" s="18" t="s">
+        <v>4456</v>
+      </c>
+      <c r="O156" s="18" t="s">
+        <v>4457</v>
+      </c>
+      <c r="Q156" s="18" t="s">
+        <v>4458</v>
+      </c>
+      <c r="S156" s="18" t="s">
+        <v>4459</v>
+      </c>
+      <c r="U156" s="18" t="s">
+        <v>4460</v>
+      </c>
+      <c r="W156" s="18" t="s">
+        <v>4461</v>
+      </c>
+    </row>
+    <row r="157" spans="1:34" ht="22.5" customHeight="1">
       <c r="A157" s="33" t="s">
         <v>323</v>
       </c>
@@ -48406,7 +48458,7 @@
         <v>3322</v>
       </c>
     </row>
-    <row r="158" spans="1:32" ht="22.5" customHeight="1">
+    <row r="158" spans="1:34" ht="22.5" customHeight="1">
       <c r="A158" s="33" t="s">
         <v>324</v>
       </c>
@@ -48443,7 +48495,7 @@
         <v>2477</v>
       </c>
     </row>
-    <row r="159" spans="1:32" ht="22.5" customHeight="1">
+    <row r="159" spans="1:34" ht="22.5" customHeight="1">
       <c r="A159" s="33" t="s">
         <v>325</v>
       </c>
@@ -48483,7 +48535,7 @@
         <v>3331</v>
       </c>
     </row>
-    <row r="160" spans="1:32" ht="22.5" customHeight="1">
+    <row r="160" spans="1:34" ht="22.5" customHeight="1">
       <c r="A160" s="33" t="s">
         <v>3332</v>
       </c>
@@ -52701,6 +52753,10 @@
         <f t="shared" si="8"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/龍息：神寂.html</v>
       </c>
+      <c r="E240" s="14" t="str">
+        <f>IF(games!I240&lt;&gt;"", games!I240, "")</f>
+        <v>還在為找不到兌換碼煩惱嗎？《龍息：神寂》這款MMORPG手遊，為你提供一個廣闊的魔幻世界，讓你沉浸在史詩級的冒險中。你將扮演天選之人，與夥伴們一起對抗邪惡的龍族，拯救瀕臨毀滅的王國。遊戲提供了多樣的職業選擇、華麗的技能特效和豐富的副本挑戰，無論是喜歡PVE的劇情黨，還是熱衷PVP的競技玩家，都能在這裡找到屬於自己的樂趣。你還在等什麼？趕快找尋你的兌換碼、禮包碼，用最快速安全的方式完成代儲值，輕鬆變強，加入這場冒險，成為傳說中的屠龍英雄吧！</v>
+      </c>
       <c r="F240" s="34" t="s">
         <v>4447</v>
       </c>
@@ -52732,7 +52788,7 @@
         <v>4446</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="22.5" customHeight="1">
+    <row r="241" spans="1:5" ht="22.5" customHeight="1">
       <c r="A241" s="13" t="str">
         <f>IF(games!A241="", "", games!A241)</f>
         <v/>
@@ -52745,8 +52801,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="242" spans="1:4" ht="22.5" customHeight="1">
+      <c r="E241" s="14" t="str">
+        <f>IF(games!I241&lt;&gt;"", games!I241, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242" spans="1:5" ht="22.5" customHeight="1">
       <c r="A242" s="13" t="str">
         <f>IF(games!A242="", "", games!A242)</f>
         <v/>
@@ -52759,8 +52819,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="243" spans="1:4" ht="22.5" customHeight="1">
+      <c r="E242" s="14" t="str">
+        <f>IF(games!I242&lt;&gt;"", games!I242, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243" spans="1:5" ht="22.5" customHeight="1">
       <c r="A243" s="13" t="str">
         <f>IF(games!A243="", "", games!A243)</f>
         <v/>
@@ -52773,8 +52837,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="244" spans="1:4" ht="22.5" customHeight="1">
+      <c r="E243" s="14" t="str">
+        <f>IF(games!I243&lt;&gt;"", games!I243, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244" spans="1:5" ht="22.5" customHeight="1">
       <c r="A244" s="13" t="str">
         <f>IF(games!A244="", "", games!A244)</f>
         <v/>
@@ -52787,8 +52855,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="245" spans="1:4" ht="22.5" customHeight="1">
+      <c r="E244" s="14" t="str">
+        <f>IF(games!I244&lt;&gt;"", games!I244, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245" spans="1:5" ht="22.5" customHeight="1">
       <c r="A245" s="13" t="str">
         <f>IF(games!A245="", "", games!A245)</f>
         <v/>
@@ -52801,8 +52873,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="246" spans="1:4" ht="22.5" customHeight="1">
+      <c r="E245" s="14" t="str">
+        <f>IF(games!I245&lt;&gt;"", games!I245, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246" spans="1:5" ht="22.5" customHeight="1">
       <c r="A246" s="13" t="str">
         <f>IF(games!A246="", "", games!A246)</f>
         <v/>
@@ -52815,8 +52891,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="247" spans="1:4" ht="22.5" customHeight="1">
+      <c r="E246" s="14" t="str">
+        <f>IF(games!I246&lt;&gt;"", games!I246, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247" spans="1:5" ht="22.5" customHeight="1">
       <c r="A247" s="13" t="str">
         <f>IF(games!A247="", "", games!A247)</f>
         <v/>
@@ -52829,8 +52909,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="248" spans="1:4" ht="22.5" customHeight="1">
+      <c r="E247" s="14" t="str">
+        <f>IF(games!I247&lt;&gt;"", games!I247, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248" spans="1:5" ht="22.5" customHeight="1">
       <c r="A248" s="13" t="str">
         <f>IF(games!A248="", "", games!A248)</f>
         <v/>
@@ -52843,8 +52927,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="249" spans="1:4" ht="22.5" customHeight="1">
+      <c r="E248" s="14" t="str">
+        <f>IF(games!I248&lt;&gt;"", games!I248, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249" spans="1:5" ht="22.5" customHeight="1">
       <c r="A249" s="13" t="str">
         <f>IF(games!A249="", "", games!A249)</f>
         <v/>
@@ -52857,8 +52945,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="250" spans="1:4" ht="22.5" customHeight="1">
+      <c r="E249" s="14" t="str">
+        <f>IF(games!I249&lt;&gt;"", games!I249, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250" spans="1:5" ht="22.5" customHeight="1">
       <c r="A250" s="13" t="str">
         <f>IF(games!A250="", "", games!A250)</f>
         <v/>
@@ -52871,8 +52963,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="251" spans="1:4" ht="22.5" customHeight="1">
+      <c r="E250" s="14" t="str">
+        <f>IF(games!I250&lt;&gt;"", games!I250, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251" spans="1:5" ht="22.5" customHeight="1">
       <c r="C251" s="13" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -52881,8 +52977,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="252" spans="1:4" ht="22.5" customHeight="1">
+      <c r="E251" s="14" t="str">
+        <f>IF(games!I251&lt;&gt;"", games!I251, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252" spans="1:5" ht="22.5" customHeight="1">
       <c r="C252" s="13" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -52891,8 +52991,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="253" spans="1:4" ht="22.5" customHeight="1">
+      <c r="E252" s="14" t="str">
+        <f>IF(games!I252&lt;&gt;"", games!I252, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" spans="1:5" ht="22.5" customHeight="1">
       <c r="C253" s="13" t="str">
         <f t="shared" ref="C253:C316" si="9">IF(A253="","", "giftcodesbanner/" &amp; A253 &amp; "-禮包碼.jpg")</f>
         <v/>
@@ -52901,8 +53005,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="254" spans="1:4" ht="22.5" customHeight="1">
+      <c r="E253" s="14" t="str">
+        <f>IF(games!I253&lt;&gt;"", games!I253, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254" spans="1:5" ht="22.5" customHeight="1">
       <c r="C254" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -52911,8 +53019,12 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="255" spans="1:4" ht="22.5" customHeight="1">
+      <c r="E254" s="14" t="str">
+        <f>IF(games!I254&lt;&gt;"", games!I254, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255" spans="1:5" ht="22.5" customHeight="1">
       <c r="C255" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -52922,7 +53034,7 @@
         <v/>
       </c>
     </row>
-    <row r="256" spans="1:4" ht="22.5" customHeight="1">
+    <row r="256" spans="1:5" ht="22.5" customHeight="1">
       <c r="C256" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6612" uniqueCount="4462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6687" uniqueCount="4498">
   <si>
     <t>Facebook</t>
   </si>
@@ -17098,98 +17098,611 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>https://apps.apple.com/tw/app/%E9%BE%8D%E6%81%AF-%E7%A5%9E%E5%AF%82/id6746432809</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/DragonheirAsia/?locale=zh_TW</t>
+  </si>
+  <si>
+    <t>l.facebook.com/l.php?u=https%3A%2F%2Fdragonheir.sgrastudio.com%2Ftw%2F%3Ffbclid%3DIwZXh0bgNhZW0CMTAAYnJpZBExMGlscTREcGtiazA0VTViTAEePRkTxRmrKwBnI5tWxvqJwaufuCd4jXTd5eudK-IZhqQKIYmURFWD44XHtB0_aem_vibZcdBkkhAu4en-CFCiKQ&amp;h=AT2OPKiGKl1LDxZay1fK746aJJSiR4fe-mgpvt9YTNn_daF-IfoBrOuNDUNeYlbcpmju2WUKuafwkz87faLGyONg4ZM632eIRVWBW6tSsnlXVcVPxaT1dPBVJM9pYHhhk2cshVUaa4Pdng&amp;__tn__=-UK-R&amp;c[0]=AT14EFIXFxuOlashKNUc5J03r-P2tdLZ_iebj3woPaMQRs_6XDYgFV17Heqly2Z_JMbADSf5ZmrV6wHkQLZ9LNF3INpW1x9X7y9J0FGwL_6ogytHCXgnsEa1QhwN1Nr0Lxv5w0IYJvKrjFUNZ-PQf72nOm6yiNuuN67ZVNWbh9CYI-FV152pOLMLEknDlsOxEzQgZxUk1YEJ3g57SpHbvIi83FP7nzKo9CH5</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.sgra.dragon&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>還在為找不到兌換碼煩惱嗎？《龍息：神寂》這款MMORPG手遊，為你提供一個廣闊的魔幻世界，讓你沉浸在史詩級的冒險中。你將扮演天選之人，與夥伴們一起對抗邪惡的龍族，拯救瀕臨毀滅的王國。遊戲提供了多樣的職業選擇、華麗的技能特效和豐富的副本挑戰，無論是喜歡PVE的劇情黨，還是熱衷PVP的競技玩家，都能在這裡找到屬於自己的樂趣。你還在等什麼？趕快找尋你的兌換碼、禮包碼，用最快速安全的方式完成代儲值，輕鬆變強，加入這場冒險，成為傳說中的屠龍英雄吧！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>REBORN1MTH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>APKPURE999</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>骰子與金幣</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MONKEYKING</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>200龍晶石</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在遊戲介面中尋找「設定」選項</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點選「兌換碼」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7000龍晶石</t>
+  </si>
+  <si>
+    <t>3500龍晶石</t>
+  </si>
+  <si>
+    <t>2100龍晶石</t>
+  </si>
+  <si>
+    <t>1050龍晶石</t>
+  </si>
+  <si>
+    <t>350龍晶石</t>
+  </si>
+  <si>
+    <t>70龍晶石</t>
+  </si>
+  <si>
+    <t>LYH2025</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C9R9U9S9H</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">RSOACT9 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SUN8ROC8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">R8O8C8 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROCSUN7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ROC777 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>龍息：神寂</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://apps.apple.com/tw/app/%E9%BE%8D%E6%81%AF-%E7%A5%9E%E5%AF%82/id6746432809</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/DragonheirAsia/?locale=zh_TW</t>
-  </si>
-  <si>
-    <t>l.facebook.com/l.php?u=https%3A%2F%2Fdragonheir.sgrastudio.com%2Ftw%2F%3Ffbclid%3DIwZXh0bgNhZW0CMTAAYnJpZBExMGlscTREcGtiazA0VTViTAEePRkTxRmrKwBnI5tWxvqJwaufuCd4jXTd5eudK-IZhqQKIYmURFWD44XHtB0_aem_vibZcdBkkhAu4en-CFCiKQ&amp;h=AT2OPKiGKl1LDxZay1fK746aJJSiR4fe-mgpvt9YTNn_daF-IfoBrOuNDUNeYlbcpmju2WUKuafwkz87faLGyONg4ZM632eIRVWBW6tSsnlXVcVPxaT1dPBVJM9pYHhhk2cshVUaa4Pdng&amp;__tn__=-UK-R&amp;c[0]=AT14EFIXFxuOlashKNUc5J03r-P2tdLZ_iebj3woPaMQRs_6XDYgFV17Heqly2Z_JMbADSf5ZmrV6wHkQLZ9LNF3INpW1x9X7y9J0FGwL_6ogytHCXgnsEa1QhwN1Nr0Lxv5w0IYJvKrjFUNZ-PQf72nOm6yiNuuN67ZVNWbh9CYI-FV152pOLMLEknDlsOxEzQgZxUk1YEJ3g57SpHbvIi83FP7nzKo9CH5</t>
-  </si>
-  <si>
-    <t>https://play.google.com/store/apps/details?id=com.sgra.dragon&amp;hl=zh_TW</t>
-  </si>
-  <si>
-    <t>還在為找不到兌換碼煩惱嗎？《龍息：神寂》這款MMORPG手遊，為你提供一個廣闊的魔幻世界，讓你沉浸在史詩級的冒險中。你將扮演天選之人，與夥伴們一起對抗邪惡的龍族，拯救瀕臨毀滅的王國。遊戲提供了多樣的職業選擇、華麗的技能特效和豐富的副本挑戰，無論是喜歡PVE的劇情黨，還是熱衷PVP的競技玩家，都能在這裡找到屬於自己的樂趣。你還在等什麼？趕快找尋你的兌換碼、禮包碼，用最快速安全的方式完成代儲值，輕鬆變強，加入這場冒險，成為傳說中的屠龍英雄吧！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>REBORN1MTH</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>APKPURE999</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>骰子與金幣</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MONKEYKING</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>200龍晶石</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>在遊戲介面中尋找「設定」選項</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>點選「兌換碼」</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>7000龍晶石</t>
-  </si>
-  <si>
-    <t>3500龍晶石</t>
-  </si>
-  <si>
-    <t>2100龍晶石</t>
-  </si>
-  <si>
-    <t>1050龍晶石</t>
-  </si>
-  <si>
-    <t>350龍晶石</t>
-  </si>
-  <si>
-    <t>70龍晶石</t>
-  </si>
-  <si>
-    <t>LYH2025</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>C9R9U9S9H</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">RSOACT9 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SUN8ROC8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">R8O8C8 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ROCSUN7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">ROC777 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩具對決</t>
+  </si>
+  <si>
+    <t>幸福都市：市長模擬器</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑道傳奇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>The kingdom</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>medieval tales</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.jsl.entco.tdi&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://tdi.jslgame.com/tw</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E7%8E%A9%E5%85%B7%E5%B0%8D%E6%B1%BA-toy-duel/id6467618612</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/JSLGAME</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.kiwigames.happycitizen.gp&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/mo/app/%E5%B9%B8%E7%A6%8F%E9%83%BD%E5%B8%82-%E5%B8%82%E9%95%B7%E6%A8%A1%E6%93%AC%E5%99%A8/id6745251520</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.igg.android.mafiamobile&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E9%BB%91%E9%81%93%E5%82%B3%E5%A5%87-mafia-mobile/id6739123904</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/the-kingdom-medieval-tales/id6744967226</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.stratospheregames.The.Kingdom.Medieval.Tales.Strategy.Building.Games&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://www.igg.com/games/</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/mt/developer/boombit-inc/id1045926022</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/playmafia.tw/</t>
+  </si>
+  <si>
+    <r>
+      <t>準備好加入這場刺激又療癒的玩具大戰了嗎？《玩具對決》是一款結合了策略、收集與即時PVP對戰的卡牌手機遊戲，讓玩家能蒐集超過百種可愛又逗趣的玩具角色，打造獨一無二的戰術牌組。遊戲戰鬥節奏明快，每次出牌都考驗著你的智慧與反應！想在玩具世界稱霸，除了磨練技術，更要善用官方釋出的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兌換碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>和</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>來快速強化陣容。此外，遊戲內提供</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，讓你能以最</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>快速</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、最</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>安全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的方式獲得資源，無後顧之憂地享受這場玩具對決！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>想親手打造一座繁榮又充滿活力的夢想都市嗎？《幸福都市：市長模擬器》將實現你的願望！這是一款高自由度的模擬經營遊戲，你將扮演一位市長，從零開始規劃土地、建設住宅與公共設施，並招募各種市民來為城市注入新生命。無論是打造熱鬧的商業區、優美的觀光景點，還是完善的工業中心，都由你一手掌握！別忘了關注官方動態，善用官方提供的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兌換碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>及</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，讓你的城市發展一日千里。遊戲也支援</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，保證</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>快速安全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，讓你輕鬆獲得資源，成為最稱職的幸福都市市長！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>《黑道傳奇》是一款以現代黑幫為背景的策略模擬遊戲。身為一名新崛起的老大，你將體驗最真實的地下世界！從經營賭場、收取保護費，到招募小弟、擴張地盤，每一步都將考驗你的手腕與決策能力。遊戲中的社交系統讓你可以與其他玩家結盟，共同對抗強敵，或是展開一場驚心動魄的火拼。想要在血腥的黑幫世界中脫穎而出，除了運籌帷幄，更要把握每一次的強化機會。善用官方釋出的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兌換碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>與</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，並透過</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>快速安全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，讓你的勢力迅速壯大，成就傳奇！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>回到那個騎士與城堡的黃金年代吧！《The kingdom：medieval tales》是一款深度十足的中世紀策略經營遊戲。在這款遊戲中，你將成為一名領主，從零開始建立並經營你的王國。透過精心規劃資源、訓練軍隊、建設防禦工事，你將抵禦來犯的敵人，並逐步擴大你的領土。遊戲提供了豐富的歷史事件與任務，讓你沉浸在真實的中世紀氛圍中。想要加速你的王國發展，別忘了善用官方提供的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兌換碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>及</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。遊戲也提供</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，讓你用最</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>快速安全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的方式獲得稀有資源，成為中世紀最強大的王者！</t>
+    </r>
+  </si>
+  <si>
+    <t>14000寶石</t>
+  </si>
+  <si>
+    <t>6500寶石</t>
+  </si>
+  <si>
+    <t>1200寶石</t>
+  </si>
+  <si>
+    <t>TOY PASS</t>
+  </si>
+  <si>
+    <t>寶石月卡</t>
+  </si>
+  <si>
+    <t>30000金條</t>
+  </si>
+  <si>
+    <t>15000金條</t>
+  </si>
+  <si>
+    <t>9000金條</t>
+  </si>
+  <si>
+    <t>7500金條</t>
+  </si>
+  <si>
+    <t>1500金條</t>
+  </si>
+  <si>
+    <t>行軍隊列禮包</t>
+  </si>
+  <si>
+    <t>建造隊列禮包</t>
+  </si>
+  <si>
+    <t>麵包店通行證T2</t>
+  </si>
+  <si>
+    <t>麵包店通行證T3</t>
+  </si>
+  <si>
+    <t>傳說中的糖果劍</t>
   </si>
 </sst>
 </file>
@@ -17611,7 +18124,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -17870,6 +18383,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -34169,110 +34683,392 @@
       </c>
     </row>
     <row r="240" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A240" t="s">
+      <c r="A240" s="102" t="s">
+        <v>4461</v>
+      </c>
+      <c r="C240" s="47" t="s">
+        <v>4437</v>
+      </c>
+      <c r="D240" s="48" t="s">
+        <v>4438</v>
+      </c>
+      <c r="E240" s="48" t="s">
         <v>4436</v>
-      </c>
-      <c r="C240" s="47" t="s">
-        <v>4438</v>
-      </c>
-      <c r="D240" s="48" t="s">
-        <v>4439</v>
-      </c>
-      <c r="E240" s="48" t="s">
-        <v>4437</v>
       </c>
       <c r="F240" s="48" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/龍息：神寂.html</v>
       </c>
       <c r="G240" s="48" t="s">
-        <v>4440</v>
+        <v>4439</v>
       </c>
       <c r="H240" s="48" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/龍息：神寂.html</v>
       </c>
       <c r="I240" s="49" t="s">
-        <v>4441</v>
+        <v>4440</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>4449</v>
+        <v>4448</v>
       </c>
       <c r="K240" s="2">
         <v>2479</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>4450</v>
+        <v>4449</v>
       </c>
       <c r="M240" s="2">
         <v>1292</v>
       </c>
       <c r="N240" s="1" t="s">
-        <v>4451</v>
+        <v>4450</v>
       </c>
       <c r="O240" s="2">
         <v>757</v>
       </c>
       <c r="P240" s="1" t="s">
-        <v>4452</v>
+        <v>4451</v>
       </c>
       <c r="Q240" s="2">
         <v>380</v>
       </c>
       <c r="R240" s="1" t="s">
-        <v>4453</v>
+        <v>4452</v>
       </c>
       <c r="S240" s="2">
         <v>140</v>
       </c>
       <c r="T240" s="1" t="s">
-        <v>4454</v>
+        <v>4453</v>
       </c>
       <c r="U240" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="241" spans="6:8" ht="22.5" customHeight="1">
+    <row r="241" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A241" s="80" t="s">
+        <v>4462</v>
+      </c>
+      <c r="C241" s="47" t="s">
+        <v>4469</v>
+      </c>
+      <c r="D241" s="47" t="s">
+        <v>4467</v>
+      </c>
+      <c r="E241" s="48" t="s">
+        <v>4468</v>
+      </c>
       <c r="F241" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/玩具對決.html</v>
+      </c>
+      <c r="G241" s="48" t="s">
+        <v>4466</v>
       </c>
       <c r="H241" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="6:8" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/玩具對決.html</v>
+      </c>
+      <c r="I241" t="s">
+        <v>4479</v>
+      </c>
+      <c r="J241" s="1" t="s">
+        <v>4483</v>
+      </c>
+      <c r="K241" s="2">
+        <v>2286</v>
+      </c>
+      <c r="L241" s="1" t="s">
+        <v>4484</v>
+      </c>
+      <c r="M241" s="2">
+        <v>1139</v>
+      </c>
+      <c r="N241" s="1" t="s">
+        <v>4206</v>
+      </c>
+      <c r="O241" s="2">
+        <v>535</v>
+      </c>
+      <c r="P241" s="1" t="s">
+        <v>4485</v>
+      </c>
+      <c r="Q241" s="2">
+        <v>248</v>
+      </c>
+      <c r="R241" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S241" s="2">
+        <v>124</v>
+      </c>
+      <c r="T241" s="1" t="s">
+        <v>3591</v>
+      </c>
+      <c r="U241" s="2">
+        <v>25</v>
+      </c>
+      <c r="V241" s="1" t="s">
+        <v>4486</v>
+      </c>
+      <c r="W241" s="2">
+        <v>248</v>
+      </c>
+      <c r="X241" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="Y241" s="2">
+        <v>171</v>
+      </c>
+      <c r="Z241" s="1" t="s">
+        <v>4487</v>
+      </c>
+      <c r="AA241" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="242" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A242" s="3" t="s">
+        <v>4463</v>
+      </c>
+      <c r="C242" s="48" t="s">
+        <v>4471</v>
+      </c>
+      <c r="D242" s="48" t="s">
+        <v>4471</v>
+      </c>
+      <c r="E242" s="48" t="s">
+        <v>4471</v>
+      </c>
       <c r="F242" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/幸福都市：市長模擬器.html</v>
+      </c>
+      <c r="G242" s="48" t="s">
+        <v>4470</v>
       </c>
       <c r="H242" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="243" spans="6:8" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/幸福都市：市長模擬器.html</v>
+      </c>
+      <c r="I242" t="s">
+        <v>4480</v>
+      </c>
+      <c r="J242" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="K242" s="2">
+        <v>2286</v>
+      </c>
+      <c r="L242" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="M242" s="2">
+        <v>1139</v>
+      </c>
+      <c r="N242" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="O242" s="2">
+        <v>535</v>
+      </c>
+      <c r="P242" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="Q242" s="2">
+        <v>457</v>
+      </c>
+      <c r="R242" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="S242" s="2">
+        <v>225</v>
+      </c>
+      <c r="T242" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="U242" s="2">
+        <v>457</v>
+      </c>
+      <c r="V242" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="W242" s="2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="243" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A243" s="3" t="s">
+        <v>4464</v>
+      </c>
+      <c r="C243" s="47" t="s">
+        <v>4478</v>
+      </c>
+      <c r="D243" s="48" t="s">
+        <v>4476</v>
+      </c>
+      <c r="E243" s="48" t="s">
+        <v>4473</v>
+      </c>
       <c r="F243" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/黑道傳奇.html</v>
+      </c>
+      <c r="G243" s="48" t="s">
+        <v>4472</v>
       </c>
       <c r="H243" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="6:8" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/黑道傳奇.html</v>
+      </c>
+      <c r="I243" t="s">
+        <v>4481</v>
+      </c>
+      <c r="J243" s="1" t="s">
+        <v>4488</v>
+      </c>
+      <c r="K243" s="2">
+        <v>2479</v>
+      </c>
+      <c r="L243" s="1" t="s">
+        <v>4489</v>
+      </c>
+      <c r="M243" s="2">
+        <v>1292</v>
+      </c>
+      <c r="N243" s="1" t="s">
+        <v>4490</v>
+      </c>
+      <c r="O243" s="2">
+        <v>757</v>
+      </c>
+      <c r="P243" s="1" t="s">
+        <v>4491</v>
+      </c>
+      <c r="Q243" s="2">
+        <v>634</v>
+      </c>
+      <c r="R243" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="S243" s="2">
+        <v>380</v>
+      </c>
+      <c r="T243" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="U243" s="2">
+        <v>256</v>
+      </c>
+      <c r="V243" s="1" t="s">
+        <v>4492</v>
+      </c>
+      <c r="W243" s="2">
+        <v>140</v>
+      </c>
+      <c r="X243" s="1" t="s">
+        <v>4493</v>
+      </c>
+      <c r="Y243" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z243" s="1" t="s">
+        <v>4494</v>
+      </c>
+      <c r="AA243" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="244" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A244" s="80" t="s">
+        <v>4465</v>
+      </c>
+      <c r="C244" s="47" t="s">
+        <v>3659</v>
+      </c>
+      <c r="D244" s="48" t="s">
+        <v>4477</v>
+      </c>
+      <c r="E244" s="48" t="s">
+        <v>4474</v>
+      </c>
       <c r="F244" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/The kingdom：medieval tales.html</v>
+      </c>
+      <c r="G244" s="48" t="s">
+        <v>4475</v>
       </c>
       <c r="H244" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="6:8" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/The kingdom：medieval tales.html</v>
+      </c>
+      <c r="I244" t="s">
+        <v>4482</v>
+      </c>
+      <c r="J244" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="K244" s="2">
+        <v>2286</v>
+      </c>
+      <c r="L244" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="M244" s="2">
+        <v>1139</v>
+      </c>
+      <c r="N244" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="O244" s="2">
+        <v>612</v>
+      </c>
+      <c r="P244" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="Q244" s="2">
+        <v>457</v>
+      </c>
+      <c r="R244" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="S244" s="2">
+        <v>225</v>
+      </c>
+      <c r="T244" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="U244" s="2">
+        <v>140</v>
+      </c>
+      <c r="V244" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="W244" s="2">
+        <v>99</v>
+      </c>
+      <c r="X244" s="1" t="s">
+        <v>4495</v>
+      </c>
+      <c r="Y244" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z244" s="1" t="s">
+        <v>4496</v>
+      </c>
+      <c r="AA244" s="2">
+        <v>302</v>
+      </c>
+      <c r="AB244" s="1" t="s">
+        <v>4497</v>
+      </c>
+      <c r="AC244" s="2">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="245" spans="1:29" ht="22.5" customHeight="1">
       <c r="F245" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -34282,7 +35078,7 @@
         <v/>
       </c>
     </row>
-    <row r="246" spans="6:8" ht="22.5" customHeight="1">
+    <row r="246" spans="1:29" ht="22.5" customHeight="1">
       <c r="F246" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -34292,7 +35088,7 @@
         <v/>
       </c>
     </row>
-    <row r="247" spans="6:8" ht="22.5" customHeight="1">
+    <row r="247" spans="1:29" ht="22.5" customHeight="1">
       <c r="F247" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -34302,7 +35098,7 @@
         <v/>
       </c>
     </row>
-    <row r="248" spans="6:8" ht="22.5" customHeight="1">
+    <row r="248" spans="1:29" ht="22.5" customHeight="1">
       <c r="F248" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -34312,7 +35108,7 @@
         <v/>
       </c>
     </row>
-    <row r="249" spans="6:8" ht="22.5" customHeight="1">
+    <row r="249" spans="1:29" ht="22.5" customHeight="1">
       <c r="F249" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -34322,7 +35118,7 @@
         <v/>
       </c>
     </row>
-    <row r="250" spans="6:8" ht="22.5" customHeight="1">
+    <row r="250" spans="1:29" ht="22.5" customHeight="1">
       <c r="F250" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -34332,7 +35128,7 @@
         <v/>
       </c>
     </row>
-    <row r="251" spans="6:8" ht="22.5" customHeight="1">
+    <row r="251" spans="1:29" ht="22.5" customHeight="1">
       <c r="F251" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -34342,7 +35138,7 @@
         <v/>
       </c>
     </row>
-    <row r="252" spans="6:8" ht="22.5" customHeight="1">
+    <row r="252" spans="1:29" ht="22.5" customHeight="1">
       <c r="F252" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -34352,7 +35148,7 @@
         <v/>
       </c>
     </row>
-    <row r="253" spans="6:8" ht="22.5" customHeight="1">
+    <row r="253" spans="1:29" ht="22.5" customHeight="1">
       <c r="F253" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -34362,7 +35158,7 @@
         <v/>
       </c>
     </row>
-    <row r="254" spans="6:8" ht="22.5" customHeight="1">
+    <row r="254" spans="1:29" ht="22.5" customHeight="1">
       <c r="F254" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -34372,7 +35168,7 @@
         <v/>
       </c>
     </row>
-    <row r="255" spans="6:8" ht="22.5" customHeight="1">
+    <row r="255" spans="1:29" ht="22.5" customHeight="1">
       <c r="F255" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -34382,7 +35178,7 @@
         <v/>
       </c>
     </row>
-    <row r="256" spans="6:8" ht="22.5" customHeight="1">
+    <row r="256" spans="1:29" ht="22.5" customHeight="1">
       <c r="F256" s="48" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -47974,7 +48770,7 @@
         <v>1922</v>
       </c>
       <c r="AG148" s="18" t="s">
-        <v>4455</v>
+        <v>4454</v>
       </c>
       <c r="AH148" s="13" t="s">
         <v>1922</v>
@@ -48400,22 +49196,22 @@
         <v>3316</v>
       </c>
       <c r="M156" s="18" t="s">
+        <v>4455</v>
+      </c>
+      <c r="O156" s="18" t="s">
         <v>4456</v>
       </c>
-      <c r="O156" s="18" t="s">
+      <c r="Q156" s="18" t="s">
         <v>4457</v>
       </c>
-      <c r="Q156" s="18" t="s">
+      <c r="S156" s="18" t="s">
         <v>4458</v>
       </c>
-      <c r="S156" s="18" t="s">
+      <c r="U156" s="18" t="s">
         <v>4459</v>
       </c>
-      <c r="U156" s="18" t="s">
+      <c r="W156" s="18" t="s">
         <v>4460</v>
-      </c>
-      <c r="W156" s="18" t="s">
-        <v>4461</v>
       </c>
     </row>
     <row r="157" spans="1:34" ht="22.5" customHeight="1">
@@ -52758,10 +53554,10 @@
         <v>還在為找不到兌換碼煩惱嗎？《龍息：神寂》這款MMORPG手遊，為你提供一個廣闊的魔幻世界，讓你沉浸在史詩級的冒險中。你將扮演天選之人，與夥伴們一起對抗邪惡的龍族，拯救瀕臨毀滅的王國。遊戲提供了多樣的職業選擇、華麗的技能特效和豐富的副本挑戰，無論是喜歡PVE的劇情黨，還是熱衷PVP的競技玩家，都能在這裡找到屬於自己的樂趣。你還在等什麼？趕快找尋你的兌換碼、禮包碼，用最快速安全的方式完成代儲值，輕鬆變強，加入這場冒險，成為傳說中的屠龍英雄吧！</v>
       </c>
       <c r="F240" s="34" t="s">
+        <v>4446</v>
+      </c>
+      <c r="G240" s="13" t="s">
         <v>4447</v>
-      </c>
-      <c r="G240" s="13" t="s">
-        <v>4448</v>
       </c>
       <c r="H240" s="13" t="s">
         <v>2633</v>
@@ -52770,97 +53566,145 @@
         <v>4406</v>
       </c>
       <c r="K240" s="17" t="s">
+        <v>4441</v>
+      </c>
+      <c r="L240" s="13" t="s">
+        <v>4443</v>
+      </c>
+      <c r="M240" s="18" t="s">
         <v>4442</v>
       </c>
-      <c r="L240" s="13" t="s">
+      <c r="N240" s="13" t="s">
+        <v>4443</v>
+      </c>
+      <c r="O240" s="18" t="s">
         <v>4444</v>
       </c>
-      <c r="M240" s="18" t="s">
-        <v>4443</v>
-      </c>
-      <c r="N240" s="13" t="s">
-        <v>4444</v>
-      </c>
-      <c r="O240" s="18" t="s">
+      <c r="P240" s="13" t="s">
         <v>4445</v>
       </c>
-      <c r="P240" s="13" t="s">
-        <v>4446</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" ht="22.5" customHeight="1">
+    </row>
+    <row r="241" spans="1:12" ht="22.5" customHeight="1">
       <c r="A241" s="13" t="str">
         <f>IF(games!A241="", "", games!A241)</f>
-        <v/>
+        <v>玩具對決</v>
       </c>
       <c r="C241" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/玩具對決-禮包碼.jpg</v>
       </c>
       <c r="D241" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/玩具對決.html</v>
       </c>
       <c r="E241" s="14" t="str">
         <f>IF(games!I241&lt;&gt;"", games!I241, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="1:5" ht="22.5" customHeight="1">
+        <v>準備好加入這場刺激又療癒的玩具大戰了嗎？《玩具對決》是一款結合了策略、收集與即時PVP對戰的卡牌手機遊戲，讓玩家能蒐集超過百種可愛又逗趣的玩具角色，打造獨一無二的戰術牌組。遊戲戰鬥節奏明快，每次出牌都考驗著你的智慧與反應！想在玩具世界稱霸，除了磨練技術，更要善用官方釋出的兌換碼和禮包碼來快速強化陣容。此外，遊戲內提供代儲值服務，讓你能以最快速、最安全的方式獲得資源，無後顧之憂地享受這場玩具對決！</v>
+      </c>
+      <c r="F241" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G241" s="76" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K241" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L241" s="76" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12" ht="22.5" customHeight="1">
       <c r="A242" s="13" t="str">
         <f>IF(games!A242="", "", games!A242)</f>
-        <v/>
+        <v>幸福都市：市長模擬器</v>
       </c>
       <c r="C242" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/幸福都市：市長模擬器-禮包碼.jpg</v>
       </c>
       <c r="D242" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/幸福都市：市長模擬器.html</v>
       </c>
       <c r="E242" s="14" t="str">
         <f>IF(games!I242&lt;&gt;"", games!I242, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243" spans="1:5" ht="22.5" customHeight="1">
+        <v>想親手打造一座繁榮又充滿活力的夢想都市嗎？《幸福都市：市長模擬器》將實現你的願望！這是一款高自由度的模擬經營遊戲，你將扮演一位市長，從零開始規劃土地、建設住宅與公共設施，並招募各種市民來為城市注入新生命。無論是打造熱鬧的商業區、優美的觀光景點，還是完善的工業中心，都由你一手掌握！別忘了關注官方動態，善用官方提供的兌換碼及禮包碼，讓你的城市發展一日千里。遊戲也支援代儲值服務，保證快速安全，讓你輕鬆獲得資源，成為最稱職的幸福都市市長！</v>
+      </c>
+      <c r="F242" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G242" s="76" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K242" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L242" s="76" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12" ht="22.5" customHeight="1">
       <c r="A243" s="13" t="str">
         <f>IF(games!A243="", "", games!A243)</f>
-        <v/>
+        <v>黑道傳奇</v>
       </c>
       <c r="C243" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/黑道傳奇-禮包碼.jpg</v>
       </c>
       <c r="D243" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/黑道傳奇.html</v>
       </c>
       <c r="E243" s="14" t="str">
         <f>IF(games!I243&lt;&gt;"", games!I243, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="1:5" ht="22.5" customHeight="1">
+        <v>《黑道傳奇》是一款以現代黑幫為背景的策略模擬遊戲。身為一名新崛起的老大，你將體驗最真實的地下世界！從經營賭場、收取保護費，到招募小弟、擴張地盤，每一步都將考驗你的手腕與決策能力。遊戲中的社交系統讓你可以與其他玩家結盟，共同對抗強敵，或是展開一場驚心動魄的火拼。想要在血腥的黑幫世界中脫穎而出，除了運籌帷幄，更要把握每一次的強化機會。善用官方釋出的兌換碼與禮包碼，並透過快速安全的代儲值服務，讓你的勢力迅速壯大，成就傳奇！</v>
+      </c>
+      <c r="F243" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G243" s="76" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K243" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L243" s="76" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12" ht="22.5" customHeight="1">
       <c r="A244" s="13" t="str">
         <f>IF(games!A244="", "", games!A244)</f>
-        <v/>
+        <v>The kingdom：medieval tales</v>
       </c>
       <c r="C244" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/The kingdom：medieval tales-禮包碼.jpg</v>
       </c>
       <c r="D244" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/The kingdom：medieval tales.html</v>
       </c>
       <c r="E244" s="14" t="str">
         <f>IF(games!I244&lt;&gt;"", games!I244, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="1:5" ht="22.5" customHeight="1">
+        <v>回到那個騎士與城堡的黃金年代吧！《The kingdom：medieval tales》是一款深度十足的中世紀策略經營遊戲。在這款遊戲中，你將成為一名領主，從零開始建立並經營你的王國。透過精心規劃資源、訓練軍隊、建設防禦工事，你將抵禦來犯的敵人，並逐步擴大你的領土。遊戲提供了豐富的歷史事件與任務，讓你沉浸在真實的中世紀氛圍中。想要加速你的王國發展，別忘了善用官方提供的兌換碼及禮包碼。遊戲也提供代儲值服務，讓你用最快速安全的方式獲得稀有資源，成為中世紀最強大的王者！</v>
+      </c>
+      <c r="F244" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G244" s="76" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K244" s="75" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L244" s="76" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12" ht="22.5" customHeight="1">
       <c r="A245" s="13" t="str">
         <f>IF(games!A245="", "", games!A245)</f>
         <v/>
@@ -52878,7 +53722,7 @@
         <v/>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="22.5" customHeight="1">
+    <row r="246" spans="1:12" ht="22.5" customHeight="1">
       <c r="A246" s="13" t="str">
         <f>IF(games!A246="", "", games!A246)</f>
         <v/>
@@ -52896,7 +53740,7 @@
         <v/>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="22.5" customHeight="1">
+    <row r="247" spans="1:12" ht="22.5" customHeight="1">
       <c r="A247" s="13" t="str">
         <f>IF(games!A247="", "", games!A247)</f>
         <v/>
@@ -52914,7 +53758,7 @@
         <v/>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="22.5" customHeight="1">
+    <row r="248" spans="1:12" ht="22.5" customHeight="1">
       <c r="A248" s="13" t="str">
         <f>IF(games!A248="", "", games!A248)</f>
         <v/>
@@ -52932,7 +53776,7 @@
         <v/>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="22.5" customHeight="1">
+    <row r="249" spans="1:12" ht="22.5" customHeight="1">
       <c r="A249" s="13" t="str">
         <f>IF(games!A249="", "", games!A249)</f>
         <v/>
@@ -52950,7 +53794,7 @@
         <v/>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="22.5" customHeight="1">
+    <row r="250" spans="1:12" ht="22.5" customHeight="1">
       <c r="A250" s="13" t="str">
         <f>IF(games!A250="", "", games!A250)</f>
         <v/>
@@ -52968,7 +53812,7 @@
         <v/>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="22.5" customHeight="1">
+    <row r="251" spans="1:12" ht="22.5" customHeight="1">
       <c r="C251" s="13" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -52982,7 +53826,7 @@
         <v/>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="22.5" customHeight="1">
+    <row r="252" spans="1:12" ht="22.5" customHeight="1">
       <c r="C252" s="13" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -52996,7 +53840,7 @@
         <v/>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="22.5" customHeight="1">
+    <row r="253" spans="1:12" ht="22.5" customHeight="1">
       <c r="C253" s="13" t="str">
         <f t="shared" ref="C253:C316" si="9">IF(A253="","", "giftcodesbanner/" &amp; A253 &amp; "-禮包碼.jpg")</f>
         <v/>
@@ -53010,7 +53854,7 @@
         <v/>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="22.5" customHeight="1">
+    <row r="254" spans="1:12" ht="22.5" customHeight="1">
       <c r="C254" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -53024,7 +53868,7 @@
         <v/>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="22.5" customHeight="1">
+    <row r="255" spans="1:12" ht="22.5" customHeight="1">
       <c r="C255" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -53034,7 +53878,7 @@
         <v/>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="22.5" customHeight="1">
+    <row r="256" spans="1:12" ht="22.5" customHeight="1">
       <c r="C256" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6687" uniqueCount="4498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6773" uniqueCount="4574">
   <si>
     <t>Facebook</t>
   </si>
@@ -16958,12 +16958,6 @@
   </si>
   <si>
     <t>8HKD遊戲禮包</t>
-  </si>
-  <si>
-    <t>74.99禮包</t>
-  </si>
-  <si>
-    <t>16.99禮包</t>
   </si>
   <si>
     <t>ALBIS777</t>
@@ -17704,12 +17698,299 @@
   <si>
     <t>傳說中的糖果劍</t>
   </si>
+  <si>
+    <t>1200元寶</t>
+  </si>
+  <si>
+    <t>一鍵每日禮包</t>
+  </si>
+  <si>
+    <t>快速作戰月卡</t>
+  </si>
+  <si>
+    <t>https://coupon.netmarble.com/tskgb</t>
+  </si>
+  <si>
+    <t>進網址兌換即可</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SENAREYOUNGLAEGI</t>
+  </si>
+  <si>
+    <t>SENAREGSIK</t>
+  </si>
+  <si>
+    <t>SENAREMOOVING</t>
+  </si>
+  <si>
+    <t>SENARESAMEWAY</t>
+  </si>
+  <si>
+    <t>SORRY4WAITING</t>
+  </si>
+  <si>
+    <t>Grave Strikers</t>
+  </si>
+  <si>
+    <t>Stellar Sanctuary</t>
+  </si>
+  <si>
+    <t>古惑仔：風雲再起</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.bandainamcoent.dbgekishinsquadra</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/dragon-ball-gekishin-squadra/id6744439943</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/grave-strikers/id6748154304</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.boltersquad.gravestrikers</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/stellar-sanctuary/id6745683002</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.pergame.starliteden</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E5%8F%A4%E6%83%91%E4%BB%94-%E9%A2%A8%E9%9B%B2%E5%86%8D%E8%B5%B7/id6749257155</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.gamexdd.ghzaz</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>七龍珠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>激震小隊</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://dbg-squadra.bn-ent.net/tw</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/gamexdd.ghz</t>
+  </si>
+  <si>
+    <t>https://ghz.gamexdd.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://stellarsanctuarygame.com/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/people/Stellar-Sanctuary/61569506387405/</t>
+  </si>
+  <si>
+    <t>https://www.boltersquad.com/</t>
+  </si>
+  <si>
+    <t>終於等到這款由萬代南夢宮娛樂開發的《七龍珠 激震小隊》！這是一款全新的動作 RPG，讓你能體驗原作經典故事，並與悟空、達爾等超人氣角色並肩作戰！遊戲主打爽快又華麗的戰鬥體驗，玩家可以自由組隊，施展各種經典招式，還能享受震撼力十足的「七龍珠」宇宙冒險。遊戲內建多種模式，包括PVP對戰、協力共鬥等，讓你可以和朋友一同挑戰強敵。別忘了關注官方社群，第一時間獲取兌換碼及禮包碼，讓你開局就贏在起跑線！此外，如果你想快速提升戰力，也能透過快速安全的代儲值服務，輕鬆擴大你的英雄陣容！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《Grave Strikers》是一款視覺風格獨特的戰術 RPG 手遊，玩家將扮演指揮官，組建一支由「靈魂」組成的強力隊伍，在這片被黑暗侵蝕的大陸上展開冒險！遊戲融合了策略布陣與即時戰鬥的元素，每一位靈魂都擁有專屬的技能與故事。透過不斷提升隊伍的實力，解鎖更多新角色，並在充滿挑戰的地下城中證明自己。關注官方社群，不錯過任何兌換碼與禮包碼的發送，讓你的冒險之路更加順暢！想要快速集結更強大的靈魂，代儲值服務是個快速安全的好選擇，讓你輕鬆面對每一個難關！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《Stellar Sanctuary》是一款科幻題材的放置 RPG 手遊，遊戲背景設定在浩瀚的宇宙中，玩家將扮演一名宇宙探險家，招募來自不同星系的英雄，一同對抗邪惡的勢力！遊戲最大的特色就是「輕鬆放置，也能變強」，即使離線也能持續獲得豐富資源，讓你的英雄隊伍不斷成長。此外，遊戲內豐富的英雄養成系統和策略性戰鬥玩法，讓你不僅可以享受掛機的樂趣，也能深入體驗戰術搭配的醍醐味。想快速獲得稀有英雄或裝備嗎？別忘了領取官方發布的兌換碼與禮包碼，或是選擇快速安全的代儲值服務，加速你的宇宙探索旅程！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>經典 IP 手遊《古惑仔：風雲再起》正式登場！遊戲以熱血沸騰的「古惑仔」世界為背景，忠實還原了電影中的經典場景和人物。玩家將能親身扮演陳浩南、山雞等傳奇人物，在銅鑼灣街頭展開一場場江湖廝殺，體驗兄弟情義與權力鬥爭的熱血故事。遊戲主打幫派戰鬥與策略養成，你可以招募小弟、壯大勢力，最終成為一方霸主。為了在江湖中站穩腳跟，別忘了領取官方提供的兌換碼和禮包碼，讓你快速提升戰力！需要更多資源來稱霸一方？快速安全的代儲值服務是你的最佳選擇，讓你輕鬆成為叱吒風雲的傳奇人物！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/db.gekishin.squadra</t>
+  </si>
+  <si>
+    <t>https://x.com/BolterSquad</t>
+  </si>
+  <si>
+    <t>龍玉E</t>
+  </si>
+  <si>
+    <t>龍玉D</t>
+  </si>
+  <si>
+    <t>龍玉C</t>
+  </si>
+  <si>
+    <t>龍玉B</t>
+  </si>
+  <si>
+    <t>龍玉A</t>
+  </si>
+  <si>
+    <t>初始禮包</t>
+  </si>
+  <si>
+    <t>迷你初始禮包</t>
+  </si>
+  <si>
+    <t>6500鑽</t>
+  </si>
+  <si>
+    <t>5000鑽</t>
+  </si>
+  <si>
+    <t>4000鑽</t>
+  </si>
+  <si>
+    <t>3280鑽</t>
+  </si>
+  <si>
+    <t>1980鑽</t>
+  </si>
+  <si>
+    <t>980鑽</t>
+  </si>
+  <si>
+    <t>680鑽</t>
+  </si>
+  <si>
+    <t>300鑽</t>
+  </si>
+  <si>
+    <t>60鑽</t>
+  </si>
+  <si>
+    <t>VIP888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7F3K9A2RZ8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石 x 20、金錢 x 30000、高級令簽 x 2、升品藥劑 x 10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石 x 20、金錢 x 55555、高級令簽 x 3、體力飲料(小) x 3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石 x 20、金錢 x 68888、高級令簽 x 3、體力飲料(小) x 5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9999寰宇幣</t>
+  </si>
+  <si>
+    <r>
+      <t>6500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>寶石</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1150寶石</t>
+  </si>
+  <si>
+    <t>550寶石</t>
+  </si>
+  <si>
+    <t>100寶石</t>
+  </si>
+  <si>
+    <t>20000信用幣</t>
+  </si>
+  <si>
+    <t>10000信用幣</t>
+  </si>
+  <si>
+    <t>4000信用幣</t>
+  </si>
+  <si>
+    <t>2000信用幣</t>
+  </si>
+  <si>
+    <t>1000信用幣</t>
+  </si>
+  <si>
+    <t>200信用幣</t>
+  </si>
+  <si>
+    <t>等待官方更新</t>
+  </si>
+  <si>
+    <t>點主畫面左上角指揮官頭像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>畫面右下「兌換碼」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點畫面左上角「設定」齒輪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UR666</t>
+  </si>
+  <si>
+    <t>UR888</t>
+  </si>
+  <si>
+    <t>TLZ66666</t>
+  </si>
+  <si>
+    <t>點主畫面左上角頭像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家資訊下方「禮包碼」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://dbg-squadra.bn-ent.net/tw/serialcode</t>
+  </si>
+  <si>
+    <t>到上方網址輸入序號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>等待官方更新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -17877,6 +18158,12 @@
       <sz val="14"/>
       <color rgb="FFE2E5E9"/>
       <name val="Segoe UI Historic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -18124,7 +18411,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -18384,6 +18671,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -34628,119 +34916,119 @@
         <v>4328</v>
       </c>
       <c r="J239" s="1" t="s">
-        <v>1660</v>
+        <v>235</v>
       </c>
       <c r="K239" s="2">
         <v>2286</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>4392</v>
+        <v>204</v>
       </c>
       <c r="M239" s="2">
-        <v>1903</v>
+        <v>1139</v>
       </c>
       <c r="N239" s="1" t="s">
-        <v>1661</v>
+        <v>1292</v>
       </c>
       <c r="O239" s="2">
-        <v>1139</v>
+        <v>757</v>
       </c>
       <c r="P239" s="1" t="s">
-        <v>1662</v>
+        <v>4496</v>
       </c>
       <c r="Q239" s="2">
-        <v>757</v>
+        <v>519</v>
       </c>
       <c r="R239" s="1" t="s">
-        <v>1663</v>
+        <v>205</v>
       </c>
       <c r="S239" s="2">
-        <v>519</v>
+        <v>256</v>
       </c>
       <c r="T239" s="1" t="s">
-        <v>4393</v>
+        <v>239</v>
       </c>
       <c r="U239" s="2">
-        <v>457</v>
+        <v>140</v>
       </c>
       <c r="V239" s="1" t="s">
-        <v>1664</v>
+        <v>240</v>
       </c>
       <c r="W239" s="2">
+        <v>27</v>
+      </c>
+      <c r="X239" s="1" t="s">
+        <v>4497</v>
+      </c>
+      <c r="Y239" s="2">
         <v>380</v>
       </c>
-      <c r="X239" s="1" t="s">
-        <v>1667</v>
-      </c>
-      <c r="Y239" s="2">
-        <v>140</v>
-      </c>
       <c r="Z239" s="1" t="s">
-        <v>4175</v>
+        <v>4498</v>
       </c>
       <c r="AA239" s="2">
-        <v>58</v>
+        <v>256</v>
       </c>
     </row>
     <row r="240" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A240" s="102" t="s">
-        <v>4461</v>
+        <v>4459</v>
       </c>
       <c r="C240" s="47" t="s">
-        <v>4437</v>
+        <v>4435</v>
       </c>
       <c r="D240" s="48" t="s">
-        <v>4438</v>
+        <v>4436</v>
       </c>
       <c r="E240" s="48" t="s">
-        <v>4436</v>
+        <v>4434</v>
       </c>
       <c r="F240" s="48" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/龍息：神寂.html</v>
       </c>
       <c r="G240" s="48" t="s">
-        <v>4439</v>
+        <v>4437</v>
       </c>
       <c r="H240" s="48" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/龍息：神寂.html</v>
       </c>
       <c r="I240" s="49" t="s">
-        <v>4440</v>
+        <v>4438</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>4448</v>
+        <v>4446</v>
       </c>
       <c r="K240" s="2">
         <v>2479</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>4449</v>
+        <v>4447</v>
       </c>
       <c r="M240" s="2">
         <v>1292</v>
       </c>
       <c r="N240" s="1" t="s">
-        <v>4450</v>
+        <v>4448</v>
       </c>
       <c r="O240" s="2">
         <v>757</v>
       </c>
       <c r="P240" s="1" t="s">
-        <v>4451</v>
+        <v>4449</v>
       </c>
       <c r="Q240" s="2">
         <v>380</v>
       </c>
       <c r="R240" s="1" t="s">
-        <v>4452</v>
+        <v>4450</v>
       </c>
       <c r="S240" s="2">
         <v>140</v>
       </c>
       <c r="T240" s="1" t="s">
-        <v>4453</v>
+        <v>4451</v>
       </c>
       <c r="U240" s="2">
         <v>50</v>
@@ -34748,39 +35036,39 @@
     </row>
     <row r="241" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A241" s="80" t="s">
-        <v>4462</v>
+        <v>4460</v>
       </c>
       <c r="C241" s="47" t="s">
-        <v>4469</v>
+        <v>4467</v>
       </c>
       <c r="D241" s="47" t="s">
-        <v>4467</v>
+        <v>4465</v>
       </c>
       <c r="E241" s="48" t="s">
-        <v>4468</v>
+        <v>4466</v>
       </c>
       <c r="F241" s="48" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/玩具對決.html</v>
       </c>
       <c r="G241" s="48" t="s">
-        <v>4466</v>
+        <v>4464</v>
       </c>
       <c r="H241" s="48" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/玩具對決.html</v>
       </c>
       <c r="I241" t="s">
-        <v>4479</v>
+        <v>4477</v>
       </c>
       <c r="J241" s="1" t="s">
-        <v>4483</v>
+        <v>4481</v>
       </c>
       <c r="K241" s="2">
         <v>2286</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>4484</v>
+        <v>4482</v>
       </c>
       <c r="M241" s="2">
         <v>1139</v>
@@ -34792,7 +35080,7 @@
         <v>535</v>
       </c>
       <c r="P241" s="1" t="s">
-        <v>4485</v>
+        <v>4483</v>
       </c>
       <c r="Q241" s="2">
         <v>248</v>
@@ -34810,7 +35098,7 @@
         <v>25</v>
       </c>
       <c r="V241" s="1" t="s">
-        <v>4486</v>
+        <v>4484</v>
       </c>
       <c r="W241" s="2">
         <v>248</v>
@@ -34822,7 +35110,7 @@
         <v>171</v>
       </c>
       <c r="Z241" s="1" t="s">
-        <v>4487</v>
+        <v>4485</v>
       </c>
       <c r="AA241" s="2">
         <v>124</v>
@@ -34830,30 +35118,30 @@
     </row>
     <row r="242" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A242" s="3" t="s">
-        <v>4463</v>
+        <v>4461</v>
       </c>
       <c r="C242" s="48" t="s">
-        <v>4471</v>
+        <v>4469</v>
       </c>
       <c r="D242" s="48" t="s">
-        <v>4471</v>
+        <v>4469</v>
       </c>
       <c r="E242" s="48" t="s">
-        <v>4471</v>
+        <v>4469</v>
       </c>
       <c r="F242" s="48" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/幸福都市：市長模擬器.html</v>
       </c>
       <c r="G242" s="48" t="s">
-        <v>4470</v>
+        <v>4468</v>
       </c>
       <c r="H242" s="48" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/幸福都市：市長模擬器.html</v>
       </c>
       <c r="I242" t="s">
-        <v>4480</v>
+        <v>4478</v>
       </c>
       <c r="J242" s="1" t="s">
         <v>301</v>
@@ -34900,51 +35188,51 @@
     </row>
     <row r="243" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A243" s="3" t="s">
-        <v>4464</v>
+        <v>4462</v>
       </c>
       <c r="C243" s="47" t="s">
-        <v>4478</v>
+        <v>4476</v>
       </c>
       <c r="D243" s="48" t="s">
-        <v>4476</v>
+        <v>4474</v>
       </c>
       <c r="E243" s="48" t="s">
-        <v>4473</v>
+        <v>4471</v>
       </c>
       <c r="F243" s="48" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/黑道傳奇.html</v>
       </c>
       <c r="G243" s="48" t="s">
-        <v>4472</v>
+        <v>4470</v>
       </c>
       <c r="H243" s="48" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/黑道傳奇.html</v>
       </c>
       <c r="I243" t="s">
-        <v>4481</v>
+        <v>4479</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>4488</v>
+        <v>4486</v>
       </c>
       <c r="K243" s="2">
         <v>2479</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>4489</v>
+        <v>4487</v>
       </c>
       <c r="M243" s="2">
         <v>1292</v>
       </c>
       <c r="N243" s="1" t="s">
-        <v>4490</v>
+        <v>4488</v>
       </c>
       <c r="O243" s="2">
         <v>757</v>
       </c>
       <c r="P243" s="1" t="s">
-        <v>4491</v>
+        <v>4489</v>
       </c>
       <c r="Q243" s="2">
         <v>634</v>
@@ -34962,19 +35250,19 @@
         <v>256</v>
       </c>
       <c r="V243" s="1" t="s">
-        <v>4492</v>
+        <v>4490</v>
       </c>
       <c r="W243" s="2">
         <v>140</v>
       </c>
       <c r="X243" s="1" t="s">
-        <v>4493</v>
+        <v>4491</v>
       </c>
       <c r="Y243" s="2">
         <v>83</v>
       </c>
       <c r="Z243" s="1" t="s">
-        <v>4494</v>
+        <v>4492</v>
       </c>
       <c r="AA243" s="2">
         <v>57</v>
@@ -34982,30 +35270,30 @@
     </row>
     <row r="244" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A244" s="80" t="s">
-        <v>4465</v>
+        <v>4463</v>
       </c>
       <c r="C244" s="47" t="s">
         <v>3659</v>
       </c>
       <c r="D244" s="48" t="s">
-        <v>4477</v>
+        <v>4475</v>
       </c>
       <c r="E244" s="48" t="s">
-        <v>4474</v>
+        <v>4472</v>
       </c>
       <c r="F244" s="48" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/The kingdom：medieval tales.html</v>
       </c>
       <c r="G244" s="48" t="s">
-        <v>4475</v>
+        <v>4473</v>
       </c>
       <c r="H244" s="48" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/The kingdom：medieval tales.html</v>
       </c>
       <c r="I244" t="s">
-        <v>4482</v>
+        <v>4480</v>
       </c>
       <c r="J244" s="1" t="s">
         <v>301</v>
@@ -35050,62 +35338,296 @@
         <v>99</v>
       </c>
       <c r="X244" s="1" t="s">
-        <v>4495</v>
+        <v>4493</v>
       </c>
       <c r="Y244" s="2">
         <v>225</v>
       </c>
       <c r="Z244" s="1" t="s">
-        <v>4496</v>
+        <v>4494</v>
       </c>
       <c r="AA244" s="2">
         <v>302</v>
       </c>
       <c r="AB244" s="1" t="s">
-        <v>4497</v>
+        <v>4495</v>
       </c>
       <c r="AC244" s="2">
         <v>612</v>
       </c>
     </row>
-    <row r="245" spans="1:29" ht="22.5" customHeight="1">
+    <row r="245" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A245" s="3" t="s">
+        <v>4517</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>4528</v>
+      </c>
+      <c r="D245" s="4" t="s">
+        <v>4518</v>
+      </c>
+      <c r="E245" s="48" t="s">
+        <v>4510</v>
+      </c>
       <c r="F245" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/七龍珠激震小隊.html</v>
+      </c>
+      <c r="G245" s="48" t="s">
+        <v>4509</v>
       </c>
       <c r="H245" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="246" spans="1:29" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/七龍珠激震小隊.html</v>
+      </c>
+      <c r="I245" s="49" t="s">
+        <v>4524</v>
+      </c>
+      <c r="J245" s="1" t="s">
+        <v>4530</v>
+      </c>
+      <c r="K245" s="2">
+        <v>2056</v>
+      </c>
+      <c r="L245" s="1" t="s">
+        <v>4531</v>
+      </c>
+      <c r="M245" s="2">
+        <v>1009</v>
+      </c>
+      <c r="N245" s="1" t="s">
+        <v>4532</v>
+      </c>
+      <c r="O245" s="2">
+        <v>519</v>
+      </c>
+      <c r="P245" s="1" t="s">
+        <v>4533</v>
+      </c>
+      <c r="Q245" s="2">
+        <v>178</v>
+      </c>
+      <c r="R245" s="1" t="s">
+        <v>4534</v>
+      </c>
+      <c r="S245" s="2">
+        <v>58</v>
+      </c>
+      <c r="T245" s="1" t="s">
+        <v>4535</v>
+      </c>
+      <c r="U245" s="2">
+        <v>1139</v>
+      </c>
+      <c r="V245" s="1" t="s">
+        <v>4536</v>
+      </c>
+      <c r="W245" s="2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="246" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A246" s="80" t="s">
+        <v>4506</v>
+      </c>
+      <c r="C246" s="47" t="s">
+        <v>4529</v>
+      </c>
+      <c r="D246" s="48" t="s">
+        <v>4523</v>
+      </c>
+      <c r="E246" s="4" t="s">
+        <v>4511</v>
+      </c>
       <c r="F246" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Grave Strikers.html</v>
+      </c>
+      <c r="G246" s="48" t="s">
+        <v>4512</v>
       </c>
       <c r="H246" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="1:29" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Grave Strikers.html</v>
+      </c>
+      <c r="I246" s="49" t="s">
+        <v>4525</v>
+      </c>
+      <c r="J246" s="1" t="s">
+        <v>4552</v>
+      </c>
+      <c r="K246" s="2">
+        <v>1139</v>
+      </c>
+      <c r="L246" s="1" t="s">
+        <v>4553</v>
+      </c>
+      <c r="M246" s="2">
+        <v>225</v>
+      </c>
+      <c r="N246" s="1" t="s">
+        <v>4554</v>
+      </c>
+      <c r="O246" s="2">
+        <v>99</v>
+      </c>
+      <c r="P246" s="1" t="s">
+        <v>4555</v>
+      </c>
+      <c r="Q246" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="247" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A247" s="80" t="s">
+        <v>4507</v>
+      </c>
+      <c r="C247" s="47" t="s">
+        <v>4522</v>
+      </c>
+      <c r="D247" s="48" t="s">
+        <v>4521</v>
+      </c>
+      <c r="E247" s="48" t="s">
+        <v>4513</v>
+      </c>
       <c r="F247" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Stellar Sanctuary.html</v>
+      </c>
+      <c r="G247" s="48" t="s">
+        <v>4514</v>
       </c>
       <c r="H247" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="1:29" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Stellar Sanctuary.html</v>
+      </c>
+      <c r="I247" s="49" t="s">
+        <v>4526</v>
+      </c>
+      <c r="J247" s="1" t="s">
+        <v>4551</v>
+      </c>
+      <c r="K247" s="2">
+        <v>2623</v>
+      </c>
+      <c r="L247" s="1" t="s">
+        <v>4556</v>
+      </c>
+      <c r="M247" s="2">
+        <v>2623</v>
+      </c>
+      <c r="N247" s="1" t="s">
+        <v>4557</v>
+      </c>
+      <c r="O247" s="2">
+        <v>1330</v>
+      </c>
+      <c r="P247" s="1" t="s">
+        <v>4558</v>
+      </c>
+      <c r="Q247" s="2">
+        <v>543</v>
+      </c>
+      <c r="R247" s="1" t="s">
+        <v>4559</v>
+      </c>
+      <c r="S247" s="2">
+        <v>271</v>
+      </c>
+      <c r="T247" s="1" t="s">
+        <v>4560</v>
+      </c>
+      <c r="U247" s="2">
+        <v>149</v>
+      </c>
+      <c r="V247" s="1" t="s">
+        <v>4561</v>
+      </c>
+      <c r="W247" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="248" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A248" s="80" t="s">
+        <v>4508</v>
+      </c>
+      <c r="C248" s="47" t="s">
+        <v>4519</v>
+      </c>
+      <c r="D248" s="4" t="s">
+        <v>4520</v>
+      </c>
+      <c r="E248" s="48" t="s">
+        <v>4515</v>
+      </c>
       <c r="F248" s="48" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/古惑仔：風雲再起.html</v>
+      </c>
+      <c r="G248" s="48" t="s">
+        <v>4516</v>
       </c>
       <c r="H248" s="48" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/古惑仔：風雲再起.html</v>
+      </c>
+      <c r="I248" s="49" t="s">
+        <v>4527</v>
+      </c>
+      <c r="J248" s="1" t="s">
+        <v>4537</v>
+      </c>
+      <c r="K248" s="2">
+        <v>2449</v>
+      </c>
+      <c r="L248" s="1" t="s">
+        <v>4538</v>
+      </c>
+      <c r="M248" s="2">
+        <v>1911</v>
+      </c>
+      <c r="N248" s="1" t="s">
+        <v>4539</v>
+      </c>
+      <c r="O248" s="2">
+        <v>1529</v>
+      </c>
+      <c r="P248" s="1" t="s">
+        <v>4540</v>
+      </c>
+      <c r="Q248" s="2">
+        <v>1254</v>
+      </c>
+      <c r="R248" s="1" t="s">
+        <v>4541</v>
+      </c>
+      <c r="S248" s="2">
+        <v>757</v>
+      </c>
+      <c r="T248" s="1" t="s">
+        <v>4542</v>
+      </c>
+      <c r="U248" s="2">
+        <v>380</v>
+      </c>
+      <c r="V248" s="1" t="s">
+        <v>4543</v>
+      </c>
+      <c r="W248" s="2">
+        <v>264</v>
+      </c>
+      <c r="X248" s="1" t="s">
+        <v>4544</v>
+      </c>
+      <c r="Y248" s="2">
+        <v>124</v>
+      </c>
+      <c r="Z248" s="1" t="s">
+        <v>4545</v>
+      </c>
+      <c r="AA248" s="2">
+        <v>25</v>
       </c>
     </row>
     <row r="249" spans="1:29" ht="22.5" customHeight="1">
@@ -38861,9 +39383,12 @@
     <hyperlink ref="C233" r:id="rId141"/>
     <hyperlink ref="G230" r:id="rId142"/>
     <hyperlink ref="C234" r:id="rId143"/>
+    <hyperlink ref="E246" r:id="rId144"/>
+    <hyperlink ref="D245" r:id="rId145"/>
+    <hyperlink ref="D248" r:id="rId146"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId144"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId147"/>
 </worksheet>
 </file>
 
@@ -48770,7 +49295,7 @@
         <v>1922</v>
       </c>
       <c r="AG148" s="18" t="s">
-        <v>4454</v>
+        <v>4452</v>
       </c>
       <c r="AH148" s="13" t="s">
         <v>1922</v>
@@ -49196,22 +49721,22 @@
         <v>3316</v>
       </c>
       <c r="M156" s="18" t="s">
+        <v>4453</v>
+      </c>
+      <c r="O156" s="18" t="s">
+        <v>4454</v>
+      </c>
+      <c r="Q156" s="18" t="s">
         <v>4455</v>
       </c>
-      <c r="O156" s="18" t="s">
+      <c r="S156" s="18" t="s">
         <v>4456</v>
       </c>
-      <c r="Q156" s="18" t="s">
+      <c r="U156" s="18" t="s">
         <v>4457</v>
       </c>
-      <c r="S156" s="18" t="s">
+      <c r="W156" s="18" t="s">
         <v>4458</v>
-      </c>
-      <c r="U156" s="18" t="s">
-        <v>4459</v>
-      </c>
-      <c r="W156" s="18" t="s">
-        <v>4460</v>
       </c>
     </row>
     <row r="157" spans="1:34" ht="22.5" customHeight="1">
@@ -52869,64 +53394,64 @@
         <v>什麼？還在為了升級煩惱，或被副本Boss虐到懷疑人生？快醒醒吧！在《阿瑞斯：命運的選擇者》中，你將扮演天選之人，解鎖傳說英雄，打造最強陣容，讓那些自以為是的敵人知道什麼叫「殘酷」的勝利。這裡的福利多到你不敢想像，各種獨家禮包碼、兌換碼隨便拿，讓你戰力起飛。覺得遊戲太肝又太慢？沒關係，我們的代儲值服務讓你體驗什麼叫「快速安全」，一秒讓你成為人上人，輕鬆碾壓所有對手，不用再當可憐的免費仔，讓別人看看什麼叫真正的歐洲血統！</v>
       </c>
       <c r="F225" s="100" t="s">
+        <v>4425</v>
+      </c>
+      <c r="G225" s="79" t="s">
+        <v>4426</v>
+      </c>
+      <c r="H225" s="79" t="s">
         <v>4427</v>
       </c>
-      <c r="G225" s="79" t="s">
+      <c r="I225" s="79" t="s">
         <v>4428</v>
       </c>
-      <c r="H225" s="79" t="s">
+      <c r="J225" s="79" t="s">
         <v>4429</v>
       </c>
-      <c r="I225" s="79" t="s">
-        <v>4430</v>
-      </c>
-      <c r="J225" s="79" t="s">
-        <v>4431</v>
-      </c>
       <c r="K225" s="79" t="s">
-        <v>4413</v>
+        <v>4411</v>
       </c>
       <c r="L225" s="76" t="s">
         <v>2648</v>
       </c>
       <c r="M225" s="79" t="s">
+        <v>4412</v>
+      </c>
+      <c r="O225" s="79" t="s">
+        <v>4413</v>
+      </c>
+      <c r="Q225" s="79" t="s">
         <v>4414</v>
       </c>
-      <c r="O225" s="79" t="s">
+      <c r="S225" s="79" t="s">
         <v>4415</v>
       </c>
-      <c r="Q225" s="79" t="s">
+      <c r="U225" s="79" t="s">
         <v>4416</v>
       </c>
-      <c r="S225" s="79" t="s">
+      <c r="W225" s="79" t="s">
         <v>4417</v>
       </c>
-      <c r="U225" s="79" t="s">
+      <c r="Y225" s="79" t="s">
         <v>4418</v>
       </c>
-      <c r="W225" s="79" t="s">
+      <c r="AA225" s="79" t="s">
         <v>4419</v>
       </c>
-      <c r="Y225" s="79" t="s">
+      <c r="AC225" s="79" t="s">
         <v>4420</v>
       </c>
-      <c r="AA225" s="79" t="s">
+      <c r="AE225" s="79" t="s">
         <v>4421</v>
       </c>
-      <c r="AC225" s="79" t="s">
+      <c r="AG225" s="79" t="s">
         <v>4422</v>
       </c>
-      <c r="AE225" s="79" t="s">
+      <c r="AI225" s="79" t="s">
         <v>4423</v>
       </c>
-      <c r="AG225" s="79" t="s">
+      <c r="AK225" s="79" t="s">
         <v>4424</v>
-      </c>
-      <c r="AI225" s="79" t="s">
-        <v>4425</v>
-      </c>
-      <c r="AK225" s="79" t="s">
-        <v>4426</v>
       </c>
     </row>
     <row r="226" spans="1:47" ht="22.5" customHeight="1">
@@ -53001,22 +53526,22 @@
         <v>4299</v>
       </c>
       <c r="Q227" s="101" t="s">
+        <v>4430</v>
+      </c>
+      <c r="R227" s="13" t="s">
+        <v>4433</v>
+      </c>
+      <c r="S227" s="101" t="s">
+        <v>4431</v>
+      </c>
+      <c r="T227" s="13" t="s">
+        <v>4433</v>
+      </c>
+      <c r="U227" s="101" t="s">
         <v>4432</v>
       </c>
-      <c r="R227" s="13" t="s">
-        <v>4435</v>
-      </c>
-      <c r="S227" s="101" t="s">
+      <c r="V227" s="13" t="s">
         <v>4433</v>
-      </c>
-      <c r="T227" s="13" t="s">
-        <v>4435</v>
-      </c>
-      <c r="U227" s="101" t="s">
-        <v>4434</v>
-      </c>
-      <c r="V227" s="13" t="s">
-        <v>4435</v>
       </c>
     </row>
     <row r="228" spans="1:47" ht="22.5" customHeight="1">
@@ -53036,17 +53561,42 @@
         <f>IF(games!I228&lt;&gt;"", games!I228, "")</f>
         <v>還在為那些看臉抽卡的遊戲心力交瘁？醒醒吧！在《量子機動隊》裡，你將化身為超能指揮官，集結各路英雄，打造一支所向披靡的隊伍，讓那些自以為是的對手嚐嚐什麼叫殘酷的勝利。我們準備了滿滿的兌換碼、禮包碼讓你開局就贏在起跑線，資源拿到手軟。覺得升級太慢太累？別擔心！我們的代儲值服務保證快速安全，讓你用最快的速度打造最強牌組，再也不用擔心牌運不佳，一秒成為牌場上的傳奇，用鈔能力向世界證明你的實力！</v>
       </c>
-      <c r="F228" s="75" t="s">
-        <v>2648</v>
+      <c r="F228" s="34" t="s">
+        <v>4569</v>
       </c>
       <c r="G228" s="76" t="s">
-        <v>2648</v>
-      </c>
-      <c r="K228" s="75" t="s">
-        <v>2648</v>
-      </c>
-      <c r="L228" s="76" t="s">
-        <v>2648</v>
+        <v>4570</v>
+      </c>
+      <c r="H228" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I228" s="13" t="s">
+        <v>3789</v>
+      </c>
+      <c r="K228" s="79" t="s">
+        <v>1784</v>
+      </c>
+      <c r="L228" s="76"/>
+      <c r="M228" s="79" t="s">
+        <v>1716</v>
+      </c>
+      <c r="O228" s="79" t="s">
+        <v>1717</v>
+      </c>
+      <c r="Q228" s="79" t="s">
+        <v>1822</v>
+      </c>
+      <c r="S228" s="79" t="s">
+        <v>4566</v>
+      </c>
+      <c r="U228" s="79" t="s">
+        <v>4567</v>
+      </c>
+      <c r="W228" s="79" t="s">
+        <v>4568</v>
+      </c>
+      <c r="Y228" s="79" t="s">
+        <v>2548</v>
       </c>
     </row>
     <row r="229" spans="1:47" ht="22.5" customHeight="1">
@@ -53304,25 +53854,25 @@
         <v>4127</v>
       </c>
       <c r="G234" s="76" t="s">
-        <v>4411</v>
+        <v>4409</v>
       </c>
       <c r="H234" s="13" t="s">
         <v>2633</v>
       </c>
       <c r="I234" s="13" t="s">
-        <v>4412</v>
+        <v>4410</v>
       </c>
       <c r="K234" s="79" t="s">
+        <v>4405</v>
+      </c>
+      <c r="L234" s="79" t="s">
         <v>4407</v>
       </c>
-      <c r="L234" s="79" t="s">
-        <v>4409</v>
-      </c>
       <c r="M234" s="79" t="s">
+        <v>4406</v>
+      </c>
+      <c r="N234" s="79" t="s">
         <v>4408</v>
-      </c>
-      <c r="N234" s="79" t="s">
-        <v>4410</v>
       </c>
     </row>
     <row r="235" spans="1:47" ht="22.5" customHeight="1">
@@ -53346,44 +53896,44 @@
         <v>4127</v>
       </c>
       <c r="G235" s="76" t="s">
-        <v>4405</v>
+        <v>4403</v>
       </c>
       <c r="H235" s="13" t="s">
         <v>2633</v>
       </c>
       <c r="I235" s="13" t="s">
-        <v>4406</v>
+        <v>4404</v>
       </c>
       <c r="K235" s="75" t="s">
-        <v>4394</v>
+        <v>4392</v>
       </c>
       <c r="L235" s="76" t="s">
         <v>2648</v>
       </c>
       <c r="M235" s="79" t="s">
+        <v>4393</v>
+      </c>
+      <c r="O235" s="79" t="s">
+        <v>4394</v>
+      </c>
+      <c r="Q235" s="79" t="s">
         <v>4395</v>
       </c>
-      <c r="O235" s="79" t="s">
+      <c r="S235" s="79" t="s">
         <v>4396</v>
       </c>
-      <c r="Q235" s="79" t="s">
+      <c r="U235" s="79" t="s">
+        <v>4394</v>
+      </c>
+      <c r="W235" s="79" t="s">
         <v>4397</v>
-      </c>
-      <c r="S235" s="79" t="s">
-        <v>4398</v>
-      </c>
-      <c r="U235" s="79" t="s">
-        <v>4396</v>
-      </c>
-      <c r="W235" s="79" t="s">
-        <v>4399</v>
       </c>
       <c r="Y235" s="99" t="s">
         <v>2301</v>
       </c>
       <c r="Z235" s="99"/>
       <c r="AA235" s="99" t="s">
-        <v>4400</v>
+        <v>4398</v>
       </c>
       <c r="AC235" s="79" t="s">
         <v>2300</v>
@@ -53404,16 +53954,16 @@
         <v>1822</v>
       </c>
       <c r="AO235" s="79" t="s">
+        <v>4399</v>
+      </c>
+      <c r="AQ235" s="79" t="s">
+        <v>4400</v>
+      </c>
+      <c r="AS235" s="79" t="s">
         <v>4401</v>
       </c>
-      <c r="AQ235" s="79" t="s">
+      <c r="AU235" s="79" t="s">
         <v>4402</v>
-      </c>
-      <c r="AS235" s="79" t="s">
-        <v>4403</v>
-      </c>
-      <c r="AU235" s="79" t="s">
-        <v>4404</v>
       </c>
     </row>
     <row r="236" spans="1:47" ht="22.5" customHeight="1">
@@ -53433,17 +53983,27 @@
         <f>IF(games!I236&lt;&gt;"", games!I236, "")</f>
         <v>還在等《七騎士 Re：BIRTH》的官方公告？醒醒吧，真正的福利都在我們這裡。我們的兌換碼和禮包碼，讓你不用看臉，直接把稀有道具帶回家。想要快速安全地變強？我們的代儲值服務讓你省去繁瑣步驟，輕鬆稱霸全場。別再當那個被虐的弱雞了，加入我們的行列，讓那些對手看看什麼叫做「資源碾壓」。這遊戲的戰略再怎麼厲害，也比不過別人用錢堆出來的戰力。別再說什麼「佛系」了，真正的佛系是資源多到用不完，而不是窮到只剩雙手合十。</v>
       </c>
-      <c r="F236" s="75" t="s">
-        <v>2648</v>
+      <c r="F236" s="100" t="s">
+        <v>4499</v>
       </c>
       <c r="G236" s="76" t="s">
-        <v>2648</v>
-      </c>
-      <c r="K236" s="75" t="s">
-        <v>2648</v>
-      </c>
-      <c r="L236" s="76" t="s">
-        <v>2648</v>
+        <v>4500</v>
+      </c>
+      <c r="K236" s="103" t="s">
+        <v>4501</v>
+      </c>
+      <c r="L236" s="76"/>
+      <c r="M236" s="103" t="s">
+        <v>4502</v>
+      </c>
+      <c r="O236" s="103" t="s">
+        <v>4503</v>
+      </c>
+      <c r="Q236" s="103" t="s">
+        <v>4504</v>
+      </c>
+      <c r="S236" s="103" t="s">
+        <v>4505</v>
       </c>
     </row>
     <row r="237" spans="1:47" ht="22.5" customHeight="1">
@@ -53554,37 +54114,37 @@
         <v>還在為找不到兌換碼煩惱嗎？《龍息：神寂》這款MMORPG手遊，為你提供一個廣闊的魔幻世界，讓你沉浸在史詩級的冒險中。你將扮演天選之人，與夥伴們一起對抗邪惡的龍族，拯救瀕臨毀滅的王國。遊戲提供了多樣的職業選擇、華麗的技能特效和豐富的副本挑戰，無論是喜歡PVE的劇情黨，還是熱衷PVP的競技玩家，都能在這裡找到屬於自己的樂趣。你還在等什麼？趕快找尋你的兌換碼、禮包碼，用最快速安全的方式完成代儲值，輕鬆變強，加入這場冒險，成為傳說中的屠龍英雄吧！</v>
       </c>
       <c r="F240" s="34" t="s">
-        <v>4446</v>
+        <v>4444</v>
       </c>
       <c r="G240" s="13" t="s">
-        <v>4447</v>
+        <v>4445</v>
       </c>
       <c r="H240" s="13" t="s">
         <v>2633</v>
       </c>
       <c r="I240" s="13" t="s">
-        <v>4406</v>
+        <v>4404</v>
       </c>
       <c r="K240" s="17" t="s">
+        <v>4439</v>
+      </c>
+      <c r="L240" s="13" t="s">
         <v>4441</v>
       </c>
-      <c r="L240" s="13" t="s">
+      <c r="M240" s="18" t="s">
+        <v>4440</v>
+      </c>
+      <c r="N240" s="13" t="s">
+        <v>4441</v>
+      </c>
+      <c r="O240" s="18" t="s">
+        <v>4442</v>
+      </c>
+      <c r="P240" s="13" t="s">
         <v>4443</v>
       </c>
-      <c r="M240" s="18" t="s">
-        <v>4442</v>
-      </c>
-      <c r="N240" s="13" t="s">
-        <v>4443</v>
-      </c>
-      <c r="O240" s="18" t="s">
-        <v>4444</v>
-      </c>
-      <c r="P240" s="13" t="s">
-        <v>4445</v>
-      </c>
-    </row>
-    <row r="241" spans="1:12" ht="22.5" customHeight="1">
+    </row>
+    <row r="241" spans="1:16" ht="22.5" customHeight="1">
       <c r="A241" s="13" t="str">
         <f>IF(games!A241="", "", games!A241)</f>
         <v>玩具對決</v>
@@ -53607,14 +54167,14 @@
       <c r="G241" s="76" t="s">
         <v>2648</v>
       </c>
-      <c r="K241" s="75" t="s">
-        <v>2648</v>
-      </c>
-      <c r="L241" s="76" t="s">
-        <v>2648</v>
-      </c>
-    </row>
-    <row r="242" spans="1:12" ht="22.5" customHeight="1">
+      <c r="K241" s="17" t="s">
+        <v>4573</v>
+      </c>
+      <c r="L241" s="13" t="s">
+        <v>4562</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16" ht="22.5" customHeight="1">
       <c r="A242" s="13" t="str">
         <f>IF(games!A242="", "", games!A242)</f>
         <v>幸福都市：市長模擬器</v>
@@ -53644,7 +54204,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="22.5" customHeight="1">
+    <row r="243" spans="1:16" ht="22.5" customHeight="1">
       <c r="A243" s="13" t="str">
         <f>IF(games!A243="", "", games!A243)</f>
         <v>黑道傳奇</v>
@@ -53674,7 +54234,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="22.5" customHeight="1">
+    <row r="244" spans="1:16" ht="22.5" customHeight="1">
       <c r="A244" s="13" t="str">
         <f>IF(games!A244="", "", games!A244)</f>
         <v>The kingdom：medieval tales</v>
@@ -53704,79 +54264,151 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="245" spans="1:12" ht="22.5" customHeight="1">
+    <row r="245" spans="1:16" ht="22.5" customHeight="1">
       <c r="A245" s="13" t="str">
         <f>IF(games!A245="", "", games!A245)</f>
-        <v/>
+        <v>七龍珠激震小隊</v>
       </c>
       <c r="C245" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/七龍珠激震小隊-禮包碼.jpg</v>
       </c>
       <c r="D245" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/七龍珠激震小隊.html</v>
       </c>
       <c r="E245" s="14" t="str">
         <f>IF(games!I245&lt;&gt;"", games!I245, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="246" spans="1:12" ht="22.5" customHeight="1">
+        <v>終於等到這款由萬代南夢宮娛樂開發的《七龍珠 激震小隊》！這是一款全新的動作 RPG，讓你能體驗原作經典故事，並與悟空、達爾等超人氣角色並肩作戰！遊戲主打爽快又華麗的戰鬥體驗，玩家可以自由組隊，施展各種經典招式，還能享受震撼力十足的「七龍珠」宇宙冒險。遊戲內建多種模式，包括PVP對戰、協力共鬥等，讓你可以和朋友一同挑戰強敵。別忘了關注官方社群，第一時間獲取兌換碼及禮包碼，讓你開局就贏在起跑線！此外，如果你想快速提升戰力，也能透過快速安全的代儲值服務，輕鬆擴大你的英雄陣容！</v>
+      </c>
+      <c r="F245" s="34" t="s">
+        <v>4571</v>
+      </c>
+      <c r="G245" s="13" t="s">
+        <v>4572</v>
+      </c>
+      <c r="K245" s="17" t="s">
+        <v>4573</v>
+      </c>
+      <c r="L245" s="13" t="s">
+        <v>4562</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16" ht="22.5" customHeight="1">
       <c r="A246" s="13" t="str">
         <f>IF(games!A246="", "", games!A246)</f>
-        <v/>
+        <v>Grave Strikers</v>
       </c>
       <c r="C246" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/Grave Strikers-禮包碼.jpg</v>
       </c>
       <c r="D246" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Grave Strikers.html</v>
       </c>
       <c r="E246" s="14" t="str">
         <f>IF(games!I246&lt;&gt;"", games!I246, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="1:12" ht="22.5" customHeight="1">
+        <v>《Grave Strikers》是一款視覺風格獨特的戰術 RPG 手遊，玩家將扮演指揮官，組建一支由「靈魂」組成的強力隊伍，在這片被黑暗侵蝕的大陸上展開冒險！遊戲融合了策略布陣與即時戰鬥的元素，每一位靈魂都擁有專屬的技能與故事。透過不斷提升隊伍的實力，解鎖更多新角色，並在充滿挑戰的地下城中證明自己。關注官方社群，不錯過任何兌換碼與禮包碼的發送，讓你的冒險之路更加順暢！想要快速集結更強大的靈魂，代儲值服務是個快速安全的好選擇，讓你輕鬆面對每一個難關！</v>
+      </c>
+      <c r="F246" s="17" t="s">
+        <v>4573</v>
+      </c>
+      <c r="G246" s="13" t="s">
+        <v>4562</v>
+      </c>
+      <c r="K246" s="17" t="s">
+        <v>4573</v>
+      </c>
+      <c r="L246" s="13" t="s">
+        <v>4562</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" ht="22.5" customHeight="1">
       <c r="A247" s="13" t="str">
         <f>IF(games!A247="", "", games!A247)</f>
-        <v/>
+        <v>Stellar Sanctuary</v>
       </c>
       <c r="C247" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/Stellar Sanctuary-禮包碼.jpg</v>
       </c>
       <c r="D247" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Stellar Sanctuary.html</v>
       </c>
       <c r="E247" s="14" t="str">
         <f>IF(games!I247&lt;&gt;"", games!I247, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="1:12" ht="22.5" customHeight="1">
+        <v>《Stellar Sanctuary》是一款科幻題材的放置 RPG 手遊，遊戲背景設定在浩瀚的宇宙中，玩家將扮演一名宇宙探險家，招募來自不同星系的英雄，一同對抗邪惡的勢力！遊戲最大的特色就是「輕鬆放置，也能變強」，即使離線也能持續獲得豐富資源，讓你的英雄隊伍不斷成長。此外，遊戲內豐富的英雄養成系統和策略性戰鬥玩法，讓你不僅可以享受掛機的樂趣，也能深入體驗戰術搭配的醍醐味。想快速獲得稀有英雄或裝備嗎？別忘了領取官方發布的兌換碼與禮包碼，或是選擇快速安全的代儲值服務，加速你的宇宙探索旅程！</v>
+      </c>
+      <c r="F247" s="34" t="s">
+        <v>4563</v>
+      </c>
+      <c r="G247" s="13" t="s">
+        <v>4564</v>
+      </c>
+      <c r="H247" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I247" s="13" t="s">
+        <v>4404</v>
+      </c>
+      <c r="K247" s="17" t="s">
+        <v>4573</v>
+      </c>
+      <c r="L247" s="13" t="s">
+        <v>4562</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" ht="22.5" customHeight="1">
       <c r="A248" s="13" t="str">
         <f>IF(games!A248="", "", games!A248)</f>
-        <v/>
+        <v>古惑仔：風雲再起</v>
       </c>
       <c r="C248" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/古惑仔：風雲再起-禮包碼.jpg</v>
       </c>
       <c r="D248" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/古惑仔：風雲再起.html</v>
       </c>
       <c r="E248" s="14" t="str">
         <f>IF(games!I248&lt;&gt;"", games!I248, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="249" spans="1:12" ht="22.5" customHeight="1">
+        <v>經典 IP 手遊《古惑仔：風雲再起》正式登場！遊戲以熱血沸騰的「古惑仔」世界為背景，忠實還原了電影中的經典場景和人物。玩家將能親身扮演陳浩南、山雞等傳奇人物，在銅鑼灣街頭展開一場場江湖廝殺，體驗兄弟情義與權力鬥爭的熱血故事。遊戲主打幫派戰鬥與策略養成，你可以招募小弟、壯大勢力，最終成為一方霸主。為了在江湖中站穩腳跟，別忘了領取官方提供的兌換碼和禮包碼，讓你快速提升戰力！需要更多資源來稱霸一方？快速安全的代儲值服務是你的最佳選擇，讓你輕鬆成為叱吒風雲的傳奇人物！</v>
+      </c>
+      <c r="F248" s="34" t="s">
+        <v>4565</v>
+      </c>
+      <c r="G248" s="13" t="s">
+        <v>4445</v>
+      </c>
+      <c r="H248" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I248" s="13" t="s">
+        <v>4404</v>
+      </c>
+      <c r="K248" s="17" t="s">
+        <v>1934</v>
+      </c>
+      <c r="L248" s="13" t="s">
+        <v>4549</v>
+      </c>
+      <c r="M248" s="18" t="s">
+        <v>4546</v>
+      </c>
+      <c r="N248" s="13" t="s">
+        <v>4550</v>
+      </c>
+      <c r="O248" s="18" t="s">
+        <v>4547</v>
+      </c>
+      <c r="P248" s="13" t="s">
+        <v>4548</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" ht="22.5" customHeight="1">
       <c r="A249" s="13" t="str">
         <f>IF(games!A249="", "", games!A249)</f>
         <v/>
@@ -53794,7 +54426,7 @@
         <v/>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="22.5" customHeight="1">
+    <row r="250" spans="1:16" ht="22.5" customHeight="1">
       <c r="A250" s="13" t="str">
         <f>IF(games!A250="", "", games!A250)</f>
         <v/>
@@ -53812,7 +54444,7 @@
         <v/>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="22.5" customHeight="1">
+    <row r="251" spans="1:16" ht="22.5" customHeight="1">
       <c r="C251" s="13" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -53826,7 +54458,7 @@
         <v/>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="22.5" customHeight="1">
+    <row r="252" spans="1:16" ht="22.5" customHeight="1">
       <c r="C252" s="13" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -53840,7 +54472,7 @@
         <v/>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="22.5" customHeight="1">
+    <row r="253" spans="1:16" ht="22.5" customHeight="1">
       <c r="C253" s="13" t="str">
         <f t="shared" ref="C253:C316" si="9">IF(A253="","", "giftcodesbanner/" &amp; A253 &amp; "-禮包碼.jpg")</f>
         <v/>
@@ -53854,7 +54486,7 @@
         <v/>
       </c>
     </row>
-    <row r="254" spans="1:12" ht="22.5" customHeight="1">
+    <row r="254" spans="1:16" ht="22.5" customHeight="1">
       <c r="C254" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -53868,7 +54500,7 @@
         <v/>
       </c>
     </row>
-    <row r="255" spans="1:12" ht="22.5" customHeight="1">
+    <row r="255" spans="1:16" ht="22.5" customHeight="1">
       <c r="C255" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -53878,7 +54510,7 @@
         <v/>
       </c>
     </row>
-    <row r="256" spans="1:12" ht="22.5" customHeight="1">
+    <row r="256" spans="1:16" ht="22.5" customHeight="1">
       <c r="C256" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55723,8 +56355,9 @@
   <hyperlinks>
     <hyperlink ref="G157" r:id="rId1"/>
     <hyperlink ref="F225" r:id="rId2"/>
+    <hyperlink ref="F236" r:id="rId3" display="https://ref.gamer.com.tw/redir.php?url=https%3A%2F%2Fcoupon.netmarble.com%2Ftskgb"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -17975,14 +17975,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>到上方網址輸入序號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>等待官方更新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>https://dbg-squadra.bn-ent.net/tw/serialcode</t>
-  </si>
-  <si>
-    <t>到上方網址輸入序號</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>等待官方更新</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -18411,7 +18412,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -18672,6 +18673,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -54168,7 +54170,7 @@
         <v>2648</v>
       </c>
       <c r="K241" s="17" t="s">
-        <v>4573</v>
+        <v>4572</v>
       </c>
       <c r="L241" s="13" t="s">
         <v>4562</v>
@@ -54281,14 +54283,14 @@
         <f>IF(games!I245&lt;&gt;"", games!I245, "")</f>
         <v>終於等到這款由萬代南夢宮娛樂開發的《七龍珠 激震小隊》！這是一款全新的動作 RPG，讓你能體驗原作經典故事，並與悟空、達爾等超人氣角色並肩作戰！遊戲主打爽快又華麗的戰鬥體驗，玩家可以自由組隊，施展各種經典招式，還能享受震撼力十足的「七龍珠」宇宙冒險。遊戲內建多種模式，包括PVP對戰、協力共鬥等，讓你可以和朋友一同挑戰強敵。別忘了關注官方社群，第一時間獲取兌換碼及禮包碼，讓你開局就贏在起跑線！此外，如果你想快速提升戰力，也能透過快速安全的代儲值服務，輕鬆擴大你的英雄陣容！</v>
       </c>
-      <c r="F245" s="34" t="s">
+      <c r="F245" s="104" t="s">
+        <v>4573</v>
+      </c>
+      <c r="G245" s="13" t="s">
         <v>4571</v>
       </c>
-      <c r="G245" s="13" t="s">
+      <c r="K245" s="17" t="s">
         <v>4572</v>
-      </c>
-      <c r="K245" s="17" t="s">
-        <v>4573</v>
       </c>
       <c r="L245" s="13" t="s">
         <v>4562</v>
@@ -54312,13 +54314,13 @@
         <v>《Grave Strikers》是一款視覺風格獨特的戰術 RPG 手遊，玩家將扮演指揮官，組建一支由「靈魂」組成的強力隊伍，在這片被黑暗侵蝕的大陸上展開冒險！遊戲融合了策略布陣與即時戰鬥的元素，每一位靈魂都擁有專屬的技能與故事。透過不斷提升隊伍的實力，解鎖更多新角色，並在充滿挑戰的地下城中證明自己。關注官方社群，不錯過任何兌換碼與禮包碼的發送，讓你的冒險之路更加順暢！想要快速集結更強大的靈魂，代儲值服務是個快速安全的好選擇，讓你輕鬆面對每一個難關！</v>
       </c>
       <c r="F246" s="17" t="s">
-        <v>4573</v>
+        <v>4572</v>
       </c>
       <c r="G246" s="13" t="s">
         <v>4562</v>
       </c>
       <c r="K246" s="17" t="s">
-        <v>4573</v>
+        <v>4572</v>
       </c>
       <c r="L246" s="13" t="s">
         <v>4562</v>
@@ -54354,7 +54356,7 @@
         <v>4404</v>
       </c>
       <c r="K247" s="17" t="s">
-        <v>4573</v>
+        <v>4572</v>
       </c>
       <c r="L247" s="13" t="s">
         <v>4562</v>
@@ -56356,8 +56358,9 @@
     <hyperlink ref="G157" r:id="rId1"/>
     <hyperlink ref="F225" r:id="rId2"/>
     <hyperlink ref="F236" r:id="rId3" display="https://ref.gamer.com.tw/redir.php?url=https%3A%2F%2Fcoupon.netmarble.com%2Ftskgb"/>
+    <hyperlink ref="F245" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6773" uniqueCount="4574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6787" uniqueCount="4587">
   <si>
     <t>Facebook</t>
   </si>
@@ -17984,6 +17984,58 @@
   </si>
   <si>
     <t>https://dbg-squadra.bn-ent.net/tw/serialcode</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuanYu777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuanYu3333</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>yjsg777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TK3333</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>無雙戰神</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>忠義武聖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>常勝孤膽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>七進七出</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ssr888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sp999</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>death444</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBu999</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>yjsgssqy</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -54025,17 +54077,60 @@
         <f>IF(games!I237&lt;&gt;"", games!I237, "")</f>
         <v>在《異界三國：死神契約》的世界裡，你還在辛辛苦苦推圖？別鬧了，你的對手早已透過我們的兌換碼和禮包碼，把戰力堆到你望塵莫及。我們的代儲值服務，保證快速又安全，讓你一秒變身課長，輕鬆超車，將那些還在農資源的玩家遠遠甩在身後。別再相信什麼「用愛發電」了，有課金才是王道。這款遊戲強調策略，但當你擁有無與倫比的資源時，任何策略都將變得簡單。想成為排行榜上的傳奇？這就是你的捷徑，省下你寶貴的睡眠時間，告別被虐的苦日子。</v>
       </c>
-      <c r="F237" s="75" t="s">
-        <v>2648</v>
+      <c r="F237" s="34" t="s">
+        <v>4127</v>
       </c>
       <c r="G237" s="76" t="s">
-        <v>2648</v>
+        <v>4403</v>
+      </c>
+      <c r="H237" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I237" s="13" t="s">
+        <v>4404</v>
       </c>
       <c r="K237" s="75" t="s">
-        <v>2648</v>
-      </c>
-      <c r="L237" s="76" t="s">
-        <v>2648</v>
+        <v>3340</v>
+      </c>
+      <c r="L237" s="76"/>
+      <c r="M237" s="18" t="s">
+        <v>4574</v>
+      </c>
+      <c r="O237" s="18" t="s">
+        <v>4575</v>
+      </c>
+      <c r="Q237" s="18" t="s">
+        <v>4576</v>
+      </c>
+      <c r="S237" s="13" t="s">
+        <v>4577</v>
+      </c>
+      <c r="U237" s="18" t="s">
+        <v>4578</v>
+      </c>
+      <c r="W237" s="18" t="s">
+        <v>4579</v>
+      </c>
+      <c r="Y237" s="18" t="s">
+        <v>4580</v>
+      </c>
+      <c r="AA237" s="18" t="s">
+        <v>4581</v>
+      </c>
+      <c r="AC237" s="18" t="s">
+        <v>4582</v>
+      </c>
+      <c r="AE237" s="18" t="s">
+        <v>4583</v>
+      </c>
+      <c r="AG237" s="18" t="s">
+        <v>4584</v>
+      </c>
+      <c r="AI237" s="18" t="s">
+        <v>4585</v>
+      </c>
+      <c r="AK237" s="18" t="s">
+        <v>4586</v>
       </c>
     </row>
     <row r="238" spans="1:47" ht="22.5" customHeight="1">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6787" uniqueCount="4587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6788" uniqueCount="4591">
   <si>
     <t>Facebook</t>
   </si>
@@ -18038,12 +18038,26 @@
     <t>yjsgssqy</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>aomage</t>
+  </si>
+  <si>
+    <t>CTYJG7</t>
+  </si>
+  <si>
+    <t>遊戲內選左上角頭像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點系統設定之後典禮包兌換</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -18218,6 +18232,21 @@
       <color rgb="FF333333"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Inherit"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -18464,7 +18493,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -18726,6 +18755,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -53961,9 +53994,7 @@
       <c r="K235" s="75" t="s">
         <v>4392</v>
       </c>
-      <c r="L235" s="76" t="s">
-        <v>2648</v>
-      </c>
+      <c r="L235" s="76"/>
       <c r="M235" s="79" t="s">
         <v>4393</v>
       </c>
@@ -54150,18 +54181,22 @@
         <f>IF(games!I238&lt;&gt;"", games!I238, "")</f>
         <v>別再當《魔法師之徒》裡的菜鳥了，想變強？先學會用我們的兌換碼和禮包碼。不用花時間刷刷刷，稀有道具直接入袋，讓你的魔法比別人的更強大。我們的代儲值服務，讓你快速又安全地擁有海量資源，將那些還在為金幣煩惱的玩家遠遠拋在腦後。別再說自己是非洲人了，是你不懂方法，懂嗎？當你擁有無限的資源時，任何魔法都將變得簡單。這款遊戲強調策略，但當你擁有無與倫比的資源時，任何策略都將變得簡單。想成為排行榜上的傳奇？這就是你的捷徑。</v>
       </c>
-      <c r="F238" s="75" t="s">
-        <v>2648</v>
+      <c r="F238" s="34" t="s">
+        <v>4127</v>
       </c>
       <c r="G238" s="76" t="s">
-        <v>2648</v>
-      </c>
-      <c r="K238" s="75" t="s">
-        <v>2648</v>
-      </c>
-      <c r="L238" s="76" t="s">
-        <v>2648</v>
-      </c>
+        <v>4403</v>
+      </c>
+      <c r="H238" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I238" s="13" t="s">
+        <v>4404</v>
+      </c>
+      <c r="K238" s="105" t="s">
+        <v>4587</v>
+      </c>
+      <c r="L238" s="76"/>
     </row>
     <row r="239" spans="1:47" ht="22.5" customHeight="1">
       <c r="A239" s="13" t="str">
@@ -54181,17 +54216,21 @@
         <v>在《三國魂將傳》中，你還在努力招募將領？別傻了，真正的強者都用兌換碼和禮包碼直接領取資源了。我們的代儲值服務，快速又安全，讓你輕鬆超越那些還在慢慢肝的玩家。別再說什麼「肝帝」了，時間寶貴，用我們的方式，把時間省下來享受遊戲，而不是被遊戲玩。想稱霸三國，就從這裡開始。這款遊戲強調策略，但當你擁有無與倫比的資源時，任何策略都將變得簡單。想成為排行榜上的傳奇？這就是你的捷徑。</v>
       </c>
       <c r="F239" s="75" t="s">
-        <v>2648</v>
+        <v>4589</v>
       </c>
       <c r="G239" s="76" t="s">
-        <v>2648</v>
-      </c>
-      <c r="K239" s="75" t="s">
-        <v>2648</v>
-      </c>
-      <c r="L239" s="76" t="s">
-        <v>2648</v>
-      </c>
+        <v>4590</v>
+      </c>
+      <c r="H239" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I239" s="13" t="s">
+        <v>4404</v>
+      </c>
+      <c r="K239" s="106" t="s">
+        <v>4588</v>
+      </c>
+      <c r="L239" s="76"/>
     </row>
     <row r="240" spans="1:47" ht="22.5" customHeight="1">
       <c r="A240" s="13" t="str">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6788" uniqueCount="4591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6867" uniqueCount="4644">
   <si>
     <t>Facebook</t>
   </si>
@@ -18051,6 +18051,192 @@
   <si>
     <t>點系統設定之後典禮包兌換</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>女神秘令</t>
+  </si>
+  <si>
+    <t>Torerowa</t>
+  </si>
+  <si>
+    <t>Ricochet Squad</t>
+  </si>
+  <si>
+    <t>https://goddessorder.kakaogames.com/zh-TW/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/GoddessOrder/</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E5%A5%B3%E7%A5%9E%E7%A7%98%E4%BB%A4-%E7%86%B1%E8%A1%80%E6%A9%AB%E5%90%91%E5%8B%95%E4%BD%9C%E5%83%8F%E7%B4%A0rpg/id6749934240?fbclid=IwY2xjawM_MNRleHRuA2FlbQIxMABicmlkETE0MVh3bk5EMjRTY05mMkpLAR4JWZ0pkLBUCyPDaqN1qsB6NRDS1iBuYF6DIQaA8szbfRf3HLasRp5gonU8_Q_aem_J5Nnn4HsKqHU-WYYlNT6Ew</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.kakaogames.gdod&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.asobimo.torerowa&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/us/app/torerowa/id6474421736</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://x.com/torerowa_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://en.torerowa.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=nice.ricochet&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/PlayRicochet/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/pl/app/ricochet-squad-pvp-shooter/id6743486517</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://niceplans.studio/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法村物語</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E9%AD%94%E6%B3%95%E6%9D%91%E7%89%A9%E8%AA%9E/id6748180418</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.magic.village.gp&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/magicvillage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《女神秘令》是一款以西方魔幻為題材的卡牌策略 RPG 手遊，遊戲主打輕鬆護肝的放置玩法，讓玩家在忙碌之餘也能輕鬆享受成長樂趣。遊戲內建豐富的女神角色，每位都有獨特的技能與華麗特效，玩家可自由搭配陣容，展開燒腦的策略對決。除了主線劇情外，還有多種副本、公會戰與競技場等多元玩法，搭配豐厚福利與兌換碼，讓新手也能快速上手。想輕鬆蒐集心儀女神、無壓力變強嗎？現在就加入《女神秘令》，透過代儲值服務可享快速安全的優惠，還有專屬禮包碼等你來領取！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《Torerowa》是一款奇幻風格的 MMORPG，以精緻的日系畫風與Q萌角色聞名。玩家將在廣闊的世界中冒險，體驗豐富的任務與劇情。遊戲提供多元職業選擇，每種職業都有獨特的技能樹與玩法，無論是PVE還是PVP，都能找到屬於自己的樂趣。此外，遊戲內還有釣魚、料理、採集等多樣生活技能，讓冒險旅程更加豐富有趣。想要輕鬆遊玩、享受自由探索的樂趣嗎？使用兌換碼與禮包碼即可獲得豐厚資源，選擇快速安全的代儲值服務，讓你輕鬆暢遊這片奇幻大陸！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《Ricochet Squad》是一款結合射擊與彈射玩法的益智休閒手遊。遊戲畫面風格清新可愛，操作簡單易懂，玩家只需透過彈射角色，擊敗地圖上的敵人即可。關卡設計充滿巧思，需要玩家動腦思考，利用地形與彈射角度來完成挑戰。除了單人闖關模式，遊戲也支援多人PVP對戰，與朋友一較高下。遊戲提供多樣角色與造型，滿足玩家蒐集慾望。想在通勤或休息時間，來一場刺激又有趣的腦力激盪嗎？輸入兌換碼與禮包碼即可領取好禮，選擇快速安全的代儲值，讓你輕鬆獲得遊戲內稀有道具！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《魔法村物語》是一款日系像素風格的經營模擬 RPG 手遊。玩家將扮演一位年輕的村長，在充滿魔法的奇幻世界中，經營並發展自己的村莊。遊戲融合了冒險、建設、養成與社交等多元玩法，玩家可以建造各種設施、招募冒險者、探索未知區域，並與其他玩家交流互動。遊戲的像素畫面精美細膩，搭配輕鬆療癒的BGM，帶給玩家獨特的遊玩體驗。想要打造屬於自己的夢幻村莊嗎？記得使用兌換碼與禮包碼來獲得豐厚資源，透過快速安全的代儲值服務，加速你的村莊發展！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>𝐓𝐘𝐒𝐐𝐔𝐀𝐃𝟐𝟓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>50000金幣+1000裝飾塵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入遊戲內的「社交選單」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在選單底部找到兌換碼輸入欄位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>全球上市後將發送「感謝禮物」</t>
+  </si>
+  <si>
+    <t>寶石禮包G</t>
+  </si>
+  <si>
+    <t>寶石禮包F</t>
+  </si>
+  <si>
+    <t>寶石禮包E</t>
+  </si>
+  <si>
+    <t>寶石禮包D</t>
+  </si>
+  <si>
+    <t>寶石禮包C</t>
+  </si>
+  <si>
+    <t>寶石禮包B</t>
+  </si>
+  <si>
+    <t>寶石禮包A</t>
+  </si>
+  <si>
+    <t>Mega鑽石禮包</t>
+  </si>
+  <si>
+    <t>Large鑽石禮包</t>
+  </si>
+  <si>
+    <t>Big鑽石禮包</t>
+  </si>
+  <si>
+    <t>Standrad鑽石禮包</t>
+  </si>
+  <si>
+    <t>Small鑽石禮包</t>
+  </si>
+  <si>
+    <t>Tiny鑽石禮包</t>
+  </si>
+  <si>
+    <t>遊戲內點左上「頭像」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>彈出選單右下方點「虛寶碼」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>少量金幣2小時*5+少量經驗2小時*5+突破合濟*100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃金招募令*2+鑽石*200</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒼芎套裝</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*300+黃金招募令*5+星之晶球*2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>花園特權</t>
+  </si>
+  <si>
+    <t>作戰/星章特權</t>
+  </si>
+  <si>
+    <t>訂閱特權</t>
   </si>
 </sst>
 </file>
@@ -35717,53 +35903,311 @@
         <v>25</v>
       </c>
     </row>
-    <row r="249" spans="1:29" ht="22.5" customHeight="1">
+    <row r="249" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A249" s="80" t="s">
+        <v>4591</v>
+      </c>
+      <c r="C249" s="47" t="s">
+        <v>4595</v>
+      </c>
+      <c r="D249" s="48" t="s">
+        <v>4594</v>
+      </c>
+      <c r="E249" s="48" t="s">
+        <v>4596</v>
+      </c>
       <c r="F249" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f t="shared" ref="F249:F253" si="8">IF(A249="","", "https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/" &amp; IF(ISNUMBER(LEFT(A249,1)*1), "game-", "") &amp; A249 &amp; ".html")</f>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/女神秘令.html</v>
+      </c>
+      <c r="G249" s="4" t="s">
+        <v>4597</v>
       </c>
       <c r="H249" s="48" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="1:29" ht="22.5" customHeight="1">
+        <f t="shared" ref="H249:H253" si="9">IF(A249="","", "https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/" &amp; IF(ISNUMBER(LEFT(A249,1)*1), "game-", "") &amp; A249 &amp; ".html")</f>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/女神秘令.html</v>
+      </c>
+      <c r="I249" s="49" t="s">
+        <v>4610</v>
+      </c>
+      <c r="J249" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="K249" s="80">
+        <v>2286</v>
+      </c>
+      <c r="L249" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="M249" s="80">
+        <v>1139</v>
+      </c>
+      <c r="N249" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="O249" s="80">
+        <v>757</v>
+      </c>
+      <c r="P249" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q249" s="80">
+        <v>519</v>
+      </c>
+      <c r="R249" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="S249" s="80">
+        <v>380</v>
+      </c>
+      <c r="T249" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="U249" s="80">
+        <v>256</v>
+      </c>
+      <c r="V249" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="W249" s="80">
+        <v>140</v>
+      </c>
+      <c r="X249" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="Y249" s="80">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="250" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A250" s="80" t="s">
+        <v>4592</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>4600</v>
+      </c>
+      <c r="D250" s="4" t="s">
+        <v>4601</v>
+      </c>
+      <c r="E250" s="4" t="s">
+        <v>4599</v>
+      </c>
       <c r="F250" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f t="shared" si="8"/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Torerowa.html</v>
+      </c>
+      <c r="G250" s="48" t="s">
+        <v>4598</v>
       </c>
       <c r="H250" s="48" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="1:29" ht="22.5" customHeight="1">
+        <f t="shared" si="9"/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Torerowa.html</v>
+      </c>
+      <c r="I250" s="49" t="s">
+        <v>4611</v>
+      </c>
+      <c r="J250" s="1" t="s">
+        <v>4622</v>
+      </c>
+      <c r="K250" s="80">
+        <v>2293</v>
+      </c>
+      <c r="L250" s="1" t="s">
+        <v>4623</v>
+      </c>
+      <c r="M250" s="80">
+        <v>1529</v>
+      </c>
+      <c r="N250" s="1" t="s">
+        <v>4624</v>
+      </c>
+      <c r="O250" s="80">
+        <v>764</v>
+      </c>
+      <c r="P250" s="1" t="s">
+        <v>4625</v>
+      </c>
+      <c r="Q250" s="80">
+        <v>465</v>
+      </c>
+      <c r="R250" s="1" t="s">
+        <v>4626</v>
+      </c>
+      <c r="S250" s="80">
+        <v>165</v>
+      </c>
+      <c r="T250" s="1" t="s">
+        <v>4627</v>
+      </c>
+      <c r="U250" s="80">
+        <v>124</v>
+      </c>
+      <c r="V250" s="1" t="s">
+        <v>4628</v>
+      </c>
+      <c r="W250" s="80">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="251" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A251" s="80" t="s">
+        <v>4593</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>4603</v>
+      </c>
+      <c r="D251" s="4" t="s">
+        <v>4605</v>
+      </c>
+      <c r="E251" s="4" t="s">
+        <v>4604</v>
+      </c>
       <c r="F251" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f t="shared" si="8"/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Ricochet Squad.html</v>
+      </c>
+      <c r="G251" s="4" t="s">
+        <v>4602</v>
       </c>
       <c r="H251" s="48" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="252" spans="1:29" ht="22.5" customHeight="1">
+        <f t="shared" si="9"/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Ricochet Squad.html</v>
+      </c>
+      <c r="I251" s="49" t="s">
+        <v>4612</v>
+      </c>
+      <c r="J251" s="1" t="s">
+        <v>4629</v>
+      </c>
+      <c r="K251" s="80">
+        <v>2286</v>
+      </c>
+      <c r="L251" s="1" t="s">
+        <v>4630</v>
+      </c>
+      <c r="M251" s="80">
+        <v>1139</v>
+      </c>
+      <c r="N251" s="1" t="s">
+        <v>4631</v>
+      </c>
+      <c r="O251" s="80">
+        <v>535</v>
+      </c>
+      <c r="P251" s="1" t="s">
+        <v>4632</v>
+      </c>
+      <c r="Q251" s="80">
+        <v>248</v>
+      </c>
+      <c r="R251" s="1" t="s">
+        <v>4633</v>
+      </c>
+      <c r="S251" s="80">
+        <v>124</v>
+      </c>
+      <c r="T251" s="1" t="s">
+        <v>4634</v>
+      </c>
+      <c r="U251" s="80">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="252" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A252" s="3" t="s">
+        <v>4606</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>4609</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>4609</v>
+      </c>
+      <c r="E252" s="48" t="s">
+        <v>4607</v>
+      </c>
       <c r="F252" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f t="shared" si="8"/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/魔法村物語.html</v>
+      </c>
+      <c r="G252" s="48" t="s">
+        <v>4608</v>
       </c>
       <c r="H252" s="48" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <f t="shared" si="9"/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/魔法村物語.html</v>
+      </c>
+      <c r="I252" s="49" t="s">
+        <v>4613</v>
+      </c>
+      <c r="J252" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K252" s="80">
+        <v>2286</v>
+      </c>
+      <c r="L252" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M252" s="80">
+        <v>1139</v>
+      </c>
+      <c r="N252" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O252" s="80">
+        <v>757</v>
+      </c>
+      <c r="P252" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q252" s="80">
+        <v>519</v>
+      </c>
+      <c r="R252" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="S252" s="80">
+        <v>248</v>
+      </c>
+      <c r="T252" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="U252" s="80">
+        <v>124</v>
+      </c>
+      <c r="V252" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W252" s="80">
+        <v>25</v>
+      </c>
+      <c r="X252" s="1" t="s">
+        <v>4641</v>
+      </c>
+      <c r="Y252" s="80">
+        <v>535</v>
+      </c>
+      <c r="Z252" s="1" t="s">
+        <v>4642</v>
+      </c>
+      <c r="AA252" s="80">
+        <v>248</v>
+      </c>
+      <c r="AB252" s="1" t="s">
+        <v>4643</v>
+      </c>
+      <c r="AC252" s="80">
+        <v>124</v>
       </c>
     </row>
     <row r="253" spans="1:29" ht="22.5" customHeight="1">
       <c r="F253" s="48" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H253" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35819,3141 +36263,3141 @@
     </row>
     <row r="259" spans="6:8" ht="22.5" customHeight="1">
       <c r="F259" s="48" t="str">
-        <f t="shared" ref="F259:F269" si="8">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
+        <f t="shared" ref="F259:F269" si="10">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
         <v/>
       </c>
       <c r="H259" s="48" t="str">
-        <f t="shared" ref="H259:H287" si="9">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
+        <f t="shared" ref="H259:H287" si="11">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
         <v/>
       </c>
     </row>
     <row r="260" spans="6:8" ht="22.5" customHeight="1">
       <c r="F260" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="H260" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="261" spans="6:8" ht="22.5" customHeight="1">
       <c r="F261" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="H261" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="262" spans="6:8" ht="22.5" customHeight="1">
       <c r="F262" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="H262" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="263" spans="6:8" ht="22.5" customHeight="1">
       <c r="F263" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="H263" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="264" spans="6:8" ht="22.5" customHeight="1">
       <c r="F264" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="H264" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="265" spans="6:8" ht="22.5" customHeight="1">
       <c r="F265" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="H265" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="266" spans="6:8" ht="22.5" customHeight="1">
       <c r="F266" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="H266" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="267" spans="6:8" ht="22.5" customHeight="1">
       <c r="F267" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="H267" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="268" spans="6:8" ht="22.5" customHeight="1">
       <c r="F268" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="H268" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="269" spans="6:8" ht="22.5" customHeight="1">
       <c r="F269" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="H269" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="270" spans="6:8" ht="22.5" customHeight="1">
       <c r="F270" s="47" t="str">
-        <f t="shared" ref="F270:F316" si="10">IF(A270="", "", "gift-codes.html?game=" &amp; A270)</f>
+        <f t="shared" ref="F270:F316" si="12">IF(A270="", "", "gift-codes.html?game=" &amp; A270)</f>
         <v/>
       </c>
       <c r="H270" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="271" spans="6:8" ht="22.5" customHeight="1">
       <c r="F271" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H271" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="272" spans="6:8" ht="22.5" customHeight="1">
       <c r="F272" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H272" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="273" spans="6:8" ht="22.5" customHeight="1">
       <c r="F273" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H273" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="274" spans="6:8" ht="22.5" customHeight="1">
       <c r="F274" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H274" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="275" spans="6:8" ht="22.5" customHeight="1">
       <c r="F275" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H275" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="276" spans="6:8" ht="22.5" customHeight="1">
       <c r="F276" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H276" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="277" spans="6:8" ht="22.5" customHeight="1">
       <c r="F277" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H277" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="278" spans="6:8" ht="22.5" customHeight="1">
       <c r="F278" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H278" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="279" spans="6:8" ht="22.5" customHeight="1">
       <c r="F279" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H279" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="280" spans="6:8" ht="22.5" customHeight="1">
       <c r="F280" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H280" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="281" spans="6:8" ht="22.5" customHeight="1">
       <c r="F281" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H281" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="282" spans="6:8" ht="22.5" customHeight="1">
       <c r="F282" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H282" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="283" spans="6:8" ht="22.5" customHeight="1">
       <c r="F283" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H283" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="284" spans="6:8" ht="22.5" customHeight="1">
       <c r="F284" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H284" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="285" spans="6:8" ht="22.5" customHeight="1">
       <c r="F285" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H285" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="286" spans="6:8" ht="22.5" customHeight="1">
       <c r="F286" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H286" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="287" spans="6:8" ht="22.5" customHeight="1">
       <c r="F287" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H287" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="288" spans="6:8" ht="22.5" customHeight="1">
       <c r="F288" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H288" s="48" t="str">
-        <f t="shared" ref="H288:H316" si="11">IF(A288="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A288)</f>
+        <f t="shared" ref="H288:H316" si="13">IF(A288="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A288)</f>
         <v/>
       </c>
     </row>
     <row r="289" spans="6:8" ht="22.5" customHeight="1">
       <c r="F289" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H289" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="290" spans="6:8" ht="22.5" customHeight="1">
       <c r="F290" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H290" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="291" spans="6:8" ht="22.5" customHeight="1">
       <c r="F291" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H291" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="292" spans="6:8" ht="22.5" customHeight="1">
       <c r="F292" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H292" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="293" spans="6:8" ht="22.5" customHeight="1">
       <c r="F293" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H293" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="294" spans="6:8" ht="22.5" customHeight="1">
       <c r="F294" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H294" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="295" spans="6:8" ht="22.5" customHeight="1">
       <c r="F295" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H295" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="296" spans="6:8" ht="22.5" customHeight="1">
       <c r="F296" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H296" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="297" spans="6:8" ht="22.5" customHeight="1">
       <c r="F297" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H297" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="298" spans="6:8" ht="22.5" customHeight="1">
       <c r="F298" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H298" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="299" spans="6:8" ht="22.5" customHeight="1">
       <c r="F299" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H299" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="300" spans="6:8" ht="22.5" customHeight="1">
       <c r="F300" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H300" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="301" spans="6:8" ht="22.5" customHeight="1">
       <c r="F301" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H301" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="302" spans="6:8" ht="22.5" customHeight="1">
       <c r="F302" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H302" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="303" spans="6:8" ht="22.5" customHeight="1">
       <c r="F303" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H303" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="304" spans="6:8" ht="22.5" customHeight="1">
       <c r="F304" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H304" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="305" spans="6:8" ht="22.5" customHeight="1">
       <c r="F305" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H305" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="306" spans="6:8" ht="22.5" customHeight="1">
       <c r="F306" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H306" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="307" spans="6:8" ht="22.5" customHeight="1">
       <c r="F307" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H307" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="308" spans="6:8" ht="22.5" customHeight="1">
       <c r="F308" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H308" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="309" spans="6:8" ht="22.5" customHeight="1">
       <c r="F309" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H309" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="310" spans="6:8" ht="22.5" customHeight="1">
       <c r="F310" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H310" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="311" spans="6:8" ht="22.5" customHeight="1">
       <c r="F311" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H311" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="312" spans="6:8" ht="22.5" customHeight="1">
       <c r="F312" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H312" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="313" spans="6:8" ht="22.5" customHeight="1">
       <c r="F313" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H313" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="314" spans="6:8" ht="22.5" customHeight="1">
       <c r="F314" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H314" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="315" spans="6:8" ht="22.5" customHeight="1">
       <c r="F315" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H315" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="316" spans="6:8" ht="22.5" customHeight="1">
       <c r="F316" s="47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H316" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="317" spans="6:8" ht="22.5" customHeight="1">
       <c r="F317" s="47" t="str">
-        <f t="shared" ref="F317:F380" si="12">IF(A317="", "", "gift-codes.html?game=" &amp; A317)</f>
+        <f t="shared" ref="F317:F380" si="14">IF(A317="", "", "gift-codes.html?game=" &amp; A317)</f>
         <v/>
       </c>
       <c r="H317" s="48" t="str">
-        <f t="shared" ref="H317:H380" si="13">IF(A317="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A317)</f>
+        <f t="shared" ref="H317:H380" si="15">IF(A317="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A317)</f>
         <v/>
       </c>
     </row>
     <row r="318" spans="6:8" ht="22.5" customHeight="1">
       <c r="F318" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H318" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="319" spans="6:8" ht="22.5" customHeight="1">
       <c r="F319" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H319" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="320" spans="6:8" ht="22.5" customHeight="1">
       <c r="F320" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H320" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="321" spans="6:8" ht="22.5" customHeight="1">
       <c r="F321" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H321" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="322" spans="6:8" ht="22.5" customHeight="1">
       <c r="F322" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H322" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="323" spans="6:8" ht="22.5" customHeight="1">
       <c r="F323" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H323" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="324" spans="6:8" ht="22.5" customHeight="1">
       <c r="F324" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H324" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="325" spans="6:8" ht="22.5" customHeight="1">
       <c r="F325" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H325" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="326" spans="6:8" ht="22.5" customHeight="1">
       <c r="F326" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H326" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="327" spans="6:8" ht="22.5" customHeight="1">
       <c r="F327" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H327" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="328" spans="6:8" ht="22.5" customHeight="1">
       <c r="F328" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H328" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="329" spans="6:8" ht="22.5" customHeight="1">
       <c r="F329" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H329" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="330" spans="6:8" ht="22.5" customHeight="1">
       <c r="F330" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H330" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="331" spans="6:8" ht="22.5" customHeight="1">
       <c r="F331" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H331" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="332" spans="6:8" ht="22.5" customHeight="1">
       <c r="F332" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H332" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="333" spans="6:8" ht="22.5" customHeight="1">
       <c r="F333" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H333" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="334" spans="6:8" ht="22.5" customHeight="1">
       <c r="F334" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H334" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="335" spans="6:8" ht="22.5" customHeight="1">
       <c r="F335" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H335" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="336" spans="6:8" ht="22.5" customHeight="1">
       <c r="F336" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H336" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="337" spans="6:8" ht="22.5" customHeight="1">
       <c r="F337" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H337" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="338" spans="6:8" ht="22.5" customHeight="1">
       <c r="F338" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H338" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="339" spans="6:8" ht="22.5" customHeight="1">
       <c r="F339" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H339" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="340" spans="6:8" ht="22.5" customHeight="1">
       <c r="F340" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H340" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="341" spans="6:8" ht="22.5" customHeight="1">
       <c r="F341" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H341" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="342" spans="6:8" ht="22.5" customHeight="1">
       <c r="F342" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H342" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="343" spans="6:8" ht="22.5" customHeight="1">
       <c r="F343" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H343" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="344" spans="6:8" ht="22.5" customHeight="1">
       <c r="F344" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H344" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="345" spans="6:8" ht="22.5" customHeight="1">
       <c r="F345" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H345" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="346" spans="6:8" ht="22.5" customHeight="1">
       <c r="F346" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H346" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="347" spans="6:8" ht="22.5" customHeight="1">
       <c r="F347" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H347" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="348" spans="6:8" ht="22.5" customHeight="1">
       <c r="F348" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H348" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="349" spans="6:8" ht="22.5" customHeight="1">
       <c r="F349" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H349" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="350" spans="6:8" ht="22.5" customHeight="1">
       <c r="F350" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H350" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="351" spans="6:8" ht="22.5" customHeight="1">
       <c r="F351" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H351" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="352" spans="6:8" ht="22.5" customHeight="1">
       <c r="F352" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H352" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="353" spans="6:8" ht="22.5" customHeight="1">
       <c r="F353" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H353" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="354" spans="6:8" ht="22.5" customHeight="1">
       <c r="F354" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H354" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="355" spans="6:8" ht="22.5" customHeight="1">
       <c r="F355" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H355" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="356" spans="6:8" ht="22.5" customHeight="1">
       <c r="F356" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H356" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="357" spans="6:8" ht="22.5" customHeight="1">
       <c r="F357" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H357" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="358" spans="6:8" ht="22.5" customHeight="1">
       <c r="F358" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H358" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="359" spans="6:8" ht="22.5" customHeight="1">
       <c r="F359" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H359" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="360" spans="6:8" ht="22.5" customHeight="1">
       <c r="F360" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H360" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="361" spans="6:8" ht="22.5" customHeight="1">
       <c r="F361" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H361" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="362" spans="6:8" ht="22.5" customHeight="1">
       <c r="F362" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H362" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="363" spans="6:8" ht="22.5" customHeight="1">
       <c r="F363" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H363" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="364" spans="6:8" ht="22.5" customHeight="1">
       <c r="F364" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H364" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="365" spans="6:8" ht="22.5" customHeight="1">
       <c r="F365" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H365" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="366" spans="6:8" ht="22.5" customHeight="1">
       <c r="F366" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H366" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="367" spans="6:8" ht="22.5" customHeight="1">
       <c r="F367" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H367" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="368" spans="6:8" ht="22.5" customHeight="1">
       <c r="F368" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H368" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="369" spans="6:8" ht="22.5" customHeight="1">
       <c r="F369" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H369" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="370" spans="6:8" ht="22.5" customHeight="1">
       <c r="F370" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H370" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="371" spans="6:8" ht="22.5" customHeight="1">
       <c r="F371" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H371" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="372" spans="6:8" ht="22.5" customHeight="1">
       <c r="F372" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H372" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="373" spans="6:8" ht="22.5" customHeight="1">
       <c r="F373" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H373" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="374" spans="6:8" ht="22.5" customHeight="1">
       <c r="F374" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H374" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="375" spans="6:8" ht="22.5" customHeight="1">
       <c r="F375" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H375" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="376" spans="6:8" ht="22.5" customHeight="1">
       <c r="F376" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H376" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="377" spans="6:8" ht="22.5" customHeight="1">
       <c r="F377" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H377" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="378" spans="6:8" ht="22.5" customHeight="1">
       <c r="F378" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H378" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="379" spans="6:8" ht="22.5" customHeight="1">
       <c r="F379" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H379" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="380" spans="6:8" ht="22.5" customHeight="1">
       <c r="F380" s="47" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H380" s="48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="381" spans="6:8" ht="22.5" customHeight="1">
       <c r="F381" s="47" t="str">
-        <f t="shared" ref="F381:F444" si="14">IF(A381="", "", "gift-codes.html?game=" &amp; A381)</f>
+        <f t="shared" ref="F381:F444" si="16">IF(A381="", "", "gift-codes.html?game=" &amp; A381)</f>
         <v/>
       </c>
       <c r="H381" s="48" t="str">
-        <f t="shared" ref="H381:H444" si="15">IF(A381="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A381)</f>
+        <f t="shared" ref="H381:H444" si="17">IF(A381="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A381)</f>
         <v/>
       </c>
     </row>
     <row r="382" spans="6:8" ht="22.5" customHeight="1">
       <c r="F382" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H382" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="383" spans="6:8" ht="22.5" customHeight="1">
       <c r="F383" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H383" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="384" spans="6:8" ht="22.5" customHeight="1">
       <c r="F384" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H384" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="385" spans="6:8" ht="22.5" customHeight="1">
       <c r="F385" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H385" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="386" spans="6:8" ht="22.5" customHeight="1">
       <c r="F386" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H386" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="387" spans="6:8" ht="22.5" customHeight="1">
       <c r="F387" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H387" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="388" spans="6:8" ht="22.5" customHeight="1">
       <c r="F388" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H388" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="389" spans="6:8" ht="22.5" customHeight="1">
       <c r="F389" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H389" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="390" spans="6:8" ht="22.5" customHeight="1">
       <c r="F390" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H390" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="391" spans="6:8" ht="22.5" customHeight="1">
       <c r="F391" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H391" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="392" spans="6:8" ht="22.5" customHeight="1">
       <c r="F392" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H392" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="393" spans="6:8" ht="22.5" customHeight="1">
       <c r="F393" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H393" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="394" spans="6:8" ht="22.5" customHeight="1">
       <c r="F394" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H394" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="395" spans="6:8" ht="22.5" customHeight="1">
       <c r="F395" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H395" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="396" spans="6:8" ht="22.5" customHeight="1">
       <c r="F396" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H396" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="397" spans="6:8" ht="22.5" customHeight="1">
       <c r="F397" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H397" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="398" spans="6:8" ht="22.5" customHeight="1">
       <c r="F398" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H398" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="399" spans="6:8" ht="22.5" customHeight="1">
       <c r="F399" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H399" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="400" spans="6:8" ht="22.5" customHeight="1">
       <c r="F400" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H400" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="401" spans="6:8" ht="22.5" customHeight="1">
       <c r="F401" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H401" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="402" spans="6:8" ht="22.5" customHeight="1">
       <c r="F402" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H402" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="403" spans="6:8" ht="22.5" customHeight="1">
       <c r="F403" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H403" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="404" spans="6:8" ht="22.5" customHeight="1">
       <c r="F404" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H404" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="405" spans="6:8" ht="22.5" customHeight="1">
       <c r="F405" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H405" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="406" spans="6:8" ht="22.5" customHeight="1">
       <c r="F406" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H406" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="407" spans="6:8" ht="22.5" customHeight="1">
       <c r="F407" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H407" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="408" spans="6:8" ht="22.5" customHeight="1">
       <c r="F408" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H408" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="409" spans="6:8" ht="22.5" customHeight="1">
       <c r="F409" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H409" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="410" spans="6:8" ht="22.5" customHeight="1">
       <c r="F410" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H410" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="411" spans="6:8" ht="22.5" customHeight="1">
       <c r="F411" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H411" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="412" spans="6:8" ht="22.5" customHeight="1">
       <c r="F412" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H412" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="413" spans="6:8" ht="22.5" customHeight="1">
       <c r="F413" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H413" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="414" spans="6:8" ht="22.5" customHeight="1">
       <c r="F414" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H414" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="415" spans="6:8" ht="22.5" customHeight="1">
       <c r="F415" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H415" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="416" spans="6:8" ht="22.5" customHeight="1">
       <c r="F416" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H416" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="417" spans="6:8" ht="22.5" customHeight="1">
       <c r="F417" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H417" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="418" spans="6:8" ht="22.5" customHeight="1">
       <c r="F418" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H418" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="419" spans="6:8" ht="22.5" customHeight="1">
       <c r="F419" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H419" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="420" spans="6:8" ht="22.5" customHeight="1">
       <c r="F420" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H420" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="421" spans="6:8" ht="22.5" customHeight="1">
       <c r="F421" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H421" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="422" spans="6:8" ht="22.5" customHeight="1">
       <c r="F422" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H422" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="423" spans="6:8" ht="22.5" customHeight="1">
       <c r="F423" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H423" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="424" spans="6:8" ht="22.5" customHeight="1">
       <c r="F424" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H424" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="425" spans="6:8" ht="22.5" customHeight="1">
       <c r="F425" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H425" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="426" spans="6:8" ht="22.5" customHeight="1">
       <c r="F426" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H426" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="427" spans="6:8" ht="22.5" customHeight="1">
       <c r="F427" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H427" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="428" spans="6:8" ht="22.5" customHeight="1">
       <c r="F428" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H428" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="429" spans="6:8" ht="22.5" customHeight="1">
       <c r="F429" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H429" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="430" spans="6:8" ht="22.5" customHeight="1">
       <c r="F430" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H430" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="431" spans="6:8" ht="22.5" customHeight="1">
       <c r="F431" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H431" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="432" spans="6:8" ht="22.5" customHeight="1">
       <c r="F432" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H432" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="433" spans="6:8" ht="22.5" customHeight="1">
       <c r="F433" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H433" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="434" spans="6:8" ht="22.5" customHeight="1">
       <c r="F434" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H434" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="435" spans="6:8" ht="22.5" customHeight="1">
       <c r="F435" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H435" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="436" spans="6:8" ht="22.5" customHeight="1">
       <c r="F436" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H436" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="437" spans="6:8">
       <c r="F437" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H437" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="438" spans="6:8">
       <c r="F438" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H438" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="439" spans="6:8">
       <c r="F439" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H439" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="440" spans="6:8">
       <c r="F440" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H440" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="441" spans="6:8">
       <c r="F441" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H441" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="442" spans="6:8">
       <c r="F442" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H442" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="443" spans="6:8">
       <c r="F443" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H443" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="444" spans="6:8">
       <c r="F444" s="47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H444" s="48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="445" spans="6:8">
       <c r="F445" s="47" t="str">
-        <f t="shared" ref="F445:F508" si="16">IF(A445="", "", "gift-codes.html?game=" &amp; A445)</f>
+        <f t="shared" ref="F445:F508" si="18">IF(A445="", "", "gift-codes.html?game=" &amp; A445)</f>
         <v/>
       </c>
       <c r="H445" s="48" t="str">
-        <f t="shared" ref="H445:H508" si="17">IF(A445="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A445)</f>
+        <f t="shared" ref="H445:H508" si="19">IF(A445="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A445)</f>
         <v/>
       </c>
     </row>
     <row r="446" spans="6:8">
       <c r="F446" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H446" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="447" spans="6:8">
       <c r="F447" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H447" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="448" spans="6:8">
       <c r="F448" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H448" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="449" spans="6:8">
       <c r="F449" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H449" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="450" spans="6:8">
       <c r="F450" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H450" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="451" spans="6:8">
       <c r="F451" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H451" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="452" spans="6:8">
       <c r="F452" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H452" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="453" spans="6:8">
       <c r="F453" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H453" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="454" spans="6:8">
       <c r="F454" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H454" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="455" spans="6:8">
       <c r="F455" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H455" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="456" spans="6:8">
       <c r="F456" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H456" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="457" spans="6:8">
       <c r="F457" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H457" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="458" spans="6:8">
       <c r="F458" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H458" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="459" spans="6:8">
       <c r="F459" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H459" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="460" spans="6:8">
       <c r="F460" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H460" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="461" spans="6:8">
       <c r="F461" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H461" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="462" spans="6:8">
       <c r="F462" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H462" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="463" spans="6:8">
       <c r="F463" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H463" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="464" spans="6:8">
       <c r="F464" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H464" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="465" spans="6:8">
       <c r="F465" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H465" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="466" spans="6:8">
       <c r="F466" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H466" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="467" spans="6:8">
       <c r="F467" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H467" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="468" spans="6:8">
       <c r="F468" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H468" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="469" spans="6:8">
       <c r="F469" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H469" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="470" spans="6:8">
       <c r="F470" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H470" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="471" spans="6:8">
       <c r="F471" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H471" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="472" spans="6:8">
       <c r="F472" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H472" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="473" spans="6:8">
       <c r="F473" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H473" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="474" spans="6:8">
       <c r="F474" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H474" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="475" spans="6:8">
       <c r="F475" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H475" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="476" spans="6:8">
       <c r="F476" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H476" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="477" spans="6:8">
       <c r="F477" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H477" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="478" spans="6:8">
       <c r="F478" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H478" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="479" spans="6:8">
       <c r="F479" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H479" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="480" spans="6:8">
       <c r="F480" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H480" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="481" spans="6:8">
       <c r="F481" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H481" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="482" spans="6:8">
       <c r="F482" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H482" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="483" spans="6:8">
       <c r="F483" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H483" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="484" spans="6:8">
       <c r="F484" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H484" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="485" spans="6:8">
       <c r="F485" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H485" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="486" spans="6:8">
       <c r="F486" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H486" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="487" spans="6:8">
       <c r="F487" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H487" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="488" spans="6:8">
       <c r="F488" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H488" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="489" spans="6:8">
       <c r="F489" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H489" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="490" spans="6:8">
       <c r="F490" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H490" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="491" spans="6:8">
       <c r="F491" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H491" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="6:8">
       <c r="F492" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H492" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="6:8">
       <c r="F493" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H493" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="6:8">
       <c r="F494" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H494" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="6:8">
       <c r="F495" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H495" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="6:8">
       <c r="F496" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H496" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="497" spans="6:8">
       <c r="F497" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H497" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="498" spans="6:8">
       <c r="F498" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H498" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="499" spans="6:8">
       <c r="F499" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H499" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="500" spans="6:8">
       <c r="F500" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H500" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="6:8">
       <c r="F501" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H501" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="502" spans="6:8">
       <c r="F502" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H502" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="503" spans="6:8">
       <c r="F503" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H503" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="504" spans="6:8">
       <c r="F504" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H504" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="505" spans="6:8">
       <c r="F505" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H505" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="506" spans="6:8">
       <c r="F506" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H506" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="507" spans="6:8">
       <c r="F507" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H507" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="508" spans="6:8">
       <c r="F508" s="47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H508" s="48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="509" spans="6:8">
       <c r="F509" s="47" t="str">
-        <f t="shared" ref="F509:F572" si="18">IF(A509="", "", "gift-codes.html?game=" &amp; A509)</f>
+        <f t="shared" ref="F509:F572" si="20">IF(A509="", "", "gift-codes.html?game=" &amp; A509)</f>
         <v/>
       </c>
       <c r="H509" s="48" t="str">
-        <f t="shared" ref="H509:H572" si="19">IF(A509="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A509)</f>
+        <f t="shared" ref="H509:H572" si="21">IF(A509="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A509)</f>
         <v/>
       </c>
     </row>
     <row r="510" spans="6:8">
       <c r="F510" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H510" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="511" spans="6:8">
       <c r="F511" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H511" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="512" spans="6:8">
       <c r="F512" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H512" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="513" spans="6:8">
       <c r="F513" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H513" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="514" spans="6:8">
       <c r="F514" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H514" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="515" spans="6:8">
       <c r="F515" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H515" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="516" spans="6:8">
       <c r="F516" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H516" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="517" spans="6:8">
       <c r="F517" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H517" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="518" spans="6:8">
       <c r="F518" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H518" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="519" spans="6:8">
       <c r="F519" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H519" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="520" spans="6:8">
       <c r="F520" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H520" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="521" spans="6:8">
       <c r="F521" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H521" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="522" spans="6:8">
       <c r="F522" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H522" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="523" spans="6:8">
       <c r="F523" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H523" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="524" spans="6:8">
       <c r="F524" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H524" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="525" spans="6:8">
       <c r="F525" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H525" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="526" spans="6:8">
       <c r="F526" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H526" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="527" spans="6:8">
       <c r="F527" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H527" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="528" spans="6:8">
       <c r="F528" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H528" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="529" spans="6:8">
       <c r="F529" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H529" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="530" spans="6:8">
       <c r="F530" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H530" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="531" spans="6:8">
       <c r="F531" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H531" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="532" spans="6:8">
       <c r="F532" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H532" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="533" spans="6:8">
       <c r="F533" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H533" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="534" spans="6:8">
       <c r="F534" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H534" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="535" spans="6:8">
       <c r="F535" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H535" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="536" spans="6:8">
       <c r="F536" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H536" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="537" spans="6:8">
       <c r="F537" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H537" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="538" spans="6:8">
       <c r="F538" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H538" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="539" spans="6:8">
       <c r="F539" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H539" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="540" spans="6:8">
       <c r="F540" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H540" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="541" spans="6:8">
       <c r="F541" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H541" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="542" spans="6:8">
       <c r="F542" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H542" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="543" spans="6:8">
       <c r="F543" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H543" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="544" spans="6:8">
       <c r="F544" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H544" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="545" spans="6:8">
       <c r="F545" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H545" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="546" spans="6:8">
       <c r="F546" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H546" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="547" spans="6:8">
       <c r="F547" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H547" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="548" spans="6:8">
       <c r="F548" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H548" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="549" spans="6:8">
       <c r="F549" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H549" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="550" spans="6:8">
       <c r="F550" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H550" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="551" spans="6:8">
       <c r="F551" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H551" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="552" spans="6:8">
       <c r="F552" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H552" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="553" spans="6:8">
       <c r="F553" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H553" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="554" spans="6:8">
       <c r="F554" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H554" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="555" spans="6:8">
       <c r="F555" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H555" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="556" spans="6:8">
       <c r="F556" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H556" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="557" spans="6:8">
       <c r="F557" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H557" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="558" spans="6:8">
       <c r="F558" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H558" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="559" spans="6:8">
       <c r="F559" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H559" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="560" spans="6:8">
       <c r="F560" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H560" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="561" spans="6:8">
       <c r="F561" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H561" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="562" spans="6:8">
       <c r="F562" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H562" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="563" spans="6:8">
       <c r="F563" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H563" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="564" spans="6:8">
       <c r="F564" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H564" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="565" spans="6:8">
       <c r="F565" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H565" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="566" spans="6:8">
       <c r="F566" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H566" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="567" spans="6:8">
       <c r="F567" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H567" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="568" spans="6:8">
       <c r="F568" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H568" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="569" spans="6:8">
       <c r="F569" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H569" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="570" spans="6:8">
       <c r="F570" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H570" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="571" spans="6:8">
       <c r="F571" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H571" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="572" spans="6:8">
       <c r="F572" s="47" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H572" s="48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -38963,7 +39407,7 @@
         <v/>
       </c>
       <c r="H573" s="48" t="str">
-        <f t="shared" ref="H573:H631" si="20">IF(A573="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A573)</f>
+        <f t="shared" ref="H573:H631" si="22">IF(A573="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A573)</f>
         <v/>
       </c>
     </row>
@@ -38973,7 +39417,7 @@
         <v/>
       </c>
       <c r="H574" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -38983,343 +39427,343 @@
         <v/>
       </c>
       <c r="H575" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="576" spans="6:8">
       <c r="H576" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="577" spans="8:8">
       <c r="H577" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="578" spans="8:8">
       <c r="H578" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="579" spans="8:8">
       <c r="H579" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="580" spans="8:8">
       <c r="H580" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="8:8">
       <c r="H581" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="8:8">
       <c r="H582" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="8:8">
       <c r="H583" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="8:8">
       <c r="H584" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="8:8">
       <c r="H585" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="8:8">
       <c r="H586" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="8:8">
       <c r="H587" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="8:8">
       <c r="H588" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="8:8">
       <c r="H589" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="8:8">
       <c r="H590" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="8:8">
       <c r="H591" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="8:8">
       <c r="H592" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="8:8">
       <c r="H593" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="8:8">
       <c r="H594" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="595" spans="8:8">
       <c r="H595" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="596" spans="8:8">
       <c r="H596" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="597" spans="8:8">
       <c r="H597" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="598" spans="8:8">
       <c r="H598" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="599" spans="8:8">
       <c r="H599" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="600" spans="8:8">
       <c r="H600" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="601" spans="8:8">
       <c r="H601" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="602" spans="8:8">
       <c r="H602" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="603" spans="8:8">
       <c r="H603" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="604" spans="8:8">
       <c r="H604" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="605" spans="8:8">
       <c r="H605" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="606" spans="8:8">
       <c r="H606" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="607" spans="8:8">
       <c r="H607" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="608" spans="8:8">
       <c r="H608" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="609" spans="8:8">
       <c r="H609" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="610" spans="8:8">
       <c r="H610" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="611" spans="8:8">
       <c r="H611" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="612" spans="8:8">
       <c r="H612" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="613" spans="8:8">
       <c r="H613" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="614" spans="8:8">
       <c r="H614" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="615" spans="8:8">
       <c r="H615" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="616" spans="8:8">
       <c r="H616" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="617" spans="8:8">
       <c r="H617" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="618" spans="8:8">
       <c r="H618" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="619" spans="8:8">
       <c r="H619" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="620" spans="8:8">
       <c r="H620" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="621" spans="8:8">
       <c r="H621" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="622" spans="8:8">
       <c r="H622" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="623" spans="8:8">
       <c r="H623" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="624" spans="8:8">
       <c r="H624" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="625" spans="8:8">
       <c r="H625" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="626" spans="8:8">
       <c r="H626" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="627" spans="8:8">
       <c r="H627" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="628" spans="8:8">
       <c r="H628" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="629" spans="8:8">
       <c r="H629" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="630" spans="8:8">
       <c r="H630" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="631" spans="8:8">
       <c r="H631" s="48" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -39473,9 +39917,19 @@
     <hyperlink ref="E246" r:id="rId144"/>
     <hyperlink ref="D245" r:id="rId145"/>
     <hyperlink ref="D248" r:id="rId146"/>
+    <hyperlink ref="G249" r:id="rId147"/>
+    <hyperlink ref="E250" r:id="rId148"/>
+    <hyperlink ref="C250" r:id="rId149"/>
+    <hyperlink ref="D250" r:id="rId150"/>
+    <hyperlink ref="G251" r:id="rId151"/>
+    <hyperlink ref="C251" r:id="rId152"/>
+    <hyperlink ref="E251" r:id="rId153"/>
+    <hyperlink ref="D251" r:id="rId154"/>
+    <hyperlink ref="C252" r:id="rId155"/>
+    <hyperlink ref="D252" r:id="rId156"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId147"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId157"/>
 </worksheet>
 </file>
 
@@ -54280,7 +54734,7 @@
         <v>4443</v>
       </c>
     </row>
-    <row r="241" spans="1:16" ht="22.5" customHeight="1">
+    <row r="241" spans="1:18" ht="22.5" customHeight="1">
       <c r="A241" s="13" t="str">
         <f>IF(games!A241="", "", games!A241)</f>
         <v>玩具對決</v>
@@ -54310,7 +54764,7 @@
         <v>4562</v>
       </c>
     </row>
-    <row r="242" spans="1:16" ht="22.5" customHeight="1">
+    <row r="242" spans="1:18" ht="22.5" customHeight="1">
       <c r="A242" s="13" t="str">
         <f>IF(games!A242="", "", games!A242)</f>
         <v>幸福都市：市長模擬器</v>
@@ -54340,7 +54794,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="243" spans="1:16" ht="22.5" customHeight="1">
+    <row r="243" spans="1:18" ht="22.5" customHeight="1">
       <c r="A243" s="13" t="str">
         <f>IF(games!A243="", "", games!A243)</f>
         <v>黑道傳奇</v>
@@ -54370,7 +54824,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="244" spans="1:16" ht="22.5" customHeight="1">
+    <row r="244" spans="1:18" ht="22.5" customHeight="1">
       <c r="A244" s="13" t="str">
         <f>IF(games!A244="", "", games!A244)</f>
         <v>The kingdom：medieval tales</v>
@@ -54400,7 +54854,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="245" spans="1:16" ht="22.5" customHeight="1">
+    <row r="245" spans="1:18" ht="22.5" customHeight="1">
       <c r="A245" s="13" t="str">
         <f>IF(games!A245="", "", games!A245)</f>
         <v>七龍珠激震小隊</v>
@@ -54430,7 +54884,7 @@
         <v>4562</v>
       </c>
     </row>
-    <row r="246" spans="1:16" ht="22.5" customHeight="1">
+    <row r="246" spans="1:18" ht="22.5" customHeight="1">
       <c r="A246" s="13" t="str">
         <f>IF(games!A246="", "", games!A246)</f>
         <v>Grave Strikers</v>
@@ -54460,7 +54914,7 @@
         <v>4562</v>
       </c>
     </row>
-    <row r="247" spans="1:16" ht="22.5" customHeight="1">
+    <row r="247" spans="1:18" ht="22.5" customHeight="1">
       <c r="A247" s="13" t="str">
         <f>IF(games!A247="", "", games!A247)</f>
         <v>Stellar Sanctuary</v>
@@ -54496,7 +54950,7 @@
         <v>4562</v>
       </c>
     </row>
-    <row r="248" spans="1:16" ht="22.5" customHeight="1">
+    <row r="248" spans="1:18" ht="22.5" customHeight="1">
       <c r="A248" s="13" t="str">
         <f>IF(games!A248="", "", games!A248)</f>
         <v>古惑仔：風雲再起</v>
@@ -54544,71 +54998,156 @@
         <v>4548</v>
       </c>
     </row>
-    <row r="249" spans="1:16" ht="22.5" customHeight="1">
+    <row r="249" spans="1:18" ht="22.5" customHeight="1">
       <c r="A249" s="13" t="str">
         <f>IF(games!A249="", "", games!A249)</f>
-        <v/>
+        <v>女神秘令</v>
       </c>
       <c r="C249" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/女神秘令-禮包碼.jpg</v>
       </c>
       <c r="D249" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/女神秘令.html</v>
       </c>
       <c r="E249" s="14" t="str">
         <f>IF(games!I249&lt;&gt;"", games!I249, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="1:16" ht="22.5" customHeight="1">
+        <v>《女神秘令》是一款以西方魔幻為題材的卡牌策略 RPG 手遊，遊戲主打輕鬆護肝的放置玩法，讓玩家在忙碌之餘也能輕鬆享受成長樂趣。遊戲內建豐富的女神角色，每位都有獨特的技能與華麗特效，玩家可自由搭配陣容，展開燒腦的策略對決。除了主線劇情外，還有多種副本、公會戰與競技場等多元玩法，搭配豐厚福利與兌換碼，讓新手也能快速上手。想輕鬆蒐集心儀女神、無壓力變強嗎？現在就加入《女神秘令》，透過代儲值服務可享快速安全的優惠，還有專屬禮包碼等你來領取！</v>
+      </c>
+      <c r="F249" s="101" t="s">
+        <v>4621</v>
+      </c>
+      <c r="K249" s="101" t="s">
+        <v>4621</v>
+      </c>
+      <c r="L249" s="101"/>
+    </row>
+    <row r="250" spans="1:18" ht="22.5" customHeight="1">
       <c r="A250" s="13" t="str">
         <f>IF(games!A250="", "", games!A250)</f>
-        <v/>
+        <v>Torerowa</v>
       </c>
       <c r="C250" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/Torerowa-禮包碼.jpg</v>
       </c>
       <c r="D250" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Torerowa.html</v>
       </c>
       <c r="E250" s="14" t="str">
         <f>IF(games!I250&lt;&gt;"", games!I250, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="1:16" ht="22.5" customHeight="1">
+        <v>《Torerowa》是一款奇幻風格的 MMORPG，以精緻的日系畫風與Q萌角色聞名。玩家將在廣闊的世界中冒險，體驗豐富的任務與劇情。遊戲提供多元職業選擇，每種職業都有獨特的技能樹與玩法，無論是PVE還是PVP，都能找到屬於自己的樂趣。此外，遊戲內還有釣魚、料理、採集等多樣生活技能，讓冒險旅程更加豐富有趣。想要輕鬆遊玩、享受自由探索的樂趣嗎？使用兌換碼與禮包碼即可獲得豐厚資源，選擇快速安全的代儲值服務，讓你輕鬆暢遊這片奇幻大陸！</v>
+      </c>
+      <c r="F250" s="17" t="s">
+        <v>4572</v>
+      </c>
+      <c r="G250" s="13" t="s">
+        <v>4562</v>
+      </c>
+      <c r="K250" s="17" t="s">
+        <v>4572</v>
+      </c>
+      <c r="L250" s="13" t="s">
+        <v>4562</v>
+      </c>
+    </row>
+    <row r="251" spans="1:18" ht="22.5" customHeight="1">
+      <c r="A251" s="13" t="str">
+        <f>IF(games!A251="", "", games!A251)</f>
+        <v>Ricochet Squad</v>
+      </c>
       <c r="C251" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/Ricochet Squad-禮包碼.jpg</v>
       </c>
       <c r="D251" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Ricochet Squad.html</v>
       </c>
       <c r="E251" s="14" t="str">
         <f>IF(games!I251&lt;&gt;"", games!I251, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252" spans="1:16" ht="22.5" customHeight="1">
+        <v>《Ricochet Squad》是一款結合射擊與彈射玩法的益智休閒手遊。遊戲畫面風格清新可愛，操作簡單易懂，玩家只需透過彈射角色，擊敗地圖上的敵人即可。關卡設計充滿巧思，需要玩家動腦思考，利用地形與彈射角度來完成挑戰。除了單人闖關模式，遊戲也支援多人PVP對戰，與朋友一較高下。遊戲提供多樣角色與造型，滿足玩家蒐集慾望。想在通勤或休息時間，來一場刺激又有趣的腦力激盪嗎？輸入兌換碼與禮包碼即可領取好禮，選擇快速安全的代儲值，讓你輕鬆獲得遊戲內稀有道具！</v>
+      </c>
+      <c r="F251" s="34" t="s">
+        <v>4619</v>
+      </c>
+      <c r="G251" s="13" t="s">
+        <v>4620</v>
+      </c>
+      <c r="H251" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I251" s="13" t="s">
+        <v>4404</v>
+      </c>
+      <c r="K251" s="17" t="s">
+        <v>4617</v>
+      </c>
+      <c r="L251" s="13" t="s">
+        <v>4618</v>
+      </c>
+    </row>
+    <row r="252" spans="1:18" ht="22.5" customHeight="1">
+      <c r="A252" s="13" t="str">
+        <f>IF(games!A252="", "", games!A252)</f>
+        <v>魔法村物語</v>
+      </c>
       <c r="C252" s="13" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>giftcodesbanner/魔法村物語-禮包碼.jpg</v>
       </c>
       <c r="D252" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/魔法村物語.html</v>
       </c>
       <c r="E252" s="14" t="str">
         <f>IF(games!I252&lt;&gt;"", games!I252, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253" spans="1:16" ht="22.5" customHeight="1">
+        <v>《魔法村物語》是一款日系像素風格的經營模擬 RPG 手遊。玩家將扮演一位年輕的村長，在充滿魔法的奇幻世界中，經營並發展自己的村莊。遊戲融合了冒險、建設、養成與社交等多元玩法，玩家可以建造各種設施、招募冒險者、探索未知區域，並與其他玩家交流互動。遊戲的像素畫面精美細膩，搭配輕鬆療癒的BGM，帶給玩家獨特的遊玩體驗。想要打造屬於自己的夢幻村莊嗎？記得使用兌換碼與禮包碼來獲得豐厚資源，透過快速安全的代儲值服務，加速你的村莊發展！</v>
+      </c>
+      <c r="F252" s="34" t="s">
+        <v>4635</v>
+      </c>
+      <c r="G252" s="13" t="s">
+        <v>4636</v>
+      </c>
+      <c r="H252" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I252" s="13" t="s">
+        <v>4404</v>
+      </c>
+      <c r="K252" s="17" t="s">
+        <v>4614</v>
+      </c>
+      <c r="L252" s="13" t="s">
+        <v>4637</v>
+      </c>
+      <c r="M252" s="18" t="s">
+        <v>4615</v>
+      </c>
+      <c r="N252" s="13" t="s">
+        <v>4638</v>
+      </c>
+      <c r="O252" s="18" t="s">
+        <v>4616</v>
+      </c>
+      <c r="P252" s="13" t="s">
+        <v>4639</v>
+      </c>
+      <c r="Q252" s="18" t="s">
+        <v>1935</v>
+      </c>
+      <c r="R252" s="13" t="s">
+        <v>4640</v>
+      </c>
+    </row>
+    <row r="253" spans="1:18" ht="22.5" customHeight="1">
+      <c r="A253" s="13" t="str">
+        <f>IF(games!A253="", "", games!A253)</f>
+        <v/>
+      </c>
       <c r="C253" s="13" t="str">
         <f t="shared" ref="C253:C316" si="9">IF(A253="","", "giftcodesbanner/" &amp; A253 &amp; "-禮包碼.jpg")</f>
         <v/>
@@ -54622,7 +55161,11 @@
         <v/>
       </c>
     </row>
-    <row r="254" spans="1:16" ht="22.5" customHeight="1">
+    <row r="254" spans="1:18" ht="22.5" customHeight="1">
+      <c r="A254" s="13" t="str">
+        <f>IF(games!A254="", "", games!A254)</f>
+        <v/>
+      </c>
       <c r="C254" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54636,7 +55179,11 @@
         <v/>
       </c>
     </row>
-    <row r="255" spans="1:16" ht="22.5" customHeight="1">
+    <row r="255" spans="1:18" ht="22.5" customHeight="1">
+      <c r="A255" s="13" t="str">
+        <f>IF(games!A255="", "", games!A255)</f>
+        <v/>
+      </c>
       <c r="C255" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54646,7 +55193,11 @@
         <v/>
       </c>
     </row>
-    <row r="256" spans="1:16" ht="22.5" customHeight="1">
+    <row r="256" spans="1:18" ht="22.5" customHeight="1">
+      <c r="A256" s="13" t="str">
+        <f>IF(games!A256="", "", games!A256)</f>
+        <v/>
+      </c>
       <c r="C256" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54656,7 +55207,11 @@
         <v/>
       </c>
     </row>
-    <row r="257" spans="3:4" ht="22.5" customHeight="1">
+    <row r="257" spans="1:4" ht="22.5" customHeight="1">
+      <c r="A257" s="13" t="str">
+        <f>IF(games!A257="", "", games!A257)</f>
+        <v/>
+      </c>
       <c r="C257" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54666,7 +55221,11 @@
         <v/>
       </c>
     </row>
-    <row r="258" spans="3:4" ht="22.5" customHeight="1">
+    <row r="258" spans="1:4" ht="22.5" customHeight="1">
+      <c r="A258" s="13" t="str">
+        <f>IF(games!A258="", "", games!A258)</f>
+        <v/>
+      </c>
       <c r="C258" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54676,7 +55235,11 @@
         <v/>
       </c>
     </row>
-    <row r="259" spans="3:4">
+    <row r="259" spans="1:4">
+      <c r="A259" s="13" t="str">
+        <f>IF(games!A259="", "", games!A259)</f>
+        <v/>
+      </c>
       <c r="C259" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54686,7 +55249,11 @@
         <v/>
       </c>
     </row>
-    <row r="260" spans="3:4">
+    <row r="260" spans="1:4">
+      <c r="A260" s="13" t="str">
+        <f>IF(games!A260="", "", games!A260)</f>
+        <v/>
+      </c>
       <c r="C260" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54696,7 +55263,11 @@
         <v/>
       </c>
     </row>
-    <row r="261" spans="3:4">
+    <row r="261" spans="1:4">
+      <c r="A261" s="13" t="str">
+        <f>IF(games!A261="", "", games!A261)</f>
+        <v/>
+      </c>
       <c r="C261" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54706,7 +55277,11 @@
         <v/>
       </c>
     </row>
-    <row r="262" spans="3:4">
+    <row r="262" spans="1:4">
+      <c r="A262" s="13" t="str">
+        <f>IF(games!A262="", "", games!A262)</f>
+        <v/>
+      </c>
       <c r="C262" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54716,7 +55291,11 @@
         <v/>
       </c>
     </row>
-    <row r="263" spans="3:4">
+    <row r="263" spans="1:4">
+      <c r="A263" s="13" t="str">
+        <f>IF(games!A263="", "", games!A263)</f>
+        <v/>
+      </c>
       <c r="C263" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54726,7 +55305,11 @@
         <v/>
       </c>
     </row>
-    <row r="264" spans="3:4">
+    <row r="264" spans="1:4">
+      <c r="A264" s="13" t="str">
+        <f>IF(games!A264="", "", games!A264)</f>
+        <v/>
+      </c>
       <c r="C264" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54736,7 +55319,11 @@
         <v/>
       </c>
     </row>
-    <row r="265" spans="3:4">
+    <row r="265" spans="1:4">
+      <c r="A265" s="13" t="str">
+        <f>IF(games!A265="", "", games!A265)</f>
+        <v/>
+      </c>
       <c r="C265" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54746,7 +55333,11 @@
         <v/>
       </c>
     </row>
-    <row r="266" spans="3:4">
+    <row r="266" spans="1:4">
+      <c r="A266" s="13" t="str">
+        <f>IF(games!A266="", "", games!A266)</f>
+        <v/>
+      </c>
       <c r="C266" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54756,7 +55347,11 @@
         <v/>
       </c>
     </row>
-    <row r="267" spans="3:4">
+    <row r="267" spans="1:4">
+      <c r="A267" s="13" t="str">
+        <f>IF(games!A267="", "", games!A267)</f>
+        <v/>
+      </c>
       <c r="C267" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54766,7 +55361,11 @@
         <v/>
       </c>
     </row>
-    <row r="268" spans="3:4">
+    <row r="268" spans="1:4">
+      <c r="A268" s="13" t="str">
+        <f>IF(games!A268="", "", games!A268)</f>
+        <v/>
+      </c>
       <c r="C268" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54776,7 +55375,11 @@
         <v/>
       </c>
     </row>
-    <row r="269" spans="3:4">
+    <row r="269" spans="1:4">
+      <c r="A269" s="13" t="str">
+        <f>IF(games!A269="", "", games!A269)</f>
+        <v/>
+      </c>
       <c r="C269" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54786,7 +55389,11 @@
         <v/>
       </c>
     </row>
-    <row r="270" spans="3:4">
+    <row r="270" spans="1:4">
+      <c r="A270" s="13" t="str">
+        <f>IF(games!A270="", "", games!A270)</f>
+        <v/>
+      </c>
       <c r="C270" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54796,7 +55403,11 @@
         <v/>
       </c>
     </row>
-    <row r="271" spans="3:4">
+    <row r="271" spans="1:4">
+      <c r="A271" s="13" t="str">
+        <f>IF(games!A271="", "", games!A271)</f>
+        <v/>
+      </c>
       <c r="C271" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54806,7 +55417,11 @@
         <v/>
       </c>
     </row>
-    <row r="272" spans="3:4">
+    <row r="272" spans="1:4">
+      <c r="A272" s="13" t="str">
+        <f>IF(games!A272="", "", games!A272)</f>
+        <v/>
+      </c>
       <c r="C272" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54816,7 +55431,11 @@
         <v/>
       </c>
     </row>
-    <row r="273" spans="3:4">
+    <row r="273" spans="1:4">
+      <c r="A273" s="13" t="str">
+        <f>IF(games!A273="", "", games!A273)</f>
+        <v/>
+      </c>
       <c r="C273" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54826,7 +55445,11 @@
         <v/>
       </c>
     </row>
-    <row r="274" spans="3:4">
+    <row r="274" spans="1:4">
+      <c r="A274" s="13" t="str">
+        <f>IF(games!A274="", "", games!A274)</f>
+        <v/>
+      </c>
       <c r="C274" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54836,7 +55459,11 @@
         <v/>
       </c>
     </row>
-    <row r="275" spans="3:4">
+    <row r="275" spans="1:4">
+      <c r="A275" s="13" t="str">
+        <f>IF(games!A275="", "", games!A275)</f>
+        <v/>
+      </c>
       <c r="C275" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54846,7 +55473,11 @@
         <v/>
       </c>
     </row>
-    <row r="276" spans="3:4">
+    <row r="276" spans="1:4">
+      <c r="A276" s="13" t="str">
+        <f>IF(games!A276="", "", games!A276)</f>
+        <v/>
+      </c>
       <c r="C276" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54856,7 +55487,11 @@
         <v/>
       </c>
     </row>
-    <row r="277" spans="3:4">
+    <row r="277" spans="1:4">
+      <c r="A277" s="13" t="str">
+        <f>IF(games!A277="", "", games!A277)</f>
+        <v/>
+      </c>
       <c r="C277" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54866,7 +55501,11 @@
         <v/>
       </c>
     </row>
-    <row r="278" spans="3:4">
+    <row r="278" spans="1:4">
+      <c r="A278" s="13" t="str">
+        <f>IF(games!A278="", "", games!A278)</f>
+        <v/>
+      </c>
       <c r="C278" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54876,7 +55515,11 @@
         <v/>
       </c>
     </row>
-    <row r="279" spans="3:4">
+    <row r="279" spans="1:4">
+      <c r="A279" s="13" t="str">
+        <f>IF(games!A279="", "", games!A279)</f>
+        <v/>
+      </c>
       <c r="C279" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54886,7 +55529,11 @@
         <v/>
       </c>
     </row>
-    <row r="280" spans="3:4">
+    <row r="280" spans="1:4">
+      <c r="A280" s="13" t="str">
+        <f>IF(games!A280="", "", games!A280)</f>
+        <v/>
+      </c>
       <c r="C280" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54896,7 +55543,11 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="3:4">
+    <row r="281" spans="1:4">
+      <c r="A281" s="13" t="str">
+        <f>IF(games!A281="", "", games!A281)</f>
+        <v/>
+      </c>
       <c r="C281" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54906,7 +55557,11 @@
         <v/>
       </c>
     </row>
-    <row r="282" spans="3:4">
+    <row r="282" spans="1:4">
+      <c r="A282" s="13" t="str">
+        <f>IF(games!A282="", "", games!A282)</f>
+        <v/>
+      </c>
       <c r="C282" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54916,7 +55571,11 @@
         <v/>
       </c>
     </row>
-    <row r="283" spans="3:4">
+    <row r="283" spans="1:4">
+      <c r="A283" s="13" t="str">
+        <f>IF(games!A283="", "", games!A283)</f>
+        <v/>
+      </c>
       <c r="C283" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54926,7 +55585,11 @@
         <v/>
       </c>
     </row>
-    <row r="284" spans="3:4">
+    <row r="284" spans="1:4">
+      <c r="A284" s="13" t="str">
+        <f>IF(games!A284="", "", games!A284)</f>
+        <v/>
+      </c>
       <c r="C284" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54936,7 +55599,11 @@
         <v/>
       </c>
     </row>
-    <row r="285" spans="3:4">
+    <row r="285" spans="1:4">
+      <c r="A285" s="13" t="str">
+        <f>IF(games!A285="", "", games!A285)</f>
+        <v/>
+      </c>
       <c r="C285" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54946,7 +55613,11 @@
         <v/>
       </c>
     </row>
-    <row r="286" spans="3:4">
+    <row r="286" spans="1:4">
+      <c r="A286" s="13" t="str">
+        <f>IF(games!A286="", "", games!A286)</f>
+        <v/>
+      </c>
       <c r="C286" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54956,7 +55627,11 @@
         <v/>
       </c>
     </row>
-    <row r="287" spans="3:4">
+    <row r="287" spans="1:4">
+      <c r="A287" s="13" t="str">
+        <f>IF(games!A287="", "", games!A287)</f>
+        <v/>
+      </c>
       <c r="C287" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54966,7 +55641,11 @@
         <v/>
       </c>
     </row>
-    <row r="288" spans="3:4">
+    <row r="288" spans="1:4">
+      <c r="A288" s="13" t="str">
+        <f>IF(games!A288="", "", games!A288)</f>
+        <v/>
+      </c>
       <c r="C288" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54976,7 +55655,11 @@
         <v/>
       </c>
     </row>
-    <row r="289" spans="3:4">
+    <row r="289" spans="1:4">
+      <c r="A289" s="13" t="str">
+        <f>IF(games!A289="", "", games!A289)</f>
+        <v/>
+      </c>
       <c r="C289" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54986,7 +55669,11 @@
         <v/>
       </c>
     </row>
-    <row r="290" spans="3:4">
+    <row r="290" spans="1:4">
+      <c r="A290" s="13" t="str">
+        <f>IF(games!A290="", "", games!A290)</f>
+        <v/>
+      </c>
       <c r="C290" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -54996,7 +55683,11 @@
         <v/>
       </c>
     </row>
-    <row r="291" spans="3:4">
+    <row r="291" spans="1:4">
+      <c r="A291" s="13" t="str">
+        <f>IF(games!A291="", "", games!A291)</f>
+        <v/>
+      </c>
       <c r="C291" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55006,7 +55697,11 @@
         <v/>
       </c>
     </row>
-    <row r="292" spans="3:4">
+    <row r="292" spans="1:4">
+      <c r="A292" s="13" t="str">
+        <f>IF(games!A292="", "", games!A292)</f>
+        <v/>
+      </c>
       <c r="C292" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55016,7 +55711,11 @@
         <v/>
       </c>
     </row>
-    <row r="293" spans="3:4">
+    <row r="293" spans="1:4">
+      <c r="A293" s="13" t="str">
+        <f>IF(games!A293="", "", games!A293)</f>
+        <v/>
+      </c>
       <c r="C293" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55026,7 +55725,11 @@
         <v/>
       </c>
     </row>
-    <row r="294" spans="3:4">
+    <row r="294" spans="1:4">
+      <c r="A294" s="13" t="str">
+        <f>IF(games!A294="", "", games!A294)</f>
+        <v/>
+      </c>
       <c r="C294" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55036,7 +55739,11 @@
         <v/>
       </c>
     </row>
-    <row r="295" spans="3:4">
+    <row r="295" spans="1:4">
+      <c r="A295" s="13" t="str">
+        <f>IF(games!A295="", "", games!A295)</f>
+        <v/>
+      </c>
       <c r="C295" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55046,7 +55753,11 @@
         <v/>
       </c>
     </row>
-    <row r="296" spans="3:4">
+    <row r="296" spans="1:4">
+      <c r="A296" s="13" t="str">
+        <f>IF(games!A296="", "", games!A296)</f>
+        <v/>
+      </c>
       <c r="C296" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55056,7 +55767,11 @@
         <v/>
       </c>
     </row>
-    <row r="297" spans="3:4">
+    <row r="297" spans="1:4">
+      <c r="A297" s="13" t="str">
+        <f>IF(games!A297="", "", games!A297)</f>
+        <v/>
+      </c>
       <c r="C297" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55066,7 +55781,11 @@
         <v/>
       </c>
     </row>
-    <row r="298" spans="3:4">
+    <row r="298" spans="1:4">
+      <c r="A298" s="13" t="str">
+        <f>IF(games!A298="", "", games!A298)</f>
+        <v/>
+      </c>
       <c r="C298" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55076,7 +55795,11 @@
         <v/>
       </c>
     </row>
-    <row r="299" spans="3:4">
+    <row r="299" spans="1:4">
+      <c r="A299" s="13" t="str">
+        <f>IF(games!A299="", "", games!A299)</f>
+        <v/>
+      </c>
       <c r="C299" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55086,7 +55809,11 @@
         <v/>
       </c>
     </row>
-    <row r="300" spans="3:4">
+    <row r="300" spans="1:4">
+      <c r="A300" s="13" t="str">
+        <f>IF(games!A300="", "", games!A300)</f>
+        <v/>
+      </c>
       <c r="C300" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55096,7 +55823,11 @@
         <v/>
       </c>
     </row>
-    <row r="301" spans="3:4">
+    <row r="301" spans="1:4">
+      <c r="A301" s="13" t="str">
+        <f>IF(games!A301="", "", games!A301)</f>
+        <v/>
+      </c>
       <c r="C301" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55106,7 +55837,11 @@
         <v/>
       </c>
     </row>
-    <row r="302" spans="3:4">
+    <row r="302" spans="1:4">
+      <c r="A302" s="13" t="str">
+        <f>IF(games!A302="", "", games!A302)</f>
+        <v/>
+      </c>
       <c r="C302" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55116,7 +55851,11 @@
         <v/>
       </c>
     </row>
-    <row r="303" spans="3:4">
+    <row r="303" spans="1:4">
+      <c r="A303" s="13" t="str">
+        <f>IF(games!A303="", "", games!A303)</f>
+        <v/>
+      </c>
       <c r="C303" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55126,7 +55865,11 @@
         <v/>
       </c>
     </row>
-    <row r="304" spans="3:4">
+    <row r="304" spans="1:4">
+      <c r="A304" s="13" t="str">
+        <f>IF(games!A304="", "", games!A304)</f>
+        <v/>
+      </c>
       <c r="C304" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55136,7 +55879,11 @@
         <v/>
       </c>
     </row>
-    <row r="305" spans="3:4">
+    <row r="305" spans="1:4">
+      <c r="A305" s="13" t="str">
+        <f>IF(games!A305="", "", games!A305)</f>
+        <v/>
+      </c>
       <c r="C305" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55146,7 +55893,11 @@
         <v/>
       </c>
     </row>
-    <row r="306" spans="3:4">
+    <row r="306" spans="1:4">
+      <c r="A306" s="13" t="str">
+        <f>IF(games!A306="", "", games!A306)</f>
+        <v/>
+      </c>
       <c r="C306" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55156,7 +55907,11 @@
         <v/>
       </c>
     </row>
-    <row r="307" spans="3:4">
+    <row r="307" spans="1:4">
+      <c r="A307" s="13" t="str">
+        <f>IF(games!A307="", "", games!A307)</f>
+        <v/>
+      </c>
       <c r="C307" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55166,7 +55921,7 @@
         <v/>
       </c>
     </row>
-    <row r="308" spans="3:4">
+    <row r="308" spans="1:4">
       <c r="C308" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55176,7 +55931,7 @@
         <v/>
       </c>
     </row>
-    <row r="309" spans="3:4">
+    <row r="309" spans="1:4">
       <c r="C309" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55186,7 +55941,7 @@
         <v/>
       </c>
     </row>
-    <row r="310" spans="3:4">
+    <row r="310" spans="1:4">
       <c r="C310" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55196,7 +55951,7 @@
         <v/>
       </c>
     </row>
-    <row r="311" spans="3:4">
+    <row r="311" spans="1:4">
       <c r="C311" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55206,7 +55961,7 @@
         <v/>
       </c>
     </row>
-    <row r="312" spans="3:4">
+    <row r="312" spans="1:4">
       <c r="C312" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55216,7 +55971,7 @@
         <v/>
       </c>
     </row>
-    <row r="313" spans="3:4">
+    <row r="313" spans="1:4">
       <c r="C313" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55226,7 +55981,7 @@
         <v/>
       </c>
     </row>
-    <row r="314" spans="3:4">
+    <row r="314" spans="1:4">
       <c r="C314" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55236,7 +55991,7 @@
         <v/>
       </c>
     </row>
-    <row r="315" spans="3:4">
+    <row r="315" spans="1:4">
       <c r="C315" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55246,7 +56001,7 @@
         <v/>
       </c>
     </row>
-    <row r="316" spans="3:4">
+    <row r="316" spans="1:4">
       <c r="C316" s="13" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -55256,7 +56011,7 @@
         <v/>
       </c>
     </row>
-    <row r="317" spans="3:4">
+    <row r="317" spans="1:4">
       <c r="C317" s="13" t="str">
         <f t="shared" ref="C317:C380" si="12">IF(A317="","", "giftcodesbanner/" &amp; A317 &amp; "-禮包碼.jpg")</f>
         <v/>
@@ -55266,7 +56021,7 @@
         <v/>
       </c>
     </row>
-    <row r="318" spans="3:4">
+    <row r="318" spans="1:4">
       <c r="C318" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -55276,7 +56031,7 @@
         <v/>
       </c>
     </row>
-    <row r="319" spans="3:4">
+    <row r="319" spans="1:4">
       <c r="C319" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -55286,7 +56041,7 @@
         <v/>
       </c>
     </row>
-    <row r="320" spans="3:4">
+    <row r="320" spans="1:4">
       <c r="C320" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6847" uniqueCount="4641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6904" uniqueCount="4685">
   <si>
     <t>Facebook</t>
   </si>
@@ -17881,6 +17881,179 @@
   <si>
     <t>鑽石x188、黃金招募令x5、少量經驗(2小時)x3</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇蹟MU：騎士袋你飛</t>
+  </si>
+  <si>
+    <t>AUR3：影月幻域</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.webzen.muidle.google</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E5%A5%87%E8%B9%9Fmu-%E9%A8%8E%E5%A3%AB%E8%A2%8B%E4%BD%A0%E9%A3%9B/id6742208743</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/MUPocketKnightsTW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.ylhd.hsjg&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/aur-3-%E5%BD%B1%E6%9C%88%E5%B9%BB%E5%9F%9F/id6747416926?ppid=0bec509b-3803-468b-a350-cf23aa3d06e3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/aur3.lunar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MUPOCKETOPEN0918</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石x500、神秘寶石x5、次元迷宮掃蕩券x3、惡魔廣場掃蕩券x3、探險掃蕩券（第5章）x2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>THANKYOUCAPTAIN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*10000+靈魂寶石*5+神秘寶石*20+放置寶箱掃蕩券*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HAPPYMUDAY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石 500個， 血色城堡掃蕩券 1個</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sssvip333</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sssvip444</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sssvip555</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sssvip666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP紅蓮聖子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>戰力直升寶箱、琉璃彩豆、月華石</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>戰力直升寶箱、洗靈露×30、天工核心×3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>獸魂抽獎券×10、進化寶石×5、青金碎×5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲主畫面左下角齒輪「設定」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>彈出書籤選擇「禮包兌換」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>右上方三條線選單點開</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>公告事項進去後選擇「序號兌換」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>各位勇者們久等了！由韓國網禪 Webzen 正版授權的《奇蹟MU：騎士袋你飛》帶你重溫感動，再現經典紅龍裝、亞特蘭蒂斯、冰風谷等場景。這款放置系手遊讓你輕鬆掛機、自動練功，上班族也能秒速升級，隨時隨地享受奇蹟世界的樂趣！遊戲內建多元玩法，除了酷炫外觀和獨特技能，還有創新的 AI 系統，讓你體驗超脫傳統的奇蹟新世代。官方提供多組兌換碼及禮包碼，讓勇者們領取豐富虛寶，輕鬆起跑。此外，遊戲支持代儲值服務，提供玩家快速安全的儲值管道，讓你輕鬆擁有神裝，傲視全服！趕快加入，與戰盟夥伴們一起重返奇蹟大陸吧！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>準備好進入充滿奇幻冒險的異世界了嗎？《AUR3：影月幻域》是一款集結高自由度、精緻畫風與流暢戰鬥的MMORPG手遊。遊戲主打無鎖定戰鬥，結合華麗的技能特效與暢快的打擊感，讓你體驗最極致的戰鬥樂趣。在這片廣闊的幻想大陸上，你可以自由探索、結交夥伴，並與強大的怪物進行史詩級對決。為了回饋廣大玩家，官方準備了多組兌換碼與禮包碼，讓各位冒險者能迅速提升戰力。遊戲內也支援代儲值服務，提供快速安全的儲值通道，讓你在遊戲中無後顧之憂。現在就拿起你的武器，加入《AUR3：影月幻域》，譜寫屬於你的傳奇篇章！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11900鑽石</t>
+  </si>
+  <si>
+    <t>移除廣告禮包</t>
+  </si>
+  <si>
+    <t>三倍鑽石爆發禮包</t>
+  </si>
+  <si>
+    <t>每月豪華探險加速禮包</t>
+  </si>
+  <si>
+    <t>每月黃金奔跑禮包</t>
+  </si>
+  <si>
+    <t>每月鑽石定期存款禮包</t>
+  </si>
+  <si>
+    <t>6480靈玉</t>
+  </si>
+  <si>
+    <t>3280靈玉</t>
+  </si>
+  <si>
+    <t>1980靈玉</t>
+  </si>
+  <si>
+    <r>
+      <t>980</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>靈玉</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>300靈玉</t>
+  </si>
+  <si>
+    <t>60靈玉</t>
+  </si>
+  <si>
+    <t>直升首儲14.99</t>
+  </si>
+  <si>
+    <t>甄品4.99</t>
   </si>
 </sst>
 </file>
@@ -34856,7 +35029,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="241" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+    <row r="241" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A241" s="71" t="s">
         <v>4427</v>
       </c>
@@ -34938,7 +35111,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="242" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+    <row r="242" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A242" s="3" t="s">
         <v>4428</v>
       </c>
@@ -35008,7 +35181,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="243" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+    <row r="243" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A243" s="3" t="s">
         <v>4429</v>
       </c>
@@ -35090,7 +35263,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="244" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+    <row r="244" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A244" s="71" t="s">
         <v>4430</v>
       </c>
@@ -35178,7 +35351,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="245" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+    <row r="245" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A245" s="3" t="s">
         <v>4484</v>
       </c>
@@ -35248,7 +35421,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="246" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+    <row r="246" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A246" s="71" t="s">
         <v>4473</v>
       </c>
@@ -35300,7 +35473,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="247" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+    <row r="247" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A247" s="71" t="s">
         <v>4474</v>
       </c>
@@ -35370,7 +35543,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="248" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+    <row r="248" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A248" s="71" t="s">
         <v>4475</v>
       </c>
@@ -35452,7 +35625,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="249" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+    <row r="249" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A249" s="71" t="s">
         <v>4558</v>
       </c>
@@ -35528,7 +35701,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+    <row r="250" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A250" s="71" t="s">
         <v>4559</v>
       </c>
@@ -35598,7 +35771,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="251" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+    <row r="251" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A251" s="71" t="s">
         <v>4560</v>
       </c>
@@ -35662,7 +35835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="252" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+    <row r="252" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A252" s="3" t="s">
         <v>4573</v>
       </c>
@@ -35750,27 +35923,177 @@
         <v>124</v>
       </c>
     </row>
-    <row r="253" spans="1:29" ht="22.5" customHeight="1">
+    <row r="253" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A253" s="71" t="s">
+        <v>4641</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>4645</v>
+      </c>
+      <c r="D253" s="4" t="s">
+        <v>4645</v>
+      </c>
+      <c r="E253" s="4" t="s">
+        <v>4644</v>
+      </c>
       <c r="F253" s="41" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/奇蹟MU：騎士袋你飛.html</v>
+      </c>
+      <c r="G253" s="4" t="s">
+        <v>4643</v>
       </c>
       <c r="H253" s="41" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="1:29" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/奇蹟MU：騎士袋你飛.html</v>
+      </c>
+      <c r="I253" s="42" t="s">
+        <v>4669</v>
+      </c>
+      <c r="J253" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="K253" s="71">
+        <v>1605</v>
+      </c>
+      <c r="L253" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="M253" s="71">
+        <v>810</v>
+      </c>
+      <c r="N253" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="O253" s="71">
+        <v>496</v>
+      </c>
+      <c r="P253" s="1" t="s">
+        <v>4671</v>
+      </c>
+      <c r="Q253" s="71">
+        <v>198</v>
+      </c>
+      <c r="R253" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="S253" s="71">
+        <v>103</v>
+      </c>
+      <c r="T253" s="1" t="s">
+        <v>3981</v>
+      </c>
+      <c r="U253" s="71">
+        <v>21</v>
+      </c>
+      <c r="V253" s="1" t="s">
+        <v>4672</v>
+      </c>
+      <c r="W253" s="71">
+        <v>163</v>
+      </c>
+      <c r="X253" s="1" t="s">
+        <v>4673</v>
+      </c>
+      <c r="Y253" s="71">
+        <v>58</v>
+      </c>
+      <c r="Z253" s="1" t="s">
+        <v>4674</v>
+      </c>
+      <c r="AA253" s="71">
+        <v>58</v>
+      </c>
+      <c r="AB253" s="1" t="s">
+        <v>4675</v>
+      </c>
+      <c r="AC253" s="71">
+        <v>58</v>
+      </c>
+      <c r="AD253" s="1" t="s">
+        <v>4676</v>
+      </c>
+      <c r="AE253" s="71">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="254" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A254" s="71" t="s">
+        <v>4642</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>4648</v>
+      </c>
+      <c r="D254" s="4" t="s">
+        <v>4648</v>
+      </c>
+      <c r="E254" s="4" t="s">
+        <v>4647</v>
+      </c>
       <c r="F254" s="41" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/AUR3：影月幻域.html</v>
+      </c>
+      <c r="G254" s="4" t="s">
+        <v>4646</v>
       </c>
       <c r="H254" s="41" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="255" spans="1:29" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/AUR3：影月幻域.html</v>
+      </c>
+      <c r="I254" s="42" t="s">
+        <v>4670</v>
+      </c>
+      <c r="J254" s="1" t="s">
+        <v>4677</v>
+      </c>
+      <c r="K254" s="71">
+        <v>1139</v>
+      </c>
+      <c r="L254" s="1" t="s">
+        <v>4678</v>
+      </c>
+      <c r="M254" s="71">
+        <v>612</v>
+      </c>
+      <c r="N254" s="1" t="s">
+        <v>4679</v>
+      </c>
+      <c r="O254" s="71">
+        <v>380</v>
+      </c>
+      <c r="P254" s="1" t="s">
+        <v>4680</v>
+      </c>
+      <c r="Q254" s="71">
+        <v>194</v>
+      </c>
+      <c r="R254" s="1" t="s">
+        <v>4681</v>
+      </c>
+      <c r="S254" s="71">
+        <v>74</v>
+      </c>
+      <c r="T254" s="1" t="s">
+        <v>4682</v>
+      </c>
+      <c r="U254" s="71">
+        <v>17</v>
+      </c>
+      <c r="V254" s="1" t="s">
+        <v>4683</v>
+      </c>
+      <c r="W254" s="71">
+        <v>194</v>
+      </c>
+      <c r="X254" s="1" t="s">
+        <v>4684</v>
+      </c>
+      <c r="Y254" s="71">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="255" spans="1:31" ht="22.5" customHeight="1">
       <c r="F255" s="41" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -35780,7 +36103,7 @@
         <v/>
       </c>
     </row>
-    <row r="256" spans="1:29" ht="22.5" customHeight="1">
+    <row r="256" spans="1:31" ht="22.5" customHeight="1">
       <c r="F256" s="41" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -39476,9 +39799,17 @@
     <hyperlink ref="D251" r:id="rId154"/>
     <hyperlink ref="C252" r:id="rId155"/>
     <hyperlink ref="D252" r:id="rId156"/>
+    <hyperlink ref="G253" r:id="rId157"/>
+    <hyperlink ref="E253" r:id="rId158"/>
+    <hyperlink ref="C253" r:id="rId159"/>
+    <hyperlink ref="D253" r:id="rId160"/>
+    <hyperlink ref="G254" r:id="rId161"/>
+    <hyperlink ref="E254" r:id="rId162"/>
+    <hyperlink ref="C254" r:id="rId163"/>
+    <hyperlink ref="D254" r:id="rId164"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId157"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId165"/>
 </worksheet>
 </file>
 
@@ -54189,7 +54520,7 @@
         <v>4410</v>
       </c>
     </row>
-    <row r="241" spans="1:22" ht="22.5" customHeight="1">
+    <row r="241" spans="1:26" ht="22.5" customHeight="1">
       <c r="A241" s="13" t="str">
         <f>IF(games!A241="", "", games!A241)</f>
         <v>玩具對決</v>
@@ -54219,7 +54550,7 @@
         <v>4529</v>
       </c>
     </row>
-    <row r="242" spans="1:22" ht="22.5" customHeight="1">
+    <row r="242" spans="1:26" ht="22.5" customHeight="1">
       <c r="A242" s="13" t="str">
         <f>IF(games!A242="", "", games!A242)</f>
         <v>幸福都市：市長模擬器</v>
@@ -54249,7 +54580,7 @@
         <v>2640</v>
       </c>
     </row>
-    <row r="243" spans="1:22" ht="22.5" customHeight="1">
+    <row r="243" spans="1:26" ht="22.5" customHeight="1">
       <c r="A243" s="13" t="str">
         <f>IF(games!A243="", "", games!A243)</f>
         <v>黑道傳奇</v>
@@ -54279,7 +54610,7 @@
         <v>2640</v>
       </c>
     </row>
-    <row r="244" spans="1:22" ht="22.5" customHeight="1">
+    <row r="244" spans="1:26" ht="22.5" customHeight="1">
       <c r="A244" s="13" t="str">
         <f>IF(games!A244="", "", games!A244)</f>
         <v>The kingdom：medieval tales</v>
@@ -54309,7 +54640,7 @@
         <v>2640</v>
       </c>
     </row>
-    <row r="245" spans="1:22" ht="22.5" customHeight="1">
+    <row r="245" spans="1:26" ht="22.5" customHeight="1">
       <c r="A245" s="13" t="str">
         <f>IF(games!A245="", "", games!A245)</f>
         <v>七龍珠激震小隊</v>
@@ -54339,7 +54670,7 @@
         <v>4529</v>
       </c>
     </row>
-    <row r="246" spans="1:22" ht="22.5" customHeight="1">
+    <row r="246" spans="1:26" ht="22.5" customHeight="1">
       <c r="A246" s="13" t="str">
         <f>IF(games!A246="", "", games!A246)</f>
         <v>Grave Strikers</v>
@@ -54369,7 +54700,7 @@
         <v>4529</v>
       </c>
     </row>
-    <row r="247" spans="1:22" ht="22.5" customHeight="1">
+    <row r="247" spans="1:26" ht="22.5" customHeight="1">
       <c r="A247" s="13" t="str">
         <f>IF(games!A247="", "", games!A247)</f>
         <v>Stellar Sanctuary</v>
@@ -54405,7 +54736,7 @@
         <v>4529</v>
       </c>
     </row>
-    <row r="248" spans="1:22" ht="22.5" customHeight="1">
+    <row r="248" spans="1:26" ht="22.5" customHeight="1">
       <c r="A248" s="13" t="str">
         <f>IF(games!A248="", "", games!A248)</f>
         <v>古惑仔：風雲再起</v>
@@ -54453,7 +54784,7 @@
         <v>4515</v>
       </c>
     </row>
-    <row r="249" spans="1:22" ht="22.5" customHeight="1">
+    <row r="249" spans="1:26" ht="22.5" customHeight="1">
       <c r="A249" s="13" t="str">
         <f>IF(games!A249="", "", games!A249)</f>
         <v>女神秘令</v>
@@ -54483,7 +54814,7 @@
         <v>4631</v>
       </c>
     </row>
-    <row r="250" spans="1:22" ht="22.5" customHeight="1">
+    <row r="250" spans="1:26" ht="22.5" customHeight="1">
       <c r="A250" s="13" t="str">
         <f>IF(games!A250="", "", games!A250)</f>
         <v>Torerowa</v>
@@ -54522,7 +54853,7 @@
         <v>4529</v>
       </c>
     </row>
-    <row r="251" spans="1:22" ht="22.5" customHeight="1">
+    <row r="251" spans="1:26" ht="22.5" customHeight="1">
       <c r="A251" s="13" t="str">
         <f>IF(games!A251="", "", games!A251)</f>
         <v>Ricochet Squad</v>
@@ -54558,7 +54889,7 @@
         <v>4585</v>
       </c>
     </row>
-    <row r="252" spans="1:22" ht="22.5" customHeight="1">
+    <row r="252" spans="1:26" ht="22.5" customHeight="1">
       <c r="A252" s="13" t="str">
         <f>IF(games!A252="", "", games!A252)</f>
         <v>魔法村物語</v>
@@ -54624,43 +54955,121 @@
         <v>4640</v>
       </c>
     </row>
-    <row r="253" spans="1:22" ht="22.5" customHeight="1">
+    <row r="253" spans="1:26" ht="22.5" customHeight="1">
       <c r="A253" s="13" t="str">
         <f>IF(games!A253="", "", games!A253)</f>
-        <v/>
+        <v>奇蹟MU：騎士袋你飛</v>
       </c>
       <c r="C253" s="13" t="str">
         <f t="shared" ref="C253:C316" si="9">IF(A253="","", "giftcodesbanner/" &amp; A253 &amp; "-禮包碼.jpg")</f>
-        <v/>
+        <v>giftcodesbanner/奇蹟MU：騎士袋你飛-禮包碼.jpg</v>
       </c>
       <c r="D253" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/奇蹟MU：騎士袋你飛.html</v>
       </c>
       <c r="E253" s="14" t="str">
         <f>IF(games!I253&lt;&gt;"", games!I253, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="1:22" ht="22.5" customHeight="1">
+        <v>各位勇者們久等了！由韓國網禪 Webzen 正版授權的《奇蹟MU：騎士袋你飛》帶你重溫感動，再現經典紅龍裝、亞特蘭蒂斯、冰風谷等場景。這款放置系手遊讓你輕鬆掛機、自動練功，上班族也能秒速升級，隨時隨地享受奇蹟世界的樂趣！遊戲內建多元玩法，除了酷炫外觀和獨特技能，還有創新的 AI 系統，讓你體驗超脫傳統的奇蹟新世代。官方提供多組兌換碼及禮包碼，讓勇者們領取豐富虛寶，輕鬆起跑。此外，遊戲支持代儲值服務，提供玩家快速安全的儲值管道，讓你輕鬆擁有神裝，傲視全服！趕快加入，與戰盟夥伴們一起重返奇蹟大陸吧！</v>
+      </c>
+      <c r="F253" s="34" t="s">
+        <v>4667</v>
+      </c>
+      <c r="G253" s="13" t="s">
+        <v>4668</v>
+      </c>
+      <c r="H253" s="13" t="s">
+        <v>2625</v>
+      </c>
+      <c r="I253" s="13" t="s">
+        <v>4371</v>
+      </c>
+      <c r="K253" s="17" t="s">
+        <v>4649</v>
+      </c>
+      <c r="L253" s="13" t="s">
+        <v>4650</v>
+      </c>
+      <c r="M253" s="18" t="s">
+        <v>4651</v>
+      </c>
+      <c r="N253" s="13" t="s">
+        <v>4652</v>
+      </c>
+      <c r="O253" s="18" t="s">
+        <v>4653</v>
+      </c>
+      <c r="P253" s="13" t="s">
+        <v>4654</v>
+      </c>
+    </row>
+    <row r="254" spans="1:26" ht="22.5" customHeight="1">
       <c r="A254" s="13" t="str">
         <f>IF(games!A254="", "", games!A254)</f>
-        <v/>
+        <v>AUR3：影月幻域</v>
       </c>
       <c r="C254" s="13" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>giftcodesbanner/AUR3：影月幻域-禮包碼.jpg</v>
       </c>
       <c r="D254" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/AUR3：影月幻域.html</v>
       </c>
       <c r="E254" s="14" t="str">
         <f>IF(games!I254&lt;&gt;"", games!I254, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255" spans="1:22" ht="22.5" customHeight="1">
+        <v>準備好進入充滿奇幻冒險的異世界了嗎？《AUR3：影月幻域》是一款集結高自由度、精緻畫風與流暢戰鬥的MMORPG手遊。遊戲主打無鎖定戰鬥，結合華麗的技能特效與暢快的打擊感，讓你體驗最極致的戰鬥樂趣。在這片廣闊的幻想大陸上，你可以自由探索、結交夥伴，並與強大的怪物進行史詩級對決。為了回饋廣大玩家，官方準備了多組兌換碼與禮包碼，讓各位冒險者能迅速提升戰力。遊戲內也支援代儲值服務，提供快速安全的儲值通道，讓你在遊戲中無後顧之憂。現在就拿起你的武器，加入《AUR3：影月幻域》，譜寫屬於你的傳奇篇章！</v>
+      </c>
+      <c r="F254" s="34" t="s">
+        <v>4665</v>
+      </c>
+      <c r="G254" s="13" t="s">
+        <v>4666</v>
+      </c>
+      <c r="H254" s="13" t="s">
+        <v>2625</v>
+      </c>
+      <c r="I254" s="13" t="s">
+        <v>4371</v>
+      </c>
+      <c r="K254" s="17" t="s">
+        <v>4655</v>
+      </c>
+      <c r="M254" s="18" t="s">
+        <v>4656</v>
+      </c>
+      <c r="O254" s="18" t="s">
+        <v>4657</v>
+      </c>
+      <c r="Q254" s="18" t="s">
+        <v>4658</v>
+      </c>
+      <c r="S254" s="18" t="s">
+        <v>4659</v>
+      </c>
+      <c r="T254" s="13" t="s">
+        <v>4661</v>
+      </c>
+      <c r="U254" s="18" t="s">
+        <v>4660</v>
+      </c>
+      <c r="V254" s="13" t="s">
+        <v>4662</v>
+      </c>
+      <c r="W254" s="18" t="s">
+        <v>4583</v>
+      </c>
+      <c r="X254" s="13" t="s">
+        <v>4663</v>
+      </c>
+      <c r="Y254" s="18" t="s">
+        <v>1933</v>
+      </c>
+      <c r="Z254" s="13" t="s">
+        <v>4664</v>
+      </c>
+    </row>
+    <row r="255" spans="1:26" ht="22.5" customHeight="1">
       <c r="A255" s="13" t="str">
         <f>IF(games!A255="", "", games!A255)</f>
         <v/>
@@ -54674,7 +55083,7 @@
         <v/>
       </c>
     </row>
-    <row r="256" spans="1:22" ht="22.5" customHeight="1">
+    <row r="256" spans="1:26" ht="22.5" customHeight="1">
       <c r="A256" s="13" t="str">
         <f>IF(games!A256="", "", games!A256)</f>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6904" uniqueCount="4685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6951" uniqueCount="4724">
   <si>
     <t>Facebook</t>
   </si>
@@ -18054,6 +18054,157 @@
   </si>
   <si>
     <t>甄品4.99</t>
+  </si>
+  <si>
+    <t>aomage666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>aomage888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mageduel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VUSWEI3QHN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Next Agers</t>
+  </si>
+  <si>
+    <t>屍不可擋</t>
+  </si>
+  <si>
+    <t>RF ONLINE NEXT</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/id6747162052</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.cayenne.ms</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/UntitledMagicalGirl.TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://jm.wasabii.com.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/Leapsofcivilization</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61580336611412</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/RFONLINENEXTtc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.camelgames.loa&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/vn/app/next-agers/id6749529571</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.camelgames.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://discord.com/invite/RFJMXzqWaK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E5%B1%8D%E4%B8%8D%E5%8F%AF%E6%93%8B-hell-zombie/id6752315777?at=1010l3Vj&amp;ct=GNN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.myplayasia.hellzombie.tw&amp;referrer=utm_source%3Dgamer.com.tw%26utm_campaign%3Dgnn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>純潔的魔法少女</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rfonlinenextgb.netmarble.com/tc</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/rf-online-next/id6740848451</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.netmarble.rfnext</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《純潔的魔法少女》是一款充滿日系動漫風格的冒險 RPG，玩家將化身為魔法少女，與夥伴們一同踏上對抗魔王的旅程。遊戲主打高自由度的策略戰鬥，玩家可自由搭配技能與裝備，打造獨一無二的戰鬥風格。除了熱血的主線劇情，還有豐富的副本挑戰、PVP 對戰與社群互動玩法，讓你與其他魔法少女們一起享受戰鬥的樂趣。遊戲內也特別為玩家準備了各種兌換碼及禮包碼，讓你輕鬆獲得珍貴道具，快速提升戰力。此外，遊戲提供代儲值服務，安全又快速，讓你無後顧之憂地暢玩！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《Next Agers》是一款以末日廢土為背景的策略 RPG，融合了 Roguelike 元素，每一次探索都是全新的體驗。玩家將在滿目瘡痍的世界中，率領你的倖存者小隊，運用智慧與策略在險惡的環境中求生。遊戲畫面精緻，角色立繪充滿特色，搭配豐富的養成系統，讓你能自由培養出獨特的英雄陣容。為了協助玩家在這危機四伏的世界中生存，官方不定時釋出兌換碼及禮包碼，提供豐富的資源獎勵。若需快速補充戰力，遊戲也提供代儲值服務，安全又快速，讓你輕鬆應對各種挑戰。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《屍不可擋》是一款爽度破表的末日生存射擊手遊，玩家將身處殭屍橫行的世界，拿起各式槍械掃蕩成群的活屍。遊戲採用俯視角設計，操作簡單直覺，搭配上滿螢幕的殭屍與刺激的射擊音效，帶來前所未有的爽快感。除了殲滅活屍，遊戲也提供了豐富的裝備升級與技能樹系統，讓你能打造出最強的生存者。別忘了定期留意官方釋出的兌換碼與禮包碼，這些都是提升戰力的重要資源。同時，若想快速獲得物資，遊戲也提供代儲值服務，快速安全，讓你專注於生存與戰鬥。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《RF ONLINE NEXT》是一款 MMORPG 手遊，繼承了經典科幻 IP《RF Online》的世界觀，將三大種族的宏大戰爭重現於手機平台。遊戲以精緻的畫面與流暢的戰鬥，帶給玩家身歷其境的史詩級體驗。玩家可以選擇加入聯盟、貝爾托或克拉，為自己的種族榮耀而戰，並在廣闊的星球上探索未知的區域。遊戲中也為玩家準備了各種兌換碼與禮包碼，協助你快速成長。若想加速角色養成，官方也提供代儲值服務，快速安全，讓你輕鬆成為戰場上的主宰。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲內關卡挑戰賽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活動期間內，參加「體育館競技」對戰並累積積分，根據積分進行排名。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>第1名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>超商禮券 NT$1,500元</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>第2名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>第3～5名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>超商禮券 NT$1,000元</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>各得超商禮券 NT$500元</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>STAYALIVE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣x1000+膠囊x10+救援物資(篝火)x10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲內右上角選單「設定」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -36093,47 +36244,120 @@
         <v>74</v>
       </c>
     </row>
-    <row r="255" spans="1:31" ht="22.5" customHeight="1">
+    <row r="255" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A255" s="3" t="s">
+        <v>4705</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>4694</v>
+      </c>
+      <c r="D255" s="4" t="s">
+        <v>4695</v>
+      </c>
+      <c r="E255" s="4" t="s">
+        <v>4692</v>
+      </c>
       <c r="F255" s="41" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/純潔的魔法少女.html</v>
+      </c>
+      <c r="G255" s="4" t="s">
+        <v>4693</v>
       </c>
       <c r="H255" s="41" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="256" spans="1:31" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/純潔的魔法少女.html</v>
+      </c>
+      <c r="I255" s="42" t="s">
+        <v>4709</v>
+      </c>
+    </row>
+    <row r="256" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A256" s="71" t="s">
+        <v>4689</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>4696</v>
+      </c>
+      <c r="D256" s="4" t="s">
+        <v>4701</v>
+      </c>
+      <c r="E256" s="4" t="s">
+        <v>4700</v>
+      </c>
       <c r="F256" s="41" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Next Agers.html</v>
+      </c>
+      <c r="G256" s="4" t="s">
+        <v>4699</v>
       </c>
       <c r="H256" s="41" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="257" spans="6:8" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Next Agers.html</v>
+      </c>
+      <c r="I256" s="42" t="s">
+        <v>4710</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A257" s="71" t="s">
+        <v>4690</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>4697</v>
+      </c>
+      <c r="D257" s="4" t="s">
+        <v>4702</v>
+      </c>
+      <c r="E257" s="4" t="s">
+        <v>4703</v>
+      </c>
       <c r="F257" s="41" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/屍不可擋.html</v>
+      </c>
+      <c r="G257" s="4" t="s">
+        <v>4704</v>
       </c>
       <c r="H257" s="41" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="258" spans="6:8" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/屍不可擋.html</v>
+      </c>
+      <c r="I257" s="42" t="s">
+        <v>4711</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A258" s="71" t="s">
+        <v>4691</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>4698</v>
+      </c>
+      <c r="D258" s="41" t="s">
+        <v>4706</v>
+      </c>
+      <c r="E258" s="4" t="s">
+        <v>4707</v>
+      </c>
       <c r="F258" s="41" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/RF ONLINE NEXT.html</v>
+      </c>
+      <c r="G258" s="4" t="s">
+        <v>4708</v>
       </c>
       <c r="H258" s="41" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="6:8" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/RF ONLINE NEXT.html</v>
+      </c>
+      <c r="I258" s="42" t="s">
+        <v>4712</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A259" s="71"/>
       <c r="F259" s="41" t="str">
         <f t="shared" ref="F259:F269" si="10">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
         <v/>
@@ -36143,7 +36367,8 @@
         <v/>
       </c>
     </row>
-    <row r="260" spans="6:8" ht="22.5" customHeight="1">
+    <row r="260" spans="1:9" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A260" s="71"/>
       <c r="F260" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36153,7 +36378,7 @@
         <v/>
       </c>
     </row>
-    <row r="261" spans="6:8" ht="22.5" customHeight="1">
+    <row r="261" spans="1:9" ht="22.5" customHeight="1">
       <c r="F261" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36163,7 +36388,7 @@
         <v/>
       </c>
     </row>
-    <row r="262" spans="6:8" ht="22.5" customHeight="1">
+    <row r="262" spans="1:9" ht="22.5" customHeight="1">
       <c r="F262" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36173,7 +36398,7 @@
         <v/>
       </c>
     </row>
-    <row r="263" spans="6:8" ht="22.5" customHeight="1">
+    <row r="263" spans="1:9" ht="22.5" customHeight="1">
       <c r="F263" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36183,7 +36408,7 @@
         <v/>
       </c>
     </row>
-    <row r="264" spans="6:8" ht="22.5" customHeight="1">
+    <row r="264" spans="1:9" ht="22.5" customHeight="1">
       <c r="F264" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36193,7 +36418,7 @@
         <v/>
       </c>
     </row>
-    <row r="265" spans="6:8" ht="22.5" customHeight="1">
+    <row r="265" spans="1:9" ht="22.5" customHeight="1">
       <c r="F265" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36203,7 +36428,7 @@
         <v/>
       </c>
     </row>
-    <row r="266" spans="6:8" ht="22.5" customHeight="1">
+    <row r="266" spans="1:9" ht="22.5" customHeight="1">
       <c r="F266" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36213,7 +36438,7 @@
         <v/>
       </c>
     </row>
-    <row r="267" spans="6:8" ht="22.5" customHeight="1">
+    <row r="267" spans="1:9" ht="22.5" customHeight="1">
       <c r="F267" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36223,7 +36448,7 @@
         <v/>
       </c>
     </row>
-    <row r="268" spans="6:8" ht="22.5" customHeight="1">
+    <row r="268" spans="1:9" ht="22.5" customHeight="1">
       <c r="F268" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36233,7 +36458,7 @@
         <v/>
       </c>
     </row>
-    <row r="269" spans="6:8" ht="22.5" customHeight="1">
+    <row r="269" spans="1:9" ht="22.5" customHeight="1">
       <c r="F269" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36243,7 +36468,7 @@
         <v/>
       </c>
     </row>
-    <row r="270" spans="6:8" ht="22.5" customHeight="1">
+    <row r="270" spans="1:9" ht="22.5" customHeight="1">
       <c r="F270" s="40" t="str">
         <f t="shared" ref="F270:F316" si="12">IF(A270="", "", "gift-codes.html?game=" &amp; A270)</f>
         <v/>
@@ -36253,7 +36478,7 @@
         <v/>
       </c>
     </row>
-    <row r="271" spans="6:8" ht="22.5" customHeight="1">
+    <row r="271" spans="1:9" ht="22.5" customHeight="1">
       <c r="F271" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -36263,7 +36488,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" spans="6:8" ht="22.5" customHeight="1">
+    <row r="272" spans="1:9" ht="22.5" customHeight="1">
       <c r="F272" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -39807,9 +40032,23 @@
     <hyperlink ref="E254" r:id="rId162"/>
     <hyperlink ref="C254" r:id="rId163"/>
     <hyperlink ref="D254" r:id="rId164"/>
+    <hyperlink ref="E255" r:id="rId165"/>
+    <hyperlink ref="G255" r:id="rId166"/>
+    <hyperlink ref="C255" r:id="rId167"/>
+    <hyperlink ref="D255" r:id="rId168"/>
+    <hyperlink ref="C256" r:id="rId169"/>
+    <hyperlink ref="C257" r:id="rId170"/>
+    <hyperlink ref="C258" r:id="rId171"/>
+    <hyperlink ref="G256" r:id="rId172"/>
+    <hyperlink ref="E256" r:id="rId173"/>
+    <hyperlink ref="D256" r:id="rId174"/>
+    <hyperlink ref="D257" r:id="rId175"/>
+    <hyperlink ref="G257" r:id="rId176"/>
+    <hyperlink ref="E257" r:id="rId177"/>
+    <hyperlink ref="G258" r:id="rId178"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId165"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId179"/>
 </worksheet>
 </file>
 
@@ -54438,6 +54677,18 @@
       <c r="K238" s="97" t="s">
         <v>4554</v>
       </c>
+      <c r="M238" s="18" t="s">
+        <v>4685</v>
+      </c>
+      <c r="O238" s="18" t="s">
+        <v>4686</v>
+      </c>
+      <c r="Q238" s="18" t="s">
+        <v>4687</v>
+      </c>
+      <c r="S238" s="18" t="s">
+        <v>4688</v>
+      </c>
     </row>
     <row r="239" spans="1:47" ht="22.5" customHeight="1">
       <c r="A239" s="13" t="str">
@@ -54831,19 +55082,13 @@
         <f>IF(games!I250&lt;&gt;"", games!I250, "")</f>
         <v>《Torerowa》是一款奇幻風格的 MMORPG，以精緻的日系畫風與Q萌角色聞名。玩家將在廣闊的世界中冒險，體驗豐富的任務與劇情。遊戲提供多元職業選擇，每種職業都有獨特的技能樹與玩法，無論是PVE還是PVP，都能找到屬於自己的樂趣。此外，遊戲內還有釣魚、料理、採集等多樣生活技能，讓冒險旅程更加豐富有趣。想要輕鬆遊玩、享受自由探索的樂趣嗎？使用兌換碼與禮包碼即可獲得豐厚資源，選擇快速安全的代儲值服務，讓你輕鬆暢遊這片奇幻大陸！</v>
       </c>
-      <c r="F250" s="17" t="s">
-        <v>4539</v>
+      <c r="F250" s="13" t="s">
+        <v>4634</v>
       </c>
       <c r="G250" s="13" t="s">
-        <v>4529</v>
+        <v>4635</v>
       </c>
       <c r="H250" s="13" t="s">
-        <v>4634</v>
-      </c>
-      <c r="I250" s="13" t="s">
-        <v>4635</v>
-      </c>
-      <c r="J250" s="13" t="s">
         <v>4636</v>
       </c>
       <c r="K250" s="17" t="s">
@@ -55072,60 +55317,123 @@
     <row r="255" spans="1:26" ht="22.5" customHeight="1">
       <c r="A255" s="13" t="str">
         <f>IF(games!A255="", "", games!A255)</f>
-        <v/>
+        <v>純潔的魔法少女</v>
       </c>
       <c r="C255" s="13" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>giftcodesbanner/純潔的魔法少女-禮包碼.jpg</v>
       </c>
       <c r="D255" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/純潔的魔法少女.html</v>
+      </c>
+      <c r="F255" s="17" t="s">
+        <v>4713</v>
+      </c>
+      <c r="G255" s="13" t="s">
+        <v>4714</v>
+      </c>
+      <c r="K255" s="17" t="s">
+        <v>4715</v>
+      </c>
+      <c r="L255" s="13" t="s">
+        <v>4716</v>
+      </c>
+      <c r="M255" s="18" t="s">
+        <v>4717</v>
+      </c>
+      <c r="N255" s="13" t="s">
+        <v>4719</v>
+      </c>
+      <c r="O255" s="18" t="s">
+        <v>4718</v>
+      </c>
+      <c r="P255" s="13" t="s">
+        <v>4720</v>
       </c>
     </row>
     <row r="256" spans="1:26" ht="22.5" customHeight="1">
       <c r="A256" s="13" t="str">
         <f>IF(games!A256="", "", games!A256)</f>
-        <v/>
+        <v>Next Agers</v>
       </c>
       <c r="C256" s="13" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>giftcodesbanner/Next Agers-禮包碼.jpg</v>
       </c>
       <c r="D256" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="257" spans="1:4" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Next Agers.html</v>
+      </c>
+      <c r="F256" s="17" t="s">
+        <v>2640</v>
+      </c>
+      <c r="G256" s="13" t="s">
+        <v>2640</v>
+      </c>
+      <c r="K256" s="17" t="s">
+        <v>2640</v>
+      </c>
+      <c r="L256" s="13" t="s">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" ht="22.5" customHeight="1">
       <c r="A257" s="13" t="str">
         <f>IF(games!A257="", "", games!A257)</f>
-        <v/>
+        <v>屍不可擋</v>
       </c>
       <c r="C257" s="13" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>giftcodesbanner/屍不可擋-禮包碼.jpg</v>
       </c>
       <c r="D257" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="258" spans="1:4" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/屍不可擋.html</v>
+      </c>
+      <c r="F257" s="34" t="s">
+        <v>4723</v>
+      </c>
+      <c r="G257" s="13" t="s">
+        <v>2625</v>
+      </c>
+      <c r="H257" s="13" t="s">
+        <v>4371</v>
+      </c>
+      <c r="K257" s="17" t="s">
+        <v>4721</v>
+      </c>
+      <c r="L257" s="13" t="s">
+        <v>4722</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" ht="22.5" customHeight="1">
       <c r="A258" s="13" t="str">
         <f>IF(games!A258="", "", games!A258)</f>
-        <v/>
+        <v>RF ONLINE NEXT</v>
       </c>
       <c r="C258" s="13" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>giftcodesbanner/RF ONLINE NEXT-禮包碼.jpg</v>
       </c>
       <c r="D258" s="13" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="1:4">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/RF ONLINE NEXT.html</v>
+      </c>
+      <c r="F258" s="17" t="s">
+        <v>4539</v>
+      </c>
+      <c r="G258" s="13" t="s">
+        <v>4529</v>
+      </c>
+      <c r="K258" s="17" t="s">
+        <v>4539</v>
+      </c>
+      <c r="L258" s="13" t="s">
+        <v>4529</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12">
       <c r="A259" s="13" t="str">
         <f>IF(games!A259="", "", games!A259)</f>
         <v/>
@@ -55139,7 +55447,7 @@
         <v/>
       </c>
     </row>
-    <row r="260" spans="1:4">
+    <row r="260" spans="1:12">
       <c r="A260" s="13" t="str">
         <f>IF(games!A260="", "", games!A260)</f>
         <v/>
@@ -55153,7 +55461,7 @@
         <v/>
       </c>
     </row>
-    <row r="261" spans="1:4">
+    <row r="261" spans="1:12">
       <c r="A261" s="13" t="str">
         <f>IF(games!A261="", "", games!A261)</f>
         <v/>
@@ -55167,7 +55475,7 @@
         <v/>
       </c>
     </row>
-    <row r="262" spans="1:4">
+    <row r="262" spans="1:12">
       <c r="A262" s="13" t="str">
         <f>IF(games!A262="", "", games!A262)</f>
         <v/>
@@ -55181,7 +55489,7 @@
         <v/>
       </c>
     </row>
-    <row r="263" spans="1:4">
+    <row r="263" spans="1:12">
       <c r="A263" s="13" t="str">
         <f>IF(games!A263="", "", games!A263)</f>
         <v/>
@@ -55195,7 +55503,7 @@
         <v/>
       </c>
     </row>
-    <row r="264" spans="1:4">
+    <row r="264" spans="1:12">
       <c r="A264" s="13" t="str">
         <f>IF(games!A264="", "", games!A264)</f>
         <v/>
@@ -55209,7 +55517,7 @@
         <v/>
       </c>
     </row>
-    <row r="265" spans="1:4">
+    <row r="265" spans="1:12">
       <c r="A265" s="13" t="str">
         <f>IF(games!A265="", "", games!A265)</f>
         <v/>
@@ -55223,7 +55531,7 @@
         <v/>
       </c>
     </row>
-    <row r="266" spans="1:4">
+    <row r="266" spans="1:12">
       <c r="A266" s="13" t="str">
         <f>IF(games!A266="", "", games!A266)</f>
         <v/>
@@ -55237,7 +55545,7 @@
         <v/>
       </c>
     </row>
-    <row r="267" spans="1:4">
+    <row r="267" spans="1:12">
       <c r="A267" s="13" t="str">
         <f>IF(games!A267="", "", games!A267)</f>
         <v/>
@@ -55251,7 +55559,7 @@
         <v/>
       </c>
     </row>
-    <row r="268" spans="1:4">
+    <row r="268" spans="1:12">
       <c r="A268" s="13" t="str">
         <f>IF(games!A268="", "", games!A268)</f>
         <v/>
@@ -55265,7 +55573,7 @@
         <v/>
       </c>
     </row>
-    <row r="269" spans="1:4">
+    <row r="269" spans="1:12">
       <c r="A269" s="13" t="str">
         <f>IF(games!A269="", "", games!A269)</f>
         <v/>
@@ -55279,7 +55587,7 @@
         <v/>
       </c>
     </row>
-    <row r="270" spans="1:4">
+    <row r="270" spans="1:12">
       <c r="A270" s="13" t="str">
         <f>IF(games!A270="", "", games!A270)</f>
         <v/>
@@ -55293,7 +55601,7 @@
         <v/>
       </c>
     </row>
-    <row r="271" spans="1:4">
+    <row r="271" spans="1:12">
       <c r="A271" s="13" t="str">
         <f>IF(games!A271="", "", games!A271)</f>
         <v/>
@@ -55307,7 +55615,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" spans="1:4">
+    <row r="272" spans="1:12">
       <c r="A272" s="13" t="str">
         <f>IF(games!A272="", "", games!A272)</f>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6951" uniqueCount="4724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6994" uniqueCount="4752">
   <si>
     <t>Facebook</t>
   </si>
@@ -18204,6 +18204,94 @@
   </si>
   <si>
     <t>遊戲內右上角選單「設定」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>98700水晶</t>
+  </si>
+  <si>
+    <t>50700水晶</t>
+  </si>
+  <si>
+    <t>29700水晶</t>
+  </si>
+  <si>
+    <t>9900水晶</t>
+  </si>
+  <si>
+    <t>5100水晶</t>
+  </si>
+  <si>
+    <t>990水晶</t>
+  </si>
+  <si>
+    <t>閃耀通行證</t>
+  </si>
+  <si>
+    <t>禮包一條龍</t>
+  </si>
+  <si>
+    <t>7000寶石</t>
+  </si>
+  <si>
+    <t>3500寶石</t>
+  </si>
+  <si>
+    <t>1400寶石</t>
+  </si>
+  <si>
+    <t>610寶石</t>
+  </si>
+  <si>
+    <t>60寶石</t>
+  </si>
+  <si>
+    <t>1790禮包</t>
+  </si>
+  <si>
+    <t>48000寶石</t>
+  </si>
+  <si>
+    <t>25200寶石</t>
+  </si>
+  <si>
+    <t>15360寶石</t>
+  </si>
+  <si>
+    <t>6720寶石</t>
+  </si>
+  <si>
+    <t>2880寶石</t>
+  </si>
+  <si>
+    <t>600寶石</t>
+  </si>
+  <si>
+    <t>轉蛋加速包</t>
+  </si>
+  <si>
+    <t>轉蛋等級提升包</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E5%B0%91%E5%A5%B3%E6%8E%8C%E9%96%80%E4%BA%BA/id6748065669</t>
+  </si>
+  <si>
+    <t>https://www.ign-m.com/works/snackygirls_tw/</t>
+  </si>
+  <si>
+    <t>https://x.com/ignm_snackygirl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>少女掌門人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.ignm.girlowners&amp;hl=zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在《少女掌門人》中，您可以體驗直式畫面單手操作的便捷，無論通勤、上學或睡前都能隨時暢玩。遊戲採用全自動戰鬥系統，少女們將會自行施展華麗必殺技與技能擊敗敵人，讓您觀看也能享受爽快戰鬥的視覺盛宴。透過無限可能的戰略組合，打造專屬您的最強戰術，提升門派實力，橫掃魔物！為了讓掌門人能夠快速成長，遊戲內設有豐富的兌換碼與禮包碼福利，提供豐厚資源助您一臂之力。此外，遊戲也支援代儲值服務，確保玩家能以快速安全的方式獲得所需物品，讓您輕鬆培育美少女角色，打造最強隊伍！立即加入，開啟您的掌門人生涯，享受培育少女、稱霸武林的成就感！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -36271,6 +36359,48 @@
       <c r="I255" s="42" t="s">
         <v>4709</v>
       </c>
+      <c r="J255" s="1" t="s">
+        <v>4724</v>
+      </c>
+      <c r="K255" s="71">
+        <v>2555</v>
+      </c>
+      <c r="L255" s="1" t="s">
+        <v>4725</v>
+      </c>
+      <c r="M255" s="71">
+        <v>1331</v>
+      </c>
+      <c r="N255" s="1" t="s">
+        <v>4726</v>
+      </c>
+      <c r="O255" s="71">
+        <v>780</v>
+      </c>
+      <c r="P255" s="1" t="s">
+        <v>4727</v>
+      </c>
+      <c r="Q255" s="71">
+        <v>264</v>
+      </c>
+      <c r="R255" s="1" t="s">
+        <v>4728</v>
+      </c>
+      <c r="S255" s="71">
+        <v>145</v>
+      </c>
+      <c r="T255" s="1" t="s">
+        <v>4729</v>
+      </c>
+      <c r="U255" s="71">
+        <v>28</v>
+      </c>
+      <c r="V255" s="1" t="s">
+        <v>4730</v>
+      </c>
+      <c r="W255" s="71">
+        <v>216</v>
+      </c>
     </row>
     <row r="256" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A256" s="71" t="s">
@@ -36299,8 +36429,50 @@
       <c r="I256" s="42" t="s">
         <v>4710</v>
       </c>
-    </row>
-    <row r="257" spans="1:9" ht="22.5" customHeight="1" thickBot="1">
+      <c r="J256" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K256" s="71">
+        <v>2702</v>
+      </c>
+      <c r="L256" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M256" s="71">
+        <v>1370</v>
+      </c>
+      <c r="N256" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O256" s="71">
+        <v>559</v>
+      </c>
+      <c r="P256" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q256" s="71">
+        <v>280</v>
+      </c>
+      <c r="R256" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="S256" s="71">
+        <v>153</v>
+      </c>
+      <c r="T256" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="U256" s="71">
+        <v>30</v>
+      </c>
+      <c r="V256" s="1" t="s">
+        <v>4731</v>
+      </c>
+      <c r="W256" s="71">
+        <v>6095</v>
+      </c>
+    </row>
+    <row r="257" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A257" s="71" t="s">
         <v>4690</v>
       </c>
@@ -36327,8 +36499,68 @@
       <c r="I257" s="42" t="s">
         <v>4711</v>
       </c>
-    </row>
-    <row r="258" spans="1:9" ht="22.5" customHeight="1" thickBot="1">
+      <c r="J257" s="1" t="s">
+        <v>4732</v>
+      </c>
+      <c r="K257" s="71">
+        <v>2355</v>
+      </c>
+      <c r="L257" s="1" t="s">
+        <v>4733</v>
+      </c>
+      <c r="M257" s="71">
+        <v>1016</v>
+      </c>
+      <c r="N257" s="1" t="s">
+        <v>4734</v>
+      </c>
+      <c r="O257" s="71">
+        <v>551</v>
+      </c>
+      <c r="P257" s="1" t="s">
+        <v>4735</v>
+      </c>
+      <c r="Q257" s="71">
+        <v>256</v>
+      </c>
+      <c r="R257" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S257" s="71">
+        <v>128</v>
+      </c>
+      <c r="T257" s="1" t="s">
+        <v>4736</v>
+      </c>
+      <c r="U257" s="71">
+        <v>26</v>
+      </c>
+      <c r="V257" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="W257" s="71">
+        <v>1961</v>
+      </c>
+      <c r="X257" s="1" t="s">
+        <v>4737</v>
+      </c>
+      <c r="Y257" s="71">
+        <v>1410</v>
+      </c>
+      <c r="Z257" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA257" s="71">
+        <v>1016</v>
+      </c>
+      <c r="AB257" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AC257" s="71">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="258" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A258" s="71" t="s">
         <v>4691</v>
       </c>
@@ -36356,18 +36588,89 @@
         <v>4712</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A259" s="71"/>
+    <row r="259" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A259" s="70" t="s">
+        <v>4749</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>4748</v>
+      </c>
+      <c r="D259" s="41" t="s">
+        <v>4747</v>
+      </c>
+      <c r="E259" s="41" t="s">
+        <v>4746</v>
+      </c>
       <c r="F259" s="41" t="str">
         <f t="shared" ref="F259:F269" si="10">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/少女掌門人.html</v>
+      </c>
+      <c r="G259" s="4" t="s">
+        <v>4750</v>
       </c>
       <c r="H259" s="41" t="str">
         <f t="shared" ref="H259:H287" si="11">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260" spans="1:9" ht="22.5" customHeight="1" thickBot="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/少女掌門人.html</v>
+      </c>
+      <c r="I259" s="42" t="s">
+        <v>4751</v>
+      </c>
+      <c r="J259" s="1" t="s">
+        <v>4738</v>
+      </c>
+      <c r="K259" s="71">
+        <v>2048</v>
+      </c>
+      <c r="L259" s="1" t="s">
+        <v>4739</v>
+      </c>
+      <c r="M259" s="71">
+        <v>1181</v>
+      </c>
+      <c r="N259" s="1" t="s">
+        <v>4740</v>
+      </c>
+      <c r="O259" s="71">
+        <v>843</v>
+      </c>
+      <c r="P259" s="1" t="s">
+        <v>4741</v>
+      </c>
+      <c r="Q259" s="71">
+        <v>423</v>
+      </c>
+      <c r="R259" s="1" t="s">
+        <v>4742</v>
+      </c>
+      <c r="S259" s="71">
+        <v>216</v>
+      </c>
+      <c r="T259" s="1" t="s">
+        <v>4743</v>
+      </c>
+      <c r="U259" s="71">
+        <v>55</v>
+      </c>
+      <c r="V259" s="1" t="s">
+        <v>3577</v>
+      </c>
+      <c r="W259" s="71">
+        <v>630</v>
+      </c>
+      <c r="X259" s="1" t="s">
+        <v>4744</v>
+      </c>
+      <c r="Y259" s="71">
+        <v>439</v>
+      </c>
+      <c r="Z259" s="1" t="s">
+        <v>4745</v>
+      </c>
+      <c r="AA259" s="71">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="260" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A260" s="71"/>
       <c r="F260" s="41" t="str">
         <f t="shared" si="10"/>
@@ -36378,7 +36681,7 @@
         <v/>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="22.5" customHeight="1">
+    <row r="261" spans="1:29" ht="22.5" customHeight="1">
       <c r="F261" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36388,7 +36691,7 @@
         <v/>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="22.5" customHeight="1">
+    <row r="262" spans="1:29" ht="22.5" customHeight="1">
       <c r="F262" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36398,7 +36701,7 @@
         <v/>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="22.5" customHeight="1">
+    <row r="263" spans="1:29" ht="22.5" customHeight="1">
       <c r="F263" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36408,7 +36711,7 @@
         <v/>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="22.5" customHeight="1">
+    <row r="264" spans="1:29" ht="22.5" customHeight="1">
       <c r="F264" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36418,7 +36721,7 @@
         <v/>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="22.5" customHeight="1">
+    <row r="265" spans="1:29" ht="22.5" customHeight="1">
       <c r="F265" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36428,7 +36731,7 @@
         <v/>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="22.5" customHeight="1">
+    <row r="266" spans="1:29" ht="22.5" customHeight="1">
       <c r="F266" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36438,7 +36741,7 @@
         <v/>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="22.5" customHeight="1">
+    <row r="267" spans="1:29" ht="22.5" customHeight="1">
       <c r="F267" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36448,7 +36751,7 @@
         <v/>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="22.5" customHeight="1">
+    <row r="268" spans="1:29" ht="22.5" customHeight="1">
       <c r="F268" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36458,7 +36761,7 @@
         <v/>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="22.5" customHeight="1">
+    <row r="269" spans="1:29" ht="22.5" customHeight="1">
       <c r="F269" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36468,7 +36771,7 @@
         <v/>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="22.5" customHeight="1">
+    <row r="270" spans="1:29" ht="22.5" customHeight="1">
       <c r="F270" s="40" t="str">
         <f t="shared" ref="F270:F316" si="12">IF(A270="", "", "gift-codes.html?game=" &amp; A270)</f>
         <v/>
@@ -36478,7 +36781,7 @@
         <v/>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="22.5" customHeight="1">
+    <row r="271" spans="1:29" ht="22.5" customHeight="1">
       <c r="F271" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -36488,7 +36791,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="22.5" customHeight="1">
+    <row r="272" spans="1:29" ht="22.5" customHeight="1">
       <c r="F272" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -40046,9 +40349,11 @@
     <hyperlink ref="G257" r:id="rId176"/>
     <hyperlink ref="E257" r:id="rId177"/>
     <hyperlink ref="G258" r:id="rId178"/>
+    <hyperlink ref="C259" r:id="rId179"/>
+    <hyperlink ref="G259" r:id="rId180"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId179"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId181"/>
 </worksheet>
 </file>
 
@@ -55436,15 +55741,27 @@
     <row r="259" spans="1:12">
       <c r="A259" s="13" t="str">
         <f>IF(games!A259="", "", games!A259)</f>
-        <v/>
+        <v>少女掌門人</v>
       </c>
       <c r="C259" s="13" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>giftcodesbanner/少女掌門人-禮包碼.jpg</v>
       </c>
       <c r="D259" s="13" t="str">
         <f t="shared" ref="D259:D269" si="10">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/少女掌門人.html</v>
+      </c>
+      <c r="F259" s="17" t="s">
+        <v>4539</v>
+      </c>
+      <c r="G259" s="13" t="s">
+        <v>4529</v>
+      </c>
+      <c r="K259" s="17" t="s">
+        <v>4539</v>
+      </c>
+      <c r="L259" s="13" t="s">
+        <v>4529</v>
       </c>
     </row>
     <row r="260" spans="1:12">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6994" uniqueCount="4752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7002" uniqueCount="4760">
   <si>
     <t>Facebook</t>
   </si>
@@ -18292,6 +18292,38 @@
   </si>
   <si>
     <t>在《少女掌門人》中，您可以體驗直式畫面單手操作的便捷，無論通勤、上學或睡前都能隨時暢玩。遊戲採用全自動戰鬥系統，少女們將會自行施展華麗必殺技與技能擊敗敵人，讓您觀看也能享受爽快戰鬥的視覺盛宴。透過無限可能的戰略組合，打造專屬您的最強戰術，提升門派實力，橫掃魔物！為了讓掌門人能夠快速成長，遊戲內設有豐富的兌換碼與禮包碼福利，提供豐厚資源助您一臂之力。此外，遊戲也支援代儲值服務，確保玩家能以快速安全的方式獲得所需物品，讓您輕鬆培育美少女角色，打造最強隊伍！立即加入，開啟您的掌門人生涯，享受培育少女、稱霸武林的成就感！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sevenknightsforever</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HAPPYFULLMOON</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>稀有四星英雄x1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄召喚使用券x20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>week8888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thanks928</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f85gar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100fo25</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -54474,6 +54506,12 @@
       <c r="Y228" s="89" t="s">
         <v>2542</v>
       </c>
+      <c r="AA228" s="18" t="s">
+        <v>4756</v>
+      </c>
+      <c r="AC228" s="18" t="s">
+        <v>4757</v>
+      </c>
     </row>
     <row r="229" spans="1:47" ht="22.5" customHeight="1">
       <c r="A229" s="13" t="str">
@@ -54877,6 +54915,18 @@
       <c r="S236" s="89" t="s">
         <v>4472</v>
       </c>
+      <c r="U236" s="18" t="s">
+        <v>4752</v>
+      </c>
+      <c r="V236" s="13" t="s">
+        <v>4754</v>
+      </c>
+      <c r="W236" s="18" t="s">
+        <v>4753</v>
+      </c>
+      <c r="X236" s="13" t="s">
+        <v>4755</v>
+      </c>
     </row>
     <row r="237" spans="1:47" ht="22.5" customHeight="1">
       <c r="A237" s="13" t="str">
@@ -55503,6 +55553,12 @@
       </c>
       <c r="V252" s="13" t="s">
         <v>4640</v>
+      </c>
+      <c r="W252" s="18" t="s">
+        <v>4759</v>
+      </c>
+      <c r="Y252" s="18" t="s">
+        <v>4758</v>
       </c>
     </row>
     <row r="253" spans="1:26" ht="22.5" customHeight="1">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7002" uniqueCount="4760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7055" uniqueCount="4804">
   <si>
     <t>Facebook</t>
   </si>
@@ -18324,6 +18324,152 @@
   </si>
   <si>
     <t>100fo25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oniro ARPG</t>
+  </si>
+  <si>
+    <t>Legend of YMIR</t>
+  </si>
+  <si>
+    <t>7200鑽石</t>
+  </si>
+  <si>
+    <t>1600鑽石</t>
+  </si>
+  <si>
+    <t>720鑽石</t>
+  </si>
+  <si>
+    <t>109鑽石</t>
+  </si>
+  <si>
+    <t>RF通行賽季1</t>
+  </si>
+  <si>
+    <t>亞克的特權</t>
+  </si>
+  <si>
+    <t>每周召喚選擇包</t>
+  </si>
+  <si>
+    <t>每月召喚精選包</t>
+  </si>
+  <si>
+    <t>每月神器包</t>
+  </si>
+  <si>
+    <t>10000機器人美元</t>
+  </si>
+  <si>
+    <t>5000機器人美元</t>
+  </si>
+  <si>
+    <t>3000機器人美元</t>
+  </si>
+  <si>
+    <t>1500機器人美元</t>
+  </si>
+  <si>
+    <t>500機器人美元</t>
+  </si>
+  <si>
+    <t>100機器人美元</t>
+  </si>
+  <si>
+    <t>廣告通行證</t>
+  </si>
+  <si>
+    <t>綜合通行證</t>
+  </si>
+  <si>
+    <t>歡迎禮包</t>
+  </si>
+  <si>
+    <t>6300+4200水晶</t>
+  </si>
+  <si>
+    <t>3090+1260水晶</t>
+  </si>
+  <si>
+    <t>1545+330水晶</t>
+  </si>
+  <si>
+    <t>600+90水晶</t>
+  </si>
+  <si>
+    <t>300+15水晶</t>
+  </si>
+  <si>
+    <t>鍛造超值包</t>
+  </si>
+  <si>
+    <t>大量寶石禮包</t>
+  </si>
+  <si>
+    <t>200鑽石</t>
+  </si>
+  <si>
+    <t>https://wsafkduelists.wingedsakura.com/zh-tw/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/LegendofYMIRGL.tw</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.WINGEDSAKURAGAMES.WingedSakuraAFKDuelists&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.wemade.ymirglobal</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/winged-sakura-afk-duelists/id6742160449</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://wsafkduelists.wingedsakura.com/zh-tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>翼之櫻：放置決鬥者</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《Winged Sakura: AFK Duelists》是一款日系動漫風格的放置型RPG手遊，玩家將化身為「主人」，在現實結構撕裂的「無盡的夢」中，召喚強大的「靈」為榮譽而戰。遊戲主打佛系放置玩法，即使離線也能獲得被動收益，讓你不必再為農資源而苦惱。核心玩法圍繞著回合制自動戰鬥，玩家需要策略性地建立和客製化你的靈隊伍，透過升級、裝備強大的寶石和解鎖天賦來擊敗強大的Boss與其他主人。遊戲內也提供多樣的PVP與PVE模式，像是公會戰、競技場排名等。為了讓玩家能更輕鬆地享受遊戲，官方時常會發放最新的兌換碼與禮包碼，如果想快速提升戰力，尋求專業的代儲值服務也是個不錯的選擇，既快速又安全，讓你無後顧之憂地重建無盡的夢，成為最強的主人！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.Redeev.Oniro</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/oniroarpg?locale=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.redeev.com/oniro/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/us/app/oniro-arpg/id6746137443</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《Oniro ARPG》是一款超現實風格的動作角色扮演遊戲，玩家將潛入一個瀕臨崩潰的夢境世界，化身為甦醒的夢行者，對抗入侵的夢魘大軍。遊戲核心特色是其快節奏的戰鬥系統，玩家可以掌握多種夢境武器，施展強大的靈能，並透過獨特的「夢境印記」系統來客製化你的技能組合，打造出千變萬化的戰鬥風格。你將穿梭於破碎的記憶與扭曲的景觀之中，挑戰巨大的頭目，揭開夢境世界背後的秘密。隨著冒險的深入，你可以解鎖並升級更強大的裝備與能力。為了讓你的夢境之旅更加順暢，別忘了隨時留意官方可能發布的兌換碼及禮包碼。如果想在遊戲初期就建立優勢，尋找專業的代儲值服務會是個好選擇，享受快速安全的交易，讓你無懼任何惡夢，成為夢境的守護者！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/legend-of-ymir/id6748295875?at=1010l3Vj&amp;ct=GNN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.legendofymir.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《Legend of Ymir》是經典 IP《傳奇》系列的嶄新篇章，由 Wemade 採用頂級 Unreal Engine 5 引擎精心打造的次世代 MMORPG。遊戲世界觀植根於神秘的北歐神話，玩家將踏上廣袤的伊米爾大陸，親身體驗一場圍繞著世界樹的史詩級戰爭。本作完美繼承了《傳奇》系列最核心的 PVP 玩法，並將其提升至全新高度，實現了超越伺服器限制的大規模攻城戰。你的每一次戰鬥，都將影響世界的格局。遊戲不僅擁有令人驚嘆的畫面表現，更強調自由成長與激烈對抗。為了讓勇士們能迅速馳騁沙場，請務必關注官方發布的最新兌換碼與禮包碼，它們是前期成長的關鍵。若想在開戰時取得先機，一個快速安全的代儲值服務將是你的得力助手，助你戰力飆升，成為伊米爾大陸上無可撼動的傳奇！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -36504,7 +36650,7 @@
         <v>6095</v>
       </c>
     </row>
-    <row r="257" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+    <row r="257" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A257" s="71" t="s">
         <v>4690</v>
       </c>
@@ -36592,7 +36738,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="258" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+    <row r="258" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A258" s="71" t="s">
         <v>4691</v>
       </c>
@@ -36619,8 +36765,74 @@
       <c r="I258" s="42" t="s">
         <v>4712</v>
       </c>
-    </row>
-    <row r="259" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="J258" s="1" t="s">
+        <v>4762</v>
+      </c>
+      <c r="K258" s="71">
+        <v>1725</v>
+      </c>
+      <c r="L258" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="M258" s="71">
+        <v>937</v>
+      </c>
+      <c r="N258" s="1" t="s">
+        <v>4763</v>
+      </c>
+      <c r="O258" s="71">
+        <v>375</v>
+      </c>
+      <c r="P258" s="1" t="s">
+        <v>4764</v>
+      </c>
+      <c r="Q258" s="71">
+        <v>184</v>
+      </c>
+      <c r="R258" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="S258" s="71">
+        <v>85</v>
+      </c>
+      <c r="T258" s="1" t="s">
+        <v>4765</v>
+      </c>
+      <c r="U258" s="71">
+        <v>28</v>
+      </c>
+      <c r="V258" s="1" t="s">
+        <v>4766</v>
+      </c>
+      <c r="W258" s="71">
+        <v>583</v>
+      </c>
+      <c r="X258" s="1" t="s">
+        <v>4767</v>
+      </c>
+      <c r="Y258" s="71">
+        <v>145</v>
+      </c>
+      <c r="Z258" s="1" t="s">
+        <v>4768</v>
+      </c>
+      <c r="AA258" s="71">
+        <v>162</v>
+      </c>
+      <c r="AB258" s="1" t="s">
+        <v>4769</v>
+      </c>
+      <c r="AC258" s="71">
+        <v>1725</v>
+      </c>
+      <c r="AD258" s="1" t="s">
+        <v>4770</v>
+      </c>
+      <c r="AE258" s="71">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="259" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A259" s="70" t="s">
         <v>4749</v>
       </c>
@@ -36702,38 +36914,236 @@
         <v>630</v>
       </c>
     </row>
-    <row r="260" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A260" s="71"/>
+    <row r="260" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A260" s="70" t="s">
+        <v>4794</v>
+      </c>
+      <c r="C260" s="40" t="s">
+        <v>4788</v>
+      </c>
+      <c r="D260" s="5" t="s">
+        <v>4793</v>
+      </c>
+      <c r="E260" s="4" t="s">
+        <v>4792</v>
+      </c>
       <c r="F260" s="41" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/翼之櫻：放置決鬥者.html</v>
+      </c>
+      <c r="G260" s="4" t="s">
+        <v>4790</v>
       </c>
       <c r="H260" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="261" spans="1:29" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/翼之櫻：放置決鬥者.html</v>
+      </c>
+      <c r="I260" s="42" t="s">
+        <v>4795</v>
+      </c>
+      <c r="J260" s="1" t="s">
+        <v>4771</v>
+      </c>
+      <c r="K260" s="71">
+        <v>2355</v>
+      </c>
+      <c r="L260" s="1" t="s">
+        <v>4772</v>
+      </c>
+      <c r="M260" s="71">
+        <v>1173</v>
+      </c>
+      <c r="N260" s="1" t="s">
+        <v>4773</v>
+      </c>
+      <c r="O260" s="71">
+        <v>780</v>
+      </c>
+      <c r="P260" s="1" t="s">
+        <v>4774</v>
+      </c>
+      <c r="Q260" s="71">
+        <v>391</v>
+      </c>
+      <c r="R260" s="1" t="s">
+        <v>4775</v>
+      </c>
+      <c r="S260" s="71">
+        <v>128</v>
+      </c>
+      <c r="T260" s="1" t="s">
+        <v>4776</v>
+      </c>
+      <c r="U260" s="71">
+        <v>26</v>
+      </c>
+      <c r="V260" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="W260" s="71">
+        <v>128</v>
+      </c>
+      <c r="X260" s="1" t="s">
+        <v>4777</v>
+      </c>
+      <c r="Y260" s="71">
+        <v>77</v>
+      </c>
+      <c r="Z260" s="1" t="s">
+        <v>4778</v>
+      </c>
+      <c r="AA260" s="71">
+        <v>176</v>
+      </c>
+      <c r="AB260" s="1" t="s">
+        <v>4779</v>
+      </c>
+      <c r="AC260" s="71">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="261" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A261" s="71" t="s">
+        <v>4760</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>4797</v>
+      </c>
+      <c r="D261" s="4" t="s">
+        <v>4798</v>
+      </c>
+      <c r="E261" s="4" t="s">
+        <v>4799</v>
+      </c>
       <c r="F261" s="41" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Oniro ARPG.html</v>
+      </c>
+      <c r="G261" s="4" t="s">
+        <v>4796</v>
       </c>
       <c r="H261" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="1:29" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Oniro ARPG.html</v>
+      </c>
+      <c r="I261" s="42" t="s">
+        <v>4800</v>
+      </c>
+      <c r="J261" s="1" t="s">
+        <v>4780</v>
+      </c>
+      <c r="K261" s="71">
+        <v>1961</v>
+      </c>
+      <c r="L261" s="1" t="s">
+        <v>4781</v>
+      </c>
+      <c r="M261" s="71">
+        <v>1016</v>
+      </c>
+      <c r="N261" s="1" t="s">
+        <v>4782</v>
+      </c>
+      <c r="O261" s="71">
+        <v>551</v>
+      </c>
+      <c r="P261" s="1" t="s">
+        <v>4783</v>
+      </c>
+      <c r="Q261" s="71">
+        <v>232</v>
+      </c>
+      <c r="R261" s="1" t="s">
+        <v>4784</v>
+      </c>
+      <c r="S261" s="71">
+        <v>102</v>
+      </c>
+      <c r="T261" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="U261" s="71">
+        <v>26</v>
+      </c>
+      <c r="V261" s="1" t="s">
+        <v>4785</v>
+      </c>
+      <c r="W261" s="71">
+        <v>622</v>
+      </c>
+      <c r="X261" s="1" t="s">
+        <v>4786</v>
+      </c>
+      <c r="Y261" s="71">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="262" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A262" s="71" t="s">
+        <v>4761</v>
+      </c>
+      <c r="C262" s="40" t="s">
+        <v>4789</v>
+      </c>
+      <c r="D262" s="4" t="s">
+        <v>4802</v>
+      </c>
+      <c r="E262" s="4" t="s">
+        <v>4801</v>
+      </c>
       <c r="F262" s="41" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Legend of YMIR.html</v>
+      </c>
+      <c r="G262" s="4" t="s">
+        <v>4791</v>
       </c>
       <c r="H262" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="263" spans="1:29" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Legend of YMIR.html</v>
+      </c>
+      <c r="I262" s="42" t="s">
+        <v>4803</v>
+      </c>
+      <c r="J262" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="K262" s="71">
+        <v>2355</v>
+      </c>
+      <c r="L262" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M262" s="71">
+        <v>1173</v>
+      </c>
+      <c r="N262" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O262" s="71">
+        <v>780</v>
+      </c>
+      <c r="P262" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="Q262" s="71">
+        <v>256</v>
+      </c>
+      <c r="R262" s="1" t="s">
+        <v>4787</v>
+      </c>
+      <c r="S262" s="71">
+        <v>128</v>
+      </c>
+      <c r="T262" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="U262" s="71">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="263" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A263" s="71"/>
       <c r="F263" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36743,7 +37153,7 @@
         <v/>
       </c>
     </row>
-    <row r="264" spans="1:29" ht="22.5" customHeight="1">
+    <row r="264" spans="1:31" ht="22.5" customHeight="1">
       <c r="F264" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36753,7 +37163,7 @@
         <v/>
       </c>
     </row>
-    <row r="265" spans="1:29" ht="22.5" customHeight="1">
+    <row r="265" spans="1:31" ht="22.5" customHeight="1">
       <c r="F265" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36763,7 +37173,7 @@
         <v/>
       </c>
     </row>
-    <row r="266" spans="1:29" ht="22.5" customHeight="1">
+    <row r="266" spans="1:31" ht="22.5" customHeight="1">
       <c r="F266" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36773,7 +37183,7 @@
         <v/>
       </c>
     </row>
-    <row r="267" spans="1:29" ht="22.5" customHeight="1">
+    <row r="267" spans="1:31" ht="22.5" customHeight="1">
       <c r="F267" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36783,7 +37193,7 @@
         <v/>
       </c>
     </row>
-    <row r="268" spans="1:29" ht="22.5" customHeight="1">
+    <row r="268" spans="1:31" ht="22.5" customHeight="1">
       <c r="F268" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36793,7 +37203,7 @@
         <v/>
       </c>
     </row>
-    <row r="269" spans="1:29" ht="22.5" customHeight="1">
+    <row r="269" spans="1:31" ht="22.5" customHeight="1">
       <c r="F269" s="41" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -36803,7 +37213,7 @@
         <v/>
       </c>
     </row>
-    <row r="270" spans="1:29" ht="22.5" customHeight="1">
+    <row r="270" spans="1:31" ht="22.5" customHeight="1">
       <c r="F270" s="40" t="str">
         <f t="shared" ref="F270:F316" si="12">IF(A270="", "", "gift-codes.html?game=" &amp; A270)</f>
         <v/>
@@ -36813,7 +37223,7 @@
         <v/>
       </c>
     </row>
-    <row r="271" spans="1:29" ht="22.5" customHeight="1">
+    <row r="271" spans="1:31" ht="22.5" customHeight="1">
       <c r="F271" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -36823,7 +37233,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" spans="1:29" ht="22.5" customHeight="1">
+    <row r="272" spans="1:31" ht="22.5" customHeight="1">
       <c r="F272" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -40383,9 +40793,19 @@
     <hyperlink ref="G258" r:id="rId178"/>
     <hyperlink ref="C259" r:id="rId179"/>
     <hyperlink ref="G259" r:id="rId180"/>
+    <hyperlink ref="G260" r:id="rId181"/>
+    <hyperlink ref="G261" r:id="rId182"/>
+    <hyperlink ref="G262" r:id="rId183"/>
+    <hyperlink ref="E260" r:id="rId184"/>
+    <hyperlink ref="D260" r:id="rId185"/>
+    <hyperlink ref="C261" r:id="rId186"/>
+    <hyperlink ref="D261" r:id="rId187"/>
+    <hyperlink ref="E261" r:id="rId188"/>
+    <hyperlink ref="E262" r:id="rId189"/>
+    <hyperlink ref="D262" r:id="rId190"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId181"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId191"/>
 </worksheet>
 </file>
 
@@ -55688,6 +56108,10 @@
         <f t="shared" si="8"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/純潔的魔法少女.html</v>
       </c>
+      <c r="E255" s="14" t="str">
+        <f>IF(games!I255&lt;&gt;"", games!I255, "")</f>
+        <v>《純潔的魔法少女》是一款充滿日系動漫風格的冒險 RPG，玩家將化身為魔法少女，與夥伴們一同踏上對抗魔王的旅程。遊戲主打高自由度的策略戰鬥，玩家可自由搭配技能與裝備，打造獨一無二的戰鬥風格。除了熱血的主線劇情，還有豐富的副本挑戰、PVP 對戰與社群互動玩法，讓你與其他魔法少女們一起享受戰鬥的樂趣。遊戲內也特別為玩家準備了各種兌換碼及禮包碼，讓你輕鬆獲得珍貴道具，快速提升戰力。此外，遊戲提供代儲值服務，安全又快速，讓你無後顧之憂地暢玩！</v>
+      </c>
       <c r="F255" s="17" t="s">
         <v>4713</v>
       </c>
@@ -55726,6 +56150,10 @@
         <f t="shared" si="8"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Next Agers.html</v>
       </c>
+      <c r="E256" s="14" t="str">
+        <f>IF(games!I256&lt;&gt;"", games!I256, "")</f>
+        <v>《Next Agers》是一款以末日廢土為背景的策略 RPG，融合了 Roguelike 元素，每一次探索都是全新的體驗。玩家將在滿目瘡痍的世界中，率領你的倖存者小隊，運用智慧與策略在險惡的環境中求生。遊戲畫面精緻，角色立繪充滿特色，搭配豐富的養成系統，讓你能自由培養出獨特的英雄陣容。為了協助玩家在這危機四伏的世界中生存，官方不定時釋出兌換碼及禮包碼，提供豐富的資源獎勵。若需快速補充戰力，遊戲也提供代儲值服務，安全又快速，讓你輕鬆應對各種挑戰。</v>
+      </c>
       <c r="F256" s="17" t="s">
         <v>2640</v>
       </c>
@@ -55752,6 +56180,10 @@
         <f t="shared" si="8"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/屍不可擋.html</v>
       </c>
+      <c r="E257" s="14" t="str">
+        <f>IF(games!I257&lt;&gt;"", games!I257, "")</f>
+        <v>《屍不可擋》是一款爽度破表的末日生存射擊手遊，玩家將身處殭屍橫行的世界，拿起各式槍械掃蕩成群的活屍。遊戲採用俯視角設計，操作簡單直覺，搭配上滿螢幕的殭屍與刺激的射擊音效，帶來前所未有的爽快感。除了殲滅活屍，遊戲也提供了豐富的裝備升級與技能樹系統，讓你能打造出最強的生存者。別忘了定期留意官方釋出的兌換碼與禮包碼，這些都是提升戰力的重要資源。同時，若想快速獲得物資，遊戲也提供代儲值服務，快速安全，讓你專注於生存與戰鬥。</v>
+      </c>
       <c r="F257" s="34" t="s">
         <v>4723</v>
       </c>
@@ -55781,6 +56213,10 @@
         <f t="shared" si="8"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/RF ONLINE NEXT.html</v>
       </c>
+      <c r="E258" s="14" t="str">
+        <f>IF(games!I258&lt;&gt;"", games!I258, "")</f>
+        <v>《RF ONLINE NEXT》是一款 MMORPG 手遊，繼承了經典科幻 IP《RF Online》的世界觀，將三大種族的宏大戰爭重現於手機平台。遊戲以精緻的畫面與流暢的戰鬥，帶給玩家身歷其境的史詩級體驗。玩家可以選擇加入聯盟、貝爾托或克拉，為自己的種族榮耀而戰，並在廣闊的星球上探索未知的區域。遊戲中也為玩家準備了各種兌換碼與禮包碼，協助你快速成長。若想加速角色養成，官方也提供代儲值服務，快速安全，讓你輕鬆成為戰場上的主宰。</v>
+      </c>
       <c r="F258" s="17" t="s">
         <v>4539</v>
       </c>
@@ -55807,6 +56243,10 @@
         <f t="shared" ref="D259:D269" si="10">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/少女掌門人.html</v>
       </c>
+      <c r="E259" s="14" t="str">
+        <f>IF(games!I259&lt;&gt;"", games!I259, "")</f>
+        <v>在《少女掌門人》中，您可以體驗直式畫面單手操作的便捷，無論通勤、上學或睡前都能隨時暢玩。遊戲採用全自動戰鬥系統，少女們將會自行施展華麗必殺技與技能擊敗敵人，讓您觀看也能享受爽快戰鬥的視覺盛宴。透過無限可能的戰略組合，打造專屬您的最強戰術，提升門派實力，橫掃魔物！為了讓掌門人能夠快速成長，遊戲內設有豐富的兌換碼與禮包碼福利，提供豐厚資源助您一臂之力。此外，遊戲也支援代儲值服務，確保玩家能以快速安全的方式獲得所需物品，讓您輕鬆培育美少女角色，打造最強隊伍！立即加入，開啟您的掌門人生涯，享受培育少女、稱霸武林的成就感！</v>
+      </c>
       <c r="F259" s="17" t="s">
         <v>4539</v>
       </c>
@@ -55823,43 +56263,55 @@
     <row r="260" spans="1:12">
       <c r="A260" s="13" t="str">
         <f>IF(games!A260="", "", games!A260)</f>
-        <v/>
+        <v>翼之櫻：放置決鬥者</v>
       </c>
       <c r="C260" s="13" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>giftcodesbanner/翼之櫻：放置決鬥者-禮包碼.jpg</v>
       </c>
       <c r="D260" s="13" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/翼之櫻：放置決鬥者.html</v>
+      </c>
+      <c r="E260" s="14" t="str">
+        <f>IF(games!I260&lt;&gt;"", games!I260, "")</f>
+        <v>《Winged Sakura: AFK Duelists》是一款日系動漫風格的放置型RPG手遊，玩家將化身為「主人」，在現實結構撕裂的「無盡的夢」中，召喚強大的「靈」為榮譽而戰。遊戲主打佛系放置玩法，即使離線也能獲得被動收益，讓你不必再為農資源而苦惱。核心玩法圍繞著回合制自動戰鬥，玩家需要策略性地建立和客製化你的靈隊伍，透過升級、裝備強大的寶石和解鎖天賦來擊敗強大的Boss與其他主人。遊戲內也提供多樣的PVP與PVE模式，像是公會戰、競技場排名等。為了讓玩家能更輕鬆地享受遊戲，官方時常會發放最新的兌換碼與禮包碼，如果想快速提升戰力，尋求專業的代儲值服務也是個不錯的選擇，既快速又安全，讓你無後顧之憂地重建無盡的夢，成為最強的主人！</v>
       </c>
     </row>
     <row r="261" spans="1:12">
       <c r="A261" s="13" t="str">
         <f>IF(games!A261="", "", games!A261)</f>
-        <v/>
+        <v>Oniro ARPG</v>
       </c>
       <c r="C261" s="13" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>giftcodesbanner/Oniro ARPG-禮包碼.jpg</v>
       </c>
       <c r="D261" s="13" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Oniro ARPG.html</v>
+      </c>
+      <c r="E261" s="14" t="str">
+        <f>IF(games!I261&lt;&gt;"", games!I261, "")</f>
+        <v>《Oniro ARPG》是一款超現實風格的動作角色扮演遊戲，玩家將潛入一個瀕臨崩潰的夢境世界，化身為甦醒的夢行者，對抗入侵的夢魘大軍。遊戲核心特色是其快節奏的戰鬥系統，玩家可以掌握多種夢境武器，施展強大的靈能，並透過獨特的「夢境印記」系統來客製化你的技能組合，打造出千變萬化的戰鬥風格。你將穿梭於破碎的記憶與扭曲的景觀之中，挑戰巨大的頭目，揭開夢境世界背後的秘密。隨著冒險的深入，你可以解鎖並升級更強大的裝備與能力。為了讓你的夢境之旅更加順暢，別忘了隨時留意官方可能發布的兌換碼及禮包碼。如果想在遊戲初期就建立優勢，尋找專業的代儲值服務會是個好選擇，享受快速安全的交易，讓你無懼任何惡夢，成為夢境的守護者！</v>
       </c>
     </row>
     <row r="262" spans="1:12">
       <c r="A262" s="13" t="str">
         <f>IF(games!A262="", "", games!A262)</f>
-        <v/>
+        <v>Legend of YMIR</v>
       </c>
       <c r="C262" s="13" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>giftcodesbanner/Legend of YMIR-禮包碼.jpg</v>
       </c>
       <c r="D262" s="13" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Legend of YMIR.html</v>
+      </c>
+      <c r="E262" s="14" t="str">
+        <f>IF(games!I262&lt;&gt;"", games!I262, "")</f>
+        <v>《Legend of Ymir》是經典 IP《傳奇》系列的嶄新篇章，由 Wemade 採用頂級 Unreal Engine 5 引擎精心打造的次世代 MMORPG。遊戲世界觀植根於神秘的北歐神話，玩家將踏上廣袤的伊米爾大陸，親身體驗一場圍繞著世界樹的史詩級戰爭。本作完美繼承了《傳奇》系列最核心的 PVP 玩法，並將其提升至全新高度，實現了超越伺服器限制的大規模攻城戰。你的每一次戰鬥，都將影響世界的格局。遊戲不僅擁有令人驚嘆的畫面表現，更強調自由成長與激烈對抗。為了讓勇士們能迅速馳騁沙場，請務必關注官方發布的最新兌換碼與禮包碼，它們是前期成長的關鍵。若想在開戰時取得先機，一個快速安全的代儲值服務將是你的得力助手，助你戰力飆升，成為伊米爾大陸上無可撼動的傳奇！</v>
       </c>
     </row>
     <row r="263" spans="1:12">
@@ -55875,6 +56327,10 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
+      <c r="E263" s="14" t="str">
+        <f>IF(games!I263&lt;&gt;"", games!I263, "")</f>
+        <v/>
+      </c>
     </row>
     <row r="264" spans="1:12">
       <c r="A264" s="13" t="str">
@@ -55889,6 +56345,10 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
+      <c r="E264" s="14" t="str">
+        <f>IF(games!I264&lt;&gt;"", games!I264, "")</f>
+        <v/>
+      </c>
     </row>
     <row r="265" spans="1:12">
       <c r="A265" s="13" t="str">
@@ -55903,6 +56363,10 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
+      <c r="E265" s="14" t="str">
+        <f>IF(games!I265&lt;&gt;"", games!I265, "")</f>
+        <v/>
+      </c>
     </row>
     <row r="266" spans="1:12">
       <c r="A266" s="13" t="str">
@@ -55917,6 +56381,10 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
+      <c r="E266" s="14" t="str">
+        <f>IF(games!I266&lt;&gt;"", games!I266, "")</f>
+        <v/>
+      </c>
     </row>
     <row r="267" spans="1:12">
       <c r="A267" s="13" t="str">
@@ -55931,6 +56399,10 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
+      <c r="E267" s="14" t="str">
+        <f>IF(games!I267&lt;&gt;"", games!I267, "")</f>
+        <v/>
+      </c>
     </row>
     <row r="268" spans="1:12">
       <c r="A268" s="13" t="str">
@@ -55945,6 +56417,10 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
+      <c r="E268" s="14" t="str">
+        <f>IF(games!I268&lt;&gt;"", games!I268, "")</f>
+        <v/>
+      </c>
     </row>
     <row r="269" spans="1:12">
       <c r="A269" s="13" t="str">
@@ -55959,6 +56435,10 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
+      <c r="E269" s="14" t="str">
+        <f>IF(games!I269&lt;&gt;"", games!I269, "")</f>
+        <v/>
+      </c>
     </row>
     <row r="270" spans="1:12">
       <c r="A270" s="13" t="str">
@@ -55973,6 +56453,10 @@
         <f t="shared" ref="D270:D316" si="11">IF(A270="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A270)</f>
         <v/>
       </c>
+      <c r="E270" s="14" t="str">
+        <f>IF(games!I270&lt;&gt;"", games!I270, "")</f>
+        <v/>
+      </c>
     </row>
     <row r="271" spans="1:12">
       <c r="A271" s="13" t="str">
@@ -55987,6 +56471,10 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
+      <c r="E271" s="14" t="str">
+        <f>IF(games!I271&lt;&gt;"", games!I271, "")</f>
+        <v/>
+      </c>
     </row>
     <row r="272" spans="1:12">
       <c r="A272" s="13" t="str">
@@ -56001,8 +56489,12 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-    </row>
-    <row r="273" spans="1:4">
+      <c r="E272" s="14" t="str">
+        <f>IF(games!I272&lt;&gt;"", games!I272, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
       <c r="A273" s="13" t="str">
         <f>IF(games!A273="", "", games!A273)</f>
         <v/>
@@ -56015,8 +56507,12 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-    </row>
-    <row r="274" spans="1:4">
+      <c r="E273" s="14" t="str">
+        <f>IF(games!I273&lt;&gt;"", games!I273, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
       <c r="A274" s="13" t="str">
         <f>IF(games!A274="", "", games!A274)</f>
         <v/>
@@ -56029,8 +56525,12 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-    </row>
-    <row r="275" spans="1:4">
+      <c r="E274" s="14" t="str">
+        <f>IF(games!I274&lt;&gt;"", games!I274, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
       <c r="A275" s="13" t="str">
         <f>IF(games!A275="", "", games!A275)</f>
         <v/>
@@ -56043,8 +56543,12 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-    </row>
-    <row r="276" spans="1:4">
+      <c r="E275" s="14" t="str">
+        <f>IF(games!I275&lt;&gt;"", games!I275, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
       <c r="A276" s="13" t="str">
         <f>IF(games!A276="", "", games!A276)</f>
         <v/>
@@ -56058,7 +56562,7 @@
         <v/>
       </c>
     </row>
-    <row r="277" spans="1:4">
+    <row r="277" spans="1:5">
       <c r="A277" s="13" t="str">
         <f>IF(games!A277="", "", games!A277)</f>
         <v/>
@@ -56072,7 +56576,7 @@
         <v/>
       </c>
     </row>
-    <row r="278" spans="1:4">
+    <row r="278" spans="1:5">
       <c r="A278" s="13" t="str">
         <f>IF(games!A278="", "", games!A278)</f>
         <v/>
@@ -56086,7 +56590,7 @@
         <v/>
       </c>
     </row>
-    <row r="279" spans="1:4">
+    <row r="279" spans="1:5">
       <c r="A279" s="13" t="str">
         <f>IF(games!A279="", "", games!A279)</f>
         <v/>
@@ -56100,7 +56604,7 @@
         <v/>
       </c>
     </row>
-    <row r="280" spans="1:4">
+    <row r="280" spans="1:5">
       <c r="A280" s="13" t="str">
         <f>IF(games!A280="", "", games!A280)</f>
         <v/>
@@ -56114,7 +56618,7 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="1:4">
+    <row r="281" spans="1:5">
       <c r="A281" s="13" t="str">
         <f>IF(games!A281="", "", games!A281)</f>
         <v/>
@@ -56128,7 +56632,7 @@
         <v/>
       </c>
     </row>
-    <row r="282" spans="1:4">
+    <row r="282" spans="1:5">
       <c r="A282" s="13" t="str">
         <f>IF(games!A282="", "", games!A282)</f>
         <v/>
@@ -56142,7 +56646,7 @@
         <v/>
       </c>
     </row>
-    <row r="283" spans="1:4">
+    <row r="283" spans="1:5">
       <c r="A283" s="13" t="str">
         <f>IF(games!A283="", "", games!A283)</f>
         <v/>
@@ -56156,7 +56660,7 @@
         <v/>
       </c>
     </row>
-    <row r="284" spans="1:4">
+    <row r="284" spans="1:5">
       <c r="A284" s="13" t="str">
         <f>IF(games!A284="", "", games!A284)</f>
         <v/>
@@ -56170,7 +56674,7 @@
         <v/>
       </c>
     </row>
-    <row r="285" spans="1:4">
+    <row r="285" spans="1:5">
       <c r="A285" s="13" t="str">
         <f>IF(games!A285="", "", games!A285)</f>
         <v/>
@@ -56184,7 +56688,7 @@
         <v/>
       </c>
     </row>
-    <row r="286" spans="1:4">
+    <row r="286" spans="1:5">
       <c r="A286" s="13" t="str">
         <f>IF(games!A286="", "", games!A286)</f>
         <v/>
@@ -56198,7 +56702,7 @@
         <v/>
       </c>
     </row>
-    <row r="287" spans="1:4">
+    <row r="287" spans="1:5">
       <c r="A287" s="13" t="str">
         <f>IF(games!A287="", "", games!A287)</f>
         <v/>
@@ -56212,7 +56716,7 @@
         <v/>
       </c>
     </row>
-    <row r="288" spans="1:4">
+    <row r="288" spans="1:5">
       <c r="A288" s="13" t="str">
         <f>IF(games!A288="", "", games!A288)</f>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7055" uniqueCount="4804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7067" uniqueCount="4804">
   <si>
     <t>Facebook</t>
   </si>
@@ -56277,6 +56277,18 @@
         <f>IF(games!I260&lt;&gt;"", games!I260, "")</f>
         <v>《Winged Sakura: AFK Duelists》是一款日系動漫風格的放置型RPG手遊，玩家將化身為「主人」，在現實結構撕裂的「無盡的夢」中，召喚強大的「靈」為榮譽而戰。遊戲主打佛系放置玩法，即使離線也能獲得被動收益，讓你不必再為農資源而苦惱。核心玩法圍繞著回合制自動戰鬥，玩家需要策略性地建立和客製化你的靈隊伍，透過升級、裝備強大的寶石和解鎖天賦來擊敗強大的Boss與其他主人。遊戲內也提供多樣的PVP與PVE模式，像是公會戰、競技場排名等。為了讓玩家能更輕鬆地享受遊戲，官方時常會發放最新的兌換碼與禮包碼，如果想快速提升戰力，尋求專業的代儲值服務也是個不錯的選擇，既快速又安全，讓你無後顧之憂地重建無盡的夢，成為最強的主人！</v>
       </c>
+      <c r="F260" s="17" t="s">
+        <v>4539</v>
+      </c>
+      <c r="G260" s="13" t="s">
+        <v>4529</v>
+      </c>
+      <c r="K260" s="17" t="s">
+        <v>4539</v>
+      </c>
+      <c r="L260" s="13" t="s">
+        <v>4529</v>
+      </c>
     </row>
     <row r="261" spans="1:12">
       <c r="A261" s="13" t="str">
@@ -56295,6 +56307,18 @@
         <f>IF(games!I261&lt;&gt;"", games!I261, "")</f>
         <v>《Oniro ARPG》是一款超現實風格的動作角色扮演遊戲，玩家將潛入一個瀕臨崩潰的夢境世界，化身為甦醒的夢行者，對抗入侵的夢魘大軍。遊戲核心特色是其快節奏的戰鬥系統，玩家可以掌握多種夢境武器，施展強大的靈能，並透過獨特的「夢境印記」系統來客製化你的技能組合，打造出千變萬化的戰鬥風格。你將穿梭於破碎的記憶與扭曲的景觀之中，挑戰巨大的頭目，揭開夢境世界背後的秘密。隨著冒險的深入，你可以解鎖並升級更強大的裝備與能力。為了讓你的夢境之旅更加順暢，別忘了隨時留意官方可能發布的兌換碼及禮包碼。如果想在遊戲初期就建立優勢，尋找專業的代儲值服務會是個好選擇，享受快速安全的交易，讓你無懼任何惡夢，成為夢境的守護者！</v>
       </c>
+      <c r="F261" s="17" t="s">
+        <v>4539</v>
+      </c>
+      <c r="G261" s="13" t="s">
+        <v>4529</v>
+      </c>
+      <c r="K261" s="17" t="s">
+        <v>4539</v>
+      </c>
+      <c r="L261" s="13" t="s">
+        <v>4529</v>
+      </c>
     </row>
     <row r="262" spans="1:12">
       <c r="A262" s="13" t="str">
@@ -56312,6 +56336,18 @@
       <c r="E262" s="14" t="str">
         <f>IF(games!I262&lt;&gt;"", games!I262, "")</f>
         <v>《Legend of Ymir》是經典 IP《傳奇》系列的嶄新篇章，由 Wemade 採用頂級 Unreal Engine 5 引擎精心打造的次世代 MMORPG。遊戲世界觀植根於神秘的北歐神話，玩家將踏上廣袤的伊米爾大陸，親身體驗一場圍繞著世界樹的史詩級戰爭。本作完美繼承了《傳奇》系列最核心的 PVP 玩法，並將其提升至全新高度，實現了超越伺服器限制的大規模攻城戰。你的每一次戰鬥，都將影響世界的格局。遊戲不僅擁有令人驚嘆的畫面表現，更強調自由成長與激烈對抗。為了讓勇士們能迅速馳騁沙場，請務必關注官方發布的最新兌換碼與禮包碼，它們是前期成長的關鍵。若想在開戰時取得先機，一個快速安全的代儲值服務將是你的得力助手，助你戰力飆升，成為伊米爾大陸上無可撼動的傳奇！</v>
+      </c>
+      <c r="F262" s="17" t="s">
+        <v>4539</v>
+      </c>
+      <c r="G262" s="13" t="s">
+        <v>4529</v>
+      </c>
+      <c r="K262" s="17" t="s">
+        <v>4539</v>
+      </c>
+      <c r="L262" s="13" t="s">
+        <v>4529</v>
       </c>
     </row>
     <row r="263" spans="1:12">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -18437,10 +18437,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>《Winged Sakura: AFK Duelists》是一款日系動漫風格的放置型RPG手遊，玩家將化身為「主人」，在現實結構撕裂的「無盡的夢」中，召喚強大的「靈」為榮譽而戰。遊戲主打佛系放置玩法，即使離線也能獲得被動收益，讓你不必再為農資源而苦惱。核心玩法圍繞著回合制自動戰鬥，玩家需要策略性地建立和客製化你的靈隊伍，透過升級、裝備強大的寶石和解鎖天賦來擊敗強大的Boss與其他主人。遊戲內也提供多樣的PVP與PVE模式，像是公會戰、競技場排名等。為了讓玩家能更輕鬆地享受遊戲，官方時常會發放最新的兌換碼與禮包碼，如果想快速提升戰力，尋求專業的代儲值服務也是個不錯的選擇，既快速又安全，讓你無後顧之憂地重建無盡的夢，成為最強的主人！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://play.google.com/store/apps/details?id=com.Redeev.Oniro</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -18457,10 +18453,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>《Oniro ARPG》是一款超現實風格的動作角色扮演遊戲，玩家將潛入一個瀕臨崩潰的夢境世界，化身為甦醒的夢行者，對抗入侵的夢魘大軍。遊戲核心特色是其快節奏的戰鬥系統，玩家可以掌握多種夢境武器，施展強大的靈能，並透過獨特的「夢境印記」系統來客製化你的技能組合，打造出千變萬化的戰鬥風格。你將穿梭於破碎的記憶與扭曲的景觀之中，挑戰巨大的頭目，揭開夢境世界背後的秘密。隨著冒險的深入，你可以解鎖並升級更強大的裝備與能力。為了讓你的夢境之旅更加順暢，別忘了隨時留意官方可能發布的兌換碼及禮包碼。如果想在遊戲初期就建立優勢，尋找專業的代儲值服務會是個好選擇，享受快速安全的交易，讓你無懼任何惡夢，成為夢境的守護者！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://apps.apple.com/tw/app/legend-of-ymir/id6748295875?at=1010l3Vj&amp;ct=GNN</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -18469,7 +18461,17 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>《Legend of Ymir》是經典 IP《傳奇》系列的嶄新篇章，由 Wemade 採用頂級 Unreal Engine 5 引擎精心打造的次世代 MMORPG。遊戲世界觀植根於神秘的北歐神話，玩家將踏上廣袤的伊米爾大陸，親身體驗一場圍繞著世界樹的史詩級戰爭。本作完美繼承了《傳奇》系列最核心的 PVP 玩法，並將其提升至全新高度，實現了超越伺服器限制的大規模攻城戰。你的每一次戰鬥，都將影響世界的格局。遊戲不僅擁有令人驚嘆的畫面表現，更強調自由成長與激烈對抗。為了讓勇士們能迅速馳騁沙場，請務必關注官方發布的最新兌換碼與禮包碼，它們是前期成長的關鍵。若想在開戰時取得先機，一個快速安全的代儲值服務將是你的得力助手，助你戰力飆升，成為伊米爾大陸上無可撼動的傳奇！</t>
+    <t>《Winged Sakura: AFK Duelists》是一款日系動漫風格的放置型RPG手遊，玩家將化身為「主人」，在現實結構撕裂的「無盡的夢」中，召喚強大的「靈」為榮譽而戰。核心玩法圍繞著回合制自動戰鬥，玩家需要策略性地建立和客製化你的靈隊伍，透過升級、裝備強大的寶石和解鎖天賦來擊敗強大的Boss與其他主人。遊戲內也提供多樣的PVP與PVE模式，像是公會戰、競技場排名等。為了讓玩家能更輕鬆地享受遊戲，官方時常會發放最新的兌換碼與禮包碼，如果想快速提升戰力，尋求專業的代儲值服務也是個不錯的選擇，既快速又安全，讓你無後顧之憂地重建無盡的夢，成為最強的主人！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">《Oniro ARPG》是一款超現實風格的動作角色扮演遊戲，玩家將潛入一個瀕臨崩潰的夢境世界，化身為甦醒的夢行者，對抗入侵的夢魘大軍。遊戲核心特色是其快節奏的戰鬥系統，玩家可以掌握多種夢境武器，施展強大的靈能，並透過獨特的「夢境印記」系統來客製化你的技能組合，打造出千變萬化的戰鬥風格。為了讓你的夢境之旅更加順暢，別忘了隨時留意官方可能發布的兌換碼及禮包碼。如果想在遊戲初期就建立優勢，尋找專業的代儲值服務會是個好選擇，享受快速安全的交易，讓你無懼任何惡夢，成為夢境的守護者！
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">《Legend of Ymir》是經典 IP《傳奇》系列的嶄新篇章，由 Wemade 採用頂級 Unreal Engine 5 引擎精心打造的次世代 MMORPG。遊戲世界觀植根於神秘的北歐神話，玩家將踏上廣袤的伊米爾大陸，親身體驗一場圍繞著世界樹的史詩級戰爭。你的每一次戰鬥，都將影響世界的格局。遊戲不僅擁有令人驚嘆的畫面表現，更強調自由成長與激烈對抗。為了讓勇士們能迅速馳騁沙場，請務必關注官方發布的最新兌換碼與禮包碼，它們是前期成長的關鍵。若想在開戰時取得先機，一個快速安全的代儲值服務將是你的得力助手，助你戰力飆升，成為伊米爾大陸上無可撼動的傳奇！
+</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -36939,7 +36941,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/翼之櫻：放置決鬥者.html</v>
       </c>
       <c r="I260" s="42" t="s">
-        <v>4795</v>
+        <v>4801</v>
       </c>
       <c r="J260" s="1" t="s">
         <v>4771</v>
@@ -37007,27 +37009,27 @@
         <v>4760</v>
       </c>
       <c r="C261" s="5" t="s">
+        <v>4796</v>
+      </c>
+      <c r="D261" s="4" t="s">
         <v>4797</v>
       </c>
-      <c r="D261" s="4" t="s">
+      <c r="E261" s="4" t="s">
         <v>4798</v>
-      </c>
-      <c r="E261" s="4" t="s">
-        <v>4799</v>
       </c>
       <c r="F261" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Oniro ARPG.html</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>4796</v>
+        <v>4795</v>
       </c>
       <c r="H261" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Oniro ARPG.html</v>
       </c>
       <c r="I261" s="42" t="s">
-        <v>4800</v>
+        <v>4802</v>
       </c>
       <c r="J261" s="1" t="s">
         <v>4780</v>
@@ -37086,10 +37088,10 @@
         <v>4789</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>4802</v>
+        <v>4800</v>
       </c>
       <c r="E262" s="4" t="s">
-        <v>4801</v>
+        <v>4799</v>
       </c>
       <c r="F262" s="41" t="str">
         <f t="shared" si="10"/>
@@ -56275,7 +56277,7 @@
       </c>
       <c r="E260" s="14" t="str">
         <f>IF(games!I260&lt;&gt;"", games!I260, "")</f>
-        <v>《Winged Sakura: AFK Duelists》是一款日系動漫風格的放置型RPG手遊，玩家將化身為「主人」，在現實結構撕裂的「無盡的夢」中，召喚強大的「靈」為榮譽而戰。遊戲主打佛系放置玩法，即使離線也能獲得被動收益，讓你不必再為農資源而苦惱。核心玩法圍繞著回合制自動戰鬥，玩家需要策略性地建立和客製化你的靈隊伍，透過升級、裝備強大的寶石和解鎖天賦來擊敗強大的Boss與其他主人。遊戲內也提供多樣的PVP與PVE模式，像是公會戰、競技場排名等。為了讓玩家能更輕鬆地享受遊戲，官方時常會發放最新的兌換碼與禮包碼，如果想快速提升戰力，尋求專業的代儲值服務也是個不錯的選擇，既快速又安全，讓你無後顧之憂地重建無盡的夢，成為最強的主人！</v>
+        <v>《Winged Sakura: AFK Duelists》是一款日系動漫風格的放置型RPG手遊，玩家將化身為「主人」，在現實結構撕裂的「無盡的夢」中，召喚強大的「靈」為榮譽而戰。核心玩法圍繞著回合制自動戰鬥，玩家需要策略性地建立和客製化你的靈隊伍，透過升級、裝備強大的寶石和解鎖天賦來擊敗強大的Boss與其他主人。遊戲內也提供多樣的PVP與PVE模式，像是公會戰、競技場排名等。為了讓玩家能更輕鬆地享受遊戲，官方時常會發放最新的兌換碼與禮包碼，如果想快速提升戰力，尋求專業的代儲值服務也是個不錯的選擇，既快速又安全，讓你無後顧之憂地重建無盡的夢，成為最強的主人！</v>
       </c>
       <c r="F260" s="17" t="s">
         <v>4539</v>
@@ -56305,7 +56307,8 @@
       </c>
       <c r="E261" s="14" t="str">
         <f>IF(games!I261&lt;&gt;"", games!I261, "")</f>
-        <v>《Oniro ARPG》是一款超現實風格的動作角色扮演遊戲，玩家將潛入一個瀕臨崩潰的夢境世界，化身為甦醒的夢行者，對抗入侵的夢魘大軍。遊戲核心特色是其快節奏的戰鬥系統，玩家可以掌握多種夢境武器，施展強大的靈能，並透過獨特的「夢境印記」系統來客製化你的技能組合，打造出千變萬化的戰鬥風格。你將穿梭於破碎的記憶與扭曲的景觀之中，挑戰巨大的頭目，揭開夢境世界背後的秘密。隨著冒險的深入，你可以解鎖並升級更強大的裝備與能力。為了讓你的夢境之旅更加順暢，別忘了隨時留意官方可能發布的兌換碼及禮包碼。如果想在遊戲初期就建立優勢，尋找專業的代儲值服務會是個好選擇，享受快速安全的交易，讓你無懼任何惡夢，成為夢境的守護者！</v>
+        <v xml:space="preserve">《Oniro ARPG》是一款超現實風格的動作角色扮演遊戲，玩家將潛入一個瀕臨崩潰的夢境世界，化身為甦醒的夢行者，對抗入侵的夢魘大軍。遊戲核心特色是其快節奏的戰鬥系統，玩家可以掌握多種夢境武器，施展強大的靈能，並透過獨特的「夢境印記」系統來客製化你的技能組合，打造出千變萬化的戰鬥風格。為了讓你的夢境之旅更加順暢，別忘了隨時留意官方可能發布的兌換碼及禮包碼。如果想在遊戲初期就建立優勢，尋找專業的代儲值服務會是個好選擇，享受快速安全的交易，讓你無懼任何惡夢，成為夢境的守護者！
+</v>
       </c>
       <c r="F261" s="17" t="s">
         <v>4539</v>
@@ -56335,7 +56338,8 @@
       </c>
       <c r="E262" s="14" t="str">
         <f>IF(games!I262&lt;&gt;"", games!I262, "")</f>
-        <v>《Legend of Ymir》是經典 IP《傳奇》系列的嶄新篇章，由 Wemade 採用頂級 Unreal Engine 5 引擎精心打造的次世代 MMORPG。遊戲世界觀植根於神秘的北歐神話，玩家將踏上廣袤的伊米爾大陸，親身體驗一場圍繞著世界樹的史詩級戰爭。本作完美繼承了《傳奇》系列最核心的 PVP 玩法，並將其提升至全新高度，實現了超越伺服器限制的大規模攻城戰。你的每一次戰鬥，都將影響世界的格局。遊戲不僅擁有令人驚嘆的畫面表現，更強調自由成長與激烈對抗。為了讓勇士們能迅速馳騁沙場，請務必關注官方發布的最新兌換碼與禮包碼，它們是前期成長的關鍵。若想在開戰時取得先機，一個快速安全的代儲值服務將是你的得力助手，助你戰力飆升，成為伊米爾大陸上無可撼動的傳奇！</v>
+        <v xml:space="preserve">《Legend of Ymir》是經典 IP《傳奇》系列的嶄新篇章，由 Wemade 採用頂級 Unreal Engine 5 引擎精心打造的次世代 MMORPG。遊戲世界觀植根於神秘的北歐神話，玩家將踏上廣袤的伊米爾大陸，親身體驗一場圍繞著世界樹的史詩級戰爭。你的每一次戰鬥，都將影響世界的格局。遊戲不僅擁有令人驚嘆的畫面表現，更強調自由成長與激烈對抗。為了讓勇士們能迅速馳騁沙場，請務必關注官方發布的最新兌換碼與禮包碼，它們是前期成長的關鍵。若想在開戰時取得先機，一個快速安全的代儲值服務將是你的得力助手，助你戰力飆升，成為伊米爾大陸上無可撼動的傳奇！
+</v>
       </c>
       <c r="F262" s="17" t="s">
         <v>4539</v>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -18461,16 +18461,18 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>《Winged Sakura: AFK Duelists》是一款日系動漫風格的放置型RPG手遊，玩家將化身為「主人」，在現實結構撕裂的「無盡的夢」中，召喚強大的「靈」為榮譽而戰。核心玩法圍繞著回合制自動戰鬥，玩家需要策略性地建立和客製化你的靈隊伍，透過升級、裝備強大的寶石和解鎖天賦來擊敗強大的Boss與其他主人。遊戲內也提供多樣的PVP與PVE模式，像是公會戰、競技場排名等。為了讓玩家能更輕鬆地享受遊戲，官方時常會發放最新的兌換碼與禮包碼，如果想快速提升戰力，尋求專業的代儲值服務也是個不錯的選擇，既快速又安全，讓你無後顧之憂地重建無盡的夢，成為最強的主人！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">《Oniro ARPG》是一款超現實風格的動作角色扮演遊戲，玩家將潛入一個瀕臨崩潰的夢境世界，化身為甦醒的夢行者，對抗入侵的夢魘大軍。遊戲核心特色是其快節奏的戰鬥系統，玩家可以掌握多種夢境武器，施展強大的靈能，並透過獨特的「夢境印記」系統來客製化你的技能組合，打造出千變萬化的戰鬥風格。為了讓你的夢境之旅更加順暢，別忘了隨時留意官方可能發布的兌換碼及禮包碼。如果想在遊戲初期就建立優勢，尋找專業的代儲值服務會是個好選擇，享受快速安全的交易，讓你無懼任何惡夢，成為夢境的守護者！
 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">《Legend of Ymir》是經典 IP《傳奇》系列的嶄新篇章，由 Wemade 採用頂級 Unreal Engine 5 引擎精心打造的次世代 MMORPG。遊戲世界觀植根於神秘的北歐神話，玩家將踏上廣袤的伊米爾大陸，親身體驗一場圍繞著世界樹的史詩級戰爭。你的每一次戰鬥，都將影響世界的格局。遊戲不僅擁有令人驚嘆的畫面表現，更強調自由成長與激烈對抗。為了讓勇士們能迅速馳騁沙場，請務必關注官方發布的最新兌換碼與禮包碼，它們是前期成長的關鍵。若想在開戰時取得先機，一個快速安全的代儲值服務將是你的得力助手，助你戰力飆升，成為伊米爾大陸上無可撼動的傳奇！
+    <t xml:space="preserve">"《Legend of Ymir》是經典 IP《傳奇》系列的嶄新篇章，由 Wemade 採用頂級 UE5 引擎精心打造的次世代 MMORPG。遊戲世界觀植根於神秘的北歐神話，玩家將踏上廣袤的伊米爾大陸，親身體驗一場圍繞著世界樹的史詩級戰爭。遊戲不僅擁有令人驚嘆的畫面表現，更強調自由成長與激烈對抗。為了讓勇士們能迅速馳騁沙場，請務必關注官方發布的最新兌換碼與禮包碼，它們是前期成長的關鍵。若想在開戰時取得先機，一個快速安全的代儲值服務將是你的得力助手，助你戰力飆升，成為伊米爾大陸上無可撼動的傳奇！
+"
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">《翼之櫻：放置決鬥者》是一款日系動漫風格的放置型RPG手遊，玩家將化身為「主人」，在現實結構撕裂的「無盡的夢」中，召喚強大的「靈」為榮譽而戰。核心玩法圍繞著回合制自動戰鬥，玩家需要透過升級、裝備強大的寶石和解鎖天賦來擊敗強大的Boss與其他主人。遊戲內也提供多樣的PVP與PVE模式，像是公會戰、競技場排名等。為了讓玩家能更輕鬆地享受遊戲，官方時常會發放最新的兌換碼與禮包碼，如果想快速提升戰力，尋求專業的代儲值服務也是個不錯的選擇，既快速又安全，讓你無後顧之憂地重建無盡的夢，成為最強的主人！
 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -36941,7 +36943,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/翼之櫻：放置決鬥者.html</v>
       </c>
       <c r="I260" s="42" t="s">
-        <v>4801</v>
+        <v>4803</v>
       </c>
       <c r="J260" s="1" t="s">
         <v>4771</v>
@@ -37029,7 +37031,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Oniro ARPG.html</v>
       </c>
       <c r="I261" s="42" t="s">
-        <v>4802</v>
+        <v>4801</v>
       </c>
       <c r="J261" s="1" t="s">
         <v>4780</v>
@@ -37105,7 +37107,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Legend of YMIR.html</v>
       </c>
       <c r="I262" s="42" t="s">
-        <v>4803</v>
+        <v>4802</v>
       </c>
       <c r="J262" s="1" t="s">
         <v>1268</v>
@@ -56277,7 +56279,8 @@
       </c>
       <c r="E260" s="14" t="str">
         <f>IF(games!I260&lt;&gt;"", games!I260, "")</f>
-        <v>《Winged Sakura: AFK Duelists》是一款日系動漫風格的放置型RPG手遊，玩家將化身為「主人」，在現實結構撕裂的「無盡的夢」中，召喚強大的「靈」為榮譽而戰。核心玩法圍繞著回合制自動戰鬥，玩家需要策略性地建立和客製化你的靈隊伍，透過升級、裝備強大的寶石和解鎖天賦來擊敗強大的Boss與其他主人。遊戲內也提供多樣的PVP與PVE模式，像是公會戰、競技場排名等。為了讓玩家能更輕鬆地享受遊戲，官方時常會發放最新的兌換碼與禮包碼，如果想快速提升戰力，尋求專業的代儲值服務也是個不錯的選擇，既快速又安全，讓你無後顧之憂地重建無盡的夢，成為最強的主人！</v>
+        <v xml:space="preserve">《翼之櫻：放置決鬥者》是一款日系動漫風格的放置型RPG手遊，玩家將化身為「主人」，在現實結構撕裂的「無盡的夢」中，召喚強大的「靈」為榮譽而戰。核心玩法圍繞著回合制自動戰鬥，玩家需要透過升級、裝備強大的寶石和解鎖天賦來擊敗強大的Boss與其他主人。遊戲內也提供多樣的PVP與PVE模式，像是公會戰、競技場排名等。為了讓玩家能更輕鬆地享受遊戲，官方時常會發放最新的兌換碼與禮包碼，如果想快速提升戰力，尋求專業的代儲值服務也是個不錯的選擇，既快速又安全，讓你無後顧之憂地重建無盡的夢，成為最強的主人！
+</v>
       </c>
       <c r="F260" s="17" t="s">
         <v>4539</v>
@@ -56338,7 +56341,8 @@
       </c>
       <c r="E262" s="14" t="str">
         <f>IF(games!I262&lt;&gt;"", games!I262, "")</f>
-        <v xml:space="preserve">《Legend of Ymir》是經典 IP《傳奇》系列的嶄新篇章，由 Wemade 採用頂級 Unreal Engine 5 引擎精心打造的次世代 MMORPG。遊戲世界觀植根於神秘的北歐神話，玩家將踏上廣袤的伊米爾大陸，親身體驗一場圍繞著世界樹的史詩級戰爭。你的每一次戰鬥，都將影響世界的格局。遊戲不僅擁有令人驚嘆的畫面表現，更強調自由成長與激烈對抗。為了讓勇士們能迅速馳騁沙場，請務必關注官方發布的最新兌換碼與禮包碼，它們是前期成長的關鍵。若想在開戰時取得先機，一個快速安全的代儲值服務將是你的得力助手，助你戰力飆升，成為伊米爾大陸上無可撼動的傳奇！
+        <v xml:space="preserve">"《Legend of Ymir》是經典 IP《傳奇》系列的嶄新篇章，由 Wemade 採用頂級 UE5 引擎精心打造的次世代 MMORPG。遊戲世界觀植根於神秘的北歐神話，玩家將踏上廣袤的伊米爾大陸，親身體驗一場圍繞著世界樹的史詩級戰爭。遊戲不僅擁有令人驚嘆的畫面表現，更強調自由成長與激烈對抗。為了讓勇士們能迅速馳騁沙場，請務必關注官方發布的最新兌換碼與禮包碼，它們是前期成長的關鍵。若想在開戰時取得先機，一個快速安全的代儲值服務將是你的得力助手，助你戰力飆升，成為伊米爾大陸上無可撼動的傳奇！
+"
 </v>
       </c>
       <c r="F262" s="17" t="s">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7067" uniqueCount="4804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7083" uniqueCount="4815">
   <si>
     <t>Facebook</t>
   </si>
@@ -18474,6 +18474,56 @@
   <si>
     <t xml:space="preserve">《翼之櫻：放置決鬥者》是一款日系動漫風格的放置型RPG手遊，玩家將化身為「主人」，在現實結構撕裂的「無盡的夢」中，召喚強大的「靈」為榮譽而戰。核心玩法圍繞著回合制自動戰鬥，玩家需要透過升級、裝備強大的寶石和解鎖天賦來擊敗強大的Boss與其他主人。遊戲內也提供多樣的PVP與PVE模式，像是公會戰、競技場排名等。為了讓玩家能更輕鬆地享受遊戲，官方時常會發放最新的兌換碼與禮包碼，如果想快速提升戰力，尋求專業的代儲值服務也是個不錯的選擇，既快速又安全，讓你無後顧之憂地重建無盡的夢，成為最強的主人！
 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>章節通行證</t>
+  </si>
+  <si>
+    <t>高塔通行證</t>
+  </si>
+  <si>
+    <t>成長通行證</t>
+  </si>
+  <si>
+    <t>黃金禮包</t>
+  </si>
+  <si>
+    <t>舊黃金禮包</t>
+  </si>
+  <si>
+    <t>S級英雄升級禮包</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/elysiathegame/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Elysia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：星空墜落</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/mo/app/elysia-%E6%98%9F%E7%A9%BA%E5%A2%9C%E8%90%BD/id6737166302?at=1010l3Vj&amp;ct=ACG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.pantheraplay.projecth&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇幻RPG大作《Elysia：星空墜落》華麗降臨！你將進入瀕臨毀滅的絕美世界，化身英雄與夥伴共尋希望。遊戲採次世代引擎打造，戰鬥特效華麗、角色模組細膩。除了沉浸式主線，更有豐富副本與策略PVP對戰等你挑戰。為慶祝上市，官方正派送海量福利，務必鎖定最新的兌換碼和禮包碼！想讓戰力快人一步？尋找可靠的代儲值管道，享受快速安全的加值體驗，讓冒險暢行無阻。立即加入《Elysia：星空墜落》，守護這片星空！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -37147,14 +37197,67 @@
       </c>
     </row>
     <row r="263" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A263" s="71"/>
+      <c r="A263" s="69" t="s">
+        <v>4811</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>4810</v>
+      </c>
+      <c r="D263" s="4" t="s">
+        <v>4810</v>
+      </c>
+      <c r="E263" s="4" t="s">
+        <v>4812</v>
+      </c>
       <c r="F263" s="41" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Elysia：星空墜落.html</v>
+      </c>
+      <c r="G263" s="4" t="s">
+        <v>4813</v>
       </c>
       <c r="H263" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Elysia：星空墜落.html</v>
+      </c>
+      <c r="I263" s="42" t="s">
+        <v>4814</v>
+      </c>
+      <c r="J263" s="1" t="s">
+        <v>4804</v>
+      </c>
+      <c r="K263" s="71">
+        <v>624</v>
+      </c>
+      <c r="L263" s="1" t="s">
+        <v>4805</v>
+      </c>
+      <c r="M263" s="71">
+        <v>624</v>
+      </c>
+      <c r="N263" s="1" t="s">
+        <v>4806</v>
+      </c>
+      <c r="O263" s="71">
+        <v>624</v>
+      </c>
+      <c r="P263" s="1" t="s">
+        <v>4807</v>
+      </c>
+      <c r="Q263" s="71">
+        <v>128</v>
+      </c>
+      <c r="R263" s="1" t="s">
+        <v>4808</v>
+      </c>
+      <c r="S263" s="71">
+        <v>256</v>
+      </c>
+      <c r="T263" s="1" t="s">
+        <v>4809</v>
+      </c>
+      <c r="U263" s="71">
+        <v>552</v>
       </c>
     </row>
     <row r="264" spans="1:31" ht="22.5" customHeight="1">
@@ -40807,9 +40910,13 @@
     <hyperlink ref="E261" r:id="rId188"/>
     <hyperlink ref="E262" r:id="rId189"/>
     <hyperlink ref="D262" r:id="rId190"/>
+    <hyperlink ref="G263" r:id="rId191"/>
+    <hyperlink ref="D263" r:id="rId192"/>
+    <hyperlink ref="E263" r:id="rId193"/>
+    <hyperlink ref="C263" r:id="rId194"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId191"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId195"/>
 </worksheet>
 </file>
 
@@ -56361,19 +56468,31 @@
     <row r="263" spans="1:12">
       <c r="A263" s="13" t="str">
         <f>IF(games!A263="", "", games!A263)</f>
-        <v/>
+        <v>Elysia：星空墜落</v>
       </c>
       <c r="C263" s="13" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>giftcodesbanner/Elysia：星空墜落-禮包碼.jpg</v>
       </c>
       <c r="D263" s="13" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Elysia：星空墜落.html</v>
       </c>
       <c r="E263" s="14" t="str">
         <f>IF(games!I263&lt;&gt;"", games!I263, "")</f>
-        <v/>
+        <v>奇幻RPG大作《Elysia：星空墜落》華麗降臨！你將進入瀕臨毀滅的絕美世界，化身英雄與夥伴共尋希望。遊戲採次世代引擎打造，戰鬥特效華麗、角色模組細膩。除了沉浸式主線，更有豐富副本與策略PVP對戰等你挑戰。為慶祝上市，官方正派送海量福利，務必鎖定最新的兌換碼和禮包碼！想讓戰力快人一步？尋找可靠的代儲值管道，享受快速安全的加值體驗，讓冒險暢行無阻。立即加入《Elysia：星空墜落》，守護這片星空！</v>
+      </c>
+      <c r="F263" s="17" t="s">
+        <v>4539</v>
+      </c>
+      <c r="G263" s="13" t="s">
+        <v>4529</v>
+      </c>
+      <c r="K263" s="17" t="s">
+        <v>4539</v>
+      </c>
+      <c r="L263" s="13" t="s">
+        <v>4529</v>
       </c>
     </row>
     <row r="264" spans="1:12">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7151" uniqueCount="4862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7199" uniqueCount="4902">
   <si>
     <t>Facebook</t>
   </si>
@@ -18796,6 +18796,147 @@
   </si>
   <si>
     <t>《嘟嘟臉惡作劇》是一款充滿日系可愛風格的放置養成遊戲。故事發生在一個充滿魔法的學院，玩家將與一群擁有特殊能力的可愛角色們相遇，一同展開奇妙的冒險。遊戲採用輕鬆的放置玩法，讓你在繁忙之餘也能享受角色養成的樂趣，並透過策略性的戰鬥配置，挑戰各種關卡。想讓你的角色們迅速成長，解鎖更多有趣劇情嗎？記得使用官方兌換碼及禮包碼，獲得大量經驗與珍稀道具！我們也提供代儲值服務，讓您快速安全地獲得所需資源，輕鬆養成最強戰隊，在嘟嘟臉的世界裡盡情惡作劇吧！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5980星鑽</t>
+  </si>
+  <si>
+    <t>2980星鑽</t>
+  </si>
+  <si>
+    <t>680星鑽</t>
+  </si>
+  <si>
+    <t>去廣告月卡</t>
+  </si>
+  <si>
+    <t>金幣月卡</t>
+  </si>
+  <si>
+    <t>尊爵通行證</t>
+  </si>
+  <si>
+    <t>99.99美金禮包</t>
+  </si>
+  <si>
+    <t>49.99美金禮包</t>
+  </si>
+  <si>
+    <t>29.99美金禮包</t>
+  </si>
+  <si>
+    <t>19.99美金禮包</t>
+  </si>
+  <si>
+    <t>14.99美金禮包</t>
+  </si>
+  <si>
+    <t>9.99美金禮包</t>
+  </si>
+  <si>
+    <t>4.99美金禮包</t>
+  </si>
+  <si>
+    <t>0.99美金禮包</t>
+  </si>
+  <si>
+    <t>2300台幣禮包</t>
+  </si>
+  <si>
+    <t>1100台幣禮包</t>
+  </si>
+  <si>
+    <t>650台幣禮包</t>
+  </si>
+  <si>
+    <t>360台幣禮包</t>
+  </si>
+  <si>
+    <t>WITHU2ND</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>JJAZAN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HAPPY2GETHER</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2YEARGIFT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>韓服</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5MANCAFE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPENTHEBAK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HANGAWIGIFT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HLM810</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HLM888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HLMAX9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HLM9AC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HLM7CX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HLM2ZY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HLMobile12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HLM5KL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HLM9KZ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>moongift</t>
+  </si>
+  <si>
+    <t>ETHERIADOKI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HYPERLINKER</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ETHERIALIFE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ETHERIA13TH</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -37594,11 +37735,65 @@
       <c r="I265" t="s">
         <v>4859</v>
       </c>
-      <c r="J265" s="47" t="s">
-        <v>4840</v>
-      </c>
-      <c r="K265" s="41" t="s">
-        <v>4841</v>
+      <c r="J265" s="1" t="s">
+        <v>4862</v>
+      </c>
+      <c r="K265" s="72">
+        <v>2371</v>
+      </c>
+      <c r="L265" s="1" t="s">
+        <v>4863</v>
+      </c>
+      <c r="M265" s="72">
+        <v>1204</v>
+      </c>
+      <c r="N265" s="1" t="s">
+        <v>1432</v>
+      </c>
+      <c r="O265" s="72">
+        <v>807</v>
+      </c>
+      <c r="P265" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="Q265" s="72">
+        <v>400</v>
+      </c>
+      <c r="R265" s="1" t="s">
+        <v>4864</v>
+      </c>
+      <c r="S265" s="72">
+        <v>269</v>
+      </c>
+      <c r="T265" s="1" t="s">
+        <v>1434</v>
+      </c>
+      <c r="U265" s="72">
+        <v>145</v>
+      </c>
+      <c r="V265" s="1" t="s">
+        <v>4865</v>
+      </c>
+      <c r="W265" s="72">
+        <v>145</v>
+      </c>
+      <c r="X265" s="1" t="s">
+        <v>4866</v>
+      </c>
+      <c r="Y265" s="72">
+        <v>145</v>
+      </c>
+      <c r="Z265" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA265" s="72">
+        <v>145</v>
+      </c>
+      <c r="AB265" s="1" t="s">
+        <v>4867</v>
+      </c>
+      <c r="AC265" s="72">
+        <v>145</v>
       </c>
     </row>
     <row r="266" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -37628,11 +37823,53 @@
       <c r="I266" s="42" t="s">
         <v>4860</v>
       </c>
-      <c r="J266" s="47" t="s">
-        <v>4840</v>
-      </c>
-      <c r="K266" s="41" t="s">
-        <v>4841</v>
+      <c r="J266" s="1" t="s">
+        <v>4868</v>
+      </c>
+      <c r="K266" s="72">
+        <v>2609</v>
+      </c>
+      <c r="L266" s="1" t="s">
+        <v>4869</v>
+      </c>
+      <c r="M266" s="72">
+        <v>1365</v>
+      </c>
+      <c r="N266" s="1" t="s">
+        <v>4870</v>
+      </c>
+      <c r="O266" s="72">
+        <v>807</v>
+      </c>
+      <c r="P266" s="1" t="s">
+        <v>4871</v>
+      </c>
+      <c r="Q266" s="72">
+        <v>546</v>
+      </c>
+      <c r="R266" s="1" t="s">
+        <v>4872</v>
+      </c>
+      <c r="S266" s="72">
+        <v>400</v>
+      </c>
+      <c r="T266" s="1" t="s">
+        <v>4873</v>
+      </c>
+      <c r="U266" s="72">
+        <v>269</v>
+      </c>
+      <c r="V266" s="1" t="s">
+        <v>4874</v>
+      </c>
+      <c r="W266" s="72">
+        <v>145</v>
+      </c>
+      <c r="X266" s="1" t="s">
+        <v>4875</v>
+      </c>
+      <c r="Y266" s="72">
+        <v>29</v>
       </c>
     </row>
     <row r="267" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -37662,11 +37899,65 @@
       <c r="I267" s="42" t="s">
         <v>4861</v>
       </c>
-      <c r="J267" s="47" t="s">
-        <v>4840</v>
-      </c>
-      <c r="K267" s="41" t="s">
-        <v>4841</v>
+      <c r="J267" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="K267" s="72">
+        <v>2371</v>
+      </c>
+      <c r="L267" s="1" t="s">
+        <v>4876</v>
+      </c>
+      <c r="M267" s="72">
+        <v>1858</v>
+      </c>
+      <c r="N267" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="O267" s="72">
+        <v>1204</v>
+      </c>
+      <c r="P267" s="1" t="s">
+        <v>4877</v>
+      </c>
+      <c r="Q267" s="72">
+        <v>889</v>
+      </c>
+      <c r="R267" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="S267" s="72">
+        <v>807</v>
+      </c>
+      <c r="T267" s="1" t="s">
+        <v>4878</v>
+      </c>
+      <c r="U267" s="72">
+        <v>530</v>
+      </c>
+      <c r="V267" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="W267" s="72">
+        <v>400</v>
+      </c>
+      <c r="X267" s="1" t="s">
+        <v>4879</v>
+      </c>
+      <c r="Y267" s="72">
+        <v>294</v>
+      </c>
+      <c r="Z267" s="1" t="s">
+        <v>4338</v>
+      </c>
+      <c r="AA267" s="72">
+        <v>196</v>
+      </c>
+      <c r="AB267" s="1" t="s">
+        <v>3955</v>
+      </c>
+      <c r="AC267" s="72">
+        <v>162</v>
       </c>
     </row>
     <row r="268" spans="1:31" ht="22.5" customHeight="1">
@@ -52641,7 +52932,7 @@
         <v>2459</v>
       </c>
     </row>
-    <row r="177" spans="1:31" ht="22.5" customHeight="1">
+    <row r="177" spans="1:39" ht="22.5" customHeight="1">
       <c r="A177" s="92" t="s">
         <v>2612</v>
       </c>
@@ -52687,7 +52978,7 @@
         <v>2471</v>
       </c>
     </row>
-    <row r="178" spans="1:31" ht="22.5" customHeight="1">
+    <row r="178" spans="1:39" ht="22.5" customHeight="1">
       <c r="A178" s="12" t="s">
         <v>3418</v>
       </c>
@@ -52742,7 +53033,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="179" spans="1:31" ht="22.5" customHeight="1">
+    <row r="179" spans="1:39" ht="22.5" customHeight="1">
       <c r="A179" s="13" t="s">
         <v>3428</v>
       </c>
@@ -52782,7 +53073,7 @@
         <v>2459</v>
       </c>
     </row>
-    <row r="180" spans="1:31" ht="22.5" customHeight="1">
+    <row r="180" spans="1:39" ht="22.5" customHeight="1">
       <c r="A180" s="12" t="s">
         <v>3430</v>
       </c>
@@ -52816,7 +53107,7 @@
         <v>3436</v>
       </c>
     </row>
-    <row r="181" spans="1:31" ht="22.5" customHeight="1">
+    <row r="181" spans="1:39" ht="22.5" customHeight="1">
       <c r="A181" s="91" t="s">
         <v>1592</v>
       </c>
@@ -52844,7 +53135,7 @@
         <v>3438</v>
       </c>
     </row>
-    <row r="182" spans="1:31" ht="22.5" customHeight="1">
+    <row r="182" spans="1:39" ht="22.5" customHeight="1">
       <c r="A182" s="91" t="s">
         <v>1597</v>
       </c>
@@ -52899,7 +53190,7 @@
         <v>3447</v>
       </c>
     </row>
-    <row r="183" spans="1:31" ht="22.5" customHeight="1">
+    <row r="183" spans="1:39" ht="22.5" customHeight="1">
       <c r="A183" s="91" t="s">
         <v>1622</v>
       </c>
@@ -52972,7 +53263,7 @@
         <v>3459</v>
       </c>
     </row>
-    <row r="184" spans="1:31" ht="22.5" customHeight="1">
+    <row r="184" spans="1:39" ht="22.5" customHeight="1">
       <c r="A184" s="13" t="s">
         <v>2627</v>
       </c>
@@ -53006,7 +53297,7 @@
         <v>3462</v>
       </c>
     </row>
-    <row r="185" spans="1:31" ht="22.5" customHeight="1">
+    <row r="185" spans="1:39" ht="22.5" customHeight="1">
       <c r="A185" s="13" t="s">
         <v>3463</v>
       </c>
@@ -53054,8 +53345,35 @@
       <c r="P185" s="13" t="s">
         <v>3654</v>
       </c>
-    </row>
-    <row r="186" spans="1:31" ht="22.5" customHeight="1">
+      <c r="Q185" s="18" t="s">
+        <v>4888</v>
+      </c>
+      <c r="S185" s="18" t="s">
+        <v>4889</v>
+      </c>
+      <c r="U185" s="18" t="s">
+        <v>4890</v>
+      </c>
+      <c r="W185" s="18" t="s">
+        <v>4891</v>
+      </c>
+      <c r="Y185" s="18" t="s">
+        <v>4892</v>
+      </c>
+      <c r="AA185" s="18" t="s">
+        <v>4893</v>
+      </c>
+      <c r="AC185" s="18" t="s">
+        <v>4894</v>
+      </c>
+      <c r="AE185" s="18" t="s">
+        <v>4895</v>
+      </c>
+      <c r="AG185" s="18" t="s">
+        <v>4896</v>
+      </c>
+    </row>
+    <row r="186" spans="1:39" ht="22.5" customHeight="1">
       <c r="A186" s="92" t="s">
         <v>2633</v>
       </c>
@@ -53095,7 +53413,7 @@
         <v>3475</v>
       </c>
     </row>
-    <row r="187" spans="1:31" ht="22.5" customHeight="1">
+    <row r="187" spans="1:39" ht="22.5" customHeight="1">
       <c r="A187" s="92" t="s">
         <v>2636</v>
       </c>
@@ -53150,7 +53468,7 @@
         <v>3486</v>
       </c>
     </row>
-    <row r="188" spans="1:31" ht="22.5" customHeight="1">
+    <row r="188" spans="1:39" ht="22.5" customHeight="1">
       <c r="A188" s="13" t="s">
         <v>3487</v>
       </c>
@@ -53190,7 +53508,7 @@
         <v>2640</v>
       </c>
     </row>
-    <row r="189" spans="1:31" ht="22.5" customHeight="1">
+    <row r="189" spans="1:39" ht="22.5" customHeight="1">
       <c r="A189" s="13" t="s">
         <v>2641</v>
       </c>
@@ -53224,7 +53542,7 @@
         <v>3493</v>
       </c>
     </row>
-    <row r="190" spans="1:31" ht="22.5" customHeight="1">
+    <row r="190" spans="1:39" ht="22.5" customHeight="1">
       <c r="A190" s="13" t="str">
         <f>games!A190</f>
         <v>伊瑟</v>
@@ -53280,8 +53598,20 @@
       <c r="AE190" s="18" t="s">
         <v>4626</v>
       </c>
-    </row>
-    <row r="191" spans="1:31" ht="22.5" customHeight="1">
+      <c r="AG190" s="18" t="s">
+        <v>4898</v>
+      </c>
+      <c r="AI190" s="18" t="s">
+        <v>4899</v>
+      </c>
+      <c r="AK190" s="18" t="s">
+        <v>4900</v>
+      </c>
+      <c r="AM190" s="18" t="s">
+        <v>4901</v>
+      </c>
+    </row>
+    <row r="191" spans="1:39" ht="22.5" customHeight="1">
       <c r="A191" s="13" t="str">
         <f>IF(games!A191="", "", games!A191)</f>
         <v>手刀搶英雄</v>
@@ -53326,7 +53656,7 @@
         <v>3523</v>
       </c>
     </row>
-    <row r="192" spans="1:31" ht="22.5" customHeight="1">
+    <row r="192" spans="1:39" ht="22.5" customHeight="1">
       <c r="A192" s="13" t="str">
         <f>IF(games!A192="", "", games!A192)</f>
         <v>荒野亂鬥</v>
@@ -55398,6 +55728,9 @@
       <c r="Y227" s="18" t="s">
         <v>4813</v>
       </c>
+      <c r="AA227" s="71" t="s">
+        <v>4897</v>
+      </c>
     </row>
     <row r="228" spans="1:47" ht="22.5" customHeight="1">
       <c r="A228" s="13" t="str">
@@ -56705,7 +57038,7 @@
         <v>2640</v>
       </c>
     </row>
-    <row r="257" spans="1:12" ht="22.5" customHeight="1">
+    <row r="257" spans="1:24" ht="22.5" customHeight="1">
       <c r="A257" s="13" t="str">
         <f>IF(games!A257="", "", games!A257)</f>
         <v>屍不可擋</v>
@@ -56738,7 +57071,7 @@
         <v>4719</v>
       </c>
     </row>
-    <row r="258" spans="1:12" ht="22.5" customHeight="1">
+    <row r="258" spans="1:24" ht="22.5" customHeight="1">
       <c r="A258" s="13" t="str">
         <f>IF(games!A258="", "", games!A258)</f>
         <v>RF ONLINE NEXT</v>
@@ -56768,7 +57101,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="259" spans="1:12">
+    <row r="259" spans="1:24">
       <c r="A259" s="13" t="str">
         <f>IF(games!A259="", "", games!A259)</f>
         <v>少女掌門人</v>
@@ -56798,7 +57131,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="260" spans="1:12">
+    <row r="260" spans="1:24">
       <c r="A260" s="13" t="str">
         <f>IF(games!A260="", "", games!A260)</f>
         <v>翼之櫻：放置決鬥者</v>
@@ -56829,7 +57162,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="261" spans="1:12">
+    <row r="261" spans="1:24">
       <c r="A261" s="13" t="str">
         <f>IF(games!A261="", "", games!A261)</f>
         <v>Oniro ARPG</v>
@@ -56860,7 +57193,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="262" spans="1:12">
+    <row r="262" spans="1:24">
       <c r="A262" s="13" t="str">
         <f>IF(games!A262="", "", games!A262)</f>
         <v>Legend of YMIR</v>
@@ -56892,7 +57225,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="263" spans="1:12">
+    <row r="263" spans="1:24">
       <c r="A263" s="13" t="str">
         <f>IF(games!A263="", "", games!A263)</f>
         <v>Elysia：星空墜落</v>
@@ -56922,7 +57255,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="264" spans="1:12">
+    <row r="264" spans="1:24">
       <c r="A264" s="13" t="str">
         <f>IF(games!A264="", "", games!A264)</f>
         <v>合併貓鎮</v>
@@ -56952,7 +57285,7 @@
         <v>4841</v>
       </c>
     </row>
-    <row r="265" spans="1:12">
+    <row r="265" spans="1:24">
       <c r="A265" s="13" t="str">
         <f>IF(games!A265="", "", games!A265)</f>
         <v>幻牌交鋒</v>
@@ -56982,7 +57315,7 @@
         <v>4841</v>
       </c>
     </row>
-    <row r="266" spans="1:12">
+    <row r="266" spans="1:24">
       <c r="A266" s="13" t="str">
         <f>IF(games!A266="", "", games!A266)</f>
         <v>激鬥！王國保衛戰</v>
@@ -57012,7 +57345,7 @@
         <v>4841</v>
       </c>
     </row>
-    <row r="267" spans="1:12">
+    <row r="267" spans="1:24">
       <c r="A267" s="13" t="str">
         <f>IF(games!A267="", "", games!A267)</f>
         <v>嘟嘟臉惡作劇</v>
@@ -57036,13 +57369,49 @@
         <v>4841</v>
       </c>
       <c r="K267" s="17" t="s">
-        <v>4842</v>
+        <v>4880</v>
       </c>
       <c r="L267" s="13" t="s">
-        <v>4841</v>
-      </c>
-    </row>
-    <row r="268" spans="1:12">
+        <v>4884</v>
+      </c>
+      <c r="M267" s="18" t="s">
+        <v>4881</v>
+      </c>
+      <c r="N267" s="13" t="s">
+        <v>4884</v>
+      </c>
+      <c r="O267" s="18" t="s">
+        <v>4882</v>
+      </c>
+      <c r="P267" s="13" t="s">
+        <v>4884</v>
+      </c>
+      <c r="Q267" s="18" t="s">
+        <v>4883</v>
+      </c>
+      <c r="R267" s="13" t="s">
+        <v>4884</v>
+      </c>
+      <c r="S267" s="18" t="s">
+        <v>4885</v>
+      </c>
+      <c r="T267" s="13" t="s">
+        <v>4884</v>
+      </c>
+      <c r="U267" s="18" t="s">
+        <v>4886</v>
+      </c>
+      <c r="V267" s="13" t="s">
+        <v>4884</v>
+      </c>
+      <c r="W267" s="18" t="s">
+        <v>4887</v>
+      </c>
+      <c r="X267" s="13" t="s">
+        <v>4884</v>
+      </c>
+    </row>
+    <row r="268" spans="1:24">
       <c r="A268" s="13" t="str">
         <f>IF(games!A268="", "", games!A268)</f>
         <v/>
@@ -57060,7 +57429,7 @@
         <v/>
       </c>
     </row>
-    <row r="269" spans="1:12">
+    <row r="269" spans="1:24">
       <c r="A269" s="13" t="str">
         <f>IF(games!A269="", "", games!A269)</f>
         <v/>
@@ -57078,7 +57447,7 @@
         <v/>
       </c>
     </row>
-    <row r="270" spans="1:12">
+    <row r="270" spans="1:24">
       <c r="A270" s="13" t="str">
         <f>IF(games!A270="", "", games!A270)</f>
         <v/>
@@ -57096,7 +57465,7 @@
         <v/>
       </c>
     </row>
-    <row r="271" spans="1:12">
+    <row r="271" spans="1:24">
       <c r="A271" s="13" t="str">
         <f>IF(games!A271="", "", games!A271)</f>
         <v/>
@@ -57114,7 +57483,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" spans="1:12">
+    <row r="272" spans="1:24">
       <c r="A272" s="13" t="str">
         <f>IF(games!A272="", "", games!A272)</f>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7199" uniqueCount="4902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7239" uniqueCount="4938">
   <si>
     <t>Facebook</t>
   </si>
@@ -18465,24 +18465,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>章節通行證</t>
-  </si>
-  <si>
-    <t>高塔通行證</t>
-  </si>
-  <si>
-    <t>成長通行證</t>
-  </si>
-  <si>
-    <t>黃金禮包</t>
-  </si>
-  <si>
-    <t>舊黃金禮包</t>
-  </si>
-  <si>
-    <t>S級英雄升級禮包</t>
-  </si>
-  <si>
     <t>https://www.facebook.com/elysiathegame/</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -18805,18 +18787,12 @@
     <t>2980星鑽</t>
   </si>
   <si>
-    <t>680星鑽</t>
-  </si>
-  <si>
     <t>去廣告月卡</t>
   </si>
   <si>
     <t>金幣月卡</t>
   </si>
   <si>
-    <t>尊爵通行證</t>
-  </si>
-  <si>
     <t>99.99美金禮包</t>
   </si>
   <si>
@@ -18938,6 +18914,165 @@
   <si>
     <t>ETHERIA13TH</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7500星晶</t>
+  </si>
+  <si>
+    <t>3700星晶</t>
+  </si>
+  <si>
+    <t>1400星晶</t>
+  </si>
+  <si>
+    <t>700星晶</t>
+  </si>
+  <si>
+    <t>300星晶</t>
+  </si>
+  <si>
+    <t>50星晶</t>
+  </si>
+  <si>
+    <t>天界祝福</t>
+  </si>
+  <si>
+    <t>星辰祝福</t>
+  </si>
+  <si>
+    <t>艾莉西亞的祝福</t>
+  </si>
+  <si>
+    <t>新手幸運包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>索拉里亞的祝福</t>
+  </si>
+  <si>
+    <t>英雄起點包</t>
+  </si>
+  <si>
+    <t>豪華通行券</t>
+  </si>
+  <si>
+    <t>我的花園世界</t>
+  </si>
+  <si>
+    <t>FLOWER</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>元寶*30+水滴*65+金幣*8888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>butterfu.u</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>閃電寶箱*1+金幣*2000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://redeem-code.eidolons-cross.com/html/TW/redeem_code/redeem-code.html</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲內右上角「選單」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>進到「設定」之後記住玩家ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>到網址內輸入ID跟禮包碼按確認即可領取</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>006892699</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600寶石邀請碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/mygardenworld.ofcl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://hjxp.floralgames.net/reserve/index.html#s1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.floralgames.hjxp&amp;referrer=utm_source%3Dgamer.com.tw%26utm_campaign%3Dgnn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E6%88%91%E7%9A%84%E8%8A%B1%E5%9C%92%E4%B8%96%E7%95%8C/id6751560944</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GD666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GD888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GD999</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GD520</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水滴*20+金幣*1000+雇傭書*5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水雞*20+金幣*1000+加速卡*20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>元寶*20+金幣*1000+花坊幣*10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*1000+加速卡*10+花坊幣*30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>進到遊戲內按右上角「設定」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點最底下的「兌換碼」選項</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《我的花園世界》是一款主打療癒種植與溫馨養成的沉浸式花園手遊，帶領玩家進入一個充滿花香的夢幻國度。你將化身為專業花藝師，親手培育超過三百種四季花卉，從播種、澆水到採摘，每一步都充滿了治癒感。遊戲玩法自由，不僅能隨心所欲地佈置你的花園，設計出獨一無二的花藝作品，還能與好友交流互動，增添許多樂趣。
+為了讓玩家快速體驗遊戲魅力，官方準備了豐富的兌換碼和禮包碼，只要輕鬆輸入序號，就能獲得稀有種子與實用道具，讓你的花園事業快速發展。遊戲也提供快速安全的代儲值服務，確保每一筆交易都安全無虞，讓你能夠無後顧之憂地沉浸在美麗的花花世界裡。現在就加入《我的花園世界》，打造屬於你的芬芳國度，開啟一段充滿愛與夢想的花藝人生！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6000元寶</t>
+  </si>
+  <si>
+    <t>1800元寶</t>
+  </si>
+  <si>
+    <t>900元寶</t>
+  </si>
+  <si>
+    <t>免廣告</t>
+  </si>
+  <si>
+    <t>VIP特權</t>
   </si>
 </sst>
 </file>
@@ -19308,7 +19443,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -19558,6 +19693,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -19863,7 +20003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ629"/>
+  <dimension ref="A1:AQ628"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="27" style="40" customWidth="1"/>
@@ -37124,7 +37264,7 @@
         <v>6095</v>
       </c>
     </row>
-    <row r="257" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+    <row r="257" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A257" s="72" t="s">
         <v>4687</v>
       </c>
@@ -37212,7 +37352,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="258" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+    <row r="258" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A258" s="72" t="s">
         <v>4688</v>
       </c>
@@ -37306,7 +37446,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="259" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+    <row r="259" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A259" s="70" t="s">
         <v>4746</v>
       </c>
@@ -37327,7 +37467,7 @@
         <v>4747</v>
       </c>
       <c r="H259" s="41" t="str">
-        <f t="shared" ref="H259:H285" si="11">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
+        <f t="shared" ref="H259:H284" si="11">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/少女掌門人.html</v>
       </c>
       <c r="I259" s="42" t="s">
@@ -37388,7 +37528,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="260" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+    <row r="260" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A260" s="70" t="s">
         <v>4791</v>
       </c>
@@ -37476,7 +37616,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="261" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+    <row r="261" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A261" s="72" t="s">
         <v>4757</v>
       </c>
@@ -37552,7 +37692,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="262" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+    <row r="262" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A262" s="72" t="s">
         <v>4758</v>
       </c>
@@ -37616,133 +37756,169 @@
         <v>77</v>
       </c>
     </row>
-    <row r="263" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+    <row r="263" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A263" s="69" t="s">
-        <v>4808</v>
+        <v>4802</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>4807</v>
+        <v>4801</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>4807</v>
+        <v>4801</v>
       </c>
       <c r="E263" s="4" t="s">
-        <v>4809</v>
+        <v>4803</v>
       </c>
       <c r="F263" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Elysia：星空墜落.html</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>4810</v>
+        <v>4804</v>
       </c>
       <c r="H263" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Elysia：星空墜落.html</v>
       </c>
       <c r="I263" s="42" t="s">
-        <v>4811</v>
+        <v>4805</v>
       </c>
       <c r="J263" s="1" t="s">
-        <v>4801</v>
+        <v>4894</v>
       </c>
       <c r="K263" s="72">
-        <v>624</v>
+        <v>2371</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>4802</v>
+        <v>4895</v>
       </c>
       <c r="M263" s="72">
-        <v>624</v>
+        <v>1204</v>
       </c>
       <c r="N263" s="1" t="s">
-        <v>4803</v>
+        <v>4896</v>
       </c>
       <c r="O263" s="72">
-        <v>624</v>
+        <v>563</v>
       </c>
       <c r="P263" s="1" t="s">
-        <v>4804</v>
+        <v>4897</v>
       </c>
       <c r="Q263" s="72">
+        <v>261</v>
+      </c>
+      <c r="R263" s="1" t="s">
+        <v>4898</v>
+      </c>
+      <c r="S263" s="72">
         <v>128</v>
       </c>
-      <c r="R263" s="1" t="s">
-        <v>4805</v>
-      </c>
-      <c r="S263" s="72">
-        <v>256</v>
-      </c>
       <c r="T263" s="1" t="s">
-        <v>4806</v>
+        <v>4899</v>
       </c>
       <c r="U263" s="72">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="264" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+        <v>26</v>
+      </c>
+      <c r="V263" s="1" t="s">
+        <v>4900</v>
+      </c>
+      <c r="W263" s="72">
+        <v>400</v>
+      </c>
+      <c r="X263" s="1" t="s">
+        <v>4901</v>
+      </c>
+      <c r="Y263" s="72">
+        <v>128</v>
+      </c>
+      <c r="Z263" s="1" t="s">
+        <v>4902</v>
+      </c>
+      <c r="AA263" s="72">
+        <v>2371</v>
+      </c>
+      <c r="AB263" s="99" t="s">
+        <v>4903</v>
+      </c>
+      <c r="AC263" s="72">
+        <v>1204</v>
+      </c>
+      <c r="AD263" s="1" t="s">
+        <v>4904</v>
+      </c>
+      <c r="AE263" s="72">
+        <v>400</v>
+      </c>
+      <c r="AF263" s="1" t="s">
+        <v>4905</v>
+      </c>
+      <c r="AG263" s="72">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="264" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A264" s="72" t="s">
-        <v>4837</v>
+        <v>4831</v>
       </c>
       <c r="E264" s="4" t="s">
-        <v>4844</v>
+        <v>4838</v>
       </c>
       <c r="F264" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/合併貓鎮.html</v>
       </c>
       <c r="G264" s="4" t="s">
-        <v>4843</v>
+        <v>4837</v>
       </c>
       <c r="H264" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/合併貓鎮.html</v>
       </c>
       <c r="I264" s="42" t="s">
-        <v>4858</v>
+        <v>4852</v>
       </c>
       <c r="J264" s="47" t="s">
-        <v>4840</v>
+        <v>4834</v>
       </c>
       <c r="K264" s="41" t="s">
+        <v>4835</v>
+      </c>
+    </row>
+    <row r="265" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A265" s="72" t="s">
+        <v>4832</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>4839</v>
+      </c>
+      <c r="D265" s="4" t="s">
         <v>4841</v>
       </c>
-    </row>
-    <row r="265" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A265" s="72" t="s">
-        <v>4838</v>
-      </c>
-      <c r="C265" s="5" t="s">
-        <v>4845</v>
-      </c>
-      <c r="D265" s="4" t="s">
-        <v>4847</v>
-      </c>
       <c r="E265" s="4" t="s">
-        <v>4848</v>
+        <v>4842</v>
       </c>
       <c r="F265" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/幻牌交鋒.html</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>4849</v>
+        <v>4843</v>
       </c>
       <c r="H265" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/幻牌交鋒.html</v>
       </c>
       <c r="I265" t="s">
-        <v>4859</v>
+        <v>4853</v>
       </c>
       <c r="J265" s="1" t="s">
-        <v>4862</v>
+        <v>4856</v>
       </c>
       <c r="K265" s="72">
         <v>2371</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>4863</v>
+        <v>4857</v>
       </c>
       <c r="M265" s="72">
         <v>1204</v>
@@ -37751,153 +37927,153 @@
         <v>1432</v>
       </c>
       <c r="O265" s="72">
-        <v>807</v>
+        <v>563</v>
       </c>
       <c r="P265" s="1" t="s">
         <v>1433</v>
       </c>
       <c r="Q265" s="72">
-        <v>400</v>
+        <v>261</v>
       </c>
       <c r="R265" s="1" t="s">
-        <v>4864</v>
+        <v>1434</v>
       </c>
       <c r="S265" s="72">
-        <v>269</v>
+        <v>128</v>
       </c>
       <c r="T265" s="1" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="U265" s="72">
-        <v>145</v>
+        <v>26</v>
       </c>
       <c r="V265" s="1" t="s">
-        <v>4865</v>
+        <v>4906</v>
       </c>
       <c r="W265" s="72">
-        <v>145</v>
+        <v>247</v>
       </c>
       <c r="X265" s="1" t="s">
-        <v>4866</v>
+        <v>196</v>
       </c>
       <c r="Y265" s="72">
-        <v>145</v>
+        <v>261</v>
       </c>
       <c r="Z265" s="1" t="s">
-        <v>196</v>
+        <v>4859</v>
       </c>
       <c r="AA265" s="72">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="AB265" s="1" t="s">
-        <v>4867</v>
+        <v>4858</v>
       </c>
       <c r="AC265" s="72">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="266" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="266" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A266" s="3" t="s">
-        <v>4850</v>
+        <v>4844</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>4851</v>
+        <v>4845</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>4854</v>
+        <v>4848</v>
       </c>
       <c r="E266" s="4" t="s">
-        <v>4853</v>
+        <v>4847</v>
       </c>
       <c r="F266" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/激鬥！王國保衛戰.html</v>
       </c>
       <c r="G266" s="4" t="s">
-        <v>4852</v>
+        <v>4846</v>
       </c>
       <c r="H266" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/激鬥！王國保衛戰.html</v>
       </c>
       <c r="I266" s="42" t="s">
+        <v>4854</v>
+      </c>
+      <c r="J266" s="1" t="s">
         <v>4860</v>
-      </c>
-      <c r="J266" s="1" t="s">
-        <v>4868</v>
       </c>
       <c r="K266" s="72">
         <v>2609</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>4869</v>
+        <v>4861</v>
       </c>
       <c r="M266" s="72">
         <v>1365</v>
       </c>
       <c r="N266" s="1" t="s">
-        <v>4870</v>
+        <v>4862</v>
       </c>
       <c r="O266" s="72">
         <v>807</v>
       </c>
       <c r="P266" s="1" t="s">
-        <v>4871</v>
+        <v>4863</v>
       </c>
       <c r="Q266" s="72">
         <v>546</v>
       </c>
       <c r="R266" s="1" t="s">
-        <v>4872</v>
+        <v>4864</v>
       </c>
       <c r="S266" s="72">
         <v>400</v>
       </c>
       <c r="T266" s="1" t="s">
-        <v>4873</v>
+        <v>4865</v>
       </c>
       <c r="U266" s="72">
         <v>269</v>
       </c>
       <c r="V266" s="1" t="s">
-        <v>4874</v>
+        <v>4866</v>
       </c>
       <c r="W266" s="72">
         <v>145</v>
       </c>
       <c r="X266" s="1" t="s">
-        <v>4875</v>
+        <v>4867</v>
       </c>
       <c r="Y266" s="72">
         <v>29</v>
       </c>
     </row>
-    <row r="267" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+    <row r="267" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A267" s="72" t="s">
-        <v>4839</v>
+        <v>4833</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>4846</v>
+        <v>4840</v>
       </c>
       <c r="D267" s="41" t="s">
-        <v>4857</v>
+        <v>4851</v>
       </c>
       <c r="E267" s="4" t="s">
-        <v>4855</v>
+        <v>4849</v>
       </c>
       <c r="F267" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/嘟嘟臉惡作劇.html</v>
       </c>
       <c r="G267" s="41" t="s">
-        <v>4856</v>
+        <v>4850</v>
       </c>
       <c r="H267" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/嘟嘟臉惡作劇.html</v>
       </c>
       <c r="I267" s="42" t="s">
-        <v>4861</v>
+        <v>4855</v>
       </c>
       <c r="J267" s="1" t="s">
         <v>301</v>
@@ -37906,7 +38082,7 @@
         <v>2371</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>4876</v>
+        <v>4868</v>
       </c>
       <c r="M267" s="72">
         <v>1858</v>
@@ -37918,7 +38094,7 @@
         <v>1204</v>
       </c>
       <c r="P267" s="1" t="s">
-        <v>4877</v>
+        <v>4869</v>
       </c>
       <c r="Q267" s="72">
         <v>889</v>
@@ -37930,7 +38106,7 @@
         <v>807</v>
       </c>
       <c r="T267" s="1" t="s">
-        <v>4878</v>
+        <v>4870</v>
       </c>
       <c r="U267" s="72">
         <v>530</v>
@@ -37942,7 +38118,7 @@
         <v>400</v>
       </c>
       <c r="X267" s="1" t="s">
-        <v>4879</v>
+        <v>4871</v>
       </c>
       <c r="Y267" s="72">
         <v>294</v>
@@ -37960,17 +38136,95 @@
         <v>162</v>
       </c>
     </row>
-    <row r="268" spans="1:31" ht="22.5" customHeight="1">
+    <row r="268" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A268" s="72" t="s">
+        <v>4907</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>4918</v>
+      </c>
+      <c r="D268" s="4" t="s">
+        <v>4919</v>
+      </c>
+      <c r="E268" s="4" t="s">
+        <v>4921</v>
+      </c>
       <c r="F268" s="40" t="str">
-        <f t="shared" ref="F268:F314" si="12">IF(A268="", "", "gift-codes.html?game=" &amp; A268)</f>
-        <v/>
+        <f t="shared" ref="F268:F313" si="12">IF(A268="", "", "gift-codes.html?game=" &amp; A268)</f>
+        <v>gift-codes.html?game=我的花園世界</v>
+      </c>
+      <c r="G268" s="4" t="s">
+        <v>4920</v>
       </c>
       <c r="H268" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="269" spans="1:31" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/我的花園世界.html</v>
+      </c>
+      <c r="I268" s="42" t="s">
+        <v>4932</v>
+      </c>
+      <c r="J268" s="1" t="s">
+        <v>4933</v>
+      </c>
+      <c r="K268" s="72">
+        <v>2609</v>
+      </c>
+      <c r="L268" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="M268" s="72">
+        <v>1365</v>
+      </c>
+      <c r="N268" s="1" t="s">
+        <v>4934</v>
+      </c>
+      <c r="O268" s="72">
+        <v>807</v>
+      </c>
+      <c r="P268" s="1" t="s">
+        <v>4460</v>
+      </c>
+      <c r="Q268" s="72">
+        <v>546</v>
+      </c>
+      <c r="R268" s="1" t="s">
+        <v>4935</v>
+      </c>
+      <c r="S268" s="72">
+        <v>400</v>
+      </c>
+      <c r="T268" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="U268" s="72">
+        <v>269</v>
+      </c>
+      <c r="V268" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="W268" s="72">
+        <v>145</v>
+      </c>
+      <c r="X268" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y268" s="72">
+        <v>29</v>
+      </c>
+      <c r="Z268" s="1" t="s">
+        <v>4936</v>
+      </c>
+      <c r="AA268" s="72">
+        <v>29</v>
+      </c>
+      <c r="AB268" s="1" t="s">
+        <v>4937</v>
+      </c>
+      <c r="AC268" s="72">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="269" spans="1:33" ht="22.5" customHeight="1">
       <c r="F269" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -37980,7 +38234,7 @@
         <v/>
       </c>
     </row>
-    <row r="270" spans="1:31" ht="22.5" customHeight="1">
+    <row r="270" spans="1:33" ht="22.5" customHeight="1">
       <c r="F270" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -37990,7 +38244,7 @@
         <v/>
       </c>
     </row>
-    <row r="271" spans="1:31" ht="22.5" customHeight="1">
+    <row r="271" spans="1:33" ht="22.5" customHeight="1">
       <c r="F271" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -38000,7 +38254,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" spans="1:31" ht="22.5" customHeight="1">
+    <row r="272" spans="1:33" ht="22.5" customHeight="1">
       <c r="F272" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -38136,7 +38390,7 @@
         <v/>
       </c>
       <c r="H285" s="41" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="H285:H313" si="13">IF(A285="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A285)</f>
         <v/>
       </c>
     </row>
@@ -38146,7 +38400,7 @@
         <v/>
       </c>
       <c r="H286" s="41" t="str">
-        <f t="shared" ref="H286:H314" si="13">IF(A286="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A286)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38422,21 +38676,21 @@
     </row>
     <row r="314" spans="6:8" ht="22.5" customHeight="1">
       <c r="F314" s="40" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="F314:F377" si="14">IF(A314="", "", "gift-codes.html?game=" &amp; A314)</f>
         <v/>
       </c>
       <c r="H314" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="H314:H377" si="15">IF(A314="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A314)</f>
         <v/>
       </c>
     </row>
     <row r="315" spans="6:8" ht="22.5" customHeight="1">
       <c r="F315" s="40" t="str">
-        <f t="shared" ref="F315:F378" si="14">IF(A315="", "", "gift-codes.html?game=" &amp; A315)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H315" s="41" t="str">
-        <f t="shared" ref="H315:H378" si="15">IF(A315="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A315)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -39062,21 +39316,21 @@
     </row>
     <row r="378" spans="6:8" ht="22.5" customHeight="1">
       <c r="F378" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="F378:F441" si="16">IF(A378="", "", "gift-codes.html?game=" &amp; A378)</f>
         <v/>
       </c>
       <c r="H378" s="41" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="H378:H441" si="17">IF(A378="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A378)</f>
         <v/>
       </c>
     </row>
     <row r="379" spans="6:8" ht="22.5" customHeight="1">
       <c r="F379" s="40" t="str">
-        <f t="shared" ref="F379:F442" si="16">IF(A379="", "", "gift-codes.html?game=" &amp; A379)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H379" s="41" t="str">
-        <f t="shared" ref="H379:H442" si="17">IF(A379="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A379)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -39620,7 +39874,7 @@
         <v/>
       </c>
     </row>
-    <row r="434" spans="6:8" ht="22.5" customHeight="1">
+    <row r="434" spans="6:8">
       <c r="F434" s="40" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -39702,21 +39956,21 @@
     </row>
     <row r="442" spans="6:8">
       <c r="F442" s="40" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="F442:F505" si="18">IF(A442="", "", "gift-codes.html?game=" &amp; A442)</f>
         <v/>
       </c>
       <c r="H442" s="41" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="H442:H505" si="19">IF(A442="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A442)</f>
         <v/>
       </c>
     </row>
     <row r="443" spans="6:8">
       <c r="F443" s="40" t="str">
-        <f t="shared" ref="F443:F506" si="18">IF(A443="", "", "gift-codes.html?game=" &amp; A443)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H443" s="41" t="str">
-        <f t="shared" ref="H443:H506" si="19">IF(A443="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A443)</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -40342,21 +40596,21 @@
     </row>
     <row r="506" spans="6:8">
       <c r="F506" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="F506:F569" si="20">IF(A506="", "", "gift-codes.html?game=" &amp; A506)</f>
         <v/>
       </c>
       <c r="H506" s="41" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="H506:H569" si="21">IF(A506="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A506)</f>
         <v/>
       </c>
     </row>
     <row r="507" spans="6:8">
       <c r="F507" s="40" t="str">
-        <f t="shared" ref="F507:F570" si="20">IF(A507="", "", "gift-codes.html?game=" &amp; A507)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H507" s="41" t="str">
-        <f t="shared" ref="H507:H570" si="21">IF(A507="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A507)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -40982,11 +41236,11 @@
     </row>
     <row r="570" spans="6:8">
       <c r="F570" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(A570="", "", "gift-codes.html?game=" &amp; A570)</f>
         <v/>
       </c>
       <c r="H570" s="41" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="H570:H628" si="22">IF(A570="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A570)</f>
         <v/>
       </c>
     </row>
@@ -40996,7 +41250,7 @@
         <v/>
       </c>
       <c r="H571" s="41" t="str">
-        <f t="shared" ref="H571:H629" si="22">IF(A571="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A571)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -41011,10 +41265,6 @@
       </c>
     </row>
     <row r="573" spans="6:8">
-      <c r="F573" s="40" t="str">
-        <f>IF(A573="", "", "gift-codes.html?game=" &amp; A573)</f>
-        <v/>
-      </c>
       <c r="H573" s="41" t="str">
         <f t="shared" si="22"/>
         <v/>
@@ -41346,12 +41596,6 @@
     </row>
     <row r="628" spans="8:8">
       <c r="H628" s="41" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-    </row>
-    <row r="629" spans="8:8">
-      <c r="H629" s="41" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -41566,15 +41810,19 @@
     <hyperlink ref="E266"/>
     <hyperlink ref="D266" r:id="rId203"/>
     <hyperlink ref="E267" r:id="rId204"/>
+    <hyperlink ref="C268" r:id="rId205"/>
+    <hyperlink ref="D268" r:id="rId206" location="s1"/>
+    <hyperlink ref="G268" r:id="rId207"/>
+    <hyperlink ref="E268" r:id="rId208"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId205"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId209"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AX437"/>
+  <dimension ref="A1:AX436"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="19.5"/>
   <cols>
     <col min="1" max="1" width="24.375" style="13" customWidth="1"/>
@@ -51919,7 +52167,7 @@
         <v>4422</v>
       </c>
       <c r="Y156" s="18" t="s">
-        <v>4831</v>
+        <v>4825</v>
       </c>
     </row>
     <row r="157" spans="1:34" ht="22.5" customHeight="1">
@@ -53346,31 +53594,31 @@
         <v>3654</v>
       </c>
       <c r="Q185" s="18" t="s">
+        <v>4880</v>
+      </c>
+      <c r="S185" s="18" t="s">
+        <v>4881</v>
+      </c>
+      <c r="U185" s="18" t="s">
+        <v>4882</v>
+      </c>
+      <c r="W185" s="18" t="s">
+        <v>4883</v>
+      </c>
+      <c r="Y185" s="18" t="s">
+        <v>4884</v>
+      </c>
+      <c r="AA185" s="18" t="s">
+        <v>4885</v>
+      </c>
+      <c r="AC185" s="18" t="s">
+        <v>4886</v>
+      </c>
+      <c r="AE185" s="18" t="s">
+        <v>4887</v>
+      </c>
+      <c r="AG185" s="18" t="s">
         <v>4888</v>
-      </c>
-      <c r="S185" s="18" t="s">
-        <v>4889</v>
-      </c>
-      <c r="U185" s="18" t="s">
-        <v>4890</v>
-      </c>
-      <c r="W185" s="18" t="s">
-        <v>4891</v>
-      </c>
-      <c r="Y185" s="18" t="s">
-        <v>4892</v>
-      </c>
-      <c r="AA185" s="18" t="s">
-        <v>4893</v>
-      </c>
-      <c r="AC185" s="18" t="s">
-        <v>4894</v>
-      </c>
-      <c r="AE185" s="18" t="s">
-        <v>4895</v>
-      </c>
-      <c r="AG185" s="18" t="s">
-        <v>4896</v>
       </c>
     </row>
     <row r="186" spans="1:39" ht="22.5" customHeight="1">
@@ -53599,16 +53847,16 @@
         <v>4626</v>
       </c>
       <c r="AG190" s="18" t="s">
-        <v>4898</v>
+        <v>4890</v>
       </c>
       <c r="AI190" s="18" t="s">
-        <v>4899</v>
+        <v>4891</v>
       </c>
       <c r="AK190" s="18" t="s">
-        <v>4900</v>
+        <v>4892</v>
       </c>
       <c r="AM190" s="18" t="s">
-        <v>4901</v>
+        <v>4893</v>
       </c>
     </row>
     <row r="191" spans="1:39" ht="22.5" customHeight="1">
@@ -54493,52 +54741,52 @@
         <v>3756</v>
       </c>
       <c r="K206" s="17" t="s">
+        <v>4808</v>
+      </c>
+      <c r="L206" s="13" t="s">
+        <v>4809</v>
+      </c>
+      <c r="M206" s="18" t="s">
+        <v>4810</v>
+      </c>
+      <c r="N206" s="13" t="s">
+        <v>4811</v>
+      </c>
+      <c r="O206" s="18" t="s">
+        <v>4812</v>
+      </c>
+      <c r="P206" s="13" t="s">
+        <v>4813</v>
+      </c>
+      <c r="Q206" s="18" t="s">
         <v>4814</v>
       </c>
-      <c r="L206" s="13" t="s">
+      <c r="R206" s="25" t="s">
         <v>4815</v>
       </c>
-      <c r="M206" s="18" t="s">
+      <c r="S206" s="18" t="s">
         <v>4816</v>
       </c>
-      <c r="N206" s="13" t="s">
+      <c r="T206" s="13" t="s">
         <v>4817</v>
       </c>
-      <c r="O206" s="18" t="s">
+      <c r="U206" s="18" t="s">
         <v>4818</v>
       </c>
-      <c r="P206" s="13" t="s">
+      <c r="V206" s="13" t="s">
         <v>4819</v>
       </c>
-      <c r="Q206" s="18" t="s">
+      <c r="W206" s="18" t="s">
         <v>4820</v>
       </c>
-      <c r="R206" s="25" t="s">
-        <v>4821</v>
-      </c>
-      <c r="S206" s="18" t="s">
+      <c r="X206" s="71" t="s">
         <v>4822</v>
       </c>
-      <c r="T206" s="13" t="s">
+      <c r="Y206" s="18" t="s">
         <v>4823</v>
       </c>
-      <c r="U206" s="18" t="s">
+      <c r="Z206" s="13" t="s">
         <v>4824</v>
-      </c>
-      <c r="V206" s="13" t="s">
-        <v>4825</v>
-      </c>
-      <c r="W206" s="18" t="s">
-        <v>4826</v>
-      </c>
-      <c r="X206" s="71" t="s">
-        <v>4828</v>
-      </c>
-      <c r="Y206" s="18" t="s">
-        <v>4829</v>
-      </c>
-      <c r="Z206" s="13" t="s">
-        <v>4830</v>
       </c>
     </row>
     <row r="207" spans="1:50" ht="22.5" customHeight="1">
@@ -54649,7 +54897,7 @@
         <v>3853</v>
       </c>
       <c r="V208" s="13" t="s">
-        <v>4827</v>
+        <v>4821</v>
       </c>
       <c r="W208" s="18" t="s">
         <v>3854</v>
@@ -55553,7 +55801,7 @@
         <v>4146</v>
       </c>
       <c r="Y224" s="18" t="s">
-        <v>4832</v>
+        <v>4826</v>
       </c>
     </row>
     <row r="225" spans="1:47" ht="22.5" customHeight="1">
@@ -55723,13 +55971,13 @@
         <v>4397</v>
       </c>
       <c r="W227" s="18" t="s">
-        <v>4812</v>
+        <v>4806</v>
       </c>
       <c r="Y227" s="18" t="s">
-        <v>4813</v>
+        <v>4807</v>
       </c>
       <c r="AA227" s="71" t="s">
-        <v>4897</v>
+        <v>4889</v>
       </c>
     </row>
     <row r="228" spans="1:47" ht="22.5" customHeight="1">
@@ -56324,7 +56572,7 @@
         <v>4685</v>
       </c>
       <c r="U238" s="18" t="s">
-        <v>4833</v>
+        <v>4827</v>
       </c>
     </row>
     <row r="239" spans="1:47" ht="22.5" customHeight="1">
@@ -56843,7 +57091,7 @@
         <v>4755</v>
       </c>
       <c r="AA252" s="18" t="s">
-        <v>4834</v>
+        <v>4828</v>
       </c>
     </row>
     <row r="253" spans="1:27" ht="22.5" customHeight="1">
@@ -56852,7 +57100,7 @@
         <v>奇蹟MU：騎士袋你飛</v>
       </c>
       <c r="C253" s="13" t="str">
-        <f t="shared" ref="C253:C314" si="9">IF(A253="","", "giftcodesbanner/" &amp; A253 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" ref="C253:C268" si="9">IF(A253="","", "giftcodesbanner/" &amp; A253 &amp; "-禮包碼.jpg")</f>
         <v>giftcodesbanner/奇蹟MU：騎士袋你飛-禮包碼.jpg</v>
       </c>
       <c r="D253" s="13" t="str">
@@ -56894,10 +57142,10 @@
         <v>4651</v>
       </c>
       <c r="Q253" s="18" t="s">
-        <v>4835</v>
+        <v>4829</v>
       </c>
       <c r="R253" s="13" t="s">
-        <v>4836</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="254" spans="1:27" ht="22.5" customHeight="1">
@@ -57118,17 +57366,23 @@
         <f>IF(games!I259&lt;&gt;"", games!I259, "")</f>
         <v>在《少女掌門人》中，您可以體驗直式畫面單手操作的便捷，無論通勤、上學或睡前都能隨時暢玩。遊戲採用全自動戰鬥系統，少女們將會自行施展華麗必殺技與技能擊敗敵人，讓您觀看也能享受爽快戰鬥的視覺盛宴。透過無限可能的戰略組合，打造專屬您的最強戰術，提升門派實力，橫掃魔物！為了讓掌門人能夠快速成長，遊戲內設有豐富的兌換碼與禮包碼福利，提供豐厚資源助您一臂之力。此外，遊戲也支援代儲值服務，確保玩家能以快速安全的方式獲得所需物品，讓您輕鬆培育美少女角色，打造最強隊伍！立即加入，開啟您的掌門人生涯，享受培育少女、稱霸武林的成就感！</v>
       </c>
-      <c r="F259" s="17" t="s">
-        <v>4536</v>
+      <c r="F259" s="34" t="s">
+        <v>4720</v>
       </c>
       <c r="G259" s="13" t="s">
-        <v>4526</v>
-      </c>
-      <c r="K259" s="17" t="s">
-        <v>4536</v>
+        <v>3641</v>
+      </c>
+      <c r="H259" s="13" t="s">
+        <v>2625</v>
+      </c>
+      <c r="I259" s="13" t="s">
+        <v>4368</v>
+      </c>
+      <c r="K259" s="101" t="s">
+        <v>4916</v>
       </c>
       <c r="L259" s="13" t="s">
-        <v>4526</v>
+        <v>4917</v>
       </c>
     </row>
     <row r="260" spans="1:24">
@@ -57273,16 +57527,16 @@
         <v>《合併貓鎮》是一款可愛風格的合併益智手機遊戲，你將扮演一位貓咪鎮長，透過不斷合併相同物品來解鎖更高級的道具，打造出一個獨一無二的貓咪天堂。遊戲擁有豐富的任務系統和多元的場景設計，讓你在輕鬆療癒的氛圍中享受策略與創造的樂趣。想讓你的貓咪小鎮更加蓬勃發展嗎？別忘了領取兌換碼和禮包碼，迅速獲得豐富資源！若想快速增強實力，也可透過我們提供的代儲值服務，享受快速安全的交易體驗，讓你輕鬆成為貓咪鎮的頂級建築師！準備好與可愛貓咪們一同探索這個充滿驚喜的世界了嗎？</v>
       </c>
       <c r="F264" s="17" t="s">
-        <v>4842</v>
+        <v>4836</v>
       </c>
       <c r="G264" s="13" t="s">
-        <v>4841</v>
+        <v>4835</v>
       </c>
       <c r="K264" s="17" t="s">
-        <v>4842</v>
+        <v>4836</v>
       </c>
       <c r="L264" s="13" t="s">
-        <v>4841</v>
+        <v>4835</v>
       </c>
     </row>
     <row r="265" spans="1:24">
@@ -57302,17 +57556,23 @@
         <f>IF(games!I265&lt;&gt;"", games!I265, "")</f>
         <v>《幻牌交鋒》是一款集換式卡牌競技手遊，遊戲將帶你進入一個由神秘卡牌主宰的奇幻世界。玩家需要精心組建卡組，運用策略與智慧，與來自各地的玩家進行刺激的即時對戰。每張卡牌都擁有獨特的技能與屬性，考驗你的戰術佈局與臨場反應。想在牌桌上稱霸一方嗎？務必關注官方兌換碼與禮包碼，獲得稀有卡牌與豐富獎勵，讓你贏在起跑點！我們也提供快速安全的代儲值服務，讓你輕鬆獲取心儀的卡牌，迅速打造出最強牌組！</v>
       </c>
-      <c r="F265" s="17" t="s">
-        <v>4842</v>
+      <c r="F265" s="100" t="s">
+        <v>4912</v>
       </c>
       <c r="G265" s="13" t="s">
-        <v>4841</v>
+        <v>4913</v>
+      </c>
+      <c r="H265" s="13" t="s">
+        <v>4914</v>
+      </c>
+      <c r="I265" s="13" t="s">
+        <v>4915</v>
       </c>
       <c r="K265" s="17" t="s">
-        <v>4842</v>
+        <v>4910</v>
       </c>
       <c r="L265" s="13" t="s">
-        <v>4841</v>
+        <v>4911</v>
       </c>
     </row>
     <row r="266" spans="1:24">
@@ -57333,16 +57593,16 @@
         <v>《激鬥！王國保衛戰》是一款塔防競技手遊，完美結合了經典塔防玩法與即時對戰元素。你將扮演指揮官，在戰場上部署防禦塔，召喚英雄，與對手鬥智鬥勇，爭奪最終的勝利。遊戲保留了原作豐富的英雄與防禦塔系統，並加入了全新的PVP模式，讓你與全球玩家展開激烈對決。想在戰場上所向披靡嗎？別錯過官方提供的兌換碼和禮包碼，讓你輕鬆獲得資源，強化你的軍隊！若想快速壯大實力，我們也提供快速安全的代儲值服務，讓你無後顧之憂地專注於策略佈局，成為真正的塔防大師！</v>
       </c>
       <c r="F266" s="17" t="s">
-        <v>4842</v>
+        <v>4836</v>
       </c>
       <c r="G266" s="13" t="s">
-        <v>4841</v>
+        <v>4835</v>
       </c>
       <c r="K266" s="17" t="s">
-        <v>4842</v>
+        <v>4836</v>
       </c>
       <c r="L266" s="13" t="s">
-        <v>4841</v>
+        <v>4835</v>
       </c>
     </row>
     <row r="267" spans="1:24">
@@ -57363,70 +57623,113 @@
         <v>《嘟嘟臉惡作劇》是一款充滿日系可愛風格的放置養成遊戲。故事發生在一個充滿魔法的學院，玩家將與一群擁有特殊能力的可愛角色們相遇，一同展開奇妙的冒險。遊戲採用輕鬆的放置玩法，讓你在繁忙之餘也能享受角色養成的樂趣，並透過策略性的戰鬥配置，挑戰各種關卡。想讓你的角色們迅速成長，解鎖更多有趣劇情嗎？記得使用官方兌換碼及禮包碼，獲得大量經驗與珍稀道具！我們也提供代儲值服務，讓您快速安全地獲得所需資源，輕鬆養成最強戰隊，在嘟嘟臉的世界裡盡情惡作劇吧！</v>
       </c>
       <c r="F267" s="17" t="s">
-        <v>4842</v>
+        <v>4836</v>
       </c>
       <c r="G267" s="13" t="s">
-        <v>4841</v>
+        <v>4835</v>
       </c>
       <c r="K267" s="17" t="s">
-        <v>4880</v>
+        <v>4872</v>
       </c>
       <c r="L267" s="13" t="s">
-        <v>4884</v>
+        <v>4876</v>
       </c>
       <c r="M267" s="18" t="s">
-        <v>4881</v>
+        <v>4873</v>
       </c>
       <c r="N267" s="13" t="s">
-        <v>4884</v>
+        <v>4876</v>
       </c>
       <c r="O267" s="18" t="s">
-        <v>4882</v>
+        <v>4874</v>
       </c>
       <c r="P267" s="13" t="s">
-        <v>4884</v>
+        <v>4876</v>
       </c>
       <c r="Q267" s="18" t="s">
-        <v>4883</v>
+        <v>4875</v>
       </c>
       <c r="R267" s="13" t="s">
-        <v>4884</v>
+        <v>4876</v>
       </c>
       <c r="S267" s="18" t="s">
-        <v>4885</v>
+        <v>4877</v>
       </c>
       <c r="T267" s="13" t="s">
-        <v>4884</v>
+        <v>4876</v>
       </c>
       <c r="U267" s="18" t="s">
-        <v>4886</v>
+        <v>4878</v>
       </c>
       <c r="V267" s="13" t="s">
-        <v>4884</v>
+        <v>4876</v>
       </c>
       <c r="W267" s="18" t="s">
-        <v>4887</v>
+        <v>4879</v>
       </c>
       <c r="X267" s="13" t="s">
-        <v>4884</v>
+        <v>4876</v>
       </c>
     </row>
     <row r="268" spans="1:24">
       <c r="A268" s="13" t="str">
         <f>IF(games!A268="", "", games!A268)</f>
-        <v/>
+        <v>我的花園世界</v>
       </c>
       <c r="C268" s="13" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>giftcodesbanner/我的花園世界-禮包碼.jpg</v>
       </c>
       <c r="D268" s="13" t="str">
-        <f t="shared" ref="D268:D314" si="11">IF(A268="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A268)</f>
-        <v/>
+        <f t="shared" ref="D268" si="11">IF(A268="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A268)</f>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=我的花園世界</v>
       </c>
       <c r="E268" s="14" t="str">
         <f>IF(games!I268&lt;&gt;"", games!I268, "")</f>
-        <v/>
+        <v>《我的花園世界》是一款主打療癒種植與溫馨養成的沉浸式花園手遊，帶領玩家進入一個充滿花香的夢幻國度。你將化身為專業花藝師，親手培育超過三百種四季花卉，從播種、澆水到採摘，每一步都充滿了治癒感。遊戲玩法自由，不僅能隨心所欲地佈置你的花園，設計出獨一無二的花藝作品，還能與好友交流互動，增添許多樂趣。
+為了讓玩家快速體驗遊戲魅力，官方準備了豐富的兌換碼和禮包碼，只要輕鬆輸入序號，就能獲得稀有種子與實用道具，讓你的花園事業快速發展。遊戲也提供快速安全的代儲值服務，確保每一筆交易都安全無虞，讓你能夠無後顧之憂地沉浸在美麗的花花世界裡。現在就加入《我的花園世界》，打造屬於你的芬芳國度，開啟一段充滿愛與夢想的花藝人生！</v>
+      </c>
+      <c r="F268" s="34" t="s">
+        <v>4930</v>
+      </c>
+      <c r="G268" s="13" t="s">
+        <v>4931</v>
+      </c>
+      <c r="H268" s="13" t="s">
+        <v>2625</v>
+      </c>
+      <c r="I268" s="13" t="s">
+        <v>4368</v>
+      </c>
+      <c r="K268" s="17" t="s">
+        <v>4908</v>
+      </c>
+      <c r="L268" s="13" t="s">
+        <v>4909</v>
+      </c>
+      <c r="M268" s="18" t="s">
+        <v>4922</v>
+      </c>
+      <c r="N268" s="13" t="s">
+        <v>4926</v>
+      </c>
+      <c r="O268" s="18" t="s">
+        <v>4923</v>
+      </c>
+      <c r="P268" s="13" t="s">
+        <v>4927</v>
+      </c>
+      <c r="Q268" s="18" t="s">
+        <v>4924</v>
+      </c>
+      <c r="R268" s="13" t="s">
+        <v>4928</v>
+      </c>
+      <c r="S268" s="18" t="s">
+        <v>4925</v>
+      </c>
+      <c r="T268" s="13" t="s">
+        <v>4929</v>
       </c>
     </row>
     <row r="269" spans="1:24">
@@ -57435,11 +57738,11 @@
         <v/>
       </c>
       <c r="C269" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A269="","", "giftcodesbanner/" &amp; A269 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D269" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A269="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A269)</f>
         <v/>
       </c>
       <c r="E269" s="14" t="str">
@@ -57453,11 +57756,11 @@
         <v/>
       </c>
       <c r="C270" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A270="","", "giftcodesbanner/" &amp; A270 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D270" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A270="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A270)</f>
         <v/>
       </c>
       <c r="E270" s="14" t="str">
@@ -57471,11 +57774,11 @@
         <v/>
       </c>
       <c r="C271" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A271="","", "giftcodesbanner/" &amp; A271 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D271" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A271="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A271)</f>
         <v/>
       </c>
       <c r="E271" s="14" t="str">
@@ -57489,11 +57792,11 @@
         <v/>
       </c>
       <c r="C272" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A272="","", "giftcodesbanner/" &amp; A272 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D272" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A272="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A272)</f>
         <v/>
       </c>
       <c r="E272" s="14" t="str">
@@ -57501,231 +57804,227 @@
         <v/>
       </c>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" spans="1:4">
       <c r="A273" s="13" t="str">
         <f>IF(games!A273="", "", games!A273)</f>
         <v/>
       </c>
       <c r="C273" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A273="","", "giftcodesbanner/" &amp; A273 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D273" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="E273" s="14" t="str">
-        <f>IF(games!I273&lt;&gt;"", games!I273, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="1:5">
+        <f>IF(A273="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A273)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
       <c r="A274" s="13" t="str">
         <f>IF(games!A274="", "", games!A274)</f>
         <v/>
       </c>
       <c r="C274" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A274="","", "giftcodesbanner/" &amp; A274 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D274" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="275" spans="1:5">
+        <f>IF(A274="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A274)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
       <c r="A275" s="13" t="str">
         <f>IF(games!A275="", "", games!A275)</f>
         <v/>
       </c>
       <c r="C275" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A275="","", "giftcodesbanner/" &amp; A275 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D275" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="276" spans="1:5">
+        <f>IF(A275="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A275)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
       <c r="A276" s="13" t="str">
         <f>IF(games!A276="", "", games!A276)</f>
         <v/>
       </c>
       <c r="C276" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A276="","", "giftcodesbanner/" &amp; A276 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D276" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="277" spans="1:5">
+        <f>IF(A276="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A276)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
       <c r="A277" s="13" t="str">
         <f>IF(games!A277="", "", games!A277)</f>
         <v/>
       </c>
       <c r="C277" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A277="","", "giftcodesbanner/" &amp; A277 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D277" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="278" spans="1:5">
+        <f>IF(A277="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A277)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
       <c r="A278" s="13" t="str">
         <f>IF(games!A278="", "", games!A278)</f>
         <v/>
       </c>
       <c r="C278" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A278="","", "giftcodesbanner/" &amp; A278 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D278" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="279" spans="1:5">
+        <f>IF(A278="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A278)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
       <c r="A279" s="13" t="str">
         <f>IF(games!A279="", "", games!A279)</f>
         <v/>
       </c>
       <c r="C279" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A279="","", "giftcodesbanner/" &amp; A279 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D279" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="280" spans="1:5">
+        <f>IF(A279="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A279)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
       <c r="A280" s="13" t="str">
         <f>IF(games!A280="", "", games!A280)</f>
         <v/>
       </c>
       <c r="C280" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A280="","", "giftcodesbanner/" &amp; A280 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D280" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="281" spans="1:5">
+        <f>IF(A280="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A280)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
       <c r="A281" s="13" t="str">
         <f>IF(games!A281="", "", games!A281)</f>
         <v/>
       </c>
       <c r="C281" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A281="","", "giftcodesbanner/" &amp; A281 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D281" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="282" spans="1:5">
+        <f>IF(A281="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A281)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
       <c r="A282" s="13" t="str">
         <f>IF(games!A282="", "", games!A282)</f>
         <v/>
       </c>
       <c r="C282" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A282="","", "giftcodesbanner/" &amp; A282 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D282" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="1:5">
+        <f>IF(A282="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A282)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
       <c r="A283" s="13" t="str">
         <f>IF(games!A283="", "", games!A283)</f>
         <v/>
       </c>
       <c r="C283" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A283="","", "giftcodesbanner/" &amp; A283 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D283" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="1:5">
+        <f>IF(A283="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A283)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
       <c r="A284" s="13" t="str">
         <f>IF(games!A284="", "", games!A284)</f>
         <v/>
       </c>
       <c r="C284" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A284="","", "giftcodesbanner/" &amp; A284 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D284" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="285" spans="1:5">
+        <f>IF(A284="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A284)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
       <c r="A285" s="13" t="str">
         <f>IF(games!A285="", "", games!A285)</f>
         <v/>
       </c>
       <c r="C285" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A285="","", "giftcodesbanner/" &amp; A285 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D285" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="286" spans="1:5">
+        <f>IF(A285="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A285)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
       <c r="A286" s="13" t="str">
         <f>IF(games!A286="", "", games!A286)</f>
         <v/>
       </c>
       <c r="C286" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A286="","", "giftcodesbanner/" &amp; A286 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D286" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="287" spans="1:5">
+        <f>IF(A286="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A286)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
       <c r="A287" s="13" t="str">
         <f>IF(games!A287="", "", games!A287)</f>
         <v/>
       </c>
       <c r="C287" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A287="","", "giftcodesbanner/" &amp; A287 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D287" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="288" spans="1:5">
+        <f>IF(A287="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A287)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
       <c r="A288" s="13" t="str">
         <f>IF(games!A288="", "", games!A288)</f>
         <v/>
       </c>
       <c r="C288" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A288="","", "giftcodesbanner/" &amp; A288 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D288" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A288="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A288)</f>
         <v/>
       </c>
     </row>
@@ -57735,11 +58034,11 @@
         <v/>
       </c>
       <c r="C289" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A289="","", "giftcodesbanner/" &amp; A289 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D289" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A289="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A289)</f>
         <v/>
       </c>
     </row>
@@ -57749,11 +58048,11 @@
         <v/>
       </c>
       <c r="C290" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A290="","", "giftcodesbanner/" &amp; A290 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D290" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A290="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A290)</f>
         <v/>
       </c>
     </row>
@@ -57763,11 +58062,11 @@
         <v/>
       </c>
       <c r="C291" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A291="","", "giftcodesbanner/" &amp; A291 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D291" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A291="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A291)</f>
         <v/>
       </c>
     </row>
@@ -57777,11 +58076,11 @@
         <v/>
       </c>
       <c r="C292" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A292="","", "giftcodesbanner/" &amp; A292 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D292" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A292="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A292)</f>
         <v/>
       </c>
     </row>
@@ -57791,11 +58090,11 @@
         <v/>
       </c>
       <c r="C293" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A293="","", "giftcodesbanner/" &amp; A293 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D293" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A293="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A293)</f>
         <v/>
       </c>
     </row>
@@ -57805,11 +58104,11 @@
         <v/>
       </c>
       <c r="C294" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A294="","", "giftcodesbanner/" &amp; A294 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D294" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A294="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A294)</f>
         <v/>
       </c>
     </row>
@@ -57819,11 +58118,11 @@
         <v/>
       </c>
       <c r="C295" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A295="","", "giftcodesbanner/" &amp; A295 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D295" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A295="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A295)</f>
         <v/>
       </c>
     </row>
@@ -57833,11 +58132,11 @@
         <v/>
       </c>
       <c r="C296" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A296="","", "giftcodesbanner/" &amp; A296 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D296" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A296="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A296)</f>
         <v/>
       </c>
     </row>
@@ -57847,11 +58146,11 @@
         <v/>
       </c>
       <c r="C297" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A297="","", "giftcodesbanner/" &amp; A297 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D297" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A297="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A297)</f>
         <v/>
       </c>
     </row>
@@ -57861,11 +58160,11 @@
         <v/>
       </c>
       <c r="C298" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A298="","", "giftcodesbanner/" &amp; A298 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D298" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A298="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A298)</f>
         <v/>
       </c>
     </row>
@@ -57875,11 +58174,11 @@
         <v/>
       </c>
       <c r="C299" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A299="","", "giftcodesbanner/" &amp; A299 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D299" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A299="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A299)</f>
         <v/>
       </c>
     </row>
@@ -57889,11 +58188,11 @@
         <v/>
       </c>
       <c r="C300" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A300="","", "giftcodesbanner/" &amp; A300 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D300" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A300="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A300)</f>
         <v/>
       </c>
     </row>
@@ -57903,11 +58202,11 @@
         <v/>
       </c>
       <c r="C301" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A301="","", "giftcodesbanner/" &amp; A301 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D301" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A301="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A301)</f>
         <v/>
       </c>
     </row>
@@ -57917,11 +58216,11 @@
         <v/>
       </c>
       <c r="C302" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A302="","", "giftcodesbanner/" &amp; A302 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D302" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A302="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A302)</f>
         <v/>
       </c>
     </row>
@@ -57931,11 +58230,11 @@
         <v/>
       </c>
       <c r="C303" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A303="","", "giftcodesbanner/" &amp; A303 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D303" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(A303="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A303)</f>
         <v/>
       </c>
     </row>
@@ -57945,129 +58244,125 @@
         <v/>
       </c>
       <c r="C304" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A304="","", "giftcodesbanner/" &amp; A304 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D304" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="305" spans="1:4">
-      <c r="A305" s="13" t="str">
-        <f>IF(games!A305="", "", games!A305)</f>
-        <v/>
-      </c>
+        <f>IF(A304="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A304)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="305" spans="3:4">
       <c r="C305" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A305="","", "giftcodesbanner/" &amp; A305 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D305" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="306" spans="1:4">
+        <f>IF(A305="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A305)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="306" spans="3:4">
       <c r="C306" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A306="","", "giftcodesbanner/" &amp; A306 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D306" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="307" spans="1:4">
+        <f>IF(A306="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A306)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="307" spans="3:4">
       <c r="C307" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A307="","", "giftcodesbanner/" &amp; A307 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D307" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="308" spans="1:4">
+        <f>IF(A307="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A307)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="308" spans="3:4">
       <c r="C308" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A308="","", "giftcodesbanner/" &amp; A308 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D308" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="309" spans="1:4">
+        <f>IF(A308="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A308)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="309" spans="3:4">
       <c r="C309" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A309="","", "giftcodesbanner/" &amp; A309 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D309" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="310" spans="1:4">
+        <f>IF(A309="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A309)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="310" spans="3:4">
       <c r="C310" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A310="","", "giftcodesbanner/" &amp; A310 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D310" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="311" spans="1:4">
+        <f>IF(A310="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A310)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="311" spans="3:4">
       <c r="C311" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A311="","", "giftcodesbanner/" &amp; A311 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D311" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="312" spans="1:4">
+        <f>IF(A311="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A311)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312" spans="3:4">
       <c r="C312" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A312="","", "giftcodesbanner/" &amp; A312 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D312" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="313" spans="1:4">
+        <f>IF(A312="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A312)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="313" spans="3:4">
       <c r="C313" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(A313="","", "giftcodesbanner/" &amp; A313 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D313" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="314" spans="1:4">
+        <f>IF(A313="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A313)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="314" spans="3:4">
       <c r="C314" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="C314:C377" si="12">IF(A314="","", "giftcodesbanner/" &amp; A314 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D314" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="315" spans="1:4">
+        <f t="shared" ref="D314:D377" si="13">IF(A314="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A314)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315" spans="3:4">
       <c r="C315" s="13" t="str">
-        <f t="shared" ref="C315:C378" si="12">IF(A315="","", "giftcodesbanner/" &amp; A315 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D315" s="13" t="str">
-        <f t="shared" ref="D315:D378" si="13">IF(A315="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A315)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="316" spans="1:4">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="316" spans="3:4">
       <c r="C316" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58077,7 +58372,7 @@
         <v/>
       </c>
     </row>
-    <row r="317" spans="1:4">
+    <row r="317" spans="3:4">
       <c r="C317" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58087,7 +58382,7 @@
         <v/>
       </c>
     </row>
-    <row r="318" spans="1:4">
+    <row r="318" spans="3:4">
       <c r="C318" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58097,7 +58392,7 @@
         <v/>
       </c>
     </row>
-    <row r="319" spans="1:4">
+    <row r="319" spans="3:4">
       <c r="C319" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58107,7 +58402,7 @@
         <v/>
       </c>
     </row>
-    <row r="320" spans="1:4">
+    <row r="320" spans="3:4">
       <c r="C320" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58689,21 +58984,21 @@
     </row>
     <row r="378" spans="3:4">
       <c r="C378" s="13" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="C378:C436" si="14">IF(A378="","", "giftcodesbanner/" &amp; A378 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D378" s="13" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="D378:D436" si="15">IF(A378="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A378)</f>
         <v/>
       </c>
     </row>
     <row r="379" spans="3:4">
       <c r="C379" s="13" t="str">
-        <f t="shared" ref="C379:C437" si="14">IF(A379="","", "giftcodesbanner/" &amp; A379 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D379" s="13" t="str">
-        <f t="shared" ref="D379:D437" si="15">IF(A379="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A379)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -59273,16 +59568,6 @@
         <v/>
       </c>
       <c r="D436" s="13" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="437" spans="3:4">
-      <c r="C437" s="13" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="D437" s="13" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -59294,8 +59579,9 @@
     <hyperlink ref="F225" r:id="rId2"/>
     <hyperlink ref="F236" r:id="rId3" display="https://ref.gamer.com.tw/redir.php?url=https%3A%2F%2Fcoupon.netmarble.com%2Ftskgb"/>
     <hyperlink ref="F245" r:id="rId4"/>
+    <hyperlink ref="F265" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -19055,11 +19055,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>《我的花園世界》是一款主打療癒種植與溫馨養成的沉浸式花園手遊，帶領玩家進入一個充滿花香的夢幻國度。你將化身為專業花藝師，親手培育超過三百種四季花卉，從播種、澆水到採摘，每一步都充滿了治癒感。遊戲玩法自由，不僅能隨心所欲地佈置你的花園，設計出獨一無二的花藝作品，還能與好友交流互動，增添許多樂趣。
-為了讓玩家快速體驗遊戲魅力，官方準備了豐富的兌換碼和禮包碼，只要輕鬆輸入序號，就能獲得稀有種子與實用道具，讓你的花園事業快速發展。遊戲也提供快速安全的代儲值服務，確保每一筆交易都安全無虞，讓你能夠無後顧之憂地沉浸在美麗的花花世界裡。現在就加入《我的花園世界》，打造屬於你的芬芳國度，開啟一段充滿愛與夢想的花藝人生！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>6000元寶</t>
   </si>
   <si>
@@ -19073,6 +19068,11 @@
   </si>
   <si>
     <t>VIP特權</t>
+  </si>
+  <si>
+    <t>《我的花園世界》是一款主打療癒種植與溫馨養成的沉浸式手遊，帶你進入一個充滿花香的夢幻國度。你將化身專業花藝師，親手培育四季花卉，從播種到採摘，每一步都充滿治癒感。遊戲玩法自由，能隨心佈置花園，設計獨特花藝作品，還能與好友交流，增添許多樂趣。
+為了讓玩家快速上手，官方準備了豐富的兌換碼和禮包碼，輸入序號就能獲得稀有種子與道具，讓你的花園事業快速發展。遊戲也提供快速安全的代儲值服務，確保交易安心無虞，讓你能夠無後顧之憂地沉浸在美麗的花花世界裡。現在就加入《我的花園世界》，開啟一段充滿愛與夢想的花藝人生吧！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -38161,10 +38161,10 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/我的花園世界.html</v>
       </c>
       <c r="I268" s="42" t="s">
+        <v>4937</v>
+      </c>
+      <c r="J268" s="1" t="s">
         <v>4932</v>
-      </c>
-      <c r="J268" s="1" t="s">
-        <v>4933</v>
       </c>
       <c r="K268" s="72">
         <v>2609</v>
@@ -38176,7 +38176,7 @@
         <v>1365</v>
       </c>
       <c r="N268" s="1" t="s">
-        <v>4934</v>
+        <v>4933</v>
       </c>
       <c r="O268" s="72">
         <v>807</v>
@@ -38188,7 +38188,7 @@
         <v>546</v>
       </c>
       <c r="R268" s="1" t="s">
-        <v>4935</v>
+        <v>4934</v>
       </c>
       <c r="S268" s="72">
         <v>400</v>
@@ -38212,13 +38212,13 @@
         <v>29</v>
       </c>
       <c r="Z268" s="1" t="s">
-        <v>4936</v>
+        <v>4935</v>
       </c>
       <c r="AA268" s="72">
         <v>29</v>
       </c>
       <c r="AB268" s="1" t="s">
-        <v>4937</v>
+        <v>4936</v>
       </c>
       <c r="AC268" s="72">
         <v>145</v>
@@ -57686,8 +57686,8 @@
       </c>
       <c r="E268" s="14" t="str">
         <f>IF(games!I268&lt;&gt;"", games!I268, "")</f>
-        <v>《我的花園世界》是一款主打療癒種植與溫馨養成的沉浸式花園手遊，帶領玩家進入一個充滿花香的夢幻國度。你將化身為專業花藝師，親手培育超過三百種四季花卉，從播種、澆水到採摘，每一步都充滿了治癒感。遊戲玩法自由，不僅能隨心所欲地佈置你的花園，設計出獨一無二的花藝作品，還能與好友交流互動，增添許多樂趣。
-為了讓玩家快速體驗遊戲魅力，官方準備了豐富的兌換碼和禮包碼，只要輕鬆輸入序號，就能獲得稀有種子與實用道具，讓你的花園事業快速發展。遊戲也提供快速安全的代儲值服務，確保每一筆交易都安全無虞，讓你能夠無後顧之憂地沉浸在美麗的花花世界裡。現在就加入《我的花園世界》，打造屬於你的芬芳國度，開啟一段充滿愛與夢想的花藝人生！</v>
+        <v>《我的花園世界》是一款主打療癒種植與溫馨養成的沉浸式手遊，帶你進入一個充滿花香的夢幻國度。你將化身專業花藝師，親手培育四季花卉，從播種到採摘，每一步都充滿治癒感。遊戲玩法自由，能隨心佈置花園，設計獨特花藝作品，還能與好友交流，增添許多樂趣。
+為了讓玩家快速上手，官方準備了豐富的兌換碼和禮包碼，輸入序號就能獲得稀有種子與道具，讓你的花園事業快速發展。遊戲也提供快速安全的代儲值服務，確保交易安心無虞，讓你能夠無後顧之憂地沉浸在美麗的花花世界裡。現在就加入《我的花園世界》，開啟一段充滿愛與夢想的花藝人生吧！</v>
       </c>
       <c r="F268" s="34" t="s">
         <v>4930</v>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -19070,8 +19070,7 @@
     <t>VIP特權</t>
   </si>
   <si>
-    <t>《我的花園世界》是一款主打療癒種植與溫馨養成的沉浸式手遊，帶你進入一個充滿花香的夢幻國度。你將化身專業花藝師，親手培育四季花卉，從播種到採摘，每一步都充滿治癒感。遊戲玩法自由，能隨心佈置花園，設計獨特花藝作品，還能與好友交流，增添許多樂趣。
-為了讓玩家快速上手，官方準備了豐富的兌換碼和禮包碼，輸入序號就能獲得稀有種子與道具，讓你的花園事業快速發展。遊戲也提供快速安全的代儲值服務，確保交易安心無虞，讓你能夠無後顧之憂地沉浸在美麗的花花世界裡。現在就加入《我的花園世界》，開啟一段充滿愛與夢想的花藝人生吧！</t>
+    <t>《我的花園世界》是由 FLORAL GAMES 推出的療癒系模擬手遊，融合花園經營、養成與社交互動。玩家將化身花藝師，親手培育多種花卉，從播種到盛開，體驗成長的喜悅。你可自由佈置花園、設計花藝作品，打造專屬的夢幻空間。官方不定期釋出禮包碼與兌換碼，輕鬆獲得稀有道具與資源。若有儲值需求，建議使用快速、安全的代儲值服務，確保交易無虞。立即加入《我的花園世界》，開啟療癒花園之旅吧！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -57686,8 +57685,7 @@
       </c>
       <c r="E268" s="14" t="str">
         <f>IF(games!I268&lt;&gt;"", games!I268, "")</f>
-        <v>《我的花園世界》是一款主打療癒種植與溫馨養成的沉浸式手遊，帶你進入一個充滿花香的夢幻國度。你將化身專業花藝師，親手培育四季花卉，從播種到採摘，每一步都充滿治癒感。遊戲玩法自由，能隨心佈置花園，設計獨特花藝作品，還能與好友交流，增添許多樂趣。
-為了讓玩家快速上手，官方準備了豐富的兌換碼和禮包碼，輸入序號就能獲得稀有種子與道具，讓你的花園事業快速發展。遊戲也提供快速安全的代儲值服務，確保交易安心無虞，讓你能夠無後顧之憂地沉浸在美麗的花花世界裡。現在就加入《我的花園世界》，開啟一段充滿愛與夢想的花藝人生吧！</v>
+        <v>《我的花園世界》是由 FLORAL GAMES 推出的療癒系模擬手遊，融合花園經營、養成與社交互動。玩家將化身花藝師，親手培育多種花卉，從播種到盛開，體驗成長的喜悅。你可自由佈置花園、設計花藝作品，打造專屬的夢幻空間。官方不定期釋出禮包碼與兌換碼，輕鬆獲得稀有道具與資源。若有儲值需求，建議使用快速、安全的代儲值服務，確保交易無虞。立即加入《我的花園世界》，開啟療癒花園之旅吧！</v>
       </c>
       <c r="F268" s="34" t="s">
         <v>4930</v>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -18956,46 +18956,114 @@
     <t>豪華通行券</t>
   </si>
   <si>
+    <t>FLOWER</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>元寶*30+水滴*65+金幣*8888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>butterfu.u</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>閃電寶箱*1+金幣*2000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://redeem-code.eidolons-cross.com/html/TW/redeem_code/redeem-code.html</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲內右上角「選單」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>進到「設定」之後記住玩家ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>到網址內輸入ID跟禮包碼按確認即可領取</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>006892699</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600寶石邀請碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://hjxp.floralgames.net/reserve/index.html#s1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E6%88%91%E7%9A%84%E8%8A%B1%E5%9C%92%E4%B8%96%E7%95%8C/id6751560944</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GD666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GD888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GD999</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GD520</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水滴*20+金幣*1000+雇傭書*5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水雞*20+金幣*1000+加速卡*20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>元寶*20+金幣*1000+花坊幣*10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*1000+加速卡*10+花坊幣*30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>進到遊戲內按右上角「設定」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點最底下的「兌換碼」選項</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6000元寶</t>
+  </si>
+  <si>
+    <t>1800元寶</t>
+  </si>
+  <si>
+    <t>900元寶</t>
+  </si>
+  <si>
+    <t>免廣告</t>
+  </si>
+  <si>
+    <t>VIP特權</t>
+  </si>
+  <si>
     <t>我的花園世界</t>
-  </si>
-  <si>
-    <t>FLOWER</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>元寶*30+水滴*65+金幣*8888</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>butterfu.u</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>閃電寶箱*1+金幣*2000</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://redeem-code.eidolons-cross.com/html/TW/redeem_code/redeem-code.html</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>遊戲內右上角「選單」</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>進到「設定」之後記住玩家ID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>到網址內輸入ID跟禮包碼按確認即可領取</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>006892699</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>600寶石邀請碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.floralgames.hjxp&amp;referrer=utm_source%3Dgamer.com.tw%26utm_campaign%3Dgnn</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -19003,74 +19071,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>https://hjxp.floralgames.net/reserve/index.html#s1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://play.google.com/store/apps/details?id=com.floralgames.hjxp&amp;referrer=utm_source%3Dgamer.com.tw%26utm_campaign%3Dgnn</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://apps.apple.com/tw/app/%E6%88%91%E7%9A%84%E8%8A%B1%E5%9C%92%E4%B8%96%E7%95%8C/id6751560944</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GD666</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GD888</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GD999</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GD520</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>水滴*20+金幣*1000+雇傭書*5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>水雞*20+金幣*1000+加速卡*20</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>元寶*20+金幣*1000+花坊幣*10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>金幣*1000+加速卡*10+花坊幣*30</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>進到遊戲內按右上角「設定」</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>點最底下的「兌換碼」選項</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>6000元寶</t>
-  </si>
-  <si>
-    <t>1800元寶</t>
-  </si>
-  <si>
-    <t>900元寶</t>
-  </si>
-  <si>
-    <t>免廣告</t>
-  </si>
-  <si>
-    <t>VIP特權</t>
-  </si>
-  <si>
-    <t>《我的花園世界》是由 FLORAL GAMES 推出的療癒系模擬手遊，融合花園經營、養成與社交互動。玩家將化身花藝師，親手培育多種花卉，從播種到盛開，體驗成長的喜悅。你可自由佈置花園、設計花藝作品，打造專屬的夢幻空間。官方不定期釋出禮包碼與兌換碼，輕鬆獲得稀有道具與資源。若有儲值需求，建議使用快速、安全的代儲值服務，確保交易無虞。立即加入《我的花園世界》，開啟療癒花園之旅吧！</t>
+    <t>踏入《我的花園世界》，一個充滿奇幻與溫馨的養成冒險，讓你在忙碌的生活中找到一片心靈綠洲！這款手遊將帶你探索魔法大陸，與可愛的花仙子們一同培育珍奇植物，從零開始打造屬於你的夢想莊園。遊戲結合了多元的養成、裝飾與社交玩法，不僅能自由裝扮你的花園，更能拜訪好友，互贈禮物，共創美好回憶。想加速成長？別擔心，豐富的兌換碼和禮包碼讓你輕鬆取得稀有資源，快速提升等級。我們也提供代儲值服務，讓你享受快速安全的交易體驗，輕鬆購入心儀的限定道具。快來加入，與全球玩家一起體驗這場療癒又趣味的園藝之旅吧！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -38136,24 +38137,24 @@
       </c>
     </row>
     <row r="268" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A268" s="72" t="s">
-        <v>4907</v>
+      <c r="A268" s="3" t="s">
+        <v>4934</v>
       </c>
       <c r="C268" s="5" t="s">
+        <v>4936</v>
+      </c>
+      <c r="D268" s="4" t="s">
+        <v>4917</v>
+      </c>
+      <c r="E268" s="4" t="s">
         <v>4918</v>
-      </c>
-      <c r="D268" s="4" t="s">
-        <v>4919</v>
-      </c>
-      <c r="E268" s="4" t="s">
-        <v>4921</v>
       </c>
       <c r="F268" s="40" t="str">
         <f t="shared" ref="F268:F313" si="12">IF(A268="", "", "gift-codes.html?game=" &amp; A268)</f>
         <v>gift-codes.html?game=我的花園世界</v>
       </c>
       <c r="G268" s="4" t="s">
-        <v>4920</v>
+        <v>4935</v>
       </c>
       <c r="H268" s="41" t="str">
         <f t="shared" si="11"/>
@@ -38163,7 +38164,7 @@
         <v>4937</v>
       </c>
       <c r="J268" s="1" t="s">
-        <v>4932</v>
+        <v>4929</v>
       </c>
       <c r="K268" s="72">
         <v>2609</v>
@@ -38175,7 +38176,7 @@
         <v>1365</v>
       </c>
       <c r="N268" s="1" t="s">
-        <v>4933</v>
+        <v>4930</v>
       </c>
       <c r="O268" s="72">
         <v>807</v>
@@ -38187,7 +38188,7 @@
         <v>546</v>
       </c>
       <c r="R268" s="1" t="s">
-        <v>4934</v>
+        <v>4931</v>
       </c>
       <c r="S268" s="72">
         <v>400</v>
@@ -38211,13 +38212,13 @@
         <v>29</v>
       </c>
       <c r="Z268" s="1" t="s">
-        <v>4935</v>
+        <v>4932</v>
       </c>
       <c r="AA268" s="72">
         <v>29</v>
       </c>
       <c r="AB268" s="1" t="s">
-        <v>4936</v>
+        <v>4933</v>
       </c>
       <c r="AC268" s="72">
         <v>145</v>
@@ -57378,10 +57379,10 @@
         <v>4368</v>
       </c>
       <c r="K259" s="101" t="s">
+        <v>4915</v>
+      </c>
+      <c r="L259" s="13" t="s">
         <v>4916</v>
-      </c>
-      <c r="L259" s="13" t="s">
-        <v>4917</v>
       </c>
     </row>
     <row r="260" spans="1:24">
@@ -57556,22 +57557,22 @@
         <v>《幻牌交鋒》是一款集換式卡牌競技手遊，遊戲將帶你進入一個由神秘卡牌主宰的奇幻世界。玩家需要精心組建卡組，運用策略與智慧，與來自各地的玩家進行刺激的即時對戰。每張卡牌都擁有獨特的技能與屬性，考驗你的戰術佈局與臨場反應。想在牌桌上稱霸一方嗎？務必關注官方兌換碼與禮包碼，獲得稀有卡牌與豐富獎勵，讓你贏在起跑點！我們也提供快速安全的代儲值服務，讓你輕鬆獲取心儀的卡牌，迅速打造出最強牌組！</v>
       </c>
       <c r="F265" s="100" t="s">
+        <v>4911</v>
+      </c>
+      <c r="G265" s="13" t="s">
         <v>4912</v>
       </c>
-      <c r="G265" s="13" t="s">
+      <c r="H265" s="13" t="s">
         <v>4913</v>
       </c>
-      <c r="H265" s="13" t="s">
+      <c r="I265" s="13" t="s">
         <v>4914</v>
       </c>
-      <c r="I265" s="13" t="s">
-        <v>4915</v>
-      </c>
       <c r="K265" s="17" t="s">
+        <v>4909</v>
+      </c>
+      <c r="L265" s="13" t="s">
         <v>4910</v>
-      </c>
-      <c r="L265" s="13" t="s">
-        <v>4911</v>
       </c>
     </row>
     <row r="266" spans="1:24">
@@ -57685,13 +57686,13 @@
       </c>
       <c r="E268" s="14" t="str">
         <f>IF(games!I268&lt;&gt;"", games!I268, "")</f>
-        <v>《我的花園世界》是由 FLORAL GAMES 推出的療癒系模擬手遊，融合花園經營、養成與社交互動。玩家將化身花藝師，親手培育多種花卉，從播種到盛開，體驗成長的喜悅。你可自由佈置花園、設計花藝作品，打造專屬的夢幻空間。官方不定期釋出禮包碼與兌換碼，輕鬆獲得稀有道具與資源。若有儲值需求，建議使用快速、安全的代儲值服務，確保交易無虞。立即加入《我的花園世界》，開啟療癒花園之旅吧！</v>
+        <v>踏入《我的花園世界》，一個充滿奇幻與溫馨的養成冒險，讓你在忙碌的生活中找到一片心靈綠洲！這款手遊將帶你探索魔法大陸，與可愛的花仙子們一同培育珍奇植物，從零開始打造屬於你的夢想莊園。遊戲結合了多元的養成、裝飾與社交玩法，不僅能自由裝扮你的花園，更能拜訪好友，互贈禮物，共創美好回憶。想加速成長？別擔心，豐富的兌換碼和禮包碼讓你輕鬆取得稀有資源，快速提升等級。我們也提供代儲值服務，讓你享受快速安全的交易體驗，輕鬆購入心儀的限定道具。快來加入，與全球玩家一起體驗這場療癒又趣味的園藝之旅吧！</v>
       </c>
       <c r="F268" s="34" t="s">
-        <v>4930</v>
+        <v>4927</v>
       </c>
       <c r="G268" s="13" t="s">
-        <v>4931</v>
+        <v>4928</v>
       </c>
       <c r="H268" s="13" t="s">
         <v>2625</v>
@@ -57700,34 +57701,34 @@
         <v>4368</v>
       </c>
       <c r="K268" s="17" t="s">
+        <v>4907</v>
+      </c>
+      <c r="L268" s="13" t="s">
         <v>4908</v>
       </c>
-      <c r="L268" s="13" t="s">
-        <v>4909</v>
-      </c>
       <c r="M268" s="18" t="s">
+        <v>4919</v>
+      </c>
+      <c r="N268" s="13" t="s">
+        <v>4923</v>
+      </c>
+      <c r="O268" s="18" t="s">
+        <v>4920</v>
+      </c>
+      <c r="P268" s="13" t="s">
+        <v>4924</v>
+      </c>
+      <c r="Q268" s="18" t="s">
+        <v>4921</v>
+      </c>
+      <c r="R268" s="13" t="s">
+        <v>4925</v>
+      </c>
+      <c r="S268" s="18" t="s">
         <v>4922</v>
       </c>
-      <c r="N268" s="13" t="s">
+      <c r="T268" s="13" t="s">
         <v>4926</v>
-      </c>
-      <c r="O268" s="18" t="s">
-        <v>4923</v>
-      </c>
-      <c r="P268" s="13" t="s">
-        <v>4927</v>
-      </c>
-      <c r="Q268" s="18" t="s">
-        <v>4924</v>
-      </c>
-      <c r="R268" s="13" t="s">
-        <v>4928</v>
-      </c>
-      <c r="S268" s="18" t="s">
-        <v>4925</v>
-      </c>
-      <c r="T268" s="13" t="s">
-        <v>4929</v>
       </c>
     </row>
     <row r="269" spans="1:24">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7239" uniqueCount="4938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7236" uniqueCount="4943">
   <si>
     <t>Facebook</t>
   </si>
@@ -18829,38 +18829,6 @@
     <t>360台幣禮包</t>
   </si>
   <si>
-    <t>WITHU2ND</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>JJAZAN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HAPPY2GETHER</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2YEARGIFT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>韓服</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>5MANCAFE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>OPENTHEBAK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HANGAWIGIFT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HLM810</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -19072,6 +19040,58 @@
   </si>
   <si>
     <t>踏入《我的花園世界》，一個充滿奇幻與溫馨的養成冒險，讓你在忙碌的生活中找到一片心靈綠洲！這款手遊將帶你探索魔法大陸，與可愛的花仙子們一同培育珍奇植物，從零開始打造屬於你的夢想莊園。遊戲結合了多元的養成、裝飾與社交玩法，不僅能自由裝扮你的花園，更能拜訪好友，互贈禮物，共創美好回憶。想加速成長？別擔心，豐富的兌換碼和禮包碼讓你輕鬆取得稀有資源，快速提升等級。我們也提供代儲值服務，讓你享受快速安全的交易體驗，輕鬆購入心儀的限定道具。快來加入，與全球玩家一起體驗這場療癒又趣味的園藝之旅吧！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TKRANKIN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRICKCAL109</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRICKCALOB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TKRELEASE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>YOMILOVEU</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TK777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TK888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TK2025</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主畫面右上角三條線「選單」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點齒輪圖按「設定」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>按右上角其他之後找到登陸兌換券</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>貼上在SSbuy複製好的禮包兌換碼點套用</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>到信箱領取兌換碼的免費禮包</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -37784,73 +37804,73 @@
         <v>4805</v>
       </c>
       <c r="J263" s="1" t="s">
-        <v>4894</v>
+        <v>4886</v>
       </c>
       <c r="K263" s="72">
         <v>2371</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>4895</v>
+        <v>4887</v>
       </c>
       <c r="M263" s="72">
         <v>1204</v>
       </c>
       <c r="N263" s="1" t="s">
-        <v>4896</v>
+        <v>4888</v>
       </c>
       <c r="O263" s="72">
         <v>563</v>
       </c>
       <c r="P263" s="1" t="s">
-        <v>4897</v>
+        <v>4889</v>
       </c>
       <c r="Q263" s="72">
         <v>261</v>
       </c>
       <c r="R263" s="1" t="s">
-        <v>4898</v>
+        <v>4890</v>
       </c>
       <c r="S263" s="72">
         <v>128</v>
       </c>
       <c r="T263" s="1" t="s">
-        <v>4899</v>
+        <v>4891</v>
       </c>
       <c r="U263" s="72">
         <v>26</v>
       </c>
       <c r="V263" s="1" t="s">
-        <v>4900</v>
+        <v>4892</v>
       </c>
       <c r="W263" s="72">
         <v>400</v>
       </c>
       <c r="X263" s="1" t="s">
-        <v>4901</v>
+        <v>4893</v>
       </c>
       <c r="Y263" s="72">
         <v>128</v>
       </c>
       <c r="Z263" s="1" t="s">
-        <v>4902</v>
+        <v>4894</v>
       </c>
       <c r="AA263" s="72">
         <v>2371</v>
       </c>
       <c r="AB263" s="99" t="s">
-        <v>4903</v>
+        <v>4895</v>
       </c>
       <c r="AC263" s="72">
         <v>1204</v>
       </c>
       <c r="AD263" s="1" t="s">
-        <v>4904</v>
+        <v>4896</v>
       </c>
       <c r="AE263" s="72">
         <v>400</v>
       </c>
       <c r="AF263" s="1" t="s">
-        <v>4905</v>
+        <v>4897</v>
       </c>
       <c r="AG263" s="72">
         <v>26</v>
@@ -37948,7 +37968,7 @@
         <v>26</v>
       </c>
       <c r="V265" s="1" t="s">
-        <v>4906</v>
+        <v>4898</v>
       </c>
       <c r="W265" s="72">
         <v>247</v>
@@ -38138,33 +38158,33 @@
     </row>
     <row r="268" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A268" s="3" t="s">
-        <v>4934</v>
+        <v>4926</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>4936</v>
+        <v>4928</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>4917</v>
+        <v>4909</v>
       </c>
       <c r="E268" s="4" t="s">
-        <v>4918</v>
+        <v>4910</v>
       </c>
       <c r="F268" s="40" t="str">
         <f t="shared" ref="F268:F313" si="12">IF(A268="", "", "gift-codes.html?game=" &amp; A268)</f>
         <v>gift-codes.html?game=我的花園世界</v>
       </c>
       <c r="G268" s="4" t="s">
-        <v>4935</v>
+        <v>4927</v>
       </c>
       <c r="H268" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/我的花園世界.html</v>
       </c>
       <c r="I268" s="42" t="s">
-        <v>4937</v>
+        <v>4929</v>
       </c>
       <c r="J268" s="1" t="s">
-        <v>4929</v>
+        <v>4921</v>
       </c>
       <c r="K268" s="72">
         <v>2609</v>
@@ -38176,7 +38196,7 @@
         <v>1365</v>
       </c>
       <c r="N268" s="1" t="s">
-        <v>4930</v>
+        <v>4922</v>
       </c>
       <c r="O268" s="72">
         <v>807</v>
@@ -38188,7 +38208,7 @@
         <v>546</v>
       </c>
       <c r="R268" s="1" t="s">
-        <v>4931</v>
+        <v>4923</v>
       </c>
       <c r="S268" s="72">
         <v>400</v>
@@ -38212,13 +38232,13 @@
         <v>29</v>
       </c>
       <c r="Z268" s="1" t="s">
-        <v>4932</v>
+        <v>4924</v>
       </c>
       <c r="AA268" s="72">
         <v>29</v>
       </c>
       <c r="AB268" s="1" t="s">
-        <v>4933</v>
+        <v>4925</v>
       </c>
       <c r="AC268" s="72">
         <v>145</v>
@@ -53594,31 +53614,31 @@
         <v>3654</v>
       </c>
       <c r="Q185" s="18" t="s">
+        <v>4872</v>
+      </c>
+      <c r="S185" s="18" t="s">
+        <v>4873</v>
+      </c>
+      <c r="U185" s="18" t="s">
+        <v>4874</v>
+      </c>
+      <c r="W185" s="18" t="s">
+        <v>4875</v>
+      </c>
+      <c r="Y185" s="18" t="s">
+        <v>4876</v>
+      </c>
+      <c r="AA185" s="18" t="s">
+        <v>4877</v>
+      </c>
+      <c r="AC185" s="18" t="s">
+        <v>4878</v>
+      </c>
+      <c r="AE185" s="18" t="s">
+        <v>4879</v>
+      </c>
+      <c r="AG185" s="18" t="s">
         <v>4880</v>
-      </c>
-      <c r="S185" s="18" t="s">
-        <v>4881</v>
-      </c>
-      <c r="U185" s="18" t="s">
-        <v>4882</v>
-      </c>
-      <c r="W185" s="18" t="s">
-        <v>4883</v>
-      </c>
-      <c r="Y185" s="18" t="s">
-        <v>4884</v>
-      </c>
-      <c r="AA185" s="18" t="s">
-        <v>4885</v>
-      </c>
-      <c r="AC185" s="18" t="s">
-        <v>4886</v>
-      </c>
-      <c r="AE185" s="18" t="s">
-        <v>4887</v>
-      </c>
-      <c r="AG185" s="18" t="s">
-        <v>4888</v>
       </c>
     </row>
     <row r="186" spans="1:39" ht="22.5" customHeight="1">
@@ -53847,16 +53867,16 @@
         <v>4626</v>
       </c>
       <c r="AG190" s="18" t="s">
-        <v>4890</v>
+        <v>4882</v>
       </c>
       <c r="AI190" s="18" t="s">
-        <v>4891</v>
+        <v>4883</v>
       </c>
       <c r="AK190" s="18" t="s">
-        <v>4892</v>
+        <v>4884</v>
       </c>
       <c r="AM190" s="18" t="s">
-        <v>4893</v>
+        <v>4885</v>
       </c>
     </row>
     <row r="191" spans="1:39" ht="22.5" customHeight="1">
@@ -55977,7 +55997,7 @@
         <v>4807</v>
       </c>
       <c r="AA227" s="71" t="s">
-        <v>4889</v>
+        <v>4881</v>
       </c>
     </row>
     <row r="228" spans="1:47" ht="22.5" customHeight="1">
@@ -57286,7 +57306,7 @@
         <v>2640</v>
       </c>
     </row>
-    <row r="257" spans="1:24" ht="22.5" customHeight="1">
+    <row r="257" spans="1:25" ht="22.5" customHeight="1">
       <c r="A257" s="13" t="str">
         <f>IF(games!A257="", "", games!A257)</f>
         <v>屍不可擋</v>
@@ -57319,7 +57339,7 @@
         <v>4719</v>
       </c>
     </row>
-    <row r="258" spans="1:24" ht="22.5" customHeight="1">
+    <row r="258" spans="1:25" ht="22.5" customHeight="1">
       <c r="A258" s="13" t="str">
         <f>IF(games!A258="", "", games!A258)</f>
         <v>RF ONLINE NEXT</v>
@@ -57349,7 +57369,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="259" spans="1:24">
+    <row r="259" spans="1:25">
       <c r="A259" s="13" t="str">
         <f>IF(games!A259="", "", games!A259)</f>
         <v>少女掌門人</v>
@@ -57379,13 +57399,13 @@
         <v>4368</v>
       </c>
       <c r="K259" s="101" t="s">
-        <v>4915</v>
+        <v>4907</v>
       </c>
       <c r="L259" s="13" t="s">
-        <v>4916</v>
-      </c>
-    </row>
-    <row r="260" spans="1:24">
+        <v>4908</v>
+      </c>
+    </row>
+    <row r="260" spans="1:25">
       <c r="A260" s="13" t="str">
         <f>IF(games!A260="", "", games!A260)</f>
         <v>翼之櫻：放置決鬥者</v>
@@ -57416,7 +57436,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="261" spans="1:24">
+    <row r="261" spans="1:25">
       <c r="A261" s="13" t="str">
         <f>IF(games!A261="", "", games!A261)</f>
         <v>Oniro ARPG</v>
@@ -57447,7 +57467,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="262" spans="1:24">
+    <row r="262" spans="1:25">
       <c r="A262" s="13" t="str">
         <f>IF(games!A262="", "", games!A262)</f>
         <v>Legend of YMIR</v>
@@ -57479,7 +57499,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="263" spans="1:24">
+    <row r="263" spans="1:25">
       <c r="A263" s="13" t="str">
         <f>IF(games!A263="", "", games!A263)</f>
         <v>Elysia：星空墜落</v>
@@ -57509,7 +57529,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="264" spans="1:24">
+    <row r="264" spans="1:25">
       <c r="A264" s="13" t="str">
         <f>IF(games!A264="", "", games!A264)</f>
         <v>合併貓鎮</v>
@@ -57539,7 +57559,7 @@
         <v>4835</v>
       </c>
     </row>
-    <row r="265" spans="1:24">
+    <row r="265" spans="1:25">
       <c r="A265" s="13" t="str">
         <f>IF(games!A265="", "", games!A265)</f>
         <v>幻牌交鋒</v>
@@ -57557,25 +57577,25 @@
         <v>《幻牌交鋒》是一款集換式卡牌競技手遊，遊戲將帶你進入一個由神秘卡牌主宰的奇幻世界。玩家需要精心組建卡組，運用策略與智慧，與來自各地的玩家進行刺激的即時對戰。每張卡牌都擁有獨特的技能與屬性，考驗你的戰術佈局與臨場反應。想在牌桌上稱霸一方嗎？務必關注官方兌換碼與禮包碼，獲得稀有卡牌與豐富獎勵，讓你贏在起跑點！我們也提供快速安全的代儲值服務，讓你輕鬆獲取心儀的卡牌，迅速打造出最強牌組！</v>
       </c>
       <c r="F265" s="100" t="s">
-        <v>4911</v>
+        <v>4903</v>
       </c>
       <c r="G265" s="13" t="s">
-        <v>4912</v>
+        <v>4904</v>
       </c>
       <c r="H265" s="13" t="s">
-        <v>4913</v>
+        <v>4905</v>
       </c>
       <c r="I265" s="13" t="s">
-        <v>4914</v>
+        <v>4906</v>
       </c>
       <c r="K265" s="17" t="s">
-        <v>4909</v>
+        <v>4901</v>
       </c>
       <c r="L265" s="13" t="s">
-        <v>4910</v>
-      </c>
-    </row>
-    <row r="266" spans="1:24">
+        <v>4902</v>
+      </c>
+    </row>
+    <row r="266" spans="1:25">
       <c r="A266" s="13" t="str">
         <f>IF(games!A266="", "", games!A266)</f>
         <v>激鬥！王國保衛戰</v>
@@ -57605,7 +57625,7 @@
         <v>4835</v>
       </c>
     </row>
-    <row r="267" spans="1:24">
+    <row r="267" spans="1:25">
       <c r="A267" s="13" t="str">
         <f>IF(games!A267="", "", games!A267)</f>
         <v>嘟嘟臉惡作劇</v>
@@ -57623,55 +57643,46 @@
         <v>《嘟嘟臉惡作劇》是一款充滿日系可愛風格的放置養成遊戲。故事發生在一個充滿魔法的學院，玩家將與一群擁有特殊能力的可愛角色們相遇，一同展開奇妙的冒險。遊戲採用輕鬆的放置玩法，讓你在繁忙之餘也能享受角色養成的樂趣，並透過策略性的戰鬥配置，挑戰各種關卡。想讓你的角色們迅速成長，解鎖更多有趣劇情嗎？記得使用官方兌換碼及禮包碼，獲得大量經驗與珍稀道具！我們也提供代儲值服務，讓您快速安全地獲得所需資源，輕鬆養成最強戰隊，在嘟嘟臉的世界裡盡情惡作劇吧！</v>
       </c>
       <c r="F267" s="17" t="s">
-        <v>4836</v>
+        <v>4938</v>
       </c>
       <c r="G267" s="13" t="s">
-        <v>4835</v>
+        <v>4939</v>
+      </c>
+      <c r="H267" s="13" t="s">
+        <v>4940</v>
+      </c>
+      <c r="I267" s="13" t="s">
+        <v>4941</v>
+      </c>
+      <c r="J267" s="13" t="s">
+        <v>4942</v>
       </c>
       <c r="K267" s="17" t="s">
-        <v>4872</v>
-      </c>
-      <c r="L267" s="13" t="s">
-        <v>4876</v>
+        <v>4930</v>
       </c>
       <c r="M267" s="18" t="s">
-        <v>4873</v>
-      </c>
-      <c r="N267" s="13" t="s">
-        <v>4876</v>
+        <v>4931</v>
       </c>
       <c r="O267" s="18" t="s">
-        <v>4874</v>
-      </c>
-      <c r="P267" s="13" t="s">
-        <v>4876</v>
+        <v>4932</v>
       </c>
       <c r="Q267" s="18" t="s">
-        <v>4875</v>
-      </c>
-      <c r="R267" s="13" t="s">
-        <v>4876</v>
+        <v>4933</v>
       </c>
       <c r="S267" s="18" t="s">
-        <v>4877</v>
-      </c>
-      <c r="T267" s="13" t="s">
-        <v>4876</v>
+        <v>4934</v>
       </c>
       <c r="U267" s="18" t="s">
-        <v>4878</v>
-      </c>
-      <c r="V267" s="13" t="s">
-        <v>4876</v>
+        <v>4935</v>
       </c>
       <c r="W267" s="18" t="s">
-        <v>4879</v>
-      </c>
-      <c r="X267" s="13" t="s">
-        <v>4876</v>
-      </c>
-    </row>
-    <row r="268" spans="1:24">
+        <v>4936</v>
+      </c>
+      <c r="Y267" s="18" t="s">
+        <v>4937</v>
+      </c>
+    </row>
+    <row r="268" spans="1:25">
       <c r="A268" s="13" t="str">
         <f>IF(games!A268="", "", games!A268)</f>
         <v>我的花園世界</v>
@@ -57689,10 +57700,10 @@
         <v>踏入《我的花園世界》，一個充滿奇幻與溫馨的養成冒險，讓你在忙碌的生活中找到一片心靈綠洲！這款手遊將帶你探索魔法大陸，與可愛的花仙子們一同培育珍奇植物，從零開始打造屬於你的夢想莊園。遊戲結合了多元的養成、裝飾與社交玩法，不僅能自由裝扮你的花園，更能拜訪好友，互贈禮物，共創美好回憶。想加速成長？別擔心，豐富的兌換碼和禮包碼讓你輕鬆取得稀有資源，快速提升等級。我們也提供代儲值服務，讓你享受快速安全的交易體驗，輕鬆購入心儀的限定道具。快來加入，與全球玩家一起體驗這場療癒又趣味的園藝之旅吧！</v>
       </c>
       <c r="F268" s="34" t="s">
-        <v>4927</v>
+        <v>4919</v>
       </c>
       <c r="G268" s="13" t="s">
-        <v>4928</v>
+        <v>4920</v>
       </c>
       <c r="H268" s="13" t="s">
         <v>2625</v>
@@ -57701,37 +57712,37 @@
         <v>4368</v>
       </c>
       <c r="K268" s="17" t="s">
-        <v>4907</v>
+        <v>4899</v>
       </c>
       <c r="L268" s="13" t="s">
-        <v>4908</v>
+        <v>4900</v>
       </c>
       <c r="M268" s="18" t="s">
-        <v>4919</v>
+        <v>4911</v>
       </c>
       <c r="N268" s="13" t="s">
-        <v>4923</v>
+        <v>4915</v>
       </c>
       <c r="O268" s="18" t="s">
-        <v>4920</v>
+        <v>4912</v>
       </c>
       <c r="P268" s="13" t="s">
-        <v>4924</v>
+        <v>4916</v>
       </c>
       <c r="Q268" s="18" t="s">
-        <v>4921</v>
+        <v>4913</v>
       </c>
       <c r="R268" s="13" t="s">
-        <v>4925</v>
+        <v>4917</v>
       </c>
       <c r="S268" s="18" t="s">
-        <v>4922</v>
+        <v>4914</v>
       </c>
       <c r="T268" s="13" t="s">
-        <v>4926</v>
-      </c>
-    </row>
-    <row r="269" spans="1:24">
+        <v>4918</v>
+      </c>
+    </row>
+    <row r="269" spans="1:25">
       <c r="A269" s="13" t="str">
         <f>IF(games!A269="", "", games!A269)</f>
         <v/>
@@ -57749,7 +57760,7 @@
         <v/>
       </c>
     </row>
-    <row r="270" spans="1:24">
+    <row r="270" spans="1:25">
       <c r="A270" s="13" t="str">
         <f>IF(games!A270="", "", games!A270)</f>
         <v/>
@@ -57767,7 +57778,7 @@
         <v/>
       </c>
     </row>
-    <row r="271" spans="1:24">
+    <row r="271" spans="1:25">
       <c r="A271" s="13" t="str">
         <f>IF(games!A271="", "", games!A271)</f>
         <v/>
@@ -57785,7 +57796,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" spans="1:24">
+    <row r="272" spans="1:25">
       <c r="A272" s="13" t="str">
         <f>IF(games!A272="", "", games!A272)</f>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7236" uniqueCount="4943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7244" uniqueCount="4955">
   <si>
     <t>Facebook</t>
   </si>
@@ -18817,18 +18817,6 @@
     <t>0.99美金禮包</t>
   </si>
   <si>
-    <t>2300台幣禮包</t>
-  </si>
-  <si>
-    <t>1100台幣禮包</t>
-  </si>
-  <si>
-    <t>650台幣禮包</t>
-  </si>
-  <si>
-    <t>360台幣禮包</t>
-  </si>
-  <si>
     <t>HLM810</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -19093,6 +19081,60 @@
   <si>
     <t>到信箱領取兌換碼的免費禮包</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使者招募券*10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>糖果*100+魔卡龍*1000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽卡券*3+一般進化卡片*50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使者招募券*3+一般進化卡片*50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使者招募券*10+抽卡券*10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水晶葉*30+魔卡龍*10K+金幣*10K</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6480水晶葉</t>
+  </si>
+  <si>
+    <t>3280水晶葉</t>
+  </si>
+  <si>
+    <t>1980水晶葉</t>
+  </si>
+  <si>
+    <t>1280水晶葉</t>
+  </si>
+  <si>
+    <t>680水晶葉</t>
+  </si>
+  <si>
+    <t>300水晶葉</t>
+  </si>
+  <si>
+    <t>60水晶葉</t>
+  </si>
+  <si>
+    <t>每日星星糖貢品</t>
+  </si>
+  <si>
+    <t>每日糖果貢品</t>
+  </si>
+  <si>
+    <t>每日水晶葉貢品</t>
   </si>
 </sst>
 </file>
@@ -37804,73 +37846,73 @@
         <v>4805</v>
       </c>
       <c r="J263" s="1" t="s">
-        <v>4886</v>
+        <v>4882</v>
       </c>
       <c r="K263" s="72">
         <v>2371</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>4887</v>
+        <v>4883</v>
       </c>
       <c r="M263" s="72">
         <v>1204</v>
       </c>
       <c r="N263" s="1" t="s">
-        <v>4888</v>
+        <v>4884</v>
       </c>
       <c r="O263" s="72">
         <v>563</v>
       </c>
       <c r="P263" s="1" t="s">
-        <v>4889</v>
+        <v>4885</v>
       </c>
       <c r="Q263" s="72">
         <v>261</v>
       </c>
       <c r="R263" s="1" t="s">
-        <v>4890</v>
+        <v>4886</v>
       </c>
       <c r="S263" s="72">
         <v>128</v>
       </c>
       <c r="T263" s="1" t="s">
-        <v>4891</v>
+        <v>4887</v>
       </c>
       <c r="U263" s="72">
         <v>26</v>
       </c>
       <c r="V263" s="1" t="s">
-        <v>4892</v>
+        <v>4888</v>
       </c>
       <c r="W263" s="72">
         <v>400</v>
       </c>
       <c r="X263" s="1" t="s">
-        <v>4893</v>
+        <v>4889</v>
       </c>
       <c r="Y263" s="72">
         <v>128</v>
       </c>
       <c r="Z263" s="1" t="s">
-        <v>4894</v>
+        <v>4890</v>
       </c>
       <c r="AA263" s="72">
         <v>2371</v>
       </c>
       <c r="AB263" s="99" t="s">
-        <v>4895</v>
+        <v>4891</v>
       </c>
       <c r="AC263" s="72">
         <v>1204</v>
       </c>
       <c r="AD263" s="1" t="s">
-        <v>4896</v>
+        <v>4892</v>
       </c>
       <c r="AE263" s="72">
         <v>400</v>
       </c>
       <c r="AF263" s="1" t="s">
-        <v>4897</v>
+        <v>4893</v>
       </c>
       <c r="AG263" s="72">
         <v>26</v>
@@ -37968,7 +38010,7 @@
         <v>26</v>
       </c>
       <c r="V265" s="1" t="s">
-        <v>4898</v>
+        <v>4894</v>
       </c>
       <c r="W265" s="72">
         <v>247</v>
@@ -38096,95 +38138,95 @@
         <v>4855</v>
       </c>
       <c r="J267" s="1" t="s">
-        <v>301</v>
+        <v>4945</v>
       </c>
       <c r="K267" s="72">
         <v>2371</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>4868</v>
+        <v>4946</v>
       </c>
       <c r="M267" s="72">
-        <v>1858</v>
+        <v>1204</v>
       </c>
       <c r="N267" s="1" t="s">
-        <v>302</v>
+        <v>4947</v>
       </c>
       <c r="O267" s="72">
-        <v>1204</v>
+        <v>807</v>
       </c>
       <c r="P267" s="1" t="s">
-        <v>4869</v>
+        <v>4948</v>
       </c>
       <c r="Q267" s="72">
-        <v>889</v>
+        <v>530</v>
       </c>
       <c r="R267" s="1" t="s">
-        <v>262</v>
+        <v>4949</v>
       </c>
       <c r="S267" s="72">
-        <v>807</v>
+        <v>294</v>
       </c>
       <c r="T267" s="1" t="s">
-        <v>4870</v>
+        <v>4950</v>
       </c>
       <c r="U267" s="72">
-        <v>530</v>
+        <v>136</v>
       </c>
       <c r="V267" s="1" t="s">
-        <v>1493</v>
+        <v>4951</v>
       </c>
       <c r="W267" s="72">
-        <v>400</v>
+        <v>29</v>
       </c>
       <c r="X267" s="1" t="s">
-        <v>4871</v>
+        <v>4952</v>
       </c>
       <c r="Y267" s="72">
-        <v>294</v>
+        <v>136</v>
       </c>
       <c r="Z267" s="1" t="s">
-        <v>4338</v>
+        <v>4953</v>
       </c>
       <c r="AA267" s="72">
+        <v>136</v>
+      </c>
+      <c r="AB267" s="1" t="s">
+        <v>4954</v>
+      </c>
+      <c r="AC267" s="72">
         <v>196</v>
-      </c>
-      <c r="AB267" s="1" t="s">
-        <v>3955</v>
-      </c>
-      <c r="AC267" s="72">
-        <v>162</v>
       </c>
     </row>
     <row r="268" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A268" s="3" t="s">
-        <v>4926</v>
+        <v>4922</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>4928</v>
+        <v>4924</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>4909</v>
+        <v>4905</v>
       </c>
       <c r="E268" s="4" t="s">
-        <v>4910</v>
+        <v>4906</v>
       </c>
       <c r="F268" s="40" t="str">
         <f t="shared" ref="F268:F313" si="12">IF(A268="", "", "gift-codes.html?game=" &amp; A268)</f>
         <v>gift-codes.html?game=我的花園世界</v>
       </c>
       <c r="G268" s="4" t="s">
-        <v>4927</v>
+        <v>4923</v>
       </c>
       <c r="H268" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/我的花園世界.html</v>
       </c>
       <c r="I268" s="42" t="s">
-        <v>4929</v>
+        <v>4925</v>
       </c>
       <c r="J268" s="1" t="s">
-        <v>4921</v>
+        <v>4917</v>
       </c>
       <c r="K268" s="72">
         <v>2609</v>
@@ -38196,7 +38238,7 @@
         <v>1365</v>
       </c>
       <c r="N268" s="1" t="s">
-        <v>4922</v>
+        <v>4918</v>
       </c>
       <c r="O268" s="72">
         <v>807</v>
@@ -38208,7 +38250,7 @@
         <v>546</v>
       </c>
       <c r="R268" s="1" t="s">
-        <v>4923</v>
+        <v>4919</v>
       </c>
       <c r="S268" s="72">
         <v>400</v>
@@ -38232,13 +38274,13 @@
         <v>29</v>
       </c>
       <c r="Z268" s="1" t="s">
-        <v>4924</v>
+        <v>4920</v>
       </c>
       <c r="AA268" s="72">
         <v>29</v>
       </c>
       <c r="AB268" s="1" t="s">
-        <v>4925</v>
+        <v>4921</v>
       </c>
       <c r="AC268" s="72">
         <v>145</v>
@@ -53614,31 +53656,31 @@
         <v>3654</v>
       </c>
       <c r="Q185" s="18" t="s">
+        <v>4868</v>
+      </c>
+      <c r="S185" s="18" t="s">
+        <v>4869</v>
+      </c>
+      <c r="U185" s="18" t="s">
+        <v>4870</v>
+      </c>
+      <c r="W185" s="18" t="s">
+        <v>4871</v>
+      </c>
+      <c r="Y185" s="18" t="s">
         <v>4872</v>
       </c>
-      <c r="S185" s="18" t="s">
+      <c r="AA185" s="18" t="s">
         <v>4873</v>
       </c>
-      <c r="U185" s="18" t="s">
+      <c r="AC185" s="18" t="s">
         <v>4874</v>
       </c>
-      <c r="W185" s="18" t="s">
+      <c r="AE185" s="18" t="s">
         <v>4875</v>
       </c>
-      <c r="Y185" s="18" t="s">
+      <c r="AG185" s="18" t="s">
         <v>4876</v>
-      </c>
-      <c r="AA185" s="18" t="s">
-        <v>4877</v>
-      </c>
-      <c r="AC185" s="18" t="s">
-        <v>4878</v>
-      </c>
-      <c r="AE185" s="18" t="s">
-        <v>4879</v>
-      </c>
-      <c r="AG185" s="18" t="s">
-        <v>4880</v>
       </c>
     </row>
     <row r="186" spans="1:39" ht="22.5" customHeight="1">
@@ -53867,16 +53909,16 @@
         <v>4626</v>
       </c>
       <c r="AG190" s="18" t="s">
-        <v>4882</v>
+        <v>4878</v>
       </c>
       <c r="AI190" s="18" t="s">
-        <v>4883</v>
+        <v>4879</v>
       </c>
       <c r="AK190" s="18" t="s">
-        <v>4884</v>
+        <v>4880</v>
       </c>
       <c r="AM190" s="18" t="s">
-        <v>4885</v>
+        <v>4881</v>
       </c>
     </row>
     <row r="191" spans="1:39" ht="22.5" customHeight="1">
@@ -55997,7 +56039,7 @@
         <v>4807</v>
       </c>
       <c r="AA227" s="71" t="s">
-        <v>4881</v>
+        <v>4877</v>
       </c>
     </row>
     <row r="228" spans="1:47" ht="22.5" customHeight="1">
@@ -57306,7 +57348,7 @@
         <v>2640</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="22.5" customHeight="1">
+    <row r="257" spans="1:26" ht="22.5" customHeight="1">
       <c r="A257" s="13" t="str">
         <f>IF(games!A257="", "", games!A257)</f>
         <v>屍不可擋</v>
@@ -57339,7 +57381,7 @@
         <v>4719</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="22.5" customHeight="1">
+    <row r="258" spans="1:26" ht="22.5" customHeight="1">
       <c r="A258" s="13" t="str">
         <f>IF(games!A258="", "", games!A258)</f>
         <v>RF ONLINE NEXT</v>
@@ -57369,7 +57411,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="259" spans="1:25">
+    <row r="259" spans="1:26">
       <c r="A259" s="13" t="str">
         <f>IF(games!A259="", "", games!A259)</f>
         <v>少女掌門人</v>
@@ -57399,13 +57441,13 @@
         <v>4368</v>
       </c>
       <c r="K259" s="101" t="s">
-        <v>4907</v>
+        <v>4903</v>
       </c>
       <c r="L259" s="13" t="s">
-        <v>4908</v>
-      </c>
-    </row>
-    <row r="260" spans="1:25">
+        <v>4904</v>
+      </c>
+    </row>
+    <row r="260" spans="1:26">
       <c r="A260" s="13" t="str">
         <f>IF(games!A260="", "", games!A260)</f>
         <v>翼之櫻：放置決鬥者</v>
@@ -57436,7 +57478,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="261" spans="1:25">
+    <row r="261" spans="1:26">
       <c r="A261" s="13" t="str">
         <f>IF(games!A261="", "", games!A261)</f>
         <v>Oniro ARPG</v>
@@ -57467,7 +57509,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="262" spans="1:25">
+    <row r="262" spans="1:26">
       <c r="A262" s="13" t="str">
         <f>IF(games!A262="", "", games!A262)</f>
         <v>Legend of YMIR</v>
@@ -57499,7 +57541,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="263" spans="1:25">
+    <row r="263" spans="1:26">
       <c r="A263" s="13" t="str">
         <f>IF(games!A263="", "", games!A263)</f>
         <v>Elysia：星空墜落</v>
@@ -57529,7 +57571,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="264" spans="1:25">
+    <row r="264" spans="1:26">
       <c r="A264" s="13" t="str">
         <f>IF(games!A264="", "", games!A264)</f>
         <v>合併貓鎮</v>
@@ -57559,7 +57601,7 @@
         <v>4835</v>
       </c>
     </row>
-    <row r="265" spans="1:25">
+    <row r="265" spans="1:26">
       <c r="A265" s="13" t="str">
         <f>IF(games!A265="", "", games!A265)</f>
         <v>幻牌交鋒</v>
@@ -57577,25 +57619,25 @@
         <v>《幻牌交鋒》是一款集換式卡牌競技手遊，遊戲將帶你進入一個由神秘卡牌主宰的奇幻世界。玩家需要精心組建卡組，運用策略與智慧，與來自各地的玩家進行刺激的即時對戰。每張卡牌都擁有獨特的技能與屬性，考驗你的戰術佈局與臨場反應。想在牌桌上稱霸一方嗎？務必關注官方兌換碼與禮包碼，獲得稀有卡牌與豐富獎勵，讓你贏在起跑點！我們也提供快速安全的代儲值服務，讓你輕鬆獲取心儀的卡牌，迅速打造出最強牌組！</v>
       </c>
       <c r="F265" s="100" t="s">
-        <v>4903</v>
+        <v>4899</v>
       </c>
       <c r="G265" s="13" t="s">
-        <v>4904</v>
+        <v>4900</v>
       </c>
       <c r="H265" s="13" t="s">
-        <v>4905</v>
+        <v>4901</v>
       </c>
       <c r="I265" s="13" t="s">
-        <v>4906</v>
+        <v>4902</v>
       </c>
       <c r="K265" s="17" t="s">
-        <v>4901</v>
+        <v>4897</v>
       </c>
       <c r="L265" s="13" t="s">
-        <v>4902</v>
-      </c>
-    </row>
-    <row r="266" spans="1:25">
+        <v>4898</v>
+      </c>
+    </row>
+    <row r="266" spans="1:26">
       <c r="A266" s="13" t="str">
         <f>IF(games!A266="", "", games!A266)</f>
         <v>激鬥！王國保衛戰</v>
@@ -57625,7 +57667,7 @@
         <v>4835</v>
       </c>
     </row>
-    <row r="267" spans="1:25">
+    <row r="267" spans="1:26">
       <c r="A267" s="13" t="str">
         <f>IF(games!A267="", "", games!A267)</f>
         <v>嘟嘟臉惡作劇</v>
@@ -57643,46 +57685,70 @@
         <v>《嘟嘟臉惡作劇》是一款充滿日系可愛風格的放置養成遊戲。故事發生在一個充滿魔法的學院，玩家將與一群擁有特殊能力的可愛角色們相遇，一同展開奇妙的冒險。遊戲採用輕鬆的放置玩法，讓你在繁忙之餘也能享受角色養成的樂趣，並透過策略性的戰鬥配置，挑戰各種關卡。想讓你的角色們迅速成長，解鎖更多有趣劇情嗎？記得使用官方兌換碼及禮包碼，獲得大量經驗與珍稀道具！我們也提供代儲值服務，讓您快速安全地獲得所需資源，輕鬆養成最強戰隊，在嘟嘟臉的世界裡盡情惡作劇吧！</v>
       </c>
       <c r="F267" s="17" t="s">
+        <v>4934</v>
+      </c>
+      <c r="G267" s="13" t="s">
+        <v>4935</v>
+      </c>
+      <c r="H267" s="13" t="s">
+        <v>4936</v>
+      </c>
+      <c r="I267" s="13" t="s">
+        <v>4937</v>
+      </c>
+      <c r="J267" s="13" t="s">
         <v>4938</v>
       </c>
-      <c r="G267" s="13" t="s">
+      <c r="K267" s="17" t="s">
+        <v>4926</v>
+      </c>
+      <c r="L267" s="13" t="s">
         <v>4939</v>
       </c>
-      <c r="H267" s="13" t="s">
+      <c r="M267" s="18" t="s">
+        <v>4927</v>
+      </c>
+      <c r="N267" s="13" t="s">
         <v>4940</v>
       </c>
-      <c r="I267" s="13" t="s">
+      <c r="O267" s="18" t="s">
+        <v>4928</v>
+      </c>
+      <c r="P267" s="13" t="s">
         <v>4941</v>
       </c>
-      <c r="J267" s="13" t="s">
+      <c r="Q267" s="18" t="s">
+        <v>4929</v>
+      </c>
+      <c r="R267" s="13" t="s">
         <v>4942</v>
       </c>
-      <c r="K267" s="17" t="s">
+      <c r="S267" s="18" t="s">
         <v>4930</v>
       </c>
-      <c r="M267" s="18" t="s">
+      <c r="T267" s="13" t="s">
+        <v>4943</v>
+      </c>
+      <c r="U267" s="18" t="s">
         <v>4931</v>
       </c>
-      <c r="O267" s="18" t="s">
+      <c r="V267" s="13" t="s">
+        <v>4944</v>
+      </c>
+      <c r="W267" s="18" t="s">
         <v>4932</v>
       </c>
-      <c r="Q267" s="18" t="s">
+      <c r="X267" s="13" t="s">
+        <v>4944</v>
+      </c>
+      <c r="Y267" s="18" t="s">
         <v>4933</v>
       </c>
-      <c r="S267" s="18" t="s">
-        <v>4934</v>
-      </c>
-      <c r="U267" s="18" t="s">
-        <v>4935</v>
-      </c>
-      <c r="W267" s="18" t="s">
-        <v>4936</v>
-      </c>
-      <c r="Y267" s="18" t="s">
-        <v>4937</v>
-      </c>
-    </row>
-    <row r="268" spans="1:25">
+      <c r="Z267" s="13" t="s">
+        <v>4944</v>
+      </c>
+    </row>
+    <row r="268" spans="1:26">
       <c r="A268" s="13" t="str">
         <f>IF(games!A268="", "", games!A268)</f>
         <v>我的花園世界</v>
@@ -57700,10 +57766,10 @@
         <v>踏入《我的花園世界》，一個充滿奇幻與溫馨的養成冒險，讓你在忙碌的生活中找到一片心靈綠洲！這款手遊將帶你探索魔法大陸，與可愛的花仙子們一同培育珍奇植物，從零開始打造屬於你的夢想莊園。遊戲結合了多元的養成、裝飾與社交玩法，不僅能自由裝扮你的花園，更能拜訪好友，互贈禮物，共創美好回憶。想加速成長？別擔心，豐富的兌換碼和禮包碼讓你輕鬆取得稀有資源，快速提升等級。我們也提供代儲值服務，讓你享受快速安全的交易體驗，輕鬆購入心儀的限定道具。快來加入，與全球玩家一起體驗這場療癒又趣味的園藝之旅吧！</v>
       </c>
       <c r="F268" s="34" t="s">
-        <v>4919</v>
+        <v>4915</v>
       </c>
       <c r="G268" s="13" t="s">
-        <v>4920</v>
+        <v>4916</v>
       </c>
       <c r="H268" s="13" t="s">
         <v>2625</v>
@@ -57712,37 +57778,37 @@
         <v>4368</v>
       </c>
       <c r="K268" s="17" t="s">
-        <v>4899</v>
+        <v>4895</v>
       </c>
       <c r="L268" s="13" t="s">
-        <v>4900</v>
+        <v>4896</v>
       </c>
       <c r="M268" s="18" t="s">
+        <v>4907</v>
+      </c>
+      <c r="N268" s="13" t="s">
         <v>4911</v>
       </c>
-      <c r="N268" s="13" t="s">
-        <v>4915</v>
-      </c>
       <c r="O268" s="18" t="s">
+        <v>4908</v>
+      </c>
+      <c r="P268" s="13" t="s">
         <v>4912</v>
       </c>
-      <c r="P268" s="13" t="s">
-        <v>4916</v>
-      </c>
       <c r="Q268" s="18" t="s">
+        <v>4909</v>
+      </c>
+      <c r="R268" s="13" t="s">
         <v>4913</v>
       </c>
-      <c r="R268" s="13" t="s">
-        <v>4917</v>
-      </c>
       <c r="S268" s="18" t="s">
+        <v>4910</v>
+      </c>
+      <c r="T268" s="13" t="s">
         <v>4914</v>
       </c>
-      <c r="T268" s="13" t="s">
-        <v>4918</v>
-      </c>
-    </row>
-    <row r="269" spans="1:25">
+    </row>
+    <row r="269" spans="1:26">
       <c r="A269" s="13" t="str">
         <f>IF(games!A269="", "", games!A269)</f>
         <v/>
@@ -57760,7 +57826,7 @@
         <v/>
       </c>
     </row>
-    <row r="270" spans="1:25">
+    <row r="270" spans="1:26">
       <c r="A270" s="13" t="str">
         <f>IF(games!A270="", "", games!A270)</f>
         <v/>
@@ -57778,7 +57844,7 @@
         <v/>
       </c>
     </row>
-    <row r="271" spans="1:25">
+    <row r="271" spans="1:26">
       <c r="A271" s="13" t="str">
         <f>IF(games!A271="", "", games!A271)</f>
         <v/>
@@ -57796,7 +57862,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" spans="1:25">
+    <row r="272" spans="1:26">
       <c r="A272" s="13" t="str">
         <f>IF(games!A272="", "", games!A272)</f>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7244" uniqueCount="4955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7347" uniqueCount="5017">
   <si>
     <t>Facebook</t>
   </si>
@@ -18992,14 +18992,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>進到遊戲內按右上角「設定」</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>點最底下的「兌換碼」選項</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>6000元寶</t>
   </si>
   <si>
@@ -19135,6 +19127,217 @@
   </si>
   <si>
     <t>每日水晶葉貢品</t>
+  </si>
+  <si>
+    <t>Awakenloop</t>
+  </si>
+  <si>
+    <t>Astellia</t>
+  </si>
+  <si>
+    <t>華夏千秋</t>
+  </si>
+  <si>
+    <t>萌塔娘</t>
+  </si>
+  <si>
+    <t>盜夢英雄2：幻野</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/Awakenloop/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/us/app/awakenloop/id6748336976</t>
+  </si>
+  <si>
+    <t>https://www.r2games.com/</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.f5game.lr</t>
+  </si>
+  <si>
+    <t>https://astellia.game.onstove.com/tw</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/astellia-m/id6749603786</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.sesisoft.astellia.google</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/AstelliaOfficial/</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.hygame.hxqq.tw.gp</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/DiGeamGirlAttack</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.digeam.a.srtw&amp;referrer=utm_source%3Dgamer.com.tw%26utm_campaign%3Dgnn</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E8%90%8C%E5%A1%94%E5%A8%98/id6747243774</t>
+  </si>
+  <si>
+    <t>https://srtw.digeam.com/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/dreamraiders2TW/</t>
+  </si>
+  <si>
+    <t>https://dm2-reservation.dreamplusgames.com/</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E7%9B%9C%E5%A4%A2%E8%8B%B1%E9%9B%842-%E5%B9%BB%E9%87%8E/id6743147434</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.mechanist.dream2.aos&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61580230375788</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/cn/app/%E5%8D%8E%E5%A4%8F%E5%8D%83%E7%A7%8B-npc%E8%87%AA%E7%94%B1%E6%94%BB%E7%95%A5/id6450168609</t>
+  </si>
+  <si>
+    <t>《Awakenloop》是一款充滿賽博龐克風格的卡牌回合制手遊，玩家將身處一個由機器人與人類共存的末日世界。遊戲主打策略性卡牌戰鬥，每張卡牌都蘊含獨特技能，如何搭配與釋放將成為戰局關鍵。除了豐富的主線劇情，遊戲也提供多樣的副本挑戰與 PvP 模式，讓你與其他玩家一較高下。現在就加入《Awakenloop》，透過兌換碼與禮包碼獲得專屬獎勵，輕鬆提升戰力，也能使用代儲值服務快速安全地補充資源，在這片混沌的廢土上開創屬於你的新紀元。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《Astellia》是一款日系風格的魔幻冒險MMORPG，帶領玩家進入一個充滿魔法與奇幻生物的艾斯提亞大陸。遊戲以其精緻的3D美術畫面與豐富的職業系統著稱，玩家可自由選擇多種職業，並透過養成可愛的「星靈」夥伴來協助戰鬥。遊戲提供多樣化的副本、世界王挑戰與公會系統，讓玩家能與好友一同探索廣闊的世界。使用兌換碼和禮包碼能輕鬆領取稀有道具，快速提升戰力，若需更多遊戲幣與資源，代儲值服務能提供你安全又快速的儲值體驗，讓你在艾斯提亞大陸的旅程更加順暢。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《華夏千秋》是一款以中國古代神話為背景的MMORPG，遊戲將玩家帶入一個波瀾壯闊的東方玄幻世界。你將化身為修仙者，體驗從凡人到仙神的蛻變歷程。遊戲結合了豐富的劇情故事與自由的戰鬥系統，還有多樣化的社交玩法，讓玩家在修仙的道路上結交同伴，並肩作戰。現在就透過兌換碼和禮包碼領取豐富資源，快速開啟你的修仙之路，若想省時省力，安全的代儲值服務能讓你在短時間內獲得豐厚的回報，輕鬆應對各種挑戰，成就千秋霸業。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《萌塔娘》是一款結合了塔防與角色養成元素的二次元策略手遊，玩家將在遊戲中與各種「塔娘」並肩作戰，守護家園。遊戲以其可愛的Q版畫風與創新的塔防玩法吸引玩家，每位塔娘都有獨特的技能與屬性，如何配置防禦陣線與策略運用將是勝利的關鍵。遊戲內提供多樣化的養成系統，讓玩家能培養出最強的塔娘戰隊。透過兌換碼與禮包碼可獲得限定獎勵，快速提升戰力，若想迅速強化隊伍，安全的代儲值服務絕對是快速又方便的選擇，讓你輕鬆守護世界的和平。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《盜夢英雄2：幻野》是一款主打橫向捲軸動作戰鬥的RPG手遊，玩家將進入一個充滿奇幻與冒險的夢境世界。遊戲以爽快的打擊感與華麗的技能特效為核心，玩家可自由組建隊伍，挑戰各種強大的魔物與敵人。豐富的劇情模式與多樣的副本挑戰讓遊戲內容更加充實，無論是PVP還是PVE玩家都能找到樂趣。現在使用兌換碼與禮包碼就能領取專屬禮品，快速提升戰力，若有額外資源需求，代儲值服務提供最快速安全的購買管道，讓你輕鬆在夢境世界中探索，成為最強的夢境英雄。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gameboys978</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HAPPYEC1008</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mewo1000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MewoMewo1008</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Onityan</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>donotnow</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TKRELEASE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRICKCALOB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRICKCAL109</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EC1010</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GIFT1010</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCMoon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC1010</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.99美金禮包</t>
+  </si>
+  <si>
+    <t>2600台幣禮包</t>
+  </si>
+  <si>
+    <t>6480銀錠禮包</t>
+  </si>
+  <si>
+    <t>4880銀錠禮包</t>
+  </si>
+  <si>
+    <t>3280銀錠禮包</t>
+  </si>
+  <si>
+    <t>2380銀錠禮包</t>
+  </si>
+  <si>
+    <t>1980銀錠禮包</t>
+  </si>
+  <si>
+    <t>1880銀錠禮包</t>
+  </si>
+  <si>
+    <t>1280銀錠禮包</t>
+  </si>
+  <si>
+    <t>980銀錠禮包</t>
+  </si>
+  <si>
+    <t>880銀錠禮包</t>
+  </si>
+  <si>
+    <t>780銀錠禮包</t>
+  </si>
+  <si>
+    <t>3290VIP專屬水晶</t>
+  </si>
+  <si>
+    <t>1690VIP專屬水晶</t>
+  </si>
+  <si>
+    <t>990VIP專屬水晶</t>
+  </si>
+  <si>
+    <t>490VIP專屬水晶</t>
+  </si>
+  <si>
+    <t>330VIP專屬水晶</t>
+  </si>
+  <si>
+    <t>170VIP專屬水晶</t>
+  </si>
+  <si>
+    <t>33VIP專屬水晶</t>
+  </si>
+  <si>
+    <t>3290禮包</t>
+  </si>
+  <si>
+    <t>830禮包</t>
+  </si>
+  <si>
+    <t>390禮包</t>
   </si>
 </sst>
 </file>
@@ -20065,7 +20268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ628"/>
+  <dimension ref="A1:AQ627"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="27" style="40" customWidth="1"/>
@@ -37529,7 +37732,7 @@
         <v>4747</v>
       </c>
       <c r="H259" s="41" t="str">
-        <f t="shared" ref="H259:H284" si="11">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
+        <f t="shared" ref="H259:H283" si="11">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/少女掌門人.html</v>
       </c>
       <c r="I259" s="42" t="s">
@@ -38138,61 +38341,61 @@
         <v>4855</v>
       </c>
       <c r="J267" s="1" t="s">
-        <v>4945</v>
+        <v>4943</v>
       </c>
       <c r="K267" s="72">
         <v>2371</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>4946</v>
+        <v>4944</v>
       </c>
       <c r="M267" s="72">
         <v>1204</v>
       </c>
       <c r="N267" s="1" t="s">
-        <v>4947</v>
+        <v>4945</v>
       </c>
       <c r="O267" s="72">
         <v>807</v>
       </c>
       <c r="P267" s="1" t="s">
-        <v>4948</v>
+        <v>4946</v>
       </c>
       <c r="Q267" s="72">
         <v>530</v>
       </c>
       <c r="R267" s="1" t="s">
-        <v>4949</v>
+        <v>4947</v>
       </c>
       <c r="S267" s="72">
         <v>294</v>
       </c>
       <c r="T267" s="1" t="s">
-        <v>4950</v>
+        <v>4948</v>
       </c>
       <c r="U267" s="72">
         <v>136</v>
       </c>
       <c r="V267" s="1" t="s">
-        <v>4951</v>
+        <v>4949</v>
       </c>
       <c r="W267" s="72">
         <v>29</v>
       </c>
       <c r="X267" s="1" t="s">
-        <v>4952</v>
+        <v>4950</v>
       </c>
       <c r="Y267" s="72">
         <v>136</v>
       </c>
       <c r="Z267" s="1" t="s">
-        <v>4953</v>
+        <v>4951</v>
       </c>
       <c r="AA267" s="72">
         <v>136</v>
       </c>
       <c r="AB267" s="1" t="s">
-        <v>4954</v>
+        <v>4952</v>
       </c>
       <c r="AC267" s="72">
         <v>196</v>
@@ -38200,10 +38403,10 @@
     </row>
     <row r="268" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A268" s="3" t="s">
+        <v>4920</v>
+      </c>
+      <c r="C268" s="5" t="s">
         <v>4922</v>
-      </c>
-      <c r="C268" s="5" t="s">
-        <v>4924</v>
       </c>
       <c r="D268" s="4" t="s">
         <v>4905</v>
@@ -38212,21 +38415,21 @@
         <v>4906</v>
       </c>
       <c r="F268" s="40" t="str">
-        <f t="shared" ref="F268:F313" si="12">IF(A268="", "", "gift-codes.html?game=" &amp; A268)</f>
+        <f t="shared" ref="F268:F312" si="12">IF(A268="", "", "gift-codes.html?game=" &amp; A268)</f>
         <v>gift-codes.html?game=我的花園世界</v>
       </c>
       <c r="G268" s="4" t="s">
-        <v>4923</v>
+        <v>4921</v>
       </c>
       <c r="H268" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/我的花園世界.html</v>
       </c>
       <c r="I268" s="42" t="s">
-        <v>4925</v>
+        <v>4923</v>
       </c>
       <c r="J268" s="1" t="s">
-        <v>4917</v>
+        <v>4915</v>
       </c>
       <c r="K268" s="72">
         <v>2609</v>
@@ -38238,7 +38441,7 @@
         <v>1365</v>
       </c>
       <c r="N268" s="1" t="s">
-        <v>4918</v>
+        <v>4916</v>
       </c>
       <c r="O268" s="72">
         <v>807</v>
@@ -38250,7 +38453,7 @@
         <v>546</v>
       </c>
       <c r="R268" s="1" t="s">
-        <v>4919</v>
+        <v>4917</v>
       </c>
       <c r="S268" s="72">
         <v>400</v>
@@ -38274,69 +38477,399 @@
         <v>29</v>
       </c>
       <c r="Z268" s="1" t="s">
-        <v>4920</v>
+        <v>4918</v>
       </c>
       <c r="AA268" s="72">
         <v>29</v>
       </c>
       <c r="AB268" s="1" t="s">
-        <v>4921</v>
+        <v>4919</v>
       </c>
       <c r="AC268" s="72">
         <v>145</v>
       </c>
     </row>
-    <row r="269" spans="1:33" ht="22.5" customHeight="1">
+    <row r="269" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A269" s="72" t="s">
+        <v>4953</v>
+      </c>
+      <c r="C269" s="5" t="s">
+        <v>4958</v>
+      </c>
+      <c r="D269" s="41" t="s">
+        <v>4960</v>
+      </c>
+      <c r="E269" s="41" t="s">
+        <v>4959</v>
+      </c>
       <c r="F269" s="40" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=Awakenloop</v>
+      </c>
+      <c r="G269" s="41" t="s">
+        <v>4961</v>
       </c>
       <c r="H269" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="270" spans="1:33" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Awakenloop.html</v>
+      </c>
+      <c r="I269" s="42" t="s">
+        <v>4977</v>
+      </c>
+      <c r="J269" s="1" t="s">
+        <v>4860</v>
+      </c>
+      <c r="K269" s="72">
+        <v>2343</v>
+      </c>
+      <c r="L269" s="1" t="s">
+        <v>4861</v>
+      </c>
+      <c r="M269" s="72">
+        <v>1190</v>
+      </c>
+      <c r="N269" s="1" t="s">
+        <v>4862</v>
+      </c>
+      <c r="O269" s="72">
+        <v>798</v>
+      </c>
+      <c r="P269" s="1" t="s">
+        <v>4863</v>
+      </c>
+      <c r="Q269" s="72">
+        <v>540</v>
+      </c>
+      <c r="R269" s="1" t="s">
+        <v>4864</v>
+      </c>
+      <c r="S269" s="72">
+        <v>395</v>
+      </c>
+      <c r="T269" s="1" t="s">
+        <v>4865</v>
+      </c>
+      <c r="U269" s="72">
+        <v>258</v>
+      </c>
+      <c r="V269" s="1" t="s">
+        <v>4866</v>
+      </c>
+      <c r="W269" s="72">
+        <v>126</v>
+      </c>
+      <c r="X269" s="1" t="s">
+        <v>4995</v>
+      </c>
+      <c r="Y269" s="72">
+        <v>52</v>
+      </c>
+      <c r="Z269" s="1" t="s">
+        <v>4867</v>
+      </c>
+      <c r="AA269" s="72">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="270" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A270" s="72" t="s">
+        <v>4954</v>
+      </c>
+      <c r="C270" s="40" t="s">
+        <v>4965</v>
+      </c>
+      <c r="D270" s="41" t="s">
+        <v>4962</v>
+      </c>
+      <c r="E270" s="41" t="s">
+        <v>4963</v>
+      </c>
       <c r="F270" s="40" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=Astellia</v>
+      </c>
+      <c r="G270" s="41" t="s">
+        <v>4964</v>
       </c>
       <c r="H270" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="271" spans="1:33" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Astellia.html</v>
+      </c>
+      <c r="I270" s="42" t="s">
+        <v>4978</v>
+      </c>
+      <c r="J270" s="1" t="s">
+        <v>4996</v>
+      </c>
+      <c r="K270" s="72">
+        <v>2076</v>
+      </c>
+      <c r="L270" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="M270" s="72">
+        <v>1030</v>
+      </c>
+      <c r="N270" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="O270" s="72">
+        <v>637</v>
+      </c>
+      <c r="P270" s="1" t="s">
+        <v>3699</v>
+      </c>
+      <c r="Q270" s="72">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="271" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A271" s="72" t="s">
+        <v>4955</v>
+      </c>
+      <c r="C271" s="40" t="s">
+        <v>4975</v>
+      </c>
+      <c r="D271" s="40" t="s">
+        <v>4975</v>
+      </c>
+      <c r="E271" s="41" t="s">
+        <v>4976</v>
+      </c>
       <c r="F271" s="40" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=華夏千秋</v>
+      </c>
+      <c r="G271" s="41" t="s">
+        <v>4966</v>
       </c>
       <c r="H271" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="272" spans="1:33" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/華夏千秋.html</v>
+      </c>
+      <c r="I271" s="42" t="s">
+        <v>4979</v>
+      </c>
+      <c r="J271" s="1" t="s">
+        <v>4997</v>
+      </c>
+      <c r="K271" s="72">
+        <v>2579</v>
+      </c>
+      <c r="L271" s="1" t="s">
+        <v>4998</v>
+      </c>
+      <c r="M271" s="72">
+        <v>1988</v>
+      </c>
+      <c r="N271" s="1" t="s">
+        <v>4999</v>
+      </c>
+      <c r="O271" s="72">
+        <v>1349</v>
+      </c>
+      <c r="P271" s="1" t="s">
+        <v>5000</v>
+      </c>
+      <c r="Q271" s="72">
+        <v>950</v>
+      </c>
+      <c r="R271" s="1" t="s">
+        <v>5001</v>
+      </c>
+      <c r="S271" s="72">
+        <v>798</v>
+      </c>
+      <c r="T271" s="1" t="s">
+        <v>5002</v>
+      </c>
+      <c r="U271" s="72">
+        <v>749</v>
+      </c>
+      <c r="V271" s="1" t="s">
+        <v>5003</v>
+      </c>
+      <c r="W271" s="72">
+        <v>540</v>
+      </c>
+      <c r="X271" s="1" t="s">
+        <v>5004</v>
+      </c>
+      <c r="Y271" s="72">
+        <v>395</v>
+      </c>
+      <c r="Z271" s="1" t="s">
+        <v>5005</v>
+      </c>
+      <c r="AA271" s="72">
+        <v>346</v>
+      </c>
+      <c r="AB271" s="1" t="s">
+        <v>5006</v>
+      </c>
+      <c r="AC271" s="72">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="272" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A272" s="72" t="s">
+        <v>4956</v>
+      </c>
+      <c r="C272" s="40" t="s">
+        <v>4967</v>
+      </c>
+      <c r="D272" s="41" t="s">
+        <v>4970</v>
+      </c>
+      <c r="E272" s="41" t="s">
+        <v>4969</v>
+      </c>
       <c r="F272" s="40" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=萌塔娘</v>
+      </c>
+      <c r="G272" s="41" t="s">
+        <v>4968</v>
       </c>
       <c r="H272" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="273" spans="6:8" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/萌塔娘.html</v>
+      </c>
+      <c r="I272" s="42" t="s">
+        <v>4980</v>
+      </c>
+      <c r="J272" s="1" t="s">
+        <v>5007</v>
+      </c>
+      <c r="K272" s="72">
+        <v>2579</v>
+      </c>
+      <c r="L272" s="1" t="s">
+        <v>5008</v>
+      </c>
+      <c r="M272" s="72">
+        <v>1349</v>
+      </c>
+      <c r="N272" s="1" t="s">
+        <v>5009</v>
+      </c>
+      <c r="O272" s="72">
+        <v>798</v>
+      </c>
+      <c r="P272" s="1" t="s">
+        <v>5010</v>
+      </c>
+      <c r="Q272" s="72">
+        <v>395</v>
+      </c>
+      <c r="R272" s="1" t="s">
+        <v>5011</v>
+      </c>
+      <c r="S272" s="72">
+        <v>266</v>
+      </c>
+      <c r="T272" s="1" t="s">
+        <v>5012</v>
+      </c>
+      <c r="U272" s="72">
+        <v>143</v>
+      </c>
+      <c r="V272" s="1" t="s">
+        <v>5013</v>
+      </c>
+      <c r="W272" s="72">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="273" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A273" s="72" t="s">
+        <v>4957</v>
+      </c>
+      <c r="C273" s="40" t="s">
+        <v>4971</v>
+      </c>
+      <c r="D273" s="41" t="s">
+        <v>4972</v>
+      </c>
+      <c r="E273" s="41" t="s">
+        <v>4973</v>
+      </c>
       <c r="F273" s="40" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=盜夢英雄2：幻野</v>
+      </c>
+      <c r="G273" s="41" t="s">
+        <v>4974</v>
       </c>
       <c r="H273" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="6:8" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/盜夢英雄2：幻野.html</v>
+      </c>
+      <c r="I273" s="42" t="s">
+        <v>4981</v>
+      </c>
+      <c r="J273" s="1" t="s">
+        <v>5014</v>
+      </c>
+      <c r="K273" s="72">
+        <v>2579</v>
+      </c>
+      <c r="L273" s="1" t="s">
+        <v>1675</v>
+      </c>
+      <c r="M273" s="72">
+        <v>1828</v>
+      </c>
+      <c r="N273" s="1" t="s">
+        <v>1676</v>
+      </c>
+      <c r="O273" s="72">
+        <v>1349</v>
+      </c>
+      <c r="P273" s="1" t="s">
+        <v>1678</v>
+      </c>
+      <c r="Q273" s="72">
+        <v>950</v>
+      </c>
+      <c r="R273" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="S273" s="72">
+        <v>798</v>
+      </c>
+      <c r="T273" s="1" t="s">
+        <v>5015</v>
+      </c>
+      <c r="U273" s="72">
+        <v>669</v>
+      </c>
+      <c r="V273" s="1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="W273" s="72">
+        <v>540</v>
+      </c>
+      <c r="X273" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y273" s="72">
+        <v>395</v>
+      </c>
+      <c r="Z273" s="1" t="s">
+        <v>5016</v>
+      </c>
+      <c r="AA273" s="72">
+        <v>314</v>
+      </c>
+      <c r="AB273" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AC273" s="72">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="274" spans="1:29" ht="22.5" customHeight="1">
       <c r="F274" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -38346,7 +38879,7 @@
         <v/>
       </c>
     </row>
-    <row r="275" spans="6:8" ht="22.5" customHeight="1">
+    <row r="275" spans="1:29" ht="22.5" customHeight="1">
       <c r="F275" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -38356,7 +38889,7 @@
         <v/>
       </c>
     </row>
-    <row r="276" spans="6:8" ht="22.5" customHeight="1">
+    <row r="276" spans="1:29" ht="22.5" customHeight="1">
       <c r="F276" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -38366,7 +38899,7 @@
         <v/>
       </c>
     </row>
-    <row r="277" spans="6:8" ht="22.5" customHeight="1">
+    <row r="277" spans="1:29" ht="22.5" customHeight="1">
       <c r="F277" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -38376,7 +38909,7 @@
         <v/>
       </c>
     </row>
-    <row r="278" spans="6:8" ht="22.5" customHeight="1">
+    <row r="278" spans="1:29" ht="22.5" customHeight="1">
       <c r="F278" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -38386,7 +38919,7 @@
         <v/>
       </c>
     </row>
-    <row r="279" spans="6:8" ht="22.5" customHeight="1">
+    <row r="279" spans="1:29" ht="22.5" customHeight="1">
       <c r="F279" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -38396,7 +38929,7 @@
         <v/>
       </c>
     </row>
-    <row r="280" spans="6:8" ht="22.5" customHeight="1">
+    <row r="280" spans="1:29" ht="22.5" customHeight="1">
       <c r="F280" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -38406,7 +38939,7 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="6:8" ht="22.5" customHeight="1">
+    <row r="281" spans="1:29" ht="22.5" customHeight="1">
       <c r="F281" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -38416,7 +38949,7 @@
         <v/>
       </c>
     </row>
-    <row r="282" spans="6:8" ht="22.5" customHeight="1">
+    <row r="282" spans="1:29" ht="22.5" customHeight="1">
       <c r="F282" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -38426,7 +38959,7 @@
         <v/>
       </c>
     </row>
-    <row r="283" spans="6:8" ht="22.5" customHeight="1">
+    <row r="283" spans="1:29" ht="22.5" customHeight="1">
       <c r="F283" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -38436,27 +38969,27 @@
         <v/>
       </c>
     </row>
-    <row r="284" spans="6:8" ht="22.5" customHeight="1">
+    <row r="284" spans="1:29" ht="22.5" customHeight="1">
       <c r="F284" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H284" s="41" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="285" spans="6:8" ht="22.5" customHeight="1">
+        <f t="shared" ref="H284:H312" si="13">IF(A284="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A284)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285" spans="1:29" ht="22.5" customHeight="1">
       <c r="F285" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H285" s="41" t="str">
-        <f t="shared" ref="H285:H313" si="13">IF(A285="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A285)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="286" spans="6:8" ht="22.5" customHeight="1">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="286" spans="1:29" ht="22.5" customHeight="1">
       <c r="F286" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -38466,7 +38999,7 @@
         <v/>
       </c>
     </row>
-    <row r="287" spans="6:8" ht="22.5" customHeight="1">
+    <row r="287" spans="1:29" ht="22.5" customHeight="1">
       <c r="F287" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -38476,7 +39009,7 @@
         <v/>
       </c>
     </row>
-    <row r="288" spans="6:8" ht="22.5" customHeight="1">
+    <row r="288" spans="1:29" ht="22.5" customHeight="1">
       <c r="F288" s="40" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -38728,21 +39261,21 @@
     </row>
     <row r="313" spans="6:8" ht="22.5" customHeight="1">
       <c r="F313" s="40" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="F313:F376" si="14">IF(A313="", "", "gift-codes.html?game=" &amp; A313)</f>
         <v/>
       </c>
       <c r="H313" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="H313:H376" si="15">IF(A313="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A313)</f>
         <v/>
       </c>
     </row>
     <row r="314" spans="6:8" ht="22.5" customHeight="1">
       <c r="F314" s="40" t="str">
-        <f t="shared" ref="F314:F377" si="14">IF(A314="", "", "gift-codes.html?game=" &amp; A314)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H314" s="41" t="str">
-        <f t="shared" ref="H314:H377" si="15">IF(A314="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A314)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -39368,21 +39901,21 @@
     </row>
     <row r="377" spans="6:8" ht="22.5" customHeight="1">
       <c r="F377" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="F377:F440" si="16">IF(A377="", "", "gift-codes.html?game=" &amp; A377)</f>
         <v/>
       </c>
       <c r="H377" s="41" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="H377:H440" si="17">IF(A377="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A377)</f>
         <v/>
       </c>
     </row>
     <row r="378" spans="6:8" ht="22.5" customHeight="1">
       <c r="F378" s="40" t="str">
-        <f t="shared" ref="F378:F441" si="16">IF(A378="", "", "gift-codes.html?game=" &amp; A378)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H378" s="41" t="str">
-        <f t="shared" ref="H378:H441" si="17">IF(A378="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A378)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -39926,7 +40459,7 @@
         <v/>
       </c>
     </row>
-    <row r="433" spans="6:8" ht="22.5" customHeight="1">
+    <row r="433" spans="6:8">
       <c r="F433" s="40" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -40008,21 +40541,21 @@
     </row>
     <row r="441" spans="6:8">
       <c r="F441" s="40" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="F441:F504" si="18">IF(A441="", "", "gift-codes.html?game=" &amp; A441)</f>
         <v/>
       </c>
       <c r="H441" s="41" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="H441:H504" si="19">IF(A441="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A441)</f>
         <v/>
       </c>
     </row>
     <row r="442" spans="6:8">
       <c r="F442" s="40" t="str">
-        <f t="shared" ref="F442:F505" si="18">IF(A442="", "", "gift-codes.html?game=" &amp; A442)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H442" s="41" t="str">
-        <f t="shared" ref="H442:H505" si="19">IF(A442="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A442)</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -40648,21 +41181,21 @@
     </row>
     <row r="505" spans="6:8">
       <c r="F505" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="F505:F568" si="20">IF(A505="", "", "gift-codes.html?game=" &amp; A505)</f>
         <v/>
       </c>
       <c r="H505" s="41" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="H505:H568" si="21">IF(A505="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A505)</f>
         <v/>
       </c>
     </row>
     <row r="506" spans="6:8">
       <c r="F506" s="40" t="str">
-        <f t="shared" ref="F506:F569" si="20">IF(A506="", "", "gift-codes.html?game=" &amp; A506)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H506" s="41" t="str">
-        <f t="shared" ref="H506:H569" si="21">IF(A506="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A506)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -41288,11 +41821,11 @@
     </row>
     <row r="569" spans="6:8">
       <c r="F569" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(A569="", "", "gift-codes.html?game=" &amp; A569)</f>
         <v/>
       </c>
       <c r="H569" s="41" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="H569:H627" si="22">IF(A569="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A569)</f>
         <v/>
       </c>
     </row>
@@ -41302,7 +41835,7 @@
         <v/>
       </c>
       <c r="H570" s="41" t="str">
-        <f t="shared" ref="H570:H628" si="22">IF(A570="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A570)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -41317,10 +41850,6 @@
       </c>
     </row>
     <row r="572" spans="6:8">
-      <c r="F572" s="40" t="str">
-        <f>IF(A572="", "", "gift-codes.html?game=" &amp; A572)</f>
-        <v/>
-      </c>
       <c r="H572" s="41" t="str">
         <f t="shared" si="22"/>
         <v/>
@@ -41652,12 +42181,6 @@
     </row>
     <row r="627" spans="8:8">
       <c r="H627" s="41" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-    </row>
-    <row r="628" spans="8:8">
-      <c r="H628" s="41" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -41876,15 +42399,16 @@
     <hyperlink ref="D268" r:id="rId206" location="s1"/>
     <hyperlink ref="G268" r:id="rId207"/>
     <hyperlink ref="E268" r:id="rId208"/>
+    <hyperlink ref="C269" r:id="rId209"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId209"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId210"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AX436"/>
+  <dimension ref="A1:AX435"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="19.5"/>
   <cols>
     <col min="1" max="1" width="24.375" style="13" customWidth="1"/>
@@ -56041,6 +56565,15 @@
       <c r="AA227" s="71" t="s">
         <v>4877</v>
       </c>
+      <c r="AC227" s="18" t="s">
+        <v>4992</v>
+      </c>
+      <c r="AE227" s="18" t="s">
+        <v>4993</v>
+      </c>
+      <c r="AG227" s="18" t="s">
+        <v>4994</v>
+      </c>
     </row>
     <row r="228" spans="1:47" ht="22.5" customHeight="1">
       <c r="A228" s="13" t="str">
@@ -57348,7 +57881,7 @@
         <v>2640</v>
       </c>
     </row>
-    <row r="257" spans="1:26" ht="22.5" customHeight="1">
+    <row r="257" spans="1:31" ht="22.5" customHeight="1">
       <c r="A257" s="13" t="str">
         <f>IF(games!A257="", "", games!A257)</f>
         <v>屍不可擋</v>
@@ -57381,7 +57914,7 @@
         <v>4719</v>
       </c>
     </row>
-    <row r="258" spans="1:26" ht="22.5" customHeight="1">
+    <row r="258" spans="1:31" ht="22.5" customHeight="1">
       <c r="A258" s="13" t="str">
         <f>IF(games!A258="", "", games!A258)</f>
         <v>RF ONLINE NEXT</v>
@@ -57411,7 +57944,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="259" spans="1:26">
+    <row r="259" spans="1:31">
       <c r="A259" s="13" t="str">
         <f>IF(games!A259="", "", games!A259)</f>
         <v>少女掌門人</v>
@@ -57447,7 +57980,7 @@
         <v>4904</v>
       </c>
     </row>
-    <row r="260" spans="1:26">
+    <row r="260" spans="1:31">
       <c r="A260" s="13" t="str">
         <f>IF(games!A260="", "", games!A260)</f>
         <v>翼之櫻：放置決鬥者</v>
@@ -57478,7 +58011,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="261" spans="1:26">
+    <row r="261" spans="1:31">
       <c r="A261" s="13" t="str">
         <f>IF(games!A261="", "", games!A261)</f>
         <v>Oniro ARPG</v>
@@ -57509,7 +58042,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="262" spans="1:26">
+    <row r="262" spans="1:31">
       <c r="A262" s="13" t="str">
         <f>IF(games!A262="", "", games!A262)</f>
         <v>Legend of YMIR</v>
@@ -57541,7 +58074,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="263" spans="1:26">
+    <row r="263" spans="1:31">
       <c r="A263" s="13" t="str">
         <f>IF(games!A263="", "", games!A263)</f>
         <v>Elysia：星空墜落</v>
@@ -57571,7 +58104,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="264" spans="1:26">
+    <row r="264" spans="1:31">
       <c r="A264" s="13" t="str">
         <f>IF(games!A264="", "", games!A264)</f>
         <v>合併貓鎮</v>
@@ -57601,7 +58134,7 @@
         <v>4835</v>
       </c>
     </row>
-    <row r="265" spans="1:26">
+    <row r="265" spans="1:31">
       <c r="A265" s="13" t="str">
         <f>IF(games!A265="", "", games!A265)</f>
         <v>幻牌交鋒</v>
@@ -57636,8 +58169,38 @@
       <c r="L265" s="13" t="s">
         <v>4898</v>
       </c>
-    </row>
-    <row r="266" spans="1:26">
+      <c r="M265" s="18" t="s">
+        <v>4982</v>
+      </c>
+      <c r="O265" s="18" t="s">
+        <v>4983</v>
+      </c>
+      <c r="Q265" s="18" t="s">
+        <v>4984</v>
+      </c>
+      <c r="S265" s="18" t="s">
+        <v>4985</v>
+      </c>
+      <c r="U265" s="18" t="s">
+        <v>4986</v>
+      </c>
+      <c r="W265" s="18" t="s">
+        <v>4987</v>
+      </c>
+      <c r="Y265" s="18" t="s">
+        <v>4988</v>
+      </c>
+      <c r="AA265" s="18" t="s">
+        <v>4989</v>
+      </c>
+      <c r="AC265" s="18" t="s">
+        <v>4990</v>
+      </c>
+      <c r="AE265" s="18" t="s">
+        <v>4991</v>
+      </c>
+    </row>
+    <row r="266" spans="1:31">
       <c r="A266" s="13" t="str">
         <f>IF(games!A266="", "", games!A266)</f>
         <v>激鬥！王國保衛戰</v>
@@ -57667,7 +58230,7 @@
         <v>4835</v>
       </c>
     </row>
-    <row r="267" spans="1:26">
+    <row r="267" spans="1:31">
       <c r="A267" s="13" t="str">
         <f>IF(games!A267="", "", games!A267)</f>
         <v>嘟嘟臉惡作劇</v>
@@ -57685,70 +58248,70 @@
         <v>《嘟嘟臉惡作劇》是一款充滿日系可愛風格的放置養成遊戲。故事發生在一個充滿魔法的學院，玩家將與一群擁有特殊能力的可愛角色們相遇，一同展開奇妙的冒險。遊戲採用輕鬆的放置玩法，讓你在繁忙之餘也能享受角色養成的樂趣，並透過策略性的戰鬥配置，挑戰各種關卡。想讓你的角色們迅速成長，解鎖更多有趣劇情嗎？記得使用官方兌換碼及禮包碼，獲得大量經驗與珍稀道具！我們也提供代儲值服務，讓您快速安全地獲得所需資源，輕鬆養成最強戰隊，在嘟嘟臉的世界裡盡情惡作劇吧！</v>
       </c>
       <c r="F267" s="17" t="s">
+        <v>4932</v>
+      </c>
+      <c r="G267" s="13" t="s">
+        <v>4933</v>
+      </c>
+      <c r="H267" s="13" t="s">
         <v>4934</v>
       </c>
-      <c r="G267" s="13" t="s">
+      <c r="I267" s="13" t="s">
         <v>4935</v>
       </c>
-      <c r="H267" s="13" t="s">
+      <c r="J267" s="13" t="s">
         <v>4936</v>
       </c>
-      <c r="I267" s="13" t="s">
+      <c r="K267" s="17" t="s">
+        <v>4924</v>
+      </c>
+      <c r="L267" s="13" t="s">
         <v>4937</v>
       </c>
-      <c r="J267" s="13" t="s">
+      <c r="M267" s="18" t="s">
+        <v>4925</v>
+      </c>
+      <c r="N267" s="13" t="s">
         <v>4938</v>
       </c>
-      <c r="K267" s="17" t="s">
+      <c r="O267" s="18" t="s">
         <v>4926</v>
       </c>
-      <c r="L267" s="13" t="s">
+      <c r="P267" s="13" t="s">
         <v>4939</v>
       </c>
-      <c r="M267" s="18" t="s">
+      <c r="Q267" s="18" t="s">
         <v>4927</v>
       </c>
-      <c r="N267" s="13" t="s">
+      <c r="R267" s="13" t="s">
         <v>4940</v>
       </c>
-      <c r="O267" s="18" t="s">
+      <c r="S267" s="18" t="s">
         <v>4928</v>
       </c>
-      <c r="P267" s="13" t="s">
+      <c r="T267" s="13" t="s">
         <v>4941</v>
       </c>
-      <c r="Q267" s="18" t="s">
+      <c r="U267" s="18" t="s">
         <v>4929</v>
       </c>
-      <c r="R267" s="13" t="s">
+      <c r="V267" s="13" t="s">
         <v>4942</v>
       </c>
-      <c r="S267" s="18" t="s">
+      <c r="W267" s="18" t="s">
         <v>4930</v>
       </c>
-      <c r="T267" s="13" t="s">
-        <v>4943</v>
-      </c>
-      <c r="U267" s="18" t="s">
+      <c r="X267" s="13" t="s">
+        <v>4942</v>
+      </c>
+      <c r="Y267" s="18" t="s">
         <v>4931</v>
       </c>
-      <c r="V267" s="13" t="s">
-        <v>4944</v>
-      </c>
-      <c r="W267" s="18" t="s">
-        <v>4932</v>
-      </c>
-      <c r="X267" s="13" t="s">
-        <v>4944</v>
-      </c>
-      <c r="Y267" s="18" t="s">
-        <v>4933</v>
-      </c>
       <c r="Z267" s="13" t="s">
-        <v>4944</v>
-      </c>
-    </row>
-    <row r="268" spans="1:26">
+        <v>4942</v>
+      </c>
+    </row>
+    <row r="268" spans="1:31">
       <c r="A268" s="13" t="str">
         <f>IF(games!A268="", "", games!A268)</f>
         <v>我的花園世界</v>
@@ -57765,11 +58328,11 @@
         <f>IF(games!I268&lt;&gt;"", games!I268, "")</f>
         <v>踏入《我的花園世界》，一個充滿奇幻與溫馨的養成冒險，讓你在忙碌的生活中找到一片心靈綠洲！這款手遊將帶你探索魔法大陸，與可愛的花仙子們一同培育珍奇植物，從零開始打造屬於你的夢想莊園。遊戲結合了多元的養成、裝飾與社交玩法，不僅能自由裝扮你的花園，更能拜訪好友，互贈禮物，共創美好回憶。想加速成長？別擔心，豐富的兌換碼和禮包碼讓你輕鬆取得稀有資源，快速提升等級。我們也提供代儲值服務，讓你享受快速安全的交易體驗，輕鬆購入心儀的限定道具。快來加入，與全球玩家一起體驗這場療癒又趣味的園藝之旅吧！</v>
       </c>
-      <c r="F268" s="34" t="s">
-        <v>4915</v>
+      <c r="F268" s="17" t="s">
+        <v>4836</v>
       </c>
       <c r="G268" s="13" t="s">
-        <v>4916</v>
+        <v>4835</v>
       </c>
       <c r="H268" s="13" t="s">
         <v>2625</v>
@@ -57808,93 +58371,157 @@
         <v>4914</v>
       </c>
     </row>
-    <row r="269" spans="1:26">
+    <row r="269" spans="1:31">
       <c r="A269" s="13" t="str">
         <f>IF(games!A269="", "", games!A269)</f>
-        <v/>
+        <v>Awakenloop</v>
       </c>
       <c r="C269" s="13" t="str">
         <f>IF(A269="","", "giftcodesbanner/" &amp; A269 &amp; "-禮包碼.jpg")</f>
-        <v/>
+        <v>giftcodesbanner/Awakenloop-禮包碼.jpg</v>
       </c>
       <c r="D269" s="13" t="str">
         <f>IF(A269="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A269)</f>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=Awakenloop</v>
       </c>
       <c r="E269" s="14" t="str">
         <f>IF(games!I269&lt;&gt;"", games!I269, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="270" spans="1:26">
+        <v>《Awakenloop》是一款充滿賽博龐克風格的卡牌回合制手遊，玩家將身處一個由機器人與人類共存的末日世界。遊戲主打策略性卡牌戰鬥，每張卡牌都蘊含獨特技能，如何搭配與釋放將成為戰局關鍵。除了豐富的主線劇情，遊戲也提供多樣的副本挑戰與 PvP 模式，讓你與其他玩家一較高下。現在就加入《Awakenloop》，透過兌換碼與禮包碼獲得專屬獎勵，輕鬆提升戰力，也能使用代儲值服務快速安全地補充資源，在這片混沌的廢土上開創屬於你的新紀元。</v>
+      </c>
+      <c r="F269" s="17" t="s">
+        <v>4836</v>
+      </c>
+      <c r="G269" s="13" t="s">
+        <v>4835</v>
+      </c>
+      <c r="K269" s="17" t="s">
+        <v>4836</v>
+      </c>
+      <c r="L269" s="13" t="s">
+        <v>4835</v>
+      </c>
+    </row>
+    <row r="270" spans="1:31">
       <c r="A270" s="13" t="str">
         <f>IF(games!A270="", "", games!A270)</f>
-        <v/>
+        <v>Astellia</v>
       </c>
       <c r="C270" s="13" t="str">
         <f>IF(A270="","", "giftcodesbanner/" &amp; A270 &amp; "-禮包碼.jpg")</f>
-        <v/>
+        <v>giftcodesbanner/Astellia-禮包碼.jpg</v>
       </c>
       <c r="D270" s="13" t="str">
         <f>IF(A270="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A270)</f>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=Astellia</v>
       </c>
       <c r="E270" s="14" t="str">
         <f>IF(games!I270&lt;&gt;"", games!I270, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="271" spans="1:26">
+        <v>《Astellia》是一款日系風格的魔幻冒險MMORPG，帶領玩家進入一個充滿魔法與奇幻生物的艾斯提亞大陸。遊戲以其精緻的3D美術畫面與豐富的職業系統著稱，玩家可自由選擇多種職業，並透過養成可愛的「星靈」夥伴來協助戰鬥。遊戲提供多樣化的副本、世界王挑戰與公會系統，讓玩家能與好友一同探索廣闊的世界。使用兌換碼和禮包碼能輕鬆領取稀有道具，快速提升戰力，若需更多遊戲幣與資源，代儲值服務能提供你安全又快速的儲值體驗，讓你在艾斯提亞大陸的旅程更加順暢。</v>
+      </c>
+      <c r="F270" s="17" t="s">
+        <v>4836</v>
+      </c>
+      <c r="G270" s="13" t="s">
+        <v>4835</v>
+      </c>
+      <c r="K270" s="17" t="s">
+        <v>4836</v>
+      </c>
+      <c r="L270" s="13" t="s">
+        <v>4835</v>
+      </c>
+    </row>
+    <row r="271" spans="1:31">
       <c r="A271" s="13" t="str">
         <f>IF(games!A271="", "", games!A271)</f>
-        <v/>
+        <v>華夏千秋</v>
       </c>
       <c r="C271" s="13" t="str">
         <f>IF(A271="","", "giftcodesbanner/" &amp; A271 &amp; "-禮包碼.jpg")</f>
-        <v/>
+        <v>giftcodesbanner/華夏千秋-禮包碼.jpg</v>
       </c>
       <c r="D271" s="13" t="str">
         <f>IF(A271="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A271)</f>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=華夏千秋</v>
       </c>
       <c r="E271" s="14" t="str">
         <f>IF(games!I271&lt;&gt;"", games!I271, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="272" spans="1:26">
+        <v>《華夏千秋》是一款以中國古代神話為背景的MMORPG，遊戲將玩家帶入一個波瀾壯闊的東方玄幻世界。你將化身為修仙者，體驗從凡人到仙神的蛻變歷程。遊戲結合了豐富的劇情故事與自由的戰鬥系統，還有多樣化的社交玩法，讓玩家在修仙的道路上結交同伴，並肩作戰。現在就透過兌換碼和禮包碼領取豐富資源，快速開啟你的修仙之路，若想省時省力，安全的代儲值服務能讓你在短時間內獲得豐厚的回報，輕鬆應對各種挑戰，成就千秋霸業。</v>
+      </c>
+      <c r="F271" s="17" t="s">
+        <v>4836</v>
+      </c>
+      <c r="G271" s="13" t="s">
+        <v>4835</v>
+      </c>
+      <c r="K271" s="17" t="s">
+        <v>4836</v>
+      </c>
+      <c r="L271" s="13" t="s">
+        <v>4835</v>
+      </c>
+    </row>
+    <row r="272" spans="1:31">
       <c r="A272" s="13" t="str">
         <f>IF(games!A272="", "", games!A272)</f>
-        <v/>
+        <v>萌塔娘</v>
       </c>
       <c r="C272" s="13" t="str">
         <f>IF(A272="","", "giftcodesbanner/" &amp; A272 &amp; "-禮包碼.jpg")</f>
-        <v/>
+        <v>giftcodesbanner/萌塔娘-禮包碼.jpg</v>
       </c>
       <c r="D272" s="13" t="str">
         <f>IF(A272="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A272)</f>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=萌塔娘</v>
       </c>
       <c r="E272" s="14" t="str">
         <f>IF(games!I272&lt;&gt;"", games!I272, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="273" spans="1:4">
+        <v>《萌塔娘》是一款結合了塔防與角色養成元素的二次元策略手遊，玩家將在遊戲中與各種「塔娘」並肩作戰，守護家園。遊戲以其可愛的Q版畫風與創新的塔防玩法吸引玩家，每位塔娘都有獨特的技能與屬性，如何配置防禦陣線與策略運用將是勝利的關鍵。遊戲內提供多樣化的養成系統，讓玩家能培養出最強的塔娘戰隊。透過兌換碼與禮包碼可獲得限定獎勵，快速提升戰力，若想迅速強化隊伍，安全的代儲值服務絕對是快速又方便的選擇，讓你輕鬆守護世界的和平。</v>
+      </c>
+      <c r="F272" s="17" t="s">
+        <v>4836</v>
+      </c>
+      <c r="G272" s="13" t="s">
+        <v>4835</v>
+      </c>
+      <c r="K272" s="17" t="s">
+        <v>4836</v>
+      </c>
+      <c r="L272" s="13" t="s">
+        <v>4835</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12">
       <c r="A273" s="13" t="str">
         <f>IF(games!A273="", "", games!A273)</f>
-        <v/>
+        <v>盜夢英雄2：幻野</v>
       </c>
       <c r="C273" s="13" t="str">
         <f>IF(A273="","", "giftcodesbanner/" &amp; A273 &amp; "-禮包碼.jpg")</f>
-        <v/>
+        <v>giftcodesbanner/盜夢英雄2：幻野-禮包碼.jpg</v>
       </c>
       <c r="D273" s="13" t="str">
         <f>IF(A273="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A273)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="1:4">
+        <v>https://www.ssbuy.tw/gift-codes.html?game=盜夢英雄2：幻野</v>
+      </c>
+      <c r="E273" s="14" t="str">
+        <f>IF(games!I273&lt;&gt;"", games!I273, "")</f>
+        <v>《盜夢英雄2：幻野》是一款主打橫向捲軸動作戰鬥的RPG手遊，玩家將進入一個充滿奇幻與冒險的夢境世界。遊戲以爽快的打擊感與華麗的技能特效為核心，玩家可自由組建隊伍，挑戰各種強大的魔物與敵人。豐富的劇情模式與多樣的副本挑戰讓遊戲內容更加充實，無論是PVP還是PVE玩家都能找到樂趣。現在使用兌換碼與禮包碼就能領取專屬禮品，快速提升戰力，若有額外資源需求，代儲值服務提供最快速安全的購買管道，讓你輕鬆在夢境世界中探索，成為最強的夢境英雄。</v>
+      </c>
+      <c r="F273" s="17" t="s">
+        <v>4836</v>
+      </c>
+      <c r="G273" s="13" t="s">
+        <v>4835</v>
+      </c>
+      <c r="K273" s="17" t="s">
+        <v>4836</v>
+      </c>
+      <c r="L273" s="13" t="s">
+        <v>4835</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12">
       <c r="A274" s="13" t="str">
         <f>IF(games!A274="", "", games!A274)</f>
         <v/>
@@ -57907,8 +58534,12 @@
         <f>IF(A274="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A274)</f>
         <v/>
       </c>
-    </row>
-    <row r="275" spans="1:4">
+      <c r="E274" s="14" t="str">
+        <f>IF(games!I274&lt;&gt;"", games!I274, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275" spans="1:12">
       <c r="A275" s="13" t="str">
         <f>IF(games!A275="", "", games!A275)</f>
         <v/>
@@ -57921,8 +58552,12 @@
         <f>IF(A275="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A275)</f>
         <v/>
       </c>
-    </row>
-    <row r="276" spans="1:4">
+      <c r="E275" s="14" t="str">
+        <f>IF(games!I275&lt;&gt;"", games!I275, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276" spans="1:12">
       <c r="A276" s="13" t="str">
         <f>IF(games!A276="", "", games!A276)</f>
         <v/>
@@ -57935,8 +58570,12 @@
         <f>IF(A276="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A276)</f>
         <v/>
       </c>
-    </row>
-    <row r="277" spans="1:4">
+      <c r="E276" s="14" t="str">
+        <f>IF(games!I276&lt;&gt;"", games!I276, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="277" spans="1:12">
       <c r="A277" s="13" t="str">
         <f>IF(games!A277="", "", games!A277)</f>
         <v/>
@@ -57949,8 +58588,12 @@
         <f>IF(A277="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A277)</f>
         <v/>
       </c>
-    </row>
-    <row r="278" spans="1:4">
+      <c r="E277" s="14" t="str">
+        <f>IF(games!I277&lt;&gt;"", games!I277, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="278" spans="1:12">
       <c r="A278" s="13" t="str">
         <f>IF(games!A278="", "", games!A278)</f>
         <v/>
@@ -57963,8 +58606,12 @@
         <f>IF(A278="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A278)</f>
         <v/>
       </c>
-    </row>
-    <row r="279" spans="1:4">
+      <c r="E278" s="14" t="str">
+        <f>IF(games!I278&lt;&gt;"", games!I278, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="279" spans="1:12">
       <c r="A279" s="13" t="str">
         <f>IF(games!A279="", "", games!A279)</f>
         <v/>
@@ -57977,8 +58624,12 @@
         <f>IF(A279="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A279)</f>
         <v/>
       </c>
-    </row>
-    <row r="280" spans="1:4">
+      <c r="E279" s="14" t="str">
+        <f>IF(games!I279&lt;&gt;"", games!I279, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280" spans="1:12">
       <c r="A280" s="13" t="str">
         <f>IF(games!A280="", "", games!A280)</f>
         <v/>
@@ -57991,8 +58642,12 @@
         <f>IF(A280="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A280)</f>
         <v/>
       </c>
-    </row>
-    <row r="281" spans="1:4">
+      <c r="E280" s="14" t="str">
+        <f>IF(games!I280&lt;&gt;"", games!I280, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281" spans="1:12">
       <c r="A281" s="13" t="str">
         <f>IF(games!A281="", "", games!A281)</f>
         <v/>
@@ -58005,8 +58660,12 @@
         <f>IF(A281="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A281)</f>
         <v/>
       </c>
-    </row>
-    <row r="282" spans="1:4">
+      <c r="E281" s="14" t="str">
+        <f>IF(games!I281&lt;&gt;"", games!I281, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="282" spans="1:12">
       <c r="A282" s="13" t="str">
         <f>IF(games!A282="", "", games!A282)</f>
         <v/>
@@ -58019,8 +58678,12 @@
         <f>IF(A282="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A282)</f>
         <v/>
       </c>
-    </row>
-    <row r="283" spans="1:4">
+      <c r="E282" s="14" t="str">
+        <f>IF(games!I282&lt;&gt;"", games!I282, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283" spans="1:12">
       <c r="A283" s="13" t="str">
         <f>IF(games!A283="", "", games!A283)</f>
         <v/>
@@ -58033,8 +58696,12 @@
         <f>IF(A283="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A283)</f>
         <v/>
       </c>
-    </row>
-    <row r="284" spans="1:4">
+      <c r="E283" s="14" t="str">
+        <f>IF(games!I283&lt;&gt;"", games!I283, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284" spans="1:12">
       <c r="A284" s="13" t="str">
         <f>IF(games!A284="", "", games!A284)</f>
         <v/>
@@ -58047,8 +58714,12 @@
         <f>IF(A284="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A284)</f>
         <v/>
       </c>
-    </row>
-    <row r="285" spans="1:4">
+      <c r="E284" s="14" t="str">
+        <f>IF(games!I284&lt;&gt;"", games!I284, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285" spans="1:12">
       <c r="A285" s="13" t="str">
         <f>IF(games!A285="", "", games!A285)</f>
         <v/>
@@ -58061,8 +58732,12 @@
         <f>IF(A285="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A285)</f>
         <v/>
       </c>
-    </row>
-    <row r="286" spans="1:4">
+      <c r="E285" s="14" t="str">
+        <f>IF(games!I285&lt;&gt;"", games!I285, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286" spans="1:12">
       <c r="A286" s="13" t="str">
         <f>IF(games!A286="", "", games!A286)</f>
         <v/>
@@ -58075,8 +58750,12 @@
         <f>IF(A286="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A286)</f>
         <v/>
       </c>
-    </row>
-    <row r="287" spans="1:4">
+      <c r="E286" s="14" t="str">
+        <f>IF(games!I286&lt;&gt;"", games!I286, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="287" spans="1:12">
       <c r="A287" s="13" t="str">
         <f>IF(games!A287="", "", games!A287)</f>
         <v/>
@@ -58089,8 +58768,12 @@
         <f>IF(A287="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A287)</f>
         <v/>
       </c>
-    </row>
-    <row r="288" spans="1:4">
+      <c r="E287" s="14" t="str">
+        <f>IF(games!I287&lt;&gt;"", games!I287, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288" spans="1:12">
       <c r="A288" s="13" t="str">
         <f>IF(games!A288="", "", games!A288)</f>
         <v/>
@@ -58103,8 +58786,12 @@
         <f>IF(A288="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A288)</f>
         <v/>
       </c>
-    </row>
-    <row r="289" spans="1:4">
+      <c r="E288" s="14" t="str">
+        <f>IF(games!I288&lt;&gt;"", games!I288, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
       <c r="A289" s="13" t="str">
         <f>IF(games!A289="", "", games!A289)</f>
         <v/>
@@ -58117,8 +58804,12 @@
         <f>IF(A289="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A289)</f>
         <v/>
       </c>
-    </row>
-    <row r="290" spans="1:4">
+      <c r="E289" s="14" t="str">
+        <f>IF(games!I289&lt;&gt;"", games!I289, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
       <c r="A290" s="13" t="str">
         <f>IF(games!A290="", "", games!A290)</f>
         <v/>
@@ -58131,8 +58822,12 @@
         <f>IF(A290="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A290)</f>
         <v/>
       </c>
-    </row>
-    <row r="291" spans="1:4">
+      <c r="E290" s="14" t="str">
+        <f>IF(games!I290&lt;&gt;"", games!I290, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
       <c r="A291" s="13" t="str">
         <f>IF(games!A291="", "", games!A291)</f>
         <v/>
@@ -58145,8 +58840,12 @@
         <f>IF(A291="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A291)</f>
         <v/>
       </c>
-    </row>
-    <row r="292" spans="1:4">
+      <c r="E291" s="14" t="str">
+        <f>IF(games!I291&lt;&gt;"", games!I291, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
       <c r="A292" s="13" t="str">
         <f>IF(games!A292="", "", games!A292)</f>
         <v/>
@@ -58159,8 +58858,12 @@
         <f>IF(A292="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A292)</f>
         <v/>
       </c>
-    </row>
-    <row r="293" spans="1:4">
+      <c r="E292" s="14" t="str">
+        <f>IF(games!I292&lt;&gt;"", games!I292, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
       <c r="A293" s="13" t="str">
         <f>IF(games!A293="", "", games!A293)</f>
         <v/>
@@ -58173,8 +58876,12 @@
         <f>IF(A293="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A293)</f>
         <v/>
       </c>
-    </row>
-    <row r="294" spans="1:4">
+      <c r="E293" s="14" t="str">
+        <f>IF(games!I293&lt;&gt;"", games!I293, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
       <c r="A294" s="13" t="str">
         <f>IF(games!A294="", "", games!A294)</f>
         <v/>
@@ -58187,8 +58894,12 @@
         <f>IF(A294="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A294)</f>
         <v/>
       </c>
-    </row>
-    <row r="295" spans="1:4">
+      <c r="E294" s="14" t="str">
+        <f>IF(games!I294&lt;&gt;"", games!I294, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
       <c r="A295" s="13" t="str">
         <f>IF(games!A295="", "", games!A295)</f>
         <v/>
@@ -58201,8 +58912,12 @@
         <f>IF(A295="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A295)</f>
         <v/>
       </c>
-    </row>
-    <row r="296" spans="1:4">
+      <c r="E295" s="14" t="str">
+        <f>IF(games!I295&lt;&gt;"", games!I295, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
       <c r="A296" s="13" t="str">
         <f>IF(games!A296="", "", games!A296)</f>
         <v/>
@@ -58215,8 +58930,12 @@
         <f>IF(A296="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A296)</f>
         <v/>
       </c>
-    </row>
-    <row r="297" spans="1:4">
+      <c r="E296" s="14" t="str">
+        <f>IF(games!I296&lt;&gt;"", games!I296, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
       <c r="A297" s="13" t="str">
         <f>IF(games!A297="", "", games!A297)</f>
         <v/>
@@ -58229,8 +58948,12 @@
         <f>IF(A297="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A297)</f>
         <v/>
       </c>
-    </row>
-    <row r="298" spans="1:4">
+      <c r="E297" s="14" t="str">
+        <f>IF(games!I297&lt;&gt;"", games!I297, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
       <c r="A298" s="13" t="str">
         <f>IF(games!A298="", "", games!A298)</f>
         <v/>
@@ -58243,8 +58966,12 @@
         <f>IF(A298="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A298)</f>
         <v/>
       </c>
-    </row>
-    <row r="299" spans="1:4">
+      <c r="E298" s="14" t="str">
+        <f>IF(games!I298&lt;&gt;"", games!I298, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
       <c r="A299" s="13" t="str">
         <f>IF(games!A299="", "", games!A299)</f>
         <v/>
@@ -58257,8 +58984,12 @@
         <f>IF(A299="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A299)</f>
         <v/>
       </c>
-    </row>
-    <row r="300" spans="1:4">
+      <c r="E299" s="14" t="str">
+        <f>IF(games!I299&lt;&gt;"", games!I299, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
       <c r="A300" s="13" t="str">
         <f>IF(games!A300="", "", games!A300)</f>
         <v/>
@@ -58271,8 +59002,12 @@
         <f>IF(A300="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A300)</f>
         <v/>
       </c>
-    </row>
-    <row r="301" spans="1:4">
+      <c r="E300" s="14" t="str">
+        <f>IF(games!I300&lt;&gt;"", games!I300, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
       <c r="A301" s="13" t="str">
         <f>IF(games!A301="", "", games!A301)</f>
         <v/>
@@ -58285,8 +59020,12 @@
         <f>IF(A301="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A301)</f>
         <v/>
       </c>
-    </row>
-    <row r="302" spans="1:4">
+      <c r="E301" s="14" t="str">
+        <f>IF(games!I301&lt;&gt;"", games!I301, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
       <c r="A302" s="13" t="str">
         <f>IF(games!A302="", "", games!A302)</f>
         <v/>
@@ -58299,8 +59038,12 @@
         <f>IF(A302="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A302)</f>
         <v/>
       </c>
-    </row>
-    <row r="303" spans="1:4">
+      <c r="E302" s="14" t="str">
+        <f>IF(games!I302&lt;&gt;"", games!I302, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
       <c r="A303" s="13" t="str">
         <f>IF(games!A303="", "", games!A303)</f>
         <v/>
@@ -58313,12 +59056,12 @@
         <f>IF(A303="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A303)</f>
         <v/>
       </c>
-    </row>
-    <row r="304" spans="1:4">
-      <c r="A304" s="13" t="str">
-        <f>IF(games!A304="", "", games!A304)</f>
-        <v/>
-      </c>
+      <c r="E303" s="14" t="str">
+        <f>IF(games!I303&lt;&gt;"", games!I303, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
       <c r="C304" s="13" t="str">
         <f>IF(A304="","", "giftcodesbanner/" &amp; A304 &amp; "-禮包碼.jpg")</f>
         <v/>
@@ -58327,8 +59070,12 @@
         <f>IF(A304="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A304)</f>
         <v/>
       </c>
-    </row>
-    <row r="305" spans="3:4">
+      <c r="E304" s="14" t="str">
+        <f>IF(games!I304&lt;&gt;"", games!I304, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="305" spans="3:5">
       <c r="C305" s="13" t="str">
         <f>IF(A305="","", "giftcodesbanner/" &amp; A305 &amp; "-禮包碼.jpg")</f>
         <v/>
@@ -58337,8 +59084,12 @@
         <f>IF(A305="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A305)</f>
         <v/>
       </c>
-    </row>
-    <row r="306" spans="3:4">
+      <c r="E305" s="14" t="str">
+        <f>IF(games!I305&lt;&gt;"", games!I305, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="306" spans="3:5">
       <c r="C306" s="13" t="str">
         <f>IF(A306="","", "giftcodesbanner/" &amp; A306 &amp; "-禮包碼.jpg")</f>
         <v/>
@@ -58347,8 +59098,12 @@
         <f>IF(A306="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A306)</f>
         <v/>
       </c>
-    </row>
-    <row r="307" spans="3:4">
+      <c r="E306" s="14" t="str">
+        <f>IF(games!I306&lt;&gt;"", games!I306, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="307" spans="3:5">
       <c r="C307" s="13" t="str">
         <f>IF(A307="","", "giftcodesbanner/" &amp; A307 &amp; "-禮包碼.jpg")</f>
         <v/>
@@ -58357,8 +59112,12 @@
         <f>IF(A307="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A307)</f>
         <v/>
       </c>
-    </row>
-    <row r="308" spans="3:4">
+      <c r="E307" s="14" t="str">
+        <f>IF(games!I307&lt;&gt;"", games!I307, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="308" spans="3:5">
       <c r="C308" s="13" t="str">
         <f>IF(A308="","", "giftcodesbanner/" &amp; A308 &amp; "-禮包碼.jpg")</f>
         <v/>
@@ -58367,8 +59126,12 @@
         <f>IF(A308="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A308)</f>
         <v/>
       </c>
-    </row>
-    <row r="309" spans="3:4">
+      <c r="E308" s="14" t="str">
+        <f>IF(games!I308&lt;&gt;"", games!I308, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="309" spans="3:5">
       <c r="C309" s="13" t="str">
         <f>IF(A309="","", "giftcodesbanner/" &amp; A309 &amp; "-禮包碼.jpg")</f>
         <v/>
@@ -58377,8 +59140,12 @@
         <f>IF(A309="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A309)</f>
         <v/>
       </c>
-    </row>
-    <row r="310" spans="3:4">
+      <c r="E309" s="14" t="str">
+        <f>IF(games!I309&lt;&gt;"", games!I309, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="310" spans="3:5">
       <c r="C310" s="13" t="str">
         <f>IF(A310="","", "giftcodesbanner/" &amp; A310 &amp; "-禮包碼.jpg")</f>
         <v/>
@@ -58387,8 +59154,12 @@
         <f>IF(A310="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A310)</f>
         <v/>
       </c>
-    </row>
-    <row r="311" spans="3:4">
+      <c r="E310" s="14" t="str">
+        <f>IF(games!I310&lt;&gt;"", games!I310, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="311" spans="3:5">
       <c r="C311" s="13" t="str">
         <f>IF(A311="","", "giftcodesbanner/" &amp; A311 &amp; "-禮包碼.jpg")</f>
         <v/>
@@ -58397,8 +59168,12 @@
         <f>IF(A311="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A311)</f>
         <v/>
       </c>
-    </row>
-    <row r="312" spans="3:4">
+      <c r="E311" s="14" t="str">
+        <f>IF(games!I311&lt;&gt;"", games!I311, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312" spans="3:5">
       <c r="C312" s="13" t="str">
         <f>IF(A312="","", "giftcodesbanner/" &amp; A312 &amp; "-禮包碼.jpg")</f>
         <v/>
@@ -58407,28 +59182,40 @@
         <f>IF(A312="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A312)</f>
         <v/>
       </c>
-    </row>
-    <row r="313" spans="3:4">
+      <c r="E312" s="14" t="str">
+        <f>IF(games!I312&lt;&gt;"", games!I312, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="313" spans="3:5">
       <c r="C313" s="13" t="str">
-        <f>IF(A313="","", "giftcodesbanner/" &amp; A313 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" ref="C313:C376" si="12">IF(A313="","", "giftcodesbanner/" &amp; A313 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D313" s="13" t="str">
-        <f>IF(A313="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A313)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="314" spans="3:4">
+        <f t="shared" ref="D313:D376" si="13">IF(A313="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A313)</f>
+        <v/>
+      </c>
+      <c r="E313" s="14" t="str">
+        <f>IF(games!I313&lt;&gt;"", games!I313, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="314" spans="3:5">
       <c r="C314" s="13" t="str">
-        <f t="shared" ref="C314:C377" si="12">IF(A314="","", "giftcodesbanner/" &amp; A314 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D314" s="13" t="str">
-        <f t="shared" ref="D314:D377" si="13">IF(A314="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A314)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="315" spans="3:4">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E314" s="14" t="str">
+        <f>IF(games!I314&lt;&gt;"", games!I314, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315" spans="3:5">
       <c r="C315" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58437,8 +59224,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="316" spans="3:4">
+      <c r="E315" s="14" t="str">
+        <f>IF(games!I315&lt;&gt;"", games!I315, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="316" spans="3:5">
       <c r="C316" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58447,8 +59238,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="317" spans="3:4">
+      <c r="E316" s="14" t="str">
+        <f>IF(games!I316&lt;&gt;"", games!I316, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="317" spans="3:5">
       <c r="C317" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58457,8 +59252,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="318" spans="3:4">
+      <c r="E317" s="14" t="str">
+        <f>IF(games!I317&lt;&gt;"", games!I317, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="318" spans="3:5">
       <c r="C318" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58467,8 +59266,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="319" spans="3:4">
+      <c r="E318" s="14" t="str">
+        <f>IF(games!I318&lt;&gt;"", games!I318, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="319" spans="3:5">
       <c r="C319" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58477,8 +59280,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="320" spans="3:4">
+      <c r="E319" s="14" t="str">
+        <f>IF(games!I319&lt;&gt;"", games!I319, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="320" spans="3:5">
       <c r="C320" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58487,8 +59294,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="321" spans="3:4">
+      <c r="E320" s="14" t="str">
+        <f>IF(games!I320&lt;&gt;"", games!I320, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="321" spans="3:5">
       <c r="C321" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58497,8 +59308,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="322" spans="3:4">
+      <c r="E321" s="14" t="str">
+        <f>IF(games!I321&lt;&gt;"", games!I321, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="322" spans="3:5">
       <c r="C322" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58507,8 +59322,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="323" spans="3:4">
+      <c r="E322" s="14" t="str">
+        <f>IF(games!I322&lt;&gt;"", games!I322, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="323" spans="3:5">
       <c r="C323" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58517,8 +59336,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="324" spans="3:4">
+      <c r="E323" s="14" t="str">
+        <f>IF(games!I323&lt;&gt;"", games!I323, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="324" spans="3:5">
       <c r="C324" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58527,8 +59350,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="325" spans="3:4">
+      <c r="E324" s="14" t="str">
+        <f>IF(games!I324&lt;&gt;"", games!I324, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="325" spans="3:5">
       <c r="C325" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58537,8 +59364,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="326" spans="3:4">
+      <c r="E325" s="14" t="str">
+        <f>IF(games!I325&lt;&gt;"", games!I325, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="326" spans="3:5">
       <c r="C326" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58547,8 +59378,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="327" spans="3:4">
+      <c r="E326" s="14" t="str">
+        <f>IF(games!I326&lt;&gt;"", games!I326, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="327" spans="3:5">
       <c r="C327" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58557,8 +59392,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="328" spans="3:4">
+      <c r="E327" s="14" t="str">
+        <f>IF(games!I327&lt;&gt;"", games!I327, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328" spans="3:5">
       <c r="C328" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58567,8 +59406,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="329" spans="3:4">
+      <c r="E328" s="14" t="str">
+        <f>IF(games!I328&lt;&gt;"", games!I328, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="329" spans="3:5">
       <c r="C329" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58577,8 +59420,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="330" spans="3:4">
+      <c r="E329" s="14" t="str">
+        <f>IF(games!I329&lt;&gt;"", games!I329, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="330" spans="3:5">
       <c r="C330" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58587,8 +59434,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="331" spans="3:4">
+      <c r="E330" s="14" t="str">
+        <f>IF(games!I330&lt;&gt;"", games!I330, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="331" spans="3:5">
       <c r="C331" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58597,8 +59448,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="332" spans="3:4">
+      <c r="E331" s="14" t="str">
+        <f>IF(games!I331&lt;&gt;"", games!I331, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="332" spans="3:5">
       <c r="C332" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58607,8 +59462,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="333" spans="3:4">
+      <c r="E332" s="14" t="str">
+        <f>IF(games!I332&lt;&gt;"", games!I332, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="333" spans="3:5">
       <c r="C333" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58617,8 +59476,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="334" spans="3:4">
+      <c r="E333" s="14" t="str">
+        <f>IF(games!I333&lt;&gt;"", games!I333, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="334" spans="3:5">
       <c r="C334" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58627,8 +59490,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="335" spans="3:4">
+      <c r="E334" s="14" t="str">
+        <f>IF(games!I334&lt;&gt;"", games!I334, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="335" spans="3:5">
       <c r="C335" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58637,8 +59504,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="336" spans="3:4">
+      <c r="E335" s="14" t="str">
+        <f>IF(games!I335&lt;&gt;"", games!I335, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="336" spans="3:5">
       <c r="C336" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58647,8 +59518,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="337" spans="3:4">
+      <c r="E336" s="14" t="str">
+        <f>IF(games!I336&lt;&gt;"", games!I336, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="337" spans="3:5">
       <c r="C337" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58657,8 +59532,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="338" spans="3:4">
+      <c r="E337" s="14" t="str">
+        <f>IF(games!I337&lt;&gt;"", games!I337, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="338" spans="3:5">
       <c r="C338" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58667,8 +59546,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="339" spans="3:4">
+      <c r="E338" s="14" t="str">
+        <f>IF(games!I338&lt;&gt;"", games!I338, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="339" spans="3:5">
       <c r="C339" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58677,8 +59560,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="340" spans="3:4">
+      <c r="E339" s="14" t="str">
+        <f>IF(games!I339&lt;&gt;"", games!I339, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340" spans="3:5">
       <c r="C340" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58687,8 +59574,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="341" spans="3:4">
+      <c r="E340" s="14" t="str">
+        <f>IF(games!I340&lt;&gt;"", games!I340, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="341" spans="3:5">
       <c r="C341" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58697,8 +59588,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="342" spans="3:4">
+      <c r="E341" s="14" t="str">
+        <f>IF(games!I341&lt;&gt;"", games!I341, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="342" spans="3:5">
       <c r="C342" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58707,8 +59602,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="343" spans="3:4">
+      <c r="E342" s="14" t="str">
+        <f>IF(games!I342&lt;&gt;"", games!I342, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="343" spans="3:5">
       <c r="C343" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58717,8 +59616,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="344" spans="3:4">
+      <c r="E343" s="14" t="str">
+        <f>IF(games!I343&lt;&gt;"", games!I343, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="344" spans="3:5">
       <c r="C344" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58727,8 +59630,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="345" spans="3:4">
+      <c r="E344" s="14" t="str">
+        <f>IF(games!I344&lt;&gt;"", games!I344, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="345" spans="3:5">
       <c r="C345" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58737,8 +59644,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="346" spans="3:4">
+      <c r="E345" s="14" t="str">
+        <f>IF(games!I345&lt;&gt;"", games!I345, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="346" spans="3:5">
       <c r="C346" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58747,8 +59658,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="347" spans="3:4">
+      <c r="E346" s="14" t="str">
+        <f>IF(games!I346&lt;&gt;"", games!I346, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="347" spans="3:5">
       <c r="C347" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58757,8 +59672,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="348" spans="3:4">
+      <c r="E347" s="14" t="str">
+        <f>IF(games!I347&lt;&gt;"", games!I347, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="348" spans="3:5">
       <c r="C348" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58767,8 +59686,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="349" spans="3:4">
+      <c r="E348" s="14" t="str">
+        <f>IF(games!I348&lt;&gt;"", games!I348, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="349" spans="3:5">
       <c r="C349" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58777,8 +59700,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="350" spans="3:4">
+      <c r="E349" s="14" t="str">
+        <f>IF(games!I349&lt;&gt;"", games!I349, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="350" spans="3:5">
       <c r="C350" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58787,8 +59714,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="351" spans="3:4">
+      <c r="E350" s="14" t="str">
+        <f>IF(games!I350&lt;&gt;"", games!I350, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="351" spans="3:5">
       <c r="C351" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58797,8 +59728,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="352" spans="3:4">
+      <c r="E351" s="14" t="str">
+        <f>IF(games!I351&lt;&gt;"", games!I351, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="352" spans="3:5">
       <c r="C352" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58807,8 +59742,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="353" spans="3:4">
+      <c r="E352" s="14" t="str">
+        <f>IF(games!I352&lt;&gt;"", games!I352, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="353" spans="3:5">
       <c r="C353" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58817,8 +59756,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="354" spans="3:4">
+      <c r="E353" s="14" t="str">
+        <f>IF(games!I353&lt;&gt;"", games!I353, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="354" spans="3:5">
       <c r="C354" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58827,8 +59770,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="355" spans="3:4">
+      <c r="E354" s="14" t="str">
+        <f>IF(games!I354&lt;&gt;"", games!I354, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="355" spans="3:5">
       <c r="C355" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58837,8 +59784,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="356" spans="3:4">
+      <c r="E355" s="14" t="str">
+        <f>IF(games!I355&lt;&gt;"", games!I355, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="356" spans="3:5">
       <c r="C356" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58847,8 +59798,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="357" spans="3:4">
+      <c r="E356" s="14" t="str">
+        <f>IF(games!I356&lt;&gt;"", games!I356, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="357" spans="3:5">
       <c r="C357" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58857,8 +59812,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="358" spans="3:4">
+      <c r="E357" s="14" t="str">
+        <f>IF(games!I357&lt;&gt;"", games!I357, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="358" spans="3:5">
       <c r="C358" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58867,8 +59826,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="359" spans="3:4">
+      <c r="E358" s="14" t="str">
+        <f>IF(games!I358&lt;&gt;"", games!I358, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="359" spans="3:5">
       <c r="C359" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58877,8 +59840,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="360" spans="3:4">
+      <c r="E359" s="14" t="str">
+        <f>IF(games!I359&lt;&gt;"", games!I359, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="360" spans="3:5">
       <c r="C360" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58887,8 +59854,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="361" spans="3:4">
+      <c r="E360" s="14" t="str">
+        <f>IF(games!I360&lt;&gt;"", games!I360, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="361" spans="3:5">
       <c r="C361" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58897,8 +59868,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="362" spans="3:4">
+      <c r="E361" s="14" t="str">
+        <f>IF(games!I361&lt;&gt;"", games!I361, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="362" spans="3:5">
       <c r="C362" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58907,8 +59882,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="363" spans="3:4">
+      <c r="E362" s="14" t="str">
+        <f>IF(games!I362&lt;&gt;"", games!I362, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="363" spans="3:5">
       <c r="C363" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58917,8 +59896,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="364" spans="3:4">
+      <c r="E363" s="14" t="str">
+        <f>IF(games!I363&lt;&gt;"", games!I363, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="364" spans="3:5">
       <c r="C364" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58927,8 +59910,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="365" spans="3:4">
+      <c r="E364" s="14" t="str">
+        <f>IF(games!I364&lt;&gt;"", games!I364, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="365" spans="3:5">
       <c r="C365" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58937,8 +59924,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="366" spans="3:4">
+      <c r="E365" s="14" t="str">
+        <f>IF(games!I365&lt;&gt;"", games!I365, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="366" spans="3:5">
       <c r="C366" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58947,8 +59938,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="367" spans="3:4">
+      <c r="E366" s="14" t="str">
+        <f>IF(games!I366&lt;&gt;"", games!I366, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="367" spans="3:5">
       <c r="C367" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58957,8 +59952,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="368" spans="3:4">
+      <c r="E367" s="14" t="str">
+        <f>IF(games!I367&lt;&gt;"", games!I367, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="368" spans="3:5">
       <c r="C368" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58967,8 +59966,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="369" spans="3:4">
+      <c r="E368" s="14" t="str">
+        <f>IF(games!I368&lt;&gt;"", games!I368, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="369" spans="3:5">
       <c r="C369" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58977,8 +59980,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="370" spans="3:4">
+      <c r="E369" s="14" t="str">
+        <f>IF(games!I369&lt;&gt;"", games!I369, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="370" spans="3:5">
       <c r="C370" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58987,8 +59994,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="371" spans="3:4">
+      <c r="E370" s="14" t="str">
+        <f>IF(games!I370&lt;&gt;"", games!I370, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="371" spans="3:5">
       <c r="C371" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -58997,8 +60008,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="372" spans="3:4">
+      <c r="E371" s="14" t="str">
+        <f>IF(games!I371&lt;&gt;"", games!I371, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="372" spans="3:5">
       <c r="C372" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -59007,8 +60022,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="373" spans="3:4">
+      <c r="E372" s="14" t="str">
+        <f>IF(games!I372&lt;&gt;"", games!I372, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="373" spans="3:5">
       <c r="C373" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -59017,8 +60036,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="374" spans="3:4">
+      <c r="E373" s="14" t="str">
+        <f>IF(games!I373&lt;&gt;"", games!I373, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="374" spans="3:5">
       <c r="C374" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -59027,8 +60050,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="375" spans="3:4">
+      <c r="E374" s="14" t="str">
+        <f>IF(games!I374&lt;&gt;"", games!I374, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="375" spans="3:5">
       <c r="C375" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -59037,8 +60064,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="376" spans="3:4">
+      <c r="E375" s="14" t="str">
+        <f>IF(games!I375&lt;&gt;"", games!I375, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="376" spans="3:5">
       <c r="C376" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -59047,28 +60078,40 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-    </row>
-    <row r="377" spans="3:4">
+      <c r="E376" s="14" t="str">
+        <f>IF(games!I376&lt;&gt;"", games!I376, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="377" spans="3:5">
       <c r="C377" s="13" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="C377:C435" si="14">IF(A377="","", "giftcodesbanner/" &amp; A377 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D377" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="378" spans="3:4">
+        <f t="shared" ref="D377:D435" si="15">IF(A377="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A377)</f>
+        <v/>
+      </c>
+      <c r="E377" s="14" t="str">
+        <f>IF(games!I377&lt;&gt;"", games!I377, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="378" spans="3:5">
       <c r="C378" s="13" t="str">
-        <f t="shared" ref="C378:C436" si="14">IF(A378="","", "giftcodesbanner/" &amp; A378 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D378" s="13" t="str">
-        <f t="shared" ref="D378:D436" si="15">IF(A378="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A378)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="379" spans="3:4">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="E378" s="14" t="str">
+        <f>IF(games!I378&lt;&gt;"", games!I378, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="379" spans="3:5">
       <c r="C379" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59077,8 +60120,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="380" spans="3:4">
+      <c r="E379" s="14" t="str">
+        <f>IF(games!I379&lt;&gt;"", games!I379, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="380" spans="3:5">
       <c r="C380" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59087,8 +60134,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="381" spans="3:4">
+      <c r="E380" s="14" t="str">
+        <f>IF(games!I380&lt;&gt;"", games!I380, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="381" spans="3:5">
       <c r="C381" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59097,8 +60148,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="382" spans="3:4">
+      <c r="E381" s="14" t="str">
+        <f>IF(games!I381&lt;&gt;"", games!I381, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="382" spans="3:5">
       <c r="C382" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59107,8 +60162,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="383" spans="3:4">
+      <c r="E382" s="14" t="str">
+        <f>IF(games!I382&lt;&gt;"", games!I382, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="383" spans="3:5">
       <c r="C383" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59117,8 +60176,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="384" spans="3:4">
+      <c r="E383" s="14" t="str">
+        <f>IF(games!I383&lt;&gt;"", games!I383, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="384" spans="3:5">
       <c r="C384" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59127,8 +60190,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="385" spans="3:4">
+      <c r="E384" s="14" t="str">
+        <f>IF(games!I384&lt;&gt;"", games!I384, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="385" spans="3:5">
       <c r="C385" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59137,8 +60204,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="386" spans="3:4">
+      <c r="E385" s="14" t="str">
+        <f>IF(games!I385&lt;&gt;"", games!I385, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="386" spans="3:5">
       <c r="C386" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59147,8 +60218,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="387" spans="3:4">
+      <c r="E386" s="14" t="str">
+        <f>IF(games!I386&lt;&gt;"", games!I386, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="387" spans="3:5">
       <c r="C387" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59157,8 +60232,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="388" spans="3:4">
+      <c r="E387" s="14" t="str">
+        <f>IF(games!I387&lt;&gt;"", games!I387, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="388" spans="3:5">
       <c r="C388" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59167,8 +60246,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="389" spans="3:4">
+      <c r="E388" s="14" t="str">
+        <f>IF(games!I388&lt;&gt;"", games!I388, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="389" spans="3:5">
       <c r="C389" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59177,8 +60260,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="390" spans="3:4">
+      <c r="E389" s="14" t="str">
+        <f>IF(games!I389&lt;&gt;"", games!I389, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="390" spans="3:5">
       <c r="C390" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59187,8 +60274,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="391" spans="3:4">
+      <c r="E390" s="14" t="str">
+        <f>IF(games!I390&lt;&gt;"", games!I390, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="391" spans="3:5">
       <c r="C391" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59197,8 +60288,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="392" spans="3:4">
+      <c r="E391" s="14" t="str">
+        <f>IF(games!I391&lt;&gt;"", games!I391, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="392" spans="3:5">
       <c r="C392" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59207,8 +60302,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="393" spans="3:4">
+      <c r="E392" s="14" t="str">
+        <f>IF(games!I392&lt;&gt;"", games!I392, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="393" spans="3:5">
       <c r="C393" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59217,8 +60316,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="394" spans="3:4">
+      <c r="E393" s="14" t="str">
+        <f>IF(games!I393&lt;&gt;"", games!I393, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="394" spans="3:5">
       <c r="C394" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59227,8 +60330,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="395" spans="3:4">
+      <c r="E394" s="14" t="str">
+        <f>IF(games!I394&lt;&gt;"", games!I394, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="395" spans="3:5">
       <c r="C395" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59237,8 +60344,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="396" spans="3:4">
+      <c r="E395" s="14" t="str">
+        <f>IF(games!I395&lt;&gt;"", games!I395, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="396" spans="3:5">
       <c r="C396" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59247,8 +60358,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="397" spans="3:4">
+      <c r="E396" s="14" t="str">
+        <f>IF(games!I396&lt;&gt;"", games!I396, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="397" spans="3:5">
       <c r="C397" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59257,8 +60372,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="398" spans="3:4">
+      <c r="E397" s="14" t="str">
+        <f>IF(games!I397&lt;&gt;"", games!I397, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="398" spans="3:5">
       <c r="C398" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59267,8 +60386,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="399" spans="3:4">
+      <c r="E398" s="14" t="str">
+        <f>IF(games!I398&lt;&gt;"", games!I398, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="399" spans="3:5">
       <c r="C399" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59277,8 +60400,12 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-    </row>
-    <row r="400" spans="3:4">
+      <c r="E399" s="14" t="str">
+        <f>IF(games!I399&lt;&gt;"", games!I399, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="400" spans="3:5">
       <c r="C400" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -59634,16 +60761,6 @@
         <v/>
       </c>
       <c r="D435" s="13" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="436" spans="3:4">
-      <c r="C436" s="13" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="D436" s="13" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7347" uniqueCount="5017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7353" uniqueCount="5023">
   <si>
     <t>Facebook</t>
   </si>
@@ -19338,6 +19338,30 @@
   </si>
   <si>
     <t>390禮包</t>
+  </si>
+  <si>
+    <t>SNOWGIFT1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>kylevsteo1016</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>teorival</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>tastemywrath</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄召喚使用券x2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*20W</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -56574,6 +56598,9 @@
       <c r="AG227" s="18" t="s">
         <v>4994</v>
       </c>
+      <c r="AI227" s="18" t="s">
+        <v>5017</v>
+      </c>
     </row>
     <row r="228" spans="1:47" ht="22.5" customHeight="1">
       <c r="A228" s="13" t="str">
@@ -57048,6 +57075,21 @@
       </c>
       <c r="X236" s="13" t="s">
         <v>4752</v>
+      </c>
+      <c r="Y236" s="18" t="s">
+        <v>5018</v>
+      </c>
+      <c r="AA236" s="18" t="s">
+        <v>5019</v>
+      </c>
+      <c r="AB236" s="13" t="s">
+        <v>5022</v>
+      </c>
+      <c r="AC236" s="18" t="s">
+        <v>5020</v>
+      </c>
+      <c r="AD236" s="13" t="s">
+        <v>5021</v>
       </c>
     </row>
     <row r="237" spans="1:47" ht="22.5" customHeight="1">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7353" uniqueCount="5023">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7379" uniqueCount="5046">
   <si>
     <t>Facebook</t>
   </si>
@@ -19362,6 +19362,86 @@
   <si>
     <t>金幣*20W</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點左上角頭像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點中間兌換碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guidepostquest</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水晶*50+契約石*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPQDYRDT6N2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水晶*80+金幣*10000+水晶錘*5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blakeisnotsmith</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水晶*50+精鐵*300+水晶錘*5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61565447815087</t>
+  </si>
+  <si>
+    <t>https://avalongames.com/?fbclid=IwY2xjawNa-u1leHRuA2FlbQIxMABicmlkETEwZW1wMHVPTlpGbExaVXJlAR48tAF1RQnz1ODNmJgXZraCxo-XNBU-gVVI9cLux22qUaXE2j_mVOfeuVAzuA_aem_yEJXKs-SdClfM-PIMAR8LQ</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E8%B2%AA%E5%A9%AA%E6%B4%9E%E7%AA%9F-%E9%87%8D%E7%94%9F/id6680191526</t>
+  </si>
+  <si>
+    <t>貪婪洞窟：重生</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.avalon.c1p.googleplay&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>貪婪洞窟：重生是一款引人入勝的地牢探險 Roguelike 手遊，作為經典《貪婪洞窟》的全新重製與進化，它邀請所有渴望探索未知與禁忌的勇士，踏上這場智慧與膽識的極限試煉！遊戲保留了原作的核心玩法，並全面升級了裝備、天賦、秘術和道具系統。每一次冒險都充滿不確定性，錯綜複雜的地形、隱秘的符文與潛伏的怪物皆為隨機生成，每次探索都是全新的體驗。玩家可利用環境、天賦與裝備的巧妙結合，在黑暗中謀求一線生機。遊戲內常有兌換碼與禮包碼可供玩家領取，配合快速安全的代儲值服務，讓你的冒險之旅更加順暢。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6480水晶</t>
+  </si>
+  <si>
+    <t>3280水晶</t>
+  </si>
+  <si>
+    <t>1280水晶</t>
+  </si>
+  <si>
+    <t>680水晶</t>
+  </si>
+  <si>
+    <t>300水晶</t>
+  </si>
+  <si>
+    <t>傳奇真知之眼禮包</t>
+  </si>
+  <si>
+    <t>傳奇蠟燭禮包</t>
+  </si>
+  <si>
+    <t>絕世寶石契約禮包</t>
+  </si>
+  <si>
+    <t>至尊寶石契約禮包</t>
   </si>
 </sst>
 </file>
@@ -38893,14 +38973,92 @@
         <v>160</v>
       </c>
     </row>
-    <row r="274" spans="1:29" ht="22.5" customHeight="1">
+    <row r="274" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A274" s="70" t="s">
+        <v>5034</v>
+      </c>
+      <c r="C274" s="40" t="s">
+        <v>5031</v>
+      </c>
+      <c r="D274" s="41" t="s">
+        <v>5032</v>
+      </c>
+      <c r="E274" s="41" t="s">
+        <v>5033</v>
+      </c>
       <c r="F274" s="40" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=貪婪洞窟：重生</v>
+      </c>
+      <c r="G274" s="4" t="s">
+        <v>5035</v>
       </c>
       <c r="H274" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/貪婪洞窟：重生.html</v>
+      </c>
+      <c r="I274" s="42" t="s">
+        <v>5036</v>
+      </c>
+      <c r="J274" s="1" t="s">
+        <v>5037</v>
+      </c>
+      <c r="K274" s="72">
+        <v>2343</v>
+      </c>
+      <c r="L274" s="1" t="s">
+        <v>5038</v>
+      </c>
+      <c r="M274" s="72">
+        <v>1190</v>
+      </c>
+      <c r="N274" s="1" t="s">
+        <v>5039</v>
+      </c>
+      <c r="O274" s="72">
+        <v>556</v>
+      </c>
+      <c r="P274" s="1" t="s">
+        <v>5040</v>
+      </c>
+      <c r="Q274" s="72">
+        <v>258</v>
+      </c>
+      <c r="R274" s="1" t="s">
+        <v>5041</v>
+      </c>
+      <c r="S274" s="72">
+        <v>126</v>
+      </c>
+      <c r="T274" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="U274" s="72">
+        <v>26</v>
+      </c>
+      <c r="V274" s="1" t="s">
+        <v>5042</v>
+      </c>
+      <c r="W274" s="72">
+        <v>556</v>
+      </c>
+      <c r="X274" s="1" t="s">
+        <v>5043</v>
+      </c>
+      <c r="Y274" s="72">
+        <v>556</v>
+      </c>
+      <c r="Z274" s="1" t="s">
+        <v>5044</v>
+      </c>
+      <c r="AA274" s="72">
+        <v>1190</v>
+      </c>
+      <c r="AB274" s="1" t="s">
+        <v>5045</v>
+      </c>
+      <c r="AC274" s="72">
+        <v>2343</v>
       </c>
     </row>
     <row r="275" spans="1:29" ht="22.5" customHeight="1">
@@ -42424,9 +42582,10 @@
     <hyperlink ref="G268" r:id="rId207"/>
     <hyperlink ref="E268" r:id="rId208"/>
     <hyperlink ref="C269" r:id="rId209"/>
+    <hyperlink ref="G274" r:id="rId210"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId210"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId211"/>
 </worksheet>
 </file>
 
@@ -58533,7 +58692,7 @@
         <v>4835</v>
       </c>
     </row>
-    <row r="273" spans="1:12">
+    <row r="273" spans="1:16">
       <c r="A273" s="13" t="str">
         <f>IF(games!A273="", "", games!A273)</f>
         <v>盜夢英雄2：幻野</v>
@@ -58563,25 +58722,55 @@
         <v>4835</v>
       </c>
     </row>
-    <row r="274" spans="1:12">
+    <row r="274" spans="1:16">
       <c r="A274" s="13" t="str">
         <f>IF(games!A274="", "", games!A274)</f>
-        <v/>
+        <v>貪婪洞窟：重生</v>
       </c>
       <c r="C274" s="13" t="str">
         <f>IF(A274="","", "giftcodesbanner/" &amp; A274 &amp; "-禮包碼.jpg")</f>
-        <v/>
+        <v>giftcodesbanner/貪婪洞窟：重生-禮包碼.jpg</v>
       </c>
       <c r="D274" s="13" t="str">
         <f>IF(A274="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A274)</f>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=貪婪洞窟：重生</v>
       </c>
       <c r="E274" s="14" t="str">
         <f>IF(games!I274&lt;&gt;"", games!I274, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="275" spans="1:12">
+        <v>貪婪洞窟：重生是一款引人入勝的地牢探險 Roguelike 手遊，作為經典《貪婪洞窟》的全新重製與進化，它邀請所有渴望探索未知與禁忌的勇士，踏上這場智慧與膽識的極限試煉！遊戲保留了原作的核心玩法，並全面升級了裝備、天賦、秘術和道具系統。每一次冒險都充滿不確定性，錯綜複雜的地形、隱秘的符文與潛伏的怪物皆為隨機生成，每次探索都是全新的體驗。玩家可利用環境、天賦與裝備的巧妙結合，在黑暗中謀求一線生機。遊戲內常有兌換碼與禮包碼可供玩家領取，配合快速安全的代儲值服務，讓你的冒險之旅更加順暢。</v>
+      </c>
+      <c r="F274" s="34" t="s">
+        <v>5023</v>
+      </c>
+      <c r="G274" s="13" t="s">
+        <v>5024</v>
+      </c>
+      <c r="H274" s="13" t="s">
+        <v>2625</v>
+      </c>
+      <c r="I274" s="13" t="s">
+        <v>4368</v>
+      </c>
+      <c r="K274" s="17" t="s">
+        <v>5025</v>
+      </c>
+      <c r="L274" s="13" t="s">
+        <v>5026</v>
+      </c>
+      <c r="M274" s="18" t="s">
+        <v>5027</v>
+      </c>
+      <c r="N274" s="13" t="s">
+        <v>5028</v>
+      </c>
+      <c r="O274" s="18" t="s">
+        <v>5029</v>
+      </c>
+      <c r="P274" s="13" t="s">
+        <v>5030</v>
+      </c>
+    </row>
+    <row r="275" spans="1:16">
       <c r="A275" s="13" t="str">
         <f>IF(games!A275="", "", games!A275)</f>
         <v/>
@@ -58599,7 +58788,7 @@
         <v/>
       </c>
     </row>
-    <row r="276" spans="1:12">
+    <row r="276" spans="1:16">
       <c r="A276" s="13" t="str">
         <f>IF(games!A276="", "", games!A276)</f>
         <v/>
@@ -58617,7 +58806,7 @@
         <v/>
       </c>
     </row>
-    <row r="277" spans="1:12">
+    <row r="277" spans="1:16">
       <c r="A277" s="13" t="str">
         <f>IF(games!A277="", "", games!A277)</f>
         <v/>
@@ -58635,7 +58824,7 @@
         <v/>
       </c>
     </row>
-    <row r="278" spans="1:12">
+    <row r="278" spans="1:16">
       <c r="A278" s="13" t="str">
         <f>IF(games!A278="", "", games!A278)</f>
         <v/>
@@ -58653,7 +58842,7 @@
         <v/>
       </c>
     </row>
-    <row r="279" spans="1:12">
+    <row r="279" spans="1:16">
       <c r="A279" s="13" t="str">
         <f>IF(games!A279="", "", games!A279)</f>
         <v/>
@@ -58671,7 +58860,7 @@
         <v/>
       </c>
     </row>
-    <row r="280" spans="1:12">
+    <row r="280" spans="1:16">
       <c r="A280" s="13" t="str">
         <f>IF(games!A280="", "", games!A280)</f>
         <v/>
@@ -58689,7 +58878,7 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="1:12">
+    <row r="281" spans="1:16">
       <c r="A281" s="13" t="str">
         <f>IF(games!A281="", "", games!A281)</f>
         <v/>
@@ -58707,7 +58896,7 @@
         <v/>
       </c>
     </row>
-    <row r="282" spans="1:12">
+    <row r="282" spans="1:16">
       <c r="A282" s="13" t="str">
         <f>IF(games!A282="", "", games!A282)</f>
         <v/>
@@ -58725,7 +58914,7 @@
         <v/>
       </c>
     </row>
-    <row r="283" spans="1:12">
+    <row r="283" spans="1:16">
       <c r="A283" s="13" t="str">
         <f>IF(games!A283="", "", games!A283)</f>
         <v/>
@@ -58743,7 +58932,7 @@
         <v/>
       </c>
     </row>
-    <row r="284" spans="1:12">
+    <row r="284" spans="1:16">
       <c r="A284" s="13" t="str">
         <f>IF(games!A284="", "", games!A284)</f>
         <v/>
@@ -58761,7 +58950,7 @@
         <v/>
       </c>
     </row>
-    <row r="285" spans="1:12">
+    <row r="285" spans="1:16">
       <c r="A285" s="13" t="str">
         <f>IF(games!A285="", "", games!A285)</f>
         <v/>
@@ -58779,7 +58968,7 @@
         <v/>
       </c>
     </row>
-    <row r="286" spans="1:12">
+    <row r="286" spans="1:16">
       <c r="A286" s="13" t="str">
         <f>IF(games!A286="", "", games!A286)</f>
         <v/>
@@ -58797,7 +58986,7 @@
         <v/>
       </c>
     </row>
-    <row r="287" spans="1:12">
+    <row r="287" spans="1:16">
       <c r="A287" s="13" t="str">
         <f>IF(games!A287="", "", games!A287)</f>
         <v/>
@@ -58815,7 +59004,7 @@
         <v/>
       </c>
     </row>
-    <row r="288" spans="1:12">
+    <row r="288" spans="1:16">
       <c r="A288" s="13" t="str">
         <f>IF(games!A288="", "", games!A288)</f>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7379" uniqueCount="5046">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7384" uniqueCount="5051">
   <si>
     <t>Facebook</t>
   </si>
@@ -17161,21 +17161,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SENAREYOUNGLAEGI</t>
-  </si>
-  <si>
-    <t>SENAREGSIK</t>
-  </si>
-  <si>
-    <t>SENAREMOOVING</t>
-  </si>
-  <si>
-    <t>SENARESAMEWAY</t>
-  </si>
-  <si>
-    <t>SORRY4WAITING</t>
-  </si>
-  <si>
     <t>Grave Strikers</t>
   </si>
   <si>
@@ -18280,22 +18265,6 @@
   </si>
   <si>
     <t>在《少女掌門人》中，您可以體驗直式畫面單手操作的便捷，無論通勤、上學或睡前都能隨時暢玩。遊戲採用全自動戰鬥系統，少女們將會自行施展華麗必殺技與技能擊敗敵人，讓您觀看也能享受爽快戰鬥的視覺盛宴。透過無限可能的戰略組合，打造專屬您的最強戰術，提升門派實力，橫掃魔物！為了讓掌門人能夠快速成長，遊戲內設有豐富的兌換碼與禮包碼福利，提供豐厚資源助您一臂之力。此外，遊戲也支援代儲值服務，確保玩家能以快速安全的方式獲得所需物品，讓您輕鬆培育美少女角色，打造最強隊伍！立即加入，開啟您的掌門人生涯，享受培育少女、稱霸武林的成就感！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sevenknightsforever</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HAPPYFULLMOON</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>稀有四星英雄x1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>英雄召喚使用券x20</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -19348,100 +19317,156 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>英雄召喚使用券x2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點左上角頭像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點中間兌換碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guidepostquest</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水晶*50+契約石*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPQDYRDT6N2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水晶*80+金幣*10000+水晶錘*5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blakeisnotsmith</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水晶*50+精鐵*300+水晶錘*5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61565447815087</t>
+  </si>
+  <si>
+    <t>https://avalongames.com/?fbclid=IwY2xjawNa-u1leHRuA2FlbQIxMABicmlkETEwZW1wMHVPTlpGbExaVXJlAR48tAF1RQnz1ODNmJgXZraCxo-XNBU-gVVI9cLux22qUaXE2j_mVOfeuVAzuA_aem_yEJXKs-SdClfM-PIMAR8LQ</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E8%B2%AA%E5%A9%AA%E6%B4%9E%E7%AA%9F-%E9%87%8D%E7%94%9F/id6680191526</t>
+  </si>
+  <si>
+    <t>貪婪洞窟：重生</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.avalon.c1p.googleplay&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>貪婪洞窟：重生是一款引人入勝的地牢探險 Roguelike 手遊，作為經典《貪婪洞窟》的全新重製與進化，它邀請所有渴望探索未知與禁忌的勇士，踏上這場智慧與膽識的極限試煉！遊戲保留了原作的核心玩法，並全面升級了裝備、天賦、秘術和道具系統。每一次冒險都充滿不確定性，錯綜複雜的地形、隱秘的符文與潛伏的怪物皆為隨機生成，每次探索都是全新的體驗。玩家可利用環境、天賦與裝備的巧妙結合，在黑暗中謀求一線生機。遊戲內常有兌換碼與禮包碼可供玩家領取，配合快速安全的代儲值服務，讓你的冒險之旅更加順暢。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6480水晶</t>
+  </si>
+  <si>
+    <t>3280水晶</t>
+  </si>
+  <si>
+    <t>1280水晶</t>
+  </si>
+  <si>
+    <t>680水晶</t>
+  </si>
+  <si>
+    <t>300水晶</t>
+  </si>
+  <si>
+    <t>傳奇真知之眼禮包</t>
+  </si>
+  <si>
+    <t>傳奇蠟燭禮包</t>
+  </si>
+  <si>
+    <t>絕世寶石契約禮包</t>
+  </si>
+  <si>
+    <t>至尊寶石契約禮包</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2025/10/16 開啟</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>kyleteostory</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄召喚使用券x10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>teorival</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>金幣 × 20W</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>tastemywrath</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>英雄召喚使用券x2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>金幣*20W</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>點左上角頭像</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>點中間兌換碼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Guidepostquest</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>水晶*50+契約石*1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CPQDYRDT6N2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>水晶*80+金幣*10000+水晶錘*5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Blakeisnotsmith</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>水晶*50+精鐵*300+水晶錘*5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.facebook.com/profile.php?id=61565447815087</t>
-  </si>
-  <si>
-    <t>https://avalongames.com/?fbclid=IwY2xjawNa-u1leHRuA2FlbQIxMABicmlkETEwZW1wMHVPTlpGbExaVXJlAR48tAF1RQnz1ODNmJgXZraCxo-XNBU-gVVI9cLux22qUaXE2j_mVOfeuVAzuA_aem_yEJXKs-SdClfM-PIMAR8LQ</t>
-  </si>
-  <si>
-    <t>https://apps.apple.com/tw/app/%E8%B2%AA%E5%A9%AA%E6%B4%9E%E7%AA%9F-%E9%87%8D%E7%94%9F/id6680191526</t>
-  </si>
-  <si>
-    <t>貪婪洞窟：重生</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://play.google.com/store/apps/details?id=com.avalon.c1p.googleplay&amp;hl=zh_TW</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>貪婪洞窟：重生是一款引人入勝的地牢探險 Roguelike 手遊，作為經典《貪婪洞窟》的全新重製與進化，它邀請所有渴望探索未知與禁忌的勇士，踏上這場智慧與膽識的極限試煉！遊戲保留了原作的核心玩法，並全面升級了裝備、天賦、秘術和道具系統。每一次冒險都充滿不確定性，錯綜複雜的地形、隱秘的符文與潛伏的怪物皆為隨機生成，每次探索都是全新的體驗。玩家可利用環境、天賦與裝備的巧妙結合，在黑暗中謀求一線生機。遊戲內常有兌換碼與禮包碼可供玩家領取，配合快速安全的代儲值服務，讓你的冒險之旅更加順暢。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>6480水晶</t>
-  </si>
-  <si>
-    <t>3280水晶</t>
-  </si>
-  <si>
-    <t>1280水晶</t>
-  </si>
-  <si>
-    <t>680水晶</t>
-  </si>
-  <si>
-    <t>300水晶</t>
-  </si>
-  <si>
-    <t>傳奇真知之眼禮包</t>
-  </si>
-  <si>
-    <t>傳奇蠟燭禮包</t>
-  </si>
-  <si>
-    <t>絕世寶石契約禮包</t>
-  </si>
-  <si>
-    <t>至尊寶石契約禮包</t>
+    <t>sevenknightsforever</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>稀有四星英雄x1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HAPPYFULLMOON</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄召喚使用券x20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HPMADAYS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOH100DAYS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOHHPNO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOHHP99</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅色石榴石 x 300</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冒險掃蕩劵 x 30、核桃麵包籃 x 10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄召喚券 x 5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -36753,69 +36778,69 @@
     </row>
     <row r="245" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A245" s="3" t="s">
-        <v>4481</v>
+        <v>4476</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>4492</v>
+        <v>4487</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>4482</v>
+        <v>4477</v>
       </c>
       <c r="E245" s="41" t="s">
-        <v>4474</v>
+        <v>4469</v>
       </c>
       <c r="F245" s="41" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/七龍珠激震小隊.html</v>
       </c>
       <c r="G245" s="41" t="s">
-        <v>4473</v>
+        <v>4468</v>
       </c>
       <c r="H245" s="41" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/七龍珠激震小隊.html</v>
       </c>
       <c r="I245" s="42" t="s">
-        <v>4488</v>
+        <v>4483</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>4494</v>
+        <v>4489</v>
       </c>
       <c r="K245" s="2">
         <v>2056</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>4495</v>
+        <v>4490</v>
       </c>
       <c r="M245" s="2">
         <v>1009</v>
       </c>
       <c r="N245" s="1" t="s">
-        <v>4496</v>
+        <v>4491</v>
       </c>
       <c r="O245" s="2">
         <v>519</v>
       </c>
       <c r="P245" s="1" t="s">
-        <v>4497</v>
+        <v>4492</v>
       </c>
       <c r="Q245" s="2">
         <v>178</v>
       </c>
       <c r="R245" s="1" t="s">
-        <v>4498</v>
+        <v>4493</v>
       </c>
       <c r="S245" s="2">
         <v>58</v>
       </c>
       <c r="T245" s="1" t="s">
-        <v>4499</v>
+        <v>4494</v>
       </c>
       <c r="U245" s="2">
         <v>1139</v>
       </c>
       <c r="V245" s="1" t="s">
-        <v>4500</v>
+        <v>4495</v>
       </c>
       <c r="W245" s="2">
         <v>256</v>
@@ -36823,51 +36848,51 @@
     </row>
     <row r="246" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A246" s="72" t="s">
+        <v>4465</v>
+      </c>
+      <c r="C246" s="40" t="s">
+        <v>4488</v>
+      </c>
+      <c r="D246" s="41" t="s">
+        <v>4482</v>
+      </c>
+      <c r="E246" s="4" t="s">
         <v>4470</v>
-      </c>
-      <c r="C246" s="40" t="s">
-        <v>4493</v>
-      </c>
-      <c r="D246" s="41" t="s">
-        <v>4487</v>
-      </c>
-      <c r="E246" s="4" t="s">
-        <v>4475</v>
       </c>
       <c r="F246" s="41" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Grave Strikers.html</v>
       </c>
       <c r="G246" s="41" t="s">
-        <v>4476</v>
+        <v>4471</v>
       </c>
       <c r="H246" s="41" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Grave Strikers.html</v>
       </c>
       <c r="I246" s="42" t="s">
-        <v>4489</v>
+        <v>4484</v>
       </c>
       <c r="J246" s="1" t="s">
-        <v>4516</v>
+        <v>4511</v>
       </c>
       <c r="K246" s="2">
         <v>1139</v>
       </c>
       <c r="L246" s="1" t="s">
-        <v>4517</v>
+        <v>4512</v>
       </c>
       <c r="M246" s="2">
         <v>225</v>
       </c>
       <c r="N246" s="1" t="s">
-        <v>4518</v>
+        <v>4513</v>
       </c>
       <c r="O246" s="2">
         <v>99</v>
       </c>
       <c r="P246" s="1" t="s">
-        <v>4519</v>
+        <v>4514</v>
       </c>
       <c r="Q246" s="2">
         <v>25</v>
@@ -36875,69 +36900,69 @@
     </row>
     <row r="247" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A247" s="72" t="s">
-        <v>4471</v>
+        <v>4466</v>
       </c>
       <c r="C247" s="40" t="s">
-        <v>4486</v>
+        <v>4481</v>
       </c>
       <c r="D247" s="41" t="s">
-        <v>4485</v>
+        <v>4480</v>
       </c>
       <c r="E247" s="41" t="s">
-        <v>4477</v>
+        <v>4472</v>
       </c>
       <c r="F247" s="41" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Stellar Sanctuary.html</v>
       </c>
       <c r="G247" s="41" t="s">
-        <v>4478</v>
+        <v>4473</v>
       </c>
       <c r="H247" s="41" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Stellar Sanctuary.html</v>
       </c>
       <c r="I247" s="42" t="s">
-        <v>4490</v>
+        <v>4485</v>
       </c>
       <c r="J247" s="1" t="s">
-        <v>4515</v>
+        <v>4510</v>
       </c>
       <c r="K247" s="2">
         <v>2623</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>4520</v>
+        <v>4515</v>
       </c>
       <c r="M247" s="2">
         <v>2623</v>
       </c>
       <c r="N247" s="1" t="s">
-        <v>4521</v>
+        <v>4516</v>
       </c>
       <c r="O247" s="2">
         <v>1330</v>
       </c>
       <c r="P247" s="1" t="s">
-        <v>4522</v>
+        <v>4517</v>
       </c>
       <c r="Q247" s="2">
         <v>543</v>
       </c>
       <c r="R247" s="1" t="s">
-        <v>4523</v>
+        <v>4518</v>
       </c>
       <c r="S247" s="2">
         <v>271</v>
       </c>
       <c r="T247" s="1" t="s">
-        <v>4524</v>
+        <v>4519</v>
       </c>
       <c r="U247" s="2">
         <v>149</v>
       </c>
       <c r="V247" s="1" t="s">
-        <v>4525</v>
+        <v>4520</v>
       </c>
       <c r="W247" s="2">
         <v>29</v>
@@ -36945,81 +36970,81 @@
     </row>
     <row r="248" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A248" s="72" t="s">
-        <v>4472</v>
+        <v>4467</v>
       </c>
       <c r="C248" s="40" t="s">
-        <v>4483</v>
+        <v>4478</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>4484</v>
+        <v>4479</v>
       </c>
       <c r="E248" s="41" t="s">
-        <v>4479</v>
+        <v>4474</v>
       </c>
       <c r="F248" s="41" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/古惑仔：風雲再起.html</v>
       </c>
       <c r="G248" s="41" t="s">
-        <v>4480</v>
+        <v>4475</v>
       </c>
       <c r="H248" s="41" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/古惑仔：風雲再起.html</v>
       </c>
       <c r="I248" s="42" t="s">
-        <v>4491</v>
+        <v>4486</v>
       </c>
       <c r="J248" s="1" t="s">
-        <v>4501</v>
+        <v>4496</v>
       </c>
       <c r="K248" s="2">
         <v>2449</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>4502</v>
+        <v>4497</v>
       </c>
       <c r="M248" s="2">
         <v>1911</v>
       </c>
       <c r="N248" s="1" t="s">
-        <v>4503</v>
+        <v>4498</v>
       </c>
       <c r="O248" s="2">
         <v>1529</v>
       </c>
       <c r="P248" s="1" t="s">
-        <v>4504</v>
+        <v>4499</v>
       </c>
       <c r="Q248" s="2">
         <v>1254</v>
       </c>
       <c r="R248" s="1" t="s">
-        <v>4505</v>
+        <v>4500</v>
       </c>
       <c r="S248" s="2">
         <v>757</v>
       </c>
       <c r="T248" s="1" t="s">
-        <v>4506</v>
+        <v>4501</v>
       </c>
       <c r="U248" s="2">
         <v>380</v>
       </c>
       <c r="V248" s="1" t="s">
-        <v>4507</v>
+        <v>4502</v>
       </c>
       <c r="W248" s="2">
         <v>264</v>
       </c>
       <c r="X248" s="1" t="s">
-        <v>4508</v>
+        <v>4503</v>
       </c>
       <c r="Y248" s="2">
         <v>124</v>
       </c>
       <c r="Z248" s="1" t="s">
-        <v>4509</v>
+        <v>4504</v>
       </c>
       <c r="AA248" s="2">
         <v>25</v>
@@ -37027,30 +37052,30 @@
     </row>
     <row r="249" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A249" s="72" t="s">
+        <v>4550</v>
+      </c>
+      <c r="C249" s="40" t="s">
+        <v>4554</v>
+      </c>
+      <c r="D249" s="41" t="s">
+        <v>4553</v>
+      </c>
+      <c r="E249" s="41" t="s">
         <v>4555</v>
-      </c>
-      <c r="C249" s="40" t="s">
-        <v>4559</v>
-      </c>
-      <c r="D249" s="41" t="s">
-        <v>4558</v>
-      </c>
-      <c r="E249" s="41" t="s">
-        <v>4560</v>
       </c>
       <c r="F249" s="41" t="str">
         <f t="shared" ref="F249:F253" si="8">IF(A249="","", "https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/" &amp; IF(ISNUMBER(LEFT(A249,1)*1), "game-", "") &amp; A249 &amp; ".html")</f>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/女神秘令.html</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>4561</v>
+        <v>4556</v>
       </c>
       <c r="H249" s="41" t="str">
         <f t="shared" ref="H249:H253" si="9">IF(A249="","", "https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/" &amp; IF(ISNUMBER(LEFT(A249,1)*1), "game-", "") &amp; A249 &amp; ".html")</f>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/女神秘令.html</v>
       </c>
       <c r="I249" s="42" t="s">
-        <v>4574</v>
+        <v>4569</v>
       </c>
       <c r="J249" s="1" t="s">
         <v>301</v>
@@ -37103,69 +37128,69 @@
     </row>
     <row r="250" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A250" s="72" t="s">
-        <v>4556</v>
+        <v>4551</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>4564</v>
+        <v>4559</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>4565</v>
+        <v>4560</v>
       </c>
       <c r="E250" s="4" t="s">
-        <v>4563</v>
+        <v>4558</v>
       </c>
       <c r="F250" s="41" t="str">
         <f t="shared" si="8"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Torerowa.html</v>
       </c>
       <c r="G250" s="41" t="s">
-        <v>4562</v>
+        <v>4557</v>
       </c>
       <c r="H250" s="41" t="str">
         <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Torerowa.html</v>
       </c>
       <c r="I250" s="42" t="s">
-        <v>4575</v>
+        <v>4570</v>
       </c>
       <c r="J250" s="1" t="s">
-        <v>4585</v>
+        <v>4580</v>
       </c>
       <c r="K250" s="72">
         <v>2293</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>4586</v>
+        <v>4581</v>
       </c>
       <c r="M250" s="72">
         <v>1529</v>
       </c>
       <c r="N250" s="1" t="s">
-        <v>4587</v>
+        <v>4582</v>
       </c>
       <c r="O250" s="72">
         <v>764</v>
       </c>
       <c r="P250" s="1" t="s">
-        <v>4588</v>
+        <v>4583</v>
       </c>
       <c r="Q250" s="72">
         <v>465</v>
       </c>
       <c r="R250" s="1" t="s">
-        <v>4589</v>
+        <v>4584</v>
       </c>
       <c r="S250" s="72">
         <v>165</v>
       </c>
       <c r="T250" s="1" t="s">
-        <v>4590</v>
+        <v>4585</v>
       </c>
       <c r="U250" s="72">
         <v>124</v>
       </c>
       <c r="V250" s="1" t="s">
-        <v>4591</v>
+        <v>4586</v>
       </c>
       <c r="W250" s="72">
         <v>33</v>
@@ -37173,63 +37198,63 @@
     </row>
     <row r="251" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A251" s="72" t="s">
-        <v>4557</v>
+        <v>4552</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>4567</v>
+        <v>4562</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>4569</v>
+        <v>4564</v>
       </c>
       <c r="E251" s="4" t="s">
-        <v>4568</v>
+        <v>4563</v>
       </c>
       <c r="F251" s="41" t="str">
         <f t="shared" si="8"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Ricochet Squad.html</v>
       </c>
       <c r="G251" s="4" t="s">
-        <v>4566</v>
+        <v>4561</v>
       </c>
       <c r="H251" s="41" t="str">
         <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Ricochet Squad.html</v>
       </c>
       <c r="I251" s="42" t="s">
-        <v>4576</v>
+        <v>4571</v>
       </c>
       <c r="J251" s="1" t="s">
-        <v>4592</v>
+        <v>4587</v>
       </c>
       <c r="K251" s="72">
         <v>2286</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>4593</v>
+        <v>4588</v>
       </c>
       <c r="M251" s="72">
         <v>1139</v>
       </c>
       <c r="N251" s="1" t="s">
-        <v>4594</v>
+        <v>4589</v>
       </c>
       <c r="O251" s="72">
         <v>535</v>
       </c>
       <c r="P251" s="1" t="s">
-        <v>4595</v>
+        <v>4590</v>
       </c>
       <c r="Q251" s="72">
         <v>248</v>
       </c>
       <c r="R251" s="1" t="s">
-        <v>4596</v>
+        <v>4591</v>
       </c>
       <c r="S251" s="72">
         <v>124</v>
       </c>
       <c r="T251" s="1" t="s">
-        <v>4597</v>
+        <v>4592</v>
       </c>
       <c r="U251" s="72">
         <v>25</v>
@@ -37237,30 +37262,30 @@
     </row>
     <row r="252" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A252" s="3" t="s">
-        <v>4570</v>
+        <v>4565</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>4573</v>
+        <v>4568</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>4573</v>
+        <v>4568</v>
       </c>
       <c r="E252" s="41" t="s">
-        <v>4571</v>
+        <v>4566</v>
       </c>
       <c r="F252" s="41" t="str">
         <f t="shared" si="8"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/魔法村物語.html</v>
       </c>
       <c r="G252" s="41" t="s">
-        <v>4572</v>
+        <v>4567</v>
       </c>
       <c r="H252" s="41" t="str">
         <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/魔法村物語.html</v>
       </c>
       <c r="I252" s="42" t="s">
-        <v>4577</v>
+        <v>4572</v>
       </c>
       <c r="J252" s="1" t="s">
         <v>12</v>
@@ -37305,19 +37330,19 @@
         <v>25</v>
       </c>
       <c r="X252" s="1" t="s">
-        <v>4604</v>
+        <v>4599</v>
       </c>
       <c r="Y252" s="72">
         <v>535</v>
       </c>
       <c r="Z252" s="1" t="s">
-        <v>4605</v>
+        <v>4600</v>
       </c>
       <c r="AA252" s="72">
         <v>248</v>
       </c>
       <c r="AB252" s="1" t="s">
-        <v>4606</v>
+        <v>4601</v>
       </c>
       <c r="AC252" s="72">
         <v>124</v>
@@ -37325,30 +37350,30 @@
     </row>
     <row r="253" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A253" s="72" t="s">
-        <v>4638</v>
+        <v>4633</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>4642</v>
+        <v>4637</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>4642</v>
+        <v>4637</v>
       </c>
       <c r="E253" s="4" t="s">
-        <v>4641</v>
+        <v>4636</v>
       </c>
       <c r="F253" s="41" t="str">
         <f t="shared" si="8"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/奇蹟MU：騎士袋你飛.html</v>
       </c>
       <c r="G253" s="4" t="s">
-        <v>4640</v>
+        <v>4635</v>
       </c>
       <c r="H253" s="41" t="str">
         <f t="shared" si="9"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/奇蹟MU：騎士袋你飛.html</v>
       </c>
       <c r="I253" s="42" t="s">
-        <v>4666</v>
+        <v>4661</v>
       </c>
       <c r="J253" s="1" t="s">
         <v>145</v>
@@ -37369,7 +37394,7 @@
         <v>496</v>
       </c>
       <c r="P253" s="1" t="s">
-        <v>4668</v>
+        <v>4663</v>
       </c>
       <c r="Q253" s="72">
         <v>198</v>
@@ -37387,31 +37412,31 @@
         <v>21</v>
       </c>
       <c r="V253" s="1" t="s">
-        <v>4669</v>
+        <v>4664</v>
       </c>
       <c r="W253" s="72">
         <v>163</v>
       </c>
       <c r="X253" s="1" t="s">
-        <v>4670</v>
+        <v>4665</v>
       </c>
       <c r="Y253" s="72">
         <v>58</v>
       </c>
       <c r="Z253" s="1" t="s">
-        <v>4671</v>
+        <v>4666</v>
       </c>
       <c r="AA253" s="72">
         <v>58</v>
       </c>
       <c r="AB253" s="1" t="s">
-        <v>4672</v>
+        <v>4667</v>
       </c>
       <c r="AC253" s="72">
         <v>58</v>
       </c>
       <c r="AD253" s="1" t="s">
-        <v>4673</v>
+        <v>4668</v>
       </c>
       <c r="AE253" s="72">
         <v>107</v>
@@ -37419,75 +37444,75 @@
     </row>
     <row r="254" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A254" s="72" t="s">
+        <v>4634</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>4640</v>
+      </c>
+      <c r="D254" s="4" t="s">
+        <v>4640</v>
+      </c>
+      <c r="E254" s="4" t="s">
         <v>4639</v>
-      </c>
-      <c r="C254" s="5" t="s">
-        <v>4645</v>
-      </c>
-      <c r="D254" s="4" t="s">
-        <v>4645</v>
-      </c>
-      <c r="E254" s="4" t="s">
-        <v>4644</v>
       </c>
       <c r="F254" s="41" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/AUR3：影月幻域.html</v>
       </c>
       <c r="G254" s="4" t="s">
-        <v>4643</v>
+        <v>4638</v>
       </c>
       <c r="H254" s="41" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/AUR3：影月幻域.html</v>
       </c>
       <c r="I254" s="42" t="s">
-        <v>4667</v>
+        <v>4662</v>
       </c>
       <c r="J254" s="1" t="s">
-        <v>4674</v>
+        <v>4669</v>
       </c>
       <c r="K254" s="72">
         <v>1139</v>
       </c>
       <c r="L254" s="1" t="s">
-        <v>4675</v>
+        <v>4670</v>
       </c>
       <c r="M254" s="72">
         <v>612</v>
       </c>
       <c r="N254" s="1" t="s">
-        <v>4676</v>
+        <v>4671</v>
       </c>
       <c r="O254" s="72">
         <v>380</v>
       </c>
       <c r="P254" s="1" t="s">
-        <v>4677</v>
+        <v>4672</v>
       </c>
       <c r="Q254" s="72">
         <v>194</v>
       </c>
       <c r="R254" s="1" t="s">
-        <v>4678</v>
+        <v>4673</v>
       </c>
       <c r="S254" s="72">
         <v>74</v>
       </c>
       <c r="T254" s="1" t="s">
-        <v>4679</v>
+        <v>4674</v>
       </c>
       <c r="U254" s="72">
         <v>17</v>
       </c>
       <c r="V254" s="1" t="s">
-        <v>4680</v>
+        <v>4675</v>
       </c>
       <c r="W254" s="72">
         <v>194</v>
       </c>
       <c r="X254" s="1" t="s">
-        <v>4681</v>
+        <v>4676</v>
       </c>
       <c r="Y254" s="72">
         <v>74</v>
@@ -37495,69 +37520,69 @@
     </row>
     <row r="255" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A255" s="3" t="s">
-        <v>4702</v>
+        <v>4697</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>4691</v>
+        <v>4686</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>4692</v>
+        <v>4687</v>
       </c>
       <c r="E255" s="4" t="s">
-        <v>4689</v>
+        <v>4684</v>
       </c>
       <c r="F255" s="41" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/純潔的魔法少女.html</v>
       </c>
       <c r="G255" s="4" t="s">
-        <v>4690</v>
+        <v>4685</v>
       </c>
       <c r="H255" s="41" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/純潔的魔法少女.html</v>
       </c>
       <c r="I255" s="42" t="s">
-        <v>4706</v>
+        <v>4701</v>
       </c>
       <c r="J255" s="1" t="s">
-        <v>4721</v>
+        <v>4716</v>
       </c>
       <c r="K255" s="72">
         <v>2555</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>4722</v>
+        <v>4717</v>
       </c>
       <c r="M255" s="72">
         <v>1331</v>
       </c>
       <c r="N255" s="1" t="s">
-        <v>4723</v>
+        <v>4718</v>
       </c>
       <c r="O255" s="72">
         <v>780</v>
       </c>
       <c r="P255" s="1" t="s">
-        <v>4724</v>
+        <v>4719</v>
       </c>
       <c r="Q255" s="72">
         <v>264</v>
       </c>
       <c r="R255" s="1" t="s">
-        <v>4725</v>
+        <v>4720</v>
       </c>
       <c r="S255" s="72">
         <v>145</v>
       </c>
       <c r="T255" s="1" t="s">
-        <v>4726</v>
+        <v>4721</v>
       </c>
       <c r="U255" s="72">
         <v>28</v>
       </c>
       <c r="V255" s="1" t="s">
-        <v>4727</v>
+        <v>4722</v>
       </c>
       <c r="W255" s="72">
         <v>216</v>
@@ -37565,30 +37590,30 @@
     </row>
     <row r="256" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A256" s="72" t="s">
-        <v>4686</v>
+        <v>4681</v>
       </c>
       <c r="C256" s="5" t="s">
+        <v>4688</v>
+      </c>
+      <c r="D256" s="4" t="s">
         <v>4693</v>
       </c>
-      <c r="D256" s="4" t="s">
-        <v>4698</v>
-      </c>
       <c r="E256" s="4" t="s">
-        <v>4697</v>
+        <v>4692</v>
       </c>
       <c r="F256" s="41" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Next Agers.html</v>
       </c>
       <c r="G256" s="4" t="s">
-        <v>4696</v>
+        <v>4691</v>
       </c>
       <c r="H256" s="41" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Next Agers.html</v>
       </c>
       <c r="I256" s="42" t="s">
-        <v>4707</v>
+        <v>4702</v>
       </c>
       <c r="J256" s="1" t="s">
         <v>4</v>
@@ -37627,7 +37652,7 @@
         <v>30</v>
       </c>
       <c r="V256" s="1" t="s">
-        <v>4728</v>
+        <v>4723</v>
       </c>
       <c r="W256" s="72">
         <v>6095</v>
@@ -37635,51 +37660,51 @@
     </row>
     <row r="257" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A257" s="72" t="s">
-        <v>4687</v>
+        <v>4682</v>
       </c>
       <c r="C257" s="5" t="s">
+        <v>4689</v>
+      </c>
+      <c r="D257" s="4" t="s">
         <v>4694</v>
       </c>
-      <c r="D257" s="4" t="s">
-        <v>4699</v>
-      </c>
       <c r="E257" s="4" t="s">
-        <v>4700</v>
+        <v>4695</v>
       </c>
       <c r="F257" s="41" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/屍不可擋.html</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>4701</v>
+        <v>4696</v>
       </c>
       <c r="H257" s="41" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/屍不可擋.html</v>
       </c>
       <c r="I257" s="42" t="s">
-        <v>4708</v>
+        <v>4703</v>
       </c>
       <c r="J257" s="1" t="s">
-        <v>4729</v>
+        <v>4724</v>
       </c>
       <c r="K257" s="72">
         <v>2355</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>4730</v>
+        <v>4725</v>
       </c>
       <c r="M257" s="72">
         <v>1016</v>
       </c>
       <c r="N257" s="1" t="s">
-        <v>4731</v>
+        <v>4726</v>
       </c>
       <c r="O257" s="72">
         <v>551</v>
       </c>
       <c r="P257" s="1" t="s">
-        <v>4732</v>
+        <v>4727</v>
       </c>
       <c r="Q257" s="72">
         <v>256</v>
@@ -37691,7 +37716,7 @@
         <v>128</v>
       </c>
       <c r="T257" s="1" t="s">
-        <v>4733</v>
+        <v>4728</v>
       </c>
       <c r="U257" s="72">
         <v>26</v>
@@ -37703,7 +37728,7 @@
         <v>1961</v>
       </c>
       <c r="X257" s="1" t="s">
-        <v>4734</v>
+        <v>4729</v>
       </c>
       <c r="Y257" s="72">
         <v>1410</v>
@@ -37723,33 +37748,33 @@
     </row>
     <row r="258" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A258" s="72" t="s">
-        <v>4688</v>
+        <v>4683</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>4695</v>
+        <v>4690</v>
       </c>
       <c r="D258" s="41" t="s">
-        <v>4703</v>
+        <v>4698</v>
       </c>
       <c r="E258" s="4" t="s">
-        <v>4704</v>
+        <v>4699</v>
       </c>
       <c r="F258" s="41" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/RF ONLINE NEXT.html</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>4705</v>
+        <v>4700</v>
       </c>
       <c r="H258" s="41" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/RF ONLINE NEXT.html</v>
       </c>
       <c r="I258" s="42" t="s">
-        <v>4709</v>
+        <v>4704</v>
       </c>
       <c r="J258" s="1" t="s">
-        <v>4759</v>
+        <v>4750</v>
       </c>
       <c r="K258" s="72">
         <v>1725</v>
@@ -37761,13 +37786,13 @@
         <v>937</v>
       </c>
       <c r="N258" s="1" t="s">
-        <v>4760</v>
+        <v>4751</v>
       </c>
       <c r="O258" s="72">
         <v>375</v>
       </c>
       <c r="P258" s="1" t="s">
-        <v>4761</v>
+        <v>4752</v>
       </c>
       <c r="Q258" s="72">
         <v>184</v>
@@ -37779,37 +37804,37 @@
         <v>85</v>
       </c>
       <c r="T258" s="1" t="s">
-        <v>4762</v>
+        <v>4753</v>
       </c>
       <c r="U258" s="72">
         <v>28</v>
       </c>
       <c r="V258" s="1" t="s">
-        <v>4763</v>
+        <v>4754</v>
       </c>
       <c r="W258" s="72">
         <v>583</v>
       </c>
       <c r="X258" s="1" t="s">
-        <v>4764</v>
+        <v>4755</v>
       </c>
       <c r="Y258" s="72">
         <v>145</v>
       </c>
       <c r="Z258" s="1" t="s">
-        <v>4765</v>
+        <v>4756</v>
       </c>
       <c r="AA258" s="72">
         <v>162</v>
       </c>
       <c r="AB258" s="1" t="s">
-        <v>4766</v>
+        <v>4757</v>
       </c>
       <c r="AC258" s="72">
         <v>1725</v>
       </c>
       <c r="AD258" s="1" t="s">
-        <v>4767</v>
+        <v>4758</v>
       </c>
       <c r="AE258" s="72">
         <v>1725</v>
@@ -37817,63 +37842,63 @@
     </row>
     <row r="259" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A259" s="70" t="s">
-        <v>4746</v>
+        <v>4741</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>4745</v>
+        <v>4740</v>
       </c>
       <c r="D259" s="41" t="s">
-        <v>4744</v>
+        <v>4739</v>
       </c>
       <c r="E259" s="41" t="s">
-        <v>4743</v>
+        <v>4738</v>
       </c>
       <c r="F259" s="41" t="str">
         <f t="shared" ref="F259:F267" si="10">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/少女掌門人.html</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>4747</v>
+        <v>4742</v>
       </c>
       <c r="H259" s="41" t="str">
         <f t="shared" ref="H259:H283" si="11">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/少女掌門人.html</v>
       </c>
       <c r="I259" s="42" t="s">
-        <v>4748</v>
+        <v>4743</v>
       </c>
       <c r="J259" s="1" t="s">
-        <v>4735</v>
+        <v>4730</v>
       </c>
       <c r="K259" s="72">
         <v>2048</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>4736</v>
+        <v>4731</v>
       </c>
       <c r="M259" s="72">
         <v>1181</v>
       </c>
       <c r="N259" s="1" t="s">
-        <v>4737</v>
+        <v>4732</v>
       </c>
       <c r="O259" s="72">
         <v>843</v>
       </c>
       <c r="P259" s="1" t="s">
-        <v>4738</v>
+        <v>4733</v>
       </c>
       <c r="Q259" s="72">
         <v>423</v>
       </c>
       <c r="R259" s="1" t="s">
-        <v>4739</v>
+        <v>4734</v>
       </c>
       <c r="S259" s="72">
         <v>216</v>
       </c>
       <c r="T259" s="1" t="s">
-        <v>4740</v>
+        <v>4735</v>
       </c>
       <c r="U259" s="72">
         <v>55</v>
@@ -37885,13 +37910,13 @@
         <v>630</v>
       </c>
       <c r="X259" s="1" t="s">
-        <v>4741</v>
+        <v>4736</v>
       </c>
       <c r="Y259" s="72">
         <v>439</v>
       </c>
       <c r="Z259" s="1" t="s">
-        <v>4742</v>
+        <v>4737</v>
       </c>
       <c r="AA259" s="72">
         <v>630</v>
@@ -37899,63 +37924,63 @@
     </row>
     <row r="260" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A260" s="70" t="s">
-        <v>4791</v>
+        <v>4782</v>
       </c>
       <c r="C260" s="40" t="s">
-        <v>4785</v>
+        <v>4776</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>4790</v>
+        <v>4781</v>
       </c>
       <c r="E260" s="4" t="s">
-        <v>4789</v>
+        <v>4780</v>
       </c>
       <c r="F260" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/翼之櫻：放置決鬥者.html</v>
       </c>
       <c r="G260" s="4" t="s">
-        <v>4787</v>
+        <v>4778</v>
       </c>
       <c r="H260" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/翼之櫻：放置決鬥者.html</v>
       </c>
       <c r="I260" s="42" t="s">
-        <v>4800</v>
+        <v>4791</v>
       </c>
       <c r="J260" s="1" t="s">
-        <v>4768</v>
+        <v>4759</v>
       </c>
       <c r="K260" s="72">
         <v>2355</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>4769</v>
+        <v>4760</v>
       </c>
       <c r="M260" s="72">
         <v>1173</v>
       </c>
       <c r="N260" s="1" t="s">
-        <v>4770</v>
+        <v>4761</v>
       </c>
       <c r="O260" s="72">
         <v>780</v>
       </c>
       <c r="P260" s="1" t="s">
-        <v>4771</v>
+        <v>4762</v>
       </c>
       <c r="Q260" s="72">
         <v>391</v>
       </c>
       <c r="R260" s="1" t="s">
-        <v>4772</v>
+        <v>4763</v>
       </c>
       <c r="S260" s="72">
         <v>128</v>
       </c>
       <c r="T260" s="1" t="s">
-        <v>4773</v>
+        <v>4764</v>
       </c>
       <c r="U260" s="72">
         <v>26</v>
@@ -37967,19 +37992,19 @@
         <v>128</v>
       </c>
       <c r="X260" s="1" t="s">
-        <v>4774</v>
+        <v>4765</v>
       </c>
       <c r="Y260" s="72">
         <v>77</v>
       </c>
       <c r="Z260" s="1" t="s">
-        <v>4775</v>
+        <v>4766</v>
       </c>
       <c r="AA260" s="72">
         <v>176</v>
       </c>
       <c r="AB260" s="1" t="s">
-        <v>4776</v>
+        <v>4767</v>
       </c>
       <c r="AC260" s="72">
         <v>551</v>
@@ -37987,57 +38012,57 @@
     </row>
     <row r="261" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A261" s="72" t="s">
-        <v>4757</v>
+        <v>4748</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>4793</v>
+        <v>4784</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>4794</v>
+        <v>4785</v>
       </c>
       <c r="E261" s="4" t="s">
-        <v>4795</v>
+        <v>4786</v>
       </c>
       <c r="F261" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Oniro ARPG.html</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>4792</v>
+        <v>4783</v>
       </c>
       <c r="H261" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Oniro ARPG.html</v>
       </c>
       <c r="I261" s="42" t="s">
-        <v>4798</v>
+        <v>4789</v>
       </c>
       <c r="J261" s="1" t="s">
-        <v>4777</v>
+        <v>4768</v>
       </c>
       <c r="K261" s="72">
         <v>1961</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>4778</v>
+        <v>4769</v>
       </c>
       <c r="M261" s="72">
         <v>1016</v>
       </c>
       <c r="N261" s="1" t="s">
-        <v>4779</v>
+        <v>4770</v>
       </c>
       <c r="O261" s="72">
         <v>551</v>
       </c>
       <c r="P261" s="1" t="s">
-        <v>4780</v>
+        <v>4771</v>
       </c>
       <c r="Q261" s="72">
         <v>232</v>
       </c>
       <c r="R261" s="1" t="s">
-        <v>4781</v>
+        <v>4772</v>
       </c>
       <c r="S261" s="72">
         <v>102</v>
@@ -38049,13 +38074,13 @@
         <v>26</v>
       </c>
       <c r="V261" s="1" t="s">
-        <v>4782</v>
+        <v>4773</v>
       </c>
       <c r="W261" s="72">
         <v>622</v>
       </c>
       <c r="X261" s="1" t="s">
-        <v>4783</v>
+        <v>4774</v>
       </c>
       <c r="Y261" s="72">
         <v>1173</v>
@@ -38063,30 +38088,30 @@
     </row>
     <row r="262" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A262" s="72" t="s">
-        <v>4758</v>
+        <v>4749</v>
       </c>
       <c r="C262" s="40" t="s">
-        <v>4786</v>
+        <v>4777</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>4797</v>
+        <v>4788</v>
       </c>
       <c r="E262" s="4" t="s">
-        <v>4796</v>
+        <v>4787</v>
       </c>
       <c r="F262" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Legend of YMIR.html</v>
       </c>
       <c r="G262" s="4" t="s">
-        <v>4788</v>
+        <v>4779</v>
       </c>
       <c r="H262" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Legend of YMIR.html</v>
       </c>
       <c r="I262" s="42" t="s">
-        <v>4799</v>
+        <v>4790</v>
       </c>
       <c r="J262" s="1" t="s">
         <v>1268</v>
@@ -38113,7 +38138,7 @@
         <v>256</v>
       </c>
       <c r="R262" s="1" t="s">
-        <v>4784</v>
+        <v>4775</v>
       </c>
       <c r="S262" s="72">
         <v>128</v>
@@ -38127,99 +38152,99 @@
     </row>
     <row r="263" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A263" s="69" t="s">
-        <v>4802</v>
+        <v>4793</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>4801</v>
+        <v>4792</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>4801</v>
+        <v>4792</v>
       </c>
       <c r="E263" s="4" t="s">
-        <v>4803</v>
+        <v>4794</v>
       </c>
       <c r="F263" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Elysia：星空墜落.html</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>4804</v>
+        <v>4795</v>
       </c>
       <c r="H263" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Elysia：星空墜落.html</v>
       </c>
       <c r="I263" s="42" t="s">
-        <v>4805</v>
+        <v>4796</v>
       </c>
       <c r="J263" s="1" t="s">
-        <v>4882</v>
+        <v>4873</v>
       </c>
       <c r="K263" s="72">
         <v>2371</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>4883</v>
+        <v>4874</v>
       </c>
       <c r="M263" s="72">
         <v>1204</v>
       </c>
       <c r="N263" s="1" t="s">
-        <v>4884</v>
+        <v>4875</v>
       </c>
       <c r="O263" s="72">
         <v>563</v>
       </c>
       <c r="P263" s="1" t="s">
-        <v>4885</v>
+        <v>4876</v>
       </c>
       <c r="Q263" s="72">
         <v>261</v>
       </c>
       <c r="R263" s="1" t="s">
-        <v>4886</v>
+        <v>4877</v>
       </c>
       <c r="S263" s="72">
         <v>128</v>
       </c>
       <c r="T263" s="1" t="s">
-        <v>4887</v>
+        <v>4878</v>
       </c>
       <c r="U263" s="72">
         <v>26</v>
       </c>
       <c r="V263" s="1" t="s">
-        <v>4888</v>
+        <v>4879</v>
       </c>
       <c r="W263" s="72">
         <v>400</v>
       </c>
       <c r="X263" s="1" t="s">
-        <v>4889</v>
+        <v>4880</v>
       </c>
       <c r="Y263" s="72">
         <v>128</v>
       </c>
       <c r="Z263" s="1" t="s">
-        <v>4890</v>
+        <v>4881</v>
       </c>
       <c r="AA263" s="72">
         <v>2371</v>
       </c>
       <c r="AB263" s="99" t="s">
-        <v>4891</v>
+        <v>4882</v>
       </c>
       <c r="AC263" s="72">
         <v>1204</v>
       </c>
       <c r="AD263" s="1" t="s">
-        <v>4892</v>
+        <v>4883</v>
       </c>
       <c r="AE263" s="72">
         <v>400</v>
       </c>
       <c r="AF263" s="1" t="s">
-        <v>4893</v>
+        <v>4884</v>
       </c>
       <c r="AG263" s="72">
         <v>26</v>
@@ -38227,67 +38252,67 @@
     </row>
     <row r="264" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A264" s="72" t="s">
-        <v>4831</v>
+        <v>4822</v>
       </c>
       <c r="E264" s="4" t="s">
-        <v>4838</v>
+        <v>4829</v>
       </c>
       <c r="F264" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/合併貓鎮.html</v>
       </c>
       <c r="G264" s="4" t="s">
-        <v>4837</v>
+        <v>4828</v>
       </c>
       <c r="H264" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/合併貓鎮.html</v>
       </c>
       <c r="I264" s="42" t="s">
-        <v>4852</v>
+        <v>4843</v>
       </c>
       <c r="J264" s="47" t="s">
-        <v>4834</v>
+        <v>4825</v>
       </c>
       <c r="K264" s="41" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
     </row>
     <row r="265" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A265" s="72" t="s">
+        <v>4823</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>4830</v>
+      </c>
+      <c r="D265" s="4" t="s">
         <v>4832</v>
       </c>
-      <c r="C265" s="5" t="s">
-        <v>4839</v>
-      </c>
-      <c r="D265" s="4" t="s">
-        <v>4841</v>
-      </c>
       <c r="E265" s="4" t="s">
-        <v>4842</v>
+        <v>4833</v>
       </c>
       <c r="F265" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/幻牌交鋒.html</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>4843</v>
+        <v>4834</v>
       </c>
       <c r="H265" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/幻牌交鋒.html</v>
       </c>
       <c r="I265" t="s">
-        <v>4853</v>
+        <v>4844</v>
       </c>
       <c r="J265" s="1" t="s">
-        <v>4856</v>
+        <v>4847</v>
       </c>
       <c r="K265" s="72">
         <v>2371</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>4857</v>
+        <v>4848</v>
       </c>
       <c r="M265" s="72">
         <v>1204</v>
@@ -38317,7 +38342,7 @@
         <v>26</v>
       </c>
       <c r="V265" s="1" t="s">
-        <v>4894</v>
+        <v>4885</v>
       </c>
       <c r="W265" s="72">
         <v>247</v>
@@ -38329,13 +38354,13 @@
         <v>261</v>
       </c>
       <c r="Z265" s="1" t="s">
-        <v>4859</v>
+        <v>4850</v>
       </c>
       <c r="AA265" s="72">
         <v>162</v>
       </c>
       <c r="AB265" s="1" t="s">
-        <v>4858</v>
+        <v>4849</v>
       </c>
       <c r="AC265" s="72">
         <v>162</v>
@@ -38343,75 +38368,75 @@
     </row>
     <row r="266" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A266" s="3" t="s">
-        <v>4844</v>
+        <v>4835</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>4845</v>
+        <v>4836</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>4848</v>
+        <v>4839</v>
       </c>
       <c r="E266" s="4" t="s">
-        <v>4847</v>
+        <v>4838</v>
       </c>
       <c r="F266" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/激鬥！王國保衛戰.html</v>
       </c>
       <c r="G266" s="4" t="s">
-        <v>4846</v>
+        <v>4837</v>
       </c>
       <c r="H266" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/激鬥！王國保衛戰.html</v>
       </c>
       <c r="I266" s="42" t="s">
-        <v>4854</v>
+        <v>4845</v>
       </c>
       <c r="J266" s="1" t="s">
-        <v>4860</v>
+        <v>4851</v>
       </c>
       <c r="K266" s="72">
         <v>2609</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>4861</v>
+        <v>4852</v>
       </c>
       <c r="M266" s="72">
         <v>1365</v>
       </c>
       <c r="N266" s="1" t="s">
-        <v>4862</v>
+        <v>4853</v>
       </c>
       <c r="O266" s="72">
         <v>807</v>
       </c>
       <c r="P266" s="1" t="s">
-        <v>4863</v>
+        <v>4854</v>
       </c>
       <c r="Q266" s="72">
         <v>546</v>
       </c>
       <c r="R266" s="1" t="s">
-        <v>4864</v>
+        <v>4855</v>
       </c>
       <c r="S266" s="72">
         <v>400</v>
       </c>
       <c r="T266" s="1" t="s">
-        <v>4865</v>
+        <v>4856</v>
       </c>
       <c r="U266" s="72">
         <v>269</v>
       </c>
       <c r="V266" s="1" t="s">
-        <v>4866</v>
+        <v>4857</v>
       </c>
       <c r="W266" s="72">
         <v>145</v>
       </c>
       <c r="X266" s="1" t="s">
-        <v>4867</v>
+        <v>4858</v>
       </c>
       <c r="Y266" s="72">
         <v>29</v>
@@ -38419,87 +38444,87 @@
     </row>
     <row r="267" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A267" s="72" t="s">
-        <v>4833</v>
+        <v>4824</v>
       </c>
       <c r="C267" s="5" t="s">
+        <v>4831</v>
+      </c>
+      <c r="D267" s="41" t="s">
+        <v>4842</v>
+      </c>
+      <c r="E267" s="4" t="s">
         <v>4840</v>
-      </c>
-      <c r="D267" s="41" t="s">
-        <v>4851</v>
-      </c>
-      <c r="E267" s="4" t="s">
-        <v>4849</v>
       </c>
       <c r="F267" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/嘟嘟臉惡作劇.html</v>
       </c>
       <c r="G267" s="41" t="s">
-        <v>4850</v>
+        <v>4841</v>
       </c>
       <c r="H267" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/嘟嘟臉惡作劇.html</v>
       </c>
       <c r="I267" s="42" t="s">
-        <v>4855</v>
+        <v>4846</v>
       </c>
       <c r="J267" s="1" t="s">
-        <v>4943</v>
+        <v>4934</v>
       </c>
       <c r="K267" s="72">
         <v>2371</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>4944</v>
+        <v>4935</v>
       </c>
       <c r="M267" s="72">
         <v>1204</v>
       </c>
       <c r="N267" s="1" t="s">
-        <v>4945</v>
+        <v>4936</v>
       </c>
       <c r="O267" s="72">
         <v>807</v>
       </c>
       <c r="P267" s="1" t="s">
-        <v>4946</v>
+        <v>4937</v>
       </c>
       <c r="Q267" s="72">
         <v>530</v>
       </c>
       <c r="R267" s="1" t="s">
-        <v>4947</v>
+        <v>4938</v>
       </c>
       <c r="S267" s="72">
         <v>294</v>
       </c>
       <c r="T267" s="1" t="s">
-        <v>4948</v>
+        <v>4939</v>
       </c>
       <c r="U267" s="72">
         <v>136</v>
       </c>
       <c r="V267" s="1" t="s">
-        <v>4949</v>
+        <v>4940</v>
       </c>
       <c r="W267" s="72">
         <v>29</v>
       </c>
       <c r="X267" s="1" t="s">
-        <v>4950</v>
+        <v>4941</v>
       </c>
       <c r="Y267" s="72">
         <v>136</v>
       </c>
       <c r="Z267" s="1" t="s">
-        <v>4951</v>
+        <v>4942</v>
       </c>
       <c r="AA267" s="72">
         <v>136</v>
       </c>
       <c r="AB267" s="1" t="s">
-        <v>4952</v>
+        <v>4943</v>
       </c>
       <c r="AC267" s="72">
         <v>196</v>
@@ -38507,33 +38532,33 @@
     </row>
     <row r="268" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A268" s="3" t="s">
-        <v>4920</v>
+        <v>4911</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>4922</v>
+        <v>4913</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>4905</v>
+        <v>4896</v>
       </c>
       <c r="E268" s="4" t="s">
-        <v>4906</v>
+        <v>4897</v>
       </c>
       <c r="F268" s="40" t="str">
         <f t="shared" ref="F268:F312" si="12">IF(A268="", "", "gift-codes.html?game=" &amp; A268)</f>
         <v>gift-codes.html?game=我的花園世界</v>
       </c>
       <c r="G268" s="4" t="s">
-        <v>4921</v>
+        <v>4912</v>
       </c>
       <c r="H268" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/我的花園世界.html</v>
       </c>
       <c r="I268" s="42" t="s">
-        <v>4923</v>
+        <v>4914</v>
       </c>
       <c r="J268" s="1" t="s">
-        <v>4915</v>
+        <v>4906</v>
       </c>
       <c r="K268" s="72">
         <v>2609</v>
@@ -38545,7 +38570,7 @@
         <v>1365</v>
       </c>
       <c r="N268" s="1" t="s">
-        <v>4916</v>
+        <v>4907</v>
       </c>
       <c r="O268" s="72">
         <v>807</v>
@@ -38557,7 +38582,7 @@
         <v>546</v>
       </c>
       <c r="R268" s="1" t="s">
-        <v>4917</v>
+        <v>4908</v>
       </c>
       <c r="S268" s="72">
         <v>400</v>
@@ -38581,13 +38606,13 @@
         <v>29</v>
       </c>
       <c r="Z268" s="1" t="s">
-        <v>4918</v>
+        <v>4909</v>
       </c>
       <c r="AA268" s="72">
         <v>29</v>
       </c>
       <c r="AB268" s="1" t="s">
-        <v>4919</v>
+        <v>4910</v>
       </c>
       <c r="AC268" s="72">
         <v>145</v>
@@ -38595,81 +38620,81 @@
     </row>
     <row r="269" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A269" s="72" t="s">
-        <v>4953</v>
+        <v>4944</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>4958</v>
+        <v>4949</v>
       </c>
       <c r="D269" s="41" t="s">
-        <v>4960</v>
+        <v>4951</v>
       </c>
       <c r="E269" s="41" t="s">
-        <v>4959</v>
+        <v>4950</v>
       </c>
       <c r="F269" s="40" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=Awakenloop</v>
       </c>
       <c r="G269" s="41" t="s">
-        <v>4961</v>
+        <v>4952</v>
       </c>
       <c r="H269" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Awakenloop.html</v>
       </c>
       <c r="I269" s="42" t="s">
-        <v>4977</v>
+        <v>4968</v>
       </c>
       <c r="J269" s="1" t="s">
-        <v>4860</v>
+        <v>4851</v>
       </c>
       <c r="K269" s="72">
         <v>2343</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>4861</v>
+        <v>4852</v>
       </c>
       <c r="M269" s="72">
         <v>1190</v>
       </c>
       <c r="N269" s="1" t="s">
-        <v>4862</v>
+        <v>4853</v>
       </c>
       <c r="O269" s="72">
         <v>798</v>
       </c>
       <c r="P269" s="1" t="s">
-        <v>4863</v>
+        <v>4854</v>
       </c>
       <c r="Q269" s="72">
         <v>540</v>
       </c>
       <c r="R269" s="1" t="s">
-        <v>4864</v>
+        <v>4855</v>
       </c>
       <c r="S269" s="72">
         <v>395</v>
       </c>
       <c r="T269" s="1" t="s">
-        <v>4865</v>
+        <v>4856</v>
       </c>
       <c r="U269" s="72">
         <v>258</v>
       </c>
       <c r="V269" s="1" t="s">
-        <v>4866</v>
+        <v>4857</v>
       </c>
       <c r="W269" s="72">
         <v>126</v>
       </c>
       <c r="X269" s="1" t="s">
-        <v>4995</v>
+        <v>4986</v>
       </c>
       <c r="Y269" s="72">
         <v>52</v>
       </c>
       <c r="Z269" s="1" t="s">
-        <v>4867</v>
+        <v>4858</v>
       </c>
       <c r="AA269" s="72">
         <v>26</v>
@@ -38677,33 +38702,33 @@
     </row>
     <row r="270" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A270" s="72" t="s">
+        <v>4945</v>
+      </c>
+      <c r="C270" s="40" t="s">
+        <v>4956</v>
+      </c>
+      <c r="D270" s="41" t="s">
+        <v>4953</v>
+      </c>
+      <c r="E270" s="41" t="s">
         <v>4954</v>
-      </c>
-      <c r="C270" s="40" t="s">
-        <v>4965</v>
-      </c>
-      <c r="D270" s="41" t="s">
-        <v>4962</v>
-      </c>
-      <c r="E270" s="41" t="s">
-        <v>4963</v>
       </c>
       <c r="F270" s="40" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=Astellia</v>
       </c>
       <c r="G270" s="41" t="s">
-        <v>4964</v>
+        <v>4955</v>
       </c>
       <c r="H270" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Astellia.html</v>
       </c>
       <c r="I270" s="42" t="s">
-        <v>4978</v>
+        <v>4969</v>
       </c>
       <c r="J270" s="1" t="s">
-        <v>4996</v>
+        <v>4987</v>
       </c>
       <c r="K270" s="72">
         <v>2076</v>
@@ -38729,87 +38754,87 @@
     </row>
     <row r="271" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A271" s="72" t="s">
-        <v>4955</v>
+        <v>4946</v>
       </c>
       <c r="C271" s="40" t="s">
-        <v>4975</v>
+        <v>4966</v>
       </c>
       <c r="D271" s="40" t="s">
-        <v>4975</v>
+        <v>4966</v>
       </c>
       <c r="E271" s="41" t="s">
-        <v>4976</v>
+        <v>4967</v>
       </c>
       <c r="F271" s="40" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=華夏千秋</v>
       </c>
       <c r="G271" s="41" t="s">
-        <v>4966</v>
+        <v>4957</v>
       </c>
       <c r="H271" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/華夏千秋.html</v>
       </c>
       <c r="I271" s="42" t="s">
-        <v>4979</v>
+        <v>4970</v>
       </c>
       <c r="J271" s="1" t="s">
-        <v>4997</v>
+        <v>4988</v>
       </c>
       <c r="K271" s="72">
         <v>2579</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>4998</v>
+        <v>4989</v>
       </c>
       <c r="M271" s="72">
         <v>1988</v>
       </c>
       <c r="N271" s="1" t="s">
-        <v>4999</v>
+        <v>4990</v>
       </c>
       <c r="O271" s="72">
         <v>1349</v>
       </c>
       <c r="P271" s="1" t="s">
-        <v>5000</v>
+        <v>4991</v>
       </c>
       <c r="Q271" s="72">
         <v>950</v>
       </c>
       <c r="R271" s="1" t="s">
-        <v>5001</v>
+        <v>4992</v>
       </c>
       <c r="S271" s="72">
         <v>798</v>
       </c>
       <c r="T271" s="1" t="s">
-        <v>5002</v>
+        <v>4993</v>
       </c>
       <c r="U271" s="72">
         <v>749</v>
       </c>
       <c r="V271" s="1" t="s">
-        <v>5003</v>
+        <v>4994</v>
       </c>
       <c r="W271" s="72">
         <v>540</v>
       </c>
       <c r="X271" s="1" t="s">
-        <v>5004</v>
+        <v>4995</v>
       </c>
       <c r="Y271" s="72">
         <v>395</v>
       </c>
       <c r="Z271" s="1" t="s">
-        <v>5005</v>
+        <v>4996</v>
       </c>
       <c r="AA271" s="72">
         <v>346</v>
       </c>
       <c r="AB271" s="1" t="s">
-        <v>5006</v>
+        <v>4997</v>
       </c>
       <c r="AC271" s="72">
         <v>314</v>
@@ -38817,69 +38842,69 @@
     </row>
     <row r="272" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A272" s="72" t="s">
-        <v>4956</v>
+        <v>4947</v>
       </c>
       <c r="C272" s="40" t="s">
-        <v>4967</v>
+        <v>4958</v>
       </c>
       <c r="D272" s="41" t="s">
-        <v>4970</v>
+        <v>4961</v>
       </c>
       <c r="E272" s="41" t="s">
-        <v>4969</v>
+        <v>4960</v>
       </c>
       <c r="F272" s="40" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=萌塔娘</v>
       </c>
       <c r="G272" s="41" t="s">
-        <v>4968</v>
+        <v>4959</v>
       </c>
       <c r="H272" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/萌塔娘.html</v>
       </c>
       <c r="I272" s="42" t="s">
-        <v>4980</v>
+        <v>4971</v>
       </c>
       <c r="J272" s="1" t="s">
-        <v>5007</v>
+        <v>4998</v>
       </c>
       <c r="K272" s="72">
         <v>2579</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>5008</v>
+        <v>4999</v>
       </c>
       <c r="M272" s="72">
         <v>1349</v>
       </c>
       <c r="N272" s="1" t="s">
-        <v>5009</v>
+        <v>5000</v>
       </c>
       <c r="O272" s="72">
         <v>798</v>
       </c>
       <c r="P272" s="1" t="s">
-        <v>5010</v>
+        <v>5001</v>
       </c>
       <c r="Q272" s="72">
         <v>395</v>
       </c>
       <c r="R272" s="1" t="s">
-        <v>5011</v>
+        <v>5002</v>
       </c>
       <c r="S272" s="72">
         <v>266</v>
       </c>
       <c r="T272" s="1" t="s">
-        <v>5012</v>
+        <v>5003</v>
       </c>
       <c r="U272" s="72">
         <v>143</v>
       </c>
       <c r="V272" s="1" t="s">
-        <v>5013</v>
+        <v>5004</v>
       </c>
       <c r="W272" s="72">
         <v>29</v>
@@ -38887,33 +38912,33 @@
     </row>
     <row r="273" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A273" s="72" t="s">
-        <v>4957</v>
+        <v>4948</v>
       </c>
       <c r="C273" s="40" t="s">
-        <v>4971</v>
+        <v>4962</v>
       </c>
       <c r="D273" s="41" t="s">
-        <v>4972</v>
+        <v>4963</v>
       </c>
       <c r="E273" s="41" t="s">
-        <v>4973</v>
+        <v>4964</v>
       </c>
       <c r="F273" s="40" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=盜夢英雄2：幻野</v>
       </c>
       <c r="G273" s="41" t="s">
-        <v>4974</v>
+        <v>4965</v>
       </c>
       <c r="H273" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/盜夢英雄2：幻野.html</v>
       </c>
       <c r="I273" s="42" t="s">
-        <v>4981</v>
+        <v>4972</v>
       </c>
       <c r="J273" s="1" t="s">
-        <v>5014</v>
+        <v>5005</v>
       </c>
       <c r="K273" s="72">
         <v>2579</v>
@@ -38943,7 +38968,7 @@
         <v>798</v>
       </c>
       <c r="T273" s="1" t="s">
-        <v>5015</v>
+        <v>5006</v>
       </c>
       <c r="U273" s="72">
         <v>669</v>
@@ -38961,7 +38986,7 @@
         <v>395</v>
       </c>
       <c r="Z273" s="1" t="s">
-        <v>5016</v>
+        <v>5007</v>
       </c>
       <c r="AA273" s="72">
         <v>314</v>
@@ -38975,57 +39000,57 @@
     </row>
     <row r="274" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A274" s="70" t="s">
-        <v>5034</v>
+        <v>5022</v>
       </c>
       <c r="C274" s="40" t="s">
-        <v>5031</v>
+        <v>5019</v>
       </c>
       <c r="D274" s="41" t="s">
-        <v>5032</v>
+        <v>5020</v>
       </c>
       <c r="E274" s="41" t="s">
-        <v>5033</v>
+        <v>5021</v>
       </c>
       <c r="F274" s="40" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=貪婪洞窟：重生</v>
       </c>
       <c r="G274" s="4" t="s">
-        <v>5035</v>
+        <v>5023</v>
       </c>
       <c r="H274" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/貪婪洞窟：重生.html</v>
       </c>
       <c r="I274" s="42" t="s">
-        <v>5036</v>
+        <v>5024</v>
       </c>
       <c r="J274" s="1" t="s">
-        <v>5037</v>
+        <v>5025</v>
       </c>
       <c r="K274" s="72">
         <v>2343</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>5038</v>
+        <v>5026</v>
       </c>
       <c r="M274" s="72">
         <v>1190</v>
       </c>
       <c r="N274" s="1" t="s">
-        <v>5039</v>
+        <v>5027</v>
       </c>
       <c r="O274" s="72">
         <v>556</v>
       </c>
       <c r="P274" s="1" t="s">
-        <v>5040</v>
+        <v>5028</v>
       </c>
       <c r="Q274" s="72">
         <v>258</v>
       </c>
       <c r="R274" s="1" t="s">
-        <v>5041</v>
+        <v>5029</v>
       </c>
       <c r="S274" s="72">
         <v>126</v>
@@ -39037,25 +39062,25 @@
         <v>26</v>
       </c>
       <c r="V274" s="1" t="s">
-        <v>5042</v>
+        <v>5030</v>
       </c>
       <c r="W274" s="72">
         <v>556</v>
       </c>
       <c r="X274" s="1" t="s">
-        <v>5043</v>
+        <v>5031</v>
       </c>
       <c r="Y274" s="72">
         <v>556</v>
       </c>
       <c r="Z274" s="1" t="s">
-        <v>5044</v>
+        <v>5032</v>
       </c>
       <c r="AA274" s="72">
         <v>1190</v>
       </c>
       <c r="AB274" s="1" t="s">
-        <v>5045</v>
+        <v>5033</v>
       </c>
       <c r="AC274" s="72">
         <v>2343</v>
@@ -50095,7 +50120,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/電鋸果汁大亂鬥.html</v>
       </c>
       <c r="E109" s="14" t="s">
-        <v>4611</v>
+        <v>4606</v>
       </c>
       <c r="F109" s="15" t="s">
         <v>1710</v>
@@ -50663,19 +50688,19 @@
         <v>2366</v>
       </c>
       <c r="S119" s="28" t="s">
-        <v>4612</v>
+        <v>4607</v>
       </c>
       <c r="T119" s="27" t="s">
         <v>2366</v>
       </c>
       <c r="U119" s="28" t="s">
-        <v>4613</v>
+        <v>4608</v>
       </c>
       <c r="V119" s="27" t="s">
         <v>2367</v>
       </c>
       <c r="W119" s="28" t="s">
-        <v>4614</v>
+        <v>4609</v>
       </c>
       <c r="X119" s="27" t="s">
         <v>2366</v>
@@ -51246,6 +51271,27 @@
       <c r="AJ127" s="13" t="s">
         <v>1920</v>
       </c>
+      <c r="AK127" s="18" t="s">
+        <v>5044</v>
+      </c>
+      <c r="AM127" s="18" t="s">
+        <v>5045</v>
+      </c>
+      <c r="AN127" s="13" t="s">
+        <v>5050</v>
+      </c>
+      <c r="AO127" s="18" t="s">
+        <v>5046</v>
+      </c>
+      <c r="AP127" s="13" t="s">
+        <v>5049</v>
+      </c>
+      <c r="AQ127" s="18" t="s">
+        <v>5047</v>
+      </c>
+      <c r="AR127" s="13" t="s">
+        <v>5048</v>
+      </c>
     </row>
     <row r="128" spans="1:50" ht="22.5" customHeight="1">
       <c r="A128" s="25" t="s">
@@ -51712,7 +51758,7 @@
         <v>1840</v>
       </c>
       <c r="K136" s="17" t="s">
-        <v>4615</v>
+        <v>4610</v>
       </c>
       <c r="L136" s="13" t="s">
         <v>3206</v>
@@ -52936,7 +52982,7 @@
         <v>4422</v>
       </c>
       <c r="Y156" s="18" t="s">
-        <v>4825</v>
+        <v>4816</v>
       </c>
     </row>
     <row r="157" spans="1:34" ht="22.5" customHeight="1">
@@ -53725,7 +53771,7 @@
     </row>
     <row r="173" spans="1:38" ht="22.5" customHeight="1">
       <c r="A173" s="91" t="s">
-        <v>4607</v>
+        <v>4602</v>
       </c>
       <c r="C173" s="13" t="str">
         <f t="shared" si="6"/>
@@ -53736,7 +53782,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/奇蹟MU：暴走之翼.html</v>
       </c>
       <c r="E173" s="38" t="s">
-        <v>4608</v>
+        <v>4603</v>
       </c>
       <c r="F173" s="34" t="s">
         <v>2598</v>
@@ -54165,7 +54211,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/超蝦大作戰.html</v>
       </c>
       <c r="E182" s="93" t="s">
-        <v>4609</v>
+        <v>4604</v>
       </c>
       <c r="F182" s="34" t="s">
         <v>3439</v>
@@ -54293,7 +54339,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/三國志Thrones.html</v>
       </c>
       <c r="E184" s="93" t="s">
-        <v>4610</v>
+        <v>4605</v>
       </c>
       <c r="F184" s="34" t="s">
         <v>2624</v>
@@ -54363,31 +54409,31 @@
         <v>3654</v>
       </c>
       <c r="Q185" s="18" t="s">
-        <v>4868</v>
+        <v>4859</v>
       </c>
       <c r="S185" s="18" t="s">
-        <v>4869</v>
+        <v>4860</v>
       </c>
       <c r="U185" s="18" t="s">
-        <v>4870</v>
+        <v>4861</v>
       </c>
       <c r="W185" s="18" t="s">
-        <v>4871</v>
+        <v>4862</v>
       </c>
       <c r="Y185" s="18" t="s">
-        <v>4872</v>
+        <v>4863</v>
       </c>
       <c r="AA185" s="18" t="s">
-        <v>4873</v>
+        <v>4864</v>
       </c>
       <c r="AC185" s="18" t="s">
-        <v>4874</v>
+        <v>4865</v>
       </c>
       <c r="AE185" s="18" t="s">
-        <v>4875</v>
+        <v>4866</v>
       </c>
       <c r="AG185" s="18" t="s">
-        <v>4876</v>
+        <v>4867</v>
       </c>
     </row>
     <row r="186" spans="1:39" ht="22.5" customHeight="1">
@@ -54583,49 +54629,49 @@
         <v>3502</v>
       </c>
       <c r="K190" s="17" t="s">
+        <v>4611</v>
+      </c>
+      <c r="M190" s="18" t="s">
+        <v>4612</v>
+      </c>
+      <c r="O190" s="18" t="s">
+        <v>4613</v>
+      </c>
+      <c r="Q190" s="18" t="s">
+        <v>4614</v>
+      </c>
+      <c r="S190" s="18" t="s">
+        <v>4615</v>
+      </c>
+      <c r="U190" s="18" t="s">
         <v>4616</v>
       </c>
-      <c r="M190" s="18" t="s">
+      <c r="W190" s="18" t="s">
         <v>4617</v>
       </c>
-      <c r="O190" s="18" t="s">
+      <c r="Y190" s="18" t="s">
         <v>4618</v>
       </c>
-      <c r="Q190" s="18" t="s">
+      <c r="AA190" s="18" t="s">
         <v>4619</v>
       </c>
-      <c r="S190" s="18" t="s">
+      <c r="AC190" s="18" t="s">
         <v>4620</v>
       </c>
-      <c r="U190" s="18" t="s">
+      <c r="AE190" s="18" t="s">
         <v>4621</v>
       </c>
-      <c r="W190" s="18" t="s">
-        <v>4622</v>
-      </c>
-      <c r="Y190" s="18" t="s">
-        <v>4623</v>
-      </c>
-      <c r="AA190" s="18" t="s">
-        <v>4624</v>
-      </c>
-      <c r="AC190" s="18" t="s">
-        <v>4625</v>
-      </c>
-      <c r="AE190" s="18" t="s">
-        <v>4626</v>
-      </c>
       <c r="AG190" s="18" t="s">
-        <v>4878</v>
+        <v>4869</v>
       </c>
       <c r="AI190" s="18" t="s">
-        <v>4879</v>
+        <v>4870</v>
       </c>
       <c r="AK190" s="18" t="s">
-        <v>4880</v>
+        <v>4871</v>
       </c>
       <c r="AM190" s="18" t="s">
-        <v>4881</v>
+        <v>4872</v>
       </c>
     </row>
     <row r="191" spans="1:39" ht="22.5" customHeight="1">
@@ -55510,52 +55556,52 @@
         <v>3756</v>
       </c>
       <c r="K206" s="17" t="s">
+        <v>4799</v>
+      </c>
+      <c r="L206" s="13" t="s">
+        <v>4800</v>
+      </c>
+      <c r="M206" s="18" t="s">
+        <v>4801</v>
+      </c>
+      <c r="N206" s="13" t="s">
+        <v>4802</v>
+      </c>
+      <c r="O206" s="18" t="s">
+        <v>4803</v>
+      </c>
+      <c r="P206" s="13" t="s">
+        <v>4804</v>
+      </c>
+      <c r="Q206" s="18" t="s">
+        <v>4805</v>
+      </c>
+      <c r="R206" s="25" t="s">
+        <v>4806</v>
+      </c>
+      <c r="S206" s="18" t="s">
+        <v>4807</v>
+      </c>
+      <c r="T206" s="13" t="s">
         <v>4808</v>
       </c>
-      <c r="L206" s="13" t="s">
+      <c r="U206" s="18" t="s">
         <v>4809</v>
       </c>
-      <c r="M206" s="18" t="s">
+      <c r="V206" s="13" t="s">
         <v>4810</v>
       </c>
-      <c r="N206" s="13" t="s">
+      <c r="W206" s="18" t="s">
         <v>4811</v>
       </c>
-      <c r="O206" s="18" t="s">
-        <v>4812</v>
-      </c>
-      <c r="P206" s="13" t="s">
+      <c r="X206" s="71" t="s">
         <v>4813</v>
       </c>
-      <c r="Q206" s="18" t="s">
+      <c r="Y206" s="18" t="s">
         <v>4814</v>
       </c>
-      <c r="R206" s="25" t="s">
+      <c r="Z206" s="13" t="s">
         <v>4815</v>
-      </c>
-      <c r="S206" s="18" t="s">
-        <v>4816</v>
-      </c>
-      <c r="T206" s="13" t="s">
-        <v>4817</v>
-      </c>
-      <c r="U206" s="18" t="s">
-        <v>4818</v>
-      </c>
-      <c r="V206" s="13" t="s">
-        <v>4819</v>
-      </c>
-      <c r="W206" s="18" t="s">
-        <v>4820</v>
-      </c>
-      <c r="X206" s="71" t="s">
-        <v>4822</v>
-      </c>
-      <c r="Y206" s="18" t="s">
-        <v>4823</v>
-      </c>
-      <c r="Z206" s="13" t="s">
-        <v>4824</v>
       </c>
     </row>
     <row r="207" spans="1:50" ht="22.5" customHeight="1">
@@ -55666,7 +55712,7 @@
         <v>3853</v>
       </c>
       <c r="V208" s="13" t="s">
-        <v>4821</v>
+        <v>4812</v>
       </c>
       <c r="W208" s="18" t="s">
         <v>3854</v>
@@ -56570,7 +56616,7 @@
         <v>4146</v>
       </c>
       <c r="Y224" s="18" t="s">
-        <v>4826</v>
+        <v>4817</v>
       </c>
     </row>
     <row r="225" spans="1:47" ht="22.5" customHeight="1">
@@ -56740,25 +56786,25 @@
         <v>4397</v>
       </c>
       <c r="W227" s="18" t="s">
-        <v>4806</v>
+        <v>4797</v>
       </c>
       <c r="Y227" s="18" t="s">
-        <v>4807</v>
+        <v>4798</v>
       </c>
       <c r="AA227" s="71" t="s">
-        <v>4877</v>
+        <v>4868</v>
       </c>
       <c r="AC227" s="18" t="s">
-        <v>4992</v>
+        <v>4983</v>
       </c>
       <c r="AE227" s="18" t="s">
-        <v>4993</v>
+        <v>4984</v>
       </c>
       <c r="AG227" s="18" t="s">
-        <v>4994</v>
+        <v>4985</v>
       </c>
       <c r="AI227" s="18" t="s">
-        <v>5017</v>
+        <v>5008</v>
       </c>
     </row>
     <row r="228" spans="1:47" ht="22.5" customHeight="1">
@@ -56779,10 +56825,10 @@
         <v>還在為那些看臉抽卡的遊戲心力交瘁？醒醒吧！在《量子機動隊》裡，你將化身為超能指揮官，集結各路英雄，打造一支所向披靡的隊伍，讓那些自以為是的對手嚐嚐什麼叫殘酷的勝利。我們準備了滿滿的兌換碼、禮包碼讓你開局就贏在起跑線，資源拿到手軟。覺得升級太慢太累？別擔心！我們的代儲值服務保證快速安全，讓你用最快的速度打造最強牌組，再也不用擔心牌運不佳，一秒成為牌場上的傳奇，用鈔能力向世界證明你的實力！</v>
       </c>
       <c r="F228" s="34" t="s">
-        <v>4533</v>
+        <v>4528</v>
       </c>
       <c r="G228" s="13" t="s">
-        <v>4534</v>
+        <v>4529</v>
       </c>
       <c r="H228" s="13" t="s">
         <v>2625</v>
@@ -56803,22 +56849,22 @@
         <v>1820</v>
       </c>
       <c r="S228" s="90" t="s">
-        <v>4530</v>
+        <v>4525</v>
       </c>
       <c r="U228" s="90" t="s">
-        <v>4531</v>
+        <v>4526</v>
       </c>
       <c r="W228" s="90" t="s">
-        <v>4532</v>
+        <v>4527</v>
       </c>
       <c r="Y228" s="90" t="s">
         <v>2542</v>
       </c>
       <c r="AA228" s="18" t="s">
-        <v>4753</v>
+        <v>4744</v>
       </c>
       <c r="AC228" s="18" t="s">
-        <v>4754</v>
+        <v>4745</v>
       </c>
     </row>
     <row r="229" spans="1:47" ht="22.5" customHeight="1">
@@ -57209,46 +57255,40 @@
         <v>4464</v>
       </c>
       <c r="K236" s="90" t="s">
-        <v>4465</v>
+        <v>5009</v>
+      </c>
+      <c r="L236" s="13" t="s">
+        <v>5034</v>
       </c>
       <c r="M236" s="90" t="s">
-        <v>4466</v>
+        <v>5035</v>
+      </c>
+      <c r="N236" s="13" t="s">
+        <v>5036</v>
       </c>
       <c r="O236" s="90" t="s">
-        <v>4467</v>
+        <v>5037</v>
+      </c>
+      <c r="P236" s="13" t="s">
+        <v>5038</v>
       </c>
       <c r="Q236" s="90" t="s">
-        <v>4468</v>
+        <v>5039</v>
+      </c>
+      <c r="R236" s="13" t="s">
+        <v>5010</v>
       </c>
       <c r="S236" s="90" t="s">
-        <v>4469</v>
+        <v>5040</v>
+      </c>
+      <c r="T236" s="13" t="s">
+        <v>5041</v>
       </c>
       <c r="U236" s="18" t="s">
-        <v>4749</v>
+        <v>5042</v>
       </c>
       <c r="V236" s="13" t="s">
-        <v>4751</v>
-      </c>
-      <c r="W236" s="18" t="s">
-        <v>4750</v>
-      </c>
-      <c r="X236" s="13" t="s">
-        <v>4752</v>
-      </c>
-      <c r="Y236" s="18" t="s">
-        <v>5018</v>
-      </c>
-      <c r="AA236" s="18" t="s">
-        <v>5019</v>
-      </c>
-      <c r="AB236" s="13" t="s">
-        <v>5022</v>
-      </c>
-      <c r="AC236" s="18" t="s">
-        <v>5020</v>
-      </c>
-      <c r="AD236" s="13" t="s">
-        <v>5021</v>
+        <v>5043</v>
       </c>
     </row>
     <row r="237" spans="1:47" ht="22.5" customHeight="1">
@@ -57284,43 +57324,43 @@
         <v>3331</v>
       </c>
       <c r="M237" s="18" t="s">
+        <v>4533</v>
+      </c>
+      <c r="O237" s="18" t="s">
+        <v>4534</v>
+      </c>
+      <c r="Q237" s="18" t="s">
+        <v>4535</v>
+      </c>
+      <c r="S237" s="13" t="s">
+        <v>4536</v>
+      </c>
+      <c r="U237" s="18" t="s">
+        <v>4537</v>
+      </c>
+      <c r="W237" s="18" t="s">
         <v>4538</v>
       </c>
-      <c r="O237" s="18" t="s">
+      <c r="Y237" s="18" t="s">
         <v>4539</v>
       </c>
-      <c r="Q237" s="18" t="s">
+      <c r="AA237" s="18" t="s">
         <v>4540</v>
       </c>
-      <c r="S237" s="13" t="s">
+      <c r="AC237" s="18" t="s">
         <v>4541</v>
       </c>
-      <c r="U237" s="18" t="s">
+      <c r="AE237" s="18" t="s">
         <v>4542</v>
       </c>
-      <c r="W237" s="18" t="s">
+      <c r="AG237" s="18" t="s">
         <v>4543</v>
       </c>
-      <c r="Y237" s="18" t="s">
+      <c r="AI237" s="18" t="s">
         <v>4544</v>
       </c>
-      <c r="AA237" s="18" t="s">
+      <c r="AK237" s="18" t="s">
         <v>4545</v>
-      </c>
-      <c r="AC237" s="18" t="s">
-        <v>4546</v>
-      </c>
-      <c r="AE237" s="18" t="s">
-        <v>4547</v>
-      </c>
-      <c r="AG237" s="18" t="s">
-        <v>4548</v>
-      </c>
-      <c r="AI237" s="18" t="s">
-        <v>4549</v>
-      </c>
-      <c r="AK237" s="18" t="s">
-        <v>4550</v>
       </c>
     </row>
     <row r="238" spans="1:47" ht="22.5" customHeight="1">
@@ -57353,22 +57393,22 @@
         <v>4368</v>
       </c>
       <c r="K238" s="98" t="s">
-        <v>4551</v>
+        <v>4546</v>
       </c>
       <c r="M238" s="18" t="s">
-        <v>4682</v>
+        <v>4677</v>
       </c>
       <c r="O238" s="18" t="s">
-        <v>4683</v>
+        <v>4678</v>
       </c>
       <c r="Q238" s="18" t="s">
-        <v>4684</v>
+        <v>4679</v>
       </c>
       <c r="S238" s="18" t="s">
-        <v>4685</v>
+        <v>4680</v>
       </c>
       <c r="U238" s="18" t="s">
-        <v>4827</v>
+        <v>4818</v>
       </c>
     </row>
     <row r="239" spans="1:47" ht="22.5" customHeight="1">
@@ -57389,10 +57429,10 @@
         <v>在《三國魂將傳》中，你還在努力招募將領？別傻了，真正的強者都用兌換碼和禮包碼直接領取資源了。我們的代儲值服務，快速又安全，讓你輕鬆超越那些還在慢慢肝的玩家。別再說什麼「肝帝」了，時間寶貴，用我們的方式，把時間省下來享受遊戲，而不是被遊戲玩。想稱霸三國，就從這裡開始。這款遊戲強調策略，但當你擁有無與倫比的資源時，任何策略都將變得簡單。想成為排行榜上的傳奇？這就是你的捷徑。</v>
       </c>
       <c r="F239" s="17" t="s">
-        <v>4553</v>
+        <v>4548</v>
       </c>
       <c r="G239" s="13" t="s">
-        <v>4554</v>
+        <v>4549</v>
       </c>
       <c r="H239" s="13" t="s">
         <v>2625</v>
@@ -57401,7 +57441,7 @@
         <v>4368</v>
       </c>
       <c r="K239" s="90" t="s">
-        <v>4552</v>
+        <v>4547</v>
       </c>
     </row>
     <row r="240" spans="1:47" ht="22.5" customHeight="1">
@@ -57476,10 +57516,10 @@
         <v>2640</v>
       </c>
       <c r="K241" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="L241" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="242" spans="1:27" ht="22.5" customHeight="1">
@@ -57590,16 +57630,16 @@
         <v>終於等到這款由萬代南夢宮娛樂開發的《七龍珠 激震小隊》！這是一款全新的動作 RPG，讓你能體驗原作經典故事，並與悟空、達爾等超人氣角色並肩作戰！遊戲主打爽快又華麗的戰鬥體驗，玩家可以自由組隊，施展各種經典招式，還能享受震撼力十足的「七龍珠」宇宙冒險。遊戲內建多種模式，包括PVP對戰、協力共鬥等，讓你可以和朋友一同挑戰強敵。別忘了關注官方社群，第一時間獲取兌換碼及禮包碼，讓你開局就贏在起跑線！此外，如果你想快速提升戰力，也能透過快速安全的代儲值服務，輕鬆擴大你的英雄陣容！</v>
       </c>
       <c r="F245" s="97" t="s">
-        <v>4537</v>
+        <v>4532</v>
       </c>
       <c r="G245" s="13" t="s">
-        <v>4535</v>
+        <v>4530</v>
       </c>
       <c r="K245" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="L245" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="246" spans="1:27" ht="22.5" customHeight="1">
@@ -57620,16 +57660,16 @@
         <v>《Grave Strikers》是一款視覺風格獨特的戰術 RPG 手遊，玩家將扮演指揮官，組建一支由「靈魂」組成的強力隊伍，在這片被黑暗侵蝕的大陸上展開冒險！遊戲融合了策略布陣與即時戰鬥的元素，每一位靈魂都擁有專屬的技能與故事。透過不斷提升隊伍的實力，解鎖更多新角色，並在充滿挑戰的地下城中證明自己。關注官方社群，不錯過任何兌換碼與禮包碼的發送，讓你的冒險之路更加順暢！想要快速集結更強大的靈魂，代儲值服務是個快速安全的好選擇，讓你輕鬆面對每一個難關！</v>
       </c>
       <c r="F246" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="G246" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
       <c r="K246" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="L246" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="247" spans="1:27" ht="22.5" customHeight="1">
@@ -57650,10 +57690,10 @@
         <v>《Stellar Sanctuary》是一款科幻題材的放置 RPG 手遊，遊戲背景設定在浩瀚的宇宙中，玩家將扮演一名宇宙探險家，招募來自不同星系的英雄，一同對抗邪惡的勢力！遊戲最大的特色就是「輕鬆放置，也能變強」，即使離線也能持續獲得豐富資源，讓你的英雄隊伍不斷成長。此外，遊戲內豐富的英雄養成系統和策略性戰鬥玩法，讓你不僅可以享受掛機的樂趣，也能深入體驗戰術搭配的醍醐味。想快速獲得稀有英雄或裝備嗎？別忘了領取官方發布的兌換碼與禮包碼，或是選擇快速安全的代儲值服務，加速你的宇宙探索旅程！</v>
       </c>
       <c r="F247" s="34" t="s">
-        <v>4527</v>
+        <v>4522</v>
       </c>
       <c r="G247" s="13" t="s">
-        <v>4528</v>
+        <v>4523</v>
       </c>
       <c r="H247" s="13" t="s">
         <v>2625</v>
@@ -57662,10 +57702,10 @@
         <v>4368</v>
       </c>
       <c r="K247" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="L247" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="248" spans="1:27" ht="22.5" customHeight="1">
@@ -57686,7 +57726,7 @@
         <v>經典 IP 手遊《古惑仔：風雲再起》正式登場！遊戲以熱血沸騰的「古惑仔」世界為背景，忠實還原了電影中的經典場景和人物。玩家將能親身扮演陳浩南、山雞等傳奇人物，在銅鑼灣街頭展開一場場江湖廝殺，體驗兄弟情義與權力鬥爭的熱血故事。遊戲主打幫派戰鬥與策略養成，你可以招募小弟、壯大勢力，最終成為一方霸主。為了在江湖中站穩腳跟，別忘了領取官方提供的兌換碼和禮包碼，讓你快速提升戰力！需要更多資源來稱霸一方？快速安全的代儲值服務是你的最佳選擇，讓你輕鬆成為叱吒風雲的傳奇人物！</v>
       </c>
       <c r="F248" s="34" t="s">
-        <v>4529</v>
+        <v>4524</v>
       </c>
       <c r="G248" s="13" t="s">
         <v>4409</v>
@@ -57701,19 +57741,19 @@
         <v>1932</v>
       </c>
       <c r="L248" s="13" t="s">
-        <v>4513</v>
+        <v>4508</v>
       </c>
       <c r="M248" s="18" t="s">
-        <v>4510</v>
+        <v>4505</v>
       </c>
       <c r="N248" s="13" t="s">
-        <v>4514</v>
+        <v>4509</v>
       </c>
       <c r="O248" s="18" t="s">
-        <v>4511</v>
+        <v>4506</v>
       </c>
       <c r="P248" s="13" t="s">
-        <v>4512</v>
+        <v>4507</v>
       </c>
     </row>
     <row r="249" spans="1:27" ht="22.5" customHeight="1">
@@ -57734,16 +57774,16 @@
         <v>《女神秘令》是一款以西方魔幻為題材的卡牌策略 RPG 手遊，遊戲主打輕鬆護肝的放置玩法，讓玩家在忙碌之餘也能輕鬆享受成長樂趣。遊戲內建豐富的女神角色，每位都有獨特的技能與華麗特效，玩家可自由搭配陣容，展開燒腦的策略對決。除了主線劇情外，還有多種副本、公會戰與競技場等多元玩法，搭配豐厚福利與兌換碼，讓新手也能快速上手。想輕鬆蒐集心儀女神、無壓力變強嗎？現在就加入《女神秘令》，透過代儲值服務可享快速安全的優惠，還有專屬禮包碼等你來領取！</v>
       </c>
       <c r="F249" s="90" t="s">
-        <v>4629</v>
+        <v>4624</v>
       </c>
       <c r="G249" s="13" t="s">
-        <v>4630</v>
+        <v>4625</v>
       </c>
       <c r="K249" s="90" t="s">
-        <v>4627</v>
+        <v>4622</v>
       </c>
       <c r="L249" s="90" t="s">
-        <v>4628</v>
+        <v>4623</v>
       </c>
     </row>
     <row r="250" spans="1:27" ht="22.5" customHeight="1">
@@ -57764,19 +57804,19 @@
         <v>《Torerowa》是一款奇幻風格的 MMORPG，以精緻的日系畫風與Q萌角色聞名。玩家將在廣闊的世界中冒險，體驗豐富的任務與劇情。遊戲提供多元職業選擇，每種職業都有獨特的技能樹與玩法，無論是PVE還是PVP，都能找到屬於自己的樂趣。此外，遊戲內還有釣魚、料理、採集等多樣生活技能，讓冒險旅程更加豐富有趣。想要輕鬆遊玩、享受自由探索的樂趣嗎？使用兌換碼與禮包碼即可獲得豐厚資源，選擇快速安全的代儲值服務，讓你輕鬆暢遊這片奇幻大陸！</v>
       </c>
       <c r="F250" s="13" t="s">
-        <v>4631</v>
+        <v>4626</v>
       </c>
       <c r="G250" s="13" t="s">
-        <v>4632</v>
+        <v>4627</v>
       </c>
       <c r="H250" s="13" t="s">
-        <v>4633</v>
+        <v>4628</v>
       </c>
       <c r="K250" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="L250" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="251" spans="1:27" ht="22.5" customHeight="1">
@@ -57797,10 +57837,10 @@
         <v>《Ricochet Squad》是一款結合射擊與彈射玩法的益智休閒手遊。遊戲畫面風格清新可愛，操作簡單易懂，玩家只需透過彈射角色，擊敗地圖上的敵人即可。關卡設計充滿巧思，需要玩家動腦思考，利用地形與彈射角度來完成挑戰。除了單人闖關模式，遊戲也支援多人PVP對戰，與朋友一較高下。遊戲提供多樣角色與造型，滿足玩家蒐集慾望。想在通勤或休息時間，來一場刺激又有趣的腦力激盪嗎？輸入兌換碼與禮包碼即可領取好禮，選擇快速安全的代儲值，讓你輕鬆獲得遊戲內稀有道具！</v>
       </c>
       <c r="F251" s="34" t="s">
-        <v>4583</v>
+        <v>4578</v>
       </c>
       <c r="G251" s="13" t="s">
-        <v>4584</v>
+        <v>4579</v>
       </c>
       <c r="H251" s="13" t="s">
         <v>2625</v>
@@ -57809,10 +57849,10 @@
         <v>4368</v>
       </c>
       <c r="K251" s="17" t="s">
-        <v>4581</v>
+        <v>4576</v>
       </c>
       <c r="L251" s="13" t="s">
-        <v>4582</v>
+        <v>4577</v>
       </c>
     </row>
     <row r="252" spans="1:27" ht="22.5" customHeight="1">
@@ -57833,10 +57873,10 @@
         <v>《魔法村物語》是一款日系像素風格的經營模擬 RPG 手遊。玩家將扮演一位年輕的村長，在充滿魔法的奇幻世界中，經營並發展自己的村莊。遊戲融合了冒險、建設、養成與社交等多元玩法，玩家可以建造各種設施、招募冒險者、探索未知區域，並與其他玩家交流互動。遊戲的像素畫面精美細膩，搭配輕鬆療癒的BGM，帶給玩家獨特的遊玩體驗。想要打造屬於自己的夢幻村莊嗎？記得使用兌換碼與禮包碼來獲得豐厚資源，透過快速安全的代儲值服務，加速你的村莊發展！</v>
       </c>
       <c r="F252" s="34" t="s">
-        <v>4598</v>
+        <v>4593</v>
       </c>
       <c r="G252" s="13" t="s">
-        <v>4599</v>
+        <v>4594</v>
       </c>
       <c r="H252" s="13" t="s">
         <v>2625</v>
@@ -57845,49 +57885,49 @@
         <v>4368</v>
       </c>
       <c r="K252" s="17" t="s">
-        <v>4578</v>
+        <v>4573</v>
       </c>
       <c r="L252" s="13" t="s">
-        <v>4600</v>
+        <v>4595</v>
       </c>
       <c r="M252" s="18" t="s">
-        <v>4579</v>
+        <v>4574</v>
       </c>
       <c r="N252" s="13" t="s">
-        <v>4601</v>
+        <v>4596</v>
       </c>
       <c r="O252" s="18" t="s">
-        <v>4580</v>
+        <v>4575</v>
       </c>
       <c r="P252" s="13" t="s">
-        <v>4602</v>
+        <v>4597</v>
       </c>
       <c r="Q252" s="18" t="s">
         <v>1933</v>
       </c>
       <c r="R252" s="13" t="s">
-        <v>4603</v>
+        <v>4598</v>
       </c>
       <c r="S252" s="18" t="s">
-        <v>4635</v>
+        <v>4630</v>
       </c>
       <c r="T252" s="13" t="s">
-        <v>4636</v>
+        <v>4631</v>
       </c>
       <c r="U252" s="18" t="s">
-        <v>4634</v>
+        <v>4629</v>
       </c>
       <c r="V252" s="13" t="s">
-        <v>4637</v>
+        <v>4632</v>
       </c>
       <c r="W252" s="18" t="s">
-        <v>4756</v>
+        <v>4747</v>
       </c>
       <c r="Y252" s="18" t="s">
-        <v>4755</v>
+        <v>4746</v>
       </c>
       <c r="AA252" s="18" t="s">
-        <v>4828</v>
+        <v>4819</v>
       </c>
     </row>
     <row r="253" spans="1:27" ht="22.5" customHeight="1">
@@ -57908,10 +57948,10 @@
         <v>各位勇者們久等了！由韓國網禪 Webzen 正版授權的《奇蹟MU：騎士袋你飛》帶你重溫感動，再現經典紅龍裝、亞特蘭蒂斯、冰風谷等場景。這款放置系手遊讓你輕鬆掛機、自動練功，上班族也能秒速升級，隨時隨地享受奇蹟世界的樂趣！遊戲內建多元玩法，除了酷炫外觀和獨特技能，還有創新的 AI 系統，讓你體驗超脫傳統的奇蹟新世代。官方提供多組兌換碼及禮包碼，讓勇者們領取豐富虛寶，輕鬆起跑。此外，遊戲支持代儲值服務，提供玩家快速安全的儲值管道，讓你輕鬆擁有神裝，傲視全服！趕快加入，與戰盟夥伴們一起重返奇蹟大陸吧！</v>
       </c>
       <c r="F253" s="34" t="s">
-        <v>4664</v>
+        <v>4659</v>
       </c>
       <c r="G253" s="13" t="s">
-        <v>4665</v>
+        <v>4660</v>
       </c>
       <c r="H253" s="13" t="s">
         <v>2625</v>
@@ -57920,28 +57960,28 @@
         <v>4368</v>
       </c>
       <c r="K253" s="17" t="s">
+        <v>4641</v>
+      </c>
+      <c r="L253" s="13" t="s">
+        <v>4642</v>
+      </c>
+      <c r="M253" s="18" t="s">
+        <v>4643</v>
+      </c>
+      <c r="N253" s="13" t="s">
+        <v>4644</v>
+      </c>
+      <c r="O253" s="18" t="s">
+        <v>4645</v>
+      </c>
+      <c r="P253" s="13" t="s">
         <v>4646</v>
       </c>
-      <c r="L253" s="13" t="s">
-        <v>4647</v>
-      </c>
-      <c r="M253" s="18" t="s">
-        <v>4648</v>
-      </c>
-      <c r="N253" s="13" t="s">
-        <v>4649</v>
-      </c>
-      <c r="O253" s="18" t="s">
-        <v>4650</v>
-      </c>
-      <c r="P253" s="13" t="s">
-        <v>4651</v>
-      </c>
       <c r="Q253" s="18" t="s">
-        <v>4829</v>
+        <v>4820</v>
       </c>
       <c r="R253" s="13" t="s">
-        <v>4830</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="254" spans="1:27" ht="22.5" customHeight="1">
@@ -57962,10 +58002,10 @@
         <v>準備好進入充滿奇幻冒險的異世界了嗎？《AUR3：影月幻域》是一款集結高自由度、精緻畫風與流暢戰鬥的MMORPG手遊。遊戲主打無鎖定戰鬥，結合華麗的技能特效與暢快的打擊感，讓你體驗最極致的戰鬥樂趣。在這片廣闊的幻想大陸上，你可以自由探索、結交夥伴，並與強大的怪物進行史詩級對決。為了回饋廣大玩家，官方準備了多組兌換碼與禮包碼，讓各位冒險者能迅速提升戰力。遊戲內也支援代儲值服務，提供快速安全的儲值通道，讓你在遊戲中無後顧之憂。現在就拿起你的武器，加入《AUR3：影月幻域》，譜寫屬於你的傳奇篇章！</v>
       </c>
       <c r="F254" s="34" t="s">
-        <v>4662</v>
+        <v>4657</v>
       </c>
       <c r="G254" s="13" t="s">
-        <v>4663</v>
+        <v>4658</v>
       </c>
       <c r="H254" s="13" t="s">
         <v>2625</v>
@@ -57974,40 +58014,40 @@
         <v>4368</v>
       </c>
       <c r="K254" s="17" t="s">
+        <v>4647</v>
+      </c>
+      <c r="M254" s="18" t="s">
+        <v>4648</v>
+      </c>
+      <c r="O254" s="18" t="s">
+        <v>4649</v>
+      </c>
+      <c r="Q254" s="18" t="s">
+        <v>4650</v>
+      </c>
+      <c r="S254" s="18" t="s">
+        <v>4651</v>
+      </c>
+      <c r="T254" s="13" t="s">
+        <v>4653</v>
+      </c>
+      <c r="U254" s="18" t="s">
         <v>4652</v>
       </c>
-      <c r="M254" s="18" t="s">
-        <v>4653</v>
-      </c>
-      <c r="O254" s="18" t="s">
+      <c r="V254" s="13" t="s">
         <v>4654</v>
       </c>
-      <c r="Q254" s="18" t="s">
+      <c r="W254" s="18" t="s">
+        <v>4575</v>
+      </c>
+      <c r="X254" s="13" t="s">
         <v>4655</v>
-      </c>
-      <c r="S254" s="18" t="s">
-        <v>4656</v>
-      </c>
-      <c r="T254" s="13" t="s">
-        <v>4658</v>
-      </c>
-      <c r="U254" s="18" t="s">
-        <v>4657</v>
-      </c>
-      <c r="V254" s="13" t="s">
-        <v>4659</v>
-      </c>
-      <c r="W254" s="18" t="s">
-        <v>4580</v>
-      </c>
-      <c r="X254" s="13" t="s">
-        <v>4660</v>
       </c>
       <c r="Y254" s="18" t="s">
         <v>1933</v>
       </c>
       <c r="Z254" s="13" t="s">
-        <v>4661</v>
+        <v>4656</v>
       </c>
     </row>
     <row r="255" spans="1:27" ht="22.5" customHeight="1">
@@ -58028,28 +58068,28 @@
         <v>《純潔的魔法少女》是一款充滿日系動漫風格的冒險 RPG，玩家將化身為魔法少女，與夥伴們一同踏上對抗魔王的旅程。遊戲主打高自由度的策略戰鬥，玩家可自由搭配技能與裝備，打造獨一無二的戰鬥風格。除了熱血的主線劇情，還有豐富的副本挑戰、PVP 對戰與社群互動玩法，讓你與其他魔法少女們一起享受戰鬥的樂趣。遊戲內也特別為玩家準備了各種兌換碼及禮包碼，讓你輕鬆獲得珍貴道具，快速提升戰力。此外，遊戲提供代儲值服務，安全又快速，讓你無後顧之憂地暢玩！</v>
       </c>
       <c r="F255" s="17" t="s">
+        <v>4705</v>
+      </c>
+      <c r="G255" s="13" t="s">
+        <v>4706</v>
+      </c>
+      <c r="K255" s="17" t="s">
+        <v>4707</v>
+      </c>
+      <c r="L255" s="13" t="s">
+        <v>4708</v>
+      </c>
+      <c r="M255" s="18" t="s">
+        <v>4709</v>
+      </c>
+      <c r="N255" s="13" t="s">
+        <v>4711</v>
+      </c>
+      <c r="O255" s="18" t="s">
         <v>4710</v>
       </c>
-      <c r="G255" s="13" t="s">
-        <v>4711</v>
-      </c>
-      <c r="K255" s="17" t="s">
+      <c r="P255" s="13" t="s">
         <v>4712</v>
-      </c>
-      <c r="L255" s="13" t="s">
-        <v>4713</v>
-      </c>
-      <c r="M255" s="18" t="s">
-        <v>4714</v>
-      </c>
-      <c r="N255" s="13" t="s">
-        <v>4716</v>
-      </c>
-      <c r="O255" s="18" t="s">
-        <v>4715</v>
-      </c>
-      <c r="P255" s="13" t="s">
-        <v>4717</v>
       </c>
     </row>
     <row r="256" spans="1:27" ht="22.5" customHeight="1">
@@ -58100,7 +58140,7 @@
         <v>《屍不可擋》是一款爽度破表的末日生存射擊手遊，玩家將身處殭屍橫行的世界，拿起各式槍械掃蕩成群的活屍。遊戲採用俯視角設計，操作簡單直覺，搭配上滿螢幕的殭屍與刺激的射擊音效，帶來前所未有的爽快感。除了殲滅活屍，遊戲也提供了豐富的裝備升級與技能樹系統，讓你能打造出最強的生存者。別忘了定期留意官方釋出的兌換碼與禮包碼，這些都是提升戰力的重要資源。同時，若想快速獲得物資，遊戲也提供代儲值服務，快速安全，讓你專注於生存與戰鬥。</v>
       </c>
       <c r="F257" s="34" t="s">
-        <v>4720</v>
+        <v>4715</v>
       </c>
       <c r="G257" s="13" t="s">
         <v>2625</v>
@@ -58109,10 +58149,10 @@
         <v>4368</v>
       </c>
       <c r="K257" s="17" t="s">
-        <v>4718</v>
+        <v>4713</v>
       </c>
       <c r="L257" s="13" t="s">
-        <v>4719</v>
+        <v>4714</v>
       </c>
     </row>
     <row r="258" spans="1:31" ht="22.5" customHeight="1">
@@ -58133,16 +58173,16 @@
         <v>《RF ONLINE NEXT》是一款 MMORPG 手遊，繼承了經典科幻 IP《RF Online》的世界觀，將三大種族的宏大戰爭重現於手機平台。遊戲以精緻的畫面與流暢的戰鬥，帶給玩家身歷其境的史詩級體驗。玩家可以選擇加入聯盟、貝爾托或克拉，為自己的種族榮耀而戰，並在廣闊的星球上探索未知的區域。遊戲中也為玩家準備了各種兌換碼與禮包碼，協助你快速成長。若想加速角色養成，官方也提供代儲值服務，快速安全，讓你輕鬆成為戰場上的主宰。</v>
       </c>
       <c r="F258" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="G258" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
       <c r="K258" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="L258" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="259" spans="1:31">
@@ -58163,7 +58203,7 @@
         <v>在《少女掌門人》中，您可以體驗直式畫面單手操作的便捷，無論通勤、上學或睡前都能隨時暢玩。遊戲採用全自動戰鬥系統，少女們將會自行施展華麗必殺技與技能擊敗敵人，讓您觀看也能享受爽快戰鬥的視覺盛宴。透過無限可能的戰略組合，打造專屬您的最強戰術，提升門派實力，橫掃魔物！為了讓掌門人能夠快速成長，遊戲內設有豐富的兌換碼與禮包碼福利，提供豐厚資源助您一臂之力。此外，遊戲也支援代儲值服務，確保玩家能以快速安全的方式獲得所需物品，讓您輕鬆培育美少女角色，打造最強隊伍！立即加入，開啟您的掌門人生涯，享受培育少女、稱霸武林的成就感！</v>
       </c>
       <c r="F259" s="34" t="s">
-        <v>4720</v>
+        <v>4715</v>
       </c>
       <c r="G259" s="13" t="s">
         <v>3641</v>
@@ -58175,10 +58215,10 @@
         <v>4368</v>
       </c>
       <c r="K259" s="101" t="s">
-        <v>4903</v>
+        <v>4894</v>
       </c>
       <c r="L259" s="13" t="s">
-        <v>4904</v>
+        <v>4895</v>
       </c>
     </row>
     <row r="260" spans="1:31">
@@ -58200,16 +58240,16 @@
 </v>
       </c>
       <c r="F260" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="G260" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
       <c r="K260" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="L260" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="261" spans="1:31">
@@ -58231,16 +58271,16 @@
 </v>
       </c>
       <c r="F261" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="G261" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
       <c r="K261" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="L261" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="262" spans="1:31">
@@ -58263,16 +58303,16 @@
 </v>
       </c>
       <c r="F262" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="G262" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
       <c r="K262" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="L262" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="263" spans="1:31">
@@ -58293,16 +58333,16 @@
         <v>奇幻RPG大作《Elysia：星空墜落》華麗降臨！你將進入瀕臨毀滅的絕美世界，化身英雄與夥伴共尋希望。遊戲採次世代引擎打造，戰鬥特效華麗、角色模組細膩。除了沉浸式主線，更有豐富副本與策略PVP對戰等你挑戰。為慶祝上市，官方正派送海量福利，務必鎖定最新的兌換碼和禮包碼！想讓戰力快人一步？尋找可靠的代儲值管道，享受快速安全的加值體驗，讓冒險暢行無阻。立即加入《Elysia：星空墜落》，守護這片星空！</v>
       </c>
       <c r="F263" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="G263" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
       <c r="K263" s="17" t="s">
-        <v>4536</v>
+        <v>4531</v>
       </c>
       <c r="L263" s="13" t="s">
-        <v>4526</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="264" spans="1:31">
@@ -58323,16 +58363,16 @@
         <v>《合併貓鎮》是一款可愛風格的合併益智手機遊戲，你將扮演一位貓咪鎮長，透過不斷合併相同物品來解鎖更高級的道具，打造出一個獨一無二的貓咪天堂。遊戲擁有豐富的任務系統和多元的場景設計，讓你在輕鬆療癒的氛圍中享受策略與創造的樂趣。想讓你的貓咪小鎮更加蓬勃發展嗎？別忘了領取兌換碼和禮包碼，迅速獲得豐富資源！若想快速增強實力，也可透過我們提供的代儲值服務，享受快速安全的交易體驗，讓你輕鬆成為貓咪鎮的頂級建築師！準備好與可愛貓咪們一同探索這個充滿驚喜的世界了嗎？</v>
       </c>
       <c r="F264" s="17" t="s">
-        <v>4836</v>
+        <v>4827</v>
       </c>
       <c r="G264" s="13" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
       <c r="K264" s="17" t="s">
-        <v>4836</v>
+        <v>4827</v>
       </c>
       <c r="L264" s="13" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
     </row>
     <row r="265" spans="1:31">
@@ -58353,52 +58393,52 @@
         <v>《幻牌交鋒》是一款集換式卡牌競技手遊，遊戲將帶你進入一個由神秘卡牌主宰的奇幻世界。玩家需要精心組建卡組，運用策略與智慧，與來自各地的玩家進行刺激的即時對戰。每張卡牌都擁有獨特的技能與屬性，考驗你的戰術佈局與臨場反應。想在牌桌上稱霸一方嗎？務必關注官方兌換碼與禮包碼，獲得稀有卡牌與豐富獎勵，讓你贏在起跑點！我們也提供快速安全的代儲值服務，讓你輕鬆獲取心儀的卡牌，迅速打造出最強牌組！</v>
       </c>
       <c r="F265" s="100" t="s">
-        <v>4899</v>
+        <v>4890</v>
       </c>
       <c r="G265" s="13" t="s">
-        <v>4900</v>
+        <v>4891</v>
       </c>
       <c r="H265" s="13" t="s">
-        <v>4901</v>
+        <v>4892</v>
       </c>
       <c r="I265" s="13" t="s">
-        <v>4902</v>
+        <v>4893</v>
       </c>
       <c r="K265" s="17" t="s">
-        <v>4897</v>
+        <v>4888</v>
       </c>
       <c r="L265" s="13" t="s">
-        <v>4898</v>
+        <v>4889</v>
       </c>
       <c r="M265" s="18" t="s">
+        <v>4973</v>
+      </c>
+      <c r="O265" s="18" t="s">
+        <v>4974</v>
+      </c>
+      <c r="Q265" s="18" t="s">
+        <v>4975</v>
+      </c>
+      <c r="S265" s="18" t="s">
+        <v>4976</v>
+      </c>
+      <c r="U265" s="18" t="s">
+        <v>4977</v>
+      </c>
+      <c r="W265" s="18" t="s">
+        <v>4978</v>
+      </c>
+      <c r="Y265" s="18" t="s">
+        <v>4979</v>
+      </c>
+      <c r="AA265" s="18" t="s">
+        <v>4980</v>
+      </c>
+      <c r="AC265" s="18" t="s">
+        <v>4981</v>
+      </c>
+      <c r="AE265" s="18" t="s">
         <v>4982</v>
-      </c>
-      <c r="O265" s="18" t="s">
-        <v>4983</v>
-      </c>
-      <c r="Q265" s="18" t="s">
-        <v>4984</v>
-      </c>
-      <c r="S265" s="18" t="s">
-        <v>4985</v>
-      </c>
-      <c r="U265" s="18" t="s">
-        <v>4986</v>
-      </c>
-      <c r="W265" s="18" t="s">
-        <v>4987</v>
-      </c>
-      <c r="Y265" s="18" t="s">
-        <v>4988</v>
-      </c>
-      <c r="AA265" s="18" t="s">
-        <v>4989</v>
-      </c>
-      <c r="AC265" s="18" t="s">
-        <v>4990</v>
-      </c>
-      <c r="AE265" s="18" t="s">
-        <v>4991</v>
       </c>
     </row>
     <row r="266" spans="1:31">
@@ -58419,16 +58459,16 @@
         <v>《激鬥！王國保衛戰》是一款塔防競技手遊，完美結合了經典塔防玩法與即時對戰元素。你將扮演指揮官，在戰場上部署防禦塔，召喚英雄，與對手鬥智鬥勇，爭奪最終的勝利。遊戲保留了原作豐富的英雄與防禦塔系統，並加入了全新的PVP模式，讓你與全球玩家展開激烈對決。想在戰場上所向披靡嗎？別錯過官方提供的兌換碼和禮包碼，讓你輕鬆獲得資源，強化你的軍隊！若想快速壯大實力，我們也提供快速安全的代儲值服務，讓你無後顧之憂地專注於策略佈局，成為真正的塔防大師！</v>
       </c>
       <c r="F266" s="17" t="s">
-        <v>4836</v>
+        <v>4827</v>
       </c>
       <c r="G266" s="13" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
       <c r="K266" s="17" t="s">
-        <v>4836</v>
+        <v>4827</v>
       </c>
       <c r="L266" s="13" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
     </row>
     <row r="267" spans="1:31">
@@ -58449,67 +58489,67 @@
         <v>《嘟嘟臉惡作劇》是一款充滿日系可愛風格的放置養成遊戲。故事發生在一個充滿魔法的學院，玩家將與一群擁有特殊能力的可愛角色們相遇，一同展開奇妙的冒險。遊戲採用輕鬆的放置玩法，讓你在繁忙之餘也能享受角色養成的樂趣，並透過策略性的戰鬥配置，挑戰各種關卡。想讓你的角色們迅速成長，解鎖更多有趣劇情嗎？記得使用官方兌換碼及禮包碼，獲得大量經驗與珍稀道具！我們也提供代儲值服務，讓您快速安全地獲得所需資源，輕鬆養成最強戰隊，在嘟嘟臉的世界裡盡情惡作劇吧！</v>
       </c>
       <c r="F267" s="17" t="s">
+        <v>4923</v>
+      </c>
+      <c r="G267" s="13" t="s">
+        <v>4924</v>
+      </c>
+      <c r="H267" s="13" t="s">
+        <v>4925</v>
+      </c>
+      <c r="I267" s="13" t="s">
+        <v>4926</v>
+      </c>
+      <c r="J267" s="13" t="s">
+        <v>4927</v>
+      </c>
+      <c r="K267" s="17" t="s">
+        <v>4915</v>
+      </c>
+      <c r="L267" s="13" t="s">
+        <v>4928</v>
+      </c>
+      <c r="M267" s="18" t="s">
+        <v>4916</v>
+      </c>
+      <c r="N267" s="13" t="s">
+        <v>4929</v>
+      </c>
+      <c r="O267" s="18" t="s">
+        <v>4917</v>
+      </c>
+      <c r="P267" s="13" t="s">
+        <v>4930</v>
+      </c>
+      <c r="Q267" s="18" t="s">
+        <v>4918</v>
+      </c>
+      <c r="R267" s="13" t="s">
+        <v>4931</v>
+      </c>
+      <c r="S267" s="18" t="s">
+        <v>4919</v>
+      </c>
+      <c r="T267" s="13" t="s">
         <v>4932</v>
       </c>
-      <c r="G267" s="13" t="s">
+      <c r="U267" s="18" t="s">
+        <v>4920</v>
+      </c>
+      <c r="V267" s="13" t="s">
         <v>4933</v>
       </c>
-      <c r="H267" s="13" t="s">
-        <v>4934</v>
-      </c>
-      <c r="I267" s="13" t="s">
-        <v>4935</v>
-      </c>
-      <c r="J267" s="13" t="s">
-        <v>4936</v>
-      </c>
-      <c r="K267" s="17" t="s">
-        <v>4924</v>
-      </c>
-      <c r="L267" s="13" t="s">
-        <v>4937</v>
-      </c>
-      <c r="M267" s="18" t="s">
-        <v>4925</v>
-      </c>
-      <c r="N267" s="13" t="s">
-        <v>4938</v>
-      </c>
-      <c r="O267" s="18" t="s">
-        <v>4926</v>
-      </c>
-      <c r="P267" s="13" t="s">
-        <v>4939</v>
-      </c>
-      <c r="Q267" s="18" t="s">
-        <v>4927</v>
-      </c>
-      <c r="R267" s="13" t="s">
-        <v>4940</v>
-      </c>
-      <c r="S267" s="18" t="s">
-        <v>4928</v>
-      </c>
-      <c r="T267" s="13" t="s">
-        <v>4941</v>
-      </c>
-      <c r="U267" s="18" t="s">
-        <v>4929</v>
-      </c>
-      <c r="V267" s="13" t="s">
-        <v>4942</v>
-      </c>
       <c r="W267" s="18" t="s">
-        <v>4930</v>
+        <v>4921</v>
       </c>
       <c r="X267" s="13" t="s">
-        <v>4942</v>
+        <v>4933</v>
       </c>
       <c r="Y267" s="18" t="s">
-        <v>4931</v>
+        <v>4922</v>
       </c>
       <c r="Z267" s="13" t="s">
-        <v>4942</v>
+        <v>4933</v>
       </c>
     </row>
     <row r="268" spans="1:31">
@@ -58530,10 +58570,10 @@
         <v>踏入《我的花園世界》，一個充滿奇幻與溫馨的養成冒險，讓你在忙碌的生活中找到一片心靈綠洲！這款手遊將帶你探索魔法大陸，與可愛的花仙子們一同培育珍奇植物，從零開始打造屬於你的夢想莊園。遊戲結合了多元的養成、裝飾與社交玩法，不僅能自由裝扮你的花園，更能拜訪好友，互贈禮物，共創美好回憶。想加速成長？別擔心，豐富的兌換碼和禮包碼讓你輕鬆取得稀有資源，快速提升等級。我們也提供代儲值服務，讓你享受快速安全的交易體驗，輕鬆購入心儀的限定道具。快來加入，與全球玩家一起體驗這場療癒又趣味的園藝之旅吧！</v>
       </c>
       <c r="F268" s="17" t="s">
-        <v>4836</v>
+        <v>4827</v>
       </c>
       <c r="G268" s="13" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
       <c r="H268" s="13" t="s">
         <v>2625</v>
@@ -58542,34 +58582,34 @@
         <v>4368</v>
       </c>
       <c r="K268" s="17" t="s">
-        <v>4895</v>
+        <v>4886</v>
       </c>
       <c r="L268" s="13" t="s">
-        <v>4896</v>
+        <v>4887</v>
       </c>
       <c r="M268" s="18" t="s">
-        <v>4907</v>
+        <v>4898</v>
       </c>
       <c r="N268" s="13" t="s">
-        <v>4911</v>
+        <v>4902</v>
       </c>
       <c r="O268" s="18" t="s">
-        <v>4908</v>
+        <v>4899</v>
       </c>
       <c r="P268" s="13" t="s">
-        <v>4912</v>
+        <v>4903</v>
       </c>
       <c r="Q268" s="18" t="s">
-        <v>4909</v>
+        <v>4900</v>
       </c>
       <c r="R268" s="13" t="s">
-        <v>4913</v>
+        <v>4904</v>
       </c>
       <c r="S268" s="18" t="s">
-        <v>4910</v>
+        <v>4901</v>
       </c>
       <c r="T268" s="13" t="s">
-        <v>4914</v>
+        <v>4905</v>
       </c>
     </row>
     <row r="269" spans="1:31">
@@ -58590,16 +58630,16 @@
         <v>《Awakenloop》是一款充滿賽博龐克風格的卡牌回合制手遊，玩家將身處一個由機器人與人類共存的末日世界。遊戲主打策略性卡牌戰鬥，每張卡牌都蘊含獨特技能，如何搭配與釋放將成為戰局關鍵。除了豐富的主線劇情，遊戲也提供多樣的副本挑戰與 PvP 模式，讓你與其他玩家一較高下。現在就加入《Awakenloop》，透過兌換碼與禮包碼獲得專屬獎勵，輕鬆提升戰力，也能使用代儲值服務快速安全地補充資源，在這片混沌的廢土上開創屬於你的新紀元。</v>
       </c>
       <c r="F269" s="17" t="s">
-        <v>4836</v>
+        <v>4827</v>
       </c>
       <c r="G269" s="13" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
       <c r="K269" s="17" t="s">
-        <v>4836</v>
+        <v>4827</v>
       </c>
       <c r="L269" s="13" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
     </row>
     <row r="270" spans="1:31">
@@ -58620,16 +58660,16 @@
         <v>《Astellia》是一款日系風格的魔幻冒險MMORPG，帶領玩家進入一個充滿魔法與奇幻生物的艾斯提亞大陸。遊戲以其精緻的3D美術畫面與豐富的職業系統著稱，玩家可自由選擇多種職業，並透過養成可愛的「星靈」夥伴來協助戰鬥。遊戲提供多樣化的副本、世界王挑戰與公會系統，讓玩家能與好友一同探索廣闊的世界。使用兌換碼和禮包碼能輕鬆領取稀有道具，快速提升戰力，若需更多遊戲幣與資源，代儲值服務能提供你安全又快速的儲值體驗，讓你在艾斯提亞大陸的旅程更加順暢。</v>
       </c>
       <c r="F270" s="17" t="s">
-        <v>4836</v>
+        <v>4827</v>
       </c>
       <c r="G270" s="13" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
       <c r="K270" s="17" t="s">
-        <v>4836</v>
+        <v>4827</v>
       </c>
       <c r="L270" s="13" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
     </row>
     <row r="271" spans="1:31">
@@ -58650,16 +58690,16 @@
         <v>《華夏千秋》是一款以中國古代神話為背景的MMORPG，遊戲將玩家帶入一個波瀾壯闊的東方玄幻世界。你將化身為修仙者，體驗從凡人到仙神的蛻變歷程。遊戲結合了豐富的劇情故事與自由的戰鬥系統，還有多樣化的社交玩法，讓玩家在修仙的道路上結交同伴，並肩作戰。現在就透過兌換碼和禮包碼領取豐富資源，快速開啟你的修仙之路，若想省時省力，安全的代儲值服務能讓你在短時間內獲得豐厚的回報，輕鬆應對各種挑戰，成就千秋霸業。</v>
       </c>
       <c r="F271" s="17" t="s">
-        <v>4836</v>
+        <v>4827</v>
       </c>
       <c r="G271" s="13" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
       <c r="K271" s="17" t="s">
-        <v>4836</v>
+        <v>4827</v>
       </c>
       <c r="L271" s="13" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
     </row>
     <row r="272" spans="1:31">
@@ -58680,16 +58720,16 @@
         <v>《萌塔娘》是一款結合了塔防與角色養成元素的二次元策略手遊，玩家將在遊戲中與各種「塔娘」並肩作戰，守護家園。遊戲以其可愛的Q版畫風與創新的塔防玩法吸引玩家，每位塔娘都有獨特的技能與屬性，如何配置防禦陣線與策略運用將是勝利的關鍵。遊戲內提供多樣化的養成系統，讓玩家能培養出最強的塔娘戰隊。透過兌換碼與禮包碼可獲得限定獎勵，快速提升戰力，若想迅速強化隊伍，安全的代儲值服務絕對是快速又方便的選擇，讓你輕鬆守護世界的和平。</v>
       </c>
       <c r="F272" s="17" t="s">
-        <v>4836</v>
+        <v>4827</v>
       </c>
       <c r="G272" s="13" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
       <c r="K272" s="17" t="s">
-        <v>4836</v>
+        <v>4827</v>
       </c>
       <c r="L272" s="13" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -58710,16 +58750,16 @@
         <v>《盜夢英雄2：幻野》是一款主打橫向捲軸動作戰鬥的RPG手遊，玩家將進入一個充滿奇幻與冒險的夢境世界。遊戲以爽快的打擊感與華麗的技能特效為核心，玩家可自由組建隊伍，挑戰各種強大的魔物與敵人。豐富的劇情模式與多樣的副本挑戰讓遊戲內容更加充實，無論是PVP還是PVE玩家都能找到樂趣。現在使用兌換碼與禮包碼就能領取專屬禮品，快速提升戰力，若有額外資源需求，代儲值服務提供最快速安全的購買管道，讓你輕鬆在夢境世界中探索，成為最強的夢境英雄。</v>
       </c>
       <c r="F273" s="17" t="s">
-        <v>4836</v>
+        <v>4827</v>
       </c>
       <c r="G273" s="13" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
       <c r="K273" s="17" t="s">
-        <v>4836</v>
+        <v>4827</v>
       </c>
       <c r="L273" s="13" t="s">
-        <v>4835</v>
+        <v>4826</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -58740,10 +58780,10 @@
         <v>貪婪洞窟：重生是一款引人入勝的地牢探險 Roguelike 手遊，作為經典《貪婪洞窟》的全新重製與進化，它邀請所有渴望探索未知與禁忌的勇士，踏上這場智慧與膽識的極限試煉！遊戲保留了原作的核心玩法，並全面升級了裝備、天賦、秘術和道具系統。每一次冒險都充滿不確定性，錯綜複雜的地形、隱秘的符文與潛伏的怪物皆為隨機生成，每次探索都是全新的體驗。玩家可利用環境、天賦與裝備的巧妙結合，在黑暗中謀求一線生機。遊戲內常有兌換碼與禮包碼可供玩家領取，配合快速安全的代儲值服務，讓你的冒險之旅更加順暢。</v>
       </c>
       <c r="F274" s="34" t="s">
-        <v>5023</v>
+        <v>5011</v>
       </c>
       <c r="G274" s="13" t="s">
-        <v>5024</v>
+        <v>5012</v>
       </c>
       <c r="H274" s="13" t="s">
         <v>2625</v>
@@ -58752,22 +58792,22 @@
         <v>4368</v>
       </c>
       <c r="K274" s="17" t="s">
-        <v>5025</v>
+        <v>5013</v>
       </c>
       <c r="L274" s="13" t="s">
-        <v>5026</v>
+        <v>5014</v>
       </c>
       <c r="M274" s="18" t="s">
-        <v>5027</v>
+        <v>5015</v>
       </c>
       <c r="N274" s="13" t="s">
-        <v>5028</v>
+        <v>5016</v>
       </c>
       <c r="O274" s="18" t="s">
-        <v>5029</v>
+        <v>5017</v>
       </c>
       <c r="P274" s="13" t="s">
-        <v>5030</v>
+        <v>5018</v>
       </c>
     </row>
     <row r="275" spans="1:16">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7384" uniqueCount="5051">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7413" uniqueCount="5078">
   <si>
     <t>Facebook</t>
   </si>
@@ -19466,6 +19466,109 @@
   </si>
   <si>
     <t>英雄召喚券 x 5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResQRushOBIsLive</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>行動力*12+鑽石*200+金幣*2000+普通招募令*5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲畫面左上角頭項</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳出方塊右上方選擇設置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點「兌換碼」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>按兌換後到信箱領取免費禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲內點選單</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點進去設定之後選擇兌換碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP6666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP7777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP8888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dream666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dream777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dream8888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>open</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*3000+金幣戰利品(4hr)*1+經驗值戰利品(4hr)*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 點擊「設定」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>「帳號資訊」頁往下滑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/resqrush.tw</t>
+  </si>
+  <si>
+    <t>WDALFA30T</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>補給箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://resqrush.wgame-hk.com/zh</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E5%B0%8F%E5%85%B5%E7%89%B9%E6%94%BB%E9%9A%8A/id6746140478</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.wgame.resqrush</t>
+  </si>
+  <si>
+    <t>小兵特攻隊</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日特價</t>
+  </si>
+  <si>
+    <t>敵軍來襲，指揮官你在哪！快來體驗結合塔防與爽快射擊的《小兵特攻隊》！遊戲主打Q版軍事風格，讓你輕鬆佈陣、火力全開，享受爆擊清場的無盡快感。別再慢慢農資源了，趕快尋找最新的禮包碼和兌換碼，領取海量福利，讓你的軍團戰力一飛沖天！想要快速升級，體驗最頂級的火力配置嗎？選擇最方便的代儲值服務，不僅提供快速安全的交易，更能讓你專注於衝鋒陷陣的樂趣，帶領你的小兵成為戰場傳奇！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -39086,14 +39189,80 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="275" spans="1:29" ht="22.5" customHeight="1">
+    <row r="275" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A275" s="70" t="s">
+        <v>5075</v>
+      </c>
+      <c r="C275" s="40" t="s">
+        <v>5069</v>
+      </c>
+      <c r="D275" s="41" t="s">
+        <v>5072</v>
+      </c>
+      <c r="E275" s="41" t="s">
+        <v>5073</v>
+      </c>
       <c r="F275" s="40" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=小兵特攻隊</v>
+      </c>
+      <c r="G275" s="41" t="s">
+        <v>5074</v>
       </c>
       <c r="H275" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/小兵特攻隊.html</v>
+      </c>
+      <c r="I275" s="42" t="s">
+        <v>5077</v>
+      </c>
+      <c r="J275" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K275" s="72">
+        <v>2302</v>
+      </c>
+      <c r="L275" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M275" s="72">
+        <v>1168</v>
+      </c>
+      <c r="N275" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O275" s="72">
+        <v>783</v>
+      </c>
+      <c r="P275" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q275" s="72">
+        <v>388</v>
+      </c>
+      <c r="R275" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S275" s="72">
+        <v>141</v>
+      </c>
+      <c r="T275" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U275" s="72">
+        <v>28</v>
+      </c>
+      <c r="V275" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="W275" s="72">
+        <v>141</v>
+      </c>
+      <c r="X275" s="1" t="s">
+        <v>5076</v>
+      </c>
+      <c r="Y275" s="72">
+        <v>141</v>
       </c>
     </row>
     <row r="276" spans="1:29" ht="22.5" customHeight="1">
@@ -58570,10 +58739,10 @@
         <v>踏入《我的花園世界》，一個充滿奇幻與溫馨的養成冒險，讓你在忙碌的生活中找到一片心靈綠洲！這款手遊將帶你探索魔法大陸，與可愛的花仙子們一同培育珍奇植物，從零開始打造屬於你的夢想莊園。遊戲結合了多元的養成、裝飾與社交玩法，不僅能自由裝扮你的花園，更能拜訪好友，互贈禮物，共創美好回憶。想加速成長？別擔心，豐富的兌換碼和禮包碼讓你輕鬆取得稀有資源，快速提升等級。我們也提供代儲值服務，讓你享受快速安全的交易體驗，輕鬆購入心儀的限定道具。快來加入，與全球玩家一起體驗這場療癒又趣味的園藝之旅吧！</v>
       </c>
       <c r="F268" s="17" t="s">
-        <v>4827</v>
+        <v>5057</v>
       </c>
       <c r="G268" s="13" t="s">
-        <v>4826</v>
+        <v>5058</v>
       </c>
       <c r="H268" s="13" t="s">
         <v>2625</v>
@@ -58720,19 +58889,19 @@
         <v>《萌塔娘》是一款結合了塔防與角色養成元素的二次元策略手遊，玩家將在遊戲中與各種「塔娘」並肩作戰，守護家園。遊戲以其可愛的Q版畫風與創新的塔防玩法吸引玩家，每位塔娘都有獨特的技能與屬性，如何配置防禦陣線與策略運用將是勝利的關鍵。遊戲內提供多樣化的養成系統，讓玩家能培養出最強的塔娘戰隊。透過兌換碼與禮包碼可獲得限定獎勵，快速提升戰力，若想迅速強化隊伍，安全的代儲值服務絕對是快速又方便的選擇，讓你輕鬆守護世界的和平。</v>
       </c>
       <c r="F272" s="17" t="s">
-        <v>4827</v>
+        <v>5067</v>
       </c>
       <c r="G272" s="13" t="s">
         <v>4826</v>
       </c>
       <c r="K272" s="17" t="s">
-        <v>4827</v>
+        <v>5065</v>
       </c>
       <c r="L272" s="13" t="s">
-        <v>4826</v>
-      </c>
-    </row>
-    <row r="273" spans="1:16">
+        <v>5066</v>
+      </c>
+    </row>
+    <row r="273" spans="1:21">
       <c r="A273" s="13" t="str">
         <f>IF(games!A273="", "", games!A273)</f>
         <v>盜夢英雄2：幻野</v>
@@ -58753,16 +58922,34 @@
         <v>4827</v>
       </c>
       <c r="G273" s="13" t="s">
-        <v>4826</v>
+        <v>5068</v>
+      </c>
+      <c r="H273" s="13" t="s">
+        <v>2625</v>
+      </c>
+      <c r="I273" s="13" t="s">
+        <v>4368</v>
       </c>
       <c r="K273" s="17" t="s">
-        <v>4827</v>
-      </c>
-      <c r="L273" s="13" t="s">
-        <v>4826</v>
-      </c>
-    </row>
-    <row r="274" spans="1:16">
+        <v>5059</v>
+      </c>
+      <c r="M273" s="18" t="s">
+        <v>5060</v>
+      </c>
+      <c r="O273" s="18" t="s">
+        <v>5061</v>
+      </c>
+      <c r="Q273" s="18" t="s">
+        <v>5062</v>
+      </c>
+      <c r="S273" s="18" t="s">
+        <v>5063</v>
+      </c>
+      <c r="U273" s="18" t="s">
+        <v>5064</v>
+      </c>
+    </row>
+    <row r="274" spans="1:21">
       <c r="A274" s="13" t="str">
         <f>IF(games!A274="", "", games!A274)</f>
         <v>貪婪洞窟：重生</v>
@@ -58810,25 +58997,52 @@
         <v>5018</v>
       </c>
     </row>
-    <row r="275" spans="1:16">
+    <row r="275" spans="1:21">
       <c r="A275" s="13" t="str">
         <f>IF(games!A275="", "", games!A275)</f>
-        <v/>
+        <v>小兵特攻隊</v>
       </c>
       <c r="C275" s="13" t="str">
         <f>IF(A275="","", "giftcodesbanner/" &amp; A275 &amp; "-禮包碼.jpg")</f>
-        <v/>
+        <v>giftcodesbanner/小兵特攻隊-禮包碼.jpg</v>
       </c>
       <c r="D275" s="13" t="str">
         <f>IF(A275="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A275)</f>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=小兵特攻隊</v>
       </c>
       <c r="E275" s="14" t="str">
         <f>IF(games!I275&lt;&gt;"", games!I275, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="276" spans="1:16">
+        <v>敵軍來襲，指揮官你在哪！快來體驗結合塔防與爽快射擊的《小兵特攻隊》！遊戲主打Q版軍事風格，讓你輕鬆佈陣、火力全開，享受爆擊清場的無盡快感。別再慢慢農資源了，趕快尋找最新的禮包碼和兌換碼，領取海量福利，讓你的軍團戰力一飛沖天！想要快速升級，體驗最頂級的火力配置嗎？選擇最方便的代儲值服務，不僅提供快速安全的交易，更能讓你專注於衝鋒陷陣的樂趣，帶領你的小兵成為戰場傳奇！</v>
+      </c>
+      <c r="F275" s="34" t="s">
+        <v>5053</v>
+      </c>
+      <c r="G275" s="13" t="s">
+        <v>5054</v>
+      </c>
+      <c r="H275" s="13" t="s">
+        <v>5055</v>
+      </c>
+      <c r="I275" s="13" t="s">
+        <v>2625</v>
+      </c>
+      <c r="J275" s="13" t="s">
+        <v>5056</v>
+      </c>
+      <c r="K275" s="18" t="s">
+        <v>5051</v>
+      </c>
+      <c r="L275" s="13" t="s">
+        <v>5052</v>
+      </c>
+      <c r="M275" s="18" t="s">
+        <v>5070</v>
+      </c>
+      <c r="N275" s="13" t="s">
+        <v>5071</v>
+      </c>
+    </row>
+    <row r="276" spans="1:21">
       <c r="A276" s="13" t="str">
         <f>IF(games!A276="", "", games!A276)</f>
         <v/>
@@ -58846,7 +59060,7 @@
         <v/>
       </c>
     </row>
-    <row r="277" spans="1:16">
+    <row r="277" spans="1:21">
       <c r="A277" s="13" t="str">
         <f>IF(games!A277="", "", games!A277)</f>
         <v/>
@@ -58864,7 +59078,7 @@
         <v/>
       </c>
     </row>
-    <row r="278" spans="1:16">
+    <row r="278" spans="1:21">
       <c r="A278" s="13" t="str">
         <f>IF(games!A278="", "", games!A278)</f>
         <v/>
@@ -58882,7 +59096,7 @@
         <v/>
       </c>
     </row>
-    <row r="279" spans="1:16">
+    <row r="279" spans="1:21">
       <c r="A279" s="13" t="str">
         <f>IF(games!A279="", "", games!A279)</f>
         <v/>
@@ -58900,7 +59114,7 @@
         <v/>
       </c>
     </row>
-    <row r="280" spans="1:16">
+    <row r="280" spans="1:21">
       <c r="A280" s="13" t="str">
         <f>IF(games!A280="", "", games!A280)</f>
         <v/>
@@ -58918,7 +59132,7 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="1:16">
+    <row r="281" spans="1:21">
       <c r="A281" s="13" t="str">
         <f>IF(games!A281="", "", games!A281)</f>
         <v/>
@@ -58936,7 +59150,7 @@
         <v/>
       </c>
     </row>
-    <row r="282" spans="1:16">
+    <row r="282" spans="1:21">
       <c r="A282" s="13" t="str">
         <f>IF(games!A282="", "", games!A282)</f>
         <v/>
@@ -58954,7 +59168,7 @@
         <v/>
       </c>
     </row>
-    <row r="283" spans="1:16">
+    <row r="283" spans="1:21">
       <c r="A283" s="13" t="str">
         <f>IF(games!A283="", "", games!A283)</f>
         <v/>
@@ -58972,7 +59186,7 @@
         <v/>
       </c>
     </row>
-    <row r="284" spans="1:16">
+    <row r="284" spans="1:21">
       <c r="A284" s="13" t="str">
         <f>IF(games!A284="", "", games!A284)</f>
         <v/>
@@ -58990,7 +59204,7 @@
         <v/>
       </c>
     </row>
-    <row r="285" spans="1:16">
+    <row r="285" spans="1:21">
       <c r="A285" s="13" t="str">
         <f>IF(games!A285="", "", games!A285)</f>
         <v/>
@@ -59008,7 +59222,7 @@
         <v/>
       </c>
     </row>
-    <row r="286" spans="1:16">
+    <row r="286" spans="1:21">
       <c r="A286" s="13" t="str">
         <f>IF(games!A286="", "", games!A286)</f>
         <v/>
@@ -59026,7 +59240,7 @@
         <v/>
       </c>
     </row>
-    <row r="287" spans="1:16">
+    <row r="287" spans="1:21">
       <c r="A287" s="13" t="str">
         <f>IF(games!A287="", "", games!A287)</f>
         <v/>
@@ -59044,7 +59258,7 @@
         <v/>
       </c>
     </row>
-    <row r="288" spans="1:16">
+    <row r="288" spans="1:21">
       <c r="A288" s="13" t="str">
         <f>IF(games!A288="", "", games!A288)</f>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7413" uniqueCount="5078">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7418" uniqueCount="5084">
   <si>
     <t>Facebook</t>
   </si>
@@ -19537,10 +19537,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>「帳號資訊」頁往下滑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.facebook.com/resqrush.tw</t>
   </si>
   <si>
@@ -19569,6 +19565,34 @@
   </si>
   <si>
     <t>敵軍來襲，指揮官你在哪！快來體驗結合塔防與爽快射擊的《小兵特攻隊》！遊戲主打Q版軍事風格，讓你輕鬆佈陣、火力全開，享受爆擊清場的無盡快感。別再慢慢農資源了，趕快尋找最新的禮包碼和兌換碼，領取海量福利，讓你的軍團戰力一飛沖天！想要快速升級，體驗最頂級的火力配置嗎？選擇最方便的代儲值服務，不僅提供快速安全的交易，更能讓你專注於衝鋒陷陣的樂趣，帶領你的小兵成為戰場傳奇！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*300+金幣*20256+定軌的石之輪*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*300+金幣*18888+定軌的石之輪*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點左上角頭像再點中間兌換碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*200+金幣*18888+定軌的石之輪*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*588+金幣*20256+定軌的石之輪*1+許願的石之輪*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*588+金幣*18888+定軌的石之輪*1+許願的石之輪*1+經驗卷軸*2000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*688+金幣*1888+許願的石之輪*4+經驗卷軸*1000</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -39191,30 +39215,30 @@
     </row>
     <row r="275" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A275" s="70" t="s">
-        <v>5075</v>
+        <v>5074</v>
       </c>
       <c r="C275" s="40" t="s">
-        <v>5069</v>
+        <v>5068</v>
       </c>
       <c r="D275" s="41" t="s">
+        <v>5071</v>
+      </c>
+      <c r="E275" s="41" t="s">
         <v>5072</v>
-      </c>
-      <c r="E275" s="41" t="s">
-        <v>5073</v>
       </c>
       <c r="F275" s="40" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=小兵特攻隊</v>
       </c>
       <c r="G275" s="41" t="s">
-        <v>5074</v>
+        <v>5073</v>
       </c>
       <c r="H275" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/小兵特攻隊.html</v>
       </c>
       <c r="I275" s="42" t="s">
-        <v>5077</v>
+        <v>5076</v>
       </c>
       <c r="J275" s="1" t="s">
         <v>12</v>
@@ -39259,7 +39283,7 @@
         <v>141</v>
       </c>
       <c r="X275" s="1" t="s">
-        <v>5076</v>
+        <v>5075</v>
       </c>
       <c r="Y275" s="72">
         <v>141</v>
@@ -58901,7 +58925,7 @@
         <v>5066</v>
       </c>
     </row>
-    <row r="273" spans="1:21">
+    <row r="273" spans="1:22">
       <c r="A273" s="13" t="str">
         <f>IF(games!A273="", "", games!A273)</f>
         <v>盜夢英雄2：幻野</v>
@@ -58918,38 +58942,53 @@
         <f>IF(games!I273&lt;&gt;"", games!I273, "")</f>
         <v>《盜夢英雄2：幻野》是一款主打橫向捲軸動作戰鬥的RPG手遊，玩家將進入一個充滿奇幻與冒險的夢境世界。遊戲以爽快的打擊感與華麗的技能特效為核心，玩家可自由組建隊伍，挑戰各種強大的魔物與敵人。豐富的劇情模式與多樣的副本挑戰讓遊戲內容更加充實，無論是PVP還是PVE玩家都能找到樂趣。現在使用兌換碼與禮包碼就能領取專屬禮品，快速提升戰力，若有額外資源需求，代儲值服務提供最快速安全的購買管道，讓你輕鬆在夢境世界中探索，成為最強的夢境英雄。</v>
       </c>
-      <c r="F273" s="17" t="s">
-        <v>4827</v>
+      <c r="F273" s="13" t="s">
+        <v>5079</v>
       </c>
       <c r="G273" s="13" t="s">
-        <v>5068</v>
+        <v>2625</v>
       </c>
       <c r="H273" s="13" t="s">
-        <v>2625</v>
-      </c>
-      <c r="I273" s="13" t="s">
         <v>4368</v>
       </c>
       <c r="K273" s="17" t="s">
         <v>5059</v>
       </c>
+      <c r="L273" s="13" t="s">
+        <v>5077</v>
+      </c>
       <c r="M273" s="18" t="s">
         <v>5060</v>
       </c>
+      <c r="N273" s="13" t="s">
+        <v>5078</v>
+      </c>
       <c r="O273" s="18" t="s">
         <v>5061</v>
       </c>
+      <c r="P273" s="13" t="s">
+        <v>5080</v>
+      </c>
       <c r="Q273" s="18" t="s">
         <v>5062</v>
       </c>
+      <c r="R273" s="13" t="s">
+        <v>5081</v>
+      </c>
       <c r="S273" s="18" t="s">
         <v>5063</v>
       </c>
+      <c r="T273" s="13" t="s">
+        <v>5082</v>
+      </c>
       <c r="U273" s="18" t="s">
         <v>5064</v>
       </c>
-    </row>
-    <row r="274" spans="1:21">
+      <c r="V273" s="13" t="s">
+        <v>5083</v>
+      </c>
+    </row>
+    <row r="274" spans="1:22">
       <c r="A274" s="13" t="str">
         <f>IF(games!A274="", "", games!A274)</f>
         <v>貪婪洞窟：重生</v>
@@ -58997,7 +59036,7 @@
         <v>5018</v>
       </c>
     </row>
-    <row r="275" spans="1:21">
+    <row r="275" spans="1:22">
       <c r="A275" s="13" t="str">
         <f>IF(games!A275="", "", games!A275)</f>
         <v>小兵特攻隊</v>
@@ -59036,13 +59075,13 @@
         <v>5052</v>
       </c>
       <c r="M275" s="18" t="s">
+        <v>5069</v>
+      </c>
+      <c r="N275" s="13" t="s">
         <v>5070</v>
       </c>
-      <c r="N275" s="13" t="s">
-        <v>5071</v>
-      </c>
-    </row>
-    <row r="276" spans="1:21">
+    </row>
+    <row r="276" spans="1:22">
       <c r="A276" s="13" t="str">
         <f>IF(games!A276="", "", games!A276)</f>
         <v/>
@@ -59060,7 +59099,7 @@
         <v/>
       </c>
     </row>
-    <row r="277" spans="1:21">
+    <row r="277" spans="1:22">
       <c r="A277" s="13" t="str">
         <f>IF(games!A277="", "", games!A277)</f>
         <v/>
@@ -59078,7 +59117,7 @@
         <v/>
       </c>
     </row>
-    <row r="278" spans="1:21">
+    <row r="278" spans="1:22">
       <c r="A278" s="13" t="str">
         <f>IF(games!A278="", "", games!A278)</f>
         <v/>
@@ -59096,7 +59135,7 @@
         <v/>
       </c>
     </row>
-    <row r="279" spans="1:21">
+    <row r="279" spans="1:22">
       <c r="A279" s="13" t="str">
         <f>IF(games!A279="", "", games!A279)</f>
         <v/>
@@ -59114,7 +59153,7 @@
         <v/>
       </c>
     </row>
-    <row r="280" spans="1:21">
+    <row r="280" spans="1:22">
       <c r="A280" s="13" t="str">
         <f>IF(games!A280="", "", games!A280)</f>
         <v/>
@@ -59132,7 +59171,7 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="1:21">
+    <row r="281" spans="1:22">
       <c r="A281" s="13" t="str">
         <f>IF(games!A281="", "", games!A281)</f>
         <v/>
@@ -59150,7 +59189,7 @@
         <v/>
       </c>
     </row>
-    <row r="282" spans="1:21">
+    <row r="282" spans="1:22">
       <c r="A282" s="13" t="str">
         <f>IF(games!A282="", "", games!A282)</f>
         <v/>
@@ -59168,7 +59207,7 @@
         <v/>
       </c>
     </row>
-    <row r="283" spans="1:21">
+    <row r="283" spans="1:22">
       <c r="A283" s="13" t="str">
         <f>IF(games!A283="", "", games!A283)</f>
         <v/>
@@ -59186,7 +59225,7 @@
         <v/>
       </c>
     </row>
-    <row r="284" spans="1:21">
+    <row r="284" spans="1:22">
       <c r="A284" s="13" t="str">
         <f>IF(games!A284="", "", games!A284)</f>
         <v/>
@@ -59204,7 +59243,7 @@
         <v/>
       </c>
     </row>
-    <row r="285" spans="1:21">
+    <row r="285" spans="1:22">
       <c r="A285" s="13" t="str">
         <f>IF(games!A285="", "", games!A285)</f>
         <v/>
@@ -59222,7 +59261,7 @@
         <v/>
       </c>
     </row>
-    <row r="286" spans="1:21">
+    <row r="286" spans="1:22">
       <c r="A286" s="13" t="str">
         <f>IF(games!A286="", "", games!A286)</f>
         <v/>
@@ -59240,7 +59279,7 @@
         <v/>
       </c>
     </row>
-    <row r="287" spans="1:21">
+    <row r="287" spans="1:22">
       <c r="A287" s="13" t="str">
         <f>IF(games!A287="", "", games!A287)</f>
         <v/>
@@ -59258,7 +59297,7 @@
         <v/>
       </c>
     </row>
-    <row r="288" spans="1:21">
+    <row r="288" spans="1:22">
       <c r="A288" s="13" t="str">
         <f>IF(games!A288="", "", games!A288)</f>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7418" uniqueCount="5084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7420" uniqueCount="5085">
   <si>
     <t>Facebook</t>
   </si>
@@ -19593,6 +19593,10 @@
   </si>
   <si>
     <t>鑽石*688+金幣*1888+許願的石之輪*4+經驗卷軸*1000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>「帳號資訊」頁往下滑</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -58916,7 +58920,13 @@
         <v>5067</v>
       </c>
       <c r="G272" s="13" t="s">
-        <v>4826</v>
+        <v>5084</v>
+      </c>
+      <c r="H272" s="13" t="s">
+        <v>2625</v>
+      </c>
+      <c r="I272" s="13" t="s">
+        <v>4368</v>
       </c>
       <c r="K272" s="17" t="s">
         <v>5065</v>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7420" uniqueCount="5085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7495" uniqueCount="5131">
   <si>
     <t>Facebook</t>
   </si>
@@ -18054,6 +18054,9 @@
     <t>RF ONLINE NEXT</t>
   </si>
   <si>
+    <t>卡厄斯夢境</t>
+  </si>
+  <si>
     <t>https://apps.apple.com/tw/app/id6747162052</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -19598,6 +19601,148 @@
   <si>
     <t>「帳號資訊」頁往下滑</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>星塔旅人</t>
+  </si>
+  <si>
+    <t>星痕共鳴</t>
+  </si>
+  <si>
+    <t>二重螺旋</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/StellaSoraCHT</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/DNAbyss.TC</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/starresonancetw</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ChaosZeroNightmareZHH</t>
+  </si>
+  <si>
+    <t>https://chaoszeronightmare.onstove.com/zh-tw?fbclid=IwY2xjawNhe6FleHRuA2FlbQIxMABicmlkETFXN0NoVk9TY0pVVEQxUk5BAR53HJhmNuib5YSSGm5y3R203Ph0dx4iqthHEQRSpmRJROqsUl3dFrJj1-Yltw_aem_545CZ6bYOLN7EgQTvyBq1w</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.smilegate.chaoszero.stove.google</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E5%8D%A1%E5%8E%84%E6%80%9D%E5%A4%A2%E5%A2%83/id6502326151</t>
+  </si>
+  <si>
+    <t>https://bpsr.haoplay.com/?fbclid=IwY2xjawNhe6hleHRuA2FlbQIxMABicmlkETFXN0NoVk9TY0pVVEQxUk5BAR7csOTUZyiX7uskjP2xNuJlPF32OqfJxod2cZbqajffS79iDmZeFJNItkpZMw_aem_CXuldrv2jz4asLGL9N3J7w</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=tw.haoplay.game.gp.xhgm</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E6%98%9F%E7%97%95%E5%85%B1%E9%B3%B4/id6737753806</t>
+  </si>
+  <si>
+    <t>https://duetnightabyss.dna-panstudio.com/zh-tw/?fbclid=IwY2xjawNhe61leHRuA2FlbQIxMABicmlkETFXN0NoVk9TY0pVVEQxUk5BAR44Fk6CPqivHJe-4JFdOii-Ya8SpQWT-setp6hu_u5OYvlq1xWPht6lt0lB3Q_aem_JjCaZGQgYe6Mnr9oTfOr1Q#/home</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.panstudio.gplay.duetnightabyss.arpg.global</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E4%BA%8C%E9%87%8D%E8%9E%BA%E6%97%8B/id6744096826</t>
+  </si>
+  <si>
+    <t>https://stellasora.stargazer-games.com/?fbclid=IwY2xjawNhe7JleHRuA2FlbQIxMABicmlkETFXN0NoVk9TY0pVVEQxUk5BAR4u1JuJdUdGOnOOFpfNjXkTLcAa1lNcztFIdw8KBcoRitLohvB7baHo4U3ycw_aem_R83k2ssF-5xsskQTVhSVvQ</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E6%98%9F%E5%A1%94%E6%97%85%E4%BA%BA/id6738902933</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.Stargazer.StellaSora</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>由艾瑞爾網路代理的銀河冒險 RPG《星塔旅人》正式登場！這趟星際之旅，你將化身為「星之活體」的持有者，與眾多獨具魅力的「旅人」相遇，共同踏上尋找銀河之心「星源晶核」的冒險。遊戲主打 Roguelike 要素與高自由度的戰鬥系統，讓每一次探索都充滿未知驚喜。為了讓各位玩家能更快養成心儀的角色，記得隨時關注官方釋出的最新兌換碼與禮包碼資訊。當然，若想在起跑點就遙遙領先，最方便的代儲值服務能提供您快速安全的課金管道，讓您的銀河霸業無後顧之憂！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Smilegate 最新力作，收集型 2D 回合制 RPG《卡厄斯夢境》來襲！遊戲以其精緻的 Live 2D 動態角色與深刻的世界觀，帶領玩家進入一場善惡界線模糊的奇幻冒險。在這個瀕臨毀滅的世界中，你將與各具特色的英雄們並肩作戰，對抗侵蝕一切的「噩夢」。遊戲策略性極高，考驗玩家的隊伍配置與戰術運用。想讓你的英雄們戰力飆升？別忘了尋找最新的兌換碼與禮包碼福利。若想更有效率地培養隊伍，選擇專業的代儲值服務，享受快速安全的交易，讓你在夢境中暢行無阻。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>全新星緣卡牌 RPG《星痕共鳴》，邀你一同編織命運的篇章。遊戲擁有宏大的世界觀與超過百萬字的豐富劇情，玩家將扮演「星源之主」，與眾多「星痕者」締結羈絆，共同對抗虛空的威脅。獨特的「星盤」系統與高策略性的卡牌戰鬥，讓每場對決都充滿變數。想要輕鬆推圖、快速成長？記得在各大社群與論壇尋找隱藏的兌換碼與禮包碼，領取豐厚資源。如果想快人一步，最聰明的選擇就是尋找可靠的代儲值管道，提供您快速安全的支援，讓你的冒險旅程更加順遂。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>備受矚目的 3D 動作 RPG《二重螺旋》強勢來襲！本作主打高速、爽快的戰鬥體驗，玩家將在一個近未來科幻世界中，扮演擁有特殊能力的「適格者」，探索神秘的「深淵」。遊戲強調華麗的連擊與多樣化的武器系統，你可以自由切換遠近程攻擊，打出屬於自己的戰鬥風格。為了讓你的探索之路更加順利，官方會不定期發放福利兌換碼與禮包碼，千萬別錯過。當然，面對強大的敵人，尋求專業的代儲值協助，以快速安全的方式強化戰力，絕對是高效的致勝關鍵。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲內右上角齒輪「設定」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>左邊第五個選項登陸優惠碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6480寶石</t>
+  </si>
+  <si>
+    <t>3280寶石</t>
+  </si>
+  <si>
+    <t>980寶石</t>
+  </si>
+  <si>
+    <t>680寶石</t>
+  </si>
+  <si>
+    <t>賽季豪華通行證</t>
+  </si>
+  <si>
+    <t>賽季普通通行證</t>
+  </si>
+  <si>
+    <t>6480月石晶胚</t>
+  </si>
+  <si>
+    <t>3280月石晶胚</t>
+  </si>
+  <si>
+    <t>1980月石晶胚</t>
+  </si>
+  <si>
+    <t>980月石晶胚</t>
+  </si>
+  <si>
+    <t>680月石晶胚</t>
+  </si>
+  <si>
+    <t>300月石晶胚</t>
+  </si>
+  <si>
+    <t>60月石晶胚</t>
+  </si>
+  <si>
+    <t>精裝詩集</t>
+  </si>
+  <si>
+    <t>待到日暖雪融限定禮包</t>
+  </si>
+  <si>
+    <t>補貼升級</t>
+  </si>
+  <si>
+    <t>每月青空禮券套裝</t>
+  </si>
+  <si>
+    <t>每月燦金閃碟套裝</t>
+  </si>
+  <si>
+    <t>啟程限定燦金閃碟套裝</t>
+  </si>
+  <si>
+    <t>開業大吉燦金閃碟套裝</t>
   </si>
 </sst>
 </file>
@@ -37651,69 +37796,69 @@
     </row>
     <row r="255" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A255" s="3" t="s">
-        <v>4697</v>
+        <v>4698</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>4686</v>
+        <v>4687</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>4687</v>
+        <v>4688</v>
       </c>
       <c r="E255" s="4" t="s">
-        <v>4684</v>
+        <v>4685</v>
       </c>
       <c r="F255" s="41" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/純潔的魔法少女.html</v>
       </c>
       <c r="G255" s="4" t="s">
-        <v>4685</v>
+        <v>4686</v>
       </c>
       <c r="H255" s="41" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/純潔的魔法少女.html</v>
       </c>
       <c r="I255" s="42" t="s">
-        <v>4701</v>
+        <v>4702</v>
       </c>
       <c r="J255" s="1" t="s">
-        <v>4716</v>
+        <v>4717</v>
       </c>
       <c r="K255" s="72">
         <v>2555</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>4717</v>
+        <v>4718</v>
       </c>
       <c r="M255" s="72">
         <v>1331</v>
       </c>
       <c r="N255" s="1" t="s">
-        <v>4718</v>
+        <v>4719</v>
       </c>
       <c r="O255" s="72">
         <v>780</v>
       </c>
       <c r="P255" s="1" t="s">
-        <v>4719</v>
+        <v>4720</v>
       </c>
       <c r="Q255" s="72">
         <v>264</v>
       </c>
       <c r="R255" s="1" t="s">
-        <v>4720</v>
+        <v>4721</v>
       </c>
       <c r="S255" s="72">
         <v>145</v>
       </c>
       <c r="T255" s="1" t="s">
-        <v>4721</v>
+        <v>4722</v>
       </c>
       <c r="U255" s="72">
         <v>28</v>
       </c>
       <c r="V255" s="1" t="s">
-        <v>4722</v>
+        <v>4723</v>
       </c>
       <c r="W255" s="72">
         <v>216</v>
@@ -37724,27 +37869,27 @@
         <v>4681</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>4688</v>
+        <v>4689</v>
       </c>
       <c r="D256" s="4" t="s">
+        <v>4694</v>
+      </c>
+      <c r="E256" s="4" t="s">
         <v>4693</v>
-      </c>
-      <c r="E256" s="4" t="s">
-        <v>4692</v>
       </c>
       <c r="F256" s="41" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Next Agers.html</v>
       </c>
       <c r="G256" s="4" t="s">
-        <v>4691</v>
+        <v>4692</v>
       </c>
       <c r="H256" s="41" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Next Agers.html</v>
       </c>
       <c r="I256" s="42" t="s">
-        <v>4702</v>
+        <v>4703</v>
       </c>
       <c r="J256" s="1" t="s">
         <v>4</v>
@@ -37783,7 +37928,7 @@
         <v>30</v>
       </c>
       <c r="V256" s="1" t="s">
-        <v>4723</v>
+        <v>4724</v>
       </c>
       <c r="W256" s="72">
         <v>6095</v>
@@ -37794,48 +37939,48 @@
         <v>4682</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>4689</v>
+        <v>4690</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>4694</v>
+        <v>4695</v>
       </c>
       <c r="E257" s="4" t="s">
-        <v>4695</v>
+        <v>4696</v>
       </c>
       <c r="F257" s="41" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/屍不可擋.html</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>4696</v>
+        <v>4697</v>
       </c>
       <c r="H257" s="41" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/屍不可擋.html</v>
       </c>
       <c r="I257" s="42" t="s">
-        <v>4703</v>
+        <v>4704</v>
       </c>
       <c r="J257" s="1" t="s">
-        <v>4724</v>
+        <v>4725</v>
       </c>
       <c r="K257" s="72">
         <v>2355</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>4725</v>
+        <v>4726</v>
       </c>
       <c r="M257" s="72">
         <v>1016</v>
       </c>
       <c r="N257" s="1" t="s">
-        <v>4726</v>
+        <v>4727</v>
       </c>
       <c r="O257" s="72">
         <v>551</v>
       </c>
       <c r="P257" s="1" t="s">
-        <v>4727</v>
+        <v>4728</v>
       </c>
       <c r="Q257" s="72">
         <v>256</v>
@@ -37847,7 +37992,7 @@
         <v>128</v>
       </c>
       <c r="T257" s="1" t="s">
-        <v>4728</v>
+        <v>4729</v>
       </c>
       <c r="U257" s="72">
         <v>26</v>
@@ -37859,7 +38004,7 @@
         <v>1961</v>
       </c>
       <c r="X257" s="1" t="s">
-        <v>4729</v>
+        <v>4730</v>
       </c>
       <c r="Y257" s="72">
         <v>1410</v>
@@ -37882,30 +38027,30 @@
         <v>4683</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>4690</v>
+        <v>4691</v>
       </c>
       <c r="D258" s="41" t="s">
-        <v>4698</v>
+        <v>4699</v>
       </c>
       <c r="E258" s="4" t="s">
-        <v>4699</v>
+        <v>4700</v>
       </c>
       <c r="F258" s="41" t="str">
         <f t="shared" si="6"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/RF ONLINE NEXT.html</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>4700</v>
+        <v>4701</v>
       </c>
       <c r="H258" s="41" t="str">
         <f t="shared" si="7"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/RF ONLINE NEXT.html</v>
       </c>
       <c r="I258" s="42" t="s">
-        <v>4704</v>
+        <v>4705</v>
       </c>
       <c r="J258" s="1" t="s">
-        <v>4750</v>
+        <v>4751</v>
       </c>
       <c r="K258" s="72">
         <v>1725</v>
@@ -37917,13 +38062,13 @@
         <v>937</v>
       </c>
       <c r="N258" s="1" t="s">
-        <v>4751</v>
+        <v>4752</v>
       </c>
       <c r="O258" s="72">
         <v>375</v>
       </c>
       <c r="P258" s="1" t="s">
-        <v>4752</v>
+        <v>4753</v>
       </c>
       <c r="Q258" s="72">
         <v>184</v>
@@ -37935,37 +38080,37 @@
         <v>85</v>
       </c>
       <c r="T258" s="1" t="s">
-        <v>4753</v>
+        <v>4754</v>
       </c>
       <c r="U258" s="72">
         <v>28</v>
       </c>
       <c r="V258" s="1" t="s">
-        <v>4754</v>
+        <v>4755</v>
       </c>
       <c r="W258" s="72">
         <v>583</v>
       </c>
       <c r="X258" s="1" t="s">
-        <v>4755</v>
+        <v>4756</v>
       </c>
       <c r="Y258" s="72">
         <v>145</v>
       </c>
       <c r="Z258" s="1" t="s">
-        <v>4756</v>
+        <v>4757</v>
       </c>
       <c r="AA258" s="72">
         <v>162</v>
       </c>
       <c r="AB258" s="1" t="s">
-        <v>4757</v>
+        <v>4758</v>
       </c>
       <c r="AC258" s="72">
         <v>1725</v>
       </c>
       <c r="AD258" s="1" t="s">
-        <v>4758</v>
+        <v>4759</v>
       </c>
       <c r="AE258" s="72">
         <v>1725</v>
@@ -37973,63 +38118,63 @@
     </row>
     <row r="259" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A259" s="70" t="s">
+        <v>4742</v>
+      </c>
+      <c r="C259" s="5" t="s">
         <v>4741</v>
       </c>
-      <c r="C259" s="5" t="s">
+      <c r="D259" s="41" t="s">
         <v>4740</v>
       </c>
-      <c r="D259" s="41" t="s">
+      <c r="E259" s="41" t="s">
         <v>4739</v>
-      </c>
-      <c r="E259" s="41" t="s">
-        <v>4738</v>
       </c>
       <c r="F259" s="41" t="str">
         <f t="shared" ref="F259:F267" si="10">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/少女掌門人.html</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>4742</v>
+        <v>4743</v>
       </c>
       <c r="H259" s="41" t="str">
         <f t="shared" ref="H259:H283" si="11">IF(A259="","", "https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/" &amp; IF(ISNUMBER(LEFT(A259,1)*1), "game-", "") &amp; A259 &amp; ".html")</f>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/少女掌門人.html</v>
       </c>
       <c r="I259" s="42" t="s">
-        <v>4743</v>
+        <v>4744</v>
       </c>
       <c r="J259" s="1" t="s">
-        <v>4730</v>
+        <v>4731</v>
       </c>
       <c r="K259" s="72">
         <v>2048</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>4731</v>
+        <v>4732</v>
       </c>
       <c r="M259" s="72">
         <v>1181</v>
       </c>
       <c r="N259" s="1" t="s">
-        <v>4732</v>
+        <v>4733</v>
       </c>
       <c r="O259" s="72">
         <v>843</v>
       </c>
       <c r="P259" s="1" t="s">
-        <v>4733</v>
+        <v>4734</v>
       </c>
       <c r="Q259" s="72">
         <v>423</v>
       </c>
       <c r="R259" s="1" t="s">
-        <v>4734</v>
+        <v>4735</v>
       </c>
       <c r="S259" s="72">
         <v>216</v>
       </c>
       <c r="T259" s="1" t="s">
-        <v>4735</v>
+        <v>4736</v>
       </c>
       <c r="U259" s="72">
         <v>55</v>
@@ -38041,13 +38186,13 @@
         <v>630</v>
       </c>
       <c r="X259" s="1" t="s">
-        <v>4736</v>
+        <v>4737</v>
       </c>
       <c r="Y259" s="72">
         <v>439</v>
       </c>
       <c r="Z259" s="1" t="s">
-        <v>4737</v>
+        <v>4738</v>
       </c>
       <c r="AA259" s="72">
         <v>630</v>
@@ -38055,63 +38200,63 @@
     </row>
     <row r="260" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A260" s="70" t="s">
+        <v>4783</v>
+      </c>
+      <c r="C260" s="40" t="s">
+        <v>4777</v>
+      </c>
+      <c r="D260" s="5" t="s">
         <v>4782</v>
       </c>
-      <c r="C260" s="40" t="s">
-        <v>4776</v>
-      </c>
-      <c r="D260" s="5" t="s">
+      <c r="E260" s="4" t="s">
         <v>4781</v>
-      </c>
-      <c r="E260" s="4" t="s">
-        <v>4780</v>
       </c>
       <c r="F260" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/翼之櫻：放置決鬥者.html</v>
       </c>
       <c r="G260" s="4" t="s">
-        <v>4778</v>
+        <v>4779</v>
       </c>
       <c r="H260" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/翼之櫻：放置決鬥者.html</v>
       </c>
       <c r="I260" s="42" t="s">
-        <v>4791</v>
+        <v>4792</v>
       </c>
       <c r="J260" s="1" t="s">
-        <v>4759</v>
+        <v>4760</v>
       </c>
       <c r="K260" s="72">
         <v>2355</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>4760</v>
+        <v>4761</v>
       </c>
       <c r="M260" s="72">
         <v>1173</v>
       </c>
       <c r="N260" s="1" t="s">
-        <v>4761</v>
+        <v>4762</v>
       </c>
       <c r="O260" s="72">
         <v>780</v>
       </c>
       <c r="P260" s="1" t="s">
-        <v>4762</v>
+        <v>4763</v>
       </c>
       <c r="Q260" s="72">
         <v>391</v>
       </c>
       <c r="R260" s="1" t="s">
-        <v>4763</v>
+        <v>4764</v>
       </c>
       <c r="S260" s="72">
         <v>128</v>
       </c>
       <c r="T260" s="1" t="s">
-        <v>4764</v>
+        <v>4765</v>
       </c>
       <c r="U260" s="72">
         <v>26</v>
@@ -38123,19 +38268,19 @@
         <v>128</v>
       </c>
       <c r="X260" s="1" t="s">
-        <v>4765</v>
+        <v>4766</v>
       </c>
       <c r="Y260" s="72">
         <v>77</v>
       </c>
       <c r="Z260" s="1" t="s">
-        <v>4766</v>
+        <v>4767</v>
       </c>
       <c r="AA260" s="72">
         <v>176</v>
       </c>
       <c r="AB260" s="1" t="s">
-        <v>4767</v>
+        <v>4768</v>
       </c>
       <c r="AC260" s="72">
         <v>551</v>
@@ -38143,57 +38288,57 @@
     </row>
     <row r="261" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A261" s="72" t="s">
-        <v>4748</v>
+        <v>4749</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>4784</v>
+        <v>4785</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>4785</v>
+        <v>4786</v>
       </c>
       <c r="E261" s="4" t="s">
-        <v>4786</v>
+        <v>4787</v>
       </c>
       <c r="F261" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Oniro ARPG.html</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>4783</v>
+        <v>4784</v>
       </c>
       <c r="H261" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Oniro ARPG.html</v>
       </c>
       <c r="I261" s="42" t="s">
-        <v>4789</v>
+        <v>4790</v>
       </c>
       <c r="J261" s="1" t="s">
-        <v>4768</v>
+        <v>4769</v>
       </c>
       <c r="K261" s="72">
         <v>1961</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>4769</v>
+        <v>4770</v>
       </c>
       <c r="M261" s="72">
         <v>1016</v>
       </c>
       <c r="N261" s="1" t="s">
-        <v>4770</v>
+        <v>4771</v>
       </c>
       <c r="O261" s="72">
         <v>551</v>
       </c>
       <c r="P261" s="1" t="s">
-        <v>4771</v>
+        <v>4772</v>
       </c>
       <c r="Q261" s="72">
         <v>232</v>
       </c>
       <c r="R261" s="1" t="s">
-        <v>4772</v>
+        <v>4773</v>
       </c>
       <c r="S261" s="72">
         <v>102</v>
@@ -38205,13 +38350,13 @@
         <v>26</v>
       </c>
       <c r="V261" s="1" t="s">
-        <v>4773</v>
+        <v>4774</v>
       </c>
       <c r="W261" s="72">
         <v>622</v>
       </c>
       <c r="X261" s="1" t="s">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="Y261" s="72">
         <v>1173</v>
@@ -38219,30 +38364,30 @@
     </row>
     <row r="262" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A262" s="72" t="s">
-        <v>4749</v>
+        <v>4750</v>
       </c>
       <c r="C262" s="40" t="s">
-        <v>4777</v>
+        <v>4778</v>
       </c>
       <c r="D262" s="4" t="s">
+        <v>4789</v>
+      </c>
+      <c r="E262" s="4" t="s">
         <v>4788</v>
-      </c>
-      <c r="E262" s="4" t="s">
-        <v>4787</v>
       </c>
       <c r="F262" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Legend of YMIR.html</v>
       </c>
       <c r="G262" s="4" t="s">
-        <v>4779</v>
+        <v>4780</v>
       </c>
       <c r="H262" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Legend of YMIR.html</v>
       </c>
       <c r="I262" s="42" t="s">
-        <v>4790</v>
+        <v>4791</v>
       </c>
       <c r="J262" s="1" t="s">
         <v>1268</v>
@@ -38269,7 +38414,7 @@
         <v>256</v>
       </c>
       <c r="R262" s="1" t="s">
-        <v>4775</v>
+        <v>4776</v>
       </c>
       <c r="S262" s="72">
         <v>128</v>
@@ -38283,99 +38428,99 @@
     </row>
     <row r="263" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A263" s="69" t="s">
+        <v>4794</v>
+      </c>
+      <c r="C263" s="5" t="s">
         <v>4793</v>
       </c>
-      <c r="C263" s="5" t="s">
-        <v>4792</v>
-      </c>
       <c r="D263" s="4" t="s">
-        <v>4792</v>
+        <v>4793</v>
       </c>
       <c r="E263" s="4" t="s">
-        <v>4794</v>
+        <v>4795</v>
       </c>
       <c r="F263" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/Elysia：星空墜落.html</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>4795</v>
+        <v>4796</v>
       </c>
       <c r="H263" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Elysia：星空墜落.html</v>
       </c>
       <c r="I263" s="42" t="s">
-        <v>4796</v>
+        <v>4797</v>
       </c>
       <c r="J263" s="1" t="s">
-        <v>4873</v>
+        <v>4874</v>
       </c>
       <c r="K263" s="72">
         <v>2371</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>4874</v>
+        <v>4875</v>
       </c>
       <c r="M263" s="72">
         <v>1204</v>
       </c>
       <c r="N263" s="1" t="s">
-        <v>4875</v>
+        <v>4876</v>
       </c>
       <c r="O263" s="72">
         <v>563</v>
       </c>
       <c r="P263" s="1" t="s">
-        <v>4876</v>
+        <v>4877</v>
       </c>
       <c r="Q263" s="72">
         <v>261</v>
       </c>
       <c r="R263" s="1" t="s">
-        <v>4877</v>
+        <v>4878</v>
       </c>
       <c r="S263" s="72">
         <v>128</v>
       </c>
       <c r="T263" s="1" t="s">
-        <v>4878</v>
+        <v>4879</v>
       </c>
       <c r="U263" s="72">
         <v>26</v>
       </c>
       <c r="V263" s="1" t="s">
-        <v>4879</v>
+        <v>4880</v>
       </c>
       <c r="W263" s="72">
         <v>400</v>
       </c>
       <c r="X263" s="1" t="s">
-        <v>4880</v>
+        <v>4881</v>
       </c>
       <c r="Y263" s="72">
         <v>128</v>
       </c>
       <c r="Z263" s="1" t="s">
-        <v>4881</v>
+        <v>4882</v>
       </c>
       <c r="AA263" s="72">
         <v>2371</v>
       </c>
       <c r="AB263" s="99" t="s">
-        <v>4882</v>
+        <v>4883</v>
       </c>
       <c r="AC263" s="72">
         <v>1204</v>
       </c>
       <c r="AD263" s="1" t="s">
-        <v>4883</v>
+        <v>4884</v>
       </c>
       <c r="AE263" s="72">
         <v>400</v>
       </c>
       <c r="AF263" s="1" t="s">
-        <v>4884</v>
+        <v>4885</v>
       </c>
       <c r="AG263" s="72">
         <v>26</v>
@@ -38383,67 +38528,67 @@
     </row>
     <row r="264" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A264" s="72" t="s">
-        <v>4822</v>
+        <v>4823</v>
       </c>
       <c r="E264" s="4" t="s">
-        <v>4829</v>
+        <v>4830</v>
       </c>
       <c r="F264" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/合併貓鎮.html</v>
       </c>
       <c r="G264" s="4" t="s">
-        <v>4828</v>
+        <v>4829</v>
       </c>
       <c r="H264" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/合併貓鎮.html</v>
       </c>
       <c r="I264" s="42" t="s">
-        <v>4843</v>
+        <v>4844</v>
       </c>
       <c r="J264" s="47" t="s">
-        <v>4825</v>
+        <v>4826</v>
       </c>
       <c r="K264" s="41" t="s">
-        <v>4826</v>
+        <v>4827</v>
       </c>
     </row>
     <row r="265" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A265" s="72" t="s">
-        <v>4823</v>
+        <v>4824</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>4830</v>
+        <v>4831</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>4832</v>
+        <v>4833</v>
       </c>
       <c r="E265" s="4" t="s">
-        <v>4833</v>
+        <v>4834</v>
       </c>
       <c r="F265" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/幻牌交鋒.html</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>4834</v>
+        <v>4835</v>
       </c>
       <c r="H265" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/幻牌交鋒.html</v>
       </c>
       <c r="I265" t="s">
-        <v>4844</v>
+        <v>4845</v>
       </c>
       <c r="J265" s="1" t="s">
-        <v>4847</v>
+        <v>4848</v>
       </c>
       <c r="K265" s="72">
         <v>2371</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>4848</v>
+        <v>4849</v>
       </c>
       <c r="M265" s="72">
         <v>1204</v>
@@ -38473,7 +38618,7 @@
         <v>26</v>
       </c>
       <c r="V265" s="1" t="s">
-        <v>4885</v>
+        <v>4886</v>
       </c>
       <c r="W265" s="72">
         <v>247</v>
@@ -38485,13 +38630,13 @@
         <v>261</v>
       </c>
       <c r="Z265" s="1" t="s">
-        <v>4850</v>
+        <v>4851</v>
       </c>
       <c r="AA265" s="72">
         <v>162</v>
       </c>
       <c r="AB265" s="1" t="s">
-        <v>4849</v>
+        <v>4850</v>
       </c>
       <c r="AC265" s="72">
         <v>162</v>
@@ -38499,75 +38644,75 @@
     </row>
     <row r="266" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A266" s="3" t="s">
-        <v>4835</v>
+        <v>4836</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>4836</v>
+        <v>4837</v>
       </c>
       <c r="D266" s="4" t="s">
+        <v>4840</v>
+      </c>
+      <c r="E266" s="4" t="s">
         <v>4839</v>
-      </c>
-      <c r="E266" s="4" t="s">
-        <v>4838</v>
       </c>
       <c r="F266" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/激鬥！王國保衛戰.html</v>
       </c>
       <c r="G266" s="4" t="s">
-        <v>4837</v>
+        <v>4838</v>
       </c>
       <c r="H266" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/激鬥！王國保衛戰.html</v>
       </c>
       <c r="I266" s="42" t="s">
-        <v>4845</v>
+        <v>4846</v>
       </c>
       <c r="J266" s="1" t="s">
-        <v>4851</v>
+        <v>4852</v>
       </c>
       <c r="K266" s="72">
         <v>2609</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>4852</v>
+        <v>4853</v>
       </c>
       <c r="M266" s="72">
         <v>1365</v>
       </c>
       <c r="N266" s="1" t="s">
-        <v>4853</v>
+        <v>4854</v>
       </c>
       <c r="O266" s="72">
         <v>807</v>
       </c>
       <c r="P266" s="1" t="s">
-        <v>4854</v>
+        <v>4855</v>
       </c>
       <c r="Q266" s="72">
         <v>546</v>
       </c>
       <c r="R266" s="1" t="s">
-        <v>4855</v>
+        <v>4856</v>
       </c>
       <c r="S266" s="72">
         <v>400</v>
       </c>
       <c r="T266" s="1" t="s">
-        <v>4856</v>
+        <v>4857</v>
       </c>
       <c r="U266" s="72">
         <v>269</v>
       </c>
       <c r="V266" s="1" t="s">
-        <v>4857</v>
+        <v>4858</v>
       </c>
       <c r="W266" s="72">
         <v>145</v>
       </c>
       <c r="X266" s="1" t="s">
-        <v>4858</v>
+        <v>4859</v>
       </c>
       <c r="Y266" s="72">
         <v>29</v>
@@ -38575,87 +38720,87 @@
     </row>
     <row r="267" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A267" s="72" t="s">
-        <v>4824</v>
+        <v>4825</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>4831</v>
+        <v>4832</v>
       </c>
       <c r="D267" s="41" t="s">
-        <v>4842</v>
+        <v>4843</v>
       </c>
       <c r="E267" s="4" t="s">
-        <v>4840</v>
+        <v>4841</v>
       </c>
       <c r="F267" s="41" t="str">
         <f t="shared" si="10"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/giftcodes/嘟嘟臉惡作劇.html</v>
       </c>
       <c r="G267" s="41" t="s">
-        <v>4841</v>
+        <v>4842</v>
       </c>
       <c r="H267" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/嘟嘟臉惡作劇.html</v>
       </c>
       <c r="I267" s="42" t="s">
-        <v>4846</v>
+        <v>4847</v>
       </c>
       <c r="J267" s="1" t="s">
-        <v>4934</v>
+        <v>4935</v>
       </c>
       <c r="K267" s="72">
         <v>2371</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>4935</v>
+        <v>4936</v>
       </c>
       <c r="M267" s="72">
         <v>1204</v>
       </c>
       <c r="N267" s="1" t="s">
-        <v>4936</v>
+        <v>4937</v>
       </c>
       <c r="O267" s="72">
         <v>807</v>
       </c>
       <c r="P267" s="1" t="s">
-        <v>4937</v>
+        <v>4938</v>
       </c>
       <c r="Q267" s="72">
         <v>530</v>
       </c>
       <c r="R267" s="1" t="s">
-        <v>4938</v>
+        <v>4939</v>
       </c>
       <c r="S267" s="72">
         <v>294</v>
       </c>
       <c r="T267" s="1" t="s">
-        <v>4939</v>
+        <v>4940</v>
       </c>
       <c r="U267" s="72">
         <v>136</v>
       </c>
       <c r="V267" s="1" t="s">
-        <v>4940</v>
+        <v>4941</v>
       </c>
       <c r="W267" s="72">
         <v>29</v>
       </c>
       <c r="X267" s="1" t="s">
-        <v>4941</v>
+        <v>4942</v>
       </c>
       <c r="Y267" s="72">
         <v>136</v>
       </c>
       <c r="Z267" s="1" t="s">
-        <v>4942</v>
+        <v>4943</v>
       </c>
       <c r="AA267" s="72">
         <v>136</v>
       </c>
       <c r="AB267" s="1" t="s">
-        <v>4943</v>
+        <v>4944</v>
       </c>
       <c r="AC267" s="72">
         <v>196</v>
@@ -38663,33 +38808,33 @@
     </row>
     <row r="268" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A268" s="3" t="s">
-        <v>4911</v>
+        <v>4912</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>4913</v>
+        <v>4914</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>4896</v>
+        <v>4897</v>
       </c>
       <c r="E268" s="4" t="s">
-        <v>4897</v>
+        <v>4898</v>
       </c>
       <c r="F268" s="40" t="str">
         <f t="shared" ref="F268:F312" si="12">IF(A268="", "", "gift-codes.html?game=" &amp; A268)</f>
         <v>gift-codes.html?game=我的花園世界</v>
       </c>
       <c r="G268" s="4" t="s">
-        <v>4912</v>
+        <v>4913</v>
       </c>
       <c r="H268" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/我的花園世界.html</v>
       </c>
       <c r="I268" s="42" t="s">
-        <v>4914</v>
+        <v>4915</v>
       </c>
       <c r="J268" s="1" t="s">
-        <v>4906</v>
+        <v>4907</v>
       </c>
       <c r="K268" s="72">
         <v>2609</v>
@@ -38701,7 +38846,7 @@
         <v>1365</v>
       </c>
       <c r="N268" s="1" t="s">
-        <v>4907</v>
+        <v>4908</v>
       </c>
       <c r="O268" s="72">
         <v>807</v>
@@ -38713,7 +38858,7 @@
         <v>546</v>
       </c>
       <c r="R268" s="1" t="s">
-        <v>4908</v>
+        <v>4909</v>
       </c>
       <c r="S268" s="72">
         <v>400</v>
@@ -38737,13 +38882,13 @@
         <v>29</v>
       </c>
       <c r="Z268" s="1" t="s">
-        <v>4909</v>
+        <v>4910</v>
       </c>
       <c r="AA268" s="72">
         <v>29</v>
       </c>
       <c r="AB268" s="1" t="s">
-        <v>4910</v>
+        <v>4911</v>
       </c>
       <c r="AC268" s="72">
         <v>145</v>
@@ -38751,81 +38896,81 @@
     </row>
     <row r="269" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A269" s="72" t="s">
-        <v>4944</v>
+        <v>4945</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>4949</v>
+        <v>4950</v>
       </c>
       <c r="D269" s="41" t="s">
+        <v>4952</v>
+      </c>
+      <c r="E269" s="41" t="s">
         <v>4951</v>
-      </c>
-      <c r="E269" s="41" t="s">
-        <v>4950</v>
       </c>
       <c r="F269" s="40" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=Awakenloop</v>
       </c>
       <c r="G269" s="41" t="s">
-        <v>4952</v>
+        <v>4953</v>
       </c>
       <c r="H269" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Awakenloop.html</v>
       </c>
       <c r="I269" s="42" t="s">
-        <v>4968</v>
+        <v>4969</v>
       </c>
       <c r="J269" s="1" t="s">
-        <v>4851</v>
+        <v>4852</v>
       </c>
       <c r="K269" s="72">
         <v>2343</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>4852</v>
+        <v>4853</v>
       </c>
       <c r="M269" s="72">
         <v>1190</v>
       </c>
       <c r="N269" s="1" t="s">
-        <v>4853</v>
+        <v>4854</v>
       </c>
       <c r="O269" s="72">
         <v>798</v>
       </c>
       <c r="P269" s="1" t="s">
-        <v>4854</v>
+        <v>4855</v>
       </c>
       <c r="Q269" s="72">
         <v>540</v>
       </c>
       <c r="R269" s="1" t="s">
-        <v>4855</v>
+        <v>4856</v>
       </c>
       <c r="S269" s="72">
         <v>395</v>
       </c>
       <c r="T269" s="1" t="s">
-        <v>4856</v>
+        <v>4857</v>
       </c>
       <c r="U269" s="72">
         <v>258</v>
       </c>
       <c r="V269" s="1" t="s">
-        <v>4857</v>
+        <v>4858</v>
       </c>
       <c r="W269" s="72">
         <v>126</v>
       </c>
       <c r="X269" s="1" t="s">
-        <v>4986</v>
+        <v>4987</v>
       </c>
       <c r="Y269" s="72">
         <v>52</v>
       </c>
       <c r="Z269" s="1" t="s">
-        <v>4858</v>
+        <v>4859</v>
       </c>
       <c r="AA269" s="72">
         <v>26</v>
@@ -38833,33 +38978,33 @@
     </row>
     <row r="270" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A270" s="72" t="s">
-        <v>4945</v>
+        <v>4946</v>
       </c>
       <c r="C270" s="40" t="s">
-        <v>4956</v>
+        <v>4957</v>
       </c>
       <c r="D270" s="41" t="s">
-        <v>4953</v>
+        <v>4954</v>
       </c>
       <c r="E270" s="41" t="s">
-        <v>4954</v>
+        <v>4955</v>
       </c>
       <c r="F270" s="40" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=Astellia</v>
       </c>
       <c r="G270" s="41" t="s">
-        <v>4955</v>
+        <v>4956</v>
       </c>
       <c r="H270" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Astellia.html</v>
       </c>
       <c r="I270" s="42" t="s">
-        <v>4969</v>
+        <v>4970</v>
       </c>
       <c r="J270" s="1" t="s">
-        <v>4987</v>
+        <v>4988</v>
       </c>
       <c r="K270" s="72">
         <v>2076</v>
@@ -38885,87 +39030,87 @@
     </row>
     <row r="271" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A271" s="72" t="s">
-        <v>4946</v>
+        <v>4947</v>
       </c>
       <c r="C271" s="40" t="s">
-        <v>4966</v>
+        <v>4967</v>
       </c>
       <c r="D271" s="40" t="s">
-        <v>4966</v>
+        <v>4967</v>
       </c>
       <c r="E271" s="41" t="s">
-        <v>4967</v>
+        <v>4968</v>
       </c>
       <c r="F271" s="40" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=華夏千秋</v>
       </c>
       <c r="G271" s="41" t="s">
-        <v>4957</v>
+        <v>4958</v>
       </c>
       <c r="H271" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/華夏千秋.html</v>
       </c>
       <c r="I271" s="42" t="s">
-        <v>4970</v>
+        <v>4971</v>
       </c>
       <c r="J271" s="1" t="s">
-        <v>4988</v>
+        <v>4989</v>
       </c>
       <c r="K271" s="72">
         <v>2579</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>4989</v>
+        <v>4990</v>
       </c>
       <c r="M271" s="72">
         <v>1988</v>
       </c>
       <c r="N271" s="1" t="s">
-        <v>4990</v>
+        <v>4991</v>
       </c>
       <c r="O271" s="72">
         <v>1349</v>
       </c>
       <c r="P271" s="1" t="s">
-        <v>4991</v>
+        <v>4992</v>
       </c>
       <c r="Q271" s="72">
         <v>950</v>
       </c>
       <c r="R271" s="1" t="s">
-        <v>4992</v>
+        <v>4993</v>
       </c>
       <c r="S271" s="72">
         <v>798</v>
       </c>
       <c r="T271" s="1" t="s">
-        <v>4993</v>
+        <v>4994</v>
       </c>
       <c r="U271" s="72">
         <v>749</v>
       </c>
       <c r="V271" s="1" t="s">
-        <v>4994</v>
+        <v>4995</v>
       </c>
       <c r="W271" s="72">
         <v>540</v>
       </c>
       <c r="X271" s="1" t="s">
-        <v>4995</v>
+        <v>4996</v>
       </c>
       <c r="Y271" s="72">
         <v>395</v>
       </c>
       <c r="Z271" s="1" t="s">
-        <v>4996</v>
+        <v>4997</v>
       </c>
       <c r="AA271" s="72">
         <v>346</v>
       </c>
       <c r="AB271" s="1" t="s">
-        <v>4997</v>
+        <v>4998</v>
       </c>
       <c r="AC271" s="72">
         <v>314</v>
@@ -38973,69 +39118,69 @@
     </row>
     <row r="272" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A272" s="72" t="s">
-        <v>4947</v>
+        <v>4948</v>
       </c>
       <c r="C272" s="40" t="s">
-        <v>4958</v>
+        <v>4959</v>
       </c>
       <c r="D272" s="41" t="s">
+        <v>4962</v>
+      </c>
+      <c r="E272" s="41" t="s">
         <v>4961</v>
-      </c>
-      <c r="E272" s="41" t="s">
-        <v>4960</v>
       </c>
       <c r="F272" s="40" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=萌塔娘</v>
       </c>
       <c r="G272" s="41" t="s">
-        <v>4959</v>
+        <v>4960</v>
       </c>
       <c r="H272" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/萌塔娘.html</v>
       </c>
       <c r="I272" s="42" t="s">
-        <v>4971</v>
+        <v>4972</v>
       </c>
       <c r="J272" s="1" t="s">
-        <v>4998</v>
+        <v>4999</v>
       </c>
       <c r="K272" s="72">
         <v>2579</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>4999</v>
+        <v>5000</v>
       </c>
       <c r="M272" s="72">
         <v>1349</v>
       </c>
       <c r="N272" s="1" t="s">
-        <v>5000</v>
+        <v>5001</v>
       </c>
       <c r="O272" s="72">
         <v>798</v>
       </c>
       <c r="P272" s="1" t="s">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="Q272" s="72">
         <v>395</v>
       </c>
       <c r="R272" s="1" t="s">
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="S272" s="72">
         <v>266</v>
       </c>
       <c r="T272" s="1" t="s">
-        <v>5003</v>
+        <v>5004</v>
       </c>
       <c r="U272" s="72">
         <v>143</v>
       </c>
       <c r="V272" s="1" t="s">
-        <v>5004</v>
+        <v>5005</v>
       </c>
       <c r="W272" s="72">
         <v>29</v>
@@ -39043,33 +39188,33 @@
     </row>
     <row r="273" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A273" s="72" t="s">
-        <v>4948</v>
+        <v>4949</v>
       </c>
       <c r="C273" s="40" t="s">
-        <v>4962</v>
+        <v>4963</v>
       </c>
       <c r="D273" s="41" t="s">
-        <v>4963</v>
+        <v>4964</v>
       </c>
       <c r="E273" s="41" t="s">
-        <v>4964</v>
+        <v>4965</v>
       </c>
       <c r="F273" s="40" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=盜夢英雄2：幻野</v>
       </c>
       <c r="G273" s="41" t="s">
-        <v>4965</v>
+        <v>4966</v>
       </c>
       <c r="H273" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/盜夢英雄2：幻野.html</v>
       </c>
       <c r="I273" s="42" t="s">
-        <v>4972</v>
+        <v>4973</v>
       </c>
       <c r="J273" s="1" t="s">
-        <v>5005</v>
+        <v>5006</v>
       </c>
       <c r="K273" s="72">
         <v>2579</v>
@@ -39099,7 +39244,7 @@
         <v>798</v>
       </c>
       <c r="T273" s="1" t="s">
-        <v>5006</v>
+        <v>5007</v>
       </c>
       <c r="U273" s="72">
         <v>669</v>
@@ -39117,7 +39262,7 @@
         <v>395</v>
       </c>
       <c r="Z273" s="1" t="s">
-        <v>5007</v>
+        <v>5008</v>
       </c>
       <c r="AA273" s="72">
         <v>314</v>
@@ -39131,57 +39276,57 @@
     </row>
     <row r="274" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A274" s="70" t="s">
+        <v>5023</v>
+      </c>
+      <c r="C274" s="40" t="s">
+        <v>5020</v>
+      </c>
+      <c r="D274" s="41" t="s">
+        <v>5021</v>
+      </c>
+      <c r="E274" s="41" t="s">
         <v>5022</v>
-      </c>
-      <c r="C274" s="40" t="s">
-        <v>5019</v>
-      </c>
-      <c r="D274" s="41" t="s">
-        <v>5020</v>
-      </c>
-      <c r="E274" s="41" t="s">
-        <v>5021</v>
       </c>
       <c r="F274" s="40" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=貪婪洞窟：重生</v>
       </c>
       <c r="G274" s="4" t="s">
-        <v>5023</v>
+        <v>5024</v>
       </c>
       <c r="H274" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/貪婪洞窟：重生.html</v>
       </c>
       <c r="I274" s="42" t="s">
-        <v>5024</v>
+        <v>5025</v>
       </c>
       <c r="J274" s="1" t="s">
-        <v>5025</v>
+        <v>5026</v>
       </c>
       <c r="K274" s="72">
         <v>2343</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>5026</v>
+        <v>5027</v>
       </c>
       <c r="M274" s="72">
         <v>1190</v>
       </c>
       <c r="N274" s="1" t="s">
-        <v>5027</v>
+        <v>5028</v>
       </c>
       <c r="O274" s="72">
         <v>556</v>
       </c>
       <c r="P274" s="1" t="s">
-        <v>5028</v>
+        <v>5029</v>
       </c>
       <c r="Q274" s="72">
         <v>258</v>
       </c>
       <c r="R274" s="1" t="s">
-        <v>5029</v>
+        <v>5030</v>
       </c>
       <c r="S274" s="72">
         <v>126</v>
@@ -39193,25 +39338,25 @@
         <v>26</v>
       </c>
       <c r="V274" s="1" t="s">
-        <v>5030</v>
+        <v>5031</v>
       </c>
       <c r="W274" s="72">
         <v>556</v>
       </c>
       <c r="X274" s="1" t="s">
-        <v>5031</v>
+        <v>5032</v>
       </c>
       <c r="Y274" s="72">
         <v>556</v>
       </c>
       <c r="Z274" s="1" t="s">
-        <v>5032</v>
+        <v>5033</v>
       </c>
       <c r="AA274" s="72">
         <v>1190</v>
       </c>
       <c r="AB274" s="1" t="s">
-        <v>5033</v>
+        <v>5034</v>
       </c>
       <c r="AC274" s="72">
         <v>2343</v>
@@ -39219,30 +39364,30 @@
     </row>
     <row r="275" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A275" s="70" t="s">
-        <v>5074</v>
+        <v>5075</v>
       </c>
       <c r="C275" s="40" t="s">
-        <v>5068</v>
+        <v>5069</v>
       </c>
       <c r="D275" s="41" t="s">
-        <v>5071</v>
+        <v>5072</v>
       </c>
       <c r="E275" s="41" t="s">
-        <v>5072</v>
+        <v>5073</v>
       </c>
       <c r="F275" s="40" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=小兵特攻隊</v>
       </c>
       <c r="G275" s="41" t="s">
-        <v>5073</v>
+        <v>5074</v>
       </c>
       <c r="H275" s="41" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/小兵特攻隊.html</v>
       </c>
       <c r="I275" s="42" t="s">
-        <v>5076</v>
+        <v>5077</v>
       </c>
       <c r="J275" s="1" t="s">
         <v>12</v>
@@ -39287,50 +39432,320 @@
         <v>141</v>
       </c>
       <c r="X275" s="1" t="s">
-        <v>5075</v>
+        <v>5076</v>
       </c>
       <c r="Y275" s="72">
         <v>141</v>
       </c>
     </row>
-    <row r="276" spans="1:29" ht="22.5" customHeight="1">
+    <row r="276" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A276" s="72" t="s">
+        <v>5086</v>
+      </c>
+      <c r="C276" s="40" t="s">
+        <v>5089</v>
+      </c>
+      <c r="D276" s="41" t="s">
+        <v>5102</v>
+      </c>
+      <c r="E276" s="41" t="s">
+        <v>5103</v>
+      </c>
       <c r="F276" s="40" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=星塔旅人</v>
+      </c>
+      <c r="G276" s="4" t="s">
+        <v>5104</v>
       </c>
       <c r="H276" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="277" spans="1:29" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/星塔旅人.html</v>
+      </c>
+      <c r="I276" s="42" t="s">
+        <v>5105</v>
+      </c>
+      <c r="J276" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="K276" s="72">
+        <v>124</v>
+      </c>
+      <c r="L276" s="1" t="s">
+        <v>5126</v>
+      </c>
+      <c r="M276" s="72">
+        <v>207</v>
+      </c>
+      <c r="N276" s="1" t="s">
+        <v>5127</v>
+      </c>
+      <c r="O276" s="72">
+        <v>475</v>
+      </c>
+      <c r="P276" s="1" t="s">
+        <v>5128</v>
+      </c>
+      <c r="Q276" s="72">
+        <v>475</v>
+      </c>
+      <c r="R276" s="1" t="s">
+        <v>5129</v>
+      </c>
+      <c r="S276" s="72">
+        <v>269</v>
+      </c>
+      <c r="T276" s="1" t="s">
+        <v>5130</v>
+      </c>
+      <c r="U276" s="72">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="277" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A277" s="72" t="s">
+        <v>4684</v>
+      </c>
+      <c r="C277" s="40" t="s">
+        <v>5092</v>
+      </c>
+      <c r="D277" s="41" t="s">
+        <v>5093</v>
+      </c>
+      <c r="E277" s="41" t="s">
+        <v>5095</v>
+      </c>
       <c r="F277" s="40" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=卡厄斯夢境</v>
+      </c>
+      <c r="G277" s="41" t="s">
+        <v>5094</v>
       </c>
       <c r="H277" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="278" spans="1:29" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/卡厄斯夢境.html</v>
+      </c>
+      <c r="I277" s="42" t="s">
+        <v>5106</v>
+      </c>
+      <c r="J277" s="1" t="s">
+        <v>5006</v>
+      </c>
+      <c r="K277" s="72">
+        <v>2533</v>
+      </c>
+      <c r="L277" s="1" t="s">
+        <v>1676</v>
+      </c>
+      <c r="M277" s="72">
+        <v>1325</v>
+      </c>
+      <c r="N277" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O277" s="72">
+        <v>783</v>
+      </c>
+      <c r="P277" s="1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="Q277" s="72">
+        <v>530</v>
+      </c>
+      <c r="R277" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="S277" s="72">
+        <v>388</v>
+      </c>
+      <c r="T277" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="U277" s="72">
+        <v>261</v>
+      </c>
+      <c r="V277" s="1" t="s">
+        <v>1682</v>
+      </c>
+      <c r="W277" s="72">
+        <v>141</v>
+      </c>
+      <c r="X277" s="1" t="s">
+        <v>1683</v>
+      </c>
+      <c r="Y277" s="72">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="278" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A278" s="72" t="s">
+        <v>5087</v>
+      </c>
+      <c r="C278" s="40" t="s">
+        <v>5091</v>
+      </c>
+      <c r="D278" s="41" t="s">
+        <v>5096</v>
+      </c>
+      <c r="E278" s="41" t="s">
+        <v>5098</v>
+      </c>
       <c r="F278" s="40" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=星痕共鳴</v>
+      </c>
+      <c r="G278" s="41" t="s">
+        <v>5097</v>
       </c>
       <c r="H278" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="279" spans="1:29" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/星痕共鳴.html</v>
+      </c>
+      <c r="I278" s="42" t="s">
+        <v>5107</v>
+      </c>
+      <c r="J278" s="1" t="s">
+        <v>5111</v>
+      </c>
+      <c r="K278" s="72">
+        <v>2533</v>
+      </c>
+      <c r="L278" s="1" t="s">
+        <v>5112</v>
+      </c>
+      <c r="M278" s="72">
+        <v>1325</v>
+      </c>
+      <c r="N278" s="1" t="s">
+        <v>3515</v>
+      </c>
+      <c r="O278" s="72">
+        <v>783</v>
+      </c>
+      <c r="P278" s="1" t="s">
+        <v>5113</v>
+      </c>
+      <c r="Q278" s="72">
+        <v>388</v>
+      </c>
+      <c r="R278" s="1" t="s">
+        <v>5114</v>
+      </c>
+      <c r="S278" s="72">
+        <v>261</v>
+      </c>
+      <c r="T278" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="U278" s="72">
+        <v>141</v>
+      </c>
+      <c r="V278" s="1" t="s">
+        <v>4729</v>
+      </c>
+      <c r="W278" s="72">
+        <v>28</v>
+      </c>
+      <c r="X278" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y278" s="72">
+        <v>141</v>
+      </c>
+      <c r="Z278" s="1" t="s">
+        <v>5115</v>
+      </c>
+      <c r="AA278" s="72">
+        <v>522</v>
+      </c>
+      <c r="AB278" s="1" t="s">
+        <v>5116</v>
+      </c>
+      <c r="AC278" s="72">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="279" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A279" s="72" t="s">
+        <v>5088</v>
+      </c>
+      <c r="C279" s="40" t="s">
+        <v>5090</v>
+      </c>
+      <c r="D279" s="41" t="s">
+        <v>5099</v>
+      </c>
+      <c r="E279" s="41" t="s">
+        <v>5101</v>
+      </c>
       <c r="F279" s="40" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=二重螺旋</v>
+      </c>
+      <c r="G279" s="41" t="s">
+        <v>5100</v>
       </c>
       <c r="H279" s="41" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/二重螺旋.html</v>
+      </c>
+      <c r="I279" s="42" t="s">
+        <v>5108</v>
+      </c>
+      <c r="J279" s="1" t="s">
+        <v>5117</v>
+      </c>
+      <c r="K279" s="72">
+        <v>2533</v>
+      </c>
+      <c r="L279" s="1" t="s">
+        <v>5118</v>
+      </c>
+      <c r="M279" s="72">
+        <v>1325</v>
+      </c>
+      <c r="N279" s="1" t="s">
+        <v>5119</v>
+      </c>
+      <c r="O279" s="72">
+        <v>783</v>
+      </c>
+      <c r="P279" s="1" t="s">
+        <v>5120</v>
+      </c>
+      <c r="Q279" s="72">
+        <v>388</v>
+      </c>
+      <c r="R279" s="1" t="s">
+        <v>5121</v>
+      </c>
+      <c r="S279" s="72">
+        <v>261</v>
+      </c>
+      <c r="T279" s="1" t="s">
+        <v>5122</v>
+      </c>
+      <c r="U279" s="72">
+        <v>141</v>
+      </c>
+      <c r="V279" s="1" t="s">
+        <v>5123</v>
+      </c>
+      <c r="W279" s="72">
+        <v>28</v>
+      </c>
+      <c r="X279" s="1" t="s">
+        <v>5124</v>
+      </c>
+      <c r="Y279" s="72">
+        <v>261</v>
+      </c>
+      <c r="Z279" s="1" t="s">
+        <v>5125</v>
+      </c>
+      <c r="AA279" s="72">
+        <v>141</v>
       </c>
     </row>
     <row r="280" spans="1:29" ht="22.5" customHeight="1">
@@ -42805,9 +43220,10 @@
     <hyperlink ref="E268" r:id="rId208"/>
     <hyperlink ref="C269" r:id="rId209"/>
     <hyperlink ref="G274" r:id="rId210"/>
+    <hyperlink ref="G276" r:id="rId211"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId211"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId212"/>
 </worksheet>
 </file>
 
@@ -51469,25 +51885,25 @@
         <v>1920</v>
       </c>
       <c r="AK127" s="18" t="s">
-        <v>5044</v>
+        <v>5045</v>
       </c>
       <c r="AM127" s="18" t="s">
-        <v>5045</v>
+        <v>5046</v>
       </c>
       <c r="AN127" s="13" t="s">
+        <v>5051</v>
+      </c>
+      <c r="AO127" s="18" t="s">
+        <v>5047</v>
+      </c>
+      <c r="AP127" s="13" t="s">
         <v>5050</v>
       </c>
-      <c r="AO127" s="18" t="s">
-        <v>5046</v>
-      </c>
-      <c r="AP127" s="13" t="s">
+      <c r="AQ127" s="18" t="s">
+        <v>5048</v>
+      </c>
+      <c r="AR127" s="13" t="s">
         <v>5049</v>
-      </c>
-      <c r="AQ127" s="18" t="s">
-        <v>5047</v>
-      </c>
-      <c r="AR127" s="13" t="s">
-        <v>5048</v>
       </c>
     </row>
     <row r="128" spans="1:50" ht="22.5" customHeight="1">
@@ -53179,7 +53595,7 @@
         <v>4422</v>
       </c>
       <c r="Y156" s="18" t="s">
-        <v>4816</v>
+        <v>4817</v>
       </c>
     </row>
     <row r="157" spans="1:34" ht="22.5" customHeight="1">
@@ -54606,31 +55022,31 @@
         <v>3654</v>
       </c>
       <c r="Q185" s="18" t="s">
-        <v>4859</v>
+        <v>4860</v>
       </c>
       <c r="S185" s="18" t="s">
-        <v>4860</v>
+        <v>4861</v>
       </c>
       <c r="U185" s="18" t="s">
-        <v>4861</v>
+        <v>4862</v>
       </c>
       <c r="W185" s="18" t="s">
-        <v>4862</v>
+        <v>4863</v>
       </c>
       <c r="Y185" s="18" t="s">
-        <v>4863</v>
+        <v>4864</v>
       </c>
       <c r="AA185" s="18" t="s">
-        <v>4864</v>
+        <v>4865</v>
       </c>
       <c r="AC185" s="18" t="s">
-        <v>4865</v>
+        <v>4866</v>
       </c>
       <c r="AE185" s="18" t="s">
-        <v>4866</v>
+        <v>4867</v>
       </c>
       <c r="AG185" s="18" t="s">
-        <v>4867</v>
+        <v>4868</v>
       </c>
     </row>
     <row r="186" spans="1:39" ht="22.5" customHeight="1">
@@ -54859,16 +55275,16 @@
         <v>4621</v>
       </c>
       <c r="AG190" s="18" t="s">
-        <v>4869</v>
+        <v>4870</v>
       </c>
       <c r="AI190" s="18" t="s">
-        <v>4870</v>
+        <v>4871</v>
       </c>
       <c r="AK190" s="18" t="s">
-        <v>4871</v>
+        <v>4872</v>
       </c>
       <c r="AM190" s="18" t="s">
-        <v>4872</v>
+        <v>4873</v>
       </c>
     </row>
     <row r="191" spans="1:39" ht="22.5" customHeight="1">
@@ -55753,52 +56169,52 @@
         <v>3756</v>
       </c>
       <c r="K206" s="17" t="s">
-        <v>4799</v>
+        <v>4800</v>
       </c>
       <c r="L206" s="13" t="s">
-        <v>4800</v>
+        <v>4801</v>
       </c>
       <c r="M206" s="18" t="s">
-        <v>4801</v>
+        <v>4802</v>
       </c>
       <c r="N206" s="13" t="s">
-        <v>4802</v>
+        <v>4803</v>
       </c>
       <c r="O206" s="18" t="s">
-        <v>4803</v>
+        <v>4804</v>
       </c>
       <c r="P206" s="13" t="s">
-        <v>4804</v>
+        <v>4805</v>
       </c>
       <c r="Q206" s="18" t="s">
-        <v>4805</v>
+        <v>4806</v>
       </c>
       <c r="R206" s="25" t="s">
-        <v>4806</v>
+        <v>4807</v>
       </c>
       <c r="S206" s="18" t="s">
-        <v>4807</v>
+        <v>4808</v>
       </c>
       <c r="T206" s="13" t="s">
-        <v>4808</v>
+        <v>4809</v>
       </c>
       <c r="U206" s="18" t="s">
-        <v>4809</v>
+        <v>4810</v>
       </c>
       <c r="V206" s="13" t="s">
-        <v>4810</v>
+        <v>4811</v>
       </c>
       <c r="W206" s="18" t="s">
-        <v>4811</v>
+        <v>4812</v>
       </c>
       <c r="X206" s="71" t="s">
-        <v>4813</v>
+        <v>4814</v>
       </c>
       <c r="Y206" s="18" t="s">
-        <v>4814</v>
+        <v>4815</v>
       </c>
       <c r="Z206" s="13" t="s">
-        <v>4815</v>
+        <v>4816</v>
       </c>
     </row>
     <row r="207" spans="1:50" ht="22.5" customHeight="1">
@@ -55909,7 +56325,7 @@
         <v>3853</v>
       </c>
       <c r="V208" s="13" t="s">
-        <v>4812</v>
+        <v>4813</v>
       </c>
       <c r="W208" s="18" t="s">
         <v>3854</v>
@@ -56813,7 +57229,7 @@
         <v>4146</v>
       </c>
       <c r="Y224" s="18" t="s">
-        <v>4817</v>
+        <v>4818</v>
       </c>
     </row>
     <row r="225" spans="1:47" ht="22.5" customHeight="1">
@@ -56983,25 +57399,25 @@
         <v>4397</v>
       </c>
       <c r="W227" s="18" t="s">
-        <v>4797</v>
+        <v>4798</v>
       </c>
       <c r="Y227" s="18" t="s">
-        <v>4798</v>
+        <v>4799</v>
       </c>
       <c r="AA227" s="71" t="s">
-        <v>4868</v>
+        <v>4869</v>
       </c>
       <c r="AC227" s="18" t="s">
-        <v>4983</v>
+        <v>4984</v>
       </c>
       <c r="AE227" s="18" t="s">
-        <v>4984</v>
+        <v>4985</v>
       </c>
       <c r="AG227" s="18" t="s">
-        <v>4985</v>
+        <v>4986</v>
       </c>
       <c r="AI227" s="18" t="s">
-        <v>5008</v>
+        <v>5009</v>
       </c>
     </row>
     <row r="228" spans="1:47" ht="22.5" customHeight="1">
@@ -57058,10 +57474,10 @@
         <v>2542</v>
       </c>
       <c r="AA228" s="18" t="s">
-        <v>4744</v>
+        <v>4745</v>
       </c>
       <c r="AC228" s="18" t="s">
-        <v>4745</v>
+        <v>4746</v>
       </c>
     </row>
     <row r="229" spans="1:47" ht="22.5" customHeight="1">
@@ -57452,40 +57868,40 @@
         <v>4464</v>
       </c>
       <c r="K236" s="90" t="s">
-        <v>5009</v>
+        <v>5010</v>
       </c>
       <c r="L236" s="13" t="s">
-        <v>5034</v>
+        <v>5035</v>
       </c>
       <c r="M236" s="90" t="s">
-        <v>5035</v>
+        <v>5036</v>
       </c>
       <c r="N236" s="13" t="s">
-        <v>5036</v>
+        <v>5037</v>
       </c>
       <c r="O236" s="90" t="s">
-        <v>5037</v>
+        <v>5038</v>
       </c>
       <c r="P236" s="13" t="s">
-        <v>5038</v>
+        <v>5039</v>
       </c>
       <c r="Q236" s="90" t="s">
-        <v>5039</v>
+        <v>5040</v>
       </c>
       <c r="R236" s="13" t="s">
-        <v>5010</v>
+        <v>5011</v>
       </c>
       <c r="S236" s="90" t="s">
-        <v>5040</v>
+        <v>5041</v>
       </c>
       <c r="T236" s="13" t="s">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="U236" s="18" t="s">
-        <v>5042</v>
+        <v>5043</v>
       </c>
       <c r="V236" s="13" t="s">
-        <v>5043</v>
+        <v>5044</v>
       </c>
     </row>
     <row r="237" spans="1:47" ht="22.5" customHeight="1">
@@ -57605,7 +58021,7 @@
         <v>4680</v>
       </c>
       <c r="U238" s="18" t="s">
-        <v>4818</v>
+        <v>4819</v>
       </c>
     </row>
     <row r="239" spans="1:47" ht="22.5" customHeight="1">
@@ -58118,13 +58534,13 @@
         <v>4632</v>
       </c>
       <c r="W252" s="18" t="s">
+        <v>4748</v>
+      </c>
+      <c r="Y252" s="18" t="s">
         <v>4747</v>
       </c>
-      <c r="Y252" s="18" t="s">
-        <v>4746</v>
-      </c>
       <c r="AA252" s="18" t="s">
-        <v>4819</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="253" spans="1:27" ht="22.5" customHeight="1">
@@ -58175,10 +58591,10 @@
         <v>4646</v>
       </c>
       <c r="Q253" s="18" t="s">
-        <v>4820</v>
+        <v>4821</v>
       </c>
       <c r="R253" s="13" t="s">
-        <v>4821</v>
+        <v>4822</v>
       </c>
     </row>
     <row r="254" spans="1:27" ht="22.5" customHeight="1">
@@ -58265,28 +58681,28 @@
         <v>《純潔的魔法少女》是一款充滿日系動漫風格的冒險 RPG，玩家將化身為魔法少女，與夥伴們一同踏上對抗魔王的旅程。遊戲主打高自由度的策略戰鬥，玩家可自由搭配技能與裝備，打造獨一無二的戰鬥風格。除了熱血的主線劇情，還有豐富的副本挑戰、PVP 對戰與社群互動玩法，讓你與其他魔法少女們一起享受戰鬥的樂趣。遊戲內也特別為玩家準備了各種兌換碼及禮包碼，讓你輕鬆獲得珍貴道具，快速提升戰力。此外，遊戲提供代儲值服務，安全又快速，讓你無後顧之憂地暢玩！</v>
       </c>
       <c r="F255" s="17" t="s">
-        <v>4705</v>
+        <v>4706</v>
       </c>
       <c r="G255" s="13" t="s">
-        <v>4706</v>
+        <v>4707</v>
       </c>
       <c r="K255" s="17" t="s">
-        <v>4707</v>
+        <v>4708</v>
       </c>
       <c r="L255" s="13" t="s">
-        <v>4708</v>
+        <v>4709</v>
       </c>
       <c r="M255" s="18" t="s">
-        <v>4709</v>
+        <v>4710</v>
       </c>
       <c r="N255" s="13" t="s">
+        <v>4712</v>
+      </c>
+      <c r="O255" s="18" t="s">
         <v>4711</v>
       </c>
-      <c r="O255" s="18" t="s">
-        <v>4710</v>
-      </c>
       <c r="P255" s="13" t="s">
-        <v>4712</v>
+        <v>4713</v>
       </c>
     </row>
     <row r="256" spans="1:27" ht="22.5" customHeight="1">
@@ -58337,7 +58753,7 @@
         <v>《屍不可擋》是一款爽度破表的末日生存射擊手遊，玩家將身處殭屍橫行的世界，拿起各式槍械掃蕩成群的活屍。遊戲採用俯視角設計，操作簡單直覺，搭配上滿螢幕的殭屍與刺激的射擊音效，帶來前所未有的爽快感。除了殲滅活屍，遊戲也提供了豐富的裝備升級與技能樹系統，讓你能打造出最強的生存者。別忘了定期留意官方釋出的兌換碼與禮包碼，這些都是提升戰力的重要資源。同時，若想快速獲得物資，遊戲也提供代儲值服務，快速安全，讓你專注於生存與戰鬥。</v>
       </c>
       <c r="F257" s="34" t="s">
-        <v>4715</v>
+        <v>4716</v>
       </c>
       <c r="G257" s="13" t="s">
         <v>2625</v>
@@ -58346,10 +58762,10 @@
         <v>4368</v>
       </c>
       <c r="K257" s="17" t="s">
-        <v>4713</v>
+        <v>4714</v>
       </c>
       <c r="L257" s="13" t="s">
-        <v>4714</v>
+        <v>4715</v>
       </c>
     </row>
     <row r="258" spans="1:31" ht="22.5" customHeight="1">
@@ -58400,7 +58816,7 @@
         <v>在《少女掌門人》中，您可以體驗直式畫面單手操作的便捷，無論通勤、上學或睡前都能隨時暢玩。遊戲採用全自動戰鬥系統，少女們將會自行施展華麗必殺技與技能擊敗敵人，讓您觀看也能享受爽快戰鬥的視覺盛宴。透過無限可能的戰略組合，打造專屬您的最強戰術，提升門派實力，橫掃魔物！為了讓掌門人能夠快速成長，遊戲內設有豐富的兌換碼與禮包碼福利，提供豐厚資源助您一臂之力。此外，遊戲也支援代儲值服務，確保玩家能以快速安全的方式獲得所需物品，讓您輕鬆培育美少女角色，打造最強隊伍！立即加入，開啟您的掌門人生涯，享受培育少女、稱霸武林的成就感！</v>
       </c>
       <c r="F259" s="34" t="s">
-        <v>4715</v>
+        <v>4716</v>
       </c>
       <c r="G259" s="13" t="s">
         <v>3641</v>
@@ -58412,10 +58828,10 @@
         <v>4368</v>
       </c>
       <c r="K259" s="101" t="s">
-        <v>4894</v>
+        <v>4895</v>
       </c>
       <c r="L259" s="13" t="s">
-        <v>4895</v>
+        <v>4896</v>
       </c>
     </row>
     <row r="260" spans="1:31">
@@ -58560,16 +58976,16 @@
         <v>《合併貓鎮》是一款可愛風格的合併益智手機遊戲，你將扮演一位貓咪鎮長，透過不斷合併相同物品來解鎖更高級的道具，打造出一個獨一無二的貓咪天堂。遊戲擁有豐富的任務系統和多元的場景設計，讓你在輕鬆療癒的氛圍中享受策略與創造的樂趣。想讓你的貓咪小鎮更加蓬勃發展嗎？別忘了領取兌換碼和禮包碼，迅速獲得豐富資源！若想快速增強實力，也可透過我們提供的代儲值服務，享受快速安全的交易體驗，讓你輕鬆成為貓咪鎮的頂級建築師！準備好與可愛貓咪們一同探索這個充滿驚喜的世界了嗎？</v>
       </c>
       <c r="F264" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="G264" s="13" t="s">
         <v>4827</v>
       </c>
-      <c r="G264" s="13" t="s">
-        <v>4826</v>
-      </c>
       <c r="K264" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="L264" s="13" t="s">
         <v>4827</v>
-      </c>
-      <c r="L264" s="13" t="s">
-        <v>4826</v>
       </c>
     </row>
     <row r="265" spans="1:31">
@@ -58590,52 +59006,52 @@
         <v>《幻牌交鋒》是一款集換式卡牌競技手遊，遊戲將帶你進入一個由神秘卡牌主宰的奇幻世界。玩家需要精心組建卡組，運用策略與智慧，與來自各地的玩家進行刺激的即時對戰。每張卡牌都擁有獨特的技能與屬性，考驗你的戰術佈局與臨場反應。想在牌桌上稱霸一方嗎？務必關注官方兌換碼與禮包碼，獲得稀有卡牌與豐富獎勵，讓你贏在起跑點！我們也提供快速安全的代儲值服務，讓你輕鬆獲取心儀的卡牌，迅速打造出最強牌組！</v>
       </c>
       <c r="F265" s="100" t="s">
+        <v>4891</v>
+      </c>
+      <c r="G265" s="13" t="s">
+        <v>4892</v>
+      </c>
+      <c r="H265" s="13" t="s">
+        <v>4893</v>
+      </c>
+      <c r="I265" s="13" t="s">
+        <v>4894</v>
+      </c>
+      <c r="K265" s="17" t="s">
+        <v>4889</v>
+      </c>
+      <c r="L265" s="13" t="s">
         <v>4890</v>
       </c>
-      <c r="G265" s="13" t="s">
-        <v>4891</v>
-      </c>
-      <c r="H265" s="13" t="s">
-        <v>4892</v>
-      </c>
-      <c r="I265" s="13" t="s">
-        <v>4893</v>
-      </c>
-      <c r="K265" s="17" t="s">
-        <v>4888</v>
-      </c>
-      <c r="L265" s="13" t="s">
-        <v>4889</v>
-      </c>
       <c r="M265" s="18" t="s">
-        <v>4973</v>
+        <v>4974</v>
       </c>
       <c r="O265" s="18" t="s">
-        <v>4974</v>
+        <v>4975</v>
       </c>
       <c r="Q265" s="18" t="s">
-        <v>4975</v>
+        <v>4976</v>
       </c>
       <c r="S265" s="18" t="s">
-        <v>4976</v>
+        <v>4977</v>
       </c>
       <c r="U265" s="18" t="s">
-        <v>4977</v>
+        <v>4978</v>
       </c>
       <c r="W265" s="18" t="s">
-        <v>4978</v>
+        <v>4979</v>
       </c>
       <c r="Y265" s="18" t="s">
-        <v>4979</v>
+        <v>4980</v>
       </c>
       <c r="AA265" s="18" t="s">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="AC265" s="18" t="s">
-        <v>4981</v>
+        <v>4982</v>
       </c>
       <c r="AE265" s="18" t="s">
-        <v>4982</v>
+        <v>4983</v>
       </c>
     </row>
     <row r="266" spans="1:31">
@@ -58656,16 +59072,16 @@
         <v>《激鬥！王國保衛戰》是一款塔防競技手遊，完美結合了經典塔防玩法與即時對戰元素。你將扮演指揮官，在戰場上部署防禦塔，召喚英雄，與對手鬥智鬥勇，爭奪最終的勝利。遊戲保留了原作豐富的英雄與防禦塔系統，並加入了全新的PVP模式，讓你與全球玩家展開激烈對決。想在戰場上所向披靡嗎？別錯過官方提供的兌換碼和禮包碼，讓你輕鬆獲得資源，強化你的軍隊！若想快速壯大實力，我們也提供快速安全的代儲值服務，讓你無後顧之憂地專注於策略佈局，成為真正的塔防大師！</v>
       </c>
       <c r="F266" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="G266" s="13" t="s">
         <v>4827</v>
       </c>
-      <c r="G266" s="13" t="s">
-        <v>4826</v>
-      </c>
       <c r="K266" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="L266" s="13" t="s">
         <v>4827</v>
-      </c>
-      <c r="L266" s="13" t="s">
-        <v>4826</v>
       </c>
     </row>
     <row r="267" spans="1:31">
@@ -58686,67 +59102,67 @@
         <v>《嘟嘟臉惡作劇》是一款充滿日系可愛風格的放置養成遊戲。故事發生在一個充滿魔法的學院，玩家將與一群擁有特殊能力的可愛角色們相遇，一同展開奇妙的冒險。遊戲採用輕鬆的放置玩法，讓你在繁忙之餘也能享受角色養成的樂趣，並透過策略性的戰鬥配置，挑戰各種關卡。想讓你的角色們迅速成長，解鎖更多有趣劇情嗎？記得使用官方兌換碼及禮包碼，獲得大量經驗與珍稀道具！我們也提供代儲值服務，讓您快速安全地獲得所需資源，輕鬆養成最強戰隊，在嘟嘟臉的世界裡盡情惡作劇吧！</v>
       </c>
       <c r="F267" s="17" t="s">
+        <v>4924</v>
+      </c>
+      <c r="G267" s="13" t="s">
+        <v>4925</v>
+      </c>
+      <c r="H267" s="13" t="s">
+        <v>4926</v>
+      </c>
+      <c r="I267" s="13" t="s">
+        <v>4927</v>
+      </c>
+      <c r="J267" s="13" t="s">
+        <v>4928</v>
+      </c>
+      <c r="K267" s="17" t="s">
+        <v>4916</v>
+      </c>
+      <c r="L267" s="13" t="s">
+        <v>4929</v>
+      </c>
+      <c r="M267" s="18" t="s">
+        <v>4917</v>
+      </c>
+      <c r="N267" s="13" t="s">
+        <v>4930</v>
+      </c>
+      <c r="O267" s="18" t="s">
+        <v>4918</v>
+      </c>
+      <c r="P267" s="13" t="s">
+        <v>4931</v>
+      </c>
+      <c r="Q267" s="18" t="s">
+        <v>4919</v>
+      </c>
+      <c r="R267" s="13" t="s">
+        <v>4932</v>
+      </c>
+      <c r="S267" s="18" t="s">
+        <v>4920</v>
+      </c>
+      <c r="T267" s="13" t="s">
+        <v>4933</v>
+      </c>
+      <c r="U267" s="18" t="s">
+        <v>4921</v>
+      </c>
+      <c r="V267" s="13" t="s">
+        <v>4934</v>
+      </c>
+      <c r="W267" s="18" t="s">
+        <v>4922</v>
+      </c>
+      <c r="X267" s="13" t="s">
+        <v>4934</v>
+      </c>
+      <c r="Y267" s="18" t="s">
         <v>4923</v>
       </c>
-      <c r="G267" s="13" t="s">
-        <v>4924</v>
-      </c>
-      <c r="H267" s="13" t="s">
-        <v>4925</v>
-      </c>
-      <c r="I267" s="13" t="s">
-        <v>4926</v>
-      </c>
-      <c r="J267" s="13" t="s">
-        <v>4927</v>
-      </c>
-      <c r="K267" s="17" t="s">
-        <v>4915</v>
-      </c>
-      <c r="L267" s="13" t="s">
-        <v>4928</v>
-      </c>
-      <c r="M267" s="18" t="s">
-        <v>4916</v>
-      </c>
-      <c r="N267" s="13" t="s">
-        <v>4929</v>
-      </c>
-      <c r="O267" s="18" t="s">
-        <v>4917</v>
-      </c>
-      <c r="P267" s="13" t="s">
-        <v>4930</v>
-      </c>
-      <c r="Q267" s="18" t="s">
-        <v>4918</v>
-      </c>
-      <c r="R267" s="13" t="s">
-        <v>4931</v>
-      </c>
-      <c r="S267" s="18" t="s">
-        <v>4919</v>
-      </c>
-      <c r="T267" s="13" t="s">
-        <v>4932</v>
-      </c>
-      <c r="U267" s="18" t="s">
-        <v>4920</v>
-      </c>
-      <c r="V267" s="13" t="s">
-        <v>4933</v>
-      </c>
-      <c r="W267" s="18" t="s">
-        <v>4921</v>
-      </c>
-      <c r="X267" s="13" t="s">
-        <v>4933</v>
-      </c>
-      <c r="Y267" s="18" t="s">
-        <v>4922</v>
-      </c>
       <c r="Z267" s="13" t="s">
-        <v>4933</v>
+        <v>4934</v>
       </c>
     </row>
     <row r="268" spans="1:31">
@@ -58767,10 +59183,10 @@
         <v>踏入《我的花園世界》，一個充滿奇幻與溫馨的養成冒險，讓你在忙碌的生活中找到一片心靈綠洲！這款手遊將帶你探索魔法大陸，與可愛的花仙子們一同培育珍奇植物，從零開始打造屬於你的夢想莊園。遊戲結合了多元的養成、裝飾與社交玩法，不僅能自由裝扮你的花園，更能拜訪好友，互贈禮物，共創美好回憶。想加速成長？別擔心，豐富的兌換碼和禮包碼讓你輕鬆取得稀有資源，快速提升等級。我們也提供代儲值服務，讓你享受快速安全的交易體驗，輕鬆購入心儀的限定道具。快來加入，與全球玩家一起體驗這場療癒又趣味的園藝之旅吧！</v>
       </c>
       <c r="F268" s="17" t="s">
-        <v>5057</v>
+        <v>5058</v>
       </c>
       <c r="G268" s="13" t="s">
-        <v>5058</v>
+        <v>5059</v>
       </c>
       <c r="H268" s="13" t="s">
         <v>2625</v>
@@ -58779,34 +59195,34 @@
         <v>4368</v>
       </c>
       <c r="K268" s="17" t="s">
-        <v>4886</v>
+        <v>4887</v>
       </c>
       <c r="L268" s="13" t="s">
-        <v>4887</v>
+        <v>4888</v>
       </c>
       <c r="M268" s="18" t="s">
-        <v>4898</v>
+        <v>4899</v>
       </c>
       <c r="N268" s="13" t="s">
+        <v>4903</v>
+      </c>
+      <c r="O268" s="18" t="s">
+        <v>4900</v>
+      </c>
+      <c r="P268" s="13" t="s">
+        <v>4904</v>
+      </c>
+      <c r="Q268" s="18" t="s">
+        <v>4901</v>
+      </c>
+      <c r="R268" s="13" t="s">
+        <v>4905</v>
+      </c>
+      <c r="S268" s="18" t="s">
         <v>4902</v>
       </c>
-      <c r="O268" s="18" t="s">
-        <v>4899</v>
-      </c>
-      <c r="P268" s="13" t="s">
-        <v>4903</v>
-      </c>
-      <c r="Q268" s="18" t="s">
-        <v>4900</v>
-      </c>
-      <c r="R268" s="13" t="s">
-        <v>4904</v>
-      </c>
-      <c r="S268" s="18" t="s">
-        <v>4901</v>
-      </c>
       <c r="T268" s="13" t="s">
-        <v>4905</v>
+        <v>4906</v>
       </c>
     </row>
     <row r="269" spans="1:31">
@@ -58827,16 +59243,16 @@
         <v>《Awakenloop》是一款充滿賽博龐克風格的卡牌回合制手遊，玩家將身處一個由機器人與人類共存的末日世界。遊戲主打策略性卡牌戰鬥，每張卡牌都蘊含獨特技能，如何搭配與釋放將成為戰局關鍵。除了豐富的主線劇情，遊戲也提供多樣的副本挑戰與 PvP 模式，讓你與其他玩家一較高下。現在就加入《Awakenloop》，透過兌換碼與禮包碼獲得專屬獎勵，輕鬆提升戰力，也能使用代儲值服務快速安全地補充資源，在這片混沌的廢土上開創屬於你的新紀元。</v>
       </c>
       <c r="F269" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="G269" s="13" t="s">
         <v>4827</v>
       </c>
-      <c r="G269" s="13" t="s">
-        <v>4826</v>
-      </c>
       <c r="K269" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="L269" s="13" t="s">
         <v>4827</v>
-      </c>
-      <c r="L269" s="13" t="s">
-        <v>4826</v>
       </c>
     </row>
     <row r="270" spans="1:31">
@@ -58857,16 +59273,16 @@
         <v>《Astellia》是一款日系風格的魔幻冒險MMORPG，帶領玩家進入一個充滿魔法與奇幻生物的艾斯提亞大陸。遊戲以其精緻的3D美術畫面與豐富的職業系統著稱，玩家可自由選擇多種職業，並透過養成可愛的「星靈」夥伴來協助戰鬥。遊戲提供多樣化的副本、世界王挑戰與公會系統，讓玩家能與好友一同探索廣闊的世界。使用兌換碼和禮包碼能輕鬆領取稀有道具，快速提升戰力，若需更多遊戲幣與資源，代儲值服務能提供你安全又快速的儲值體驗，讓你在艾斯提亞大陸的旅程更加順暢。</v>
       </c>
       <c r="F270" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="G270" s="13" t="s">
         <v>4827</v>
       </c>
-      <c r="G270" s="13" t="s">
-        <v>4826</v>
-      </c>
       <c r="K270" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="L270" s="13" t="s">
         <v>4827</v>
-      </c>
-      <c r="L270" s="13" t="s">
-        <v>4826</v>
       </c>
     </row>
     <row r="271" spans="1:31">
@@ -58887,16 +59303,16 @@
         <v>《華夏千秋》是一款以中國古代神話為背景的MMORPG，遊戲將玩家帶入一個波瀾壯闊的東方玄幻世界。你將化身為修仙者，體驗從凡人到仙神的蛻變歷程。遊戲結合了豐富的劇情故事與自由的戰鬥系統，還有多樣化的社交玩法，讓玩家在修仙的道路上結交同伴，並肩作戰。現在就透過兌換碼和禮包碼領取豐富資源，快速開啟你的修仙之路，若想省時省力，安全的代儲值服務能讓你在短時間內獲得豐厚的回報，輕鬆應對各種挑戰，成就千秋霸業。</v>
       </c>
       <c r="F271" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="G271" s="13" t="s">
         <v>4827</v>
       </c>
-      <c r="G271" s="13" t="s">
-        <v>4826</v>
-      </c>
       <c r="K271" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="L271" s="13" t="s">
         <v>4827</v>
-      </c>
-      <c r="L271" s="13" t="s">
-        <v>4826</v>
       </c>
     </row>
     <row r="272" spans="1:31">
@@ -58917,10 +59333,10 @@
         <v>《萌塔娘》是一款結合了塔防與角色養成元素的二次元策略手遊，玩家將在遊戲中與各種「塔娘」並肩作戰，守護家園。遊戲以其可愛的Q版畫風與創新的塔防玩法吸引玩家，每位塔娘都有獨特的技能與屬性，如何配置防禦陣線與策略運用將是勝利的關鍵。遊戲內提供多樣化的養成系統，讓玩家能培養出最強的塔娘戰隊。透過兌換碼與禮包碼可獲得限定獎勵，快速提升戰力，若想迅速強化隊伍，安全的代儲值服務絕對是快速又方便的選擇，讓你輕鬆守護世界的和平。</v>
       </c>
       <c r="F272" s="17" t="s">
-        <v>5067</v>
+        <v>5068</v>
       </c>
       <c r="G272" s="13" t="s">
-        <v>5084</v>
+        <v>5085</v>
       </c>
       <c r="H272" s="13" t="s">
         <v>2625</v>
@@ -58929,10 +59345,10 @@
         <v>4368</v>
       </c>
       <c r="K272" s="17" t="s">
-        <v>5065</v>
+        <v>5066</v>
       </c>
       <c r="L272" s="13" t="s">
-        <v>5066</v>
+        <v>5067</v>
       </c>
     </row>
     <row r="273" spans="1:22">
@@ -58953,7 +59369,7 @@
         <v>《盜夢英雄2：幻野》是一款主打橫向捲軸動作戰鬥的RPG手遊，玩家將進入一個充滿奇幻與冒險的夢境世界。遊戲以爽快的打擊感與華麗的技能特效為核心，玩家可自由組建隊伍，挑戰各種強大的魔物與敵人。豐富的劇情模式與多樣的副本挑戰讓遊戲內容更加充實，無論是PVP還是PVE玩家都能找到樂趣。現在使用兌換碼與禮包碼就能領取專屬禮品，快速提升戰力，若有額外資源需求，代儲值服務提供最快速安全的購買管道，讓你輕鬆在夢境世界中探索，成為最強的夢境英雄。</v>
       </c>
       <c r="F273" s="13" t="s">
-        <v>5079</v>
+        <v>5080</v>
       </c>
       <c r="G273" s="13" t="s">
         <v>2625</v>
@@ -58962,40 +59378,40 @@
         <v>4368</v>
       </c>
       <c r="K273" s="17" t="s">
-        <v>5059</v>
+        <v>5060</v>
       </c>
       <c r="L273" s="13" t="s">
-        <v>5077</v>
+        <v>5078</v>
       </c>
       <c r="M273" s="18" t="s">
-        <v>5060</v>
+        <v>5061</v>
       </c>
       <c r="N273" s="13" t="s">
-        <v>5078</v>
+        <v>5079</v>
       </c>
       <c r="O273" s="18" t="s">
-        <v>5061</v>
+        <v>5062</v>
       </c>
       <c r="P273" s="13" t="s">
-        <v>5080</v>
+        <v>5081</v>
       </c>
       <c r="Q273" s="18" t="s">
-        <v>5062</v>
+        <v>5063</v>
       </c>
       <c r="R273" s="13" t="s">
-        <v>5081</v>
+        <v>5082</v>
       </c>
       <c r="S273" s="18" t="s">
-        <v>5063</v>
+        <v>5064</v>
       </c>
       <c r="T273" s="13" t="s">
-        <v>5082</v>
+        <v>5083</v>
       </c>
       <c r="U273" s="18" t="s">
-        <v>5064</v>
+        <v>5065</v>
       </c>
       <c r="V273" s="13" t="s">
-        <v>5083</v>
+        <v>5084</v>
       </c>
     </row>
     <row r="274" spans="1:22">
@@ -59016,10 +59432,10 @@
         <v>貪婪洞窟：重生是一款引人入勝的地牢探險 Roguelike 手遊，作為經典《貪婪洞窟》的全新重製與進化，它邀請所有渴望探索未知與禁忌的勇士，踏上這場智慧與膽識的極限試煉！遊戲保留了原作的核心玩法，並全面升級了裝備、天賦、秘術和道具系統。每一次冒險都充滿不確定性，錯綜複雜的地形、隱秘的符文與潛伏的怪物皆為隨機生成，每次探索都是全新的體驗。玩家可利用環境、天賦與裝備的巧妙結合，在黑暗中謀求一線生機。遊戲內常有兌換碼與禮包碼可供玩家領取，配合快速安全的代儲值服務，讓你的冒險之旅更加順暢。</v>
       </c>
       <c r="F274" s="34" t="s">
-        <v>5011</v>
+        <v>5012</v>
       </c>
       <c r="G274" s="13" t="s">
-        <v>5012</v>
+        <v>5013</v>
       </c>
       <c r="H274" s="13" t="s">
         <v>2625</v>
@@ -59028,22 +59444,22 @@
         <v>4368</v>
       </c>
       <c r="K274" s="17" t="s">
-        <v>5013</v>
+        <v>5014</v>
       </c>
       <c r="L274" s="13" t="s">
-        <v>5014</v>
+        <v>5015</v>
       </c>
       <c r="M274" s="18" t="s">
-        <v>5015</v>
+        <v>5016</v>
       </c>
       <c r="N274" s="13" t="s">
-        <v>5016</v>
+        <v>5017</v>
       </c>
       <c r="O274" s="18" t="s">
-        <v>5017</v>
+        <v>5018</v>
       </c>
       <c r="P274" s="13" t="s">
-        <v>5018</v>
+        <v>5019</v>
       </c>
     </row>
     <row r="275" spans="1:22">
@@ -59064,103 +59480,157 @@
         <v>敵軍來襲，指揮官你在哪！快來體驗結合塔防與爽快射擊的《小兵特攻隊》！遊戲主打Q版軍事風格，讓你輕鬆佈陣、火力全開，享受爆擊清場的無盡快感。別再慢慢農資源了，趕快尋找最新的禮包碼和兌換碼，領取海量福利，讓你的軍團戰力一飛沖天！想要快速升級，體驗最頂級的火力配置嗎？選擇最方便的代儲值服務，不僅提供快速安全的交易，更能讓你專注於衝鋒陷陣的樂趣，帶領你的小兵成為戰場傳奇！</v>
       </c>
       <c r="F275" s="34" t="s">
-        <v>5053</v>
+        <v>5054</v>
       </c>
       <c r="G275" s="13" t="s">
-        <v>5054</v>
+        <v>5055</v>
       </c>
       <c r="H275" s="13" t="s">
-        <v>5055</v>
+        <v>5056</v>
       </c>
       <c r="I275" s="13" t="s">
         <v>2625</v>
       </c>
       <c r="J275" s="13" t="s">
-        <v>5056</v>
+        <v>5057</v>
       </c>
       <c r="K275" s="18" t="s">
-        <v>5051</v>
+        <v>5052</v>
       </c>
       <c r="L275" s="13" t="s">
-        <v>5052</v>
+        <v>5053</v>
       </c>
       <c r="M275" s="18" t="s">
-        <v>5069</v>
+        <v>5070</v>
       </c>
       <c r="N275" s="13" t="s">
-        <v>5070</v>
+        <v>5071</v>
       </c>
     </row>
     <row r="276" spans="1:22">
       <c r="A276" s="13" t="str">
         <f>IF(games!A276="", "", games!A276)</f>
-        <v/>
+        <v>星塔旅人</v>
       </c>
       <c r="C276" s="13" t="str">
         <f>IF(A276="","", "giftcodesbanner/" &amp; A276 &amp; "-禮包碼.jpg")</f>
-        <v/>
+        <v>giftcodesbanner/星塔旅人-禮包碼.jpg</v>
       </c>
       <c r="D276" s="13" t="str">
         <f>IF(A276="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A276)</f>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=星塔旅人</v>
       </c>
       <c r="E276" s="14" t="str">
         <f>IF(games!I276&lt;&gt;"", games!I276, "")</f>
-        <v/>
+        <v>由艾瑞爾網路代理的銀河冒險 RPG《星塔旅人》正式登場！這趟星際之旅，你將化身為「星之活體」的持有者，與眾多獨具魅力的「旅人」相遇，共同踏上尋找銀河之心「星源晶核」的冒險。遊戲主打 Roguelike 要素與高自由度的戰鬥系統，讓每一次探索都充滿未知驚喜。為了讓各位玩家能更快養成心儀的角色，記得隨時關注官方釋出的最新兌換碼與禮包碼資訊。當然，若想在起跑點就遙遙領先，最方便的代儲值服務能提供您快速安全的課金管道，讓您的銀河霸業無後顧之憂！</v>
+      </c>
+      <c r="F276" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="G276" s="13" t="s">
+        <v>4827</v>
+      </c>
+      <c r="K276" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="L276" s="13" t="s">
+        <v>4827</v>
       </c>
     </row>
     <row r="277" spans="1:22">
       <c r="A277" s="13" t="str">
         <f>IF(games!A277="", "", games!A277)</f>
-        <v/>
+        <v>卡厄斯夢境</v>
       </c>
       <c r="C277" s="13" t="str">
         <f>IF(A277="","", "giftcodesbanner/" &amp; A277 &amp; "-禮包碼.jpg")</f>
-        <v/>
+        <v>giftcodesbanner/卡厄斯夢境-禮包碼.jpg</v>
       </c>
       <c r="D277" s="13" t="str">
         <f>IF(A277="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A277)</f>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=卡厄斯夢境</v>
       </c>
       <c r="E277" s="14" t="str">
         <f>IF(games!I277&lt;&gt;"", games!I277, "")</f>
-        <v/>
+        <v>Smilegate 最新力作，收集型 2D 回合制 RPG《卡厄斯夢境》來襲！遊戲以其精緻的 Live 2D 動態角色與深刻的世界觀，帶領玩家進入一場善惡界線模糊的奇幻冒險。在這個瀕臨毀滅的世界中，你將與各具特色的英雄們並肩作戰，對抗侵蝕一切的「噩夢」。遊戲策略性極高，考驗玩家的隊伍配置與戰術運用。想讓你的英雄們戰力飆升？別忘了尋找最新的兌換碼與禮包碼福利。若想更有效率地培養隊伍，選擇專業的代儲值服務，享受快速安全的交易，讓你在夢境中暢行無阻。</v>
+      </c>
+      <c r="F277" s="17" t="s">
+        <v>5109</v>
+      </c>
+      <c r="G277" s="13" t="s">
+        <v>5110</v>
+      </c>
+      <c r="H277" s="13" t="s">
+        <v>2625</v>
+      </c>
+      <c r="I277" s="13" t="s">
+        <v>4368</v>
+      </c>
+      <c r="K277" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="L277" s="13" t="s">
+        <v>4827</v>
       </c>
     </row>
     <row r="278" spans="1:22">
       <c r="A278" s="13" t="str">
         <f>IF(games!A278="", "", games!A278)</f>
-        <v/>
+        <v>星痕共鳴</v>
       </c>
       <c r="C278" s="13" t="str">
         <f>IF(A278="","", "giftcodesbanner/" &amp; A278 &amp; "-禮包碼.jpg")</f>
-        <v/>
+        <v>giftcodesbanner/星痕共鳴-禮包碼.jpg</v>
       </c>
       <c r="D278" s="13" t="str">
         <f>IF(A278="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A278)</f>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=星痕共鳴</v>
       </c>
       <c r="E278" s="14" t="str">
         <f>IF(games!I278&lt;&gt;"", games!I278, "")</f>
-        <v/>
+        <v>全新星緣卡牌 RPG《星痕共鳴》，邀你一同編織命運的篇章。遊戲擁有宏大的世界觀與超過百萬字的豐富劇情，玩家將扮演「星源之主」，與眾多「星痕者」締結羈絆，共同對抗虛空的威脅。獨特的「星盤」系統與高策略性的卡牌戰鬥，讓每場對決都充滿變數。想要輕鬆推圖、快速成長？記得在各大社群與論壇尋找隱藏的兌換碼與禮包碼，領取豐厚資源。如果想快人一步，最聰明的選擇就是尋找可靠的代儲值管道，提供您快速安全的支援，讓你的冒險旅程更加順遂。</v>
+      </c>
+      <c r="F278" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="G278" s="13" t="s">
+        <v>4827</v>
+      </c>
+      <c r="K278" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="L278" s="13" t="s">
+        <v>4827</v>
       </c>
     </row>
     <row r="279" spans="1:22">
       <c r="A279" s="13" t="str">
         <f>IF(games!A279="", "", games!A279)</f>
-        <v/>
+        <v>二重螺旋</v>
       </c>
       <c r="C279" s="13" t="str">
         <f>IF(A279="","", "giftcodesbanner/" &amp; A279 &amp; "-禮包碼.jpg")</f>
-        <v/>
+        <v>giftcodesbanner/二重螺旋-禮包碼.jpg</v>
       </c>
       <c r="D279" s="13" t="str">
         <f>IF(A279="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A279)</f>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=二重螺旋</v>
       </c>
       <c r="E279" s="14" t="str">
         <f>IF(games!I279&lt;&gt;"", games!I279, "")</f>
-        <v/>
+        <v>備受矚目的 3D 動作 RPG《二重螺旋》強勢來襲！本作主打高速、爽快的戰鬥體驗，玩家將在一個近未來科幻世界中，扮演擁有特殊能力的「適格者」，探索神秘的「深淵」。遊戲強調華麗的連擊與多樣化的武器系統，你可以自由切換遠近程攻擊，打出屬於自己的戰鬥風格。為了讓你的探索之路更加順利，官方會不定期發放福利兌換碼與禮包碼，千萬別錯過。當然，面對強大的敵人，尋求專業的代儲值協助，以快速安全的方式強化戰力，絕對是高效的致勝關鍵。</v>
+      </c>
+      <c r="F279" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="G279" s="13" t="s">
+        <v>4827</v>
+      </c>
+      <c r="K279" s="17" t="s">
+        <v>4828</v>
+      </c>
+      <c r="L279" s="13" t="s">
+        <v>4827</v>
       </c>
     </row>
     <row r="280" spans="1:22">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7495" uniqueCount="5131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7501" uniqueCount="5135">
   <si>
     <t>Facebook</t>
   </si>
@@ -19743,6 +19743,22 @@
   </si>
   <si>
     <t>開業大吉燦金閃碟套裝</t>
+  </si>
+  <si>
+    <t>RR1475</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPEN2025</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP999</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -59351,7 +59367,7 @@
         <v>5067</v>
       </c>
     </row>
-    <row r="273" spans="1:22">
+    <row r="273" spans="1:25">
       <c r="A273" s="13" t="str">
         <f>IF(games!A273="", "", games!A273)</f>
         <v>盜夢英雄2：幻野</v>
@@ -59414,7 +59430,7 @@
         <v>5084</v>
       </c>
     </row>
-    <row r="274" spans="1:22">
+    <row r="274" spans="1:25">
       <c r="A274" s="13" t="str">
         <f>IF(games!A274="", "", games!A274)</f>
         <v>貪婪洞窟：重生</v>
@@ -59462,7 +59478,7 @@
         <v>5019</v>
       </c>
     </row>
-    <row r="275" spans="1:22">
+    <row r="275" spans="1:25">
       <c r="A275" s="13" t="str">
         <f>IF(games!A275="", "", games!A275)</f>
         <v>小兵特攻隊</v>
@@ -59506,8 +59522,26 @@
       <c r="N275" s="13" t="s">
         <v>5071</v>
       </c>
-    </row>
-    <row r="276" spans="1:22">
+      <c r="O275" s="18" t="s">
+        <v>5131</v>
+      </c>
+      <c r="Q275" s="18" t="s">
+        <v>5132</v>
+      </c>
+      <c r="S275" s="18" t="s">
+        <v>5133</v>
+      </c>
+      <c r="U275" s="18" t="s">
+        <v>2056</v>
+      </c>
+      <c r="W275" s="18" t="s">
+        <v>4575</v>
+      </c>
+      <c r="Y275" s="18" t="s">
+        <v>5134</v>
+      </c>
+    </row>
+    <row r="276" spans="1:25">
       <c r="A276" s="13" t="str">
         <f>IF(games!A276="", "", games!A276)</f>
         <v>星塔旅人</v>
@@ -59537,7 +59571,7 @@
         <v>4827</v>
       </c>
     </row>
-    <row r="277" spans="1:22">
+    <row r="277" spans="1:25">
       <c r="A277" s="13" t="str">
         <f>IF(games!A277="", "", games!A277)</f>
         <v>卡厄斯夢境</v>
@@ -59573,7 +59607,7 @@
         <v>4827</v>
       </c>
     </row>
-    <row r="278" spans="1:22">
+    <row r="278" spans="1:25">
       <c r="A278" s="13" t="str">
         <f>IF(games!A278="", "", games!A278)</f>
         <v>星痕共鳴</v>
@@ -59603,7 +59637,7 @@
         <v>4827</v>
       </c>
     </row>
-    <row r="279" spans="1:22">
+    <row r="279" spans="1:25">
       <c r="A279" s="13" t="str">
         <f>IF(games!A279="", "", games!A279)</f>
         <v>二重螺旋</v>
@@ -59633,7 +59667,7 @@
         <v>4827</v>
       </c>
     </row>
-    <row r="280" spans="1:22">
+    <row r="280" spans="1:25">
       <c r="A280" s="13" t="str">
         <f>IF(games!A280="", "", games!A280)</f>
         <v/>
@@ -59651,7 +59685,7 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="1:22">
+    <row r="281" spans="1:25">
       <c r="A281" s="13" t="str">
         <f>IF(games!A281="", "", games!A281)</f>
         <v/>
@@ -59669,7 +59703,7 @@
         <v/>
       </c>
     </row>
-    <row r="282" spans="1:22">
+    <row r="282" spans="1:25">
       <c r="A282" s="13" t="str">
         <f>IF(games!A282="", "", games!A282)</f>
         <v/>
@@ -59687,7 +59721,7 @@
         <v/>
       </c>
     </row>
-    <row r="283" spans="1:22">
+    <row r="283" spans="1:25">
       <c r="A283" s="13" t="str">
         <f>IF(games!A283="", "", games!A283)</f>
         <v/>
@@ -59705,7 +59739,7 @@
         <v/>
       </c>
     </row>
-    <row r="284" spans="1:22">
+    <row r="284" spans="1:25">
       <c r="A284" s="13" t="str">
         <f>IF(games!A284="", "", games!A284)</f>
         <v/>
@@ -59723,7 +59757,7 @@
         <v/>
       </c>
     </row>
-    <row r="285" spans="1:22">
+    <row r="285" spans="1:25">
       <c r="A285" s="13" t="str">
         <f>IF(games!A285="", "", games!A285)</f>
         <v/>
@@ -59741,7 +59775,7 @@
         <v/>
       </c>
     </row>
-    <row r="286" spans="1:22">
+    <row r="286" spans="1:25">
       <c r="A286" s="13" t="str">
         <f>IF(games!A286="", "", games!A286)</f>
         <v/>
@@ -59759,7 +59793,7 @@
         <v/>
       </c>
     </row>
-    <row r="287" spans="1:22">
+    <row r="287" spans="1:25">
       <c r="A287" s="13" t="str">
         <f>IF(games!A287="", "", games!A287)</f>
         <v/>
@@ -59777,7 +59811,7 @@
         <v/>
       </c>
     </row>
-    <row r="288" spans="1:22">
+    <row r="288" spans="1:25">
       <c r="A288" s="13" t="str">
         <f>IF(games!A288="", "", games!A288)</f>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7501" uniqueCount="5135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7505" uniqueCount="5143">
   <si>
     <t>Facebook</t>
   </si>
@@ -19758,6 +19758,38 @@
   </si>
   <si>
     <t>VIP999</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOSSGIFT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IAMBOSS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>星之沙*100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>華美的鑲邊*5+朵拉*5000+前倍的旅行傳記*5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://stellasora.stargazer-games.com/redemption</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>到上方遊戲兌換網站</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>輸入UID之後輸入序號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點確認兌換後到遊戲內信箱領取</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -59558,17 +59590,29 @@
         <f>IF(games!I276&lt;&gt;"", games!I276, "")</f>
         <v>由艾瑞爾網路代理的銀河冒險 RPG《星塔旅人》正式登場！這趟星際之旅，你將化身為「星之活體」的持有者，與眾多獨具魅力的「旅人」相遇，共同踏上尋找銀河之心「星源晶核」的冒險。遊戲主打 Roguelike 要素與高自由度的戰鬥系統，讓每一次探索都充滿未知驚喜。為了讓各位玩家能更快養成心儀的角色，記得隨時關注官方釋出的最新兌換碼與禮包碼資訊。當然，若想在起跑點就遙遙領先，最方便的代儲值服務能提供您快速安全的課金管道，讓您的銀河霸業無後顧之憂！</v>
       </c>
-      <c r="F276" s="17" t="s">
-        <v>4828</v>
+      <c r="F276" s="100" t="s">
+        <v>5139</v>
       </c>
       <c r="G276" s="13" t="s">
-        <v>4827</v>
+        <v>5140</v>
+      </c>
+      <c r="H276" s="13" t="s">
+        <v>5141</v>
+      </c>
+      <c r="I276" s="13" t="s">
+        <v>5142</v>
       </c>
       <c r="K276" s="17" t="s">
-        <v>4828</v>
+        <v>5135</v>
       </c>
       <c r="L276" s="13" t="s">
-        <v>4827</v>
+        <v>5137</v>
+      </c>
+      <c r="M276" s="18" t="s">
+        <v>5136</v>
+      </c>
+      <c r="N276" s="13" t="s">
+        <v>5138</v>
       </c>
     </row>
     <row r="277" spans="1:25">
@@ -61811,8 +61855,9 @@
     <hyperlink ref="F236" r:id="rId3" display="https://ref.gamer.com.tw/redir.php?url=https%3A%2F%2Fcoupon.netmarble.com%2Ftskgb"/>
     <hyperlink ref="F245" r:id="rId4"/>
     <hyperlink ref="F265" r:id="rId5"/>
+    <hyperlink ref="F276" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -19699,14 +19699,6 @@
     <t>電馭通行證</t>
   </si>
   <si>
-    <t>《電馭跑酷》這不是你阿嬤的公園散步，這是一場高速、玩命的都市障礙賽。玩家將扮演反抗軍的跑酷精英，在高聳入雲的摩天大樓間飛簷走壁，閃避企業保全的致命追擊與無人機的雷射掃描。遊戲主打流暢到不科學的動作系統，結合了滑鏟、二段跳與牆面奔跑，每一次的跳躍都考驗著你的反應極限。想在起跑點就領先那些菜鳥？別忘了上網找最新的「兌換碼」，輸入後就能拿到初期資源。當然，遊戲內的「禮包碼」也別錯過，各種稀有造型等你解鎖。想要更快地強化你的裝備，尋求專業的「代儲值」服務是個聰明的捷徑，保證快速安全讓你無後顧之憂地稱霸這座數位牢籠。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>《火焰紋章Shadows》是的，你沒看錯，你的隊伍中……藏著一名背叛者！玩家在運籌帷幄、指揮英雄走位的同時，還必須在有限的回合內，透過戰鬥中的蛛絲馬跡找出誰是「影子」。本作繼承了系列的精美立繪與深度職業系統，但每場戰鬥都充滿了猜忌與不安。想在開局就取得優勢，揪出內鬼？記得先領取官方發送的「兌換碼」，充實你的兵源。隨著進度推進，各種隱藏的「禮包碼」更是兵家必爭之地。為了更有效率地培養你的主力部隊，許多老玩家會選擇「代儲值」來購買稀有資源，選擇信譽良好、保證「快速安全」的服務，才能讓你專心應對眼前的戰局與背後的謊言。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>2600秘寶石</t>
   </si>
   <si>
@@ -19735,6 +19727,14 @@
   </si>
   <si>
     <t>最新價格請洽Line@</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《電馭跑酷》這不是你阿嬤的公園散步，這是一場高速、玩命的都市障礙賽。玩家將扮演反抗軍的跑酷精英，在高聳入雲的摩天大樓間飛簷走壁，閃避企業保全的致命追擊。遊戲主打流暢到不科學的動作系統，結合了滑鏟、二段跳與牆面奔跑，每一次的跳躍都考驗著你的反應極限。想在起跑點就領先那些菜鳥？別忘了上網找最新的「兌換碼」，輸入後就能拿到初期資源。當然，遊戲內的「禮包碼」也別錯過。想要更快地強化你的裝備，尋求專業的「代儲值」服務是個聰明的捷徑，保證快速安全讓你無後顧之憂地稱霸這座數位牢籠。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《火焰紋章Shadows》你的隊伍中藏著一名背叛者！玩家在運籌帷幄同時，還必須在有限的回合內，透過戰鬥中的蛛絲馬跡找出誰是「影子」。本作繼承了系列的精美立繪與深度職業系統，但每場戰鬥都充滿了猜忌與不安。想在開局就取得優勢，揪出內鬼？記得先領取官方發送的兌換碼，充實你的兵源。隨著進度推進，各種隱藏的禮包碼更是兵家必爭之地。為了更有效率地培養你的主力部隊，許多老玩家會選擇「代儲值」來購買稀有資源，選擇信譽良好、保證快速安全的服務，才能讓你專心應對眼前的戰局與背後的謊言。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -39688,7 +39688,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/電馭跑酷.html</v>
       </c>
       <c r="I280" s="67" t="s">
-        <v>5160</v>
+        <v>5170</v>
       </c>
       <c r="J280" s="1" t="s">
         <v>5153</v>
@@ -39733,7 +39733,7 @@
         <v>248</v>
       </c>
       <c r="X280" s="2" t="s">
-        <v>5171</v>
+        <v>5169</v>
       </c>
     </row>
     <row r="281" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
@@ -39761,64 +39761,64 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/火焰紋章Shadows.html</v>
       </c>
       <c r="I281" s="67" t="s">
-        <v>5161</v>
+        <v>5171</v>
       </c>
       <c r="J281" s="1" t="s">
-        <v>5162</v>
+        <v>5160</v>
       </c>
       <c r="K281" s="59">
         <v>1549</v>
       </c>
       <c r="L281" s="1" t="s">
-        <v>5163</v>
+        <v>5161</v>
       </c>
       <c r="M281" s="59">
         <v>1030</v>
       </c>
       <c r="N281" s="1" t="s">
-        <v>5164</v>
+        <v>5162</v>
       </c>
       <c r="O281" s="59">
         <v>673</v>
       </c>
       <c r="P281" s="1" t="s">
-        <v>5165</v>
+        <v>5163</v>
       </c>
       <c r="Q281" s="59">
         <v>344</v>
       </c>
       <c r="R281" s="1" t="s">
-        <v>5166</v>
+        <v>5164</v>
       </c>
       <c r="S281" s="59">
         <v>157</v>
       </c>
       <c r="T281" s="1" t="s">
-        <v>5167</v>
+        <v>5165</v>
       </c>
       <c r="U281" s="59">
         <v>81</v>
       </c>
       <c r="V281" s="1" t="s">
-        <v>5168</v>
+        <v>5166</v>
       </c>
       <c r="W281" s="59">
         <v>17</v>
       </c>
       <c r="X281" s="1" t="s">
-        <v>5169</v>
+        <v>5167</v>
       </c>
       <c r="Y281" s="59">
         <v>244</v>
       </c>
       <c r="Z281" s="1" t="s">
-        <v>5170</v>
+        <v>5168</v>
       </c>
       <c r="AA281" s="59">
         <v>139</v>
       </c>
       <c r="AB281" s="2" t="s">
-        <v>5171</v>
+        <v>5169</v>
       </c>
     </row>
     <row r="282" spans="1:29" ht="22.5" customHeight="1">
@@ -59735,7 +59735,7 @@
       </c>
       <c r="E280" s="11" t="str">
         <f>IF(games!I280&lt;&gt;"", games!I280, "")</f>
-        <v>《電馭跑酷》這不是你阿嬤的公園散步，這是一場高速、玩命的都市障礙賽。玩家將扮演反抗軍的跑酷精英，在高聳入雲的摩天大樓間飛簷走壁，閃避企業保全的致命追擊與無人機的雷射掃描。遊戲主打流暢到不科學的動作系統，結合了滑鏟、二段跳與牆面奔跑，每一次的跳躍都考驗著你的反應極限。想在起跑點就領先那些菜鳥？別忘了上網找最新的「兌換碼」，輸入後就能拿到初期資源。當然，遊戲內的「禮包碼」也別錯過，各種稀有造型等你解鎖。想要更快地強化你的裝備，尋求專業的「代儲值」服務是個聰明的捷徑，保證快速安全讓你無後顧之憂地稱霸這座數位牢籠。</v>
+        <v>《電馭跑酷》這不是你阿嬤的公園散步，這是一場高速、玩命的都市障礙賽。玩家將扮演反抗軍的跑酷精英，在高聳入雲的摩天大樓間飛簷走壁，閃避企業保全的致命追擊。遊戲主打流暢到不科學的動作系統，結合了滑鏟、二段跳與牆面奔跑，每一次的跳躍都考驗著你的反應極限。想在起跑點就領先那些菜鳥？別忘了上網找最新的「兌換碼」，輸入後就能拿到初期資源。當然，遊戲內的「禮包碼」也別錯過。想要更快地強化你的裝備，尋求專業的「代儲值」服務是個聰明的捷徑，保證快速安全讓你無後顧之憂地稱霸這座數位牢籠。</v>
       </c>
       <c r="F280" s="14" t="s">
         <v>4811</v>
@@ -59765,7 +59765,7 @@
       </c>
       <c r="E281" s="11" t="str">
         <f>IF(games!I281&lt;&gt;"", games!I281, "")</f>
-        <v>《火焰紋章Shadows》是的，你沒看錯，你的隊伍中……藏著一名背叛者！玩家在運籌帷幄、指揮英雄走位的同時，還必須在有限的回合內，透過戰鬥中的蛛絲馬跡找出誰是「影子」。本作繼承了系列的精美立繪與深度職業系統，但每場戰鬥都充滿了猜忌與不安。想在開局就取得優勢，揪出內鬼？記得先領取官方發送的「兌換碼」，充實你的兵源。隨著進度推進，各種隱藏的「禮包碼」更是兵家必爭之地。為了更有效率地培養你的主力部隊，許多老玩家會選擇「代儲值」來購買稀有資源，選擇信譽良好、保證「快速安全」的服務，才能讓你專心應對眼前的戰局與背後的謊言。</v>
+        <v>《火焰紋章Shadows》你的隊伍中藏著一名背叛者！玩家在運籌帷幄同時，還必須在有限的回合內，透過戰鬥中的蛛絲馬跡找出誰是「影子」。本作繼承了系列的精美立繪與深度職業系統，但每場戰鬥都充滿了猜忌與不安。想在開局就取得優勢，揪出內鬼？記得先領取官方發送的兌換碼，充實你的兵源。隨著進度推進，各種隱藏的禮包碼更是兵家必爭之地。為了更有效率地培養你的主力部隊，許多老玩家會選擇「代儲值」來購買稀有資源，選擇信譽良好、保證快速安全的服務，才能讓你專心應對眼前的戰局與背後的謊言。</v>
       </c>
       <c r="F281" s="14" t="s">
         <v>4811</v>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -39735,6 +39735,9 @@
       <c r="X280" s="2" t="s">
         <v>5169</v>
       </c>
+      <c r="Y280" s="38">
+        <v>666</v>
+      </c>
     </row>
     <row r="281" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A281" s="55" t="s">
@@ -39819,6 +39822,9 @@
       </c>
       <c r="AB281" s="2" t="s">
         <v>5169</v>
+      </c>
+      <c r="AC281" s="38">
+        <v>666</v>
       </c>
     </row>
     <row r="282" spans="1:29" ht="22.5" customHeight="1">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7543" uniqueCount="5172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7613" uniqueCount="5225">
   <si>
     <t>Facebook</t>
   </si>
@@ -19737,12 +19737,199 @@
     <t>《火焰紋章Shadows》你的隊伍中藏著一名背叛者！玩家在運籌帷幄同時，還必須在有限的回合內，透過戰鬥中的蛛絲馬跡找出誰是「影子」。本作繼承了系列的精美立繪與深度職業系統，但每場戰鬥都充滿了猜忌與不安。想在開局就取得優勢，揪出內鬼？記得先領取官方發送的兌換碼，充實你的兵源。隨著進度推進，各種隱藏的禮包碼更是兵家必爭之地。為了更有效率地培養你的主力部隊，許多老玩家會選擇「代儲值」來購買稀有資源，選擇信譽良好、保證快速安全的服務，才能讓你專心應對眼前的戰局與背後的謊言。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>1980水晶</t>
+  </si>
+  <si>
+    <t>980水晶</t>
+  </si>
+  <si>
+    <t>死靈之書月禮包</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/StoneAgePW.TC</t>
+  </si>
+  <si>
+    <t>https://stoneage.netmarble.com/tc/?fbclid=IwY2xjawNpUptleHRuA2FlbQIxMABicmlkETF3S1BCMXJDRHZjbVRVUk1zAR4nTTOPlNXGxdlWskAfF35YQMP4uZD2bWuuccP6PWKJPn95mlZCXuXzxX2uUQ_aem_x86QOulC2aS21RXQAoKSSw</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E7%9F%B3%E5%99%A8%E6%99%82%E4%BB%A3-%E5%AF%B5%E7%89%A9%E4%B8%96%E7%95%8C/id6737408689?l=zh</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/BluePlanetBK</t>
+  </si>
+  <si>
+    <t>https://www.blueplanetbk.com/?fbclid=IwY2xjawMuDaxleHRuA2FlbQIxMABicmlkETFTc2N5eG0wQUcyQ1NCUmNlAR5ewHwDUlAZAVZoCzJ1dv2zYlHNQfML3R3DAQ5UPsbCxBJzguTmcX9-cQfoYw_aem_AsL3fnuAl-fsLHsaYYGz7Q</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E8%94%9A%E8%97%8D%E6%98%9F%E7%90%83-%E5%9C%8B%E7%8E%8B%E5%BE%88%E5%BF%99/id6749769179</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/honeytraptw</t>
+  </si>
+  <si>
+    <t>https://lmsg.onefungame.com/act/pre?utm=fbtsj&amp;fbclid=IwY2xjawNpU2JleHRuA2FlbQIxMABicmlkETEwdDJpT3RaN1hVY2w2U09RAR7ForkiEMoPXyIVmO6wgrqIx4fdyO9Y4hzZeH9U1npq42jol8EiVMMYMFexJw_aem_QudBmxYKO6RpqEpMpR6tuw</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E8%83%B8%E6%87%B7%E4%B8%89%E5%9C%8B-%E7%BE%8E%E4%BA%BA%E8%A8%88/id6751325286?pid=fbtsj</t>
+  </si>
+  <si>
+    <t>1650禮包</t>
+  </si>
+  <si>
+    <t>1320禮包</t>
+  </si>
+  <si>
+    <t>1000禮包</t>
+  </si>
+  <si>
+    <t>820禮包</t>
+  </si>
+  <si>
+    <t>430禮包</t>
+  </si>
+  <si>
+    <t>99.99美禮包</t>
+  </si>
+  <si>
+    <t>59.99美禮包</t>
+  </si>
+  <si>
+    <t>49.99美禮包</t>
+  </si>
+  <si>
+    <t>29.99美禮包</t>
+  </si>
+  <si>
+    <t>24.99美禮包</t>
+  </si>
+  <si>
+    <t>14.99美禮包</t>
+  </si>
+  <si>
+    <t>9.99美禮包</t>
+  </si>
+  <si>
+    <t>4.99美禮包</t>
+  </si>
+  <si>
+    <t>石器時代：寵物世界</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔚藍星球：國王很忙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胸懷三國：美人計</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.netmarble.stonkey</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.blueplanetm.gp&amp;shortlink=mqju4p0s&amp;c=xx_250918_fb_02&amp;pid=fb%E7%A4%BE%E7%BE%A4&amp;af_xp=custom&amp;source_caller=ui</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.lmsg.twgp&amp;pcampaignid=&amp;utm_source=fbtsj&amp;referrer=utm_source%3Dfbtsj%26click_id%3D0a59691a-1a07-4136-9587-ed1a409fffd9_fbtsj</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>經典IP《石器時代》正版授權的回合制策略大作回來啦！本作完美還原端遊，上百種寵物任你策略搭配，更支援手機、電腦多端互通，隨時都能上線抓寵。還在煩惱找不到最新的兌換碼跟禮包碼嗎？別擔心，我們都幫你準備好了！現在就跟上尼斯大陸的冒險，體驗最原汁原味的感動，需要代儲值也沒問題，絕對快速安全，讓你輕鬆跟上夥伴們的腳步，重溫年少的夢中情寵！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025年最值得一玩的全新萌系塔防手遊來啦！邪惡哥布林入侵，身為國王守護者的你，必須招募英雄抵禦入侵。遊戲主打英雄2合1加上局內3重隨機玩法，每局都有上百種策略搭配，就算是休閒玩家也能3秒上手！還在網路上苦苦搜尋可用的禮包碼和兌換碼嗎？別浪費時間了！想要快速升級，享受最爽快的割草感，尋找快速安全的代儲值服務會是你最好的選擇，立即為了蔚藍星球而戰！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>美少女三國RPG手遊參上！遊戲擁有眾多經典三國名將，搭配緊張刺激的養成戰鬥系統，讓玩家可以體驗高潮連擊的激爽和無限養成的快樂。獨特的武將風格立繪，在既定特色上增添更多風味，絕對是視覺饗宴。還在為了找不到最新的禮包碼而煩惱嗎？想要輕鬆養成武將，解鎖所有外觀，最聰明的方式就是尋找快速安全的代儲值管道，立即領取你的兌換碼福利，在三國世界中無往不利！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALMVIP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AWKLLAUNCH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*100+火神能量*4+金幣*50000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點遊戲內左上角頭像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>彈出視窗下方「Redeem Code」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點擊左上角頭像，進入設定介面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>招募帖*10、古玉*300</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新手禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>再點擊介面左下方的禮包碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在輸入框中輸入您的禮包碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>vip777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>vip888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WildsCommunity666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dreamtogether</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*500+金幣*18888+許願的時之輪*1+定軌的時之輪*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*588+金幣*20000+許願的時之輪*3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*888+金幣*1888+許願的時之輪*2+定軌的時之輪*2+突破藥水*200</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*688+金幣*20258+許願的時之輪*2+史詩璀璨魂晶*50+經驗卷軸*5000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -19835,6 +20022,13 @@
       <family val="1"/>
       <charset val="136"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="5">
@@ -20081,7 +20275,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -20283,6 +20477,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -39444,54 +39641,50 @@
       <c r="I277" s="39" t="s">
         <v>5088</v>
       </c>
-      <c r="J277" s="53" t="s">
-        <v>4988</v>
-      </c>
-      <c r="K277" s="55">
-        <v>2533</v>
-      </c>
-      <c r="L277" s="53" t="s">
-        <v>1676</v>
-      </c>
-      <c r="M277" s="55">
-        <v>1325</v>
-      </c>
-      <c r="N277" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="O277" s="55">
-        <v>783</v>
-      </c>
-      <c r="P277" s="53" t="s">
-        <v>1679</v>
-      </c>
-      <c r="Q277" s="55">
-        <v>530</v>
-      </c>
-      <c r="R277" s="53" t="s">
-        <v>153</v>
-      </c>
-      <c r="S277" s="55">
-        <v>388</v>
-      </c>
-      <c r="T277" s="53" t="s">
-        <v>1680</v>
-      </c>
-      <c r="U277" s="55">
-        <v>261</v>
-      </c>
-      <c r="V277" s="53" t="s">
-        <v>1682</v>
-      </c>
-      <c r="W277" s="55">
-        <v>141</v>
-      </c>
-      <c r="X277" s="53" t="s">
-        <v>1683</v>
-      </c>
-      <c r="Y277" s="55">
-        <v>28</v>
-      </c>
+      <c r="J277" s="1" t="s">
+        <v>5008</v>
+      </c>
+      <c r="K277" s="59">
+        <v>2655</v>
+      </c>
+      <c r="L277" s="1" t="s">
+        <v>5009</v>
+      </c>
+      <c r="M277" s="59">
+        <v>1389</v>
+      </c>
+      <c r="N277" s="1" t="s">
+        <v>5172</v>
+      </c>
+      <c r="O277" s="59">
+        <v>821</v>
+      </c>
+      <c r="P277" s="1" t="s">
+        <v>5173</v>
+      </c>
+      <c r="Q277" s="59">
+        <v>407</v>
+      </c>
+      <c r="R277" s="1" t="s">
+        <v>5012</v>
+      </c>
+      <c r="S277" s="59">
+        <v>147</v>
+      </c>
+      <c r="T277" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="U277" s="59">
+        <v>29</v>
+      </c>
+      <c r="V277" s="1" t="s">
+        <v>5174</v>
+      </c>
+      <c r="W277" s="59">
+        <v>147</v>
+      </c>
+      <c r="X277" s="53"/>
+      <c r="Y277" s="55"/>
     </row>
     <row r="278" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A278" s="55" t="s">
@@ -39827,34 +40020,256 @@
         <v>666</v>
       </c>
     </row>
-    <row r="282" spans="1:29" ht="22.5" customHeight="1">
+    <row r="282" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A282" s="83" t="s">
+        <v>5197</v>
+      </c>
+      <c r="C282" s="37" t="s">
+        <v>5175</v>
+      </c>
+      <c r="D282" s="38" t="s">
+        <v>5176</v>
+      </c>
+      <c r="E282" s="38" t="s">
+        <v>5177</v>
+      </c>
       <c r="F282" s="37" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=石器時代：寵物世界</v>
+      </c>
+      <c r="G282" s="2" t="s">
+        <v>5200</v>
       </c>
       <c r="H282" s="38" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="1:29" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/石器時代：寵物世界.html</v>
+      </c>
+      <c r="I282" s="39" t="s">
+        <v>5203</v>
+      </c>
+      <c r="J282" s="1" t="s">
+        <v>4988</v>
+      </c>
+      <c r="K282" s="59">
+        <v>2655</v>
+      </c>
+      <c r="L282" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M282" s="59">
+        <v>2047</v>
+      </c>
+      <c r="N282" s="1" t="s">
+        <v>5184</v>
+      </c>
+      <c r="O282" s="59">
+        <v>1357</v>
+      </c>
+      <c r="P282" s="1" t="s">
+        <v>5185</v>
+      </c>
+      <c r="Q282" s="59">
+        <v>1085</v>
+      </c>
+      <c r="R282" s="1" t="s">
+        <v>5186</v>
+      </c>
+      <c r="S282" s="59">
+        <v>822</v>
+      </c>
+      <c r="T282" s="1" t="s">
+        <v>5187</v>
+      </c>
+      <c r="U282" s="59">
+        <v>680</v>
+      </c>
+      <c r="V282" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="W282" s="59">
+        <v>572</v>
+      </c>
+      <c r="X282" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y282" s="59">
+        <v>407</v>
+      </c>
+      <c r="Z282" s="1" t="s">
+        <v>5188</v>
+      </c>
+      <c r="AA282" s="59">
+        <v>357</v>
+      </c>
+      <c r="AB282" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="AC282" s="59">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="283" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A283" s="83" t="s">
+        <v>5198</v>
+      </c>
+      <c r="C283" s="37" t="s">
+        <v>5178</v>
+      </c>
+      <c r="D283" s="38" t="s">
+        <v>5179</v>
+      </c>
+      <c r="E283" s="38" t="s">
+        <v>5180</v>
+      </c>
       <c r="F283" s="37" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=蔚藍星球：國王很忙</v>
+      </c>
+      <c r="G283" s="2" t="s">
+        <v>5201</v>
       </c>
       <c r="H283" s="38" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="1:29" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/蔚藍星球：國王很忙.html</v>
+      </c>
+      <c r="I283" s="39" t="s">
+        <v>5204</v>
+      </c>
+      <c r="J283" s="1" t="s">
+        <v>5189</v>
+      </c>
+      <c r="K283" s="59">
+        <v>2655</v>
+      </c>
+      <c r="L283" s="1" t="s">
+        <v>5190</v>
+      </c>
+      <c r="M283" s="59">
+        <v>1644</v>
+      </c>
+      <c r="N283" s="1" t="s">
+        <v>5191</v>
+      </c>
+      <c r="O283" s="59">
+        <v>1389</v>
+      </c>
+      <c r="P283" s="1" t="s">
+        <v>5192</v>
+      </c>
+      <c r="Q283" s="59">
+        <v>821</v>
+      </c>
+      <c r="R283" s="1" t="s">
+        <v>5193</v>
+      </c>
+      <c r="S283" s="59">
+        <v>655</v>
+      </c>
+      <c r="T283" s="1" t="s">
+        <v>5194</v>
+      </c>
+      <c r="U283" s="59">
+        <v>407</v>
+      </c>
+      <c r="V283" s="1" t="s">
+        <v>5195</v>
+      </c>
+      <c r="W283" s="59">
+        <v>274</v>
+      </c>
+      <c r="X283" s="1" t="s">
+        <v>5196</v>
+      </c>
+      <c r="Y283" s="59">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="284" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A284" s="83" t="s">
+        <v>5199</v>
+      </c>
+      <c r="C284" s="37" t="s">
+        <v>5181</v>
+      </c>
+      <c r="D284" s="38" t="s">
+        <v>5182</v>
+      </c>
+      <c r="E284" s="38" t="s">
+        <v>5183</v>
+      </c>
       <c r="F284" s="37" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=胸懷三國：美人計</v>
+      </c>
+      <c r="G284" s="2" t="s">
+        <v>5202</v>
       </c>
       <c r="H284" s="38" t="str">
         <f t="shared" ref="H284:H312" si="13">IF(A284="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A284)</f>
-        <v/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=胸懷三國：美人計</v>
+      </c>
+      <c r="I284" s="39" t="s">
+        <v>5205</v>
+      </c>
+      <c r="J284" s="1" t="s">
+        <v>4988</v>
+      </c>
+      <c r="K284" s="59">
+        <v>2655</v>
+      </c>
+      <c r="L284" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M284" s="59">
+        <v>2047</v>
+      </c>
+      <c r="N284" s="1" t="s">
+        <v>5184</v>
+      </c>
+      <c r="O284" s="59">
+        <v>1357</v>
+      </c>
+      <c r="P284" s="1" t="s">
+        <v>5185</v>
+      </c>
+      <c r="Q284" s="59">
+        <v>1085</v>
+      </c>
+      <c r="R284" s="1" t="s">
+        <v>5186</v>
+      </c>
+      <c r="S284" s="59">
+        <v>822</v>
+      </c>
+      <c r="T284" s="1" t="s">
+        <v>5187</v>
+      </c>
+      <c r="U284" s="59">
+        <v>680</v>
+      </c>
+      <c r="V284" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="W284" s="59">
+        <v>572</v>
+      </c>
+      <c r="X284" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y284" s="59">
+        <v>407</v>
+      </c>
+      <c r="Z284" s="1" t="s">
+        <v>5188</v>
+      </c>
+      <c r="AA284" s="59">
+        <v>357</v>
+      </c>
+      <c r="AB284" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="AC284" s="59">
+        <v>274</v>
       </c>
     </row>
     <row r="285" spans="1:29" ht="22.5" customHeight="1">
@@ -43269,8 +43684,8 @@
     <hyperlink ref="E265" r:id="rId200"/>
     <hyperlink ref="G265" r:id="rId201"/>
     <hyperlink ref="C266" r:id="rId202"/>
-    <hyperlink ref="G266"/>
-    <hyperlink ref="E266"/>
+    <hyperlink ref="G266" display="https://play.google.com/store/apps/details?id=com.ironhidegames.kingdomrush.mp&amp;referrer=utm_source%3Dyoutube_trailer%26utm_medium%3Dvideo_description%26utm_campaign%3Dpreregister&amp;fbclid=IwY2xjawNQd0VleHRuA2FlbQIxMABicmlkETFXVWp5cHFhSmxFZG90ekszAR4uAZJuIjB"/>
+    <hyperlink ref="E266" display="https://apps.apple.com/us/app/kingdom-rush-battles-td-game/id6746510979?utm_source=youtube_announcement&amp;utm_medium=video_description&amp;utm_campaign=preregister&amp;fbclid=IwY2xjawNQd0VleHRuA2FlbQIxMABicmlkETFXVWp5cHFhSmxFZG90ekszAR7_UANYOjn8d8HOJwOwxa2wTJ0TEl4P"/>
     <hyperlink ref="D266" r:id="rId203"/>
     <hyperlink ref="E267" r:id="rId204"/>
     <hyperlink ref="C268" r:id="rId205"/>
@@ -43284,9 +43699,12 @@
     <hyperlink ref="G281" r:id="rId213"/>
     <hyperlink ref="AB281" r:id="rId214"/>
     <hyperlink ref="X280" r:id="rId215"/>
+    <hyperlink ref="G282" r:id="rId216"/>
+    <hyperlink ref="G283" r:id="rId217"/>
+    <hyperlink ref="G284" r:id="rId218"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId216"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId219"/>
 </worksheet>
 </file>
 
@@ -59294,11 +59712,11 @@
         <v>Awakenloop</v>
       </c>
       <c r="C269" s="10" t="str">
-        <f>IF(A269="","", "giftcodesbanner/" &amp; A269 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" ref="C269:C312" si="12">IF(A269="","", "giftcodesbanner/" &amp; A269 &amp; "-禮包碼.jpg")</f>
         <v>giftcodesbanner/Awakenloop-禮包碼.jpg</v>
       </c>
       <c r="D269" s="10" t="str">
-        <f>IF(A269="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A269)</f>
+        <f t="shared" ref="D269:D312" si="13">IF(A269="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A269)</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=Awakenloop</v>
       </c>
       <c r="E269" s="11" t="str">
@@ -59306,16 +59724,28 @@
         <v>《Awakenloop》是一款充滿賽博龐克風格的卡牌回合制手遊，玩家將身處一個由機器人與人類共存的末日世界。遊戲主打策略性卡牌戰鬥，每張卡牌都蘊含獨特技能，如何搭配與釋放將成為戰局關鍵。除了豐富的主線劇情，遊戲也提供多樣的副本挑戰與 PvP 模式，讓你與其他玩家一較高下。現在就加入《Awakenloop》，透過兌換碼與禮包碼獲得專屬獎勵，輕鬆提升戰力，也能使用代儲值服務快速安全地補充資源，在這片混沌的廢土上開創屬於你的新紀元。</v>
       </c>
       <c r="F269" s="14" t="s">
-        <v>4811</v>
+        <v>5210</v>
       </c>
       <c r="G269" s="10" t="s">
-        <v>4810</v>
+        <v>5211</v>
+      </c>
+      <c r="H269" s="10" t="s">
+        <v>2625</v>
+      </c>
+      <c r="I269" s="10" t="s">
+        <v>4360</v>
       </c>
       <c r="K269" s="14" t="s">
-        <v>4811</v>
+        <v>5206</v>
       </c>
       <c r="L269" s="10" t="s">
-        <v>4810</v>
+        <v>5209</v>
+      </c>
+      <c r="M269" s="15" t="s">
+        <v>5207</v>
+      </c>
+      <c r="N269" s="10" t="s">
+        <v>5208</v>
       </c>
     </row>
     <row r="270" spans="1:31">
@@ -59324,11 +59754,11 @@
         <v>Astellia</v>
       </c>
       <c r="C270" s="10" t="str">
-        <f>IF(A270="","", "giftcodesbanner/" &amp; A270 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v>giftcodesbanner/Astellia-禮包碼.jpg</v>
       </c>
       <c r="D270" s="10" t="str">
-        <f>IF(A270="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A270)</f>
+        <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=Astellia</v>
       </c>
       <c r="E270" s="11" t="str">
@@ -59354,11 +59784,11 @@
         <v>華夏千秋</v>
       </c>
       <c r="C271" s="10" t="str">
-        <f>IF(A271="","", "giftcodesbanner/" &amp; A271 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v>giftcodesbanner/華夏千秋-禮包碼.jpg</v>
       </c>
       <c r="D271" s="10" t="str">
-        <f>IF(A271="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A271)</f>
+        <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=華夏千秋</v>
       </c>
       <c r="E271" s="11" t="str">
@@ -59384,11 +59814,11 @@
         <v>萌塔娘</v>
       </c>
       <c r="C272" s="10" t="str">
-        <f>IF(A272="","", "giftcodesbanner/" &amp; A272 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v>giftcodesbanner/萌塔娘-禮包碼.jpg</v>
       </c>
       <c r="D272" s="10" t="str">
-        <f>IF(A272="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A272)</f>
+        <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=萌塔娘</v>
       </c>
       <c r="E272" s="11" t="str">
@@ -59414,17 +59844,17 @@
         <v>5049</v>
       </c>
     </row>
-    <row r="273" spans="1:25">
+    <row r="273" spans="1:30">
       <c r="A273" s="10" t="str">
         <f>IF(games!A273="", "", games!A273)</f>
         <v>盜夢英雄2：幻野</v>
       </c>
       <c r="C273" s="10" t="str">
-        <f>IF(A273="","", "giftcodesbanner/" &amp; A273 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v>giftcodesbanner/盜夢英雄2：幻野-禮包碼.jpg</v>
       </c>
       <c r="D273" s="10" t="str">
-        <f>IF(A273="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A273)</f>
+        <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=盜夢英雄2：幻野</v>
       </c>
       <c r="E273" s="11" t="str">
@@ -59476,18 +59906,42 @@
       <c r="V273" s="10" t="s">
         <v>5066</v>
       </c>
-    </row>
-    <row r="274" spans="1:25">
+      <c r="W273" s="15" t="s">
+        <v>5217</v>
+      </c>
+      <c r="X273" s="10" t="s">
+        <v>5221</v>
+      </c>
+      <c r="Y273" s="15" t="s">
+        <v>5218</v>
+      </c>
+      <c r="Z273" s="10" t="s">
+        <v>5222</v>
+      </c>
+      <c r="AA273" s="15" t="s">
+        <v>5219</v>
+      </c>
+      <c r="AB273" s="10" t="s">
+        <v>5223</v>
+      </c>
+      <c r="AC273" s="15" t="s">
+        <v>5220</v>
+      </c>
+      <c r="AD273" s="10" t="s">
+        <v>5224</v>
+      </c>
+    </row>
+    <row r="274" spans="1:30">
       <c r="A274" s="10" t="str">
         <f>IF(games!A274="", "", games!A274)</f>
         <v>貪婪洞窟：重生</v>
       </c>
       <c r="C274" s="10" t="str">
-        <f>IF(A274="","", "giftcodesbanner/" &amp; A274 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v>giftcodesbanner/貪婪洞窟：重生-禮包碼.jpg</v>
       </c>
       <c r="D274" s="10" t="str">
-        <f>IF(A274="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A274)</f>
+        <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=貪婪洞窟：重生</v>
       </c>
       <c r="E274" s="11" t="str">
@@ -59525,17 +59979,17 @@
         <v>5001</v>
       </c>
     </row>
-    <row r="275" spans="1:25">
+    <row r="275" spans="1:30">
       <c r="A275" s="10" t="str">
         <f>IF(games!A275="", "", games!A275)</f>
         <v>小兵特攻隊</v>
       </c>
       <c r="C275" s="10" t="str">
-        <f>IF(A275="","", "giftcodesbanner/" &amp; A275 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v>giftcodesbanner/小兵特攻隊-禮包碼.jpg</v>
       </c>
       <c r="D275" s="10" t="str">
-        <f>IF(A275="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A275)</f>
+        <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=小兵特攻隊</v>
       </c>
       <c r="E275" s="11" t="str">
@@ -59588,17 +60042,17 @@
         <v>5116</v>
       </c>
     </row>
-    <row r="276" spans="1:25">
+    <row r="276" spans="1:30">
       <c r="A276" s="10" t="str">
         <f>IF(games!A276="", "", games!A276)</f>
         <v>星塔旅人</v>
       </c>
       <c r="C276" s="10" t="str">
-        <f>IF(A276="","", "giftcodesbanner/" &amp; A276 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v>giftcodesbanner/星塔旅人-禮包碼.jpg</v>
       </c>
       <c r="D276" s="10" t="str">
-        <f>IF(A276="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A276)</f>
+        <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=星塔旅人</v>
       </c>
       <c r="E276" s="11" t="str">
@@ -59630,17 +60084,17 @@
         <v>5120</v>
       </c>
     </row>
-    <row r="277" spans="1:25">
+    <row r="277" spans="1:30">
       <c r="A277" s="10" t="str">
         <f>IF(games!A277="", "", games!A277)</f>
         <v>卡厄斯夢境</v>
       </c>
       <c r="C277" s="10" t="str">
-        <f>IF(A277="","", "giftcodesbanner/" &amp; A277 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v>giftcodesbanner/卡厄斯夢境-禮包碼.jpg</v>
       </c>
       <c r="D277" s="10" t="str">
-        <f>IF(A277="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A277)</f>
+        <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=卡厄斯夢境</v>
       </c>
       <c r="E277" s="11" t="str">
@@ -59666,17 +60120,17 @@
         <v>4810</v>
       </c>
     </row>
-    <row r="278" spans="1:25">
+    <row r="278" spans="1:30">
       <c r="A278" s="10" t="str">
         <f>IF(games!A278="", "", games!A278)</f>
         <v>星痕共鳴</v>
       </c>
       <c r="C278" s="10" t="str">
-        <f>IF(A278="","", "giftcodesbanner/" &amp; A278 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v>giftcodesbanner/星痕共鳴-禮包碼.jpg</v>
       </c>
       <c r="D278" s="10" t="str">
-        <f>IF(A278="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A278)</f>
+        <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=星痕共鳴</v>
       </c>
       <c r="E278" s="11" t="str">
@@ -59696,17 +60150,17 @@
         <v>4810</v>
       </c>
     </row>
-    <row r="279" spans="1:25">
+    <row r="279" spans="1:30">
       <c r="A279" s="10" t="str">
         <f>IF(games!A279="", "", games!A279)</f>
         <v>二重螺旋</v>
       </c>
       <c r="C279" s="10" t="str">
-        <f>IF(A279="","", "giftcodesbanner/" &amp; A279 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v>giftcodesbanner/二重螺旋-禮包碼.jpg</v>
       </c>
       <c r="D279" s="10" t="str">
-        <f>IF(A279="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A279)</f>
+        <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=二重螺旋</v>
       </c>
       <c r="E279" s="11" t="str">
@@ -59726,17 +60180,17 @@
         <v>4810</v>
       </c>
     </row>
-    <row r="280" spans="1:25">
+    <row r="280" spans="1:30">
       <c r="A280" s="10" t="str">
         <f>IF(games!A280="", "", games!A280)</f>
         <v>電馭跑酷</v>
       </c>
       <c r="C280" s="10" t="str">
-        <f>IF(A280="","", "giftcodesbanner/" &amp; A280 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v>giftcodesbanner/電馭跑酷-禮包碼.jpg</v>
       </c>
       <c r="D280" s="10" t="str">
-        <f>IF(A280="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A280)</f>
+        <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=電馭跑酷</v>
       </c>
       <c r="E280" s="11" t="str">
@@ -59756,17 +60210,17 @@
         <v>4810</v>
       </c>
     </row>
-    <row r="281" spans="1:25">
+    <row r="281" spans="1:30">
       <c r="A281" s="10" t="str">
         <f>IF(games!A281="", "", games!A281)</f>
         <v>火焰紋章Shadows</v>
       </c>
       <c r="C281" s="10" t="str">
-        <f>IF(A281="","", "giftcodesbanner/" &amp; A281 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v>giftcodesbanner/火焰紋章Shadows-禮包碼.jpg</v>
       </c>
       <c r="D281" s="10" t="str">
-        <f>IF(A281="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A281)</f>
+        <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/gift-codes.html?game=火焰紋章Shadows</v>
       </c>
       <c r="E281" s="11" t="str">
@@ -59786,71 +60240,110 @@
         <v>4810</v>
       </c>
     </row>
-    <row r="282" spans="1:25">
+    <row r="282" spans="1:30">
       <c r="A282" s="10" t="str">
         <f>IF(games!A282="", "", games!A282)</f>
-        <v/>
+        <v>石器時代：寵物世界</v>
       </c>
       <c r="C282" s="10" t="str">
-        <f>IF(A282="","", "giftcodesbanner/" &amp; A282 &amp; "-禮包碼.jpg")</f>
-        <v/>
+        <f t="shared" si="12"/>
+        <v>giftcodesbanner/石器時代：寵物世界-禮包碼.jpg</v>
       </c>
       <c r="D282" s="10" t="str">
-        <f>IF(A282="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A282)</f>
-        <v/>
+        <f t="shared" si="13"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=石器時代：寵物世界</v>
       </c>
       <c r="E282" s="11" t="str">
         <f>IF(games!I282&lt;&gt;"", games!I282, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="1:25">
+        <v>經典IP《石器時代》正版授權的回合制策略大作回來啦！本作完美還原端遊，上百種寵物任你策略搭配，更支援手機、電腦多端互通，隨時都能上線抓寵。還在煩惱找不到最新的兌換碼跟禮包碼嗎？別擔心，我們都幫你準備好了！現在就跟上尼斯大陸的冒險，體驗最原汁原味的感動，需要代儲值也沒問題，絕對快速安全，讓你輕鬆跟上夥伴們的腳步，重溫年少的夢中情寵！</v>
+      </c>
+      <c r="F282" s="14" t="s">
+        <v>4809</v>
+      </c>
+      <c r="G282" s="10" t="s">
+        <v>4809</v>
+      </c>
+      <c r="K282" s="14" t="s">
+        <v>4809</v>
+      </c>
+      <c r="L282" s="10" t="s">
+        <v>4809</v>
+      </c>
+    </row>
+    <row r="283" spans="1:30">
       <c r="A283" s="10" t="str">
         <f>IF(games!A283="", "", games!A283)</f>
-        <v/>
+        <v>蔚藍星球：國王很忙</v>
       </c>
       <c r="C283" s="10" t="str">
-        <f>IF(A283="","", "giftcodesbanner/" &amp; A283 &amp; "-禮包碼.jpg")</f>
-        <v/>
+        <f t="shared" si="12"/>
+        <v>giftcodesbanner/蔚藍星球：國王很忙-禮包碼.jpg</v>
       </c>
       <c r="D283" s="10" t="str">
-        <f>IF(A283="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A283)</f>
-        <v/>
+        <f t="shared" si="13"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=蔚藍星球：國王很忙</v>
       </c>
       <c r="E283" s="11" t="str">
         <f>IF(games!I283&lt;&gt;"", games!I283, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="1:25">
+        <v>2025年最值得一玩的全新萌系塔防手遊來啦！邪惡哥布林入侵，身為國王守護者的你，必須招募英雄抵禦入侵。遊戲主打英雄2合1加上局內3重隨機玩法，每局都有上百種策略搭配，就算是休閒玩家也能3秒上手！還在網路上苦苦搜尋可用的禮包碼和兌換碼嗎？別浪費時間了！想要快速升級，享受最爽快的割草感，尋找快速安全的代儲值服務會是你最好的選擇，立即為了蔚藍星球而戰！</v>
+      </c>
+      <c r="F283" s="14" t="s">
+        <v>4809</v>
+      </c>
+      <c r="G283" s="10" t="s">
+        <v>4809</v>
+      </c>
+      <c r="K283" s="14" t="s">
+        <v>4809</v>
+      </c>
+      <c r="L283" s="10" t="s">
+        <v>4809</v>
+      </c>
+    </row>
+    <row r="284" spans="1:30">
       <c r="A284" s="10" t="str">
         <f>IF(games!A284="", "", games!A284)</f>
-        <v/>
+        <v>胸懷三國：美人計</v>
       </c>
       <c r="C284" s="10" t="str">
-        <f>IF(A284="","", "giftcodesbanner/" &amp; A284 &amp; "-禮包碼.jpg")</f>
-        <v/>
+        <f t="shared" si="12"/>
+        <v>giftcodesbanner/胸懷三國：美人計-禮包碼.jpg</v>
       </c>
       <c r="D284" s="10" t="str">
-        <f>IF(A284="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A284)</f>
-        <v/>
+        <f t="shared" si="13"/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=胸懷三國：美人計</v>
       </c>
       <c r="E284" s="11" t="str">
         <f>IF(games!I284&lt;&gt;"", games!I284, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="285" spans="1:25">
+        <v>美少女三國RPG手遊參上！遊戲擁有眾多經典三國名將，搭配緊張刺激的養成戰鬥系統，讓玩家可以體驗高潮連擊的激爽和無限養成的快樂。獨特的武將風格立繪，在既定特色上增添更多風味，絕對是視覺饗宴。還在為了找不到最新的禮包碼而煩惱嗎？想要輕鬆養成武將，解鎖所有外觀，最聰明的方式就是尋找快速安全的代儲值管道，立即領取你的兌換碼福利，在三國世界中無往不利！</v>
+      </c>
+      <c r="F284" s="14" t="s">
+        <v>5212</v>
+      </c>
+      <c r="G284" s="10" t="s">
+        <v>5215</v>
+      </c>
+      <c r="H284" s="10" t="s">
+        <v>5216</v>
+      </c>
+      <c r="K284" s="14" t="s">
+        <v>5214</v>
+      </c>
+      <c r="L284" s="10" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="285" spans="1:30">
       <c r="A285" s="10" t="str">
         <f>IF(games!A285="", "", games!A285)</f>
         <v/>
       </c>
       <c r="C285" s="10" t="str">
-        <f>IF(A285="","", "giftcodesbanner/" &amp; A285 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D285" s="10" t="str">
-        <f>IF(A285="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A285)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E285" s="11" t="str">
@@ -59858,17 +60351,17 @@
         <v/>
       </c>
     </row>
-    <row r="286" spans="1:25">
+    <row r="286" spans="1:30">
       <c r="A286" s="10" t="str">
         <f>IF(games!A286="", "", games!A286)</f>
         <v/>
       </c>
       <c r="C286" s="10" t="str">
-        <f>IF(A286="","", "giftcodesbanner/" &amp; A286 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D286" s="10" t="str">
-        <f>IF(A286="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A286)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E286" s="11" t="str">
@@ -59876,17 +60369,17 @@
         <v/>
       </c>
     </row>
-    <row r="287" spans="1:25">
+    <row r="287" spans="1:30">
       <c r="A287" s="10" t="str">
         <f>IF(games!A287="", "", games!A287)</f>
         <v/>
       </c>
       <c r="C287" s="10" t="str">
-        <f>IF(A287="","", "giftcodesbanner/" &amp; A287 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D287" s="10" t="str">
-        <f>IF(A287="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A287)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E287" s="11" t="str">
@@ -59894,17 +60387,17 @@
         <v/>
       </c>
     </row>
-    <row r="288" spans="1:25">
+    <row r="288" spans="1:30">
       <c r="A288" s="10" t="str">
         <f>IF(games!A288="", "", games!A288)</f>
         <v/>
       </c>
       <c r="C288" s="10" t="str">
-        <f>IF(A288="","", "giftcodesbanner/" &amp; A288 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D288" s="10" t="str">
-        <f>IF(A288="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A288)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E288" s="11" t="str">
@@ -59918,11 +60411,11 @@
         <v/>
       </c>
       <c r="C289" s="10" t="str">
-        <f>IF(A289="","", "giftcodesbanner/" &amp; A289 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D289" s="10" t="str">
-        <f>IF(A289="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A289)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E289" s="11" t="str">
@@ -59936,11 +60429,11 @@
         <v/>
       </c>
       <c r="C290" s="10" t="str">
-        <f>IF(A290="","", "giftcodesbanner/" &amp; A290 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D290" s="10" t="str">
-        <f>IF(A290="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A290)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E290" s="11" t="str">
@@ -59954,11 +60447,11 @@
         <v/>
       </c>
       <c r="C291" s="10" t="str">
-        <f>IF(A291="","", "giftcodesbanner/" &amp; A291 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D291" s="10" t="str">
-        <f>IF(A291="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A291)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E291" s="11" t="str">
@@ -59972,11 +60465,11 @@
         <v/>
       </c>
       <c r="C292" s="10" t="str">
-        <f>IF(A292="","", "giftcodesbanner/" &amp; A292 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D292" s="10" t="str">
-        <f>IF(A292="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A292)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E292" s="11" t="str">
@@ -59990,11 +60483,11 @@
         <v/>
       </c>
       <c r="C293" s="10" t="str">
-        <f>IF(A293="","", "giftcodesbanner/" &amp; A293 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D293" s="10" t="str">
-        <f>IF(A293="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A293)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E293" s="11" t="str">
@@ -60008,11 +60501,11 @@
         <v/>
       </c>
       <c r="C294" s="10" t="str">
-        <f>IF(A294="","", "giftcodesbanner/" &amp; A294 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D294" s="10" t="str">
-        <f>IF(A294="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A294)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E294" s="11" t="str">
@@ -60026,11 +60519,11 @@
         <v/>
       </c>
       <c r="C295" s="10" t="str">
-        <f>IF(A295="","", "giftcodesbanner/" &amp; A295 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D295" s="10" t="str">
-        <f>IF(A295="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A295)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E295" s="11" t="str">
@@ -60044,11 +60537,11 @@
         <v/>
       </c>
       <c r="C296" s="10" t="str">
-        <f>IF(A296="","", "giftcodesbanner/" &amp; A296 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D296" s="10" t="str">
-        <f>IF(A296="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A296)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E296" s="11" t="str">
@@ -60062,11 +60555,11 @@
         <v/>
       </c>
       <c r="C297" s="10" t="str">
-        <f>IF(A297="","", "giftcodesbanner/" &amp; A297 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D297" s="10" t="str">
-        <f>IF(A297="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A297)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E297" s="11" t="str">
@@ -60080,11 +60573,11 @@
         <v/>
       </c>
       <c r="C298" s="10" t="str">
-        <f>IF(A298="","", "giftcodesbanner/" &amp; A298 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D298" s="10" t="str">
-        <f>IF(A298="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A298)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E298" s="11" t="str">
@@ -60098,11 +60591,11 @@
         <v/>
       </c>
       <c r="C299" s="10" t="str">
-        <f>IF(A299="","", "giftcodesbanner/" &amp; A299 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D299" s="10" t="str">
-        <f>IF(A299="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A299)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E299" s="11" t="str">
@@ -60116,11 +60609,11 @@
         <v/>
       </c>
       <c r="C300" s="10" t="str">
-        <f>IF(A300="","", "giftcodesbanner/" &amp; A300 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D300" s="10" t="str">
-        <f>IF(A300="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A300)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E300" s="11" t="str">
@@ -60134,11 +60627,11 @@
         <v/>
       </c>
       <c r="C301" s="10" t="str">
-        <f>IF(A301="","", "giftcodesbanner/" &amp; A301 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D301" s="10" t="str">
-        <f>IF(A301="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A301)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E301" s="11" t="str">
@@ -60152,11 +60645,11 @@
         <v/>
       </c>
       <c r="C302" s="10" t="str">
-        <f>IF(A302="","", "giftcodesbanner/" &amp; A302 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D302" s="10" t="str">
-        <f>IF(A302="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A302)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E302" s="11" t="str">
@@ -60170,11 +60663,11 @@
         <v/>
       </c>
       <c r="C303" s="10" t="str">
-        <f>IF(A303="","", "giftcodesbanner/" &amp; A303 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D303" s="10" t="str">
-        <f>IF(A303="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A303)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E303" s="11" t="str">
@@ -60184,11 +60677,11 @@
     </row>
     <row r="304" spans="1:5">
       <c r="C304" s="10" t="str">
-        <f>IF(A304="","", "giftcodesbanner/" &amp; A304 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D304" s="10" t="str">
-        <f>IF(A304="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A304)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E304" s="11" t="str">
@@ -60198,11 +60691,11 @@
     </row>
     <row r="305" spans="3:5">
       <c r="C305" s="10" t="str">
-        <f>IF(A305="","", "giftcodesbanner/" &amp; A305 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D305" s="10" t="str">
-        <f>IF(A305="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A305)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E305" s="11" t="str">
@@ -60212,11 +60705,11 @@
     </row>
     <row r="306" spans="3:5">
       <c r="C306" s="10" t="str">
-        <f>IF(A306="","", "giftcodesbanner/" &amp; A306 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D306" s="10" t="str">
-        <f>IF(A306="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A306)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E306" s="11" t="str">
@@ -60226,11 +60719,11 @@
     </row>
     <row r="307" spans="3:5">
       <c r="C307" s="10" t="str">
-        <f>IF(A307="","", "giftcodesbanner/" &amp; A307 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D307" s="10" t="str">
-        <f>IF(A307="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A307)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E307" s="11" t="str">
@@ -60240,11 +60733,11 @@
     </row>
     <row r="308" spans="3:5">
       <c r="C308" s="10" t="str">
-        <f>IF(A308="","", "giftcodesbanner/" &amp; A308 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D308" s="10" t="str">
-        <f>IF(A308="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A308)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E308" s="11" t="str">
@@ -60254,11 +60747,11 @@
     </row>
     <row r="309" spans="3:5">
       <c r="C309" s="10" t="str">
-        <f>IF(A309="","", "giftcodesbanner/" &amp; A309 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D309" s="10" t="str">
-        <f>IF(A309="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A309)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E309" s="11" t="str">
@@ -60268,11 +60761,11 @@
     </row>
     <row r="310" spans="3:5">
       <c r="C310" s="10" t="str">
-        <f>IF(A310="","", "giftcodesbanner/" &amp; A310 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D310" s="10" t="str">
-        <f>IF(A310="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A310)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E310" s="11" t="str">
@@ -60282,11 +60775,11 @@
     </row>
     <row r="311" spans="3:5">
       <c r="C311" s="10" t="str">
-        <f>IF(A311="","", "giftcodesbanner/" &amp; A311 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D311" s="10" t="str">
-        <f>IF(A311="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A311)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E311" s="11" t="str">
@@ -60296,11 +60789,11 @@
     </row>
     <row r="312" spans="3:5">
       <c r="C312" s="10" t="str">
-        <f>IF(A312="","", "giftcodesbanner/" &amp; A312 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="D312" s="10" t="str">
-        <f>IF(A312="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A312)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E312" s="11" t="str">
@@ -60310,11 +60803,11 @@
     </row>
     <row r="313" spans="3:5">
       <c r="C313" s="10" t="str">
-        <f t="shared" ref="C313:C376" si="12">IF(A313="","", "giftcodesbanner/" &amp; A313 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" ref="C313:C376" si="14">IF(A313="","", "giftcodesbanner/" &amp; A313 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D313" s="10" t="str">
-        <f t="shared" ref="D313:D376" si="13">IF(A313="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A313)</f>
+        <f t="shared" ref="D313:D376" si="15">IF(A313="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A313)</f>
         <v/>
       </c>
       <c r="E313" s="11" t="str">
@@ -60324,11 +60817,11 @@
     </row>
     <row r="314" spans="3:5">
       <c r="C314" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D314" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E314" s="11" t="str">
@@ -60338,11 +60831,11 @@
     </row>
     <row r="315" spans="3:5">
       <c r="C315" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D315" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E315" s="11" t="str">
@@ -60352,11 +60845,11 @@
     </row>
     <row r="316" spans="3:5">
       <c r="C316" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D316" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E316" s="11" t="str">
@@ -60366,11 +60859,11 @@
     </row>
     <row r="317" spans="3:5">
       <c r="C317" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D317" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E317" s="11" t="str">
@@ -60380,11 +60873,11 @@
     </row>
     <row r="318" spans="3:5">
       <c r="C318" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D318" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E318" s="11" t="str">
@@ -60394,11 +60887,11 @@
     </row>
     <row r="319" spans="3:5">
       <c r="C319" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D319" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E319" s="11" t="str">
@@ -60408,11 +60901,11 @@
     </row>
     <row r="320" spans="3:5">
       <c r="C320" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D320" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E320" s="11" t="str">
@@ -60422,11 +60915,11 @@
     </row>
     <row r="321" spans="3:5">
       <c r="C321" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D321" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E321" s="11" t="str">
@@ -60436,11 +60929,11 @@
     </row>
     <row r="322" spans="3:5">
       <c r="C322" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D322" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E322" s="11" t="str">
@@ -60450,11 +60943,11 @@
     </row>
     <row r="323" spans="3:5">
       <c r="C323" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D323" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E323" s="11" t="str">
@@ -60464,11 +60957,11 @@
     </row>
     <row r="324" spans="3:5">
       <c r="C324" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D324" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E324" s="11" t="str">
@@ -60478,11 +60971,11 @@
     </row>
     <row r="325" spans="3:5">
       <c r="C325" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D325" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E325" s="11" t="str">
@@ -60492,11 +60985,11 @@
     </row>
     <row r="326" spans="3:5">
       <c r="C326" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D326" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E326" s="11" t="str">
@@ -60506,11 +60999,11 @@
     </row>
     <row r="327" spans="3:5">
       <c r="C327" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D327" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E327" s="11" t="str">
@@ -60520,11 +61013,11 @@
     </row>
     <row r="328" spans="3:5">
       <c r="C328" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D328" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E328" s="11" t="str">
@@ -60534,11 +61027,11 @@
     </row>
     <row r="329" spans="3:5">
       <c r="C329" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D329" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E329" s="11" t="str">
@@ -60548,11 +61041,11 @@
     </row>
     <row r="330" spans="3:5">
       <c r="C330" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D330" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E330" s="11" t="str">
@@ -60562,11 +61055,11 @@
     </row>
     <row r="331" spans="3:5">
       <c r="C331" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D331" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E331" s="11" t="str">
@@ -60576,11 +61069,11 @@
     </row>
     <row r="332" spans="3:5">
       <c r="C332" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D332" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E332" s="11" t="str">
@@ -60590,11 +61083,11 @@
     </row>
     <row r="333" spans="3:5">
       <c r="C333" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D333" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E333" s="11" t="str">
@@ -60604,11 +61097,11 @@
     </row>
     <row r="334" spans="3:5">
       <c r="C334" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D334" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E334" s="11" t="str">
@@ -60618,11 +61111,11 @@
     </row>
     <row r="335" spans="3:5">
       <c r="C335" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D335" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E335" s="11" t="str">
@@ -60632,11 +61125,11 @@
     </row>
     <row r="336" spans="3:5">
       <c r="C336" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D336" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E336" s="11" t="str">
@@ -60646,11 +61139,11 @@
     </row>
     <row r="337" spans="3:5">
       <c r="C337" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D337" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E337" s="11" t="str">
@@ -60660,11 +61153,11 @@
     </row>
     <row r="338" spans="3:5">
       <c r="C338" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D338" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E338" s="11" t="str">
@@ -60674,11 +61167,11 @@
     </row>
     <row r="339" spans="3:5">
       <c r="C339" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D339" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E339" s="11" t="str">
@@ -60688,11 +61181,11 @@
     </row>
     <row r="340" spans="3:5">
       <c r="C340" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D340" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E340" s="11" t="str">
@@ -60702,11 +61195,11 @@
     </row>
     <row r="341" spans="3:5">
       <c r="C341" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D341" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E341" s="11" t="str">
@@ -60716,11 +61209,11 @@
     </row>
     <row r="342" spans="3:5">
       <c r="C342" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D342" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E342" s="11" t="str">
@@ -60730,11 +61223,11 @@
     </row>
     <row r="343" spans="3:5">
       <c r="C343" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D343" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E343" s="11" t="str">
@@ -60744,11 +61237,11 @@
     </row>
     <row r="344" spans="3:5">
       <c r="C344" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D344" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E344" s="11" t="str">
@@ -60758,11 +61251,11 @@
     </row>
     <row r="345" spans="3:5">
       <c r="C345" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D345" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E345" s="11" t="str">
@@ -60772,11 +61265,11 @@
     </row>
     <row r="346" spans="3:5">
       <c r="C346" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D346" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E346" s="11" t="str">
@@ -60786,11 +61279,11 @@
     </row>
     <row r="347" spans="3:5">
       <c r="C347" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D347" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E347" s="11" t="str">
@@ -60800,11 +61293,11 @@
     </row>
     <row r="348" spans="3:5">
       <c r="C348" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D348" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E348" s="11" t="str">
@@ -60814,11 +61307,11 @@
     </row>
     <row r="349" spans="3:5">
       <c r="C349" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D349" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E349" s="11" t="str">
@@ -60828,11 +61321,11 @@
     </row>
     <row r="350" spans="3:5">
       <c r="C350" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D350" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E350" s="11" t="str">
@@ -60842,11 +61335,11 @@
     </row>
     <row r="351" spans="3:5">
       <c r="C351" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D351" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E351" s="11" t="str">
@@ -60856,11 +61349,11 @@
     </row>
     <row r="352" spans="3:5">
       <c r="C352" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D352" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E352" s="11" t="str">
@@ -60870,11 +61363,11 @@
     </row>
     <row r="353" spans="3:5">
       <c r="C353" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D353" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E353" s="11" t="str">
@@ -60884,11 +61377,11 @@
     </row>
     <row r="354" spans="3:5">
       <c r="C354" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D354" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E354" s="11" t="str">
@@ -60898,11 +61391,11 @@
     </row>
     <row r="355" spans="3:5">
       <c r="C355" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D355" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E355" s="11" t="str">
@@ -60912,11 +61405,11 @@
     </row>
     <row r="356" spans="3:5">
       <c r="C356" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D356" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E356" s="11" t="str">
@@ -60926,11 +61419,11 @@
     </row>
     <row r="357" spans="3:5">
       <c r="C357" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D357" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E357" s="11" t="str">
@@ -60940,11 +61433,11 @@
     </row>
     <row r="358" spans="3:5">
       <c r="C358" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D358" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E358" s="11" t="str">
@@ -60954,11 +61447,11 @@
     </row>
     <row r="359" spans="3:5">
       <c r="C359" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D359" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E359" s="11" t="str">
@@ -60968,11 +61461,11 @@
     </row>
     <row r="360" spans="3:5">
       <c r="C360" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D360" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E360" s="11" t="str">
@@ -60982,11 +61475,11 @@
     </row>
     <row r="361" spans="3:5">
       <c r="C361" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D361" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E361" s="11" t="str">
@@ -60996,11 +61489,11 @@
     </row>
     <row r="362" spans="3:5">
       <c r="C362" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D362" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E362" s="11" t="str">
@@ -61010,11 +61503,11 @@
     </row>
     <row r="363" spans="3:5">
       <c r="C363" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D363" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E363" s="11" t="str">
@@ -61024,11 +61517,11 @@
     </row>
     <row r="364" spans="3:5">
       <c r="C364" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D364" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E364" s="11" t="str">
@@ -61038,11 +61531,11 @@
     </row>
     <row r="365" spans="3:5">
       <c r="C365" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D365" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E365" s="11" t="str">
@@ -61052,11 +61545,11 @@
     </row>
     <row r="366" spans="3:5">
       <c r="C366" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D366" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E366" s="11" t="str">
@@ -61066,11 +61559,11 @@
     </row>
     <row r="367" spans="3:5">
       <c r="C367" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D367" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E367" s="11" t="str">
@@ -61080,11 +61573,11 @@
     </row>
     <row r="368" spans="3:5">
       <c r="C368" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D368" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E368" s="11" t="str">
@@ -61094,11 +61587,11 @@
     </row>
     <row r="369" spans="3:5">
       <c r="C369" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D369" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E369" s="11" t="str">
@@ -61108,11 +61601,11 @@
     </row>
     <row r="370" spans="3:5">
       <c r="C370" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D370" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E370" s="11" t="str">
@@ -61122,11 +61615,11 @@
     </row>
     <row r="371" spans="3:5">
       <c r="C371" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D371" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E371" s="11" t="str">
@@ -61136,11 +61629,11 @@
     </row>
     <row r="372" spans="3:5">
       <c r="C372" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D372" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E372" s="11" t="str">
@@ -61150,11 +61643,11 @@
     </row>
     <row r="373" spans="3:5">
       <c r="C373" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D373" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E373" s="11" t="str">
@@ -61164,11 +61657,11 @@
     </row>
     <row r="374" spans="3:5">
       <c r="C374" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D374" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E374" s="11" t="str">
@@ -61178,11 +61671,11 @@
     </row>
     <row r="375" spans="3:5">
       <c r="C375" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D375" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E375" s="11" t="str">
@@ -61192,11 +61685,11 @@
     </row>
     <row r="376" spans="3:5">
       <c r="C376" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D376" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E376" s="11" t="str">
@@ -61206,11 +61699,11 @@
     </row>
     <row r="377" spans="3:5">
       <c r="C377" s="10" t="str">
-        <f t="shared" ref="C377:C435" si="14">IF(A377="","", "giftcodesbanner/" &amp; A377 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" ref="C377:C435" si="16">IF(A377="","", "giftcodesbanner/" &amp; A377 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D377" s="10" t="str">
-        <f t="shared" ref="D377:D435" si="15">IF(A377="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A377)</f>
+        <f t="shared" ref="D377:D435" si="17">IF(A377="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A377)</f>
         <v/>
       </c>
       <c r="E377" s="11" t="str">
@@ -61220,11 +61713,11 @@
     </row>
     <row r="378" spans="3:5">
       <c r="C378" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D378" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E378" s="11" t="str">
@@ -61234,11 +61727,11 @@
     </row>
     <row r="379" spans="3:5">
       <c r="C379" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D379" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E379" s="11" t="str">
@@ -61248,11 +61741,11 @@
     </row>
     <row r="380" spans="3:5">
       <c r="C380" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D380" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E380" s="11" t="str">
@@ -61262,11 +61755,11 @@
     </row>
     <row r="381" spans="3:5">
       <c r="C381" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D381" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E381" s="11" t="str">
@@ -61276,11 +61769,11 @@
     </row>
     <row r="382" spans="3:5">
       <c r="C382" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D382" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E382" s="11" t="str">
@@ -61290,11 +61783,11 @@
     </row>
     <row r="383" spans="3:5">
       <c r="C383" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D383" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E383" s="11" t="str">
@@ -61304,11 +61797,11 @@
     </row>
     <row r="384" spans="3:5">
       <c r="C384" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D384" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E384" s="11" t="str">
@@ -61318,11 +61811,11 @@
     </row>
     <row r="385" spans="3:5">
       <c r="C385" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D385" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E385" s="11" t="str">
@@ -61332,11 +61825,11 @@
     </row>
     <row r="386" spans="3:5">
       <c r="C386" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D386" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E386" s="11" t="str">
@@ -61346,11 +61839,11 @@
     </row>
     <row r="387" spans="3:5">
       <c r="C387" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D387" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E387" s="11" t="str">
@@ -61360,11 +61853,11 @@
     </row>
     <row r="388" spans="3:5">
       <c r="C388" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D388" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E388" s="11" t="str">
@@ -61374,11 +61867,11 @@
     </row>
     <row r="389" spans="3:5">
       <c r="C389" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D389" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E389" s="11" t="str">
@@ -61388,11 +61881,11 @@
     </row>
     <row r="390" spans="3:5">
       <c r="C390" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D390" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E390" s="11" t="str">
@@ -61402,11 +61895,11 @@
     </row>
     <row r="391" spans="3:5">
       <c r="C391" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D391" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E391" s="11" t="str">
@@ -61416,11 +61909,11 @@
     </row>
     <row r="392" spans="3:5">
       <c r="C392" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D392" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E392" s="11" t="str">
@@ -61430,11 +61923,11 @@
     </row>
     <row r="393" spans="3:5">
       <c r="C393" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D393" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E393" s="11" t="str">
@@ -61444,11 +61937,11 @@
     </row>
     <row r="394" spans="3:5">
       <c r="C394" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D394" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E394" s="11" t="str">
@@ -61458,11 +61951,11 @@
     </row>
     <row r="395" spans="3:5">
       <c r="C395" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D395" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E395" s="11" t="str">
@@ -61472,11 +61965,11 @@
     </row>
     <row r="396" spans="3:5">
       <c r="C396" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D396" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E396" s="11" t="str">
@@ -61486,11 +61979,11 @@
     </row>
     <row r="397" spans="3:5">
       <c r="C397" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D397" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E397" s="11" t="str">
@@ -61500,11 +61993,11 @@
     </row>
     <row r="398" spans="3:5">
       <c r="C398" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D398" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E398" s="11" t="str">
@@ -61514,11 +62007,11 @@
     </row>
     <row r="399" spans="3:5">
       <c r="C399" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D399" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E399" s="11" t="str">
@@ -61528,361 +62021,361 @@
     </row>
     <row r="400" spans="3:5">
       <c r="C400" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D400" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="401" spans="3:4">
       <c r="C401" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D401" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="402" spans="3:4">
       <c r="C402" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D402" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="403" spans="3:4">
       <c r="C403" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D403" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="404" spans="3:4">
       <c r="C404" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D404" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="405" spans="3:4">
       <c r="C405" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D405" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="406" spans="3:4">
       <c r="C406" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D406" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="407" spans="3:4">
       <c r="C407" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D407" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="408" spans="3:4">
       <c r="C408" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D408" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="409" spans="3:4">
       <c r="C409" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D409" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="410" spans="3:4">
       <c r="C410" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D410" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="411" spans="3:4">
       <c r="C411" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D411" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="412" spans="3:4">
       <c r="C412" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D412" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="413" spans="3:4">
       <c r="C413" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D413" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="414" spans="3:4">
       <c r="C414" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D414" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="415" spans="3:4">
       <c r="C415" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D415" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="416" spans="3:4">
       <c r="C416" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D416" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="417" spans="3:4">
       <c r="C417" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D417" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="418" spans="3:4">
       <c r="C418" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D418" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="419" spans="3:4">
       <c r="C419" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D419" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="420" spans="3:4">
       <c r="C420" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D420" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="421" spans="3:4">
       <c r="C421" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D421" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="422" spans="3:4">
       <c r="C422" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D422" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="423" spans="3:4">
       <c r="C423" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D423" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="424" spans="3:4">
       <c r="C424" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D424" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="425" spans="3:4">
       <c r="C425" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D425" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="426" spans="3:4">
       <c r="C426" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D426" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="427" spans="3:4">
       <c r="C427" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D427" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="428" spans="3:4">
       <c r="C428" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D428" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="429" spans="3:4">
       <c r="C429" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D429" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="430" spans="3:4">
       <c r="C430" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D430" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="431" spans="3:4">
       <c r="C431" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D431" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="432" spans="3:4">
       <c r="C432" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D432" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="433" spans="3:4">
       <c r="C433" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D433" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="434" spans="3:4">
       <c r="C434" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D434" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="435" spans="3:4">
       <c r="C435" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D435" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7613" uniqueCount="5225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7627" uniqueCount="5239">
   <si>
     <t>Facebook</t>
   </si>
@@ -19813,115 +19813,171 @@
     <t>4.99美禮包</t>
   </si>
   <si>
+    <t>蔚藍星球：國王很忙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胸懷三國：美人計</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.netmarble.stonkey</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.blueplanetm.gp&amp;shortlink=mqju4p0s&amp;c=xx_250918_fb_02&amp;pid=fb%E7%A4%BE%E7%BE%A4&amp;af_xp=custom&amp;source_caller=ui</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.lmsg.twgp&amp;pcampaignid=&amp;utm_source=fbtsj&amp;referrer=utm_source%3Dfbtsj%26click_id%3D0a59691a-1a07-4136-9587-ed1a409fffd9_fbtsj</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>經典IP《石器時代》正版授權的回合制策略大作回來啦！本作完美還原端遊，上百種寵物任你策略搭配，更支援手機、電腦多端互通，隨時都能上線抓寵。還在煩惱找不到最新的兌換碼跟禮包碼嗎？別擔心，我們都幫你準備好了！現在就跟上尼斯大陸的冒險，體驗最原汁原味的感動，需要代儲值也沒問題，絕對快速安全，讓你輕鬆跟上夥伴們的腳步，重溫年少的夢中情寵！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025年最值得一玩的全新萌系塔防手遊來啦！邪惡哥布林入侵，身為國王守護者的你，必須招募英雄抵禦入侵。遊戲主打英雄2合1加上局內3重隨機玩法，每局都有上百種策略搭配，就算是休閒玩家也能3秒上手！還在網路上苦苦搜尋可用的禮包碼和兌換碼嗎？別浪費時間了！想要快速升級，享受最爽快的割草感，尋找快速安全的代儲值服務會是你最好的選擇，立即為了蔚藍星球而戰！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>美少女三國RPG手遊參上！遊戲擁有眾多經典三國名將，搭配緊張刺激的養成戰鬥系統，讓玩家可以體驗高潮連擊的激爽和無限養成的快樂。獨特的武將風格立繪，在既定特色上增添更多風味，絕對是視覺饗宴。還在為了找不到最新的禮包碼而煩惱嗎？想要輕鬆養成武將，解鎖所有外觀，最聰明的方式就是尋找快速安全的代儲值管道，立即領取你的兌換碼福利，在三國世界中無往不利！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALMVIP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AWKLLAUNCH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*100+火神能量*4+金幣*50000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點遊戲內左上角頭像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>彈出視窗下方「Redeem Code」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點擊左上角頭像，進入設定介面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>招募帖*10、古玉*300</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新手禮包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>再點擊介面左下方的禮包碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在輸入框中輸入您的禮包碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>vip777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>vip888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WildsCommunity666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dreamtogether</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*500+金幣*18888+許願的時之輪*1+定軌的時之輪*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*588+金幣*20000+許願的時之輪*3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*888+金幣*1888+許願的時之輪*2+定軌的時之輪*2+突破藥水*200</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石*688+金幣*20258+許願的時之輪*2+史詩璀璨魂晶*50+經驗卷軸*5000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>石器時代：寵物世界</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>蔚藍星球：國王很忙</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>胸懷三國：美人計</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://play.google.com/store/apps/details?id=com.netmarble.stonkey</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://play.google.com/store/apps/details?id=com.blueplanetm.gp&amp;shortlink=mqju4p0s&amp;c=xx_250918_fb_02&amp;pid=fb%E7%A4%BE%E7%BE%A4&amp;af_xp=custom&amp;source_caller=ui</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://play.google.com/store/apps/details?id=com.lmsg.twgp&amp;pcampaignid=&amp;utm_source=fbtsj&amp;referrer=utm_source%3Dfbtsj%26click_id%3D0a59691a-1a07-4136-9587-ed1a409fffd9_fbtsj</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>經典IP《石器時代》正版授權的回合制策略大作回來啦！本作完美還原端遊，上百種寵物任你策略搭配，更支援手機、電腦多端互通，隨時都能上線抓寵。還在煩惱找不到最新的兌換碼跟禮包碼嗎？別擔心，我們都幫你準備好了！現在就跟上尼斯大陸的冒險，體驗最原汁原味的感動，需要代儲值也沒問題，絕對快速安全，讓你輕鬆跟上夥伴們的腳步，重溫年少的夢中情寵！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025年最值得一玩的全新萌系塔防手遊來啦！邪惡哥布林入侵，身為國王守護者的你，必須招募英雄抵禦入侵。遊戲主打英雄2合1加上局內3重隨機玩法，每局都有上百種策略搭配，就算是休閒玩家也能3秒上手！還在網路上苦苦搜尋可用的禮包碼和兌換碼嗎？別浪費時間了！想要快速升級，享受最爽快的割草感，尋找快速安全的代儲值服務會是你最好的選擇，立即為了蔚藍星球而戰！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>美少女三國RPG手遊參上！遊戲擁有眾多經典三國名將，搭配緊張刺激的養成戰鬥系統，讓玩家可以體驗高潮連擊的激爽和無限養成的快樂。獨特的武將風格立繪，在既定特色上增添更多風味，絕對是視覺饗宴。還在為了找不到最新的禮包碼而煩惱嗎？想要輕鬆養成武將，解鎖所有外觀，最聰明的方式就是尋找快速安全的代儲值管道，立即領取你的兌換碼福利，在三國世界中無往不利！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALMVIP</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AWKLLAUNCH</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*100+火神能量*4+金幣*50000</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石禮包</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>點遊戲內左上角頭像</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>彈出視窗下方「Redeem Code」</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>點擊左上角頭像，進入設定介面</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>招募帖*10、古玉*300</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>新手禮包</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>再點擊介面左下方的禮包碼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>在輸入框中輸入您的禮包碼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>vip777</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>vip888</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>WildsCommunity666</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>dreamtogether</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*500+金幣*18888+許願的時之輪*1+定軌的時之輪*1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*588+金幣*20000+許願的時之輪*3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*888+金幣*1888+許願的時之輪*2+定軌的時之輪*2+突破藥水*200</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石*688+金幣*20258+許願的時之輪*2+史詩璀璨魂晶*50+經驗卷軸*5000</t>
+    <t>HAPPYKYLEWK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KYLETEO4EVER</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LEGENDKYLE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>REBIRTHKYLE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KYLEGIFT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHAINOFKYLE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KYLEWKSTART</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pick Up 英雄召喚使用券 x10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣 x100W、進化材料選擇箱(上) x30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄召喚使用券 x10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pick Up 英雄召喚使用券 x10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寵物召喚使用券 x10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑰匙箱 x10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑰匙箱 x10</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -40022,7 +40078,7 @@
     </row>
     <row r="282" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A282" s="83" t="s">
-        <v>5197</v>
+        <v>5224</v>
       </c>
       <c r="C282" s="37" t="s">
         <v>5175</v>
@@ -40038,14 +40094,14 @@
         <v>gift-codes.html?game=石器時代：寵物世界</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>5200</v>
+        <v>5199</v>
       </c>
       <c r="H282" s="38" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/石器時代：寵物世界.html</v>
       </c>
       <c r="I282" s="39" t="s">
-        <v>5203</v>
+        <v>5202</v>
       </c>
       <c r="J282" s="1" t="s">
         <v>4988</v>
@@ -40110,7 +40166,7 @@
     </row>
     <row r="283" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A283" s="83" t="s">
-        <v>5198</v>
+        <v>5197</v>
       </c>
       <c r="C283" s="37" t="s">
         <v>5178</v>
@@ -40126,14 +40182,14 @@
         <v>gift-codes.html?game=蔚藍星球：國王很忙</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>5201</v>
+        <v>5200</v>
       </c>
       <c r="H283" s="38" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/蔚藍星球：國王很忙.html</v>
       </c>
       <c r="I283" s="39" t="s">
-        <v>5204</v>
+        <v>5203</v>
       </c>
       <c r="J283" s="1" t="s">
         <v>5189</v>
@@ -40186,7 +40242,7 @@
     </row>
     <row r="284" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A284" s="83" t="s">
-        <v>5199</v>
+        <v>5198</v>
       </c>
       <c r="C284" s="37" t="s">
         <v>5181</v>
@@ -40202,14 +40258,14 @@
         <v>gift-codes.html?game=胸懷三國：美人計</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>5202</v>
+        <v>5201</v>
       </c>
       <c r="H284" s="38" t="str">
         <f t="shared" ref="H284:H312" si="13">IF(A284="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A284)</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=胸懷三國：美人計</v>
       </c>
       <c r="I284" s="39" t="s">
-        <v>5205</v>
+        <v>5204</v>
       </c>
       <c r="J284" s="1" t="s">
         <v>4988</v>
@@ -58384,6 +58440,48 @@
       <c r="V236" s="10" t="s">
         <v>5026</v>
       </c>
+      <c r="W236" s="15" t="s">
+        <v>5225</v>
+      </c>
+      <c r="X236" s="10" t="s">
+        <v>5238</v>
+      </c>
+      <c r="Y236" s="15" t="s">
+        <v>5226</v>
+      </c>
+      <c r="Z236" s="10" t="s">
+        <v>5237</v>
+      </c>
+      <c r="AA236" s="15" t="s">
+        <v>5227</v>
+      </c>
+      <c r="AB236" s="10" t="s">
+        <v>5236</v>
+      </c>
+      <c r="AC236" s="15" t="s">
+        <v>5228</v>
+      </c>
+      <c r="AD236" s="10" t="s">
+        <v>5235</v>
+      </c>
+      <c r="AE236" s="15" t="s">
+        <v>5229</v>
+      </c>
+      <c r="AF236" s="10" t="s">
+        <v>5234</v>
+      </c>
+      <c r="AG236" s="15" t="s">
+        <v>5230</v>
+      </c>
+      <c r="AH236" s="10" t="s">
+        <v>5233</v>
+      </c>
+      <c r="AI236" s="15" t="s">
+        <v>5231</v>
+      </c>
+      <c r="AJ236" s="10" t="s">
+        <v>5232</v>
+      </c>
     </row>
     <row r="237" spans="1:47" ht="22.5" customHeight="1">
       <c r="A237" s="10" t="str">
@@ -59724,10 +59822,10 @@
         <v>《Awakenloop》是一款充滿賽博龐克風格的卡牌回合制手遊，玩家將身處一個由機器人與人類共存的末日世界。遊戲主打策略性卡牌戰鬥，每張卡牌都蘊含獨特技能，如何搭配與釋放將成為戰局關鍵。除了豐富的主線劇情，遊戲也提供多樣的副本挑戰與 PvP 模式，讓你與其他玩家一較高下。現在就加入《Awakenloop》，透過兌換碼與禮包碼獲得專屬獎勵，輕鬆提升戰力，也能使用代儲值服務快速安全地補充資源，在這片混沌的廢土上開創屬於你的新紀元。</v>
       </c>
       <c r="F269" s="14" t="s">
+        <v>5209</v>
+      </c>
+      <c r="G269" s="10" t="s">
         <v>5210</v>
-      </c>
-      <c r="G269" s="10" t="s">
-        <v>5211</v>
       </c>
       <c r="H269" s="10" t="s">
         <v>2625</v>
@@ -59736,16 +59834,16 @@
         <v>4360</v>
       </c>
       <c r="K269" s="14" t="s">
+        <v>5205</v>
+      </c>
+      <c r="L269" s="10" t="s">
+        <v>5208</v>
+      </c>
+      <c r="M269" s="15" t="s">
         <v>5206</v>
       </c>
-      <c r="L269" s="10" t="s">
-        <v>5209</v>
-      </c>
-      <c r="M269" s="15" t="s">
+      <c r="N269" s="10" t="s">
         <v>5207</v>
-      </c>
-      <c r="N269" s="10" t="s">
-        <v>5208</v>
       </c>
     </row>
     <row r="270" spans="1:31">
@@ -59907,28 +60005,28 @@
         <v>5066</v>
       </c>
       <c r="W273" s="15" t="s">
+        <v>5216</v>
+      </c>
+      <c r="X273" s="10" t="s">
+        <v>5220</v>
+      </c>
+      <c r="Y273" s="15" t="s">
         <v>5217</v>
       </c>
-      <c r="X273" s="10" t="s">
+      <c r="Z273" s="10" t="s">
         <v>5221</v>
       </c>
-      <c r="Y273" s="15" t="s">
+      <c r="AA273" s="15" t="s">
         <v>5218</v>
       </c>
-      <c r="Z273" s="10" t="s">
+      <c r="AB273" s="10" t="s">
         <v>5222</v>
       </c>
-      <c r="AA273" s="15" t="s">
+      <c r="AC273" s="15" t="s">
         <v>5219</v>
       </c>
-      <c r="AB273" s="10" t="s">
+      <c r="AD273" s="10" t="s">
         <v>5223</v>
-      </c>
-      <c r="AC273" s="15" t="s">
-        <v>5220</v>
-      </c>
-      <c r="AD273" s="10" t="s">
-        <v>5224</v>
       </c>
     </row>
     <row r="274" spans="1:30">
@@ -60318,19 +60416,19 @@
         <v>美少女三國RPG手遊參上！遊戲擁有眾多經典三國名將，搭配緊張刺激的養成戰鬥系統，讓玩家可以體驗高潮連擊的激爽和無限養成的快樂。獨特的武將風格立繪，在既定特色上增添更多風味，絕對是視覺饗宴。還在為了找不到最新的禮包碼而煩惱嗎？想要輕鬆養成武將，解鎖所有外觀，最聰明的方式就是尋找快速安全的代儲值管道，立即領取你的兌換碼福利，在三國世界中無往不利！</v>
       </c>
       <c r="F284" s="14" t="s">
+        <v>5211</v>
+      </c>
+      <c r="G284" s="10" t="s">
+        <v>5214</v>
+      </c>
+      <c r="H284" s="10" t="s">
+        <v>5215</v>
+      </c>
+      <c r="K284" s="14" t="s">
+        <v>5213</v>
+      </c>
+      <c r="L284" s="10" t="s">
         <v>5212</v>
-      </c>
-      <c r="G284" s="10" t="s">
-        <v>5215</v>
-      </c>
-      <c r="H284" s="10" t="s">
-        <v>5216</v>
-      </c>
-      <c r="K284" s="14" t="s">
-        <v>5214</v>
-      </c>
-      <c r="L284" s="10" t="s">
-        <v>5213</v>
       </c>
     </row>
     <row r="285" spans="1:30">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7651" uniqueCount="5263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7674" uniqueCount="5277">
   <si>
     <t>Facebook</t>
   </si>
@@ -20041,9 +20041,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>十二之天M Reborn》誓言找回當年的感動，讓玩家重溫三大勢力（神劍門、逍遙派、夢魘聖教）的激情對決。這款遊戲主打的就是一個原汁原味，熟悉的場景、懷舊的BGM，以及那令人又愛又恨的勢力戰。準備好再次投身這場無盡的江湖恩怨了嗎？老玩家們都知道，想在勢力戰中脫穎而出，光靠情懷可不夠。大家都在蹲點最新的禮包碼，希望能搶先一步強化裝備。官方發放的兌換碼雖然不無小補，但真正的強者懂得利用資源。想要快速提升戰力，不妨考慮專業的代儲值服務。與其在戰場上被當小兵清掉，不如透過快速安全的管道補足元寶，讓你的角色戰力飆升，在龍瀑鎮插旗，重現當年的榮光！</t>
-  </si>
-  <si>
     <t>十二之天M</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -20052,15 +20049,75 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>準備好你的弓箭，面對排山倒海的敵人了嗎？《弓箭英雄：塔防》是一款結合了塔防策略與Roguelite元素的超休閒遊戲。你將扮演一名孤獨的弓箭手，必須利用地形和不斷升級的技能，抵禦一波又一波的怪物入侵。遊戲的畫風簡潔明瞭，但戰鬥的刺激感可一點都沒少。每次升級都能三選一技能，是要彈射、冰凍還是連射？選錯了可能下一秒就躺平。玩家們都在瘋狂尋找最新的兌換碼，希望能開局就拿到神裝。別忘了，強大的火力支援是守塔的關鍵，這時候就需要可靠的代儲值服務來幫你一把。想要穩穩通關，拿到稀有的禮包碼獎勵嗎？與其苦苦硬撐，不如尋求快速安全的代儲值，讓你的箭塔升到滿級，輕鬆碾壓所有來犯的敵人，成為真正的塔防大師！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>籃球粉注意！正版授權的《NBA巔峰對決》終於來了。這款主打真人PVP的籃球手遊，讓你能操控喜愛的NBA球星，在球場上來一場快節奏的3v3、5v5，甚至1v1單挑。遊戲強調操作手感與球星的專屬技能，想秀一波高難度灌籃或致命三分球？全看你的技術。但說真的，想在天梯上爬分，光有技術還不夠，球員的養成才是關鍵。新手們別再傻傻地問兌換碼在哪了，那點資源根本不夠看。想要打造你的夢幻陣容，把傳奇球星都納入麾下，可靠的代儲值才是捷徑。別家還在慢慢存資源，你已經透過快速安全的儲值拿到關鍵禮包碼，直接抽爆卡池，讓你的隊伍戰力登頂，在球場上制霸全場！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>又一款三國策略遊戲？先別急著滑掉！《三國志：王戰》是一款主打快節奏的SLG手遊，標榜著15天一賽季的急速征戰。在這裡，你不用再苦苦熬夜農地、屯兵，而是要把握黃金時間，快速發展內政、招募名將，與盟友一同攻城掠地。遊戲強調即時戰略操作，微操走位、技能施放時機都可能逆轉戰局。當然，想在短短15天內統一天下，光靠策略可不夠。新手們拚命搜尋的兌換碼，拿到的資源可能還不夠升一座主城。真正的王者都懂得運用代儲值服務，在開局就快人一步。別再猶豫了，利用快速安全的管道取得珍稀禮包碼與資源，迅速拉高戰力，在賽季結束前稱霸全服！</t>
+    <t>等待遊戲公司更新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>等待遊戲公司更新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>URTHESTAR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPARK4U</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>400薔薇寶石（綁定）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>400薔薇寶石（綁定）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點出選單後右上角「設定」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>左邊書籤選擇房子圖案</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家頭像右方「兌換碼」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DNARELEASE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DNAFREEPLAY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DNA1028</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DNALAUNCH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲內選單按「設定」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>準備好你的弓箭，面對排山倒海的敵人了嗎？《弓箭英雄：塔防》是一款結合了塔防策略與Roguelite元素的超休閒遊戲。遊戲的畫風簡潔明瞭，但戰鬥的刺激感可一點都沒少。每次升級都能三選一技能，是要彈射、冰凍還是連射？選錯了可能下一秒就躺平。玩家們都在瘋狂尋找最新的兌換碼，希望能開局就拿到神裝。別忘了，強大的火力支援是守塔的關鍵，這時候就需要可靠的代儲值服務來幫你一把。想要穩穩通關，拿到稀有的禮包碼獎勵嗎？與其苦苦硬撐，不如尋求快速安全的代儲值，讓你的箭塔升到滿級，輕鬆碾壓所有來犯的敵人，成為真正的塔防大師！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《十二之天M Reborn》誓言找回當年的感動，讓玩家重溫三大勢力的激情對決。這款遊戲主打的就是一個原汁原味，熟悉的場景、懷舊的BGM，以及那令人又愛又恨的勢力戰。準備好再次投身這場無盡的江湖恩怨了嗎？大家都在蹲點最新的禮包碼，希望能搶先一步強化裝備。官方發放的兌換碼雖然不無小補，但真正的強者懂得利用資源。想要快速提升戰力，不妨考慮專業的代儲值服務。與其在戰場上被當小兵清掉，不如透過快速安全的管道補足元寶，讓你的角色戰力飆升，在龍瀑鎮插旗，重現當年的榮光！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正版授權的《NBA巔峰對決》終於來了。這款主打真人PVP的籃球手遊，讓你能操控喜愛的NBA球星。遊戲強調操作手感與球星的專屬技能，想秀一波高難度灌籃或致命三分球？全看你的技術。但說真的，想在天梯上爬分，球員的養成才是關鍵。新手們別再傻傻地問兌換碼在哪了，那點資源根本不夠看。想要打造你的夢幻陣容，把傳奇球星都納入麾下，可靠的代儲值才是捷徑。別家還在慢慢存資源，你已經透過快速安全的儲值拿到關鍵禮包碼，直接抽爆卡池，讓你的隊伍戰力登頂，在球場上制霸全場！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>又一款三國策略遊戲？先別急著滑掉！《三國志：王戰》是一款主打快節奏的SLG手遊，標榜著15天一賽季的急速征戰。在這裡，你不用再苦苦熬夜農地、屯兵，而是要把握黃金時間，快速發展內政、招募名將，與盟友一同攻城掠地。當然，想在短短15天內統一天下，光靠策略可不夠。新手們拚命搜尋的兌換碼，拿到的資源可能還不夠升一座主城。真正的王者都懂得運用代儲值服務，在開局就快人一步。別再猶豫了，利用快速安全的管道取得珍稀禮包碼與資源，迅速拉高戰力，在賽季結束前稱霸全服！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -40437,12 +40494,12 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=弓箭英雄：塔防</v>
       </c>
       <c r="I285" s="37" t="s">
-        <v>5260</v>
+        <v>5273</v>
       </c>
     </row>
     <row r="286" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A286" s="82" t="s">
-        <v>5258</v>
+        <v>5257</v>
       </c>
       <c r="C286" s="35" t="s">
         <v>5241</v>
@@ -40465,12 +40522,12 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=十二之天M</v>
       </c>
       <c r="I286" s="64" t="s">
-        <v>5257</v>
+        <v>5274</v>
       </c>
     </row>
     <row r="287" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
       <c r="A287" s="82" t="s">
-        <v>5259</v>
+        <v>5258</v>
       </c>
       <c r="C287" s="35" t="s">
         <v>5245</v>
@@ -40493,7 +40550,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=NBA巔峰對決</v>
       </c>
       <c r="I287" s="37" t="s">
-        <v>5261</v>
+        <v>5275</v>
       </c>
     </row>
     <row r="288" spans="1:29" ht="22.5" customHeight="1" thickBot="1">
@@ -40521,7 +40578,7 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=三國志：王戰</v>
       </c>
       <c r="I288" s="37" t="s">
-        <v>5262</v>
+        <v>5276</v>
       </c>
     </row>
     <row r="289" spans="6:8" ht="22.5" customHeight="1">
@@ -60396,16 +60453,25 @@
         <v>全新星緣卡牌 RPG《星痕共鳴》，邀你一同編織命運的篇章。遊戲擁有宏大的世界觀與超過百萬字的豐富劇情，玩家將扮演「星源之主」，與眾多「星痕者」締結羈絆，共同對抗虛空的威脅。獨特的「星盤」系統與高策略性的卡牌戰鬥，讓每場對決都充滿變數。想要輕鬆推圖、快速成長？記得在各大社群與論壇尋找隱藏的兌換碼與禮包碼，領取豐厚資源。如果想快人一步，最聰明的選擇就是尋找可靠的代儲值管道，提供您快速安全的支援，讓你的冒險旅程更加順遂。</v>
       </c>
       <c r="F278" s="12" t="s">
-        <v>4811</v>
+        <v>5265</v>
       </c>
       <c r="G278" s="8" t="s">
-        <v>4810</v>
+        <v>5266</v>
+      </c>
+      <c r="H278" s="8" t="s">
+        <v>5267</v>
       </c>
       <c r="K278" s="12" t="s">
-        <v>4811</v>
+        <v>5261</v>
       </c>
       <c r="L278" s="8" t="s">
-        <v>4810</v>
+        <v>5264</v>
+      </c>
+      <c r="M278" s="13" t="s">
+        <v>5262</v>
+      </c>
+      <c r="N278" s="8" t="s">
+        <v>5263</v>
       </c>
     </row>
     <row r="279" spans="1:30">
@@ -60426,16 +60492,28 @@
         <v>備受矚目的 3D 動作 RPG《二重螺旋》強勢來襲！本作主打高速、爽快的戰鬥體驗，玩家將在一個近未來科幻世界中，扮演擁有特殊能力的「適格者」，探索神秘的「深淵」。遊戲強調華麗的連擊與多樣化的武器系統，你可以自由切換遠近程攻擊，打出屬於自己的戰鬥風格。為了讓你的探索之路更加順利，官方會不定期發放福利兌換碼與禮包碼，千萬別錯過。當然，面對強大的敵人，尋求專業的代儲值協助，以快速安全的方式強化戰力，絕對是高效的致勝關鍵。</v>
       </c>
       <c r="F279" s="12" t="s">
-        <v>4811</v>
+        <v>5272</v>
       </c>
       <c r="G279" s="8" t="s">
-        <v>4810</v>
+        <v>3641</v>
+      </c>
+      <c r="H279" s="8" t="s">
+        <v>2625</v>
+      </c>
+      <c r="I279" s="8" t="s">
+        <v>4360</v>
       </c>
       <c r="K279" s="12" t="s">
-        <v>4811</v>
-      </c>
-      <c r="L279" s="8" t="s">
-        <v>4810</v>
+        <v>5268</v>
+      </c>
+      <c r="M279" s="13" t="s">
+        <v>5269</v>
+      </c>
+      <c r="O279" s="13" t="s">
+        <v>5270</v>
+      </c>
+      <c r="Q279" s="13" t="s">
+        <v>5271</v>
       </c>
     </row>
     <row r="280" spans="1:30">
@@ -60606,7 +60684,19 @@
       </c>
       <c r="E285" s="9" t="str">
         <f>IF(games!I285&lt;&gt;"", games!I285, "")</f>
-        <v>準備好你的弓箭，面對排山倒海的敵人了嗎？《弓箭英雄：塔防》是一款結合了塔防策略與Roguelite元素的超休閒遊戲。你將扮演一名孤獨的弓箭手，必須利用地形和不斷升級的技能，抵禦一波又一波的怪物入侵。遊戲的畫風簡潔明瞭，但戰鬥的刺激感可一點都沒少。每次升級都能三選一技能，是要彈射、冰凍還是連射？選錯了可能下一秒就躺平。玩家們都在瘋狂尋找最新的兌換碼，希望能開局就拿到神裝。別忘了，強大的火力支援是守塔的關鍵，這時候就需要可靠的代儲值服務來幫你一把。想要穩穩通關，拿到稀有的禮包碼獎勵嗎？與其苦苦硬撐，不如尋求快速安全的代儲值，讓你的箭塔升到滿級，輕鬆碾壓所有來犯的敵人，成為真正的塔防大師！</v>
+        <v>準備好你的弓箭，面對排山倒海的敵人了嗎？《弓箭英雄：塔防》是一款結合了塔防策略與Roguelite元素的超休閒遊戲。遊戲的畫風簡潔明瞭，但戰鬥的刺激感可一點都沒少。每次升級都能三選一技能，是要彈射、冰凍還是連射？選錯了可能下一秒就躺平。玩家們都在瘋狂尋找最新的兌換碼，希望能開局就拿到神裝。別忘了，強大的火力支援是守塔的關鍵，這時候就需要可靠的代儲值服務來幫你一把。想要穩穩通關，拿到稀有的禮包碼獎勵嗎？與其苦苦硬撐，不如尋求快速安全的代儲值，讓你的箭塔升到滿級，輕鬆碾壓所有來犯的敵人，成為真正的塔防大師！</v>
+      </c>
+      <c r="F285" s="12" t="s">
+        <v>5260</v>
+      </c>
+      <c r="G285" s="8" t="s">
+        <v>5259</v>
+      </c>
+      <c r="K285" s="12" t="s">
+        <v>5260</v>
+      </c>
+      <c r="L285" s="8" t="s">
+        <v>5259</v>
       </c>
     </row>
     <row r="286" spans="1:30">
@@ -60624,7 +60714,19 @@
       </c>
       <c r="E286" s="9" t="str">
         <f>IF(games!I286&lt;&gt;"", games!I286, "")</f>
-        <v>十二之天M Reborn》誓言找回當年的感動，讓玩家重溫三大勢力（神劍門、逍遙派、夢魘聖教）的激情對決。這款遊戲主打的就是一個原汁原味，熟悉的場景、懷舊的BGM，以及那令人又愛又恨的勢力戰。準備好再次投身這場無盡的江湖恩怨了嗎？老玩家們都知道，想在勢力戰中脫穎而出，光靠情懷可不夠。大家都在蹲點最新的禮包碼，希望能搶先一步強化裝備。官方發放的兌換碼雖然不無小補，但真正的強者懂得利用資源。想要快速提升戰力，不妨考慮專業的代儲值服務。與其在戰場上被當小兵清掉，不如透過快速安全的管道補足元寶，讓你的角色戰力飆升，在龍瀑鎮插旗，重現當年的榮光！</v>
+        <v>《十二之天M Reborn》誓言找回當年的感動，讓玩家重溫三大勢力的激情對決。這款遊戲主打的就是一個原汁原味，熟悉的場景、懷舊的BGM，以及那令人又愛又恨的勢力戰。準備好再次投身這場無盡的江湖恩怨了嗎？大家都在蹲點最新的禮包碼，希望能搶先一步強化裝備。官方發放的兌換碼雖然不無小補，但真正的強者懂得利用資源。想要快速提升戰力，不妨考慮專業的代儲值服務。與其在戰場上被當小兵清掉，不如透過快速安全的管道補足元寶，讓你的角色戰力飆升，在龍瀑鎮插旗，重現當年的榮光！</v>
+      </c>
+      <c r="F286" s="12" t="s">
+        <v>5260</v>
+      </c>
+      <c r="G286" s="8" t="s">
+        <v>5259</v>
+      </c>
+      <c r="K286" s="12" t="s">
+        <v>5260</v>
+      </c>
+      <c r="L286" s="8" t="s">
+        <v>5259</v>
       </c>
     </row>
     <row r="287" spans="1:30">
@@ -60642,7 +60744,19 @@
       </c>
       <c r="E287" s="9" t="str">
         <f>IF(games!I287&lt;&gt;"", games!I287, "")</f>
-        <v>籃球粉注意！正版授權的《NBA巔峰對決》終於來了。這款主打真人PVP的籃球手遊，讓你能操控喜愛的NBA球星，在球場上來一場快節奏的3v3、5v5，甚至1v1單挑。遊戲強調操作手感與球星的專屬技能，想秀一波高難度灌籃或致命三分球？全看你的技術。但說真的，想在天梯上爬分，光有技術還不夠，球員的養成才是關鍵。新手們別再傻傻地問兌換碼在哪了，那點資源根本不夠看。想要打造你的夢幻陣容，把傳奇球星都納入麾下，可靠的代儲值才是捷徑。別家還在慢慢存資源，你已經透過快速安全的儲值拿到關鍵禮包碼，直接抽爆卡池，讓你的隊伍戰力登頂，在球場上制霸全場！</v>
+        <v>正版授權的《NBA巔峰對決》終於來了。這款主打真人PVP的籃球手遊，讓你能操控喜愛的NBA球星。遊戲強調操作手感與球星的專屬技能，想秀一波高難度灌籃或致命三分球？全看你的技術。但說真的，想在天梯上爬分，球員的養成才是關鍵。新手們別再傻傻地問兌換碼在哪了，那點資源根本不夠看。想要打造你的夢幻陣容，把傳奇球星都納入麾下，可靠的代儲值才是捷徑。別家還在慢慢存資源，你已經透過快速安全的儲值拿到關鍵禮包碼，直接抽爆卡池，讓你的隊伍戰力登頂，在球場上制霸全場！</v>
+      </c>
+      <c r="F287" s="12" t="s">
+        <v>5260</v>
+      </c>
+      <c r="G287" s="8" t="s">
+        <v>5259</v>
+      </c>
+      <c r="K287" s="12" t="s">
+        <v>5260</v>
+      </c>
+      <c r="L287" s="8" t="s">
+        <v>5259</v>
       </c>
     </row>
     <row r="288" spans="1:30">
@@ -60660,7 +60774,19 @@
       </c>
       <c r="E288" s="9" t="str">
         <f>IF(games!I288&lt;&gt;"", games!I288, "")</f>
-        <v>又一款三國策略遊戲？先別急著滑掉！《三國志：王戰》是一款主打快節奏的SLG手遊，標榜著15天一賽季的急速征戰。在這裡，你不用再苦苦熬夜農地、屯兵，而是要把握黃金時間，快速發展內政、招募名將，與盟友一同攻城掠地。遊戲強調即時戰略操作，微操走位、技能施放時機都可能逆轉戰局。當然，想在短短15天內統一天下，光靠策略可不夠。新手們拚命搜尋的兌換碼，拿到的資源可能還不夠升一座主城。真正的王者都懂得運用代儲值服務，在開局就快人一步。別再猶豫了，利用快速安全的管道取得珍稀禮包碼與資源，迅速拉高戰力，在賽季結束前稱霸全服！</v>
+        <v>又一款三國策略遊戲？先別急著滑掉！《三國志：王戰》是一款主打快節奏的SLG手遊，標榜著15天一賽季的急速征戰。在這裡，你不用再苦苦熬夜農地、屯兵，而是要把握黃金時間，快速發展內政、招募名將，與盟友一同攻城掠地。當然，想在短短15天內統一天下，光靠策略可不夠。新手們拚命搜尋的兌換碼，拿到的資源可能還不夠升一座主城。真正的王者都懂得運用代儲值服務，在開局就快人一步。別再猶豫了，利用快速安全的管道取得珍稀禮包碼與資源，迅速拉高戰力，在賽季結束前稱霸全服！</v>
+      </c>
+      <c r="F288" s="12" t="s">
+        <v>5260</v>
+      </c>
+      <c r="G288" s="8" t="s">
+        <v>5259</v>
+      </c>
+      <c r="K288" s="12" t="s">
+        <v>5260</v>
+      </c>
+      <c r="L288" s="8" t="s">
+        <v>5259</v>
       </c>
     </row>
     <row r="289" spans="1:5">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7804" uniqueCount="5280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7853" uniqueCount="5337">
   <si>
     <t>Facebook</t>
   </si>
@@ -18634,21 +18634,6 @@
   </si>
   <si>
     <t>待到日暖雪融限定禮包</t>
-  </si>
-  <si>
-    <t>補貼升級</t>
-  </si>
-  <si>
-    <t>每月青空禮券套裝</t>
-  </si>
-  <si>
-    <t>每月燦金閃碟套裝</t>
-  </si>
-  <si>
-    <t>啟程限定燦金閃碟套裝</t>
-  </si>
-  <si>
-    <t>開業大吉燦金閃碟套裝</t>
   </si>
   <si>
     <t>RR1475</t>
@@ -20128,6 +20113,229 @@
   </si>
   <si>
     <t>準備好你的弓箭，面對排山倒海的敵人了嗎？《弓箭英雄：塔防》是一款結合了塔防策略與Roguelite元素的超休閒遊戲。每次升級都能三選一技能，是要彈射、冰凍還是連射？選錯了可能下一秒就躺平。玩家們都在瘋狂尋找最新的兌換碼，希望能開局就拿到神裝。別忘了，強大的火力支援是守塔的關鍵，這時候就需要可靠的代儲值服務來幫你一把。想要穩穩通關，拿到稀有的禮包碼獎勵嗎？與其苦苦硬撐，不如尋求快速安全的代儲值，讓你的箭塔升到滿級，輕鬆碾壓所有來犯的敵人，成為真正的塔防大師！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>8500星之彩</t>
+  </si>
+  <si>
+    <t>4300星之彩</t>
+  </si>
+  <si>
+    <t>2200星之彩</t>
+  </si>
+  <si>
+    <t>1015星之彩</t>
+  </si>
+  <si>
+    <t>490星之彩</t>
+  </si>
+  <si>
+    <t>230星之彩</t>
+  </si>
+  <si>
+    <t>75星之彩</t>
+  </si>
+  <si>
+    <t>盈月星願</t>
+  </si>
+  <si>
+    <t>485000金幣</t>
+  </si>
+  <si>
+    <t>237000金幣</t>
+  </si>
+  <si>
+    <t>137000金幣</t>
+  </si>
+  <si>
+    <t>67000金幣</t>
+  </si>
+  <si>
+    <t>金幣定額券A</t>
+  </si>
+  <si>
+    <t>金幣定額券B</t>
+  </si>
+  <si>
+    <t>金幣定額券C</t>
+  </si>
+  <si>
+    <t>6000古玉</t>
+  </si>
+  <si>
+    <t>3000古玉</t>
+  </si>
+  <si>
+    <t>1800古玉</t>
+  </si>
+  <si>
+    <t>1200古玉</t>
+  </si>
+  <si>
+    <t>900古玉</t>
+  </si>
+  <si>
+    <t>600古玉</t>
+  </si>
+  <si>
+    <t>300古玉</t>
+  </si>
+  <si>
+    <t>60古玉</t>
+  </si>
+  <si>
+    <t>簽到基金</t>
+  </si>
+  <si>
+    <t>自選SP+神兵</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COACH2025 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLAYERXP5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEAMFUND3K</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NBA2025LEGEND</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIPGIFT2025</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教練經驗*1000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>球員經驗*5000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>球隊資金*3000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>隨機金卡*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特訓材料*100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲內點設定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>進到兌換碼畫面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOSS666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BB666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XY666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NIU666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNA666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>APRIL666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SARA666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>古玉*100+招募帖*2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>古玉*100+突破晶石*200</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>古玉*100+金幣*10萬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>招募帖*2+水晶補給大*3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>招募帖*2+金幣補給大*3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>招募帖*2+修為補給大*3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>古玉*300+武將修為*20萬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>古玉*300+突破晶石*300</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>招募帖*2+金幣補給大*3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>招募帖*2+金幣補給大*3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>招募帖*2+水晶補給大*3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>古玉*300+友情點*100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>古玉*300+金幣*20萬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陣營招募帖*1+水晶補給大*3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陣營招募帖*2+招募帖*2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -27278,7 +27486,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/電鋸果汁大亂鬥.html</v>
       </c>
       <c r="I109" s="45" t="s">
-        <v>5142</v>
+        <v>5137</v>
       </c>
       <c r="J109" s="59" t="s">
         <v>1275</v>
@@ -35748,10 +35956,10 @@
         <v>85</v>
       </c>
       <c r="AH223" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AI223" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="224" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -35818,10 +36026,10 @@
         <v>28</v>
       </c>
       <c r="V224" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="W224" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="225" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -35934,10 +36142,10 @@
         <v>124</v>
       </c>
       <c r="V226" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="W226" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="227" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36034,10 +36242,10 @@
         <v>519</v>
       </c>
       <c r="AF227" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AG227" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="228" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36128,10 +36336,10 @@
         <v>27</v>
       </c>
       <c r="AD228" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE228" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="229" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36159,7 +36367,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/呷飽未？殭殭醬.html</v>
       </c>
       <c r="I229" s="66" t="s">
-        <v>5143</v>
+        <v>5138</v>
       </c>
       <c r="J229" s="59" t="s">
         <v>3720</v>
@@ -36222,15 +36430,15 @@
         <v>132</v>
       </c>
       <c r="AD229" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE229" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="230" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
       <c r="A230" s="54" t="s">
-        <v>5134</v>
+        <v>5129</v>
       </c>
       <c r="C230" s="36" t="s">
         <v>4180</v>
@@ -36253,7 +36461,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/XXL猛漢町.html</v>
       </c>
       <c r="I230" s="66" t="s">
-        <v>5144</v>
+        <v>5139</v>
       </c>
       <c r="J230" s="52" t="s">
         <v>4231</v>
@@ -36328,15 +36536,15 @@
         <v>329</v>
       </c>
       <c r="AH230" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AI230" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="231" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
       <c r="A231" s="54" t="s">
-        <v>5135</v>
+        <v>5130</v>
       </c>
       <c r="C231" s="79" t="s">
         <v>4190</v>
@@ -36359,7 +36567,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Dead Impact：Survival Online.html</v>
       </c>
       <c r="I231" s="66" t="s">
-        <v>5145</v>
+        <v>5140</v>
       </c>
       <c r="J231" s="59" t="s">
         <v>4159</v>
@@ -36416,10 +36624,10 @@
         <v>535</v>
       </c>
       <c r="AB231" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AC231" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="232" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36447,7 +36655,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/無限子彈.html</v>
       </c>
       <c r="I232" s="66" t="s">
-        <v>5146</v>
+        <v>5141</v>
       </c>
       <c r="J232" s="59" t="s">
         <v>4167</v>
@@ -36510,10 +36718,10 @@
         <v>279</v>
       </c>
       <c r="AD232" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE232" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="233" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36541,7 +36749,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Dunkadillo.html</v>
       </c>
       <c r="I233" s="66" t="s">
-        <v>5147</v>
+        <v>5142</v>
       </c>
       <c r="J233" s="59" t="s">
         <v>4175</v>
@@ -36638,10 +36846,10 @@
         <v>83</v>
       </c>
       <c r="AD234" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE234" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="235" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36726,10 +36934,10 @@
         <v>74</v>
       </c>
       <c r="AB235" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AC235" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="236" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36826,10 +37034,10 @@
         <v>27</v>
       </c>
       <c r="AF236" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AG236" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="237" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36920,10 +37128,10 @@
         <v>27</v>
       </c>
       <c r="AD237" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE237" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="238" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36996,10 +37204,10 @@
         <v>27</v>
       </c>
       <c r="X238" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="Y238" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="239" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37084,10 +37292,10 @@
         <v>256</v>
       </c>
       <c r="AB239" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AC239" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="240" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37154,10 +37362,10 @@
         <v>50</v>
       </c>
       <c r="V240" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="W240" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="241" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37185,7 +37393,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/玩具對決.html</v>
       </c>
       <c r="I241" s="66" t="s">
-        <v>5148</v>
+        <v>5143</v>
       </c>
       <c r="J241" s="52" t="s">
         <v>4432</v>
@@ -37242,10 +37450,10 @@
         <v>124</v>
       </c>
       <c r="AB241" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AC241" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="242" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37273,7 +37481,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/幸福都市：市長模擬器.html</v>
       </c>
       <c r="I242" s="66" t="s">
-        <v>5149</v>
+        <v>5144</v>
       </c>
       <c r="J242" s="52" t="s">
         <v>301</v>
@@ -37318,10 +37526,10 @@
         <v>248</v>
       </c>
       <c r="X242" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="Y242" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="243" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37349,7 +37557,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/黑道傳奇.html</v>
       </c>
       <c r="I243" s="66" t="s">
-        <v>5150</v>
+        <v>5145</v>
       </c>
       <c r="J243" s="52" t="s">
         <v>4437</v>
@@ -37406,15 +37614,15 @@
         <v>57</v>
       </c>
       <c r="AB243" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AC243" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="244" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A244" s="54" t="s">
-        <v>5136</v>
+        <v>5131</v>
       </c>
       <c r="C244" s="36" t="s">
         <v>3626</v>
@@ -37437,7 +37645,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/The kingdom：medieval tales.html</v>
       </c>
       <c r="I244" s="66" t="s">
-        <v>5151</v>
+        <v>5146</v>
       </c>
       <c r="J244" s="52" t="s">
         <v>301</v>
@@ -37500,15 +37708,15 @@
         <v>612</v>
       </c>
       <c r="AD244" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE244" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="245" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A245" s="54" t="s">
-        <v>5137</v>
+        <v>5132</v>
       </c>
       <c r="C245" s="79" t="s">
         <v>4473</v>
@@ -37576,10 +37784,10 @@
         <v>256</v>
       </c>
       <c r="X245" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="Y245" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="246" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37610,7 +37818,7 @@
         <v>4470</v>
       </c>
       <c r="J246" s="52" t="s">
-        <v>5138</v>
+        <v>5133</v>
       </c>
       <c r="K246" s="51">
         <v>1139</v>
@@ -37634,10 +37842,10 @@
         <v>25</v>
       </c>
       <c r="R246" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="S246" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="247" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37710,10 +37918,10 @@
         <v>29</v>
       </c>
       <c r="X247" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="Y247" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="248" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37798,10 +38006,10 @@
         <v>25</v>
       </c>
       <c r="AB248" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AC248" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="249" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37880,10 +38088,10 @@
         <v>27</v>
       </c>
       <c r="Z249" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AA249" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="250" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37956,10 +38164,10 @@
         <v>33</v>
       </c>
       <c r="X250" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="Y250" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="251" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38026,10 +38234,10 @@
         <v>25</v>
       </c>
       <c r="V251" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="W251" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="252" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38120,10 +38328,10 @@
         <v>124</v>
       </c>
       <c r="AD252" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE252" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="253" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38220,10 +38428,10 @@
         <v>107</v>
       </c>
       <c r="AF253" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AG253" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="254" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38272,7 +38480,7 @@
         <v>380</v>
       </c>
       <c r="P254" s="52" t="s">
-        <v>5139</v>
+        <v>5134</v>
       </c>
       <c r="Q254" s="54">
         <v>194</v>
@@ -38302,10 +38510,10 @@
         <v>74</v>
       </c>
       <c r="Z254" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AA254" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="255" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38378,10 +38586,10 @@
         <v>216</v>
       </c>
       <c r="X255" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="Y255" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="256" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38454,10 +38662,10 @@
         <v>6095</v>
       </c>
       <c r="X256" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="Y256" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="257" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38548,10 +38756,10 @@
         <v>551</v>
       </c>
       <c r="AD257" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE257" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="258" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38648,10 +38856,10 @@
         <v>1725</v>
       </c>
       <c r="AF258" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AG258" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="259" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38736,10 +38944,10 @@
         <v>630</v>
       </c>
       <c r="AB259" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AC259" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="260" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38830,10 +39038,10 @@
         <v>551</v>
       </c>
       <c r="AD260" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE260" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="261" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38912,10 +39120,10 @@
         <v>1173</v>
       </c>
       <c r="Z261" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AA261" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="262" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38982,15 +39190,15 @@
         <v>77</v>
       </c>
       <c r="V262" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="W262" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="263" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
       <c r="A263" s="66" t="s">
-        <v>5140</v>
+        <v>5135</v>
       </c>
       <c r="C263" s="79" t="s">
         <v>4777</v>
@@ -39088,10 +39296,10 @@
         <v>26</v>
       </c>
       <c r="AH263" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AI263" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="264" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39147,7 +39355,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/幻牌交鋒.html</v>
       </c>
       <c r="I265" s="66" t="s">
-        <v>5152</v>
+        <v>5147</v>
       </c>
       <c r="J265" s="52" t="s">
         <v>4830</v>
@@ -39210,10 +39418,10 @@
         <v>162</v>
       </c>
       <c r="AD265" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE265" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="266" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39292,10 +39500,10 @@
         <v>29</v>
       </c>
       <c r="Z266" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AA266" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="267" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39386,10 +39594,10 @@
         <v>196</v>
       </c>
       <c r="AD267" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE267" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="268" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39480,10 +39688,10 @@
         <v>145</v>
       </c>
       <c r="AD268" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE268" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="269" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39568,10 +39776,10 @@
         <v>26</v>
       </c>
       <c r="AB269" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AC269" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="270" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39626,10 +39834,10 @@
         <v>227</v>
       </c>
       <c r="R270" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="S270" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="271" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39720,10 +39928,10 @@
         <v>314</v>
       </c>
       <c r="AD271" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE271" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="272" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39796,10 +40004,10 @@
         <v>29</v>
       </c>
       <c r="X272" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="Y272" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="273" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -39890,10 +40098,10 @@
         <v>160</v>
       </c>
       <c r="AD273" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE273" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="274" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -39984,10 +40192,10 @@
         <v>2343</v>
       </c>
       <c r="AD274" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE274" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="275" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40066,10 +40274,10 @@
         <v>141</v>
       </c>
       <c r="Z275" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AA275" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="276" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40099,47 +40307,59 @@
       <c r="I276" s="38" t="s">
         <v>5087</v>
       </c>
-      <c r="J276" s="52" t="s">
-        <v>107</v>
-      </c>
-      <c r="K276" s="54">
-        <v>124</v>
-      </c>
-      <c r="L276" s="52" t="s">
-        <v>5108</v>
-      </c>
-      <c r="M276" s="54">
-        <v>207</v>
-      </c>
-      <c r="N276" s="52" t="s">
-        <v>5109</v>
-      </c>
-      <c r="O276" s="54">
-        <v>475</v>
-      </c>
-      <c r="P276" s="52" t="s">
-        <v>5110</v>
-      </c>
-      <c r="Q276" s="54">
-        <v>475</v>
-      </c>
-      <c r="R276" s="52" t="s">
-        <v>5111</v>
-      </c>
-      <c r="S276" s="54">
-        <v>269</v>
-      </c>
-      <c r="T276" s="52" t="s">
-        <v>5112</v>
-      </c>
-      <c r="U276" s="54">
-        <v>388</v>
-      </c>
-      <c r="V276" s="82" t="s">
-        <v>5169</v>
-      </c>
-      <c r="W276" s="85" t="s">
+      <c r="J276" s="1" t="s">
+        <v>5275</v>
+      </c>
+      <c r="K276" s="58">
+        <v>2477</v>
+      </c>
+      <c r="L276" s="1" t="s">
         <v>5276</v>
+      </c>
+      <c r="M276" s="58">
+        <v>1346</v>
+      </c>
+      <c r="N276" s="1" t="s">
+        <v>5277</v>
+      </c>
+      <c r="O276" s="58">
+        <v>713</v>
+      </c>
+      <c r="P276" s="1" t="s">
+        <v>5278</v>
+      </c>
+      <c r="Q276" s="58">
+        <v>340</v>
+      </c>
+      <c r="R276" s="1" t="s">
+        <v>5279</v>
+      </c>
+      <c r="S276" s="58">
+        <v>169</v>
+      </c>
+      <c r="T276" s="1" t="s">
+        <v>5280</v>
+      </c>
+      <c r="U276" s="58">
+        <v>82</v>
+      </c>
+      <c r="V276" s="1" t="s">
+        <v>5281</v>
+      </c>
+      <c r="W276" s="58">
+        <v>30</v>
+      </c>
+      <c r="X276" s="1" t="s">
+        <v>5282</v>
+      </c>
+      <c r="Y276" s="58">
+        <v>133</v>
+      </c>
+      <c r="Z276" s="82" t="s">
+        <v>5164</v>
+      </c>
+      <c r="AA276" s="85" t="s">
+        <v>5271</v>
       </c>
     </row>
     <row r="277" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40182,13 +40402,13 @@
         <v>1389</v>
       </c>
       <c r="N277" s="83" t="s">
-        <v>5172</v>
+        <v>5167</v>
       </c>
       <c r="O277" s="84">
         <v>821</v>
       </c>
       <c r="P277" s="83" t="s">
-        <v>5173</v>
+        <v>5168</v>
       </c>
       <c r="Q277" s="84">
         <v>407</v>
@@ -40206,7 +40426,7 @@
         <v>29</v>
       </c>
       <c r="V277" s="83" t="s">
-        <v>5174</v>
+        <v>5169</v>
       </c>
       <c r="W277" s="84">
         <v>147</v>
@@ -40214,10 +40434,10 @@
       <c r="X277" s="52"/>
       <c r="Y277" s="54"/>
       <c r="Z277" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AA277" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="278" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40308,10 +40528,10 @@
         <v>261</v>
       </c>
       <c r="AD278" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE278" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="279" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40396,202 +40616,202 @@
         <v>141</v>
       </c>
       <c r="AB279" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AC279" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="280" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A280" s="54" t="s">
-        <v>5131</v>
+        <v>5126</v>
       </c>
       <c r="C280" s="36" t="s">
-        <v>5128</v>
+        <v>5123</v>
       </c>
       <c r="D280" s="37" t="s">
-        <v>5129</v>
+        <v>5124</v>
       </c>
       <c r="E280" s="37" t="s">
-        <v>5127</v>
+        <v>5122</v>
       </c>
       <c r="F280" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=電馭跑酷</v>
       </c>
       <c r="G280" s="44" t="s">
-        <v>5132</v>
+        <v>5127</v>
       </c>
       <c r="H280" s="37" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/電馭跑酷.html</v>
       </c>
       <c r="I280" s="66" t="s">
-        <v>5170</v>
+        <v>5165</v>
       </c>
       <c r="J280" s="83" t="s">
-        <v>5153</v>
+        <v>5148</v>
       </c>
       <c r="K280" s="84">
         <v>2302</v>
       </c>
       <c r="L280" s="83" t="s">
-        <v>5154</v>
+        <v>5149</v>
       </c>
       <c r="M280" s="84">
         <v>1168</v>
       </c>
       <c r="N280" s="83" t="s">
-        <v>5155</v>
+        <v>5150</v>
       </c>
       <c r="O280" s="84">
         <v>467</v>
       </c>
       <c r="P280" s="83" t="s">
-        <v>5156</v>
+        <v>5151</v>
       </c>
       <c r="Q280" s="84">
         <v>248</v>
       </c>
       <c r="R280" s="83" t="s">
-        <v>5157</v>
+        <v>5152</v>
       </c>
       <c r="S280" s="84">
         <v>124</v>
       </c>
       <c r="T280" s="83" t="s">
-        <v>5158</v>
+        <v>5153</v>
       </c>
       <c r="U280" s="84">
         <v>51</v>
       </c>
       <c r="V280" s="83" t="s">
-        <v>5159</v>
+        <v>5154</v>
       </c>
       <c r="W280" s="84">
         <v>248</v>
       </c>
       <c r="X280" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="Y280" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="281" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A281" s="54" t="s">
-        <v>5141</v>
+        <v>5136</v>
       </c>
       <c r="C281" s="36" t="s">
-        <v>5130</v>
+        <v>5125</v>
       </c>
       <c r="D281" s="37" t="s">
-        <v>5126</v>
+        <v>5121</v>
       </c>
       <c r="E281" s="37" t="s">
-        <v>5125</v>
+        <v>5120</v>
       </c>
       <c r="F281" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=火焰紋章Shadows</v>
       </c>
       <c r="G281" s="44" t="s">
-        <v>5133</v>
+        <v>5128</v>
       </c>
       <c r="H281" s="37" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/火焰紋章Shadows.html</v>
       </c>
       <c r="I281" s="66" t="s">
-        <v>5171</v>
+        <v>5166</v>
       </c>
       <c r="J281" s="83" t="s">
-        <v>5160</v>
+        <v>5155</v>
       </c>
       <c r="K281" s="84">
         <v>1549</v>
       </c>
       <c r="L281" s="83" t="s">
-        <v>5161</v>
+        <v>5156</v>
       </c>
       <c r="M281" s="84">
         <v>1030</v>
       </c>
       <c r="N281" s="83" t="s">
-        <v>5162</v>
+        <v>5157</v>
       </c>
       <c r="O281" s="84">
         <v>673</v>
       </c>
       <c r="P281" s="83" t="s">
-        <v>5163</v>
+        <v>5158</v>
       </c>
       <c r="Q281" s="84">
         <v>344</v>
       </c>
       <c r="R281" s="83" t="s">
-        <v>5164</v>
+        <v>5159</v>
       </c>
       <c r="S281" s="84">
         <v>157</v>
       </c>
       <c r="T281" s="83" t="s">
-        <v>5165</v>
+        <v>5160</v>
       </c>
       <c r="U281" s="84">
         <v>81</v>
       </c>
       <c r="V281" s="83" t="s">
-        <v>5166</v>
+        <v>5161</v>
       </c>
       <c r="W281" s="84">
         <v>17</v>
       </c>
       <c r="X281" s="83" t="s">
-        <v>5167</v>
+        <v>5162</v>
       </c>
       <c r="Y281" s="84">
         <v>244</v>
       </c>
       <c r="Z281" s="83" t="s">
-        <v>5168</v>
+        <v>5163</v>
       </c>
       <c r="AA281" s="84">
         <v>139</v>
       </c>
       <c r="AB281" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AC281" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="282" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A282" s="84" t="s">
-        <v>5222</v>
+        <v>5217</v>
       </c>
       <c r="C282" s="36" t="s">
-        <v>5175</v>
+        <v>5170</v>
       </c>
       <c r="D282" s="37" t="s">
-        <v>5176</v>
+        <v>5171</v>
       </c>
       <c r="E282" s="37" t="s">
-        <v>5177</v>
+        <v>5172</v>
       </c>
       <c r="F282" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=石器時代：寵物世界</v>
       </c>
       <c r="G282" s="82" t="s">
-        <v>5199</v>
+        <v>5194</v>
       </c>
       <c r="H282" s="37" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/石器時代：寵物世界.html</v>
       </c>
       <c r="I282" s="38" t="s">
-        <v>5202</v>
+        <v>5197</v>
       </c>
       <c r="J282" s="83" t="s">
         <v>4988</v>
@@ -40606,25 +40826,25 @@
         <v>2047</v>
       </c>
       <c r="N282" s="83" t="s">
-        <v>5184</v>
+        <v>5179</v>
       </c>
       <c r="O282" s="84">
         <v>1357</v>
       </c>
       <c r="P282" s="83" t="s">
-        <v>5185</v>
+        <v>5180</v>
       </c>
       <c r="Q282" s="84">
         <v>1085</v>
       </c>
       <c r="R282" s="83" t="s">
-        <v>5186</v>
+        <v>5181</v>
       </c>
       <c r="S282" s="84">
         <v>822</v>
       </c>
       <c r="T282" s="83" t="s">
-        <v>5187</v>
+        <v>5182</v>
       </c>
       <c r="U282" s="84">
         <v>680</v>
@@ -40642,7 +40862,7 @@
         <v>407</v>
       </c>
       <c r="Z282" s="83" t="s">
-        <v>5188</v>
+        <v>5183</v>
       </c>
       <c r="AA282" s="84">
         <v>357</v>
@@ -40654,217 +40874,217 @@
         <v>274</v>
       </c>
       <c r="AD282" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE282" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="283" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A283" s="84" t="s">
-        <v>5197</v>
+        <v>5192</v>
       </c>
       <c r="C283" s="36" t="s">
-        <v>5178</v>
+        <v>5173</v>
       </c>
       <c r="D283" s="37" t="s">
-        <v>5179</v>
+        <v>5174</v>
       </c>
       <c r="E283" s="37" t="s">
-        <v>5180</v>
+        <v>5175</v>
       </c>
       <c r="F283" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=蔚藍星球：國王很忙</v>
       </c>
       <c r="G283" s="82" t="s">
-        <v>5200</v>
+        <v>5195</v>
       </c>
       <c r="H283" s="37" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/蔚藍星球：國王很忙.html</v>
       </c>
       <c r="I283" s="38" t="s">
-        <v>5203</v>
+        <v>5198</v>
       </c>
       <c r="J283" s="83" t="s">
-        <v>5189</v>
+        <v>5184</v>
       </c>
       <c r="K283" s="84">
         <v>2655</v>
       </c>
       <c r="L283" s="83" t="s">
-        <v>5190</v>
+        <v>5185</v>
       </c>
       <c r="M283" s="84">
         <v>1644</v>
       </c>
       <c r="N283" s="83" t="s">
-        <v>5191</v>
+        <v>5186</v>
       </c>
       <c r="O283" s="84">
         <v>1389</v>
       </c>
       <c r="P283" s="83" t="s">
-        <v>5192</v>
+        <v>5187</v>
       </c>
       <c r="Q283" s="84">
         <v>821</v>
       </c>
       <c r="R283" s="83" t="s">
-        <v>5193</v>
+        <v>5188</v>
       </c>
       <c r="S283" s="84">
         <v>655</v>
       </c>
       <c r="T283" s="83" t="s">
-        <v>5194</v>
+        <v>5189</v>
       </c>
       <c r="U283" s="84">
         <v>407</v>
       </c>
       <c r="V283" s="83" t="s">
-        <v>5195</v>
+        <v>5190</v>
       </c>
       <c r="W283" s="84">
         <v>274</v>
       </c>
       <c r="X283" s="83" t="s">
-        <v>5196</v>
+        <v>5191</v>
       </c>
       <c r="Y283" s="84">
         <v>147</v>
       </c>
       <c r="Z283" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AA283" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="284" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A284" s="84" t="s">
-        <v>5198</v>
+        <v>5193</v>
       </c>
       <c r="C284" s="36" t="s">
-        <v>5181</v>
+        <v>5176</v>
       </c>
       <c r="D284" s="37" t="s">
-        <v>5182</v>
+        <v>5177</v>
       </c>
       <c r="E284" s="37" t="s">
-        <v>5183</v>
+        <v>5178</v>
       </c>
       <c r="F284" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=胸懷三國：美人計</v>
       </c>
       <c r="G284" s="82" t="s">
-        <v>5201</v>
+        <v>5196</v>
       </c>
       <c r="H284" s="37" t="str">
         <f t="shared" ref="H284:H312" si="13">IF(A284="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A284)</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=胸懷三國：美人計</v>
       </c>
       <c r="I284" s="38" t="s">
-        <v>5204</v>
-      </c>
-      <c r="J284" s="83" t="s">
-        <v>4988</v>
-      </c>
-      <c r="K284" s="84">
-        <v>2655</v>
-      </c>
-      <c r="L284" s="83" t="s">
-        <v>1674</v>
-      </c>
-      <c r="M284" s="84">
-        <v>2047</v>
-      </c>
-      <c r="N284" s="83" t="s">
-        <v>5184</v>
-      </c>
-      <c r="O284" s="84">
-        <v>1357</v>
-      </c>
-      <c r="P284" s="83" t="s">
-        <v>5185</v>
-      </c>
-      <c r="Q284" s="84">
-        <v>1085</v>
-      </c>
-      <c r="R284" s="83" t="s">
-        <v>5186</v>
-      </c>
-      <c r="S284" s="84">
-        <v>822</v>
-      </c>
-      <c r="T284" s="83" t="s">
-        <v>5187</v>
-      </c>
-      <c r="U284" s="84">
-        <v>680</v>
-      </c>
-      <c r="V284" s="83" t="s">
-        <v>152</v>
-      </c>
-      <c r="W284" s="84">
-        <v>572</v>
-      </c>
-      <c r="X284" s="83" t="s">
-        <v>153</v>
-      </c>
-      <c r="Y284" s="84">
-        <v>407</v>
-      </c>
-      <c r="Z284" s="83" t="s">
-        <v>5188</v>
-      </c>
-      <c r="AA284" s="84">
-        <v>357</v>
-      </c>
-      <c r="AB284" s="83" t="s">
-        <v>1680</v>
-      </c>
-      <c r="AC284" s="84">
-        <v>274</v>
+        <v>5199</v>
+      </c>
+      <c r="J284" s="1" t="s">
+        <v>5290</v>
+      </c>
+      <c r="K284" s="58">
+        <v>2717</v>
+      </c>
+      <c r="L284" s="1" t="s">
+        <v>5291</v>
+      </c>
+      <c r="M284" s="58">
+        <v>1388</v>
+      </c>
+      <c r="N284" s="1" t="s">
+        <v>5292</v>
+      </c>
+      <c r="O284" s="58">
+        <v>841</v>
+      </c>
+      <c r="P284" s="1" t="s">
+        <v>5293</v>
+      </c>
+      <c r="Q284" s="58">
+        <v>586</v>
+      </c>
+      <c r="R284" s="1" t="s">
+        <v>5294</v>
+      </c>
+      <c r="S284" s="58">
+        <v>416</v>
+      </c>
+      <c r="T284" s="1" t="s">
+        <v>5295</v>
+      </c>
+      <c r="U284" s="58">
+        <v>280</v>
+      </c>
+      <c r="V284" s="1" t="s">
+        <v>5296</v>
+      </c>
+      <c r="W284" s="58">
+        <v>146</v>
+      </c>
+      <c r="X284" s="1" t="s">
+        <v>5297</v>
+      </c>
+      <c r="Y284" s="58">
+        <v>30</v>
+      </c>
+      <c r="Z284" s="1" t="s">
+        <v>5298</v>
+      </c>
+      <c r="AA284" s="58">
+        <v>416</v>
+      </c>
+      <c r="AB284" s="1" t="s">
+        <v>5299</v>
+      </c>
+      <c r="AC284" s="58">
+        <v>586</v>
       </c>
       <c r="AD284" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="AE284" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="285" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A285" s="84" t="s">
-        <v>5249</v>
+        <v>5244</v>
       </c>
       <c r="C285" s="36" t="s">
-        <v>5247</v>
+        <v>5242</v>
       </c>
       <c r="D285" s="37" t="s">
-        <v>5248</v>
+        <v>5243</v>
       </c>
       <c r="E285" s="37" t="s">
-        <v>5237</v>
+        <v>5232</v>
       </c>
       <c r="F285" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=弓箭英雄：塔防</v>
       </c>
       <c r="G285" s="82" t="s">
-        <v>5250</v>
+        <v>5245</v>
       </c>
       <c r="H285" s="37" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=弓箭英雄：塔防</v>
       </c>
       <c r="I285" s="38" t="s">
-        <v>5279</v>
+        <v>5274</v>
       </c>
       <c r="J285" s="1" t="s">
-        <v>5274</v>
+        <v>5269</v>
       </c>
       <c r="K285" s="58">
         <v>2469</v>
@@ -40894,118 +41114,172 @@
         <v>133</v>
       </c>
       <c r="T285" s="1" t="s">
-        <v>5275</v>
+        <v>5270</v>
       </c>
       <c r="U285" s="58">
         <v>27</v>
       </c>
       <c r="V285" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="W285" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="286" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A286" s="84" t="s">
-        <v>5255</v>
+        <v>5250</v>
       </c>
       <c r="C286" s="36" t="s">
-        <v>5239</v>
+        <v>5234</v>
       </c>
       <c r="D286" s="37" t="s">
-        <v>5238</v>
+        <v>5233</v>
       </c>
       <c r="E286" s="37" t="s">
-        <v>5240</v>
+        <v>5235</v>
       </c>
       <c r="F286" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=十二之天M</v>
       </c>
       <c r="G286" s="82" t="s">
-        <v>5251</v>
+        <v>5246</v>
       </c>
       <c r="H286" s="37" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=十二之天M</v>
       </c>
       <c r="I286" s="66" t="s">
+        <v>5266</v>
+      </c>
+      <c r="J286" s="1" t="s">
+        <v>5283</v>
+      </c>
+      <c r="K286" s="58">
+        <v>2717</v>
+      </c>
+      <c r="L286" s="1" t="s">
+        <v>5284</v>
+      </c>
+      <c r="M286" s="58">
+        <v>1422</v>
+      </c>
+      <c r="N286" s="1" t="s">
+        <v>5285</v>
+      </c>
+      <c r="O286" s="58">
+        <v>840</v>
+      </c>
+      <c r="P286" s="1" t="s">
+        <v>5286</v>
+      </c>
+      <c r="Q286" s="58">
+        <v>416</v>
+      </c>
+      <c r="R286" s="1" t="s">
+        <v>1536</v>
+      </c>
+      <c r="S286" s="58">
+        <v>151</v>
+      </c>
+      <c r="T286" s="1" t="s">
+        <v>1538</v>
+      </c>
+      <c r="U286" s="58">
+        <v>30</v>
+      </c>
+      <c r="V286" s="1" t="s">
+        <v>5287</v>
+      </c>
+      <c r="W286" s="58">
+        <v>213</v>
+      </c>
+      <c r="X286" s="1" t="s">
+        <v>5288</v>
+      </c>
+      <c r="Y286" s="58">
+        <v>357</v>
+      </c>
+      <c r="Z286" s="1" t="s">
+        <v>5289</v>
+      </c>
+      <c r="AA286" s="58">
+        <v>705</v>
+      </c>
+      <c r="AB286" s="82" t="s">
+        <v>5164</v>
+      </c>
+      <c r="AC286" s="85" t="s">
         <v>5271</v>
-      </c>
-      <c r="J286" s="82" t="s">
-        <v>5169</v>
-      </c>
-      <c r="K286" s="85" t="s">
-        <v>5276</v>
       </c>
     </row>
     <row r="287" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A287" s="84" t="s">
-        <v>5256</v>
+        <v>5251</v>
       </c>
       <c r="C287" s="36" t="s">
-        <v>5243</v>
+        <v>5238</v>
       </c>
       <c r="D287" s="37" t="s">
-        <v>5242</v>
+        <v>5237</v>
       </c>
       <c r="E287" s="37" t="s">
-        <v>5241</v>
+        <v>5236</v>
       </c>
       <c r="F287" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=NBA巔峰對決</v>
       </c>
       <c r="G287" s="82" t="s">
-        <v>5252</v>
+        <v>5247</v>
       </c>
       <c r="H287" s="37" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=NBA巔峰對決</v>
       </c>
       <c r="I287" s="38" t="s">
-        <v>5272</v>
+        <v>5267</v>
       </c>
       <c r="J287" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="K287" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="288" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A288" s="84" t="s">
-        <v>5253</v>
+        <v>5248</v>
       </c>
       <c r="C288" s="36" t="s">
-        <v>5246</v>
+        <v>5241</v>
       </c>
       <c r="D288" s="37" t="s">
-        <v>5245</v>
+        <v>5240</v>
       </c>
       <c r="E288" s="37" t="s">
-        <v>5244</v>
+        <v>5239</v>
       </c>
       <c r="F288" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=三國志：王戰</v>
       </c>
       <c r="G288" s="82" t="s">
-        <v>5254</v>
+        <v>5249</v>
       </c>
       <c r="H288" s="37" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=三國志：王戰</v>
       </c>
       <c r="I288" s="38" t="s">
-        <v>5273</v>
+        <v>5268</v>
       </c>
       <c r="J288" s="82" t="s">
-        <v>5169</v>
+        <v>5164</v>
       </c>
       <c r="K288" s="85" t="s">
-        <v>5276</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="289" spans="6:8" ht="22.5" customHeight="1">
@@ -44409,60 +44683,60 @@
     <hyperlink ref="AB279" r:id="rId227"/>
     <hyperlink ref="AD278" r:id="rId228"/>
     <hyperlink ref="Z277" r:id="rId229"/>
-    <hyperlink ref="V276" r:id="rId230"/>
-    <hyperlink ref="Z275" r:id="rId231"/>
-    <hyperlink ref="AD274" r:id="rId232"/>
-    <hyperlink ref="AD273" r:id="rId233"/>
-    <hyperlink ref="X272" r:id="rId234"/>
-    <hyperlink ref="AD271" r:id="rId235"/>
-    <hyperlink ref="R270" r:id="rId236"/>
-    <hyperlink ref="AB269" r:id="rId237"/>
-    <hyperlink ref="AD268" r:id="rId238"/>
-    <hyperlink ref="AD267" r:id="rId239"/>
-    <hyperlink ref="Z266" r:id="rId240"/>
-    <hyperlink ref="AD265" r:id="rId241"/>
-    <hyperlink ref="AH263" r:id="rId242"/>
-    <hyperlink ref="V262" r:id="rId243"/>
-    <hyperlink ref="Z261" r:id="rId244"/>
-    <hyperlink ref="AD260" r:id="rId245"/>
-    <hyperlink ref="AB259" r:id="rId246"/>
-    <hyperlink ref="AF258" r:id="rId247"/>
-    <hyperlink ref="AD257" r:id="rId248"/>
-    <hyperlink ref="X256" r:id="rId249"/>
-    <hyperlink ref="X255" r:id="rId250"/>
-    <hyperlink ref="Z254" r:id="rId251"/>
-    <hyperlink ref="AF253" r:id="rId252"/>
-    <hyperlink ref="AD252" r:id="rId253"/>
-    <hyperlink ref="V251" r:id="rId254"/>
-    <hyperlink ref="X250" r:id="rId255"/>
-    <hyperlink ref="Z249" r:id="rId256"/>
-    <hyperlink ref="AB248" r:id="rId257"/>
-    <hyperlink ref="X247" r:id="rId258"/>
-    <hyperlink ref="R246" r:id="rId259"/>
-    <hyperlink ref="X245" r:id="rId260"/>
-    <hyperlink ref="AD244" r:id="rId261"/>
-    <hyperlink ref="AB243" r:id="rId262"/>
-    <hyperlink ref="X242" r:id="rId263"/>
-    <hyperlink ref="AB241" r:id="rId264"/>
-    <hyperlink ref="V240" r:id="rId265"/>
-    <hyperlink ref="AB239" r:id="rId266"/>
-    <hyperlink ref="X238" r:id="rId267"/>
-    <hyperlink ref="AD237" r:id="rId268"/>
-    <hyperlink ref="AF236" r:id="rId269"/>
-    <hyperlink ref="AB235" r:id="rId270"/>
-    <hyperlink ref="AD234" r:id="rId271"/>
-    <hyperlink ref="AD232" r:id="rId272"/>
-    <hyperlink ref="AB231" r:id="rId273"/>
-    <hyperlink ref="AH230" r:id="rId274"/>
-    <hyperlink ref="AD229" r:id="rId275"/>
-    <hyperlink ref="AD228" r:id="rId276"/>
-    <hyperlink ref="AF227" r:id="rId277"/>
-    <hyperlink ref="V226" r:id="rId278"/>
-    <hyperlink ref="V224" r:id="rId279"/>
-    <hyperlink ref="AH223" r:id="rId280"/>
-    <hyperlink ref="J287" r:id="rId281"/>
-    <hyperlink ref="J288" r:id="rId282"/>
-    <hyperlink ref="J286" r:id="rId283"/>
+    <hyperlink ref="Z275" r:id="rId230"/>
+    <hyperlink ref="AD274" r:id="rId231"/>
+    <hyperlink ref="AD273" r:id="rId232"/>
+    <hyperlink ref="X272" r:id="rId233"/>
+    <hyperlink ref="AD271" r:id="rId234"/>
+    <hyperlink ref="R270" r:id="rId235"/>
+    <hyperlink ref="AB269" r:id="rId236"/>
+    <hyperlink ref="AD268" r:id="rId237"/>
+    <hyperlink ref="AD267" r:id="rId238"/>
+    <hyperlink ref="Z266" r:id="rId239"/>
+    <hyperlink ref="AD265" r:id="rId240"/>
+    <hyperlink ref="AH263" r:id="rId241"/>
+    <hyperlink ref="V262" r:id="rId242"/>
+    <hyperlink ref="Z261" r:id="rId243"/>
+    <hyperlink ref="AD260" r:id="rId244"/>
+    <hyperlink ref="AB259" r:id="rId245"/>
+    <hyperlink ref="AF258" r:id="rId246"/>
+    <hyperlink ref="AD257" r:id="rId247"/>
+    <hyperlink ref="X256" r:id="rId248"/>
+    <hyperlink ref="X255" r:id="rId249"/>
+    <hyperlink ref="Z254" r:id="rId250"/>
+    <hyperlink ref="AF253" r:id="rId251"/>
+    <hyperlink ref="AD252" r:id="rId252"/>
+    <hyperlink ref="V251" r:id="rId253"/>
+    <hyperlink ref="X250" r:id="rId254"/>
+    <hyperlink ref="Z249" r:id="rId255"/>
+    <hyperlink ref="AB248" r:id="rId256"/>
+    <hyperlink ref="X247" r:id="rId257"/>
+    <hyperlink ref="R246" r:id="rId258"/>
+    <hyperlink ref="X245" r:id="rId259"/>
+    <hyperlink ref="AD244" r:id="rId260"/>
+    <hyperlink ref="AB243" r:id="rId261"/>
+    <hyperlink ref="X242" r:id="rId262"/>
+    <hyperlink ref="AB241" r:id="rId263"/>
+    <hyperlink ref="V240" r:id="rId264"/>
+    <hyperlink ref="AB239" r:id="rId265"/>
+    <hyperlink ref="X238" r:id="rId266"/>
+    <hyperlink ref="AD237" r:id="rId267"/>
+    <hyperlink ref="AF236" r:id="rId268"/>
+    <hyperlink ref="AB235" r:id="rId269"/>
+    <hyperlink ref="AD234" r:id="rId270"/>
+    <hyperlink ref="AD232" r:id="rId271"/>
+    <hyperlink ref="AB231" r:id="rId272"/>
+    <hyperlink ref="AH230" r:id="rId273"/>
+    <hyperlink ref="AD229" r:id="rId274"/>
+    <hyperlink ref="AD228" r:id="rId275"/>
+    <hyperlink ref="AF227" r:id="rId276"/>
+    <hyperlink ref="V226" r:id="rId277"/>
+    <hyperlink ref="V224" r:id="rId278"/>
+    <hyperlink ref="AH223" r:id="rId279"/>
+    <hyperlink ref="J287" r:id="rId280"/>
+    <hyperlink ref="J288" r:id="rId281"/>
+    <hyperlink ref="Z276" r:id="rId282"/>
+    <hyperlink ref="AB286" r:id="rId283"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId284"/>
@@ -59146,46 +59420,46 @@
         <v>5026</v>
       </c>
       <c r="W236" s="14" t="s">
+        <v>5218</v>
+      </c>
+      <c r="X236" s="9" t="s">
+        <v>5231</v>
+      </c>
+      <c r="Y236" s="14" t="s">
+        <v>5219</v>
+      </c>
+      <c r="Z236" s="9" t="s">
+        <v>5230</v>
+      </c>
+      <c r="AA236" s="14" t="s">
+        <v>5220</v>
+      </c>
+      <c r="AB236" s="9" t="s">
+        <v>5229</v>
+      </c>
+      <c r="AC236" s="14" t="s">
+        <v>5221</v>
+      </c>
+      <c r="AD236" s="9" t="s">
+        <v>5228</v>
+      </c>
+      <c r="AE236" s="14" t="s">
+        <v>5222</v>
+      </c>
+      <c r="AF236" s="9" t="s">
+        <v>5227</v>
+      </c>
+      <c r="AG236" s="14" t="s">
         <v>5223</v>
       </c>
-      <c r="X236" s="9" t="s">
-        <v>5236</v>
-      </c>
-      <c r="Y236" s="14" t="s">
+      <c r="AH236" s="9" t="s">
+        <v>5226</v>
+      </c>
+      <c r="AI236" s="14" t="s">
         <v>5224</v>
       </c>
-      <c r="Z236" s="9" t="s">
-        <v>5235</v>
-      </c>
-      <c r="AA236" s="14" t="s">
+      <c r="AJ236" s="9" t="s">
         <v>5225</v>
-      </c>
-      <c r="AB236" s="9" t="s">
-        <v>5234</v>
-      </c>
-      <c r="AC236" s="14" t="s">
-        <v>5226</v>
-      </c>
-      <c r="AD236" s="9" t="s">
-        <v>5233</v>
-      </c>
-      <c r="AE236" s="14" t="s">
-        <v>5227</v>
-      </c>
-      <c r="AF236" s="9" t="s">
-        <v>5232</v>
-      </c>
-      <c r="AG236" s="14" t="s">
-        <v>5228</v>
-      </c>
-      <c r="AH236" s="9" t="s">
-        <v>5231</v>
-      </c>
-      <c r="AI236" s="14" t="s">
-        <v>5229</v>
-      </c>
-      <c r="AJ236" s="9" t="s">
-        <v>5230</v>
       </c>
     </row>
     <row r="237" spans="1:47" ht="22.5" customHeight="1">
@@ -60527,10 +60801,10 @@
         <v>《Awakenloop》是一款充滿賽博龐克風格的卡牌回合制手遊，玩家將身處一個由機器人與人類共存的末日世界。遊戲主打策略性卡牌戰鬥，每張卡牌都蘊含獨特技能，如何搭配與釋放將成為戰局關鍵。除了豐富的主線劇情，遊戲也提供多樣的副本挑戰與 PvP 模式，讓你與其他玩家一較高下。現在就加入《Awakenloop》，透過兌換碼與禮包碼獲得專屬獎勵，輕鬆提升戰力，也能使用代儲值服務快速安全地補充資源，在這片混沌的廢土上開創屬於你的新紀元。</v>
       </c>
       <c r="F269" s="13" t="s">
-        <v>5209</v>
+        <v>5204</v>
       </c>
       <c r="G269" s="9" t="s">
-        <v>5210</v>
+        <v>5205</v>
       </c>
       <c r="H269" s="9" t="s">
         <v>2625</v>
@@ -60539,16 +60813,16 @@
         <v>4360</v>
       </c>
       <c r="K269" s="13" t="s">
-        <v>5205</v>
+        <v>5200</v>
       </c>
       <c r="L269" s="9" t="s">
-        <v>5208</v>
+        <v>5203</v>
       </c>
       <c r="M269" s="14" t="s">
-        <v>5206</v>
+        <v>5201</v>
       </c>
       <c r="N269" s="9" t="s">
-        <v>5207</v>
+        <v>5202</v>
       </c>
     </row>
     <row r="270" spans="1:31">
@@ -60647,7 +60921,7 @@
         <v>5049</v>
       </c>
     </row>
-    <row r="273" spans="1:30">
+    <row r="273" spans="1:40">
       <c r="A273" s="9" t="str">
         <f>IF(games!A273="", "", games!A273)</f>
         <v>盜夢英雄2：幻野</v>
@@ -60710,31 +60984,31 @@
         <v>5066</v>
       </c>
       <c r="W273" s="14" t="s">
+        <v>5209</v>
+      </c>
+      <c r="X273" s="9" t="s">
+        <v>5213</v>
+      </c>
+      <c r="Y273" s="14" t="s">
+        <v>5210</v>
+      </c>
+      <c r="Z273" s="9" t="s">
         <v>5214</v>
       </c>
-      <c r="X273" s="9" t="s">
-        <v>5218</v>
-      </c>
-      <c r="Y273" s="14" t="s">
+      <c r="AA273" s="14" t="s">
+        <v>5211</v>
+      </c>
+      <c r="AB273" s="9" t="s">
         <v>5215</v>
       </c>
-      <c r="Z273" s="9" t="s">
-        <v>5219</v>
-      </c>
-      <c r="AA273" s="14" t="s">
+      <c r="AC273" s="14" t="s">
+        <v>5212</v>
+      </c>
+      <c r="AD273" s="9" t="s">
         <v>5216</v>
       </c>
-      <c r="AB273" s="9" t="s">
-        <v>5220</v>
-      </c>
-      <c r="AC273" s="14" t="s">
-        <v>5217</v>
-      </c>
-      <c r="AD273" s="9" t="s">
-        <v>5221</v>
-      </c>
-    </row>
-    <row r="274" spans="1:30">
+    </row>
+    <row r="274" spans="1:40">
       <c r="A274" s="9" t="str">
         <f>IF(games!A274="", "", games!A274)</f>
         <v>貪婪洞窟：重生</v>
@@ -60782,7 +61056,7 @@
         <v>5001</v>
       </c>
     </row>
-    <row r="275" spans="1:30">
+    <row r="275" spans="1:40">
       <c r="A275" s="9" t="str">
         <f>IF(games!A275="", "", games!A275)</f>
         <v>小兵特攻隊</v>
@@ -60827,13 +61101,13 @@
         <v>5053</v>
       </c>
       <c r="O275" s="14" t="s">
-        <v>5113</v>
+        <v>5108</v>
       </c>
       <c r="Q275" s="14" t="s">
-        <v>5114</v>
+        <v>5109</v>
       </c>
       <c r="S275" s="14" t="s">
-        <v>5115</v>
+        <v>5110</v>
       </c>
       <c r="U275" s="14" t="s">
         <v>2056</v>
@@ -60842,10 +61116,10 @@
         <v>4560</v>
       </c>
       <c r="Y275" s="14" t="s">
-        <v>5116</v>
-      </c>
-    </row>
-    <row r="276" spans="1:30">
+        <v>5111</v>
+      </c>
+    </row>
+    <row r="276" spans="1:40">
       <c r="A276" s="9" t="str">
         <f>IF(games!A276="", "", games!A276)</f>
         <v>星塔旅人</v>
@@ -60863,31 +61137,31 @@
         <v>由艾瑞爾網路代理的銀河冒險 RPG《星塔旅人》正式登場！這趟星際之旅，你將化身為「星之活體」的持有者，與眾多獨具魅力的「旅人」相遇，共同踏上尋找銀河之心「星源晶核」的冒險。遊戲主打 Roguelike 要素與高自由度的戰鬥系統，讓每一次探索都充滿未知驚喜。為了讓各位玩家能更快養成心儀的角色，記得隨時關注官方釋出的最新兌換碼與禮包碼資訊。當然，若想在起跑點就遙遙領先，最方便的代儲值服務能提供您快速安全的課金管道，讓您的銀河霸業無後顧之憂！</v>
       </c>
       <c r="F276" s="77" t="s">
-        <v>5121</v>
+        <v>5116</v>
       </c>
       <c r="G276" s="9" t="s">
-        <v>5122</v>
+        <v>5117</v>
       </c>
       <c r="H276" s="9" t="s">
-        <v>5123</v>
+        <v>5118</v>
       </c>
       <c r="I276" s="9" t="s">
-        <v>5124</v>
+        <v>5119</v>
       </c>
       <c r="K276" s="13" t="s">
-        <v>5117</v>
+        <v>5112</v>
       </c>
       <c r="L276" s="9" t="s">
-        <v>5119</v>
+        <v>5114</v>
       </c>
       <c r="M276" s="14" t="s">
-        <v>5118</v>
+        <v>5113</v>
       </c>
       <c r="N276" s="9" t="s">
-        <v>5120</v>
-      </c>
-    </row>
-    <row r="277" spans="1:30">
+        <v>5115</v>
+      </c>
+    </row>
+    <row r="277" spans="1:40">
       <c r="A277" s="9" t="str">
         <f>IF(games!A277="", "", games!A277)</f>
         <v>卡厄斯夢境</v>
@@ -60923,7 +61197,7 @@
         <v>4810</v>
       </c>
     </row>
-    <row r="278" spans="1:30">
+    <row r="278" spans="1:40">
       <c r="A278" s="9" t="str">
         <f>IF(games!A278="", "", games!A278)</f>
         <v>星痕共鳴</v>
@@ -60941,28 +61215,28 @@
         <v>全新星緣卡牌 RPG《星痕共鳴》，邀你一同編織命運的篇章。遊戲擁有宏大的世界觀與超過百萬字的豐富劇情，玩家將扮演「星源之主」，與眾多「星痕者」締結羈絆，共同對抗虛空的威脅。獨特的「星盤」系統與高策略性的卡牌戰鬥，讓每場對決都充滿變數。想要輕鬆推圖、快速成長？記得在各大社群與論壇尋找隱藏的兌換碼與禮包碼，領取豐厚資源。如果想快人一步，最聰明的選擇就是尋找可靠的代儲值管道，提供您快速安全的支援，讓你的冒險旅程更加順遂。</v>
       </c>
       <c r="F278" s="13" t="s">
-        <v>5263</v>
+        <v>5258</v>
       </c>
       <c r="G278" s="9" t="s">
-        <v>5264</v>
+        <v>5259</v>
       </c>
       <c r="H278" s="9" t="s">
-        <v>5265</v>
+        <v>5260</v>
       </c>
       <c r="K278" s="13" t="s">
-        <v>5259</v>
+        <v>5254</v>
       </c>
       <c r="L278" s="9" t="s">
-        <v>5262</v>
+        <v>5257</v>
       </c>
       <c r="M278" s="14" t="s">
-        <v>5260</v>
+        <v>5255</v>
       </c>
       <c r="N278" s="9" t="s">
-        <v>5261</v>
-      </c>
-    </row>
-    <row r="279" spans="1:30">
+        <v>5256</v>
+      </c>
+    </row>
+    <row r="279" spans="1:40">
       <c r="A279" s="9" t="str">
         <f>IF(games!A279="", "", games!A279)</f>
         <v>二重螺旋</v>
@@ -60980,7 +61254,7 @@
         <v>備受矚目的 3D 動作 RPG《二重螺旋》強勢來襲！本作主打高速、爽快的戰鬥體驗，玩家將在一個近未來科幻世界中，扮演擁有特殊能力的「適格者」，探索神秘的「深淵」。遊戲強調華麗的連擊與多樣化的武器系統，你可以自由切換遠近程攻擊，打出屬於自己的戰鬥風格。為了讓你的探索之路更加順利，官方會不定期發放福利兌換碼與禮包碼，千萬別錯過。當然，面對強大的敵人，尋求專業的代儲值協助，以快速安全的方式強化戰力，絕對是高效的致勝關鍵。</v>
       </c>
       <c r="F279" s="13" t="s">
-        <v>5270</v>
+        <v>5265</v>
       </c>
       <c r="G279" s="9" t="s">
         <v>3641</v>
@@ -60992,19 +61266,19 @@
         <v>4360</v>
       </c>
       <c r="K279" s="13" t="s">
-        <v>5266</v>
+        <v>5261</v>
       </c>
       <c r="M279" s="14" t="s">
-        <v>5267</v>
+        <v>5262</v>
       </c>
       <c r="O279" s="14" t="s">
-        <v>5268</v>
+        <v>5263</v>
       </c>
       <c r="Q279" s="14" t="s">
-        <v>5269</v>
-      </c>
-    </row>
-    <row r="280" spans="1:30">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="280" spans="1:40">
       <c r="A280" s="9" t="str">
         <f>IF(games!A280="", "", games!A280)</f>
         <v>電馭跑酷</v>
@@ -61034,7 +61308,7 @@
         <v>4810</v>
       </c>
     </row>
-    <row r="281" spans="1:30">
+    <row r="281" spans="1:40">
       <c r="A281" s="9" t="str">
         <f>IF(games!A281="", "", games!A281)</f>
         <v>火焰紋章Shadows</v>
@@ -61064,7 +61338,7 @@
         <v>4810</v>
       </c>
     </row>
-    <row r="282" spans="1:30">
+    <row r="282" spans="1:40">
       <c r="A282" s="9" t="str">
         <f>IF(games!A282="", "", games!A282)</f>
         <v>石器時代：寵物世界</v>
@@ -61094,7 +61368,7 @@
         <v>4809</v>
       </c>
     </row>
-    <row r="283" spans="1:30">
+    <row r="283" spans="1:40">
       <c r="A283" s="9" t="str">
         <f>IF(games!A283="", "", games!A283)</f>
         <v>蔚藍星球：國王很忙</v>
@@ -61124,7 +61398,7 @@
         <v>4809</v>
       </c>
     </row>
-    <row r="284" spans="1:30">
+    <row r="284" spans="1:40">
       <c r="A284" s="9" t="str">
         <f>IF(games!A284="", "", games!A284)</f>
         <v>胸懷三國：美人計</v>
@@ -61142,22 +61416,106 @@
         <v>美少女三國RPG手遊參上！遊戲擁有眾多經典三國名將，搭配緊張刺激的養成戰鬥系統，讓玩家可以體驗高潮連擊的激爽和無限養成的快樂。獨特的武將風格立繪，在既定特色上增添更多風味，絕對是視覺饗宴。還在為了找不到最新的禮包碼而煩惱嗎？想要輕鬆養成武將，解鎖所有外觀，最聰明的方式就是尋找快速安全的代儲值管道，立即領取你的兌換碼福利，在三國世界中無往不利！</v>
       </c>
       <c r="F284" s="13" t="s">
-        <v>5211</v>
+        <v>5206</v>
       </c>
       <c r="G284" s="9" t="s">
-        <v>5212</v>
+        <v>5207</v>
       </c>
       <c r="H284" s="9" t="s">
-        <v>5213</v>
+        <v>5208</v>
       </c>
       <c r="K284" s="13" t="s">
-        <v>5277</v>
+        <v>5272</v>
+      </c>
+      <c r="L284" s="9" t="s">
+        <v>5336</v>
       </c>
       <c r="M284" s="14" t="s">
-        <v>5278</v>
-      </c>
-    </row>
-    <row r="285" spans="1:30">
+        <v>5273</v>
+      </c>
+      <c r="N284" s="9" t="s">
+        <v>5335</v>
+      </c>
+      <c r="O284" s="14" t="s">
+        <v>5312</v>
+      </c>
+      <c r="P284" s="9" t="s">
+        <v>5334</v>
+      </c>
+      <c r="Q284" s="14" t="s">
+        <v>5313</v>
+      </c>
+      <c r="R284" s="9" t="s">
+        <v>5333</v>
+      </c>
+      <c r="S284" s="14" t="s">
+        <v>5314</v>
+      </c>
+      <c r="T284" s="9" t="s">
+        <v>5332</v>
+      </c>
+      <c r="U284" s="14" t="s">
+        <v>5315</v>
+      </c>
+      <c r="V284" s="9" t="s">
+        <v>5331</v>
+      </c>
+      <c r="W284" s="14" t="s">
+        <v>5316</v>
+      </c>
+      <c r="X284" s="9" t="s">
+        <v>5330</v>
+      </c>
+      <c r="Y284" s="14" t="s">
+        <v>5317</v>
+      </c>
+      <c r="Z284" s="9" t="s">
+        <v>5329</v>
+      </c>
+      <c r="AA284" s="14" t="s">
+        <v>5318</v>
+      </c>
+      <c r="AB284" s="9" t="s">
+        <v>5328</v>
+      </c>
+      <c r="AC284" s="14" t="s">
+        <v>1932</v>
+      </c>
+      <c r="AD284" s="9" t="s">
+        <v>5327</v>
+      </c>
+      <c r="AE284" s="14" t="s">
+        <v>5319</v>
+      </c>
+      <c r="AF284" s="9" t="s">
+        <v>5326</v>
+      </c>
+      <c r="AG284" s="14" t="s">
+        <v>5320</v>
+      </c>
+      <c r="AH284" s="9" t="s">
+        <v>5325</v>
+      </c>
+      <c r="AI284" s="14" t="s">
+        <v>5321</v>
+      </c>
+      <c r="AJ284" s="9" t="s">
+        <v>5324</v>
+      </c>
+      <c r="AK284" s="14" t="s">
+        <v>2199</v>
+      </c>
+      <c r="AL284" s="9" t="s">
+        <v>5323</v>
+      </c>
+      <c r="AM284" s="14" t="s">
+        <v>2200</v>
+      </c>
+      <c r="AN284" s="9" t="s">
+        <v>5322</v>
+      </c>
+    </row>
+    <row r="285" spans="1:40">
       <c r="A285" s="9" t="str">
         <f>IF(games!A285="", "", games!A285)</f>
         <v>弓箭英雄：塔防</v>
@@ -61175,19 +61533,19 @@
         <v>準備好你的弓箭，面對排山倒海的敵人了嗎？《弓箭英雄：塔防》是一款結合了塔防策略與Roguelite元素的超休閒遊戲。每次升級都能三選一技能，是要彈射、冰凍還是連射？選錯了可能下一秒就躺平。玩家們都在瘋狂尋找最新的兌換碼，希望能開局就拿到神裝。別忘了，強大的火力支援是守塔的關鍵，這時候就需要可靠的代儲值服務來幫你一把。想要穩穩通關，拿到稀有的禮包碼獎勵嗎？與其苦苦硬撐，不如尋求快速安全的代儲值，讓你的箭塔升到滿級，輕鬆碾壓所有來犯的敵人，成為真正的塔防大師！</v>
       </c>
       <c r="F285" s="13" t="s">
-        <v>5258</v>
+        <v>5253</v>
       </c>
       <c r="G285" s="9" t="s">
-        <v>5257</v>
+        <v>5252</v>
       </c>
       <c r="K285" s="13" t="s">
-        <v>5258</v>
+        <v>5253</v>
       </c>
       <c r="L285" s="9" t="s">
-        <v>5257</v>
-      </c>
-    </row>
-    <row r="286" spans="1:30">
+        <v>5252</v>
+      </c>
+    </row>
+    <row r="286" spans="1:40">
       <c r="A286" s="9" t="str">
         <f>IF(games!A286="", "", games!A286)</f>
         <v>十二之天M</v>
@@ -61205,19 +61563,19 @@
         <v>《十二之天M Reborn》誓言找回當年的感動，讓玩家重溫三大勢力的激情對決。這款遊戲主打的就是一個原汁原味，熟悉的場景、懷舊的BGM，以及那令人又愛又恨的勢力戰。準備好再次投身這場無盡的江湖恩怨了嗎？大家都在蹲點最新的禮包碼，希望能搶先一步強化裝備。官方發放的兌換碼雖然不無小補，但真正的強者懂得利用資源。想要快速提升戰力，不妨考慮專業的代儲值服務。與其在戰場上被當小兵清掉，不如透過快速安全的管道補足元寶，讓你的角色戰力飆升，在龍瀑鎮插旗，重現當年的榮光！</v>
       </c>
       <c r="F286" s="13" t="s">
-        <v>5258</v>
+        <v>5253</v>
       </c>
       <c r="G286" s="9" t="s">
-        <v>5257</v>
+        <v>5252</v>
       </c>
       <c r="K286" s="13" t="s">
-        <v>5258</v>
+        <v>5253</v>
       </c>
       <c r="L286" s="9" t="s">
-        <v>5257</v>
-      </c>
-    </row>
-    <row r="287" spans="1:30">
+        <v>5252</v>
+      </c>
+    </row>
+    <row r="287" spans="1:40">
       <c r="A287" s="9" t="str">
         <f>IF(games!A287="", "", games!A287)</f>
         <v>NBA巔峰對決</v>
@@ -61235,19 +61593,49 @@
         <v>正版授權的《NBA巔峰對決》終於來了。這款主打真人PVP的籃球手遊，讓你能操控喜愛的NBA球星。遊戲強調操作手感與球星的專屬技能，想秀一波高難度灌籃或致命三分球？全看你的技術。但說真的，想在天梯上爬分，球員的養成才是關鍵。新手們別再傻傻地問兌換碼在哪了，那點資源根本不夠看。想要打造你的夢幻陣容，把傳奇球星都納入麾下，可靠的代儲值才是捷徑。別家還在慢慢存資源，你已經透過快速安全的儲值拿到關鍵禮包碼，直接抽爆卡池，讓你的隊伍戰力登頂，在球場上制霸全場！</v>
       </c>
       <c r="F287" s="13" t="s">
-        <v>5258</v>
+        <v>5310</v>
       </c>
       <c r="G287" s="9" t="s">
-        <v>5257</v>
+        <v>5311</v>
+      </c>
+      <c r="H287" s="9" t="s">
+        <v>2625</v>
+      </c>
+      <c r="I287" s="9" t="s">
+        <v>4360</v>
       </c>
       <c r="K287" s="13" t="s">
-        <v>5258</v>
+        <v>5300</v>
       </c>
       <c r="L287" s="9" t="s">
-        <v>5257</v>
-      </c>
-    </row>
-    <row r="288" spans="1:30">
+        <v>5305</v>
+      </c>
+      <c r="M287" s="14" t="s">
+        <v>5301</v>
+      </c>
+      <c r="N287" s="9" t="s">
+        <v>5306</v>
+      </c>
+      <c r="O287" s="14" t="s">
+        <v>5302</v>
+      </c>
+      <c r="P287" s="9" t="s">
+        <v>5307</v>
+      </c>
+      <c r="Q287" s="14" t="s">
+        <v>5303</v>
+      </c>
+      <c r="R287" s="9" t="s">
+        <v>5308</v>
+      </c>
+      <c r="S287" s="14" t="s">
+        <v>5304</v>
+      </c>
+      <c r="T287" s="9" t="s">
+        <v>5309</v>
+      </c>
+    </row>
+    <row r="288" spans="1:40">
       <c r="A288" s="9" t="str">
         <f>IF(games!A288="", "", games!A288)</f>
         <v>三國志：王戰</v>
@@ -61265,16 +61653,16 @@
         <v>又一款三國策略遊戲？先別急著滑掉！《三國志：王戰》是一款主打快節奏的SLG手遊，標榜著15天一賽季的急速征戰。在這裡，你不用再苦苦熬夜農地、屯兵，而是要把握黃金時間，快速發展內政、招募名將，與盟友一同攻城掠地。當然，想在短短15天內統一天下，光靠策略可不夠。新手們拚命搜尋的兌換碼，拿到的資源可能還不夠升一座主城。真正的王者都懂得運用代儲值服務，在開局就快人一步。別再猶豫了，利用快速安全的管道取得珍稀禮包碼與資源，迅速拉高戰力，在賽季結束前稱霸全服！</v>
       </c>
       <c r="F288" s="13" t="s">
-        <v>5258</v>
+        <v>5253</v>
       </c>
       <c r="G288" s="9" t="s">
-        <v>5257</v>
+        <v>5252</v>
       </c>
       <c r="K288" s="13" t="s">
-        <v>5258</v>
+        <v>5253</v>
       </c>
       <c r="L288" s="9" t="s">
-        <v>5257</v>
+        <v>5252</v>
       </c>
     </row>
     <row r="289" spans="1:5">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7853" uniqueCount="5337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7870" uniqueCount="5354">
   <si>
     <t>Facebook</t>
   </si>
@@ -20078,10 +20078,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>遊戲內選單按「設定」</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>《十二之天M Reborn》誓言找回當年的感動，讓玩家重溫三大勢力的激情對決。這款遊戲主打的就是一個原汁原味，熟悉的場景、懷舊的BGM，以及那令人又愛又恨的勢力戰。準備好再次投身這場無盡的江湖恩怨了嗎？大家都在蹲點最新的禮包碼，希望能搶先一步強化裝備。官方發放的兌換碼雖然不無小補，但真正的強者懂得利用資源。想要快速提升戰力，不妨考慮專業的代儲值服務。與其在戰場上被當小兵清掉，不如透過快速安全的管道補足元寶，讓你的角色戰力飆升，在龍瀑鎮插旗，重現當年的榮光！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -20336,6 +20332,78 @@
   </si>
   <si>
     <t>陣營招募帖*2+招募帖*2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點遊戲主畫面左上角的頭像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到下方禮包碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KING333</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KING888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIP888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲內左上角選單按「設定」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>按上方書籤三個點「其他」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>進入使用兌換碼按「使用」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DENAABINIJI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EPICGAMESDNA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DNAGLOBAL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DNALIVE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DNABYSSGIFT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DNAGIFT</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -35959,7 +36027,7 @@
         <v>5164</v>
       </c>
       <c r="AI223" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="224" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36029,7 +36097,7 @@
         <v>5164</v>
       </c>
       <c r="W224" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="225" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36145,7 +36213,7 @@
         <v>5164</v>
       </c>
       <c r="W226" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="227" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36245,7 +36313,7 @@
         <v>5164</v>
       </c>
       <c r="AG227" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="228" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36339,7 +36407,7 @@
         <v>5164</v>
       </c>
       <c r="AE228" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="229" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36433,7 +36501,7 @@
         <v>5164</v>
       </c>
       <c r="AE229" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="230" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36539,7 +36607,7 @@
         <v>5164</v>
       </c>
       <c r="AI230" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="231" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36627,7 +36695,7 @@
         <v>5164</v>
       </c>
       <c r="AC231" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="232" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36721,7 +36789,7 @@
         <v>5164</v>
       </c>
       <c r="AE232" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="233" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36849,7 +36917,7 @@
         <v>5164</v>
       </c>
       <c r="AE234" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="235" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36937,7 +37005,7 @@
         <v>5164</v>
       </c>
       <c r="AC235" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="236" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37037,7 +37105,7 @@
         <v>5164</v>
       </c>
       <c r="AG236" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="237" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37131,7 +37199,7 @@
         <v>5164</v>
       </c>
       <c r="AE237" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="238" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37207,7 +37275,7 @@
         <v>5164</v>
       </c>
       <c r="Y238" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="239" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37295,7 +37363,7 @@
         <v>5164</v>
       </c>
       <c r="AC239" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="240" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37365,7 +37433,7 @@
         <v>5164</v>
       </c>
       <c r="W240" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="241" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37453,7 +37521,7 @@
         <v>5164</v>
       </c>
       <c r="AC241" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="242" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37529,7 +37597,7 @@
         <v>5164</v>
       </c>
       <c r="Y242" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="243" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37617,7 +37685,7 @@
         <v>5164</v>
       </c>
       <c r="AC243" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="244" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37711,7 +37779,7 @@
         <v>5164</v>
       </c>
       <c r="AE244" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="245" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37787,7 +37855,7 @@
         <v>5164</v>
       </c>
       <c r="Y245" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="246" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37845,7 +37913,7 @@
         <v>5164</v>
       </c>
       <c r="S246" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="247" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37921,7 +37989,7 @@
         <v>5164</v>
       </c>
       <c r="Y247" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="248" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38009,7 +38077,7 @@
         <v>5164</v>
       </c>
       <c r="AC248" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="249" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38091,7 +38159,7 @@
         <v>5164</v>
       </c>
       <c r="AA249" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="250" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38167,7 +38235,7 @@
         <v>5164</v>
       </c>
       <c r="Y250" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="251" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38237,7 +38305,7 @@
         <v>5164</v>
       </c>
       <c r="W251" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="252" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38331,7 +38399,7 @@
         <v>5164</v>
       </c>
       <c r="AE252" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="253" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38431,7 +38499,7 @@
         <v>5164</v>
       </c>
       <c r="AG253" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="254" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38513,7 +38581,7 @@
         <v>5164</v>
       </c>
       <c r="AA254" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="255" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38589,7 +38657,7 @@
         <v>5164</v>
       </c>
       <c r="Y255" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="256" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38665,7 +38733,7 @@
         <v>5164</v>
       </c>
       <c r="Y256" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="257" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38759,7 +38827,7 @@
         <v>5164</v>
       </c>
       <c r="AE257" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="258" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38859,7 +38927,7 @@
         <v>5164</v>
       </c>
       <c r="AG258" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="259" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38947,7 +39015,7 @@
         <v>5164</v>
       </c>
       <c r="AC259" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="260" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39041,7 +39109,7 @@
         <v>5164</v>
       </c>
       <c r="AE260" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="261" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39123,7 +39191,7 @@
         <v>5164</v>
       </c>
       <c r="AA261" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="262" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39193,7 +39261,7 @@
         <v>5164</v>
       </c>
       <c r="W262" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="263" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39299,7 +39367,7 @@
         <v>5164</v>
       </c>
       <c r="AI263" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="264" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39421,7 +39489,7 @@
         <v>5164</v>
       </c>
       <c r="AE265" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="266" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39503,7 +39571,7 @@
         <v>5164</v>
       </c>
       <c r="AA266" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="267" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39597,7 +39665,7 @@
         <v>5164</v>
       </c>
       <c r="AE267" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="268" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39691,7 +39759,7 @@
         <v>5164</v>
       </c>
       <c r="AE268" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="269" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39779,7 +39847,7 @@
         <v>5164</v>
       </c>
       <c r="AC269" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="270" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39837,7 +39905,7 @@
         <v>5164</v>
       </c>
       <c r="S270" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="271" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39931,7 +39999,7 @@
         <v>5164</v>
       </c>
       <c r="AE271" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="272" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40007,7 +40075,7 @@
         <v>5164</v>
       </c>
       <c r="Y272" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="273" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40101,7 +40169,7 @@
         <v>5164</v>
       </c>
       <c r="AE273" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="274" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40195,7 +40263,7 @@
         <v>5164</v>
       </c>
       <c r="AE274" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="275" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40277,7 +40345,7 @@
         <v>5164</v>
       </c>
       <c r="AA275" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="276" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40308,49 +40376,49 @@
         <v>5087</v>
       </c>
       <c r="J276" s="1" t="s">
-        <v>5275</v>
+        <v>5274</v>
       </c>
       <c r="K276" s="58">
         <v>2477</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>5276</v>
+        <v>5275</v>
       </c>
       <c r="M276" s="58">
         <v>1346</v>
       </c>
       <c r="N276" s="1" t="s">
-        <v>5277</v>
+        <v>5276</v>
       </c>
       <c r="O276" s="58">
         <v>713</v>
       </c>
       <c r="P276" s="1" t="s">
-        <v>5278</v>
+        <v>5277</v>
       </c>
       <c r="Q276" s="58">
         <v>340</v>
       </c>
       <c r="R276" s="1" t="s">
-        <v>5279</v>
+        <v>5278</v>
       </c>
       <c r="S276" s="58">
         <v>169</v>
       </c>
       <c r="T276" s="1" t="s">
-        <v>5280</v>
+        <v>5279</v>
       </c>
       <c r="U276" s="58">
         <v>82</v>
       </c>
       <c r="V276" s="1" t="s">
-        <v>5281</v>
+        <v>5280</v>
       </c>
       <c r="W276" s="58">
         <v>30</v>
       </c>
       <c r="X276" s="1" t="s">
-        <v>5282</v>
+        <v>5281</v>
       </c>
       <c r="Y276" s="58">
         <v>133</v>
@@ -40359,7 +40427,7 @@
         <v>5164</v>
       </c>
       <c r="AA276" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="277" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40437,7 +40505,7 @@
         <v>5164</v>
       </c>
       <c r="AA277" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="278" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40531,7 +40599,7 @@
         <v>5164</v>
       </c>
       <c r="AE278" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="279" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40619,7 +40687,7 @@
         <v>5164</v>
       </c>
       <c r="AC279" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="280" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40695,7 +40763,7 @@
         <v>5164</v>
       </c>
       <c r="Y280" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="281" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40783,7 +40851,7 @@
         <v>5164</v>
       </c>
       <c r="AC281" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="282" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40877,7 +40945,7 @@
         <v>5164</v>
       </c>
       <c r="AE282" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="283" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40959,7 +41027,7 @@
         <v>5164</v>
       </c>
       <c r="AA283" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="284" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40990,61 +41058,61 @@
         <v>5199</v>
       </c>
       <c r="J284" s="1" t="s">
-        <v>5290</v>
+        <v>5289</v>
       </c>
       <c r="K284" s="58">
         <v>2717</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>5291</v>
+        <v>5290</v>
       </c>
       <c r="M284" s="58">
         <v>1388</v>
       </c>
       <c r="N284" s="1" t="s">
-        <v>5292</v>
+        <v>5291</v>
       </c>
       <c r="O284" s="58">
         <v>841</v>
       </c>
       <c r="P284" s="1" t="s">
-        <v>5293</v>
+        <v>5292</v>
       </c>
       <c r="Q284" s="58">
         <v>586</v>
       </c>
       <c r="R284" s="1" t="s">
-        <v>5294</v>
+        <v>5293</v>
       </c>
       <c r="S284" s="58">
         <v>416</v>
       </c>
       <c r="T284" s="1" t="s">
-        <v>5295</v>
+        <v>5294</v>
       </c>
       <c r="U284" s="58">
         <v>280</v>
       </c>
       <c r="V284" s="1" t="s">
-        <v>5296</v>
+        <v>5295</v>
       </c>
       <c r="W284" s="58">
         <v>146</v>
       </c>
       <c r="X284" s="1" t="s">
-        <v>5297</v>
+        <v>5296</v>
       </c>
       <c r="Y284" s="58">
         <v>30</v>
       </c>
       <c r="Z284" s="1" t="s">
-        <v>5298</v>
+        <v>5297</v>
       </c>
       <c r="AA284" s="58">
         <v>416</v>
       </c>
       <c r="AB284" s="1" t="s">
-        <v>5299</v>
+        <v>5298</v>
       </c>
       <c r="AC284" s="58">
         <v>586</v>
@@ -41053,7 +41121,7 @@
         <v>5164</v>
       </c>
       <c r="AE284" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="285" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -41081,10 +41149,10 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=弓箭英雄：塔防</v>
       </c>
       <c r="I285" s="38" t="s">
-        <v>5274</v>
+        <v>5273</v>
       </c>
       <c r="J285" s="1" t="s">
-        <v>5269</v>
+        <v>5268</v>
       </c>
       <c r="K285" s="58">
         <v>2469</v>
@@ -41114,7 +41182,7 @@
         <v>133</v>
       </c>
       <c r="T285" s="1" t="s">
-        <v>5270</v>
+        <v>5269</v>
       </c>
       <c r="U285" s="58">
         <v>27</v>
@@ -41123,7 +41191,7 @@
         <v>5164</v>
       </c>
       <c r="W285" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="286" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -41151,28 +41219,28 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=十二之天M</v>
       </c>
       <c r="I286" s="66" t="s">
-        <v>5266</v>
+        <v>5265</v>
       </c>
       <c r="J286" s="1" t="s">
-        <v>5283</v>
+        <v>5282</v>
       </c>
       <c r="K286" s="58">
         <v>2717</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>5284</v>
+        <v>5283</v>
       </c>
       <c r="M286" s="58">
         <v>1422</v>
       </c>
       <c r="N286" s="1" t="s">
-        <v>5285</v>
+        <v>5284</v>
       </c>
       <c r="O286" s="58">
         <v>840</v>
       </c>
       <c r="P286" s="1" t="s">
-        <v>5286</v>
+        <v>5285</v>
       </c>
       <c r="Q286" s="58">
         <v>416</v>
@@ -41190,19 +41258,19 @@
         <v>30</v>
       </c>
       <c r="V286" s="1" t="s">
-        <v>5287</v>
+        <v>5286</v>
       </c>
       <c r="W286" s="58">
         <v>213</v>
       </c>
       <c r="X286" s="1" t="s">
-        <v>5288</v>
+        <v>5287</v>
       </c>
       <c r="Y286" s="58">
         <v>357</v>
       </c>
       <c r="Z286" s="1" t="s">
-        <v>5289</v>
+        <v>5288</v>
       </c>
       <c r="AA286" s="58">
         <v>705</v>
@@ -41211,7 +41279,7 @@
         <v>5164</v>
       </c>
       <c r="AC286" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="287" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -41239,13 +41307,13 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=NBA巔峰對決</v>
       </c>
       <c r="I287" s="38" t="s">
-        <v>5267</v>
+        <v>5266</v>
       </c>
       <c r="J287" s="82" t="s">
         <v>5164</v>
       </c>
       <c r="K287" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="288" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -41273,13 +41341,13 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=三國志：王戰</v>
       </c>
       <c r="I288" s="38" t="s">
-        <v>5268</v>
+        <v>5267</v>
       </c>
       <c r="J288" s="82" t="s">
         <v>5164</v>
       </c>
       <c r="K288" s="85" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="289" spans="6:8" ht="22.5" customHeight="1">
@@ -61254,15 +61322,18 @@
         <v>備受矚目的 3D 動作 RPG《二重螺旋》強勢來襲！本作主打高速、爽快的戰鬥體驗，玩家將在一個近未來科幻世界中，扮演擁有特殊能力的「適格者」，探索神秘的「深淵」。遊戲強調華麗的連擊與多樣化的武器系統，你可以自由切換遠近程攻擊，打出屬於自己的戰鬥風格。為了讓你的探索之路更加順利，官方會不定期發放福利兌換碼與禮包碼，千萬別錯過。當然，面對強大的敵人，尋求專業的代儲值協助，以快速安全的方式強化戰力，絕對是高效的致勝關鍵。</v>
       </c>
       <c r="F279" s="13" t="s">
-        <v>5265</v>
+        <v>5345</v>
       </c>
       <c r="G279" s="9" t="s">
-        <v>3641</v>
+        <v>5346</v>
       </c>
       <c r="H279" s="9" t="s">
+        <v>5347</v>
+      </c>
+      <c r="I279" s="9" t="s">
         <v>2625</v>
       </c>
-      <c r="I279" s="9" t="s">
+      <c r="J279" s="9" t="s">
         <v>4360</v>
       </c>
       <c r="K279" s="13" t="s">
@@ -61276,6 +61347,24 @@
       </c>
       <c r="Q279" s="14" t="s">
         <v>5264</v>
+      </c>
+      <c r="S279" s="14" t="s">
+        <v>5348</v>
+      </c>
+      <c r="U279" s="14" t="s">
+        <v>5349</v>
+      </c>
+      <c r="W279" s="14" t="s">
+        <v>5350</v>
+      </c>
+      <c r="Y279" s="14" t="s">
+        <v>5351</v>
+      </c>
+      <c r="AA279" s="14" t="s">
+        <v>5353</v>
+      </c>
+      <c r="AC279" s="14" t="s">
+        <v>5352</v>
       </c>
     </row>
     <row r="280" spans="1:40">
@@ -61386,16 +61475,46 @@
         <v>2025年最值得一玩的全新萌系塔防手遊來啦！邪惡哥布林入侵，身為國王守護者的你，必須招募英雄抵禦入侵。遊戲主打英雄2合1加上局內3重隨機玩法，每局都有上百種策略搭配，就算是休閒玩家也能3秒上手！還在網路上苦苦搜尋可用的禮包碼和兌換碼嗎？別浪費時間了！想要快速升級，享受最爽快的割草感，尋找快速安全的代儲值服務會是你最好的選擇，立即為了蔚藍星球而戰！</v>
       </c>
       <c r="F283" s="13" t="s">
-        <v>4809</v>
+        <v>5336</v>
       </c>
       <c r="G283" s="9" t="s">
-        <v>4809</v>
+        <v>5337</v>
+      </c>
+      <c r="H283" s="9" t="s">
+        <v>2625</v>
+      </c>
+      <c r="I283" s="9" t="s">
+        <v>4360</v>
       </c>
       <c r="K283" s="13" t="s">
-        <v>4809</v>
-      </c>
-      <c r="L283" s="9" t="s">
-        <v>4809</v>
+        <v>5338</v>
+      </c>
+      <c r="M283" s="14" t="s">
+        <v>4141</v>
+      </c>
+      <c r="O283" s="14" t="s">
+        <v>4140</v>
+      </c>
+      <c r="Q283" s="14" t="s">
+        <v>5339</v>
+      </c>
+      <c r="S283" s="14" t="s">
+        <v>5340</v>
+      </c>
+      <c r="U283" s="14" t="s">
+        <v>5341</v>
+      </c>
+      <c r="W283" s="14" t="s">
+        <v>5342</v>
+      </c>
+      <c r="Y283" s="14" t="s">
+        <v>5343</v>
+      </c>
+      <c r="AA283" s="14" t="s">
+        <v>2056</v>
+      </c>
+      <c r="AC283" s="14" t="s">
+        <v>5344</v>
       </c>
     </row>
     <row r="284" spans="1:40">
@@ -61425,94 +61544,94 @@
         <v>5208</v>
       </c>
       <c r="K284" s="13" t="s">
+        <v>5271</v>
+      </c>
+      <c r="L284" s="9" t="s">
+        <v>5335</v>
+      </c>
+      <c r="M284" s="14" t="s">
         <v>5272</v>
       </c>
-      <c r="L284" s="9" t="s">
-        <v>5336</v>
-      </c>
-      <c r="M284" s="14" t="s">
-        <v>5273</v>
-      </c>
       <c r="N284" s="9" t="s">
-        <v>5335</v>
+        <v>5334</v>
       </c>
       <c r="O284" s="14" t="s">
+        <v>5311</v>
+      </c>
+      <c r="P284" s="9" t="s">
+        <v>5333</v>
+      </c>
+      <c r="Q284" s="14" t="s">
         <v>5312</v>
       </c>
-      <c r="P284" s="9" t="s">
-        <v>5334</v>
-      </c>
-      <c r="Q284" s="14" t="s">
+      <c r="R284" s="9" t="s">
+        <v>5332</v>
+      </c>
+      <c r="S284" s="14" t="s">
         <v>5313</v>
       </c>
-      <c r="R284" s="9" t="s">
-        <v>5333</v>
-      </c>
-      <c r="S284" s="14" t="s">
+      <c r="T284" s="9" t="s">
+        <v>5331</v>
+      </c>
+      <c r="U284" s="14" t="s">
         <v>5314</v>
       </c>
-      <c r="T284" s="9" t="s">
-        <v>5332</v>
-      </c>
-      <c r="U284" s="14" t="s">
+      <c r="V284" s="9" t="s">
+        <v>5330</v>
+      </c>
+      <c r="W284" s="14" t="s">
         <v>5315</v>
       </c>
-      <c r="V284" s="9" t="s">
-        <v>5331</v>
-      </c>
-      <c r="W284" s="14" t="s">
+      <c r="X284" s="9" t="s">
+        <v>5329</v>
+      </c>
+      <c r="Y284" s="14" t="s">
         <v>5316</v>
       </c>
-      <c r="X284" s="9" t="s">
-        <v>5330</v>
-      </c>
-      <c r="Y284" s="14" t="s">
+      <c r="Z284" s="9" t="s">
+        <v>5328</v>
+      </c>
+      <c r="AA284" s="14" t="s">
         <v>5317</v>
       </c>
-      <c r="Z284" s="9" t="s">
-        <v>5329</v>
-      </c>
-      <c r="AA284" s="14" t="s">
-        <v>5318</v>
-      </c>
       <c r="AB284" s="9" t="s">
-        <v>5328</v>
+        <v>5327</v>
       </c>
       <c r="AC284" s="14" t="s">
         <v>1932</v>
       </c>
       <c r="AD284" s="9" t="s">
-        <v>5327</v>
+        <v>5326</v>
       </c>
       <c r="AE284" s="14" t="s">
+        <v>5318</v>
+      </c>
+      <c r="AF284" s="9" t="s">
+        <v>5325</v>
+      </c>
+      <c r="AG284" s="14" t="s">
         <v>5319</v>
       </c>
-      <c r="AF284" s="9" t="s">
-        <v>5326</v>
-      </c>
-      <c r="AG284" s="14" t="s">
+      <c r="AH284" s="9" t="s">
+        <v>5324</v>
+      </c>
+      <c r="AI284" s="14" t="s">
         <v>5320</v>
       </c>
-      <c r="AH284" s="9" t="s">
-        <v>5325</v>
-      </c>
-      <c r="AI284" s="14" t="s">
-        <v>5321</v>
-      </c>
       <c r="AJ284" s="9" t="s">
-        <v>5324</v>
+        <v>5323</v>
       </c>
       <c r="AK284" s="14" t="s">
         <v>2199</v>
       </c>
       <c r="AL284" s="9" t="s">
-        <v>5323</v>
+        <v>5322</v>
       </c>
       <c r="AM284" s="14" t="s">
         <v>2200</v>
       </c>
       <c r="AN284" s="9" t="s">
-        <v>5322</v>
+        <v>5321</v>
       </c>
     </row>
     <row r="285" spans="1:40">
@@ -61593,10 +61712,10 @@
         <v>正版授權的《NBA巔峰對決》終於來了。這款主打真人PVP的籃球手遊，讓你能操控喜愛的NBA球星。遊戲強調操作手感與球星的專屬技能，想秀一波高難度灌籃或致命三分球？全看你的技術。但說真的，想在天梯上爬分，球員的養成才是關鍵。新手們別再傻傻地問兌換碼在哪了，那點資源根本不夠看。想要打造你的夢幻陣容，把傳奇球星都納入麾下，可靠的代儲值才是捷徑。別家還在慢慢存資源，你已經透過快速安全的儲值拿到關鍵禮包碼，直接抽爆卡池，讓你的隊伍戰力登頂，在球場上制霸全場！</v>
       </c>
       <c r="F287" s="13" t="s">
+        <v>5309</v>
+      </c>
+      <c r="G287" s="9" t="s">
         <v>5310</v>
-      </c>
-      <c r="G287" s="9" t="s">
-        <v>5311</v>
       </c>
       <c r="H287" s="9" t="s">
         <v>2625</v>
@@ -61605,34 +61724,34 @@
         <v>4360</v>
       </c>
       <c r="K287" s="13" t="s">
+        <v>5299</v>
+      </c>
+      <c r="L287" s="9" t="s">
+        <v>5304</v>
+      </c>
+      <c r="M287" s="14" t="s">
         <v>5300</v>
       </c>
-      <c r="L287" s="9" t="s">
+      <c r="N287" s="9" t="s">
         <v>5305</v>
       </c>
-      <c r="M287" s="14" t="s">
+      <c r="O287" s="14" t="s">
         <v>5301</v>
       </c>
-      <c r="N287" s="9" t="s">
+      <c r="P287" s="9" t="s">
         <v>5306</v>
       </c>
-      <c r="O287" s="14" t="s">
+      <c r="Q287" s="14" t="s">
         <v>5302</v>
       </c>
-      <c r="P287" s="9" t="s">
+      <c r="R287" s="9" t="s">
         <v>5307</v>
       </c>
-      <c r="Q287" s="14" t="s">
+      <c r="S287" s="14" t="s">
         <v>5303</v>
       </c>
-      <c r="R287" s="9" t="s">
+      <c r="T287" s="9" t="s">
         <v>5308</v>
-      </c>
-      <c r="S287" s="14" t="s">
-        <v>5304</v>
-      </c>
-      <c r="T287" s="9" t="s">
-        <v>5309</v>
       </c>
     </row>
     <row r="288" spans="1:40">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7870" uniqueCount="5354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7870" uniqueCount="5352">
   <si>
     <t>Facebook</t>
   </si>
@@ -19774,30 +19774,6 @@
     <t>430禮包</t>
   </si>
   <si>
-    <t>99.99美禮包</t>
-  </si>
-  <si>
-    <t>59.99美禮包</t>
-  </si>
-  <si>
-    <t>49.99美禮包</t>
-  </si>
-  <si>
-    <t>29.99美禮包</t>
-  </si>
-  <si>
-    <t>24.99美禮包</t>
-  </si>
-  <si>
-    <t>14.99美禮包</t>
-  </si>
-  <si>
-    <t>9.99美禮包</t>
-  </si>
-  <si>
-    <t>4.99美禮包</t>
-  </si>
-  <si>
     <t>蔚藍星球：國王很忙</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -20405,6 +20381,24 @@
   <si>
     <t>DNAGIFT</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7680鑽石</t>
+  </si>
+  <si>
+    <t>3800鑽石</t>
+  </si>
+  <si>
+    <t>1450鑽石</t>
+  </si>
+  <si>
+    <t>1080鑽石</t>
+  </si>
+  <si>
+    <t>福利月卡</t>
+  </si>
+  <si>
+    <t>免廣月卡</t>
   </si>
 </sst>
 </file>
@@ -36027,7 +36021,7 @@
         <v>5164</v>
       </c>
       <c r="AI223" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="224" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36097,7 +36091,7 @@
         <v>5164</v>
       </c>
       <c r="W224" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="225" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36213,7 +36207,7 @@
         <v>5164</v>
       </c>
       <c r="W226" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="227" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36313,7 +36307,7 @@
         <v>5164</v>
       </c>
       <c r="AG227" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="228" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36407,7 +36401,7 @@
         <v>5164</v>
       </c>
       <c r="AE228" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="229" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36501,7 +36495,7 @@
         <v>5164</v>
       </c>
       <c r="AE229" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="230" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36607,7 +36601,7 @@
         <v>5164</v>
       </c>
       <c r="AI230" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="231" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36695,7 +36689,7 @@
         <v>5164</v>
       </c>
       <c r="AC231" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="232" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36789,7 +36783,7 @@
         <v>5164</v>
       </c>
       <c r="AE232" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="233" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36917,7 +36911,7 @@
         <v>5164</v>
       </c>
       <c r="AE234" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="235" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37005,7 +36999,7 @@
         <v>5164</v>
       </c>
       <c r="AC235" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="236" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37105,7 +37099,7 @@
         <v>5164</v>
       </c>
       <c r="AG236" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="237" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37199,7 +37193,7 @@
         <v>5164</v>
       </c>
       <c r="AE237" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="238" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37275,7 +37269,7 @@
         <v>5164</v>
       </c>
       <c r="Y238" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="239" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37363,7 +37357,7 @@
         <v>5164</v>
       </c>
       <c r="AC239" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="240" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37433,7 +37427,7 @@
         <v>5164</v>
       </c>
       <c r="W240" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="241" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37521,7 +37515,7 @@
         <v>5164</v>
       </c>
       <c r="AC241" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="242" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37597,7 +37591,7 @@
         <v>5164</v>
       </c>
       <c r="Y242" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="243" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37685,7 +37679,7 @@
         <v>5164</v>
       </c>
       <c r="AC243" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="244" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37779,7 +37773,7 @@
         <v>5164</v>
       </c>
       <c r="AE244" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="245" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37855,7 +37849,7 @@
         <v>5164</v>
       </c>
       <c r="Y245" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="246" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37913,7 +37907,7 @@
         <v>5164</v>
       </c>
       <c r="S246" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="247" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37989,7 +37983,7 @@
         <v>5164</v>
       </c>
       <c r="Y247" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="248" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38077,7 +38071,7 @@
         <v>5164</v>
       </c>
       <c r="AC248" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="249" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38159,7 +38153,7 @@
         <v>5164</v>
       </c>
       <c r="AA249" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="250" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38235,7 +38229,7 @@
         <v>5164</v>
       </c>
       <c r="Y250" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="251" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38305,7 +38299,7 @@
         <v>5164</v>
       </c>
       <c r="W251" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="252" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38399,7 +38393,7 @@
         <v>5164</v>
       </c>
       <c r="AE252" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="253" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38499,7 +38493,7 @@
         <v>5164</v>
       </c>
       <c r="AG253" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="254" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38581,7 +38575,7 @@
         <v>5164</v>
       </c>
       <c r="AA254" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="255" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38657,7 +38651,7 @@
         <v>5164</v>
       </c>
       <c r="Y255" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="256" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38733,7 +38727,7 @@
         <v>5164</v>
       </c>
       <c r="Y256" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="257" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38827,7 +38821,7 @@
         <v>5164</v>
       </c>
       <c r="AE257" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="258" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38927,7 +38921,7 @@
         <v>5164</v>
       </c>
       <c r="AG258" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="259" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39015,7 +39009,7 @@
         <v>5164</v>
       </c>
       <c r="AC259" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="260" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39109,7 +39103,7 @@
         <v>5164</v>
       </c>
       <c r="AE260" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="261" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39191,7 +39185,7 @@
         <v>5164</v>
       </c>
       <c r="AA261" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="262" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39261,7 +39255,7 @@
         <v>5164</v>
       </c>
       <c r="W262" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="263" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39367,7 +39361,7 @@
         <v>5164</v>
       </c>
       <c r="AI263" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="264" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39489,7 +39483,7 @@
         <v>5164</v>
       </c>
       <c r="AE265" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="266" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39571,7 +39565,7 @@
         <v>5164</v>
       </c>
       <c r="AA266" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="267" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39665,7 +39659,7 @@
         <v>5164</v>
       </c>
       <c r="AE267" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="268" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39759,7 +39753,7 @@
         <v>5164</v>
       </c>
       <c r="AE268" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="269" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39847,7 +39841,7 @@
         <v>5164</v>
       </c>
       <c r="AC269" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="270" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39905,7 +39899,7 @@
         <v>5164</v>
       </c>
       <c r="S270" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="271" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39999,7 +39993,7 @@
         <v>5164</v>
       </c>
       <c r="AE271" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="272" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40075,7 +40069,7 @@
         <v>5164</v>
       </c>
       <c r="Y272" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="273" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40169,7 +40163,7 @@
         <v>5164</v>
       </c>
       <c r="AE273" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="274" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40263,7 +40257,7 @@
         <v>5164</v>
       </c>
       <c r="AE274" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="275" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40345,7 +40339,7 @@
         <v>5164</v>
       </c>
       <c r="AA275" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="276" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40376,49 +40370,49 @@
         <v>5087</v>
       </c>
       <c r="J276" s="1" t="s">
-        <v>5274</v>
+        <v>5266</v>
       </c>
       <c r="K276" s="58">
         <v>2477</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>5275</v>
+        <v>5267</v>
       </c>
       <c r="M276" s="58">
         <v>1346</v>
       </c>
       <c r="N276" s="1" t="s">
-        <v>5276</v>
+        <v>5268</v>
       </c>
       <c r="O276" s="58">
         <v>713</v>
       </c>
       <c r="P276" s="1" t="s">
-        <v>5277</v>
+        <v>5269</v>
       </c>
       <c r="Q276" s="58">
         <v>340</v>
       </c>
       <c r="R276" s="1" t="s">
-        <v>5278</v>
+        <v>5270</v>
       </c>
       <c r="S276" s="58">
         <v>169</v>
       </c>
       <c r="T276" s="1" t="s">
-        <v>5279</v>
+        <v>5271</v>
       </c>
       <c r="U276" s="58">
         <v>82</v>
       </c>
       <c r="V276" s="1" t="s">
-        <v>5280</v>
+        <v>5272</v>
       </c>
       <c r="W276" s="58">
         <v>30</v>
       </c>
       <c r="X276" s="1" t="s">
-        <v>5281</v>
+        <v>5273</v>
       </c>
       <c r="Y276" s="58">
         <v>133</v>
@@ -40427,7 +40421,7 @@
         <v>5164</v>
       </c>
       <c r="AA276" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="277" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40505,7 +40499,7 @@
         <v>5164</v>
       </c>
       <c r="AA277" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="278" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40599,7 +40593,7 @@
         <v>5164</v>
       </c>
       <c r="AE278" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="279" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40687,7 +40681,7 @@
         <v>5164</v>
       </c>
       <c r="AC279" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="280" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40763,7 +40757,7 @@
         <v>5164</v>
       </c>
       <c r="Y280" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="281" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40851,12 +40845,12 @@
         <v>5164</v>
       </c>
       <c r="AC281" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="282" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A282" s="84" t="s">
-        <v>5217</v>
+        <v>5209</v>
       </c>
       <c r="C282" s="36" t="s">
         <v>5170</v>
@@ -40872,14 +40866,14 @@
         <v>gift-codes.html?game=石器時代：寵物世界</v>
       </c>
       <c r="G282" s="82" t="s">
-        <v>5194</v>
+        <v>5186</v>
       </c>
       <c r="H282" s="37" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/石器時代：寵物世界.html</v>
       </c>
       <c r="I282" s="38" t="s">
-        <v>5197</v>
+        <v>5189</v>
       </c>
       <c r="J282" s="83" t="s">
         <v>4988</v>
@@ -40945,12 +40939,12 @@
         <v>5164</v>
       </c>
       <c r="AE282" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="283" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A283" s="84" t="s">
-        <v>5192</v>
+        <v>5184</v>
       </c>
       <c r="C283" s="36" t="s">
         <v>5173</v>
@@ -40966,73 +40960,73 @@
         <v>gift-codes.html?game=蔚藍星球：國王很忙</v>
       </c>
       <c r="G283" s="82" t="s">
-        <v>5195</v>
+        <v>5187</v>
       </c>
       <c r="H283" s="37" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/蔚藍星球：國王很忙.html</v>
       </c>
       <c r="I283" s="38" t="s">
-        <v>5198</v>
-      </c>
-      <c r="J283" s="83" t="s">
-        <v>5184</v>
-      </c>
-      <c r="K283" s="84">
-        <v>2655</v>
-      </c>
-      <c r="L283" s="83" t="s">
-        <v>5185</v>
-      </c>
-      <c r="M283" s="84">
-        <v>1644</v>
-      </c>
-      <c r="N283" s="83" t="s">
-        <v>5186</v>
-      </c>
-      <c r="O283" s="84">
-        <v>1389</v>
-      </c>
-      <c r="P283" s="83" t="s">
-        <v>5187</v>
-      </c>
-      <c r="Q283" s="84">
-        <v>821</v>
-      </c>
-      <c r="R283" s="83" t="s">
-        <v>5188</v>
-      </c>
-      <c r="S283" s="84">
-        <v>655</v>
-      </c>
-      <c r="T283" s="83" t="s">
-        <v>5189</v>
-      </c>
-      <c r="U283" s="84">
-        <v>407</v>
-      </c>
-      <c r="V283" s="83" t="s">
         <v>5190</v>
       </c>
-      <c r="W283" s="84">
-        <v>274</v>
-      </c>
-      <c r="X283" s="83" t="s">
-        <v>5191</v>
-      </c>
-      <c r="Y283" s="84">
-        <v>147</v>
+      <c r="J283" s="1" t="s">
+        <v>5346</v>
+      </c>
+      <c r="K283" s="58">
+        <v>2717</v>
+      </c>
+      <c r="L283" s="1" t="s">
+        <v>5347</v>
+      </c>
+      <c r="M283" s="58">
+        <v>1422</v>
+      </c>
+      <c r="N283" s="1" t="s">
+        <v>5348</v>
+      </c>
+      <c r="O283" s="58">
+        <v>586</v>
+      </c>
+      <c r="P283" s="1" t="s">
+        <v>5349</v>
+      </c>
+      <c r="Q283" s="58">
+        <v>416</v>
+      </c>
+      <c r="R283" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="S283" s="58">
+        <v>151</v>
+      </c>
+      <c r="T283" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U283" s="58">
+        <v>30</v>
+      </c>
+      <c r="V283" s="1" t="s">
+        <v>5350</v>
+      </c>
+      <c r="W283" s="58">
+        <v>151</v>
+      </c>
+      <c r="X283" s="1" t="s">
+        <v>5351</v>
+      </c>
+      <c r="Y283" s="58">
+        <v>89</v>
       </c>
       <c r="Z283" s="82" t="s">
         <v>5164</v>
       </c>
       <c r="AA283" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="284" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A284" s="84" t="s">
-        <v>5193</v>
+        <v>5185</v>
       </c>
       <c r="C284" s="36" t="s">
         <v>5176</v>
@@ -41048,71 +41042,71 @@
         <v>gift-codes.html?game=胸懷三國：美人計</v>
       </c>
       <c r="G284" s="82" t="s">
-        <v>5196</v>
+        <v>5188</v>
       </c>
       <c r="H284" s="37" t="str">
         <f t="shared" ref="H284:H312" si="13">IF(A284="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A284)</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=胸懷三國：美人計</v>
       </c>
       <c r="I284" s="38" t="s">
-        <v>5199</v>
+        <v>5191</v>
       </c>
       <c r="J284" s="1" t="s">
-        <v>5289</v>
+        <v>5281</v>
       </c>
       <c r="K284" s="58">
         <v>2717</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>5290</v>
+        <v>5282</v>
       </c>
       <c r="M284" s="58">
         <v>1388</v>
       </c>
       <c r="N284" s="1" t="s">
-        <v>5291</v>
+        <v>5283</v>
       </c>
       <c r="O284" s="58">
         <v>841</v>
       </c>
       <c r="P284" s="1" t="s">
-        <v>5292</v>
+        <v>5284</v>
       </c>
       <c r="Q284" s="58">
         <v>586</v>
       </c>
       <c r="R284" s="1" t="s">
-        <v>5293</v>
+        <v>5285</v>
       </c>
       <c r="S284" s="58">
         <v>416</v>
       </c>
       <c r="T284" s="1" t="s">
-        <v>5294</v>
+        <v>5286</v>
       </c>
       <c r="U284" s="58">
         <v>280</v>
       </c>
       <c r="V284" s="1" t="s">
-        <v>5295</v>
+        <v>5287</v>
       </c>
       <c r="W284" s="58">
         <v>146</v>
       </c>
       <c r="X284" s="1" t="s">
-        <v>5296</v>
+        <v>5288</v>
       </c>
       <c r="Y284" s="58">
         <v>30</v>
       </c>
       <c r="Z284" s="1" t="s">
-        <v>5297</v>
+        <v>5289</v>
       </c>
       <c r="AA284" s="58">
         <v>416</v>
       </c>
       <c r="AB284" s="1" t="s">
-        <v>5298</v>
+        <v>5290</v>
       </c>
       <c r="AC284" s="58">
         <v>586</v>
@@ -41121,38 +41115,38 @@
         <v>5164</v>
       </c>
       <c r="AE284" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="285" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A285" s="84" t="s">
-        <v>5244</v>
+        <v>5236</v>
       </c>
       <c r="C285" s="36" t="s">
-        <v>5242</v>
+        <v>5234</v>
       </c>
       <c r="D285" s="37" t="s">
-        <v>5243</v>
+        <v>5235</v>
       </c>
       <c r="E285" s="37" t="s">
-        <v>5232</v>
+        <v>5224</v>
       </c>
       <c r="F285" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=弓箭英雄：塔防</v>
       </c>
       <c r="G285" s="82" t="s">
-        <v>5245</v>
+        <v>5237</v>
       </c>
       <c r="H285" s="37" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=弓箭英雄：塔防</v>
       </c>
       <c r="I285" s="38" t="s">
-        <v>5273</v>
+        <v>5265</v>
       </c>
       <c r="J285" s="1" t="s">
-        <v>5268</v>
+        <v>5260</v>
       </c>
       <c r="K285" s="58">
         <v>2469</v>
@@ -41182,7 +41176,7 @@
         <v>133</v>
       </c>
       <c r="T285" s="1" t="s">
-        <v>5269</v>
+        <v>5261</v>
       </c>
       <c r="U285" s="58">
         <v>27</v>
@@ -41191,56 +41185,56 @@
         <v>5164</v>
       </c>
       <c r="W285" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="286" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A286" s="84" t="s">
-        <v>5250</v>
+        <v>5242</v>
       </c>
       <c r="C286" s="36" t="s">
-        <v>5234</v>
+        <v>5226</v>
       </c>
       <c r="D286" s="37" t="s">
-        <v>5233</v>
+        <v>5225</v>
       </c>
       <c r="E286" s="37" t="s">
-        <v>5235</v>
+        <v>5227</v>
       </c>
       <c r="F286" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=十二之天M</v>
       </c>
       <c r="G286" s="82" t="s">
-        <v>5246</v>
+        <v>5238</v>
       </c>
       <c r="H286" s="37" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=十二之天M</v>
       </c>
       <c r="I286" s="66" t="s">
-        <v>5265</v>
+        <v>5257</v>
       </c>
       <c r="J286" s="1" t="s">
-        <v>5282</v>
+        <v>5274</v>
       </c>
       <c r="K286" s="58">
         <v>2717</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>5283</v>
+        <v>5275</v>
       </c>
       <c r="M286" s="58">
         <v>1422</v>
       </c>
       <c r="N286" s="1" t="s">
-        <v>5284</v>
+        <v>5276</v>
       </c>
       <c r="O286" s="58">
         <v>840</v>
       </c>
       <c r="P286" s="1" t="s">
-        <v>5285</v>
+        <v>5277</v>
       </c>
       <c r="Q286" s="58">
         <v>416</v>
@@ -41258,19 +41252,19 @@
         <v>30</v>
       </c>
       <c r="V286" s="1" t="s">
-        <v>5286</v>
+        <v>5278</v>
       </c>
       <c r="W286" s="58">
         <v>213</v>
       </c>
       <c r="X286" s="1" t="s">
-        <v>5287</v>
+        <v>5279</v>
       </c>
       <c r="Y286" s="58">
         <v>357</v>
       </c>
       <c r="Z286" s="1" t="s">
-        <v>5288</v>
+        <v>5280</v>
       </c>
       <c r="AA286" s="58">
         <v>705</v>
@@ -41279,75 +41273,75 @@
         <v>5164</v>
       </c>
       <c r="AC286" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="287" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A287" s="84" t="s">
-        <v>5251</v>
+        <v>5243</v>
       </c>
       <c r="C287" s="36" t="s">
-        <v>5238</v>
+        <v>5230</v>
       </c>
       <c r="D287" s="37" t="s">
-        <v>5237</v>
+        <v>5229</v>
       </c>
       <c r="E287" s="37" t="s">
-        <v>5236</v>
+        <v>5228</v>
       </c>
       <c r="F287" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=NBA巔峰對決</v>
       </c>
       <c r="G287" s="82" t="s">
-        <v>5247</v>
+        <v>5239</v>
       </c>
       <c r="H287" s="37" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=NBA巔峰對決</v>
       </c>
       <c r="I287" s="38" t="s">
-        <v>5266</v>
+        <v>5258</v>
       </c>
       <c r="J287" s="82" t="s">
         <v>5164</v>
       </c>
       <c r="K287" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="288" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A288" s="84" t="s">
-        <v>5248</v>
+        <v>5240</v>
       </c>
       <c r="C288" s="36" t="s">
-        <v>5241</v>
+        <v>5233</v>
       </c>
       <c r="D288" s="37" t="s">
-        <v>5240</v>
+        <v>5232</v>
       </c>
       <c r="E288" s="37" t="s">
-        <v>5239</v>
+        <v>5231</v>
       </c>
       <c r="F288" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=三國志：王戰</v>
       </c>
       <c r="G288" s="82" t="s">
-        <v>5249</v>
+        <v>5241</v>
       </c>
       <c r="H288" s="37" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=三國志：王戰</v>
       </c>
       <c r="I288" s="38" t="s">
-        <v>5267</v>
+        <v>5259</v>
       </c>
       <c r="J288" s="82" t="s">
         <v>5164</v>
       </c>
       <c r="K288" s="85" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="289" spans="6:8" ht="22.5" customHeight="1">
@@ -59488,46 +59482,46 @@
         <v>5026</v>
       </c>
       <c r="W236" s="14" t="s">
+        <v>5210</v>
+      </c>
+      <c r="X236" s="9" t="s">
+        <v>5223</v>
+      </c>
+      <c r="Y236" s="14" t="s">
+        <v>5211</v>
+      </c>
+      <c r="Z236" s="9" t="s">
+        <v>5222</v>
+      </c>
+      <c r="AA236" s="14" t="s">
+        <v>5212</v>
+      </c>
+      <c r="AB236" s="9" t="s">
+        <v>5221</v>
+      </c>
+      <c r="AC236" s="14" t="s">
+        <v>5213</v>
+      </c>
+      <c r="AD236" s="9" t="s">
+        <v>5220</v>
+      </c>
+      <c r="AE236" s="14" t="s">
+        <v>5214</v>
+      </c>
+      <c r="AF236" s="9" t="s">
+        <v>5219</v>
+      </c>
+      <c r="AG236" s="14" t="s">
+        <v>5215</v>
+      </c>
+      <c r="AH236" s="9" t="s">
         <v>5218</v>
       </c>
-      <c r="X236" s="9" t="s">
-        <v>5231</v>
-      </c>
-      <c r="Y236" s="14" t="s">
-        <v>5219</v>
-      </c>
-      <c r="Z236" s="9" t="s">
-        <v>5230</v>
-      </c>
-      <c r="AA236" s="14" t="s">
-        <v>5220</v>
-      </c>
-      <c r="AB236" s="9" t="s">
-        <v>5229</v>
-      </c>
-      <c r="AC236" s="14" t="s">
-        <v>5221</v>
-      </c>
-      <c r="AD236" s="9" t="s">
-        <v>5228</v>
-      </c>
-      <c r="AE236" s="14" t="s">
-        <v>5222</v>
-      </c>
-      <c r="AF236" s="9" t="s">
-        <v>5227</v>
-      </c>
-      <c r="AG236" s="14" t="s">
-        <v>5223</v>
-      </c>
-      <c r="AH236" s="9" t="s">
-        <v>5226</v>
-      </c>
       <c r="AI236" s="14" t="s">
-        <v>5224</v>
+        <v>5216</v>
       </c>
       <c r="AJ236" s="9" t="s">
-        <v>5225</v>
+        <v>5217</v>
       </c>
     </row>
     <row r="237" spans="1:47" ht="22.5" customHeight="1">
@@ -60869,10 +60863,10 @@
         <v>《Awakenloop》是一款充滿賽博龐克風格的卡牌回合制手遊，玩家將身處一個由機器人與人類共存的末日世界。遊戲主打策略性卡牌戰鬥，每張卡牌都蘊含獨特技能，如何搭配與釋放將成為戰局關鍵。除了豐富的主線劇情，遊戲也提供多樣的副本挑戰與 PvP 模式，讓你與其他玩家一較高下。現在就加入《Awakenloop》，透過兌換碼與禮包碼獲得專屬獎勵，輕鬆提升戰力，也能使用代儲值服務快速安全地補充資源，在這片混沌的廢土上開創屬於你的新紀元。</v>
       </c>
       <c r="F269" s="13" t="s">
-        <v>5204</v>
+        <v>5196</v>
       </c>
       <c r="G269" s="9" t="s">
-        <v>5205</v>
+        <v>5197</v>
       </c>
       <c r="H269" s="9" t="s">
         <v>2625</v>
@@ -60881,16 +60875,16 @@
         <v>4360</v>
       </c>
       <c r="K269" s="13" t="s">
-        <v>5200</v>
+        <v>5192</v>
       </c>
       <c r="L269" s="9" t="s">
-        <v>5203</v>
+        <v>5195</v>
       </c>
       <c r="M269" s="14" t="s">
-        <v>5201</v>
+        <v>5193</v>
       </c>
       <c r="N269" s="9" t="s">
-        <v>5202</v>
+        <v>5194</v>
       </c>
     </row>
     <row r="270" spans="1:31">
@@ -61052,28 +61046,28 @@
         <v>5066</v>
       </c>
       <c r="W273" s="14" t="s">
-        <v>5209</v>
+        <v>5201</v>
       </c>
       <c r="X273" s="9" t="s">
-        <v>5213</v>
+        <v>5205</v>
       </c>
       <c r="Y273" s="14" t="s">
-        <v>5210</v>
+        <v>5202</v>
       </c>
       <c r="Z273" s="9" t="s">
-        <v>5214</v>
+        <v>5206</v>
       </c>
       <c r="AA273" s="14" t="s">
-        <v>5211</v>
+        <v>5203</v>
       </c>
       <c r="AB273" s="9" t="s">
-        <v>5215</v>
+        <v>5207</v>
       </c>
       <c r="AC273" s="14" t="s">
-        <v>5212</v>
+        <v>5204</v>
       </c>
       <c r="AD273" s="9" t="s">
-        <v>5216</v>
+        <v>5208</v>
       </c>
     </row>
     <row r="274" spans="1:40">
@@ -61283,25 +61277,25 @@
         <v>全新星緣卡牌 RPG《星痕共鳴》，邀你一同編織命運的篇章。遊戲擁有宏大的世界觀與超過百萬字的豐富劇情，玩家將扮演「星源之主」，與眾多「星痕者」締結羈絆，共同對抗虛空的威脅。獨特的「星盤」系統與高策略性的卡牌戰鬥，讓每場對決都充滿變數。想要輕鬆推圖、快速成長？記得在各大社群與論壇尋找隱藏的兌換碼與禮包碼，領取豐厚資源。如果想快人一步，最聰明的選擇就是尋找可靠的代儲值管道，提供您快速安全的支援，讓你的冒險旅程更加順遂。</v>
       </c>
       <c r="F278" s="13" t="s">
-        <v>5258</v>
+        <v>5250</v>
       </c>
       <c r="G278" s="9" t="s">
-        <v>5259</v>
+        <v>5251</v>
       </c>
       <c r="H278" s="9" t="s">
-        <v>5260</v>
+        <v>5252</v>
       </c>
       <c r="K278" s="13" t="s">
-        <v>5254</v>
+        <v>5246</v>
       </c>
       <c r="L278" s="9" t="s">
-        <v>5257</v>
+        <v>5249</v>
       </c>
       <c r="M278" s="14" t="s">
-        <v>5255</v>
+        <v>5247</v>
       </c>
       <c r="N278" s="9" t="s">
-        <v>5256</v>
+        <v>5248</v>
       </c>
     </row>
     <row r="279" spans="1:40">
@@ -61322,13 +61316,13 @@
         <v>備受矚目的 3D 動作 RPG《二重螺旋》強勢來襲！本作主打高速、爽快的戰鬥體驗，玩家將在一個近未來科幻世界中，扮演擁有特殊能力的「適格者」，探索神秘的「深淵」。遊戲強調華麗的連擊與多樣化的武器系統，你可以自由切換遠近程攻擊，打出屬於自己的戰鬥風格。為了讓你的探索之路更加順利，官方會不定期發放福利兌換碼與禮包碼，千萬別錯過。當然，面對強大的敵人，尋求專業的代儲值協助，以快速安全的方式強化戰力，絕對是高效的致勝關鍵。</v>
       </c>
       <c r="F279" s="13" t="s">
-        <v>5345</v>
+        <v>5337</v>
       </c>
       <c r="G279" s="9" t="s">
-        <v>5346</v>
+        <v>5338</v>
       </c>
       <c r="H279" s="9" t="s">
-        <v>5347</v>
+        <v>5339</v>
       </c>
       <c r="I279" s="9" t="s">
         <v>2625</v>
@@ -61337,34 +61331,34 @@
         <v>4360</v>
       </c>
       <c r="K279" s="13" t="s">
-        <v>5261</v>
+        <v>5253</v>
       </c>
       <c r="M279" s="14" t="s">
-        <v>5262</v>
+        <v>5254</v>
       </c>
       <c r="O279" s="14" t="s">
-        <v>5263</v>
+        <v>5255</v>
       </c>
       <c r="Q279" s="14" t="s">
-        <v>5264</v>
+        <v>5256</v>
       </c>
       <c r="S279" s="14" t="s">
-        <v>5348</v>
+        <v>5340</v>
       </c>
       <c r="U279" s="14" t="s">
-        <v>5349</v>
+        <v>5341</v>
       </c>
       <c r="W279" s="14" t="s">
-        <v>5350</v>
+        <v>5342</v>
       </c>
       <c r="Y279" s="14" t="s">
-        <v>5351</v>
+        <v>5343</v>
       </c>
       <c r="AA279" s="14" t="s">
-        <v>5353</v>
+        <v>5345</v>
       </c>
       <c r="AC279" s="14" t="s">
-        <v>5352</v>
+        <v>5344</v>
       </c>
     </row>
     <row r="280" spans="1:40">
@@ -61475,10 +61469,10 @@
         <v>2025年最值得一玩的全新萌系塔防手遊來啦！邪惡哥布林入侵，身為國王守護者的你，必須招募英雄抵禦入侵。遊戲主打英雄2合1加上局內3重隨機玩法，每局都有上百種策略搭配，就算是休閒玩家也能3秒上手！還在網路上苦苦搜尋可用的禮包碼和兌換碼嗎？別浪費時間了！想要快速升級，享受最爽快的割草感，尋找快速安全的代儲值服務會是你最好的選擇，立即為了蔚藍星球而戰！</v>
       </c>
       <c r="F283" s="13" t="s">
-        <v>5336</v>
+        <v>5328</v>
       </c>
       <c r="G283" s="9" t="s">
-        <v>5337</v>
+        <v>5329</v>
       </c>
       <c r="H283" s="9" t="s">
         <v>2625</v>
@@ -61487,7 +61481,7 @@
         <v>4360</v>
       </c>
       <c r="K283" s="13" t="s">
-        <v>5338</v>
+        <v>5330</v>
       </c>
       <c r="M283" s="14" t="s">
         <v>4141</v>
@@ -61496,25 +61490,25 @@
         <v>4140</v>
       </c>
       <c r="Q283" s="14" t="s">
-        <v>5339</v>
+        <v>5331</v>
       </c>
       <c r="S283" s="14" t="s">
-        <v>5340</v>
+        <v>5332</v>
       </c>
       <c r="U283" s="14" t="s">
-        <v>5341</v>
+        <v>5333</v>
       </c>
       <c r="W283" s="14" t="s">
-        <v>5342</v>
+        <v>5334</v>
       </c>
       <c r="Y283" s="14" t="s">
-        <v>5343</v>
+        <v>5335</v>
       </c>
       <c r="AA283" s="14" t="s">
         <v>2056</v>
       </c>
       <c r="AC283" s="14" t="s">
-        <v>5344</v>
+        <v>5336</v>
       </c>
     </row>
     <row r="284" spans="1:40">
@@ -61535,103 +61529,103 @@
         <v>美少女三國RPG手遊參上！遊戲擁有眾多經典三國名將，搭配緊張刺激的養成戰鬥系統，讓玩家可以體驗高潮連擊的激爽和無限養成的快樂。獨特的武將風格立繪，在既定特色上增添更多風味，絕對是視覺饗宴。還在為了找不到最新的禮包碼而煩惱嗎？想要輕鬆養成武將，解鎖所有外觀，最聰明的方式就是尋找快速安全的代儲值管道，立即領取你的兌換碼福利，在三國世界中無往不利！</v>
       </c>
       <c r="F284" s="13" t="s">
-        <v>5206</v>
+        <v>5198</v>
       </c>
       <c r="G284" s="9" t="s">
-        <v>5207</v>
+        <v>5199</v>
       </c>
       <c r="H284" s="9" t="s">
-        <v>5208</v>
+        <v>5200</v>
       </c>
       <c r="K284" s="13" t="s">
-        <v>5271</v>
+        <v>5263</v>
       </c>
       <c r="L284" s="9" t="s">
-        <v>5335</v>
+        <v>5327</v>
       </c>
       <c r="M284" s="14" t="s">
-        <v>5272</v>
+        <v>5264</v>
       </c>
       <c r="N284" s="9" t="s">
-        <v>5334</v>
+        <v>5326</v>
       </c>
       <c r="O284" s="14" t="s">
-        <v>5311</v>
+        <v>5303</v>
       </c>
       <c r="P284" s="9" t="s">
-        <v>5333</v>
+        <v>5325</v>
       </c>
       <c r="Q284" s="14" t="s">
-        <v>5312</v>
+        <v>5304</v>
       </c>
       <c r="R284" s="9" t="s">
-        <v>5332</v>
+        <v>5324</v>
       </c>
       <c r="S284" s="14" t="s">
-        <v>5313</v>
+        <v>5305</v>
       </c>
       <c r="T284" s="9" t="s">
-        <v>5331</v>
+        <v>5323</v>
       </c>
       <c r="U284" s="14" t="s">
-        <v>5314</v>
+        <v>5306</v>
       </c>
       <c r="V284" s="9" t="s">
-        <v>5330</v>
+        <v>5322</v>
       </c>
       <c r="W284" s="14" t="s">
-        <v>5315</v>
+        <v>5307</v>
       </c>
       <c r="X284" s="9" t="s">
-        <v>5329</v>
+        <v>5321</v>
       </c>
       <c r="Y284" s="14" t="s">
-        <v>5316</v>
+        <v>5308</v>
       </c>
       <c r="Z284" s="9" t="s">
-        <v>5328</v>
+        <v>5320</v>
       </c>
       <c r="AA284" s="14" t="s">
-        <v>5317</v>
+        <v>5309</v>
       </c>
       <c r="AB284" s="9" t="s">
-        <v>5327</v>
+        <v>5319</v>
       </c>
       <c r="AC284" s="14" t="s">
         <v>1932</v>
       </c>
       <c r="AD284" s="9" t="s">
-        <v>5326</v>
+        <v>5318</v>
       </c>
       <c r="AE284" s="14" t="s">
-        <v>5318</v>
+        <v>5310</v>
       </c>
       <c r="AF284" s="9" t="s">
-        <v>5325</v>
+        <v>5317</v>
       </c>
       <c r="AG284" s="14" t="s">
-        <v>5319</v>
+        <v>5311</v>
       </c>
       <c r="AH284" s="9" t="s">
-        <v>5324</v>
+        <v>5316</v>
       </c>
       <c r="AI284" s="14" t="s">
-        <v>5320</v>
+        <v>5312</v>
       </c>
       <c r="AJ284" s="9" t="s">
-        <v>5323</v>
+        <v>5315</v>
       </c>
       <c r="AK284" s="14" t="s">
         <v>2199</v>
       </c>
       <c r="AL284" s="9" t="s">
-        <v>5322</v>
+        <v>5314</v>
       </c>
       <c r="AM284" s="14" t="s">
         <v>2200</v>
       </c>
       <c r="AN284" s="9" t="s">
-        <v>5321</v>
+        <v>5313</v>
       </c>
     </row>
     <row r="285" spans="1:40">
@@ -61652,16 +61646,16 @@
         <v>準備好你的弓箭，面對排山倒海的敵人了嗎？《弓箭英雄：塔防》是一款結合了塔防策略與Roguelite元素的超休閒遊戲。每次升級都能三選一技能，是要彈射、冰凍還是連射？選錯了可能下一秒就躺平。玩家們都在瘋狂尋找最新的兌換碼，希望能開局就拿到神裝。別忘了，強大的火力支援是守塔的關鍵，這時候就需要可靠的代儲值服務來幫你一把。想要穩穩通關，拿到稀有的禮包碼獎勵嗎？與其苦苦硬撐，不如尋求快速安全的代儲值，讓你的箭塔升到滿級，輕鬆碾壓所有來犯的敵人，成為真正的塔防大師！</v>
       </c>
       <c r="F285" s="13" t="s">
-        <v>5253</v>
+        <v>5245</v>
       </c>
       <c r="G285" s="9" t="s">
-        <v>5252</v>
+        <v>5244</v>
       </c>
       <c r="K285" s="13" t="s">
-        <v>5253</v>
+        <v>5245</v>
       </c>
       <c r="L285" s="9" t="s">
-        <v>5252</v>
+        <v>5244</v>
       </c>
     </row>
     <row r="286" spans="1:40">
@@ -61682,16 +61676,16 @@
         <v>《十二之天M Reborn》誓言找回當年的感動，讓玩家重溫三大勢力的激情對決。這款遊戲主打的就是一個原汁原味，熟悉的場景、懷舊的BGM，以及那令人又愛又恨的勢力戰。準備好再次投身這場無盡的江湖恩怨了嗎？大家都在蹲點最新的禮包碼，希望能搶先一步強化裝備。官方發放的兌換碼雖然不無小補，但真正的強者懂得利用資源。想要快速提升戰力，不妨考慮專業的代儲值服務。與其在戰場上被當小兵清掉，不如透過快速安全的管道補足元寶，讓你的角色戰力飆升，在龍瀑鎮插旗，重現當年的榮光！</v>
       </c>
       <c r="F286" s="13" t="s">
-        <v>5253</v>
+        <v>5245</v>
       </c>
       <c r="G286" s="9" t="s">
-        <v>5252</v>
+        <v>5244</v>
       </c>
       <c r="K286" s="13" t="s">
-        <v>5253</v>
+        <v>5245</v>
       </c>
       <c r="L286" s="9" t="s">
-        <v>5252</v>
+        <v>5244</v>
       </c>
     </row>
     <row r="287" spans="1:40">
@@ -61712,10 +61706,10 @@
         <v>正版授權的《NBA巔峰對決》終於來了。這款主打真人PVP的籃球手遊，讓你能操控喜愛的NBA球星。遊戲強調操作手感與球星的專屬技能，想秀一波高難度灌籃或致命三分球？全看你的技術。但說真的，想在天梯上爬分，球員的養成才是關鍵。新手們別再傻傻地問兌換碼在哪了，那點資源根本不夠看。想要打造你的夢幻陣容，把傳奇球星都納入麾下，可靠的代儲值才是捷徑。別家還在慢慢存資源，你已經透過快速安全的儲值拿到關鍵禮包碼，直接抽爆卡池，讓你的隊伍戰力登頂，在球場上制霸全場！</v>
       </c>
       <c r="F287" s="13" t="s">
-        <v>5309</v>
+        <v>5301</v>
       </c>
       <c r="G287" s="9" t="s">
-        <v>5310</v>
+        <v>5302</v>
       </c>
       <c r="H287" s="9" t="s">
         <v>2625</v>
@@ -61724,34 +61718,34 @@
         <v>4360</v>
       </c>
       <c r="K287" s="13" t="s">
+        <v>5291</v>
+      </c>
+      <c r="L287" s="9" t="s">
+        <v>5296</v>
+      </c>
+      <c r="M287" s="14" t="s">
+        <v>5292</v>
+      </c>
+      <c r="N287" s="9" t="s">
+        <v>5297</v>
+      </c>
+      <c r="O287" s="14" t="s">
+        <v>5293</v>
+      </c>
+      <c r="P287" s="9" t="s">
+        <v>5298</v>
+      </c>
+      <c r="Q287" s="14" t="s">
+        <v>5294</v>
+      </c>
+      <c r="R287" s="9" t="s">
         <v>5299</v>
       </c>
-      <c r="L287" s="9" t="s">
-        <v>5304</v>
-      </c>
-      <c r="M287" s="14" t="s">
+      <c r="S287" s="14" t="s">
+        <v>5295</v>
+      </c>
+      <c r="T287" s="9" t="s">
         <v>5300</v>
-      </c>
-      <c r="N287" s="9" t="s">
-        <v>5305</v>
-      </c>
-      <c r="O287" s="14" t="s">
-        <v>5301</v>
-      </c>
-      <c r="P287" s="9" t="s">
-        <v>5306</v>
-      </c>
-      <c r="Q287" s="14" t="s">
-        <v>5302</v>
-      </c>
-      <c r="R287" s="9" t="s">
-        <v>5307</v>
-      </c>
-      <c r="S287" s="14" t="s">
-        <v>5303</v>
-      </c>
-      <c r="T287" s="9" t="s">
-        <v>5308</v>
       </c>
     </row>
     <row r="288" spans="1:40">
@@ -61772,16 +61766,16 @@
         <v>又一款三國策略遊戲？先別急著滑掉！《三國志：王戰》是一款主打快節奏的SLG手遊，標榜著15天一賽季的急速征戰。在這裡，你不用再苦苦熬夜農地、屯兵，而是要把握黃金時間，快速發展內政、招募名將，與盟友一同攻城掠地。當然，想在短短15天內統一天下，光靠策略可不夠。新手們拚命搜尋的兌換碼，拿到的資源可能還不夠升一座主城。真正的王者都懂得運用代儲值服務，在開局就快人一步。別再猶豫了，利用快速安全的管道取得珍稀禮包碼與資源，迅速拉高戰力，在賽季結束前稱霸全服！</v>
       </c>
       <c r="F288" s="13" t="s">
-        <v>5253</v>
+        <v>5245</v>
       </c>
       <c r="G288" s="9" t="s">
-        <v>5252</v>
+        <v>5244</v>
       </c>
       <c r="K288" s="13" t="s">
-        <v>5253</v>
+        <v>5245</v>
       </c>
       <c r="L288" s="9" t="s">
-        <v>5252</v>
+        <v>5244</v>
       </c>
     </row>
     <row r="289" spans="1:5">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7870" uniqueCount="5352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7898" uniqueCount="5376">
   <si>
     <t>Facebook</t>
   </si>
@@ -20399,6 +20399,87 @@
   </si>
   <si>
     <t>免廣月卡</t>
+  </si>
+  <si>
+    <t>招募券*5+金幣*500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>體力*10+金幣*500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>招募券*5+金幣*500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寶錘*1+金幣*500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>體力*10+金幣*500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣*1000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>全套裝備鍛造書</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>招募券*2+金幣*500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>信長 霸道</t>
+  </si>
+  <si>
+    <t>https://www.gamecity.com.tw/nobunaga_hadou/</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=jp.co.koeitecmo.Power&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E4%BF%A1%E9%95%B7%E4%B9%8B%E9%87%8E%E6%9C%9B-%E9%9C%B8%E9%81%93/id1619722298</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/nobunaga.hadou.tw/</t>
+  </si>
+  <si>
+    <t>小判11800禮包</t>
+  </si>
+  <si>
+    <t>小判6000禮包</t>
+  </si>
+  <si>
+    <t>小判3000禮包</t>
+  </si>
+  <si>
+    <t>小判2000禮包</t>
+  </si>
+  <si>
+    <t>小判800禮包</t>
+  </si>
+  <si>
+    <t>小判160禮包</t>
+  </si>
+  <si>
+    <t>無限期通行證</t>
+  </si>
+  <si>
+    <t>90天通行證</t>
+  </si>
+  <si>
+    <t>30天通行證</t>
+  </si>
+  <si>
+    <t>屋敷LV通行證</t>
+  </si>
+  <si>
+    <t>光榮特庫摩出品，正統信長之野望系列最新力作《信長之野望 霸道》終於登場！這次玩家將化身侍奉各地大名的領主，在MMO化的戰國世界中，與同勢力的盟友們一同奮戰，體驗四季變化的精美3D地圖與緊張刺激的攻城戰。想在亂世中快人一步？別忘了到處尋找隱藏的兌換碼與禮包碼，領取初期資源。當然，若想讓統一天下的霸業之路更加順遂，尋找快速安全的代儲值服務也是各位城主大人們的必修課，畢竟在戰場上，兵貴神速啊！立即投身亂世，與盟友們共創霸業！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -20761,7 +20842,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -20960,6 +21041,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -36017,10 +36099,10 @@
       <c r="AG223" s="62">
         <v>85</v>
       </c>
-      <c r="AH223" s="82" t="s">
+      <c r="AH223" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AI223" s="85" t="s">
+      <c r="AI223" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -36087,10 +36169,10 @@
       <c r="U224" s="62">
         <v>28</v>
       </c>
-      <c r="V224" s="82" t="s">
+      <c r="V224" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="W224" s="85" t="s">
+      <c r="W224" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -36203,10 +36285,10 @@
       <c r="U226" s="62">
         <v>124</v>
       </c>
-      <c r="V226" s="82" t="s">
+      <c r="V226" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="W226" s="85" t="s">
+      <c r="W226" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -36303,10 +36385,10 @@
       <c r="AE227" s="62">
         <v>519</v>
       </c>
-      <c r="AF227" s="82" t="s">
+      <c r="AF227" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AG227" s="85" t="s">
+      <c r="AG227" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -36397,10 +36479,10 @@
       <c r="AC228" s="62">
         <v>27</v>
       </c>
-      <c r="AD228" s="82" t="s">
+      <c r="AD228" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE228" s="85" t="s">
+      <c r="AE228" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -36491,10 +36573,10 @@
       <c r="AC229" s="62">
         <v>132</v>
       </c>
-      <c r="AD229" s="82" t="s">
+      <c r="AD229" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE229" s="85" t="s">
+      <c r="AE229" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -36597,10 +36679,10 @@
       <c r="AG230" s="51">
         <v>329</v>
       </c>
-      <c r="AH230" s="82" t="s">
+      <c r="AH230" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AI230" s="85" t="s">
+      <c r="AI230" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -36685,10 +36767,10 @@
       <c r="AA231" s="62">
         <v>535</v>
       </c>
-      <c r="AB231" s="82" t="s">
+      <c r="AB231" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AC231" s="85" t="s">
+      <c r="AC231" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -36779,10 +36861,10 @@
       <c r="AC232" s="62">
         <v>279</v>
       </c>
-      <c r="AD232" s="82" t="s">
+      <c r="AD232" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE232" s="85" t="s">
+      <c r="AE232" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -36907,10 +36989,10 @@
       <c r="AC234" s="51">
         <v>83</v>
       </c>
-      <c r="AD234" s="82" t="s">
+      <c r="AD234" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE234" s="85" t="s">
+      <c r="AE234" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -36995,10 +37077,10 @@
       <c r="AA235" s="51">
         <v>74</v>
       </c>
-      <c r="AB235" s="82" t="s">
+      <c r="AB235" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AC235" s="85" t="s">
+      <c r="AC235" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -37095,10 +37177,10 @@
       <c r="AE236" s="51">
         <v>27</v>
       </c>
-      <c r="AF236" s="82" t="s">
+      <c r="AF236" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AG236" s="85" t="s">
+      <c r="AG236" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -37189,10 +37271,10 @@
       <c r="AC237" s="51">
         <v>27</v>
       </c>
-      <c r="AD237" s="82" t="s">
+      <c r="AD237" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE237" s="85" t="s">
+      <c r="AE237" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -37265,10 +37347,10 @@
       <c r="W238" s="51">
         <v>27</v>
       </c>
-      <c r="X238" s="82" t="s">
+      <c r="X238" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="Y238" s="85" t="s">
+      <c r="Y238" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -37353,10 +37435,10 @@
       <c r="AA239" s="51">
         <v>256</v>
       </c>
-      <c r="AB239" s="82" t="s">
+      <c r="AB239" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AC239" s="85" t="s">
+      <c r="AC239" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -37423,10 +37505,10 @@
       <c r="U240" s="51">
         <v>50</v>
       </c>
-      <c r="V240" s="82" t="s">
+      <c r="V240" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="W240" s="85" t="s">
+      <c r="W240" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -37511,10 +37593,10 @@
       <c r="AA241" s="51">
         <v>124</v>
       </c>
-      <c r="AB241" s="82" t="s">
+      <c r="AB241" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AC241" s="85" t="s">
+      <c r="AC241" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -37587,10 +37669,10 @@
       <c r="W242" s="51">
         <v>248</v>
       </c>
-      <c r="X242" s="82" t="s">
+      <c r="X242" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="Y242" s="85" t="s">
+      <c r="Y242" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -37675,10 +37757,10 @@
       <c r="AA243" s="51">
         <v>57</v>
       </c>
-      <c r="AB243" s="82" t="s">
+      <c r="AB243" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AC243" s="85" t="s">
+      <c r="AC243" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -37769,10 +37851,10 @@
       <c r="AC244" s="51">
         <v>612</v>
       </c>
-      <c r="AD244" s="82" t="s">
+      <c r="AD244" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE244" s="85" t="s">
+      <c r="AE244" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -37845,10 +37927,10 @@
       <c r="W245" s="51">
         <v>256</v>
       </c>
-      <c r="X245" s="82" t="s">
+      <c r="X245" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="Y245" s="85" t="s">
+      <c r="Y245" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -37903,10 +37985,10 @@
       <c r="Q246" s="51">
         <v>25</v>
       </c>
-      <c r="R246" s="82" t="s">
+      <c r="R246" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="S246" s="85" t="s">
+      <c r="S246" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -37979,10 +38061,10 @@
       <c r="W247" s="51">
         <v>29</v>
       </c>
-      <c r="X247" s="82" t="s">
+      <c r="X247" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="Y247" s="85" t="s">
+      <c r="Y247" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -38067,10 +38149,10 @@
       <c r="AA248" s="51">
         <v>25</v>
       </c>
-      <c r="AB248" s="82" t="s">
+      <c r="AB248" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AC248" s="85" t="s">
+      <c r="AC248" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -38149,10 +38231,10 @@
       <c r="Y249" s="54">
         <v>27</v>
       </c>
-      <c r="Z249" s="82" t="s">
+      <c r="Z249" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AA249" s="85" t="s">
+      <c r="AA249" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -38225,10 +38307,10 @@
       <c r="W250" s="54">
         <v>33</v>
       </c>
-      <c r="X250" s="82" t="s">
+      <c r="X250" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="Y250" s="85" t="s">
+      <c r="Y250" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -38295,10 +38377,10 @@
       <c r="U251" s="54">
         <v>25</v>
       </c>
-      <c r="V251" s="82" t="s">
+      <c r="V251" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="W251" s="85" t="s">
+      <c r="W251" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -38389,10 +38471,10 @@
       <c r="AC252" s="54">
         <v>124</v>
       </c>
-      <c r="AD252" s="82" t="s">
+      <c r="AD252" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE252" s="85" t="s">
+      <c r="AE252" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -38489,10 +38571,10 @@
       <c r="AE253" s="54">
         <v>107</v>
       </c>
-      <c r="AF253" s="82" t="s">
+      <c r="AF253" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AG253" s="85" t="s">
+      <c r="AG253" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -38571,10 +38653,10 @@
       <c r="Y254" s="54">
         <v>74</v>
       </c>
-      <c r="Z254" s="82" t="s">
+      <c r="Z254" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AA254" s="85" t="s">
+      <c r="AA254" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -38647,10 +38729,10 @@
       <c r="W255" s="54">
         <v>216</v>
       </c>
-      <c r="X255" s="82" t="s">
+      <c r="X255" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="Y255" s="85" t="s">
+      <c r="Y255" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -38723,10 +38805,10 @@
       <c r="W256" s="54">
         <v>6095</v>
       </c>
-      <c r="X256" s="82" t="s">
+      <c r="X256" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="Y256" s="85" t="s">
+      <c r="Y256" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -38817,10 +38899,10 @@
       <c r="AC257" s="54">
         <v>551</v>
       </c>
-      <c r="AD257" s="82" t="s">
+      <c r="AD257" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE257" s="85" t="s">
+      <c r="AE257" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -38917,10 +38999,10 @@
       <c r="AE258" s="54">
         <v>1725</v>
       </c>
-      <c r="AF258" s="82" t="s">
+      <c r="AF258" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AG258" s="85" t="s">
+      <c r="AG258" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -39005,10 +39087,10 @@
       <c r="AA259" s="54">
         <v>630</v>
       </c>
-      <c r="AB259" s="82" t="s">
+      <c r="AB259" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AC259" s="85" t="s">
+      <c r="AC259" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -39099,10 +39181,10 @@
       <c r="AC260" s="54">
         <v>551</v>
       </c>
-      <c r="AD260" s="82" t="s">
+      <c r="AD260" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE260" s="85" t="s">
+      <c r="AE260" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -39181,10 +39263,10 @@
       <c r="Y261" s="54">
         <v>1173</v>
       </c>
-      <c r="Z261" s="82" t="s">
+      <c r="Z261" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AA261" s="85" t="s">
+      <c r="AA261" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -39251,10 +39333,10 @@
       <c r="U262" s="54">
         <v>77</v>
       </c>
-      <c r="V262" s="82" t="s">
+      <c r="V262" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="W262" s="85" t="s">
+      <c r="W262" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -39357,10 +39439,10 @@
       <c r="AG263" s="54">
         <v>26</v>
       </c>
-      <c r="AH263" s="82" t="s">
+      <c r="AH263" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AI263" s="85" t="s">
+      <c r="AI263" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -39479,10 +39561,10 @@
       <c r="AC265" s="54">
         <v>162</v>
       </c>
-      <c r="AD265" s="82" t="s">
+      <c r="AD265" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE265" s="85" t="s">
+      <c r="AE265" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -39561,10 +39643,10 @@
       <c r="Y266" s="54">
         <v>29</v>
       </c>
-      <c r="Z266" s="82" t="s">
+      <c r="Z266" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AA266" s="85" t="s">
+      <c r="AA266" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -39655,10 +39737,10 @@
       <c r="AC267" s="54">
         <v>196</v>
       </c>
-      <c r="AD267" s="82" t="s">
+      <c r="AD267" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE267" s="85" t="s">
+      <c r="AE267" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -39749,10 +39831,10 @@
       <c r="AC268" s="54">
         <v>145</v>
       </c>
-      <c r="AD268" s="82" t="s">
+      <c r="AD268" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE268" s="85" t="s">
+      <c r="AE268" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -39837,10 +39919,10 @@
       <c r="AA269" s="54">
         <v>26</v>
       </c>
-      <c r="AB269" s="82" t="s">
+      <c r="AB269" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AC269" s="85" t="s">
+      <c r="AC269" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -39895,10 +39977,10 @@
       <c r="Q270" s="54">
         <v>227</v>
       </c>
-      <c r="R270" s="82" t="s">
+      <c r="R270" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="S270" s="85" t="s">
+      <c r="S270" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -39989,10 +40071,10 @@
       <c r="AC271" s="54">
         <v>314</v>
       </c>
-      <c r="AD271" s="82" t="s">
+      <c r="AD271" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE271" s="85" t="s">
+      <c r="AE271" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -40065,10 +40147,10 @@
       <c r="W272" s="54">
         <v>29</v>
       </c>
-      <c r="X272" s="82" t="s">
+      <c r="X272" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="Y272" s="85" t="s">
+      <c r="Y272" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -40159,10 +40241,10 @@
       <c r="AC273" s="54">
         <v>160</v>
       </c>
-      <c r="AD273" s="82" t="s">
+      <c r="AD273" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE273" s="85" t="s">
+      <c r="AE273" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -40253,10 +40335,10 @@
       <c r="AC274" s="54">
         <v>2343</v>
       </c>
-      <c r="AD274" s="82" t="s">
+      <c r="AD274" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE274" s="85" t="s">
+      <c r="AE274" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -40335,10 +40417,10 @@
       <c r="Y275" s="54">
         <v>141</v>
       </c>
-      <c r="Z275" s="82" t="s">
+      <c r="Z275" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AA275" s="85" t="s">
+      <c r="AA275" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -40417,10 +40499,10 @@
       <c r="Y276" s="58">
         <v>133</v>
       </c>
-      <c r="Z276" s="82" t="s">
+      <c r="Z276" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AA276" s="85" t="s">
+      <c r="AA276" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -40451,54 +40533,54 @@
       <c r="I277" s="38" t="s">
         <v>5088</v>
       </c>
-      <c r="J277" s="83" t="s">
+      <c r="J277" s="84" t="s">
         <v>5008</v>
       </c>
-      <c r="K277" s="84">
+      <c r="K277" s="85">
         <v>2655</v>
       </c>
-      <c r="L277" s="83" t="s">
+      <c r="L277" s="84" t="s">
         <v>5009</v>
       </c>
-      <c r="M277" s="84">
+      <c r="M277" s="85">
         <v>1389</v>
       </c>
-      <c r="N277" s="83" t="s">
+      <c r="N277" s="84" t="s">
         <v>5167</v>
       </c>
-      <c r="O277" s="84">
+      <c r="O277" s="85">
         <v>821</v>
       </c>
-      <c r="P277" s="83" t="s">
+      <c r="P277" s="84" t="s">
         <v>5168</v>
       </c>
-      <c r="Q277" s="84">
+      <c r="Q277" s="85">
         <v>407</v>
       </c>
-      <c r="R277" s="83" t="s">
+      <c r="R277" s="84" t="s">
         <v>5012</v>
       </c>
-      <c r="S277" s="84">
+      <c r="S277" s="85">
         <v>147</v>
       </c>
-      <c r="T277" s="83" t="s">
+      <c r="T277" s="84" t="s">
         <v>1377</v>
       </c>
-      <c r="U277" s="84">
+      <c r="U277" s="85">
         <v>29</v>
       </c>
-      <c r="V277" s="83" t="s">
+      <c r="V277" s="84" t="s">
         <v>5169</v>
       </c>
-      <c r="W277" s="84">
+      <c r="W277" s="85">
         <v>147</v>
       </c>
       <c r="X277" s="52"/>
       <c r="Y277" s="54"/>
-      <c r="Z277" s="82" t="s">
+      <c r="Z277" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AA277" s="85" t="s">
+      <c r="AA277" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -40589,10 +40671,10 @@
       <c r="AC278" s="54">
         <v>261</v>
       </c>
-      <c r="AD278" s="82" t="s">
+      <c r="AD278" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE278" s="85" t="s">
+      <c r="AE278" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -40677,10 +40759,10 @@
       <c r="AA279" s="54">
         <v>141</v>
       </c>
-      <c r="AB279" s="82" t="s">
+      <c r="AB279" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AC279" s="85" t="s">
+      <c r="AC279" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -40711,52 +40793,52 @@
       <c r="I280" s="66" t="s">
         <v>5165</v>
       </c>
-      <c r="J280" s="83" t="s">
+      <c r="J280" s="84" t="s">
         <v>5148</v>
       </c>
-      <c r="K280" s="84">
+      <c r="K280" s="85">
         <v>2302</v>
       </c>
-      <c r="L280" s="83" t="s">
+      <c r="L280" s="84" t="s">
         <v>5149</v>
       </c>
-      <c r="M280" s="84">
+      <c r="M280" s="85">
         <v>1168</v>
       </c>
-      <c r="N280" s="83" t="s">
+      <c r="N280" s="84" t="s">
         <v>5150</v>
       </c>
-      <c r="O280" s="84">
+      <c r="O280" s="85">
         <v>467</v>
       </c>
-      <c r="P280" s="83" t="s">
+      <c r="P280" s="84" t="s">
         <v>5151</v>
       </c>
-      <c r="Q280" s="84">
+      <c r="Q280" s="85">
         <v>248</v>
       </c>
-      <c r="R280" s="83" t="s">
+      <c r="R280" s="84" t="s">
         <v>5152</v>
       </c>
-      <c r="S280" s="84">
+      <c r="S280" s="85">
         <v>124</v>
       </c>
-      <c r="T280" s="83" t="s">
+      <c r="T280" s="84" t="s">
         <v>5153</v>
       </c>
-      <c r="U280" s="84">
+      <c r="U280" s="85">
         <v>51</v>
       </c>
-      <c r="V280" s="83" t="s">
+      <c r="V280" s="84" t="s">
         <v>5154</v>
       </c>
-      <c r="W280" s="84">
+      <c r="W280" s="85">
         <v>248</v>
       </c>
-      <c r="X280" s="82" t="s">
+      <c r="X280" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="Y280" s="85" t="s">
+      <c r="Y280" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
@@ -40787,69 +40869,69 @@
       <c r="I281" s="66" t="s">
         <v>5166</v>
       </c>
-      <c r="J281" s="83" t="s">
+      <c r="J281" s="84" t="s">
         <v>5155</v>
       </c>
-      <c r="K281" s="84">
+      <c r="K281" s="85">
         <v>1549</v>
       </c>
-      <c r="L281" s="83" t="s">
+      <c r="L281" s="84" t="s">
         <v>5156</v>
       </c>
-      <c r="M281" s="84">
+      <c r="M281" s="85">
         <v>1030</v>
       </c>
-      <c r="N281" s="83" t="s">
+      <c r="N281" s="84" t="s">
         <v>5157</v>
       </c>
-      <c r="O281" s="84">
+      <c r="O281" s="85">
         <v>673</v>
       </c>
-      <c r="P281" s="83" t="s">
+      <c r="P281" s="84" t="s">
         <v>5158</v>
       </c>
-      <c r="Q281" s="84">
+      <c r="Q281" s="85">
         <v>344</v>
       </c>
-      <c r="R281" s="83" t="s">
+      <c r="R281" s="84" t="s">
         <v>5159</v>
       </c>
-      <c r="S281" s="84">
+      <c r="S281" s="85">
         <v>157</v>
       </c>
-      <c r="T281" s="83" t="s">
+      <c r="T281" s="84" t="s">
         <v>5160</v>
       </c>
-      <c r="U281" s="84">
+      <c r="U281" s="85">
         <v>81</v>
       </c>
-      <c r="V281" s="83" t="s">
+      <c r="V281" s="84" t="s">
         <v>5161</v>
       </c>
-      <c r="W281" s="84">
+      <c r="W281" s="85">
         <v>17</v>
       </c>
-      <c r="X281" s="83" t="s">
+      <c r="X281" s="84" t="s">
         <v>5162</v>
       </c>
-      <c r="Y281" s="84">
+      <c r="Y281" s="85">
         <v>244</v>
       </c>
-      <c r="Z281" s="83" t="s">
+      <c r="Z281" s="84" t="s">
         <v>5163</v>
       </c>
-      <c r="AA281" s="84">
+      <c r="AA281" s="85">
         <v>139</v>
       </c>
-      <c r="AB281" s="82" t="s">
+      <c r="AB281" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AC281" s="85" t="s">
+      <c r="AC281" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
     <row r="282" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A282" s="84" t="s">
+      <c r="A282" s="85" t="s">
         <v>5209</v>
       </c>
       <c r="C282" s="36" t="s">
@@ -40865,7 +40947,7 @@
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=石器時代：寵物世界</v>
       </c>
-      <c r="G282" s="82" t="s">
+      <c r="G282" s="83" t="s">
         <v>5186</v>
       </c>
       <c r="H282" s="37" t="str">
@@ -40875,75 +40957,75 @@
       <c r="I282" s="38" t="s">
         <v>5189</v>
       </c>
-      <c r="J282" s="83" t="s">
+      <c r="J282" s="84" t="s">
         <v>4988</v>
       </c>
-      <c r="K282" s="84">
+      <c r="K282" s="85">
         <v>2655</v>
       </c>
-      <c r="L282" s="83" t="s">
+      <c r="L282" s="84" t="s">
         <v>1674</v>
       </c>
-      <c r="M282" s="84">
+      <c r="M282" s="85">
         <v>2047</v>
       </c>
-      <c r="N282" s="83" t="s">
+      <c r="N282" s="84" t="s">
         <v>5179</v>
       </c>
-      <c r="O282" s="84">
+      <c r="O282" s="85">
         <v>1357</v>
       </c>
-      <c r="P282" s="83" t="s">
+      <c r="P282" s="84" t="s">
         <v>5180</v>
       </c>
-      <c r="Q282" s="84">
+      <c r="Q282" s="85">
         <v>1085</v>
       </c>
-      <c r="R282" s="83" t="s">
+      <c r="R282" s="84" t="s">
         <v>5181</v>
       </c>
-      <c r="S282" s="84">
+      <c r="S282" s="85">
         <v>822</v>
       </c>
-      <c r="T282" s="83" t="s">
+      <c r="T282" s="84" t="s">
         <v>5182</v>
       </c>
-      <c r="U282" s="84">
+      <c r="U282" s="85">
         <v>680</v>
       </c>
-      <c r="V282" s="83" t="s">
+      <c r="V282" s="84" t="s">
         <v>152</v>
       </c>
-      <c r="W282" s="84">
+      <c r="W282" s="85">
         <v>572</v>
       </c>
-      <c r="X282" s="83" t="s">
+      <c r="X282" s="84" t="s">
         <v>153</v>
       </c>
-      <c r="Y282" s="84">
+      <c r="Y282" s="85">
         <v>407</v>
       </c>
-      <c r="Z282" s="83" t="s">
+      <c r="Z282" s="84" t="s">
         <v>5183</v>
       </c>
-      <c r="AA282" s="84">
+      <c r="AA282" s="85">
         <v>357</v>
       </c>
-      <c r="AB282" s="83" t="s">
+      <c r="AB282" s="84" t="s">
         <v>1680</v>
       </c>
-      <c r="AC282" s="84">
+      <c r="AC282" s="85">
         <v>274</v>
       </c>
-      <c r="AD282" s="82" t="s">
+      <c r="AD282" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE282" s="85" t="s">
+      <c r="AE282" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
     <row r="283" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A283" s="84" t="s">
+      <c r="A283" s="85" t="s">
         <v>5184</v>
       </c>
       <c r="C283" s="36" t="s">
@@ -40959,7 +41041,7 @@
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=蔚藍星球：國王很忙</v>
       </c>
-      <c r="G283" s="82" t="s">
+      <c r="G283" s="83" t="s">
         <v>5187</v>
       </c>
       <c r="H283" s="37" t="str">
@@ -41017,15 +41099,15 @@
       <c r="Y283" s="58">
         <v>89</v>
       </c>
-      <c r="Z283" s="82" t="s">
+      <c r="Z283" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AA283" s="85" t="s">
+      <c r="AA283" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
     <row r="284" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A284" s="84" t="s">
+      <c r="A284" s="85" t="s">
         <v>5185</v>
       </c>
       <c r="C284" s="36" t="s">
@@ -41041,7 +41123,7 @@
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=胸懷三國：美人計</v>
       </c>
-      <c r="G284" s="82" t="s">
+      <c r="G284" s="83" t="s">
         <v>5188</v>
       </c>
       <c r="H284" s="37" t="str">
@@ -41111,15 +41193,15 @@
       <c r="AC284" s="58">
         <v>586</v>
       </c>
-      <c r="AD284" s="82" t="s">
+      <c r="AD284" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AE284" s="85" t="s">
+      <c r="AE284" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
     <row r="285" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A285" s="84" t="s">
+      <c r="A285" s="85" t="s">
         <v>5236</v>
       </c>
       <c r="C285" s="36" t="s">
@@ -41135,7 +41217,7 @@
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=弓箭英雄：塔防</v>
       </c>
-      <c r="G285" s="82" t="s">
+      <c r="G285" s="83" t="s">
         <v>5237</v>
       </c>
       <c r="H285" s="37" t="str">
@@ -41181,15 +41263,15 @@
       <c r="U285" s="58">
         <v>27</v>
       </c>
-      <c r="V285" s="82" t="s">
+      <c r="V285" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="W285" s="85" t="s">
+      <c r="W285" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
     <row r="286" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A286" s="84" t="s">
+      <c r="A286" s="85" t="s">
         <v>5242</v>
       </c>
       <c r="C286" s="36" t="s">
@@ -41205,7 +41287,7 @@
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=十二之天M</v>
       </c>
-      <c r="G286" s="82" t="s">
+      <c r="G286" s="83" t="s">
         <v>5238</v>
       </c>
       <c r="H286" s="37" t="str">
@@ -41269,15 +41351,15 @@
       <c r="AA286" s="58">
         <v>705</v>
       </c>
-      <c r="AB286" s="82" t="s">
+      <c r="AB286" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="AC286" s="85" t="s">
+      <c r="AC286" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
     <row r="287" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A287" s="84" t="s">
+      <c r="A287" s="85" t="s">
         <v>5243</v>
       </c>
       <c r="C287" s="36" t="s">
@@ -41293,7 +41375,7 @@
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=NBA巔峰對決</v>
       </c>
-      <c r="G287" s="82" t="s">
+      <c r="G287" s="83" t="s">
         <v>5239</v>
       </c>
       <c r="H287" s="37" t="str">
@@ -41303,15 +41385,15 @@
       <c r="I287" s="38" t="s">
         <v>5258</v>
       </c>
-      <c r="J287" s="82" t="s">
+      <c r="J287" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="K287" s="85" t="s">
+      <c r="K287" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
     <row r="288" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A288" s="84" t="s">
+      <c r="A288" s="85" t="s">
         <v>5240</v>
       </c>
       <c r="C288" s="36" t="s">
@@ -41327,7 +41409,7 @@
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=三國志：王戰</v>
       </c>
-      <c r="G288" s="82" t="s">
+      <c r="G288" s="83" t="s">
         <v>5241</v>
       </c>
       <c r="H288" s="37" t="str">
@@ -41337,24 +41419,108 @@
       <c r="I288" s="38" t="s">
         <v>5259</v>
       </c>
-      <c r="J288" s="82" t="s">
+      <c r="J288" s="83" t="s">
         <v>5164</v>
       </c>
-      <c r="K288" s="85" t="s">
+      <c r="K288" s="86" t="s">
         <v>5262</v>
       </c>
     </row>
-    <row r="289" spans="6:8" ht="22.5" customHeight="1">
+    <row r="289" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A289" s="82" t="s">
+        <v>5360</v>
+      </c>
+      <c r="C289" s="36" t="s">
+        <v>5364</v>
+      </c>
+      <c r="D289" s="37" t="s">
+        <v>5361</v>
+      </c>
+      <c r="E289" s="37" t="s">
+        <v>5363</v>
+      </c>
       <c r="F289" s="36" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=信長 霸道</v>
+      </c>
+      <c r="G289" s="37" t="s">
+        <v>5362</v>
       </c>
       <c r="H289" s="37" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="290" spans="6:8" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/game-detail.html?game=信長 霸道</v>
+      </c>
+      <c r="I289" s="38" t="s">
+        <v>5375</v>
+      </c>
+      <c r="J289" s="1" t="s">
+        <v>5365</v>
+      </c>
+      <c r="K289" s="58">
+        <v>2086</v>
+      </c>
+      <c r="L289" s="1" t="s">
+        <v>5366</v>
+      </c>
+      <c r="M289" s="58">
+        <v>1051</v>
+      </c>
+      <c r="N289" s="1" t="s">
+        <v>5367</v>
+      </c>
+      <c r="O289" s="58">
+        <v>531</v>
+      </c>
+      <c r="P289" s="1" t="s">
+        <v>5368</v>
+      </c>
+      <c r="Q289" s="58">
+        <v>357</v>
+      </c>
+      <c r="R289" s="1" t="s">
+        <v>5369</v>
+      </c>
+      <c r="S289" s="58">
+        <v>149</v>
+      </c>
+      <c r="T289" s="1" t="s">
+        <v>5370</v>
+      </c>
+      <c r="U289" s="58">
+        <v>32</v>
+      </c>
+      <c r="V289" s="1" t="s">
+        <v>5371</v>
+      </c>
+      <c r="W289" s="58">
+        <v>1051</v>
+      </c>
+      <c r="X289" s="1" t="s">
+        <v>5372</v>
+      </c>
+      <c r="Y289" s="58">
+        <v>531</v>
+      </c>
+      <c r="Z289" s="1" t="s">
+        <v>5373</v>
+      </c>
+      <c r="AA289" s="58">
+        <v>186</v>
+      </c>
+      <c r="AB289" s="1" t="s">
+        <v>5374</v>
+      </c>
+      <c r="AC289" s="58">
+        <v>357</v>
+      </c>
+      <c r="AD289" s="83" t="s">
+        <v>5164</v>
+      </c>
+      <c r="AE289" s="86" t="s">
+        <v>5262</v>
+      </c>
+    </row>
+    <row r="290" spans="1:31" ht="22.5" customHeight="1">
       <c r="F290" s="36" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -41364,7 +41530,7 @@
         <v/>
       </c>
     </row>
-    <row r="291" spans="6:8" ht="22.5" customHeight="1">
+    <row r="291" spans="1:31" ht="22.5" customHeight="1">
       <c r="F291" s="36" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -41374,7 +41540,7 @@
         <v/>
       </c>
     </row>
-    <row r="292" spans="6:8" ht="22.5" customHeight="1">
+    <row r="292" spans="1:31" ht="22.5" customHeight="1">
       <c r="F292" s="36" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -41384,7 +41550,7 @@
         <v/>
       </c>
     </row>
-    <row r="293" spans="6:8" ht="22.5" customHeight="1">
+    <row r="293" spans="1:31" ht="22.5" customHeight="1">
       <c r="F293" s="36" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -41394,7 +41560,7 @@
         <v/>
       </c>
     </row>
-    <row r="294" spans="6:8" ht="22.5" customHeight="1">
+    <row r="294" spans="1:31" ht="22.5" customHeight="1">
       <c r="F294" s="36" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -41404,7 +41570,7 @@
         <v/>
       </c>
     </row>
-    <row r="295" spans="6:8" ht="22.5" customHeight="1">
+    <row r="295" spans="1:31" ht="22.5" customHeight="1">
       <c r="F295" s="36" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -41414,7 +41580,7 @@
         <v/>
       </c>
     </row>
-    <row r="296" spans="6:8" ht="22.5" customHeight="1">
+    <row r="296" spans="1:31" ht="22.5" customHeight="1">
       <c r="F296" s="36" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -41424,7 +41590,7 @@
         <v/>
       </c>
     </row>
-    <row r="297" spans="6:8" ht="22.5" customHeight="1">
+    <row r="297" spans="1:31" ht="22.5" customHeight="1">
       <c r="F297" s="36" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -41434,7 +41600,7 @@
         <v/>
       </c>
     </row>
-    <row r="298" spans="6:8" ht="22.5" customHeight="1">
+    <row r="298" spans="1:31" ht="22.5" customHeight="1">
       <c r="F298" s="36" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -41444,7 +41610,7 @@
         <v/>
       </c>
     </row>
-    <row r="299" spans="6:8" ht="22.5" customHeight="1">
+    <row r="299" spans="1:31" ht="22.5" customHeight="1">
       <c r="F299" s="36" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -41454,7 +41620,7 @@
         <v/>
       </c>
     </row>
-    <row r="300" spans="6:8" ht="22.5" customHeight="1">
+    <row r="300" spans="1:31" ht="22.5" customHeight="1">
       <c r="F300" s="36" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -41464,7 +41630,7 @@
         <v/>
       </c>
     </row>
-    <row r="301" spans="6:8" ht="22.5" customHeight="1">
+    <row r="301" spans="1:31" ht="22.5" customHeight="1">
       <c r="F301" s="36" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -41474,7 +41640,7 @@
         <v/>
       </c>
     </row>
-    <row r="302" spans="6:8" ht="22.5" customHeight="1">
+    <row r="302" spans="1:31" ht="22.5" customHeight="1">
       <c r="F302" s="36" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -41484,7 +41650,7 @@
         <v/>
       </c>
     </row>
-    <row r="303" spans="6:8" ht="22.5" customHeight="1">
+    <row r="303" spans="1:31" ht="22.5" customHeight="1">
       <c r="F303" s="36" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -41494,7 +41660,7 @@
         <v/>
       </c>
     </row>
-    <row r="304" spans="6:8" ht="22.5" customHeight="1">
+    <row r="304" spans="1:31" ht="22.5" customHeight="1">
       <c r="F304" s="36" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -44799,9 +44965,10 @@
     <hyperlink ref="J288" r:id="rId281"/>
     <hyperlink ref="Z276" r:id="rId282"/>
     <hyperlink ref="AB286" r:id="rId283"/>
+    <hyperlink ref="AD289" r:id="rId284"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId284"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId285"/>
 </worksheet>
 </file>
 
@@ -61483,32 +61650,62 @@
       <c r="K283" s="13" t="s">
         <v>5330</v>
       </c>
+      <c r="L283" s="9" t="s">
+        <v>5352</v>
+      </c>
       <c r="M283" s="14" t="s">
         <v>4141</v>
       </c>
+      <c r="N283" s="9" t="s">
+        <v>5353</v>
+      </c>
       <c r="O283" s="14" t="s">
         <v>4140</v>
       </c>
+      <c r="P283" s="9" t="s">
+        <v>5354</v>
+      </c>
       <c r="Q283" s="14" t="s">
         <v>5331</v>
       </c>
+      <c r="R283" s="9" t="s">
+        <v>5355</v>
+      </c>
       <c r="S283" s="14" t="s">
         <v>5332</v>
       </c>
+      <c r="T283" s="9" t="s">
+        <v>5356</v>
+      </c>
       <c r="U283" s="14" t="s">
         <v>5333</v>
       </c>
+      <c r="V283" s="9" t="s">
+        <v>5356</v>
+      </c>
       <c r="W283" s="14" t="s">
         <v>5334</v>
       </c>
+      <c r="X283" s="9" t="s">
+        <v>5356</v>
+      </c>
       <c r="Y283" s="14" t="s">
         <v>5335</v>
       </c>
+      <c r="Z283" s="9" t="s">
+        <v>5357</v>
+      </c>
       <c r="AA283" s="14" t="s">
         <v>2056</v>
       </c>
+      <c r="AB283" s="9" t="s">
+        <v>5358</v>
+      </c>
       <c r="AC283" s="14" t="s">
         <v>5336</v>
+      </c>
+      <c r="AD283" s="9" t="s">
+        <v>5359</v>
       </c>
     </row>
     <row r="284" spans="1:40">
@@ -61781,19 +61978,19 @@
     <row r="289" spans="1:5">
       <c r="A289" s="9" t="str">
         <f>IF(games!A289="", "", games!A289)</f>
-        <v/>
+        <v>信長 霸道</v>
       </c>
       <c r="C289" s="9" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>giftcodesbanner/信長 霸道-禮包碼.jpg</v>
       </c>
       <c r="D289" s="9" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=信長 霸道</v>
       </c>
       <c r="E289" s="10" t="str">
         <f>IF(games!I289&lt;&gt;"", games!I289, "")</f>
-        <v/>
+        <v>光榮特庫摩出品，正統信長之野望系列最新力作《信長之野望 霸道》終於登場！這次玩家將化身侍奉各地大名的領主，在MMO化的戰國世界中，與同勢力的盟友們一同奮戰，體驗四季變化的精美3D地圖與緊張刺激的攻城戰。想在亂世中快人一步？別忘了到處尋找隱藏的兌換碼與禮包碼，領取初期資源。當然，若想讓統一天下的霸業之路更加順遂，尋找快速安全的代儲值服務也是各位城主大人們的必修課，畢竟在戰場上，兵貴神速啊！立即投身亂世，與盟友們共創霸業！</v>
       </c>
     </row>
     <row r="290" spans="1:5">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7898" uniqueCount="5376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7910" uniqueCount="5384">
   <si>
     <t>Facebook</t>
   </si>
@@ -18621,19 +18621,10 @@
     <t>980月石晶胚</t>
   </si>
   <si>
-    <t>680月石晶胚</t>
-  </si>
-  <si>
     <t>300月石晶胚</t>
   </si>
   <si>
     <t>60月石晶胚</t>
-  </si>
-  <si>
-    <t>精裝詩集</t>
-  </si>
-  <si>
-    <t>待到日暖雪融限定禮包</t>
   </si>
   <si>
     <t>RR1475</t>
@@ -20480,6 +20471,49 @@
   <si>
     <t>光榮特庫摩出品，正統信長之野望系列最新力作《信長之野望 霸道》終於登場！這次玩家將化身侍奉各地大名的領主，在MMO化的戰國世界中，與同勢力的盟友們一同奮戰，體驗四季變化的精美3D地圖與緊張刺激的攻城戰。想在亂世中快人一步？別忘了到處尋找隱藏的兌換碼與禮包碼，領取初期資源。當然，若想讓統一天下的霸業之路更加順遂，尋找快速安全的代儲值服務也是各位城主大人們的必修課，畢竟在戰場上，兵貴神速啊！立即投身亂世，與盟友們共創霸業！</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>月石*100+深紅凝珠*100+戰鬥旋律三*3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>月石*100+深紅凝珠*100+武器說明書三*3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>月石*100+深紅凝珠*100+銅幣*30000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>銅幣*30000+武器說明書一*10+戰鬥旋律一*10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深紅凝珠*200+銅幣*20000+委託手冊一*2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>銅幣*10000+戰鬥旋律一*5+初級武器部件握柄*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>月石*20+銅幣*20000+戰鬥旋律一*10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>銅幣*10000+委託手冊一*2+初級武器部件刀刃*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深紅凝珠*100+銅幣*20000+戰鬥旋律一*5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>月石*20+銅幣*20000+戰鬥旋律一*10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>月度訂單</t>
   </si>
 </sst>
 </file>
@@ -27630,7 +27664,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/電鋸果汁大亂鬥.html</v>
       </c>
       <c r="I109" s="45" t="s">
-        <v>5137</v>
+        <v>5134</v>
       </c>
       <c r="J109" s="59" t="s">
         <v>1275</v>
@@ -36100,10 +36134,10 @@
         <v>85</v>
       </c>
       <c r="AH223" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AI223" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="224" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36170,10 +36204,10 @@
         <v>28</v>
       </c>
       <c r="V224" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="W224" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="225" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36286,10 +36320,10 @@
         <v>124</v>
       </c>
       <c r="V226" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="W226" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="227" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36386,10 +36420,10 @@
         <v>519</v>
       </c>
       <c r="AF227" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AG227" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="228" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36480,10 +36514,10 @@
         <v>27</v>
       </c>
       <c r="AD228" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE228" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="229" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36511,7 +36545,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/呷飽未？殭殭醬.html</v>
       </c>
       <c r="I229" s="66" t="s">
-        <v>5138</v>
+        <v>5135</v>
       </c>
       <c r="J229" s="59" t="s">
         <v>3720</v>
@@ -36574,15 +36608,15 @@
         <v>132</v>
       </c>
       <c r="AD229" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE229" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="230" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
       <c r="A230" s="54" t="s">
-        <v>5129</v>
+        <v>5126</v>
       </c>
       <c r="C230" s="36" t="s">
         <v>4180</v>
@@ -36605,7 +36639,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/XXL猛漢町.html</v>
       </c>
       <c r="I230" s="66" t="s">
-        <v>5139</v>
+        <v>5136</v>
       </c>
       <c r="J230" s="52" t="s">
         <v>4231</v>
@@ -36680,15 +36714,15 @@
         <v>329</v>
       </c>
       <c r="AH230" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AI230" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="231" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
       <c r="A231" s="54" t="s">
-        <v>5130</v>
+        <v>5127</v>
       </c>
       <c r="C231" s="79" t="s">
         <v>4190</v>
@@ -36711,7 +36745,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Dead Impact：Survival Online.html</v>
       </c>
       <c r="I231" s="66" t="s">
-        <v>5140</v>
+        <v>5137</v>
       </c>
       <c r="J231" s="59" t="s">
         <v>4159</v>
@@ -36768,10 +36802,10 @@
         <v>535</v>
       </c>
       <c r="AB231" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AC231" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="232" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36799,7 +36833,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/無限子彈.html</v>
       </c>
       <c r="I232" s="66" t="s">
-        <v>5141</v>
+        <v>5138</v>
       </c>
       <c r="J232" s="59" t="s">
         <v>4167</v>
@@ -36862,10 +36896,10 @@
         <v>279</v>
       </c>
       <c r="AD232" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE232" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="233" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -36893,7 +36927,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/Dunkadillo.html</v>
       </c>
       <c r="I233" s="66" t="s">
-        <v>5142</v>
+        <v>5139</v>
       </c>
       <c r="J233" s="59" t="s">
         <v>4175</v>
@@ -36990,10 +37024,10 @@
         <v>83</v>
       </c>
       <c r="AD234" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE234" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="235" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37078,10 +37112,10 @@
         <v>74</v>
       </c>
       <c r="AB235" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AC235" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="236" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37178,10 +37212,10 @@
         <v>27</v>
       </c>
       <c r="AF236" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AG236" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="237" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37272,10 +37306,10 @@
         <v>27</v>
       </c>
       <c r="AD237" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE237" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="238" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37348,10 +37382,10 @@
         <v>27</v>
       </c>
       <c r="X238" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="Y238" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="239" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37436,10 +37470,10 @@
         <v>256</v>
       </c>
       <c r="AB239" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AC239" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="240" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37506,10 +37540,10 @@
         <v>50</v>
       </c>
       <c r="V240" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="W240" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="241" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37537,7 +37571,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/玩具對決.html</v>
       </c>
       <c r="I241" s="66" t="s">
-        <v>5143</v>
+        <v>5140</v>
       </c>
       <c r="J241" s="52" t="s">
         <v>4432</v>
@@ -37594,10 +37628,10 @@
         <v>124</v>
       </c>
       <c r="AB241" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AC241" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="242" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37625,7 +37659,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/幸福都市：市長模擬器.html</v>
       </c>
       <c r="I242" s="66" t="s">
-        <v>5144</v>
+        <v>5141</v>
       </c>
       <c r="J242" s="52" t="s">
         <v>301</v>
@@ -37670,10 +37704,10 @@
         <v>248</v>
       </c>
       <c r="X242" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="Y242" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="243" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37701,7 +37735,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/黑道傳奇.html</v>
       </c>
       <c r="I243" s="66" t="s">
-        <v>5145</v>
+        <v>5142</v>
       </c>
       <c r="J243" s="52" t="s">
         <v>4437</v>
@@ -37758,15 +37792,15 @@
         <v>57</v>
       </c>
       <c r="AB243" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AC243" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="244" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A244" s="54" t="s">
-        <v>5131</v>
+        <v>5128</v>
       </c>
       <c r="C244" s="36" t="s">
         <v>3626</v>
@@ -37789,7 +37823,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/The kingdom：medieval tales.html</v>
       </c>
       <c r="I244" s="66" t="s">
-        <v>5146</v>
+        <v>5143</v>
       </c>
       <c r="J244" s="52" t="s">
         <v>301</v>
@@ -37852,15 +37886,15 @@
         <v>612</v>
       </c>
       <c r="AD244" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE244" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="245" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
       <c r="A245" s="54" t="s">
-        <v>5132</v>
+        <v>5129</v>
       </c>
       <c r="C245" s="79" t="s">
         <v>4473</v>
@@ -37928,10 +37962,10 @@
         <v>256</v>
       </c>
       <c r="X245" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="Y245" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="246" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -37962,7 +37996,7 @@
         <v>4470</v>
       </c>
       <c r="J246" s="52" t="s">
-        <v>5133</v>
+        <v>5130</v>
       </c>
       <c r="K246" s="51">
         <v>1139</v>
@@ -37986,10 +38020,10 @@
         <v>25</v>
       </c>
       <c r="R246" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="S246" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="247" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38062,10 +38096,10 @@
         <v>29</v>
       </c>
       <c r="X247" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="Y247" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="248" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38150,10 +38184,10 @@
         <v>25</v>
       </c>
       <c r="AB248" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AC248" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="249" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38232,10 +38266,10 @@
         <v>27</v>
       </c>
       <c r="Z249" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AA249" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="250" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38308,10 +38342,10 @@
         <v>33</v>
       </c>
       <c r="X250" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="Y250" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="251" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38378,10 +38412,10 @@
         <v>25</v>
       </c>
       <c r="V251" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="W251" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="252" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38472,10 +38506,10 @@
         <v>124</v>
       </c>
       <c r="AD252" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE252" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="253" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38572,10 +38606,10 @@
         <v>107</v>
       </c>
       <c r="AF253" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AG253" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="254" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38624,7 +38658,7 @@
         <v>380</v>
       </c>
       <c r="P254" s="52" t="s">
-        <v>5134</v>
+        <v>5131</v>
       </c>
       <c r="Q254" s="54">
         <v>194</v>
@@ -38654,10 +38688,10 @@
         <v>74</v>
       </c>
       <c r="Z254" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AA254" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="255" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38730,10 +38764,10 @@
         <v>216</v>
       </c>
       <c r="X255" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="Y255" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="256" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38806,10 +38840,10 @@
         <v>6095</v>
       </c>
       <c r="X256" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="Y256" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="257" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38900,10 +38934,10 @@
         <v>551</v>
       </c>
       <c r="AD257" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE257" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="258" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39000,10 +39034,10 @@
         <v>1725</v>
       </c>
       <c r="AF258" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AG258" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="259" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39088,10 +39122,10 @@
         <v>630</v>
       </c>
       <c r="AB259" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AC259" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="260" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39182,10 +39216,10 @@
         <v>551</v>
       </c>
       <c r="AD260" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE260" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="261" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39264,10 +39298,10 @@
         <v>1173</v>
       </c>
       <c r="Z261" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AA261" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="262" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39334,15 +39368,15 @@
         <v>77</v>
       </c>
       <c r="V262" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="W262" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="263" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
       <c r="A263" s="66" t="s">
-        <v>5135</v>
+        <v>5132</v>
       </c>
       <c r="C263" s="79" t="s">
         <v>4777</v>
@@ -39440,10 +39474,10 @@
         <v>26</v>
       </c>
       <c r="AH263" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AI263" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="264" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39499,7 +39533,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/幻牌交鋒.html</v>
       </c>
       <c r="I265" s="66" t="s">
-        <v>5147</v>
+        <v>5144</v>
       </c>
       <c r="J265" s="52" t="s">
         <v>4830</v>
@@ -39562,10 +39596,10 @@
         <v>162</v>
       </c>
       <c r="AD265" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE265" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="266" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39644,10 +39678,10 @@
         <v>29</v>
       </c>
       <c r="Z266" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AA266" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="267" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39738,10 +39772,10 @@
         <v>196</v>
       </c>
       <c r="AD267" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE267" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="268" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39832,10 +39866,10 @@
         <v>145</v>
       </c>
       <c r="AD268" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE268" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="269" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39920,10 +39954,10 @@
         <v>26</v>
       </c>
       <c r="AB269" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AC269" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="270" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39978,10 +40012,10 @@
         <v>227</v>
       </c>
       <c r="R270" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="S270" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="271" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40072,10 +40106,10 @@
         <v>314</v>
       </c>
       <c r="AD271" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE271" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="272" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40148,10 +40182,10 @@
         <v>29</v>
       </c>
       <c r="X272" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="Y272" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="273" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40242,10 +40276,10 @@
         <v>160</v>
       </c>
       <c r="AD273" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE273" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="274" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40336,10 +40370,10 @@
         <v>2343</v>
       </c>
       <c r="AD274" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE274" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="275" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40418,10 +40452,10 @@
         <v>141</v>
       </c>
       <c r="Z275" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AA275" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="276" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40452,58 +40486,58 @@
         <v>5087</v>
       </c>
       <c r="J276" s="1" t="s">
-        <v>5266</v>
+        <v>5263</v>
       </c>
       <c r="K276" s="58">
         <v>2477</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>5267</v>
+        <v>5264</v>
       </c>
       <c r="M276" s="58">
         <v>1346</v>
       </c>
       <c r="N276" s="1" t="s">
-        <v>5268</v>
+        <v>5265</v>
       </c>
       <c r="O276" s="58">
         <v>713</v>
       </c>
       <c r="P276" s="1" t="s">
-        <v>5269</v>
+        <v>5266</v>
       </c>
       <c r="Q276" s="58">
         <v>340</v>
       </c>
       <c r="R276" s="1" t="s">
-        <v>5270</v>
+        <v>5267</v>
       </c>
       <c r="S276" s="58">
         <v>169</v>
       </c>
       <c r="T276" s="1" t="s">
-        <v>5271</v>
+        <v>5268</v>
       </c>
       <c r="U276" s="58">
         <v>82</v>
       </c>
       <c r="V276" s="1" t="s">
-        <v>5272</v>
+        <v>5269</v>
       </c>
       <c r="W276" s="58">
         <v>30</v>
       </c>
       <c r="X276" s="1" t="s">
-        <v>5273</v>
+        <v>5270</v>
       </c>
       <c r="Y276" s="58">
         <v>133</v>
       </c>
       <c r="Z276" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AA276" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="277" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40546,13 +40580,13 @@
         <v>1389</v>
       </c>
       <c r="N277" s="84" t="s">
-        <v>5167</v>
+        <v>5164</v>
       </c>
       <c r="O277" s="85">
         <v>821</v>
       </c>
       <c r="P277" s="84" t="s">
-        <v>5168</v>
+        <v>5165</v>
       </c>
       <c r="Q277" s="85">
         <v>407</v>
@@ -40570,7 +40604,7 @@
         <v>29</v>
       </c>
       <c r="V277" s="84" t="s">
-        <v>5169</v>
+        <v>5166</v>
       </c>
       <c r="W277" s="85">
         <v>147</v>
@@ -40578,10 +40612,10 @@
       <c r="X277" s="52"/>
       <c r="Y277" s="54"/>
       <c r="Z277" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AA277" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="278" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40672,10 +40706,10 @@
         <v>261</v>
       </c>
       <c r="AD278" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE278" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="279" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -40705,257 +40739,249 @@
       <c r="I279" s="38" t="s">
         <v>5090</v>
       </c>
-      <c r="J279" s="52" t="s">
+      <c r="J279" s="1" t="s">
         <v>5099</v>
       </c>
-      <c r="K279" s="54">
-        <v>2533</v>
-      </c>
-      <c r="L279" s="52" t="s">
+      <c r="K279" s="58">
+        <v>2717</v>
+      </c>
+      <c r="L279" s="1" t="s">
         <v>5100</v>
       </c>
-      <c r="M279" s="54">
-        <v>1325</v>
-      </c>
-      <c r="N279" s="52" t="s">
+      <c r="M279" s="58">
+        <v>1422</v>
+      </c>
+      <c r="N279" s="1" t="s">
         <v>5101</v>
       </c>
-      <c r="O279" s="54">
-        <v>783</v>
-      </c>
-      <c r="P279" s="52" t="s">
+      <c r="O279" s="58">
+        <v>840</v>
+      </c>
+      <c r="P279" s="1" t="s">
         <v>5102</v>
       </c>
-      <c r="Q279" s="54">
-        <v>388</v>
-      </c>
-      <c r="R279" s="52" t="s">
+      <c r="Q279" s="58">
+        <v>416</v>
+      </c>
+      <c r="R279" s="1" t="s">
         <v>5103</v>
       </c>
-      <c r="S279" s="54">
-        <v>261</v>
-      </c>
-      <c r="T279" s="52" t="s">
+      <c r="S279" s="58">
+        <v>151</v>
+      </c>
+      <c r="T279" s="1" t="s">
         <v>5104</v>
       </c>
-      <c r="U279" s="54">
-        <v>141</v>
-      </c>
-      <c r="V279" s="52" t="s">
-        <v>5105</v>
-      </c>
-      <c r="W279" s="54">
-        <v>28</v>
-      </c>
-      <c r="X279" s="52" t="s">
-        <v>5106</v>
-      </c>
-      <c r="Y279" s="54">
-        <v>261</v>
-      </c>
-      <c r="Z279" s="52" t="s">
-        <v>5107</v>
-      </c>
-      <c r="AA279" s="54">
-        <v>141</v>
-      </c>
-      <c r="AB279" s="83" t="s">
-        <v>5164</v>
-      </c>
-      <c r="AC279" s="86" t="s">
-        <v>5262</v>
-      </c>
+      <c r="U279" s="58">
+        <v>30</v>
+      </c>
+      <c r="V279" s="1" t="s">
+        <v>5383</v>
+      </c>
+      <c r="W279" s="58">
+        <v>151</v>
+      </c>
+      <c r="X279" s="83" t="s">
+        <v>5161</v>
+      </c>
+      <c r="Y279" s="86" t="s">
+        <v>5259</v>
+      </c>
+      <c r="Z279" s="52"/>
+      <c r="AA279" s="54"/>
+      <c r="AB279" s="83"/>
+      <c r="AC279" s="86"/>
     </row>
     <row r="280" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A280" s="54" t="s">
-        <v>5126</v>
+        <v>5123</v>
       </c>
       <c r="C280" s="36" t="s">
-        <v>5123</v>
+        <v>5120</v>
       </c>
       <c r="D280" s="37" t="s">
-        <v>5124</v>
+        <v>5121</v>
       </c>
       <c r="E280" s="37" t="s">
-        <v>5122</v>
+        <v>5119</v>
       </c>
       <c r="F280" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=電馭跑酷</v>
       </c>
       <c r="G280" s="44" t="s">
-        <v>5127</v>
+        <v>5124</v>
       </c>
       <c r="H280" s="37" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/電馭跑酷.html</v>
       </c>
       <c r="I280" s="66" t="s">
-        <v>5165</v>
+        <v>5162</v>
       </c>
       <c r="J280" s="84" t="s">
-        <v>5148</v>
+        <v>5145</v>
       </c>
       <c r="K280" s="85">
         <v>2302</v>
       </c>
       <c r="L280" s="84" t="s">
-        <v>5149</v>
+        <v>5146</v>
       </c>
       <c r="M280" s="85">
         <v>1168</v>
       </c>
       <c r="N280" s="84" t="s">
-        <v>5150</v>
+        <v>5147</v>
       </c>
       <c r="O280" s="85">
         <v>467</v>
       </c>
       <c r="P280" s="84" t="s">
-        <v>5151</v>
+        <v>5148</v>
       </c>
       <c r="Q280" s="85">
         <v>248</v>
       </c>
       <c r="R280" s="84" t="s">
-        <v>5152</v>
+        <v>5149</v>
       </c>
       <c r="S280" s="85">
         <v>124</v>
       </c>
       <c r="T280" s="84" t="s">
-        <v>5153</v>
+        <v>5150</v>
       </c>
       <c r="U280" s="85">
         <v>51</v>
       </c>
       <c r="V280" s="84" t="s">
-        <v>5154</v>
+        <v>5151</v>
       </c>
       <c r="W280" s="85">
         <v>248</v>
       </c>
       <c r="X280" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="Y280" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="281" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A281" s="54" t="s">
-        <v>5136</v>
+        <v>5133</v>
       </c>
       <c r="C281" s="36" t="s">
-        <v>5125</v>
+        <v>5122</v>
       </c>
       <c r="D281" s="37" t="s">
-        <v>5121</v>
+        <v>5118</v>
       </c>
       <c r="E281" s="37" t="s">
-        <v>5120</v>
+        <v>5117</v>
       </c>
       <c r="F281" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=火焰紋章Shadows</v>
       </c>
       <c r="G281" s="44" t="s">
-        <v>5128</v>
+        <v>5125</v>
       </c>
       <c r="H281" s="37" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/火焰紋章Shadows.html</v>
       </c>
       <c r="I281" s="66" t="s">
-        <v>5166</v>
+        <v>5163</v>
       </c>
       <c r="J281" s="84" t="s">
-        <v>5155</v>
+        <v>5152</v>
       </c>
       <c r="K281" s="85">
         <v>1549</v>
       </c>
       <c r="L281" s="84" t="s">
-        <v>5156</v>
+        <v>5153</v>
       </c>
       <c r="M281" s="85">
         <v>1030</v>
       </c>
       <c r="N281" s="84" t="s">
-        <v>5157</v>
+        <v>5154</v>
       </c>
       <c r="O281" s="85">
         <v>673</v>
       </c>
       <c r="P281" s="84" t="s">
-        <v>5158</v>
+        <v>5155</v>
       </c>
       <c r="Q281" s="85">
         <v>344</v>
       </c>
       <c r="R281" s="84" t="s">
-        <v>5159</v>
+        <v>5156</v>
       </c>
       <c r="S281" s="85">
         <v>157</v>
       </c>
       <c r="T281" s="84" t="s">
-        <v>5160</v>
+        <v>5157</v>
       </c>
       <c r="U281" s="85">
         <v>81</v>
       </c>
       <c r="V281" s="84" t="s">
-        <v>5161</v>
+        <v>5158</v>
       </c>
       <c r="W281" s="85">
         <v>17</v>
       </c>
       <c r="X281" s="84" t="s">
-        <v>5162</v>
+        <v>5159</v>
       </c>
       <c r="Y281" s="85">
         <v>244</v>
       </c>
       <c r="Z281" s="84" t="s">
-        <v>5163</v>
+        <v>5160</v>
       </c>
       <c r="AA281" s="85">
         <v>139</v>
       </c>
       <c r="AB281" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AC281" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="282" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A282" s="85" t="s">
-        <v>5209</v>
+        <v>5206</v>
       </c>
       <c r="C282" s="36" t="s">
-        <v>5170</v>
+        <v>5167</v>
       </c>
       <c r="D282" s="37" t="s">
-        <v>5171</v>
+        <v>5168</v>
       </c>
       <c r="E282" s="37" t="s">
-        <v>5172</v>
+        <v>5169</v>
       </c>
       <c r="F282" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=石器時代：寵物世界</v>
       </c>
       <c r="G282" s="83" t="s">
-        <v>5186</v>
+        <v>5183</v>
       </c>
       <c r="H282" s="37" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/石器時代：寵物世界.html</v>
       </c>
       <c r="I282" s="38" t="s">
-        <v>5189</v>
+        <v>5186</v>
       </c>
       <c r="J282" s="84" t="s">
         <v>4988</v>
@@ -40970,25 +40996,25 @@
         <v>2047</v>
       </c>
       <c r="N282" s="84" t="s">
-        <v>5179</v>
+        <v>5176</v>
       </c>
       <c r="O282" s="85">
         <v>1357</v>
       </c>
       <c r="P282" s="84" t="s">
-        <v>5180</v>
+        <v>5177</v>
       </c>
       <c r="Q282" s="85">
         <v>1085</v>
       </c>
       <c r="R282" s="84" t="s">
-        <v>5181</v>
+        <v>5178</v>
       </c>
       <c r="S282" s="85">
         <v>822</v>
       </c>
       <c r="T282" s="84" t="s">
-        <v>5182</v>
+        <v>5179</v>
       </c>
       <c r="U282" s="85">
         <v>680</v>
@@ -41006,7 +41032,7 @@
         <v>407</v>
       </c>
       <c r="Z282" s="84" t="s">
-        <v>5183</v>
+        <v>5180</v>
       </c>
       <c r="AA282" s="85">
         <v>357</v>
@@ -41018,59 +41044,59 @@
         <v>274</v>
       </c>
       <c r="AD282" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE282" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="283" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A283" s="85" t="s">
-        <v>5184</v>
+        <v>5181</v>
       </c>
       <c r="C283" s="36" t="s">
-        <v>5173</v>
+        <v>5170</v>
       </c>
       <c r="D283" s="37" t="s">
-        <v>5174</v>
+        <v>5171</v>
       </c>
       <c r="E283" s="37" t="s">
-        <v>5175</v>
+        <v>5172</v>
       </c>
       <c r="F283" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=蔚藍星球：國王很忙</v>
       </c>
       <c r="G283" s="83" t="s">
-        <v>5187</v>
+        <v>5184</v>
       </c>
       <c r="H283" s="37" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/蔚藍星球：國王很忙.html</v>
       </c>
       <c r="I283" s="38" t="s">
-        <v>5190</v>
+        <v>5187</v>
       </c>
       <c r="J283" s="1" t="s">
-        <v>5346</v>
+        <v>5343</v>
       </c>
       <c r="K283" s="58">
         <v>2717</v>
       </c>
       <c r="L283" s="1" t="s">
-        <v>5347</v>
+        <v>5344</v>
       </c>
       <c r="M283" s="58">
         <v>1422</v>
       </c>
       <c r="N283" s="1" t="s">
-        <v>5348</v>
+        <v>5345</v>
       </c>
       <c r="O283" s="58">
         <v>586</v>
       </c>
       <c r="P283" s="1" t="s">
-        <v>5349</v>
+        <v>5346</v>
       </c>
       <c r="Q283" s="58">
         <v>416</v>
@@ -41088,147 +41114,147 @@
         <v>30</v>
       </c>
       <c r="V283" s="1" t="s">
-        <v>5350</v>
+        <v>5347</v>
       </c>
       <c r="W283" s="58">
         <v>151</v>
       </c>
       <c r="X283" s="1" t="s">
-        <v>5351</v>
+        <v>5348</v>
       </c>
       <c r="Y283" s="58">
         <v>89</v>
       </c>
       <c r="Z283" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AA283" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="284" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A284" s="85" t="s">
-        <v>5185</v>
+        <v>5182</v>
       </c>
       <c r="C284" s="36" t="s">
-        <v>5176</v>
+        <v>5173</v>
       </c>
       <c r="D284" s="37" t="s">
-        <v>5177</v>
+        <v>5174</v>
       </c>
       <c r="E284" s="37" t="s">
-        <v>5178</v>
+        <v>5175</v>
       </c>
       <c r="F284" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=胸懷三國：美人計</v>
       </c>
       <c r="G284" s="83" t="s">
-        <v>5188</v>
+        <v>5185</v>
       </c>
       <c r="H284" s="37" t="str">
         <f t="shared" ref="H284:H312" si="13">IF(A284="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A284)</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=胸懷三國：美人計</v>
       </c>
       <c r="I284" s="38" t="s">
-        <v>5191</v>
+        <v>5188</v>
       </c>
       <c r="J284" s="1" t="s">
-        <v>5281</v>
+        <v>5278</v>
       </c>
       <c r="K284" s="58">
         <v>2717</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>5282</v>
+        <v>5279</v>
       </c>
       <c r="M284" s="58">
         <v>1388</v>
       </c>
       <c r="N284" s="1" t="s">
-        <v>5283</v>
+        <v>5280</v>
       </c>
       <c r="O284" s="58">
         <v>841</v>
       </c>
       <c r="P284" s="1" t="s">
-        <v>5284</v>
+        <v>5281</v>
       </c>
       <c r="Q284" s="58">
         <v>586</v>
       </c>
       <c r="R284" s="1" t="s">
-        <v>5285</v>
+        <v>5282</v>
       </c>
       <c r="S284" s="58">
         <v>416</v>
       </c>
       <c r="T284" s="1" t="s">
-        <v>5286</v>
+        <v>5283</v>
       </c>
       <c r="U284" s="58">
         <v>280</v>
       </c>
       <c r="V284" s="1" t="s">
-        <v>5287</v>
+        <v>5284</v>
       </c>
       <c r="W284" s="58">
         <v>146</v>
       </c>
       <c r="X284" s="1" t="s">
-        <v>5288</v>
+        <v>5285</v>
       </c>
       <c r="Y284" s="58">
         <v>30</v>
       </c>
       <c r="Z284" s="1" t="s">
-        <v>5289</v>
+        <v>5286</v>
       </c>
       <c r="AA284" s="58">
         <v>416</v>
       </c>
       <c r="AB284" s="1" t="s">
-        <v>5290</v>
+        <v>5287</v>
       </c>
       <c r="AC284" s="58">
         <v>586</v>
       </c>
       <c r="AD284" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE284" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="285" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A285" s="85" t="s">
-        <v>5236</v>
+        <v>5233</v>
       </c>
       <c r="C285" s="36" t="s">
-        <v>5234</v>
+        <v>5231</v>
       </c>
       <c r="D285" s="37" t="s">
-        <v>5235</v>
+        <v>5232</v>
       </c>
       <c r="E285" s="37" t="s">
-        <v>5224</v>
+        <v>5221</v>
       </c>
       <c r="F285" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=弓箭英雄：塔防</v>
       </c>
       <c r="G285" s="83" t="s">
-        <v>5237</v>
+        <v>5234</v>
       </c>
       <c r="H285" s="37" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=弓箭英雄：塔防</v>
       </c>
       <c r="I285" s="38" t="s">
-        <v>5265</v>
+        <v>5262</v>
       </c>
       <c r="J285" s="1" t="s">
-        <v>5260</v>
+        <v>5257</v>
       </c>
       <c r="K285" s="58">
         <v>2469</v>
@@ -41258,65 +41284,65 @@
         <v>133</v>
       </c>
       <c r="T285" s="1" t="s">
-        <v>5261</v>
+        <v>5258</v>
       </c>
       <c r="U285" s="58">
         <v>27</v>
       </c>
       <c r="V285" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="W285" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="286" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A286" s="85" t="s">
-        <v>5242</v>
+        <v>5239</v>
       </c>
       <c r="C286" s="36" t="s">
-        <v>5226</v>
+        <v>5223</v>
       </c>
       <c r="D286" s="37" t="s">
-        <v>5225</v>
+        <v>5222</v>
       </c>
       <c r="E286" s="37" t="s">
-        <v>5227</v>
+        <v>5224</v>
       </c>
       <c r="F286" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=十二之天M</v>
       </c>
       <c r="G286" s="83" t="s">
-        <v>5238</v>
+        <v>5235</v>
       </c>
       <c r="H286" s="37" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=十二之天M</v>
       </c>
       <c r="I286" s="66" t="s">
-        <v>5257</v>
+        <v>5254</v>
       </c>
       <c r="J286" s="1" t="s">
-        <v>5274</v>
+        <v>5271</v>
       </c>
       <c r="K286" s="58">
         <v>2717</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>5275</v>
+        <v>5272</v>
       </c>
       <c r="M286" s="58">
         <v>1422</v>
       </c>
       <c r="N286" s="1" t="s">
-        <v>5276</v>
+        <v>5273</v>
       </c>
       <c r="O286" s="58">
         <v>840</v>
       </c>
       <c r="P286" s="1" t="s">
-        <v>5277</v>
+        <v>5274</v>
       </c>
       <c r="Q286" s="58">
         <v>416</v>
@@ -41334,190 +41360,190 @@
         <v>30</v>
       </c>
       <c r="V286" s="1" t="s">
-        <v>5278</v>
+        <v>5275</v>
       </c>
       <c r="W286" s="58">
         <v>213</v>
       </c>
       <c r="X286" s="1" t="s">
-        <v>5279</v>
+        <v>5276</v>
       </c>
       <c r="Y286" s="58">
         <v>357</v>
       </c>
       <c r="Z286" s="1" t="s">
-        <v>5280</v>
+        <v>5277</v>
       </c>
       <c r="AA286" s="58">
         <v>705</v>
       </c>
       <c r="AB286" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AC286" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="287" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A287" s="85" t="s">
-        <v>5243</v>
+        <v>5240</v>
       </c>
       <c r="C287" s="36" t="s">
-        <v>5230</v>
+        <v>5227</v>
       </c>
       <c r="D287" s="37" t="s">
-        <v>5229</v>
+        <v>5226</v>
       </c>
       <c r="E287" s="37" t="s">
-        <v>5228</v>
+        <v>5225</v>
       </c>
       <c r="F287" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=NBA巔峰對決</v>
       </c>
       <c r="G287" s="83" t="s">
-        <v>5239</v>
+        <v>5236</v>
       </c>
       <c r="H287" s="37" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=NBA巔峰對決</v>
       </c>
       <c r="I287" s="38" t="s">
-        <v>5258</v>
+        <v>5255</v>
       </c>
       <c r="J287" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="K287" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="288" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A288" s="85" t="s">
-        <v>5240</v>
+        <v>5237</v>
       </c>
       <c r="C288" s="36" t="s">
-        <v>5233</v>
+        <v>5230</v>
       </c>
       <c r="D288" s="37" t="s">
-        <v>5232</v>
+        <v>5229</v>
       </c>
       <c r="E288" s="37" t="s">
-        <v>5231</v>
+        <v>5228</v>
       </c>
       <c r="F288" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=三國志：王戰</v>
       </c>
       <c r="G288" s="83" t="s">
-        <v>5241</v>
+        <v>5238</v>
       </c>
       <c r="H288" s="37" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=三國志：王戰</v>
       </c>
       <c r="I288" s="38" t="s">
+        <v>5256</v>
+      </c>
+      <c r="J288" s="83" t="s">
+        <v>5161</v>
+      </c>
+      <c r="K288" s="86" t="s">
         <v>5259</v>
-      </c>
-      <c r="J288" s="83" t="s">
-        <v>5164</v>
-      </c>
-      <c r="K288" s="86" t="s">
-        <v>5262</v>
       </c>
     </row>
     <row r="289" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A289" s="82" t="s">
+        <v>5357</v>
+      </c>
+      <c r="C289" s="36" t="s">
+        <v>5361</v>
+      </c>
+      <c r="D289" s="37" t="s">
+        <v>5358</v>
+      </c>
+      <c r="E289" s="37" t="s">
         <v>5360</v>
-      </c>
-      <c r="C289" s="36" t="s">
-        <v>5364</v>
-      </c>
-      <c r="D289" s="37" t="s">
-        <v>5361</v>
-      </c>
-      <c r="E289" s="37" t="s">
-        <v>5363</v>
       </c>
       <c r="F289" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=信長 霸道</v>
       </c>
       <c r="G289" s="37" t="s">
-        <v>5362</v>
+        <v>5359</v>
       </c>
       <c r="H289" s="37" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=信長 霸道</v>
       </c>
       <c r="I289" s="38" t="s">
-        <v>5375</v>
+        <v>5372</v>
       </c>
       <c r="J289" s="1" t="s">
-        <v>5365</v>
+        <v>5362</v>
       </c>
       <c r="K289" s="58">
         <v>2086</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>5366</v>
+        <v>5363</v>
       </c>
       <c r="M289" s="58">
         <v>1051</v>
       </c>
       <c r="N289" s="1" t="s">
-        <v>5367</v>
+        <v>5364</v>
       </c>
       <c r="O289" s="58">
         <v>531</v>
       </c>
       <c r="P289" s="1" t="s">
-        <v>5368</v>
+        <v>5365</v>
       </c>
       <c r="Q289" s="58">
         <v>357</v>
       </c>
       <c r="R289" s="1" t="s">
-        <v>5369</v>
+        <v>5366</v>
       </c>
       <c r="S289" s="58">
         <v>149</v>
       </c>
       <c r="T289" s="1" t="s">
-        <v>5370</v>
+        <v>5367</v>
       </c>
       <c r="U289" s="58">
         <v>32</v>
       </c>
       <c r="V289" s="1" t="s">
-        <v>5371</v>
+        <v>5368</v>
       </c>
       <c r="W289" s="58">
         <v>1051</v>
       </c>
       <c r="X289" s="1" t="s">
-        <v>5372</v>
+        <v>5369</v>
       </c>
       <c r="Y289" s="58">
         <v>531</v>
       </c>
       <c r="Z289" s="1" t="s">
-        <v>5373</v>
+        <v>5370</v>
       </c>
       <c r="AA289" s="58">
         <v>186</v>
       </c>
       <c r="AB289" s="1" t="s">
-        <v>5374</v>
+        <v>5371</v>
       </c>
       <c r="AC289" s="58">
         <v>357</v>
       </c>
       <c r="AD289" s="83" t="s">
-        <v>5164</v>
+        <v>5161</v>
       </c>
       <c r="AE289" s="86" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="290" spans="1:31" ht="22.5" customHeight="1">
@@ -44908,64 +44934,64 @@
     <hyperlink ref="AD282" r:id="rId224"/>
     <hyperlink ref="Z283" r:id="rId225"/>
     <hyperlink ref="AD284" r:id="rId226"/>
-    <hyperlink ref="AB279" r:id="rId227"/>
-    <hyperlink ref="AD278" r:id="rId228"/>
-    <hyperlink ref="Z277" r:id="rId229"/>
-    <hyperlink ref="Z275" r:id="rId230"/>
-    <hyperlink ref="AD274" r:id="rId231"/>
-    <hyperlink ref="AD273" r:id="rId232"/>
-    <hyperlink ref="X272" r:id="rId233"/>
-    <hyperlink ref="AD271" r:id="rId234"/>
-    <hyperlink ref="R270" r:id="rId235"/>
-    <hyperlink ref="AB269" r:id="rId236"/>
-    <hyperlink ref="AD268" r:id="rId237"/>
-    <hyperlink ref="AD267" r:id="rId238"/>
-    <hyperlink ref="Z266" r:id="rId239"/>
-    <hyperlink ref="AD265" r:id="rId240"/>
-    <hyperlink ref="AH263" r:id="rId241"/>
-    <hyperlink ref="V262" r:id="rId242"/>
-    <hyperlink ref="Z261" r:id="rId243"/>
-    <hyperlink ref="AD260" r:id="rId244"/>
-    <hyperlink ref="AB259" r:id="rId245"/>
-    <hyperlink ref="AF258" r:id="rId246"/>
-    <hyperlink ref="AD257" r:id="rId247"/>
-    <hyperlink ref="X256" r:id="rId248"/>
-    <hyperlink ref="X255" r:id="rId249"/>
-    <hyperlink ref="Z254" r:id="rId250"/>
-    <hyperlink ref="AF253" r:id="rId251"/>
-    <hyperlink ref="AD252" r:id="rId252"/>
-    <hyperlink ref="V251" r:id="rId253"/>
-    <hyperlink ref="X250" r:id="rId254"/>
-    <hyperlink ref="Z249" r:id="rId255"/>
-    <hyperlink ref="AB248" r:id="rId256"/>
-    <hyperlink ref="X247" r:id="rId257"/>
-    <hyperlink ref="R246" r:id="rId258"/>
-    <hyperlink ref="X245" r:id="rId259"/>
-    <hyperlink ref="AD244" r:id="rId260"/>
-    <hyperlink ref="AB243" r:id="rId261"/>
-    <hyperlink ref="X242" r:id="rId262"/>
-    <hyperlink ref="AB241" r:id="rId263"/>
-    <hyperlink ref="V240" r:id="rId264"/>
-    <hyperlink ref="AB239" r:id="rId265"/>
-    <hyperlink ref="X238" r:id="rId266"/>
-    <hyperlink ref="AD237" r:id="rId267"/>
-    <hyperlink ref="AF236" r:id="rId268"/>
-    <hyperlink ref="AB235" r:id="rId269"/>
-    <hyperlink ref="AD234" r:id="rId270"/>
-    <hyperlink ref="AD232" r:id="rId271"/>
-    <hyperlink ref="AB231" r:id="rId272"/>
-    <hyperlink ref="AH230" r:id="rId273"/>
-    <hyperlink ref="AD229" r:id="rId274"/>
-    <hyperlink ref="AD228" r:id="rId275"/>
-    <hyperlink ref="AF227" r:id="rId276"/>
-    <hyperlink ref="V226" r:id="rId277"/>
-    <hyperlink ref="V224" r:id="rId278"/>
-    <hyperlink ref="AH223" r:id="rId279"/>
-    <hyperlink ref="J287" r:id="rId280"/>
-    <hyperlink ref="J288" r:id="rId281"/>
-    <hyperlink ref="Z276" r:id="rId282"/>
-    <hyperlink ref="AB286" r:id="rId283"/>
-    <hyperlink ref="AD289" r:id="rId284"/>
+    <hyperlink ref="AD278" r:id="rId227"/>
+    <hyperlink ref="Z277" r:id="rId228"/>
+    <hyperlink ref="Z275" r:id="rId229"/>
+    <hyperlink ref="AD274" r:id="rId230"/>
+    <hyperlink ref="AD273" r:id="rId231"/>
+    <hyperlink ref="X272" r:id="rId232"/>
+    <hyperlink ref="AD271" r:id="rId233"/>
+    <hyperlink ref="R270" r:id="rId234"/>
+    <hyperlink ref="AB269" r:id="rId235"/>
+    <hyperlink ref="AD268" r:id="rId236"/>
+    <hyperlink ref="AD267" r:id="rId237"/>
+    <hyperlink ref="Z266" r:id="rId238"/>
+    <hyperlink ref="AD265" r:id="rId239"/>
+    <hyperlink ref="AH263" r:id="rId240"/>
+    <hyperlink ref="V262" r:id="rId241"/>
+    <hyperlink ref="Z261" r:id="rId242"/>
+    <hyperlink ref="AD260" r:id="rId243"/>
+    <hyperlink ref="AB259" r:id="rId244"/>
+    <hyperlink ref="AF258" r:id="rId245"/>
+    <hyperlink ref="AD257" r:id="rId246"/>
+    <hyperlink ref="X256" r:id="rId247"/>
+    <hyperlink ref="X255" r:id="rId248"/>
+    <hyperlink ref="Z254" r:id="rId249"/>
+    <hyperlink ref="AF253" r:id="rId250"/>
+    <hyperlink ref="AD252" r:id="rId251"/>
+    <hyperlink ref="V251" r:id="rId252"/>
+    <hyperlink ref="X250" r:id="rId253"/>
+    <hyperlink ref="Z249" r:id="rId254"/>
+    <hyperlink ref="AB248" r:id="rId255"/>
+    <hyperlink ref="X247" r:id="rId256"/>
+    <hyperlink ref="R246" r:id="rId257"/>
+    <hyperlink ref="X245" r:id="rId258"/>
+    <hyperlink ref="AD244" r:id="rId259"/>
+    <hyperlink ref="AB243" r:id="rId260"/>
+    <hyperlink ref="X242" r:id="rId261"/>
+    <hyperlink ref="AB241" r:id="rId262"/>
+    <hyperlink ref="V240" r:id="rId263"/>
+    <hyperlink ref="AB239" r:id="rId264"/>
+    <hyperlink ref="X238" r:id="rId265"/>
+    <hyperlink ref="AD237" r:id="rId266"/>
+    <hyperlink ref="AF236" r:id="rId267"/>
+    <hyperlink ref="AB235" r:id="rId268"/>
+    <hyperlink ref="AD234" r:id="rId269"/>
+    <hyperlink ref="AD232" r:id="rId270"/>
+    <hyperlink ref="AB231" r:id="rId271"/>
+    <hyperlink ref="AH230" r:id="rId272"/>
+    <hyperlink ref="AD229" r:id="rId273"/>
+    <hyperlink ref="AD228" r:id="rId274"/>
+    <hyperlink ref="AF227" r:id="rId275"/>
+    <hyperlink ref="V226" r:id="rId276"/>
+    <hyperlink ref="V224" r:id="rId277"/>
+    <hyperlink ref="AH223" r:id="rId278"/>
+    <hyperlink ref="J287" r:id="rId279"/>
+    <hyperlink ref="J288" r:id="rId280"/>
+    <hyperlink ref="Z276" r:id="rId281"/>
+    <hyperlink ref="AB286" r:id="rId282"/>
+    <hyperlink ref="AD289" r:id="rId283"/>
+    <hyperlink ref="X279" r:id="rId284"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId285"/>
@@ -59649,46 +59675,46 @@
         <v>5026</v>
       </c>
       <c r="W236" s="14" t="s">
+        <v>5207</v>
+      </c>
+      <c r="X236" s="9" t="s">
+        <v>5220</v>
+      </c>
+      <c r="Y236" s="14" t="s">
+        <v>5208</v>
+      </c>
+      <c r="Z236" s="9" t="s">
+        <v>5219</v>
+      </c>
+      <c r="AA236" s="14" t="s">
+        <v>5209</v>
+      </c>
+      <c r="AB236" s="9" t="s">
+        <v>5218</v>
+      </c>
+      <c r="AC236" s="14" t="s">
         <v>5210</v>
       </c>
-      <c r="X236" s="9" t="s">
-        <v>5223</v>
-      </c>
-      <c r="Y236" s="14" t="s">
+      <c r="AD236" s="9" t="s">
+        <v>5217</v>
+      </c>
+      <c r="AE236" s="14" t="s">
         <v>5211</v>
       </c>
-      <c r="Z236" s="9" t="s">
-        <v>5222</v>
-      </c>
-      <c r="AA236" s="14" t="s">
+      <c r="AF236" s="9" t="s">
+        <v>5216</v>
+      </c>
+      <c r="AG236" s="14" t="s">
         <v>5212</v>
       </c>
-      <c r="AB236" s="9" t="s">
-        <v>5221</v>
-      </c>
-      <c r="AC236" s="14" t="s">
+      <c r="AH236" s="9" t="s">
+        <v>5215</v>
+      </c>
+      <c r="AI236" s="14" t="s">
         <v>5213</v>
       </c>
-      <c r="AD236" s="9" t="s">
-        <v>5220</v>
-      </c>
-      <c r="AE236" s="14" t="s">
+      <c r="AJ236" s="9" t="s">
         <v>5214</v>
-      </c>
-      <c r="AF236" s="9" t="s">
-        <v>5219</v>
-      </c>
-      <c r="AG236" s="14" t="s">
-        <v>5215</v>
-      </c>
-      <c r="AH236" s="9" t="s">
-        <v>5218</v>
-      </c>
-      <c r="AI236" s="14" t="s">
-        <v>5216</v>
-      </c>
-      <c r="AJ236" s="9" t="s">
-        <v>5217</v>
       </c>
     </row>
     <row r="237" spans="1:47" ht="22.5" customHeight="1">
@@ -61030,10 +61056,10 @@
         <v>《Awakenloop》是一款充滿賽博龐克風格的卡牌回合制手遊，玩家將身處一個由機器人與人類共存的末日世界。遊戲主打策略性卡牌戰鬥，每張卡牌都蘊含獨特技能，如何搭配與釋放將成為戰局關鍵。除了豐富的主線劇情，遊戲也提供多樣的副本挑戰與 PvP 模式，讓你與其他玩家一較高下。現在就加入《Awakenloop》，透過兌換碼與禮包碼獲得專屬獎勵，輕鬆提升戰力，也能使用代儲值服務快速安全地補充資源，在這片混沌的廢土上開創屬於你的新紀元。</v>
       </c>
       <c r="F269" s="13" t="s">
-        <v>5196</v>
+        <v>5193</v>
       </c>
       <c r="G269" s="9" t="s">
-        <v>5197</v>
+        <v>5194</v>
       </c>
       <c r="H269" s="9" t="s">
         <v>2625</v>
@@ -61042,16 +61068,16 @@
         <v>4360</v>
       </c>
       <c r="K269" s="13" t="s">
+        <v>5189</v>
+      </c>
+      <c r="L269" s="9" t="s">
         <v>5192</v>
       </c>
-      <c r="L269" s="9" t="s">
-        <v>5195</v>
-      </c>
       <c r="M269" s="14" t="s">
-        <v>5193</v>
+        <v>5190</v>
       </c>
       <c r="N269" s="9" t="s">
-        <v>5194</v>
+        <v>5191</v>
       </c>
     </row>
     <row r="270" spans="1:31">
@@ -61213,28 +61239,28 @@
         <v>5066</v>
       </c>
       <c r="W273" s="14" t="s">
+        <v>5198</v>
+      </c>
+      <c r="X273" s="9" t="s">
+        <v>5202</v>
+      </c>
+      <c r="Y273" s="14" t="s">
+        <v>5199</v>
+      </c>
+      <c r="Z273" s="9" t="s">
+        <v>5203</v>
+      </c>
+      <c r="AA273" s="14" t="s">
+        <v>5200</v>
+      </c>
+      <c r="AB273" s="9" t="s">
+        <v>5204</v>
+      </c>
+      <c r="AC273" s="14" t="s">
         <v>5201</v>
       </c>
-      <c r="X273" s="9" t="s">
+      <c r="AD273" s="9" t="s">
         <v>5205</v>
-      </c>
-      <c r="Y273" s="14" t="s">
-        <v>5202</v>
-      </c>
-      <c r="Z273" s="9" t="s">
-        <v>5206</v>
-      </c>
-      <c r="AA273" s="14" t="s">
-        <v>5203</v>
-      </c>
-      <c r="AB273" s="9" t="s">
-        <v>5207</v>
-      </c>
-      <c r="AC273" s="14" t="s">
-        <v>5204</v>
-      </c>
-      <c r="AD273" s="9" t="s">
-        <v>5208</v>
       </c>
     </row>
     <row r="274" spans="1:40">
@@ -61330,13 +61356,13 @@
         <v>5053</v>
       </c>
       <c r="O275" s="14" t="s">
-        <v>5108</v>
+        <v>5105</v>
       </c>
       <c r="Q275" s="14" t="s">
-        <v>5109</v>
+        <v>5106</v>
       </c>
       <c r="S275" s="14" t="s">
-        <v>5110</v>
+        <v>5107</v>
       </c>
       <c r="U275" s="14" t="s">
         <v>2056</v>
@@ -61345,7 +61371,7 @@
         <v>4560</v>
       </c>
       <c r="Y275" s="14" t="s">
-        <v>5111</v>
+        <v>5108</v>
       </c>
     </row>
     <row r="276" spans="1:40">
@@ -61366,28 +61392,28 @@
         <v>由艾瑞爾網路代理的銀河冒險 RPG《星塔旅人》正式登場！這趟星際之旅，你將化身為「星之活體」的持有者，與眾多獨具魅力的「旅人」相遇，共同踏上尋找銀河之心「星源晶核」的冒險。遊戲主打 Roguelike 要素與高自由度的戰鬥系統，讓每一次探索都充滿未知驚喜。為了讓各位玩家能更快養成心儀的角色，記得隨時關注官方釋出的最新兌換碼與禮包碼資訊。當然，若想在起跑點就遙遙領先，最方便的代儲值服務能提供您快速安全的課金管道，讓您的銀河霸業無後顧之憂！</v>
       </c>
       <c r="F276" s="77" t="s">
+        <v>5113</v>
+      </c>
+      <c r="G276" s="9" t="s">
+        <v>5114</v>
+      </c>
+      <c r="H276" s="9" t="s">
+        <v>5115</v>
+      </c>
+      <c r="I276" s="9" t="s">
         <v>5116</v>
       </c>
-      <c r="G276" s="9" t="s">
-        <v>5117</v>
-      </c>
-      <c r="H276" s="9" t="s">
-        <v>5118</v>
-      </c>
-      <c r="I276" s="9" t="s">
-        <v>5119</v>
-      </c>
       <c r="K276" s="13" t="s">
+        <v>5109</v>
+      </c>
+      <c r="L276" s="9" t="s">
+        <v>5111</v>
+      </c>
+      <c r="M276" s="14" t="s">
+        <v>5110</v>
+      </c>
+      <c r="N276" s="9" t="s">
         <v>5112</v>
-      </c>
-      <c r="L276" s="9" t="s">
-        <v>5114</v>
-      </c>
-      <c r="M276" s="14" t="s">
-        <v>5113</v>
-      </c>
-      <c r="N276" s="9" t="s">
-        <v>5115</v>
       </c>
     </row>
     <row r="277" spans="1:40">
@@ -61444,25 +61470,25 @@
         <v>全新星緣卡牌 RPG《星痕共鳴》，邀你一同編織命運的篇章。遊戲擁有宏大的世界觀與超過百萬字的豐富劇情，玩家將扮演「星源之主」，與眾多「星痕者」締結羈絆，共同對抗虛空的威脅。獨特的「星盤」系統與高策略性的卡牌戰鬥，讓每場對決都充滿變數。想要輕鬆推圖、快速成長？記得在各大社群與論壇尋找隱藏的兌換碼與禮包碼，領取豐厚資源。如果想快人一步，最聰明的選擇就是尋找可靠的代儲值管道，提供您快速安全的支援，讓你的冒險旅程更加順遂。</v>
       </c>
       <c r="F278" s="13" t="s">
-        <v>5250</v>
+        <v>5247</v>
       </c>
       <c r="G278" s="9" t="s">
-        <v>5251</v>
+        <v>5248</v>
       </c>
       <c r="H278" s="9" t="s">
-        <v>5252</v>
+        <v>5249</v>
       </c>
       <c r="K278" s="13" t="s">
+        <v>5243</v>
+      </c>
+      <c r="L278" s="9" t="s">
         <v>5246</v>
       </c>
-      <c r="L278" s="9" t="s">
-        <v>5249</v>
-      </c>
       <c r="M278" s="14" t="s">
-        <v>5247</v>
+        <v>5244</v>
       </c>
       <c r="N278" s="9" t="s">
-        <v>5248</v>
+        <v>5245</v>
       </c>
     </row>
     <row r="279" spans="1:40">
@@ -61483,13 +61509,13 @@
         <v>備受矚目的 3D 動作 RPG《二重螺旋》強勢來襲！本作主打高速、爽快的戰鬥體驗，玩家將在一個近未來科幻世界中，扮演擁有特殊能力的「適格者」，探索神秘的「深淵」。遊戲強調華麗的連擊與多樣化的武器系統，你可以自由切換遠近程攻擊，打出屬於自己的戰鬥風格。為了讓你的探索之路更加順利，官方會不定期發放福利兌換碼與禮包碼，千萬別錯過。當然，面對強大的敵人，尋求專業的代儲值協助，以快速安全的方式強化戰力，絕對是高效的致勝關鍵。</v>
       </c>
       <c r="F279" s="13" t="s">
-        <v>5337</v>
+        <v>5334</v>
       </c>
       <c r="G279" s="9" t="s">
-        <v>5338</v>
+        <v>5335</v>
       </c>
       <c r="H279" s="9" t="s">
-        <v>5339</v>
+        <v>5336</v>
       </c>
       <c r="I279" s="9" t="s">
         <v>2625</v>
@@ -61498,34 +61524,64 @@
         <v>4360</v>
       </c>
       <c r="K279" s="13" t="s">
+        <v>5250</v>
+      </c>
+      <c r="L279" s="9" t="s">
+        <v>5373</v>
+      </c>
+      <c r="M279" s="14" t="s">
+        <v>5251</v>
+      </c>
+      <c r="N279" s="9" t="s">
+        <v>5374</v>
+      </c>
+      <c r="O279" s="14" t="s">
+        <v>5252</v>
+      </c>
+      <c r="P279" s="9" t="s">
+        <v>5375</v>
+      </c>
+      <c r="Q279" s="14" t="s">
         <v>5253</v>
       </c>
-      <c r="M279" s="14" t="s">
-        <v>5254</v>
-      </c>
-      <c r="O279" s="14" t="s">
-        <v>5255</v>
-      </c>
-      <c r="Q279" s="14" t="s">
-        <v>5256</v>
+      <c r="R279" s="9" t="s">
+        <v>5376</v>
       </c>
       <c r="S279" s="14" t="s">
+        <v>5337</v>
+      </c>
+      <c r="T279" s="9" t="s">
+        <v>5377</v>
+      </c>
+      <c r="U279" s="14" t="s">
+        <v>5338</v>
+      </c>
+      <c r="V279" s="9" t="s">
+        <v>5378</v>
+      </c>
+      <c r="W279" s="14" t="s">
+        <v>5339</v>
+      </c>
+      <c r="X279" s="9" t="s">
+        <v>5379</v>
+      </c>
+      <c r="Y279" s="14" t="s">
         <v>5340</v>
       </c>
-      <c r="U279" s="14" t="s">
+      <c r="Z279" s="9" t="s">
+        <v>5380</v>
+      </c>
+      <c r="AA279" s="14" t="s">
+        <v>5342</v>
+      </c>
+      <c r="AB279" s="9" t="s">
+        <v>5381</v>
+      </c>
+      <c r="AC279" s="14" t="s">
         <v>5341</v>
       </c>
-      <c r="W279" s="14" t="s">
-        <v>5342</v>
-      </c>
-      <c r="Y279" s="14" t="s">
-        <v>5343</v>
-      </c>
-      <c r="AA279" s="14" t="s">
-        <v>5345</v>
-      </c>
-      <c r="AC279" s="14" t="s">
-        <v>5344</v>
+      <c r="AD279" s="9" t="s">
+        <v>5382</v>
       </c>
     </row>
     <row r="280" spans="1:40">
@@ -61636,10 +61692,10 @@
         <v>2025年最值得一玩的全新萌系塔防手遊來啦！邪惡哥布林入侵，身為國王守護者的你，必須招募英雄抵禦入侵。遊戲主打英雄2合1加上局內3重隨機玩法，每局都有上百種策略搭配，就算是休閒玩家也能3秒上手！還在網路上苦苦搜尋可用的禮包碼和兌換碼嗎？別浪費時間了！想要快速升級，享受最爽快的割草感，尋找快速安全的代儲值服務會是你最好的選擇，立即為了蔚藍星球而戰！</v>
       </c>
       <c r="F283" s="13" t="s">
-        <v>5328</v>
+        <v>5325</v>
       </c>
       <c r="G283" s="9" t="s">
-        <v>5329</v>
+        <v>5326</v>
       </c>
       <c r="H283" s="9" t="s">
         <v>2625</v>
@@ -61648,64 +61704,64 @@
         <v>4360</v>
       </c>
       <c r="K283" s="13" t="s">
-        <v>5330</v>
+        <v>5327</v>
       </c>
       <c r="L283" s="9" t="s">
-        <v>5352</v>
+        <v>5349</v>
       </c>
       <c r="M283" s="14" t="s">
         <v>4141</v>
       </c>
       <c r="N283" s="9" t="s">
-        <v>5353</v>
+        <v>5350</v>
       </c>
       <c r="O283" s="14" t="s">
         <v>4140</v>
       </c>
       <c r="P283" s="9" t="s">
+        <v>5351</v>
+      </c>
+      <c r="Q283" s="14" t="s">
+        <v>5328</v>
+      </c>
+      <c r="R283" s="9" t="s">
+        <v>5352</v>
+      </c>
+      <c r="S283" s="14" t="s">
+        <v>5329</v>
+      </c>
+      <c r="T283" s="9" t="s">
+        <v>5353</v>
+      </c>
+      <c r="U283" s="14" t="s">
+        <v>5330</v>
+      </c>
+      <c r="V283" s="9" t="s">
+        <v>5353</v>
+      </c>
+      <c r="W283" s="14" t="s">
+        <v>5331</v>
+      </c>
+      <c r="X283" s="9" t="s">
+        <v>5353</v>
+      </c>
+      <c r="Y283" s="14" t="s">
+        <v>5332</v>
+      </c>
+      <c r="Z283" s="9" t="s">
         <v>5354</v>
-      </c>
-      <c r="Q283" s="14" t="s">
-        <v>5331</v>
-      </c>
-      <c r="R283" s="9" t="s">
-        <v>5355</v>
-      </c>
-      <c r="S283" s="14" t="s">
-        <v>5332</v>
-      </c>
-      <c r="T283" s="9" t="s">
-        <v>5356</v>
-      </c>
-      <c r="U283" s="14" t="s">
-        <v>5333</v>
-      </c>
-      <c r="V283" s="9" t="s">
-        <v>5356</v>
-      </c>
-      <c r="W283" s="14" t="s">
-        <v>5334</v>
-      </c>
-      <c r="X283" s="9" t="s">
-        <v>5356</v>
-      </c>
-      <c r="Y283" s="14" t="s">
-        <v>5335</v>
-      </c>
-      <c r="Z283" s="9" t="s">
-        <v>5357</v>
       </c>
       <c r="AA283" s="14" t="s">
         <v>2056</v>
       </c>
       <c r="AB283" s="9" t="s">
-        <v>5358</v>
+        <v>5355</v>
       </c>
       <c r="AC283" s="14" t="s">
-        <v>5336</v>
+        <v>5333</v>
       </c>
       <c r="AD283" s="9" t="s">
-        <v>5359</v>
+        <v>5356</v>
       </c>
     </row>
     <row r="284" spans="1:40">
@@ -61726,103 +61782,103 @@
         <v>美少女三國RPG手遊參上！遊戲擁有眾多經典三國名將，搭配緊張刺激的養成戰鬥系統，讓玩家可以體驗高潮連擊的激爽和無限養成的快樂。獨特的武將風格立繪，在既定特色上增添更多風味，絕對是視覺饗宴。還在為了找不到最新的禮包碼而煩惱嗎？想要輕鬆養成武將，解鎖所有外觀，最聰明的方式就是尋找快速安全的代儲值管道，立即領取你的兌換碼福利，在三國世界中無往不利！</v>
       </c>
       <c r="F284" s="13" t="s">
-        <v>5198</v>
+        <v>5195</v>
       </c>
       <c r="G284" s="9" t="s">
-        <v>5199</v>
+        <v>5196</v>
       </c>
       <c r="H284" s="9" t="s">
-        <v>5200</v>
+        <v>5197</v>
       </c>
       <c r="K284" s="13" t="s">
-        <v>5263</v>
+        <v>5260</v>
       </c>
       <c r="L284" s="9" t="s">
-        <v>5327</v>
+        <v>5324</v>
       </c>
       <c r="M284" s="14" t="s">
-        <v>5264</v>
+        <v>5261</v>
       </c>
       <c r="N284" s="9" t="s">
-        <v>5326</v>
+        <v>5323</v>
       </c>
       <c r="O284" s="14" t="s">
+        <v>5300</v>
+      </c>
+      <c r="P284" s="9" t="s">
+        <v>5322</v>
+      </c>
+      <c r="Q284" s="14" t="s">
+        <v>5301</v>
+      </c>
+      <c r="R284" s="9" t="s">
+        <v>5321</v>
+      </c>
+      <c r="S284" s="14" t="s">
+        <v>5302</v>
+      </c>
+      <c r="T284" s="9" t="s">
+        <v>5320</v>
+      </c>
+      <c r="U284" s="14" t="s">
         <v>5303</v>
       </c>
-      <c r="P284" s="9" t="s">
-        <v>5325</v>
-      </c>
-      <c r="Q284" s="14" t="s">
+      <c r="V284" s="9" t="s">
+        <v>5319</v>
+      </c>
+      <c r="W284" s="14" t="s">
         <v>5304</v>
       </c>
-      <c r="R284" s="9" t="s">
-        <v>5324</v>
-      </c>
-      <c r="S284" s="14" t="s">
+      <c r="X284" s="9" t="s">
+        <v>5318</v>
+      </c>
+      <c r="Y284" s="14" t="s">
         <v>5305</v>
       </c>
-      <c r="T284" s="9" t="s">
-        <v>5323</v>
-      </c>
-      <c r="U284" s="14" t="s">
+      <c r="Z284" s="9" t="s">
+        <v>5317</v>
+      </c>
+      <c r="AA284" s="14" t="s">
         <v>5306</v>
       </c>
-      <c r="V284" s="9" t="s">
-        <v>5322</v>
-      </c>
-      <c r="W284" s="14" t="s">
-        <v>5307</v>
-      </c>
-      <c r="X284" s="9" t="s">
-        <v>5321</v>
-      </c>
-      <c r="Y284" s="14" t="s">
-        <v>5308</v>
-      </c>
-      <c r="Z284" s="9" t="s">
-        <v>5320</v>
-      </c>
-      <c r="AA284" s="14" t="s">
-        <v>5309</v>
-      </c>
       <c r="AB284" s="9" t="s">
-        <v>5319</v>
+        <v>5316</v>
       </c>
       <c r="AC284" s="14" t="s">
         <v>1932</v>
       </c>
       <c r="AD284" s="9" t="s">
-        <v>5318</v>
+        <v>5315</v>
       </c>
       <c r="AE284" s="14" t="s">
-        <v>5310</v>
+        <v>5307</v>
       </c>
       <c r="AF284" s="9" t="s">
-        <v>5317</v>
+        <v>5314</v>
       </c>
       <c r="AG284" s="14" t="s">
-        <v>5311</v>
+        <v>5308</v>
       </c>
       <c r="AH284" s="9" t="s">
-        <v>5316</v>
+        <v>5313</v>
       </c>
       <c r="AI284" s="14" t="s">
+        <v>5309</v>
+      </c>
+      <c r="AJ284" s="9" t="s">
         <v>5312</v>
-      </c>
-      <c r="AJ284" s="9" t="s">
-        <v>5315</v>
       </c>
       <c r="AK284" s="14" t="s">
         <v>2199</v>
       </c>
       <c r="AL284" s="9" t="s">
-        <v>5314</v>
+        <v>5311</v>
       </c>
       <c r="AM284" s="14" t="s">
         <v>2200</v>
       </c>
       <c r="AN284" s="9" t="s">
-        <v>5313</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="285" spans="1:40">
@@ -61843,16 +61899,16 @@
         <v>準備好你的弓箭，面對排山倒海的敵人了嗎？《弓箭英雄：塔防》是一款結合了塔防策略與Roguelite元素的超休閒遊戲。每次升級都能三選一技能，是要彈射、冰凍還是連射？選錯了可能下一秒就躺平。玩家們都在瘋狂尋找最新的兌換碼，希望能開局就拿到神裝。別忘了，強大的火力支援是守塔的關鍵，這時候就需要可靠的代儲值服務來幫你一把。想要穩穩通關，拿到稀有的禮包碼獎勵嗎？與其苦苦硬撐，不如尋求快速安全的代儲值，讓你的箭塔升到滿級，輕鬆碾壓所有來犯的敵人，成為真正的塔防大師！</v>
       </c>
       <c r="F285" s="13" t="s">
-        <v>5245</v>
+        <v>5242</v>
       </c>
       <c r="G285" s="9" t="s">
-        <v>5244</v>
+        <v>5241</v>
       </c>
       <c r="K285" s="13" t="s">
-        <v>5245</v>
+        <v>5242</v>
       </c>
       <c r="L285" s="9" t="s">
-        <v>5244</v>
+        <v>5241</v>
       </c>
     </row>
     <row r="286" spans="1:40">
@@ -61873,16 +61929,16 @@
         <v>《十二之天M Reborn》誓言找回當年的感動，讓玩家重溫三大勢力的激情對決。這款遊戲主打的就是一個原汁原味，熟悉的場景、懷舊的BGM，以及那令人又愛又恨的勢力戰。準備好再次投身這場無盡的江湖恩怨了嗎？大家都在蹲點最新的禮包碼，希望能搶先一步強化裝備。官方發放的兌換碼雖然不無小補，但真正的強者懂得利用資源。想要快速提升戰力，不妨考慮專業的代儲值服務。與其在戰場上被當小兵清掉，不如透過快速安全的管道補足元寶，讓你的角色戰力飆升，在龍瀑鎮插旗，重現當年的榮光！</v>
       </c>
       <c r="F286" s="13" t="s">
-        <v>5245</v>
+        <v>5242</v>
       </c>
       <c r="G286" s="9" t="s">
-        <v>5244</v>
+        <v>5241</v>
       </c>
       <c r="K286" s="13" t="s">
-        <v>5245</v>
+        <v>5242</v>
       </c>
       <c r="L286" s="9" t="s">
-        <v>5244</v>
+        <v>5241</v>
       </c>
     </row>
     <row r="287" spans="1:40">
@@ -61903,10 +61959,10 @@
         <v>正版授權的《NBA巔峰對決》終於來了。這款主打真人PVP的籃球手遊，讓你能操控喜愛的NBA球星。遊戲強調操作手感與球星的專屬技能，想秀一波高難度灌籃或致命三分球？全看你的技術。但說真的，想在天梯上爬分，球員的養成才是關鍵。新手們別再傻傻地問兌換碼在哪了，那點資源根本不夠看。想要打造你的夢幻陣容，把傳奇球星都納入麾下，可靠的代儲值才是捷徑。別家還在慢慢存資源，你已經透過快速安全的儲值拿到關鍵禮包碼，直接抽爆卡池，讓你的隊伍戰力登頂，在球場上制霸全場！</v>
       </c>
       <c r="F287" s="13" t="s">
-        <v>5301</v>
+        <v>5298</v>
       </c>
       <c r="G287" s="9" t="s">
-        <v>5302</v>
+        <v>5299</v>
       </c>
       <c r="H287" s="9" t="s">
         <v>2625</v>
@@ -61915,34 +61971,34 @@
         <v>4360</v>
       </c>
       <c r="K287" s="13" t="s">
+        <v>5288</v>
+      </c>
+      <c r="L287" s="9" t="s">
+        <v>5293</v>
+      </c>
+      <c r="M287" s="14" t="s">
+        <v>5289</v>
+      </c>
+      <c r="N287" s="9" t="s">
+        <v>5294</v>
+      </c>
+      <c r="O287" s="14" t="s">
+        <v>5290</v>
+      </c>
+      <c r="P287" s="9" t="s">
+        <v>5295</v>
+      </c>
+      <c r="Q287" s="14" t="s">
         <v>5291</v>
       </c>
-      <c r="L287" s="9" t="s">
+      <c r="R287" s="9" t="s">
         <v>5296</v>
       </c>
-      <c r="M287" s="14" t="s">
+      <c r="S287" s="14" t="s">
         <v>5292</v>
       </c>
-      <c r="N287" s="9" t="s">
+      <c r="T287" s="9" t="s">
         <v>5297</v>
-      </c>
-      <c r="O287" s="14" t="s">
-        <v>5293</v>
-      </c>
-      <c r="P287" s="9" t="s">
-        <v>5298</v>
-      </c>
-      <c r="Q287" s="14" t="s">
-        <v>5294</v>
-      </c>
-      <c r="R287" s="9" t="s">
-        <v>5299</v>
-      </c>
-      <c r="S287" s="14" t="s">
-        <v>5295</v>
-      </c>
-      <c r="T287" s="9" t="s">
-        <v>5300</v>
       </c>
     </row>
     <row r="288" spans="1:40">
@@ -61963,19 +62019,19 @@
         <v>又一款三國策略遊戲？先別急著滑掉！《三國志：王戰》是一款主打快節奏的SLG手遊，標榜著15天一賽季的急速征戰。在這裡，你不用再苦苦熬夜農地、屯兵，而是要把握黃金時間，快速發展內政、招募名將，與盟友一同攻城掠地。當然，想在短短15天內統一天下，光靠策略可不夠。新手們拚命搜尋的兌換碼，拿到的資源可能還不夠升一座主城。真正的王者都懂得運用代儲值服務，在開局就快人一步。別再猶豫了，利用快速安全的管道取得珍稀禮包碼與資源，迅速拉高戰力，在賽季結束前稱霸全服！</v>
       </c>
       <c r="F288" s="13" t="s">
-        <v>5245</v>
+        <v>5242</v>
       </c>
       <c r="G288" s="9" t="s">
-        <v>5244</v>
+        <v>5241</v>
       </c>
       <c r="K288" s="13" t="s">
-        <v>5245</v>
+        <v>5242</v>
       </c>
       <c r="L288" s="9" t="s">
-        <v>5244</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5">
+        <v>5241</v>
+      </c>
+    </row>
+    <row r="289" spans="1:12">
       <c r="A289" s="9" t="str">
         <f>IF(games!A289="", "", games!A289)</f>
         <v>信長 霸道</v>
@@ -61992,8 +62048,20 @@
         <f>IF(games!I289&lt;&gt;"", games!I289, "")</f>
         <v>光榮特庫摩出品，正統信長之野望系列最新力作《信長之野望 霸道》終於登場！這次玩家將化身侍奉各地大名的領主，在MMO化的戰國世界中，與同勢力的盟友們一同奮戰，體驗四季變化的精美3D地圖與緊張刺激的攻城戰。想在亂世中快人一步？別忘了到處尋找隱藏的兌換碼與禮包碼，領取初期資源。當然，若想讓統一天下的霸業之路更加順遂，尋找快速安全的代儲值服務也是各位城主大人們的必修課，畢竟在戰場上，兵貴神速啊！立即投身亂世，與盟友們共創霸業！</v>
       </c>
-    </row>
-    <row r="290" spans="1:5">
+      <c r="F289" s="13" t="s">
+        <v>5242</v>
+      </c>
+      <c r="G289" s="9" t="s">
+        <v>5241</v>
+      </c>
+      <c r="K289" s="13" t="s">
+        <v>5242</v>
+      </c>
+      <c r="L289" s="9" t="s">
+        <v>5241</v>
+      </c>
+    </row>
+    <row r="290" spans="1:12">
       <c r="A290" s="9" t="str">
         <f>IF(games!A290="", "", games!A290)</f>
         <v/>
@@ -62011,7 +62079,7 @@
         <v/>
       </c>
     </row>
-    <row r="291" spans="1:5">
+    <row r="291" spans="1:12">
       <c r="A291" s="9" t="str">
         <f>IF(games!A291="", "", games!A291)</f>
         <v/>
@@ -62029,7 +62097,7 @@
         <v/>
       </c>
     </row>
-    <row r="292" spans="1:5">
+    <row r="292" spans="1:12">
       <c r="A292" s="9" t="str">
         <f>IF(games!A292="", "", games!A292)</f>
         <v/>
@@ -62047,7 +62115,7 @@
         <v/>
       </c>
     </row>
-    <row r="293" spans="1:5">
+    <row r="293" spans="1:12">
       <c r="A293" s="9" t="str">
         <f>IF(games!A293="", "", games!A293)</f>
         <v/>
@@ -62065,7 +62133,7 @@
         <v/>
       </c>
     </row>
-    <row r="294" spans="1:5">
+    <row r="294" spans="1:12">
       <c r="A294" s="9" t="str">
         <f>IF(games!A294="", "", games!A294)</f>
         <v/>
@@ -62083,7 +62151,7 @@
         <v/>
       </c>
     </row>
-    <row r="295" spans="1:5">
+    <row r="295" spans="1:12">
       <c r="A295" s="9" t="str">
         <f>IF(games!A295="", "", games!A295)</f>
         <v/>
@@ -62101,7 +62169,7 @@
         <v/>
       </c>
     </row>
-    <row r="296" spans="1:5">
+    <row r="296" spans="1:12">
       <c r="A296" s="9" t="str">
         <f>IF(games!A296="", "", games!A296)</f>
         <v/>
@@ -62119,7 +62187,7 @@
         <v/>
       </c>
     </row>
-    <row r="297" spans="1:5">
+    <row r="297" spans="1:12">
       <c r="A297" s="9" t="str">
         <f>IF(games!A297="", "", games!A297)</f>
         <v/>
@@ -62137,7 +62205,7 @@
         <v/>
       </c>
     </row>
-    <row r="298" spans="1:5">
+    <row r="298" spans="1:12">
       <c r="A298" s="9" t="str">
         <f>IF(games!A298="", "", games!A298)</f>
         <v/>
@@ -62155,7 +62223,7 @@
         <v/>
       </c>
     </row>
-    <row r="299" spans="1:5">
+    <row r="299" spans="1:12">
       <c r="A299" s="9" t="str">
         <f>IF(games!A299="", "", games!A299)</f>
         <v/>
@@ -62173,7 +62241,7 @@
         <v/>
       </c>
     </row>
-    <row r="300" spans="1:5">
+    <row r="300" spans="1:12">
       <c r="A300" s="9" t="str">
         <f>IF(games!A300="", "", games!A300)</f>
         <v/>
@@ -62191,7 +62259,7 @@
         <v/>
       </c>
     </row>
-    <row r="301" spans="1:5">
+    <row r="301" spans="1:12">
       <c r="A301" s="9" t="str">
         <f>IF(games!A301="", "", games!A301)</f>
         <v/>
@@ -62209,7 +62277,7 @@
         <v/>
       </c>
     </row>
-    <row r="302" spans="1:5">
+    <row r="302" spans="1:12">
       <c r="A302" s="9" t="str">
         <f>IF(games!A302="", "", games!A302)</f>
         <v/>
@@ -62227,7 +62295,7 @@
         <v/>
       </c>
     </row>
-    <row r="303" spans="1:5">
+    <row r="303" spans="1:12">
       <c r="A303" s="9" t="str">
         <f>IF(games!A303="", "", games!A303)</f>
         <v/>
@@ -62245,7 +62313,7 @@
         <v/>
       </c>
     </row>
-    <row r="304" spans="1:5">
+    <row r="304" spans="1:12">
       <c r="C304" s="9" t="str">
         <f t="shared" si="12"/>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -40571,7 +40571,7 @@
         <v>5008</v>
       </c>
       <c r="K277" s="85">
-        <v>2655</v>
+        <v>2230</v>
       </c>
       <c r="L277" s="84" t="s">
         <v>5009</v>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7910" uniqueCount="5384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7908" uniqueCount="5382">
   <si>
     <t>Facebook</t>
   </si>
@@ -20154,54 +20154,6 @@
     <t>自選SP+神兵</t>
   </si>
   <si>
-    <t xml:space="preserve">COACH2025 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PLAYERXP5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TEAMFUND3K</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NBA2025LEGEND</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>VIPGIFT2025</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>教練經驗*1000</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>球員經驗*5000</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>球隊資金*3000</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>隨機金卡*1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>特訓材料*100</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>遊戲內點設定</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>進到兌換碼畫面</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>BOSS666</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -20514,6 +20466,46 @@
   </si>
   <si>
     <t>月度訂單</t>
+  </si>
+  <si>
+    <t>榜一全服同慶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>緯緯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>瑋瑋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>現役球員包*1+經驗金卡*3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>林書緯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高錦瑋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲內右上方點齒輪「設定」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>左邊書籤滑到底找到「禮包碼」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>開服首日限定資源禮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>現役球員包*1+資金*100萬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -40776,7 +40768,7 @@
         <v>30</v>
       </c>
       <c r="V279" s="1" t="s">
-        <v>5383</v>
+        <v>5371</v>
       </c>
       <c r="W279" s="58">
         <v>151</v>
@@ -41078,25 +41070,25 @@
         <v>5187</v>
       </c>
       <c r="J283" s="1" t="s">
-        <v>5343</v>
+        <v>5331</v>
       </c>
       <c r="K283" s="58">
         <v>2717</v>
       </c>
       <c r="L283" s="1" t="s">
-        <v>5344</v>
+        <v>5332</v>
       </c>
       <c r="M283" s="58">
         <v>1422</v>
       </c>
       <c r="N283" s="1" t="s">
-        <v>5345</v>
+        <v>5333</v>
       </c>
       <c r="O283" s="58">
         <v>586</v>
       </c>
       <c r="P283" s="1" t="s">
-        <v>5346</v>
+        <v>5334</v>
       </c>
       <c r="Q283" s="58">
         <v>416</v>
@@ -41114,13 +41106,13 @@
         <v>30</v>
       </c>
       <c r="V283" s="1" t="s">
-        <v>5347</v>
+        <v>5335</v>
       </c>
       <c r="W283" s="58">
         <v>151</v>
       </c>
       <c r="X283" s="1" t="s">
-        <v>5348</v>
+        <v>5336</v>
       </c>
       <c r="Y283" s="58">
         <v>89</v>
@@ -41454,87 +41446,87 @@
     </row>
     <row r="289" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A289" s="82" t="s">
-        <v>5357</v>
+        <v>5345</v>
       </c>
       <c r="C289" s="36" t="s">
-        <v>5361</v>
+        <v>5349</v>
       </c>
       <c r="D289" s="37" t="s">
-        <v>5358</v>
+        <v>5346</v>
       </c>
       <c r="E289" s="37" t="s">
-        <v>5360</v>
+        <v>5348</v>
       </c>
       <c r="F289" s="36" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=信長 霸道</v>
       </c>
       <c r="G289" s="37" t="s">
-        <v>5359</v>
+        <v>5347</v>
       </c>
       <c r="H289" s="37" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=信長 霸道</v>
       </c>
       <c r="I289" s="38" t="s">
-        <v>5372</v>
+        <v>5360</v>
       </c>
       <c r="J289" s="1" t="s">
-        <v>5362</v>
+        <v>5350</v>
       </c>
       <c r="K289" s="58">
         <v>2086</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>5363</v>
+        <v>5351</v>
       </c>
       <c r="M289" s="58">
         <v>1051</v>
       </c>
       <c r="N289" s="1" t="s">
-        <v>5364</v>
+        <v>5352</v>
       </c>
       <c r="O289" s="58">
         <v>531</v>
       </c>
       <c r="P289" s="1" t="s">
-        <v>5365</v>
+        <v>5353</v>
       </c>
       <c r="Q289" s="58">
         <v>357</v>
       </c>
       <c r="R289" s="1" t="s">
-        <v>5366</v>
+        <v>5354</v>
       </c>
       <c r="S289" s="58">
         <v>149</v>
       </c>
       <c r="T289" s="1" t="s">
-        <v>5367</v>
+        <v>5355</v>
       </c>
       <c r="U289" s="58">
         <v>32</v>
       </c>
       <c r="V289" s="1" t="s">
-        <v>5368</v>
+        <v>5356</v>
       </c>
       <c r="W289" s="58">
         <v>1051</v>
       </c>
       <c r="X289" s="1" t="s">
-        <v>5369</v>
+        <v>5357</v>
       </c>
       <c r="Y289" s="58">
         <v>531</v>
       </c>
       <c r="Z289" s="1" t="s">
-        <v>5370</v>
+        <v>5358</v>
       </c>
       <c r="AA289" s="58">
         <v>186</v>
       </c>
       <c r="AB289" s="1" t="s">
-        <v>5371</v>
+        <v>5359</v>
       </c>
       <c r="AC289" s="58">
         <v>357</v>
@@ -61509,13 +61501,13 @@
         <v>備受矚目的 3D 動作 RPG《二重螺旋》強勢來襲！本作主打高速、爽快的戰鬥體驗，玩家將在一個近未來科幻世界中，扮演擁有特殊能力的「適格者」，探索神秘的「深淵」。遊戲強調華麗的連擊與多樣化的武器系統，你可以自由切換遠近程攻擊，打出屬於自己的戰鬥風格。為了讓你的探索之路更加順利，官方會不定期發放福利兌換碼與禮包碼，千萬別錯過。當然，面對強大的敵人，尋求專業的代儲值協助，以快速安全的方式強化戰力，絕對是高效的致勝關鍵。</v>
       </c>
       <c r="F279" s="13" t="s">
-        <v>5334</v>
+        <v>5322</v>
       </c>
       <c r="G279" s="9" t="s">
-        <v>5335</v>
+        <v>5323</v>
       </c>
       <c r="H279" s="9" t="s">
-        <v>5336</v>
+        <v>5324</v>
       </c>
       <c r="I279" s="9" t="s">
         <v>2625</v>
@@ -61527,61 +61519,61 @@
         <v>5250</v>
       </c>
       <c r="L279" s="9" t="s">
-        <v>5373</v>
+        <v>5361</v>
       </c>
       <c r="M279" s="14" t="s">
         <v>5251</v>
       </c>
       <c r="N279" s="9" t="s">
-        <v>5374</v>
+        <v>5362</v>
       </c>
       <c r="O279" s="14" t="s">
         <v>5252</v>
       </c>
       <c r="P279" s="9" t="s">
-        <v>5375</v>
+        <v>5363</v>
       </c>
       <c r="Q279" s="14" t="s">
         <v>5253</v>
       </c>
       <c r="R279" s="9" t="s">
-        <v>5376</v>
+        <v>5364</v>
       </c>
       <c r="S279" s="14" t="s">
-        <v>5337</v>
+        <v>5325</v>
       </c>
       <c r="T279" s="9" t="s">
-        <v>5377</v>
+        <v>5365</v>
       </c>
       <c r="U279" s="14" t="s">
-        <v>5338</v>
+        <v>5326</v>
       </c>
       <c r="V279" s="9" t="s">
-        <v>5378</v>
+        <v>5366</v>
       </c>
       <c r="W279" s="14" t="s">
-        <v>5339</v>
+        <v>5327</v>
       </c>
       <c r="X279" s="9" t="s">
-        <v>5379</v>
+        <v>5367</v>
       </c>
       <c r="Y279" s="14" t="s">
-        <v>5340</v>
+        <v>5328</v>
       </c>
       <c r="Z279" s="9" t="s">
-        <v>5380</v>
+        <v>5368</v>
       </c>
       <c r="AA279" s="14" t="s">
-        <v>5342</v>
+        <v>5330</v>
       </c>
       <c r="AB279" s="9" t="s">
-        <v>5381</v>
+        <v>5369</v>
       </c>
       <c r="AC279" s="14" t="s">
-        <v>5341</v>
+        <v>5329</v>
       </c>
       <c r="AD279" s="9" t="s">
-        <v>5382</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="280" spans="1:40">
@@ -61692,10 +61684,10 @@
         <v>2025年最值得一玩的全新萌系塔防手遊來啦！邪惡哥布林入侵，身為國王守護者的你，必須招募英雄抵禦入侵。遊戲主打英雄2合1加上局內3重隨機玩法，每局都有上百種策略搭配，就算是休閒玩家也能3秒上手！還在網路上苦苦搜尋可用的禮包碼和兌換碼嗎？別浪費時間了！想要快速升級，享受最爽快的割草感，尋找快速安全的代儲值服務會是你最好的選擇，立即為了蔚藍星球而戰！</v>
       </c>
       <c r="F283" s="13" t="s">
-        <v>5325</v>
+        <v>5313</v>
       </c>
       <c r="G283" s="9" t="s">
-        <v>5326</v>
+        <v>5314</v>
       </c>
       <c r="H283" s="9" t="s">
         <v>2625</v>
@@ -61704,64 +61696,64 @@
         <v>4360</v>
       </c>
       <c r="K283" s="13" t="s">
-        <v>5327</v>
+        <v>5315</v>
       </c>
       <c r="L283" s="9" t="s">
-        <v>5349</v>
+        <v>5337</v>
       </c>
       <c r="M283" s="14" t="s">
         <v>4141</v>
       </c>
       <c r="N283" s="9" t="s">
-        <v>5350</v>
+        <v>5338</v>
       </c>
       <c r="O283" s="14" t="s">
         <v>4140</v>
       </c>
       <c r="P283" s="9" t="s">
-        <v>5351</v>
+        <v>5339</v>
       </c>
       <c r="Q283" s="14" t="s">
-        <v>5328</v>
+        <v>5316</v>
       </c>
       <c r="R283" s="9" t="s">
-        <v>5352</v>
+        <v>5340</v>
       </c>
       <c r="S283" s="14" t="s">
-        <v>5329</v>
+        <v>5317</v>
       </c>
       <c r="T283" s="9" t="s">
-        <v>5353</v>
+        <v>5341</v>
       </c>
       <c r="U283" s="14" t="s">
-        <v>5330</v>
+        <v>5318</v>
       </c>
       <c r="V283" s="9" t="s">
-        <v>5353</v>
+        <v>5341</v>
       </c>
       <c r="W283" s="14" t="s">
-        <v>5331</v>
+        <v>5319</v>
       </c>
       <c r="X283" s="9" t="s">
-        <v>5353</v>
+        <v>5341</v>
       </c>
       <c r="Y283" s="14" t="s">
-        <v>5332</v>
+        <v>5320</v>
       </c>
       <c r="Z283" s="9" t="s">
-        <v>5354</v>
+        <v>5342</v>
       </c>
       <c r="AA283" s="14" t="s">
         <v>2056</v>
       </c>
       <c r="AB283" s="9" t="s">
-        <v>5355</v>
+        <v>5343</v>
       </c>
       <c r="AC283" s="14" t="s">
-        <v>5333</v>
+        <v>5321</v>
       </c>
       <c r="AD283" s="9" t="s">
-        <v>5356</v>
+        <v>5344</v>
       </c>
     </row>
     <row r="284" spans="1:40">
@@ -61794,91 +61786,91 @@
         <v>5260</v>
       </c>
       <c r="L284" s="9" t="s">
-        <v>5324</v>
+        <v>5312</v>
       </c>
       <c r="M284" s="14" t="s">
         <v>5261</v>
       </c>
       <c r="N284" s="9" t="s">
-        <v>5323</v>
+        <v>5311</v>
       </c>
       <c r="O284" s="14" t="s">
-        <v>5300</v>
+        <v>5288</v>
       </c>
       <c r="P284" s="9" t="s">
-        <v>5322</v>
+        <v>5310</v>
       </c>
       <c r="Q284" s="14" t="s">
-        <v>5301</v>
+        <v>5289</v>
       </c>
       <c r="R284" s="9" t="s">
-        <v>5321</v>
+        <v>5309</v>
       </c>
       <c r="S284" s="14" t="s">
-        <v>5302</v>
+        <v>5290</v>
       </c>
       <c r="T284" s="9" t="s">
-        <v>5320</v>
+        <v>5308</v>
       </c>
       <c r="U284" s="14" t="s">
-        <v>5303</v>
+        <v>5291</v>
       </c>
       <c r="V284" s="9" t="s">
-        <v>5319</v>
+        <v>5307</v>
       </c>
       <c r="W284" s="14" t="s">
+        <v>5292</v>
+      </c>
+      <c r="X284" s="9" t="s">
+        <v>5306</v>
+      </c>
+      <c r="Y284" s="14" t="s">
+        <v>5293</v>
+      </c>
+      <c r="Z284" s="9" t="s">
+        <v>5305</v>
+      </c>
+      <c r="AA284" s="14" t="s">
+        <v>5294</v>
+      </c>
+      <c r="AB284" s="9" t="s">
         <v>5304</v>
-      </c>
-      <c r="X284" s="9" t="s">
-        <v>5318</v>
-      </c>
-      <c r="Y284" s="14" t="s">
-        <v>5305</v>
-      </c>
-      <c r="Z284" s="9" t="s">
-        <v>5317</v>
-      </c>
-      <c r="AA284" s="14" t="s">
-        <v>5306</v>
-      </c>
-      <c r="AB284" s="9" t="s">
-        <v>5316</v>
       </c>
       <c r="AC284" s="14" t="s">
         <v>1932</v>
       </c>
       <c r="AD284" s="9" t="s">
-        <v>5315</v>
+        <v>5303</v>
       </c>
       <c r="AE284" s="14" t="s">
-        <v>5307</v>
+        <v>5295</v>
       </c>
       <c r="AF284" s="9" t="s">
-        <v>5314</v>
+        <v>5302</v>
       </c>
       <c r="AG284" s="14" t="s">
-        <v>5308</v>
+        <v>5296</v>
       </c>
       <c r="AH284" s="9" t="s">
-        <v>5313</v>
+        <v>5301</v>
       </c>
       <c r="AI284" s="14" t="s">
-        <v>5309</v>
+        <v>5297</v>
       </c>
       <c r="AJ284" s="9" t="s">
-        <v>5312</v>
+        <v>5300</v>
       </c>
       <c r="AK284" s="14" t="s">
         <v>2199</v>
       </c>
       <c r="AL284" s="9" t="s">
-        <v>5311</v>
+        <v>5299</v>
       </c>
       <c r="AM284" s="14" t="s">
         <v>2200</v>
       </c>
       <c r="AN284" s="9" t="s">
-        <v>5310</v>
+        <v>5298</v>
       </c>
     </row>
     <row r="285" spans="1:40">
@@ -61959,10 +61951,10 @@
         <v>正版授權的《NBA巔峰對決》終於來了。這款主打真人PVP的籃球手遊，讓你能操控喜愛的NBA球星。遊戲強調操作手感與球星的專屬技能，想秀一波高難度灌籃或致命三分球？全看你的技術。但說真的，想在天梯上爬分，球員的養成才是關鍵。新手們別再傻傻地問兌換碼在哪了，那點資源根本不夠看。想要打造你的夢幻陣容，把傳奇球星都納入麾下，可靠的代儲值才是捷徑。別家還在慢慢存資源，你已經透過快速安全的儲值拿到關鍵禮包碼，直接抽爆卡池，讓你的隊伍戰力登頂，在球場上制霸全場！</v>
       </c>
       <c r="F287" s="13" t="s">
-        <v>5298</v>
+        <v>5378</v>
       </c>
       <c r="G287" s="9" t="s">
-        <v>5299</v>
+        <v>5379</v>
       </c>
       <c r="H287" s="9" t="s">
         <v>2625</v>
@@ -61970,35 +61962,29 @@
       <c r="I287" s="9" t="s">
         <v>4360</v>
       </c>
-      <c r="K287" s="13" t="s">
-        <v>5288</v>
+      <c r="K287" s="14" t="s">
+        <v>5372</v>
       </c>
       <c r="L287" s="9" t="s">
-        <v>5293</v>
+        <v>5375</v>
       </c>
       <c r="M287" s="14" t="s">
-        <v>5289</v>
+        <v>5373</v>
       </c>
       <c r="N287" s="9" t="s">
-        <v>5294</v>
+        <v>5376</v>
       </c>
       <c r="O287" s="14" t="s">
-        <v>5290</v>
+        <v>5374</v>
       </c>
       <c r="P287" s="9" t="s">
-        <v>5295</v>
+        <v>5377</v>
       </c>
       <c r="Q287" s="14" t="s">
-        <v>5291</v>
+        <v>5380</v>
       </c>
       <c r="R287" s="9" t="s">
-        <v>5296</v>
-      </c>
-      <c r="S287" s="14" t="s">
-        <v>5292</v>
-      </c>
-      <c r="T287" s="9" t="s">
-        <v>5297</v>
+        <v>5381</v>
       </c>
     </row>
     <row r="288" spans="1:40">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7908" uniqueCount="5382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7917" uniqueCount="5390">
   <si>
     <t>Facebook</t>
   </si>
@@ -20506,6 +20506,30 @@
   <si>
     <t>現役球員包*1+資金*100萬</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6480G幣</t>
+  </si>
+  <si>
+    <t>3280G幣</t>
+  </si>
+  <si>
+    <t>1980G幣</t>
+  </si>
+  <si>
+    <t>1280G幣</t>
+  </si>
+  <si>
+    <t>680G幣</t>
+  </si>
+  <si>
+    <t>300G幣</t>
+  </si>
+  <si>
+    <t>60G幣</t>
+  </si>
+  <si>
+    <t>10G幣</t>
   </si>
 </sst>
 </file>
@@ -41403,10 +41427,64 @@
       <c r="I287" s="38" t="s">
         <v>5255</v>
       </c>
-      <c r="J287" s="83" t="s">
+      <c r="J287" s="1" t="s">
+        <v>5382</v>
+      </c>
+      <c r="K287" s="58">
+        <v>2717</v>
+      </c>
+      <c r="L287" s="1" t="s">
+        <v>5383</v>
+      </c>
+      <c r="M287" s="58">
+        <v>1422</v>
+      </c>
+      <c r="N287" s="1" t="s">
+        <v>5384</v>
+      </c>
+      <c r="O287" s="58">
+        <v>840</v>
+      </c>
+      <c r="P287" s="1" t="s">
+        <v>5385</v>
+      </c>
+      <c r="Q287" s="58">
+        <v>586</v>
+      </c>
+      <c r="R287" s="1" t="s">
+        <v>5386</v>
+      </c>
+      <c r="S287" s="58">
+        <v>297</v>
+      </c>
+      <c r="T287" s="1" t="s">
+        <v>5387</v>
+      </c>
+      <c r="U287" s="58">
+        <v>146</v>
+      </c>
+      <c r="V287" s="1" t="s">
+        <v>5388</v>
+      </c>
+      <c r="W287" s="58">
+        <v>30</v>
+      </c>
+      <c r="X287" s="1" t="s">
+        <v>5389</v>
+      </c>
+      <c r="Y287" s="58">
+        <v>9</v>
+      </c>
+      <c r="Z287" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AA287" s="58">
+        <v>146</v>
+      </c>
+      <c r="AB287" s="83" t="s">
         <v>5161</v>
       </c>
-      <c r="K287" s="86" t="s">
+      <c r="AC287" s="86" t="s">
         <v>5259</v>
       </c>
     </row>
@@ -44978,12 +45056,12 @@
     <hyperlink ref="V226" r:id="rId276"/>
     <hyperlink ref="V224" r:id="rId277"/>
     <hyperlink ref="AH223" r:id="rId278"/>
-    <hyperlink ref="J287" r:id="rId279"/>
-    <hyperlink ref="J288" r:id="rId280"/>
-    <hyperlink ref="Z276" r:id="rId281"/>
-    <hyperlink ref="AB286" r:id="rId282"/>
-    <hyperlink ref="AD289" r:id="rId283"/>
-    <hyperlink ref="X279" r:id="rId284"/>
+    <hyperlink ref="J288" r:id="rId279"/>
+    <hyperlink ref="Z276" r:id="rId280"/>
+    <hyperlink ref="AB286" r:id="rId281"/>
+    <hyperlink ref="AD289" r:id="rId282"/>
+    <hyperlink ref="X279" r:id="rId283"/>
+    <hyperlink ref="AB287" r:id="rId284"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId285"/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8019" uniqueCount="5461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8036" uniqueCount="5481">
   <si>
     <t>Facebook</t>
   </si>
@@ -20800,12 +20800,91 @@
     <t>ID：@ssbuy</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>https://www.runewaker.com/promocode/ark-phantasia</t>
+  </si>
+  <si>
+    <t>到下方官網輸入PID跟禮包碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PID 可在遊戲主畫面左上角頭像右側找到，點擊即可複製。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最新優惠馬上問問Line@客服</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPEN666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>召喚水晶*3+一小時經驗藥水箱*5+一小時金幣箱*5+能量寶箱*5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKY666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKY888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKY999</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVIP888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMO666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMO888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMO999</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲內點齒輪「設定」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>進到禮包碼/兌換碼畫面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NIU666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MIBIN666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VINSON666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TUTU666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -20922,6 +21001,12 @@
       <family val="1"/>
       <charset val="136"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFF3F5F7"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -21168,7 +21253,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -21386,6 +21471,8 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -62712,14 +62799,14 @@
       <c r="F288" s="14" t="s">
         <v>5241</v>
       </c>
-      <c r="K288" s="78" t="s">
-        <v>5459</v>
+      <c r="K288" s="89" t="s">
+        <v>5464</v>
       </c>
       <c r="L288" s="10" t="s">
-        <v>5460</v>
-      </c>
-    </row>
-    <row r="289" spans="1:12">
+        <v>5458</v>
+      </c>
+    </row>
+    <row r="289" spans="1:27">
       <c r="A289" s="10" t="str">
         <f>IF(games!A289="", "", games!A289)</f>
         <v>信長 霸道</v>
@@ -62739,14 +62826,14 @@
       <c r="F289" s="14" t="s">
         <v>5241</v>
       </c>
-      <c r="K289" s="78" t="s">
-        <v>5459</v>
+      <c r="K289" s="89" t="s">
+        <v>5464</v>
       </c>
       <c r="L289" s="10" t="s">
         <v>5458</v>
       </c>
     </row>
-    <row r="290" spans="1:12">
+    <row r="290" spans="1:27">
       <c r="A290" s="10" t="str">
         <f>IF(games!A290="", "", games!A290)</f>
         <v>勇者前線Versus</v>
@@ -62766,14 +62853,14 @@
       <c r="F290" s="14" t="s">
         <v>5241</v>
       </c>
-      <c r="K290" s="78" t="s">
-        <v>5459</v>
+      <c r="K290" s="89" t="s">
+        <v>5464</v>
       </c>
       <c r="L290" s="10" t="s">
         <v>5458</v>
       </c>
     </row>
-    <row r="291" spans="1:12">
+    <row r="291" spans="1:27">
       <c r="A291" s="10" t="str">
         <f>IF(games!A291="", "", games!A291)</f>
         <v>幻域方舟</v>
@@ -62791,16 +62878,28 @@
         <v xml:space="preserve">台廠自製的ARPG《幻域方舟》終於上線了，號稱高自由度打擊感，但我們都知道，重點還是刷刷刷。與其花時間農素材，不如先上網搜刮最新的兌換碼和禮包碼。遊戲裡的禮包是不是又貴又坑？別擔心，聰明的玩家都懂用代儲值，享受快速安全的服務，用最少的錢拿到最多資源，這才是高人一等的玩法。 </v>
       </c>
       <c r="F291" s="14" t="s">
-        <v>5241</v>
+        <v>5462</v>
+      </c>
+      <c r="G291" s="10" t="s">
+        <v>5461</v>
+      </c>
+      <c r="H291" s="10" t="s">
+        <v>5463</v>
       </c>
       <c r="K291" s="78" t="s">
-        <v>5459</v>
+        <v>5465</v>
       </c>
       <c r="L291" s="10" t="s">
+        <v>5466</v>
+      </c>
+      <c r="M291" s="89" t="s">
+        <v>5464</v>
+      </c>
+      <c r="N291" s="10" t="s">
         <v>5458</v>
       </c>
     </row>
-    <row r="292" spans="1:12">
+    <row r="292" spans="1:27">
       <c r="A292" s="10" t="str">
         <f>IF(games!A292="", "", games!A292)</f>
         <v>開天</v>
@@ -62818,16 +62917,44 @@
         <v>又一款免洗武俠《開天》來了，看這名字就知道又是那套開局送VIP，戰力膨脹的套路。反正大家都是進來割草的，誰還在乎劇情？重點是福利！別忘了每天蹲點找兌換碼和禮包碼，能拿多少是多少。如果想當服霸，靠遊戲裡送的根本不夠，直接找代儲值才是捷徑，保證快速安全，讓你戰力飆升，霸服就是這麼簡單。</v>
       </c>
       <c r="F292" s="14" t="s">
-        <v>5241</v>
-      </c>
-      <c r="K292" s="78" t="s">
-        <v>5459</v>
-      </c>
-      <c r="L292" s="10" t="s">
-        <v>5458</v>
-      </c>
-    </row>
-    <row r="293" spans="1:12">
+        <v>5475</v>
+      </c>
+      <c r="G292" s="10" t="s">
+        <v>5476</v>
+      </c>
+      <c r="H292" s="10" t="s">
+        <v>2625</v>
+      </c>
+      <c r="K292" s="89" t="s">
+        <v>5467</v>
+      </c>
+      <c r="M292" s="15" t="s">
+        <v>5468</v>
+      </c>
+      <c r="N292" s="90"/>
+      <c r="O292" s="15" t="s">
+        <v>5469</v>
+      </c>
+      <c r="Q292" s="15" t="s">
+        <v>5470</v>
+      </c>
+      <c r="S292" s="15" t="s">
+        <v>5471</v>
+      </c>
+      <c r="U292" s="15" t="s">
+        <v>1933</v>
+      </c>
+      <c r="W292" s="15" t="s">
+        <v>5472</v>
+      </c>
+      <c r="Y292" s="15" t="s">
+        <v>5473</v>
+      </c>
+      <c r="AA292" s="15" t="s">
+        <v>5474</v>
+      </c>
+    </row>
+    <row r="293" spans="1:27">
       <c r="A293" s="10" t="str">
         <f>IF(games!A293="", "", games!A293)</f>
         <v>人人有功練：腸仔江湖見</v>
@@ -62845,16 +62972,28 @@
         <v>《人人有功練：腸仔江湖見》這名字真是……有夠ㄎㄧㄤ。號稱躺著練功，我看是躺著儲值吧？這種放置遊戲，比的就是誰的資源多。開局先別急著衝，把所有兌換碼、禮包碼都輸入一遍才是正事。覺得官方送太少？想一步登天？內行的都知道找代儲值，保證快速安全，讓你用新台幣教訓那些無課玩家，輕鬆當大俠。</v>
       </c>
       <c r="F293" s="14" t="s">
-        <v>5241</v>
-      </c>
-      <c r="K293" s="78" t="s">
-        <v>5459</v>
-      </c>
-      <c r="L293" s="10" t="s">
-        <v>5458</v>
-      </c>
-    </row>
-    <row r="294" spans="1:12">
+        <v>5475</v>
+      </c>
+      <c r="G293" s="10" t="s">
+        <v>5476</v>
+      </c>
+      <c r="H293" s="10" t="s">
+        <v>2625</v>
+      </c>
+      <c r="K293" s="89" t="s">
+        <v>5477</v>
+      </c>
+      <c r="M293" s="15" t="s">
+        <v>5478</v>
+      </c>
+      <c r="O293" s="15" t="s">
+        <v>5479</v>
+      </c>
+      <c r="Q293" s="15" t="s">
+        <v>5480</v>
+      </c>
+    </row>
+    <row r="294" spans="1:27">
       <c r="A294" s="10" t="str">
         <f>IF(games!A294="", "", games!A294)</f>
         <v>楓之谷：放置冒險記</v>
@@ -62874,14 +63013,14 @@
       <c r="F294" s="14" t="s">
         <v>5241</v>
       </c>
-      <c r="K294" s="78" t="s">
-        <v>5459</v>
+      <c r="K294" s="89" t="s">
+        <v>5464</v>
       </c>
       <c r="L294" s="10" t="s">
         <v>5458</v>
       </c>
     </row>
-    <row r="295" spans="1:12">
+    <row r="295" spans="1:27">
       <c r="A295" s="10" t="str">
         <f>IF(games!A295="", "", games!A295)</f>
         <v>Shiba Wars：Goddess Link TD</v>
@@ -62901,14 +63040,14 @@
       <c r="F295" s="14" t="s">
         <v>5241</v>
       </c>
-      <c r="K295" s="78" t="s">
-        <v>5459</v>
+      <c r="K295" s="89" t="s">
+        <v>5464</v>
       </c>
       <c r="L295" s="10" t="s">
         <v>5458</v>
       </c>
     </row>
-    <row r="296" spans="1:12">
+    <row r="296" spans="1:27">
       <c r="A296" s="10" t="str">
         <f>IF(games!A296="", "", games!A296)</f>
         <v>熱血江湖：福利加強版</v>
@@ -62928,14 +63067,14 @@
       <c r="F296" s="14" t="s">
         <v>5241</v>
       </c>
-      <c r="K296" s="78" t="s">
-        <v>5459</v>
+      <c r="K296" s="89" t="s">
+        <v>5464</v>
       </c>
       <c r="L296" s="10" t="s">
         <v>5458</v>
       </c>
     </row>
-    <row r="297" spans="1:12">
+    <row r="297" spans="1:27">
       <c r="A297" s="10" t="str">
         <f>IF(games!A297="", "", games!A297)</f>
         <v/>
@@ -62953,7 +63092,7 @@
         <v/>
       </c>
     </row>
-    <row r="298" spans="1:12">
+    <row r="298" spans="1:27">
       <c r="A298" s="10" t="str">
         <f>IF(games!A298="", "", games!A298)</f>
         <v/>
@@ -62971,7 +63110,7 @@
         <v/>
       </c>
     </row>
-    <row r="299" spans="1:12">
+    <row r="299" spans="1:27">
       <c r="A299" s="10" t="str">
         <f>IF(games!A299="", "", games!A299)</f>
         <v/>
@@ -62989,7 +63128,7 @@
         <v/>
       </c>
     </row>
-    <row r="300" spans="1:12">
+    <row r="300" spans="1:27">
       <c r="A300" s="10" t="str">
         <f>IF(games!A300="", "", games!A300)</f>
         <v/>
@@ -63007,7 +63146,7 @@
         <v/>
       </c>
     </row>
-    <row r="301" spans="1:12">
+    <row r="301" spans="1:27">
       <c r="A301" s="10" t="str">
         <f>IF(games!A301="", "", games!A301)</f>
         <v/>
@@ -63025,7 +63164,7 @@
         <v/>
       </c>
     </row>
-    <row r="302" spans="1:12">
+    <row r="302" spans="1:27">
       <c r="A302" s="10" t="str">
         <f>IF(games!A302="", "", games!A302)</f>
         <v/>
@@ -63043,7 +63182,7 @@
         <v/>
       </c>
     </row>
-    <row r="303" spans="1:12">
+    <row r="303" spans="1:27">
       <c r="A303" s="10" t="str">
         <f>IF(games!A303="", "", games!A303)</f>
         <v/>
@@ -63061,7 +63200,7 @@
         <v/>
       </c>
     </row>
-    <row r="304" spans="1:12">
+    <row r="304" spans="1:27">
       <c r="C304" s="10" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -64774,22 +64913,20 @@
     <hyperlink ref="F245" r:id="rId4"/>
     <hyperlink ref="F265" r:id="rId5"/>
     <hyperlink ref="F276" r:id="rId6"/>
-    <hyperlink ref="K288" r:id="rId7"/>
-    <hyperlink ref="K289" r:id="rId8"/>
-    <hyperlink ref="K290" r:id="rId9"/>
-    <hyperlink ref="K291" r:id="rId10"/>
-    <hyperlink ref="K292" r:id="rId11"/>
-    <hyperlink ref="K293" r:id="rId12"/>
-    <hyperlink ref="K294" r:id="rId13"/>
-    <hyperlink ref="K295" r:id="rId14"/>
-    <hyperlink ref="K296" r:id="rId15"/>
-    <hyperlink ref="K280" r:id="rId16"/>
-    <hyperlink ref="K281" r:id="rId17"/>
-    <hyperlink ref="K282" r:id="rId18"/>
-    <hyperlink ref="K285" r:id="rId19"/>
-    <hyperlink ref="K286" r:id="rId20"/>
+    <hyperlink ref="K280" r:id="rId7"/>
+    <hyperlink ref="K281" r:id="rId8"/>
+    <hyperlink ref="K282" r:id="rId9"/>
+    <hyperlink ref="K285" r:id="rId10"/>
+    <hyperlink ref="K286" r:id="rId11"/>
+    <hyperlink ref="M291" r:id="rId12"/>
+    <hyperlink ref="K288" r:id="rId13"/>
+    <hyperlink ref="K289" r:id="rId14"/>
+    <hyperlink ref="K290" r:id="rId15"/>
+    <hyperlink ref="K294" r:id="rId16"/>
+    <hyperlink ref="K295" r:id="rId17"/>
+    <hyperlink ref="K296" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId21"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>
--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8036" uniqueCount="5481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8056" uniqueCount="5481">
   <si>
     <t>Facebook</t>
   </si>
@@ -61975,7 +61975,7 @@
         <v>5049</v>
       </c>
     </row>
-    <row r="273" spans="1:40">
+    <row r="273" spans="1:42">
       <c r="A273" s="10" t="str">
         <f>IF(games!A273="", "", games!A273)</f>
         <v>盜夢英雄2：幻野</v>
@@ -62062,7 +62062,7 @@
         <v>5205</v>
       </c>
     </row>
-    <row r="274" spans="1:40">
+    <row r="274" spans="1:42">
       <c r="A274" s="10" t="str">
         <f>IF(games!A274="", "", games!A274)</f>
         <v>貪婪洞窟：重生</v>
@@ -62109,8 +62109,14 @@
       <c r="P274" s="10" t="s">
         <v>5001</v>
       </c>
-    </row>
-    <row r="275" spans="1:40">
+      <c r="Q274" s="89" t="s">
+        <v>5464</v>
+      </c>
+      <c r="R274" s="10" t="s">
+        <v>5458</v>
+      </c>
+    </row>
+    <row r="275" spans="1:42">
       <c r="A275" s="10" t="str">
         <f>IF(games!A275="", "", games!A275)</f>
         <v>小兵特攻隊</v>
@@ -62172,8 +62178,14 @@
       <c r="Y275" s="15" t="s">
         <v>5108</v>
       </c>
-    </row>
-    <row r="276" spans="1:40">
+      <c r="AA275" s="89" t="s">
+        <v>5464</v>
+      </c>
+      <c r="AB275" s="10" t="s">
+        <v>5458</v>
+      </c>
+    </row>
+    <row r="276" spans="1:42">
       <c r="A276" s="10" t="str">
         <f>IF(games!A276="", "", games!A276)</f>
         <v>星塔旅人</v>
@@ -62214,8 +62226,14 @@
       <c r="N276" s="10" t="s">
         <v>5112</v>
       </c>
-    </row>
-    <row r="277" spans="1:40">
+      <c r="Q276" s="89" t="s">
+        <v>5464</v>
+      </c>
+      <c r="R276" s="10" t="s">
+        <v>5458</v>
+      </c>
+    </row>
+    <row r="277" spans="1:42">
       <c r="A277" s="10" t="str">
         <f>IF(games!A277="", "", games!A277)</f>
         <v>卡厄斯夢境</v>
@@ -62244,14 +62262,14 @@
       <c r="I277" s="10" t="s">
         <v>4360</v>
       </c>
-      <c r="K277" s="14" t="s">
-        <v>4811</v>
+      <c r="K277" s="89" t="s">
+        <v>5464</v>
       </c>
       <c r="L277" s="10" t="s">
-        <v>4810</v>
-      </c>
-    </row>
-    <row r="278" spans="1:40">
+        <v>5458</v>
+      </c>
+    </row>
+    <row r="278" spans="1:42">
       <c r="A278" s="10" t="str">
         <f>IF(games!A278="", "", games!A278)</f>
         <v>星痕共鳴</v>
@@ -62289,8 +62307,14 @@
       <c r="N278" s="10" t="s">
         <v>5244</v>
       </c>
-    </row>
-    <row r="279" spans="1:40">
+      <c r="O278" s="89" t="s">
+        <v>5464</v>
+      </c>
+      <c r="P278" s="10" t="s">
+        <v>5458</v>
+      </c>
+    </row>
+    <row r="279" spans="1:42">
       <c r="A279" s="10" t="str">
         <f>IF(games!A279="", "", games!A279)</f>
         <v>二重螺旋</v>
@@ -62382,8 +62406,14 @@
       <c r="AD279" s="10" t="s">
         <v>5369</v>
       </c>
-    </row>
-    <row r="280" spans="1:40">
+      <c r="AG279" s="89" t="s">
+        <v>5464</v>
+      </c>
+      <c r="AH279" s="10" t="s">
+        <v>5458</v>
+      </c>
+    </row>
+    <row r="280" spans="1:42">
       <c r="A280" s="10" t="str">
         <f>IF(games!A280="", "", games!A280)</f>
         <v>電馭跑酷</v>
@@ -62410,7 +62440,7 @@
         <v>5460</v>
       </c>
     </row>
-    <row r="281" spans="1:40">
+    <row r="281" spans="1:42">
       <c r="A281" s="10" t="str">
         <f>IF(games!A281="", "", games!A281)</f>
         <v>火焰紋章Shadows</v>
@@ -62437,7 +62467,7 @@
         <v>5460</v>
       </c>
     </row>
-    <row r="282" spans="1:40">
+    <row r="282" spans="1:42">
       <c r="A282" s="10" t="str">
         <f>IF(games!A282="", "", games!A282)</f>
         <v>石器時代：寵物世界</v>
@@ -62464,7 +62494,7 @@
         <v>5460</v>
       </c>
     </row>
-    <row r="283" spans="1:40">
+    <row r="283" spans="1:42">
       <c r="A283" s="10" t="str">
         <f>IF(games!A283="", "", games!A283)</f>
         <v>蔚藍星球：國王很忙</v>
@@ -62553,8 +62583,14 @@
       <c r="AD283" s="10" t="s">
         <v>5343</v>
       </c>
-    </row>
-    <row r="284" spans="1:40">
+      <c r="AE283" s="89" t="s">
+        <v>5464</v>
+      </c>
+      <c r="AF283" s="10" t="s">
+        <v>5458</v>
+      </c>
+    </row>
+    <row r="284" spans="1:42">
       <c r="A284" s="10" t="str">
         <f>IF(games!A284="", "", games!A284)</f>
         <v>胸懷三國：美人計</v>
@@ -62670,8 +62706,14 @@
       <c r="AN284" s="10" t="s">
         <v>5297</v>
       </c>
-    </row>
-    <row r="285" spans="1:40">
+      <c r="AO284" s="89" t="s">
+        <v>5464</v>
+      </c>
+      <c r="AP284" s="10" t="s">
+        <v>5458</v>
+      </c>
+    </row>
+    <row r="285" spans="1:42">
       <c r="A285" s="10" t="str">
         <f>IF(games!A285="", "", games!A285)</f>
         <v>弓箭英雄：塔防</v>
@@ -62698,7 +62740,7 @@
         <v>5460</v>
       </c>
     </row>
-    <row r="286" spans="1:40">
+    <row r="286" spans="1:42">
       <c r="A286" s="10" t="str">
         <f>IF(games!A286="", "", games!A286)</f>
         <v>十二之天M</v>
@@ -62725,7 +62767,7 @@
         <v>5460</v>
       </c>
     </row>
-    <row r="287" spans="1:40">
+    <row r="287" spans="1:42">
       <c r="A287" s="10" t="str">
         <f>IF(games!A287="", "", games!A287)</f>
         <v>NBA巔峰對決</v>
@@ -62778,8 +62820,14 @@
       <c r="R287" s="10" t="s">
         <v>5380</v>
       </c>
-    </row>
-    <row r="288" spans="1:40">
+      <c r="S287" s="89" t="s">
+        <v>5464</v>
+      </c>
+      <c r="T287" s="10" t="s">
+        <v>5458</v>
+      </c>
+    </row>
+    <row r="288" spans="1:42">
       <c r="A288" s="10" t="str">
         <f>IF(games!A288="", "", games!A288)</f>
         <v>三國志：王戰</v>
@@ -62806,7 +62854,7 @@
         <v>5458</v>
       </c>
     </row>
-    <row r="289" spans="1:27">
+    <row r="289" spans="1:30">
       <c r="A289" s="10" t="str">
         <f>IF(games!A289="", "", games!A289)</f>
         <v>信長 霸道</v>
@@ -62833,7 +62881,7 @@
         <v>5458</v>
       </c>
     </row>
-    <row r="290" spans="1:27">
+    <row r="290" spans="1:30">
       <c r="A290" s="10" t="str">
         <f>IF(games!A290="", "", games!A290)</f>
         <v>勇者前線Versus</v>
@@ -62860,7 +62908,7 @@
         <v>5458</v>
       </c>
     </row>
-    <row r="291" spans="1:27">
+    <row r="291" spans="1:30">
       <c r="A291" s="10" t="str">
         <f>IF(games!A291="", "", games!A291)</f>
         <v>幻域方舟</v>
@@ -62899,7 +62947,7 @@
         <v>5458</v>
       </c>
     </row>
-    <row r="292" spans="1:27">
+    <row r="292" spans="1:30">
       <c r="A292" s="10" t="str">
         <f>IF(games!A292="", "", games!A292)</f>
         <v>開天</v>
@@ -62953,8 +63001,14 @@
       <c r="AA292" s="15" t="s">
         <v>5474</v>
       </c>
-    </row>
-    <row r="293" spans="1:27">
+      <c r="AC292" s="89" t="s">
+        <v>5464</v>
+      </c>
+      <c r="AD292" s="10" t="s">
+        <v>5458</v>
+      </c>
+    </row>
+    <row r="293" spans="1:30">
       <c r="A293" s="10" t="str">
         <f>IF(games!A293="", "", games!A293)</f>
         <v>人人有功練：腸仔江湖見</v>
@@ -62992,8 +63046,14 @@
       <c r="Q293" s="15" t="s">
         <v>5480</v>
       </c>
-    </row>
-    <row r="294" spans="1:27">
+      <c r="S293" s="89" t="s">
+        <v>5464</v>
+      </c>
+      <c r="T293" s="10" t="s">
+        <v>5458</v>
+      </c>
+    </row>
+    <row r="294" spans="1:30">
       <c r="A294" s="10" t="str">
         <f>IF(games!A294="", "", games!A294)</f>
         <v>楓之谷：放置冒險記</v>
@@ -63020,7 +63080,7 @@
         <v>5458</v>
       </c>
     </row>
-    <row r="295" spans="1:27">
+    <row r="295" spans="1:30">
       <c r="A295" s="10" t="str">
         <f>IF(games!A295="", "", games!A295)</f>
         <v>Shiba Wars：Goddess Link TD</v>
@@ -63047,7 +63107,7 @@
         <v>5458</v>
       </c>
     </row>
-    <row r="296" spans="1:27">
+    <row r="296" spans="1:30">
       <c r="A296" s="10" t="str">
         <f>IF(games!A296="", "", games!A296)</f>
         <v>熱血江湖：福利加強版</v>
@@ -63074,7 +63134,7 @@
         <v>5458</v>
       </c>
     </row>
-    <row r="297" spans="1:27">
+    <row r="297" spans="1:30">
       <c r="A297" s="10" t="str">
         <f>IF(games!A297="", "", games!A297)</f>
         <v/>
@@ -63092,7 +63152,7 @@
         <v/>
       </c>
     </row>
-    <row r="298" spans="1:27">
+    <row r="298" spans="1:30">
       <c r="A298" s="10" t="str">
         <f>IF(games!A298="", "", games!A298)</f>
         <v/>
@@ -63110,7 +63170,7 @@
         <v/>
       </c>
     </row>
-    <row r="299" spans="1:27">
+    <row r="299" spans="1:30">
       <c r="A299" s="10" t="str">
         <f>IF(games!A299="", "", games!A299)</f>
         <v/>
@@ -63128,7 +63188,7 @@
         <v/>
       </c>
     </row>
-    <row r="300" spans="1:27">
+    <row r="300" spans="1:30">
       <c r="A300" s="10" t="str">
         <f>IF(games!A300="", "", games!A300)</f>
         <v/>
@@ -63146,7 +63206,7 @@
         <v/>
       </c>
     </row>
-    <row r="301" spans="1:27">
+    <row r="301" spans="1:30">
       <c r="A301" s="10" t="str">
         <f>IF(games!A301="", "", games!A301)</f>
         <v/>
@@ -63164,7 +63224,7 @@
         <v/>
       </c>
     </row>
-    <row r="302" spans="1:27">
+    <row r="302" spans="1:30">
       <c r="A302" s="10" t="str">
         <f>IF(games!A302="", "", games!A302)</f>
         <v/>
@@ -63182,7 +63242,7 @@
         <v/>
       </c>
     </row>
-    <row r="303" spans="1:27">
+    <row r="303" spans="1:30">
       <c r="A303" s="10" t="str">
         <f>IF(games!A303="", "", games!A303)</f>
         <v/>
@@ -63200,7 +63260,7 @@
         <v/>
       </c>
     </row>
-    <row r="304" spans="1:27">
+    <row r="304" spans="1:30">
       <c r="C304" s="10" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -64925,8 +64985,19 @@
     <hyperlink ref="K294" r:id="rId16"/>
     <hyperlink ref="K295" r:id="rId17"/>
     <hyperlink ref="K296" r:id="rId18"/>
+    <hyperlink ref="AC292" r:id="rId19"/>
+    <hyperlink ref="S293" r:id="rId20"/>
+    <hyperlink ref="S287" r:id="rId21"/>
+    <hyperlink ref="AO284" r:id="rId22"/>
+    <hyperlink ref="AE283" r:id="rId23"/>
+    <hyperlink ref="AG279" r:id="rId24"/>
+    <hyperlink ref="O278" r:id="rId25"/>
+    <hyperlink ref="K277" r:id="rId26"/>
+    <hyperlink ref="Q276" r:id="rId27"/>
+    <hyperlink ref="AA275" r:id="rId28"/>
+    <hyperlink ref="Q274" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId30"/>
 </worksheet>
 </file>
--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8056" uniqueCount="5481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8060" uniqueCount="5485">
   <si>
     <t>Facebook</t>
   </si>
@@ -20877,6 +20877,20 @@
   </si>
   <si>
     <t>TUTU666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雙冠全服同慶禮</t>
+  </si>
+  <si>
+    <t>我們球場見</t>
+  </si>
+  <si>
+    <t>SNAKEBALL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Busyking666</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -62583,10 +62597,16 @@
       <c r="AD283" s="10" t="s">
         <v>5343</v>
       </c>
-      <c r="AE283" s="89" t="s">
+      <c r="AE283" s="15" t="s">
+        <v>5483</v>
+      </c>
+      <c r="AG283" s="15" t="s">
+        <v>5484</v>
+      </c>
+      <c r="AI283" s="89" t="s">
         <v>5464</v>
       </c>
-      <c r="AF283" s="10" t="s">
+      <c r="AJ283" s="10" t="s">
         <v>5458</v>
       </c>
     </row>
@@ -62820,10 +62840,16 @@
       <c r="R287" s="10" t="s">
         <v>5380</v>
       </c>
-      <c r="S287" s="89" t="s">
+      <c r="S287" t="s">
+        <v>5481</v>
+      </c>
+      <c r="U287" t="s">
+        <v>5482</v>
+      </c>
+      <c r="W287" s="89" t="s">
         <v>5464</v>
       </c>
-      <c r="T287" s="10" t="s">
+      <c r="X287" s="10" t="s">
         <v>5458</v>
       </c>
     </row>
@@ -64987,9 +65013,9 @@
     <hyperlink ref="K296" r:id="rId18"/>
     <hyperlink ref="AC292" r:id="rId19"/>
     <hyperlink ref="S293" r:id="rId20"/>
-    <hyperlink ref="S287" r:id="rId21"/>
+    <hyperlink ref="W287" r:id="rId21"/>
     <hyperlink ref="AO284" r:id="rId22"/>
-    <hyperlink ref="AE283" r:id="rId23"/>
+    <hyperlink ref="AI283" r:id="rId23"/>
     <hyperlink ref="AG279" r:id="rId24"/>
     <hyperlink ref="O278" r:id="rId25"/>
     <hyperlink ref="K277" r:id="rId26"/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8060" uniqueCount="5485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8061" uniqueCount="5486">
   <si>
     <t>Facebook</t>
   </si>
@@ -20893,12 +20893,15 @@
     <t>Busyking666</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>LC3529</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -21021,6 +21024,13 @@
       <color rgb="FFF3F5F7"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="5">
@@ -21267,7 +21277,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -21487,6 +21497,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -42427,6 +42440,9 @@
       </c>
       <c r="K296" s="88" t="s">
         <v>5258</v>
+      </c>
+      <c r="L296" s="91" t="s">
+        <v>5485</v>
       </c>
     </row>
     <row r="297" spans="1:31" ht="22.5" customHeight="1">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -42441,9 +42441,6 @@
       <c r="K296" s="88" t="s">
         <v>5258</v>
       </c>
-      <c r="L296" s="91" t="s">
-        <v>5485</v>
-      </c>
     </row>
     <row r="297" spans="1:31" ht="22.5" customHeight="1">
       <c r="F297" s="37" t="str">
@@ -63169,10 +63166,13 @@
       <c r="F296" s="14" t="s">
         <v>5241</v>
       </c>
-      <c r="K296" s="89" t="s">
+      <c r="K296" s="91" t="s">
+        <v>5485</v>
+      </c>
+      <c r="M296" s="89" t="s">
         <v>5464</v>
       </c>
-      <c r="L296" s="10" t="s">
+      <c r="N296" s="10" t="s">
         <v>5458</v>
       </c>
     </row>
@@ -65026,7 +65026,7 @@
     <hyperlink ref="K290" r:id="rId15"/>
     <hyperlink ref="K294" r:id="rId16"/>
     <hyperlink ref="K295" r:id="rId17"/>
-    <hyperlink ref="K296" r:id="rId18"/>
+    <hyperlink ref="M296" r:id="rId18"/>
     <hyperlink ref="AC292" r:id="rId19"/>
     <hyperlink ref="S293" r:id="rId20"/>
     <hyperlink ref="W287" r:id="rId21"/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8061" uniqueCount="5486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8112" uniqueCount="5516">
   <si>
     <t>Facebook</t>
   </si>
@@ -20591,9 +20591,6 @@
     <t>https://www.facebook.com/RexuejianghuFuliban/</t>
   </si>
   <si>
-    <t>https://www.youtube.com/@%E7%86%B1%E8%A1%80%E6%B1%9F%E6%B9%96%E7%A6%8F%E5%88%A9%E5%8A%A0%E5%BC%B7%E7%89%88</t>
-  </si>
-  <si>
     <t>https://apps.apple.com/hk/app/%E7%86%B1%E8%A1%80%E6%B1%9F%E6%B9%96-%E7%A6%8F%E5%88%A9%E5%8A%A0%E5%BC%B7%E7%89%88/id6741752911?mt=8</t>
   </si>
   <si>
@@ -20895,6 +20892,121 @@
   </si>
   <si>
     <t>LC3529</t>
+  </si>
+  <si>
+    <t>VIP666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SAUSAGE666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KONGFU888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RRYGL1750</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RRYGL2025</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KONGFU666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://hot.hkxingyou.com/?fbclid=IwY2xjawN6le5leHRuA2FlbQIxMABicmlkETF4Z01XclVaSjJuNzRmRmVnc3J0YwZhcHBfaWQQMjIyMDM5MTc4ODIwMDg5MgABHl_s0cNDCfj3ZY0eWSq6xL0ncGPJ2v6usbbIGqAT3ZUs7UlAdvRxG8YiPcS9_aem_EFvqS2HMThXZEBi3_Ojt5A</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61578381937617#</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E7%86%B1%E8%A1%80%E4%B8%BB%E5%85%ACgo-%E4%B8%89%E5%9C%8B%E8%82%89%E9%B4%BFrpg%E6%89%8B%E9%81%8A/id6746403728</t>
+  </si>
+  <si>
+    <t>20251031GIFT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">20251024GIFT </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20251017GIFT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20251010GIFT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">XEQC24 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025GO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主畫面左上方三條線「選單」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>點進設置之後中間點「兌換碼」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>熱血主公Go!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.furywing.rxzggo.free&amp;fbclid=IwY2xjawN6lllleHRuA2FlbQIxMABicmlkETF4Z01XclVaSjJuNzRmRmVnc3J0YwZhcHBfaWQQMjIyMDM5MTc4ODIwMDg5MgABHl-Zq6JKMWFJ470D5XHqwMKfpCTTfCQhB2c-G4zkH_T7ZHL2tVY-tMx3tMJE_aem_HV89nRhsIdGCR2vehyIo7w</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《熱血主公Go!》是一款結合Roguelike培育、RPG冒險與街機動作元素的三國手遊。玩家將扮演主公，踏上匡扶漢室的征途，招募趙雲、呂布等傳奇名將。遊戲主打懷舊街機畫風與隨機流派組合，戰鬥體驗絕不重複！官方不斷釋出最新的兌換碼與禮包碼，讓玩家輕鬆升級。若想快速提升戰力，尋找代儲值服務也是一種選擇，務必確保快速安全，避免受騙。立即加入，體驗放置休閒與熱血PVP對戰的雙重樂趣！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>648玉璧</t>
+  </si>
+  <si>
+    <t>328玉璧</t>
+  </si>
+  <si>
+    <t>198玉璧</t>
+  </si>
+  <si>
+    <t>98玉璧</t>
+  </si>
+  <si>
+    <t>30玉璧</t>
+  </si>
+  <si>
+    <t>6玉璧</t>
+  </si>
+  <si>
+    <t>主畫面上方打鼓圖案「活動」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>左邊書籤點「兌換碼」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>已過期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最新儲值優惠馬上問問Line@客服</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LINE ID：@ssbuy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -21805,7 +21917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ627"/>
+  <dimension ref="A1:AQ626"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="27" style="37" customWidth="1"/>
@@ -40204,7 +40316,7 @@
         <v>4880</v>
       </c>
       <c r="F268" s="37" t="str">
-        <f t="shared" ref="F268:F312" si="12">IF(A268="", "", "gift-codes.html?game=" &amp; A268)</f>
+        <f t="shared" ref="F268:F311" si="12">IF(A268="", "", "gift-codes.html?game=" &amp; A268)</f>
         <v>gift-codes.html?game=我的花園世界</v>
       </c>
       <c r="G268" s="45" t="s">
@@ -41565,7 +41677,7 @@
         <v>5185</v>
       </c>
       <c r="H284" s="38" t="str">
-        <f t="shared" ref="H284:H312" si="13">IF(A284="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A284)</f>
+        <f t="shared" ref="H284:H311" si="13">IF(A284="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A284)</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=胸懷三國：美人計</v>
       </c>
       <c r="I284" s="39" t="s">
@@ -42014,7 +42126,7 @@
     </row>
     <row r="290" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A290" s="59" t="s">
-        <v>5444</v>
+        <v>5443</v>
       </c>
       <c r="C290" s="37" t="s">
         <v>5391</v>
@@ -42030,17 +42142,17 @@
         <v>gift-codes.html?game=勇者前線Versus</v>
       </c>
       <c r="G290" s="38" t="s">
-        <v>5415</v>
+        <v>5414</v>
       </c>
       <c r="H290" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=勇者前線Versus</v>
       </c>
       <c r="I290" s="39" t="s">
-        <v>5451</v>
+        <v>5450</v>
       </c>
       <c r="J290" s="2" t="s">
-        <v>5428</v>
+        <v>5427</v>
       </c>
       <c r="K290" s="88" t="s">
         <v>5258</v>
@@ -42048,7 +42160,7 @@
     </row>
     <row r="291" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A291" s="83" t="s">
-        <v>5445</v>
+        <v>5444</v>
       </c>
       <c r="C291" s="37" t="s">
         <v>5392</v>
@@ -42071,10 +42183,10 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=幻域方舟</v>
       </c>
       <c r="I291" s="39" t="s">
-        <v>5452</v>
+        <v>5451</v>
       </c>
       <c r="J291" s="2" t="s">
-        <v>5428</v>
+        <v>5427</v>
       </c>
       <c r="K291" s="88" t="s">
         <v>5258</v>
@@ -42082,7 +42194,7 @@
     </row>
     <row r="292" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A292" s="83" t="s">
-        <v>5446</v>
+        <v>5445</v>
       </c>
       <c r="C292" s="37" t="s">
         <v>5396</v>
@@ -42105,10 +42217,10 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=開天</v>
       </c>
       <c r="I292" s="39" t="s">
-        <v>5453</v>
+        <v>5452</v>
       </c>
       <c r="J292" s="2" t="s">
-        <v>5428</v>
+        <v>5427</v>
       </c>
       <c r="K292" s="88" t="s">
         <v>5258</v>
@@ -42120,7 +42232,7 @@
         <v>2717</v>
       </c>
       <c r="N292" s="1" t="s">
-        <v>5416</v>
+        <v>5415</v>
       </c>
       <c r="O292" s="59">
         <v>2095</v>
@@ -42132,25 +42244,25 @@
         <v>1388</v>
       </c>
       <c r="R292" s="1" t="s">
-        <v>5417</v>
+        <v>5416</v>
       </c>
       <c r="S292" s="59">
         <v>1194</v>
       </c>
       <c r="T292" s="1" t="s">
-        <v>5418</v>
+        <v>5417</v>
       </c>
       <c r="U292" s="59">
         <v>840</v>
       </c>
       <c r="V292" s="1" t="s">
-        <v>5419</v>
+        <v>5418</v>
       </c>
       <c r="W292" s="59">
         <v>815</v>
       </c>
       <c r="X292" s="1" t="s">
-        <v>5420</v>
+        <v>5419</v>
       </c>
       <c r="Y292" s="59">
         <v>756</v>
@@ -42170,7 +42282,7 @@
     </row>
     <row r="293" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A293" s="83" t="s">
-        <v>5447</v>
+        <v>5446</v>
       </c>
       <c r="C293" s="37" t="s">
         <v>5400</v>
@@ -42193,52 +42305,52 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=人人有功練：腸仔江湖見</v>
       </c>
       <c r="I293" s="39" t="s">
-        <v>5454</v>
+        <v>5453</v>
       </c>
       <c r="J293" s="2" t="s">
-        <v>5428</v>
+        <v>5427</v>
       </c>
       <c r="K293" s="88" t="s">
         <v>5258</v>
       </c>
       <c r="L293" s="1" t="s">
-        <v>5421</v>
+        <v>5420</v>
       </c>
       <c r="M293" s="59">
         <v>2717</v>
       </c>
       <c r="N293" s="1" t="s">
-        <v>5422</v>
+        <v>5421</v>
       </c>
       <c r="O293" s="59">
         <v>1422</v>
       </c>
       <c r="P293" s="1" t="s">
-        <v>5423</v>
+        <v>5422</v>
       </c>
       <c r="Q293" s="59">
         <v>840</v>
       </c>
       <c r="R293" s="1" t="s">
-        <v>5424</v>
+        <v>5423</v>
       </c>
       <c r="S293" s="59">
         <v>620</v>
       </c>
       <c r="T293" s="1" t="s">
-        <v>5425</v>
+        <v>5424</v>
       </c>
       <c r="U293" s="59">
         <v>318</v>
       </c>
       <c r="V293" s="1" t="s">
-        <v>5426</v>
+        <v>5425</v>
       </c>
       <c r="W293" s="59">
         <v>151</v>
       </c>
       <c r="X293" s="1" t="s">
-        <v>5427</v>
+        <v>5426</v>
       </c>
       <c r="Y293" s="59">
         <v>30</v>
@@ -42246,7 +42358,7 @@
     </row>
     <row r="294" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A294" s="83" t="s">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="C294" s="38" t="s">
         <v>5406</v>
@@ -42269,58 +42381,58 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=楓之谷：放置冒險記</v>
       </c>
       <c r="I294" s="39" t="s">
-        <v>5455</v>
+        <v>5454</v>
       </c>
       <c r="J294" s="2" t="s">
-        <v>5428</v>
+        <v>5427</v>
       </c>
       <c r="K294" s="88" t="s">
         <v>5258</v>
       </c>
       <c r="L294" s="1" t="s">
-        <v>5429</v>
+        <v>5428</v>
       </c>
       <c r="M294" s="59">
         <v>2469</v>
       </c>
       <c r="N294" s="1" t="s">
-        <v>5430</v>
+        <v>5429</v>
       </c>
       <c r="O294" s="59">
         <v>1253</v>
       </c>
       <c r="P294" s="1" t="s">
-        <v>5431</v>
+        <v>5430</v>
       </c>
       <c r="Q294" s="59">
         <v>1085</v>
       </c>
       <c r="R294" s="1" t="s">
-        <v>5432</v>
+        <v>5431</v>
       </c>
       <c r="S294" s="59">
         <v>840</v>
       </c>
       <c r="T294" s="1" t="s">
-        <v>5433</v>
+        <v>5432</v>
       </c>
       <c r="U294" s="59">
         <v>569</v>
       </c>
       <c r="V294" s="1" t="s">
-        <v>5434</v>
+        <v>5433</v>
       </c>
       <c r="W294" s="59">
         <v>272</v>
       </c>
       <c r="X294" s="1" t="s">
-        <v>5435</v>
+        <v>5434</v>
       </c>
       <c r="Y294" s="59">
         <v>195</v>
       </c>
       <c r="Z294" s="1" t="s">
-        <v>5436</v>
+        <v>5435</v>
       </c>
       <c r="AA294" s="59">
         <v>106</v>
@@ -42328,13 +42440,13 @@
     </row>
     <row r="295" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A295" s="59" t="s">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="C295" s="37" t="s">
-        <v>5414</v>
+        <v>5413</v>
       </c>
       <c r="D295" s="38" t="s">
-        <v>5413</v>
+        <v>5412</v>
       </c>
       <c r="E295" s="38" t="s">
         <v>5408</v>
@@ -42351,52 +42463,52 @@
         <v>https://www.ssbuy.tw/game-detail.html?game=Shiba Wars：Goddess Link TD</v>
       </c>
       <c r="I295" s="39" t="s">
-        <v>5456</v>
+        <v>5455</v>
       </c>
       <c r="J295" s="2" t="s">
-        <v>5428</v>
+        <v>5427</v>
       </c>
       <c r="K295" s="88" t="s">
         <v>5258</v>
       </c>
       <c r="L295" s="1" t="s">
-        <v>5437</v>
+        <v>5436</v>
       </c>
       <c r="M295" s="59">
         <v>1926</v>
       </c>
       <c r="N295" s="1" t="s">
-        <v>5438</v>
+        <v>5437</v>
       </c>
       <c r="O295" s="59">
         <v>1253</v>
       </c>
       <c r="P295" s="1" t="s">
-        <v>5439</v>
+        <v>5438</v>
       </c>
       <c r="Q295" s="59">
         <v>586</v>
       </c>
       <c r="R295" s="1" t="s">
-        <v>5440</v>
+        <v>5439</v>
       </c>
       <c r="S295" s="59">
         <v>272</v>
       </c>
       <c r="T295" s="1" t="s">
-        <v>5441</v>
+        <v>5440</v>
       </c>
       <c r="U295" s="59">
         <v>195</v>
       </c>
       <c r="V295" s="1" t="s">
-        <v>5442</v>
+        <v>5441</v>
       </c>
       <c r="W295" s="59">
         <v>82</v>
       </c>
       <c r="X295" s="1" t="s">
-        <v>5443</v>
+        <v>5442</v>
       </c>
       <c r="Y295" s="59">
         <v>55</v>
@@ -42410,46 +42522,154 @@
     </row>
     <row r="296" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A296" s="83" t="s">
-        <v>5450</v>
+        <v>5449</v>
       </c>
       <c r="C296" s="37" t="s">
         <v>5409</v>
       </c>
       <c r="D296" s="38" t="s">
+        <v>5491</v>
+      </c>
+      <c r="E296" s="38" t="s">
         <v>5410</v>
-      </c>
-      <c r="E296" s="38" t="s">
-        <v>5411</v>
       </c>
       <c r="F296" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=熱血江湖：福利加強版</v>
       </c>
       <c r="G296" s="38" t="s">
-        <v>5412</v>
+        <v>5411</v>
       </c>
       <c r="H296" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=熱血江湖：福利加強版</v>
       </c>
       <c r="I296" s="39" t="s">
-        <v>5457</v>
+        <v>5456</v>
       </c>
       <c r="J296" s="2" t="s">
-        <v>5428</v>
+        <v>5427</v>
       </c>
       <c r="K296" s="88" t="s">
         <v>5258</v>
       </c>
-    </row>
-    <row r="297" spans="1:31" ht="22.5" customHeight="1">
+      <c r="L296" s="1" t="s">
+        <v>4889</v>
+      </c>
+      <c r="M296" s="59">
+        <v>2763</v>
+      </c>
+      <c r="N296" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="O296" s="59">
+        <v>1446</v>
+      </c>
+      <c r="P296" s="1" t="s">
+        <v>4890</v>
+      </c>
+      <c r="Q296" s="59">
+        <v>855</v>
+      </c>
+      <c r="R296" s="1" t="s">
+        <v>4447</v>
+      </c>
+      <c r="S296" s="59">
+        <v>578</v>
+      </c>
+      <c r="T296" s="1" t="s">
+        <v>4891</v>
+      </c>
+      <c r="U296" s="59">
+        <v>423</v>
+      </c>
+      <c r="V296" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="W296" s="59">
+        <v>285</v>
+      </c>
+      <c r="X296" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="Y296" s="59">
+        <v>153</v>
+      </c>
+      <c r="Z296" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA296" s="59">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="297" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A297" s="37" t="s">
+        <v>5502</v>
+      </c>
+      <c r="C297" s="37" t="s">
+        <v>5492</v>
+      </c>
+      <c r="D297" s="37" t="s">
+        <v>5492</v>
+      </c>
+      <c r="E297" s="38" t="s">
+        <v>5493</v>
+      </c>
       <c r="F297" s="37" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=熱血主公Go!</v>
+      </c>
+      <c r="G297" s="2" t="s">
+        <v>5503</v>
       </c>
       <c r="H297" s="38" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=熱血主公Go!</v>
+      </c>
+      <c r="I297" s="39" t="s">
+        <v>5504</v>
+      </c>
+      <c r="J297" s="2" t="s">
+        <v>5427</v>
+      </c>
+      <c r="K297" s="88" t="s">
+        <v>5258</v>
+      </c>
+      <c r="L297" s="1" t="s">
+        <v>5505</v>
+      </c>
+      <c r="M297" s="59">
+        <v>2511</v>
+      </c>
+      <c r="N297" s="1" t="s">
+        <v>5506</v>
+      </c>
+      <c r="O297" s="59">
+        <v>1275</v>
+      </c>
+      <c r="P297" s="1" t="s">
+        <v>5507</v>
+      </c>
+      <c r="Q297" s="59">
+        <v>855</v>
+      </c>
+      <c r="R297" s="1" t="s">
+        <v>5508</v>
+      </c>
+      <c r="S297" s="59">
+        <v>423</v>
+      </c>
+      <c r="T297" s="1" t="s">
+        <v>5509</v>
+      </c>
+      <c r="U297" s="59">
+        <v>153</v>
+      </c>
+      <c r="V297" s="1" t="s">
+        <v>5510</v>
+      </c>
+      <c r="W297" s="59">
+        <v>31</v>
       </c>
     </row>
     <row r="298" spans="1:31" ht="22.5" customHeight="1">
@@ -42594,21 +42814,21 @@
     </row>
     <row r="312" spans="6:8" ht="22.5" customHeight="1">
       <c r="F312" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="F312:F375" si="14">IF(A312="", "", "gift-codes.html?game=" &amp; A312)</f>
         <v/>
       </c>
       <c r="H312" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="H312:H375" si="15">IF(A312="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A312)</f>
         <v/>
       </c>
     </row>
     <row r="313" spans="6:8" ht="22.5" customHeight="1">
       <c r="F313" s="37" t="str">
-        <f t="shared" ref="F313:F376" si="14">IF(A313="", "", "gift-codes.html?game=" &amp; A313)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H313" s="38" t="str">
-        <f t="shared" ref="H313:H376" si="15">IF(A313="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A313)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -43234,21 +43454,21 @@
     </row>
     <row r="376" spans="6:8" ht="22.5" customHeight="1">
       <c r="F376" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="F376:F439" si="16">IF(A376="", "", "gift-codes.html?game=" &amp; A376)</f>
         <v/>
       </c>
       <c r="H376" s="38" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="H376:H439" si="17">IF(A376="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A376)</f>
         <v/>
       </c>
     </row>
     <row r="377" spans="6:8" ht="22.5" customHeight="1">
       <c r="F377" s="37" t="str">
-        <f t="shared" ref="F377:F440" si="16">IF(A377="", "", "gift-codes.html?game=" &amp; A377)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H377" s="38" t="str">
-        <f t="shared" ref="H377:H440" si="17">IF(A377="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A377)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -43792,7 +44012,7 @@
         <v/>
       </c>
     </row>
-    <row r="432" spans="6:8" ht="22.5" customHeight="1">
+    <row r="432" spans="6:8">
       <c r="F432" s="37" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -43874,21 +44094,21 @@
     </row>
     <row r="440" spans="6:8">
       <c r="F440" s="37" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="F440:F503" si="18">IF(A440="", "", "gift-codes.html?game=" &amp; A440)</f>
         <v/>
       </c>
       <c r="H440" s="38" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="H440:H503" si="19">IF(A440="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A440)</f>
         <v/>
       </c>
     </row>
     <row r="441" spans="6:8">
       <c r="F441" s="37" t="str">
-        <f t="shared" ref="F441:F504" si="18">IF(A441="", "", "gift-codes.html?game=" &amp; A441)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H441" s="38" t="str">
-        <f t="shared" ref="H441:H504" si="19">IF(A441="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A441)</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -44514,21 +44734,21 @@
     </row>
     <row r="504" spans="6:8">
       <c r="F504" s="37" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="F504:F567" si="20">IF(A504="", "", "gift-codes.html?game=" &amp; A504)</f>
         <v/>
       </c>
       <c r="H504" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="H504:H567" si="21">IF(A504="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A504)</f>
         <v/>
       </c>
     </row>
     <row r="505" spans="6:8">
       <c r="F505" s="37" t="str">
-        <f t="shared" ref="F505:F568" si="20">IF(A505="", "", "gift-codes.html?game=" &amp; A505)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H505" s="38" t="str">
-        <f t="shared" ref="H505:H568" si="21">IF(A505="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A505)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -45154,11 +45374,11 @@
     </row>
     <row r="568" spans="6:8">
       <c r="F568" s="37" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(A568="", "", "gift-codes.html?game=" &amp; A568)</f>
         <v/>
       </c>
       <c r="H568" s="38" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="H568:H626" si="22">IF(A568="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A568)</f>
         <v/>
       </c>
     </row>
@@ -45168,7 +45388,7 @@
         <v/>
       </c>
       <c r="H569" s="38" t="str">
-        <f t="shared" ref="H569:H627" si="22">IF(A569="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A569)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -45183,10 +45403,6 @@
       </c>
     </row>
     <row r="571" spans="6:8">
-      <c r="F571" s="37" t="str">
-        <f>IF(A571="", "", "gift-codes.html?game=" &amp; A571)</f>
-        <v/>
-      </c>
       <c r="H571" s="38" t="str">
         <f t="shared" si="22"/>
         <v/>
@@ -45518,12 +45734,6 @@
     </row>
     <row r="626" spans="8:8">
       <c r="H626" s="38" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-    </row>
-    <row r="627" spans="8:8">
-      <c r="H627" s="38" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -45818,6 +46028,7 @@
     <hyperlink ref="AD289" r:id="rId282"/>
     <hyperlink ref="X279" r:id="rId283"/>
     <hyperlink ref="AB287" r:id="rId284"/>
+    <hyperlink ref="G297"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId285"/>
@@ -45826,7 +46037,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AX435"/>
+  <dimension ref="A1:AX434"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="19.5"/>
   <cols>
     <col min="1" max="1" width="24.375" style="10" customWidth="1"/>
@@ -61870,11 +62081,11 @@
         <v>Awakenloop</v>
       </c>
       <c r="C269" s="10" t="str">
-        <f t="shared" ref="C269:C312" si="12">IF(A269="","", "giftcodesbanner/" &amp; A269 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" ref="C269:C311" si="12">IF(A269="","", "giftcodesbanner/" &amp; A269 &amp; "-禮包碼.jpg")</f>
         <v>giftcodesbanner/Awakenloop-禮包碼.jpg</v>
       </c>
       <c r="D269" s="10" t="str">
-        <f t="shared" ref="D269:D312" si="13">IF(A269="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A269)</f>
+        <f t="shared" ref="D269:D311" si="13">IF(A269="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A269)</f>
         <v>https://www.ssbuy.tw/gift-codes.html?game=Awakenloop</v>
       </c>
       <c r="E269" s="11" t="str">
@@ -62137,10 +62348,10 @@
         <v>5001</v>
       </c>
       <c r="Q274" s="89" t="s">
-        <v>5464</v>
+        <v>5463</v>
       </c>
       <c r="R274" s="10" t="s">
-        <v>5458</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="275" spans="1:42">
@@ -62206,10 +62417,10 @@
         <v>5108</v>
       </c>
       <c r="AA275" s="89" t="s">
-        <v>5464</v>
+        <v>5463</v>
       </c>
       <c r="AB275" s="10" t="s">
-        <v>5458</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="276" spans="1:42">
@@ -62254,10 +62465,10 @@
         <v>5112</v>
       </c>
       <c r="Q276" s="89" t="s">
-        <v>5464</v>
+        <v>5463</v>
       </c>
       <c r="R276" s="10" t="s">
-        <v>5458</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="277" spans="1:42">
@@ -62290,10 +62501,10 @@
         <v>4360</v>
       </c>
       <c r="K277" s="89" t="s">
-        <v>5464</v>
+        <v>5463</v>
       </c>
       <c r="L277" s="10" t="s">
-        <v>5458</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="278" spans="1:42">
@@ -62335,10 +62546,10 @@
         <v>5244</v>
       </c>
       <c r="O278" s="89" t="s">
-        <v>5464</v>
+        <v>5463</v>
       </c>
       <c r="P278" s="10" t="s">
-        <v>5458</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="279" spans="1:42">
@@ -62434,10 +62645,10 @@
         <v>5369</v>
       </c>
       <c r="AG279" s="89" t="s">
-        <v>5464</v>
+        <v>5463</v>
       </c>
       <c r="AH279" s="10" t="s">
-        <v>5458</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="280" spans="1:42">
@@ -62461,10 +62672,10 @@
         <v>5241</v>
       </c>
       <c r="K280" s="78" t="s">
+        <v>5458</v>
+      </c>
+      <c r="L280" s="10" t="s">
         <v>5459</v>
-      </c>
-      <c r="L280" s="10" t="s">
-        <v>5460</v>
       </c>
     </row>
     <row r="281" spans="1:42">
@@ -62488,10 +62699,10 @@
         <v>5241</v>
       </c>
       <c r="K281" s="78" t="s">
+        <v>5458</v>
+      </c>
+      <c r="L281" s="10" t="s">
         <v>5459</v>
-      </c>
-      <c r="L281" s="10" t="s">
-        <v>5460</v>
       </c>
     </row>
     <row r="282" spans="1:42">
@@ -62515,10 +62726,10 @@
         <v>5241</v>
       </c>
       <c r="K282" s="78" t="s">
+        <v>5458</v>
+      </c>
+      <c r="L282" s="10" t="s">
         <v>5459</v>
-      </c>
-      <c r="L282" s="10" t="s">
-        <v>5460</v>
       </c>
     </row>
     <row r="283" spans="1:42">
@@ -62611,16 +62822,16 @@
         <v>5343</v>
       </c>
       <c r="AE283" s="15" t="s">
+        <v>5482</v>
+      </c>
+      <c r="AG283" s="15" t="s">
         <v>5483</v>
       </c>
-      <c r="AG283" s="15" t="s">
-        <v>5484</v>
-      </c>
       <c r="AI283" s="89" t="s">
-        <v>5464</v>
+        <v>5463</v>
       </c>
       <c r="AJ283" s="10" t="s">
-        <v>5458</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="284" spans="1:42">
@@ -62740,10 +62951,10 @@
         <v>5297</v>
       </c>
       <c r="AO284" s="89" t="s">
-        <v>5464</v>
+        <v>5463</v>
       </c>
       <c r="AP284" s="10" t="s">
-        <v>5458</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="285" spans="1:42">
@@ -62766,11 +62977,11 @@
       <c r="F285" s="14" t="s">
         <v>5241</v>
       </c>
-      <c r="K285" s="78" t="s">
-        <v>5459</v>
+      <c r="K285" s="89" t="s">
+        <v>5514</v>
       </c>
       <c r="L285" s="10" t="s">
-        <v>5460</v>
+        <v>5515</v>
       </c>
     </row>
     <row r="286" spans="1:42">
@@ -62793,11 +63004,11 @@
       <c r="F286" s="14" t="s">
         <v>5241</v>
       </c>
-      <c r="K286" s="78" t="s">
-        <v>5459</v>
+      <c r="K286" s="89" t="s">
+        <v>5514</v>
       </c>
       <c r="L286" s="10" t="s">
-        <v>5460</v>
+        <v>5515</v>
       </c>
     </row>
     <row r="287" spans="1:42">
@@ -62854,16 +63065,16 @@
         <v>5380</v>
       </c>
       <c r="S287" t="s">
+        <v>5480</v>
+      </c>
+      <c r="U287" t="s">
         <v>5481</v>
       </c>
-      <c r="U287" t="s">
-        <v>5482</v>
-      </c>
       <c r="W287" s="89" t="s">
-        <v>5464</v>
+        <v>5463</v>
       </c>
       <c r="X287" s="10" t="s">
-        <v>5458</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="288" spans="1:42">
@@ -62887,13 +63098,13 @@
         <v>5241</v>
       </c>
       <c r="K288" s="89" t="s">
-        <v>5464</v>
+        <v>5514</v>
       </c>
       <c r="L288" s="10" t="s">
-        <v>5458</v>
-      </c>
-    </row>
-    <row r="289" spans="1:30">
+        <v>5515</v>
+      </c>
+    </row>
+    <row r="289" spans="1:38">
       <c r="A289" s="10" t="str">
         <f>IF(games!A289="", "", games!A289)</f>
         <v>信長 霸道</v>
@@ -62914,13 +63125,13 @@
         <v>5241</v>
       </c>
       <c r="K289" s="89" t="s">
-        <v>5464</v>
+        <v>5514</v>
       </c>
       <c r="L289" s="10" t="s">
-        <v>5458</v>
-      </c>
-    </row>
-    <row r="290" spans="1:30">
+        <v>5515</v>
+      </c>
+    </row>
+    <row r="290" spans="1:38">
       <c r="A290" s="10" t="str">
         <f>IF(games!A290="", "", games!A290)</f>
         <v>勇者前線Versus</v>
@@ -62941,13 +63152,13 @@
         <v>5241</v>
       </c>
       <c r="K290" s="89" t="s">
-        <v>5464</v>
+        <v>5514</v>
       </c>
       <c r="L290" s="10" t="s">
-        <v>5458</v>
-      </c>
-    </row>
-    <row r="291" spans="1:30">
+        <v>5515</v>
+      </c>
+    </row>
+    <row r="291" spans="1:38">
       <c r="A291" s="10" t="str">
         <f>IF(games!A291="", "", games!A291)</f>
         <v>幻域方舟</v>
@@ -62965,28 +63176,28 @@
         <v xml:space="preserve">台廠自製的ARPG《幻域方舟》終於上線了，號稱高自由度打擊感，但我們都知道，重點還是刷刷刷。與其花時間農素材，不如先上網搜刮最新的兌換碼和禮包碼。遊戲裡的禮包是不是又貴又坑？別擔心，聰明的玩家都懂用代儲值，享受快速安全的服務，用最少的錢拿到最多資源，這才是高人一等的玩法。 </v>
       </c>
       <c r="F291" s="14" t="s">
+        <v>5461</v>
+      </c>
+      <c r="G291" s="10" t="s">
+        <v>5460</v>
+      </c>
+      <c r="H291" s="10" t="s">
         <v>5462</v>
       </c>
-      <c r="G291" s="10" t="s">
-        <v>5461</v>
-      </c>
-      <c r="H291" s="10" t="s">
-        <v>5463</v>
-      </c>
       <c r="K291" s="78" t="s">
+        <v>5464</v>
+      </c>
+      <c r="L291" s="10" t="s">
         <v>5465</v>
       </c>
-      <c r="L291" s="10" t="s">
-        <v>5466</v>
-      </c>
       <c r="M291" s="89" t="s">
-        <v>5464</v>
+        <v>5514</v>
       </c>
       <c r="N291" s="10" t="s">
-        <v>5458</v>
-      </c>
-    </row>
-    <row r="292" spans="1:30">
+        <v>5515</v>
+      </c>
+    </row>
+    <row r="292" spans="1:38">
       <c r="A292" s="10" t="str">
         <f>IF(games!A292="", "", games!A292)</f>
         <v>開天</v>
@@ -63004,50 +63215,50 @@
         <v>又一款免洗武俠《開天》來了，看這名字就知道又是那套開局送VIP，戰力膨脹的套路。反正大家都是進來割草的，誰還在乎劇情？重點是福利！別忘了每天蹲點找兌換碼和禮包碼，能拿多少是多少。如果想當服霸，靠遊戲裡送的根本不夠，直接找代儲值才是捷徑，保證快速安全，讓你戰力飆升，霸服就是這麼簡單。</v>
       </c>
       <c r="F292" s="14" t="s">
+        <v>5474</v>
+      </c>
+      <c r="G292" s="10" t="s">
         <v>5475</v>
-      </c>
-      <c r="G292" s="10" t="s">
-        <v>5476</v>
       </c>
       <c r="H292" s="10" t="s">
         <v>2625</v>
       </c>
       <c r="K292" s="89" t="s">
+        <v>5466</v>
+      </c>
+      <c r="M292" s="15" t="s">
         <v>5467</v>
-      </c>
-      <c r="M292" s="15" t="s">
-        <v>5468</v>
       </c>
       <c r="N292" s="90"/>
       <c r="O292" s="15" t="s">
+        <v>5468</v>
+      </c>
+      <c r="Q292" s="15" t="s">
         <v>5469</v>
       </c>
-      <c r="Q292" s="15" t="s">
+      <c r="S292" s="15" t="s">
         <v>5470</v>
-      </c>
-      <c r="S292" s="15" t="s">
-        <v>5471</v>
       </c>
       <c r="U292" s="15" t="s">
         <v>1933</v>
       </c>
       <c r="W292" s="15" t="s">
+        <v>5471</v>
+      </c>
+      <c r="Y292" s="15" t="s">
         <v>5472</v>
       </c>
-      <c r="Y292" s="15" t="s">
+      <c r="AA292" s="15" t="s">
         <v>5473</v>
       </c>
-      <c r="AA292" s="15" t="s">
-        <v>5474</v>
-      </c>
       <c r="AC292" s="89" t="s">
-        <v>5464</v>
+        <v>5463</v>
       </c>
       <c r="AD292" s="10" t="s">
-        <v>5458</v>
-      </c>
-    </row>
-    <row r="293" spans="1:30">
+        <v>5457</v>
+      </c>
+    </row>
+    <row r="293" spans="1:38">
       <c r="A293" s="10" t="str">
         <f>IF(games!A293="", "", games!A293)</f>
         <v>人人有功練：腸仔江湖見</v>
@@ -63065,34 +63276,61 @@
         <v>《人人有功練：腸仔江湖見》這名字真是……有夠ㄎㄧㄤ。號稱躺著練功，我看是躺著儲值吧？這種放置遊戲，比的就是誰的資源多。開局先別急著衝，把所有兌換碼、禮包碼都輸入一遍才是正事。覺得官方送太少？想一步登天？內行的都知道找代儲值，保證快速安全，讓你用新台幣教訓那些無課玩家，輕鬆當大俠。</v>
       </c>
       <c r="F293" s="14" t="s">
+        <v>5474</v>
+      </c>
+      <c r="G293" s="10" t="s">
         <v>5475</v>
-      </c>
-      <c r="G293" s="10" t="s">
-        <v>5476</v>
       </c>
       <c r="H293" s="10" t="s">
         <v>2625</v>
       </c>
       <c r="K293" s="89" t="s">
+        <v>5476</v>
+      </c>
+      <c r="M293" s="15" t="s">
         <v>5477</v>
       </c>
-      <c r="M293" s="15" t="s">
+      <c r="O293" s="15" t="s">
         <v>5478</v>
       </c>
-      <c r="O293" s="15" t="s">
+      <c r="Q293" s="15" t="s">
         <v>5479</v>
       </c>
-      <c r="Q293" s="15" t="s">
-        <v>5480</v>
-      </c>
-      <c r="S293" s="89" t="s">
-        <v>5464</v>
-      </c>
-      <c r="T293" s="10" t="s">
-        <v>5458</v>
-      </c>
-    </row>
-    <row r="294" spans="1:30">
+      <c r="S293" s="15" t="s">
+        <v>5485</v>
+      </c>
+      <c r="U293" s="15" t="s">
+        <v>5294</v>
+      </c>
+      <c r="W293" s="15" t="s">
+        <v>1841</v>
+      </c>
+      <c r="Y293" s="15" t="s">
+        <v>5486</v>
+      </c>
+      <c r="AA293" s="15" t="s">
+        <v>5487</v>
+      </c>
+      <c r="AC293" s="15" t="s">
+        <v>2912</v>
+      </c>
+      <c r="AE293" s="15" t="s">
+        <v>5488</v>
+      </c>
+      <c r="AG293" s="15" t="s">
+        <v>5489</v>
+      </c>
+      <c r="AI293" s="15" t="s">
+        <v>5490</v>
+      </c>
+      <c r="AK293" s="89" t="s">
+        <v>5463</v>
+      </c>
+      <c r="AL293" s="10" t="s">
+        <v>5457</v>
+      </c>
+    </row>
+    <row r="294" spans="1:38">
       <c r="A294" s="10" t="str">
         <f>IF(games!A294="", "", games!A294)</f>
         <v>楓之谷：放置冒險記</v>
@@ -63113,13 +63351,13 @@
         <v>5241</v>
       </c>
       <c r="K294" s="89" t="s">
-        <v>5464</v>
+        <v>5514</v>
       </c>
       <c r="L294" s="10" t="s">
-        <v>5458</v>
-      </c>
-    </row>
-    <row r="295" spans="1:30">
+        <v>5515</v>
+      </c>
+    </row>
+    <row r="295" spans="1:38">
       <c r="A295" s="10" t="str">
         <f>IF(games!A295="", "", games!A295)</f>
         <v>Shiba Wars：Goddess Link TD</v>
@@ -63140,13 +63378,13 @@
         <v>5241</v>
       </c>
       <c r="K295" s="89" t="s">
-        <v>5464</v>
+        <v>5514</v>
       </c>
       <c r="L295" s="10" t="s">
-        <v>5458</v>
-      </c>
-    </row>
-    <row r="296" spans="1:30">
+        <v>5515</v>
+      </c>
+    </row>
+    <row r="296" spans="1:38">
       <c r="A296" s="10" t="str">
         <f>IF(games!A296="", "", games!A296)</f>
         <v>熱血江湖：福利加強版</v>
@@ -63164,37 +63402,97 @@
         <v>經典老IP《熱血江湖》又來了，還自稱「福利加強版」，真是此地無銀三百兩。福利再加強，有比得上課金嗎？新手們別傻了，乖乖上網找最新的兌換碼、禮包碼才是真的。想在正邪大戰中出人頭地？靠官方福利你只能當砲灰。快找代儲值服務，快速安全幫你一步到位，直接+15神裝，重溫當年的課金霸主快感！</v>
       </c>
       <c r="F296" s="14" t="s">
-        <v>5241</v>
+        <v>5511</v>
+      </c>
+      <c r="G296" s="10" t="s">
+        <v>5512</v>
+      </c>
+      <c r="H296" s="10" t="s">
+        <v>2625</v>
       </c>
       <c r="K296" s="91" t="s">
-        <v>5485</v>
+        <v>5484</v>
+      </c>
+      <c r="L296" s="10" t="s">
+        <v>5513</v>
       </c>
       <c r="M296" s="89" t="s">
-        <v>5464</v>
+        <v>5514</v>
       </c>
       <c r="N296" s="10" t="s">
-        <v>5458</v>
-      </c>
-    </row>
-    <row r="297" spans="1:30">
+        <v>5515</v>
+      </c>
+    </row>
+    <row r="297" spans="1:38">
       <c r="A297" s="10" t="str">
         <f>IF(games!A297="", "", games!A297)</f>
-        <v/>
+        <v>熱血主公Go!</v>
       </c>
       <c r="C297" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>giftcodesbanner/熱血主公Go!-禮包碼.jpg</v>
       </c>
       <c r="D297" s="10" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=熱血主公Go!</v>
       </c>
       <c r="E297" s="11" t="str">
         <f>IF(games!I297&lt;&gt;"", games!I297, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="1:30">
+        <v>《熱血主公Go!》是一款結合Roguelike培育、RPG冒險與街機動作元素的三國手遊。玩家將扮演主公，踏上匡扶漢室的征途，招募趙雲、呂布等傳奇名將。遊戲主打懷舊街機畫風與隨機流派組合，戰鬥體驗絕不重複！官方不斷釋出最新的兌換碼與禮包碼，讓玩家輕鬆升級。若想快速提升戰力，尋找代儲值服務也是一種選擇，務必確保快速安全，避免受騙。立即加入，體驗放置休閒與熱血PVP對戰的雙重樂趣！</v>
+      </c>
+      <c r="F297" s="31" t="s">
+        <v>5500</v>
+      </c>
+      <c r="G297" s="10" t="s">
+        <v>5501</v>
+      </c>
+      <c r="H297" s="10" t="s">
+        <v>2625</v>
+      </c>
+      <c r="K297" s="14" t="s">
+        <v>5499</v>
+      </c>
+      <c r="L297" s="10" t="s">
+        <v>5513</v>
+      </c>
+      <c r="M297" s="10" t="s">
+        <v>5494</v>
+      </c>
+      <c r="N297" s="10" t="s">
+        <v>5513</v>
+      </c>
+      <c r="O297" s="15" t="s">
+        <v>5495</v>
+      </c>
+      <c r="P297" s="10" t="s">
+        <v>5513</v>
+      </c>
+      <c r="Q297" s="15" t="s">
+        <v>5496</v>
+      </c>
+      <c r="R297" s="10" t="s">
+        <v>5513</v>
+      </c>
+      <c r="S297" s="15" t="s">
+        <v>5497</v>
+      </c>
+      <c r="T297" s="10" t="s">
+        <v>5513</v>
+      </c>
+      <c r="U297" s="15" t="s">
+        <v>5498</v>
+      </c>
+      <c r="V297" s="10" t="s">
+        <v>5513</v>
+      </c>
+      <c r="W297" s="89" t="s">
+        <v>5514</v>
+      </c>
+      <c r="X297" s="10" t="s">
+        <v>5515</v>
+      </c>
+    </row>
+    <row r="298" spans="1:38">
       <c r="A298" s="10" t="str">
         <f>IF(games!A298="", "", games!A298)</f>
         <v/>
@@ -63212,7 +63510,7 @@
         <v/>
       </c>
     </row>
-    <row r="299" spans="1:30">
+    <row r="299" spans="1:38">
       <c r="A299" s="10" t="str">
         <f>IF(games!A299="", "", games!A299)</f>
         <v/>
@@ -63230,7 +63528,7 @@
         <v/>
       </c>
     </row>
-    <row r="300" spans="1:30">
+    <row r="300" spans="1:38">
       <c r="A300" s="10" t="str">
         <f>IF(games!A300="", "", games!A300)</f>
         <v/>
@@ -63248,7 +63546,7 @@
         <v/>
       </c>
     </row>
-    <row r="301" spans="1:30">
+    <row r="301" spans="1:38">
       <c r="A301" s="10" t="str">
         <f>IF(games!A301="", "", games!A301)</f>
         <v/>
@@ -63266,7 +63564,7 @@
         <v/>
       </c>
     </row>
-    <row r="302" spans="1:30">
+    <row r="302" spans="1:38">
       <c r="A302" s="10" t="str">
         <f>IF(games!A302="", "", games!A302)</f>
         <v/>
@@ -63284,11 +63582,7 @@
         <v/>
       </c>
     </row>
-    <row r="303" spans="1:30">
-      <c r="A303" s="10" t="str">
-        <f>IF(games!A303="", "", games!A303)</f>
-        <v/>
-      </c>
+    <row r="303" spans="1:38">
       <c r="C303" s="10" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -63302,7 +63596,7 @@
         <v/>
       </c>
     </row>
-    <row r="304" spans="1:30">
+    <row r="304" spans="1:38">
       <c r="C304" s="10" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -63416,11 +63710,11 @@
     </row>
     <row r="312" spans="3:5">
       <c r="C312" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="C312:C375" si="14">IF(A312="","", "giftcodesbanner/" &amp; A312 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D312" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="D312:D375" si="15">IF(A312="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A312)</f>
         <v/>
       </c>
       <c r="E312" s="11" t="str">
@@ -63430,11 +63724,11 @@
     </row>
     <row r="313" spans="3:5">
       <c r="C313" s="10" t="str">
-        <f t="shared" ref="C313:C376" si="14">IF(A313="","", "giftcodesbanner/" &amp; A313 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="D313" s="10" t="str">
-        <f t="shared" ref="D313:D376" si="15">IF(A313="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A313)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="E313" s="11" t="str">
@@ -64312,11 +64606,11 @@
     </row>
     <row r="376" spans="3:5">
       <c r="C376" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="C376:C434" si="16">IF(A376="","", "giftcodesbanner/" &amp; A376 &amp; "-禮包碼.jpg")</f>
         <v/>
       </c>
       <c r="D376" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="D376:D434" si="17">IF(A376="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A376)</f>
         <v/>
       </c>
       <c r="E376" s="11" t="str">
@@ -64326,11 +64620,11 @@
     </row>
     <row r="377" spans="3:5">
       <c r="C377" s="10" t="str">
-        <f t="shared" ref="C377:C435" si="16">IF(A377="","", "giftcodesbanner/" &amp; A377 &amp; "-禮包碼.jpg")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D377" s="10" t="str">
-        <f t="shared" ref="D377:D435" si="17">IF(A377="","", "https://www.ssbuy.tw/gift-codes.html?game="&amp;A377)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E377" s="11" t="str">
@@ -64641,10 +64935,6 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E399" s="11" t="str">
-        <f>IF(games!I399&lt;&gt;"", games!I399, "")</f>
-        <v/>
-      </c>
     </row>
     <row r="400" spans="3:5">
       <c r="C400" s="10" t="str">
@@ -64992,16 +65282,6 @@
         <v/>
       </c>
       <c r="D434" s="10" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="435" spans="3:4">
-      <c r="C435" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="D435" s="10" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -65018,28 +65298,29 @@
     <hyperlink ref="K280" r:id="rId7"/>
     <hyperlink ref="K281" r:id="rId8"/>
     <hyperlink ref="K282" r:id="rId9"/>
-    <hyperlink ref="K285" r:id="rId10"/>
-    <hyperlink ref="K286" r:id="rId11"/>
-    <hyperlink ref="M291" r:id="rId12"/>
-    <hyperlink ref="K288" r:id="rId13"/>
-    <hyperlink ref="K289" r:id="rId14"/>
-    <hyperlink ref="K290" r:id="rId15"/>
-    <hyperlink ref="K294" r:id="rId16"/>
-    <hyperlink ref="K295" r:id="rId17"/>
-    <hyperlink ref="M296" r:id="rId18"/>
-    <hyperlink ref="AC292" r:id="rId19"/>
-    <hyperlink ref="S293" r:id="rId20"/>
-    <hyperlink ref="W287" r:id="rId21"/>
-    <hyperlink ref="AO284" r:id="rId22"/>
-    <hyperlink ref="AI283" r:id="rId23"/>
-    <hyperlink ref="AG279" r:id="rId24"/>
-    <hyperlink ref="O278" r:id="rId25"/>
-    <hyperlink ref="K277" r:id="rId26"/>
-    <hyperlink ref="Q276" r:id="rId27"/>
-    <hyperlink ref="AA275" r:id="rId28"/>
-    <hyperlink ref="Q274" r:id="rId29"/>
+    <hyperlink ref="AC292" r:id="rId10"/>
+    <hyperlink ref="AK293" r:id="rId11"/>
+    <hyperlink ref="W287" r:id="rId12"/>
+    <hyperlink ref="AO284" r:id="rId13"/>
+    <hyperlink ref="AI283" r:id="rId14"/>
+    <hyperlink ref="AG279" r:id="rId15"/>
+    <hyperlink ref="O278" r:id="rId16"/>
+    <hyperlink ref="K277" r:id="rId17"/>
+    <hyperlink ref="Q276" r:id="rId18"/>
+    <hyperlink ref="AA275" r:id="rId19"/>
+    <hyperlink ref="Q274" r:id="rId20"/>
+    <hyperlink ref="W297" r:id="rId21"/>
+    <hyperlink ref="M296" r:id="rId22"/>
+    <hyperlink ref="K295" r:id="rId23"/>
+    <hyperlink ref="K294" r:id="rId24"/>
+    <hyperlink ref="M291" r:id="rId25"/>
+    <hyperlink ref="K290" r:id="rId26"/>
+    <hyperlink ref="K289" r:id="rId27"/>
+    <hyperlink ref="K288" r:id="rId28"/>
+    <hyperlink ref="K285" r:id="rId29"/>
+    <hyperlink ref="K286" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId30"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>
 </worksheet>
 </file>
--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -20959,10 +20959,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>熱血主公Go!</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://play.google.com/store/apps/details?id=com.furywing.rxzggo.free&amp;fbclid=IwY2xjawN6lllleHRuA2FlbQIxMABicmlkETF4Z01XclVaSjJuNzRmRmVnc3J0YwZhcHBfaWQQMjIyMDM5MTc4ODIwMDg5MgABHl-Zq6JKMWFJ470D5XHqwMKfpCTTfCQhB2c-G4zkH_T7ZHL2tVY-tMx3tMJE_aem_HV89nRhsIdGCR2vehyIo7w</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -21006,6 +21002,10 @@
   </si>
   <si>
     <t>LINE ID：@ssbuy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>熱血主公Go</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -42604,7 +42604,7 @@
     </row>
     <row r="297" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A297" s="37" t="s">
-        <v>5502</v>
+        <v>5515</v>
       </c>
       <c r="C297" s="37" t="s">
         <v>5492</v>
@@ -42617,17 +42617,17 @@
       </c>
       <c r="F297" s="37" t="str">
         <f t="shared" si="12"/>
-        <v>gift-codes.html?game=熱血主公Go!</v>
+        <v>gift-codes.html?game=熱血主公Go</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>5503</v>
+        <v>5502</v>
       </c>
       <c r="H297" s="38" t="str">
         <f t="shared" si="13"/>
-        <v>https://www.ssbuy.tw/game-detail.html?game=熱血主公Go!</v>
+        <v>https://www.ssbuy.tw/game-detail.html?game=熱血主公Go</v>
       </c>
       <c r="I297" s="39" t="s">
-        <v>5504</v>
+        <v>5503</v>
       </c>
       <c r="J297" s="2" t="s">
         <v>5427</v>
@@ -42636,37 +42636,37 @@
         <v>5258</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>5505</v>
+        <v>5504</v>
       </c>
       <c r="M297" s="59">
         <v>2511</v>
       </c>
       <c r="N297" s="1" t="s">
-        <v>5506</v>
+        <v>5505</v>
       </c>
       <c r="O297" s="59">
         <v>1275</v>
       </c>
       <c r="P297" s="1" t="s">
-        <v>5507</v>
+        <v>5506</v>
       </c>
       <c r="Q297" s="59">
         <v>855</v>
       </c>
       <c r="R297" s="1" t="s">
-        <v>5508</v>
+        <v>5507</v>
       </c>
       <c r="S297" s="59">
         <v>423</v>
       </c>
       <c r="T297" s="1" t="s">
-        <v>5509</v>
+        <v>5508</v>
       </c>
       <c r="U297" s="59">
         <v>153</v>
       </c>
       <c r="V297" s="1" t="s">
-        <v>5510</v>
+        <v>5509</v>
       </c>
       <c r="W297" s="59">
         <v>31</v>
@@ -62978,10 +62978,10 @@
         <v>5241</v>
       </c>
       <c r="K285" s="89" t="s">
+        <v>5513</v>
+      </c>
+      <c r="L285" s="10" t="s">
         <v>5514</v>
-      </c>
-      <c r="L285" s="10" t="s">
-        <v>5515</v>
       </c>
     </row>
     <row r="286" spans="1:42">
@@ -63005,10 +63005,10 @@
         <v>5241</v>
       </c>
       <c r="K286" s="89" t="s">
+        <v>5513</v>
+      </c>
+      <c r="L286" s="10" t="s">
         <v>5514</v>
-      </c>
-      <c r="L286" s="10" t="s">
-        <v>5515</v>
       </c>
     </row>
     <row r="287" spans="1:42">
@@ -63098,10 +63098,10 @@
         <v>5241</v>
       </c>
       <c r="K288" s="89" t="s">
+        <v>5513</v>
+      </c>
+      <c r="L288" s="10" t="s">
         <v>5514</v>
-      </c>
-      <c r="L288" s="10" t="s">
-        <v>5515</v>
       </c>
     </row>
     <row r="289" spans="1:38">
@@ -63125,10 +63125,10 @@
         <v>5241</v>
       </c>
       <c r="K289" s="89" t="s">
+        <v>5513</v>
+      </c>
+      <c r="L289" s="10" t="s">
         <v>5514</v>
-      </c>
-      <c r="L289" s="10" t="s">
-        <v>5515</v>
       </c>
     </row>
     <row r="290" spans="1:38">
@@ -63152,10 +63152,10 @@
         <v>5241</v>
       </c>
       <c r="K290" s="89" t="s">
+        <v>5513</v>
+      </c>
+      <c r="L290" s="10" t="s">
         <v>5514</v>
-      </c>
-      <c r="L290" s="10" t="s">
-        <v>5515</v>
       </c>
     </row>
     <row r="291" spans="1:38">
@@ -63191,10 +63191,10 @@
         <v>5465</v>
       </c>
       <c r="M291" s="89" t="s">
+        <v>5513</v>
+      </c>
+      <c r="N291" s="10" t="s">
         <v>5514</v>
-      </c>
-      <c r="N291" s="10" t="s">
-        <v>5515</v>
       </c>
     </row>
     <row r="292" spans="1:38">
@@ -63351,10 +63351,10 @@
         <v>5241</v>
       </c>
       <c r="K294" s="89" t="s">
+        <v>5513</v>
+      </c>
+      <c r="L294" s="10" t="s">
         <v>5514</v>
-      </c>
-      <c r="L294" s="10" t="s">
-        <v>5515</v>
       </c>
     </row>
     <row r="295" spans="1:38">
@@ -63378,10 +63378,10 @@
         <v>5241</v>
       </c>
       <c r="K295" s="89" t="s">
+        <v>5513</v>
+      </c>
+      <c r="L295" s="10" t="s">
         <v>5514</v>
-      </c>
-      <c r="L295" s="10" t="s">
-        <v>5515</v>
       </c>
     </row>
     <row r="296" spans="1:38">
@@ -63402,10 +63402,10 @@
         <v>經典老IP《熱血江湖》又來了，還自稱「福利加強版」，真是此地無銀三百兩。福利再加強，有比得上課金嗎？新手們別傻了，乖乖上網找最新的兌換碼、禮包碼才是真的。想在正邪大戰中出人頭地？靠官方福利你只能當砲灰。快找代儲值服務，快速安全幫你一步到位，直接+15神裝，重溫當年的課金霸主快感！</v>
       </c>
       <c r="F296" s="14" t="s">
+        <v>5510</v>
+      </c>
+      <c r="G296" s="10" t="s">
         <v>5511</v>
-      </c>
-      <c r="G296" s="10" t="s">
-        <v>5512</v>
       </c>
       <c r="H296" s="10" t="s">
         <v>2625</v>
@@ -63414,27 +63414,27 @@
         <v>5484</v>
       </c>
       <c r="L296" s="10" t="s">
+        <v>5512</v>
+      </c>
+      <c r="M296" s="89" t="s">
         <v>5513</v>
       </c>
-      <c r="M296" s="89" t="s">
+      <c r="N296" s="10" t="s">
         <v>5514</v>
-      </c>
-      <c r="N296" s="10" t="s">
-        <v>5515</v>
       </c>
     </row>
     <row r="297" spans="1:38">
       <c r="A297" s="10" t="str">
         <f>IF(games!A297="", "", games!A297)</f>
-        <v>熱血主公Go!</v>
+        <v>熱血主公Go</v>
       </c>
       <c r="C297" s="10" t="str">
         <f t="shared" si="12"/>
-        <v>giftcodesbanner/熱血主公Go!-禮包碼.jpg</v>
+        <v>giftcodesbanner/熱血主公Go-禮包碼.jpg</v>
       </c>
       <c r="D297" s="10" t="str">
         <f t="shared" si="13"/>
-        <v>https://www.ssbuy.tw/gift-codes.html?game=熱血主公Go!</v>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=熱血主公Go</v>
       </c>
       <c r="E297" s="11" t="str">
         <f>IF(games!I297&lt;&gt;"", games!I297, "")</f>
@@ -63453,43 +63453,43 @@
         <v>5499</v>
       </c>
       <c r="L297" s="10" t="s">
-        <v>5513</v>
+        <v>5512</v>
       </c>
       <c r="M297" s="10" t="s">
         <v>5494</v>
       </c>
       <c r="N297" s="10" t="s">
-        <v>5513</v>
+        <v>5512</v>
       </c>
       <c r="O297" s="15" t="s">
         <v>5495</v>
       </c>
       <c r="P297" s="10" t="s">
-        <v>5513</v>
+        <v>5512</v>
       </c>
       <c r="Q297" s="15" t="s">
         <v>5496</v>
       </c>
       <c r="R297" s="10" t="s">
-        <v>5513</v>
+        <v>5512</v>
       </c>
       <c r="S297" s="15" t="s">
         <v>5497</v>
       </c>
       <c r="T297" s="10" t="s">
-        <v>5513</v>
+        <v>5512</v>
       </c>
       <c r="U297" s="15" t="s">
         <v>5498</v>
       </c>
       <c r="V297" s="10" t="s">
+        <v>5512</v>
+      </c>
+      <c r="W297" s="89" t="s">
         <v>5513</v>
       </c>
-      <c r="W297" s="89" t="s">
+      <c r="X297" s="10" t="s">
         <v>5514</v>
-      </c>
-      <c r="X297" s="10" t="s">
-        <v>5515</v>
       </c>
     </row>
     <row r="298" spans="1:38">

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8112" uniqueCount="5516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8131" uniqueCount="5536">
   <si>
     <t>Facebook</t>
   </si>
@@ -20891,9 +20891,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>LC3529</t>
-  </si>
-  <si>
     <t>VIP666</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -21006,6 +21003,90 @@
   </si>
   <si>
     <t>熱血主公Go</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HOT500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HOT666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HOT777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HOT888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HOT999</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSSVIP666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSSVIP777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSSVIP888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSSVIP999</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>yuanbao666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>JIMMY888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SQDN1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SQDN2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SQDN3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SQDN7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KK877</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LAUNCH88</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>開天1104</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>瑤瑤win</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>applewin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WEEK2A</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -42528,7 +42609,7 @@
         <v>5409</v>
       </c>
       <c r="D296" s="38" t="s">
-        <v>5491</v>
+        <v>5490</v>
       </c>
       <c r="E296" s="38" t="s">
         <v>5410</v>
@@ -42604,30 +42685,30 @@
     </row>
     <row r="297" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A297" s="37" t="s">
-        <v>5515</v>
+        <v>5514</v>
       </c>
       <c r="C297" s="37" t="s">
+        <v>5491</v>
+      </c>
+      <c r="D297" s="37" t="s">
+        <v>5491</v>
+      </c>
+      <c r="E297" s="38" t="s">
         <v>5492</v>
-      </c>
-      <c r="D297" s="37" t="s">
-        <v>5492</v>
-      </c>
-      <c r="E297" s="38" t="s">
-        <v>5493</v>
       </c>
       <c r="F297" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=熱血主公Go</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>5502</v>
+        <v>5501</v>
       </c>
       <c r="H297" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=熱血主公Go</v>
       </c>
       <c r="I297" s="39" t="s">
-        <v>5503</v>
+        <v>5502</v>
       </c>
       <c r="J297" s="2" t="s">
         <v>5427</v>
@@ -42636,37 +42717,37 @@
         <v>5258</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>5504</v>
+        <v>5503</v>
       </c>
       <c r="M297" s="59">
         <v>2511</v>
       </c>
       <c r="N297" s="1" t="s">
-        <v>5505</v>
+        <v>5504</v>
       </c>
       <c r="O297" s="59">
         <v>1275</v>
       </c>
       <c r="P297" s="1" t="s">
-        <v>5506</v>
+        <v>5505</v>
       </c>
       <c r="Q297" s="59">
         <v>855</v>
       </c>
       <c r="R297" s="1" t="s">
-        <v>5507</v>
+        <v>5506</v>
       </c>
       <c r="S297" s="59">
         <v>423</v>
       </c>
       <c r="T297" s="1" t="s">
-        <v>5508</v>
+        <v>5507</v>
       </c>
       <c r="U297" s="59">
         <v>153</v>
       </c>
       <c r="V297" s="1" t="s">
-        <v>5509</v>
+        <v>5508</v>
       </c>
       <c r="W297" s="59">
         <v>31</v>
@@ -62978,10 +63059,10 @@
         <v>5241</v>
       </c>
       <c r="K285" s="89" t="s">
+        <v>5512</v>
+      </c>
+      <c r="L285" s="10" t="s">
         <v>5513</v>
-      </c>
-      <c r="L285" s="10" t="s">
-        <v>5514</v>
       </c>
     </row>
     <row r="286" spans="1:42">
@@ -63005,10 +63086,10 @@
         <v>5241</v>
       </c>
       <c r="K286" s="89" t="s">
+        <v>5512</v>
+      </c>
+      <c r="L286" s="10" t="s">
         <v>5513</v>
-      </c>
-      <c r="L286" s="10" t="s">
-        <v>5514</v>
       </c>
     </row>
     <row r="287" spans="1:42">
@@ -63098,13 +63179,13 @@
         <v>5241</v>
       </c>
       <c r="K288" s="89" t="s">
+        <v>5512</v>
+      </c>
+      <c r="L288" s="10" t="s">
         <v>5513</v>
       </c>
-      <c r="L288" s="10" t="s">
-        <v>5514</v>
-      </c>
-    </row>
-    <row r="289" spans="1:38">
+    </row>
+    <row r="289" spans="1:49">
       <c r="A289" s="10" t="str">
         <f>IF(games!A289="", "", games!A289)</f>
         <v>信長 霸道</v>
@@ -63125,13 +63206,13 @@
         <v>5241</v>
       </c>
       <c r="K289" s="89" t="s">
+        <v>5512</v>
+      </c>
+      <c r="L289" s="10" t="s">
         <v>5513</v>
       </c>
-      <c r="L289" s="10" t="s">
-        <v>5514</v>
-      </c>
-    </row>
-    <row r="290" spans="1:38">
+    </row>
+    <row r="290" spans="1:49">
       <c r="A290" s="10" t="str">
         <f>IF(games!A290="", "", games!A290)</f>
         <v>勇者前線Versus</v>
@@ -63152,13 +63233,13 @@
         <v>5241</v>
       </c>
       <c r="K290" s="89" t="s">
+        <v>5512</v>
+      </c>
+      <c r="L290" s="10" t="s">
         <v>5513</v>
       </c>
-      <c r="L290" s="10" t="s">
-        <v>5514</v>
-      </c>
-    </row>
-    <row r="291" spans="1:38">
+    </row>
+    <row r="291" spans="1:49">
       <c r="A291" s="10" t="str">
         <f>IF(games!A291="", "", games!A291)</f>
         <v>幻域方舟</v>
@@ -63191,13 +63272,19 @@
         <v>5465</v>
       </c>
       <c r="M291" s="89" t="s">
+        <v>5512</v>
+      </c>
+      <c r="N291" s="10" t="s">
         <v>5513</v>
       </c>
-      <c r="N291" s="10" t="s">
-        <v>5514</v>
-      </c>
-    </row>
-    <row r="292" spans="1:38">
+      <c r="AC291" s="89" t="s">
+        <v>5463</v>
+      </c>
+      <c r="AD291" s="10" t="s">
+        <v>5457</v>
+      </c>
+    </row>
+    <row r="292" spans="1:49">
       <c r="A292" s="10" t="str">
         <f>IF(games!A292="", "", games!A292)</f>
         <v>開天</v>
@@ -63251,14 +63338,41 @@
       <c r="AA292" s="15" t="s">
         <v>5473</v>
       </c>
-      <c r="AC292" s="89" t="s">
-        <v>5463</v>
-      </c>
-      <c r="AD292" s="10" t="s">
-        <v>5457</v>
-      </c>
-    </row>
-    <row r="293" spans="1:38">
+      <c r="AC292" s="15" t="s">
+        <v>5525</v>
+      </c>
+      <c r="AE292" s="15" t="s">
+        <v>5526</v>
+      </c>
+      <c r="AG292" s="15" t="s">
+        <v>5527</v>
+      </c>
+      <c r="AI292" s="15" t="s">
+        <v>5528</v>
+      </c>
+      <c r="AK292" s="15" t="s">
+        <v>5529</v>
+      </c>
+      <c r="AM292" s="15" t="s">
+        <v>5530</v>
+      </c>
+      <c r="AO292" s="15" t="s">
+        <v>5531</v>
+      </c>
+      <c r="AQ292" s="15" t="s">
+        <v>5532</v>
+      </c>
+      <c r="AS292" s="15" t="s">
+        <v>5533</v>
+      </c>
+      <c r="AU292" s="15" t="s">
+        <v>5534</v>
+      </c>
+      <c r="AW292" s="15" t="s">
+        <v>5535</v>
+      </c>
+    </row>
+    <row r="293" spans="1:49">
       <c r="A293" s="10" t="str">
         <f>IF(games!A293="", "", games!A293)</f>
         <v>人人有功練：腸仔江湖見</v>
@@ -63297,7 +63411,7 @@
         <v>5479</v>
       </c>
       <c r="S293" s="15" t="s">
-        <v>5485</v>
+        <v>5484</v>
       </c>
       <c r="U293" s="15" t="s">
         <v>5294</v>
@@ -63306,22 +63420,22 @@
         <v>1841</v>
       </c>
       <c r="Y293" s="15" t="s">
+        <v>5485</v>
+      </c>
+      <c r="AA293" s="15" t="s">
         <v>5486</v>
-      </c>
-      <c r="AA293" s="15" t="s">
-        <v>5487</v>
       </c>
       <c r="AC293" s="15" t="s">
         <v>2912</v>
       </c>
       <c r="AE293" s="15" t="s">
+        <v>5487</v>
+      </c>
+      <c r="AG293" s="15" t="s">
         <v>5488</v>
       </c>
-      <c r="AG293" s="15" t="s">
+      <c r="AI293" s="15" t="s">
         <v>5489</v>
-      </c>
-      <c r="AI293" s="15" t="s">
-        <v>5490</v>
       </c>
       <c r="AK293" s="89" t="s">
         <v>5463</v>
@@ -63330,7 +63444,7 @@
         <v>5457</v>
       </c>
     </row>
-    <row r="294" spans="1:38">
+    <row r="294" spans="1:49">
       <c r="A294" s="10" t="str">
         <f>IF(games!A294="", "", games!A294)</f>
         <v>楓之谷：放置冒險記</v>
@@ -63351,13 +63465,13 @@
         <v>5241</v>
       </c>
       <c r="K294" s="89" t="s">
+        <v>5512</v>
+      </c>
+      <c r="L294" s="10" t="s">
         <v>5513</v>
       </c>
-      <c r="L294" s="10" t="s">
-        <v>5514</v>
-      </c>
-    </row>
-    <row r="295" spans="1:38">
+    </row>
+    <row r="295" spans="1:49">
       <c r="A295" s="10" t="str">
         <f>IF(games!A295="", "", games!A295)</f>
         <v>Shiba Wars：Goddess Link TD</v>
@@ -63378,13 +63492,13 @@
         <v>5241</v>
       </c>
       <c r="K295" s="89" t="s">
+        <v>5512</v>
+      </c>
+      <c r="L295" s="10" t="s">
         <v>5513</v>
       </c>
-      <c r="L295" s="10" t="s">
-        <v>5514</v>
-      </c>
-    </row>
-    <row r="296" spans="1:38">
+    </row>
+    <row r="296" spans="1:49">
       <c r="A296" s="10" t="str">
         <f>IF(games!A296="", "", games!A296)</f>
         <v>熱血江湖：福利加強版</v>
@@ -63402,28 +63516,61 @@
         <v>經典老IP《熱血江湖》又來了，還自稱「福利加強版」，真是此地無銀三百兩。福利再加強，有比得上課金嗎？新手們別傻了，乖乖上網找最新的兌換碼、禮包碼才是真的。想在正邪大戰中出人頭地？靠官方福利你只能當砲灰。快找代儲值服務，快速安全幫你一步到位，直接+15神裝，重溫當年的課金霸主快感！</v>
       </c>
       <c r="F296" s="14" t="s">
+        <v>5509</v>
+      </c>
+      <c r="G296" s="10" t="s">
         <v>5510</v>
-      </c>
-      <c r="G296" s="10" t="s">
-        <v>5511</v>
       </c>
       <c r="H296" s="10" t="s">
         <v>2625</v>
       </c>
-      <c r="K296" s="91" t="s">
-        <v>5484</v>
-      </c>
-      <c r="L296" s="10" t="s">
+      <c r="K296" s="91">
+        <v>666666</v>
+      </c>
+      <c r="M296" s="15">
+        <v>777777</v>
+      </c>
+      <c r="O296" s="15">
+        <v>888888</v>
+      </c>
+      <c r="Q296" s="15" t="s">
+        <v>5515</v>
+      </c>
+      <c r="S296" s="15" t="s">
+        <v>5516</v>
+      </c>
+      <c r="U296" s="15" t="s">
+        <v>5517</v>
+      </c>
+      <c r="W296" s="15" t="s">
+        <v>5518</v>
+      </c>
+      <c r="Y296" s="15" t="s">
+        <v>5519</v>
+      </c>
+      <c r="AA296" s="15" t="s">
+        <v>5520</v>
+      </c>
+      <c r="AC296" s="15" t="s">
+        <v>5521</v>
+      </c>
+      <c r="AE296" s="15" t="s">
+        <v>5522</v>
+      </c>
+      <c r="AG296" s="15" t="s">
+        <v>5523</v>
+      </c>
+      <c r="AI296" s="15" t="s">
+        <v>5524</v>
+      </c>
+      <c r="AK296" s="89" t="s">
         <v>5512</v>
       </c>
-      <c r="M296" s="89" t="s">
+      <c r="AL296" s="10" t="s">
         <v>5513</v>
       </c>
-      <c r="N296" s="10" t="s">
-        <v>5514</v>
-      </c>
-    </row>
-    <row r="297" spans="1:38">
+    </row>
+    <row r="297" spans="1:49">
       <c r="A297" s="10" t="str">
         <f>IF(games!A297="", "", games!A297)</f>
         <v>熱血主公Go</v>
@@ -63441,58 +63588,58 @@
         <v>《熱血主公Go!》是一款結合Roguelike培育、RPG冒險與街機動作元素的三國手遊。玩家將扮演主公，踏上匡扶漢室的征途，招募趙雲、呂布等傳奇名將。遊戲主打懷舊街機畫風與隨機流派組合，戰鬥體驗絕不重複！官方不斷釋出最新的兌換碼與禮包碼，讓玩家輕鬆升級。若想快速提升戰力，尋找代儲值服務也是一種選擇，務必確保快速安全，避免受騙。立即加入，體驗放置休閒與熱血PVP對戰的雙重樂趣！</v>
       </c>
       <c r="F297" s="31" t="s">
+        <v>5499</v>
+      </c>
+      <c r="G297" s="10" t="s">
         <v>5500</v>
-      </c>
-      <c r="G297" s="10" t="s">
-        <v>5501</v>
       </c>
       <c r="H297" s="10" t="s">
         <v>2625</v>
       </c>
       <c r="K297" s="14" t="s">
-        <v>5499</v>
+        <v>5498</v>
       </c>
       <c r="L297" s="10" t="s">
+        <v>5511</v>
+      </c>
+      <c r="M297" s="10" t="s">
+        <v>5493</v>
+      </c>
+      <c r="N297" s="10" t="s">
+        <v>5511</v>
+      </c>
+      <c r="O297" s="15" t="s">
+        <v>5494</v>
+      </c>
+      <c r="P297" s="10" t="s">
+        <v>5511</v>
+      </c>
+      <c r="Q297" s="15" t="s">
+        <v>5495</v>
+      </c>
+      <c r="R297" s="10" t="s">
+        <v>5511</v>
+      </c>
+      <c r="S297" s="15" t="s">
+        <v>5496</v>
+      </c>
+      <c r="T297" s="10" t="s">
+        <v>5511</v>
+      </c>
+      <c r="U297" s="15" t="s">
+        <v>5497</v>
+      </c>
+      <c r="V297" s="10" t="s">
+        <v>5511</v>
+      </c>
+      <c r="W297" s="89" t="s">
         <v>5512</v>
       </c>
-      <c r="M297" s="10" t="s">
-        <v>5494</v>
-      </c>
-      <c r="N297" s="10" t="s">
-        <v>5512</v>
-      </c>
-      <c r="O297" s="15" t="s">
-        <v>5495</v>
-      </c>
-      <c r="P297" s="10" t="s">
-        <v>5512</v>
-      </c>
-      <c r="Q297" s="15" t="s">
-        <v>5496</v>
-      </c>
-      <c r="R297" s="10" t="s">
-        <v>5512</v>
-      </c>
-      <c r="S297" s="15" t="s">
-        <v>5497</v>
-      </c>
-      <c r="T297" s="10" t="s">
-        <v>5512</v>
-      </c>
-      <c r="U297" s="15" t="s">
-        <v>5498</v>
-      </c>
-      <c r="V297" s="10" t="s">
-        <v>5512</v>
-      </c>
-      <c r="W297" s="89" t="s">
+      <c r="X297" s="10" t="s">
         <v>5513</v>
       </c>
-      <c r="X297" s="10" t="s">
-        <v>5514</v>
-      </c>
-    </row>
-    <row r="298" spans="1:38">
+    </row>
+    <row r="298" spans="1:49">
       <c r="A298" s="10" t="str">
         <f>IF(games!A298="", "", games!A298)</f>
         <v/>
@@ -63509,8 +63656,9 @@
         <f>IF(games!I298&lt;&gt;"", games!I298, "")</f>
         <v/>
       </c>
-    </row>
-    <row r="299" spans="1:38">
+      <c r="K298" s="89"/>
+    </row>
+    <row r="299" spans="1:49">
       <c r="A299" s="10" t="str">
         <f>IF(games!A299="", "", games!A299)</f>
         <v/>
@@ -63528,7 +63676,7 @@
         <v/>
       </c>
     </row>
-    <row r="300" spans="1:38">
+    <row r="300" spans="1:49">
       <c r="A300" s="10" t="str">
         <f>IF(games!A300="", "", games!A300)</f>
         <v/>
@@ -63546,7 +63694,7 @@
         <v/>
       </c>
     </row>
-    <row r="301" spans="1:38">
+    <row r="301" spans="1:49">
       <c r="A301" s="10" t="str">
         <f>IF(games!A301="", "", games!A301)</f>
         <v/>
@@ -63564,7 +63712,7 @@
         <v/>
       </c>
     </row>
-    <row r="302" spans="1:38">
+    <row r="302" spans="1:49">
       <c r="A302" s="10" t="str">
         <f>IF(games!A302="", "", games!A302)</f>
         <v/>
@@ -63582,7 +63730,7 @@
         <v/>
       </c>
     </row>
-    <row r="303" spans="1:38">
+    <row r="303" spans="1:49">
       <c r="C303" s="10" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -63596,7 +63744,7 @@
         <v/>
       </c>
     </row>
-    <row r="304" spans="1:38">
+    <row r="304" spans="1:49">
       <c r="C304" s="10" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -65298,7 +65446,7 @@
     <hyperlink ref="K280" r:id="rId7"/>
     <hyperlink ref="K281" r:id="rId8"/>
     <hyperlink ref="K282" r:id="rId9"/>
-    <hyperlink ref="AC292" r:id="rId10"/>
+    <hyperlink ref="AC291" r:id="rId10"/>
     <hyperlink ref="AK293" r:id="rId11"/>
     <hyperlink ref="W287" r:id="rId12"/>
     <hyperlink ref="AO284" r:id="rId13"/>
@@ -65310,15 +65458,15 @@
     <hyperlink ref="AA275" r:id="rId19"/>
     <hyperlink ref="Q274" r:id="rId20"/>
     <hyperlink ref="W297" r:id="rId21"/>
-    <hyperlink ref="M296" r:id="rId22"/>
-    <hyperlink ref="K295" r:id="rId23"/>
-    <hyperlink ref="K294" r:id="rId24"/>
-    <hyperlink ref="M291" r:id="rId25"/>
-    <hyperlink ref="K290" r:id="rId26"/>
-    <hyperlink ref="K289" r:id="rId27"/>
-    <hyperlink ref="K288" r:id="rId28"/>
-    <hyperlink ref="K285" r:id="rId29"/>
-    <hyperlink ref="K286" r:id="rId30"/>
+    <hyperlink ref="K295" r:id="rId22"/>
+    <hyperlink ref="K294" r:id="rId23"/>
+    <hyperlink ref="M291" r:id="rId24"/>
+    <hyperlink ref="K290" r:id="rId25"/>
+    <hyperlink ref="K289" r:id="rId26"/>
+    <hyperlink ref="K288" r:id="rId27"/>
+    <hyperlink ref="K285" r:id="rId28"/>
+    <hyperlink ref="K286" r:id="rId29"/>
+    <hyperlink ref="AK296" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8131" uniqueCount="5536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8189" uniqueCount="5576">
   <si>
     <t>Facebook</t>
   </si>
@@ -21089,12 +21089,141 @@
     <t>WEEK2A</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>https://www.facebook.com/WelcomeToDreamland.official/</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E6%AD%A1%E8%BF%8E%E4%BE%86%E5%88%B0%E5%A4%A2%E6%A8%82%E5%9C%92/id6748006168</t>
+  </si>
+  <si>
+    <t>https://mly.poseidongame.com/</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.NiAlInteractive.Cryowar&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://www.cryowar.com/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/cryowar/?locale=zh_HK</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/cryowar/id6444241874</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.ghostshippublishing.deeprockgalacticsurvivor</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/us/app/deep-rock-galactic-survivor/id6742194903</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/JoinDeepRock/</t>
+  </si>
+  <si>
+    <t>https://www.deeprockgalactic.com/</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E7%86%B1%E8%A1%80%E6%8E%92%E7%90%83%E5%B0%91%E5%A5%B3/id6737681316</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.daerigame.volleygirls</t>
+  </si>
+  <si>
+    <t>https://discord.com/invite/jqUKG7bFxV</t>
+  </si>
+  <si>
+    <t>歡迎來到夢樂園</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cryowar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深岩銀河：倖存者</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>熱血排球少女</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.poseidongame.dsl&amp;hl=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>「歡迎來到夢樂園」隆重開幕！這款女性向輕喜劇異界冒險手遊，讓你化身管理者重建樂園。還在為資源煩惱？別傻了，快找最新的禮包碼和兌換碼才是王道。當然，想一步登天，最快速安全的代儲值服務也不能少，讓你輕鬆應對各種挑戰，與夥伴們踏上夢幻旅程。別再慢慢農了，聰明的管理者都懂。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">「Cryowar」是一款基於Solana的即時多人PVP競技場NFT遊戲。還在手動農資源？真是辛苦了。想在戰場上快人一步，你需要的不只是技術，更是海量的禮包碼與兌換碼。當然，為了打造最強裝備，尋求快速安全的代儲值服務也是必要的捷徑。別再當個苦哈哈的戰士，立即強化你的英雄，主宰競技場吧！ </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>「深岩銀河：倖存者」登陸手機！這款單人倖存者類自動射擊遊戲，讓你單槍匹馬對抗Hoxxes星球。以為光靠技術就能活下去？別天真了，沒有最新的禮包碼和兌換碼，你連蟲潮都撐不過。想挖礦挖得更深，升級更猛？快速安全的代儲值服務是你唯一的希望。別再掙扎了，矮人，快武裝自己！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>「熱血排球少女」開打！這款4v4排球對戰遊戲，讓你打造夢幻隊伍。還在苦練發球跟扣殺？別傻了，這年頭想赢，靠的是源源不絕的禮包碼和兌換碼。想讓你的少女選手快速升級，制霸全國大賽？快速安全的代儲值服務才是致勝關鍵。別再慢慢培養了，立即組建最強隊伍，拿下冠軍吧！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>216虹光鑽</t>
+  </si>
+  <si>
+    <t>113虹光鑽</t>
+  </si>
+  <si>
+    <t>56虹光鑽</t>
+  </si>
+  <si>
+    <t>31虹光鑽</t>
+  </si>
+  <si>
+    <t>22虹光鑽</t>
+  </si>
+  <si>
+    <t>10虹光鑽</t>
+  </si>
+  <si>
+    <t>2虹光鑽</t>
+  </si>
+  <si>
+    <t>體力周卡</t>
+  </si>
+  <si>
+    <t>信賴周卡</t>
+  </si>
+  <si>
+    <t>43200水晶球</t>
+  </si>
+  <si>
+    <t>24000水晶球</t>
+  </si>
+  <si>
+    <t>14400水晶球</t>
+  </si>
+  <si>
+    <t>4800水晶球</t>
+  </si>
+  <si>
+    <t>2400水晶球</t>
+  </si>
+  <si>
+    <t>PRO30日通行證</t>
+  </si>
+  <si>
+    <t>30日通行證</t>
+  </si>
+  <si>
+    <t>30日會員</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -21224,6 +21353,12 @@
       <name val="Arial Unicode MS"/>
       <family val="2"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF5F6368"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -21470,7 +21605,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -21693,6 +21828,8 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -42753,44 +42890,248 @@
         <v>31</v>
       </c>
     </row>
-    <row r="298" spans="1:31" ht="22.5" customHeight="1">
+    <row r="298" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A298" s="83" t="s">
+        <v>5550</v>
+      </c>
+      <c r="C298" s="37" t="s">
+        <v>5536</v>
+      </c>
+      <c r="D298" s="38" t="s">
+        <v>5538</v>
+      </c>
+      <c r="E298" s="38" t="s">
+        <v>5537</v>
+      </c>
       <c r="F298" s="37" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=歡迎來到夢樂園</v>
+      </c>
+      <c r="G298" s="2" t="s">
+        <v>5554</v>
       </c>
       <c r="H298" s="38" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="299" spans="1:31" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/game-detail.html?game=歡迎來到夢樂園</v>
+      </c>
+      <c r="I298" s="39" t="s">
+        <v>5555</v>
+      </c>
+      <c r="J298" s="2" t="s">
+        <v>5427</v>
+      </c>
+      <c r="K298" s="88" t="s">
+        <v>5258</v>
+      </c>
+      <c r="L298" s="1" t="s">
+        <v>5559</v>
+      </c>
+      <c r="M298" s="59">
+        <v>2763</v>
+      </c>
+      <c r="N298" s="1" t="s">
+        <v>5560</v>
+      </c>
+      <c r="O298" s="59">
+        <v>1446</v>
+      </c>
+      <c r="P298" s="1" t="s">
+        <v>5561</v>
+      </c>
+      <c r="Q298" s="59">
+        <v>751</v>
+      </c>
+      <c r="R298" s="1" t="s">
+        <v>5562</v>
+      </c>
+      <c r="S298" s="59">
+        <v>371</v>
+      </c>
+      <c r="T298" s="1" t="s">
+        <v>5563</v>
+      </c>
+      <c r="U298" s="59">
+        <v>319</v>
+      </c>
+      <c r="V298" s="1" t="s">
+        <v>5564</v>
+      </c>
+      <c r="W298" s="59">
+        <v>117</v>
+      </c>
+      <c r="X298" s="1" t="s">
+        <v>5565</v>
+      </c>
+      <c r="Y298" s="59">
+        <v>46</v>
+      </c>
+      <c r="Z298" s="1" t="s">
+        <v>5566</v>
+      </c>
+      <c r="AA298" s="59">
+        <v>117</v>
+      </c>
+      <c r="AB298" s="1" t="s">
+        <v>5567</v>
+      </c>
+      <c r="AC298" s="59">
+        <v>90</v>
+      </c>
+      <c r="AD298" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE298" s="59">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="299" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A299" s="59" t="s">
+        <v>5551</v>
+      </c>
+      <c r="C299" s="37" t="s">
+        <v>5541</v>
+      </c>
+      <c r="D299" s="38" t="s">
+        <v>5540</v>
+      </c>
+      <c r="E299" s="38" t="s">
+        <v>5542</v>
+      </c>
       <c r="F299" s="37" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=Cryowar</v>
+      </c>
+      <c r="G299" s="38" t="s">
+        <v>5539</v>
       </c>
       <c r="H299" s="38" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="300" spans="1:31" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/game-detail.html?game=Cryowar</v>
+      </c>
+      <c r="I299" s="39" t="s">
+        <v>5556</v>
+      </c>
+      <c r="J299" s="2" t="s">
+        <v>5427</v>
+      </c>
+      <c r="K299" s="88" t="s">
+        <v>5258</v>
+      </c>
+    </row>
+    <row r="300" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A300" s="83" t="s">
+        <v>5552</v>
+      </c>
+      <c r="C300" s="37" t="s">
+        <v>5545</v>
+      </c>
+      <c r="D300" s="38" t="s">
+        <v>5546</v>
+      </c>
+      <c r="E300" s="38" t="s">
+        <v>5544</v>
+      </c>
       <c r="F300" s="37" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=深岩銀河：倖存者</v>
+      </c>
+      <c r="G300" s="38" t="s">
+        <v>5543</v>
       </c>
       <c r="H300" s="38" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="301" spans="1:31" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/game-detail.html?game=深岩銀河：倖存者</v>
+      </c>
+      <c r="I300" s="39" t="s">
+        <v>5557</v>
+      </c>
+      <c r="J300" s="2" t="s">
+        <v>5427</v>
+      </c>
+      <c r="K300" s="88" t="s">
+        <v>5258</v>
+      </c>
+    </row>
+    <row r="301" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A301" s="93" t="s">
+        <v>5553</v>
+      </c>
+      <c r="C301" s="92" t="s">
+        <v>5549</v>
+      </c>
+      <c r="D301" s="38" t="s">
+        <v>3688</v>
+      </c>
+      <c r="E301" s="38" t="s">
+        <v>5547</v>
+      </c>
       <c r="F301" s="37" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=熱血排球少女</v>
+      </c>
+      <c r="G301" s="38" t="s">
+        <v>5548</v>
       </c>
       <c r="H301" s="38" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=熱血排球少女</v>
+      </c>
+      <c r="I301" s="39" t="s">
+        <v>5558</v>
+      </c>
+      <c r="J301" s="2" t="s">
+        <v>5427</v>
+      </c>
+      <c r="K301" s="88" t="s">
+        <v>5258</v>
+      </c>
+      <c r="L301" s="1" t="s">
+        <v>5568</v>
+      </c>
+      <c r="M301" s="59">
+        <v>1959</v>
+      </c>
+      <c r="N301" s="1" t="s">
+        <v>5569</v>
+      </c>
+      <c r="O301" s="59">
+        <v>1104</v>
+      </c>
+      <c r="P301" s="1" t="s">
+        <v>5570</v>
+      </c>
+      <c r="Q301" s="59">
+        <v>682</v>
+      </c>
+      <c r="R301" s="1" t="s">
+        <v>5571</v>
+      </c>
+      <c r="S301" s="59">
+        <v>262</v>
+      </c>
+      <c r="T301" s="1" t="s">
+        <v>5572</v>
+      </c>
+      <c r="U301" s="59">
+        <v>108</v>
+      </c>
+      <c r="V301" s="1" t="s">
+        <v>5573</v>
+      </c>
+      <c r="W301" s="59">
+        <v>1104</v>
+      </c>
+      <c r="X301" s="1" t="s">
+        <v>5574</v>
+      </c>
+      <c r="Y301" s="59">
+        <v>276</v>
+      </c>
+      <c r="Z301" s="1" t="s">
+        <v>5575</v>
+      </c>
+      <c r="AA301" s="59">
+        <v>108</v>
       </c>
     </row>
     <row r="302" spans="1:31" ht="22.5" customHeight="1">
@@ -46110,9 +46451,10 @@
     <hyperlink ref="X279" r:id="rId283"/>
     <hyperlink ref="AB287" r:id="rId284"/>
     <hyperlink ref="G297"/>
+    <hyperlink ref="G298" r:id="rId285"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId285"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId286"/>
 </worksheet>
 </file>
 
@@ -63642,74 +63984,97 @@
     <row r="298" spans="1:49">
       <c r="A298" s="10" t="str">
         <f>IF(games!A298="", "", games!A298)</f>
-        <v/>
+        <v>歡迎來到夢樂園</v>
       </c>
       <c r="C298" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>giftcodesbanner/歡迎來到夢樂園-禮包碼.jpg</v>
       </c>
       <c r="D298" s="10" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=歡迎來到夢樂園</v>
       </c>
       <c r="E298" s="11" t="str">
         <f>IF(games!I298&lt;&gt;"", games!I298, "")</f>
-        <v/>
-      </c>
-      <c r="K298" s="89"/>
+        <v>「歡迎來到夢樂園」隆重開幕！這款女性向輕喜劇異界冒險手遊，讓你化身管理者重建樂園。還在為資源煩惱？別傻了，快找最新的禮包碼和兌換碼才是王道。當然，想一步登天，最快速安全的代儲值服務也不能少，讓你輕鬆應對各種挑戰，與夥伴們踏上夢幻旅程。別再慢慢農了，聰明的管理者都懂。</v>
+      </c>
+      <c r="K298" s="89" t="s">
+        <v>5512</v>
+      </c>
+      <c r="L298" s="10" t="s">
+        <v>5513</v>
+      </c>
     </row>
     <row r="299" spans="1:49">
       <c r="A299" s="10" t="str">
         <f>IF(games!A299="", "", games!A299)</f>
-        <v/>
+        <v>Cryowar</v>
       </c>
       <c r="C299" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>giftcodesbanner/Cryowar-禮包碼.jpg</v>
       </c>
       <c r="D299" s="10" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=Cryowar</v>
       </c>
       <c r="E299" s="11" t="str">
         <f>IF(games!I299&lt;&gt;"", games!I299, "")</f>
-        <v/>
+        <v xml:space="preserve">「Cryowar」是一款基於Solana的即時多人PVP競技場NFT遊戲。還在手動農資源？真是辛苦了。想在戰場上快人一步，你需要的不只是技術，更是海量的禮包碼與兌換碼。當然，為了打造最強裝備，尋求快速安全的代儲值服務也是必要的捷徑。別再當個苦哈哈的戰士，立即強化你的英雄，主宰競技場吧！ </v>
+      </c>
+      <c r="K299" s="89" t="s">
+        <v>5512</v>
+      </c>
+      <c r="L299" s="10" t="s">
+        <v>5513</v>
       </c>
     </row>
     <row r="300" spans="1:49">
       <c r="A300" s="10" t="str">
         <f>IF(games!A300="", "", games!A300)</f>
-        <v/>
+        <v>深岩銀河：倖存者</v>
       </c>
       <c r="C300" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>giftcodesbanner/深岩銀河：倖存者-禮包碼.jpg</v>
       </c>
       <c r="D300" s="10" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=深岩銀河：倖存者</v>
       </c>
       <c r="E300" s="11" t="str">
         <f>IF(games!I300&lt;&gt;"", games!I300, "")</f>
-        <v/>
+        <v>「深岩銀河：倖存者」登陸手機！這款單人倖存者類自動射擊遊戲，讓你單槍匹馬對抗Hoxxes星球。以為光靠技術就能活下去？別天真了，沒有最新的禮包碼和兌換碼，你連蟲潮都撐不過。想挖礦挖得更深，升級更猛？快速安全的代儲值服務是你唯一的希望。別再掙扎了，矮人，快武裝自己！</v>
+      </c>
+      <c r="K300" s="89" t="s">
+        <v>5512</v>
+      </c>
+      <c r="L300" s="10" t="s">
+        <v>5513</v>
       </c>
     </row>
     <row r="301" spans="1:49">
       <c r="A301" s="10" t="str">
         <f>IF(games!A301="", "", games!A301)</f>
-        <v/>
+        <v>熱血排球少女</v>
       </c>
       <c r="C301" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>giftcodesbanner/熱血排球少女-禮包碼.jpg</v>
       </c>
       <c r="D301" s="10" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=熱血排球少女</v>
       </c>
       <c r="E301" s="11" t="str">
         <f>IF(games!I301&lt;&gt;"", games!I301, "")</f>
-        <v/>
+        <v>「熱血排球少女」開打！這款4v4排球對戰遊戲，讓你打造夢幻隊伍。還在苦練發球跟扣殺？別傻了，這年頭想赢，靠的是源源不絕的禮包碼和兌換碼。想讓你的少女選手快速升級，制霸全國大賽？快速安全的代儲值服務才是致勝關鍵。別再慢慢培養了，立即組建最強隊伍，拿下冠軍吧！</v>
+      </c>
+      <c r="K301" s="89" t="s">
+        <v>5512</v>
+      </c>
+      <c r="L301" s="10" t="s">
+        <v>5513</v>
       </c>
     </row>
     <row r="302" spans="1:49">
@@ -65467,8 +65832,12 @@
     <hyperlink ref="K285" r:id="rId28"/>
     <hyperlink ref="K286" r:id="rId29"/>
     <hyperlink ref="AK296" r:id="rId30"/>
+    <hyperlink ref="K298" r:id="rId31"/>
+    <hyperlink ref="K299" r:id="rId32"/>
+    <hyperlink ref="K300" r:id="rId33"/>
+    <hyperlink ref="K301" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId35"/>
 </worksheet>
 </file>
--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8189" uniqueCount="5576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8192" uniqueCount="5579">
   <si>
     <t>Facebook</t>
   </si>
@@ -21217,6 +21217,15 @@
   </si>
   <si>
     <t>30日會員</t>
+  </si>
+  <si>
+    <t>Jetpack Joyride Racing</t>
+  </si>
+  <si>
+    <t>三國格子爭奪戰</t>
+  </si>
+  <si>
+    <t>貓茶小當家：掌櫃養成記</t>
   </si>
 </sst>
 </file>
@@ -43134,34 +43143,43 @@
         <v>108</v>
       </c>
     </row>
-    <row r="302" spans="1:31" ht="22.5" customHeight="1">
+    <row r="302" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A302" s="59" t="s">
+        <v>5576</v>
+      </c>
       <c r="F302" s="37" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=Jetpack Joyride Racing</v>
       </c>
       <c r="H302" s="38" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="303" spans="1:31" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/game-detail.html?game=Jetpack Joyride Racing</v>
+      </c>
+    </row>
+    <row r="303" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A303" s="59" t="s">
+        <v>5577</v>
+      </c>
       <c r="F303" s="37" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=三國格子爭奪戰</v>
       </c>
       <c r="H303" s="38" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="304" spans="1:31" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/game-detail.html?game=三國格子爭奪戰</v>
+      </c>
+    </row>
+    <row r="304" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A304" s="59" t="s">
+        <v>5578</v>
+      </c>
       <c r="F304" s="37" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=貓茶小當家：掌櫃養成記</v>
       </c>
       <c r="H304" s="38" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=貓茶小當家：掌櫃養成記</v>
       </c>
     </row>
     <row r="305" spans="6:8" ht="22.5" customHeight="1">
@@ -64080,15 +64098,15 @@
     <row r="302" spans="1:49">
       <c r="A302" s="10" t="str">
         <f>IF(games!A302="", "", games!A302)</f>
-        <v/>
+        <v>Jetpack Joyride Racing</v>
       </c>
       <c r="C302" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>giftcodesbanner/Jetpack Joyride Racing-禮包碼.jpg</v>
       </c>
       <c r="D302" s="10" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=Jetpack Joyride Racing</v>
       </c>
       <c r="E302" s="11" t="str">
         <f>IF(games!I302&lt;&gt;"", games!I302, "")</f>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8192" uniqueCount="5579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8214" uniqueCount="5601">
   <si>
     <t>Facebook</t>
   </si>
@@ -21226,6 +21226,72 @@
   </si>
   <si>
     <t>貓茶小當家：掌櫃養成記</t>
+  </si>
+  <si>
+    <t>Viladia：精靈村的時光</t>
+  </si>
+  <si>
+    <t>G9：特功聯盟</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/us/app/jetpack-joyride-racing/id6740550251</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.halfbrick.aeroracer</t>
+  </si>
+  <si>
+    <t>https://www.halfbrick.com/games/jetpack-joyride-racing</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/jetpackjoyride/</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/hk/app/%E4%B8%89%E5%9C%8B%E6%A0%BC%E5%AD%90%E7%88%AD%E5%A5%AA%E6%88%B0/id6752283990</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.cardclash.android&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://tkcc.cloudoceanstar.com/index.html?langs=tc</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61582585780146</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.dreamland.cat.story&amp;hl=zh_TW</t>
+  </si>
+  <si>
+    <t>https://www.catdream.net/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/catdreamhmt/</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E8%B2%93%E8%8C%B6%E5%B0%8F%E7%95%B6%E5%AE%B6-%E6%8E%8C%E6%AB%83%E9%A4%8A%E6%88%90%E8%A8%98/id6749299768</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/viladia-%E7%B2%BE%E9%9D%88%E6%9D%91%E7%9A%84%E6%99%82%E5%85%89/id6670186613</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.selvasai.ttrebirth</t>
+  </si>
+  <si>
+    <t>https://www.selvasai.com/</t>
+  </si>
+  <si>
+    <t>https://g9.interserv.com.tw/order/</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/g9-%E7%89%B9%E6%94%BB%E8%81%AF%E7%9B%9F-g9-league-of-aces/id6502381302</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.InterServ.G9_aos&amp;referrer=utm_source%3Dgamer.com.tw%26utm_campaign%3Dgnn</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/G9LoAAsia/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61568844742817</t>
   </si>
 </sst>
 </file>
@@ -43147,10 +43213,22 @@
       <c r="A302" s="59" t="s">
         <v>5576</v>
       </c>
+      <c r="C302" s="37" t="s">
+        <v>5584</v>
+      </c>
+      <c r="D302" s="38" t="s">
+        <v>5583</v>
+      </c>
+      <c r="E302" s="38" t="s">
+        <v>5581</v>
+      </c>
       <c r="F302" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=Jetpack Joyride Racing</v>
       </c>
+      <c r="G302" s="38" t="s">
+        <v>5582</v>
+      </c>
       <c r="H302" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=Jetpack Joyride Racing</v>
@@ -43160,10 +43238,22 @@
       <c r="A303" s="59" t="s">
         <v>5577</v>
       </c>
+      <c r="C303" s="37" t="s">
+        <v>5588</v>
+      </c>
+      <c r="D303" s="38" t="s">
+        <v>5587</v>
+      </c>
+      <c r="E303" s="38" t="s">
+        <v>5585</v>
+      </c>
       <c r="F303" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=三國格子爭奪戰</v>
       </c>
+      <c r="G303" s="38" t="s">
+        <v>5586</v>
+      </c>
       <c r="H303" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=三國格子爭奪戰</v>
@@ -43173,36 +43263,78 @@
       <c r="A304" s="59" t="s">
         <v>5578</v>
       </c>
+      <c r="C304" s="37" t="s">
+        <v>5591</v>
+      </c>
+      <c r="D304" s="38" t="s">
+        <v>5590</v>
+      </c>
+      <c r="E304" s="38" t="s">
+        <v>5592</v>
+      </c>
       <c r="F304" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=貓茶小當家：掌櫃養成記</v>
       </c>
+      <c r="G304" s="38" t="s">
+        <v>5589</v>
+      </c>
       <c r="H304" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=貓茶小當家：掌櫃養成記</v>
       </c>
     </row>
-    <row r="305" spans="6:8" ht="22.5" customHeight="1">
+    <row r="305" spans="1:8" ht="22.5" customHeight="1">
+      <c r="A305" s="84" t="s">
+        <v>5579</v>
+      </c>
+      <c r="C305" s="37" t="s">
+        <v>5600</v>
+      </c>
+      <c r="D305" s="38" t="s">
+        <v>5595</v>
+      </c>
+      <c r="E305" s="38" t="s">
+        <v>5593</v>
+      </c>
       <c r="F305" s="37" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=Viladia：精靈村的時光</v>
+      </c>
+      <c r="G305" s="38" t="s">
+        <v>5594</v>
       </c>
       <c r="H305" s="38" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="306" spans="6:8" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/game-detail.html?game=Viladia：精靈村的時光</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" ht="22.5" customHeight="1">
+      <c r="A306" s="84" t="s">
+        <v>5580</v>
+      </c>
+      <c r="C306" s="37" t="s">
+        <v>5599</v>
+      </c>
+      <c r="D306" s="38" t="s">
+        <v>5596</v>
+      </c>
+      <c r="E306" s="38" t="s">
+        <v>5597</v>
+      </c>
       <c r="F306" s="37" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>gift-codes.html?game=G9：特功聯盟</v>
+      </c>
+      <c r="G306" s="38" t="s">
+        <v>5598</v>
       </c>
       <c r="H306" s="38" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="307" spans="6:8" ht="22.5" customHeight="1">
+        <v>https://www.ssbuy.tw/game-detail.html?game=G9：特功聯盟</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" ht="22.5" customHeight="1">
       <c r="F307" s="37" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -43212,7 +43344,7 @@
         <v/>
       </c>
     </row>
-    <row r="308" spans="6:8" ht="22.5" customHeight="1">
+    <row r="308" spans="1:8" ht="22.5" customHeight="1">
       <c r="F308" s="37" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -43222,7 +43354,7 @@
         <v/>
       </c>
     </row>
-    <row r="309" spans="6:8" ht="22.5" customHeight="1">
+    <row r="309" spans="1:8" ht="22.5" customHeight="1">
       <c r="F309" s="37" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -43232,7 +43364,7 @@
         <v/>
       </c>
     </row>
-    <row r="310" spans="6:8" ht="22.5" customHeight="1">
+    <row r="310" spans="1:8" ht="22.5" customHeight="1">
       <c r="F310" s="37" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -43242,7 +43374,7 @@
         <v/>
       </c>
     </row>
-    <row r="311" spans="6:8" ht="22.5" customHeight="1">
+    <row r="311" spans="1:8" ht="22.5" customHeight="1">
       <c r="F311" s="37" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -43252,7 +43384,7 @@
         <v/>
       </c>
     </row>
-    <row r="312" spans="6:8" ht="22.5" customHeight="1">
+    <row r="312" spans="1:8" ht="22.5" customHeight="1">
       <c r="F312" s="37" t="str">
         <f t="shared" ref="F312:F375" si="14">IF(A312="", "", "gift-codes.html?game=" &amp; A312)</f>
         <v/>
@@ -43262,7 +43394,7 @@
         <v/>
       </c>
     </row>
-    <row r="313" spans="6:8" ht="22.5" customHeight="1">
+    <row r="313" spans="1:8" ht="22.5" customHeight="1">
       <c r="F313" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -43272,7 +43404,7 @@
         <v/>
       </c>
     </row>
-    <row r="314" spans="6:8" ht="22.5" customHeight="1">
+    <row r="314" spans="1:8" ht="22.5" customHeight="1">
       <c r="F314" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -43282,7 +43414,7 @@
         <v/>
       </c>
     </row>
-    <row r="315" spans="6:8" ht="22.5" customHeight="1">
+    <row r="315" spans="1:8" ht="22.5" customHeight="1">
       <c r="F315" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -43292,7 +43424,7 @@
         <v/>
       </c>
     </row>
-    <row r="316" spans="6:8" ht="22.5" customHeight="1">
+    <row r="316" spans="1:8" ht="22.5" customHeight="1">
       <c r="F316" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -43302,7 +43434,7 @@
         <v/>
       </c>
     </row>
-    <row r="317" spans="6:8" ht="22.5" customHeight="1">
+    <row r="317" spans="1:8" ht="22.5" customHeight="1">
       <c r="F317" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -43312,7 +43444,7 @@
         <v/>
       </c>
     </row>
-    <row r="318" spans="6:8" ht="22.5" customHeight="1">
+    <row r="318" spans="1:8" ht="22.5" customHeight="1">
       <c r="F318" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -43322,7 +43454,7 @@
         <v/>
       </c>
     </row>
-    <row r="319" spans="6:8" ht="22.5" customHeight="1">
+    <row r="319" spans="1:8" ht="22.5" customHeight="1">
       <c r="F319" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -43332,7 +43464,7 @@
         <v/>
       </c>
     </row>
-    <row r="320" spans="6:8" ht="22.5" customHeight="1">
+    <row r="320" spans="1:8" ht="22.5" customHeight="1">
       <c r="F320" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>

--- a/detail_giftcode/data/gamedata.xlsx
+++ b/detail_giftcode/data/gamedata.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8214" uniqueCount="5601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8274" uniqueCount="5624">
   <si>
     <t>Facebook</t>
   </si>
@@ -19702,10 +19702,6 @@
     <t>新手支援禮包</t>
   </si>
   <si>
-    <t>最新價格請洽Line@</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>《電馭跑酷》這不是你阿嬤的公園散步，這是一場高速、玩命的都市障礙賽。玩家將扮演反抗軍的跑酷精英，在高聳入雲的摩天大樓間飛簷走壁，閃避企業保全的致命追擊。遊戲主打流暢到不科學的動作系統，結合了滑鏟、二段跳與牆面奔跑，每一次的跳躍都考驗著你的反應極限。想在起跑點就領先那些菜鳥？別忘了上網找最新的「兌換碼」，輸入後就能拿到初期資源。當然，遊戲內的「禮包碼」也別錯過。想要更快地強化你的裝備，尋求專業的「代儲值」服務是個聰明的捷徑，保證快速安全讓你無後顧之憂地稱霸這座數位牢籠。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -19897,22 +19893,18 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>金幣 x100W、進化材料選擇箱(上) x30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄召喚使用券 x10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Pick Up 英雄召喚使用券 x10</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>金幣 x100W、進化材料選擇箱(上) x30</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>英雄召喚使用券 x10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pick Up 英雄召喚使用券 x10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>寵物召喚使用券 x10</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -20059,10 +20051,6 @@
     <t>80鑽石</t>
   </si>
   <si>
-    <t>@ssbuy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>welcomedc</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -20640,6 +20628,9 @@
   </si>
   <si>
     <t>33代幣</t>
+  </si>
+  <si>
+    <t>最新優惠價格請洽Line@</t>
   </si>
   <si>
     <t>最新優惠價格請洽Line@</t>
@@ -20999,6 +20990,9 @@
   </si>
   <si>
     <t>LINE ID：@ssbuy</t>
+  </si>
+  <si>
+    <t>LINE ID：@ssbuy</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -21292,6 +21286,92 @@
   </si>
   <si>
     <t>https://www.facebook.com/profile.php?id=61568844742817</t>
+  </si>
+  <si>
+    <t>HSENAFBOX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEVENKNIGHTSFOREVER</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pick Up 英雄召喚使用券 x10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寵物召喚券*5、100萬金幣、鑰匙箱*3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>四星英雄凱爾*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>稀有四星英雄自選券*1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>給糖也搗蛋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>九九重陽敬老愛老</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>乖乖看完的你最棒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜光鑽x300、體力x100、金幣x2萬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜光鑽x300、體力x100、金幣x2萬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡陋突破隨機材料包x10、金幣x10萬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遊戲主畫面左上角「四方塊」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>「設置」→「兌換碼」</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>99.99面額禮包</t>
+  </si>
+  <si>
+    <t>49.99面額禮包</t>
+  </si>
+  <si>
+    <t>29.99面額禮包</t>
+  </si>
+  <si>
+    <t>19.99面額禮包</t>
+  </si>
+  <si>
+    <t>14.99面額禮包</t>
+  </si>
+  <si>
+    <t>9.99面額禮包</t>
+  </si>
+  <si>
+    <t>4.99面額禮包</t>
+  </si>
+  <si>
+    <t>3.99面額禮包</t>
+  </si>
+  <si>
+    <t>1.99面額禮包</t>
+  </si>
+  <si>
+    <t>年卡</t>
   </si>
 </sst>
 </file>
@@ -36951,10 +37031,10 @@
         <v>85</v>
       </c>
       <c r="AH223" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AI223" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="224" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37021,10 +37101,10 @@
         <v>28</v>
       </c>
       <c r="V224" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="W224" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="225" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37137,10 +37217,10 @@
         <v>124</v>
       </c>
       <c r="V226" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="W226" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="227" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37237,10 +37317,10 @@
         <v>519</v>
       </c>
       <c r="AF227" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AG227" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="228" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37331,10 +37411,10 @@
         <v>27</v>
       </c>
       <c r="AD228" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE228" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="229" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37425,10 +37505,10 @@
         <v>132</v>
       </c>
       <c r="AD229" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE229" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="230" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37531,10 +37611,10 @@
         <v>329</v>
       </c>
       <c r="AH230" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AI230" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="231" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37619,10 +37699,10 @@
         <v>535</v>
       </c>
       <c r="AB231" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AC231" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="232" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37713,10 +37793,10 @@
         <v>279</v>
       </c>
       <c r="AD232" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE232" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="233" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37841,10 +37921,10 @@
         <v>83</v>
       </c>
       <c r="AD234" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE234" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="235" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -37929,10 +38009,10 @@
         <v>74</v>
       </c>
       <c r="AB235" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AC235" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="236" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38029,10 +38109,10 @@
         <v>27</v>
       </c>
       <c r="AF236" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AG236" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="237" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38123,10 +38203,10 @@
         <v>27</v>
       </c>
       <c r="AD237" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE237" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="238" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38199,10 +38279,10 @@
         <v>27</v>
       </c>
       <c r="X238" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="Y238" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="239" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38287,10 +38367,10 @@
         <v>256</v>
       </c>
       <c r="AB239" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AC239" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="240" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -38357,10 +38437,10 @@
         <v>50</v>
       </c>
       <c r="V240" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="W240" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="241" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38445,10 +38525,10 @@
         <v>124</v>
       </c>
       <c r="AB241" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AC241" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="242" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38521,10 +38601,10 @@
         <v>248</v>
       </c>
       <c r="X242" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="Y242" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="243" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38609,10 +38689,10 @@
         <v>57</v>
       </c>
       <c r="AB243" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AC243" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="244" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38703,10 +38783,10 @@
         <v>612</v>
       </c>
       <c r="AD244" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE244" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="245" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38779,10 +38859,10 @@
         <v>256</v>
       </c>
       <c r="X245" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="Y245" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="246" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38837,10 +38917,10 @@
         <v>25</v>
       </c>
       <c r="R246" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="S246" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="247" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -38913,10 +38993,10 @@
         <v>29</v>
       </c>
       <c r="X247" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="Y247" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="248" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -39001,10 +39081,10 @@
         <v>25</v>
       </c>
       <c r="AB248" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AC248" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="249" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -39083,10 +39163,10 @@
         <v>27</v>
       </c>
       <c r="Z249" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AA249" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="250" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -39159,10 +39239,10 @@
         <v>33</v>
       </c>
       <c r="X250" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="Y250" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="251" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -39229,10 +39309,10 @@
         <v>25</v>
       </c>
       <c r="V251" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="W251" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="252" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -39323,10 +39403,10 @@
         <v>124</v>
       </c>
       <c r="AD252" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE252" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="253" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -39423,10 +39503,10 @@
         <v>107</v>
       </c>
       <c r="AF253" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AG253" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="254" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -39505,10 +39585,10 @@
         <v>74</v>
       </c>
       <c r="Z254" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AA254" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="255" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -39581,10 +39661,10 @@
         <v>216</v>
       </c>
       <c r="X255" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="Y255" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="256" spans="1:33" ht="22.5" customHeight="1" thickBot="1">
@@ -39657,10 +39737,10 @@
         <v>6095</v>
       </c>
       <c r="X256" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="Y256" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="257" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39751,10 +39831,10 @@
         <v>551</v>
       </c>
       <c r="AD257" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE257" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="258" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39851,10 +39931,10 @@
         <v>1725</v>
       </c>
       <c r="AF258" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AG258" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="259" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -39939,10 +40019,10 @@
         <v>630</v>
       </c>
       <c r="AB259" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AC259" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="260" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40033,10 +40113,10 @@
         <v>551</v>
       </c>
       <c r="AD260" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE260" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="261" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40115,10 +40195,10 @@
         <v>1173</v>
       </c>
       <c r="Z261" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AA261" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="262" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40185,10 +40265,10 @@
         <v>77</v>
       </c>
       <c r="V262" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="W262" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="263" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40291,10 +40371,10 @@
         <v>26</v>
       </c>
       <c r="AH263" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AI263" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="264" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40413,10 +40493,10 @@
         <v>162</v>
       </c>
       <c r="AD265" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE265" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="266" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40495,10 +40575,10 @@
         <v>29</v>
       </c>
       <c r="Z266" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AA266" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="267" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40589,10 +40669,10 @@
         <v>196</v>
       </c>
       <c r="AD267" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE267" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="268" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40683,10 +40763,10 @@
         <v>145</v>
       </c>
       <c r="AD268" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE268" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="269" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40771,10 +40851,10 @@
         <v>26</v>
       </c>
       <c r="AB269" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AC269" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="270" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40829,10 +40909,10 @@
         <v>227</v>
       </c>
       <c r="R270" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="S270" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="271" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40923,10 +41003,10 @@
         <v>314</v>
       </c>
       <c r="AD271" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE271" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="272" spans="1:35" ht="22.5" customHeight="1" thickBot="1">
@@ -40999,10 +41079,10 @@
         <v>29</v>
       </c>
       <c r="X272" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="Y272" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="273" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -41093,10 +41173,10 @@
         <v>160</v>
       </c>
       <c r="AD273" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE273" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="274" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -41187,10 +41267,10 @@
         <v>2343</v>
       </c>
       <c r="AD274" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE274" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="275" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -41269,10 +41349,10 @@
         <v>141</v>
       </c>
       <c r="Z275" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AA275" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="276" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -41303,58 +41383,58 @@
         <v>5087</v>
       </c>
       <c r="J276" s="1" t="s">
-        <v>5262</v>
+        <v>5259</v>
       </c>
       <c r="K276" s="59">
         <v>2477</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>5263</v>
+        <v>5260</v>
       </c>
       <c r="M276" s="59">
         <v>1346</v>
       </c>
       <c r="N276" s="1" t="s">
-        <v>5264</v>
+        <v>5261</v>
       </c>
       <c r="O276" s="59">
         <v>713</v>
       </c>
       <c r="P276" s="1" t="s">
-        <v>5265</v>
+        <v>5262</v>
       </c>
       <c r="Q276" s="59">
         <v>340</v>
       </c>
       <c r="R276" s="1" t="s">
-        <v>5266</v>
+        <v>5263</v>
       </c>
       <c r="S276" s="59">
         <v>169</v>
       </c>
       <c r="T276" s="1" t="s">
-        <v>5267</v>
+        <v>5264</v>
       </c>
       <c r="U276" s="59">
         <v>82</v>
       </c>
       <c r="V276" s="1" t="s">
-        <v>5268</v>
+        <v>5265</v>
       </c>
       <c r="W276" s="59">
         <v>30</v>
       </c>
       <c r="X276" s="1" t="s">
-        <v>5269</v>
+        <v>5266</v>
       </c>
       <c r="Y276" s="59">
         <v>133</v>
       </c>
       <c r="Z276" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AA276" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="277" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -41397,13 +41477,13 @@
         <v>1389</v>
       </c>
       <c r="N277" s="86" t="s">
-        <v>5164</v>
+        <v>5163</v>
       </c>
       <c r="O277" s="87">
         <v>821</v>
       </c>
       <c r="P277" s="86" t="s">
-        <v>5165</v>
+        <v>5164</v>
       </c>
       <c r="Q277" s="87">
         <v>407</v>
@@ -41421,7 +41501,7 @@
         <v>29</v>
       </c>
       <c r="V277" s="86" t="s">
-        <v>5166</v>
+        <v>5165</v>
       </c>
       <c r="W277" s="87">
         <v>147</v>
@@ -41429,10 +41509,10 @@
       <c r="X277" s="53"/>
       <c r="Y277" s="55"/>
       <c r="Z277" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AA277" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="278" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -41523,10 +41603,10 @@
         <v>261</v>
       </c>
       <c r="AD278" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE278" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="279" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -41593,16 +41673,16 @@
         <v>30</v>
       </c>
       <c r="V279" s="1" t="s">
-        <v>5370</v>
+        <v>5367</v>
       </c>
       <c r="W279" s="59">
         <v>151</v>
       </c>
       <c r="X279" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="Y279" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
       <c r="Z279" s="53"/>
       <c r="AA279" s="55"/>
@@ -41634,7 +41714,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/電馭跑酷.html</v>
       </c>
       <c r="I280" s="67" t="s">
-        <v>5162</v>
+        <v>5161</v>
       </c>
       <c r="J280" s="86" t="s">
         <v>5145</v>
@@ -41679,10 +41759,10 @@
         <v>248</v>
       </c>
       <c r="X280" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="Y280" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="281" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
@@ -41710,7 +41790,7 @@
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/火焰紋章Shadows.html</v>
       </c>
       <c r="I281" s="67" t="s">
-        <v>5163</v>
+        <v>5162</v>
       </c>
       <c r="J281" s="86" t="s">
         <v>5152</v>
@@ -41767,38 +41847,38 @@
         <v>139</v>
       </c>
       <c r="AB281" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AC281" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="282" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A282" s="87" t="s">
-        <v>5206</v>
+        <v>5205</v>
       </c>
       <c r="C282" s="37" t="s">
+        <v>5166</v>
+      </c>
+      <c r="D282" s="38" t="s">
         <v>5167</v>
       </c>
-      <c r="D282" s="38" t="s">
+      <c r="E282" s="38" t="s">
         <v>5168</v>
-      </c>
-      <c r="E282" s="38" t="s">
-        <v>5169</v>
       </c>
       <c r="F282" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=石器時代：寵物世界</v>
       </c>
       <c r="G282" s="85" t="s">
-        <v>5183</v>
+        <v>5182</v>
       </c>
       <c r="H282" s="38" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/石器時代：寵物世界.html</v>
       </c>
       <c r="I282" s="39" t="s">
-        <v>5186</v>
+        <v>5185</v>
       </c>
       <c r="J282" s="86" t="s">
         <v>4988</v>
@@ -41813,25 +41893,25 @@
         <v>2047</v>
       </c>
       <c r="N282" s="86" t="s">
-        <v>5176</v>
+        <v>5175</v>
       </c>
       <c r="O282" s="87">
         <v>1357</v>
       </c>
       <c r="P282" s="86" t="s">
-        <v>5177</v>
+        <v>5176</v>
       </c>
       <c r="Q282" s="87">
         <v>1085</v>
       </c>
       <c r="R282" s="86" t="s">
-        <v>5178</v>
+        <v>5177</v>
       </c>
       <c r="S282" s="87">
         <v>822</v>
       </c>
       <c r="T282" s="86" t="s">
-        <v>5179</v>
+        <v>5178</v>
       </c>
       <c r="U282" s="87">
         <v>680</v>
@@ -41849,7 +41929,7 @@
         <v>407</v>
       </c>
       <c r="Z282" s="86" t="s">
-        <v>5180</v>
+        <v>5179</v>
       </c>
       <c r="AA282" s="87">
         <v>357</v>
@@ -41861,59 +41941,59 @@
         <v>274</v>
       </c>
       <c r="AD282" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE282" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="283" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A283" s="87" t="s">
-        <v>5181</v>
+        <v>5180</v>
       </c>
       <c r="C283" s="37" t="s">
+        <v>5169</v>
+      </c>
+      <c r="D283" s="38" t="s">
         <v>5170</v>
       </c>
-      <c r="D283" s="38" t="s">
+      <c r="E283" s="38" t="s">
         <v>5171</v>
-      </c>
-      <c r="E283" s="38" t="s">
-        <v>5172</v>
       </c>
       <c r="F283" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=蔚藍星球：國王很忙</v>
       </c>
       <c r="G283" s="85" t="s">
-        <v>5184</v>
+        <v>5183</v>
       </c>
       <c r="H283" s="38" t="str">
         <f t="shared" si="11"/>
         <v>https://www.ssbuy.tw/detail_giftcode/dist/gamedetail/蔚藍星球：國王很忙.html</v>
       </c>
       <c r="I283" s="39" t="s">
-        <v>5187</v>
+        <v>5186</v>
       </c>
       <c r="J283" s="1" t="s">
-        <v>5330</v>
+        <v>5327</v>
       </c>
       <c r="K283" s="59">
         <v>2717</v>
       </c>
       <c r="L283" s="1" t="s">
-        <v>5331</v>
+        <v>5328</v>
       </c>
       <c r="M283" s="59">
         <v>1422</v>
       </c>
       <c r="N283" s="1" t="s">
-        <v>5332</v>
+        <v>5329</v>
       </c>
       <c r="O283" s="59">
         <v>586</v>
       </c>
       <c r="P283" s="1" t="s">
-        <v>5333</v>
+        <v>5330</v>
       </c>
       <c r="Q283" s="59">
         <v>416</v>
@@ -41931,147 +42011,147 @@
         <v>30</v>
       </c>
       <c r="V283" s="1" t="s">
-        <v>5334</v>
+        <v>5331</v>
       </c>
       <c r="W283" s="59">
         <v>151</v>
       </c>
       <c r="X283" s="1" t="s">
-        <v>5335</v>
+        <v>5332</v>
       </c>
       <c r="Y283" s="59">
         <v>89</v>
       </c>
       <c r="Z283" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AA283" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="284" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A284" s="87" t="s">
-        <v>5182</v>
+        <v>5181</v>
       </c>
       <c r="C284" s="37" t="s">
+        <v>5172</v>
+      </c>
+      <c r="D284" s="38" t="s">
         <v>5173</v>
       </c>
-      <c r="D284" s="38" t="s">
+      <c r="E284" s="38" t="s">
         <v>5174</v>
-      </c>
-      <c r="E284" s="38" t="s">
-        <v>5175</v>
       </c>
       <c r="F284" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=胸懷三國：美人計</v>
       </c>
       <c r="G284" s="85" t="s">
-        <v>5185</v>
+        <v>5184</v>
       </c>
       <c r="H284" s="38" t="str">
         <f t="shared" ref="H284:H311" si="13">IF(A284="", "", "https://www.ssbuy.tw/game-detail.html?game="&amp;A284)</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=胸懷三國：美人計</v>
       </c>
       <c r="I284" s="39" t="s">
-        <v>5188</v>
+        <v>5187</v>
       </c>
       <c r="J284" s="1" t="s">
-        <v>5277</v>
+        <v>5274</v>
       </c>
       <c r="K284" s="59">
         <v>2717</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>5278</v>
+        <v>5275</v>
       </c>
       <c r="M284" s="59">
         <v>1388</v>
       </c>
       <c r="N284" s="1" t="s">
-        <v>5279</v>
+        <v>5276</v>
       </c>
       <c r="O284" s="59">
         <v>841</v>
       </c>
       <c r="P284" s="1" t="s">
-        <v>5280</v>
+        <v>5277</v>
       </c>
       <c r="Q284" s="59">
         <v>586</v>
       </c>
       <c r="R284" s="1" t="s">
-        <v>5281</v>
+        <v>5278</v>
       </c>
       <c r="S284" s="59">
         <v>416</v>
       </c>
       <c r="T284" s="1" t="s">
-        <v>5282</v>
+        <v>5279</v>
       </c>
       <c r="U284" s="59">
         <v>280</v>
       </c>
       <c r="V284" s="1" t="s">
-        <v>5283</v>
+        <v>5280</v>
       </c>
       <c r="W284" s="59">
         <v>146</v>
       </c>
       <c r="X284" s="1" t="s">
-        <v>5284</v>
+        <v>5281</v>
       </c>
       <c r="Y284" s="59">
         <v>30</v>
       </c>
       <c r="Z284" s="1" t="s">
-        <v>5285</v>
+        <v>5282</v>
       </c>
       <c r="AA284" s="59">
         <v>416</v>
       </c>
       <c r="AB284" s="1" t="s">
-        <v>5286</v>
+        <v>5283</v>
       </c>
       <c r="AC284" s="59">
         <v>586</v>
       </c>
       <c r="AD284" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE284" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="285" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A285" s="87" t="s">
-        <v>5233</v>
+        <v>5231</v>
       </c>
       <c r="C285" s="37" t="s">
-        <v>5231</v>
+        <v>5229</v>
       </c>
       <c r="D285" s="38" t="s">
-        <v>5232</v>
+        <v>5230</v>
       </c>
       <c r="E285" s="38" t="s">
-        <v>5221</v>
+        <v>5219</v>
       </c>
       <c r="F285" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=弓箭英雄：塔防</v>
       </c>
       <c r="G285" s="85" t="s">
-        <v>5234</v>
+        <v>5232</v>
       </c>
       <c r="H285" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=弓箭英雄：塔防</v>
       </c>
       <c r="I285" s="39" t="s">
-        <v>5261</v>
+        <v>5258</v>
       </c>
       <c r="J285" s="1" t="s">
-        <v>5256</v>
+        <v>5254</v>
       </c>
       <c r="K285" s="59">
         <v>2469</v>
@@ -42101,65 +42181,65 @@
         <v>133</v>
       </c>
       <c r="T285" s="1" t="s">
-        <v>5257</v>
+        <v>5255</v>
       </c>
       <c r="U285" s="59">
         <v>27</v>
       </c>
       <c r="V285" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="W285" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="286" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A286" s="87" t="s">
-        <v>5239</v>
+        <v>5237</v>
       </c>
       <c r="C286" s="37" t="s">
-        <v>5223</v>
+        <v>5221</v>
       </c>
       <c r="D286" s="38" t="s">
+        <v>5220</v>
+      </c>
+      <c r="E286" s="38" t="s">
         <v>5222</v>
-      </c>
-      <c r="E286" s="38" t="s">
-        <v>5224</v>
       </c>
       <c r="F286" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=十二之天M</v>
       </c>
       <c r="G286" s="85" t="s">
-        <v>5235</v>
+        <v>5233</v>
       </c>
       <c r="H286" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=十二之天M</v>
       </c>
       <c r="I286" s="67" t="s">
-        <v>5253</v>
+        <v>5251</v>
       </c>
       <c r="J286" s="1" t="s">
-        <v>5270</v>
+        <v>5267</v>
       </c>
       <c r="K286" s="59">
         <v>2717</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>5271</v>
+        <v>5268</v>
       </c>
       <c r="M286" s="59">
         <v>1422</v>
       </c>
       <c r="N286" s="1" t="s">
-        <v>5272</v>
+        <v>5269</v>
       </c>
       <c r="O286" s="59">
         <v>840</v>
       </c>
       <c r="P286" s="1" t="s">
-        <v>5273</v>
+        <v>5270</v>
       </c>
       <c r="Q286" s="59">
         <v>416</v>
@@ -42177,101 +42257,101 @@
         <v>30</v>
       </c>
       <c r="V286" s="1" t="s">
-        <v>5274</v>
+        <v>5271</v>
       </c>
       <c r="W286" s="59">
         <v>213</v>
       </c>
       <c r="X286" s="1" t="s">
-        <v>5275</v>
+        <v>5272</v>
       </c>
       <c r="Y286" s="59">
         <v>357</v>
       </c>
       <c r="Z286" s="1" t="s">
-        <v>5276</v>
+        <v>5273</v>
       </c>
       <c r="AA286" s="59">
         <v>705</v>
       </c>
       <c r="AB286" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AC286" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="287" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A287" s="87" t="s">
-        <v>5240</v>
+        <v>5238</v>
       </c>
       <c r="C287" s="37" t="s">
-        <v>5227</v>
+        <v>5225</v>
       </c>
       <c r="D287" s="38" t="s">
-        <v>5226</v>
+        <v>5224</v>
       </c>
       <c r="E287" s="38" t="s">
-        <v>5225</v>
+        <v>5223</v>
       </c>
       <c r="F287" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=NBA巔峰對決</v>
       </c>
       <c r="G287" s="85" t="s">
-        <v>5236</v>
+        <v>5234</v>
       </c>
       <c r="H287" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=NBA巔峰對決</v>
       </c>
       <c r="I287" s="39" t="s">
-        <v>5254</v>
+        <v>5252</v>
       </c>
       <c r="J287" s="1" t="s">
-        <v>5381</v>
+        <v>5378</v>
       </c>
       <c r="K287" s="59">
         <v>2717</v>
       </c>
       <c r="L287" s="1" t="s">
-        <v>5382</v>
+        <v>5379</v>
       </c>
       <c r="M287" s="59">
         <v>1422</v>
       </c>
       <c r="N287" s="1" t="s">
-        <v>5383</v>
+        <v>5380</v>
       </c>
       <c r="O287" s="59">
         <v>840</v>
       </c>
       <c r="P287" s="1" t="s">
-        <v>5384</v>
+        <v>5381</v>
       </c>
       <c r="Q287" s="59">
         <v>586</v>
       </c>
       <c r="R287" s="1" t="s">
-        <v>5385</v>
+        <v>5382</v>
       </c>
       <c r="S287" s="59">
         <v>297</v>
       </c>
       <c r="T287" s="1" t="s">
-        <v>5386</v>
+        <v>5383</v>
       </c>
       <c r="U287" s="59">
         <v>146</v>
       </c>
       <c r="V287" s="1" t="s">
-        <v>5387</v>
+        <v>5384</v>
       </c>
       <c r="W287" s="59">
         <v>30</v>
       </c>
       <c r="X287" s="1" t="s">
-        <v>5388</v>
+        <v>5385</v>
       </c>
       <c r="Y287" s="59">
         <v>9</v>
@@ -42283,240 +42363,240 @@
         <v>146</v>
       </c>
       <c r="AB287" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AC287" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="288" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A288" s="87" t="s">
-        <v>5237</v>
+        <v>5235</v>
       </c>
       <c r="C288" s="37" t="s">
-        <v>5230</v>
+        <v>5228</v>
       </c>
       <c r="D288" s="38" t="s">
-        <v>5229</v>
+        <v>5227</v>
       </c>
       <c r="E288" s="38" t="s">
-        <v>5228</v>
+        <v>5226</v>
       </c>
       <c r="F288" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=三國志：王戰</v>
       </c>
       <c r="G288" s="85" t="s">
-        <v>5238</v>
+        <v>5236</v>
       </c>
       <c r="H288" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=三國志：王戰</v>
       </c>
       <c r="I288" s="39" t="s">
-        <v>5255</v>
+        <v>5253</v>
       </c>
       <c r="J288" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="K288" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="289" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A289" s="84" t="s">
+        <v>5341</v>
+      </c>
+      <c r="C289" s="37" t="s">
+        <v>5345</v>
+      </c>
+      <c r="D289" s="38" t="s">
+        <v>5342</v>
+      </c>
+      <c r="E289" s="38" t="s">
         <v>5344</v>
-      </c>
-      <c r="C289" s="37" t="s">
-        <v>5348</v>
-      </c>
-      <c r="D289" s="38" t="s">
-        <v>5345</v>
-      </c>
-      <c r="E289" s="38" t="s">
-        <v>5347</v>
       </c>
       <c r="F289" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=信長 霸道</v>
       </c>
       <c r="G289" s="38" t="s">
-        <v>5346</v>
+        <v>5343</v>
       </c>
       <c r="H289" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=信長 霸道</v>
       </c>
       <c r="I289" s="39" t="s">
-        <v>5359</v>
+        <v>5356</v>
       </c>
       <c r="J289" s="1" t="s">
-        <v>5349</v>
+        <v>5346</v>
       </c>
       <c r="K289" s="59">
         <v>2086</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>5350</v>
+        <v>5347</v>
       </c>
       <c r="M289" s="59">
         <v>1051</v>
       </c>
       <c r="N289" s="1" t="s">
-        <v>5351</v>
+        <v>5348</v>
       </c>
       <c r="O289" s="59">
         <v>531</v>
       </c>
       <c r="P289" s="1" t="s">
-        <v>5352</v>
+        <v>5349</v>
       </c>
       <c r="Q289" s="59">
         <v>357</v>
       </c>
       <c r="R289" s="1" t="s">
-        <v>5353</v>
+        <v>5350</v>
       </c>
       <c r="S289" s="59">
         <v>149</v>
       </c>
       <c r="T289" s="1" t="s">
-        <v>5354</v>
+        <v>5351</v>
       </c>
       <c r="U289" s="59">
         <v>32</v>
       </c>
       <c r="V289" s="1" t="s">
-        <v>5355</v>
+        <v>5352</v>
       </c>
       <c r="W289" s="59">
         <v>1051</v>
       </c>
       <c r="X289" s="1" t="s">
-        <v>5356</v>
+        <v>5353</v>
       </c>
       <c r="Y289" s="59">
         <v>531</v>
       </c>
       <c r="Z289" s="1" t="s">
-        <v>5357</v>
+        <v>5354</v>
       </c>
       <c r="AA289" s="59">
         <v>186</v>
       </c>
       <c r="AB289" s="1" t="s">
-        <v>5358</v>
+        <v>5355</v>
       </c>
       <c r="AC289" s="59">
         <v>357</v>
       </c>
       <c r="AD289" s="85" t="s">
-        <v>5161</v>
+        <v>5424</v>
       </c>
       <c r="AE289" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="290" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A290" s="59" t="s">
-        <v>5443</v>
+        <v>5441</v>
       </c>
       <c r="C290" s="37" t="s">
-        <v>5391</v>
+        <v>5388</v>
       </c>
       <c r="D290" s="38" t="s">
-        <v>5390</v>
+        <v>5387</v>
       </c>
       <c r="E290" s="38" t="s">
-        <v>5389</v>
+        <v>5386</v>
       </c>
       <c r="F290" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=勇者前線Versus</v>
       </c>
       <c r="G290" s="38" t="s">
-        <v>5414</v>
+        <v>5411</v>
       </c>
       <c r="H290" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=勇者前線Versus</v>
       </c>
       <c r="I290" s="39" t="s">
-        <v>5450</v>
+        <v>5448</v>
       </c>
       <c r="J290" s="2" t="s">
-        <v>5427</v>
+        <v>5425</v>
       </c>
       <c r="K290" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="291" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A291" s="83" t="s">
-        <v>5444</v>
+        <v>5442</v>
       </c>
       <c r="C291" s="37" t="s">
-        <v>5392</v>
+        <v>5389</v>
       </c>
       <c r="D291" s="38" t="s">
-        <v>5393</v>
+        <v>5390</v>
       </c>
       <c r="E291" s="38" t="s">
-        <v>5394</v>
+        <v>5391</v>
       </c>
       <c r="F291" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=幻域方舟</v>
       </c>
       <c r="G291" s="38" t="s">
-        <v>5395</v>
+        <v>5392</v>
       </c>
       <c r="H291" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=幻域方舟</v>
       </c>
       <c r="I291" s="39" t="s">
-        <v>5451</v>
+        <v>5449</v>
       </c>
       <c r="J291" s="2" t="s">
-        <v>5427</v>
+        <v>5425</v>
       </c>
       <c r="K291" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="292" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A292" s="83" t="s">
-        <v>5445</v>
+        <v>5443</v>
       </c>
       <c r="C292" s="37" t="s">
-        <v>5396</v>
+        <v>5393</v>
       </c>
       <c r="D292" s="38" t="s">
-        <v>5397</v>
+        <v>5394</v>
       </c>
       <c r="E292" s="38" t="s">
-        <v>5398</v>
+        <v>5395</v>
       </c>
       <c r="F292" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=開天</v>
       </c>
       <c r="G292" s="38" t="s">
-        <v>5399</v>
+        <v>5396</v>
       </c>
       <c r="H292" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=開天</v>
       </c>
       <c r="I292" s="39" t="s">
-        <v>5452</v>
+        <v>5450</v>
       </c>
       <c r="J292" s="2" t="s">
-        <v>5427</v>
+        <v>5425</v>
       </c>
       <c r="K292" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
       <c r="L292" s="1" t="s">
         <v>1514</v>
@@ -42525,7 +42605,7 @@
         <v>2717</v>
       </c>
       <c r="N292" s="1" t="s">
-        <v>5415</v>
+        <v>5412</v>
       </c>
       <c r="O292" s="59">
         <v>2095</v>
@@ -42537,25 +42617,25 @@
         <v>1388</v>
       </c>
       <c r="R292" s="1" t="s">
-        <v>5416</v>
+        <v>5413</v>
       </c>
       <c r="S292" s="59">
         <v>1194</v>
       </c>
       <c r="T292" s="1" t="s">
-        <v>5417</v>
+        <v>5414</v>
       </c>
       <c r="U292" s="59">
         <v>840</v>
       </c>
       <c r="V292" s="1" t="s">
-        <v>5418</v>
+        <v>5415</v>
       </c>
       <c r="W292" s="59">
         <v>815</v>
       </c>
       <c r="X292" s="1" t="s">
-        <v>5419</v>
+        <v>5416</v>
       </c>
       <c r="Y292" s="59">
         <v>756</v>
@@ -42575,75 +42655,75 @@
     </row>
     <row r="293" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A293" s="83" t="s">
-        <v>5446</v>
+        <v>5444</v>
       </c>
       <c r="C293" s="37" t="s">
+        <v>5397</v>
+      </c>
+      <c r="D293" s="38" t="s">
         <v>5400</v>
       </c>
-      <c r="D293" s="38" t="s">
-        <v>5403</v>
-      </c>
       <c r="E293" s="38" t="s">
-        <v>5402</v>
+        <v>5399</v>
       </c>
       <c r="F293" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=人人有功練：腸仔江湖見</v>
       </c>
       <c r="G293" s="38" t="s">
-        <v>5401</v>
+        <v>5398</v>
       </c>
       <c r="H293" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=人人有功練：腸仔江湖見</v>
       </c>
       <c r="I293" s="39" t="s">
-        <v>5453</v>
+        <v>5451</v>
       </c>
       <c r="J293" s="2" t="s">
-        <v>5427</v>
+        <v>5425</v>
       </c>
       <c r="K293" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
       <c r="L293" s="1" t="s">
-        <v>5420</v>
+        <v>5417</v>
       </c>
       <c r="M293" s="59">
         <v>2717</v>
       </c>
       <c r="N293" s="1" t="s">
-        <v>5421</v>
+        <v>5418</v>
       </c>
       <c r="O293" s="59">
         <v>1422</v>
       </c>
       <c r="P293" s="1" t="s">
-        <v>5422</v>
+        <v>5419</v>
       </c>
       <c r="Q293" s="59">
         <v>840</v>
       </c>
       <c r="R293" s="1" t="s">
-        <v>5423</v>
+        <v>5420</v>
       </c>
       <c r="S293" s="59">
         <v>620</v>
       </c>
       <c r="T293" s="1" t="s">
-        <v>5424</v>
+        <v>5421</v>
       </c>
       <c r="U293" s="59">
         <v>318</v>
       </c>
       <c r="V293" s="1" t="s">
-        <v>5425</v>
+        <v>5422</v>
       </c>
       <c r="W293" s="59">
         <v>151</v>
       </c>
       <c r="X293" s="1" t="s">
-        <v>5426</v>
+        <v>5423</v>
       </c>
       <c r="Y293" s="59">
         <v>30</v>
@@ -42651,81 +42731,81 @@
     </row>
     <row r="294" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A294" s="83" t="s">
-        <v>5447</v>
+        <v>5445</v>
       </c>
       <c r="C294" s="38" t="s">
-        <v>5406</v>
+        <v>5403</v>
       </c>
       <c r="D294" s="38" t="s">
-        <v>5406</v>
+        <v>5403</v>
       </c>
       <c r="E294" s="38" t="s">
-        <v>5404</v>
+        <v>5401</v>
       </c>
       <c r="F294" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=楓之谷：放置冒險記</v>
       </c>
       <c r="G294" s="38" t="s">
-        <v>5405</v>
+        <v>5402</v>
       </c>
       <c r="H294" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=楓之谷：放置冒險記</v>
       </c>
       <c r="I294" s="39" t="s">
-        <v>5454</v>
+        <v>5452</v>
       </c>
       <c r="J294" s="2" t="s">
-        <v>5427</v>
+        <v>5425</v>
       </c>
       <c r="K294" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
       <c r="L294" s="1" t="s">
-        <v>5428</v>
+        <v>5426</v>
       </c>
       <c r="M294" s="59">
         <v>2469</v>
       </c>
       <c r="N294" s="1" t="s">
-        <v>5429</v>
+        <v>5427</v>
       </c>
       <c r="O294" s="59">
         <v>1253</v>
       </c>
       <c r="P294" s="1" t="s">
-        <v>5430</v>
+        <v>5428</v>
       </c>
       <c r="Q294" s="59">
         <v>1085</v>
       </c>
       <c r="R294" s="1" t="s">
-        <v>5431</v>
+        <v>5429</v>
       </c>
       <c r="S294" s="59">
         <v>840</v>
       </c>
       <c r="T294" s="1" t="s">
-        <v>5432</v>
+        <v>5430</v>
       </c>
       <c r="U294" s="59">
         <v>569</v>
       </c>
       <c r="V294" s="1" t="s">
-        <v>5433</v>
+        <v>5431</v>
       </c>
       <c r="W294" s="59">
         <v>272</v>
       </c>
       <c r="X294" s="1" t="s">
-        <v>5434</v>
+        <v>5432</v>
       </c>
       <c r="Y294" s="59">
         <v>195</v>
       </c>
       <c r="Z294" s="1" t="s">
-        <v>5435</v>
+        <v>5433</v>
       </c>
       <c r="AA294" s="59">
         <v>106</v>
@@ -42733,75 +42813,75 @@
     </row>
     <row r="295" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A295" s="59" t="s">
-        <v>5448</v>
+        <v>5446</v>
       </c>
       <c r="C295" s="37" t="s">
-        <v>5413</v>
+        <v>5410</v>
       </c>
       <c r="D295" s="38" t="s">
-        <v>5412</v>
+        <v>5409</v>
       </c>
       <c r="E295" s="38" t="s">
-        <v>5408</v>
+        <v>5405</v>
       </c>
       <c r="F295" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=Shiba Wars：Goddess Link TD</v>
       </c>
       <c r="G295" s="38" t="s">
-        <v>5407</v>
+        <v>5404</v>
       </c>
       <c r="H295" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=Shiba Wars：Goddess Link TD</v>
       </c>
       <c r="I295" s="39" t="s">
-        <v>5455</v>
+        <v>5453</v>
       </c>
       <c r="J295" s="2" t="s">
-        <v>5427</v>
+        <v>5425</v>
       </c>
       <c r="K295" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
       <c r="L295" s="1" t="s">
-        <v>5436</v>
+        <v>5434</v>
       </c>
       <c r="M295" s="59">
         <v>1926</v>
       </c>
       <c r="N295" s="1" t="s">
-        <v>5437</v>
+        <v>5435</v>
       </c>
       <c r="O295" s="59">
         <v>1253</v>
       </c>
       <c r="P295" s="1" t="s">
-        <v>5438</v>
+        <v>5436</v>
       </c>
       <c r="Q295" s="59">
         <v>586</v>
       </c>
       <c r="R295" s="1" t="s">
-        <v>5439</v>
+        <v>5437</v>
       </c>
       <c r="S295" s="59">
         <v>272</v>
       </c>
       <c r="T295" s="1" t="s">
-        <v>5440</v>
+        <v>5438</v>
       </c>
       <c r="U295" s="59">
         <v>195</v>
       </c>
       <c r="V295" s="1" t="s">
-        <v>5441</v>
+        <v>5439</v>
       </c>
       <c r="W295" s="59">
         <v>82</v>
       </c>
       <c r="X295" s="1" t="s">
-        <v>5442</v>
+        <v>5440</v>
       </c>
       <c r="Y295" s="59">
         <v>55</v>
@@ -42815,36 +42895,36 @@
     </row>
     <row r="296" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A296" s="83" t="s">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="C296" s="37" t="s">
-        <v>5409</v>
+        <v>5406</v>
       </c>
       <c r="D296" s="38" t="s">
-        <v>5490</v>
+        <v>5488</v>
       </c>
       <c r="E296" s="38" t="s">
-        <v>5410</v>
+        <v>5407</v>
       </c>
       <c r="F296" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=熱血江湖：福利加強版</v>
       </c>
       <c r="G296" s="38" t="s">
-        <v>5411</v>
+        <v>5408</v>
       </c>
       <c r="H296" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=熱血江湖：福利加強版</v>
       </c>
       <c r="I296" s="39" t="s">
-        <v>5456</v>
+        <v>5454</v>
       </c>
       <c r="J296" s="2" t="s">
-        <v>5427</v>
+        <v>5425</v>
       </c>
       <c r="K296" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
       <c r="L296" s="1" t="s">
         <v>4889</v>
@@ -42897,69 +42977,69 @@
     </row>
     <row r="297" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A297" s="37" t="s">
-        <v>5514</v>
+        <v>5513</v>
       </c>
       <c r="C297" s="37" t="s">
-        <v>5491</v>
+        <v>5489</v>
       </c>
       <c r="D297" s="37" t="s">
-        <v>5491</v>
+        <v>5489</v>
       </c>
       <c r="E297" s="38" t="s">
-        <v>5492</v>
+        <v>5490</v>
       </c>
       <c r="F297" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=熱血主公Go</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>5501</v>
+        <v>5499</v>
       </c>
       <c r="H297" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=熱血主公Go</v>
       </c>
       <c r="I297" s="39" t="s">
-        <v>5502</v>
+        <v>5500</v>
       </c>
       <c r="J297" s="2" t="s">
-        <v>5427</v>
+        <v>5425</v>
       </c>
       <c r="K297" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>5503</v>
+        <v>5501</v>
       </c>
       <c r="M297" s="59">
         <v>2511</v>
       </c>
       <c r="N297" s="1" t="s">
-        <v>5504</v>
+        <v>5502</v>
       </c>
       <c r="O297" s="59">
         <v>1275</v>
       </c>
       <c r="P297" s="1" t="s">
-        <v>5505</v>
+        <v>5503</v>
       </c>
       <c r="Q297" s="59">
         <v>855</v>
       </c>
       <c r="R297" s="1" t="s">
-        <v>5506</v>
+        <v>5504</v>
       </c>
       <c r="S297" s="59">
         <v>423</v>
       </c>
       <c r="T297" s="1" t="s">
-        <v>5507</v>
+        <v>5505</v>
       </c>
       <c r="U297" s="59">
         <v>153</v>
       </c>
       <c r="V297" s="1" t="s">
-        <v>5508</v>
+        <v>5506</v>
       </c>
       <c r="W297" s="59">
         <v>31</v>
@@ -42967,87 +43047,87 @@
     </row>
     <row r="298" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A298" s="83" t="s">
-        <v>5550</v>
+        <v>5549</v>
       </c>
       <c r="C298" s="37" t="s">
+        <v>5535</v>
+      </c>
+      <c r="D298" s="38" t="s">
+        <v>5537</v>
+      </c>
+      <c r="E298" s="38" t="s">
         <v>5536</v>
-      </c>
-      <c r="D298" s="38" t="s">
-        <v>5538</v>
-      </c>
-      <c r="E298" s="38" t="s">
-        <v>5537</v>
       </c>
       <c r="F298" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=歡迎來到夢樂園</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>5554</v>
+        <v>5553</v>
       </c>
       <c r="H298" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=歡迎來到夢樂園</v>
       </c>
       <c r="I298" s="39" t="s">
-        <v>5555</v>
+        <v>5554</v>
       </c>
       <c r="J298" s="2" t="s">
-        <v>5427</v>
+        <v>5425</v>
       </c>
       <c r="K298" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
       <c r="L298" s="1" t="s">
-        <v>5559</v>
+        <v>5558</v>
       </c>
       <c r="M298" s="59">
         <v>2763</v>
       </c>
       <c r="N298" s="1" t="s">
-        <v>5560</v>
+        <v>5559</v>
       </c>
       <c r="O298" s="59">
         <v>1446</v>
       </c>
       <c r="P298" s="1" t="s">
-        <v>5561</v>
+        <v>5560</v>
       </c>
       <c r="Q298" s="59">
         <v>751</v>
       </c>
       <c r="R298" s="1" t="s">
-        <v>5562</v>
+        <v>5561</v>
       </c>
       <c r="S298" s="59">
         <v>371</v>
       </c>
       <c r="T298" s="1" t="s">
-        <v>5563</v>
+        <v>5562</v>
       </c>
       <c r="U298" s="59">
         <v>319</v>
       </c>
       <c r="V298" s="1" t="s">
-        <v>5564</v>
+        <v>5563</v>
       </c>
       <c r="W298" s="59">
         <v>117</v>
       </c>
       <c r="X298" s="1" t="s">
-        <v>5565</v>
+        <v>5564</v>
       </c>
       <c r="Y298" s="59">
         <v>46</v>
       </c>
       <c r="Z298" s="1" t="s">
-        <v>5566</v>
+        <v>5565</v>
       </c>
       <c r="AA298" s="59">
         <v>117</v>
       </c>
       <c r="AB298" s="1" t="s">
-        <v>5567</v>
+        <v>5566</v>
       </c>
       <c r="AC298" s="59">
         <v>90</v>
@@ -43061,149 +43141,149 @@
     </row>
     <row r="299" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A299" s="59" t="s">
-        <v>5551</v>
+        <v>5550</v>
       </c>
       <c r="C299" s="37" t="s">
+        <v>5540</v>
+      </c>
+      <c r="D299" s="38" t="s">
+        <v>5539</v>
+      </c>
+      <c r="E299" s="38" t="s">
         <v>5541</v>
-      </c>
-      <c r="D299" s="38" t="s">
-        <v>5540</v>
-      </c>
-      <c r="E299" s="38" t="s">
-        <v>5542</v>
       </c>
       <c r="F299" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=Cryowar</v>
       </c>
       <c r="G299" s="38" t="s">
-        <v>5539</v>
+        <v>5538</v>
       </c>
       <c r="H299" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=Cryowar</v>
       </c>
       <c r="I299" s="39" t="s">
-        <v>5556</v>
+        <v>5555</v>
       </c>
       <c r="J299" s="2" t="s">
-        <v>5427</v>
+        <v>5425</v>
       </c>
       <c r="K299" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="300" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A300" s="83" t="s">
-        <v>5552</v>
+        <v>5551</v>
       </c>
       <c r="C300" s="37" t="s">
+        <v>5544</v>
+      </c>
+      <c r="D300" s="38" t="s">
         <v>5545</v>
       </c>
-      <c r="D300" s="38" t="s">
-        <v>5546</v>
-      </c>
       <c r="E300" s="38" t="s">
-        <v>5544</v>
+        <v>5543</v>
       </c>
       <c r="F300" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=深岩銀河：倖存者</v>
       </c>
       <c r="G300" s="38" t="s">
-        <v>5543</v>
+        <v>5542</v>
       </c>
       <c r="H300" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=深岩銀河：倖存者</v>
       </c>
       <c r="I300" s="39" t="s">
-        <v>5557</v>
+        <v>5556</v>
       </c>
       <c r="J300" s="2" t="s">
-        <v>5427</v>
+        <v>5425</v>
       </c>
       <c r="K300" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="301" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A301" s="93" t="s">
-        <v>5553</v>
+        <v>5552</v>
       </c>
       <c r="C301" s="92" t="s">
-        <v>5549</v>
+        <v>5548</v>
       </c>
       <c r="D301" s="38" t="s">
         <v>3688</v>
       </c>
       <c r="E301" s="38" t="s">
-        <v>5547</v>
+        <v>5546</v>
       </c>
       <c r="F301" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=熱血排球少女</v>
       </c>
       <c r="G301" s="38" t="s">
-        <v>5548</v>
+        <v>5547</v>
       </c>
       <c r="H301" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=熱血排球少女</v>
       </c>
       <c r="I301" s="39" t="s">
-        <v>5558</v>
+        <v>5557</v>
       </c>
       <c r="J301" s="2" t="s">
-        <v>5427</v>
+        <v>5425</v>
       </c>
       <c r="K301" s="88" t="s">
-        <v>5258</v>
+        <v>5511</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>5568</v>
+        <v>5567</v>
       </c>
       <c r="M301" s="59">
         <v>1959</v>
       </c>
       <c r="N301" s="1" t="s">
-        <v>5569</v>
+        <v>5568</v>
       </c>
       <c r="O301" s="59">
         <v>1104</v>
       </c>
       <c r="P301" s="1" t="s">
-        <v>5570</v>
+        <v>5569</v>
       </c>
       <c r="Q301" s="59">
         <v>682</v>
       </c>
       <c r="R301" s="1" t="s">
-        <v>5571</v>
+        <v>5570</v>
       </c>
       <c r="S301" s="59">
         <v>262</v>
       </c>
       <c r="T301" s="1" t="s">
-        <v>5572</v>
+        <v>5571</v>
       </c>
       <c r="U301" s="59">
         <v>108</v>
       </c>
       <c r="V301" s="1" t="s">
-        <v>5573</v>
+        <v>5572</v>
       </c>
       <c r="W301" s="59">
         <v>1104</v>
       </c>
       <c r="X301" s="1" t="s">
-        <v>5574</v>
+        <v>5573</v>
       </c>
       <c r="Y301" s="59">
         <v>276</v>
       </c>
       <c r="Z301" s="1" t="s">
-        <v>5575</v>
+        <v>5574</v>
       </c>
       <c r="AA301" s="59">
         <v>108</v>
@@ -43211,130 +43291,262 @@
     </row>
     <row r="302" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A302" s="59" t="s">
-        <v>5576</v>
+        <v>5575</v>
       </c>
       <c r="C302" s="37" t="s">
-        <v>5584</v>
+        <v>5583</v>
       </c>
       <c r="D302" s="38" t="s">
-        <v>5583</v>
+        <v>5582</v>
       </c>
       <c r="E302" s="38" t="s">
-        <v>5581</v>
+        <v>5580</v>
       </c>
       <c r="F302" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=Jetpack Joyride Racing</v>
       </c>
       <c r="G302" s="38" t="s">
-        <v>5582</v>
+        <v>5581</v>
       </c>
       <c r="H302" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=Jetpack Joyride Racing</v>
       </c>
+      <c r="J302" s="2" t="s">
+        <v>5425</v>
+      </c>
+      <c r="K302" s="88" t="s">
+        <v>5511</v>
+      </c>
+      <c r="L302" s="1" t="s">
+        <v>5623</v>
+      </c>
+      <c r="M302" s="59">
+        <v>864</v>
+      </c>
+      <c r="N302" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="O302" s="59">
+        <v>84</v>
+      </c>
     </row>
     <row r="303" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A303" s="59" t="s">
-        <v>5577</v>
+        <v>5576</v>
       </c>
       <c r="C303" s="37" t="s">
-        <v>5588</v>
+        <v>5587</v>
       </c>
       <c r="D303" s="38" t="s">
-        <v>5587</v>
+        <v>5586</v>
       </c>
       <c r="E303" s="38" t="s">
-        <v>5585</v>
+        <v>5584</v>
       </c>
       <c r="F303" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=三國格子爭奪戰</v>
       </c>
       <c r="G303" s="38" t="s">
-        <v>5586</v>
+        <v>5585</v>
       </c>
       <c r="H303" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=三國格子爭奪戰</v>
       </c>
+      <c r="J303" s="2" t="s">
+        <v>5425</v>
+      </c>
+      <c r="K303" s="88" t="s">
+        <v>5511</v>
+      </c>
+      <c r="L303" s="1" t="s">
+        <v>5008</v>
+      </c>
+      <c r="M303" s="59">
+        <v>2793</v>
+      </c>
+      <c r="N303" s="1" t="s">
+        <v>5009</v>
+      </c>
+      <c r="O303" s="59">
+        <v>1462</v>
+      </c>
+      <c r="P303" s="1" t="s">
+        <v>5010</v>
+      </c>
+      <c r="Q303" s="59">
+        <v>585</v>
+      </c>
+      <c r="R303" s="1" t="s">
+        <v>5011</v>
+      </c>
+      <c r="S303" s="59">
+        <v>288</v>
+      </c>
+      <c r="T303" s="1" t="s">
+        <v>5012</v>
+      </c>
+      <c r="U303" s="59">
+        <v>155</v>
+      </c>
+      <c r="V303" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="W303" s="59">
+        <v>31</v>
+      </c>
     </row>
     <row r="304" spans="1:31" ht="22.5" customHeight="1" thickBot="1">
       <c r="A304" s="59" t="s">
-        <v>5578</v>
+        <v>5577</v>
       </c>
       <c r="C304" s="37" t="s">
+        <v>5590</v>
+      </c>
+      <c r="D304" s="38" t="s">
+        <v>5589</v>
+      </c>
+      <c r="E304" s="38" t="s">
         <v>5591</v>
-      </c>
-      <c r="D304" s="38" t="s">
-        <v>5590</v>
-      </c>
-      <c r="E304" s="38" t="s">
-        <v>5592</v>
       </c>
       <c r="F304" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=貓茶小當家：掌櫃養成記</v>
       </c>
       <c r="G304" s="38" t="s">
-        <v>5589</v>
+        <v>5588</v>
       </c>
       <c r="H304" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=貓茶小當家：掌櫃養成記</v>
       </c>
-    </row>
-    <row r="305" spans="1:8" ht="22.5" customHeight="1">
+      <c r="J304" s="2" t="s">
+        <v>5425</v>
+      </c>
+      <c r="K304" s="88" t="s">
+        <v>5511</v>
+      </c>
+      <c r="L304" s="1" t="s">
+        <v>5614</v>
+      </c>
+      <c r="M304" s="59">
+        <v>2539</v>
+      </c>
+      <c r="N304" s="1" t="s">
+        <v>5615</v>
+      </c>
+      <c r="O304" s="59">
+        <v>1289</v>
+      </c>
+      <c r="P304" s="1" t="s">
+        <v>5616</v>
+      </c>
+      <c r="Q304" s="59">
+        <v>864</v>
+      </c>
+      <c r="R304" s="1" t="s">
+        <v>5617</v>
+      </c>
+      <c r="S304" s="59">
+        <v>602</v>
+      </c>
+      <c r="T304" s="1" t="s">
+        <v>5618</v>
+      </c>
+      <c r="U304" s="59">
+        <v>428</v>
+      </c>
+      <c r="V304" s="1" t="s">
+        <v>5619</v>
+      </c>
+      <c r="W304" s="59">
+        <v>279</v>
+      </c>
+      <c r="X304" s="1" t="s">
+        <v>5620</v>
+      </c>
+      <c r="Y304" s="59">
+        <v>137</v>
+      </c>
+      <c r="Z304" s="1" t="s">
+        <v>5621</v>
+      </c>
+      <c r="AA304" s="59">
+        <v>110</v>
+      </c>
+      <c r="AB304" s="1" t="s">
+        <v>5622</v>
+      </c>
+      <c r="AC304" s="59">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11" ht="22.5" customHeight="1">
       <c r="A305" s="84" t="s">
-        <v>5579</v>
+        <v>5578</v>
       </c>
       <c r="C305" s="37" t="s">
-        <v>5600</v>
+        <v>5599</v>
       </c>
       <c r="D305" s="38" t="s">
-        <v>5595</v>
+        <v>5594</v>
       </c>
       <c r="E305" s="38" t="s">
-        <v>5593</v>
+        <v>5592</v>
       </c>
       <c r="F305" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=Viladia：精靈村的時光</v>
       </c>
       <c r="G305" s="38" t="s">
-        <v>5594</v>
+        <v>5593</v>
       </c>
       <c r="H305" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=Viladia：精靈村的時光</v>
       </c>
-    </row>
-    <row r="306" spans="1:8" ht="22.5" customHeight="1">
+      <c r="J305" s="2" t="s">
+        <v>5425</v>
+      </c>
+      <c r="K305" s="88" t="s">
+        <v>5511</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11" ht="22.5" customHeight="1">
       <c r="A306" s="84" t="s">
-        <v>5580</v>
+        <v>5579</v>
       </c>
       <c r="C306" s="37" t="s">
-        <v>5599</v>
+        <v>5598</v>
       </c>
       <c r="D306" s="38" t="s">
+        <v>5595</v>
+      </c>
+      <c r="E306" s="38" t="s">
         <v>5596</v>
-      </c>
-      <c r="E306" s="38" t="s">
-        <v>5597</v>
       </c>
       <c r="F306" s="37" t="str">
         <f t="shared" si="12"/>
         <v>gift-codes.html?game=G9：特功聯盟</v>
       </c>
       <c r="G306" s="38" t="s">
-        <v>5598</v>
+        <v>5597</v>
       </c>
       <c r="H306" s="38" t="str">
         <f t="shared" si="13"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=G9：特功聯盟</v>
       </c>
-    </row>
-    <row r="307" spans="1:8" ht="22.5" customHeight="1">
+      <c r="J306" s="2" t="s">
+        <v>5425</v>
+      </c>
+      <c r="K306" s="88" t="s">
+        <v>5511</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11" ht="22.5" customHeight="1">
       <c r="F307" s="37" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -43344,7 +43556,7 @@
         <v/>
       </c>
     </row>
-    <row r="308" spans="1:8" ht="22.5" customHeight="1">
+    <row r="308" spans="1:11" ht="22.5" customHeight="1">
       <c r="F308" s="37" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -43354,7 +43566,7 @@
         <v/>
       </c>
     </row>
-    <row r="309" spans="1:8" ht="22.5" customHeight="1">
+    <row r="309" spans="1:11" ht="22.5" customHeight="1">
       <c r="F309" s="37" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -43364,7 +43576,7 @@
         <v/>
       </c>
     </row>
-    <row r="310" spans="1:8" ht="22.5" customHeight="1">
+    <row r="310" spans="1:11" ht="22.5" customHeight="1">
       <c r="F310" s="37" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -43374,7 +43586,7 @@
         <v/>
       </c>
     </row>
-    <row r="311" spans="1:8" ht="22.5" customHeight="1">
+    <row r="311" spans="1:11" ht="22.5" customHeight="1">
       <c r="F311" s="37" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -43384,7 +43596,7 @@
         <v/>
       </c>
     </row>
-    <row r="312" spans="1:8" ht="22.5" customHeight="1">
+    <row r="312" spans="1:11" ht="22.5" customHeight="1">
       <c r="F312" s="37" t="str">
         <f t="shared" ref="F312:F375" si="14">IF(A312="", "", "gift-codes.html?game=" &amp; A312)</f>
         <v/>
@@ -43394,7 +43606,7 @@
         <v/>
       </c>
     </row>
-    <row r="313" spans="1:8" ht="22.5" customHeight="1">
+    <row r="313" spans="1:11" ht="22.5" customHeight="1">
       <c r="F313" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -43404,7 +43616,7 @@
         <v/>
       </c>
     </row>
-    <row r="314" spans="1:8" ht="22.5" customHeight="1">
+    <row r="314" spans="1:11" ht="22.5" customHeight="1">
       <c r="F314" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -43414,7 +43626,7 @@
         <v/>
       </c>
     </row>
-    <row r="315" spans="1:8" ht="22.5" customHeight="1">
+    <row r="315" spans="1:11" ht="22.5" customHeight="1">
       <c r="F315" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -43424,7 +43636,7 @@
         <v/>
       </c>
     </row>
-    <row r="316" spans="1:8" ht="22.5" customHeight="1">
+    <row r="316" spans="1:11" ht="22.5" customHeight="1">
       <c r="F316" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -43434,7 +43646,7 @@
         <v/>
       </c>
     </row>
-    <row r="317" spans="1:8" ht="22.5" customHeight="1">
+    <row r="317" spans="1:11" ht="22.5" customHeight="1">
       <c r="F317" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -43444,7 +43656,7 @@
         <v/>
       </c>
     </row>
-    <row r="318" spans="1:8" ht="22.5" customHeight="1">
+    <row r="318" spans="1:11" ht="22.5" customHeight="1">
       <c r="F318" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -43454,7 +43666,7 @@
         <v/>
       </c>
     </row>
-    <row r="319" spans="1:8" ht="22.5" customHeight="1">
+    <row r="319" spans="1:11" ht="22.5" customHeight="1">
       <c r="F319" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -43464,7 +43676,7 @@
         <v/>
       </c>
     </row>
-    <row r="320" spans="1:8" ht="22.5" customHeight="1">
+    <row r="320" spans="1:11" ht="22.5" customHeight="1">
       <c r="F320" s="37" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -46529,8 +46741,8 @@
     <hyperlink ref="G276" r:id="rId211"/>
     <hyperlink ref="G280" r:id="rId212"/>
     <hyperlink ref="G281" r:id="rId213"/>
-    <hyperlink ref="AB281" r:id="rId214"/>
-    <hyperlink ref="X280" r:id="rId215"/>
+    <hyperlink ref="AB281" r:id="rId214" display="最新價格請洽Line@"/>
+    <hyperlink ref="X280" r:id="rId215" display="最新價格請洽Line@"/>
     <hyperlink ref="G282" r:id="rId216"/>
     <hyperlink ref="G283" r:id="rId217"/>
     <hyperlink ref="G284" r:id="rId218"/>
@@ -46538,68 +46750,68 @@
     <hyperlink ref="G286" r:id="rId220"/>
     <hyperlink ref="G287" r:id="rId221"/>
     <hyperlink ref="G288" r:id="rId222"/>
-    <hyperlink ref="V285" r:id="rId223"/>
-    <hyperlink ref="AD282" r:id="rId224"/>
-    <hyperlink ref="Z283" r:id="rId225"/>
-    <hyperlink ref="AD284" r:id="rId226"/>
-    <hyperlink ref="AD278" r:id="rId227"/>
-    <hyperlink ref="Z277" r:id="rId228"/>
-    <hyperlink ref="Z275" r:id="rId229"/>
-    <hyperlink ref="AD274" r:id="rId230"/>
-    <hyperlink ref="AD273" r:id="rId231"/>
-    <hyperlink ref="X272" r:id="rId232"/>
-    <hyperlink ref="AD271" r:id="rId233"/>
-    <hyperlink ref="R270" r:id="rId234"/>
-    <hyperlink ref="AB269" r:id="rId235"/>
-    <hyperlink ref="AD268" r:id="rId236"/>
-    <hyperlink ref="AD267" r:id="rId237"/>
-    <hyperlink ref="Z266" r:id="rId238"/>
-    <hyperlink ref="AD265" r:id="rId239"/>
-    <hyperlink ref="AH263" r:id="rId240"/>
-    <hyperlink ref="V262" r:id="rId241"/>
-    <hyperlink ref="Z261" r:id="rId242"/>
-    <hyperlink ref="AD260" r:id="rId243"/>
-    <hyperlink ref="AB259" r:id="rId244"/>
-    <hyperlink ref="AF258" r:id="rId245"/>
-    <hyperlink ref="AD257" r:id="rId246"/>
-    <hyperlink ref="X256" r:id="rId247"/>
-    <hyperlink ref="X255" r:id="rId248"/>
-    <hyperlink ref="Z254" r:id="rId249"/>
-    <hyperlink ref="AF253" r:id="rId250"/>
-    <hyperlink ref="AD252" r:id="rId251"/>
-    <hyperlink ref="V251" r:id="rId252"/>
-    <hyperlink ref="X250" r:id="rId253"/>
-    <hyperlink ref="Z249" r:id="rId254"/>
-    <hyperlink ref="AB248" r:id="rId255"/>
-    <hyperlink ref="X247" r:id="rId256"/>
-    <hyperlink ref="R246" r:id="rId257"/>
-    <hyperlink ref="X245" r:id="rId258"/>
-    <hyperlink ref="AD244" r:id="rId259"/>
-    <hyperlink ref="AB243" r:id="rId260"/>
-    <hyperlink ref="X242" r:id="rId261"/>
-    <hyperlink ref="AB241" r:id="rId262"/>
-    <hyperlink ref="V240" r:id="rId263"/>
-    <hyperlink ref="AB239" r:id="rId264"/>
-    <hyperlink ref="X238" r:id="rId265"/>
-    <hyperlink ref="AD237" r:id="rId266"/>
-    <hyperlink ref="AF236" r:id="rId267"/>
-    <hyperlink ref="AB235" r:id="rId268"/>
-    <hyperlink ref="AD234" r:id="rId269"/>
-    <hyperlink ref="AD232" r:id="rId270"/>
-    <hyperlink ref="AB231" r:id="rId271"/>
-    <hyperlink ref="AH230" r:id="rId272"/>
-    <hyperlink ref="AD229" r:id="rId273"/>
-    <hyperlink ref="AD228" r:id="rId274"/>
-    <hyperlink ref="AF227" r:id="rId275"/>
-    <hyperlink ref="V226" r:id="rId276"/>
-    <hyperlink ref="V224" r:id="rId277"/>
-    <hyperlink ref="AH223" r:id="rId278"/>
-    <hyperlink ref="J288" r:id="rId279"/>
-    <hyperlink ref="Z276" r:id="rId280"/>
-    <hyperlink ref="AB286" r:id="rId281"/>
-    <hyperlink ref="AD289" r:id="rId282"/>
-    <hyperlink ref="X279" r:id="rId283"/>
-    <hyperlink ref="AB287" r:id="rId284"/>
+    <hyperlink ref="V285" r:id="rId223" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD282" r:id="rId224" display="最新價格請洽Line@"/>
+    <hyperlink ref="Z283" r:id="rId225" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD284" r:id="rId226" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD278" r:id="rId227" display="最新價格請洽Line@"/>
+    <hyperlink ref="Z277" r:id="rId228" display="最新價格請洽Line@"/>
+    <hyperlink ref="Z275" r:id="rId229" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD274" r:id="rId230" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD273" r:id="rId231" display="最新價格請洽Line@"/>
+    <hyperlink ref="X272" r:id="rId232" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD271" r:id="rId233" display="最新價格請洽Line@"/>
+    <hyperlink ref="R270" r:id="rId234" display="最新價格請洽Line@"/>
+    <hyperlink ref="AB269" r:id="rId235" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD268" r:id="rId236" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD267" r:id="rId237" display="最新價格請洽Line@"/>
+    <hyperlink ref="Z266" r:id="rId238" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD265" r:id="rId239" display="最新價格請洽Line@"/>
+    <hyperlink ref="AH263" r:id="rId240" display="最新價格請洽Line@"/>
+    <hyperlink ref="V262" r:id="rId241" display="最新價格請洽Line@"/>
+    <hyperlink ref="Z261" r:id="rId242" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD260" r:id="rId243" display="最新價格請洽Line@"/>
+    <hyperlink ref="AB259" r:id="rId244" display="最新價格請洽Line@"/>
+    <hyperlink ref="AF258" r:id="rId245" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD257" r:id="rId246" display="最新價格請洽Line@"/>
+    <hyperlink ref="X256" r:id="rId247" display="最新價格請洽Line@"/>
+    <hyperlink ref="X255" r:id="rId248" display="最新價格請洽Line@"/>
+    <hyperlink ref="Z254" r:id="rId249" display="最新價格請洽Line@"/>
+    <hyperlink ref="AF253" r:id="rId250" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD252" r:id="rId251" display="最新價格請洽Line@"/>
+    <hyperlink ref="V251" r:id="rId252" display="最新價格請洽Line@"/>
+    <hyperlink ref="X250" r:id="rId253" display="最新價格請洽Line@"/>
+    <hyperlink ref="Z249" r:id="rId254" display="最新價格請洽Line@"/>
+    <hyperlink ref="AB248" r:id="rId255" display="最新價格請洽Line@"/>
+    <hyperlink ref="X247" r:id="rId256" display="最新價格請洽Line@"/>
+    <hyperlink ref="R246" r:id="rId257" display="最新價格請洽Line@"/>
+    <hyperlink ref="X245" r:id="rId258" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD244" r:id="rId259" display="最新價格請洽Line@"/>
+    <hyperlink ref="AB243" r:id="rId260" display="最新價格請洽Line@"/>
+    <hyperlink ref="X242" r:id="rId261" display="最新價格請洽Line@"/>
+    <hyperlink ref="AB241" r:id="rId262" display="最新價格請洽Line@"/>
+    <hyperlink ref="V240" r:id="rId263" display="最新價格請洽Line@"/>
+    <hyperlink ref="AB239" r:id="rId264" display="最新價格請洽Line@"/>
+    <hyperlink ref="X238" r:id="rId265" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD237" r:id="rId266" display="最新價格請洽Line@"/>
+    <hyperlink ref="AF236" r:id="rId267" display="最新價格請洽Line@"/>
+    <hyperlink ref="AB235" r:id="rId268" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD234" r:id="rId269" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD232" r:id="rId270" display="最新價格請洽Line@"/>
+    <hyperlink ref="AB231" r:id="rId271" display="最新價格請洽Line@"/>
+    <hyperlink ref="AH230" r:id="rId272" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD229" r:id="rId273" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD228" r:id="rId274" display="最新價格請洽Line@"/>
+    <hyperlink ref="AF227" r:id="rId275" display="最新價格請洽Line@"/>
+    <hyperlink ref="V226" r:id="rId276" display="最新價格請洽Line@"/>
+    <hyperlink ref="V224" r:id="rId277" display="最新價格請洽Line@"/>
+    <hyperlink ref="AH223" r:id="rId278" display="最新價格請洽Line@"/>
+    <hyperlink ref="J288" r:id="rId279" display="最新價格請洽Line@"/>
+    <hyperlink ref="Z276" r:id="rId280" display="最新價格請洽Line@"/>
+    <hyperlink ref="AB286" r:id="rId281" display="最新價格請洽Line@"/>
+    <hyperlink ref="AD289" r:id="rId282" display="最新價格請洽Line@"/>
+    <hyperlink ref="X279" r:id="rId283" display="最新價格請洽Line@"/>
+    <hyperlink ref="AB287" r:id="rId284" display="最新價格請洽Line@"/>
     <hyperlink ref="G297"/>
     <hyperlink ref="G298" r:id="rId285"/>
   </hyperlinks>
@@ -61285,46 +61497,64 @@
         <v>5026</v>
       </c>
       <c r="W236" s="15" t="s">
+        <v>5206</v>
+      </c>
+      <c r="X236" s="10" t="s">
+        <v>5218</v>
+      </c>
+      <c r="Y236" s="15" t="s">
         <v>5207</v>
       </c>
-      <c r="X236" s="10" t="s">
-        <v>5220</v>
-      </c>
-      <c r="Y236" s="15" t="s">
+      <c r="Z236" s="10" t="s">
+        <v>5217</v>
+      </c>
+      <c r="AA236" s="15" t="s">
         <v>5208</v>
       </c>
-      <c r="Z236" s="10" t="s">
-        <v>5219</v>
-      </c>
-      <c r="AA236" s="15" t="s">
+      <c r="AB236" s="10" t="s">
+        <v>5216</v>
+      </c>
+      <c r="AC236" s="15" t="s">
         <v>5209</v>
       </c>
-      <c r="AB236" s="10" t="s">
-        <v>5218</v>
-      </c>
-      <c r="AC236" s="15" t="s">
+      <c r="AD236" s="10" t="s">
+        <v>5215</v>
+      </c>
+      <c r="AE236" s="15" t="s">
         <v>5210</v>
       </c>
-      <c r="AD236" s="10" t="s">
-        <v>5217</v>
-      </c>
-      <c r="AE236" s="15" t="s">
+      <c r="AF236" s="10" t="s">
+        <v>5214</v>
+      </c>
+      <c r="AG236" s="15" t="s">
         <v>5211</v>
       </c>
-      <c r="AF236" s="10" t="s">
-        <v>5216</v>
-      </c>
-      <c r="AG236" s="15" t="s">
+      <c r="AH236" s="10" t="s">
+        <v>5213</v>
+      </c>
+      <c r="AI236" s="15" t="s">
         <v>5212</v>
       </c>
-      <c r="AH236" s="10" t="s">
-        <v>5215</v>
-      </c>
-      <c r="AI236" s="15" t="s">
-        <v>5213</v>
-      </c>
       <c r="AJ236" s="10" t="s">
-        <v>5214</v>
+        <v>5602</v>
+      </c>
+      <c r="AK236" s="15" t="s">
+        <v>5600</v>
+      </c>
+      <c r="AL236" s="10" t="s">
+        <v>5603</v>
+      </c>
+      <c r="AM236" s="15" t="s">
+        <v>4992</v>
+      </c>
+      <c r="AN236" s="10" t="s">
+        <v>5604</v>
+      </c>
+      <c r="AO236" s="15" t="s">
+        <v>5601</v>
+      </c>
+      <c r="AP236" s="10" t="s">
+        <v>5605</v>
       </c>
     </row>
     <row r="237" spans="1:47" ht="22.5" customHeight="1">
@@ -62666,10 +62896,10 @@
         <v>《Awakenloop》是一款充滿賽博龐克風格的卡牌回合制手遊，玩家將身處一個由機器人與人類共存的末日世界。遊戲主打策略性卡牌戰鬥，每張卡牌都蘊含獨特技能，如何搭配與釋放將成為戰局關鍵。除了豐富的主線劇情，遊戲也提供多樣的副本挑戰與 PvP 模式，讓你與其他玩家一較高下。現在就加入《Awakenloop》，透過兌換碼與禮包碼獲得專屬獎勵，輕鬆提升戰力，也能使用代儲值服務快速安全地補充資源，在這片混沌的廢土上開創屬於你的新紀元。</v>
       </c>
       <c r="F269" s="14" t="s">
+        <v>5192</v>
+      </c>
+      <c r="G269" s="10" t="s">
         <v>5193</v>
-      </c>
-      <c r="G269" s="10" t="s">
-        <v>5194</v>
       </c>
       <c r="H269" s="10" t="s">
         <v>2625</v>
@@ -62678,16 +62908,16 @@
         <v>4360</v>
       </c>
       <c r="K269" s="14" t="s">
+        <v>5188</v>
+      </c>
+      <c r="L269" s="10" t="s">
+        <v>5191</v>
+      </c>
+      <c r="M269" s="15" t="s">
         <v>5189</v>
       </c>
-      <c r="L269" s="10" t="s">
-        <v>5192</v>
-      </c>
-      <c r="M269" s="15" t="s">
+      <c r="N269" s="10" t="s">
         <v>5190</v>
-      </c>
-      <c r="N269" s="10" t="s">
-        <v>5191</v>
       </c>
     </row>
     <row r="270" spans="1:31">
@@ -62849,28 +63079,28 @@
         <v>5066</v>
       </c>
       <c r="W273" s="15" t="s">
+        <v>5197</v>
+      </c>
+      <c r="X273" s="10" t="s">
+        <v>5201</v>
+      </c>
+      <c r="Y273" s="15" t="s">
         <v>5198</v>
       </c>
-      <c r="X273" s="10" t="s">
+      <c r="Z273" s="10" t="s">
         <v>5202</v>
       </c>
-      <c r="Y273" s="15" t="s">
+      <c r="AA273" s="15" t="s">
         <v>5199</v>
       </c>
-      <c r="Z273" s="10" t="s">
+      <c r="AB273" s="10" t="s">
         <v>5203</v>
       </c>
-      <c r="AA273" s="15" t="s">
+      <c r="AC273" s="15" t="s">
         <v>5200</v>
       </c>
-      <c r="AB273" s="10" t="s">
+      <c r="AD273" s="10" t="s">
         <v>5204</v>
-      </c>
-      <c r="AC273" s="15" t="s">
-        <v>5201</v>
-      </c>
-      <c r="AD273" s="10" t="s">
-        <v>5205</v>
       </c>
     </row>
     <row r="274" spans="1:42">
@@ -62921,10 +63151,10 @@
         <v>5001</v>
       </c>
       <c r="Q274" s="89" t="s">
-        <v>5463</v>
+        <v>5461</v>
       </c>
       <c r="R274" s="10" t="s">
-        <v>5457</v>
+        <v>5455</v>
       </c>
     </row>
     <row r="275" spans="1:42">
@@ -62990,10 +63220,10 @@
         <v>5108</v>
       </c>
       <c r="AA275" s="89" t="s">
-        <v>5463</v>
+        <v>5461</v>
       </c>
       <c r="AB275" s="10" t="s">
-        <v>5457</v>
+        <v>5455</v>
       </c>
     </row>
     <row r="276" spans="1:42">
@@ -63038,10 +63268,10 @@
         <v>5112</v>
       </c>
       <c r="Q276" s="89" t="s">
-        <v>5463</v>
+        <v>5461</v>
       </c>
       <c r="R276" s="10" t="s">
-        <v>5457</v>
+        <v>5455</v>
       </c>
     </row>
     <row r="277" spans="1:42">
@@ -63074,10 +63304,10 @@
         <v>4360</v>
       </c>
       <c r="K277" s="89" t="s">
-        <v>5463</v>
+        <v>5461</v>
       </c>
       <c r="L277" s="10" t="s">
-        <v>5457</v>
+        <v>5455</v>
       </c>
     </row>
     <row r="278" spans="1:42">
@@ -63098,31 +63328,31 @@
         <v>全新星緣卡牌 RPG《星痕共鳴》，邀你一同編織命運的篇章。遊戲擁有宏大的世界觀與超過百萬字的豐富劇情，玩家將扮演「星源之主」，與眾多「星痕者」締結羈絆，共同對抗虛空的威脅。獨特的「星盤」系統與高策略性的卡牌戰鬥，讓每場對決都充滿變數。想要輕鬆推圖、快速成長？記得在各大社群與論壇尋找隱藏的兌換碼與禮包碼，領取豐厚資源。如果想快人一步，最聰明的選擇就是尋找可靠的代儲值管道，提供您快速安全的支援，讓你的冒險旅程更加順遂。</v>
       </c>
       <c r="F278" s="14" t="s">
+        <v>5244</v>
+      </c>
+      <c r="G278" s="10" t="s">
+        <v>5245</v>
+      </c>
+      <c r="H278" s="10" t="s">
         <v>5246</v>
       </c>
-      <c r="G278" s="10" t="s">
-        <v>5247</v>
-      </c>
-      <c r="H278" s="10" t="s">
-        <v>5248</v>
-      </c>
       <c r="K278" s="14" t="s">
+        <v>5240</v>
+      </c>
+      <c r="L278" s="10" t="s">
+        <v>5243</v>
+      </c>
+      <c r="M278" s="15" t="s">
+        <v>5241</v>
+      </c>
+      <c r="N278" s="10" t="s">
         <v>5242</v>
       </c>
-      <c r="L278" s="10" t="s">
-        <v>5245</v>
-      </c>
-      <c r="M278" s="15" t="s">
-        <v>5243</v>
-      </c>
-      <c r="N278" s="10" t="s">
-        <v>5244</v>
-      </c>
       <c r="O278" s="89" t="s">
-        <v>5463</v>
+        <v>5461</v>
       </c>
       <c r="P278" s="10" t="s">
-        <v>5457</v>
+        <v>5455</v>
       </c>
     </row>
     <row r="279" spans="1:42">
@@ -63143,13 +63373,13 @@
         <v>備受矚目的 3D 動作 RPG《二重螺旋》強勢來襲！本作主打高速、爽快的戰鬥體驗，玩家將在一個近未來科幻世界中，扮演擁有特殊能力的「適格者」，探索神秘的「深淵」。遊戲強調華麗的連擊與多樣化的武器系統，你可以自由切換遠近程攻擊，打出屬於自己的戰鬥風格。為了讓你的探索之路更加順利，官方會不定期發放福利兌換碼與禮包碼，千萬別錯過。當然，面對強大的敵人，尋求專業的代儲值協助，以快速安全的方式強化戰力，絕對是高效的致勝關鍵。</v>
       </c>
       <c r="F279" s="14" t="s">
-        <v>5321</v>
+        <v>5318</v>
       </c>
       <c r="G279" s="10" t="s">
-        <v>5322</v>
+        <v>5319</v>
       </c>
       <c r="H279" s="10" t="s">
-        <v>5323</v>
+        <v>5320</v>
       </c>
       <c r="I279" s="10" t="s">
         <v>2625</v>
@@ -63158,70 +63388,70 @@
         <v>4360</v>
       </c>
       <c r="K279" s="14" t="s">
+        <v>5247</v>
+      </c>
+      <c r="L279" s="10" t="s">
+        <v>5357</v>
+      </c>
+      <c r="M279" s="15" t="s">
+        <v>5248</v>
+      </c>
+      <c r="N279" s="10" t="s">
+        <v>5358</v>
+      </c>
+      <c r="O279" s="15" t="s">
         <v>5249</v>
       </c>
-      <c r="L279" s="10" t="s">
+      <c r="P279" s="10" t="s">
+        <v>5359</v>
+      </c>
+      <c r="Q279" s="15" t="s">
+        <v>5250</v>
+      </c>
+      <c r="R279" s="10" t="s">
         <v>5360</v>
       </c>
-      <c r="M279" s="15" t="s">
-        <v>5250</v>
-      </c>
-      <c r="N279" s="10" t="s">
+      <c r="S279" s="15" t="s">
+        <v>5321</v>
+      </c>
+      <c r="T279" s="10" t="s">
         <v>5361</v>
       </c>
-      <c r="O279" s="15" t="s">
-        <v>5251</v>
-      </c>
-      <c r="P279" s="10" t="s">
+      <c r="U279" s="15" t="s">
+        <v>5322</v>
+      </c>
+      <c r="V279" s="10" t="s">
         <v>5362</v>
       </c>
-      <c r="Q279" s="15" t="s">
-        <v>5252</v>
-      </c>
-      <c r="R279" s="10" t="s">
+      <c r="W279" s="15" t="s">
+        <v>5323</v>
+      </c>
+      <c r="X279" s="10" t="s">
         <v>5363</v>
       </c>
-      <c r="S279" s="15" t="s">
+      <c r="Y279" s="15" t="s">
         <v>5324</v>
       </c>
-      <c r="T279" s="10" t="s">
+      <c r="Z279" s="10" t="s">
         <v>5364</v>
       </c>
-      <c r="U279" s="15" t="s">
+      <c r="AA279" s="15" t="s">
+        <v>5326</v>
+      </c>
+      <c r="AB279" s="10" t="s">
+        <v>5365</v>
+      </c>
+      <c r="AC279" s="15" t="s">
         <v>5325</v>
       </c>
-      <c r="V279" s="10" t="s">
-        <v>5365</v>
-      </c>
-      <c r="W279" s="15" t="s">
-        <v>5326</v>
-      </c>
-      <c r="X279" s="10" t="s">
+      <c r="AD279" s="10" t="s">
         <v>5366</v>
       </c>
-      <c r="Y279" s="15" t="s">
-        <v>5327</v>
-      </c>
-      <c r="Z279" s="10" t="s">
-        <v>5367</v>
-      </c>
-      <c r="AA279" s="15" t="s">
-        <v>5329</v>
-      </c>
-      <c r="AB279" s="10" t="s">
-        <v>5368</v>
-      </c>
-      <c r="AC279" s="15" t="s">
-        <v>5328</v>
-      </c>
-      <c r="AD279" s="10" t="s">
-        <v>5369</v>
-      </c>
       <c r="AG279" s="89" t="s">
-        <v>5463</v>
+        <v>5461</v>
       </c>
       <c r="AH279" s="10" t="s">
-        <v>5457</v>
+        <v>5455</v>
       </c>
     </row>
     <row r="280" spans="1:42">
@@ -63242,13 +63472,13 @@
         <v>《電馭跑酷》這不是你阿嬤的公園散步，這是一場高速、玩命的都市障礙賽。玩家將扮演反抗軍的跑酷精英，在高聳入雲的摩天大樓間飛簷走壁，閃避企業保全的致命追擊。遊戲主打流暢到不科學的動作系統，結合了滑鏟、二段跳與牆面奔跑，每一次的跳躍都考驗著你的反應極限。想在起跑點就領先那些菜鳥？別忘了上網找最新的「兌換碼」，輸入後就能拿到初期資源。當然，遊戲內的「禮包碼」也別錯過。想要更快地強化你的裝備，尋求專業的「代儲值」服務是個聰明的捷徑，保證快速安全讓你無後顧之憂地稱霸這座數位牢籠。</v>
       </c>
       <c r="F280" s="14" t="s">
-        <v>5241</v>
+        <v>5239</v>
       </c>
       <c r="K280" s="78" t="s">
-        <v>5458</v>
+        <v>5456</v>
       </c>
       <c r="L280" s="10" t="s">
-        <v>5459</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="281" spans="1:42">
@@ -63269,13 +63499,13 @@
         <v>《火焰紋章Shadows》你的隊伍中藏著一名背叛者！玩家在運籌帷幄同時，還必須在有限的回合內，透過戰鬥中的蛛絲馬跡找出誰是「影子」。本作繼承了系列的精美立繪與深度職業系統，但每場戰鬥都充滿了猜忌與不安。想在開局就取得優勢，揪出內鬼？記得先領取官方發送的兌換碼，充實你的兵源。隨著進度推進，各種隱藏的禮包碼更是兵家必爭之地。為了更有效率地培養你的主力部隊，許多老玩家會選擇「代儲值」來購買稀有資源，選擇信譽良好、保證快速安全的服務，才能讓你專心應對眼前的戰局與背後的謊言。</v>
       </c>
       <c r="F281" s="14" t="s">
-        <v>5241</v>
+        <v>5239</v>
       </c>
       <c r="K281" s="78" t="s">
-        <v>5458</v>
+        <v>5456</v>
       </c>
       <c r="L281" s="10" t="s">
-        <v>5459</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="282" spans="1:42">
@@ -63296,13 +63526,13 @@
         <v>經典IP《石器時代》正版授權的回合制策略大作回來啦！本作完美還原端遊，上百種寵物任你策略搭配，更支援手機、電腦多端互通，隨時都能上線抓寵。還在煩惱找不到最新的兌換碼跟禮包碼嗎？別擔心，我們都幫你準備好了！現在就跟上尼斯大陸的冒險，體驗最原汁原味的感動，需要代儲值也沒問題，絕對快速安全，讓你輕鬆跟上夥伴們的腳步，重溫年少的夢中情寵！</v>
       </c>
       <c r="F282" s="14" t="s">
-        <v>5241</v>
+        <v>5239</v>
       </c>
       <c r="K282" s="78" t="s">
-        <v>5458</v>
+        <v>5456</v>
       </c>
       <c r="L282" s="10" t="s">
-        <v>5459</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="283" spans="1:42">
@@ -63323,10 +63553,10 @@
         <v>2025年最值得一玩的全新萌系塔防手遊來啦！邪惡哥布林入侵，身為國王守護者的你，必須招募英雄抵禦入侵。遊戲主打英雄2合1加上局內3重隨機玩法，每局都有上百種策略搭配，就算是休閒玩家也能3秒上手！還在網路上苦苦搜尋可用的禮包碼和兌換碼嗎？別浪費時間了！想要快速升級，享受最爽快的割草感，尋找快速安全的代儲值服務會是你最好的選擇，立即為了蔚藍星球而戰！</v>
       </c>
       <c r="F283" s="14" t="s">
-        <v>5312</v>
+        <v>5309</v>
       </c>
       <c r="G283" s="10" t="s">
-        <v>5313</v>
+        <v>5310</v>
       </c>
       <c r="H283" s="10" t="s">
         <v>2625</v>
@@ -63335,76 +63565,76 @@
         <v>4360</v>
       </c>
       <c r="K283" s="14" t="s">
-        <v>5314</v>
+        <v>5311</v>
       </c>
       <c r="L283" s="10" t="s">
-        <v>5336</v>
+        <v>5333</v>
       </c>
       <c r="M283" s="15" t="s">
         <v>4141</v>
       </c>
       <c r="N283" s="10" t="s">
-        <v>5337</v>
+        <v>5334</v>
       </c>
       <c r="O283" s="15" t="s">
         <v>4140</v>
       </c>
       <c r="P283" s="10" t="s">
+        <v>5335</v>
+      </c>
+      <c r="Q283" s="15" t="s">
+        <v>5312</v>
+      </c>
+      <c r="R283" s="10" t="s">
+        <v>5336</v>
+      </c>
+      <c r="S283" s="15" t="s">
+        <v>5313</v>
+      </c>
+      <c r="T283" s="10" t="s">
+        <v>5337</v>
+      </c>
+      <c r="U283" s="15" t="s">
+        <v>5314</v>
+      </c>
+      <c r="V283" s="10" t="s">
+        <v>5337</v>
+      </c>
+      <c r="W283" s="15" t="s">
+        <v>5315</v>
+      </c>
+      <c r="X283" s="10" t="s">
+        <v>5337</v>
+      </c>
+      <c r="Y283" s="15" t="s">
+        <v>5316</v>
+      </c>
+      <c r="Z283" s="10" t="s">
         <v>5338</v>
-      </c>
-      <c r="Q283" s="15" t="s">
-        <v>5315</v>
-      </c>
-      <c r="R283" s="10" t="s">
-        <v>5339</v>
-      </c>
-      <c r="S283" s="15" t="s">
-        <v>5316</v>
-      </c>
-      <c r="T283" s="10" t="s">
-        <v>5340</v>
-      </c>
-      <c r="U283" s="15" t="s">
-        <v>5317</v>
-      </c>
-      <c r="V283" s="10" t="s">
-        <v>5340</v>
-      </c>
-      <c r="W283" s="15" t="s">
-        <v>5318</v>
-      </c>
-      <c r="X283" s="10" t="s">
-        <v>5340</v>
-      </c>
-      <c r="Y283" s="15" t="s">
-        <v>5319</v>
-      </c>
-      <c r="Z283" s="10" t="s">
-        <v>5341</v>
       </c>
       <c r="AA283" s="15" t="s">
         <v>2056</v>
       </c>
       <c r="AB283" s="10" t="s">
-        <v>5342</v>
+        <v>5339</v>
       </c>
       <c r="AC283" s="15" t="s">
-        <v>5320</v>
+        <v>5317</v>
       </c>
       <c r="AD283" s="10" t="s">
-        <v>5343</v>
+        <v>5340</v>
       </c>
       <c r="AE283" s="15" t="s">
-        <v>5482</v>
+        <v>5480</v>
       </c>
       <c r="AG283" s="15" t="s">
-        <v>5483</v>
+        <v>5481</v>
       </c>
       <c r="AI283" s="89" t="s">
-        <v>5463</v>
+        <v>5461</v>
       </c>
       <c r="AJ283" s="10" t="s">
-        <v>5457</v>
+        <v>5455</v>
       </c>
     </row>
     <row r="284" spans="1:42">
@@ -63425,109 +63655,109 @@
         <v>美少女三國RPG手遊參上！遊戲擁有眾多經典三國名將，搭配緊張刺激的養成戰鬥系統，讓玩家可以體驗高潮連擊的激爽和無限養成的快樂。獨特的武將風格立繪，在既定特色上增添更多風味，絕對是視覺饗宴。還在為了找不到最新的禮包碼而煩惱嗎？想要輕鬆養成武將，解鎖所有外觀，最聰明的方式就是尋找快速安全的代儲值管道，立即領取你的兌換碼福利，在三國世界中無往不利！</v>
       </c>
       <c r="F284" s="14" t="s">
+        <v>5194</v>
+      </c>
+      <c r="G284" s="10" t="s">
         <v>5195</v>
       </c>
-      <c r="G284" s="10" t="s">
+      <c r="H284" s="10" t="s">
         <v>5196</v>
       </c>
-      <c r="H284" s="10" t="s">
-        <v>5197</v>
-      </c>
       <c r="K284" s="14" t="s">
-        <v>5259</v>
+        <v>5256</v>
       </c>
       <c r="L284" s="10" t="s">
-        <v>5311</v>
+        <v>5308</v>
       </c>
       <c r="M284" s="15" t="s">
-        <v>5260</v>
+        <v>5257</v>
       </c>
       <c r="N284" s="10" t="s">
-        <v>5310</v>
+        <v>5307</v>
       </c>
       <c r="O284" s="15" t="s">
+        <v>5284</v>
+      </c>
+      <c r="P284" s="10" t="s">
+        <v>5306</v>
+      </c>
+      <c r="Q284" s="15" t="s">
+        <v>5285</v>
+      </c>
+      <c r="R284" s="10" t="s">
+        <v>5305</v>
+      </c>
+      <c r="S284" s="15" t="s">
+        <v>5286</v>
+      </c>
+      <c r="T284" s="10" t="s">
+        <v>5304</v>
+      </c>
+      <c r="U284" s="15" t="s">
         <v>5287</v>
       </c>
-      <c r="P284" s="10" t="s">
-        <v>5309</v>
-      </c>
-      <c r="Q284" s="15" t="s">
+      <c r="V284" s="10" t="s">
+        <v>5303</v>
+      </c>
+      <c r="W284" s="15" t="s">
         <v>5288</v>
       </c>
-      <c r="R284" s="10" t="s">
-        <v>5308</v>
-      </c>
-      <c r="S284" s="15" t="s">
+      <c r="X284" s="10" t="s">
+        <v>5302</v>
+      </c>
+      <c r="Y284" s="15" t="s">
         <v>5289</v>
       </c>
-      <c r="T284" s="10" t="s">
-        <v>5307</v>
-      </c>
-      <c r="U284" s="15" t="s">
+      <c r="Z284" s="10" t="s">
+        <v>5301</v>
+      </c>
+      <c r="AA284" s="15" t="s">
         <v>5290</v>
       </c>
-      <c r="V284" s="10" t="s">
-        <v>5306</v>
-      </c>
-      <c r="W284" s="15" t="s">
-        <v>5291</v>
-      </c>
-      <c r="X284" s="10" t="s">
-        <v>5305</v>
-      </c>
-      <c r="Y284" s="15" t="s">
-        <v>5292</v>
-      </c>
-      <c r="Z284" s="10" t="s">
-        <v>5304</v>
-      </c>
-      <c r="AA284" s="15" t="s">
-        <v>5293</v>
-      </c>
       <c r="AB284" s="10" t="s">
-        <v>5303</v>
+        <v>5300</v>
       </c>
       <c r="AC284" s="15" t="s">
         <v>1932</v>
       </c>
       <c r="AD284" s="10" t="s">
-        <v>5302</v>
+        <v>5299</v>
       </c>
       <c r="AE284" s="15" t="s">
-        <v>5294</v>
+        <v>5291</v>
       </c>
       <c r="AF284" s="10" t="s">
-        <v>5301</v>
+        <v>5298</v>
       </c>
       <c r="AG284" s="15" t="s">
-        <v>5295</v>
+        <v>5292</v>
       </c>
       <c r="AH284" s="10" t="s">
-        <v>5300</v>
+        <v>5297</v>
       </c>
       <c r="AI284" s="15" t="s">
+        <v>5293</v>
+      </c>
+      <c r="AJ284" s="10" t="s">
         <v>5296</v>
-      </c>
-      <c r="AJ284" s="10" t="s">
-        <v>5299</v>
       </c>
       <c r="AK284" s="15" t="s">
         <v>2199</v>
       </c>
       <c r="AL284" s="10" t="s">
-        <v>5298</v>
+        <v>5295</v>
       </c>
       <c r="AM284" s="15" t="s">
         <v>2200</v>
       </c>
       <c r="AN284" s="10" t="s">
-        <v>5297</v>
+        <v>5294</v>
       </c>
       <c r="AO284" s="89" t="s">
-        <v>5463</v>
+        <v>5461</v>
       </c>
       <c r="AP284" s="10" t="s">
-        <v>5457</v>
+        <v>5455</v>
       </c>
     </row>
     <row r="285" spans="1:42">
@@ -63548,13 +63778,13 @@
         <v>準備好你的弓箭，面對排山倒海的敵人了嗎？《弓箭英雄：塔防》是一款結合了塔防策略與Roguelite元素的超休閒遊戲。每次升級都能三選一技能，是要彈射、冰凍還是連射？選錯了可能下一秒就躺平。玩家們都在瘋狂尋找最新的兌換碼，希望能開局就拿到神裝。別忘了，強大的火力支援是守塔的關鍵，這時候就需要可靠的代儲值服務來幫你一把。想要穩穩通關，拿到稀有的禮包碼獎勵嗎？與其苦苦硬撐，不如尋求快速安全的代儲值，讓你的箭塔升到滿級，輕鬆碾壓所有來犯的敵人，成為真正的塔防大師！</v>
       </c>
       <c r="F285" s="14" t="s">
-        <v>5241</v>
+        <v>5239</v>
       </c>
       <c r="K285" s="89" t="s">
+        <v>5510</v>
+      </c>
+      <c r="L285" s="10" t="s">
         <v>5512</v>
-      </c>
-      <c r="L285" s="10" t="s">
-        <v>5513</v>
       </c>
     </row>
     <row r="286" spans="1:42">
@@ -63575,13 +63805,13 @@
         <v>《十二之天M Reborn》誓言找回當年的感動，讓玩家重溫三大勢力的激情對決。這款遊戲主打的就是一個原汁原味，熟悉的場景、懷舊的BGM，以及那令人又愛又恨的勢力戰。準備好再次投身這場無盡的江湖恩怨了嗎？大家都在蹲點最新的禮包碼，希望能搶先一步強化裝備。官方發放的兌換碼雖然不無小補，但真正的強者懂得利用資源。想要快速提升戰力，不妨考慮專業的代儲值服務。與其在戰場上被當小兵清掉，不如透過快速安全的管道補足元寶，讓你的角色戰力飆升，在龍瀑鎮插旗，重現當年的榮光！</v>
       </c>
       <c r="F286" s="14" t="s">
-        <v>5241</v>
+        <v>5239</v>
       </c>
       <c r="K286" s="89" t="s">
+        <v>5510</v>
+      </c>
+      <c r="L286" s="10" t="s">
         <v>5512</v>
-      </c>
-      <c r="L286" s="10" t="s">
-        <v>5513</v>
       </c>
     </row>
     <row r="287" spans="1:42">
@@ -63602,10 +63832,10 @@
         <v>正版授權的《NBA巔峰對決》終於來了。這款主打真人PVP的籃球手遊，讓你能操控喜愛的NBA球星。遊戲強調操作手感與球星的專屬技能，想秀一波高難度灌籃或致命三分球？全看你的技術。但說真的，想在天梯上爬分，球員的養成才是關鍵。新手們別再傻傻地問兌換碼在哪了，那點資源根本不夠看。想要打造你的夢幻陣容，把傳奇球星都納入麾下，可靠的代儲值才是捷徑。別家還在慢慢存資源，你已經透過快速安全的儲值拿到關鍵禮包碼，直接抽爆卡池，讓你的隊伍戰力登頂，在球場上制霸全場！</v>
       </c>
       <c r="F287" s="14" t="s">
-        <v>5377</v>
+        <v>5374</v>
       </c>
       <c r="G287" s="10" t="s">
-        <v>5378</v>
+        <v>5375</v>
       </c>
       <c r="H287" s="10" t="s">
         <v>2625</v>
@@ -63614,40 +63844,40 @@
         <v>4360</v>
       </c>
       <c r="K287" s="15" t="s">
+        <v>5368</v>
+      </c>
+      <c r="L287" s="10" t="s">
         <v>5371</v>
       </c>
-      <c r="L287" s="10" t="s">
-        <v>5374</v>
-      </c>
       <c r="M287" s="15" t="s">
+        <v>5369</v>
+      </c>
+      <c r="N287" s="10" t="s">
         <v>5372</v>
       </c>
-      <c r="N287" s="10" t="s">
-        <v>5375</v>
-      </c>
       <c r="O287" s="15" t="s">
+        <v>5370</v>
+      </c>
+      <c r="P287" s="10" t="s">
         <v>5373</v>
       </c>
-      <c r="P287" s="10" t="s">
+      <c r="Q287" s="15" t="s">
         <v>5376</v>
       </c>
-      <c r="Q287" s="15" t="s">
-        <v>5379</v>
-      </c>
       <c r="R287" s="10" t="s">
-        <v>5380</v>
+        <v>5377</v>
       </c>
       <c r="S287" t="s">
-        <v>5480</v>
+        <v>5478</v>
       </c>
       <c r="U287" t="s">
-        <v>5481</v>
+        <v>5479</v>
       </c>
       <c r="W287" s="89" t="s">
-        <v>5463</v>
+        <v>5461</v>
       </c>
       <c r="X287" s="10" t="s">
-        <v>5457</v>
+        <v>5455</v>
       </c>
     </row>
     <row r="288" spans="1:42">
@@ -63668,13 +63898,13 @@
         <v>又一款三國策略遊戲？先別急著滑掉！《三國志：王戰》是一款主打快節奏的SLG手遊，標榜著15天一賽季的急速征戰。在這裡，你不用再苦苦熬夜農地、屯兵，而是要把握黃金時間，快速發展內政、招募名將，與盟友一同攻城掠地。當然，想在短短15天內統一天下，光靠策略可不夠。新手們拚命搜尋的兌換碼，拿到的資源可能還不夠升一座主城。真正的王者都懂得運用代儲值服務，在開局就快人一步。別再猶豫了，利用快速安全的管道取得珍稀禮包碼與資源，迅速拉高戰力，在賽季結束前稱霸全服！</v>
       </c>
       <c r="F288" s="14" t="s">
-        <v>5241</v>
+        <v>5239</v>
       </c>
       <c r="K288" s="89" t="s">
+        <v>5510</v>
+      </c>
+      <c r="L288" s="10" t="s">
         <v>5512</v>
-      </c>
-      <c r="L288" s="10" t="s">
-        <v>5513</v>
       </c>
     </row>
     <row r="289" spans="1:49">
@@ -63695,13 +63925,13 @@
         <v>光榮特庫摩出品，正統信長之野望系列最新力作《信長之野望 霸道》終於登場！這次玩家將化身侍奉各地大名的領主，在MMO化的戰國世界中，與同勢力的盟友們一同奮戰，體驗四季變化的精美3D地圖與緊張刺激的攻城戰。想在亂世中快人一步？別忘了到處尋找隱藏的兌換碼與禮包碼，領取初期資源。當然，若想讓統一天下的霸業之路更加順遂，尋找快速安全的代儲值服務也是各位城主大人們的必修課，畢竟在戰場上，兵貴神速啊！立即投身亂世，與盟友們共創霸業！</v>
       </c>
       <c r="F289" s="14" t="s">
-        <v>5241</v>
+        <v>5239</v>
       </c>
       <c r="K289" s="89" t="s">
+        <v>5510</v>
+      </c>
+      <c r="L289" s="10" t="s">
         <v>5512</v>
-      </c>
-      <c r="L289" s="10" t="s">
-        <v>5513</v>
       </c>
     </row>
     <row r="290" spans="1:49">
@@ -63722,13 +63952,13 @@
         <v>經典IP《勇者前線》竟然還能出新作？這次是對戰遊戲《Versus》，看來是想再炒一波冷飯。玩家們別傻傻地等官方福利了，趕快去找兌換碼跟禮包碼比較實在。如果想在起跑點就碾壓對手，不如直接找代儲值，保證快速安全，讓你省時省力，把別人當草虐。別再慢慢農了，課金才是王道！</v>
       </c>
       <c r="F290" s="14" t="s">
-        <v>5241</v>
+        <v>5239</v>
       </c>
       <c r="K290" s="89" t="s">
+        <v>5510</v>
+      </c>
+      <c r="L290" s="10" t="s">
         <v>5512</v>
-      </c>
-      <c r="L290" s="10" t="s">
-        <v>5513</v>
       </c>
     </row>
     <row r="291" spans="1:49">
@@ -63749,31 +63979,31 @@
         <v xml:space="preserve">台廠自製的ARPG《幻域方舟》終於上線了，號稱高自由度打擊感，但我們都知道，重點還是刷刷刷。與其花時間農素材，不如先上網搜刮最新的兌換碼和禮包碼。遊戲裡的禮包是不是又貴又坑？別擔心，聰明的玩家都懂用代儲值，享受快速安全的服務，用最少的錢拿到最多資源，這才是高人一等的玩法。 </v>
       </c>
       <c r="F291" s="14" t="s">
+        <v>5459</v>
+      </c>
+      <c r="G291" s="10" t="s">
+        <v>5458</v>
+      </c>
+      <c r="H291" s="10" t="s">
+        <v>5460</v>
+      </c>
+      <c r="K291" s="78" t="s">
+        <v>5462</v>
+      </c>
+      <c r="L291" s="10" t="s">
+        <v>5463</v>
+      </c>
+      <c r="M291" s="89" t="s">
+        <v>5510</v>
+      </c>
+      <c r="N291" s="10" t="s">
+        <v>5512</v>
+      </c>
+      <c r="AC291" s="89" t="s">
         <v>5461</v>
       </c>
-      <c r="G291" s="10" t="s">
-        <v>5460</v>
-      </c>
-      <c r="H291" s="10" t="s">
-        <v>5462</v>
-      </c>
-      <c r="K291" s="78" t="s">
-        <v>5464</v>
-      </c>
-      <c r="L291" s="10" t="s">
-        <v>5465</v>
-      </c>
-      <c r="M291" s="89" t="s">
-        <v>5512</v>
-      </c>
-      <c r="N291" s="10" t="s">
-        <v>5513</v>
-      </c>
-      <c r="AC291" s="89" t="s">
-        <v>5463</v>
-      </c>
       <c r="AD291" s="10" t="s">
-        <v>5457</v>
+        <v>5455</v>
       </c>
     </row>
     <row r="292" spans="1:49">
@@ -63794,74 +64024,74 @@
         <v>又一款免洗武俠《開天》來了，看這名字就知道又是那套開局送VIP，戰力膨脹的套路。反正大家都是進來割草的，誰還在乎劇情？重點是福利！別忘了每天蹲點找兌換碼和禮包碼，能拿多少是多少。如果想當服霸，靠遊戲裡送的根本不夠，直接找代儲值才是捷徑，保證快速安全，讓你戰力飆升，霸服就是這麼簡單。</v>
       </c>
       <c r="F292" s="14" t="s">
-        <v>5474</v>
+        <v>5472</v>
       </c>
       <c r="G292" s="10" t="s">
-        <v>5475</v>
+        <v>5473</v>
       </c>
       <c r="H292" s="10" t="s">
         <v>2625</v>
       </c>
       <c r="K292" s="89" t="s">
-        <v>5466</v>
+        <v>5464</v>
       </c>
       <c r="M292" s="15" t="s">
-        <v>5467</v>
+        <v>5465</v>
       </c>
       <c r="N292" s="90"/>
       <c r="O292" s="15" t="s">
+        <v>5466</v>
+      </c>
+      <c r="Q292" s="15" t="s">
+        <v>5467</v>
+      </c>
+      <c r="S292" s="15" t="s">
         <v>5468</v>
-      </c>
-      <c r="Q292" s="15" t="s">
-        <v>5469</v>
-      </c>
-      <c r="S292" s="15" t="s">
-        <v>5470</v>
       </c>
       <c r="U292" s="15" t="s">
         <v>1933</v>
       </c>
       <c r="W292" s="15" t="s">
+        <v>5469</v>
+      </c>
+      <c r="Y292" s="15" t="s">
+        <v>5470</v>
+      </c>
+      <c r="AA292" s="15" t="s">
         <v>5471</v>
       </c>
-      <c r="Y292" s="15" t="s">
-        <v>5472</v>
-      </c>
-      <c r="AA292" s="15" t="s">
-        <v>5473</v>
-      </c>
       <c r="AC292" s="15" t="s">
+        <v>5524</v>
+      </c>
+      <c r="AE292" s="15" t="s">
         <v>5525</v>
       </c>
-      <c r="AE292" s="15" t="s">
+      <c r="AG292" s="15" t="s">
         <v>5526</v>
       </c>
-      <c r="AG292" s="15" t="s">
+      <c r="AI292" s="15" t="s">
         <v>5527</v>
       </c>
-      <c r="AI292" s="15" t="s">
+      <c r="AK292" s="15" t="s">
         <v>5528</v>
       </c>
-      <c r="AK292" s="15" t="s">
+      <c r="AM292" s="15" t="s">
         <v>5529</v>
       </c>
-      <c r="AM292" s="15" t="s">
+      <c r="AO292" s="15" t="s">
         <v>5530</v>
       </c>
-      <c r="AO292" s="15" t="s">
+      <c r="AQ292" s="15" t="s">
         <v>5531</v>
       </c>
-      <c r="AQ292" s="15" t="s">
+      <c r="AS292" s="15" t="s">
         <v>5532</v>
       </c>
-      <c r="AS292" s="15" t="s">
+      <c r="AU292" s="15" t="s">
         <v>5533</v>
       </c>
-      <c r="AU292" s="15" t="s">
+      <c r="AW292" s="15" t="s">
         <v>5534</v>
-      </c>
-      <c r="AW292" s="15" t="s">
-        <v>5535</v>
       </c>
     </row>
     <row r="293" spans="1:49">
@@ -63882,58 +64112,58 @@
         <v>《人人有功練：腸仔江湖見》這名字真是……有夠ㄎㄧㄤ。號稱躺著練功，我看是躺著儲值吧？這種放置遊戲，比的就是誰的資源多。開局先別急著衝，把所有兌換碼、禮包碼都輸入一遍才是正事。覺得官方送太少？想一步登天？內行的都知道找代儲值，保證快速安全，讓你用新台幣教訓那些無課玩家，輕鬆當大俠。</v>
       </c>
       <c r="F293" s="14" t="s">
-        <v>5474</v>
+        <v>5472</v>
       </c>
       <c r="G293" s="10" t="s">
-        <v>5475</v>
+        <v>5473</v>
       </c>
       <c r="H293" s="10" t="s">
         <v>2625</v>
       </c>
       <c r="K293" s="89" t="s">
+        <v>5474</v>
+      </c>
+      <c r="M293" s="15" t="s">
+        <v>5475</v>
+      </c>
+      <c r="O293" s="15" t="s">
         <v>5476</v>
       </c>
-      <c r="M293" s="15" t="s">
+      <c r="Q293" s="15" t="s">
         <v>5477</v>
       </c>
-      <c r="O293" s="15" t="s">
-        <v>5478</v>
-      </c>
-      <c r="Q293" s="15" t="s">
-        <v>5479</v>
-      </c>
       <c r="S293" s="15" t="s">
-        <v>5484</v>
+        <v>5482</v>
       </c>
       <c r="U293" s="15" t="s">
-        <v>5294</v>
+        <v>5291</v>
       </c>
       <c r="W293" s="15" t="s">
         <v>1841</v>
       </c>
       <c r="Y293" s="15" t="s">
-        <v>5485</v>
+        <v>5483</v>
       </c>
       <c r="AA293" s="15" t="s">
-        <v>5486</v>
+        <v>5484</v>
       </c>
       <c r="AC293" s="15" t="s">
         <v>2912</v>
       </c>
       <c r="AE293" s="15" t="s">
+        <v>5485</v>
+      </c>
+      <c r="AG293" s="15" t="s">
+        <v>5486</v>
+      </c>
+      <c r="AI293" s="15" t="s">
         <v>5487</v>
       </c>
-      <c r="AG293" s="15" t="s">
-        <v>5488</v>
-      </c>
-      <c r="AI293" s="15" t="s">
-        <v>5489</v>
-      </c>
       <c r="AK293" s="89" t="s">
-        <v>5463</v>
+        <v>5461</v>
       </c>
       <c r="AL293" s="10" t="s">
-        <v>5457</v>
+        <v>5455</v>
       </c>
     </row>
     <row r="294" spans="1:49">
@@ -63954,13 +64184,13 @@
         <v>什麼？《楓之谷》也出手遊放置版了？Nexon真是把IP利用到極致，連骨髓都不放過。反正又是賣情懷，大家也準備好荷包了。別傻傻地當免費勞工，開局先搜爆兌換碼和禮包碼，把能拿的都拿光。想重溫當年的課長快感？找代儲值就對了，絕對快速安全，讓你輕鬆掛機，戰力輾壓那些還在手動練功的「肝」苦人。</v>
       </c>
       <c r="F294" s="14" t="s">
-        <v>5241</v>
+        <v>5239</v>
       </c>
       <c r="K294" s="89" t="s">
+        <v>5510</v>
+      </c>
+      <c r="L294" s="10" t="s">
         <v>5512</v>
-      </c>
-      <c r="L294" s="10" t="s">
-        <v>5513</v>
       </c>
     </row>
     <row r="295" spans="1:49">
@@ -63981,13 +64211,13 @@
         <v xml:space="preserve">這款《Shiba Wars：Goddess Link TD》看起來又是個賣婆的塔防遊戲，配上柴犬...這組合真奇妙。反正重點不是塔防，是收集老婆吧！想把女神抽滿抽爆，光靠遊戲送的兌換碼跟禮包碼哪夠用？別猶豫了，直接找代儲值服務，快速安全幫你搞定一切，讓你用最省的力氣，組建最強大的老婆後宮團，輕鬆躺贏。 </v>
       </c>
       <c r="F295" s="14" t="s">
-        <v>5241</v>
+        <v>5239</v>
       </c>
       <c r="K295" s="89" t="s">
+        <v>5510</v>
+      </c>
+      <c r="L295" s="10" t="s">
         <v>5512</v>
-      </c>
-      <c r="L295" s="10" t="s">
-        <v>5513</v>
       </c>
     </row>
     <row r="296" spans="1:49">
@@ -64008,10 +64238,10 @@
         <v>經典老IP《熱血江湖》又來了，還自稱「福利加強版」，真是此地無銀三百兩。福利再加強，有比得上課金嗎？新手們別傻了，乖乖上網找最新的兌換碼、禮包碼才是真的。想在正邪大戰中出人頭地？靠官方福利你只能當砲灰。快找代儲值服務，快速安全幫你一步到位，直接+15神裝，重溫當年的課金霸主快感！</v>
       </c>
       <c r="F296" s="14" t="s">
-        <v>5509</v>
+        <v>5507</v>
       </c>
       <c r="G296" s="10" t="s">
-        <v>5510</v>
+        <v>5508</v>
       </c>
       <c r="H296" s="10" t="s">
         <v>2625</v>
@@ -64026,40 +64256,40 @@
         <v>888888</v>
       </c>
       <c r="Q296" s="15" t="s">
+        <v>5514</v>
+      </c>
+      <c r="S296" s="15" t="s">
         <v>5515</v>
       </c>
-      <c r="S296" s="15" t="s">
+      <c r="U296" s="15" t="s">
         <v>5516</v>
       </c>
-      <c r="U296" s="15" t="s">
+      <c r="W296" s="15" t="s">
         <v>5517</v>
       </c>
-      <c r="W296" s="15" t="s">
+      <c r="Y296" s="15" t="s">
         <v>5518</v>
       </c>
-      <c r="Y296" s="15" t="s">
+      <c r="AA296" s="15" t="s">
         <v>5519</v>
       </c>
-      <c r="AA296" s="15" t="s">
+      <c r="AC296" s="15" t="s">
         <v>5520</v>
       </c>
-      <c r="AC296" s="15" t="s">
+      <c r="AE296" s="15" t="s">
         <v>5521</v>
       </c>
-      <c r="AE296" s="15" t="s">
+      <c r="AG296" s="15" t="s">
         <v>5522</v>
       </c>
-      <c r="AG296" s="15" t="s">
+      <c r="AI296" s="15" t="s">
         <v>5523</v>
       </c>
-      <c r="AI296" s="15" t="s">
-        <v>5524</v>
-      </c>
       <c r="AK296" s="89" t="s">
+        <v>5510</v>
+      </c>
+      <c r="AL296" s="10" t="s">
         <v>5512</v>
-      </c>
-      <c r="AL296" s="10" t="s">
-        <v>5513</v>
       </c>
     </row>
     <row r="297" spans="1:49">
@@ -64080,55 +64310,55 @@
         <v>《熱血主公Go!》是一款結合Roguelike培育、RPG冒險與街機動作元素的三國手遊。玩家將扮演主公，踏上匡扶漢室的征途，招募趙雲、呂布等傳奇名將。遊戲主打懷舊街機畫風與隨機流派組合，戰鬥體驗絕不重複！官方不斷釋出最新的兌換碼與禮包碼，讓玩家輕鬆升級。若想快速提升戰力，尋找代儲值服務也是一種選擇，務必確保快速安全，避免受騙。立即加入，體驗放置休閒與熱血PVP對戰的雙重樂趣！</v>
       </c>
       <c r="F297" s="31" t="s">
-        <v>5499</v>
+        <v>5497</v>
       </c>
       <c r="G297" s="10" t="s">
-        <v>5500</v>
+        <v>5498</v>
       </c>
       <c r="H297" s="10" t="s">
         <v>2625</v>
       </c>
       <c r="K297" s="14" t="s">
-        <v>5498</v>
+        <v>5496</v>
       </c>
       <c r="L297" s="10" t="s">
-        <v>5511</v>
+        <v>5509</v>
       </c>
       <c r="M297" s="10" t="s">
+        <v>5491</v>
+      </c>
+      <c r="N297" s="10" t="s">
+        <v>5509</v>
+      </c>
+      <c r="O297" s="15" t="s">
+        <v>5492</v>
+      </c>
+      <c r="P297" s="10" t="s">
+        <v>5509</v>
+      </c>
+      <c r="Q297" s="15" t="s">
         <v>5493</v>
       </c>
-      <c r="N297" s="10" t="s">
-        <v>5511</v>
-      </c>
-      <c r="O297" s="15" t="s">
+      <c r="R297" s="10" t="s">
+        <v>5509</v>
+      </c>
+      <c r="S297" s="15" t="s">
         <v>5494</v>
       </c>
-      <c r="P297" s="10" t="s">
-        <v>5511</v>
-      </c>
-      <c r="Q297" s="15" t="s">
+      <c r="T297" s="10" t="s">
+        <v>5509</v>
+      </c>
+      <c r="U297" s="15" t="s">
         <v>5495</v>
       </c>
-      <c r="R297" s="10" t="s">
-        <v>5511</v>
-      </c>
-      <c r="S297" s="15" t="s">
-        <v>5496</v>
-      </c>
-      <c r="T297" s="10" t="s">
-        <v>5511</v>
-      </c>
-      <c r="U297" s="15" t="s">
-        <v>5497</v>
-      </c>
       <c r="V297" s="10" t="s">
-        <v>5511</v>
+        <v>5509</v>
       </c>
       <c r="W297" s="89" t="s">
+        <v>5510</v>
+      </c>
+      <c r="X297" s="10" t="s">
         <v>5512</v>
-      </c>
-      <c r="X297" s="10" t="s">
-        <v>5513</v>
       </c>
     </row>
     <row r="298" spans="1:49">
@@ -64148,11 +64378,38 @@
         <f>IF(games!I298&lt;&gt;"", games!I298, "")</f>
         <v>「歡迎來到夢樂園」隆重開幕！這款女性向輕喜劇異界冒險手遊，讓你化身管理者重建樂園。還在為資源煩惱？別傻了，快找最新的禮包碼和兌換碼才是王道。當然，想一步登天，最快速安全的代儲值服務也不能少，讓你輕鬆應對各種挑戰，與夥伴們踏上夢幻旅程。別再慢慢農了，聰明的管理者都懂。</v>
       </c>
+      <c r="F298" s="31" t="s">
+        <v>5612</v>
+      </c>
+      <c r="G298" s="10" t="s">
+        <v>5613</v>
+      </c>
+      <c r="H298" s="10" t="s">
+        <v>2625</v>
+      </c>
       <c r="K298" s="89" t="s">
+        <v>5510</v>
+      </c>
+      <c r="L298" s="10" t="s">
         <v>5512</v>
       </c>
-      <c r="L298" s="10" t="s">
-        <v>5513</v>
+      <c r="M298" s="15" t="s">
+        <v>5606</v>
+      </c>
+      <c r="N298" s="10" t="s">
+        <v>5609</v>
+      </c>
+      <c r="O298" s="15" t="s">
+        <v>5607</v>
+      </c>
+      <c r="P298" s="10" t="s">
+        <v>5610</v>
+      </c>
+      <c r="Q298" s="15" t="s">
+        <v>5608</v>
+      </c>
+      <c r="R298" s="10" t="s">
+        <v>5611</v>
       </c>
     </row>
     <row r="299" spans="1:49">
@@ -64172,11 +64429,14 @@
         <f>IF(games!I299&lt;&gt;"", games!I299, "")</f>
         <v xml:space="preserve">「Cryowar」是一款基於Solana的即時多人PVP競技場NFT遊戲。還在手動農資源？真是辛苦了。想在戰場上快人一步，你需要的不只是技術，更是海量的禮包碼與兌換碼。當然，為了打造最強裝備，尋求快速安全的代儲值服務也是必要的捷徑。別再當個苦哈哈的戰士，立即強化你的英雄，主宰競技場吧！ </v>
       </c>
+      <c r="F299" s="14" t="s">
+        <v>5239</v>
+      </c>
       <c r="K299" s="89" t="s">
+        <v>5510</v>
+      </c>
+      <c r="L299" s="10" t="s">
         <v>5512</v>
-      </c>
-      <c r="L299" s="10" t="s">
-        <v>5513</v>
       </c>
     </row>
     <row r="300" spans="1:49">
@@ -64196,11 +64456,14 @@
         <f>IF(games!I300&lt;&gt;"", games!I300, "")</f>
         <v>「深岩銀河：倖存者」登陸手機！這款單人倖存者類自動射擊遊戲，讓你單槍匹馬對抗Hoxxes星球。以為光靠技術就能活下去？別天真了，沒有最新的禮包碼和兌換碼，你連蟲潮都撐不過。想挖礦挖得更深，升級更猛？快速安全的代儲值服務是你唯一的希望。別再掙扎了，矮人，快武裝自己！</v>
       </c>
+      <c r="F300" s="14" t="s">
+        <v>5239</v>
+      </c>
       <c r="K300" s="89" t="s">
+        <v>5510</v>
+      </c>
+      <c r="L300" s="10" t="s">
         <v>5512</v>
-      </c>
-      <c r="L300" s="10" t="s">
-        <v>5513</v>
       </c>
     </row>
     <row r="301" spans="1:49">
@@ -64220,11 +64483,14 @@
         <f>IF(games!I301&lt;&gt;"", games!I301, "")</f>
         <v>「熱血排球少女」開打！這款4v4排球對戰遊戲，讓你打造夢幻隊伍。還在苦練發球跟扣殺？別傻了，這年頭想赢，靠的是源源不絕的禮包碼和兌換碼。想讓你的少女選手快速升級，制霸全國大賽？快速安全的代儲值服務才是致勝關鍵。別再慢慢培養了，立即組建最強隊伍，拿下冠軍吧！</v>
       </c>
+      <c r="F301" s="14" t="s">
+        <v>5239</v>
+      </c>
       <c r="K301" s="89" t="s">
+        <v>5510</v>
+      </c>
+      <c r="L301" s="10" t="s">
         <v>5512</v>
-      </c>
-      <c r="L301" s="10" t="s">
-        <v>5513</v>
       </c>
     </row>
     <row r="302" spans="1:49">
@@ -64244,64 +64510,129 @@
         <f>IF(games!I302&lt;&gt;"", games!I302, "")</f>
         <v/>
       </c>
+      <c r="F302" s="14" t="s">
+        <v>5239</v>
+      </c>
+      <c r="K302" s="89" t="s">
+        <v>5510</v>
+      </c>
+      <c r="L302" s="10" t="s">
+        <v>5512</v>
+      </c>
     </row>
     <row r="303" spans="1:49">
+      <c r="A303" s="10" t="str">
+        <f>IF(games!A303="", "", games!A303)</f>
+        <v>三國格子爭奪戰</v>
+      </c>
       <c r="C303" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>giftcodesbanner/三國格子爭奪戰-禮包碼.jpg</v>
       </c>
       <c r="D303" s="10" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>https://www.ssbuy.tw/gift-codes.html?game=三國格子爭奪戰</v>
       </c>
       <c r="E303" s="11" t="str">
         <f>IF(games!I303